--- a/1XW_TradeBlotter_Web.xlsx
+++ b/1XW_TradeBlotter_Web.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0a601c1c2ba3d9f4/Trading/The Strategy Project/1XW Website/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="132" documentId="13_ncr:1_{6F5069F1-F0E7-4440-AA6D-4AFA11BBED1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D497F5F5-2BF1-4E62-8AD6-A664C4481A0D}"/>
+  <xr:revisionPtr revIDLastSave="146" documentId="13_ncr:1_{6F5069F1-F0E7-4440-AA6D-4AFA11BBED1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A834F952-FDCD-4925-A9A9-BF13E3D8F658}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="22695" windowHeight="14476" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="22695" windowHeight="14476" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Blotter" sheetId="3" r:id="rId1"/>
@@ -116,7 +116,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="943" uniqueCount="316">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="851" uniqueCount="320">
   <si>
     <t>WEEK</t>
   </si>
@@ -509,9 +509,6 @@
   </si>
   <si>
     <t>Commodities</t>
-  </si>
-  <si>
-    <t>Stocks</t>
   </si>
   <si>
     <t>THEME</t>
@@ -1073,10 +1070,25 @@
     <t>FGBL 20260608 M</t>
   </si>
   <si>
-    <t>BTC_PAXOS</t>
-  </si>
-  <si>
     <t>BTC.USD-PAXOS</t>
+  </si>
+  <si>
+    <t>INFO</t>
+  </si>
+  <si>
+    <t>Starting. host=127.0.0.1 port=7497 clientId=11 mktDataType=3 interval=0.25s</t>
+  </si>
+  <si>
+    <t>Connected to TWS.</t>
+  </si>
+  <si>
+    <t>Loaded 35 contracts from Symbols sheet.</t>
+  </si>
+  <si>
+    <t>Spot</t>
+  </si>
+  <si>
+    <t>SELL</t>
   </si>
 </sst>
 </file>
@@ -1089,14 +1101,14 @@
     <numFmt numFmtId="165" formatCode="#,##0.0"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
     <numFmt numFmtId="167" formatCode="#,##0.0000"/>
-    <numFmt numFmtId="169" formatCode="#,##0.000_ ;\-#,##0.000\ "/>
-    <numFmt numFmtId="170" formatCode="#,##0.000;\-#,##0.000"/>
-    <numFmt numFmtId="171" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
-    <numFmt numFmtId="172" formatCode="0.000%"/>
-    <numFmt numFmtId="173" formatCode="#,##0.00_ ;\-#,##0.00\ "/>
-    <numFmt numFmtId="174" formatCode="#,##0_-;\-#,##0_-;_-;_-@_-"/>
-    <numFmt numFmtId="175" formatCode="#,##0.00_-;\-#,##0.00_-;_-;_-@_-"/>
-    <numFmt numFmtId="176" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="168" formatCode="#,##0.000_ ;\-#,##0.000\ "/>
+    <numFmt numFmtId="169" formatCode="#,##0.000;\-#,##0.000"/>
+    <numFmt numFmtId="170" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
+    <numFmt numFmtId="171" formatCode="0.000%"/>
+    <numFmt numFmtId="172" formatCode="#,##0.00_ ;\-#,##0.00\ "/>
+    <numFmt numFmtId="173" formatCode="#,##0_-;\-#,##0_-;_-;_-@_-"/>
+    <numFmt numFmtId="174" formatCode="#,##0.00_-;\-#,##0.00_-;_-;_-@_-"/>
+    <numFmt numFmtId="175" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="20" x14ac:knownFonts="1">
     <font>
@@ -1399,10 +1411,10 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="170" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="169" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
@@ -1420,7 +1432,7 @@
     <xf numFmtId="15" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="171" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="170" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1429,7 +1441,7 @@
     <xf numFmtId="43" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="170" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1455,15 +1467,15 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="172" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="173" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="172" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="172" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -1473,22 +1485,22 @@
     <xf numFmtId="37" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="174" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="173" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="173" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="174" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="175" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="174" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="173" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="175" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -1497,7 +1509,7 @@
     <xf numFmtId="10" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="174" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="173" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="17" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1507,7 +1519,7 @@
     <xf numFmtId="16" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="175" fontId="3" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="15" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1735,7 +1747,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-5.0036685890297861E-4</c:v>
+                  <c:v>6.3893581138096955E-4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1889,7 +1901,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-5.0036685890297861E-4</c:v>
+                  <c:v>6.3893581138096955E-4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2280,7 +2292,7 @@
                   <c:v>1000</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>999.49963314109698</c:v>
+                  <c:v>1000.638935811381</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2621,7 +2633,7 @@
                 <c:formatCode>0.00%</c:formatCode>
                 <c:ptCount val="52"/>
                 <c:pt idx="0">
-                  <c:v>-1.0000000000000009E-2</c:v>
+                  <c:v>6.3893581138096955E-4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2678,7 +2690,7 @@
                 <c:formatCode>0.00%</c:formatCode>
                 <c:ptCount val="52"/>
                 <c:pt idx="0">
-                  <c:v>-5.0036685890297861E-4</c:v>
+                  <c:v>6.3893581138096955E-4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3325,10 +3337,10 @@
   <sheetData>
     <row r="1" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B1" s="32" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C1" s="79">
-        <v>46085</v>
+        <v>46088</v>
       </c>
     </row>
     <row r="2" spans="2:11" x14ac:dyDescent="0.4">
@@ -3353,13 +3365,13 @@
       </c>
       <c r="C3" s="28">
         <f ca="1">OFFSET(NAV!B1,MATCH(C1,NAV!B:B,1),8)</f>
-        <v>999499.63314109703</v>
+        <v>1000638.935811381</v>
       </c>
       <c r="E3" s="47" t="s">
         <v>130</v>
       </c>
       <c r="F3" s="47" t="s">
-        <v>131</v>
+        <v>318</v>
       </c>
       <c r="G3" s="47"/>
       <c r="H3" s="28"/>
@@ -3370,7 +3382,7 @@
       </c>
       <c r="C4" s="28">
         <f>SUM(N18:N1012)</f>
-        <v>-500.36685890301305</v>
+        <v>638.93581138100001</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="47" t="s">
@@ -3384,15 +3396,15 @@
     </row>
     <row r="5" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B5" s="32" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C5" s="3">
         <f ca="1">OFFSET(NAV!B1,MATCH(C1,NAV!B:B,1),11)</f>
-        <v>-5.0036685890297861E-4</v>
+        <v>6.3893581138096955E-4</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="47" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F5" s="47" t="s">
         <v>53</v>
@@ -3403,11 +3415,11 @@
     </row>
     <row r="6" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B6" s="32" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C6" s="3">
         <f ca="1">OFFSET(NAV!B1,MATCH(C1,NAV!B:B,1),12)</f>
-        <v>-5.0036685890297861E-4</v>
+        <v>6.3893581138096955E-4</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="47"/>
@@ -3418,7 +3430,7 @@
     </row>
     <row r="7" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B7" s="32" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C7" s="28">
         <f>Cash_Mgmt!H13</f>
@@ -3436,15 +3448,15 @@
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B8" s="32" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C8" s="28">
         <f>C4+C7</f>
-        <v>-500.36685890301305</v>
+        <v>638.93581138100001</v>
       </c>
       <c r="D8" s="3">
         <f ca="1">C5+D7</f>
-        <v>-5.0036685890297861E-4</v>
+        <v>6.3893581138096955E-4</v>
       </c>
       <c r="G8" s="47"/>
       <c r="H8" s="51"/>
@@ -3501,39 +3513,39 @@
       </c>
       <c r="C12" s="28" cm="1">
         <f t="array" ref="C12">SUM((PLB!G4:G999="O")*(PLB!E4:E999))</f>
-        <v>10500</v>
+        <v>0</v>
       </c>
       <c r="D12" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>1.0505256482187962E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B13" s="32" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C13" s="28">
         <f t="array" ref="C13">SUM((PLB!G4:G999="O")*(PLB!D4:D999))</f>
-        <v>-500.36685890301305</v>
+        <v>0</v>
       </c>
       <c r="D13" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>-5.0061735123456267E-4</v>
+        <v>0</v>
       </c>
       <c r="F13" s="59"/>
       <c r="G13" s="59"/>
     </row>
     <row r="14" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B14" s="32" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C14" s="28">
         <f>C12+C13</f>
-        <v>9999.6331410969869</v>
+        <v>0</v>
       </c>
       <c r="D14" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>1.00046391309534E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="2:28" x14ac:dyDescent="0.4">
@@ -3553,7 +3565,7 @@
         <v>2</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H17" s="4" t="s">
         <v>107</v>
@@ -3613,12 +3625,12 @@
     </row>
     <row r="18" spans="2:28" x14ac:dyDescent="0.4">
       <c r="B18" s="9" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C18" s="12"/>
       <c r="D18" s="12"/>
       <c r="E18" s="10" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F18" s="12"/>
       <c r="G18" s="12"/>
@@ -3647,19 +3659,19 @@
     </row>
     <row r="19" spans="2:28" x14ac:dyDescent="0.4">
       <c r="B19" s="9" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C19" s="10">
         <v>1</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>129</v>
       </c>
       <c r="F19" s="10" t="s">
-        <v>131</v>
+        <v>318</v>
       </c>
       <c r="G19" s="28">
         <f>VLOOKUP(D19,Multiplier!B:I,8,0)</f>
@@ -3670,7 +3682,7 @@
       </c>
       <c r="I19" s="28">
         <f t="array" ref="I19">SUM((Trades!V$2:V$9999)*(Trades!U$2:U$9999=Blotter!B19)*(Trades!$T$2:T$9999=Blotter!C19))</f>
-        <v>49.999999999999993</v>
+        <v>0</v>
       </c>
       <c r="J19" s="28">
         <f>VLOOKUP(D19,Multiplier!B:D,2,0)</f>
@@ -3678,19 +3690,19 @@
       </c>
       <c r="K19" s="29">
         <f t="shared" ref="K19" si="1">L19-N19/(H19*J19)</f>
-        <v>1986.6573371780603</v>
+        <v>1987.22128377238</v>
       </c>
       <c r="L19" s="29">
         <f t="shared" ref="L19" si="2">IF(I19=0,IF(H19&gt;0,X19,Y19),Z19)</f>
-        <v>1976.65</v>
+        <v>2000</v>
       </c>
       <c r="M19" s="28">
         <f t="shared" ref="M19" si="3">I19*J19*L19</f>
-        <v>98832.499999999985</v>
+        <v>0</v>
       </c>
       <c r="N19" s="28">
         <f t="array" ref="N19">-SUM((Trades!T$2:T$9999=Blotter!C19)*(Trades!U$2:U$9999=Blotter!B19)*(Trades!V$2:V$9999)*(Trades!W$2:W$9999))*J19+SUM((Trades!T$2:T$9999=Blotter!C19)*(Trades!U$2:U$9999=Blotter!B19)*(Trades!X$2:X$9999))+(L19*I19)*J19</f>
-        <v>-500.36685890301305</v>
+        <v>638.93581138100001</v>
       </c>
       <c r="O19" s="29">
         <f>VLOOKUP(D19,Multiplier!B:H,3,0)</f>
@@ -3706,31 +3718,31 @@
       </c>
       <c r="S19" s="29">
         <f t="shared" ref="S19" si="5">IF(OR(F19="Futures",F19="Stocks"),IF(I19=0,0,IF(I19&gt;0,L19-O19,L19+O19)),0)</f>
-        <v>1836.65</v>
+        <v>0</v>
       </c>
       <c r="T19" s="3">
         <f t="shared" ref="T19" si="6">IF(S19&gt;0,IF(ISNUMBER(S19/L19-1),S19/L19-1,0),0)</f>
-        <v>-7.082690410543091E-2</v>
+        <v>0</v>
       </c>
       <c r="U19" s="29">
         <f t="shared" ref="U19" si="7">IF(OR(F19="Futures",F19="Stocks"),IF(I19=0,0,IF(I19&gt;0,K19-P19,K19+P19)),0)</f>
-        <v>1776.6573371780603</v>
+        <v>0</v>
       </c>
       <c r="V19" s="3">
         <f t="shared" ref="V19" si="8">IF(U19&gt;0,IF(ISNUMBER(U19/L19-1),U19/L19-1,0),0)</f>
-        <v>-0.10117757965342367</v>
+        <v>0</v>
       </c>
       <c r="X19" s="34">
         <f t="array" ref="X19">IF(ISNUMBER(SUM((Trades!T$2:T$9999=Blotter!C19)*(Trades!U$2:U$9999=Blotter!B19)*(Trades!W$2:W$9999)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0))/SUM((Trades!T$2:T$9999=Blotter!C19)*(Trades!U$2:U$9999=Blotter!B19)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0))),SUM((Trades!T$2:T$9999=Blotter!C19)*(Trades!U$2:U$9999=Blotter!B19)*(Trades!W$2:W$9999)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0))/SUM((Trades!T$2:T$9999=Blotter!C19)*(Trades!U$2:U$9999=Blotter!B19)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0)),0)</f>
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="Y19" s="34">
         <f t="array" ref="Y19">IF(ISNUMBER(SUM((Trades!T$2:T$9999=Blotter!C19)*(Trades!U$2:U$9999=Blotter!B19)*(Trades!W$2:W$9999)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&gt;0))/SUM((Trades!T$2:T$9999=Blotter!C19)*(Trades!U$2:U$9999=Blotter!B19)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&gt;0))),SUM((Trades!T$2:T$9999=Blotter!C19)*(Trades!U$2:U$9999=Blotter!B19)*(Trades!W$2:W$9999)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&gt;0))/SUM((Trades!T$2:T$9999=Blotter!C19)*(Trades!U$2:U$9999=Blotter!B19)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&gt;0)),0)</f>
-        <v>1983.0877791756002</v>
+        <v>1986.6</v>
       </c>
       <c r="Z19" s="35">
         <f>IF(C$2="Last",IF(ISNUMBER(VLOOKUP(B19,Prices!A:L,8,0)),VLOOKUP(B19,Prices!A:L,8,0),0),IF(ISNUMBER(VLOOKUP(B19,Prices!A:L,12,0)),VLOOKUP(B19,Prices!A:L,12,0),0))</f>
-        <v>1976.65</v>
+        <v>2151.6</v>
       </c>
       <c r="AB19" s="29"/>
     </row>
@@ -5403,7 +5415,7 @@
       <formula>$I19&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations disablePrompts="1" count="2">
+  <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E18:E81" xr:uid="{AC88AEA5-902E-420C-9C45-273DF27D0711}">
       <formula1>$E$2:$E$9</formula1>
     </dataValidation>
@@ -5443,73 +5455,73 @@
   <sheetData>
     <row r="1" spans="1:32" x14ac:dyDescent="0.4">
       <c r="A1" s="86" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B1" s="86" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C1" s="86" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D1" s="86" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E1" s="86" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F1" s="86" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G1" s="86" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H1" s="86" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="I1" s="86" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="J1" s="86" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="K1" s="86" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="L1" s="86" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="M1" s="86" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="N1" s="86" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="O1" s="86" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P1" s="86" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="Q1" s="86" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="R1" s="86" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="S1" s="86" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="T1" s="86" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="U1" s="86" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="V1" s="86" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="W1" s="86" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="X1" s="84"/>
       <c r="Y1" s="84"/>
@@ -5523,7 +5535,7 @@
     </row>
     <row r="2" spans="1:32" x14ac:dyDescent="0.4">
       <c r="A2" s="81" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B2" s="81">
         <v>649180678</v>
@@ -5535,7 +5547,7 @@
         <v>21</v>
       </c>
       <c r="E2" s="81" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="F2" s="81" t="s">
         <v>84</v>
@@ -5544,31 +5556,31 @@
         <v>63</v>
       </c>
       <c r="H2" s="91">
-        <v>6905</v>
+        <v>6924.25</v>
       </c>
       <c r="I2" s="91">
-        <v>6904</v>
+        <v>6924.25</v>
       </c>
       <c r="J2" s="91">
-        <v>6905</v>
+        <v>6925.25</v>
       </c>
       <c r="K2" s="91">
-        <v>6904.5</v>
+        <v>6924.75</v>
       </c>
       <c r="L2" s="91">
-        <v>6876.5</v>
+        <v>6928.5</v>
       </c>
       <c r="M2" s="91">
-        <v>6865</v>
+        <v>6933.75</v>
       </c>
       <c r="N2" s="91">
-        <v>6907.75</v>
+        <v>6953.5</v>
       </c>
       <c r="O2" s="91">
-        <v>6825.5</v>
+        <v>6893</v>
       </c>
       <c r="P2" s="91">
-        <v>5617</v>
+        <v>3414</v>
       </c>
       <c r="Q2" s="91"/>
       <c r="R2" s="91"/>
@@ -5576,10 +5588,10 @@
       <c r="T2" s="91"/>
       <c r="U2" s="91"/>
       <c r="V2" s="85">
-        <v>46085.623020833336</v>
+        <v>46086.543333333335</v>
       </c>
       <c r="W2" s="81" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="X2" s="81"/>
       <c r="Y2" s="81"/>
@@ -5587,7 +5599,7 @@
     </row>
     <row r="3" spans="1:32" x14ac:dyDescent="0.4">
       <c r="A3" s="81" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B3" s="81">
         <v>750150196</v>
@@ -5599,7 +5611,7 @@
         <v>22</v>
       </c>
       <c r="E3" s="81" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F3" s="81" t="s">
         <v>84</v>
@@ -5608,31 +5620,31 @@
         <v>63</v>
       </c>
       <c r="H3" s="91">
-        <v>25126.25</v>
+        <v>25336.5</v>
       </c>
       <c r="I3" s="91">
-        <v>25126.25</v>
+        <v>25332.75</v>
       </c>
       <c r="J3" s="91">
-        <v>25130.5</v>
+        <v>25338</v>
       </c>
       <c r="K3" s="91">
-        <v>25128.375</v>
+        <v>25335.375</v>
       </c>
       <c r="L3" s="91">
-        <v>24970</v>
+        <v>25347</v>
       </c>
       <c r="M3" s="91">
-        <v>24921.5</v>
+        <v>25367.75</v>
       </c>
       <c r="N3" s="91">
-        <v>25138.5</v>
+        <v>25460.5</v>
       </c>
       <c r="O3" s="91">
-        <v>24712.5</v>
+        <v>25189.5</v>
       </c>
       <c r="P3" s="91">
-        <v>3240</v>
+        <v>999</v>
       </c>
       <c r="Q3" s="91"/>
       <c r="R3" s="91"/>
@@ -5640,10 +5652,10 @@
       <c r="T3" s="91"/>
       <c r="U3" s="91"/>
       <c r="V3" s="85">
-        <v>46085.623020833336</v>
+        <v>46086.543333333335</v>
       </c>
       <c r="W3" s="81" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="X3" s="81"/>
       <c r="Y3" s="81"/>
@@ -5651,7 +5663,7 @@
     </row>
     <row r="4" spans="1:32" x14ac:dyDescent="0.4">
       <c r="A4" s="81" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B4" s="81">
         <v>770561234</v>
@@ -5663,7 +5675,7 @@
         <v>23</v>
       </c>
       <c r="E4" s="81" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F4" s="81" t="s">
         <v>84</v>
@@ -5672,31 +5684,31 @@
         <v>63</v>
       </c>
       <c r="H4" s="91">
-        <v>2648.8</v>
+        <v>2645.5</v>
       </c>
       <c r="I4" s="91">
-        <v>2650.1</v>
+        <v>2645</v>
       </c>
       <c r="J4" s="91">
-        <v>2651.2</v>
+        <v>2645.7</v>
       </c>
       <c r="K4" s="91">
-        <v>2650.6499999999996</v>
+        <v>2645.35</v>
       </c>
       <c r="L4" s="91">
-        <v>2629</v>
+        <v>2655.1</v>
       </c>
       <c r="M4" s="91">
-        <v>2621.5</v>
+        <v>2655.8</v>
       </c>
       <c r="N4" s="91">
-        <v>2652.3</v>
+        <v>2659.7</v>
       </c>
       <c r="O4" s="91">
-        <v>2602</v>
+        <v>2632.8</v>
       </c>
       <c r="P4" s="91">
-        <v>344</v>
+        <v>333</v>
       </c>
       <c r="Q4" s="91"/>
       <c r="R4" s="91"/>
@@ -5704,10 +5716,10 @@
       <c r="T4" s="91"/>
       <c r="U4" s="91"/>
       <c r="V4" s="85">
-        <v>46085.623020833336</v>
+        <v>46086.543333333335</v>
       </c>
       <c r="W4" s="81" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="X4" s="81"/>
       <c r="Y4" s="81"/>
@@ -5715,7 +5727,7 @@
     </row>
     <row r="5" spans="1:32" x14ac:dyDescent="0.4">
       <c r="A5" s="81" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B5" s="81">
         <v>638120304</v>
@@ -5727,7 +5739,7 @@
         <v>64</v>
       </c>
       <c r="E5" s="81" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F5" s="81" t="s">
         <v>85</v>
@@ -5736,31 +5748,31 @@
         <v>60</v>
       </c>
       <c r="H5" s="91">
-        <v>5813</v>
+        <v>5825</v>
       </c>
       <c r="I5" s="91">
-        <v>5820</v>
+        <v>5816</v>
       </c>
       <c r="J5" s="91">
-        <v>5822</v>
+        <v>5818</v>
       </c>
       <c r="K5" s="91">
-        <v>5821</v>
+        <v>5817</v>
       </c>
       <c r="L5" s="91">
-        <v>5710</v>
+        <v>5816</v>
       </c>
       <c r="M5" s="91">
-        <v>5767</v>
+        <v>5850</v>
       </c>
       <c r="N5" s="91">
-        <v>5829</v>
+        <v>5854</v>
       </c>
       <c r="O5" s="91">
-        <v>5683</v>
+        <v>5761</v>
       </c>
       <c r="P5" s="91">
-        <v>859</v>
+        <v>481</v>
       </c>
       <c r="Q5" s="91"/>
       <c r="R5" s="91"/>
@@ -5768,10 +5780,10 @@
       <c r="T5" s="91"/>
       <c r="U5" s="91"/>
       <c r="V5" s="85">
-        <v>46085.623020833336</v>
+        <v>46086.543333333335</v>
       </c>
       <c r="W5" s="81" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="X5" s="81"/>
       <c r="Y5" s="81"/>
@@ -5779,7 +5791,7 @@
     </row>
     <row r="6" spans="1:32" x14ac:dyDescent="0.4">
       <c r="A6" s="81" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B6" s="81">
         <v>638120262</v>
@@ -5791,7 +5803,7 @@
         <v>66</v>
       </c>
       <c r="E6" s="81" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="F6" s="81" t="s">
         <v>85</v>
@@ -5800,31 +5812,31 @@
         <v>60</v>
       </c>
       <c r="H6" s="91">
-        <v>24428</v>
+        <v>24493</v>
       </c>
       <c r="I6" s="91">
-        <v>24411</v>
+        <v>24444</v>
       </c>
       <c r="J6" s="91">
-        <v>24431</v>
+        <v>24460</v>
       </c>
       <c r="K6" s="91">
-        <v>24421</v>
+        <v>24452</v>
       </c>
       <c r="L6" s="91">
-        <v>23982</v>
+        <v>24460</v>
       </c>
       <c r="M6" s="91">
-        <v>24119</v>
+        <v>24531</v>
       </c>
       <c r="N6" s="91">
-        <v>24455</v>
+        <v>24550</v>
       </c>
       <c r="O6" s="91">
-        <v>24038</v>
+        <v>24280</v>
       </c>
       <c r="P6" s="91">
-        <v>27</v>
+        <v>61</v>
       </c>
       <c r="Q6" s="91"/>
       <c r="R6" s="91"/>
@@ -5832,10 +5844,10 @@
       <c r="T6" s="91"/>
       <c r="U6" s="91"/>
       <c r="V6" s="85">
-        <v>46085.623020833336</v>
+        <v>46086.543333333335</v>
       </c>
       <c r="W6" s="81" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="X6" s="81"/>
       <c r="Y6" s="81"/>
@@ -5843,7 +5855,7 @@
     </row>
     <row r="7" spans="1:32" x14ac:dyDescent="0.4">
       <c r="A7" s="1" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B7" s="1">
         <v>635680486</v>
@@ -5855,7 +5867,7 @@
         <v>67</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>84</v>
@@ -5864,31 +5876,31 @@
         <v>61</v>
       </c>
       <c r="H7" s="93">
-        <v>55770</v>
+        <v>55595</v>
       </c>
       <c r="I7" s="93">
-        <v>55750</v>
+        <v>55585</v>
       </c>
       <c r="J7" s="93">
-        <v>55790</v>
+        <v>55605</v>
       </c>
       <c r="K7" s="93">
-        <v>55770</v>
+        <v>55595</v>
       </c>
       <c r="L7" s="93">
-        <v>55135</v>
+        <v>56150</v>
       </c>
       <c r="M7" s="93">
-        <v>54800</v>
+        <v>56000</v>
       </c>
       <c r="N7" s="93">
-        <v>56000</v>
+        <v>56390</v>
       </c>
       <c r="O7" s="93">
-        <v>53460</v>
+        <v>54770</v>
       </c>
       <c r="P7" s="93">
-        <v>535</v>
+        <v>513</v>
       </c>
       <c r="Q7" s="93"/>
       <c r="R7" s="93"/>
@@ -5896,15 +5908,15 @@
       <c r="T7" s="93"/>
       <c r="U7" s="93"/>
       <c r="V7" s="92">
-        <v>46085.623020833336</v>
+        <v>46086.543333333335</v>
       </c>
       <c r="W7" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="8" spans="1:32" x14ac:dyDescent="0.4">
       <c r="A8" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B8" s="1">
         <v>304037436</v>
@@ -5916,7 +5928,7 @@
         <v>24</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>65</v>
@@ -5925,31 +5937,31 @@
         <v>63</v>
       </c>
       <c r="H8" s="93">
-        <v>73.81</v>
+        <v>76.95</v>
       </c>
       <c r="I8" s="93">
-        <v>73.8</v>
+        <v>76.94</v>
       </c>
       <c r="J8" s="93">
-        <v>73.819999999999993</v>
+        <v>76.95</v>
       </c>
       <c r="K8" s="93">
-        <v>73.81</v>
+        <v>76.944999999999993</v>
       </c>
       <c r="L8" s="93">
-        <v>74.56</v>
+        <v>74.66</v>
       </c>
       <c r="M8" s="93">
-        <v>74.739999999999995</v>
+        <v>76.150000000000006</v>
       </c>
       <c r="N8" s="93">
-        <v>77.23</v>
+        <v>78.09</v>
       </c>
       <c r="O8" s="93">
-        <v>73.31</v>
+        <v>74.97</v>
       </c>
       <c r="P8" s="93">
-        <v>278772</v>
+        <v>187336</v>
       </c>
       <c r="Q8" s="93"/>
       <c r="R8" s="93"/>
@@ -5957,15 +5969,15 @@
       <c r="T8" s="93"/>
       <c r="U8" s="93"/>
       <c r="V8" s="92">
-        <v>46085.623020833336</v>
+        <v>46086.543333333335</v>
       </c>
       <c r="W8" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="9" spans="1:32" x14ac:dyDescent="0.4">
       <c r="A9" s="1" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B9" s="1">
         <v>269460069</v>
@@ -5977,7 +5989,7 @@
         <v>5</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>65</v>
@@ -5986,31 +5998,31 @@
         <v>63</v>
       </c>
       <c r="H9" s="93">
-        <v>3.1190000000000002</v>
+        <v>3.1859999999999999</v>
       </c>
       <c r="I9" s="93">
-        <v>3.1190000000000002</v>
+        <v>3.1850000000000001</v>
       </c>
       <c r="J9" s="93">
-        <v>3.1219999999999999</v>
+        <v>3.1869999999999998</v>
       </c>
       <c r="K9" s="93">
-        <v>3.1204999999999998</v>
+        <v>3.1859999999999999</v>
       </c>
       <c r="L9" s="93">
-        <v>3.2280000000000002</v>
+        <v>3.1110000000000002</v>
       </c>
       <c r="M9" s="93">
-        <v>3.214</v>
+        <v>3.1280000000000001</v>
       </c>
       <c r="N9" s="93">
-        <v>3.2530000000000001</v>
+        <v>3.202</v>
       </c>
       <c r="O9" s="93">
-        <v>3.1070000000000002</v>
+        <v>3.1280000000000001</v>
       </c>
       <c r="P9" s="93">
-        <v>7534</v>
+        <v>3218</v>
       </c>
       <c r="Q9" s="93"/>
       <c r="R9" s="93"/>
@@ -6018,15 +6030,15 @@
       <c r="T9" s="93"/>
       <c r="U9" s="93"/>
       <c r="V9" s="92">
-        <v>46085.623020833336</v>
+        <v>46086.543333333335</v>
       </c>
       <c r="W9" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="10" spans="1:32" x14ac:dyDescent="0.4">
       <c r="A10" s="1" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B10" s="1">
         <v>600696533</v>
@@ -6038,7 +6050,7 @@
         <v>9</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>65</v>
@@ -6047,31 +6059,31 @@
         <v>63</v>
       </c>
       <c r="H10" s="93">
-        <v>2.4119000000000002</v>
+        <v>2.5028999999999999</v>
       </c>
       <c r="I10" s="93">
-        <v>2.4117000000000002</v>
+        <v>2.5023</v>
       </c>
       <c r="J10" s="93">
-        <v>2.4121999999999999</v>
+        <v>2.5028999999999999</v>
       </c>
       <c r="K10" s="93">
-        <v>2.41195</v>
+        <v>2.5026000000000002</v>
       </c>
       <c r="L10" s="93">
-        <v>2.4209000000000001</v>
+        <v>2.4462999999999999</v>
       </c>
       <c r="M10" s="93">
-        <v>2.4260999999999999</v>
+        <v>2.4544999999999999</v>
       </c>
       <c r="N10" s="93">
-        <v>2.4925000000000002</v>
+        <v>2.5459999999999998</v>
       </c>
       <c r="O10" s="93">
-        <v>2.4083000000000001</v>
+        <v>2.4462000000000002</v>
       </c>
       <c r="P10" s="93">
-        <v>34984</v>
+        <v>47319</v>
       </c>
       <c r="Q10" s="93"/>
       <c r="R10" s="93"/>
@@ -6079,15 +6091,15 @@
       <c r="T10" s="93"/>
       <c r="U10" s="93"/>
       <c r="V10" s="92">
-        <v>46085.623020833336</v>
+        <v>46086.543333333335</v>
       </c>
       <c r="W10" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="11" spans="1:32" x14ac:dyDescent="0.4">
       <c r="A11" s="1" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B11" s="1">
         <v>430360630</v>
@@ -6099,7 +6111,7 @@
         <v>26</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>86</v>
@@ -6108,31 +6120,31 @@
         <v>63</v>
       </c>
       <c r="H11" s="93">
-        <v>5238.3999999999996</v>
+        <v>5214.8999999999996</v>
       </c>
       <c r="I11" s="93">
-        <v>5240.5</v>
+        <v>5213.7</v>
       </c>
       <c r="J11" s="93">
-        <v>5241.3999999999996</v>
+        <v>5214.1000000000004</v>
       </c>
       <c r="K11" s="93">
-        <v>5240.95</v>
+        <v>5213.8999999999996</v>
       </c>
       <c r="L11" s="93">
-        <v>5162.2</v>
+        <v>5173.3</v>
       </c>
       <c r="M11" s="93">
-        <v>5158.2</v>
+        <v>5199</v>
       </c>
       <c r="N11" s="93">
-        <v>5256.9</v>
+        <v>5241.5</v>
       </c>
       <c r="O11" s="93">
-        <v>5151</v>
+        <v>5168.8999999999996</v>
       </c>
       <c r="P11" s="93">
-        <v>4826</v>
+        <v>2040</v>
       </c>
       <c r="Q11" s="93"/>
       <c r="R11" s="93"/>
@@ -6140,15 +6152,15 @@
       <c r="T11" s="93"/>
       <c r="U11" s="93"/>
       <c r="V11" s="92">
-        <v>46085.623020833336</v>
+        <v>46086.543333333335</v>
       </c>
       <c r="W11" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="12" spans="1:32" x14ac:dyDescent="0.4">
       <c r="A12" s="1" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B12" s="1">
         <v>760200596</v>
@@ -6160,7 +6172,7 @@
         <v>27</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>86</v>
@@ -6169,31 +6181,31 @@
         <v>63</v>
       </c>
       <c r="H12" s="93">
-        <v>86.33</v>
+        <v>85.084999999999994</v>
       </c>
       <c r="I12" s="93">
-        <v>86.215000000000003</v>
+        <v>84.94</v>
       </c>
       <c r="J12" s="93">
-        <v>86.28</v>
+        <v>84.995000000000005</v>
       </c>
       <c r="K12" s="93">
-        <v>86.247500000000002</v>
+        <v>84.967500000000001</v>
       </c>
       <c r="L12" s="93">
-        <v>83.78</v>
+        <v>83.495000000000005</v>
       </c>
       <c r="M12" s="93">
-        <v>83.784999999999997</v>
+        <v>84.674999999999997</v>
       </c>
       <c r="N12" s="93">
-        <v>87.18</v>
+        <v>85.984999999999999</v>
       </c>
       <c r="O12" s="93">
-        <v>83.504999999999995</v>
+        <v>83</v>
       </c>
       <c r="P12" s="93">
-        <v>85</v>
+        <v>53</v>
       </c>
       <c r="Q12" s="93"/>
       <c r="R12" s="93"/>
@@ -6201,15 +6213,15 @@
       <c r="T12" s="93"/>
       <c r="U12" s="93"/>
       <c r="V12" s="92">
-        <v>46085.623020833336</v>
+        <v>46086.543333333335</v>
       </c>
       <c r="W12" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="13" spans="1:32" x14ac:dyDescent="0.4">
       <c r="A13" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B13" s="1">
         <v>712565973</v>
@@ -6221,7 +6233,7 @@
         <v>25</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>86</v>
@@ -6230,31 +6242,31 @@
         <v>63</v>
       </c>
       <c r="H13" s="93">
-        <v>5.9450000000000003</v>
+        <v>5.8574999999999999</v>
       </c>
       <c r="I13" s="93">
-        <v>5.9494999999999996</v>
+        <v>5.8630000000000004</v>
       </c>
       <c r="J13" s="93">
-        <v>5.9509999999999996</v>
+        <v>5.8650000000000002</v>
       </c>
       <c r="K13" s="93">
-        <v>5.9502499999999996</v>
+        <v>5.8640000000000008</v>
       </c>
       <c r="L13" s="93">
-        <v>5.8544999999999998</v>
+        <v>5.9355000000000002</v>
       </c>
       <c r="M13" s="93">
-        <v>5.8810000000000002</v>
+        <v>5.96</v>
       </c>
       <c r="N13" s="93">
-        <v>5.9850000000000003</v>
+        <v>5.9740000000000002</v>
       </c>
       <c r="O13" s="93">
-        <v>5.8765000000000001</v>
+        <v>5.8540000000000001</v>
       </c>
       <c r="P13" s="93">
-        <v>104</v>
+        <v>32</v>
       </c>
       <c r="Q13" s="93"/>
       <c r="R13" s="93"/>
@@ -6262,15 +6274,15 @@
       <c r="T13" s="93"/>
       <c r="U13" s="93"/>
       <c r="V13" s="92">
-        <v>46085.623020833336</v>
+        <v>46086.543333333335</v>
       </c>
       <c r="W13" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="14" spans="1:32" x14ac:dyDescent="0.4">
       <c r="A14" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B14" s="1">
         <v>671574022</v>
@@ -6282,7 +6294,7 @@
         <v>28</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>87</v>
@@ -6291,31 +6303,31 @@
         <v>63</v>
       </c>
       <c r="H14" s="93">
-        <v>442.75</v>
+        <v>446</v>
       </c>
       <c r="I14" s="93">
-        <v>-100</v>
+        <v>445.75</v>
       </c>
       <c r="J14" s="93">
-        <v>-100</v>
+        <v>446</v>
       </c>
       <c r="K14" s="93">
-        <v>-100</v>
+        <v>445.875</v>
       </c>
       <c r="L14" s="93">
-        <v>446.5</v>
+        <v>443.75</v>
       </c>
       <c r="M14" s="93">
-        <v>446</v>
+        <v>442.5</v>
       </c>
       <c r="N14" s="93">
-        <v>447</v>
+        <v>446.25</v>
       </c>
       <c r="O14" s="93">
         <v>442.5</v>
       </c>
       <c r="P14" s="93">
-        <v>30434</v>
+        <v>16675</v>
       </c>
       <c r="Q14" s="93"/>
       <c r="R14" s="93"/>
@@ -6323,15 +6335,15 @@
       <c r="T14" s="93"/>
       <c r="U14" s="93"/>
       <c r="V14" s="92">
-        <v>46085.623020833336</v>
+        <v>46086.543333333335</v>
       </c>
       <c r="W14" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="15" spans="1:32" x14ac:dyDescent="0.4">
       <c r="A15" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B15" s="1">
         <v>642254817</v>
@@ -6343,7 +6355,7 @@
         <v>29</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>87</v>
@@ -6352,31 +6364,31 @@
         <v>63</v>
       </c>
       <c r="H15" s="93">
-        <v>566.75</v>
+        <v>576.25</v>
       </c>
       <c r="I15" s="93">
-        <v>-100</v>
+        <v>576.25</v>
       </c>
       <c r="J15" s="93">
-        <v>-100</v>
+        <v>576.5</v>
       </c>
       <c r="K15" s="93">
-        <v>-100</v>
+        <v>576.375</v>
       </c>
       <c r="L15" s="93">
-        <v>574</v>
+        <v>568.25</v>
       </c>
       <c r="M15" s="93">
-        <v>574</v>
+        <v>568.25</v>
       </c>
       <c r="N15" s="93">
-        <v>577</v>
+        <v>576.75</v>
       </c>
       <c r="O15" s="93">
-        <v>564.5</v>
+        <v>568</v>
       </c>
       <c r="P15" s="93">
-        <v>17338</v>
+        <v>11237</v>
       </c>
       <c r="Q15" s="93"/>
       <c r="R15" s="93"/>
@@ -6384,15 +6396,15 @@
       <c r="T15" s="93"/>
       <c r="U15" s="93"/>
       <c r="V15" s="92">
-        <v>46085.623020833336</v>
+        <v>46086.543333333335</v>
       </c>
       <c r="W15" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="16" spans="1:32" x14ac:dyDescent="0.4">
       <c r="A16" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B16" s="1">
         <v>665643569</v>
@@ -6404,7 +6416,7 @@
         <v>31</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>87</v>
@@ -6413,31 +6425,31 @@
         <v>63</v>
       </c>
       <c r="H16" s="93">
+        <v>1173.25</v>
+      </c>
+      <c r="I16" s="93">
+        <v>1173.25</v>
+      </c>
+      <c r="J16" s="93">
+        <v>1173.5</v>
+      </c>
+      <c r="K16" s="93">
+        <v>1173.375</v>
+      </c>
+      <c r="L16" s="93">
+        <v>1169.5</v>
+      </c>
+      <c r="M16" s="93">
         <v>1168.25</v>
       </c>
-      <c r="I16" s="93">
-        <v>-100</v>
-      </c>
-      <c r="J16" s="93">
-        <v>-100</v>
-      </c>
-      <c r="K16" s="93">
-        <v>-100</v>
-      </c>
-      <c r="L16" s="93">
-        <v>1170.5</v>
-      </c>
-      <c r="M16" s="93">
-        <v>1171</v>
-      </c>
       <c r="N16" s="93">
-        <v>1175.75</v>
+        <v>1175</v>
       </c>
       <c r="O16" s="93">
-        <v>1166.25</v>
+        <v>1167.5</v>
       </c>
       <c r="P16" s="93">
-        <v>21900</v>
+        <v>13447</v>
       </c>
       <c r="Q16" s="93"/>
       <c r="R16" s="93"/>
@@ -6445,15 +6457,15 @@
       <c r="T16" s="93"/>
       <c r="U16" s="93"/>
       <c r="V16" s="92">
-        <v>46085.623020833336</v>
+        <v>46086.543333333335</v>
       </c>
       <c r="W16" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="17" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A17" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B17" s="1">
         <v>634760175</v>
@@ -6465,7 +6477,7 @@
         <v>32</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>69</v>
@@ -6474,31 +6486,31 @@
         <v>63</v>
       </c>
       <c r="H17" s="93">
-        <v>13.81</v>
+        <v>13.72</v>
       </c>
       <c r="I17" s="93">
-        <v>13.81</v>
+        <v>13.71</v>
       </c>
       <c r="J17" s="93">
-        <v>13.82</v>
+        <v>13.72</v>
       </c>
       <c r="K17" s="93">
-        <v>13.815000000000001</v>
+        <v>13.715</v>
       </c>
       <c r="L17" s="93">
-        <v>13.93</v>
+        <v>13.73</v>
       </c>
       <c r="M17" s="93">
-        <v>13.97</v>
+        <v>13.74</v>
       </c>
       <c r="N17" s="93">
-        <v>14.07</v>
+        <v>13.8</v>
       </c>
       <c r="O17" s="93">
-        <v>13.75</v>
+        <v>13.61</v>
       </c>
       <c r="P17" s="93">
-        <v>35203</v>
+        <v>17987</v>
       </c>
       <c r="Q17" s="93"/>
       <c r="R17" s="93"/>
@@ -6506,15 +6518,15 @@
       <c r="T17" s="93"/>
       <c r="U17" s="93"/>
       <c r="V17" s="92">
-        <v>46085.623020833336</v>
+        <v>46086.543333333335</v>
       </c>
       <c r="W17" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="18" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A18" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B18" s="1">
         <v>634760204</v>
@@ -6526,7 +6538,7 @@
         <v>33</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>69</v>
@@ -6535,31 +6547,31 @@
         <v>63</v>
       </c>
       <c r="H18" s="93">
-        <v>286.85000000000002</v>
+        <v>288.64999999999998</v>
       </c>
       <c r="I18" s="93">
-        <v>286.8</v>
+        <v>288.60000000000002</v>
       </c>
       <c r="J18" s="93">
-        <v>286.89999999999998</v>
+        <v>288.7</v>
       </c>
       <c r="K18" s="93">
-        <v>286.85000000000002</v>
+        <v>288.64999999999998</v>
       </c>
       <c r="L18" s="93">
-        <v>283.14999999999998</v>
+        <v>286.25</v>
       </c>
       <c r="M18" s="93">
-        <v>283.5</v>
+        <v>287.05</v>
       </c>
       <c r="N18" s="93">
-        <v>288.55</v>
+        <v>288.85000000000002</v>
       </c>
       <c r="O18" s="93">
-        <v>282.39999999999998</v>
+        <v>285</v>
       </c>
       <c r="P18" s="93">
-        <v>4938</v>
+        <v>1625</v>
       </c>
       <c r="Q18" s="93"/>
       <c r="R18" s="93"/>
@@ -6567,15 +6579,15 @@
       <c r="T18" s="93"/>
       <c r="U18" s="93"/>
       <c r="V18" s="92">
-        <v>46085.623020833336</v>
+        <v>46086.543333333335</v>
       </c>
       <c r="W18" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="19" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A19" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B19" s="1">
         <v>707621000</v>
@@ -6587,7 +6599,7 @@
         <v>34</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>69</v>
@@ -6596,31 +6608,31 @@
         <v>63</v>
       </c>
       <c r="H19" s="93">
-        <v>3042</v>
+        <v>3045</v>
       </c>
       <c r="I19" s="93">
-        <v>3041</v>
+        <v>3043</v>
       </c>
       <c r="J19" s="93">
-        <v>3043</v>
+        <v>3046</v>
       </c>
       <c r="K19" s="93">
-        <v>3042</v>
+        <v>3044.5</v>
       </c>
       <c r="L19" s="93">
-        <v>3015</v>
+        <v>3060</v>
       </c>
       <c r="M19" s="93">
-        <v>3014</v>
+        <v>3045</v>
       </c>
       <c r="N19" s="93">
-        <v>3097</v>
+        <v>3074</v>
       </c>
       <c r="O19" s="93">
-        <v>3005</v>
+        <v>3027</v>
       </c>
       <c r="P19" s="93">
-        <v>3707</v>
+        <v>2029</v>
       </c>
       <c r="Q19" s="93"/>
       <c r="R19" s="93"/>
@@ -6628,15 +6640,15 @@
       <c r="T19" s="93"/>
       <c r="U19" s="93"/>
       <c r="V19" s="92">
-        <v>46085.623020833336</v>
+        <v>46086.543333333335</v>
       </c>
       <c r="W19" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="20" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A20" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B20" s="1">
         <v>634760245</v>
@@ -6648,7 +6660,7 @@
         <v>70</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>69</v>
@@ -6657,31 +6669,31 @@
         <v>63</v>
       </c>
       <c r="H20" s="93">
+        <v>64.12</v>
+      </c>
+      <c r="I20" s="93">
+        <v>64.12</v>
+      </c>
+      <c r="J20" s="93">
+        <v>64.14</v>
+      </c>
+      <c r="K20" s="93">
+        <v>64.13</v>
+      </c>
+      <c r="L20" s="93">
+        <v>64.16</v>
+      </c>
+      <c r="M20" s="93">
+        <v>64.25</v>
+      </c>
+      <c r="N20" s="93">
         <v>64.45</v>
       </c>
-      <c r="I20" s="93">
-        <v>64.44</v>
-      </c>
-      <c r="J20" s="93">
-        <v>64.459999999999994</v>
-      </c>
-      <c r="K20" s="93">
-        <v>64.449999999999989</v>
-      </c>
-      <c r="L20" s="93">
-        <v>64.040000000000006</v>
-      </c>
-      <c r="M20" s="93">
-        <v>64.16</v>
-      </c>
-      <c r="N20" s="93">
-        <v>64.88</v>
-      </c>
       <c r="O20" s="93">
-        <v>64.06</v>
+        <v>63.96</v>
       </c>
       <c r="P20" s="93">
-        <v>11315</v>
+        <v>4962</v>
       </c>
       <c r="Q20" s="93"/>
       <c r="R20" s="93"/>
@@ -6689,10 +6701,10 @@
       <c r="T20" s="93"/>
       <c r="U20" s="93"/>
       <c r="V20" s="92">
-        <v>46085.623020833336</v>
+        <v>46086.543333333335</v>
       </c>
       <c r="W20" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="21" spans="1:23" x14ac:dyDescent="0.4">
@@ -6709,7 +6721,7 @@
         <v>35</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>84</v>
@@ -6730,15 +6742,19 @@
         <v>-100</v>
       </c>
       <c r="L21" s="93">
-        <v>234.125</v>
+        <v>238.35</v>
       </c>
       <c r="M21" s="93">
-        <v>231</v>
-      </c>
-      <c r="N21" s="93"/>
-      <c r="O21" s="93"/>
+        <v>235</v>
+      </c>
+      <c r="N21" s="93">
+        <v>239</v>
+      </c>
+      <c r="O21" s="93">
+        <v>234.8</v>
+      </c>
       <c r="P21" s="93">
-        <v>0</v>
+        <v>32462</v>
       </c>
       <c r="Q21" s="93"/>
       <c r="R21" s="93"/>
@@ -6746,10 +6762,10 @@
       <c r="T21" s="93"/>
       <c r="U21" s="93"/>
       <c r="V21" s="92">
-        <v>46085.623020833336</v>
+        <v>46086.543333333335</v>
       </c>
       <c r="W21" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="22" spans="1:23" x14ac:dyDescent="0.4">
@@ -6766,7 +6782,7 @@
         <v>36</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>84</v>
@@ -6787,15 +6803,19 @@
         <v>-100</v>
       </c>
       <c r="L22" s="93">
-        <v>349.35</v>
+        <v>357</v>
       </c>
       <c r="M22" s="93">
-        <v>345.95</v>
-      </c>
-      <c r="N22" s="93"/>
-      <c r="O22" s="93"/>
+        <v>350.55</v>
+      </c>
+      <c r="N22" s="93">
+        <v>357.42500000000001</v>
+      </c>
+      <c r="O22" s="93">
+        <v>350.52499999999998</v>
+      </c>
       <c r="P22" s="93">
-        <v>0</v>
+        <v>6355</v>
       </c>
       <c r="Q22" s="93"/>
       <c r="R22" s="93"/>
@@ -6803,15 +6823,15 @@
       <c r="T22" s="93"/>
       <c r="U22" s="93"/>
       <c r="V22" s="92">
-        <v>46085.623020833336</v>
+        <v>46086.543333333335</v>
       </c>
       <c r="W22" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="23" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A23" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B23" s="1">
         <v>735014937</v>
@@ -6823,7 +6843,7 @@
         <v>37</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>84</v>
@@ -6844,15 +6864,19 @@
         <v>-100</v>
       </c>
       <c r="L23" s="93">
-        <v>95.75</v>
+        <v>97.075000000000003</v>
       </c>
       <c r="M23" s="93">
-        <v>95.575000000000003</v>
-      </c>
-      <c r="N23" s="93"/>
-      <c r="O23" s="93"/>
+        <v>95.85</v>
+      </c>
+      <c r="N23" s="93">
+        <v>97.3</v>
+      </c>
+      <c r="O23" s="93">
+        <v>95.674999999999997</v>
+      </c>
       <c r="P23" s="93">
-        <v>0</v>
+        <v>23682</v>
       </c>
       <c r="Q23" s="93"/>
       <c r="R23" s="93"/>
@@ -6860,15 +6884,15 @@
       <c r="T23" s="93"/>
       <c r="U23" s="93"/>
       <c r="V23" s="92">
-        <v>46085.623020833336</v>
+        <v>46086.543333333335</v>
       </c>
       <c r="W23" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="24" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A24" s="1" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B24" s="1">
         <v>792232100</v>
@@ -6880,7 +6904,7 @@
         <v>38</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>69</v>
@@ -6889,31 +6913,31 @@
         <v>63</v>
       </c>
       <c r="H24" s="93">
-        <v>98.495000000000005</v>
+        <v>98.68</v>
       </c>
       <c r="I24" s="93">
-        <v>98.48</v>
+        <v>98.674999999999997</v>
       </c>
       <c r="J24" s="93">
-        <v>98.495000000000005</v>
+        <v>98.685000000000002</v>
       </c>
       <c r="K24" s="93">
-        <v>98.487500000000011</v>
+        <v>98.68</v>
       </c>
       <c r="L24" s="93">
-        <v>98.704999999999998</v>
+        <v>98.43</v>
       </c>
       <c r="M24" s="93">
-        <v>98.844999999999999</v>
+        <v>98.375</v>
       </c>
       <c r="N24" s="93">
-        <v>98.97</v>
+        <v>98.88</v>
       </c>
       <c r="O24" s="93">
-        <v>98.375</v>
+        <v>98.364999999999995</v>
       </c>
       <c r="P24" s="93">
-        <v>783</v>
+        <v>1858</v>
       </c>
       <c r="Q24" s="93"/>
       <c r="R24" s="93"/>
@@ -6921,15 +6945,15 @@
       <c r="T24" s="93"/>
       <c r="U24" s="93"/>
       <c r="V24" s="92">
-        <v>46085.623020833336</v>
+        <v>46086.543333333335</v>
       </c>
       <c r="W24" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="25" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A25" s="1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B25" s="1">
         <v>496647057</v>
@@ -6941,7 +6965,7 @@
         <v>60</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>84</v>
@@ -6950,31 +6974,31 @@
         <v>63</v>
       </c>
       <c r="H25" s="93">
-        <v>1.1697</v>
+        <v>1.1664000000000001</v>
       </c>
       <c r="I25" s="93">
-        <v>1.1695500000000001</v>
+        <v>1.16635</v>
       </c>
       <c r="J25" s="93">
+        <v>1.1664000000000001</v>
+      </c>
+      <c r="K25" s="93">
+        <v>1.1663749999999999</v>
+      </c>
+      <c r="L25" s="93">
         <v>1.1696500000000001</v>
       </c>
-      <c r="K25" s="93">
-        <v>1.1696</v>
-      </c>
-      <c r="L25" s="93">
-        <v>1.1670499999999999</v>
-      </c>
       <c r="M25" s="93">
-        <v>1.16665</v>
+        <v>1.1692</v>
       </c>
       <c r="N25" s="93">
-        <v>1.1712</v>
+        <v>1.17025</v>
       </c>
       <c r="O25" s="93">
-        <v>1.1632</v>
+        <v>1.1636500000000001</v>
       </c>
       <c r="P25" s="93">
-        <v>10742</v>
+        <v>15398</v>
       </c>
       <c r="Q25" s="93"/>
       <c r="R25" s="93"/>
@@ -6982,15 +7006,15 @@
       <c r="T25" s="93"/>
       <c r="U25" s="93"/>
       <c r="V25" s="92">
-        <v>46085.623020833336</v>
+        <v>46086.543333333335</v>
       </c>
       <c r="W25" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="26" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A26" s="1" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B26" s="1">
         <v>496647091</v>
@@ -7002,7 +7026,7 @@
         <v>79</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>84</v>
@@ -7011,31 +7035,31 @@
         <v>63</v>
       </c>
       <c r="H26" s="93">
-        <v>1.3368</v>
+        <v>1.3363</v>
       </c>
       <c r="I26" s="93">
+        <v>1.3364</v>
+      </c>
+      <c r="J26" s="93">
+        <v>1.3366</v>
+      </c>
+      <c r="K26" s="93">
+        <v>1.3365</v>
+      </c>
+      <c r="L26" s="93">
+        <v>1.3375999999999999</v>
+      </c>
+      <c r="M26" s="93">
         <v>1.3371</v>
       </c>
-      <c r="J26" s="93">
-        <v>1.3371999999999999</v>
-      </c>
-      <c r="K26" s="93">
-        <v>1.3371499999999998</v>
-      </c>
-      <c r="L26" s="93">
-        <v>1.3357000000000001</v>
-      </c>
-      <c r="M26" s="93">
-        <v>1.3354999999999999</v>
-      </c>
       <c r="N26" s="93">
-        <v>1.3404</v>
+        <v>1.3387</v>
       </c>
       <c r="O26" s="93">
-        <v>1.3306</v>
+        <v>1.3308</v>
       </c>
       <c r="P26" s="93">
-        <v>18018</v>
+        <v>27021</v>
       </c>
       <c r="Q26" s="93"/>
       <c r="R26" s="93"/>
@@ -7043,15 +7067,15 @@
       <c r="T26" s="93"/>
       <c r="U26" s="93"/>
       <c r="V26" s="92">
-        <v>46085.623020833336</v>
+        <v>46086.543333333335</v>
       </c>
       <c r="W26" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="27" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A27" s="1" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B27" s="1">
         <v>496647108</v>
@@ -7063,7 +7087,7 @@
         <v>61</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>84</v>
@@ -7072,31 +7096,31 @@
         <v>63</v>
       </c>
       <c r="H27" s="93">
-        <v>6.417E-3</v>
+        <v>6.4105000000000004E-3</v>
       </c>
       <c r="I27" s="93">
-        <v>6.4165000000000003E-3</v>
+        <v>6.4105000000000004E-3</v>
       </c>
       <c r="J27" s="93">
-        <v>6.417E-3</v>
+        <v>6.411E-3</v>
       </c>
       <c r="K27" s="93">
-        <v>6.4167500000000006E-3</v>
+        <v>6.4107499999999998E-3</v>
       </c>
       <c r="L27" s="93">
-        <v>6.398E-3</v>
+        <v>6.4250000000000002E-3</v>
       </c>
       <c r="M27" s="93">
-        <v>6.4019999999999997E-3</v>
+        <v>6.4215000000000001E-3</v>
       </c>
       <c r="N27" s="93">
-        <v>6.4304999999999996E-3</v>
+        <v>6.4454999999999998E-3</v>
       </c>
       <c r="O27" s="93">
-        <v>6.3899999999999998E-3</v>
+        <v>6.4079999999999996E-3</v>
       </c>
       <c r="P27" s="93">
-        <v>5552</v>
+        <v>4671</v>
       </c>
       <c r="Q27" s="93"/>
       <c r="R27" s="93"/>
@@ -7104,15 +7128,15 @@
       <c r="T27" s="93"/>
       <c r="U27" s="93"/>
       <c r="V27" s="92">
-        <v>46085.623020833336</v>
+        <v>46086.543333333335</v>
       </c>
       <c r="W27" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="28" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A28" s="1" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B28" s="1">
         <v>496879111</v>
@@ -7124,7 +7148,7 @@
         <v>81</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>84</v>
@@ -7133,31 +7157,31 @@
         <v>63</v>
       </c>
       <c r="H28" s="93">
-        <v>0.73480000000000001</v>
+        <v>0.7369</v>
       </c>
       <c r="I28" s="93">
-        <v>0.73480000000000001</v>
+        <v>0.73680000000000001</v>
       </c>
       <c r="J28" s="93">
-        <v>0.7349</v>
+        <v>0.73685</v>
       </c>
       <c r="K28" s="93">
-        <v>0.73485</v>
+        <v>0.73682500000000006</v>
       </c>
       <c r="L28" s="93">
-        <v>0.73475000000000001</v>
+        <v>0.73665000000000003</v>
       </c>
       <c r="M28" s="93">
-        <v>0.73455000000000004</v>
+        <v>0.73629999999999995</v>
       </c>
       <c r="N28" s="93">
-        <v>0.73604999999999998</v>
+        <v>0.73699999999999999</v>
       </c>
       <c r="O28" s="93">
-        <v>0.73309999999999997</v>
+        <v>0.73470000000000002</v>
       </c>
       <c r="P28" s="93">
-        <v>888</v>
+        <v>1076</v>
       </c>
       <c r="Q28" s="93"/>
       <c r="R28" s="93"/>
@@ -7165,15 +7189,15 @@
       <c r="T28" s="93"/>
       <c r="U28" s="93"/>
       <c r="V28" s="92">
-        <v>46085.623020833336</v>
+        <v>46086.543333333335</v>
       </c>
       <c r="W28" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="29" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A29" s="1" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B29" s="1">
         <v>496647009</v>
@@ -7185,7 +7209,7 @@
         <v>83</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>84</v>
@@ -7194,31 +7218,31 @@
         <v>63</v>
       </c>
       <c r="H29" s="93">
-        <v>0.70469999999999999</v>
+        <v>0.70430000000000004</v>
       </c>
       <c r="I29" s="93">
-        <v>0.70484999999999998</v>
+        <v>0.70440000000000003</v>
       </c>
       <c r="J29" s="93">
-        <v>0.70489999999999997</v>
+        <v>0.70450000000000002</v>
       </c>
       <c r="K29" s="93">
-        <v>0.70487499999999992</v>
+        <v>0.70445000000000002</v>
       </c>
       <c r="L29" s="93">
-        <v>0.70365</v>
+        <v>0.70760000000000001</v>
       </c>
       <c r="M29" s="93">
-        <v>0.70325000000000004</v>
+        <v>0.70709999999999995</v>
       </c>
       <c r="N29" s="93">
-        <v>0.70660000000000001</v>
+        <v>0.70830000000000004</v>
       </c>
       <c r="O29" s="93">
-        <v>0.69794999999999996</v>
+        <v>0.70055000000000001</v>
       </c>
       <c r="P29" s="93">
-        <v>11874</v>
+        <v>4540</v>
       </c>
       <c r="Q29" s="93"/>
       <c r="R29" s="93"/>
@@ -7226,15 +7250,15 @@
       <c r="T29" s="93"/>
       <c r="U29" s="93"/>
       <c r="V29" s="92">
-        <v>46085.623020833336</v>
+        <v>46086.543333333335</v>
       </c>
       <c r="W29" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="30" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A30" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B30" s="1">
         <v>815824224</v>
@@ -7246,7 +7270,7 @@
         <v>46</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>87</v>
@@ -7255,31 +7279,31 @@
         <v>63</v>
       </c>
       <c r="H30" s="93">
-        <v>117.21875</v>
+        <v>116.46875</v>
       </c>
       <c r="I30" s="93">
-        <v>117.1875</v>
+        <v>116.4375</v>
       </c>
       <c r="J30" s="93">
-        <v>117.21875</v>
+        <v>116.46875</v>
       </c>
       <c r="K30" s="93">
-        <v>117.203125</v>
+        <v>116.453125</v>
       </c>
       <c r="L30" s="93">
-        <v>117.28125</v>
+        <v>117.0625</v>
       </c>
       <c r="M30" s="93">
-        <v>117.21875</v>
+        <v>116.78125</v>
       </c>
       <c r="N30" s="93">
-        <v>117.5</v>
+        <v>116.875</v>
       </c>
       <c r="O30" s="93">
-        <v>116.6875</v>
+        <v>116.21875</v>
       </c>
       <c r="P30" s="93">
-        <v>159392</v>
+        <v>122848</v>
       </c>
       <c r="Q30" s="93"/>
       <c r="R30" s="93"/>
@@ -7287,15 +7311,15 @@
       <c r="T30" s="93"/>
       <c r="U30" s="93"/>
       <c r="V30" s="92">
-        <v>46085.623020833336</v>
+        <v>46086.543333333335</v>
       </c>
       <c r="W30" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="31" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A31" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B31" s="1">
         <v>815824229</v>
@@ -7307,7 +7331,7 @@
         <v>72</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>87</v>
@@ -7316,31 +7340,31 @@
         <v>63</v>
       </c>
       <c r="H31" s="93">
-        <v>112.984375</v>
+        <v>112.546875</v>
       </c>
       <c r="I31" s="93">
-        <v>112.96875</v>
+        <v>112.53125</v>
       </c>
       <c r="J31" s="93">
-        <v>112.984375</v>
+        <v>112.546875</v>
       </c>
       <c r="K31" s="93">
-        <v>112.9765625</v>
+        <v>112.5390625</v>
       </c>
       <c r="L31" s="93">
-        <v>113.015625</v>
+        <v>112.8125</v>
       </c>
       <c r="M31" s="93">
-        <v>113</v>
+        <v>112.703125</v>
       </c>
       <c r="N31" s="93">
-        <v>113.09375</v>
+        <v>112.75</v>
       </c>
       <c r="O31" s="93">
-        <v>112.75</v>
+        <v>112.484375</v>
       </c>
       <c r="P31" s="93">
-        <v>930333</v>
+        <v>587278</v>
       </c>
       <c r="Q31" s="93"/>
       <c r="R31" s="93"/>
@@ -7348,15 +7372,15 @@
       <c r="T31" s="93"/>
       <c r="U31" s="93"/>
       <c r="V31" s="92">
-        <v>46085.623020833336</v>
+        <v>46086.543333333335</v>
       </c>
       <c r="W31" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="32" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A32" s="1" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B32" s="1">
         <v>813041669</v>
@@ -7368,7 +7392,7 @@
         <v>74</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>85</v>
@@ -7377,31 +7401,31 @@
         <v>60</v>
       </c>
       <c r="H32" s="93">
-        <v>128.07</v>
+        <v>127.61</v>
       </c>
       <c r="I32" s="93">
-        <v>128.07</v>
+        <v>127.61</v>
       </c>
       <c r="J32" s="93">
-        <v>128.08000000000001</v>
+        <v>127.62</v>
       </c>
       <c r="K32" s="93">
-        <v>128.07499999999999</v>
+        <v>127.61500000000001</v>
       </c>
       <c r="L32" s="93">
-        <v>127.91</v>
+        <v>128.24</v>
       </c>
       <c r="M32" s="93">
-        <v>128.15</v>
+        <v>128</v>
       </c>
       <c r="N32" s="93">
-        <v>128.28</v>
+        <v>128.03</v>
       </c>
       <c r="O32" s="93">
-        <v>127.78</v>
+        <v>127.57</v>
       </c>
       <c r="P32" s="93">
-        <v>449788</v>
+        <v>766781</v>
       </c>
       <c r="Q32" s="93"/>
       <c r="R32" s="93"/>
@@ -7409,15 +7433,15 @@
       <c r="T32" s="93"/>
       <c r="U32" s="93"/>
       <c r="V32" s="92">
-        <v>46085.623020833336</v>
+        <v>46086.543333333335</v>
       </c>
       <c r="W32" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="33" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A33" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B33" s="1">
         <v>813041681</v>
@@ -7429,7 +7453,7 @@
         <v>76</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>85</v>
@@ -7438,31 +7462,31 @@
         <v>60</v>
       </c>
       <c r="H33" s="93">
-        <v>111.4</v>
+        <v>111.06</v>
       </c>
       <c r="I33" s="93">
-        <v>111.4</v>
+        <v>111.06</v>
       </c>
       <c r="J33" s="93">
+        <v>111.08</v>
+      </c>
+      <c r="K33" s="93">
+        <v>111.07</v>
+      </c>
+      <c r="L33" s="93">
+        <v>111.76</v>
+      </c>
+      <c r="M33" s="93">
         <v>111.42</v>
       </c>
-      <c r="K33" s="93">
-        <v>111.41</v>
-      </c>
-      <c r="L33" s="93">
-        <v>111.6</v>
-      </c>
-      <c r="M33" s="93">
-        <v>112.1</v>
-      </c>
       <c r="N33" s="93">
-        <v>112.1</v>
+        <v>111.58</v>
       </c>
       <c r="O33" s="93">
-        <v>111.16</v>
+        <v>110.54</v>
       </c>
       <c r="P33" s="93">
-        <v>60703</v>
+        <v>95740</v>
       </c>
       <c r="Q33" s="93"/>
       <c r="R33" s="93"/>
@@ -7470,15 +7494,15 @@
       <c r="T33" s="93"/>
       <c r="U33" s="93"/>
       <c r="V33" s="92">
-        <v>46085.623020833336</v>
+        <v>46086.543333333335</v>
       </c>
       <c r="W33" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="34" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A34" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B34" s="1">
         <v>813041663</v>
@@ -7490,7 +7514,7 @@
         <v>47</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>85</v>
@@ -7499,31 +7523,31 @@
         <v>60</v>
       </c>
       <c r="H34" s="93">
-        <v>120.44</v>
+        <v>119.94</v>
       </c>
       <c r="I34" s="93">
-        <v>120.43</v>
+        <v>119.93</v>
       </c>
       <c r="J34" s="93">
-        <v>120.44</v>
+        <v>119.94</v>
       </c>
       <c r="K34" s="93">
-        <v>120.435</v>
+        <v>119.935</v>
       </c>
       <c r="L34" s="93">
-        <v>119.96</v>
+        <v>120.61</v>
       </c>
       <c r="M34" s="93">
+        <v>120.26</v>
+      </c>
+      <c r="N34" s="93">
+        <v>120.61</v>
+      </c>
+      <c r="O34" s="93">
         <v>119.9</v>
       </c>
-      <c r="N34" s="93">
-        <v>120.67</v>
-      </c>
-      <c r="O34" s="93">
-        <v>119.6</v>
-      </c>
       <c r="P34" s="93">
-        <v>199359</v>
+        <v>273348</v>
       </c>
       <c r="Q34" s="93"/>
       <c r="R34" s="93"/>
@@ -7531,58 +7555,58 @@
       <c r="T34" s="93"/>
       <c r="U34" s="93"/>
       <c r="V34" s="92">
-        <v>46085.623020833336</v>
+        <v>46086.543333333335</v>
       </c>
       <c r="W34" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="35" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A35" s="1" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B35" s="1">
         <v>479624278</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D35" s="1" t="s">
         <v>44</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="G35" s="1" t="s">
         <v>63</v>
       </c>
       <c r="H35" s="93">
-        <v>71506.25</v>
+        <v>72839.25</v>
       </c>
       <c r="I35" s="93">
-        <v>71506</v>
+        <v>72839.25</v>
       </c>
       <c r="J35" s="93">
-        <v>71506.25</v>
+        <v>72839.5</v>
       </c>
       <c r="K35" s="93">
-        <v>71506.125</v>
+        <v>72839.375</v>
       </c>
       <c r="L35" s="93">
-        <v>68240.25</v>
+        <v>73084</v>
       </c>
       <c r="M35" s="93"/>
       <c r="N35" s="93">
-        <v>72013.25</v>
+        <v>74269.5</v>
       </c>
       <c r="O35" s="93">
-        <v>66150.25</v>
+        <v>67063</v>
       </c>
       <c r="P35" s="93">
-        <v>284.87729122000002</v>
+        <v>186.00945229999999</v>
       </c>
       <c r="Q35" s="93"/>
       <c r="R35" s="93"/>
@@ -7590,58 +7614,58 @@
       <c r="T35" s="93"/>
       <c r="U35" s="93"/>
       <c r="V35" s="92">
-        <v>46085.623020833336</v>
+        <v>46086.543333333335</v>
       </c>
       <c r="W35" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="36" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A36" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B36" s="1">
         <v>495759171</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D36" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="G36" s="1" t="s">
         <v>63</v>
       </c>
       <c r="H36" s="93">
-        <v>2065.5</v>
+        <v>2134.5500000000002</v>
       </c>
       <c r="I36" s="93">
-        <v>2065.4499999999998</v>
+        <v>2134.9</v>
       </c>
       <c r="J36" s="93">
-        <v>2065.5</v>
+        <v>2134.9499999999998</v>
       </c>
       <c r="K36" s="93">
-        <v>2065.4749999999999</v>
+        <v>2134.9250000000002</v>
       </c>
       <c r="L36" s="93">
-        <v>1976.65</v>
+        <v>2151.6</v>
       </c>
       <c r="M36" s="93"/>
       <c r="N36" s="93">
-        <v>2090.5</v>
+        <v>2198.1999999999998</v>
       </c>
       <c r="O36" s="93">
-        <v>1929.75</v>
+        <v>1945.25</v>
       </c>
       <c r="P36" s="93">
-        <v>1735.4761382900001</v>
+        <v>1219.64086456</v>
       </c>
       <c r="Q36" s="93"/>
       <c r="R36" s="93"/>
@@ -7649,10 +7673,10 @@
       <c r="T36" s="93"/>
       <c r="U36" s="93"/>
       <c r="V36" s="92">
-        <v>46085.623020833336</v>
+        <v>46086.543333333335</v>
       </c>
       <c r="W36" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="37" spans="1:23" x14ac:dyDescent="0.4">
@@ -7836,29 +7860,47 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1" s="86" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B1" s="86" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C1" s="86" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A2" s="87"/>
-      <c r="B2" s="84"/>
-      <c r="C2" s="84"/>
+      <c r="A2" s="87">
+        <v>46086.543078703704</v>
+      </c>
+      <c r="B2" s="84" t="s">
+        <v>314</v>
+      </c>
+      <c r="C2" s="84" t="s">
+        <v>315</v>
+      </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A3" s="87"/>
-      <c r="B3" s="84"/>
-      <c r="C3" s="84"/>
+      <c r="A3" s="87">
+        <v>46086.543090277781</v>
+      </c>
+      <c r="B3" s="84" t="s">
+        <v>314</v>
+      </c>
+      <c r="C3" s="84" t="s">
+        <v>316</v>
+      </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A4" s="87"/>
-      <c r="B4" s="84"/>
-      <c r="C4" s="84"/>
+      <c r="A4" s="87">
+        <v>46086.54310185185</v>
+      </c>
+      <c r="B4" s="84" t="s">
+        <v>314</v>
+      </c>
+      <c r="C4" s="84" t="s">
+        <v>317</v>
+      </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A5" s="85"/>
@@ -7992,7 +8034,7 @@
     <row r="2" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B2" s="56"/>
       <c r="C2" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>51</v>
@@ -8004,15 +8046,15 @@
         <v>52</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B3" s="17" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C3" s="17"/>
       <c r="D3" s="10"/>
@@ -8025,7 +8067,7 @@
     </row>
     <row r="4" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B4" s="17" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C4" s="17"/>
       <c r="D4" s="10"/>
@@ -8039,7 +8081,7 @@
     </row>
     <row r="5" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B5" s="17" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C5" s="17"/>
       <c r="D5" s="10"/>
@@ -8053,7 +8095,7 @@
     </row>
     <row r="6" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B6" s="17" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C6" s="17"/>
       <c r="D6" s="10"/>
@@ -8067,7 +8109,7 @@
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B7" s="17" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C7" s="17"/>
       <c r="D7" s="10"/>
@@ -8081,7 +8123,7 @@
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B8" s="17" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C8" s="17"/>
       <c r="D8" s="10"/>
@@ -8092,7 +8134,7 @@
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B9" s="17" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C9" s="62"/>
       <c r="D9" s="27"/>
@@ -8103,7 +8145,7 @@
     </row>
     <row r="10" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B10" s="17" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C10" s="62"/>
       <c r="D10" s="27"/>
@@ -8114,7 +8156,7 @@
     </row>
     <row r="11" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B11" s="17" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C11" s="62"/>
       <c r="D11" s="27"/>
@@ -8125,7 +8167,7 @@
     </row>
     <row r="12" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B12" s="52" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C12" s="58"/>
       <c r="D12" s="54"/>
@@ -8136,7 +8178,7 @@
     </row>
     <row r="13" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B13" s="17" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C13" s="17"/>
       <c r="D13" s="10"/>
@@ -8201,46 +8243,46 @@
   <sheetData>
     <row r="2" spans="2:18" x14ac:dyDescent="0.4">
       <c r="B2" s="38" t="s">
+        <v>170</v>
+      </c>
+      <c r="C2" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="D2" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="E2" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="F2" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="E2" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="F2" s="4" t="s">
+      <c r="G2" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="H2" s="4" t="s">
         <v>174</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>175</v>
       </c>
       <c r="I2" s="4" t="s">
         <v>55</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="K2" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="M2" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="N2" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="O2" s="4" t="s">
         <v>176</v>
-      </c>
-      <c r="L2" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="M2" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="N2" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="O2" s="4" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="3" spans="2:18" x14ac:dyDescent="0.4">
@@ -8330,11 +8372,11 @@
       <c r="H5" s="67"/>
       <c r="I5" s="70">
         <f>Blotter!C$4-SUM(NAV!I$4:I4)</f>
-        <v>-500.36685890301305</v>
+        <v>638.93581138100001</v>
       </c>
       <c r="J5" s="70">
         <f t="shared" si="2"/>
-        <v>999499.63314109703</v>
+        <v>1000638.935811381</v>
       </c>
       <c r="K5" s="70">
         <f t="shared" si="3"/>
@@ -8342,19 +8384,19 @@
       </c>
       <c r="L5" s="71">
         <f t="shared" si="4"/>
-        <v>999.49963314109698</v>
+        <v>1000.638935811381</v>
       </c>
       <c r="M5" s="72">
         <f t="shared" si="5"/>
-        <v>-5.0036685890297861E-4</v>
+        <v>6.3893581138096955E-4</v>
       </c>
       <c r="N5" s="73">
         <f t="shared" ref="N5" si="6">L5/L4-1</f>
-        <v>-5.0036685890297861E-4</v>
+        <v>6.3893581138096955E-4</v>
       </c>
       <c r="O5" s="75">
         <f>STDEVP(N$4:N5)*SQRT(12)</f>
-        <v>8.6666082204360647E-4</v>
+        <v>1.1066692880870841E-3</v>
       </c>
     </row>
     <row r="6" spans="2:18" ht="14.25" x14ac:dyDescent="0.4">
@@ -8636,31 +8678,31 @@
         <v>7</v>
       </c>
       <c r="H2" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="I2" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="J2" s="8" t="s">
         <v>162</v>
       </c>
-      <c r="I2" s="8" t="s">
+      <c r="K2" s="8" t="s">
         <v>166</v>
       </c>
-      <c r="J2" s="8" t="s">
+      <c r="L2" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="M2" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="K2" s="8" t="s">
-        <v>167</v>
-      </c>
-      <c r="L2" s="8" t="s">
+      <c r="N2" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="O2" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="P2" s="4" t="s">
         <v>168</v>
-      </c>
-      <c r="M2" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="N2" s="8" t="s">
-        <v>166</v>
-      </c>
-      <c r="O2" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="P2" s="4" t="s">
-        <v>169</v>
       </c>
       <c r="Q2" s="4" t="s">
         <v>56</v>
@@ -8678,20 +8720,20 @@
         <v>2</v>
       </c>
       <c r="W2" s="38" t="s">
+        <v>131</v>
+      </c>
+      <c r="X2" s="38" t="s">
         <v>132</v>
-      </c>
-      <c r="X2" s="38" t="s">
-        <v>133</v>
       </c>
       <c r="Y2" s="12"/>
       <c r="Z2" s="38" t="s">
         <v>2</v>
       </c>
       <c r="AA2" s="38" t="s">
+        <v>131</v>
+      </c>
+      <c r="AB2" s="38" t="s">
         <v>132</v>
-      </c>
-      <c r="AB2" s="38" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="3" spans="2:28" x14ac:dyDescent="0.4">
@@ -8743,7 +8785,7 @@
       </c>
       <c r="D4" s="6">
         <f t="array" ref="D4">SUM((Blotter!C$19:C$1013=C4)*(Blotter!N$19:N$1013)*1)</f>
-        <v>-500.36685890301305</v>
+        <v>638.93581138100001</v>
       </c>
       <c r="E4" s="6">
         <f t="array" ref="E4">SUM((Blotter!B$19:C$1013=C4)*(Blotter!R$19:R$1013)*1)</f>
@@ -8751,32 +8793,32 @@
       </c>
       <c r="F4" s="30">
         <f t="shared" ref="F4" si="0">IF(ISNUMBER(D4/E4),D4/E4,0)</f>
-        <v>-4.7653986562191719E-2</v>
+        <v>6.0851029655333337E-2</v>
       </c>
       <c r="G4" s="36" t="str">
         <f t="array" ref="G4">IF(SUM((Blotter!C$19:C$1013=PLB!C4)*(Blotter!M$19:M$1013))=0,"C","O")</f>
-        <v>O</v>
+        <v>C</v>
       </c>
       <c r="H4" s="16">
         <f>J3+D4</f>
-        <v>999499.63314109703</v>
+        <v>1000638.935811381</v>
       </c>
       <c r="I4" s="16"/>
       <c r="J4" s="16">
         <f>H4+I4</f>
-        <v>999499.63314109703</v>
+        <v>1000638.935811381</v>
       </c>
       <c r="K4" s="3">
         <f>H4/J3-1</f>
-        <v>-5.0036685890297861E-4</v>
+        <v>6.3893581138096955E-4</v>
       </c>
       <c r="L4" s="3">
         <f>(1+K4)*(1+L3)-1</f>
-        <v>-5.0036685890297861E-4</v>
+        <v>6.3893581138096955E-4</v>
       </c>
       <c r="M4" s="6">
         <f>O3-IF(G4="O",O3*1%,-D4)</f>
-        <v>990000</v>
+        <v>1000638.935811381</v>
       </c>
       <c r="N4" s="16">
         <f>I4</f>
@@ -8784,15 +8826,15 @@
       </c>
       <c r="O4" s="6">
         <f>M4+N4</f>
-        <v>990000</v>
+        <v>1000638.935811381</v>
       </c>
       <c r="P4" s="3">
         <f>M4/O3-1</f>
-        <v>-1.0000000000000009E-2</v>
+        <v>6.3893581138096955E-4</v>
       </c>
       <c r="Q4" s="3">
         <f>(1+P4)*(1+Q3)-1</f>
-        <v>-1.0000000000000009E-2</v>
+        <v>6.3893581138096955E-4</v>
       </c>
       <c r="R4" s="3">
         <f>(1-1%)*(1+R3)-1</f>
@@ -8807,7 +8849,7 @@
         <v>1</v>
       </c>
       <c r="V4" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="5" spans="2:28" x14ac:dyDescent="0.4">
@@ -10070,22 +10112,22 @@
         <v>16</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H2" s="4" t="s">
         <v>18</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="J2" s="4" t="s">
         <v>95</v>
       </c>
       <c r="K2" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="L2" s="4" t="s">
         <v>190</v>
-      </c>
-      <c r="L2" s="4" t="s">
-        <v>191</v>
       </c>
       <c r="N2" s="4" t="s">
         <v>19</v>
@@ -11393,7 +11435,7 @@
     </row>
     <row r="38" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B38" s="17" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C38" s="18">
         <v>100</v>
@@ -11427,7 +11469,7 @@
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B39" s="17" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C39" s="18">
         <v>100</v>
@@ -11461,7 +11503,7 @@
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B40" s="17" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C40" s="18">
         <v>1</v>
@@ -11495,7 +11537,7 @@
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B41" s="17" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C41" s="18">
         <v>1</v>
@@ -11537,7 +11579,7 @@
     </row>
     <row r="42" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B42" s="17" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C42" s="18">
         <v>1</v>
@@ -11571,7 +11613,7 @@
     </row>
     <row r="43" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B43" s="9" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C43" s="18">
         <v>1</v>
@@ -11722,19 +11764,19 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>63</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>200</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>201</v>
       </c>
       <c r="H2" s="1">
         <v>1</v>
@@ -11746,10 +11788,10 @@
         <v>91</v>
       </c>
       <c r="N2" s="1">
-        <v>6.1104121999999998</v>
+        <v>50</v>
       </c>
       <c r="O2" s="1">
-        <v>1983</v>
+        <v>1986.6</v>
       </c>
       <c r="P2" s="1">
         <v>12116.947392599999</v>
@@ -11770,18 +11812,18 @@
       </c>
       <c r="V2" s="42">
         <f>N2</f>
-        <v>6.1104121999999998</v>
+        <v>50</v>
       </c>
       <c r="W2" s="42">
         <f>O2</f>
-        <v>1983</v>
+        <v>1986.6</v>
       </c>
       <c r="X2" s="42">
         <f>Q2</f>
         <v>-21.810505307</v>
       </c>
       <c r="Z2" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="AC2" s="44"/>
       <c r="AD2" s="45"/>
@@ -11789,40 +11831,40 @@
     </row>
     <row r="3" spans="1:31" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>63</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>200</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>201</v>
       </c>
       <c r="H3" s="1">
         <v>1</v>
       </c>
       <c r="L3" s="44">
-        <v>46084</v>
+        <v>46087</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>91</v>
+        <v>319</v>
       </c>
       <c r="N3" s="1">
-        <v>5.8970321700000001</v>
+        <v>-50</v>
       </c>
       <c r="O3" s="1">
-        <v>1983.1</v>
+        <v>2000</v>
       </c>
       <c r="P3" s="1">
-        <v>11694.404496327001</v>
+        <v>-6000</v>
       </c>
       <c r="Q3" s="1">
-        <v>-21.049928092999998</v>
+        <v>-9.2536833119999997</v>
       </c>
       <c r="R3" s="1" t="s">
         <v>63</v>
@@ -11837,1096 +11879,835 @@
       </c>
       <c r="V3" s="42">
         <f t="shared" ref="V3:V17" si="1">N3</f>
-        <v>5.8970321700000001</v>
+        <v>-50</v>
       </c>
       <c r="W3" s="42">
         <f t="shared" ref="W3:W17" si="2">O3</f>
-        <v>1983.1</v>
+        <v>2000</v>
       </c>
       <c r="X3" s="42">
         <f t="shared" ref="X3:X17" si="3">Q3</f>
-        <v>-21.049928092999998</v>
+        <v>-9.2536833119999997</v>
       </c>
       <c r="AC3" s="44"/>
       <c r="AD3" s="45"/>
       <c r="AE3" s="41"/>
     </row>
     <row r="4" spans="1:31" x14ac:dyDescent="0.4">
-      <c r="A4" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="H4" s="1">
-        <v>1</v>
-      </c>
-      <c r="L4" s="44">
-        <v>46084</v>
-      </c>
-      <c r="M4" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="N4" s="1">
-        <v>3.9942700000000003E-3</v>
-      </c>
-      <c r="O4" s="1">
-        <v>1983.1</v>
-      </c>
-      <c r="P4" s="1">
-        <v>7.9210368369999999</v>
-      </c>
-      <c r="Q4" s="1">
-        <v>-1.4257865999999999E-2</v>
-      </c>
-      <c r="R4" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="T4" s="43">
+      <c r="T4" s="43" t="str">
         <f>IF(ISNUMBER(VLOOKUP(U4,Blotter!B:C,2,0)),VLOOKUP(U4,Blotter!B:C,2,0),"")</f>
-        <v>1</v>
-      </c>
-      <c r="U4" s="42" t="str">
+        <v/>
+      </c>
+      <c r="U4" s="42">
         <f t="shared" si="0"/>
-        <v>ETH.USD-PAXOS</v>
+        <v>0</v>
       </c>
       <c r="V4" s="42">
         <f t="shared" si="1"/>
-        <v>3.9942700000000003E-3</v>
+        <v>0</v>
       </c>
       <c r="W4" s="42">
         <f t="shared" si="2"/>
-        <v>1983.1</v>
+        <v>0</v>
       </c>
       <c r="X4" s="42">
         <f t="shared" si="3"/>
-        <v>-1.4257865999999999E-2</v>
+        <v>0</v>
       </c>
       <c r="AC4" s="44"/>
       <c r="AD4" s="45"/>
       <c r="AE4" s="41"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.4">
-      <c r="A5" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="H5" s="1">
-        <v>1</v>
-      </c>
-      <c r="L5" s="44">
-        <v>46084</v>
-      </c>
-      <c r="M5" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="N5" s="1">
-        <v>0.54177474999999997</v>
-      </c>
-      <c r="O5" s="1">
-        <v>1983.1</v>
-      </c>
-      <c r="P5" s="1">
-        <v>1074.393506725</v>
-      </c>
-      <c r="Q5" s="1">
-        <v>-1.933908312</v>
-      </c>
-      <c r="R5" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="T5" s="43">
+      <c r="T5" s="43" t="str">
         <f>IF(ISNUMBER(VLOOKUP(U5,Blotter!B:C,2,0)),VLOOKUP(U5,Blotter!B:C,2,0),"")</f>
-        <v>1</v>
-      </c>
-      <c r="U5" s="42" t="str">
+        <v/>
+      </c>
+      <c r="U5" s="42">
         <f t="shared" si="0"/>
-        <v>ETH.USD-PAXOS</v>
+        <v>0</v>
       </c>
       <c r="V5" s="42">
         <f t="shared" si="1"/>
-        <v>0.54177474999999997</v>
+        <v>0</v>
       </c>
       <c r="W5" s="42">
         <f t="shared" si="2"/>
-        <v>1983.1</v>
+        <v>0</v>
       </c>
       <c r="X5" s="42">
         <f t="shared" si="3"/>
-        <v>-1.933908312</v>
+        <v>0</v>
       </c>
       <c r="AC5" s="44"/>
       <c r="AD5" s="45"/>
       <c r="AE5" s="41"/>
     </row>
     <row r="6" spans="1:31" x14ac:dyDescent="0.4">
-      <c r="A6" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="H6" s="1">
-        <v>1</v>
-      </c>
-      <c r="L6" s="44">
-        <v>46084</v>
-      </c>
-      <c r="M6" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="N6" s="1">
-        <v>1.5427200000000001</v>
-      </c>
-      <c r="O6" s="1">
-        <v>1983.1</v>
-      </c>
-      <c r="P6" s="1">
-        <v>3059.3680319999999</v>
-      </c>
-      <c r="Q6" s="1">
-        <v>-5.5068624579999996</v>
-      </c>
-      <c r="R6" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="T6" s="43">
+      <c r="T6" s="43" t="str">
         <f>IF(ISNUMBER(VLOOKUP(U6,Blotter!B:C,2,0)),VLOOKUP(U6,Blotter!B:C,2,0),"")</f>
-        <v>1</v>
-      </c>
-      <c r="U6" s="42" t="str">
+        <v/>
+      </c>
+      <c r="U6" s="42">
         <f t="shared" si="0"/>
-        <v>ETH.USD-PAXOS</v>
+        <v>0</v>
       </c>
       <c r="V6" s="42">
         <f t="shared" si="1"/>
-        <v>1.5427200000000001</v>
+        <v>0</v>
       </c>
       <c r="W6" s="42">
         <f t="shared" si="2"/>
-        <v>1983.1</v>
+        <v>0</v>
       </c>
       <c r="X6" s="42">
         <f t="shared" si="3"/>
-        <v>-5.5068624579999996</v>
+        <v>0</v>
       </c>
       <c r="AC6" s="44"/>
       <c r="AD6" s="45"/>
       <c r="AE6" s="41"/>
     </row>
     <row r="7" spans="1:31" x14ac:dyDescent="0.4">
-      <c r="A7" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="H7" s="1">
-        <v>1</v>
-      </c>
-      <c r="L7" s="44">
-        <v>46084</v>
-      </c>
-      <c r="M7" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="N7" s="1">
-        <v>0.22177047999999999</v>
-      </c>
-      <c r="O7" s="1">
-        <v>1983.1</v>
-      </c>
-      <c r="P7" s="1">
-        <v>439.79303888800001</v>
-      </c>
-      <c r="Q7" s="1">
-        <v>-0.79162747</v>
-      </c>
-      <c r="R7" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="T7" s="43">
+      <c r="T7" s="43" t="str">
         <f>IF(ISNUMBER(VLOOKUP(U7,Blotter!B:C,2,0)),VLOOKUP(U7,Blotter!B:C,2,0),"")</f>
-        <v>1</v>
-      </c>
-      <c r="U7" s="42" t="str">
+        <v/>
+      </c>
+      <c r="U7" s="42">
         <f t="shared" si="0"/>
-        <v>ETH.USD-PAXOS</v>
+        <v>0</v>
       </c>
       <c r="V7" s="42">
         <f t="shared" si="1"/>
-        <v>0.22177047999999999</v>
+        <v>0</v>
       </c>
       <c r="W7" s="42">
         <f t="shared" si="2"/>
-        <v>1983.1</v>
+        <v>0</v>
       </c>
       <c r="X7" s="42">
         <f t="shared" si="3"/>
-        <v>-0.79162747</v>
+        <v>0</v>
       </c>
       <c r="AC7" s="44"/>
       <c r="AD7" s="45"/>
       <c r="AE7" s="41"/>
     </row>
     <row r="8" spans="1:31" x14ac:dyDescent="0.4">
-      <c r="A8" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="H8" s="1">
-        <v>1</v>
-      </c>
-      <c r="L8" s="44">
-        <v>46084</v>
-      </c>
-      <c r="M8" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="N8" s="1">
-        <v>0.20808973</v>
-      </c>
-      <c r="O8" s="1">
-        <v>1983.1</v>
-      </c>
-      <c r="P8" s="1">
-        <v>412.66274356299999</v>
-      </c>
-      <c r="Q8" s="1">
-        <v>-0.74279293800000001</v>
-      </c>
-      <c r="R8" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="T8" s="43">
+      <c r="T8" s="43" t="str">
         <f>IF(ISNUMBER(VLOOKUP(U8,Blotter!B:C,2,0)),VLOOKUP(U8,Blotter!B:C,2,0),"")</f>
-        <v>1</v>
-      </c>
-      <c r="U8" s="42" t="str">
+        <v/>
+      </c>
+      <c r="U8" s="42">
         <f t="shared" si="0"/>
-        <v>ETH.USD-PAXOS</v>
+        <v>0</v>
       </c>
       <c r="V8" s="42">
         <f t="shared" si="1"/>
-        <v>0.20808973</v>
+        <v>0</v>
       </c>
       <c r="W8" s="42">
         <f t="shared" si="2"/>
-        <v>1983.1</v>
+        <v>0</v>
       </c>
       <c r="X8" s="42">
         <f t="shared" si="3"/>
-        <v>-0.74279293800000001</v>
+        <v>0</v>
       </c>
       <c r="AC8" s="44"/>
       <c r="AD8" s="45"/>
       <c r="AE8" s="41"/>
     </row>
     <row r="9" spans="1:31" x14ac:dyDescent="0.4">
-      <c r="A9" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="H9" s="1">
-        <v>1</v>
-      </c>
-      <c r="L9" s="44">
-        <v>46084</v>
-      </c>
-      <c r="M9" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="N9" s="1">
-        <v>1.6103536000000001</v>
-      </c>
-      <c r="O9" s="1">
-        <v>1983.1</v>
-      </c>
-      <c r="P9" s="1">
-        <v>3193.4922241600002</v>
-      </c>
-      <c r="Q9" s="1">
-        <v>-5.7482860029999996</v>
-      </c>
-      <c r="R9" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="T9" s="43">
+      <c r="T9" s="43" t="str">
         <f>IF(ISNUMBER(VLOOKUP(U9,Blotter!B:C,2,0)),VLOOKUP(U9,Blotter!B:C,2,0),"")</f>
-        <v>1</v>
-      </c>
-      <c r="U9" s="42" t="str">
+        <v/>
+      </c>
+      <c r="U9" s="42">
         <f t="shared" si="0"/>
-        <v>ETH.USD-PAXOS</v>
+        <v>0</v>
       </c>
       <c r="V9" s="42">
         <f t="shared" si="1"/>
-        <v>1.6103536000000001</v>
+        <v>0</v>
       </c>
       <c r="W9" s="42">
         <f t="shared" si="2"/>
-        <v>1983.1</v>
+        <v>0</v>
       </c>
       <c r="X9" s="42">
         <f t="shared" si="3"/>
-        <v>-5.7482860029999996</v>
+        <v>0</v>
       </c>
       <c r="AC9" s="44"/>
       <c r="AD9" s="45"/>
       <c r="AE9" s="41"/>
     </row>
     <row r="10" spans="1:31" x14ac:dyDescent="0.4">
-      <c r="A10" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="H10" s="1">
-        <v>1</v>
-      </c>
-      <c r="L10" s="44">
-        <v>46084</v>
-      </c>
-      <c r="M10" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="N10" s="1">
-        <v>0.21435478999999999</v>
-      </c>
-      <c r="O10" s="1">
-        <v>1983.1</v>
-      </c>
-      <c r="P10" s="1">
-        <v>425.08698404900002</v>
-      </c>
-      <c r="Q10" s="1">
-        <v>-0.76515657100000001</v>
-      </c>
-      <c r="R10" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="T10" s="43">
+      <c r="T10" s="43" t="str">
         <f>IF(ISNUMBER(VLOOKUP(U10,Blotter!B:C,2,0)),VLOOKUP(U10,Blotter!B:C,2,0),"")</f>
-        <v>1</v>
-      </c>
-      <c r="U10" s="42" t="str">
+        <v/>
+      </c>
+      <c r="U10" s="42">
         <f t="shared" si="0"/>
-        <v>ETH.USD-PAXOS</v>
+        <v>0</v>
       </c>
       <c r="V10" s="42">
         <f t="shared" si="1"/>
-        <v>0.21435478999999999</v>
+        <v>0</v>
       </c>
       <c r="W10" s="42">
         <f t="shared" si="2"/>
-        <v>1983.1</v>
+        <v>0</v>
       </c>
       <c r="X10" s="42">
         <f t="shared" si="3"/>
-        <v>-0.76515657100000001</v>
+        <v>0</v>
       </c>
       <c r="AC10" s="44"/>
       <c r="AD10" s="45"/>
       <c r="AE10" s="41"/>
     </row>
     <row r="11" spans="1:31" x14ac:dyDescent="0.4">
-      <c r="A11" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="H11" s="1">
-        <v>1</v>
-      </c>
-      <c r="L11" s="44">
-        <v>46084</v>
-      </c>
-      <c r="M11" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="N11" s="1">
-        <v>0.26617475000000002</v>
-      </c>
-      <c r="O11" s="1">
-        <v>1983.1</v>
-      </c>
-      <c r="P11" s="1">
-        <v>527.85114672500004</v>
-      </c>
-      <c r="Q11" s="1">
-        <v>-0.95013206400000005</v>
-      </c>
-      <c r="R11" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="T11" s="43">
+      <c r="T11" s="43" t="str">
         <f>IF(ISNUMBER(VLOOKUP(U11,Blotter!B:C,2,0)),VLOOKUP(U11,Blotter!B:C,2,0),"")</f>
-        <v>1</v>
-      </c>
-      <c r="U11" s="42" t="str">
+        <v/>
+      </c>
+      <c r="U11" s="42">
         <f t="shared" si="0"/>
-        <v>ETH.USD-PAXOS</v>
+        <v>0</v>
       </c>
       <c r="V11" s="42">
         <f t="shared" si="1"/>
-        <v>0.26617475000000002</v>
+        <v>0</v>
       </c>
       <c r="W11" s="42">
         <f t="shared" si="2"/>
-        <v>1983.1</v>
+        <v>0</v>
       </c>
       <c r="X11" s="42">
         <f t="shared" si="3"/>
-        <v>-0.95013206400000005</v>
+        <v>0</v>
       </c>
       <c r="AC11" s="44"/>
       <c r="AD11" s="45"/>
       <c r="AE11" s="41"/>
     </row>
     <row r="12" spans="1:31" x14ac:dyDescent="0.4">
-      <c r="A12" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="H12" s="1">
-        <v>1</v>
-      </c>
-      <c r="L12" s="44">
-        <v>46084</v>
-      </c>
-      <c r="M12" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="N12" s="1">
-        <v>6.1193113600000002</v>
-      </c>
-      <c r="O12" s="1">
-        <v>1983.1</v>
-      </c>
-      <c r="P12" s="1">
-        <v>12135.206358015999</v>
-      </c>
-      <c r="Q12" s="1">
-        <v>-21.843371443999999</v>
-      </c>
-      <c r="R12" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="T12" s="43">
+      <c r="T12" s="43" t="str">
         <f>IF(ISNUMBER(VLOOKUP(U12,Blotter!B:C,2,0)),VLOOKUP(U12,Blotter!B:C,2,0),"")</f>
-        <v>1</v>
-      </c>
-      <c r="U12" s="42" t="str">
+        <v/>
+      </c>
+      <c r="U12" s="42">
         <f t="shared" si="0"/>
-        <v>ETH.USD-PAXOS</v>
+        <v>0</v>
       </c>
       <c r="V12" s="42">
         <f t="shared" si="1"/>
-        <v>6.1193113600000002</v>
+        <v>0</v>
       </c>
       <c r="W12" s="42">
         <f t="shared" si="2"/>
-        <v>1983.1</v>
+        <v>0</v>
       </c>
       <c r="X12" s="42">
         <f t="shared" si="3"/>
-        <v>-21.843371443999999</v>
+        <v>0</v>
       </c>
       <c r="AC12" s="44"/>
       <c r="AD12" s="45"/>
       <c r="AE12" s="41"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.4">
-      <c r="A13" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="H13" s="1">
-        <v>1</v>
-      </c>
-      <c r="L13" s="44">
-        <v>46084</v>
-      </c>
-      <c r="M13" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="N13" s="1">
-        <v>6.1754577399999997</v>
-      </c>
-      <c r="O13" s="1">
-        <v>1983.1</v>
-      </c>
-      <c r="P13" s="1">
-        <v>12246.550244194001</v>
-      </c>
-      <c r="Q13" s="1">
-        <v>-22.043790439999999</v>
-      </c>
-      <c r="R13" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="T13" s="43">
+      <c r="T13" s="43" t="str">
         <f>IF(ISNUMBER(VLOOKUP(U13,Blotter!B:C,2,0)),VLOOKUP(U13,Blotter!B:C,2,0),"")</f>
-        <v>1</v>
-      </c>
-      <c r="U13" s="42" t="str">
+        <v/>
+      </c>
+      <c r="U13" s="42">
         <f t="shared" si="0"/>
-        <v>ETH.USD-PAXOS</v>
+        <v>0</v>
       </c>
       <c r="V13" s="42">
         <f t="shared" si="1"/>
-        <v>6.1754577399999997</v>
+        <v>0</v>
       </c>
       <c r="W13" s="42">
         <f t="shared" si="2"/>
-        <v>1983.1</v>
+        <v>0</v>
       </c>
       <c r="X13" s="42">
         <f t="shared" si="3"/>
-        <v>-22.043790439999999</v>
+        <v>0</v>
       </c>
       <c r="AC13" s="44"/>
       <c r="AD13" s="45"/>
       <c r="AE13" s="41"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.4">
-      <c r="A14" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="H14" s="1">
-        <v>1</v>
-      </c>
-      <c r="L14" s="44">
-        <v>46084</v>
-      </c>
-      <c r="M14" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="N14" s="1">
-        <v>6.1710219200000003</v>
-      </c>
-      <c r="O14" s="1">
-        <v>1983.1</v>
-      </c>
-      <c r="P14" s="1">
-        <v>12237.753569552</v>
-      </c>
-      <c r="Q14" s="1">
-        <v>-22.027956424999999</v>
-      </c>
-      <c r="R14" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="T14" s="43">
+      <c r="T14" s="43" t="str">
         <f>IF(ISNUMBER(VLOOKUP(U14,Blotter!B:C,2,0)),VLOOKUP(U14,Blotter!B:C,2,0),"")</f>
-        <v>1</v>
-      </c>
-      <c r="U14" s="42" t="str">
+        <v/>
+      </c>
+      <c r="U14" s="42">
         <f t="shared" si="0"/>
-        <v>ETH.USD-PAXOS</v>
+        <v>0</v>
       </c>
       <c r="V14" s="42">
         <f t="shared" si="1"/>
-        <v>6.1710219200000003</v>
+        <v>0</v>
       </c>
       <c r="W14" s="42">
         <f t="shared" si="2"/>
-        <v>1983.1</v>
+        <v>0</v>
       </c>
       <c r="X14" s="42">
         <f t="shared" si="3"/>
-        <v>-22.027956424999999</v>
+        <v>0</v>
       </c>
       <c r="AC14" s="44"/>
       <c r="AD14" s="45"/>
       <c r="AE14" s="41"/>
     </row>
     <row r="15" spans="1:31" x14ac:dyDescent="0.4">
-      <c r="A15" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="H15" s="1">
-        <v>1</v>
-      </c>
-      <c r="L15" s="44">
-        <v>46084</v>
-      </c>
-      <c r="M15" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="N15" s="1">
-        <v>6.1193113600000002</v>
-      </c>
-      <c r="O15" s="1">
-        <v>1983.1</v>
-      </c>
-      <c r="P15" s="1">
-        <v>12135.206358015999</v>
-      </c>
-      <c r="Q15" s="1">
-        <v>-21.843371443999999</v>
-      </c>
-      <c r="R15" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="T15" s="43">
+      <c r="T15" s="43" t="str">
         <f>IF(ISNUMBER(VLOOKUP(U15,Blotter!B:C,2,0)),VLOOKUP(U15,Blotter!B:C,2,0),"")</f>
-        <v>1</v>
-      </c>
-      <c r="U15" s="42" t="str">
+        <v/>
+      </c>
+      <c r="U15" s="42">
         <f t="shared" si="0"/>
-        <v>ETH.USD-PAXOS</v>
+        <v>0</v>
       </c>
       <c r="V15" s="42">
         <f t="shared" si="1"/>
-        <v>6.1193113600000002</v>
+        <v>0</v>
       </c>
       <c r="W15" s="42">
         <f t="shared" si="2"/>
-        <v>1983.1</v>
+        <v>0</v>
       </c>
       <c r="X15" s="42">
         <f t="shared" si="3"/>
-        <v>-21.843371443999999</v>
+        <v>0</v>
       </c>
       <c r="AC15" s="44"/>
       <c r="AD15" s="45"/>
       <c r="AE15" s="41"/>
     </row>
     <row r="16" spans="1:31" x14ac:dyDescent="0.4">
-      <c r="A16" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="H16" s="1">
-        <v>1</v>
-      </c>
-      <c r="L16" s="44">
-        <v>46084</v>
-      </c>
-      <c r="M16" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="N16" s="1">
-        <v>6.1193113600000002</v>
-      </c>
-      <c r="O16" s="1">
-        <v>1983.1</v>
-      </c>
-      <c r="P16" s="1">
-        <v>12135.206358015999</v>
-      </c>
-      <c r="Q16" s="1">
-        <v>-21.843371443999999</v>
-      </c>
-      <c r="R16" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="T16" s="43">
+      <c r="T16" s="43" t="str">
         <f>IF(ISNUMBER(VLOOKUP(U16,Blotter!B:C,2,0)),VLOOKUP(U16,Blotter!B:C,2,0),"")</f>
-        <v>1</v>
-      </c>
-      <c r="U16" s="42" t="str">
+        <v/>
+      </c>
+      <c r="U16" s="42">
         <f t="shared" si="0"/>
-        <v>ETH.USD-PAXOS</v>
+        <v>0</v>
       </c>
       <c r="V16" s="42">
         <f t="shared" si="1"/>
-        <v>6.1193113600000002</v>
+        <v>0</v>
       </c>
       <c r="W16" s="42">
         <f t="shared" si="2"/>
-        <v>1983.1</v>
+        <v>0</v>
       </c>
       <c r="X16" s="42">
         <f t="shared" si="3"/>
-        <v>-21.843371443999999</v>
+        <v>0</v>
       </c>
       <c r="AC16" s="44"/>
       <c r="AD16" s="45"/>
       <c r="AE16" s="41"/>
     </row>
-    <row r="17" spans="1:31" x14ac:dyDescent="0.4">
-      <c r="A17" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="H17" s="1">
-        <v>1</v>
-      </c>
-      <c r="L17" s="44">
-        <v>46084</v>
-      </c>
-      <c r="M17" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="N17" s="1">
-        <v>2.6789095199999999</v>
-      </c>
-      <c r="O17" s="1">
-        <v>1983.1</v>
-      </c>
-      <c r="P17" s="1">
-        <v>5312.5454691120003</v>
-      </c>
-      <c r="Q17" s="1">
-        <v>-9.5625818440000003</v>
-      </c>
-      <c r="R17" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="T17" s="43">
+    <row r="17" spans="20:31" x14ac:dyDescent="0.4">
+      <c r="T17" s="43" t="str">
         <f>IF(ISNUMBER(VLOOKUP(U17,Blotter!B:C,2,0)),VLOOKUP(U17,Blotter!B:C,2,0),"")</f>
-        <v>1</v>
-      </c>
-      <c r="U17" s="42" t="str">
+        <v/>
+      </c>
+      <c r="U17" s="42">
         <f t="shared" si="0"/>
-        <v>ETH.USD-PAXOS</v>
+        <v>0</v>
       </c>
       <c r="V17" s="42">
         <f t="shared" si="1"/>
-        <v>2.6789095199999999</v>
+        <v>0</v>
       </c>
       <c r="W17" s="42">
         <f t="shared" si="2"/>
-        <v>1983.1</v>
+        <v>0</v>
       </c>
       <c r="X17" s="42">
         <f t="shared" si="3"/>
-        <v>-9.5625818440000003</v>
+        <v>0</v>
       </c>
       <c r="AC17" s="44"/>
       <c r="AD17" s="45"/>
       <c r="AE17" s="41"/>
     </row>
-    <row r="18" spans="1:31" x14ac:dyDescent="0.4">
-      <c r="T18" s="43"/>
-      <c r="U18" s="42"/>
-      <c r="V18" s="42"/>
-      <c r="W18" s="42"/>
-      <c r="X18" s="42"/>
+    <row r="18" spans="20:31" x14ac:dyDescent="0.4">
+      <c r="T18" s="43" t="str">
+        <f>IF(ISNUMBER(VLOOKUP(U18,Blotter!B:C,2,0)),VLOOKUP(U18,Blotter!B:C,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="U18" s="42">
+        <f t="shared" ref="U18:U36" si="4">D18</f>
+        <v>0</v>
+      </c>
+      <c r="V18" s="42">
+        <f t="shared" ref="V18:V36" si="5">N18</f>
+        <v>0</v>
+      </c>
+      <c r="W18" s="42">
+        <f t="shared" ref="W18:W36" si="6">O18</f>
+        <v>0</v>
+      </c>
+      <c r="X18" s="42">
+        <f t="shared" ref="X18:X36" si="7">Q18</f>
+        <v>0</v>
+      </c>
       <c r="AC18" s="44"/>
       <c r="AD18" s="45"/>
       <c r="AE18" s="41"/>
     </row>
-    <row r="19" spans="1:31" x14ac:dyDescent="0.4">
-      <c r="T19" s="43"/>
-      <c r="U19" s="42"/>
-      <c r="V19" s="42"/>
-      <c r="W19" s="42"/>
-      <c r="X19" s="42"/>
+    <row r="19" spans="20:31" x14ac:dyDescent="0.4">
+      <c r="T19" s="43" t="str">
+        <f>IF(ISNUMBER(VLOOKUP(U19,Blotter!B:C,2,0)),VLOOKUP(U19,Blotter!B:C,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="U19" s="42">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V19" s="42">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W19" s="42">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="X19" s="42">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
       <c r="AC19" s="44"/>
       <c r="AD19" s="45"/>
       <c r="AE19" s="41"/>
     </row>
-    <row r="20" spans="1:31" x14ac:dyDescent="0.4">
-      <c r="T20" s="43"/>
-      <c r="U20" s="42"/>
-      <c r="V20" s="42"/>
-      <c r="W20" s="42"/>
-      <c r="X20" s="42"/>
+    <row r="20" spans="20:31" x14ac:dyDescent="0.4">
+      <c r="T20" s="43" t="str">
+        <f>IF(ISNUMBER(VLOOKUP(U20,Blotter!B:C,2,0)),VLOOKUP(U20,Blotter!B:C,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="U20" s="42">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V20" s="42">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W20" s="42">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="X20" s="42">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
       <c r="AC20" s="44"/>
       <c r="AD20" s="45"/>
       <c r="AE20" s="41"/>
     </row>
-    <row r="21" spans="1:31" x14ac:dyDescent="0.4">
-      <c r="T21" s="43"/>
-      <c r="U21" s="42"/>
-      <c r="V21" s="42"/>
-      <c r="W21" s="42"/>
-      <c r="X21" s="42"/>
+    <row r="21" spans="20:31" x14ac:dyDescent="0.4">
+      <c r="T21" s="43" t="str">
+        <f>IF(ISNUMBER(VLOOKUP(U21,Blotter!B:C,2,0)),VLOOKUP(U21,Blotter!B:C,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="U21" s="42">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V21" s="42">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W21" s="42">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="X21" s="42">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
       <c r="AC21" s="44"/>
       <c r="AD21" s="45"/>
       <c r="AE21" s="41"/>
     </row>
-    <row r="22" spans="1:31" x14ac:dyDescent="0.4">
-      <c r="T22" s="43"/>
-      <c r="U22" s="42"/>
-      <c r="V22" s="42"/>
-      <c r="W22" s="42"/>
-      <c r="X22" s="42"/>
+    <row r="22" spans="20:31" x14ac:dyDescent="0.4">
+      <c r="T22" s="43" t="str">
+        <f>IF(ISNUMBER(VLOOKUP(U22,Blotter!B:C,2,0)),VLOOKUP(U22,Blotter!B:C,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="U22" s="42">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V22" s="42">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W22" s="42">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="X22" s="42">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
       <c r="AC22" s="44"/>
       <c r="AD22" s="45"/>
       <c r="AE22" s="41"/>
     </row>
-    <row r="23" spans="1:31" x14ac:dyDescent="0.4">
-      <c r="T23" s="43"/>
-      <c r="U23" s="42"/>
-      <c r="V23" s="42"/>
-      <c r="W23" s="42"/>
-      <c r="X23" s="42"/>
+    <row r="23" spans="20:31" x14ac:dyDescent="0.4">
+      <c r="T23" s="43" t="str">
+        <f>IF(ISNUMBER(VLOOKUP(U23,Blotter!B:C,2,0)),VLOOKUP(U23,Blotter!B:C,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="U23" s="42">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V23" s="42">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W23" s="42">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="X23" s="42">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
       <c r="AC23" s="44"/>
       <c r="AD23" s="45"/>
       <c r="AE23" s="41"/>
     </row>
-    <row r="24" spans="1:31" x14ac:dyDescent="0.4">
-      <c r="T24" s="43"/>
-      <c r="U24" s="42"/>
-      <c r="V24" s="42"/>
-      <c r="W24" s="42"/>
-      <c r="X24" s="42"/>
+    <row r="24" spans="20:31" x14ac:dyDescent="0.4">
+      <c r="T24" s="43" t="str">
+        <f>IF(ISNUMBER(VLOOKUP(U24,Blotter!B:C,2,0)),VLOOKUP(U24,Blotter!B:C,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="U24" s="42">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V24" s="42">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W24" s="42">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="X24" s="42">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
       <c r="AC24" s="44"/>
       <c r="AD24" s="45"/>
       <c r="AE24" s="41"/>
     </row>
-    <row r="25" spans="1:31" x14ac:dyDescent="0.4">
-      <c r="T25" s="43"/>
-      <c r="U25" s="42"/>
-      <c r="V25" s="42"/>
-      <c r="W25" s="42"/>
-      <c r="X25" s="42"/>
+    <row r="25" spans="20:31" x14ac:dyDescent="0.4">
+      <c r="T25" s="43" t="str">
+        <f>IF(ISNUMBER(VLOOKUP(U25,Blotter!B:C,2,0)),VLOOKUP(U25,Blotter!B:C,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="U25" s="42">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V25" s="42">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W25" s="42">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="X25" s="42">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
       <c r="AC25" s="44"/>
       <c r="AD25" s="45"/>
       <c r="AE25" s="41"/>
     </row>
-    <row r="26" spans="1:31" x14ac:dyDescent="0.4">
-      <c r="T26" s="43"/>
-      <c r="U26" s="42"/>
-      <c r="V26" s="42"/>
-      <c r="W26" s="42"/>
-      <c r="X26" s="42"/>
+    <row r="26" spans="20:31" x14ac:dyDescent="0.4">
+      <c r="T26" s="43" t="str">
+        <f>IF(ISNUMBER(VLOOKUP(U26,Blotter!B:C,2,0)),VLOOKUP(U26,Blotter!B:C,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="U26" s="42">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V26" s="42">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W26" s="42">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="X26" s="42">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
       <c r="AC26" s="44"/>
       <c r="AD26" s="45"/>
       <c r="AE26" s="41"/>
     </row>
-    <row r="27" spans="1:31" x14ac:dyDescent="0.4">
-      <c r="T27" s="43"/>
-      <c r="U27" s="42"/>
-      <c r="V27" s="42"/>
-      <c r="W27" s="42"/>
-      <c r="X27" s="42"/>
+    <row r="27" spans="20:31" x14ac:dyDescent="0.4">
+      <c r="T27" s="43" t="str">
+        <f>IF(ISNUMBER(VLOOKUP(U27,Blotter!B:C,2,0)),VLOOKUP(U27,Blotter!B:C,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="U27" s="42">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V27" s="42">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W27" s="42">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="X27" s="42">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
       <c r="AC27" s="44"/>
       <c r="AD27" s="45"/>
       <c r="AE27" s="41"/>
     </row>
-    <row r="28" spans="1:31" x14ac:dyDescent="0.4">
-      <c r="T28" s="43"/>
-      <c r="U28" s="42"/>
-      <c r="V28" s="42"/>
-      <c r="W28" s="42"/>
-      <c r="X28" s="42"/>
+    <row r="28" spans="20:31" x14ac:dyDescent="0.4">
+      <c r="T28" s="43" t="str">
+        <f>IF(ISNUMBER(VLOOKUP(U28,Blotter!B:C,2,0)),VLOOKUP(U28,Blotter!B:C,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="U28" s="42">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V28" s="42">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W28" s="42">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="X28" s="42">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
       <c r="AC28" s="44"/>
       <c r="AD28" s="45"/>
       <c r="AE28" s="41"/>
     </row>
-    <row r="29" spans="1:31" x14ac:dyDescent="0.4">
-      <c r="T29" s="43"/>
-      <c r="U29" s="42"/>
-      <c r="V29" s="42"/>
-      <c r="W29" s="42"/>
-      <c r="X29" s="42"/>
+    <row r="29" spans="20:31" x14ac:dyDescent="0.4">
+      <c r="T29" s="43" t="str">
+        <f>IF(ISNUMBER(VLOOKUP(U29,Blotter!B:C,2,0)),VLOOKUP(U29,Blotter!B:C,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="U29" s="42">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V29" s="42">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W29" s="42">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="X29" s="42">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
       <c r="AC29" s="44"/>
       <c r="AD29" s="45"/>
       <c r="AE29" s="41"/>
     </row>
-    <row r="30" spans="1:31" x14ac:dyDescent="0.4">
-      <c r="T30" s="43"/>
-      <c r="U30" s="42"/>
-      <c r="V30" s="42"/>
-      <c r="W30" s="42"/>
-      <c r="X30" s="42"/>
+    <row r="30" spans="20:31" x14ac:dyDescent="0.4">
+      <c r="T30" s="43" t="str">
+        <f>IF(ISNUMBER(VLOOKUP(U30,Blotter!B:C,2,0)),VLOOKUP(U30,Blotter!B:C,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="U30" s="42">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V30" s="42">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W30" s="42">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="X30" s="42">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
       <c r="AC30" s="44"/>
       <c r="AD30" s="45"/>
       <c r="AE30" s="41"/>
     </row>
-    <row r="31" spans="1:31" x14ac:dyDescent="0.4">
-      <c r="T31" s="43"/>
-      <c r="U31" s="42"/>
-      <c r="V31" s="42"/>
-      <c r="W31" s="42"/>
-      <c r="X31" s="42"/>
+    <row r="31" spans="20:31" x14ac:dyDescent="0.4">
+      <c r="T31" s="43" t="str">
+        <f>IF(ISNUMBER(VLOOKUP(U31,Blotter!B:C,2,0)),VLOOKUP(U31,Blotter!B:C,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="U31" s="42">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V31" s="42">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W31" s="42">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="X31" s="42">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
       <c r="AC31" s="44"/>
       <c r="AD31" s="45"/>
       <c r="AE31" s="41"/>
     </row>
-    <row r="32" spans="1:31" x14ac:dyDescent="0.4">
-      <c r="T32" s="43"/>
-      <c r="U32" s="42"/>
-      <c r="V32" s="42"/>
-      <c r="W32" s="42"/>
-      <c r="X32" s="42"/>
+    <row r="32" spans="20:31" x14ac:dyDescent="0.4">
+      <c r="T32" s="43" t="str">
+        <f>IF(ISNUMBER(VLOOKUP(U32,Blotter!B:C,2,0)),VLOOKUP(U32,Blotter!B:C,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="U32" s="42">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V32" s="42">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W32" s="42">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="X32" s="42">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
       <c r="AC32" s="44"/>
       <c r="AD32" s="45"/>
       <c r="AE32" s="41"/>
     </row>
     <row r="33" spans="20:31" x14ac:dyDescent="0.4">
-      <c r="T33" s="43"/>
-      <c r="U33" s="42"/>
-      <c r="V33" s="42"/>
-      <c r="W33" s="42"/>
-      <c r="X33" s="42"/>
+      <c r="T33" s="43" t="str">
+        <f>IF(ISNUMBER(VLOOKUP(U33,Blotter!B:C,2,0)),VLOOKUP(U33,Blotter!B:C,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="U33" s="42">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V33" s="42">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W33" s="42">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="X33" s="42">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
       <c r="AC33" s="44"/>
       <c r="AD33" s="45"/>
       <c r="AE33" s="41"/>
     </row>
     <row r="34" spans="20:31" x14ac:dyDescent="0.4">
-      <c r="T34" s="43"/>
-      <c r="U34" s="42"/>
-      <c r="V34" s="42"/>
-      <c r="W34" s="42"/>
-      <c r="X34" s="42"/>
+      <c r="T34" s="43" t="str">
+        <f>IF(ISNUMBER(VLOOKUP(U34,Blotter!B:C,2,0)),VLOOKUP(U34,Blotter!B:C,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="U34" s="42">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V34" s="42">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W34" s="42">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="X34" s="42">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="35" spans="20:31" x14ac:dyDescent="0.4">
-      <c r="T35" s="43"/>
-      <c r="U35" s="42"/>
-      <c r="V35" s="42"/>
-      <c r="W35" s="42"/>
-      <c r="X35" s="42"/>
+      <c r="T35" s="43" t="str">
+        <f>IF(ISNUMBER(VLOOKUP(U35,Blotter!B:C,2,0)),VLOOKUP(U35,Blotter!B:C,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="U35" s="42">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V35" s="42">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W35" s="42">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="X35" s="42">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="36" spans="20:31" x14ac:dyDescent="0.4">
-      <c r="T36" s="43"/>
-      <c r="U36" s="42"/>
-      <c r="V36" s="42"/>
-      <c r="W36" s="42"/>
-      <c r="X36" s="42"/>
+      <c r="T36" s="43" t="str">
+        <f>IF(ISNUMBER(VLOOKUP(U36,Blotter!B:C,2,0)),VLOOKUP(U36,Blotter!B:C,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="U36" s="42">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V36" s="42">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W36" s="42">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="X36" s="42">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="37" spans="20:31" x14ac:dyDescent="0.4">
       <c r="T37" s="43"/>
@@ -20621,21 +20402,21 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A1" s="90" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B1" s="56"/>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A3" s="80" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B3" s="89" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A4" s="80" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B4" s="89">
         <v>7497</v>
@@ -20643,7 +20424,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A5" s="80" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B5" s="89">
         <v>11</v>
@@ -20651,7 +20432,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A6" s="80" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B6" s="89">
         <v>0.25</v>
@@ -20659,15 +20440,15 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A7" s="80" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B7" s="89" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A8" s="80" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B8" s="89">
         <v>3</v>
@@ -20675,22 +20456,22 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A10" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A11" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A12" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A13" s="1" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
   </sheetData>
@@ -20721,43 +20502,43 @@
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A1" s="82" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B1" s="82" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C1" s="82" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D1" s="82" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E1" s="82" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F1" s="82" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G1" s="82" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H1" s="82" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="I1" s="82" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="J1" s="82" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="K1" s="82" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="L1" s="82" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="M1" s="82" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.4">
@@ -20765,7 +20546,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="88" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C2" s="88" t="s">
         <v>62</v>
@@ -20780,7 +20561,7 @@
         <v>63</v>
       </c>
       <c r="G2" s="88" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H2" s="88"/>
       <c r="I2" s="88"/>
@@ -20794,7 +20575,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="88" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C3" s="88" t="s">
         <v>62</v>
@@ -20809,7 +20590,7 @@
         <v>63</v>
       </c>
       <c r="G3" s="88" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H3" s="88"/>
       <c r="I3" s="88"/>
@@ -20823,7 +20604,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="88" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C4" s="88" t="s">
         <v>62</v>
@@ -20838,7 +20619,7 @@
         <v>63</v>
       </c>
       <c r="G4" s="88" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H4" s="88"/>
       <c r="I4" s="88"/>
@@ -20852,13 +20633,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="88" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C5" s="88" t="s">
         <v>62</v>
       </c>
       <c r="D5" s="88" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E5" s="88" t="s">
         <v>85</v>
@@ -20867,13 +20648,13 @@
         <v>60</v>
       </c>
       <c r="G5" s="88" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H5" s="88"/>
       <c r="I5" s="88"/>
       <c r="J5" s="88"/>
       <c r="K5" s="88" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="L5" s="88"/>
       <c r="M5" s="88"/>
@@ -20883,7 +20664,7 @@
         <v>1</v>
       </c>
       <c r="B6" s="88" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C6" s="88" t="s">
         <v>62</v>
@@ -20898,13 +20679,13 @@
         <v>60</v>
       </c>
       <c r="G6" s="88" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H6" s="88"/>
       <c r="I6" s="88"/>
       <c r="J6" s="88"/>
       <c r="K6" s="88" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="L6" s="88"/>
       <c r="M6" s="88"/>
@@ -20914,7 +20695,7 @@
         <v>1</v>
       </c>
       <c r="B7" s="88" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C7" s="88" t="s">
         <v>62</v>
@@ -20929,7 +20710,7 @@
         <v>61</v>
       </c>
       <c r="G7" s="88" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H7" s="88"/>
       <c r="I7" s="88"/>
@@ -20947,7 +20728,7 @@
         <v>1</v>
       </c>
       <c r="B8" s="88" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C8" s="88" t="s">
         <v>62</v>
@@ -20978,7 +20759,7 @@
         <v>1</v>
       </c>
       <c r="B9" s="88" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C9" s="88" t="s">
         <v>62</v>
@@ -20993,7 +20774,7 @@
         <v>63</v>
       </c>
       <c r="G9" s="88" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H9" s="88"/>
       <c r="I9" s="88"/>
@@ -21009,7 +20790,7 @@
         <v>1</v>
       </c>
       <c r="B10" s="88" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C10" s="88" t="s">
         <v>62</v>
@@ -21024,7 +20805,7 @@
         <v>63</v>
       </c>
       <c r="G10" s="88" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H10" s="88"/>
       <c r="I10" s="88"/>
@@ -21040,7 +20821,7 @@
         <v>1</v>
       </c>
       <c r="B11" s="88" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C11" s="88" t="s">
         <v>62</v>
@@ -21055,7 +20836,7 @@
         <v>63</v>
       </c>
       <c r="G11" s="88" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H11" s="88"/>
       <c r="I11" s="88"/>
@@ -21071,7 +20852,7 @@
         <v>1</v>
       </c>
       <c r="B12" s="88" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C12" s="88" t="s">
         <v>62</v>
@@ -21086,7 +20867,7 @@
         <v>63</v>
       </c>
       <c r="G12" s="88" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H12" s="88"/>
       <c r="I12" s="88"/>
@@ -21102,7 +20883,7 @@
         <v>1</v>
       </c>
       <c r="B13" s="88" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C13" s="88" t="s">
         <v>62</v>
@@ -21117,7 +20898,7 @@
         <v>63</v>
       </c>
       <c r="G13" s="88" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H13" s="88"/>
       <c r="I13" s="88"/>
@@ -21133,7 +20914,7 @@
         <v>1</v>
       </c>
       <c r="B14" s="88" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C14" s="88" t="s">
         <v>62</v>
@@ -21164,7 +20945,7 @@
         <v>1</v>
       </c>
       <c r="B15" s="88" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C15" s="88" t="s">
         <v>62</v>
@@ -21195,7 +20976,7 @@
         <v>1</v>
       </c>
       <c r="B16" s="88" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C16" s="88" t="s">
         <v>62</v>
@@ -21226,7 +21007,7 @@
         <v>1</v>
       </c>
       <c r="B17" s="88" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C17" s="88" t="s">
         <v>62</v>
@@ -21257,7 +21038,7 @@
         <v>1</v>
       </c>
       <c r="B18" s="88" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C18" s="88" t="s">
         <v>62</v>
@@ -21288,7 +21069,7 @@
         <v>1</v>
       </c>
       <c r="B19" s="88" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C19" s="88" t="s">
         <v>62</v>
@@ -21319,7 +21100,7 @@
         <v>1</v>
       </c>
       <c r="B20" s="88" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C20" s="88" t="s">
         <v>62</v>
@@ -21412,7 +21193,7 @@
         <v>1</v>
       </c>
       <c r="B23" s="88" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C23" s="88" t="s">
         <v>62</v>
@@ -21443,7 +21224,7 @@
         <v>1</v>
       </c>
       <c r="B24" s="88" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C24" s="88" t="s">
         <v>62</v>
@@ -21458,7 +21239,7 @@
         <v>63</v>
       </c>
       <c r="G24" s="88" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H24" s="88"/>
       <c r="I24" s="88"/>
@@ -21474,7 +21255,7 @@
         <v>1</v>
       </c>
       <c r="B25" s="88" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C25" s="88" t="s">
         <v>62</v>
@@ -21489,7 +21270,7 @@
         <v>63</v>
       </c>
       <c r="G25" s="88" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H25" s="88"/>
       <c r="I25" s="88"/>
@@ -21505,7 +21286,7 @@
         <v>1</v>
       </c>
       <c r="B26" s="88" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C26" s="88" t="s">
         <v>62</v>
@@ -21520,7 +21301,7 @@
         <v>63</v>
       </c>
       <c r="G26" s="88" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H26" s="88"/>
       <c r="I26" s="88"/>
@@ -21536,7 +21317,7 @@
         <v>1</v>
       </c>
       <c r="B27" s="88" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C27" s="88" t="s">
         <v>62</v>
@@ -21551,7 +21332,7 @@
         <v>63</v>
       </c>
       <c r="G27" s="88" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H27" s="88"/>
       <c r="I27" s="88"/>
@@ -21567,7 +21348,7 @@
         <v>1</v>
       </c>
       <c r="B28" s="88" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C28" s="88" t="s">
         <v>62</v>
@@ -21582,7 +21363,7 @@
         <v>63</v>
       </c>
       <c r="G28" s="88" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H28" s="88"/>
       <c r="I28" s="88"/>
@@ -21598,7 +21379,7 @@
         <v>1</v>
       </c>
       <c r="B29" s="88" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C29" s="88" t="s">
         <v>62</v>
@@ -21613,7 +21394,7 @@
         <v>63</v>
       </c>
       <c r="G29" s="88" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H29" s="88"/>
       <c r="I29" s="88"/>
@@ -21629,7 +21410,7 @@
         <v>1</v>
       </c>
       <c r="B30" s="88" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C30" s="88" t="s">
         <v>62</v>
@@ -21644,7 +21425,7 @@
         <v>63</v>
       </c>
       <c r="G30" s="88" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H30" s="88"/>
       <c r="I30" s="88"/>
@@ -21660,7 +21441,7 @@
         <v>1</v>
       </c>
       <c r="B31" s="88" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C31" s="88" t="s">
         <v>62</v>
@@ -21675,7 +21456,7 @@
         <v>63</v>
       </c>
       <c r="G31" s="88" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H31" s="88"/>
       <c r="I31" s="88"/>
@@ -21691,13 +21472,13 @@
         <v>1</v>
       </c>
       <c r="B32" s="88" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C32" s="88" t="s">
         <v>62</v>
       </c>
       <c r="D32" s="88" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E32" s="88" t="s">
         <v>85</v>
@@ -21706,13 +21487,13 @@
         <v>60</v>
       </c>
       <c r="G32" s="88" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H32" s="88"/>
       <c r="I32" s="88"/>
       <c r="J32" s="88"/>
       <c r="K32" s="88" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="L32" s="88"/>
       <c r="M32" s="88"/>
@@ -21722,13 +21503,13 @@
         <v>1</v>
       </c>
       <c r="B33" s="88" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C33" s="88" t="s">
         <v>62</v>
       </c>
       <c r="D33" s="88" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="E33" s="88" t="s">
         <v>85</v>
@@ -21737,13 +21518,13 @@
         <v>60</v>
       </c>
       <c r="G33" s="88" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H33" s="88"/>
       <c r="I33" s="88"/>
       <c r="J33" s="88"/>
       <c r="K33" s="88" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="L33" s="88"/>
       <c r="M33" s="88"/>
@@ -21753,13 +21534,13 @@
         <v>1</v>
       </c>
       <c r="B34" s="88" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C34" s="88" t="s">
         <v>62</v>
       </c>
       <c r="D34" s="88" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E34" s="88" t="s">
         <v>85</v>
@@ -21768,13 +21549,13 @@
         <v>60</v>
       </c>
       <c r="G34" s="88" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H34" s="88"/>
       <c r="I34" s="88"/>
       <c r="J34" s="88"/>
       <c r="K34" s="88" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="M34" s="88"/>
     </row>
@@ -21783,16 +21564,16 @@
         <v>1</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C35" s="88" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D35" s="88" t="s">
         <v>44</v>
       </c>
       <c r="E35" s="88" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F35" s="88" t="s">
         <v>63</v>
@@ -21805,16 +21586,16 @@
         <v>1</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C36" s="88" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D36" s="88" t="s">
         <v>45</v>
       </c>
       <c r="E36" s="88" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F36" s="88" t="s">
         <v>63</v>
@@ -21940,7 +21721,7 @@
     </row>
     <row r="55" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C55" s="31" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D55" s="31" t="s">
         <v>27</v>
@@ -21974,7 +21755,7 @@
     </row>
     <row r="57" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C57" s="31" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D57" s="31" t="s">
         <v>28</v>
@@ -21991,7 +21772,7 @@
     </row>
     <row r="58" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C58" s="31" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D58" s="31" t="s">
         <v>29</v>
@@ -22008,7 +21789,7 @@
     </row>
     <row r="59" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C59" s="31" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D59" s="31" t="s">
         <v>31</v>
@@ -22025,7 +21806,7 @@
     </row>
     <row r="60" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C60" s="31" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D60" s="31" t="s">
         <v>32</v>
@@ -22042,7 +21823,7 @@
     </row>
     <row r="61" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C61" s="31" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D61" s="31" t="s">
         <v>33</v>
@@ -22059,7 +21840,7 @@
     </row>
     <row r="62" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C62" s="31" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D62" s="31" t="s">
         <v>34</v>
@@ -22076,7 +21857,7 @@
     </row>
     <row r="63" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C63" s="31" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D63" s="31" t="s">
         <v>70</v>
@@ -22127,7 +21908,7 @@
     </row>
     <row r="66" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C66" s="31" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D66" s="31" t="s">
         <v>37</v>

--- a/1XW_TradeBlotter_Web.xlsx
+++ b/1XW_TradeBlotter_Web.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0a601c1c2ba3d9f4/Trading/The Strategy Project/1XW Website/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="146" documentId="13_ncr:1_{6F5069F1-F0E7-4440-AA6D-4AFA11BBED1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A834F952-FDCD-4925-A9A9-BF13E3D8F658}"/>
+  <xr:revisionPtr revIDLastSave="161" documentId="13_ncr:1_{6F5069F1-F0E7-4440-AA6D-4AFA11BBED1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ED251AEA-9BD5-42B6-BFF0-1E71639FD1C2}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="22695" windowHeight="14476" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="22695" windowHeight="14476" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Blotter" sheetId="3" r:id="rId1"/>
@@ -1320,7 +1320,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="94">
+  <cellXfs count="95">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1555,6 +1555,9 @@
     </xf>
     <xf numFmtId="22" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="43" fontId="3" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="2" builtinId="3"/>
@@ -2618,10 +2621,10 @@
                 <c:formatCode>d\-mmm\-yy</c:formatCode>
                 <c:ptCount val="52"/>
                 <c:pt idx="0">
-                  <c:v>46060</c:v>
+                  <c:v>46088</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>46067</c:v>
+                  <c:v>46095</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8737,7 +8740,9 @@
       </c>
     </row>
     <row r="3" spans="2:28" x14ac:dyDescent="0.4">
-      <c r="B3" s="39"/>
+      <c r="B3" s="40">
+        <v>46081</v>
+      </c>
       <c r="C3" s="5">
         <v>0</v>
       </c>
@@ -8756,7 +8761,9 @@
         <v>1000000</v>
       </c>
       <c r="K3" s="16"/>
-      <c r="L3" s="15"/>
+      <c r="L3" s="94">
+        <v>0</v>
+      </c>
       <c r="M3" s="15">
         <f>H3</f>
         <v>0</v>
@@ -8769,7 +8776,10 @@
         <v>1000000</v>
       </c>
       <c r="P3" s="15"/>
-      <c r="R3" s="3">
+      <c r="Q3" s="94">
+        <v>0</v>
+      </c>
+      <c r="R3" s="94">
         <v>0</v>
       </c>
       <c r="T3" s="39"/>
@@ -8777,7 +8787,7 @@
     </row>
     <row r="4" spans="2:28" x14ac:dyDescent="0.4">
       <c r="B4" s="40">
-        <v>46060</v>
+        <v>46088</v>
       </c>
       <c r="C4" s="5">
         <f>C3+1</f>
@@ -8842,7 +8852,7 @@
       </c>
       <c r="T4" s="40">
         <f>B4</f>
-        <v>46060</v>
+        <v>46088</v>
       </c>
       <c r="U4" s="5">
         <f>C4</f>
@@ -8855,7 +8865,7 @@
     <row r="5" spans="2:28" x14ac:dyDescent="0.4">
       <c r="B5" s="40">
         <f>B4+7</f>
-        <v>46067</v>
+        <v>46095</v>
       </c>
       <c r="C5" s="5">
         <f>C4+1</f>
@@ -8878,7 +8888,7 @@
       <c r="R5" s="3"/>
       <c r="T5" s="40">
         <f t="shared" ref="T5" si="1">B5</f>
-        <v>46067</v>
+        <v>46095</v>
       </c>
       <c r="U5" s="5">
         <f t="shared" ref="U5" si="2">C5</f>

--- a/1XW_TradeBlotter_Web.xlsx
+++ b/1XW_TradeBlotter_Web.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0a601c1c2ba3d9f4/Trading/The Strategy Project/1XW Website/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="161" documentId="13_ncr:1_{6F5069F1-F0E7-4440-AA6D-4AFA11BBED1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ED251AEA-9BD5-42B6-BFF0-1E71639FD1C2}"/>
+  <xr:revisionPtr revIDLastSave="193" documentId="13_ncr:1_{6F5069F1-F0E7-4440-AA6D-4AFA11BBED1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{30A6B0A4-2787-4DFA-BF4B-184701D21F10}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="22695" windowHeight="14476" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="22695" windowHeight="14476" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Blotter" sheetId="3" r:id="rId1"/>
@@ -116,7 +116,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="851" uniqueCount="320">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="871" uniqueCount="321">
   <si>
     <t>WEEK</t>
   </si>
@@ -1089,6 +1089,9 @@
   </si>
   <si>
     <t>SELL</t>
+  </si>
+  <si>
+    <t>Long CC</t>
   </si>
 </sst>
 </file>
@@ -1750,7 +1753,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>6.3893581138096955E-4</c:v>
+                  <c:v>-1.1787469392599004E-4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1904,7 +1907,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>6.3893581138096955E-4</c:v>
+                  <c:v>-1.1787469392599004E-4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2295,7 +2298,7 @@
                   <c:v>1000</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1000.638935811381</c:v>
+                  <c:v>999.88212530607404</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2566,6 +2569,9 @@
                 <c:pt idx="0">
                   <c:v>-1.0000000000000009E-2</c:v>
                 </c:pt>
+                <c:pt idx="1">
+                  <c:v>-1.9900000000000029E-2</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -2636,7 +2642,10 @@
                 <c:formatCode>0.00%</c:formatCode>
                 <c:ptCount val="52"/>
                 <c:pt idx="0">
-                  <c:v>6.3893581138096955E-4</c:v>
+                  <c:v>-1.0000000000000009E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-1.9900000000000029E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2693,7 +2702,10 @@
                 <c:formatCode>0.00%</c:formatCode>
                 <c:ptCount val="52"/>
                 <c:pt idx="0">
-                  <c:v>6.3893581138096955E-4</c:v>
+                  <c:v>-1.1787469392599004E-4</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-1.1787469392599004E-4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3343,7 +3355,7 @@
         <v>170</v>
       </c>
       <c r="C1" s="79">
-        <v>46088</v>
+        <v>46090</v>
       </c>
     </row>
     <row r="2" spans="2:11" x14ac:dyDescent="0.4">
@@ -3368,7 +3380,7 @@
       </c>
       <c r="C3" s="28">
         <f ca="1">OFFSET(NAV!B1,MATCH(C1,NAV!B:B,1),8)</f>
-        <v>1000638.935811381</v>
+        <v>999882.12530607404</v>
       </c>
       <c r="E3" s="47" t="s">
         <v>130</v>
@@ -3385,7 +3397,7 @@
       </c>
       <c r="C4" s="28">
         <f>SUM(N18:N1012)</f>
-        <v>638.93581138100001</v>
+        <v>-117.87469392600178</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="47" t="s">
@@ -3403,7 +3415,7 @@
       </c>
       <c r="C5" s="3">
         <f ca="1">OFFSET(NAV!B1,MATCH(C1,NAV!B:B,1),11)</f>
-        <v>6.3893581138096955E-4</v>
+        <v>-1.1787469392599004E-4</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="47" t="s">
@@ -3422,7 +3434,7 @@
       </c>
       <c r="C6" s="3">
         <f ca="1">OFFSET(NAV!B1,MATCH(C1,NAV!B:B,1),12)</f>
-        <v>6.3893581138096955E-4</v>
+        <v>-1.1787469392599004E-4</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="47"/>
@@ -3455,11 +3467,11 @@
       </c>
       <c r="C8" s="28">
         <f>C4+C7</f>
-        <v>638.93581138100001</v>
+        <v>-117.87469392600178</v>
       </c>
       <c r="D8" s="3">
         <f ca="1">C5+D7</f>
-        <v>6.3893581138096955E-4</v>
+        <v>-1.1787469392599004E-4</v>
       </c>
       <c r="G8" s="47"/>
       <c r="H8" s="51"/>
@@ -3471,11 +3483,11 @@
       </c>
       <c r="C9" s="28">
         <f t="array" ref="C9">SUM((F19:F112="Futures")*(M19:M112))</f>
-        <v>0</v>
+        <v>96900</v>
       </c>
       <c r="D9" s="3">
         <f ca="1">C9/$C$3</f>
-        <v>0</v>
+        <v>9.6911423404371713E-2</v>
       </c>
       <c r="E9" s="47"/>
       <c r="F9" s="47"/>
@@ -3516,11 +3528,11 @@
       </c>
       <c r="C12" s="28" cm="1">
         <f t="array" ref="C12">SUM((PLB!G4:G999="O")*(PLB!E4:E999))</f>
-        <v>0</v>
+        <v>19500</v>
       </c>
       <c r="D12" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
+        <v>1.9502298827505146E-2</v>
       </c>
     </row>
     <row r="13" spans="2:11" x14ac:dyDescent="0.4">
@@ -3529,11 +3541,11 @@
       </c>
       <c r="C13" s="28">
         <f t="array" ref="C13">SUM((PLB!G4:G999="O")*(PLB!D4:D999))</f>
-        <v>0</v>
+        <v>-117.87469392600178</v>
       </c>
       <c r="D13" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
+        <v>-1.1788859000746627E-4</v>
       </c>
       <c r="F13" s="59"/>
       <c r="G13" s="59"/>
@@ -3544,11 +3556,11 @@
       </c>
       <c r="C14" s="28">
         <f>C12+C13</f>
-        <v>0</v>
+        <v>19382.125306073998</v>
       </c>
       <c r="D14" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
+        <v>1.9384410237497679E-2</v>
       </c>
     </row>
     <row r="17" spans="2:28" x14ac:dyDescent="0.4">
@@ -3685,7 +3697,7 @@
       </c>
       <c r="I19" s="28">
         <f t="array" ref="I19">SUM((Trades!V$2:V$9999)*(Trades!U$2:U$9999=Blotter!B19)*(Trades!$T$2:T$9999=Blotter!C19))</f>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J19" s="28">
         <f>VLOOKUP(D19,Multiplier!B:D,2,0)</f>
@@ -3693,19 +3705,19 @@
       </c>
       <c r="K19" s="29">
         <f t="shared" ref="K19" si="1">L19-N19/(H19*J19)</f>
-        <v>1987.22128377238</v>
+        <v>1966.65749387852</v>
       </c>
       <c r="L19" s="29">
         <f t="shared" ref="L19" si="2">IF(I19=0,IF(H19&gt;0,X19,Y19),Z19)</f>
-        <v>2000</v>
+        <v>1964.3</v>
       </c>
       <c r="M19" s="28">
         <f t="shared" ref="M19" si="3">I19*J19*L19</f>
-        <v>0</v>
+        <v>98215</v>
       </c>
       <c r="N19" s="28">
         <f t="array" ref="N19">-SUM((Trades!T$2:T$9999=Blotter!C19)*(Trades!U$2:U$9999=Blotter!B19)*(Trades!V$2:V$9999)*(Trades!W$2:W$9999))*J19+SUM((Trades!T$2:T$9999=Blotter!C19)*(Trades!U$2:U$9999=Blotter!B19)*(Trades!X$2:X$9999))+(L19*I19)*J19</f>
-        <v>638.93581138100001</v>
+        <v>-117.87469392600178</v>
       </c>
       <c r="O19" s="29">
         <f>VLOOKUP(D19,Multiplier!B:H,3,0)</f>
@@ -3720,20 +3732,20 @@
         <v>10500</v>
       </c>
       <c r="S19" s="29">
-        <f t="shared" ref="S19" si="5">IF(OR(F19="Futures",F19="Stocks"),IF(I19=0,0,IF(I19&gt;0,L19-O19,L19+O19)),0)</f>
-        <v>0</v>
+        <f>IF(OR(F19="Futures",F19="Spot"),IF(I19=0,0,IF(I19&gt;0,L19-O19,L19+O19)),0)</f>
+        <v>1824.3</v>
       </c>
       <c r="T19" s="3">
-        <f t="shared" ref="T19" si="6">IF(S19&gt;0,IF(ISNUMBER(S19/L19-1),S19/L19-1,0),0)</f>
-        <v>0</v>
+        <f t="shared" ref="T19" si="5">IF(S19&gt;0,IF(ISNUMBER(S19/L19-1),S19/L19-1,0),0)</f>
+        <v>-7.1272208929389569E-2</v>
       </c>
       <c r="U19" s="29">
-        <f t="shared" ref="U19" si="7">IF(OR(F19="Futures",F19="Stocks"),IF(I19=0,0,IF(I19&gt;0,K19-P19,K19+P19)),0)</f>
-        <v>0</v>
+        <f>IF(OR(F19="Futures",F19="Spot"),IF(I19=0,0,IF(I19&gt;0,K19-P19,K19+P19)),0)</f>
+        <v>1756.65749387852</v>
       </c>
       <c r="V19" s="3">
-        <f t="shared" ref="V19" si="8">IF(U19&gt;0,IF(ISNUMBER(U19/L19-1),U19/L19-1,0),0)</f>
-        <v>0</v>
+        <f t="shared" ref="V19" si="6">IF(U19&gt;0,IF(ISNUMBER(U19/L19-1),U19/L19-1,0),0)</f>
+        <v>-0.10570814342080126</v>
       </c>
       <c r="X19" s="34">
         <f t="array" ref="X19">IF(ISNUMBER(SUM((Trades!T$2:T$9999=Blotter!C19)*(Trades!U$2:U$9999=Blotter!B19)*(Trades!W$2:W$9999)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0))/SUM((Trades!T$2:T$9999=Blotter!C19)*(Trades!U$2:U$9999=Blotter!B19)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0))),SUM((Trades!T$2:T$9999=Blotter!C19)*(Trades!U$2:U$9999=Blotter!B19)*(Trades!W$2:W$9999)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0))/SUM((Trades!T$2:T$9999=Blotter!C19)*(Trades!U$2:U$9999=Blotter!B19)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0)),0)</f>
@@ -3741,39 +3753,101 @@
       </c>
       <c r="Y19" s="34">
         <f t="array" ref="Y19">IF(ISNUMBER(SUM((Trades!T$2:T$9999=Blotter!C19)*(Trades!U$2:U$9999=Blotter!B19)*(Trades!W$2:W$9999)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&gt;0))/SUM((Trades!T$2:T$9999=Blotter!C19)*(Trades!U$2:U$9999=Blotter!B19)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&gt;0))),SUM((Trades!T$2:T$9999=Blotter!C19)*(Trades!U$2:U$9999=Blotter!B19)*(Trades!W$2:W$9999)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&gt;0))/SUM((Trades!T$2:T$9999=Blotter!C19)*(Trades!U$2:U$9999=Blotter!B19)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&gt;0)),0)</f>
-        <v>1986.6</v>
+        <v>1982.8</v>
       </c>
       <c r="Z19" s="35">
         <f>IF(C$2="Last",IF(ISNUMBER(VLOOKUP(B19,Prices!A:L,8,0)),VLOOKUP(B19,Prices!A:L,8,0),0),IF(ISNUMBER(VLOOKUP(B19,Prices!A:L,12,0)),VLOOKUP(B19,Prices!A:L,12,0),0))</f>
-        <v>2151.6</v>
+        <v>1964.3</v>
       </c>
       <c r="AB19" s="29"/>
     </row>
     <row r="20" spans="2:28" x14ac:dyDescent="0.4">
-      <c r="B20" s="9"/>
-      <c r="C20" s="10"/>
-      <c r="D20" s="10"/>
-      <c r="E20" s="10"/>
-      <c r="F20" s="10"/>
-      <c r="G20" s="28"/>
-      <c r="H20" s="11"/>
-      <c r="I20" s="29"/>
-      <c r="J20" s="28"/>
-      <c r="K20" s="29"/>
-      <c r="L20" s="29"/>
-      <c r="M20" s="28"/>
-      <c r="N20" s="28"/>
-      <c r="O20" s="29"/>
-      <c r="P20" s="27"/>
+      <c r="B20" s="9" t="s">
+        <v>305</v>
+      </c>
+      <c r="C20" s="10">
+        <v>2</v>
+      </c>
+      <c r="D20" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="E20" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="F20" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="G20" s="28">
+        <f>VLOOKUP(D20,Multiplier!B:I,8,0)</f>
+        <v>4</v>
+      </c>
+      <c r="H20" s="11">
+        <v>3</v>
+      </c>
+      <c r="I20" s="28">
+        <f t="array" ref="I20">SUM((Trades!V$2:V$9999)*(Trades!U$2:U$9999=Blotter!B20)*(Trades!$T$2:T$9999=Blotter!C20))</f>
+        <v>3</v>
+      </c>
+      <c r="J20" s="28">
+        <f>VLOOKUP(D20,Multiplier!B:D,2,0)</f>
+        <v>10</v>
+      </c>
+      <c r="K20" s="29">
+        <f t="shared" ref="K20" si="7">L20-N20/(H20*J20)</f>
+        <v>3230</v>
+      </c>
+      <c r="L20" s="29">
+        <f t="shared" ref="L20" si="8">IF(I20=0,IF(H20&gt;0,X20,Y20),Z20)</f>
+        <v>3230</v>
+      </c>
+      <c r="M20" s="28">
+        <f t="shared" ref="M20" si="9">I20*J20*L20</f>
+        <v>96900</v>
+      </c>
+      <c r="N20" s="28">
+        <f t="array" ref="N20">-SUM((Trades!T$2:T$9999=Blotter!C20)*(Trades!U$2:U$9999=Blotter!B20)*(Trades!V$2:V$9999)*(Trades!W$2:W$9999))*J20+SUM((Trades!T$2:T$9999=Blotter!C20)*(Trades!U$2:U$9999=Blotter!B20)*(Trades!X$2:X$9999))+(L20*I20)*J20</f>
+        <v>0</v>
+      </c>
+      <c r="O20" s="29">
+        <f>VLOOKUP(D20,Multiplier!B:H,3,0)</f>
+        <v>205</v>
+      </c>
+      <c r="P20" s="27">
+        <v>300</v>
+      </c>
       <c r="Q20" s="27"/>
-      <c r="R20" s="28"/>
-      <c r="S20" s="29"/>
-      <c r="T20" s="3"/>
-      <c r="U20" s="29"/>
-      <c r="V20" s="3"/>
-      <c r="X20" s="34"/>
-      <c r="Y20" s="34"/>
-      <c r="Z20" s="35"/>
+      <c r="R20" s="28">
+        <f t="shared" ref="R20" si="10">(1-Q20)*P20*J20*H20</f>
+        <v>9000</v>
+      </c>
+      <c r="S20" s="29">
+        <f>IF(OR(F20="Futures",F20="Spot"),IF(I20=0,0,IF(I20&gt;0,L20-O20,L20+O20)),0)</f>
+        <v>3025</v>
+      </c>
+      <c r="T20" s="3">
+        <f t="shared" ref="T20" si="11">IF(S20&gt;0,IF(ISNUMBER(S20/L20-1),S20/L20-1,0),0)</f>
+        <v>-6.3467492260061875E-2</v>
+      </c>
+      <c r="U20" s="29">
+        <f t="shared" ref="U20" si="12">IF(OR(F20="Futures",F20="Stocks"),IF(I20=0,0,IF(I20&gt;0,K20-P20,K20+P20)),0)</f>
+        <v>2930</v>
+      </c>
+      <c r="V20" s="3">
+        <f t="shared" ref="V20" si="13">IF(U20&gt;0,IF(ISNUMBER(U20/L20-1),U20/L20-1,0),0)</f>
+        <v>-9.2879256965944235E-2</v>
+      </c>
+      <c r="X20" s="34">
+        <f t="array" ref="X20">IF(ISNUMBER(SUM((Trades!T$2:T$9999=Blotter!C20)*(Trades!U$2:U$9999=Blotter!B20)*(Trades!W$2:W$9999)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0))/SUM((Trades!T$2:T$9999=Blotter!C20)*(Trades!U$2:U$9999=Blotter!B20)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0))),SUM((Trades!T$2:T$9999=Blotter!C20)*(Trades!U$2:U$9999=Blotter!B20)*(Trades!W$2:W$9999)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0))/SUM((Trades!T$2:T$9999=Blotter!C20)*(Trades!U$2:U$9999=Blotter!B20)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0)),0)</f>
+        <v>0</v>
+      </c>
+      <c r="Y20" s="34">
+        <f t="array" ref="Y20">IF(ISNUMBER(SUM((Trades!T$2:T$9999=Blotter!C20)*(Trades!U$2:U$9999=Blotter!B20)*(Trades!W$2:W$9999)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&gt;0))/SUM((Trades!T$2:T$9999=Blotter!C20)*(Trades!U$2:U$9999=Blotter!B20)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&gt;0))),SUM((Trades!T$2:T$9999=Blotter!C20)*(Trades!U$2:U$9999=Blotter!B20)*(Trades!W$2:W$9999)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&gt;0))/SUM((Trades!T$2:T$9999=Blotter!C20)*(Trades!U$2:U$9999=Blotter!B20)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&gt;0)),0)</f>
+        <v>3230</v>
+      </c>
+      <c r="Z20" s="35">
+        <f>IF(C$2="Last",IF(ISNUMBER(VLOOKUP(B20,Prices!A:L,8,0)),VLOOKUP(B20,Prices!A:L,8,0),0),IF(ISNUMBER(VLOOKUP(B20,Prices!A:L,12,0)),VLOOKUP(B20,Prices!A:L,12,0),0))</f>
+        <v>3230</v>
+      </c>
       <c r="AB20" s="29"/>
     </row>
     <row r="21" spans="2:28" x14ac:dyDescent="0.4">
@@ -5559,31 +5633,31 @@
         <v>63</v>
       </c>
       <c r="H2" s="91">
-        <v>6924.25</v>
+        <v>6694.5</v>
       </c>
       <c r="I2" s="91">
-        <v>6924.25</v>
+        <v>6693.5</v>
       </c>
       <c r="J2" s="91">
-        <v>6925.25</v>
+        <v>6694.5</v>
       </c>
       <c r="K2" s="91">
-        <v>6924.75</v>
+        <v>6694</v>
       </c>
       <c r="L2" s="91">
-        <v>6928.5</v>
+        <v>6794</v>
       </c>
       <c r="M2" s="91">
-        <v>6933.75</v>
+        <v>6742.5</v>
       </c>
       <c r="N2" s="91">
-        <v>6953.5</v>
+        <v>6742.5</v>
       </c>
       <c r="O2" s="91">
-        <v>6893</v>
+        <v>6631.5</v>
       </c>
       <c r="P2" s="91">
-        <v>3414</v>
+        <v>10075</v>
       </c>
       <c r="Q2" s="91"/>
       <c r="R2" s="91"/>
@@ -5591,7 +5665,7 @@
       <c r="T2" s="91"/>
       <c r="U2" s="91"/>
       <c r="V2" s="85">
-        <v>46086.543333333335</v>
+        <v>46090.384814814817</v>
       </c>
       <c r="W2" s="81" t="s">
         <v>278</v>
@@ -5623,31 +5697,31 @@
         <v>63</v>
       </c>
       <c r="H3" s="91">
-        <v>25336.5</v>
+        <v>24491.25</v>
       </c>
       <c r="I3" s="91">
-        <v>25332.75</v>
+        <v>24478.25</v>
       </c>
       <c r="J3" s="91">
-        <v>25338</v>
+        <v>24484.25</v>
       </c>
       <c r="K3" s="91">
-        <v>25335.375</v>
+        <v>24481.25</v>
       </c>
       <c r="L3" s="91">
-        <v>25347</v>
+        <v>24883.25</v>
       </c>
       <c r="M3" s="91">
-        <v>25367.75</v>
+        <v>24764.75</v>
       </c>
       <c r="N3" s="91">
-        <v>25460.5</v>
+        <v>24764.75</v>
       </c>
       <c r="O3" s="91">
-        <v>25189.5</v>
+        <v>24212.25</v>
       </c>
       <c r="P3" s="91">
-        <v>999</v>
+        <v>2804</v>
       </c>
       <c r="Q3" s="91"/>
       <c r="R3" s="91"/>
@@ -5655,7 +5729,7 @@
       <c r="T3" s="91"/>
       <c r="U3" s="91"/>
       <c r="V3" s="85">
-        <v>46086.543333333335</v>
+        <v>46090.384814814817</v>
       </c>
       <c r="W3" s="81" t="s">
         <v>278</v>
@@ -5687,31 +5761,31 @@
         <v>63</v>
       </c>
       <c r="H4" s="91">
-        <v>2645.5</v>
+        <v>2476.9</v>
       </c>
       <c r="I4" s="91">
-        <v>2645</v>
+        <v>2474.6999999999998</v>
       </c>
       <c r="J4" s="91">
-        <v>2645.7</v>
+        <v>2476</v>
       </c>
       <c r="K4" s="91">
-        <v>2645.35</v>
+        <v>2475.35</v>
       </c>
       <c r="L4" s="91">
-        <v>2655.1</v>
+        <v>2543.4</v>
       </c>
       <c r="M4" s="91">
-        <v>2655.8</v>
+        <v>2524.9</v>
       </c>
       <c r="N4" s="91">
-        <v>2659.7</v>
+        <v>2524.9</v>
       </c>
       <c r="O4" s="91">
-        <v>2632.8</v>
+        <v>2434</v>
       </c>
       <c r="P4" s="91">
-        <v>333</v>
+        <v>1238</v>
       </c>
       <c r="Q4" s="91"/>
       <c r="R4" s="91"/>
@@ -5719,7 +5793,7 @@
       <c r="T4" s="91"/>
       <c r="U4" s="91"/>
       <c r="V4" s="85">
-        <v>46086.543333333335</v>
+        <v>46090.384814814817</v>
       </c>
       <c r="W4" s="81" t="s">
         <v>278</v>
@@ -5751,31 +5825,31 @@
         <v>60</v>
       </c>
       <c r="H5" s="91">
-        <v>5825</v>
+        <v>5495</v>
       </c>
       <c r="I5" s="91">
-        <v>5816</v>
+        <v>5501</v>
       </c>
       <c r="J5" s="91">
-        <v>5818</v>
+        <v>5504</v>
       </c>
       <c r="K5" s="91">
-        <v>5817</v>
+        <v>5502.5</v>
       </c>
       <c r="L5" s="91">
-        <v>5816</v>
+        <v>5645</v>
       </c>
       <c r="M5" s="91">
-        <v>5850</v>
+        <v>5545</v>
       </c>
       <c r="N5" s="91">
-        <v>5854</v>
+        <v>5545</v>
       </c>
       <c r="O5" s="91">
-        <v>5761</v>
+        <v>5463</v>
       </c>
       <c r="P5" s="91">
-        <v>481</v>
+        <v>1994</v>
       </c>
       <c r="Q5" s="91"/>
       <c r="R5" s="91"/>
@@ -5783,7 +5857,7 @@
       <c r="T5" s="91"/>
       <c r="U5" s="91"/>
       <c r="V5" s="85">
-        <v>46086.543333333335</v>
+        <v>46090.384814814817</v>
       </c>
       <c r="W5" s="81" t="s">
         <v>278</v>
@@ -5815,31 +5889,31 @@
         <v>60</v>
       </c>
       <c r="H6" s="91">
-        <v>24493</v>
+        <v>23227</v>
       </c>
       <c r="I6" s="91">
-        <v>24444</v>
+        <v>23184</v>
       </c>
       <c r="J6" s="91">
-        <v>24460</v>
+        <v>23242</v>
       </c>
       <c r="K6" s="91">
-        <v>24452</v>
+        <v>23213</v>
       </c>
       <c r="L6" s="91">
-        <v>24460</v>
+        <v>23768</v>
       </c>
       <c r="M6" s="91">
-        <v>24531</v>
+        <v>23369</v>
       </c>
       <c r="N6" s="91">
-        <v>24550</v>
+        <v>23369</v>
       </c>
       <c r="O6" s="91">
-        <v>24280</v>
+        <v>22955</v>
       </c>
       <c r="P6" s="91">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="Q6" s="91"/>
       <c r="R6" s="91"/>
@@ -5847,7 +5921,7 @@
       <c r="T6" s="91"/>
       <c r="U6" s="91"/>
       <c r="V6" s="85">
-        <v>46086.543333333335</v>
+        <v>46090.384814814817</v>
       </c>
       <c r="W6" s="81" t="s">
         <v>278</v>
@@ -5879,31 +5953,31 @@
         <v>61</v>
       </c>
       <c r="H7" s="93">
-        <v>55595</v>
+        <v>52490</v>
       </c>
       <c r="I7" s="93">
-        <v>55585</v>
+        <v>52135</v>
       </c>
       <c r="J7" s="93">
-        <v>55605</v>
+        <v>52185</v>
       </c>
       <c r="K7" s="93">
-        <v>55595</v>
+        <v>52160</v>
       </c>
       <c r="L7" s="93">
-        <v>56150</v>
+        <v>53800</v>
       </c>
       <c r="M7" s="93">
-        <v>56000</v>
+        <v>53130</v>
       </c>
       <c r="N7" s="93">
-        <v>56390</v>
+        <v>53130</v>
       </c>
       <c r="O7" s="93">
-        <v>54770</v>
+        <v>51025</v>
       </c>
       <c r="P7" s="93">
-        <v>513</v>
+        <v>4322</v>
       </c>
       <c r="Q7" s="93"/>
       <c r="R7" s="93"/>
@@ -5911,7 +5985,7 @@
       <c r="T7" s="93"/>
       <c r="U7" s="93"/>
       <c r="V7" s="92">
-        <v>46086.543333333335</v>
+        <v>46090.384814814817</v>
       </c>
       <c r="W7" s="1" t="s">
         <v>278</v>
@@ -5940,31 +6014,31 @@
         <v>63</v>
       </c>
       <c r="H8" s="93">
-        <v>76.95</v>
+        <v>102.13</v>
       </c>
       <c r="I8" s="93">
-        <v>76.94</v>
+        <v>102.11</v>
       </c>
       <c r="J8" s="93">
-        <v>76.95</v>
+        <v>102.16</v>
       </c>
       <c r="K8" s="93">
-        <v>76.944999999999993</v>
+        <v>102.13499999999999</v>
       </c>
       <c r="L8" s="93">
-        <v>74.66</v>
+        <v>90.9</v>
       </c>
       <c r="M8" s="93">
-        <v>76.150000000000006</v>
+        <v>98</v>
       </c>
       <c r="N8" s="93">
-        <v>78.09</v>
+        <v>119.48</v>
       </c>
       <c r="O8" s="93">
-        <v>74.97</v>
+        <v>98</v>
       </c>
       <c r="P8" s="93">
-        <v>187336</v>
+        <v>429857</v>
       </c>
       <c r="Q8" s="93"/>
       <c r="R8" s="93"/>
@@ -5972,7 +6046,7 @@
       <c r="T8" s="93"/>
       <c r="U8" s="93"/>
       <c r="V8" s="92">
-        <v>46086.543333333335</v>
+        <v>46090.384814814817</v>
       </c>
       <c r="W8" s="1" t="s">
         <v>278</v>
@@ -6001,31 +6075,31 @@
         <v>63</v>
       </c>
       <c r="H9" s="93">
-        <v>3.1859999999999999</v>
+        <v>3.4980000000000002</v>
       </c>
       <c r="I9" s="93">
-        <v>3.1850000000000001</v>
+        <v>3.4950000000000001</v>
       </c>
       <c r="J9" s="93">
-        <v>3.1869999999999998</v>
+        <v>3.4990000000000001</v>
       </c>
       <c r="K9" s="93">
-        <v>3.1859999999999999</v>
+        <v>3.4969999999999999</v>
       </c>
       <c r="L9" s="93">
-        <v>3.1110000000000002</v>
+        <v>3.351</v>
       </c>
       <c r="M9" s="93">
-        <v>3.1280000000000001</v>
+        <v>3.4289999999999998</v>
       </c>
       <c r="N9" s="93">
-        <v>3.202</v>
+        <v>3.6219999999999999</v>
       </c>
       <c r="O9" s="93">
-        <v>3.1280000000000001</v>
+        <v>3.4289999999999998</v>
       </c>
       <c r="P9" s="93">
-        <v>3218</v>
+        <v>12611</v>
       </c>
       <c r="Q9" s="93"/>
       <c r="R9" s="93"/>
@@ -6033,7 +6107,7 @@
       <c r="T9" s="93"/>
       <c r="U9" s="93"/>
       <c r="V9" s="92">
-        <v>46086.543333333335</v>
+        <v>46090.384814814817</v>
       </c>
       <c r="W9" s="1" t="s">
         <v>278</v>
@@ -6062,31 +6136,31 @@
         <v>63</v>
       </c>
       <c r="H10" s="93">
-        <v>2.5028999999999999</v>
+        <v>2.8633000000000002</v>
       </c>
       <c r="I10" s="93">
-        <v>2.5023</v>
+        <v>2.8628</v>
       </c>
       <c r="J10" s="93">
-        <v>2.5028999999999999</v>
+        <v>2.8645999999999998</v>
       </c>
       <c r="K10" s="93">
-        <v>2.5026000000000002</v>
+        <v>2.8636999999999997</v>
       </c>
       <c r="L10" s="93">
-        <v>2.4462999999999999</v>
+        <v>2.6303999999999998</v>
       </c>
       <c r="M10" s="93">
-        <v>2.4544999999999999</v>
+        <v>2.7</v>
       </c>
       <c r="N10" s="93">
-        <v>2.5459999999999998</v>
+        <v>3.0407000000000002</v>
       </c>
       <c r="O10" s="93">
-        <v>2.4462000000000002</v>
+        <v>2.6825000000000001</v>
       </c>
       <c r="P10" s="93">
-        <v>47319</v>
+        <v>43129</v>
       </c>
       <c r="Q10" s="93"/>
       <c r="R10" s="93"/>
@@ -6094,7 +6168,7 @@
       <c r="T10" s="93"/>
       <c r="U10" s="93"/>
       <c r="V10" s="92">
-        <v>46086.543333333335</v>
+        <v>46090.384814814817</v>
       </c>
       <c r="W10" s="1" t="s">
         <v>278</v>
@@ -6123,31 +6197,31 @@
         <v>63</v>
       </c>
       <c r="H11" s="93">
-        <v>5214.8999999999996</v>
+        <v>5152.7</v>
       </c>
       <c r="I11" s="93">
-        <v>5213.7</v>
+        <v>5155</v>
       </c>
       <c r="J11" s="93">
-        <v>5214.1000000000004</v>
+        <v>5155.7</v>
       </c>
       <c r="K11" s="93">
-        <v>5213.8999999999996</v>
+        <v>5155.3500000000004</v>
       </c>
       <c r="L11" s="93">
-        <v>5173.3</v>
+        <v>5197.8999999999996</v>
       </c>
       <c r="M11" s="93">
-        <v>5199</v>
+        <v>5236</v>
       </c>
       <c r="N11" s="93">
-        <v>5241.5</v>
+        <v>5244.3</v>
       </c>
       <c r="O11" s="93">
-        <v>5168.8999999999996</v>
+        <v>5060</v>
       </c>
       <c r="P11" s="93">
-        <v>2040</v>
+        <v>5510</v>
       </c>
       <c r="Q11" s="93"/>
       <c r="R11" s="93"/>
@@ -6155,7 +6229,7 @@
       <c r="T11" s="93"/>
       <c r="U11" s="93"/>
       <c r="V11" s="92">
-        <v>46086.543333333335</v>
+        <v>46090.384814814817</v>
       </c>
       <c r="W11" s="1" t="s">
         <v>278</v>
@@ -6184,31 +6258,31 @@
         <v>63</v>
       </c>
       <c r="H12" s="93">
-        <v>85.084999999999994</v>
+        <v>84.045000000000002</v>
       </c>
       <c r="I12" s="93">
-        <v>84.94</v>
+        <v>84.14</v>
       </c>
       <c r="J12" s="93">
-        <v>84.995000000000005</v>
+        <v>84.204999999999998</v>
       </c>
       <c r="K12" s="93">
-        <v>84.967500000000001</v>
+        <v>84.172499999999999</v>
       </c>
       <c r="L12" s="93">
-        <v>83.495000000000005</v>
+        <v>84.62</v>
       </c>
       <c r="M12" s="93">
-        <v>84.674999999999997</v>
+        <v>84.805000000000007</v>
       </c>
       <c r="N12" s="93">
-        <v>85.984999999999999</v>
+        <v>85.155000000000001</v>
       </c>
       <c r="O12" s="93">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="P12" s="93">
-        <v>53</v>
+        <v>268</v>
       </c>
       <c r="Q12" s="93"/>
       <c r="R12" s="93"/>
@@ -6216,7 +6290,7 @@
       <c r="T12" s="93"/>
       <c r="U12" s="93"/>
       <c r="V12" s="92">
-        <v>46086.543333333335</v>
+        <v>46090.384814814817</v>
       </c>
       <c r="W12" s="1" t="s">
         <v>278</v>
@@ -6245,31 +6319,31 @@
         <v>63</v>
       </c>
       <c r="H13" s="93">
-        <v>5.8574999999999999</v>
+        <v>5.7809999999999997</v>
       </c>
       <c r="I13" s="93">
-        <v>5.8630000000000004</v>
+        <v>5.7765000000000004</v>
       </c>
       <c r="J13" s="93">
-        <v>5.8650000000000002</v>
+        <v>5.7785000000000002</v>
       </c>
       <c r="K13" s="93">
-        <v>5.8640000000000008</v>
+        <v>5.7774999999999999</v>
       </c>
       <c r="L13" s="93">
-        <v>5.9355000000000002</v>
+        <v>5.835</v>
       </c>
       <c r="M13" s="93">
-        <v>5.96</v>
+        <v>5.8</v>
       </c>
       <c r="N13" s="93">
-        <v>5.9740000000000002</v>
+        <v>5.8</v>
       </c>
       <c r="O13" s="93">
-        <v>5.8540000000000001</v>
+        <v>5.6784999999999997</v>
       </c>
       <c r="P13" s="93">
-        <v>32</v>
+        <v>111</v>
       </c>
       <c r="Q13" s="93"/>
       <c r="R13" s="93"/>
@@ -6277,7 +6351,7 @@
       <c r="T13" s="93"/>
       <c r="U13" s="93"/>
       <c r="V13" s="92">
-        <v>46086.543333333335</v>
+        <v>46090.384814814817</v>
       </c>
       <c r="W13" s="1" t="s">
         <v>278</v>
@@ -6306,31 +6380,31 @@
         <v>63</v>
       </c>
       <c r="H14" s="93">
-        <v>446</v>
+        <v>468</v>
       </c>
       <c r="I14" s="93">
-        <v>445.75</v>
+        <v>467.75</v>
       </c>
       <c r="J14" s="93">
-        <v>446</v>
+        <v>468</v>
       </c>
       <c r="K14" s="93">
-        <v>445.875</v>
+        <v>467.875</v>
       </c>
       <c r="L14" s="93">
-        <v>443.75</v>
+        <v>460.5</v>
       </c>
       <c r="M14" s="93">
-        <v>442.5</v>
+        <v>464</v>
       </c>
       <c r="N14" s="93">
-        <v>446.25</v>
+        <v>476</v>
       </c>
       <c r="O14" s="93">
-        <v>442.5</v>
+        <v>463</v>
       </c>
       <c r="P14" s="93">
-        <v>16675</v>
+        <v>121260</v>
       </c>
       <c r="Q14" s="93"/>
       <c r="R14" s="93"/>
@@ -6338,7 +6412,7 @@
       <c r="T14" s="93"/>
       <c r="U14" s="93"/>
       <c r="V14" s="92">
-        <v>46086.543333333335</v>
+        <v>46090.384814814817</v>
       </c>
       <c r="W14" s="1" t="s">
         <v>278</v>
@@ -6367,31 +6441,31 @@
         <v>63</v>
       </c>
       <c r="H15" s="93">
-        <v>576.25</v>
+        <v>622.75</v>
       </c>
       <c r="I15" s="93">
-        <v>576.25</v>
+        <v>622.75</v>
       </c>
       <c r="J15" s="93">
-        <v>576.5</v>
+        <v>623</v>
       </c>
       <c r="K15" s="93">
-        <v>576.375</v>
+        <v>622.875</v>
       </c>
       <c r="L15" s="93">
-        <v>568.25</v>
+        <v>616.75</v>
       </c>
       <c r="M15" s="93">
-        <v>568.25</v>
+        <v>625</v>
       </c>
       <c r="N15" s="93">
-        <v>576.75</v>
+        <v>641.75</v>
       </c>
       <c r="O15" s="93">
-        <v>568</v>
+        <v>622</v>
       </c>
       <c r="P15" s="93">
-        <v>11237</v>
+        <v>34661</v>
       </c>
       <c r="Q15" s="93"/>
       <c r="R15" s="93"/>
@@ -6399,7 +6473,7 @@
       <c r="T15" s="93"/>
       <c r="U15" s="93"/>
       <c r="V15" s="92">
-        <v>46086.543333333335</v>
+        <v>46090.384814814817</v>
       </c>
       <c r="W15" s="1" t="s">
         <v>278</v>
@@ -6428,31 +6502,31 @@
         <v>63</v>
       </c>
       <c r="H16" s="93">
-        <v>1173.25</v>
+        <v>1216.5</v>
       </c>
       <c r="I16" s="93">
-        <v>1173.25</v>
+        <v>1216.5</v>
       </c>
       <c r="J16" s="93">
-        <v>1173.5</v>
+        <v>1216.75</v>
       </c>
       <c r="K16" s="93">
-        <v>1173.375</v>
+        <v>1216.625</v>
       </c>
       <c r="L16" s="93">
-        <v>1169.5</v>
+        <v>1200.75</v>
       </c>
       <c r="M16" s="93">
-        <v>1168.25</v>
+        <v>1219.5</v>
       </c>
       <c r="N16" s="93">
-        <v>1175</v>
+        <v>1233.75</v>
       </c>
       <c r="O16" s="93">
-        <v>1167.5</v>
+        <v>1210.5</v>
       </c>
       <c r="P16" s="93">
-        <v>13447</v>
+        <v>62655</v>
       </c>
       <c r="Q16" s="93"/>
       <c r="R16" s="93"/>
@@ -6460,7 +6534,7 @@
       <c r="T16" s="93"/>
       <c r="U16" s="93"/>
       <c r="V16" s="92">
-        <v>46086.543333333335</v>
+        <v>46090.384814814817</v>
       </c>
       <c r="W16" s="1" t="s">
         <v>278</v>
@@ -6489,31 +6563,27 @@
         <v>63</v>
       </c>
       <c r="H17" s="93">
-        <v>13.72</v>
+        <v>0</v>
       </c>
       <c r="I17" s="93">
-        <v>13.71</v>
+        <v>-100</v>
       </c>
       <c r="J17" s="93">
-        <v>13.72</v>
+        <v>-100</v>
       </c>
       <c r="K17" s="93">
-        <v>13.715</v>
+        <v>-100</v>
       </c>
       <c r="L17" s="93">
-        <v>13.73</v>
+        <v>14.1</v>
       </c>
       <c r="M17" s="93">
-        <v>13.74</v>
-      </c>
-      <c r="N17" s="93">
-        <v>13.8</v>
-      </c>
-      <c r="O17" s="93">
-        <v>13.61</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N17" s="93"/>
+      <c r="O17" s="93"/>
       <c r="P17" s="93">
-        <v>17987</v>
+        <v>0</v>
       </c>
       <c r="Q17" s="93"/>
       <c r="R17" s="93"/>
@@ -6521,7 +6591,7 @@
       <c r="T17" s="93"/>
       <c r="U17" s="93"/>
       <c r="V17" s="92">
-        <v>46086.543333333335</v>
+        <v>46090.384814814817</v>
       </c>
       <c r="W17" s="1" t="s">
         <v>278</v>
@@ -6550,31 +6620,27 @@
         <v>63</v>
       </c>
       <c r="H18" s="93">
-        <v>288.64999999999998</v>
+        <v>0</v>
       </c>
       <c r="I18" s="93">
-        <v>288.60000000000002</v>
+        <v>-100</v>
       </c>
       <c r="J18" s="93">
-        <v>288.7</v>
+        <v>-100</v>
       </c>
       <c r="K18" s="93">
-        <v>288.64999999999998</v>
+        <v>-100</v>
       </c>
       <c r="L18" s="93">
-        <v>286.25</v>
+        <v>293.3</v>
       </c>
       <c r="M18" s="93">
-        <v>287.05</v>
-      </c>
-      <c r="N18" s="93">
-        <v>288.85000000000002</v>
-      </c>
-      <c r="O18" s="93">
-        <v>285</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N18" s="93"/>
+      <c r="O18" s="93"/>
       <c r="P18" s="93">
-        <v>1625</v>
+        <v>0</v>
       </c>
       <c r="Q18" s="93"/>
       <c r="R18" s="93"/>
@@ -6582,7 +6648,7 @@
       <c r="T18" s="93"/>
       <c r="U18" s="93"/>
       <c r="V18" s="92">
-        <v>46086.543333333335</v>
+        <v>46090.384814814817</v>
       </c>
       <c r="W18" s="1" t="s">
         <v>278</v>
@@ -6590,7 +6656,7 @@
     </row>
     <row r="19" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A19" s="1" t="s">
-        <v>196</v>
+        <v>305</v>
       </c>
       <c r="B19" s="1">
         <v>707621000</v>
@@ -6611,31 +6677,27 @@
         <v>63</v>
       </c>
       <c r="H19" s="93">
-        <v>3045</v>
+        <v>0</v>
       </c>
       <c r="I19" s="93">
-        <v>3043</v>
+        <v>-1</v>
       </c>
       <c r="J19" s="93">
-        <v>3046</v>
+        <v>-1</v>
       </c>
       <c r="K19" s="93">
-        <v>3044.5</v>
+        <v>-1</v>
       </c>
       <c r="L19" s="93">
-        <v>3060</v>
+        <v>3230</v>
       </c>
       <c r="M19" s="93">
-        <v>3045</v>
-      </c>
-      <c r="N19" s="93">
-        <v>3074</v>
-      </c>
-      <c r="O19" s="93">
-        <v>3027</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N19" s="93"/>
+      <c r="O19" s="93"/>
       <c r="P19" s="93">
-        <v>2029</v>
+        <v>0</v>
       </c>
       <c r="Q19" s="93"/>
       <c r="R19" s="93"/>
@@ -6643,7 +6705,7 @@
       <c r="T19" s="93"/>
       <c r="U19" s="93"/>
       <c r="V19" s="92">
-        <v>46086.543333333335</v>
+        <v>46090.384814814817</v>
       </c>
       <c r="W19" s="1" t="s">
         <v>278</v>
@@ -6672,31 +6734,31 @@
         <v>63</v>
       </c>
       <c r="H20" s="93">
-        <v>64.12</v>
+        <v>64.63</v>
       </c>
       <c r="I20" s="93">
-        <v>64.12</v>
+        <v>64.62</v>
       </c>
       <c r="J20" s="93">
-        <v>64.14</v>
+        <v>64.64</v>
       </c>
       <c r="K20" s="93">
-        <v>64.13</v>
+        <v>64.63</v>
       </c>
       <c r="L20" s="93">
-        <v>64.16</v>
+        <v>64.2</v>
       </c>
       <c r="M20" s="93">
-        <v>64.25</v>
+        <v>64.2</v>
       </c>
       <c r="N20" s="93">
-        <v>64.45</v>
+        <v>65.02</v>
       </c>
       <c r="O20" s="93">
-        <v>63.96</v>
+        <v>64.08</v>
       </c>
       <c r="P20" s="93">
-        <v>4962</v>
+        <v>9893</v>
       </c>
       <c r="Q20" s="93"/>
       <c r="R20" s="93"/>
@@ -6704,7 +6766,7 @@
       <c r="T20" s="93"/>
       <c r="U20" s="93"/>
       <c r="V20" s="92">
-        <v>46086.543333333335</v>
+        <v>46090.384814814817</v>
       </c>
       <c r="W20" s="1" t="s">
         <v>278</v>
@@ -6745,19 +6807,15 @@
         <v>-100</v>
       </c>
       <c r="L21" s="93">
-        <v>238.35</v>
+        <v>234.57499999999999</v>
       </c>
       <c r="M21" s="93">
-        <v>235</v>
-      </c>
-      <c r="N21" s="93">
-        <v>239</v>
-      </c>
-      <c r="O21" s="93">
-        <v>234.8</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N21" s="93"/>
+      <c r="O21" s="93"/>
       <c r="P21" s="93">
-        <v>32462</v>
+        <v>0</v>
       </c>
       <c r="Q21" s="93"/>
       <c r="R21" s="93"/>
@@ -6765,7 +6823,7 @@
       <c r="T21" s="93"/>
       <c r="U21" s="93"/>
       <c r="V21" s="92">
-        <v>46086.543333333335</v>
+        <v>46090.384814814817</v>
       </c>
       <c r="W21" s="1" t="s">
         <v>278</v>
@@ -6806,19 +6864,15 @@
         <v>-100</v>
       </c>
       <c r="L22" s="93">
-        <v>357</v>
+        <v>348.07499999999999</v>
       </c>
       <c r="M22" s="93">
-        <v>350.55</v>
-      </c>
-      <c r="N22" s="93">
-        <v>357.42500000000001</v>
-      </c>
-      <c r="O22" s="93">
-        <v>350.52499999999998</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N22" s="93"/>
+      <c r="O22" s="93"/>
       <c r="P22" s="93">
-        <v>6355</v>
+        <v>0</v>
       </c>
       <c r="Q22" s="93"/>
       <c r="R22" s="93"/>
@@ -6826,7 +6880,7 @@
       <c r="T22" s="93"/>
       <c r="U22" s="93"/>
       <c r="V22" s="92">
-        <v>46086.543333333335</v>
+        <v>46090.384814814817</v>
       </c>
       <c r="W22" s="1" t="s">
         <v>278</v>
@@ -6867,19 +6921,15 @@
         <v>-100</v>
       </c>
       <c r="L23" s="93">
-        <v>97.075000000000003</v>
+        <v>95.625</v>
       </c>
       <c r="M23" s="93">
-        <v>95.85</v>
-      </c>
-      <c r="N23" s="93">
-        <v>97.3</v>
-      </c>
-      <c r="O23" s="93">
-        <v>95.674999999999997</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N23" s="93"/>
+      <c r="O23" s="93"/>
       <c r="P23" s="93">
-        <v>23682</v>
+        <v>0</v>
       </c>
       <c r="Q23" s="93"/>
       <c r="R23" s="93"/>
@@ -6887,7 +6937,7 @@
       <c r="T23" s="93"/>
       <c r="U23" s="93"/>
       <c r="V23" s="92">
-        <v>46086.543333333335</v>
+        <v>46090.384814814817</v>
       </c>
       <c r="W23" s="1" t="s">
         <v>278</v>
@@ -6916,31 +6966,31 @@
         <v>63</v>
       </c>
       <c r="H24" s="93">
-        <v>98.68</v>
+        <v>99.02</v>
       </c>
       <c r="I24" s="93">
-        <v>98.674999999999997</v>
+        <v>99.02</v>
       </c>
       <c r="J24" s="93">
-        <v>98.685000000000002</v>
+        <v>99.03</v>
       </c>
       <c r="K24" s="93">
-        <v>98.68</v>
+        <v>99.025000000000006</v>
       </c>
       <c r="L24" s="93">
-        <v>98.43</v>
+        <v>98.71</v>
       </c>
       <c r="M24" s="93">
-        <v>98.375</v>
+        <v>99.04</v>
       </c>
       <c r="N24" s="93">
-        <v>98.88</v>
+        <v>99.435000000000002</v>
       </c>
       <c r="O24" s="93">
-        <v>98.364999999999995</v>
+        <v>98.965000000000003</v>
       </c>
       <c r="P24" s="93">
-        <v>1858</v>
+        <v>3043</v>
       </c>
       <c r="Q24" s="93"/>
       <c r="R24" s="93"/>
@@ -6948,7 +6998,7 @@
       <c r="T24" s="93"/>
       <c r="U24" s="93"/>
       <c r="V24" s="92">
-        <v>46086.543333333335</v>
+        <v>46090.384814814817</v>
       </c>
       <c r="W24" s="1" t="s">
         <v>278</v>
@@ -6977,31 +7027,31 @@
         <v>63</v>
       </c>
       <c r="H25" s="93">
-        <v>1.1664000000000001</v>
+        <v>1.1616500000000001</v>
       </c>
       <c r="I25" s="93">
-        <v>1.16635</v>
+        <v>1.1614500000000001</v>
       </c>
       <c r="J25" s="93">
-        <v>1.1664000000000001</v>
+        <v>1.1615500000000001</v>
       </c>
       <c r="K25" s="93">
-        <v>1.1663749999999999</v>
+        <v>1.1615000000000002</v>
       </c>
       <c r="L25" s="93">
-        <v>1.1696500000000001</v>
+        <v>1.1655500000000001</v>
       </c>
       <c r="M25" s="93">
-        <v>1.1692</v>
+        <v>1.1604000000000001</v>
       </c>
       <c r="N25" s="93">
-        <v>1.17025</v>
+        <v>1.16245</v>
       </c>
       <c r="O25" s="93">
-        <v>1.1636500000000001</v>
+        <v>1.1560999999999999</v>
       </c>
       <c r="P25" s="93">
-        <v>15398</v>
+        <v>14661</v>
       </c>
       <c r="Q25" s="93"/>
       <c r="R25" s="93"/>
@@ -7009,7 +7059,7 @@
       <c r="T25" s="93"/>
       <c r="U25" s="93"/>
       <c r="V25" s="92">
-        <v>46086.543333333335</v>
+        <v>46090.384814814817</v>
       </c>
       <c r="W25" s="1" t="s">
         <v>278</v>
@@ -7038,31 +7088,31 @@
         <v>63</v>
       </c>
       <c r="H26" s="93">
-        <v>1.3363</v>
+        <v>1.3347</v>
       </c>
       <c r="I26" s="93">
-        <v>1.3364</v>
+        <v>1.3344</v>
       </c>
       <c r="J26" s="93">
-        <v>1.3366</v>
+        <v>1.3346</v>
       </c>
       <c r="K26" s="93">
-        <v>1.3365</v>
+        <v>1.3345</v>
       </c>
       <c r="L26" s="93">
-        <v>1.3375999999999999</v>
+        <v>1.3387</v>
       </c>
       <c r="M26" s="93">
-        <v>1.3371</v>
+        <v>1.3351</v>
       </c>
       <c r="N26" s="93">
-        <v>1.3387</v>
+        <v>1.3351</v>
       </c>
       <c r="O26" s="93">
-        <v>1.3308</v>
+        <v>1.3283</v>
       </c>
       <c r="P26" s="93">
-        <v>27021</v>
+        <v>10401</v>
       </c>
       <c r="Q26" s="93"/>
       <c r="R26" s="93"/>
@@ -7070,7 +7120,7 @@
       <c r="T26" s="93"/>
       <c r="U26" s="93"/>
       <c r="V26" s="92">
-        <v>46086.543333333335</v>
+        <v>46090.384814814817</v>
       </c>
       <c r="W26" s="1" t="s">
         <v>278</v>
@@ -7099,31 +7149,31 @@
         <v>63</v>
       </c>
       <c r="H27" s="93">
-        <v>6.4105000000000004E-3</v>
+        <v>6.3670000000000003E-3</v>
       </c>
       <c r="I27" s="93">
-        <v>6.4105000000000004E-3</v>
+        <v>6.3660000000000001E-3</v>
       </c>
       <c r="J27" s="93">
-        <v>6.411E-3</v>
+        <v>6.3670000000000003E-3</v>
       </c>
       <c r="K27" s="93">
-        <v>6.4107499999999998E-3</v>
+        <v>6.3665000000000006E-3</v>
       </c>
       <c r="L27" s="93">
-        <v>6.4250000000000002E-3</v>
+        <v>6.3879999999999996E-3</v>
       </c>
       <c r="M27" s="93">
-        <v>6.4215000000000001E-3</v>
+        <v>6.3800000000000003E-3</v>
       </c>
       <c r="N27" s="93">
-        <v>6.4454999999999998E-3</v>
+        <v>6.3800000000000003E-3</v>
       </c>
       <c r="O27" s="93">
-        <v>6.4079999999999996E-3</v>
+        <v>6.3464999999999997E-3</v>
       </c>
       <c r="P27" s="93">
-        <v>4671</v>
+        <v>30276</v>
       </c>
       <c r="Q27" s="93"/>
       <c r="R27" s="93"/>
@@ -7131,7 +7181,7 @@
       <c r="T27" s="93"/>
       <c r="U27" s="93"/>
       <c r="V27" s="92">
-        <v>46086.543333333335</v>
+        <v>46090.384814814817</v>
       </c>
       <c r="W27" s="1" t="s">
         <v>278</v>
@@ -7160,31 +7210,31 @@
         <v>63</v>
       </c>
       <c r="H28" s="93">
-        <v>0.7369</v>
+        <v>0.74080000000000001</v>
       </c>
       <c r="I28" s="93">
-        <v>0.73680000000000001</v>
+        <v>0.74070000000000003</v>
       </c>
       <c r="J28" s="93">
-        <v>0.73685</v>
+        <v>0.74080000000000001</v>
       </c>
       <c r="K28" s="93">
-        <v>0.73682500000000006</v>
+        <v>0.74075000000000002</v>
       </c>
       <c r="L28" s="93">
-        <v>0.73665000000000003</v>
+        <v>0.73919999999999997</v>
       </c>
       <c r="M28" s="93">
-        <v>0.73629999999999995</v>
+        <v>0.73875000000000002</v>
       </c>
       <c r="N28" s="93">
-        <v>0.73699999999999999</v>
+        <v>0.74139999999999995</v>
       </c>
       <c r="O28" s="93">
-        <v>0.73470000000000002</v>
+        <v>0.73799999999999999</v>
       </c>
       <c r="P28" s="93">
-        <v>1076</v>
+        <v>3189</v>
       </c>
       <c r="Q28" s="93"/>
       <c r="R28" s="93"/>
@@ -7192,7 +7242,7 @@
       <c r="T28" s="93"/>
       <c r="U28" s="93"/>
       <c r="V28" s="92">
-        <v>46086.543333333335</v>
+        <v>46090.384814814817</v>
       </c>
       <c r="W28" s="1" t="s">
         <v>278</v>
@@ -7221,31 +7271,31 @@
         <v>63</v>
       </c>
       <c r="H29" s="93">
-        <v>0.70430000000000004</v>
+        <v>0.7</v>
       </c>
       <c r="I29" s="93">
-        <v>0.70440000000000003</v>
+        <v>0.69989999999999997</v>
       </c>
       <c r="J29" s="93">
-        <v>0.70450000000000002</v>
+        <v>0.7</v>
       </c>
       <c r="K29" s="93">
-        <v>0.70445000000000002</v>
+        <v>0.69994999999999996</v>
       </c>
       <c r="L29" s="93">
-        <v>0.70760000000000001</v>
+        <v>0.70189999999999997</v>
       </c>
       <c r="M29" s="93">
-        <v>0.70709999999999995</v>
+        <v>0.69835000000000003</v>
       </c>
       <c r="N29" s="93">
-        <v>0.70830000000000004</v>
+        <v>0.70155000000000001</v>
       </c>
       <c r="O29" s="93">
-        <v>0.70055000000000001</v>
+        <v>0.69489999999999996</v>
       </c>
       <c r="P29" s="93">
-        <v>4540</v>
+        <v>11221</v>
       </c>
       <c r="Q29" s="93"/>
       <c r="R29" s="93"/>
@@ -7253,7 +7303,7 @@
       <c r="T29" s="93"/>
       <c r="U29" s="93"/>
       <c r="V29" s="92">
-        <v>46086.543333333335</v>
+        <v>46090.384814814817</v>
       </c>
       <c r="W29" s="1" t="s">
         <v>278</v>
@@ -7282,31 +7332,31 @@
         <v>63</v>
       </c>
       <c r="H30" s="93">
-        <v>116.46875</v>
+        <v>115.40625</v>
       </c>
       <c r="I30" s="93">
-        <v>116.4375</v>
+        <v>115.375</v>
       </c>
       <c r="J30" s="93">
-        <v>116.46875</v>
+        <v>115.40625</v>
       </c>
       <c r="K30" s="93">
-        <v>116.453125</v>
+        <v>115.390625</v>
       </c>
       <c r="L30" s="93">
-        <v>117.0625</v>
+        <v>116.1875</v>
       </c>
       <c r="M30" s="93">
-        <v>116.78125</v>
+        <v>115.8125</v>
       </c>
       <c r="N30" s="93">
-        <v>116.875</v>
+        <v>115.84375</v>
       </c>
       <c r="O30" s="93">
-        <v>116.21875</v>
+        <v>115.0625</v>
       </c>
       <c r="P30" s="93">
-        <v>122848</v>
+        <v>116350</v>
       </c>
       <c r="Q30" s="93"/>
       <c r="R30" s="93"/>
@@ -7314,7 +7364,7 @@
       <c r="T30" s="93"/>
       <c r="U30" s="93"/>
       <c r="V30" s="92">
-        <v>46086.543333333335</v>
+        <v>46090.384814814817</v>
       </c>
       <c r="W30" s="1" t="s">
         <v>278</v>
@@ -7343,31 +7393,31 @@
         <v>63</v>
       </c>
       <c r="H31" s="93">
-        <v>112.546875</v>
+        <v>111.984375</v>
       </c>
       <c r="I31" s="93">
-        <v>112.53125</v>
+        <v>111.984375</v>
       </c>
       <c r="J31" s="93">
-        <v>112.546875</v>
+        <v>112</v>
       </c>
       <c r="K31" s="93">
-        <v>112.5390625</v>
+        <v>111.9921875</v>
       </c>
       <c r="L31" s="93">
-        <v>112.8125</v>
+        <v>112.4375</v>
       </c>
       <c r="M31" s="93">
-        <v>112.703125</v>
+        <v>112.1875</v>
       </c>
       <c r="N31" s="93">
-        <v>112.75</v>
+        <v>112.203125</v>
       </c>
       <c r="O31" s="93">
-        <v>112.484375</v>
+        <v>111.828125</v>
       </c>
       <c r="P31" s="93">
-        <v>587278</v>
+        <v>637038</v>
       </c>
       <c r="Q31" s="93"/>
       <c r="R31" s="93"/>
@@ -7375,7 +7425,7 @@
       <c r="T31" s="93"/>
       <c r="U31" s="93"/>
       <c r="V31" s="92">
-        <v>46086.543333333335</v>
+        <v>46090.384814814817</v>
       </c>
       <c r="W31" s="1" t="s">
         <v>278</v>
@@ -7404,31 +7454,31 @@
         <v>60</v>
       </c>
       <c r="H32" s="93">
-        <v>127.61</v>
+        <v>126.5</v>
       </c>
       <c r="I32" s="93">
-        <v>127.61</v>
+        <v>126.49</v>
       </c>
       <c r="J32" s="93">
-        <v>127.62</v>
+        <v>126.5</v>
       </c>
       <c r="K32" s="93">
-        <v>127.61500000000001</v>
+        <v>126.495</v>
       </c>
       <c r="L32" s="93">
-        <v>128.24</v>
+        <v>126.93</v>
       </c>
       <c r="M32" s="93">
-        <v>128</v>
+        <v>126.7</v>
       </c>
       <c r="N32" s="93">
-        <v>128.03</v>
+        <v>126.7</v>
       </c>
       <c r="O32" s="93">
-        <v>127.57</v>
+        <v>125.94</v>
       </c>
       <c r="P32" s="93">
-        <v>766781</v>
+        <v>353033</v>
       </c>
       <c r="Q32" s="93"/>
       <c r="R32" s="93"/>
@@ -7436,7 +7486,7 @@
       <c r="T32" s="93"/>
       <c r="U32" s="93"/>
       <c r="V32" s="92">
-        <v>46086.543333333335</v>
+        <v>46090.384814814817</v>
       </c>
       <c r="W32" s="1" t="s">
         <v>278</v>
@@ -7465,31 +7515,31 @@
         <v>60</v>
       </c>
       <c r="H33" s="93">
-        <v>111.06</v>
+        <v>111.38</v>
       </c>
       <c r="I33" s="93">
-        <v>111.06</v>
+        <v>111.36</v>
       </c>
       <c r="J33" s="93">
-        <v>111.08</v>
+        <v>111.38</v>
       </c>
       <c r="K33" s="93">
-        <v>111.07</v>
+        <v>111.37</v>
       </c>
       <c r="L33" s="93">
-        <v>111.76</v>
+        <v>110.88</v>
       </c>
       <c r="M33" s="93">
-        <v>111.42</v>
+        <v>111</v>
       </c>
       <c r="N33" s="93">
-        <v>111.58</v>
+        <v>111.64</v>
       </c>
       <c r="O33" s="93">
-        <v>110.54</v>
+        <v>110.14</v>
       </c>
       <c r="P33" s="93">
-        <v>95740</v>
+        <v>49976</v>
       </c>
       <c r="Q33" s="93"/>
       <c r="R33" s="93"/>
@@ -7497,7 +7547,7 @@
       <c r="T33" s="93"/>
       <c r="U33" s="93"/>
       <c r="V33" s="92">
-        <v>46086.543333333335</v>
+        <v>46090.384814814817</v>
       </c>
       <c r="W33" s="1" t="s">
         <v>278</v>
@@ -7526,31 +7576,31 @@
         <v>60</v>
       </c>
       <c r="H34" s="93">
-        <v>119.94</v>
+        <v>117.61</v>
       </c>
       <c r="I34" s="93">
-        <v>119.93</v>
+        <v>117.61</v>
       </c>
       <c r="J34" s="93">
-        <v>119.94</v>
+        <v>117.62</v>
       </c>
       <c r="K34" s="93">
-        <v>119.935</v>
+        <v>117.61500000000001</v>
       </c>
       <c r="L34" s="93">
-        <v>120.61</v>
+        <v>118.6</v>
       </c>
       <c r="M34" s="93">
-        <v>120.26</v>
+        <v>117.62</v>
       </c>
       <c r="N34" s="93">
-        <v>120.61</v>
+        <v>117.84</v>
       </c>
       <c r="O34" s="93">
-        <v>119.9</v>
+        <v>117.42</v>
       </c>
       <c r="P34" s="93">
-        <v>273348</v>
+        <v>81733</v>
       </c>
       <c r="Q34" s="93"/>
       <c r="R34" s="93"/>
@@ -7558,7 +7608,7 @@
       <c r="T34" s="93"/>
       <c r="U34" s="93"/>
       <c r="V34" s="92">
-        <v>46086.543333333335</v>
+        <v>46090.384814814817</v>
       </c>
       <c r="W34" s="1" t="s">
         <v>278</v>
@@ -7587,29 +7637,29 @@
         <v>63</v>
       </c>
       <c r="H35" s="93">
-        <v>72839.25</v>
+        <v>67524.5</v>
       </c>
       <c r="I35" s="93">
-        <v>72839.25</v>
+        <v>67524.5</v>
       </c>
       <c r="J35" s="93">
-        <v>72839.5</v>
+        <v>67524.75</v>
       </c>
       <c r="K35" s="93">
-        <v>72839.375</v>
+        <v>67524.625</v>
       </c>
       <c r="L35" s="93">
-        <v>73084</v>
+        <v>67317.25</v>
       </c>
       <c r="M35" s="93"/>
       <c r="N35" s="93">
-        <v>74269.5</v>
+        <v>68748</v>
       </c>
       <c r="O35" s="93">
-        <v>67063</v>
+        <v>65471</v>
       </c>
       <c r="P35" s="93">
-        <v>186.00945229999999</v>
+        <v>148.76280749</v>
       </c>
       <c r="Q35" s="93"/>
       <c r="R35" s="93"/>
@@ -7617,7 +7667,7 @@
       <c r="T35" s="93"/>
       <c r="U35" s="93"/>
       <c r="V35" s="92">
-        <v>46086.543333333335</v>
+        <v>46090.384814814817</v>
       </c>
       <c r="W35" s="1" t="s">
         <v>278</v>
@@ -7646,29 +7696,29 @@
         <v>63</v>
       </c>
       <c r="H36" s="93">
-        <v>2134.5500000000002</v>
+        <v>1985.5</v>
       </c>
       <c r="I36" s="93">
-        <v>2134.9</v>
+        <v>1985.45</v>
       </c>
       <c r="J36" s="93">
-        <v>2134.9499999999998</v>
+        <v>1985.5</v>
       </c>
       <c r="K36" s="93">
-        <v>2134.9250000000002</v>
+        <v>1985.4749999999999</v>
       </c>
       <c r="L36" s="93">
-        <v>2151.6</v>
+        <v>1964.3</v>
       </c>
       <c r="M36" s="93"/>
       <c r="N36" s="93">
-        <v>2198.1999999999998</v>
+        <v>2013.05</v>
       </c>
       <c r="O36" s="93">
-        <v>1945.25</v>
+        <v>1914.8</v>
       </c>
       <c r="P36" s="93">
-        <v>1219.64086456</v>
+        <v>1704.4242436699999</v>
       </c>
       <c r="Q36" s="93"/>
       <c r="R36" s="93"/>
@@ -7676,7 +7726,7 @@
       <c r="T36" s="93"/>
       <c r="U36" s="93"/>
       <c r="V36" s="92">
-        <v>46086.543333333335</v>
+        <v>46090.384814814817</v>
       </c>
       <c r="W36" s="1" t="s">
         <v>278</v>
@@ -7906,15 +7956,37 @@
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A5" s="85"/>
+      <c r="A5" s="85">
+        <v>46090.383530092593</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>315</v>
+      </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A6" s="85"/>
+      <c r="A6" s="85">
+        <v>46090.38354166667</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>316</v>
+      </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A7" s="85"/>
-      <c r="B7" s="81"/>
-      <c r="C7" s="81"/>
+      <c r="A7" s="85">
+        <v>46090.38354166667</v>
+      </c>
+      <c r="B7" s="81" t="s">
+        <v>314</v>
+      </c>
+      <c r="C7" s="81" t="s">
+        <v>317</v>
+      </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A8" s="85"/>
@@ -8375,11 +8447,11 @@
       <c r="H5" s="67"/>
       <c r="I5" s="70">
         <f>Blotter!C$4-SUM(NAV!I$4:I4)</f>
-        <v>638.93581138100001</v>
+        <v>-117.87469392600178</v>
       </c>
       <c r="J5" s="70">
         <f t="shared" si="2"/>
-        <v>1000638.935811381</v>
+        <v>999882.12530607404</v>
       </c>
       <c r="K5" s="70">
         <f t="shared" si="3"/>
@@ -8387,19 +8459,19 @@
       </c>
       <c r="L5" s="71">
         <f t="shared" si="4"/>
-        <v>1000.638935811381</v>
+        <v>999.88212530607404</v>
       </c>
       <c r="M5" s="72">
         <f t="shared" si="5"/>
-        <v>6.3893581138096955E-4</v>
+        <v>-1.1787469392599004E-4</v>
       </c>
       <c r="N5" s="73">
         <f t="shared" ref="N5" si="6">L5/L4-1</f>
-        <v>6.3893581138096955E-4</v>
+        <v>-1.1787469392599004E-4</v>
       </c>
       <c r="O5" s="75">
         <f>STDEVP(N$4:N5)*SQRT(12)</f>
-        <v>1.1066692880870841E-3</v>
+        <v>2.0416495880644527E-4</v>
       </c>
     </row>
     <row r="6" spans="2:18" ht="14.25" x14ac:dyDescent="0.4">
@@ -8795,7 +8867,7 @@
       </c>
       <c r="D4" s="6">
         <f t="array" ref="D4">SUM((Blotter!C$19:C$1013=C4)*(Blotter!N$19:N$1013)*1)</f>
-        <v>638.93581138100001</v>
+        <v>-117.87469392600178</v>
       </c>
       <c r="E4" s="6">
         <f t="array" ref="E4">SUM((Blotter!B$19:C$1013=C4)*(Blotter!R$19:R$1013)*1)</f>
@@ -8803,32 +8875,32 @@
       </c>
       <c r="F4" s="30">
         <f t="shared" ref="F4" si="0">IF(ISNUMBER(D4/E4),D4/E4,0)</f>
-        <v>6.0851029655333337E-2</v>
+        <v>-1.1226161326285884E-2</v>
       </c>
       <c r="G4" s="36" t="str">
         <f t="array" ref="G4">IF(SUM((Blotter!C$19:C$1013=PLB!C4)*(Blotter!M$19:M$1013))=0,"C","O")</f>
-        <v>C</v>
+        <v>O</v>
       </c>
       <c r="H4" s="16">
         <f>J3+D4</f>
-        <v>1000638.935811381</v>
+        <v>999882.12530607404</v>
       </c>
       <c r="I4" s="16"/>
       <c r="J4" s="16">
         <f>H4+I4</f>
-        <v>1000638.935811381</v>
+        <v>999882.12530607404</v>
       </c>
       <c r="K4" s="3">
         <f>H4/J3-1</f>
-        <v>6.3893581138096955E-4</v>
+        <v>-1.1787469392599004E-4</v>
       </c>
       <c r="L4" s="3">
         <f>(1+K4)*(1+L3)-1</f>
-        <v>6.3893581138096955E-4</v>
+        <v>-1.1787469392599004E-4</v>
       </c>
       <c r="M4" s="6">
         <f>O3-IF(G4="O",O3*1%,-D4)</f>
-        <v>1000638.935811381</v>
+        <v>990000</v>
       </c>
       <c r="N4" s="16">
         <f>I4</f>
@@ -8836,15 +8908,15 @@
       </c>
       <c r="O4" s="6">
         <f>M4+N4</f>
-        <v>1000638.935811381</v>
+        <v>990000</v>
       </c>
       <c r="P4" s="3">
         <f>M4/O3-1</f>
-        <v>6.3893581138096955E-4</v>
+        <v>-1.0000000000000009E-2</v>
       </c>
       <c r="Q4" s="3">
         <f>(1+P4)*(1+Q3)-1</f>
-        <v>6.3893581138096955E-4</v>
+        <v>-1.0000000000000009E-2</v>
       </c>
       <c r="R4" s="3">
         <f>(1-1%)*(1+R3)-1</f>
@@ -8871,28 +8943,73 @@
         <f>C4+1</f>
         <v>2</v>
       </c>
-      <c r="D5" s="6"/>
-      <c r="E5" s="6"/>
-      <c r="F5" s="30"/>
-      <c r="G5" s="36"/>
-      <c r="H5" s="16"/>
+      <c r="D5" s="6">
+        <f t="array" ref="D5">SUM((Blotter!C$19:C$1013=C5)*(Blotter!N$19:N$1013)*1)</f>
+        <v>0</v>
+      </c>
+      <c r="E5" s="6">
+        <f t="array" ref="E5">SUM((Blotter!B$19:C$1013=C5)*(Blotter!R$19:R$1013)*1)</f>
+        <v>9000</v>
+      </c>
+      <c r="F5" s="30">
+        <f t="shared" ref="F5" si="1">IF(ISNUMBER(D5/E5),D5/E5,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G5" s="36" t="str">
+        <f t="array" ref="G5">IF(SUM((Blotter!C$19:C$1013=PLB!C5)*(Blotter!M$19:M$1013))=0,"C","O")</f>
+        <v>O</v>
+      </c>
+      <c r="H5" s="16">
+        <f>J4+D5</f>
+        <v>999882.12530607404</v>
+      </c>
       <c r="I5" s="16"/>
-      <c r="J5" s="16"/>
-      <c r="K5" s="3"/>
-      <c r="L5" s="3"/>
-      <c r="M5" s="6"/>
-      <c r="N5" s="16"/>
-      <c r="O5" s="6"/>
-      <c r="P5" s="3"/>
-      <c r="Q5" s="3"/>
-      <c r="R5" s="3"/>
+      <c r="J5" s="16">
+        <f>H5+I5</f>
+        <v>999882.12530607404</v>
+      </c>
+      <c r="K5" s="3">
+        <f>H5/J4-1</f>
+        <v>0</v>
+      </c>
+      <c r="L5" s="3">
+        <f>(1+K5)*(1+L4)-1</f>
+        <v>-1.1787469392599004E-4</v>
+      </c>
+      <c r="M5" s="6">
+        <f>O4-IF(G5="O",O4*1%,-D5)</f>
+        <v>980100</v>
+      </c>
+      <c r="N5" s="16">
+        <f>I5</f>
+        <v>0</v>
+      </c>
+      <c r="O5" s="6">
+        <f>M5+N5</f>
+        <v>980100</v>
+      </c>
+      <c r="P5" s="3">
+        <f>M5/O4-1</f>
+        <v>-1.0000000000000009E-2</v>
+      </c>
+      <c r="Q5" s="3">
+        <f>(1+P5)*(1+Q4)-1</f>
+        <v>-1.9900000000000029E-2</v>
+      </c>
+      <c r="R5" s="3">
+        <f>(1-1%)*(1+R4)-1</f>
+        <v>-1.9900000000000029E-2</v>
+      </c>
       <c r="T5" s="40">
-        <f t="shared" ref="T5" si="1">B5</f>
+        <f t="shared" ref="T5" si="2">B5</f>
         <v>46095</v>
       </c>
       <c r="U5" s="5">
-        <f t="shared" ref="U5" si="2">C5</f>
+        <f t="shared" ref="U5" si="3">C5</f>
         <v>2</v>
+      </c>
+      <c r="V5" s="1" t="s">
+        <v>320</v>
       </c>
     </row>
     <row r="6" spans="2:28" x14ac:dyDescent="0.4">
@@ -10788,7 +10905,7 @@
         <v>10</v>
       </c>
       <c r="D19" s="19">
-        <v>400</v>
+        <v>205</v>
       </c>
       <c r="E19" s="20">
         <f t="shared" si="1"/>
@@ -10804,22 +10921,22 @@
       </c>
       <c r="H19" s="23">
         <f t="shared" si="0"/>
-        <v>1.6666666666666667</v>
+        <v>3.2520325203252032</v>
       </c>
       <c r="I19" s="61">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J19" s="18">
-        <v>8300</v>
+        <v>3230</v>
       </c>
       <c r="K19" s="3">
         <f>J19*H19*C19/$N$3</f>
-        <v>0.13833333333333334</v>
+        <v>0.10504065040650407</v>
       </c>
       <c r="L19" s="3">
         <f>J19*I19*C19/$N$3</f>
-        <v>0.16600000000000001</v>
+        <v>0.12920000000000001</v>
       </c>
     </row>
     <row r="20" spans="2:12" x14ac:dyDescent="0.4">
@@ -11904,46 +12021,103 @@
       <c r="AE3" s="41"/>
     </row>
     <row r="4" spans="1:31" x14ac:dyDescent="0.4">
-      <c r="T4" s="43" t="str">
+      <c r="A4" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="H4" s="1">
+        <v>1</v>
+      </c>
+      <c r="L4" s="44">
+        <v>46084</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="N4" s="1">
+        <v>50</v>
+      </c>
+      <c r="O4" s="1">
+        <v>1979</v>
+      </c>
+      <c r="P4" s="1">
+        <v>12116.947392599999</v>
+      </c>
+      <c r="Q4" s="1">
+        <v>-21.810505307</v>
+      </c>
+      <c r="R4" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="T4" s="43">
         <f>IF(ISNUMBER(VLOOKUP(U4,Blotter!B:C,2,0)),VLOOKUP(U4,Blotter!B:C,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="U4" s="42">
+        <v>1</v>
+      </c>
+      <c r="U4" s="42" t="str">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>ETH.USD-PAXOS</v>
       </c>
       <c r="V4" s="42">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="W4" s="42">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1979</v>
       </c>
       <c r="X4" s="42">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>-21.810505307</v>
       </c>
       <c r="AC4" s="44"/>
       <c r="AD4" s="45"/>
       <c r="AE4" s="41"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.4">
-      <c r="T5" s="43" t="str">
+      <c r="D5" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="H5" s="1">
+        <v>10</v>
+      </c>
+      <c r="L5" s="44">
+        <v>46090</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="N5" s="1">
+        <v>3</v>
+      </c>
+      <c r="O5" s="1">
+        <v>3230</v>
+      </c>
+      <c r="T5" s="43">
         <f>IF(ISNUMBER(VLOOKUP(U5,Blotter!B:C,2,0)),VLOOKUP(U5,Blotter!B:C,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="U5" s="42">
+        <v>2</v>
+      </c>
+      <c r="U5" s="42" t="str">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>CCK6</v>
       </c>
       <c r="V5" s="42">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W5" s="42">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3230</v>
       </c>
       <c r="X5" s="42">
         <f t="shared" si="3"/>
@@ -11959,19 +12133,19 @@
         <v/>
       </c>
       <c r="U6" s="42">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="U6" si="4">D6</f>
         <v>0</v>
       </c>
       <c r="V6" s="42">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="V6" si="5">N6</f>
         <v>0</v>
       </c>
       <c r="W6" s="42">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="W6" si="6">O6</f>
         <v>0</v>
       </c>
       <c r="X6" s="42">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="X6" si="7">Q6</f>
         <v>0</v>
       </c>
       <c r="AC6" s="44"/>
@@ -12259,19 +12433,19 @@
         <v/>
       </c>
       <c r="U18" s="42">
-        <f t="shared" ref="U18:U36" si="4">D18</f>
+        <f t="shared" ref="U18:U36" si="8">D18</f>
         <v>0</v>
       </c>
       <c r="V18" s="42">
-        <f t="shared" ref="V18:V36" si="5">N18</f>
+        <f t="shared" ref="V18:V36" si="9">N18</f>
         <v>0</v>
       </c>
       <c r="W18" s="42">
-        <f t="shared" ref="W18:W36" si="6">O18</f>
+        <f t="shared" ref="W18:W36" si="10">O18</f>
         <v>0</v>
       </c>
       <c r="X18" s="42">
-        <f t="shared" ref="X18:X36" si="7">Q18</f>
+        <f t="shared" ref="X18:X36" si="11">Q18</f>
         <v>0</v>
       </c>
       <c r="AC18" s="44"/>
@@ -12284,19 +12458,19 @@
         <v/>
       </c>
       <c r="U19" s="42">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="V19" s="42">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="W19" s="42">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="X19" s="42">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AC19" s="44"/>
@@ -12309,19 +12483,19 @@
         <v/>
       </c>
       <c r="U20" s="42">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="V20" s="42">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="W20" s="42">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="X20" s="42">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AC20" s="44"/>
@@ -12334,19 +12508,19 @@
         <v/>
       </c>
       <c r="U21" s="42">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="V21" s="42">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="W21" s="42">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="X21" s="42">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AC21" s="44"/>
@@ -12359,19 +12533,19 @@
         <v/>
       </c>
       <c r="U22" s="42">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="V22" s="42">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="W22" s="42">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="X22" s="42">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AC22" s="44"/>
@@ -12384,19 +12558,19 @@
         <v/>
       </c>
       <c r="U23" s="42">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="V23" s="42">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="W23" s="42">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="X23" s="42">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AC23" s="44"/>
@@ -12409,19 +12583,19 @@
         <v/>
       </c>
       <c r="U24" s="42">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="V24" s="42">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="W24" s="42">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="X24" s="42">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AC24" s="44"/>
@@ -12434,19 +12608,19 @@
         <v/>
       </c>
       <c r="U25" s="42">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="V25" s="42">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="W25" s="42">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="X25" s="42">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AC25" s="44"/>
@@ -12459,19 +12633,19 @@
         <v/>
       </c>
       <c r="U26" s="42">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="V26" s="42">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="W26" s="42">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="X26" s="42">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AC26" s="44"/>
@@ -12484,19 +12658,19 @@
         <v/>
       </c>
       <c r="U27" s="42">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="V27" s="42">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="W27" s="42">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="X27" s="42">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AC27" s="44"/>
@@ -12509,19 +12683,19 @@
         <v/>
       </c>
       <c r="U28" s="42">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="V28" s="42">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="W28" s="42">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="X28" s="42">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AC28" s="44"/>
@@ -12534,19 +12708,19 @@
         <v/>
       </c>
       <c r="U29" s="42">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="V29" s="42">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="W29" s="42">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="X29" s="42">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AC29" s="44"/>
@@ -12559,19 +12733,19 @@
         <v/>
       </c>
       <c r="U30" s="42">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="V30" s="42">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="W30" s="42">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="X30" s="42">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AC30" s="44"/>
@@ -12584,19 +12758,19 @@
         <v/>
       </c>
       <c r="U31" s="42">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="V31" s="42">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="W31" s="42">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="X31" s="42">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AC31" s="44"/>
@@ -12609,19 +12783,19 @@
         <v/>
       </c>
       <c r="U32" s="42">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="V32" s="42">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="W32" s="42">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="X32" s="42">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AC32" s="44"/>
@@ -12634,19 +12808,19 @@
         <v/>
       </c>
       <c r="U33" s="42">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="V33" s="42">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="W33" s="42">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="X33" s="42">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AC33" s="44"/>
@@ -12659,19 +12833,19 @@
         <v/>
       </c>
       <c r="U34" s="42">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="V34" s="42">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="W34" s="42">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="X34" s="42">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -12681,19 +12855,19 @@
         <v/>
       </c>
       <c r="U35" s="42">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="V35" s="42">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="W35" s="42">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="X35" s="42">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -12703,19 +12877,19 @@
         <v/>
       </c>
       <c r="U36" s="42">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="V36" s="42">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="W36" s="42">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="X36" s="42">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -21079,7 +21253,7 @@
         <v>1</v>
       </c>
       <c r="B19" s="88" t="s">
-        <v>196</v>
+        <v>305</v>
       </c>
       <c r="C19" s="88" t="s">
         <v>62</v>

--- a/1XW_TradeBlotter_Web.xlsx
+++ b/1XW_TradeBlotter_Web.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0a601c1c2ba3d9f4/Trading/The Strategy Project/1XW Website/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="193" documentId="13_ncr:1_{6F5069F1-F0E7-4440-AA6D-4AFA11BBED1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{30A6B0A4-2787-4DFA-BF4B-184701D21F10}"/>
+  <xr:revisionPtr revIDLastSave="200" documentId="13_ncr:1_{6F5069F1-F0E7-4440-AA6D-4AFA11BBED1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9A14DF97-A68F-4AEF-A2B9-892D8DCF8FBD}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="22695" windowHeight="14476" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -116,7 +116,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="871" uniqueCount="321">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="877" uniqueCount="321">
   <si>
     <t>WEEK</t>
   </si>
@@ -293,9 +293,6 @@
   </si>
   <si>
     <t>Strike</t>
-  </si>
-  <si>
-    <t>Close</t>
   </si>
   <si>
     <t>EUR</t>
@@ -1092,6 +1089,9 @@
   </si>
   <si>
     <t>Long CC</t>
+  </si>
+  <si>
+    <t>Last</t>
   </si>
 </sst>
 </file>
@@ -1323,7 +1323,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="95">
+  <cellXfs count="96">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1561,6 +1561,9 @@
     <xf numFmtId="10" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="37" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="2" builtinId="3"/>
@@ -1753,7 +1756,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-1.1787469392599004E-4</c:v>
+                  <c:v>5.7946253060741082E-3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1907,7 +1910,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-1.1787469392599004E-4</c:v>
+                  <c:v>5.7946253060741082E-3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2298,7 +2301,7 @@
                   <c:v>1000</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>999.88212530607404</c:v>
+                  <c:v>1005.7946253060741</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2702,10 +2705,10 @@
                 <c:formatCode>0.00%</c:formatCode>
                 <c:ptCount val="52"/>
                 <c:pt idx="0">
-                  <c:v>-1.1787469392599004E-4</c:v>
+                  <c:v>3.184625306074107E-3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-1.1787469392599004E-4</c:v>
+                  <c:v>5.7946253060741082E-3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3352,7 +3355,7 @@
   <sheetData>
     <row r="1" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B1" s="32" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C1" s="79">
         <v>46090</v>
@@ -3360,13 +3363,13 @@
     </row>
     <row r="2" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B2" s="32" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C2" s="37" t="s">
-        <v>59</v>
+        <v>320</v>
       </c>
       <c r="E2" s="47" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F2" s="47" t="s">
         <v>6</v>
@@ -3376,17 +3379,17 @@
     </row>
     <row r="3" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B3" s="32" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C3" s="28">
         <f ca="1">OFFSET(NAV!B1,MATCH(C1,NAV!B:B,1),8)</f>
-        <v>999882.12530607404</v>
+        <v>1005794.625306074</v>
       </c>
       <c r="E3" s="47" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F3" s="47" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="G3" s="47"/>
       <c r="H3" s="28"/>
@@ -3397,29 +3400,29 @@
       </c>
       <c r="C4" s="28">
         <f>SUM(N18:N1012)</f>
-        <v>-117.87469392600178</v>
+        <v>5794.6253060739982</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="47" t="s">
         <v>20</v>
       </c>
       <c r="F4" s="47" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G4" s="47"/>
       <c r="H4" s="28"/>
     </row>
     <row r="5" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B5" s="32" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C5" s="3">
         <f ca="1">OFFSET(NAV!B1,MATCH(C1,NAV!B:B,1),11)</f>
-        <v>-1.1787469392599004E-4</v>
+        <v>5.7946253060741082E-3</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="47" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F5" s="47" t="s">
         <v>53</v>
@@ -3430,11 +3433,11 @@
     </row>
     <row r="6" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B6" s="32" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C6" s="3">
         <f ca="1">OFFSET(NAV!B1,MATCH(C1,NAV!B:B,1),12)</f>
-        <v>-1.1787469392599004E-4</v>
+        <v>5.7946253060741082E-3</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="47"/>
@@ -3445,7 +3448,7 @@
     </row>
     <row r="7" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B7" s="32" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C7" s="28">
         <f>Cash_Mgmt!H13</f>
@@ -3463,15 +3466,15 @@
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B8" s="32" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C8" s="28">
         <f>C4+C7</f>
-        <v>-117.87469392600178</v>
+        <v>5794.6253060739982</v>
       </c>
       <c r="D8" s="3">
         <f ca="1">C5+D7</f>
-        <v>-1.1787469392599004E-4</v>
+        <v>5.7946253060741082E-3</v>
       </c>
       <c r="G8" s="47"/>
       <c r="H8" s="51"/>
@@ -3479,15 +3482,15 @@
     </row>
     <row r="9" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B9" s="32" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C9" s="28">
         <f t="array" ref="C9">SUM((F19:F112="Futures")*(M19:M112))</f>
-        <v>96900</v>
+        <v>99660</v>
       </c>
       <c r="D9" s="3">
         <f ca="1">C9/$C$3</f>
-        <v>9.6911423404371713E-2</v>
+        <v>9.9085834714688792E-2</v>
       </c>
       <c r="E9" s="47"/>
       <c r="F9" s="47"/>
@@ -3497,7 +3500,7 @@
     </row>
     <row r="10" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B10" s="32" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C10" s="28">
         <f t="array" ref="C10">SUM((F19:F1012="Call")*(M19:M1012))</f>
@@ -3511,7 +3514,7 @@
     </row>
     <row r="11" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B11" s="32" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C11" s="28">
         <f t="array" ref="C11">SUM((F19:F212="Put")*(M19:M212))</f>
@@ -3524,7 +3527,7 @@
     </row>
     <row r="12" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B12" s="32" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C12" s="28" cm="1">
         <f t="array" ref="C12">SUM((PLB!G4:G999="O")*(PLB!E4:E999))</f>
@@ -3532,40 +3535,40 @@
       </c>
       <c r="D12" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>1.9502298827505146E-2</v>
+        <v>1.938765579908119E-2</v>
       </c>
     </row>
     <row r="13" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B13" s="32" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C13" s="28">
         <f t="array" ref="C13">SUM((PLB!G4:G999="O")*(PLB!D4:D999))</f>
-        <v>-117.87469392600178</v>
+        <v>5794.6253060739982</v>
       </c>
       <c r="D13" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>-1.1788859000746627E-4</v>
+        <v>5.7612410727593934E-3</v>
       </c>
       <c r="F13" s="59"/>
       <c r="G13" s="59"/>
     </row>
     <row r="14" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B14" s="32" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C14" s="28">
         <f>C12+C13</f>
-        <v>19382.125306073998</v>
+        <v>25294.625306073998</v>
       </c>
       <c r="D14" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>1.9384410237497679E-2</v>
+        <v>2.5148896871840583E-2</v>
       </c>
     </row>
     <row r="17" spans="2:28" x14ac:dyDescent="0.4">
       <c r="B17" s="38" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>0</v>
@@ -3574,16 +3577,16 @@
         <v>1</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F17" s="4" t="s">
         <v>2</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="I17" s="4" t="s">
         <v>10</v>
@@ -3598,7 +3601,7 @@
         <v>52</v>
       </c>
       <c r="M17" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="N17" s="4" t="s">
         <v>55</v>
@@ -3607,45 +3610,45 @@
         <v>14</v>
       </c>
       <c r="P17" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q17" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="R17" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="Q17" s="4" t="s">
+      <c r="S17" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="R17" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="S17" s="4" t="s">
+      <c r="T17" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="U17" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="T17" s="4" t="s">
+      <c r="V17" s="4" t="s">
         <v>122</v>
-      </c>
-      <c r="U17" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="V17" s="4" t="s">
-        <v>123</v>
       </c>
       <c r="W17" s="32"/>
       <c r="X17" s="33" t="s">
+        <v>109</v>
+      </c>
+      <c r="Y17" s="33" t="s">
+        <v>108</v>
+      </c>
+      <c r="Z17" s="33" t="s">
         <v>110</v>
-      </c>
-      <c r="Y17" s="33" t="s">
-        <v>109</v>
-      </c>
-      <c r="Z17" s="33" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="18" spans="2:28" x14ac:dyDescent="0.4">
       <c r="B18" s="9" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C18" s="12"/>
       <c r="D18" s="12"/>
       <c r="E18" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F18" s="12"/>
       <c r="G18" s="12"/>
@@ -3655,7 +3658,7 @@
       <c r="K18" s="12"/>
       <c r="L18" s="12"/>
       <c r="M18" s="12"/>
-      <c r="N18" s="28">
+      <c r="N18" s="95">
         <f>Cash_Mgmt!G13</f>
         <v>0</v>
       </c>
@@ -3674,19 +3677,19 @@
     </row>
     <row r="19" spans="2:28" x14ac:dyDescent="0.4">
       <c r="B19" s="9" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C19" s="10">
         <v>1</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F19" s="10" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="G19" s="28">
         <f>VLOOKUP(D19,Multiplier!B:I,8,0)</f>
@@ -3709,15 +3712,15 @@
       </c>
       <c r="L19" s="29">
         <f t="shared" ref="L19" si="2">IF(I19=0,IF(H19&gt;0,X19,Y19),Z19)</f>
-        <v>1964.3</v>
+        <v>2030.35</v>
       </c>
       <c r="M19" s="28">
         <f t="shared" ref="M19" si="3">I19*J19*L19</f>
-        <v>98215</v>
-      </c>
-      <c r="N19" s="28">
+        <v>101517.5</v>
+      </c>
+      <c r="N19" s="95">
         <f t="array" ref="N19">-SUM((Trades!T$2:T$9999=Blotter!C19)*(Trades!U$2:U$9999=Blotter!B19)*(Trades!V$2:V$9999)*(Trades!W$2:W$9999))*J19+SUM((Trades!T$2:T$9999=Blotter!C19)*(Trades!U$2:U$9999=Blotter!B19)*(Trades!X$2:X$9999))+(L19*I19)*J19</f>
-        <v>-117.87469392600178</v>
+        <v>3184.6253060739982</v>
       </c>
       <c r="O19" s="29">
         <f>VLOOKUP(D19,Multiplier!B:H,3,0)</f>
@@ -3733,11 +3736,11 @@
       </c>
       <c r="S19" s="29">
         <f>IF(OR(F19="Futures",F19="Spot"),IF(I19=0,0,IF(I19&gt;0,L19-O19,L19+O19)),0)</f>
-        <v>1824.3</v>
+        <v>1890.35</v>
       </c>
       <c r="T19" s="3">
         <f t="shared" ref="T19" si="5">IF(S19&gt;0,IF(ISNUMBER(S19/L19-1),S19/L19-1,0),0)</f>
-        <v>-7.1272208929389569E-2</v>
+        <v>-6.8953628684709556E-2</v>
       </c>
       <c r="U19" s="29">
         <f>IF(OR(F19="Futures",F19="Spot"),IF(I19=0,0,IF(I19&gt;0,K19-P19,K19+P19)),0)</f>
@@ -3745,7 +3748,7 @@
       </c>
       <c r="V19" s="3">
         <f t="shared" ref="V19" si="6">IF(U19&gt;0,IF(ISNUMBER(U19/L19-1),U19/L19-1,0),0)</f>
-        <v>-0.10570814342080126</v>
+        <v>-0.13480065314920087</v>
       </c>
       <c r="X19" s="34">
         <f t="array" ref="X19">IF(ISNUMBER(SUM((Trades!T$2:T$9999=Blotter!C19)*(Trades!U$2:U$9999=Blotter!B19)*(Trades!W$2:W$9999)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0))/SUM((Trades!T$2:T$9999=Blotter!C19)*(Trades!U$2:U$9999=Blotter!B19)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0))),SUM((Trades!T$2:T$9999=Blotter!C19)*(Trades!U$2:U$9999=Blotter!B19)*(Trades!W$2:W$9999)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0))/SUM((Trades!T$2:T$9999=Blotter!C19)*(Trades!U$2:U$9999=Blotter!B19)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0)),0)</f>
@@ -3757,13 +3760,13 @@
       </c>
       <c r="Z19" s="35">
         <f>IF(C$2="Last",IF(ISNUMBER(VLOOKUP(B19,Prices!A:L,8,0)),VLOOKUP(B19,Prices!A:L,8,0),0),IF(ISNUMBER(VLOOKUP(B19,Prices!A:L,12,0)),VLOOKUP(B19,Prices!A:L,12,0),0))</f>
-        <v>1964.3</v>
+        <v>2030.35</v>
       </c>
       <c r="AB19" s="29"/>
     </row>
     <row r="20" spans="2:28" x14ac:dyDescent="0.4">
       <c r="B20" s="9" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C20" s="10">
         <v>2</v>
@@ -3772,7 +3775,7 @@
         <v>34</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F20" s="10" t="s">
         <v>6</v>
@@ -3794,19 +3797,19 @@
       </c>
       <c r="K20" s="29">
         <f t="shared" ref="K20" si="7">L20-N20/(H20*J20)</f>
-        <v>3230</v>
+        <v>3235</v>
       </c>
       <c r="L20" s="29">
         <f t="shared" ref="L20" si="8">IF(I20=0,IF(H20&gt;0,X20,Y20),Z20)</f>
-        <v>3230</v>
+        <v>3322</v>
       </c>
       <c r="M20" s="28">
         <f t="shared" ref="M20" si="9">I20*J20*L20</f>
-        <v>96900</v>
-      </c>
-      <c r="N20" s="28">
+        <v>99660</v>
+      </c>
+      <c r="N20" s="95">
         <f t="array" ref="N20">-SUM((Trades!T$2:T$9999=Blotter!C20)*(Trades!U$2:U$9999=Blotter!B20)*(Trades!V$2:V$9999)*(Trades!W$2:W$9999))*J20+SUM((Trades!T$2:T$9999=Blotter!C20)*(Trades!U$2:U$9999=Blotter!B20)*(Trades!X$2:X$9999))+(L20*I20)*J20</f>
-        <v>0</v>
+        <v>2610</v>
       </c>
       <c r="O20" s="29">
         <f>VLOOKUP(D20,Multiplier!B:H,3,0)</f>
@@ -3822,19 +3825,19 @@
       </c>
       <c r="S20" s="29">
         <f>IF(OR(F20="Futures",F20="Spot"),IF(I20=0,0,IF(I20&gt;0,L20-O20,L20+O20)),0)</f>
-        <v>3025</v>
+        <v>3117</v>
       </c>
       <c r="T20" s="3">
         <f t="shared" ref="T20" si="11">IF(S20&gt;0,IF(ISNUMBER(S20/L20-1),S20/L20-1,0),0)</f>
-        <v>-6.3467492260061875E-2</v>
+        <v>-6.1709813365442456E-2</v>
       </c>
       <c r="U20" s="29">
         <f t="shared" ref="U20" si="12">IF(OR(F20="Futures",F20="Stocks"),IF(I20=0,0,IF(I20&gt;0,K20-P20,K20+P20)),0)</f>
-        <v>2930</v>
+        <v>2935</v>
       </c>
       <c r="V20" s="3">
         <f t="shared" ref="V20" si="13">IF(U20&gt;0,IF(ISNUMBER(U20/L20-1),U20/L20-1,0),0)</f>
-        <v>-9.2879256965944235E-2</v>
+        <v>-0.11649608669476219</v>
       </c>
       <c r="X20" s="34">
         <f t="array" ref="X20">IF(ISNUMBER(SUM((Trades!T$2:T$9999=Blotter!C20)*(Trades!U$2:U$9999=Blotter!B20)*(Trades!W$2:W$9999)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0))/SUM((Trades!T$2:T$9999=Blotter!C20)*(Trades!U$2:U$9999=Blotter!B20)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0))),SUM((Trades!T$2:T$9999=Blotter!C20)*(Trades!U$2:U$9999=Blotter!B20)*(Trades!W$2:W$9999)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0))/SUM((Trades!T$2:T$9999=Blotter!C20)*(Trades!U$2:U$9999=Blotter!B20)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0)),0)</f>
@@ -3842,11 +3845,11 @@
       </c>
       <c r="Y20" s="34">
         <f t="array" ref="Y20">IF(ISNUMBER(SUM((Trades!T$2:T$9999=Blotter!C20)*(Trades!U$2:U$9999=Blotter!B20)*(Trades!W$2:W$9999)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&gt;0))/SUM((Trades!T$2:T$9999=Blotter!C20)*(Trades!U$2:U$9999=Blotter!B20)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&gt;0))),SUM((Trades!T$2:T$9999=Blotter!C20)*(Trades!U$2:U$9999=Blotter!B20)*(Trades!W$2:W$9999)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&gt;0))/SUM((Trades!T$2:T$9999=Blotter!C20)*(Trades!U$2:U$9999=Blotter!B20)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&gt;0)),0)</f>
-        <v>3230</v>
+        <v>3235</v>
       </c>
       <c r="Z20" s="35">
         <f>IF(C$2="Last",IF(ISNUMBER(VLOOKUP(B20,Prices!A:L,8,0)),VLOOKUP(B20,Prices!A:L,8,0),0),IF(ISNUMBER(VLOOKUP(B20,Prices!A:L,12,0)),VLOOKUP(B20,Prices!A:L,12,0),0))</f>
-        <v>3230</v>
+        <v>3322</v>
       </c>
       <c r="AB20" s="29"/>
     </row>
@@ -5532,73 +5535,73 @@
   <sheetData>
     <row r="1" spans="1:32" x14ac:dyDescent="0.4">
       <c r="A1" s="86" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B1" s="86" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C1" s="86" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D1" s="86" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E1" s="86" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F1" s="86" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G1" s="86" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H1" s="86" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="I1" s="86" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="J1" s="86" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="K1" s="86" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="L1" s="86" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="M1" s="86" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="N1" s="86" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="O1" s="86" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="P1" s="86" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="Q1" s="86" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="R1" s="86" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="S1" s="86" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="T1" s="86" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="U1" s="86" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="V1" s="86" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="W1" s="86" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="X1" s="84"/>
       <c r="Y1" s="84"/>
@@ -5612,37 +5615,37 @@
     </row>
     <row r="2" spans="1:32" x14ac:dyDescent="0.4">
       <c r="A2" s="81" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B2" s="81">
         <v>649180678</v>
       </c>
       <c r="C2" s="81" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D2" s="81" t="s">
         <v>21</v>
       </c>
       <c r="E2" s="81" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="F2" s="81" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G2" s="81" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H2" s="91">
-        <v>6694.5</v>
+        <v>6842.5</v>
       </c>
       <c r="I2" s="91">
-        <v>6693.5</v>
+        <v>6841.75</v>
       </c>
       <c r="J2" s="91">
-        <v>6694.5</v>
+        <v>6842.75</v>
       </c>
       <c r="K2" s="91">
-        <v>6694</v>
+        <v>6842.25</v>
       </c>
       <c r="L2" s="91">
         <v>6794</v>
@@ -5651,13 +5654,13 @@
         <v>6742.5</v>
       </c>
       <c r="N2" s="91">
-        <v>6742.5</v>
+        <v>6869.75</v>
       </c>
       <c r="O2" s="91">
         <v>6631.5</v>
       </c>
       <c r="P2" s="91">
-        <v>10075</v>
+        <v>48568</v>
       </c>
       <c r="Q2" s="91"/>
       <c r="R2" s="91"/>
@@ -5665,10 +5668,10 @@
       <c r="T2" s="91"/>
       <c r="U2" s="91"/>
       <c r="V2" s="85">
-        <v>46090.384814814817</v>
+        <v>46090.869606481479</v>
       </c>
       <c r="W2" s="81" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="X2" s="81"/>
       <c r="Y2" s="81"/>
@@ -5676,37 +5679,37 @@
     </row>
     <row r="3" spans="1:32" x14ac:dyDescent="0.4">
       <c r="A3" s="81" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B3" s="81">
         <v>750150196</v>
       </c>
       <c r="C3" s="81" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D3" s="81" t="s">
         <v>22</v>
       </c>
       <c r="E3" s="81" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F3" s="81" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G3" s="81" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H3" s="91">
-        <v>24491.25</v>
+        <v>25164.75</v>
       </c>
       <c r="I3" s="91">
-        <v>24478.25</v>
+        <v>25159.25</v>
       </c>
       <c r="J3" s="91">
-        <v>24484.25</v>
+        <v>25163.75</v>
       </c>
       <c r="K3" s="91">
-        <v>24481.25</v>
+        <v>25161.5</v>
       </c>
       <c r="L3" s="91">
         <v>24883.25</v>
@@ -5715,13 +5718,13 @@
         <v>24764.75</v>
       </c>
       <c r="N3" s="91">
-        <v>24764.75</v>
+        <v>25271.25</v>
       </c>
       <c r="O3" s="91">
         <v>24212.25</v>
       </c>
       <c r="P3" s="91">
-        <v>2804</v>
+        <v>9846</v>
       </c>
       <c r="Q3" s="91"/>
       <c r="R3" s="91"/>
@@ -5729,10 +5732,10 @@
       <c r="T3" s="91"/>
       <c r="U3" s="91"/>
       <c r="V3" s="85">
-        <v>46090.384814814817</v>
+        <v>46090.869606481479</v>
       </c>
       <c r="W3" s="81" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="X3" s="81"/>
       <c r="Y3" s="81"/>
@@ -5740,37 +5743,37 @@
     </row>
     <row r="4" spans="1:32" x14ac:dyDescent="0.4">
       <c r="A4" s="81" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B4" s="81">
         <v>770561234</v>
       </c>
       <c r="C4" s="81" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D4" s="81" t="s">
         <v>23</v>
       </c>
       <c r="E4" s="81" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F4" s="81" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G4" s="81" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H4" s="91">
-        <v>2476.9</v>
+        <v>2569.4</v>
       </c>
       <c r="I4" s="91">
-        <v>2474.6999999999998</v>
+        <v>2569.5</v>
       </c>
       <c r="J4" s="91">
-        <v>2476</v>
+        <v>2570.1999999999998</v>
       </c>
       <c r="K4" s="91">
-        <v>2475.35</v>
+        <v>2569.85</v>
       </c>
       <c r="L4" s="91">
         <v>2543.4</v>
@@ -5779,13 +5782,13 @@
         <v>2524.9</v>
       </c>
       <c r="N4" s="91">
-        <v>2524.9</v>
+        <v>2580.5</v>
       </c>
       <c r="O4" s="91">
         <v>2434</v>
       </c>
       <c r="P4" s="91">
-        <v>1238</v>
+        <v>4749</v>
       </c>
       <c r="Q4" s="91"/>
       <c r="R4" s="91"/>
@@ -5793,10 +5796,10 @@
       <c r="T4" s="91"/>
       <c r="U4" s="91"/>
       <c r="V4" s="85">
-        <v>46090.384814814817</v>
+        <v>46090.869606481479</v>
       </c>
       <c r="W4" s="81" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="X4" s="81"/>
       <c r="Y4" s="81"/>
@@ -5804,37 +5807,37 @@
     </row>
     <row r="5" spans="1:32" x14ac:dyDescent="0.4">
       <c r="A5" s="81" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B5" s="81">
         <v>638120304</v>
       </c>
       <c r="C5" s="81" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D5" s="81" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E5" s="81" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F5" s="81" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G5" s="81" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H5" s="91">
-        <v>5495</v>
+        <v>5728</v>
       </c>
       <c r="I5" s="91">
-        <v>5501</v>
+        <v>5732</v>
       </c>
       <c r="J5" s="91">
-        <v>5504</v>
+        <v>5736</v>
       </c>
       <c r="K5" s="91">
-        <v>5502.5</v>
+        <v>5734</v>
       </c>
       <c r="L5" s="91">
         <v>5645</v>
@@ -5843,13 +5846,13 @@
         <v>5545</v>
       </c>
       <c r="N5" s="91">
-        <v>5545</v>
+        <v>5759</v>
       </c>
       <c r="O5" s="91">
         <v>5463</v>
       </c>
       <c r="P5" s="91">
-        <v>1994</v>
+        <v>6993</v>
       </c>
       <c r="Q5" s="91"/>
       <c r="R5" s="91"/>
@@ -5857,10 +5860,10 @@
       <c r="T5" s="91"/>
       <c r="U5" s="91"/>
       <c r="V5" s="85">
-        <v>46090.384814814817</v>
+        <v>46090.869606481479</v>
       </c>
       <c r="W5" s="81" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="X5" s="81"/>
       <c r="Y5" s="81"/>
@@ -5868,37 +5871,37 @@
     </row>
     <row r="6" spans="1:32" x14ac:dyDescent="0.4">
       <c r="A6" s="81" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B6" s="81">
         <v>638120262</v>
       </c>
       <c r="C6" s="81" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D6" s="81" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E6" s="81" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F6" s="81" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G6" s="81" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H6" s="91">
-        <v>23227</v>
+        <v>24017</v>
       </c>
       <c r="I6" s="91">
-        <v>23184</v>
+        <v>24023</v>
       </c>
       <c r="J6" s="91">
-        <v>23242</v>
+        <v>24045</v>
       </c>
       <c r="K6" s="91">
-        <v>23213</v>
+        <v>24034</v>
       </c>
       <c r="L6" s="91">
         <v>23768</v>
@@ -5907,13 +5910,13 @@
         <v>23369</v>
       </c>
       <c r="N6" s="91">
-        <v>23369</v>
+        <v>24160</v>
       </c>
       <c r="O6" s="91">
         <v>22955</v>
       </c>
       <c r="P6" s="91">
-        <v>58</v>
+        <v>144</v>
       </c>
       <c r="Q6" s="91"/>
       <c r="R6" s="91"/>
@@ -5921,10 +5924,10 @@
       <c r="T6" s="91"/>
       <c r="U6" s="91"/>
       <c r="V6" s="85">
-        <v>46090.384814814817</v>
+        <v>46090.869606481479</v>
       </c>
       <c r="W6" s="81" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="X6" s="81"/>
       <c r="Y6" s="81"/>
@@ -5932,37 +5935,37 @@
     </row>
     <row r="7" spans="1:32" x14ac:dyDescent="0.4">
       <c r="A7" s="1" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B7" s="1">
         <v>635680486</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H7" s="93">
-        <v>52490</v>
+        <v>54405</v>
       </c>
       <c r="I7" s="93">
-        <v>52135</v>
+        <v>54390</v>
       </c>
       <c r="J7" s="93">
-        <v>52185</v>
+        <v>54410</v>
       </c>
       <c r="K7" s="93">
-        <v>52160</v>
+        <v>54400</v>
       </c>
       <c r="L7" s="93">
         <v>53800</v>
@@ -5971,13 +5974,13 @@
         <v>53130</v>
       </c>
       <c r="N7" s="93">
-        <v>53130</v>
+        <v>54710</v>
       </c>
       <c r="O7" s="93">
         <v>51025</v>
       </c>
       <c r="P7" s="93">
-        <v>4322</v>
+        <v>12345</v>
       </c>
       <c r="Q7" s="93"/>
       <c r="R7" s="93"/>
@@ -5985,45 +5988,45 @@
       <c r="T7" s="93"/>
       <c r="U7" s="93"/>
       <c r="V7" s="92">
-        <v>46090.384814814817</v>
+        <v>46090.869606481479</v>
       </c>
       <c r="W7" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="8" spans="1:32" x14ac:dyDescent="0.4">
       <c r="A8" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B8" s="1">
         <v>304037436</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H8" s="93">
-        <v>102.13</v>
+        <v>86</v>
       </c>
       <c r="I8" s="93">
-        <v>102.11</v>
+        <v>85.91</v>
       </c>
       <c r="J8" s="93">
-        <v>102.16</v>
+        <v>86.04</v>
       </c>
       <c r="K8" s="93">
-        <v>102.13499999999999</v>
+        <v>85.974999999999994</v>
       </c>
       <c r="L8" s="93">
         <v>90.9</v>
@@ -6035,10 +6038,10 @@
         <v>119.48</v>
       </c>
       <c r="O8" s="93">
-        <v>98</v>
+        <v>81.19</v>
       </c>
       <c r="P8" s="93">
-        <v>429857</v>
+        <v>1016579</v>
       </c>
       <c r="Q8" s="93"/>
       <c r="R8" s="93"/>
@@ -6046,45 +6049,45 @@
       <c r="T8" s="93"/>
       <c r="U8" s="93"/>
       <c r="V8" s="92">
-        <v>46090.384814814817</v>
+        <v>46090.869606481479</v>
       </c>
       <c r="W8" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="9" spans="1:32" x14ac:dyDescent="0.4">
       <c r="A9" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B9" s="1">
         <v>269460069</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H9" s="93">
-        <v>3.4980000000000002</v>
+        <v>3.214</v>
       </c>
       <c r="I9" s="93">
-        <v>3.4950000000000001</v>
+        <v>3.214</v>
       </c>
       <c r="J9" s="93">
-        <v>3.4990000000000001</v>
+        <v>3.2170000000000001</v>
       </c>
       <c r="K9" s="93">
-        <v>3.4969999999999999</v>
+        <v>3.2155</v>
       </c>
       <c r="L9" s="93">
         <v>3.351</v>
@@ -6096,10 +6099,10 @@
         <v>3.6219999999999999</v>
       </c>
       <c r="O9" s="93">
-        <v>3.4289999999999998</v>
+        <v>3.2050000000000001</v>
       </c>
       <c r="P9" s="93">
-        <v>12611</v>
+        <v>54695</v>
       </c>
       <c r="Q9" s="93"/>
       <c r="R9" s="93"/>
@@ -6107,45 +6110,45 @@
       <c r="T9" s="93"/>
       <c r="U9" s="93"/>
       <c r="V9" s="92">
-        <v>46090.384814814817</v>
+        <v>46090.869606481479</v>
       </c>
       <c r="W9" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="10" spans="1:32" x14ac:dyDescent="0.4">
       <c r="A10" s="1" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B10" s="1">
         <v>600696533</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H10" s="93">
-        <v>2.8633000000000002</v>
+        <v>2.5518000000000001</v>
       </c>
       <c r="I10" s="93">
-        <v>2.8628</v>
+        <v>2.5472000000000001</v>
       </c>
       <c r="J10" s="93">
-        <v>2.8645999999999998</v>
+        <v>2.5529999999999999</v>
       </c>
       <c r="K10" s="93">
-        <v>2.8636999999999997</v>
+        <v>2.5501</v>
       </c>
       <c r="L10" s="93">
         <v>2.6303999999999998</v>
@@ -6157,10 +6160,10 @@
         <v>3.0407000000000002</v>
       </c>
       <c r="O10" s="93">
-        <v>2.6825000000000001</v>
+        <v>2.4373999999999998</v>
       </c>
       <c r="P10" s="93">
-        <v>43129</v>
+        <v>120434</v>
       </c>
       <c r="Q10" s="93"/>
       <c r="R10" s="93"/>
@@ -6168,45 +6171,45 @@
       <c r="T10" s="93"/>
       <c r="U10" s="93"/>
       <c r="V10" s="92">
-        <v>46090.384814814817</v>
+        <v>46090.869606481479</v>
       </c>
       <c r="W10" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="11" spans="1:32" x14ac:dyDescent="0.4">
       <c r="A11" s="1" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B11" s="1">
         <v>430360630</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>26</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H11" s="93">
-        <v>5152.7</v>
+        <v>5181.5</v>
       </c>
       <c r="I11" s="93">
-        <v>5155</v>
+        <v>5181.3999999999996</v>
       </c>
       <c r="J11" s="93">
-        <v>5155.7</v>
+        <v>5182.1000000000004</v>
       </c>
       <c r="K11" s="93">
-        <v>5155.3500000000004</v>
+        <v>5181.75</v>
       </c>
       <c r="L11" s="93">
         <v>5197.8999999999996</v>
@@ -6221,7 +6224,7 @@
         <v>5060</v>
       </c>
       <c r="P11" s="93">
-        <v>5510</v>
+        <v>31318</v>
       </c>
       <c r="Q11" s="93"/>
       <c r="R11" s="93"/>
@@ -6229,45 +6232,45 @@
       <c r="T11" s="93"/>
       <c r="U11" s="93"/>
       <c r="V11" s="92">
-        <v>46090.384814814817</v>
+        <v>46090.869606481479</v>
       </c>
       <c r="W11" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="12" spans="1:32" x14ac:dyDescent="0.4">
       <c r="A12" s="1" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B12" s="1">
         <v>760200596</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>27</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H12" s="93">
-        <v>84.045000000000002</v>
+        <v>86.76</v>
       </c>
       <c r="I12" s="93">
-        <v>84.14</v>
+        <v>86.644999999999996</v>
       </c>
       <c r="J12" s="93">
-        <v>84.204999999999998</v>
+        <v>86.69</v>
       </c>
       <c r="K12" s="93">
-        <v>84.172499999999999</v>
+        <v>86.66749999999999</v>
       </c>
       <c r="L12" s="93">
         <v>84.62</v>
@@ -6276,13 +6279,13 @@
         <v>84.805000000000007</v>
       </c>
       <c r="N12" s="93">
-        <v>85.155000000000001</v>
+        <v>87.185000000000002</v>
       </c>
       <c r="O12" s="93">
         <v>80</v>
       </c>
       <c r="P12" s="93">
-        <v>268</v>
+        <v>331</v>
       </c>
       <c r="Q12" s="93"/>
       <c r="R12" s="93"/>
@@ -6290,45 +6293,45 @@
       <c r="T12" s="93"/>
       <c r="U12" s="93"/>
       <c r="V12" s="92">
-        <v>46090.384814814817</v>
+        <v>46090.869606481479</v>
       </c>
       <c r="W12" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="13" spans="1:32" x14ac:dyDescent="0.4">
       <c r="A13" s="1" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B13" s="1">
         <v>712565973</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>25</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H13" s="93">
-        <v>5.7809999999999997</v>
+        <v>5.8784999999999998</v>
       </c>
       <c r="I13" s="93">
-        <v>5.7765000000000004</v>
+        <v>5.8985000000000003</v>
       </c>
       <c r="J13" s="93">
-        <v>5.7785000000000002</v>
+        <v>5.9</v>
       </c>
       <c r="K13" s="93">
-        <v>5.7774999999999999</v>
+        <v>5.8992500000000003</v>
       </c>
       <c r="L13" s="93">
         <v>5.835</v>
@@ -6337,13 +6340,13 @@
         <v>5.8</v>
       </c>
       <c r="N13" s="93">
-        <v>5.8</v>
+        <v>5.8784999999999998</v>
       </c>
       <c r="O13" s="93">
         <v>5.6784999999999997</v>
       </c>
       <c r="P13" s="93">
-        <v>111</v>
+        <v>547</v>
       </c>
       <c r="Q13" s="93"/>
       <c r="R13" s="93"/>
@@ -6351,45 +6354,45 @@
       <c r="T13" s="93"/>
       <c r="U13" s="93"/>
       <c r="V13" s="92">
-        <v>46090.384814814817</v>
+        <v>46090.869606481479</v>
       </c>
       <c r="W13" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="14" spans="1:32" x14ac:dyDescent="0.4">
       <c r="A14" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B14" s="1">
         <v>671574022</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>28</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H14" s="93">
-        <v>468</v>
+        <v>453.25</v>
       </c>
       <c r="I14" s="93">
-        <v>467.75</v>
+        <v>-100</v>
       </c>
       <c r="J14" s="93">
-        <v>468</v>
+        <v>-100</v>
       </c>
       <c r="K14" s="93">
-        <v>467.875</v>
+        <v>-100</v>
       </c>
       <c r="L14" s="93">
         <v>460.5</v>
@@ -6401,10 +6404,10 @@
         <v>476</v>
       </c>
       <c r="O14" s="93">
-        <v>463</v>
+        <v>453</v>
       </c>
       <c r="P14" s="93">
-        <v>121260</v>
+        <v>411655</v>
       </c>
       <c r="Q14" s="93"/>
       <c r="R14" s="93"/>
@@ -6412,45 +6415,45 @@
       <c r="T14" s="93"/>
       <c r="U14" s="93"/>
       <c r="V14" s="92">
-        <v>46090.384814814817</v>
+        <v>46090.869606481479</v>
       </c>
       <c r="W14" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="15" spans="1:32" x14ac:dyDescent="0.4">
       <c r="A15" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B15" s="1">
         <v>642254817</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>29</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H15" s="93">
-        <v>622.75</v>
+        <v>602.5</v>
       </c>
       <c r="I15" s="93">
-        <v>622.75</v>
+        <v>-100</v>
       </c>
       <c r="J15" s="93">
-        <v>623</v>
+        <v>-100</v>
       </c>
       <c r="K15" s="93">
-        <v>622.875</v>
+        <v>-100</v>
       </c>
       <c r="L15" s="93">
         <v>616.75</v>
@@ -6462,10 +6465,10 @@
         <v>641.75</v>
       </c>
       <c r="O15" s="93">
-        <v>622</v>
+        <v>601.25</v>
       </c>
       <c r="P15" s="93">
-        <v>34661</v>
+        <v>159696</v>
       </c>
       <c r="Q15" s="93"/>
       <c r="R15" s="93"/>
@@ -6473,45 +6476,45 @@
       <c r="T15" s="93"/>
       <c r="U15" s="93"/>
       <c r="V15" s="92">
-        <v>46090.384814814817</v>
+        <v>46090.869606481479</v>
       </c>
       <c r="W15" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="16" spans="1:32" x14ac:dyDescent="0.4">
       <c r="A16" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B16" s="1">
         <v>665643569</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>31</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H16" s="93">
-        <v>1216.5</v>
+        <v>1196.25</v>
       </c>
       <c r="I16" s="93">
-        <v>1216.5</v>
+        <v>-100</v>
       </c>
       <c r="J16" s="93">
-        <v>1216.75</v>
+        <v>-100</v>
       </c>
       <c r="K16" s="93">
-        <v>1216.625</v>
+        <v>-100</v>
       </c>
       <c r="L16" s="93">
         <v>1200.75</v>
@@ -6523,10 +6526,10 @@
         <v>1233.75</v>
       </c>
       <c r="O16" s="93">
-        <v>1210.5</v>
+        <v>1193</v>
       </c>
       <c r="P16" s="93">
-        <v>62655</v>
+        <v>185177</v>
       </c>
       <c r="Q16" s="93"/>
       <c r="R16" s="93"/>
@@ -6534,36 +6537,36 @@
       <c r="T16" s="93"/>
       <c r="U16" s="93"/>
       <c r="V16" s="92">
-        <v>46090.384814814817</v>
+        <v>46090.869606481479</v>
       </c>
       <c r="W16" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="17" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A17" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B17" s="1">
         <v>634760175</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>32</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H17" s="93">
-        <v>0</v>
+        <v>14.62</v>
       </c>
       <c r="I17" s="93">
         <v>-100</v>
@@ -6578,12 +6581,16 @@
         <v>14.1</v>
       </c>
       <c r="M17" s="93">
-        <v>0</v>
-      </c>
-      <c r="N17" s="93"/>
-      <c r="O17" s="93"/>
+        <v>14.26</v>
+      </c>
+      <c r="N17" s="93">
+        <v>14.64</v>
+      </c>
+      <c r="O17" s="93">
+        <v>14.25</v>
+      </c>
       <c r="P17" s="93">
-        <v>0</v>
+        <v>149066</v>
       </c>
       <c r="Q17" s="93"/>
       <c r="R17" s="93"/>
@@ -6591,36 +6598,36 @@
       <c r="T17" s="93"/>
       <c r="U17" s="93"/>
       <c r="V17" s="92">
-        <v>46090.384814814817</v>
+        <v>46090.869606481479</v>
       </c>
       <c r="W17" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="18" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A18" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B18" s="1">
         <v>634760204</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>33</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H18" s="93">
-        <v>0</v>
+        <v>297.10000000000002</v>
       </c>
       <c r="I18" s="93">
         <v>-100</v>
@@ -6635,12 +6642,16 @@
         <v>293.3</v>
       </c>
       <c r="M18" s="93">
-        <v>0</v>
-      </c>
-      <c r="N18" s="93"/>
-      <c r="O18" s="93"/>
+        <v>296.95</v>
+      </c>
+      <c r="N18" s="93">
+        <v>301.64999999999998</v>
+      </c>
+      <c r="O18" s="93">
+        <v>293.14999999999998</v>
+      </c>
       <c r="P18" s="93">
-        <v>0</v>
+        <v>16842</v>
       </c>
       <c r="Q18" s="93"/>
       <c r="R18" s="93"/>
@@ -6648,36 +6659,36 @@
       <c r="T18" s="93"/>
       <c r="U18" s="93"/>
       <c r="V18" s="92">
-        <v>46090.384814814817</v>
+        <v>46090.869606481479</v>
       </c>
       <c r="W18" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="19" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A19" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B19" s="1">
         <v>707621000</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>34</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H19" s="93">
-        <v>0</v>
+        <v>3322</v>
       </c>
       <c r="I19" s="93">
         <v>-1</v>
@@ -6692,12 +6703,16 @@
         <v>3230</v>
       </c>
       <c r="M19" s="93">
-        <v>0</v>
-      </c>
-      <c r="N19" s="93"/>
-      <c r="O19" s="93"/>
+        <v>3225</v>
+      </c>
+      <c r="N19" s="93">
+        <v>3330</v>
+      </c>
+      <c r="O19" s="93">
+        <v>3179</v>
+      </c>
       <c r="P19" s="93">
-        <v>0</v>
+        <v>18447</v>
       </c>
       <c r="Q19" s="93"/>
       <c r="R19" s="93"/>
@@ -6705,45 +6720,45 @@
       <c r="T19" s="93"/>
       <c r="U19" s="93"/>
       <c r="V19" s="92">
-        <v>46090.384814814817</v>
+        <v>46090.869606481479</v>
       </c>
       <c r="W19" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="20" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A20" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B20" s="1">
         <v>634760245</v>
       </c>
       <c r="C20" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="G20" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="D20" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="G20" s="1" t="s">
-        <v>63</v>
-      </c>
       <c r="H20" s="93">
-        <v>64.63</v>
+        <v>64.680000000000007</v>
       </c>
       <c r="I20" s="93">
-        <v>64.62</v>
+        <v>-100</v>
       </c>
       <c r="J20" s="93">
-        <v>64.64</v>
+        <v>-100</v>
       </c>
       <c r="K20" s="93">
-        <v>64.63</v>
+        <v>-100</v>
       </c>
       <c r="L20" s="93">
         <v>64.2</v>
@@ -6758,7 +6773,7 @@
         <v>64.08</v>
       </c>
       <c r="P20" s="93">
-        <v>9893</v>
+        <v>32607</v>
       </c>
       <c r="Q20" s="93"/>
       <c r="R20" s="93"/>
@@ -6766,10 +6781,10 @@
       <c r="T20" s="93"/>
       <c r="U20" s="93"/>
       <c r="V20" s="92">
-        <v>46090.384814814817</v>
+        <v>46090.869606481479</v>
       </c>
       <c r="W20" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="21" spans="1:23" x14ac:dyDescent="0.4">
@@ -6780,22 +6795,22 @@
         <v>738739101</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>35</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H21" s="93">
-        <v>0</v>
+        <v>230.125</v>
       </c>
       <c r="I21" s="93">
         <v>-100</v>
@@ -6810,12 +6825,16 @@
         <v>234.57499999999999</v>
       </c>
       <c r="M21" s="93">
-        <v>0</v>
-      </c>
-      <c r="N21" s="93"/>
-      <c r="O21" s="93"/>
+        <v>228.07499999999999</v>
+      </c>
+      <c r="N21" s="93">
+        <v>230.92500000000001</v>
+      </c>
+      <c r="O21" s="93">
+        <v>227.32499999999999</v>
+      </c>
       <c r="P21" s="93">
-        <v>0</v>
+        <v>38861</v>
       </c>
       <c r="Q21" s="93"/>
       <c r="R21" s="93"/>
@@ -6823,10 +6842,10 @@
       <c r="T21" s="93"/>
       <c r="U21" s="93"/>
       <c r="V21" s="92">
-        <v>46090.384814814817</v>
+        <v>46090.869606481479</v>
       </c>
       <c r="W21" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="22" spans="1:23" x14ac:dyDescent="0.4">
@@ -6837,22 +6856,22 @@
         <v>786686904</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>36</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H22" s="93">
-        <v>0</v>
+        <v>342.95</v>
       </c>
       <c r="I22" s="93">
         <v>-100</v>
@@ -6867,12 +6886,16 @@
         <v>348.07499999999999</v>
       </c>
       <c r="M22" s="93">
-        <v>0</v>
-      </c>
-      <c r="N22" s="93"/>
-      <c r="O22" s="93"/>
+        <v>339.7</v>
+      </c>
+      <c r="N22" s="93">
+        <v>343.625</v>
+      </c>
+      <c r="O22" s="93">
+        <v>338.82499999999999</v>
+      </c>
       <c r="P22" s="93">
-        <v>0</v>
+        <v>11896</v>
       </c>
       <c r="Q22" s="93"/>
       <c r="R22" s="93"/>
@@ -6880,36 +6903,36 @@
       <c r="T22" s="93"/>
       <c r="U22" s="93"/>
       <c r="V22" s="92">
-        <v>46090.384814814817</v>
+        <v>46090.869606481479</v>
       </c>
       <c r="W22" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="23" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A23" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B23" s="1">
         <v>735014937</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>37</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H23" s="93">
-        <v>0</v>
+        <v>94.825000000000003</v>
       </c>
       <c r="I23" s="93">
         <v>-100</v>
@@ -6924,12 +6947,16 @@
         <v>95.625</v>
       </c>
       <c r="M23" s="93">
-        <v>0</v>
-      </c>
-      <c r="N23" s="93"/>
-      <c r="O23" s="93"/>
+        <v>95.35</v>
+      </c>
+      <c r="N23" s="93">
+        <v>95.5</v>
+      </c>
+      <c r="O23" s="93">
+        <v>94.1</v>
+      </c>
       <c r="P23" s="93">
-        <v>0</v>
+        <v>30165</v>
       </c>
       <c r="Q23" s="93"/>
       <c r="R23" s="93"/>
@@ -6937,45 +6964,45 @@
       <c r="T23" s="93"/>
       <c r="U23" s="93"/>
       <c r="V23" s="92">
-        <v>46090.384814814817</v>
+        <v>46090.869606481479</v>
       </c>
       <c r="W23" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="24" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A24" s="1" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B24" s="1">
         <v>792232100</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>38</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H24" s="93">
-        <v>99.02</v>
+        <v>98.625</v>
       </c>
       <c r="I24" s="93">
-        <v>99.02</v>
+        <v>98.63</v>
       </c>
       <c r="J24" s="93">
-        <v>99.03</v>
+        <v>98.635000000000005</v>
       </c>
       <c r="K24" s="93">
-        <v>99.025000000000006</v>
+        <v>98.632499999999993</v>
       </c>
       <c r="L24" s="93">
         <v>98.71</v>
@@ -6987,10 +7014,10 @@
         <v>99.435000000000002</v>
       </c>
       <c r="O24" s="93">
-        <v>98.965000000000003</v>
+        <v>98.564999999999998</v>
       </c>
       <c r="P24" s="93">
-        <v>3043</v>
+        <v>11235</v>
       </c>
       <c r="Q24" s="93"/>
       <c r="R24" s="93"/>
@@ -6998,45 +7025,45 @@
       <c r="T24" s="93"/>
       <c r="U24" s="93"/>
       <c r="V24" s="92">
-        <v>46090.384814814817</v>
+        <v>46090.869606481479</v>
       </c>
       <c r="W24" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="25" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A25" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B25" s="1">
         <v>496647057</v>
       </c>
       <c r="C25" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="G25" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="D25" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>290</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="G25" s="1" t="s">
-        <v>63</v>
-      </c>
       <c r="H25" s="93">
-        <v>1.1616500000000001</v>
+        <v>1.1669499999999999</v>
       </c>
       <c r="I25" s="93">
-        <v>1.1614500000000001</v>
+        <v>1.1669499999999999</v>
       </c>
       <c r="J25" s="93">
-        <v>1.1615500000000001</v>
+        <v>1.1670499999999999</v>
       </c>
       <c r="K25" s="93">
-        <v>1.1615000000000002</v>
+        <v>1.1669999999999998</v>
       </c>
       <c r="L25" s="93">
         <v>1.1655500000000001</v>
@@ -7045,13 +7072,13 @@
         <v>1.1604000000000001</v>
       </c>
       <c r="N25" s="93">
-        <v>1.16245</v>
+        <v>1.1675500000000001</v>
       </c>
       <c r="O25" s="93">
         <v>1.1560999999999999</v>
       </c>
       <c r="P25" s="93">
-        <v>14661</v>
+        <v>153875</v>
       </c>
       <c r="Q25" s="93"/>
       <c r="R25" s="93"/>
@@ -7059,45 +7086,45 @@
       <c r="T25" s="93"/>
       <c r="U25" s="93"/>
       <c r="V25" s="92">
-        <v>46090.384814814817</v>
+        <v>46090.869606481479</v>
       </c>
       <c r="W25" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="26" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A26" s="1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B26" s="1">
         <v>496647091</v>
       </c>
       <c r="C26" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="G26" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="D26" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="G26" s="1" t="s">
-        <v>63</v>
-      </c>
       <c r="H26" s="93">
-        <v>1.3347</v>
+        <v>1.3428</v>
       </c>
       <c r="I26" s="93">
-        <v>1.3344</v>
+        <v>1.3427</v>
       </c>
       <c r="J26" s="93">
-        <v>1.3346</v>
+        <v>1.3429</v>
       </c>
       <c r="K26" s="93">
-        <v>1.3345</v>
+        <v>1.3428</v>
       </c>
       <c r="L26" s="93">
         <v>1.3387</v>
@@ -7106,13 +7133,13 @@
         <v>1.3351</v>
       </c>
       <c r="N26" s="93">
-        <v>1.3351</v>
+        <v>1.3438000000000001</v>
       </c>
       <c r="O26" s="93">
         <v>1.3283</v>
       </c>
       <c r="P26" s="93">
-        <v>10401</v>
+        <v>72466</v>
       </c>
       <c r="Q26" s="93"/>
       <c r="R26" s="93"/>
@@ -7120,45 +7147,45 @@
       <c r="T26" s="93"/>
       <c r="U26" s="93"/>
       <c r="V26" s="92">
-        <v>46090.384814814817</v>
+        <v>46090.869606481479</v>
       </c>
       <c r="W26" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="27" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A27" s="1" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B27" s="1">
         <v>496647108</v>
       </c>
       <c r="C27" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="G27" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="D27" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="G27" s="1" t="s">
-        <v>63</v>
-      </c>
       <c r="H27" s="93">
-        <v>6.3670000000000003E-3</v>
+        <v>6.3889999999999997E-3</v>
       </c>
       <c r="I27" s="93">
-        <v>6.3660000000000001E-3</v>
+        <v>6.3885000000000001E-3</v>
       </c>
       <c r="J27" s="93">
-        <v>6.3670000000000003E-3</v>
+        <v>6.3895000000000002E-3</v>
       </c>
       <c r="K27" s="93">
-        <v>6.3665000000000006E-3</v>
+        <v>6.3890000000000006E-3</v>
       </c>
       <c r="L27" s="93">
         <v>6.3879999999999996E-3</v>
@@ -7167,13 +7194,13 @@
         <v>6.3800000000000003E-3</v>
       </c>
       <c r="N27" s="93">
-        <v>6.3800000000000003E-3</v>
+        <v>6.3905000000000003E-3</v>
       </c>
       <c r="O27" s="93">
         <v>6.3464999999999997E-3</v>
       </c>
       <c r="P27" s="93">
-        <v>30276</v>
+        <v>85160</v>
       </c>
       <c r="Q27" s="93"/>
       <c r="R27" s="93"/>
@@ -7181,45 +7208,45 @@
       <c r="T27" s="93"/>
       <c r="U27" s="93"/>
       <c r="V27" s="92">
-        <v>46090.384814814817</v>
+        <v>46090.869606481479</v>
       </c>
       <c r="W27" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="28" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A28" s="1" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B28" s="1">
         <v>496879111</v>
       </c>
       <c r="C28" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="G28" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="D28" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="G28" s="1" t="s">
-        <v>63</v>
-      </c>
       <c r="H28" s="93">
-        <v>0.74080000000000001</v>
+        <v>0.73980000000000001</v>
       </c>
       <c r="I28" s="93">
-        <v>0.74070000000000003</v>
+        <v>0.73975000000000002</v>
       </c>
       <c r="J28" s="93">
-        <v>0.74080000000000001</v>
+        <v>0.73985000000000001</v>
       </c>
       <c r="K28" s="93">
-        <v>0.74075000000000002</v>
+        <v>0.73980000000000001</v>
       </c>
       <c r="L28" s="93">
         <v>0.73919999999999997</v>
@@ -7228,13 +7255,13 @@
         <v>0.73875000000000002</v>
       </c>
       <c r="N28" s="93">
-        <v>0.74139999999999995</v>
+        <v>0.74250000000000005</v>
       </c>
       <c r="O28" s="93">
         <v>0.73799999999999999</v>
       </c>
       <c r="P28" s="93">
-        <v>3189</v>
+        <v>30906</v>
       </c>
       <c r="Q28" s="93"/>
       <c r="R28" s="93"/>
@@ -7242,45 +7269,45 @@
       <c r="T28" s="93"/>
       <c r="U28" s="93"/>
       <c r="V28" s="92">
-        <v>46090.384814814817</v>
+        <v>46090.869606481479</v>
       </c>
       <c r="W28" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="29" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A29" s="1" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B29" s="1">
         <v>496647009</v>
       </c>
       <c r="C29" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="G29" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="D29" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>294</v>
-      </c>
-      <c r="F29" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="G29" s="1" t="s">
-        <v>63</v>
-      </c>
       <c r="H29" s="93">
-        <v>0.7</v>
+        <v>0.70650000000000002</v>
       </c>
       <c r="I29" s="93">
-        <v>0.69989999999999997</v>
+        <v>0.70650000000000002</v>
       </c>
       <c r="J29" s="93">
-        <v>0.7</v>
+        <v>0.70655000000000001</v>
       </c>
       <c r="K29" s="93">
-        <v>0.69994999999999996</v>
+        <v>0.70652500000000007</v>
       </c>
       <c r="L29" s="93">
         <v>0.70189999999999997</v>
@@ -7289,13 +7316,13 @@
         <v>0.69835000000000003</v>
       </c>
       <c r="N29" s="93">
-        <v>0.70155000000000001</v>
+        <v>0.70730000000000004</v>
       </c>
       <c r="O29" s="93">
         <v>0.69489999999999996</v>
       </c>
       <c r="P29" s="93">
-        <v>11221</v>
+        <v>62742</v>
       </c>
       <c r="Q29" s="93"/>
       <c r="R29" s="93"/>
@@ -7303,45 +7330,45 @@
       <c r="T29" s="93"/>
       <c r="U29" s="93"/>
       <c r="V29" s="92">
-        <v>46090.384814814817</v>
+        <v>46090.869606481479</v>
       </c>
       <c r="W29" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="30" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A30" s="1" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B30" s="1">
         <v>815824224</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>46</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H30" s="93">
-        <v>115.40625</v>
+        <v>116.625</v>
       </c>
       <c r="I30" s="93">
-        <v>115.375</v>
+        <v>116.625</v>
       </c>
       <c r="J30" s="93">
-        <v>115.40625</v>
+        <v>116.65625</v>
       </c>
       <c r="K30" s="93">
-        <v>115.390625</v>
+        <v>116.640625</v>
       </c>
       <c r="L30" s="93">
         <v>116.1875</v>
@@ -7350,13 +7377,13 @@
         <v>115.8125</v>
       </c>
       <c r="N30" s="93">
-        <v>115.84375</v>
+        <v>116.71875</v>
       </c>
       <c r="O30" s="93">
         <v>115.0625</v>
       </c>
       <c r="P30" s="93">
-        <v>116350</v>
+        <v>566117</v>
       </c>
       <c r="Q30" s="93"/>
       <c r="R30" s="93"/>
@@ -7364,45 +7391,45 @@
       <c r="T30" s="93"/>
       <c r="U30" s="93"/>
       <c r="V30" s="92">
-        <v>46090.384814814817</v>
+        <v>46090.869606481479</v>
       </c>
       <c r="W30" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="31" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A31" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B31" s="1">
         <v>815824229</v>
       </c>
       <c r="C31" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="G31" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="D31" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="G31" s="1" t="s">
-        <v>63</v>
-      </c>
       <c r="H31" s="93">
-        <v>111.984375</v>
+        <v>112.59375</v>
       </c>
       <c r="I31" s="93">
-        <v>111.984375</v>
+        <v>112.59375</v>
       </c>
       <c r="J31" s="93">
-        <v>112</v>
+        <v>112.609375</v>
       </c>
       <c r="K31" s="93">
-        <v>111.9921875</v>
+        <v>112.6015625</v>
       </c>
       <c r="L31" s="93">
         <v>112.4375</v>
@@ -7411,13 +7438,13 @@
         <v>112.1875</v>
       </c>
       <c r="N31" s="93">
-        <v>112.203125</v>
+        <v>112.671875</v>
       </c>
       <c r="O31" s="93">
         <v>111.828125</v>
       </c>
       <c r="P31" s="93">
-        <v>637038</v>
+        <v>2658505</v>
       </c>
       <c r="Q31" s="93"/>
       <c r="R31" s="93"/>
@@ -7425,45 +7452,45 @@
       <c r="T31" s="93"/>
       <c r="U31" s="93"/>
       <c r="V31" s="92">
-        <v>46090.384814814817</v>
+        <v>46090.869606481479</v>
       </c>
       <c r="W31" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="32" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A32" s="1" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B32" s="1">
         <v>813041669</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H32" s="93">
-        <v>126.5</v>
+        <v>127.42</v>
       </c>
       <c r="I32" s="93">
-        <v>126.49</v>
+        <v>127.42</v>
       </c>
       <c r="J32" s="93">
-        <v>126.5</v>
+        <v>127.43</v>
       </c>
       <c r="K32" s="93">
-        <v>126.495</v>
+        <v>127.42500000000001</v>
       </c>
       <c r="L32" s="93">
         <v>126.93</v>
@@ -7472,13 +7499,13 @@
         <v>126.7</v>
       </c>
       <c r="N32" s="93">
-        <v>126.7</v>
+        <v>127.48</v>
       </c>
       <c r="O32" s="93">
         <v>125.94</v>
       </c>
       <c r="P32" s="93">
-        <v>353033</v>
+        <v>2145114</v>
       </c>
       <c r="Q32" s="93"/>
       <c r="R32" s="93"/>
@@ -7486,45 +7513,45 @@
       <c r="T32" s="93"/>
       <c r="U32" s="93"/>
       <c r="V32" s="92">
-        <v>46090.384814814817</v>
+        <v>46090.869606481479</v>
       </c>
       <c r="W32" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="33" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A33" s="1" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B33" s="1">
         <v>813041681</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H33" s="93">
-        <v>111.38</v>
+        <v>111.44</v>
       </c>
       <c r="I33" s="93">
-        <v>111.36</v>
+        <v>111.42</v>
       </c>
       <c r="J33" s="93">
-        <v>111.38</v>
+        <v>111.44</v>
       </c>
       <c r="K33" s="93">
-        <v>111.37</v>
+        <v>111.43</v>
       </c>
       <c r="L33" s="93">
         <v>110.88</v>
@@ -7533,13 +7560,13 @@
         <v>111</v>
       </c>
       <c r="N33" s="93">
-        <v>111.64</v>
+        <v>111.7</v>
       </c>
       <c r="O33" s="93">
         <v>110.14</v>
       </c>
       <c r="P33" s="93">
-        <v>49976</v>
+        <v>328496</v>
       </c>
       <c r="Q33" s="93"/>
       <c r="R33" s="93"/>
@@ -7547,45 +7574,45 @@
       <c r="T33" s="93"/>
       <c r="U33" s="93"/>
       <c r="V33" s="92">
-        <v>46090.384814814817</v>
+        <v>46090.869606481479</v>
       </c>
       <c r="W33" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="34" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A34" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B34" s="1">
         <v>813041663</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D34" s="1" t="s">
         <v>47</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H34" s="93">
-        <v>117.61</v>
+        <v>118.77</v>
       </c>
       <c r="I34" s="93">
-        <v>117.61</v>
+        <v>-1</v>
       </c>
       <c r="J34" s="93">
-        <v>117.62</v>
+        <v>-1</v>
       </c>
       <c r="K34" s="93">
-        <v>117.61500000000001</v>
+        <v>-1</v>
       </c>
       <c r="L34" s="93">
         <v>118.6</v>
@@ -7594,13 +7621,13 @@
         <v>117.62</v>
       </c>
       <c r="N34" s="93">
-        <v>117.84</v>
+        <v>118.97</v>
       </c>
       <c r="O34" s="93">
         <v>117.42</v>
       </c>
       <c r="P34" s="93">
-        <v>81733</v>
+        <v>705078</v>
       </c>
       <c r="Q34" s="93"/>
       <c r="R34" s="93"/>
@@ -7608,58 +7635,58 @@
       <c r="T34" s="93"/>
       <c r="U34" s="93"/>
       <c r="V34" s="92">
-        <v>46090.384814814817</v>
+        <v>46090.869606481479</v>
       </c>
       <c r="W34" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="35" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A35" s="1" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B35" s="1">
         <v>479624278</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D35" s="1" t="s">
         <v>44</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H35" s="93">
-        <v>67524.5</v>
+        <v>68902.75</v>
       </c>
       <c r="I35" s="93">
-        <v>67524.5</v>
+        <v>68902.75</v>
       </c>
       <c r="J35" s="93">
-        <v>67524.75</v>
+        <v>68903</v>
       </c>
       <c r="K35" s="93">
-        <v>67524.625</v>
+        <v>68902.875</v>
       </c>
       <c r="L35" s="93">
         <v>67317.25</v>
       </c>
       <c r="M35" s="93"/>
       <c r="N35" s="93">
-        <v>68748</v>
+        <v>69646.5</v>
       </c>
       <c r="O35" s="93">
         <v>65471</v>
       </c>
       <c r="P35" s="93">
-        <v>148.76280749</v>
+        <v>351.10540517999999</v>
       </c>
       <c r="Q35" s="93"/>
       <c r="R35" s="93"/>
@@ -7667,58 +7694,58 @@
       <c r="T35" s="93"/>
       <c r="U35" s="93"/>
       <c r="V35" s="92">
-        <v>46090.384814814817</v>
+        <v>46090.869606481479</v>
       </c>
       <c r="W35" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="36" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A36" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B36" s="1">
         <v>495759171</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D36" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H36" s="93">
-        <v>1985.5</v>
+        <v>2030.35</v>
       </c>
       <c r="I36" s="93">
-        <v>1985.45</v>
+        <v>2030.35</v>
       </c>
       <c r="J36" s="93">
-        <v>1985.5</v>
+        <v>2030.4</v>
       </c>
       <c r="K36" s="93">
-        <v>1985.4749999999999</v>
+        <v>2030.375</v>
       </c>
       <c r="L36" s="93">
         <v>1964.3</v>
       </c>
       <c r="M36" s="93"/>
       <c r="N36" s="93">
-        <v>2013.05</v>
+        <v>2056.0500000000002</v>
       </c>
       <c r="O36" s="93">
         <v>1914.8</v>
       </c>
       <c r="P36" s="93">
-        <v>1704.4242436699999</v>
+        <v>3593.66171377</v>
       </c>
       <c r="Q36" s="93"/>
       <c r="R36" s="93"/>
@@ -7726,10 +7753,10 @@
       <c r="T36" s="93"/>
       <c r="U36" s="93"/>
       <c r="V36" s="92">
-        <v>46090.384814814817</v>
+        <v>46090.869606481479</v>
       </c>
       <c r="W36" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="37" spans="1:23" x14ac:dyDescent="0.4">
@@ -7913,13 +7940,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1" s="86" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B1" s="86" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C1" s="86" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.4">
@@ -7927,10 +7954,10 @@
         <v>46086.543078703704</v>
       </c>
       <c r="B2" s="84" t="s">
+        <v>313</v>
+      </c>
+      <c r="C2" s="84" t="s">
         <v>314</v>
-      </c>
-      <c r="C2" s="84" t="s">
-        <v>315</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.4">
@@ -7938,10 +7965,10 @@
         <v>46086.543090277781</v>
       </c>
       <c r="B3" s="84" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C3" s="84" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.4">
@@ -7949,10 +7976,10 @@
         <v>46086.54310185185</v>
       </c>
       <c r="B4" s="84" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C4" s="84" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.4">
@@ -7960,10 +7987,10 @@
         <v>46090.383530092593</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>314</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>315</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.4">
@@ -7971,10 +7998,10 @@
         <v>46090.38354166667</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.4">
@@ -7982,24 +8009,44 @@
         <v>46090.38354166667</v>
       </c>
       <c r="B7" s="81" t="s">
+        <v>313</v>
+      </c>
+      <c r="C7" s="81" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A8" s="85">
+        <v>46090.869409722225</v>
+      </c>
+      <c r="B8" s="81" t="s">
+        <v>313</v>
+      </c>
+      <c r="C8" s="81" t="s">
         <v>314</v>
       </c>
-      <c r="C7" s="81" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A8" s="85"/>
-      <c r="B8" s="81"/>
-      <c r="C8" s="81"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A9" s="85"/>
-      <c r="B9" s="81"/>
-      <c r="C9" s="81"/>
+      <c r="A9" s="85">
+        <v>46090.869409722225</v>
+      </c>
+      <c r="B9" s="81" t="s">
+        <v>313</v>
+      </c>
+      <c r="C9" s="81" t="s">
+        <v>315</v>
+      </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A10" s="85"/>
+      <c r="A10" s="85">
+        <v>46090.869409722225</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>316</v>
+      </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A11" s="85"/>
@@ -8109,7 +8156,7 @@
     <row r="2" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B2" s="56"/>
       <c r="C2" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>51</v>
@@ -8121,15 +8168,15 @@
         <v>52</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B3" s="17" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C3" s="17"/>
       <c r="D3" s="10"/>
@@ -8142,7 +8189,7 @@
     </row>
     <row r="4" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B4" s="17" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C4" s="17"/>
       <c r="D4" s="10"/>
@@ -8156,7 +8203,7 @@
     </row>
     <row r="5" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B5" s="17" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C5" s="17"/>
       <c r="D5" s="10"/>
@@ -8170,7 +8217,7 @@
     </row>
     <row r="6" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B6" s="17" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C6" s="17"/>
       <c r="D6" s="10"/>
@@ -8184,7 +8231,7 @@
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B7" s="17" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C7" s="17"/>
       <c r="D7" s="10"/>
@@ -8198,7 +8245,7 @@
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B8" s="17" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C8" s="17"/>
       <c r="D8" s="10"/>
@@ -8209,7 +8256,7 @@
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B9" s="17" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C9" s="62"/>
       <c r="D9" s="27"/>
@@ -8220,7 +8267,7 @@
     </row>
     <row r="10" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B10" s="17" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C10" s="62"/>
       <c r="D10" s="27"/>
@@ -8231,7 +8278,7 @@
     </row>
     <row r="11" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B11" s="17" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C11" s="62"/>
       <c r="D11" s="27"/>
@@ -8242,7 +8289,7 @@
     </row>
     <row r="12" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B12" s="52" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C12" s="58"/>
       <c r="D12" s="54"/>
@@ -8253,7 +8300,7 @@
     </row>
     <row r="13" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B13" s="17" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C13" s="17"/>
       <c r="D13" s="10"/>
@@ -8318,46 +8365,46 @@
   <sheetData>
     <row r="2" spans="2:18" x14ac:dyDescent="0.4">
       <c r="B2" s="38" t="s">
+        <v>169</v>
+      </c>
+      <c r="C2" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="D2" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="E2" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="F2" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="E2" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="F2" s="4" t="s">
+      <c r="G2" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="H2" s="4" t="s">
         <v>173</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>179</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>174</v>
       </c>
       <c r="I2" s="4" t="s">
         <v>55</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K2" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="M2" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="N2" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="O2" s="4" t="s">
         <v>175</v>
-      </c>
-      <c r="L2" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="M2" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="N2" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="O2" s="4" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="3" spans="2:18" x14ac:dyDescent="0.4">
@@ -8447,11 +8494,11 @@
       <c r="H5" s="67"/>
       <c r="I5" s="70">
         <f>Blotter!C$4-SUM(NAV!I$4:I4)</f>
-        <v>-117.87469392600178</v>
+        <v>5794.6253060739982</v>
       </c>
       <c r="J5" s="70">
         <f t="shared" si="2"/>
-        <v>999882.12530607404</v>
+        <v>1005794.625306074</v>
       </c>
       <c r="K5" s="70">
         <f t="shared" si="3"/>
@@ -8459,19 +8506,19 @@
       </c>
       <c r="L5" s="71">
         <f t="shared" si="4"/>
-        <v>999.88212530607404</v>
+        <v>1005.7946253060741</v>
       </c>
       <c r="M5" s="72">
         <f t="shared" si="5"/>
-        <v>-1.1787469392599004E-4</v>
+        <v>5.7946253060741082E-3</v>
       </c>
       <c r="N5" s="73">
         <f t="shared" ref="N5" si="6">L5/L4-1</f>
-        <v>-1.1787469392599004E-4</v>
+        <v>5.7946253060741082E-3</v>
       </c>
       <c r="O5" s="75">
         <f>STDEVP(N$4:N5)*SQRT(12)</f>
-        <v>2.0416495880644527E-4</v>
+        <v>1.0036585440944712E-2</v>
       </c>
     </row>
     <row r="6" spans="2:18" ht="14.25" x14ac:dyDescent="0.4">
@@ -8753,37 +8800,37 @@
         <v>7</v>
       </c>
       <c r="H2" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="I2" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="J2" s="8" t="s">
         <v>161</v>
       </c>
-      <c r="I2" s="8" t="s">
+      <c r="K2" s="8" t="s">
         <v>165</v>
       </c>
-      <c r="J2" s="8" t="s">
+      <c r="L2" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="M2" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="K2" s="8" t="s">
-        <v>166</v>
-      </c>
-      <c r="L2" s="8" t="s">
+      <c r="N2" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="O2" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="P2" s="4" t="s">
         <v>167</v>
-      </c>
-      <c r="M2" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="N2" s="8" t="s">
-        <v>165</v>
-      </c>
-      <c r="O2" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="P2" s="4" t="s">
-        <v>168</v>
       </c>
       <c r="Q2" s="4" t="s">
         <v>56</v>
       </c>
       <c r="R2" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="T2" s="38" t="s">
         <v>8</v>
@@ -8795,20 +8842,20 @@
         <v>2</v>
       </c>
       <c r="W2" s="38" t="s">
+        <v>130</v>
+      </c>
+      <c r="X2" s="38" t="s">
         <v>131</v>
-      </c>
-      <c r="X2" s="38" t="s">
-        <v>132</v>
       </c>
       <c r="Y2" s="12"/>
       <c r="Z2" s="38" t="s">
         <v>2</v>
       </c>
       <c r="AA2" s="38" t="s">
+        <v>130</v>
+      </c>
+      <c r="AB2" s="38" t="s">
         <v>131</v>
-      </c>
-      <c r="AB2" s="38" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="3" spans="2:28" x14ac:dyDescent="0.4">
@@ -8867,7 +8914,7 @@
       </c>
       <c r="D4" s="6">
         <f t="array" ref="D4">SUM((Blotter!C$19:C$1013=C4)*(Blotter!N$19:N$1013)*1)</f>
-        <v>-117.87469392600178</v>
+        <v>3184.6253060739982</v>
       </c>
       <c r="E4" s="6">
         <f t="array" ref="E4">SUM((Blotter!B$19:C$1013=C4)*(Blotter!R$19:R$1013)*1)</f>
@@ -8875,7 +8922,7 @@
       </c>
       <c r="F4" s="30">
         <f t="shared" ref="F4" si="0">IF(ISNUMBER(D4/E4),D4/E4,0)</f>
-        <v>-1.1226161326285884E-2</v>
+        <v>0.30329764819752364</v>
       </c>
       <c r="G4" s="36" t="str">
         <f t="array" ref="G4">IF(SUM((Blotter!C$19:C$1013=PLB!C4)*(Blotter!M$19:M$1013))=0,"C","O")</f>
@@ -8883,20 +8930,20 @@
       </c>
       <c r="H4" s="16">
         <f>J3+D4</f>
-        <v>999882.12530607404</v>
+        <v>1003184.625306074</v>
       </c>
       <c r="I4" s="16"/>
       <c r="J4" s="16">
         <f>H4+I4</f>
-        <v>999882.12530607404</v>
+        <v>1003184.625306074</v>
       </c>
       <c r="K4" s="3">
         <f>H4/J3-1</f>
-        <v>-1.1787469392599004E-4</v>
+        <v>3.184625306074107E-3</v>
       </c>
       <c r="L4" s="3">
         <f>(1+K4)*(1+L3)-1</f>
-        <v>-1.1787469392599004E-4</v>
+        <v>3.184625306074107E-3</v>
       </c>
       <c r="M4" s="6">
         <f>O3-IF(G4="O",O3*1%,-D4)</f>
@@ -8931,7 +8978,7 @@
         <v>1</v>
       </c>
       <c r="V4" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="5" spans="2:28" x14ac:dyDescent="0.4">
@@ -8945,7 +8992,7 @@
       </c>
       <c r="D5" s="6">
         <f t="array" ref="D5">SUM((Blotter!C$19:C$1013=C5)*(Blotter!N$19:N$1013)*1)</f>
-        <v>0</v>
+        <v>2610</v>
       </c>
       <c r="E5" s="6">
         <f t="array" ref="E5">SUM((Blotter!B$19:C$1013=C5)*(Blotter!R$19:R$1013)*1)</f>
@@ -8953,7 +9000,7 @@
       </c>
       <c r="F5" s="30">
         <f t="shared" ref="F5" si="1">IF(ISNUMBER(D5/E5),D5/E5,0)</f>
-        <v>0</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="G5" s="36" t="str">
         <f t="array" ref="G5">IF(SUM((Blotter!C$19:C$1013=PLB!C5)*(Blotter!M$19:M$1013))=0,"C","O")</f>
@@ -8961,20 +9008,20 @@
       </c>
       <c r="H5" s="16">
         <f>J4+D5</f>
-        <v>999882.12530607404</v>
+        <v>1005794.625306074</v>
       </c>
       <c r="I5" s="16"/>
       <c r="J5" s="16">
         <f>H5+I5</f>
-        <v>999882.12530607404</v>
+        <v>1005794.625306074</v>
       </c>
       <c r="K5" s="3">
         <f>H5/J4-1</f>
-        <v>0</v>
+        <v>2.6017145141190579E-3</v>
       </c>
       <c r="L5" s="3">
         <f>(1+K5)*(1+L4)-1</f>
-        <v>-1.1787469392599004E-4</v>
+        <v>5.7946253060741082E-3</v>
       </c>
       <c r="M5" s="6">
         <f>O4-IF(G5="O",O4*1%,-D5)</f>
@@ -9009,7 +9056,7 @@
         <v>2</v>
       </c>
       <c r="V5" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="6" spans="2:28" x14ac:dyDescent="0.4">
@@ -10239,22 +10286,22 @@
         <v>16</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H2" s="4" t="s">
         <v>18</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="K2" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="L2" s="4" t="s">
         <v>189</v>
-      </c>
-      <c r="L2" s="4" t="s">
-        <v>190</v>
       </c>
       <c r="N2" s="4" t="s">
         <v>19</v>
@@ -10941,7 +10988,7 @@
     </row>
     <row r="20" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B20" s="17" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C20" s="18">
         <v>500</v>
@@ -11528,7 +11575,7 @@
     </row>
     <row r="37" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B37" s="17" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C37" s="18">
         <v>100</v>
@@ -11562,7 +11609,7 @@
     </row>
     <row r="38" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B38" s="17" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C38" s="18">
         <v>100</v>
@@ -11596,7 +11643,7 @@
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B39" s="17" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C39" s="18">
         <v>100</v>
@@ -11630,7 +11677,7 @@
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B40" s="17" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C40" s="18">
         <v>1</v>
@@ -11664,7 +11711,7 @@
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B41" s="17" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C41" s="18">
         <v>1</v>
@@ -11706,7 +11753,7 @@
     </row>
     <row r="42" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B42" s="17" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C42" s="18">
         <v>1</v>
@@ -11740,7 +11787,7 @@
     </row>
     <row r="43" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B43" s="9" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C43" s="18">
         <v>1</v>
@@ -11817,25 +11864,25 @@
   <sheetData>
     <row r="1" spans="1:31" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>57</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H1" s="2" t="s">
         <v>13</v>
@@ -11844,66 +11891,66 @@
         <v>58</v>
       </c>
       <c r="J1" s="48" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="L1" s="48" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N1" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="O1" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="P1" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Q1" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="R1" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="T1" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="U1" s="2" t="s">
         <v>12</v>
       </c>
       <c r="V1" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="W1" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="X1" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>199</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>200</v>
       </c>
       <c r="H2" s="1">
         <v>1</v>
@@ -11912,7 +11959,7 @@
         <v>46084</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="N2" s="1">
         <v>50</v>
@@ -11927,7 +11974,7 @@
         <v>-21.810505307</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="T2" s="43">
         <f>IF(ISNUMBER(VLOOKUP(U2,Blotter!B:C,2,0)),VLOOKUP(U2,Blotter!B:C,2,0),"")</f>
@@ -11950,7 +11997,7 @@
         <v>-21.810505307</v>
       </c>
       <c r="Z2" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="AC2" s="44"/>
       <c r="AD2" s="45"/>
@@ -11958,19 +12005,19 @@
     </row>
     <row r="3" spans="1:31" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>199</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>200</v>
       </c>
       <c r="H3" s="1">
         <v>1</v>
@@ -11979,7 +12026,7 @@
         <v>46087</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="N3" s="1">
         <v>-50</v>
@@ -11994,7 +12041,7 @@
         <v>-9.2536833119999997</v>
       </c>
       <c r="R3" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="T3" s="43">
         <f>IF(ISNUMBER(VLOOKUP(U3,Blotter!B:C,2,0)),VLOOKUP(U3,Blotter!B:C,2,0),"")</f>
@@ -12022,19 +12069,19 @@
     </row>
     <row r="4" spans="1:31" x14ac:dyDescent="0.4">
       <c r="A4" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="C4" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>199</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>200</v>
       </c>
       <c r="H4" s="1">
         <v>1</v>
@@ -12043,7 +12090,7 @@
         <v>46084</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="N4" s="1">
         <v>50</v>
@@ -12058,7 +12105,7 @@
         <v>-21.810505307</v>
       </c>
       <c r="R4" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="T4" s="43">
         <f>IF(ISNUMBER(VLOOKUP(U4,Blotter!B:C,2,0)),VLOOKUP(U4,Blotter!B:C,2,0),"")</f>
@@ -12086,7 +12133,7 @@
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.4">
       <c r="D5" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H5" s="1">
         <v>10</v>
@@ -12095,13 +12142,13 @@
         <v>46090</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="N5" s="1">
         <v>3</v>
       </c>
       <c r="O5" s="1">
-        <v>3230</v>
+        <v>3235</v>
       </c>
       <c r="T5" s="43">
         <f>IF(ISNUMBER(VLOOKUP(U5,Blotter!B:C,2,0)),VLOOKUP(U5,Blotter!B:C,2,0),"")</f>
@@ -12117,7 +12164,7 @@
       </c>
       <c r="W5" s="42">
         <f t="shared" si="2"/>
-        <v>3230</v>
+        <v>3235</v>
       </c>
       <c r="X5" s="42">
         <f t="shared" si="3"/>
@@ -20586,21 +20633,21 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A1" s="90" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B1" s="56"/>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A3" s="80" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B3" s="89" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A4" s="80" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B4" s="89">
         <v>7497</v>
@@ -20608,7 +20655,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A5" s="80" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B5" s="89">
         <v>11</v>
@@ -20616,7 +20663,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A6" s="80" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B6" s="89">
         <v>0.25</v>
@@ -20624,15 +20671,15 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A7" s="80" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B7" s="89" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A8" s="80" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B8" s="89">
         <v>3</v>
@@ -20640,22 +20687,22 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A10" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A11" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A12" s="1" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A13" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
   </sheetData>
@@ -20686,43 +20733,43 @@
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A1" s="82" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B1" s="82" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C1" s="82" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D1" s="82" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E1" s="82" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F1" s="82" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="G1" s="82" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H1" s="82" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="I1" s="82" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="J1" s="82" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="K1" s="82" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="L1" s="82" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="M1" s="82" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.4">
@@ -20730,22 +20777,22 @@
         <v>1</v>
       </c>
       <c r="B2" s="88" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C2" s="88" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D2" s="88" t="s">
         <v>21</v>
       </c>
       <c r="E2" s="88" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F2" s="88" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G2" s="88" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H2" s="88"/>
       <c r="I2" s="88"/>
@@ -20759,22 +20806,22 @@
         <v>1</v>
       </c>
       <c r="B3" s="88" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C3" s="88" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D3" s="88" t="s">
         <v>22</v>
       </c>
       <c r="E3" s="88" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F3" s="88" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G3" s="88" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H3" s="88"/>
       <c r="I3" s="88"/>
@@ -20788,22 +20835,22 @@
         <v>1</v>
       </c>
       <c r="B4" s="88" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C4" s="88" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D4" s="88" t="s">
         <v>23</v>
       </c>
       <c r="E4" s="88" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F4" s="88" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G4" s="88" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H4" s="88"/>
       <c r="I4" s="88"/>
@@ -20817,28 +20864,28 @@
         <v>1</v>
       </c>
       <c r="B5" s="88" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C5" s="88" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D5" s="88" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E5" s="88" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F5" s="88" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G5" s="88" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H5" s="88"/>
       <c r="I5" s="88"/>
       <c r="J5" s="88"/>
       <c r="K5" s="88" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="L5" s="88"/>
       <c r="M5" s="88"/>
@@ -20848,28 +20895,28 @@
         <v>1</v>
       </c>
       <c r="B6" s="88" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C6" s="88" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D6" s="88" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E6" s="88" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F6" s="88" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G6" s="88" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H6" s="88"/>
       <c r="I6" s="88"/>
       <c r="J6" s="88"/>
       <c r="K6" s="88" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="L6" s="88"/>
       <c r="M6" s="88"/>
@@ -20879,22 +20926,22 @@
         <v>1</v>
       </c>
       <c r="B7" s="88" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C7" s="88" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D7" s="88" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E7" s="88" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F7" s="88" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G7" s="88" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H7" s="88"/>
       <c r="I7" s="88"/>
@@ -20902,7 +20949,7 @@
         <v>500</v>
       </c>
       <c r="K7" s="88" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="L7" s="88"/>
       <c r="M7" s="88"/>
@@ -20912,19 +20959,19 @@
         <v>1</v>
       </c>
       <c r="B8" s="88" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C8" s="88" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D8" s="88" t="s">
         <v>24</v>
       </c>
       <c r="E8" s="88" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F8" s="88" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G8" s="88">
         <v>202604</v>
@@ -20943,22 +20990,22 @@
         <v>1</v>
       </c>
       <c r="B9" s="88" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C9" s="88" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D9" s="88" t="s">
         <v>5</v>
       </c>
       <c r="E9" s="88" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F9" s="88" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G9" s="88" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H9" s="88"/>
       <c r="I9" s="88"/>
@@ -20974,22 +21021,22 @@
         <v>1</v>
       </c>
       <c r="B10" s="88" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C10" s="88" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D10" s="88" t="s">
         <v>9</v>
       </c>
       <c r="E10" s="88" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F10" s="88" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G10" s="88" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H10" s="88"/>
       <c r="I10" s="88"/>
@@ -21005,22 +21052,22 @@
         <v>1</v>
       </c>
       <c r="B11" s="88" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C11" s="88" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D11" s="88" t="s">
         <v>26</v>
       </c>
       <c r="E11" s="88" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F11" s="88" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G11" s="88" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H11" s="88"/>
       <c r="I11" s="88"/>
@@ -21036,22 +21083,22 @@
         <v>1</v>
       </c>
       <c r="B12" s="88" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C12" s="88" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D12" s="88" t="s">
         <v>27</v>
       </c>
       <c r="E12" s="88" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F12" s="88" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G12" s="88" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H12" s="88"/>
       <c r="I12" s="88"/>
@@ -21067,22 +21114,22 @@
         <v>1</v>
       </c>
       <c r="B13" s="88" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C13" s="88" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D13" s="88" t="s">
         <v>25</v>
       </c>
       <c r="E13" s="88" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F13" s="88" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G13" s="88" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H13" s="88"/>
       <c r="I13" s="88"/>
@@ -21098,19 +21145,19 @@
         <v>1</v>
       </c>
       <c r="B14" s="88" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C14" s="88" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D14" s="88" t="s">
         <v>28</v>
       </c>
       <c r="E14" s="88" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F14" s="88" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G14" s="88">
         <v>202605</v>
@@ -21129,19 +21176,19 @@
         <v>1</v>
       </c>
       <c r="B15" s="88" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C15" s="88" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D15" s="88" t="s">
         <v>29</v>
       </c>
       <c r="E15" s="88" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F15" s="88" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G15" s="88">
         <v>202605</v>
@@ -21160,19 +21207,19 @@
         <v>1</v>
       </c>
       <c r="B16" s="88" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C16" s="88" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D16" s="88" t="s">
         <v>31</v>
       </c>
       <c r="E16" s="88" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F16" s="88" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G16" s="88">
         <v>202605</v>
@@ -21191,19 +21238,19 @@
         <v>1</v>
       </c>
       <c r="B17" s="88" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C17" s="88" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D17" s="88" t="s">
         <v>32</v>
       </c>
       <c r="E17" s="88" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F17" s="88" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G17" s="88">
         <v>202605</v>
@@ -21222,19 +21269,19 @@
         <v>1</v>
       </c>
       <c r="B18" s="88" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C18" s="88" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D18" s="88" t="s">
         <v>33</v>
       </c>
       <c r="E18" s="88" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F18" s="88" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G18" s="88">
         <v>202605</v>
@@ -21253,19 +21300,19 @@
         <v>1</v>
       </c>
       <c r="B19" s="88" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C19" s="88" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D19" s="88" t="s">
         <v>34</v>
       </c>
       <c r="E19" s="88" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F19" s="88" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G19" s="88">
         <v>202605</v>
@@ -21284,19 +21331,19 @@
         <v>1</v>
       </c>
       <c r="B20" s="88" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C20" s="88" t="s">
+        <v>61</v>
+      </c>
+      <c r="D20" s="88" t="s">
+        <v>69</v>
+      </c>
+      <c r="E20" s="88" t="s">
+        <v>68</v>
+      </c>
+      <c r="F20" s="88" t="s">
         <v>62</v>
-      </c>
-      <c r="D20" s="88" t="s">
-        <v>70</v>
-      </c>
-      <c r="E20" s="88" t="s">
-        <v>69</v>
-      </c>
-      <c r="F20" s="88" t="s">
-        <v>63</v>
       </c>
       <c r="G20" s="88">
         <v>202605</v>
@@ -21305,7 +21352,7 @@
       <c r="I20" s="88"/>
       <c r="J20" s="88"/>
       <c r="K20" s="88" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L20" s="88"/>
       <c r="M20" s="88"/>
@@ -21318,16 +21365,16 @@
         <v>35</v>
       </c>
       <c r="C21" s="88" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D21" s="88" t="s">
         <v>35</v>
       </c>
       <c r="E21" s="88" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F21" s="88" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G21" s="88">
         <v>202604</v>
@@ -21349,16 +21396,16 @@
         <v>36</v>
       </c>
       <c r="C22" s="88" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D22" s="88" t="s">
         <v>36</v>
       </c>
       <c r="E22" s="88" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F22" s="88" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G22" s="88">
         <v>202605</v>
@@ -21377,19 +21424,19 @@
         <v>1</v>
       </c>
       <c r="B23" s="88" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C23" s="88" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D23" s="88" t="s">
         <v>37</v>
       </c>
       <c r="E23" s="88" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F23" s="88" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G23" s="88">
         <v>202604</v>
@@ -21408,22 +21455,22 @@
         <v>1</v>
       </c>
       <c r="B24" s="88" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C24" s="88" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D24" s="88" t="s">
         <v>38</v>
       </c>
       <c r="E24" s="88" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F24" s="88" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G24" s="88" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H24" s="88"/>
       <c r="I24" s="88"/>
@@ -21439,22 +21486,22 @@
         <v>1</v>
       </c>
       <c r="B25" s="88" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C25" s="88" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D25" s="88" t="s">
         <v>42</v>
       </c>
       <c r="E25" s="88" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F25" s="88" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G25" s="88" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H25" s="88"/>
       <c r="I25" s="88"/>
@@ -21470,22 +21517,22 @@
         <v>1</v>
       </c>
       <c r="B26" s="88" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C26" s="88" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D26" s="88" t="s">
         <v>40</v>
       </c>
       <c r="E26" s="88" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F26" s="88" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G26" s="88" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H26" s="88"/>
       <c r="I26" s="88"/>
@@ -21501,22 +21548,22 @@
         <v>1</v>
       </c>
       <c r="B27" s="88" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C27" s="88" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D27" s="88" t="s">
         <v>43</v>
       </c>
       <c r="E27" s="88" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F27" s="88" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G27" s="88" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H27" s="88"/>
       <c r="I27" s="88"/>
@@ -21532,22 +21579,22 @@
         <v>1</v>
       </c>
       <c r="B28" s="88" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C28" s="88" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D28" s="88" t="s">
         <v>41</v>
       </c>
       <c r="E28" s="88" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F28" s="88" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G28" s="88" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H28" s="88"/>
       <c r="I28" s="88"/>
@@ -21563,22 +21610,22 @@
         <v>1</v>
       </c>
       <c r="B29" s="88" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C29" s="88" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D29" s="88" t="s">
         <v>39</v>
       </c>
       <c r="E29" s="88" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F29" s="88" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G29" s="88" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H29" s="88"/>
       <c r="I29" s="88"/>
@@ -21594,22 +21641,22 @@
         <v>1</v>
       </c>
       <c r="B30" s="88" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C30" s="88" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D30" s="88" t="s">
         <v>46</v>
       </c>
       <c r="E30" s="88" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F30" s="88" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G30" s="88" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H30" s="88"/>
       <c r="I30" s="88"/>
@@ -21625,28 +21672,28 @@
         <v>1</v>
       </c>
       <c r="B31" s="88" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C31" s="88" t="s">
+        <v>61</v>
+      </c>
+      <c r="D31" s="88" t="s">
+        <v>71</v>
+      </c>
+      <c r="E31" s="88" t="s">
+        <v>86</v>
+      </c>
+      <c r="F31" s="88" t="s">
         <v>62</v>
       </c>
-      <c r="D31" s="88" t="s">
-        <v>72</v>
-      </c>
-      <c r="E31" s="88" t="s">
-        <v>87</v>
-      </c>
-      <c r="F31" s="88" t="s">
-        <v>63</v>
-      </c>
       <c r="G31" s="88" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H31" s="88"/>
       <c r="I31" s="88"/>
       <c r="J31" s="88"/>
       <c r="K31" s="88" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L31" s="88"/>
       <c r="M31" s="88"/>
@@ -21656,28 +21703,28 @@
         <v>1</v>
       </c>
       <c r="B32" s="88" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C32" s="88" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D32" s="88" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E32" s="88" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F32" s="88" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G32" s="88" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H32" s="88"/>
       <c r="I32" s="88"/>
       <c r="J32" s="88"/>
       <c r="K32" s="88" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="L32" s="88"/>
       <c r="M32" s="88"/>
@@ -21687,28 +21734,28 @@
         <v>1</v>
       </c>
       <c r="B33" s="88" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C33" s="88" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D33" s="88" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E33" s="88" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F33" s="88" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G33" s="88" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H33" s="88"/>
       <c r="I33" s="88"/>
       <c r="J33" s="88"/>
       <c r="K33" s="88" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="L33" s="88"/>
       <c r="M33" s="88"/>
@@ -21718,28 +21765,28 @@
         <v>1</v>
       </c>
       <c r="B34" s="88" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C34" s="88" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D34" s="88" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="E34" s="88" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F34" s="88" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G34" s="88" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H34" s="88"/>
       <c r="I34" s="88"/>
       <c r="J34" s="88"/>
       <c r="K34" s="88" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="M34" s="88"/>
     </row>
@@ -21748,19 +21795,19 @@
         <v>1</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C35" s="88" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D35" s="88" t="s">
         <v>44</v>
       </c>
       <c r="E35" s="88" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F35" s="88" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="L35" s="88"/>
       <c r="M35" s="88"/>
@@ -21770,19 +21817,19 @@
         <v>1</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C36" s="88" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D36" s="88" t="s">
         <v>45</v>
       </c>
       <c r="E36" s="88" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F36" s="88" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G36" s="88"/>
       <c r="H36" s="88"/>
@@ -21905,155 +21952,155 @@
     </row>
     <row r="55" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C55" s="31" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D55" s="31" t="s">
         <v>27</v>
       </c>
       <c r="E55" s="31" t="s">
+        <v>61</v>
+      </c>
+      <c r="F55" s="31" t="s">
+        <v>85</v>
+      </c>
+      <c r="G55" s="31" t="s">
         <v>62</v>
-      </c>
-      <c r="F55" s="31" t="s">
-        <v>86</v>
-      </c>
-      <c r="G55" s="31" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="56" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C56" s="31" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D56" s="31" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E56" s="31" t="s">
+        <v>61</v>
+      </c>
+      <c r="F56" s="31" t="s">
+        <v>64</v>
+      </c>
+      <c r="G56" s="31" t="s">
         <v>62</v>
-      </c>
-      <c r="F56" s="31" t="s">
-        <v>65</v>
-      </c>
-      <c r="G56" s="31" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="57" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C57" s="31" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D57" s="31" t="s">
         <v>28</v>
       </c>
       <c r="E57" s="31" t="s">
+        <v>61</v>
+      </c>
+      <c r="F57" s="31" t="s">
+        <v>86</v>
+      </c>
+      <c r="G57" s="31" t="s">
         <v>62</v>
-      </c>
-      <c r="F57" s="31" t="s">
-        <v>87</v>
-      </c>
-      <c r="G57" s="31" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="58" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C58" s="31" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D58" s="31" t="s">
         <v>29</v>
       </c>
       <c r="E58" s="31" t="s">
+        <v>61</v>
+      </c>
+      <c r="F58" s="31" t="s">
+        <v>86</v>
+      </c>
+      <c r="G58" s="31" t="s">
         <v>62</v>
-      </c>
-      <c r="F58" s="31" t="s">
-        <v>87</v>
-      </c>
-      <c r="G58" s="31" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="59" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C59" s="31" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D59" s="31" t="s">
         <v>31</v>
       </c>
       <c r="E59" s="31" t="s">
+        <v>61</v>
+      </c>
+      <c r="F59" s="31" t="s">
+        <v>86</v>
+      </c>
+      <c r="G59" s="31" t="s">
         <v>62</v>
-      </c>
-      <c r="F59" s="31" t="s">
-        <v>87</v>
-      </c>
-      <c r="G59" s="31" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="60" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C60" s="31" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D60" s="31" t="s">
         <v>32</v>
       </c>
       <c r="E60" s="31" t="s">
+        <v>61</v>
+      </c>
+      <c r="F60" s="31" t="s">
+        <v>68</v>
+      </c>
+      <c r="G60" s="31" t="s">
         <v>62</v>
-      </c>
-      <c r="F60" s="31" t="s">
-        <v>69</v>
-      </c>
-      <c r="G60" s="31" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="61" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C61" s="31" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D61" s="31" t="s">
         <v>33</v>
       </c>
       <c r="E61" s="31" t="s">
+        <v>61</v>
+      </c>
+      <c r="F61" s="31" t="s">
+        <v>68</v>
+      </c>
+      <c r="G61" s="31" t="s">
         <v>62</v>
-      </c>
-      <c r="F61" s="31" t="s">
-        <v>69</v>
-      </c>
-      <c r="G61" s="31" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="62" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C62" s="31" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D62" s="31" t="s">
         <v>34</v>
       </c>
       <c r="E62" s="31" t="s">
+        <v>61</v>
+      </c>
+      <c r="F62" s="31" t="s">
+        <v>68</v>
+      </c>
+      <c r="G62" s="31" t="s">
         <v>62</v>
-      </c>
-      <c r="F62" s="31" t="s">
-        <v>69</v>
-      </c>
-      <c r="G62" s="31" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="63" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C63" s="31" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D63" s="31" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E63" s="31" t="s">
+        <v>61</v>
+      </c>
+      <c r="F63" s="31" t="s">
+        <v>68</v>
+      </c>
+      <c r="G63" s="31" t="s">
         <v>62</v>
-      </c>
-      <c r="F63" s="31" t="s">
-        <v>69</v>
-      </c>
-      <c r="G63" s="31" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="64" spans="3:7" x14ac:dyDescent="0.4">
@@ -22064,13 +22111,13 @@
         <v>35</v>
       </c>
       <c r="E64" s="31" t="s">
+        <v>61</v>
+      </c>
+      <c r="F64" s="31" t="s">
+        <v>83</v>
+      </c>
+      <c r="G64" s="31" t="s">
         <v>62</v>
-      </c>
-      <c r="F64" s="31" t="s">
-        <v>84</v>
-      </c>
-      <c r="G64" s="31" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="65" spans="3:7" x14ac:dyDescent="0.4">
@@ -22081,30 +22128,30 @@
         <v>36</v>
       </c>
       <c r="E65" s="31" t="s">
+        <v>61</v>
+      </c>
+      <c r="F65" s="31" t="s">
+        <v>83</v>
+      </c>
+      <c r="G65" s="31" t="s">
         <v>62</v>
-      </c>
-      <c r="F65" s="31" t="s">
-        <v>84</v>
-      </c>
-      <c r="G65" s="31" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="66" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C66" s="31" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D66" s="31" t="s">
         <v>37</v>
       </c>
       <c r="E66" s="31" t="s">
+        <v>61</v>
+      </c>
+      <c r="F66" s="31" t="s">
+        <v>83</v>
+      </c>
+      <c r="G66" s="31" t="s">
         <v>62</v>
-      </c>
-      <c r="F66" s="31" t="s">
-        <v>84</v>
-      </c>
-      <c r="G66" s="31" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="67" spans="3:7" ht="14.25" x14ac:dyDescent="0.45">
@@ -22116,19 +22163,19 @@
     </row>
     <row r="68" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C68" s="31" t="s">
+        <v>70</v>
+      </c>
+      <c r="D68" s="31" t="s">
         <v>71</v>
       </c>
-      <c r="D68" s="31" t="s">
-        <v>72</v>
-      </c>
       <c r="E68" s="31" t="s">
+        <v>61</v>
+      </c>
+      <c r="F68" s="31" t="s">
+        <v>86</v>
+      </c>
+      <c r="G68" s="31" t="s">
         <v>62</v>
-      </c>
-      <c r="F68" s="31" t="s">
-        <v>87</v>
-      </c>
-      <c r="G68" s="31" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="69" spans="3:7" x14ac:dyDescent="0.4">
@@ -22139,81 +22186,81 @@
         <v>46</v>
       </c>
       <c r="E69" s="31" t="s">
+        <v>61</v>
+      </c>
+      <c r="F69" s="31" t="s">
+        <v>86</v>
+      </c>
+      <c r="G69" s="31" t="s">
         <v>62</v>
-      </c>
-      <c r="F69" s="31" t="s">
-        <v>87</v>
-      </c>
-      <c r="G69" s="31" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="70" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C70" s="31" t="s">
+        <v>72</v>
+      </c>
+      <c r="D70" s="31" t="s">
         <v>73</v>
       </c>
-      <c r="D70" s="31" t="s">
-        <v>74</v>
-      </c>
       <c r="E70" s="31" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F70" s="31" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G70" s="31" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="71" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C71" s="31" t="s">
+        <v>74</v>
+      </c>
+      <c r="D71" s="31" t="s">
         <v>75</v>
       </c>
-      <c r="D71" s="31" t="s">
-        <v>76</v>
-      </c>
       <c r="E71" s="31" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F71" s="31" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G71" s="31" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="72" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C72" s="31" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D72" s="31" t="s">
         <v>47</v>
       </c>
       <c r="E72" s="31" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F72" s="31" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G72" s="31" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="73" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C73" s="31" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D73" s="31" t="s">
         <v>38</v>
       </c>
       <c r="E73" s="31" t="s">
+        <v>61</v>
+      </c>
+      <c r="F73" s="31" t="s">
+        <v>68</v>
+      </c>
+      <c r="G73" s="31" t="s">
         <v>62</v>
-      </c>
-      <c r="F73" s="31" t="s">
-        <v>69</v>
-      </c>
-      <c r="G73" s="31" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="74" spans="3:7" x14ac:dyDescent="0.4">
@@ -22221,16 +22268,16 @@
         <v>42</v>
       </c>
       <c r="D74" s="31" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E74" s="31" t="s">
+        <v>61</v>
+      </c>
+      <c r="F74" s="31" t="s">
+        <v>83</v>
+      </c>
+      <c r="G74" s="31" t="s">
         <v>62</v>
-      </c>
-      <c r="F74" s="31" t="s">
-        <v>84</v>
-      </c>
-      <c r="G74" s="31" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="75" spans="3:7" x14ac:dyDescent="0.4">
@@ -22238,16 +22285,16 @@
         <v>40</v>
       </c>
       <c r="D75" s="31" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E75" s="31" t="s">
+        <v>61</v>
+      </c>
+      <c r="F75" s="31" t="s">
+        <v>83</v>
+      </c>
+      <c r="G75" s="31" t="s">
         <v>62</v>
-      </c>
-      <c r="F75" s="31" t="s">
-        <v>84</v>
-      </c>
-      <c r="G75" s="31" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="76" spans="3:7" x14ac:dyDescent="0.4">
@@ -22255,50 +22302,50 @@
         <v>43</v>
       </c>
       <c r="D76" s="31" t="s">
+        <v>60</v>
+      </c>
+      <c r="E76" s="31" t="s">
         <v>61</v>
       </c>
-      <c r="E76" s="31" t="s">
+      <c r="F76" s="31" t="s">
+        <v>83</v>
+      </c>
+      <c r="G76" s="31" t="s">
         <v>62</v>
-      </c>
-      <c r="F76" s="31" t="s">
-        <v>84</v>
-      </c>
-      <c r="G76" s="31" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="77" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C77" s="31" t="s">
+        <v>79</v>
+      </c>
+      <c r="D77" s="31" t="s">
         <v>80</v>
       </c>
-      <c r="D77" s="31" t="s">
-        <v>81</v>
-      </c>
       <c r="E77" s="31" t="s">
+        <v>61</v>
+      </c>
+      <c r="F77" s="31" t="s">
+        <v>83</v>
+      </c>
+      <c r="G77" s="31" t="s">
         <v>62</v>
-      </c>
-      <c r="F77" s="31" t="s">
-        <v>84</v>
-      </c>
-      <c r="G77" s="31" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="78" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C78" s="31" t="s">
+        <v>81</v>
+      </c>
+      <c r="D78" s="31" t="s">
         <v>82</v>
       </c>
-      <c r="D78" s="31" t="s">
+      <c r="E78" s="31" t="s">
+        <v>61</v>
+      </c>
+      <c r="F78" s="31" t="s">
         <v>83</v>
       </c>
-      <c r="E78" s="31" t="s">
+      <c r="G78" s="31" t="s">
         <v>62</v>
-      </c>
-      <c r="F78" s="31" t="s">
-        <v>84</v>
-      </c>
-      <c r="G78" s="31" t="s">
-        <v>63</v>
       </c>
     </row>
   </sheetData>

--- a/1XW_TradeBlotter_Web.xlsx
+++ b/1XW_TradeBlotter_Web.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0a601c1c2ba3d9f4/Trading/The Strategy Project/1XW Website/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="200" documentId="13_ncr:1_{6F5069F1-F0E7-4440-AA6D-4AFA11BBED1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9A14DF97-A68F-4AEF-A2B9-892D8DCF8FBD}"/>
+  <xr:revisionPtr revIDLastSave="249" documentId="13_ncr:1_{6F5069F1-F0E7-4440-AA6D-4AFA11BBED1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2B162599-3CD8-462F-8665-2026C82478A7}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="22695" windowHeight="14476" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="22695" windowHeight="14476" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Blotter" sheetId="3" r:id="rId1"/>
@@ -116,7 +116,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="877" uniqueCount="321">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1129" uniqueCount="330">
   <si>
     <t>WEEK</t>
   </si>
@@ -1092,6 +1092,33 @@
   </si>
   <si>
     <t>Last</t>
+  </si>
+  <si>
+    <t>DUP242961</t>
+  </si>
+  <si>
+    <t>CC 14MAY26</t>
+  </si>
+  <si>
+    <t>BOND</t>
+  </si>
+  <si>
+    <t>T 2 1/2 03/31/27</t>
+  </si>
+  <si>
+    <t>T</t>
+  </si>
+  <si>
+    <t>Tokenization / Financial Institutions adoption</t>
+  </si>
+  <si>
+    <t>Weekly doji + weekly up in the $2000 price area</t>
+  </si>
+  <si>
+    <t>Ivory Coast and Ghana supply destruction / HF speculation / Production adjustment to price from companies</t>
+  </si>
+  <si>
+    <t>Retrace to the pre breakout price region ~$3000. Inside week + weekly up</t>
   </si>
 </sst>
 </file>
@@ -1323,7 +1350,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="96">
+  <cellXfs count="97">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1564,6 +1591,9 @@
     <xf numFmtId="37" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="10" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="2" builtinId="3"/>
@@ -1756,7 +1786,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>5.7946253060741082E-3</c:v>
+                  <c:v>3.6645906320098565E-3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1910,7 +1940,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>5.7946253060741082E-3</c:v>
+                  <c:v>3.6645906320098565E-3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2301,7 +2331,7 @@
                   <c:v>1000</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1005.7946253060741</c:v>
+                  <c:v>1003.6645906320099</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2645,10 +2675,10 @@
                 <c:formatCode>0.00%</c:formatCode>
                 <c:ptCount val="52"/>
                 <c:pt idx="0">
-                  <c:v>-1.0000000000000009E-2</c:v>
+                  <c:v>5.2224063201000703E-4</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-1.9900000000000029E-2</c:v>
+                  <c:v>-9.482981774310062E-3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2705,10 +2735,10 @@
                 <c:formatCode>0.00%</c:formatCode>
                 <c:ptCount val="52"/>
                 <c:pt idx="0">
-                  <c:v>3.184625306074107E-3</c:v>
+                  <c:v>5.2224063201000703E-4</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>5.7946253060741082E-3</c:v>
+                  <c:v>3.1233306320099796E-3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3383,7 +3413,7 @@
       </c>
       <c r="C3" s="28">
         <f ca="1">OFFSET(NAV!B1,MATCH(C1,NAV!B:B,1),8)</f>
-        <v>1005794.625306074</v>
+        <v>1003664.5906320099</v>
       </c>
       <c r="E3" s="47" t="s">
         <v>129</v>
@@ -3400,7 +3430,7 @@
       </c>
       <c r="C4" s="28">
         <f>SUM(N18:N1012)</f>
-        <v>5794.6253060739982</v>
+        <v>3664.5906320098998</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="47" t="s">
@@ -3418,7 +3448,7 @@
       </c>
       <c r="C5" s="3">
         <f ca="1">OFFSET(NAV!B1,MATCH(C1,NAV!B:B,1),11)</f>
-        <v>5.7946253060741082E-3</v>
+        <v>3.6645906320098565E-3</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="47" t="s">
@@ -3437,7 +3467,7 @@
       </c>
       <c r="C6" s="3">
         <f ca="1">OFFSET(NAV!B1,MATCH(C1,NAV!B:B,1),12)</f>
-        <v>5.7946253060741082E-3</v>
+        <v>3.6645906320098565E-3</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="47"/>
@@ -3452,11 +3482,11 @@
       </c>
       <c r="C7" s="28">
         <f>Cash_Mgmt!H13</f>
-        <v>0</v>
+        <v>35858.739999999954</v>
       </c>
       <c r="D7" s="3">
         <f ca="1">C7/C3</f>
-        <v>0</v>
+        <v>3.5727812194131132E-2</v>
       </c>
       <c r="E7" s="47"/>
       <c r="F7" s="47"/>
@@ -3470,11 +3500,11 @@
       </c>
       <c r="C8" s="28">
         <f>C4+C7</f>
-        <v>5794.6253060739982</v>
+        <v>39523.330632009856</v>
       </c>
       <c r="D8" s="3">
         <f ca="1">C5+D7</f>
-        <v>5.7946253060741082E-3</v>
+        <v>3.9392402826140989E-2</v>
       </c>
       <c r="G8" s="47"/>
       <c r="H8" s="51"/>
@@ -3490,7 +3520,7 @@
       </c>
       <c r="D9" s="3">
         <f ca="1">C9/$C$3</f>
-        <v>9.9085834714688792E-2</v>
+        <v>9.9296120367506305E-2</v>
       </c>
       <c r="E9" s="47"/>
       <c r="F9" s="47"/>
@@ -3531,11 +3561,11 @@
       </c>
       <c r="C12" s="28" cm="1">
         <f t="array" ref="C12">SUM((PLB!G4:G999="O")*(PLB!E4:E999))</f>
-        <v>19500</v>
+        <v>9000</v>
       </c>
       <c r="D12" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>1.938765579908119E-2</v>
+        <v>8.9671391060360903E-3</v>
       </c>
     </row>
     <row r="13" spans="2:11" x14ac:dyDescent="0.4">
@@ -3544,11 +3574,11 @@
       </c>
       <c r="C13" s="28">
         <f t="array" ref="C13">SUM((PLB!G4:G999="O")*(PLB!D4:D999))</f>
-        <v>5794.6253060739982</v>
+        <v>2601.0899999999965</v>
       </c>
       <c r="D13" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>5.7612410727593934E-3</v>
+        <v>2.591592873035487E-3</v>
       </c>
       <c r="F13" s="59"/>
       <c r="G13" s="59"/>
@@ -3559,11 +3589,11 @@
       </c>
       <c r="C14" s="28">
         <f>C12+C13</f>
-        <v>25294.625306073998</v>
+        <v>11601.089999999997</v>
       </c>
       <c r="D14" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>2.5148896871840583E-2</v>
+        <v>1.1558731979071578E-2</v>
       </c>
     </row>
     <row r="17" spans="2:28" x14ac:dyDescent="0.4">
@@ -3660,7 +3690,7 @@
       <c r="M18" s="12"/>
       <c r="N18" s="95">
         <f>Cash_Mgmt!G13</f>
-        <v>0</v>
+        <v>541.25999999990927</v>
       </c>
       <c r="O18" s="12"/>
       <c r="P18" s="12"/>
@@ -3699,8 +3729,8 @@
         <v>50</v>
       </c>
       <c r="I19" s="28">
-        <f t="array" ref="I19">SUM((Trades!V$2:V$9999)*(Trades!U$2:U$9999=Blotter!B19)*(Trades!$T$2:T$9999=Blotter!C19))</f>
-        <v>50</v>
+        <f t="array" ref="I19">ROUND(SUM((Trades!V$2:V$9999)*(Trades!U$2:U$9999=Blotter!B19)*(Trades!$T$2:T$9999=Blotter!C19)),8)</f>
+        <v>0</v>
       </c>
       <c r="J19" s="28">
         <f>VLOOKUP(D19,Multiplier!B:D,2,0)</f>
@@ -3708,19 +3738,19 @@
       </c>
       <c r="K19" s="29">
         <f t="shared" ref="K19" si="1">L19-N19/(H19*J19)</f>
-        <v>1966.65749387852</v>
+        <v>1989.6625719211397</v>
       </c>
       <c r="L19" s="29">
         <f t="shared" ref="L19" si="2">IF(I19=0,IF(H19&gt;0,X19,Y19),Z19)</f>
-        <v>2030.35</v>
+        <v>2000.1073845613396</v>
       </c>
       <c r="M19" s="28">
         <f t="shared" ref="M19" si="3">I19*J19*L19</f>
-        <v>101517.5</v>
+        <v>0</v>
       </c>
       <c r="N19" s="95">
         <f t="array" ref="N19">-SUM((Trades!T$2:T$9999=Blotter!C19)*(Trades!U$2:U$9999=Blotter!B19)*(Trades!V$2:V$9999)*(Trades!W$2:W$9999))*J19+SUM((Trades!T$2:T$9999=Blotter!C19)*(Trades!U$2:U$9999=Blotter!B19)*(Trades!X$2:X$9999))+(L19*I19)*J19</f>
-        <v>3184.6253060739982</v>
+        <v>522.24063200999399</v>
       </c>
       <c r="O19" s="29">
         <f>VLOOKUP(D19,Multiplier!B:H,3,0)</f>
@@ -3736,27 +3766,27 @@
       </c>
       <c r="S19" s="29">
         <f>IF(OR(F19="Futures",F19="Spot"),IF(I19=0,0,IF(I19&gt;0,L19-O19,L19+O19)),0)</f>
-        <v>1890.35</v>
+        <v>0</v>
       </c>
       <c r="T19" s="3">
         <f t="shared" ref="T19" si="5">IF(S19&gt;0,IF(ISNUMBER(S19/L19-1),S19/L19-1,0),0)</f>
-        <v>-6.8953628684709556E-2</v>
+        <v>0</v>
       </c>
       <c r="U19" s="29">
         <f>IF(OR(F19="Futures",F19="Spot"),IF(I19=0,0,IF(I19&gt;0,K19-P19,K19+P19)),0)</f>
-        <v>1756.65749387852</v>
+        <v>0</v>
       </c>
       <c r="V19" s="3">
         <f t="shared" ref="V19" si="6">IF(U19&gt;0,IF(ISNUMBER(U19/L19-1),U19/L19-1,0),0)</f>
-        <v>-0.13480065314920087</v>
+        <v>0</v>
       </c>
       <c r="X19" s="34">
         <f t="array" ref="X19">IF(ISNUMBER(SUM((Trades!T$2:T$9999=Blotter!C19)*(Trades!U$2:U$9999=Blotter!B19)*(Trades!W$2:W$9999)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0))/SUM((Trades!T$2:T$9999=Blotter!C19)*(Trades!U$2:U$9999=Blotter!B19)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0))),SUM((Trades!T$2:T$9999=Blotter!C19)*(Trades!U$2:U$9999=Blotter!B19)*(Trades!W$2:W$9999)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0))/SUM((Trades!T$2:T$9999=Blotter!C19)*(Trades!U$2:U$9999=Blotter!B19)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0)),0)</f>
-        <v>2000</v>
+        <v>2000.1073845613396</v>
       </c>
       <c r="Y19" s="34">
         <f t="array" ref="Y19">IF(ISNUMBER(SUM((Trades!T$2:T$9999=Blotter!C19)*(Trades!U$2:U$9999=Blotter!B19)*(Trades!W$2:W$9999)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&gt;0))/SUM((Trades!T$2:T$9999=Blotter!C19)*(Trades!U$2:U$9999=Blotter!B19)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&gt;0))),SUM((Trades!T$2:T$9999=Blotter!C19)*(Trades!U$2:U$9999=Blotter!B19)*(Trades!W$2:W$9999)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&gt;0))/SUM((Trades!T$2:T$9999=Blotter!C19)*(Trades!U$2:U$9999=Blotter!B19)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&gt;0)),0)</f>
-        <v>1982.8</v>
+        <v>1983.0877791756002</v>
       </c>
       <c r="Z19" s="35">
         <f>IF(C$2="Last",IF(ISNUMBER(VLOOKUP(B19,Prices!A:L,8,0)),VLOOKUP(B19,Prices!A:L,8,0),0),IF(ISNUMBER(VLOOKUP(B19,Prices!A:L,12,0)),VLOOKUP(B19,Prices!A:L,12,0),0))</f>
@@ -3788,7 +3818,7 @@
         <v>3</v>
       </c>
       <c r="I20" s="28">
-        <f t="array" ref="I20">SUM((Trades!V$2:V$9999)*(Trades!U$2:U$9999=Blotter!B20)*(Trades!$T$2:T$9999=Blotter!C20))</f>
+        <f t="array" ref="I20">ROUND(SUM((Trades!V$2:V$9999)*(Trades!U$2:U$9999=Blotter!B20)*(Trades!$T$2:T$9999=Blotter!C20)),8)</f>
         <v>3</v>
       </c>
       <c r="J20" s="28">
@@ -3797,7 +3827,7 @@
       </c>
       <c r="K20" s="29">
         <f t="shared" ref="K20" si="7">L20-N20/(H20*J20)</f>
-        <v>3235</v>
+        <v>3235.297</v>
       </c>
       <c r="L20" s="29">
         <f t="shared" ref="L20" si="8">IF(I20=0,IF(H20&gt;0,X20,Y20),Z20)</f>
@@ -3809,7 +3839,7 @@
       </c>
       <c r="N20" s="95">
         <f t="array" ref="N20">-SUM((Trades!T$2:T$9999=Blotter!C20)*(Trades!U$2:U$9999=Blotter!B20)*(Trades!V$2:V$9999)*(Trades!W$2:W$9999))*J20+SUM((Trades!T$2:T$9999=Blotter!C20)*(Trades!U$2:U$9999=Blotter!B20)*(Trades!X$2:X$9999))+(L20*I20)*J20</f>
-        <v>2610</v>
+        <v>2601.0899999999965</v>
       </c>
       <c r="O20" s="29">
         <f>VLOOKUP(D20,Multiplier!B:H,3,0)</f>
@@ -3833,11 +3863,11 @@
       </c>
       <c r="U20" s="29">
         <f t="shared" ref="U20" si="12">IF(OR(F20="Futures",F20="Stocks"),IF(I20=0,0,IF(I20&gt;0,K20-P20,K20+P20)),0)</f>
-        <v>2935</v>
+        <v>2935.297</v>
       </c>
       <c r="V20" s="3">
         <f t="shared" ref="V20" si="13">IF(U20&gt;0,IF(ISNUMBER(U20/L20-1),U20/L20-1,0),0)</f>
-        <v>-0.11649608669476219</v>
+        <v>-0.11640668272125221</v>
       </c>
       <c r="X20" s="34">
         <f t="array" ref="X20">IF(ISNUMBER(SUM((Trades!T$2:T$9999=Blotter!C20)*(Trades!U$2:U$9999=Blotter!B20)*(Trades!W$2:W$9999)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0))/SUM((Trades!T$2:T$9999=Blotter!C20)*(Trades!U$2:U$9999=Blotter!B20)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0))),SUM((Trades!T$2:T$9999=Blotter!C20)*(Trades!U$2:U$9999=Blotter!B20)*(Trades!W$2:W$9999)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0))/SUM((Trades!T$2:T$9999=Blotter!C20)*(Trades!U$2:U$9999=Blotter!B20)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0)),0)</f>
@@ -8183,9 +8213,12 @@
       <c r="E3" s="10"/>
       <c r="F3" s="10"/>
       <c r="G3" s="15">
-        <v>0</v>
-      </c>
-      <c r="H3" s="51"/>
+        <v>-11195.05</v>
+      </c>
+      <c r="H3" s="6">
+        <f>-G3</f>
+        <v>11195.05</v>
+      </c>
     </row>
     <row r="4" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B4" s="17" t="s">
@@ -8195,10 +8228,12 @@
       <c r="D4" s="10"/>
       <c r="E4" s="10"/>
       <c r="F4" s="10"/>
-      <c r="G4" s="15"/>
+      <c r="G4" s="15">
+        <v>11636.31</v>
+      </c>
       <c r="H4" s="6">
         <f>-G4</f>
-        <v>0</v>
+        <v>-11636.31</v>
       </c>
     </row>
     <row r="5" spans="2:8" x14ac:dyDescent="0.4">
@@ -8210,10 +8245,7 @@
       <c r="E5" s="10"/>
       <c r="F5" s="10"/>
       <c r="G5" s="15"/>
-      <c r="H5" s="6">
-        <f>(C9*E9*100)</f>
-        <v>0</v>
-      </c>
+      <c r="H5" s="6"/>
     </row>
     <row r="6" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B6" s="17" t="s">
@@ -8224,10 +8256,7 @@
       <c r="E6" s="10"/>
       <c r="F6" s="10"/>
       <c r="G6" s="15"/>
-      <c r="H6" s="6">
-        <f>(C10*E10*100)</f>
-        <v>0</v>
-      </c>
+      <c r="H6" s="6"/>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B7" s="17" t="s">
@@ -8238,21 +8267,26 @@
       <c r="E7" s="10"/>
       <c r="F7" s="10"/>
       <c r="G7" s="15"/>
-      <c r="H7" s="6">
-        <f>(C11*E11*100)</f>
-        <v>0</v>
-      </c>
+      <c r="H7" s="6"/>
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B8" s="17" t="s">
         <v>154</v>
       </c>
-      <c r="C8" s="17"/>
+      <c r="C8" s="96">
+        <v>2.5000000000000001E-2</v>
+      </c>
       <c r="D8" s="10"/>
-      <c r="E8" s="10"/>
+      <c r="E8" s="11">
+        <f>E12</f>
+        <v>10000</v>
+      </c>
       <c r="F8" s="10"/>
       <c r="G8" s="15"/>
-      <c r="H8" s="6"/>
+      <c r="H8" s="6">
+        <f>(C8*E8*100)</f>
+        <v>25000</v>
+      </c>
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B9" s="17" t="s">
@@ -8292,11 +8326,23 @@
         <v>134</v>
       </c>
       <c r="C12" s="58"/>
-      <c r="D12" s="54"/>
-      <c r="E12" s="55"/>
-      <c r="F12" s="54"/>
-      <c r="G12" s="65"/>
-      <c r="H12" s="65"/>
+      <c r="D12" s="54">
+        <v>98.87</v>
+      </c>
+      <c r="E12" s="55">
+        <v>10000</v>
+      </c>
+      <c r="F12" s="54">
+        <v>98.88</v>
+      </c>
+      <c r="G12" s="65">
+        <f>(F12-D12)*E12</f>
+        <v>99.999999999909051</v>
+      </c>
+      <c r="H12" s="65">
+        <f>(100-D12)*E12</f>
+        <v>11299.999999999955</v>
+      </c>
     </row>
     <row r="13" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B13" s="17" t="s">
@@ -8308,11 +8354,11 @@
       <c r="F13" s="10"/>
       <c r="G13" s="6">
         <f>SUM(G3:G12)</f>
-        <v>0</v>
+        <v>541.25999999990927</v>
       </c>
       <c r="H13" s="6">
         <f>SUM(H3:H12)</f>
-        <v>0</v>
+        <v>35858.739999999954</v>
       </c>
     </row>
   </sheetData>
@@ -8324,12 +8370,12 @@
       <formula>$L13&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H4:H12">
+  <conditionalFormatting sqref="H3:H12">
     <cfRule type="expression" dxfId="1" priority="1">
-      <formula>$L4&lt;0</formula>
+      <formula>$L3&lt;0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="0" priority="2">
-      <formula>$L4&gt;0</formula>
+      <formula>$L3&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8494,11 +8540,11 @@
       <c r="H5" s="67"/>
       <c r="I5" s="70">
         <f>Blotter!C$4-SUM(NAV!I$4:I4)</f>
-        <v>5794.6253060739982</v>
+        <v>3664.5906320098998</v>
       </c>
       <c r="J5" s="70">
         <f t="shared" si="2"/>
-        <v>1005794.625306074</v>
+        <v>1003664.5906320099</v>
       </c>
       <c r="K5" s="70">
         <f t="shared" si="3"/>
@@ -8506,19 +8552,19 @@
       </c>
       <c r="L5" s="71">
         <f t="shared" si="4"/>
-        <v>1005.7946253060741</v>
+        <v>1003.6645906320099</v>
       </c>
       <c r="M5" s="72">
         <f t="shared" si="5"/>
-        <v>5.7946253060741082E-3</v>
+        <v>3.6645906320098565E-3</v>
       </c>
       <c r="N5" s="73">
         <f t="shared" ref="N5" si="6">L5/L4-1</f>
-        <v>5.7946253060741082E-3</v>
+        <v>3.6645906320098565E-3</v>
       </c>
       <c r="O5" s="75">
         <f>STDEVP(N$4:N5)*SQRT(12)</f>
-        <v>1.0036585440944712E-2</v>
+        <v>6.3472571635820136E-3</v>
       </c>
     </row>
     <row r="6" spans="2:18" ht="14.25" x14ac:dyDescent="0.4">
@@ -8914,7 +8960,7 @@
       </c>
       <c r="D4" s="6">
         <f t="array" ref="D4">SUM((Blotter!C$19:C$1013=C4)*(Blotter!N$19:N$1013)*1)</f>
-        <v>3184.6253060739982</v>
+        <v>522.24063200999399</v>
       </c>
       <c r="E4" s="6">
         <f t="array" ref="E4">SUM((Blotter!B$19:C$1013=C4)*(Blotter!R$19:R$1013)*1)</f>
@@ -8922,32 +8968,32 @@
       </c>
       <c r="F4" s="30">
         <f t="shared" ref="F4" si="0">IF(ISNUMBER(D4/E4),D4/E4,0)</f>
-        <v>0.30329764819752364</v>
+        <v>4.9737203048570856E-2</v>
       </c>
       <c r="G4" s="36" t="str">
         <f t="array" ref="G4">IF(SUM((Blotter!C$19:C$1013=PLB!C4)*(Blotter!M$19:M$1013))=0,"C","O")</f>
-        <v>O</v>
+        <v>C</v>
       </c>
       <c r="H4" s="16">
         <f>J3+D4</f>
-        <v>1003184.625306074</v>
+        <v>1000522.24063201</v>
       </c>
       <c r="I4" s="16"/>
       <c r="J4" s="16">
         <f>H4+I4</f>
-        <v>1003184.625306074</v>
+        <v>1000522.24063201</v>
       </c>
       <c r="K4" s="3">
         <f>H4/J3-1</f>
-        <v>3.184625306074107E-3</v>
+        <v>5.2224063201000703E-4</v>
       </c>
       <c r="L4" s="3">
         <f>(1+K4)*(1+L3)-1</f>
-        <v>3.184625306074107E-3</v>
+        <v>5.2224063201000703E-4</v>
       </c>
       <c r="M4" s="6">
         <f>O3-IF(G4="O",O3*1%,-D4)</f>
-        <v>990000</v>
+        <v>1000522.24063201</v>
       </c>
       <c r="N4" s="16">
         <f>I4</f>
@@ -8955,15 +9001,15 @@
       </c>
       <c r="O4" s="6">
         <f>M4+N4</f>
-        <v>990000</v>
+        <v>1000522.24063201</v>
       </c>
       <c r="P4" s="3">
         <f>M4/O3-1</f>
-        <v>-1.0000000000000009E-2</v>
+        <v>5.2224063201000703E-4</v>
       </c>
       <c r="Q4" s="3">
         <f>(1+P4)*(1+Q3)-1</f>
-        <v>-1.0000000000000009E-2</v>
+        <v>5.2224063201000703E-4</v>
       </c>
       <c r="R4" s="3">
         <f>(1-1%)*(1+R3)-1</f>
@@ -8979,6 +9025,12 @@
       </c>
       <c r="V4" s="1" t="s">
         <v>202</v>
+      </c>
+      <c r="W4" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="X4" s="1" t="s">
+        <v>327</v>
       </c>
     </row>
     <row r="5" spans="2:28" x14ac:dyDescent="0.4">
@@ -8992,7 +9044,7 @@
       </c>
       <c r="D5" s="6">
         <f t="array" ref="D5">SUM((Blotter!C$19:C$1013=C5)*(Blotter!N$19:N$1013)*1)</f>
-        <v>2610</v>
+        <v>2601.0899999999965</v>
       </c>
       <c r="E5" s="6">
         <f t="array" ref="E5">SUM((Blotter!B$19:C$1013=C5)*(Blotter!R$19:R$1013)*1)</f>
@@ -9000,7 +9052,7 @@
       </c>
       <c r="F5" s="30">
         <f t="shared" ref="F5" si="1">IF(ISNUMBER(D5/E5),D5/E5,0)</f>
-        <v>0.28999999999999998</v>
+        <v>0.2890099999999996</v>
       </c>
       <c r="G5" s="36" t="str">
         <f t="array" ref="G5">IF(SUM((Blotter!C$19:C$1013=PLB!C5)*(Blotter!M$19:M$1013))=0,"C","O")</f>
@@ -9008,24 +9060,24 @@
       </c>
       <c r="H5" s="16">
         <f>J4+D5</f>
-        <v>1005794.625306074</v>
+        <v>1003123.33063201</v>
       </c>
       <c r="I5" s="16"/>
       <c r="J5" s="16">
         <f>H5+I5</f>
-        <v>1005794.625306074</v>
+        <v>1003123.33063201</v>
       </c>
       <c r="K5" s="3">
         <f>H5/J4-1</f>
-        <v>2.6017145141190579E-3</v>
+        <v>2.5997323141531137E-3</v>
       </c>
       <c r="L5" s="3">
         <f>(1+K5)*(1+L4)-1</f>
-        <v>5.7946253060741082E-3</v>
+        <v>3.1233306320099796E-3</v>
       </c>
       <c r="M5" s="6">
         <f>O4-IF(G5="O",O4*1%,-D5)</f>
-        <v>980100</v>
+        <v>990517.01822568988</v>
       </c>
       <c r="N5" s="16">
         <f>I5</f>
@@ -9033,7 +9085,7 @@
       </c>
       <c r="O5" s="6">
         <f>M5+N5</f>
-        <v>980100</v>
+        <v>990517.01822568988</v>
       </c>
       <c r="P5" s="3">
         <f>M5/O4-1</f>
@@ -9041,7 +9093,7 @@
       </c>
       <c r="Q5" s="3">
         <f>(1+P5)*(1+Q4)-1</f>
-        <v>-1.9900000000000029E-2</v>
+        <v>-9.482981774310062E-3</v>
       </c>
       <c r="R5" s="3">
         <f>(1-1%)*(1+R4)-1</f>
@@ -9057,6 +9109,12 @@
       </c>
       <c r="V5" s="1" t="s">
         <v>319</v>
+      </c>
+      <c r="W5" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="X5" s="1" t="s">
+        <v>329</v>
       </c>
     </row>
     <row r="6" spans="2:28" x14ac:dyDescent="0.4">
@@ -11938,63 +11996,72 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>196</v>
+        <v>321</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>62</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>197</v>
+        <v>61</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>198</v>
+        <v>304</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>199</v>
+        <v>322</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>34</v>
       </c>
       <c r="H2" s="1">
-        <v>1</v>
+        <v>10</v>
+      </c>
+      <c r="J2" s="44">
+        <v>46156</v>
       </c>
       <c r="L2" s="44">
-        <v>46084</v>
+        <v>46090</v>
       </c>
       <c r="M2" s="1" t="s">
         <v>90</v>
       </c>
       <c r="N2" s="1">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="O2" s="1">
-        <v>1986.6</v>
+        <v>3235</v>
       </c>
       <c r="P2" s="1">
-        <v>12116.947392599999</v>
+        <v>32350</v>
       </c>
       <c r="Q2" s="1">
-        <v>-21.810505307</v>
+        <v>-2.97</v>
       </c>
       <c r="R2" s="1" t="s">
         <v>62</v>
       </c>
       <c r="T2" s="43">
         <f>IF(ISNUMBER(VLOOKUP(U2,Blotter!B:C,2,0)),VLOOKUP(U2,Blotter!B:C,2,0),"")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U2" s="42" t="str">
         <f>D2</f>
-        <v>ETH.USD-PAXOS</v>
+        <v>CCK6</v>
       </c>
       <c r="V2" s="42">
         <f>N2</f>
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="W2" s="42">
         <f>O2</f>
-        <v>1986.6</v>
+        <v>3235</v>
       </c>
       <c r="X2" s="42">
         <f>Q2</f>
-        <v>-21.810505307</v>
+        <v>-2.97</v>
       </c>
       <c r="Z2" s="1" t="s">
         <v>132</v>
@@ -12005,63 +12072,72 @@
     </row>
     <row r="3" spans="1:31" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
-        <v>196</v>
+        <v>321</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>62</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>197</v>
+        <v>61</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>198</v>
+        <v>304</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>199</v>
+        <v>322</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>34</v>
       </c>
       <c r="H3" s="1">
-        <v>1</v>
+        <v>10</v>
+      </c>
+      <c r="J3" s="44">
+        <v>46156</v>
       </c>
       <c r="L3" s="44">
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>318</v>
+        <v>90</v>
       </c>
       <c r="N3" s="1">
-        <v>-50</v>
+        <v>2</v>
       </c>
       <c r="O3" s="1">
-        <v>2000</v>
+        <v>3235</v>
       </c>
       <c r="P3" s="1">
-        <v>-6000</v>
+        <v>64700</v>
       </c>
       <c r="Q3" s="1">
-        <v>-9.2536833119999997</v>
+        <v>-5.94</v>
       </c>
       <c r="R3" s="1" t="s">
         <v>62</v>
       </c>
       <c r="T3" s="43">
         <f>IF(ISNUMBER(VLOOKUP(U3,Blotter!B:C,2,0)),VLOOKUP(U3,Blotter!B:C,2,0),"")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U3" s="42" t="str">
         <f t="shared" ref="U3:U17" si="0">D3</f>
-        <v>ETH.USD-PAXOS</v>
+        <v>CCK6</v>
       </c>
       <c r="V3" s="42">
         <f t="shared" ref="V3:V17" si="1">N3</f>
-        <v>-50</v>
+        <v>2</v>
       </c>
       <c r="W3" s="42">
         <f t="shared" ref="W3:W17" si="2">O3</f>
-        <v>2000</v>
+        <v>3235</v>
       </c>
       <c r="X3" s="42">
         <f t="shared" ref="X3:X17" si="3">Q3</f>
-        <v>-9.2536833119999997</v>
+        <v>-5.94</v>
       </c>
       <c r="AC3" s="44"/>
       <c r="AD3" s="45"/>
@@ -12069,955 +12145,2351 @@
     </row>
     <row r="4" spans="1:31" x14ac:dyDescent="0.4">
       <c r="A4" s="1" t="s">
-        <v>196</v>
+        <v>321</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>62</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>197</v>
+        <v>323</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>198</v>
+        <v>324</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>199</v>
+        <v>324</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>325</v>
       </c>
       <c r="H4" s="1">
         <v>1</v>
       </c>
       <c r="L4" s="44">
-        <v>46084</v>
+        <v>46090</v>
       </c>
       <c r="M4" s="1" t="s">
         <v>90</v>
       </c>
       <c r="N4" s="1">
-        <v>50</v>
+        <v>1000000</v>
       </c>
       <c r="O4" s="1">
-        <v>1979</v>
+        <v>98.875</v>
       </c>
       <c r="P4" s="1">
-        <v>12116.947392599999</v>
+        <v>988750</v>
       </c>
       <c r="Q4" s="1">
-        <v>-21.810505307</v>
+        <v>-20</v>
       </c>
       <c r="R4" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="T4" s="43">
+      <c r="T4" s="43" t="str">
         <f>IF(ISNUMBER(VLOOKUP(U4,Blotter!B:C,2,0)),VLOOKUP(U4,Blotter!B:C,2,0),"")</f>
-        <v>1</v>
+        <v/>
       </c>
       <c r="U4" s="42" t="str">
         <f t="shared" si="0"/>
-        <v>ETH.USD-PAXOS</v>
+        <v>T 2 1/2 03/31/27</v>
       </c>
       <c r="V4" s="42">
         <f t="shared" si="1"/>
-        <v>50</v>
+        <v>1000000</v>
       </c>
       <c r="W4" s="42">
         <f t="shared" si="2"/>
-        <v>1979</v>
+        <v>98.875</v>
       </c>
       <c r="X4" s="42">
         <f t="shared" si="3"/>
-        <v>-21.810505307</v>
+        <v>-20</v>
       </c>
       <c r="AC4" s="44"/>
       <c r="AD4" s="45"/>
       <c r="AE4" s="41"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.4">
+      <c r="A5" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>197</v>
+      </c>
       <c r="D5" s="1" t="s">
-        <v>304</v>
+        <v>198</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>199</v>
       </c>
       <c r="H5" s="1">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="L5" s="44">
-        <v>46090</v>
+        <v>46084</v>
       </c>
       <c r="M5" s="1" t="s">
         <v>90</v>
       </c>
       <c r="N5" s="1">
-        <v>3</v>
+        <f>6.1104122</f>
+        <v>6.1104121999999998</v>
       </c>
       <c r="O5" s="1">
-        <v>3235</v>
+        <v>1983</v>
+      </c>
+      <c r="P5" s="1">
+        <v>12116.947392599999</v>
+      </c>
+      <c r="Q5" s="1">
+        <v>-21.810505307</v>
+      </c>
+      <c r="R5" s="1" t="s">
+        <v>62</v>
       </c>
       <c r="T5" s="43">
         <f>IF(ISNUMBER(VLOOKUP(U5,Blotter!B:C,2,0)),VLOOKUP(U5,Blotter!B:C,2,0),"")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U5" s="42" t="str">
         <f t="shared" si="0"/>
-        <v>CCK6</v>
+        <v>ETH.USD-PAXOS</v>
       </c>
       <c r="V5" s="42">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>6.1104121999999998</v>
       </c>
       <c r="W5" s="42">
         <f t="shared" si="2"/>
-        <v>3235</v>
+        <v>1983</v>
       </c>
       <c r="X5" s="42">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>-21.810505307</v>
       </c>
       <c r="AC5" s="44"/>
       <c r="AD5" s="45"/>
       <c r="AE5" s="41"/>
     </row>
     <row r="6" spans="1:31" x14ac:dyDescent="0.4">
-      <c r="T6" s="43" t="str">
+      <c r="A6" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="H6" s="1">
+        <v>1</v>
+      </c>
+      <c r="L6" s="44">
+        <v>46084</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="N6" s="1">
+        <v>5.8970321700000001</v>
+      </c>
+      <c r="O6" s="1">
+        <v>1983.1</v>
+      </c>
+      <c r="P6" s="1">
+        <v>11694.404496327001</v>
+      </c>
+      <c r="Q6" s="1">
+        <v>-21.049928092999998</v>
+      </c>
+      <c r="R6" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="T6" s="43">
         <f>IF(ISNUMBER(VLOOKUP(U6,Blotter!B:C,2,0)),VLOOKUP(U6,Blotter!B:C,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="U6" s="42">
+        <v>1</v>
+      </c>
+      <c r="U6" s="42" t="str">
         <f t="shared" ref="U6" si="4">D6</f>
-        <v>0</v>
+        <v>ETH.USD-PAXOS</v>
       </c>
       <c r="V6" s="42">
         <f t="shared" ref="V6" si="5">N6</f>
-        <v>0</v>
+        <v>5.8970321700000001</v>
       </c>
       <c r="W6" s="42">
         <f t="shared" ref="W6" si="6">O6</f>
-        <v>0</v>
+        <v>1983.1</v>
       </c>
       <c r="X6" s="42">
         <f t="shared" ref="X6" si="7">Q6</f>
-        <v>0</v>
+        <v>-21.049928092999998</v>
       </c>
       <c r="AC6" s="44"/>
       <c r="AD6" s="45"/>
       <c r="AE6" s="41"/>
     </row>
     <row r="7" spans="1:31" x14ac:dyDescent="0.4">
-      <c r="T7" s="43" t="str">
+      <c r="A7" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="H7" s="1">
+        <v>1</v>
+      </c>
+      <c r="L7" s="44">
+        <v>46084</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="N7" s="1">
+        <v>3.9942700000000003E-3</v>
+      </c>
+      <c r="O7" s="1">
+        <v>1983.1</v>
+      </c>
+      <c r="P7" s="1">
+        <v>7.9210368369999999</v>
+      </c>
+      <c r="Q7" s="1">
+        <v>-1.4257865999999999E-2</v>
+      </c>
+      <c r="R7" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="T7" s="43">
         <f>IF(ISNUMBER(VLOOKUP(U7,Blotter!B:C,2,0)),VLOOKUP(U7,Blotter!B:C,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="U7" s="42">
+        <v>1</v>
+      </c>
+      <c r="U7" s="42" t="str">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>ETH.USD-PAXOS</v>
       </c>
       <c r="V7" s="42">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>3.9942700000000003E-3</v>
       </c>
       <c r="W7" s="42">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1983.1</v>
       </c>
       <c r="X7" s="42">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>-1.4257865999999999E-2</v>
       </c>
       <c r="AC7" s="44"/>
       <c r="AD7" s="45"/>
       <c r="AE7" s="41"/>
     </row>
     <row r="8" spans="1:31" x14ac:dyDescent="0.4">
-      <c r="T8" s="43" t="str">
+      <c r="A8" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="H8" s="1">
+        <v>1</v>
+      </c>
+      <c r="L8" s="44">
+        <v>46084</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="N8" s="1">
+        <v>0.54177474999999997</v>
+      </c>
+      <c r="O8" s="1">
+        <v>1983.1</v>
+      </c>
+      <c r="P8" s="1">
+        <v>1074.393506725</v>
+      </c>
+      <c r="Q8" s="1">
+        <v>-1.933908312</v>
+      </c>
+      <c r="R8" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="T8" s="43">
         <f>IF(ISNUMBER(VLOOKUP(U8,Blotter!B:C,2,0)),VLOOKUP(U8,Blotter!B:C,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="U8" s="42">
+        <v>1</v>
+      </c>
+      <c r="U8" s="42" t="str">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>ETH.USD-PAXOS</v>
       </c>
       <c r="V8" s="42">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.54177474999999997</v>
       </c>
       <c r="W8" s="42">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1983.1</v>
       </c>
       <c r="X8" s="42">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>-1.933908312</v>
       </c>
       <c r="AC8" s="44"/>
       <c r="AD8" s="45"/>
       <c r="AE8" s="41"/>
     </row>
     <row r="9" spans="1:31" x14ac:dyDescent="0.4">
-      <c r="T9" s="43" t="str">
+      <c r="A9" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="H9" s="1">
+        <v>1</v>
+      </c>
+      <c r="L9" s="44">
+        <v>46084</v>
+      </c>
+      <c r="M9" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="N9" s="1">
+        <v>1.5427200000000001</v>
+      </c>
+      <c r="O9" s="1">
+        <v>1983.1</v>
+      </c>
+      <c r="P9" s="1">
+        <v>3059.3680319999999</v>
+      </c>
+      <c r="Q9" s="1">
+        <v>-5.5068624579999996</v>
+      </c>
+      <c r="R9" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="T9" s="43">
         <f>IF(ISNUMBER(VLOOKUP(U9,Blotter!B:C,2,0)),VLOOKUP(U9,Blotter!B:C,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="U9" s="42">
+        <v>1</v>
+      </c>
+      <c r="U9" s="42" t="str">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>ETH.USD-PAXOS</v>
       </c>
       <c r="V9" s="42">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.5427200000000001</v>
       </c>
       <c r="W9" s="42">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1983.1</v>
       </c>
       <c r="X9" s="42">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>-5.5068624579999996</v>
       </c>
       <c r="AC9" s="44"/>
       <c r="AD9" s="45"/>
       <c r="AE9" s="41"/>
     </row>
     <row r="10" spans="1:31" x14ac:dyDescent="0.4">
-      <c r="T10" s="43" t="str">
+      <c r="A10" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="H10" s="1">
+        <v>1</v>
+      </c>
+      <c r="L10" s="44">
+        <v>46084</v>
+      </c>
+      <c r="M10" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="N10" s="1">
+        <v>0.22177047999999999</v>
+      </c>
+      <c r="O10" s="1">
+        <v>1983.1</v>
+      </c>
+      <c r="P10" s="1">
+        <v>439.79303888800001</v>
+      </c>
+      <c r="Q10" s="1">
+        <v>-0.79162747</v>
+      </c>
+      <c r="R10" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="T10" s="43">
         <f>IF(ISNUMBER(VLOOKUP(U10,Blotter!B:C,2,0)),VLOOKUP(U10,Blotter!B:C,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="U10" s="42">
+        <v>1</v>
+      </c>
+      <c r="U10" s="42" t="str">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>ETH.USD-PAXOS</v>
       </c>
       <c r="V10" s="42">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.22177047999999999</v>
       </c>
       <c r="W10" s="42">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1983.1</v>
       </c>
       <c r="X10" s="42">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>-0.79162747</v>
       </c>
       <c r="AC10" s="44"/>
       <c r="AD10" s="45"/>
       <c r="AE10" s="41"/>
     </row>
     <row r="11" spans="1:31" x14ac:dyDescent="0.4">
-      <c r="T11" s="43" t="str">
+      <c r="A11" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="H11" s="1">
+        <v>1</v>
+      </c>
+      <c r="L11" s="44">
+        <v>46084</v>
+      </c>
+      <c r="M11" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="N11" s="1">
+        <v>0.20808973</v>
+      </c>
+      <c r="O11" s="1">
+        <v>1983.1</v>
+      </c>
+      <c r="P11" s="1">
+        <v>412.66274356299999</v>
+      </c>
+      <c r="Q11" s="1">
+        <v>-0.74279293800000001</v>
+      </c>
+      <c r="R11" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="T11" s="43">
         <f>IF(ISNUMBER(VLOOKUP(U11,Blotter!B:C,2,0)),VLOOKUP(U11,Blotter!B:C,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="U11" s="42">
+        <v>1</v>
+      </c>
+      <c r="U11" s="42" t="str">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>ETH.USD-PAXOS</v>
       </c>
       <c r="V11" s="42">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.20808973</v>
       </c>
       <c r="W11" s="42">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1983.1</v>
       </c>
       <c r="X11" s="42">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>-0.74279293800000001</v>
       </c>
       <c r="AC11" s="44"/>
       <c r="AD11" s="45"/>
       <c r="AE11" s="41"/>
     </row>
     <row r="12" spans="1:31" x14ac:dyDescent="0.4">
-      <c r="T12" s="43" t="str">
+      <c r="A12" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="H12" s="1">
+        <v>1</v>
+      </c>
+      <c r="L12" s="44">
+        <v>46084</v>
+      </c>
+      <c r="M12" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="N12" s="1">
+        <v>1.6103536000000001</v>
+      </c>
+      <c r="O12" s="1">
+        <v>1983.1</v>
+      </c>
+      <c r="P12" s="1">
+        <v>3193.4922241600002</v>
+      </c>
+      <c r="Q12" s="1">
+        <v>-5.7482860029999996</v>
+      </c>
+      <c r="R12" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="T12" s="43">
         <f>IF(ISNUMBER(VLOOKUP(U12,Blotter!B:C,2,0)),VLOOKUP(U12,Blotter!B:C,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="U12" s="42">
+        <v>1</v>
+      </c>
+      <c r="U12" s="42" t="str">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>ETH.USD-PAXOS</v>
       </c>
       <c r="V12" s="42">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.6103536000000001</v>
       </c>
       <c r="W12" s="42">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1983.1</v>
       </c>
       <c r="X12" s="42">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>-5.7482860029999996</v>
       </c>
       <c r="AC12" s="44"/>
       <c r="AD12" s="45"/>
       <c r="AE12" s="41"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.4">
-      <c r="T13" s="43" t="str">
+      <c r="A13" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="H13" s="1">
+        <v>1</v>
+      </c>
+      <c r="L13" s="44">
+        <v>46084</v>
+      </c>
+      <c r="M13" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="N13" s="1">
+        <v>0.21435478999999999</v>
+      </c>
+      <c r="O13" s="1">
+        <v>1983.1</v>
+      </c>
+      <c r="P13" s="1">
+        <v>425.08698404900002</v>
+      </c>
+      <c r="Q13" s="1">
+        <v>-0.76515657100000001</v>
+      </c>
+      <c r="R13" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="T13" s="43">
         <f>IF(ISNUMBER(VLOOKUP(U13,Blotter!B:C,2,0)),VLOOKUP(U13,Blotter!B:C,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="U13" s="42">
+        <v>1</v>
+      </c>
+      <c r="U13" s="42" t="str">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>ETH.USD-PAXOS</v>
       </c>
       <c r="V13" s="42">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.21435478999999999</v>
       </c>
       <c r="W13" s="42">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1983.1</v>
       </c>
       <c r="X13" s="42">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>-0.76515657100000001</v>
       </c>
       <c r="AC13" s="44"/>
       <c r="AD13" s="45"/>
       <c r="AE13" s="41"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.4">
-      <c r="T14" s="43" t="str">
+      <c r="A14" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="H14" s="1">
+        <v>1</v>
+      </c>
+      <c r="L14" s="44">
+        <v>46084</v>
+      </c>
+      <c r="M14" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="N14" s="1">
+        <v>0.26617475000000002</v>
+      </c>
+      <c r="O14" s="1">
+        <v>1983.1</v>
+      </c>
+      <c r="P14" s="1">
+        <v>527.85114672500004</v>
+      </c>
+      <c r="Q14" s="1">
+        <v>-0.95013206400000005</v>
+      </c>
+      <c r="R14" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="T14" s="43">
         <f>IF(ISNUMBER(VLOOKUP(U14,Blotter!B:C,2,0)),VLOOKUP(U14,Blotter!B:C,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="U14" s="42">
+        <v>1</v>
+      </c>
+      <c r="U14" s="42" t="str">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>ETH.USD-PAXOS</v>
       </c>
       <c r="V14" s="42">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.26617475000000002</v>
       </c>
       <c r="W14" s="42">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1983.1</v>
       </c>
       <c r="X14" s="42">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>-0.95013206400000005</v>
       </c>
       <c r="AC14" s="44"/>
       <c r="AD14" s="45"/>
       <c r="AE14" s="41"/>
     </row>
     <row r="15" spans="1:31" x14ac:dyDescent="0.4">
-      <c r="T15" s="43" t="str">
+      <c r="A15" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="H15" s="1">
+        <v>1</v>
+      </c>
+      <c r="L15" s="44">
+        <v>46084</v>
+      </c>
+      <c r="M15" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="N15" s="1">
+        <v>6.1193113600000002</v>
+      </c>
+      <c r="O15" s="1">
+        <v>1983.1</v>
+      </c>
+      <c r="P15" s="1">
+        <v>12135.206358015999</v>
+      </c>
+      <c r="Q15" s="1">
+        <v>-21.843371443999999</v>
+      </c>
+      <c r="R15" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="T15" s="43">
         <f>IF(ISNUMBER(VLOOKUP(U15,Blotter!B:C,2,0)),VLOOKUP(U15,Blotter!B:C,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="U15" s="42">
+        <v>1</v>
+      </c>
+      <c r="U15" s="42" t="str">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>ETH.USD-PAXOS</v>
       </c>
       <c r="V15" s="42">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>6.1193113600000002</v>
       </c>
       <c r="W15" s="42">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1983.1</v>
       </c>
       <c r="X15" s="42">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>-21.843371443999999</v>
       </c>
       <c r="AC15" s="44"/>
       <c r="AD15" s="45"/>
       <c r="AE15" s="41"/>
     </row>
     <row r="16" spans="1:31" x14ac:dyDescent="0.4">
-      <c r="T16" s="43" t="str">
+      <c r="A16" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="H16" s="1">
+        <v>1</v>
+      </c>
+      <c r="L16" s="44">
+        <v>46084</v>
+      </c>
+      <c r="M16" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="N16" s="1">
+        <v>6.1754577399999997</v>
+      </c>
+      <c r="O16" s="1">
+        <v>1983.1</v>
+      </c>
+      <c r="P16" s="1">
+        <v>12246.550244194001</v>
+      </c>
+      <c r="Q16" s="1">
+        <v>-22.043790439999999</v>
+      </c>
+      <c r="R16" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="T16" s="43">
         <f>IF(ISNUMBER(VLOOKUP(U16,Blotter!B:C,2,0)),VLOOKUP(U16,Blotter!B:C,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="U16" s="42">
+        <v>1</v>
+      </c>
+      <c r="U16" s="42" t="str">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>ETH.USD-PAXOS</v>
       </c>
       <c r="V16" s="42">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>6.1754577399999997</v>
       </c>
       <c r="W16" s="42">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1983.1</v>
       </c>
       <c r="X16" s="42">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>-22.043790439999999</v>
       </c>
       <c r="AC16" s="44"/>
       <c r="AD16" s="45"/>
       <c r="AE16" s="41"/>
     </row>
-    <row r="17" spans="20:31" x14ac:dyDescent="0.4">
-      <c r="T17" s="43" t="str">
+    <row r="17" spans="1:31" x14ac:dyDescent="0.4">
+      <c r="A17" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="H17" s="1">
+        <v>1</v>
+      </c>
+      <c r="L17" s="44">
+        <v>46084</v>
+      </c>
+      <c r="M17" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="N17" s="1">
+        <v>6.1710219200000003</v>
+      </c>
+      <c r="O17" s="1">
+        <v>1983.1</v>
+      </c>
+      <c r="P17" s="1">
+        <v>12237.753569552</v>
+      </c>
+      <c r="Q17" s="1">
+        <v>-22.027956424999999</v>
+      </c>
+      <c r="R17" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="T17" s="43">
         <f>IF(ISNUMBER(VLOOKUP(U17,Blotter!B:C,2,0)),VLOOKUP(U17,Blotter!B:C,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="U17" s="42">
+        <v>1</v>
+      </c>
+      <c r="U17" s="42" t="str">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>ETH.USD-PAXOS</v>
       </c>
       <c r="V17" s="42">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>6.1710219200000003</v>
       </c>
       <c r="W17" s="42">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1983.1</v>
       </c>
       <c r="X17" s="42">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>-22.027956424999999</v>
       </c>
       <c r="AC17" s="44"/>
       <c r="AD17" s="45"/>
       <c r="AE17" s="41"/>
     </row>
-    <row r="18" spans="20:31" x14ac:dyDescent="0.4">
-      <c r="T18" s="43" t="str">
+    <row r="18" spans="1:31" x14ac:dyDescent="0.4">
+      <c r="A18" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="H18" s="1">
+        <v>1</v>
+      </c>
+      <c r="L18" s="44">
+        <v>46084</v>
+      </c>
+      <c r="M18" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="N18" s="1">
+        <v>6.1193113600000002</v>
+      </c>
+      <c r="O18" s="1">
+        <v>1983.1</v>
+      </c>
+      <c r="P18" s="1">
+        <v>12135.206358015999</v>
+      </c>
+      <c r="Q18" s="1">
+        <v>-21.843371443999999</v>
+      </c>
+      <c r="R18" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="T18" s="43">
         <f>IF(ISNUMBER(VLOOKUP(U18,Blotter!B:C,2,0)),VLOOKUP(U18,Blotter!B:C,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="U18" s="42">
+        <v>1</v>
+      </c>
+      <c r="U18" s="42" t="str">
         <f t="shared" ref="U18:U36" si="8">D18</f>
-        <v>0</v>
+        <v>ETH.USD-PAXOS</v>
       </c>
       <c r="V18" s="42">
         <f t="shared" ref="V18:V36" si="9">N18</f>
-        <v>0</v>
+        <v>6.1193113600000002</v>
       </c>
       <c r="W18" s="42">
         <f t="shared" ref="W18:W36" si="10">O18</f>
-        <v>0</v>
+        <v>1983.1</v>
       </c>
       <c r="X18" s="42">
         <f t="shared" ref="X18:X36" si="11">Q18</f>
-        <v>0</v>
+        <v>-21.843371443999999</v>
       </c>
       <c r="AC18" s="44"/>
       <c r="AD18" s="45"/>
       <c r="AE18" s="41"/>
     </row>
-    <row r="19" spans="20:31" x14ac:dyDescent="0.4">
-      <c r="T19" s="43" t="str">
+    <row r="19" spans="1:31" x14ac:dyDescent="0.4">
+      <c r="A19" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="H19" s="1">
+        <v>1</v>
+      </c>
+      <c r="L19" s="44">
+        <v>46084</v>
+      </c>
+      <c r="M19" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="N19" s="1">
+        <v>6.1193113600000002</v>
+      </c>
+      <c r="O19" s="1">
+        <v>1983.1</v>
+      </c>
+      <c r="P19" s="1">
+        <v>12135.206358015999</v>
+      </c>
+      <c r="Q19" s="1">
+        <v>-21.843371443999999</v>
+      </c>
+      <c r="R19" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="T19" s="43">
         <f>IF(ISNUMBER(VLOOKUP(U19,Blotter!B:C,2,0)),VLOOKUP(U19,Blotter!B:C,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="U19" s="42">
+        <v>1</v>
+      </c>
+      <c r="U19" s="42" t="str">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>ETH.USD-PAXOS</v>
       </c>
       <c r="V19" s="42">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>6.1193113600000002</v>
       </c>
       <c r="W19" s="42">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>1983.1</v>
       </c>
       <c r="X19" s="42">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>-21.843371443999999</v>
       </c>
       <c r="AC19" s="44"/>
       <c r="AD19" s="45"/>
       <c r="AE19" s="41"/>
     </row>
-    <row r="20" spans="20:31" x14ac:dyDescent="0.4">
-      <c r="T20" s="43" t="str">
+    <row r="20" spans="1:31" x14ac:dyDescent="0.4">
+      <c r="A20" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="H20" s="1">
+        <v>1</v>
+      </c>
+      <c r="L20" s="44">
+        <v>46084</v>
+      </c>
+      <c r="M20" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="N20" s="1">
+        <v>2.6789095199999999</v>
+      </c>
+      <c r="O20" s="1">
+        <v>1983.1</v>
+      </c>
+      <c r="P20" s="1">
+        <v>5312.5454691120003</v>
+      </c>
+      <c r="Q20" s="1">
+        <v>-9.5625818440000003</v>
+      </c>
+      <c r="R20" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="T20" s="43">
         <f>IF(ISNUMBER(VLOOKUP(U20,Blotter!B:C,2,0)),VLOOKUP(U20,Blotter!B:C,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="U20" s="42">
+        <v>1</v>
+      </c>
+      <c r="U20" s="42" t="str">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>ETH.USD-PAXOS</v>
       </c>
       <c r="V20" s="42">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>2.6789095199999999</v>
       </c>
       <c r="W20" s="42">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>1983.1</v>
       </c>
       <c r="X20" s="42">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>-9.5625818440000003</v>
       </c>
       <c r="AC20" s="44"/>
       <c r="AD20" s="45"/>
       <c r="AE20" s="41"/>
     </row>
-    <row r="21" spans="20:31" x14ac:dyDescent="0.4">
-      <c r="T21" s="43" t="str">
+    <row r="21" spans="1:31" x14ac:dyDescent="0.4">
+      <c r="A21" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="H21" s="1">
+        <v>1</v>
+      </c>
+      <c r="L21" s="44">
+        <v>46087</v>
+      </c>
+      <c r="M21" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="N21" s="1">
+        <v>-3</v>
+      </c>
+      <c r="O21" s="1">
+        <v>2000</v>
+      </c>
+      <c r="P21" s="1">
+        <v>-6000</v>
+      </c>
+      <c r="Q21" s="1">
+        <v>-9.2536833119999997</v>
+      </c>
+      <c r="R21" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="T21" s="43">
         <f>IF(ISNUMBER(VLOOKUP(U21,Blotter!B:C,2,0)),VLOOKUP(U21,Blotter!B:C,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="U21" s="42">
+        <v>1</v>
+      </c>
+      <c r="U21" s="42" t="str">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>ETH.USD-PAXOS</v>
       </c>
       <c r="V21" s="42">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="W21" s="42">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="X21" s="42">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>-9.2536833119999997</v>
       </c>
       <c r="AC21" s="44"/>
       <c r="AD21" s="45"/>
       <c r="AE21" s="41"/>
     </row>
-    <row r="22" spans="20:31" x14ac:dyDescent="0.4">
-      <c r="T22" s="43" t="str">
+    <row r="22" spans="1:31" x14ac:dyDescent="0.4">
+      <c r="A22" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="H22" s="1">
+        <v>1</v>
+      </c>
+      <c r="L22" s="44">
+        <v>46087</v>
+      </c>
+      <c r="M22" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="N22" s="1">
+        <v>-5.4977520200000001</v>
+      </c>
+      <c r="O22" s="1">
+        <v>2000</v>
+      </c>
+      <c r="P22" s="1">
+        <v>-10995.50404</v>
+      </c>
+      <c r="Q22" s="1">
+        <v>-16.49325606</v>
+      </c>
+      <c r="R22" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="T22" s="43">
         <f>IF(ISNUMBER(VLOOKUP(U22,Blotter!B:C,2,0)),VLOOKUP(U22,Blotter!B:C,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="U22" s="42">
+        <v>1</v>
+      </c>
+      <c r="U22" s="42" t="str">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>ETH.USD-PAXOS</v>
       </c>
       <c r="V22" s="42">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-5.4977520200000001</v>
       </c>
       <c r="W22" s="42">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="X22" s="42">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>-16.49325606</v>
       </c>
       <c r="AC22" s="44"/>
       <c r="AD22" s="45"/>
       <c r="AE22" s="41"/>
     </row>
-    <row r="23" spans="20:31" x14ac:dyDescent="0.4">
-      <c r="T23" s="43" t="str">
+    <row r="23" spans="1:31" x14ac:dyDescent="0.4">
+      <c r="A23" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="H23" s="1">
+        <v>1</v>
+      </c>
+      <c r="L23" s="44">
+        <v>46087</v>
+      </c>
+      <c r="M23" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="N23" s="1">
+        <v>-5.5477520199999999</v>
+      </c>
+      <c r="O23" s="1">
+        <v>2000</v>
+      </c>
+      <c r="P23" s="1">
+        <v>-11095.50404</v>
+      </c>
+      <c r="Q23" s="1">
+        <v>-16.643256059999999</v>
+      </c>
+      <c r="R23" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="T23" s="43">
         <f>IF(ISNUMBER(VLOOKUP(U23,Blotter!B:C,2,0)),VLOOKUP(U23,Blotter!B:C,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="U23" s="42">
+        <v>1</v>
+      </c>
+      <c r="U23" s="42" t="str">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>ETH.USD-PAXOS</v>
       </c>
       <c r="V23" s="42">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-5.5477520199999999</v>
       </c>
       <c r="W23" s="42">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="X23" s="42">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>-16.643256059999999</v>
       </c>
       <c r="AC23" s="44"/>
       <c r="AD23" s="45"/>
       <c r="AE23" s="41"/>
     </row>
-    <row r="24" spans="20:31" x14ac:dyDescent="0.4">
-      <c r="T24" s="43" t="str">
+    <row r="24" spans="1:31" x14ac:dyDescent="0.4">
+      <c r="A24" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="H24" s="1">
+        <v>1</v>
+      </c>
+      <c r="L24" s="44">
+        <v>46087</v>
+      </c>
+      <c r="M24" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="N24" s="1">
+        <v>-5.7895520200000004</v>
+      </c>
+      <c r="O24" s="1">
+        <v>2000</v>
+      </c>
+      <c r="P24" s="1">
+        <v>-11579.10404</v>
+      </c>
+      <c r="Q24" s="1">
+        <v>-17.368656059999999</v>
+      </c>
+      <c r="R24" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="T24" s="43">
         <f>IF(ISNUMBER(VLOOKUP(U24,Blotter!B:C,2,0)),VLOOKUP(U24,Blotter!B:C,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="U24" s="42">
+        <v>1</v>
+      </c>
+      <c r="U24" s="42" t="str">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>ETH.USD-PAXOS</v>
       </c>
       <c r="V24" s="42">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-5.7895520200000004</v>
       </c>
       <c r="W24" s="42">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="X24" s="42">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>-17.368656059999999</v>
       </c>
       <c r="AC24" s="44"/>
       <c r="AD24" s="45"/>
       <c r="AE24" s="41"/>
     </row>
-    <row r="25" spans="20:31" x14ac:dyDescent="0.4">
-      <c r="T25" s="43" t="str">
+    <row r="25" spans="1:31" x14ac:dyDescent="0.4">
+      <c r="A25" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="H25" s="1">
+        <v>1</v>
+      </c>
+      <c r="L25" s="44">
+        <v>46087</v>
+      </c>
+      <c r="M25" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="N25" s="1">
+        <v>-0.05</v>
+      </c>
+      <c r="O25" s="1">
+        <v>2000</v>
+      </c>
+      <c r="P25" s="1">
+        <v>-100</v>
+      </c>
+      <c r="Q25" s="1">
+        <v>-0.15</v>
+      </c>
+      <c r="R25" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="T25" s="43">
         <f>IF(ISNUMBER(VLOOKUP(U25,Blotter!B:C,2,0)),VLOOKUP(U25,Blotter!B:C,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="U25" s="42">
+        <v>1</v>
+      </c>
+      <c r="U25" s="42" t="str">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>ETH.USD-PAXOS</v>
       </c>
       <c r="V25" s="42">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="W25" s="42">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="X25" s="42">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>-0.15</v>
       </c>
       <c r="AC25" s="44"/>
       <c r="AD25" s="45"/>
       <c r="AE25" s="41"/>
     </row>
-    <row r="26" spans="20:31" x14ac:dyDescent="0.4">
-      <c r="T26" s="43" t="str">
+    <row r="26" spans="1:31" x14ac:dyDescent="0.4">
+      <c r="A26" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="H26" s="1">
+        <v>1</v>
+      </c>
+      <c r="L26" s="44">
+        <v>46087</v>
+      </c>
+      <c r="M26" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="N26" s="1">
+        <v>-0.2918</v>
+      </c>
+      <c r="O26" s="1">
+        <v>2000</v>
+      </c>
+      <c r="P26" s="1">
+        <v>-583.6</v>
+      </c>
+      <c r="Q26" s="1">
+        <v>-0.87539999999999996</v>
+      </c>
+      <c r="R26" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="T26" s="43">
         <f>IF(ISNUMBER(VLOOKUP(U26,Blotter!B:C,2,0)),VLOOKUP(U26,Blotter!B:C,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="U26" s="42">
+        <v>1</v>
+      </c>
+      <c r="U26" s="42" t="str">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>ETH.USD-PAXOS</v>
       </c>
       <c r="V26" s="42">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-0.2918</v>
       </c>
       <c r="W26" s="42">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="X26" s="42">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>-0.87539999999999996</v>
       </c>
       <c r="AC26" s="44"/>
       <c r="AD26" s="45"/>
       <c r="AE26" s="41"/>
     </row>
-    <row r="27" spans="20:31" x14ac:dyDescent="0.4">
-      <c r="T27" s="43" t="str">
+    <row r="27" spans="1:31" x14ac:dyDescent="0.4">
+      <c r="A27" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="H27" s="1">
+        <v>1</v>
+      </c>
+      <c r="L27" s="44">
+        <v>46087</v>
+      </c>
+      <c r="M27" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="N27" s="1">
+        <v>-5.7895520200000004</v>
+      </c>
+      <c r="O27" s="1">
+        <v>2000</v>
+      </c>
+      <c r="P27" s="1">
+        <v>-11579.10404</v>
+      </c>
+      <c r="Q27" s="1">
+        <v>-17.368656059999999</v>
+      </c>
+      <c r="R27" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="T27" s="43">
         <f>IF(ISNUMBER(VLOOKUP(U27,Blotter!B:C,2,0)),VLOOKUP(U27,Blotter!B:C,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="U27" s="42">
+        <v>1</v>
+      </c>
+      <c r="U27" s="42" t="str">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>ETH.USD-PAXOS</v>
       </c>
       <c r="V27" s="42">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-5.7895520200000004</v>
       </c>
       <c r="W27" s="42">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="X27" s="42">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>-17.368656059999999</v>
       </c>
       <c r="AC27" s="44"/>
       <c r="AD27" s="45"/>
       <c r="AE27" s="41"/>
     </row>
-    <row r="28" spans="20:31" x14ac:dyDescent="0.4">
-      <c r="T28" s="43" t="str">
+    <row r="28" spans="1:31" x14ac:dyDescent="0.4">
+      <c r="A28" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="H28" s="1">
+        <v>1</v>
+      </c>
+      <c r="L28" s="44">
+        <v>46087</v>
+      </c>
+      <c r="M28" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="N28" s="1">
+        <v>-0.24179999999999999</v>
+      </c>
+      <c r="O28" s="1">
+        <v>2000</v>
+      </c>
+      <c r="P28" s="1">
+        <v>-483.6</v>
+      </c>
+      <c r="Q28" s="1">
+        <v>-0.72540000000000004</v>
+      </c>
+      <c r="R28" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="T28" s="43">
         <f>IF(ISNUMBER(VLOOKUP(U28,Blotter!B:C,2,0)),VLOOKUP(U28,Blotter!B:C,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="U28" s="42">
+        <v>1</v>
+      </c>
+      <c r="U28" s="42" t="str">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>ETH.USD-PAXOS</v>
       </c>
       <c r="V28" s="42">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-0.24179999999999999</v>
       </c>
       <c r="W28" s="42">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="X28" s="42">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>-0.72540000000000004</v>
       </c>
       <c r="AC28" s="44"/>
       <c r="AD28" s="45"/>
       <c r="AE28" s="41"/>
     </row>
-    <row r="29" spans="20:31" x14ac:dyDescent="0.4">
-      <c r="T29" s="43" t="str">
+    <row r="29" spans="1:31" x14ac:dyDescent="0.4">
+      <c r="A29" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="H29" s="1">
+        <v>1</v>
+      </c>
+      <c r="L29" s="44">
+        <v>46087</v>
+      </c>
+      <c r="M29" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="N29" s="1">
+        <v>-0.24179999999999999</v>
+      </c>
+      <c r="O29" s="1">
+        <v>2000</v>
+      </c>
+      <c r="P29" s="1">
+        <v>-483.6</v>
+      </c>
+      <c r="Q29" s="1">
+        <v>-0.72540000000000004</v>
+      </c>
+      <c r="R29" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="T29" s="43">
         <f>IF(ISNUMBER(VLOOKUP(U29,Blotter!B:C,2,0)),VLOOKUP(U29,Blotter!B:C,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="U29" s="42">
+        <v>1</v>
+      </c>
+      <c r="U29" s="42" t="str">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>ETH.USD-PAXOS</v>
       </c>
       <c r="V29" s="42">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-0.24179999999999999</v>
       </c>
       <c r="W29" s="42">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="X29" s="42">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>-0.72540000000000004</v>
       </c>
       <c r="AC29" s="44"/>
       <c r="AD29" s="45"/>
       <c r="AE29" s="41"/>
     </row>
-    <row r="30" spans="20:31" x14ac:dyDescent="0.4">
-      <c r="T30" s="43" t="str">
+    <row r="30" spans="1:31" x14ac:dyDescent="0.4">
+      <c r="A30" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="H30" s="1">
+        <v>1</v>
+      </c>
+      <c r="L30" s="44">
+        <v>46087</v>
+      </c>
+      <c r="M30" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="N30" s="1">
+        <v>-5.9996570199999999</v>
+      </c>
+      <c r="O30" s="1">
+        <v>2000</v>
+      </c>
+      <c r="P30" s="1">
+        <v>-11999.314039999999</v>
+      </c>
+      <c r="Q30" s="1">
+        <v>-17.998971059999999</v>
+      </c>
+      <c r="R30" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="T30" s="43">
         <f>IF(ISNUMBER(VLOOKUP(U30,Blotter!B:C,2,0)),VLOOKUP(U30,Blotter!B:C,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="U30" s="42">
+        <v>1</v>
+      </c>
+      <c r="U30" s="42" t="str">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>ETH.USD-PAXOS</v>
       </c>
       <c r="V30" s="42">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-5.9996570199999999</v>
       </c>
       <c r="W30" s="42">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="X30" s="42">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>-17.998971059999999</v>
       </c>
       <c r="AC30" s="44"/>
       <c r="AD30" s="45"/>
       <c r="AE30" s="41"/>
     </row>
-    <row r="31" spans="20:31" x14ac:dyDescent="0.4">
-      <c r="T31" s="43" t="str">
+    <row r="31" spans="1:31" x14ac:dyDescent="0.4">
+      <c r="A31" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="H31" s="1">
+        <v>1</v>
+      </c>
+      <c r="L31" s="44">
+        <v>46087</v>
+      </c>
+      <c r="M31" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="N31" s="1">
+        <v>-2.4973153799999999</v>
+      </c>
+      <c r="O31" s="1">
+        <v>2002.15</v>
+      </c>
+      <c r="P31" s="1">
+        <v>-4999.9999880670002</v>
+      </c>
+      <c r="Q31" s="1">
+        <v>-7.4999999820000003</v>
+      </c>
+      <c r="R31" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="T31" s="43">
         <f>IF(ISNUMBER(VLOOKUP(U31,Blotter!B:C,2,0)),VLOOKUP(U31,Blotter!B:C,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="U31" s="42">
+        <v>1</v>
+      </c>
+      <c r="U31" s="42" t="str">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>ETH.USD-PAXOS</v>
       </c>
       <c r="V31" s="42">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-2.4973153799999999</v>
       </c>
       <c r="W31" s="42">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>2002.15</v>
       </c>
       <c r="X31" s="42">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>-7.4999999820000003</v>
       </c>
       <c r="AC31" s="44"/>
       <c r="AD31" s="45"/>
       <c r="AE31" s="41"/>
     </row>
-    <row r="32" spans="20:31" x14ac:dyDescent="0.4">
-      <c r="T32" s="43" t="str">
+    <row r="32" spans="1:31" x14ac:dyDescent="0.4">
+      <c r="A32" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="H32" s="1">
+        <v>1</v>
+      </c>
+      <c r="L32" s="44">
+        <v>46087</v>
+      </c>
+      <c r="M32" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="N32" s="1">
+        <v>-1.0847240199999999</v>
+      </c>
+      <c r="O32" s="1">
+        <v>2000</v>
+      </c>
+      <c r="P32" s="1">
+        <v>-2169.4480400000002</v>
+      </c>
+      <c r="Q32" s="1">
+        <v>-3.2541720600000001</v>
+      </c>
+      <c r="R32" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="T32" s="43">
         <f>IF(ISNUMBER(VLOOKUP(U32,Blotter!B:C,2,0)),VLOOKUP(U32,Blotter!B:C,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="U32" s="42">
+        <v>1</v>
+      </c>
+      <c r="U32" s="42" t="str">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>ETH.USD-PAXOS</v>
       </c>
       <c r="V32" s="42">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-1.0847240199999999</v>
       </c>
       <c r="W32" s="42">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="X32" s="42">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>-3.2541720600000001</v>
       </c>
       <c r="AC32" s="44"/>
       <c r="AD32" s="45"/>
       <c r="AE32" s="41"/>
     </row>
-    <row r="33" spans="20:31" x14ac:dyDescent="0.4">
-      <c r="T33" s="43" t="str">
+    <row r="33" spans="1:31" x14ac:dyDescent="0.4">
+      <c r="A33" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="H33" s="1">
+        <v>1</v>
+      </c>
+      <c r="L33" s="44">
+        <v>46087</v>
+      </c>
+      <c r="M33" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="N33" s="1">
+        <v>-0.21252689</v>
+      </c>
+      <c r="O33" s="1">
+        <v>2000</v>
+      </c>
+      <c r="P33" s="1">
+        <v>-425.05378000000002</v>
+      </c>
+      <c r="Q33" s="1">
+        <v>-0.63758066999999996</v>
+      </c>
+      <c r="R33" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="T33" s="43">
         <f>IF(ISNUMBER(VLOOKUP(U33,Blotter!B:C,2,0)),VLOOKUP(U33,Blotter!B:C,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="U33" s="42">
+        <v>1</v>
+      </c>
+      <c r="U33" s="42" t="str">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>ETH.USD-PAXOS</v>
       </c>
       <c r="V33" s="42">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-0.21252689</v>
       </c>
       <c r="W33" s="42">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="X33" s="42">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>-0.63758066999999996</v>
       </c>
       <c r="AC33" s="44"/>
       <c r="AD33" s="45"/>
       <c r="AE33" s="41"/>
     </row>
-    <row r="34" spans="20:31" x14ac:dyDescent="0.4">
-      <c r="T34" s="43" t="str">
+    <row r="34" spans="1:31" x14ac:dyDescent="0.4">
+      <c r="A34" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="H34" s="1">
+        <v>1</v>
+      </c>
+      <c r="L34" s="44">
+        <v>46087</v>
+      </c>
+      <c r="M34" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="N34" s="1">
+        <v>-2.2592068799999998</v>
+      </c>
+      <c r="O34" s="1">
+        <v>2000</v>
+      </c>
+      <c r="P34" s="1">
+        <v>-4518.4137600000004</v>
+      </c>
+      <c r="Q34" s="1">
+        <v>-6.7776206400000003</v>
+      </c>
+      <c r="R34" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="T34" s="43">
         <f>IF(ISNUMBER(VLOOKUP(U34,Blotter!B:C,2,0)),VLOOKUP(U34,Blotter!B:C,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="U34" s="42">
+        <v>1</v>
+      </c>
+      <c r="U34" s="42" t="str">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>ETH.USD-PAXOS</v>
       </c>
       <c r="V34" s="42">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-2.2592068799999998</v>
       </c>
       <c r="W34" s="42">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="X34" s="42">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="20:31" x14ac:dyDescent="0.4">
-      <c r="T35" s="43" t="str">
+        <v>-6.7776206400000003</v>
+      </c>
+    </row>
+    <row r="35" spans="1:31" x14ac:dyDescent="0.4">
+      <c r="A35" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="H35" s="1">
+        <v>1</v>
+      </c>
+      <c r="L35" s="44">
+        <v>46087</v>
+      </c>
+      <c r="M35" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="N35" s="1">
+        <v>-1.96740688</v>
+      </c>
+      <c r="O35" s="1">
+        <v>2000</v>
+      </c>
+      <c r="P35" s="1">
+        <v>-3934.81376</v>
+      </c>
+      <c r="Q35" s="1">
+        <v>-5.9022206400000004</v>
+      </c>
+      <c r="R35" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="T35" s="43">
         <f>IF(ISNUMBER(VLOOKUP(U35,Blotter!B:C,2,0)),VLOOKUP(U35,Blotter!B:C,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="U35" s="42">
+        <v>1</v>
+      </c>
+      <c r="U35" s="42" t="str">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>ETH.USD-PAXOS</v>
       </c>
       <c r="V35" s="42">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-1.96740688</v>
       </c>
       <c r="W35" s="42">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="X35" s="42">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="20:31" x14ac:dyDescent="0.4">
-      <c r="T36" s="43" t="str">
+        <v>-5.9022206400000004</v>
+      </c>
+    </row>
+    <row r="36" spans="1:31" x14ac:dyDescent="0.4">
+      <c r="A36" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="H36" s="1">
+        <v>1</v>
+      </c>
+      <c r="L36" s="44">
+        <v>46087</v>
+      </c>
+      <c r="M36" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="N36" s="1">
+        <v>-4.0489291700000001</v>
+      </c>
+      <c r="O36" s="1">
+        <v>2000</v>
+      </c>
+      <c r="P36" s="1">
+        <v>-8097.8583399999998</v>
+      </c>
+      <c r="Q36" s="1">
+        <v>-12.146787509999999</v>
+      </c>
+      <c r="R36" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="T36" s="43">
         <f>IF(ISNUMBER(VLOOKUP(U36,Blotter!B:C,2,0)),VLOOKUP(U36,Blotter!B:C,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="U36" s="42">
+        <v>1</v>
+      </c>
+      <c r="U36" s="42" t="str">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>ETH.USD-PAXOS</v>
       </c>
       <c r="V36" s="42">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-4.0489291700000001</v>
       </c>
       <c r="W36" s="42">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="X36" s="42">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="20:31" x14ac:dyDescent="0.4">
-      <c r="T37" s="43"/>
-      <c r="U37" s="42"/>
-      <c r="V37" s="42"/>
-      <c r="W37" s="42"/>
-      <c r="X37" s="42"/>
-    </row>
-    <row r="38" spans="20:31" x14ac:dyDescent="0.4">
-      <c r="T38" s="43"/>
-      <c r="U38" s="42"/>
-      <c r="V38" s="42"/>
-      <c r="W38" s="42"/>
-      <c r="X38" s="42"/>
-    </row>
-    <row r="39" spans="20:31" x14ac:dyDescent="0.4">
-      <c r="T39" s="43"/>
-      <c r="U39" s="42"/>
-      <c r="V39" s="42"/>
-      <c r="W39" s="42"/>
-      <c r="X39" s="42"/>
-    </row>
-    <row r="40" spans="20:31" x14ac:dyDescent="0.4">
+        <v>-12.146787509999999</v>
+      </c>
+    </row>
+    <row r="37" spans="1:31" x14ac:dyDescent="0.4">
+      <c r="A37" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="H37" s="1">
+        <v>1</v>
+      </c>
+      <c r="L37" s="44">
+        <v>46087</v>
+      </c>
+      <c r="M37" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="N37" s="1">
+        <v>-3.5134851600000001</v>
+      </c>
+      <c r="O37" s="1">
+        <v>2000</v>
+      </c>
+      <c r="P37" s="1">
+        <v>-7026.9703200000004</v>
+      </c>
+      <c r="Q37" s="1">
+        <v>-10.54045548</v>
+      </c>
+      <c r="R37" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="T37" s="43">
+        <f>IF(ISNUMBER(VLOOKUP(U37,Blotter!B:C,2,0)),VLOOKUP(U37,Blotter!B:C,2,0),"")</f>
+        <v>1</v>
+      </c>
+      <c r="U37" s="42" t="str">
+        <f t="shared" ref="U37:U39" si="12">D37</f>
+        <v>ETH.USD-PAXOS</v>
+      </c>
+      <c r="V37" s="42">
+        <f t="shared" ref="V37:V39" si="13">N37</f>
+        <v>-3.5134851600000001</v>
+      </c>
+      <c r="W37" s="42">
+        <f t="shared" ref="W37:W39" si="14">O37</f>
+        <v>2000</v>
+      </c>
+      <c r="X37" s="42">
+        <f t="shared" ref="X37:X39" si="15">Q37</f>
+        <v>-10.54045548</v>
+      </c>
+    </row>
+    <row r="38" spans="1:31" x14ac:dyDescent="0.4">
+      <c r="A38" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="H38" s="1">
+        <v>1</v>
+      </c>
+      <c r="L38" s="44">
+        <v>46087</v>
+      </c>
+      <c r="M38" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="N38" s="1">
+        <v>-1.45325536</v>
+      </c>
+      <c r="O38" s="1">
+        <v>2000</v>
+      </c>
+      <c r="P38" s="1">
+        <v>-2906.5107200000002</v>
+      </c>
+      <c r="Q38" s="1">
+        <v>-4.35976608</v>
+      </c>
+      <c r="R38" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="T38" s="43">
+        <f>IF(ISNUMBER(VLOOKUP(U38,Blotter!B:C,2,0)),VLOOKUP(U38,Blotter!B:C,2,0),"")</f>
+        <v>1</v>
+      </c>
+      <c r="U38" s="42" t="str">
+        <f t="shared" si="12"/>
+        <v>ETH.USD-PAXOS</v>
+      </c>
+      <c r="V38" s="42">
+        <f t="shared" si="13"/>
+        <v>-1.45325536</v>
+      </c>
+      <c r="W38" s="42">
+        <f t="shared" si="14"/>
+        <v>2000</v>
+      </c>
+      <c r="X38" s="42">
+        <f t="shared" si="15"/>
+        <v>-4.35976608</v>
+      </c>
+    </row>
+    <row r="39" spans="1:31" x14ac:dyDescent="0.4">
+      <c r="A39" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="H39" s="1">
+        <v>1</v>
+      </c>
+      <c r="L39" s="44">
+        <v>46087</v>
+      </c>
+      <c r="M39" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="N39" s="1">
+        <v>-0.51348516</v>
+      </c>
+      <c r="O39" s="1">
+        <v>2000</v>
+      </c>
+      <c r="P39" s="1">
+        <v>-1026.9703199999999</v>
+      </c>
+      <c r="Q39" s="1">
+        <v>-1.5404554800000001</v>
+      </c>
+      <c r="R39" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="T39" s="43">
+        <f>IF(ISNUMBER(VLOOKUP(U39,Blotter!B:C,2,0)),VLOOKUP(U39,Blotter!B:C,2,0),"")</f>
+        <v>1</v>
+      </c>
+      <c r="U39" s="42" t="str">
+        <f t="shared" si="12"/>
+        <v>ETH.USD-PAXOS</v>
+      </c>
+      <c r="V39" s="42">
+        <f t="shared" si="13"/>
+        <v>-0.51348516</v>
+      </c>
+      <c r="W39" s="42">
+        <f t="shared" si="14"/>
+        <v>2000</v>
+      </c>
+      <c r="X39" s="42">
+        <f t="shared" si="15"/>
+        <v>-1.5404554800000001</v>
+      </c>
+    </row>
+    <row r="40" spans="1:31" x14ac:dyDescent="0.4">
       <c r="T40" s="43"/>
       <c r="U40" s="42"/>
       <c r="V40" s="42"/>
       <c r="W40" s="42"/>
       <c r="X40" s="42"/>
     </row>
-    <row r="41" spans="20:31" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:31" x14ac:dyDescent="0.4">
       <c r="T41" s="43"/>
       <c r="U41" s="42"/>
       <c r="V41" s="42"/>
       <c r="W41" s="42"/>
       <c r="X41" s="42"/>
     </row>
-    <row r="42" spans="20:31" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:31" x14ac:dyDescent="0.4">
       <c r="T42" s="43"/>
       <c r="U42" s="42"/>
       <c r="V42" s="42"/>
       <c r="W42" s="42"/>
       <c r="X42" s="42"/>
     </row>
-    <row r="43" spans="20:31" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:31" x14ac:dyDescent="0.4">
       <c r="T43" s="43"/>
       <c r="U43" s="42"/>
       <c r="V43" s="42"/>
       <c r="W43" s="42"/>
       <c r="X43" s="42"/>
     </row>
-    <row r="44" spans="20:31" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:31" x14ac:dyDescent="0.4">
       <c r="T44" s="43"/>
       <c r="U44" s="42"/>
       <c r="V44" s="42"/>
       <c r="W44" s="42"/>
       <c r="X44" s="42"/>
     </row>
-    <row r="45" spans="20:31" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:31" x14ac:dyDescent="0.4">
       <c r="T45" s="43"/>
       <c r="U45" s="42"/>
       <c r="V45" s="42"/>
       <c r="W45" s="42"/>
       <c r="X45" s="42"/>
     </row>
-    <row r="46" spans="20:31" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:31" x14ac:dyDescent="0.4">
       <c r="T46" s="43"/>
       <c r="U46" s="42"/>
       <c r="V46" s="42"/>
       <c r="W46" s="42"/>
       <c r="X46" s="42"/>
     </row>
-    <row r="47" spans="20:31" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:31" x14ac:dyDescent="0.4">
       <c r="T47" s="43"/>
       <c r="U47" s="42"/>
       <c r="V47" s="42"/>
       <c r="W47" s="42"/>
       <c r="X47" s="42"/>
     </row>
-    <row r="48" spans="20:31" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:31" x14ac:dyDescent="0.4">
       <c r="T48" s="43"/>
       <c r="U48" s="42"/>
       <c r="V48" s="42"/>

--- a/1XW_TradeBlotter_Web.xlsx
+++ b/1XW_TradeBlotter_Web.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0a601c1c2ba3d9f4/Trading/The Strategy Project/1XW Website/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="249" documentId="13_ncr:1_{6F5069F1-F0E7-4440-AA6D-4AFA11BBED1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2B162599-3CD8-462F-8665-2026C82478A7}"/>
+  <xr:revisionPtr revIDLastSave="253" documentId="13_ncr:1_{6F5069F1-F0E7-4440-AA6D-4AFA11BBED1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B131FD68-2782-436E-ACAA-2515342E383A}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="22695" windowHeight="14476" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="22695" windowHeight="14476" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Blotter" sheetId="3" r:id="rId1"/>
@@ -116,7 +116,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1129" uniqueCount="330">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1135" uniqueCount="330">
   <si>
     <t>WEEK</t>
   </si>
@@ -1091,9 +1091,6 @@
     <t>Long CC</t>
   </si>
   <si>
-    <t>Last</t>
-  </si>
-  <si>
     <t>DUP242961</t>
   </si>
   <si>
@@ -1119,6 +1116,9 @@
   </si>
   <si>
     <t>Retrace to the pre breakout price region ~$3000. Inside week + weekly up</t>
+  </si>
+  <si>
+    <t>Close</t>
   </si>
 </sst>
 </file>
@@ -1786,7 +1786,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3.6645906320098565E-3</c:v>
+                  <c:v>7.4145906320099986E-3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1940,7 +1940,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3.6645906320098565E-3</c:v>
+                  <c:v>7.4145906320099986E-3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2331,7 +2331,7 @@
                   <c:v>1000</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1003.6645906320099</c:v>
+                  <c:v>1007.4145906320099</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2738,7 +2738,7 @@
                   <c:v>5.2224063201000703E-4</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>3.1233306320099796E-3</c:v>
+                  <c:v>6.8733306320101217E-3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3396,7 +3396,7 @@
         <v>112</v>
       </c>
       <c r="C2" s="37" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="E2" s="47" t="s">
         <v>128</v>
@@ -3413,7 +3413,7 @@
       </c>
       <c r="C3" s="28">
         <f ca="1">OFFSET(NAV!B1,MATCH(C1,NAV!B:B,1),8)</f>
-        <v>1003664.5906320099</v>
+        <v>1007414.5906320099</v>
       </c>
       <c r="E3" s="47" t="s">
         <v>129</v>
@@ -3430,7 +3430,7 @@
       </c>
       <c r="C4" s="28">
         <f>SUM(N18:N1012)</f>
-        <v>3664.5906320098998</v>
+        <v>7414.5906320099002</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="47" t="s">
@@ -3448,7 +3448,7 @@
       </c>
       <c r="C5" s="3">
         <f ca="1">OFFSET(NAV!B1,MATCH(C1,NAV!B:B,1),11)</f>
-        <v>3.6645906320098565E-3</v>
+        <v>7.4145906320099986E-3</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="47" t="s">
@@ -3467,7 +3467,7 @@
       </c>
       <c r="C6" s="3">
         <f ca="1">OFFSET(NAV!B1,MATCH(C1,NAV!B:B,1),12)</f>
-        <v>3.6645906320098565E-3</v>
+        <v>7.4145906320099986E-3</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="47"/>
@@ -3486,7 +3486,7 @@
       </c>
       <c r="D7" s="3">
         <f ca="1">C7/C3</f>
-        <v>3.5727812194131132E-2</v>
+        <v>3.5594818988579149E-2</v>
       </c>
       <c r="E7" s="47"/>
       <c r="F7" s="47"/>
@@ -3500,11 +3500,11 @@
       </c>
       <c r="C8" s="28">
         <f>C4+C7</f>
-        <v>39523.330632009856</v>
+        <v>43273.330632009856</v>
       </c>
       <c r="D8" s="3">
         <f ca="1">C5+D7</f>
-        <v>3.9392402826140989E-2</v>
+        <v>4.3009409620589148E-2</v>
       </c>
       <c r="G8" s="47"/>
       <c r="H8" s="51"/>
@@ -3516,11 +3516,11 @@
       </c>
       <c r="C9" s="28">
         <f t="array" ref="C9">SUM((F19:F112="Futures")*(M19:M112))</f>
-        <v>99660</v>
+        <v>103410</v>
       </c>
       <c r="D9" s="3">
         <f ca="1">C9/$C$3</f>
-        <v>9.9296120367506305E-2</v>
+        <v>0.10264890042452619</v>
       </c>
       <c r="E9" s="47"/>
       <c r="F9" s="47"/>
@@ -3565,7 +3565,7 @@
       </c>
       <c r="D12" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>8.9671391060360903E-3</v>
+        <v>8.933759828070164E-3</v>
       </c>
     </row>
     <row r="13" spans="2:11" x14ac:dyDescent="0.4">
@@ -3574,11 +3574,11 @@
       </c>
       <c r="C13" s="28">
         <f t="array" ref="C13">SUM((PLB!G4:G999="O")*(PLB!D4:D999))</f>
-        <v>2601.0899999999965</v>
+        <v>6351.0899999999965</v>
       </c>
       <c r="D13" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>2.591592873035487E-3</v>
+        <v>6.304345856273123E-3</v>
       </c>
       <c r="F13" s="59"/>
       <c r="G13" s="59"/>
@@ -3589,11 +3589,11 @@
       </c>
       <c r="C14" s="28">
         <f>C12+C13</f>
-        <v>11601.089999999997</v>
+        <v>15351.089999999997</v>
       </c>
       <c r="D14" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>1.1558731979071578E-2</v>
+        <v>1.5238105684343289E-2</v>
       </c>
     </row>
     <row r="17" spans="2:28" x14ac:dyDescent="0.4">
@@ -3790,7 +3790,7 @@
       </c>
       <c r="Z19" s="35">
         <f>IF(C$2="Last",IF(ISNUMBER(VLOOKUP(B19,Prices!A:L,8,0)),VLOOKUP(B19,Prices!A:L,8,0),0),IF(ISNUMBER(VLOOKUP(B19,Prices!A:L,12,0)),VLOOKUP(B19,Prices!A:L,12,0),0))</f>
-        <v>2030.35</v>
+        <v>2037.15</v>
       </c>
       <c r="AB19" s="29"/>
     </row>
@@ -3831,15 +3831,15 @@
       </c>
       <c r="L20" s="29">
         <f t="shared" ref="L20" si="8">IF(I20=0,IF(H20&gt;0,X20,Y20),Z20)</f>
-        <v>3322</v>
+        <v>3447</v>
       </c>
       <c r="M20" s="28">
         <f t="shared" ref="M20" si="9">I20*J20*L20</f>
-        <v>99660</v>
+        <v>103410</v>
       </c>
       <c r="N20" s="95">
         <f t="array" ref="N20">-SUM((Trades!T$2:T$9999=Blotter!C20)*(Trades!U$2:U$9999=Blotter!B20)*(Trades!V$2:V$9999)*(Trades!W$2:W$9999))*J20+SUM((Trades!T$2:T$9999=Blotter!C20)*(Trades!U$2:U$9999=Blotter!B20)*(Trades!X$2:X$9999))+(L20*I20)*J20</f>
-        <v>2601.0899999999965</v>
+        <v>6351.0899999999965</v>
       </c>
       <c r="O20" s="29">
         <f>VLOOKUP(D20,Multiplier!B:H,3,0)</f>
@@ -3855,11 +3855,11 @@
       </c>
       <c r="S20" s="29">
         <f>IF(OR(F20="Futures",F20="Spot"),IF(I20=0,0,IF(I20&gt;0,L20-O20,L20+O20)),0)</f>
-        <v>3117</v>
+        <v>3242</v>
       </c>
       <c r="T20" s="3">
         <f t="shared" ref="T20" si="11">IF(S20&gt;0,IF(ISNUMBER(S20/L20-1),S20/L20-1,0),0)</f>
-        <v>-6.1709813365442456E-2</v>
+        <v>-5.9472004641717424E-2</v>
       </c>
       <c r="U20" s="29">
         <f t="shared" ref="U20" si="12">IF(OR(F20="Futures",F20="Stocks"),IF(I20=0,0,IF(I20&gt;0,K20-P20,K20+P20)),0)</f>
@@ -3867,7 +3867,7 @@
       </c>
       <c r="V20" s="3">
         <f t="shared" ref="V20" si="13">IF(U20&gt;0,IF(ISNUMBER(U20/L20-1),U20/L20-1,0),0)</f>
-        <v>-0.11640668272125221</v>
+        <v>-0.1484487960545402</v>
       </c>
       <c r="X20" s="34">
         <f t="array" ref="X20">IF(ISNUMBER(SUM((Trades!T$2:T$9999=Blotter!C20)*(Trades!U$2:U$9999=Blotter!B20)*(Trades!W$2:W$9999)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0))/SUM((Trades!T$2:T$9999=Blotter!C20)*(Trades!U$2:U$9999=Blotter!B20)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0))),SUM((Trades!T$2:T$9999=Blotter!C20)*(Trades!U$2:U$9999=Blotter!B20)*(Trades!W$2:W$9999)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0))/SUM((Trades!T$2:T$9999=Blotter!C20)*(Trades!U$2:U$9999=Blotter!B20)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0)),0)</f>
@@ -3879,7 +3879,7 @@
       </c>
       <c r="Z20" s="35">
         <f>IF(C$2="Last",IF(ISNUMBER(VLOOKUP(B20,Prices!A:L,8,0)),VLOOKUP(B20,Prices!A:L,8,0),0),IF(ISNUMBER(VLOOKUP(B20,Prices!A:L,12,0)),VLOOKUP(B20,Prices!A:L,12,0),0))</f>
-        <v>3322</v>
+        <v>3447</v>
       </c>
       <c r="AB20" s="29"/>
     </row>
@@ -5666,31 +5666,31 @@
         <v>62</v>
       </c>
       <c r="H2" s="91">
-        <v>6842.5</v>
+        <v>6832</v>
       </c>
       <c r="I2" s="91">
-        <v>6841.75</v>
+        <v>6832.75</v>
       </c>
       <c r="J2" s="91">
-        <v>6842.75</v>
+        <v>6833.75</v>
       </c>
       <c r="K2" s="91">
-        <v>6842.25</v>
+        <v>6833.25</v>
       </c>
       <c r="L2" s="91">
-        <v>6794</v>
+        <v>6838</v>
       </c>
       <c r="M2" s="91">
-        <v>6742.5</v>
+        <v>6846.25</v>
       </c>
       <c r="N2" s="91">
-        <v>6869.75</v>
+        <v>6873.25</v>
       </c>
       <c r="O2" s="91">
-        <v>6631.5</v>
+        <v>6832</v>
       </c>
       <c r="P2" s="91">
-        <v>48568</v>
+        <v>2484</v>
       </c>
       <c r="Q2" s="91"/>
       <c r="R2" s="91"/>
@@ -5698,7 +5698,7 @@
       <c r="T2" s="91"/>
       <c r="U2" s="91"/>
       <c r="V2" s="85">
-        <v>46090.869606481479</v>
+        <v>46092.416759259257</v>
       </c>
       <c r="W2" s="81" t="s">
         <v>277</v>
@@ -5730,31 +5730,31 @@
         <v>62</v>
       </c>
       <c r="H3" s="91">
-        <v>25164.75</v>
+        <v>25199</v>
       </c>
       <c r="I3" s="91">
-        <v>25159.25</v>
+        <v>25182.75</v>
       </c>
       <c r="J3" s="91">
-        <v>25163.75</v>
+        <v>25186.75</v>
       </c>
       <c r="K3" s="91">
-        <v>25161.5</v>
+        <v>25184.75</v>
       </c>
       <c r="L3" s="91">
-        <v>24883.25</v>
+        <v>25199.5</v>
       </c>
       <c r="M3" s="91">
-        <v>24764.75</v>
+        <v>25220</v>
       </c>
       <c r="N3" s="91">
-        <v>25271.25</v>
+        <v>25338</v>
       </c>
       <c r="O3" s="91">
-        <v>24212.25</v>
+        <v>25170.75</v>
       </c>
       <c r="P3" s="91">
-        <v>9846</v>
+        <v>742</v>
       </c>
       <c r="Q3" s="91"/>
       <c r="R3" s="91"/>
@@ -5762,7 +5762,7 @@
       <c r="T3" s="91"/>
       <c r="U3" s="91"/>
       <c r="V3" s="85">
-        <v>46090.869606481479</v>
+        <v>46092.416759259257</v>
       </c>
       <c r="W3" s="81" t="s">
         <v>277</v>
@@ -5794,31 +5794,31 @@
         <v>62</v>
       </c>
       <c r="H4" s="91">
-        <v>2569.4</v>
+        <v>2557.8000000000002</v>
       </c>
       <c r="I4" s="91">
-        <v>2569.5</v>
+        <v>2556.9</v>
       </c>
       <c r="J4" s="91">
-        <v>2570.1999999999998</v>
+        <v>2557.5</v>
       </c>
       <c r="K4" s="91">
-        <v>2569.85</v>
+        <v>2557.1999999999998</v>
       </c>
       <c r="L4" s="91">
-        <v>2543.4</v>
+        <v>2566.9</v>
       </c>
       <c r="M4" s="91">
-        <v>2524.9</v>
+        <v>2570.3000000000002</v>
       </c>
       <c r="N4" s="91">
-        <v>2580.5</v>
+        <v>2583.1999999999998</v>
       </c>
       <c r="O4" s="91">
-        <v>2434</v>
+        <v>2556.8000000000002</v>
       </c>
       <c r="P4" s="91">
-        <v>4749</v>
+        <v>293</v>
       </c>
       <c r="Q4" s="91"/>
       <c r="R4" s="91"/>
@@ -5826,7 +5826,7 @@
       <c r="T4" s="91"/>
       <c r="U4" s="91"/>
       <c r="V4" s="85">
-        <v>46090.869606481479</v>
+        <v>46092.416759259257</v>
       </c>
       <c r="W4" s="81" t="s">
         <v>277</v>
@@ -5858,31 +5858,31 @@
         <v>59</v>
       </c>
       <c r="H5" s="91">
-        <v>5728</v>
+        <v>5710</v>
       </c>
       <c r="I5" s="91">
-        <v>5732</v>
+        <v>5706</v>
       </c>
       <c r="J5" s="91">
-        <v>5736</v>
+        <v>5707</v>
       </c>
       <c r="K5" s="91">
-        <v>5734</v>
+        <v>5706.5</v>
       </c>
       <c r="L5" s="91">
-        <v>5645</v>
+        <v>5771</v>
       </c>
       <c r="M5" s="91">
-        <v>5545</v>
+        <v>5741</v>
       </c>
       <c r="N5" s="91">
-        <v>5759</v>
+        <v>5770</v>
       </c>
       <c r="O5" s="91">
-        <v>5463</v>
+        <v>5698</v>
       </c>
       <c r="P5" s="91">
-        <v>6993</v>
+        <v>930</v>
       </c>
       <c r="Q5" s="91"/>
       <c r="R5" s="91"/>
@@ -5890,7 +5890,7 @@
       <c r="T5" s="91"/>
       <c r="U5" s="91"/>
       <c r="V5" s="85">
-        <v>46090.869606481479</v>
+        <v>46092.416759259257</v>
       </c>
       <c r="W5" s="81" t="s">
         <v>277</v>
@@ -5922,31 +5922,31 @@
         <v>59</v>
       </c>
       <c r="H6" s="91">
-        <v>24017</v>
+        <v>23814</v>
       </c>
       <c r="I6" s="91">
-        <v>24023</v>
+        <v>23822</v>
       </c>
       <c r="J6" s="91">
-        <v>24045</v>
+        <v>23883</v>
       </c>
       <c r="K6" s="91">
-        <v>24034</v>
+        <v>23852.5</v>
       </c>
       <c r="L6" s="91">
-        <v>23768</v>
+        <v>24173</v>
       </c>
       <c r="M6" s="91">
-        <v>23369</v>
+        <v>24207</v>
       </c>
       <c r="N6" s="91">
-        <v>24160</v>
+        <v>24207</v>
       </c>
       <c r="O6" s="91">
-        <v>22955</v>
+        <v>23814</v>
       </c>
       <c r="P6" s="91">
-        <v>144</v>
+        <v>29</v>
       </c>
       <c r="Q6" s="91"/>
       <c r="R6" s="91"/>
@@ -5954,7 +5954,7 @@
       <c r="T6" s="91"/>
       <c r="U6" s="91"/>
       <c r="V6" s="85">
-        <v>46090.869606481479</v>
+        <v>46092.416759259257</v>
       </c>
       <c r="W6" s="81" t="s">
         <v>277</v>
@@ -5989,28 +5989,28 @@
         <v>54405</v>
       </c>
       <c r="I7" s="93">
-        <v>54390</v>
+        <v>54395</v>
       </c>
       <c r="J7" s="93">
-        <v>54410</v>
+        <v>54405</v>
       </c>
       <c r="K7" s="93">
         <v>54400</v>
       </c>
       <c r="L7" s="93">
-        <v>53800</v>
+        <v>54675</v>
       </c>
       <c r="M7" s="93">
-        <v>53130</v>
+        <v>54700</v>
       </c>
       <c r="N7" s="93">
-        <v>54710</v>
+        <v>55535</v>
       </c>
       <c r="O7" s="93">
-        <v>51025</v>
+        <v>54340</v>
       </c>
       <c r="P7" s="93">
-        <v>12345</v>
+        <v>10307</v>
       </c>
       <c r="Q7" s="93"/>
       <c r="R7" s="93"/>
@@ -6018,7 +6018,7 @@
       <c r="T7" s="93"/>
       <c r="U7" s="93"/>
       <c r="V7" s="92">
-        <v>46090.869606481479</v>
+        <v>46092.416759259257</v>
       </c>
       <c r="W7" s="1" t="s">
         <v>277</v>
@@ -6047,31 +6047,31 @@
         <v>62</v>
       </c>
       <c r="H8" s="93">
-        <v>86</v>
+        <v>85.63</v>
       </c>
       <c r="I8" s="93">
-        <v>85.91</v>
+        <v>85.62</v>
       </c>
       <c r="J8" s="93">
-        <v>86.04</v>
+        <v>85.64</v>
       </c>
       <c r="K8" s="93">
-        <v>85.974999999999994</v>
+        <v>85.63</v>
       </c>
       <c r="L8" s="93">
-        <v>90.9</v>
+        <v>83.45</v>
       </c>
       <c r="M8" s="93">
-        <v>98</v>
+        <v>86.89</v>
       </c>
       <c r="N8" s="93">
-        <v>119.48</v>
+        <v>88.59</v>
       </c>
       <c r="O8" s="93">
-        <v>81.19</v>
+        <v>81.790000000000006</v>
       </c>
       <c r="P8" s="93">
-        <v>1016579</v>
+        <v>126856</v>
       </c>
       <c r="Q8" s="93"/>
       <c r="R8" s="93"/>
@@ -6079,7 +6079,7 @@
       <c r="T8" s="93"/>
       <c r="U8" s="93"/>
       <c r="V8" s="92">
-        <v>46090.869606481479</v>
+        <v>46092.416759259257</v>
       </c>
       <c r="W8" s="1" t="s">
         <v>277</v>
@@ -6108,31 +6108,31 @@
         <v>62</v>
       </c>
       <c r="H9" s="93">
-        <v>3.214</v>
+        <v>3.2309999999999999</v>
       </c>
       <c r="I9" s="93">
-        <v>3.214</v>
+        <v>3.2330000000000001</v>
       </c>
       <c r="J9" s="93">
-        <v>3.2170000000000001</v>
+        <v>3.2349999999999999</v>
       </c>
       <c r="K9" s="93">
-        <v>3.2155</v>
+        <v>3.234</v>
       </c>
       <c r="L9" s="93">
-        <v>3.351</v>
+        <v>3.1829999999999998</v>
       </c>
       <c r="M9" s="93">
-        <v>3.4289999999999998</v>
+        <v>3.2130000000000001</v>
       </c>
       <c r="N9" s="93">
-        <v>3.6219999999999999</v>
+        <v>3.24</v>
       </c>
       <c r="O9" s="93">
-        <v>3.2050000000000001</v>
+        <v>3.1859999999999999</v>
       </c>
       <c r="P9" s="93">
-        <v>54695</v>
+        <v>2013</v>
       </c>
       <c r="Q9" s="93"/>
       <c r="R9" s="93"/>
@@ -6140,7 +6140,7 @@
       <c r="T9" s="93"/>
       <c r="U9" s="93"/>
       <c r="V9" s="92">
-        <v>46090.869606481479</v>
+        <v>46092.416759259257</v>
       </c>
       <c r="W9" s="1" t="s">
         <v>277</v>
@@ -6169,31 +6169,31 @@
         <v>62</v>
       </c>
       <c r="H10" s="93">
-        <v>2.5518000000000001</v>
+        <v>2.5867</v>
       </c>
       <c r="I10" s="93">
-        <v>2.5472000000000001</v>
+        <v>2.5870000000000002</v>
       </c>
       <c r="J10" s="93">
-        <v>2.5529999999999999</v>
+        <v>2.5878999999999999</v>
       </c>
       <c r="K10" s="93">
-        <v>2.5501</v>
+        <v>2.58745</v>
       </c>
       <c r="L10" s="93">
-        <v>2.6303999999999998</v>
+        <v>2.5423</v>
       </c>
       <c r="M10" s="93">
-        <v>2.7</v>
+        <v>2.6063999999999998</v>
       </c>
       <c r="N10" s="93">
-        <v>3.0407000000000002</v>
+        <v>2.6387999999999998</v>
       </c>
       <c r="O10" s="93">
-        <v>2.4373999999999998</v>
+        <v>2.5327999999999999</v>
       </c>
       <c r="P10" s="93">
-        <v>120434</v>
+        <v>10234</v>
       </c>
       <c r="Q10" s="93"/>
       <c r="R10" s="93"/>
@@ -6201,7 +6201,7 @@
       <c r="T10" s="93"/>
       <c r="U10" s="93"/>
       <c r="V10" s="92">
-        <v>46090.869606481479</v>
+        <v>46092.416759259257</v>
       </c>
       <c r="W10" s="1" t="s">
         <v>277</v>
@@ -6230,31 +6230,31 @@
         <v>62</v>
       </c>
       <c r="H11" s="93">
-        <v>5181.5</v>
+        <v>5231.7</v>
       </c>
       <c r="I11" s="93">
-        <v>5181.3999999999996</v>
+        <v>5231.8</v>
       </c>
       <c r="J11" s="93">
-        <v>5182.1000000000004</v>
+        <v>5232.3</v>
       </c>
       <c r="K11" s="93">
-        <v>5181.75</v>
+        <v>5232.05</v>
       </c>
       <c r="L11" s="93">
-        <v>5197.8999999999996</v>
+        <v>5281.5</v>
       </c>
       <c r="M11" s="93">
-        <v>5236</v>
+        <v>5234.3999999999996</v>
       </c>
       <c r="N11" s="93">
-        <v>5244.3</v>
+        <v>5269.5</v>
       </c>
       <c r="O11" s="93">
-        <v>5060</v>
+        <v>5224</v>
       </c>
       <c r="P11" s="93">
-        <v>31318</v>
+        <v>2674</v>
       </c>
       <c r="Q11" s="93"/>
       <c r="R11" s="93"/>
@@ -6262,7 +6262,7 @@
       <c r="T11" s="93"/>
       <c r="U11" s="93"/>
       <c r="V11" s="92">
-        <v>46090.869606481479</v>
+        <v>46092.416759259257</v>
       </c>
       <c r="W11" s="1" t="s">
         <v>277</v>
@@ -6291,31 +6291,31 @@
         <v>62</v>
       </c>
       <c r="H12" s="93">
-        <v>86.76</v>
+        <v>87.125</v>
       </c>
       <c r="I12" s="93">
-        <v>86.644999999999996</v>
+        <v>87.655000000000001</v>
       </c>
       <c r="J12" s="93">
-        <v>86.69</v>
+        <v>87.7</v>
       </c>
       <c r="K12" s="93">
-        <v>86.66749999999999</v>
+        <v>87.677500000000009</v>
       </c>
       <c r="L12" s="93">
-        <v>84.62</v>
+        <v>89.91</v>
       </c>
       <c r="M12" s="93">
-        <v>84.805000000000007</v>
+        <v>89.7</v>
       </c>
       <c r="N12" s="93">
-        <v>87.185000000000002</v>
+        <v>90.015000000000001</v>
       </c>
       <c r="O12" s="93">
-        <v>80</v>
+        <v>87.125</v>
       </c>
       <c r="P12" s="93">
-        <v>331</v>
+        <v>38</v>
       </c>
       <c r="Q12" s="93"/>
       <c r="R12" s="93"/>
@@ -6323,7 +6323,7 @@
       <c r="T12" s="93"/>
       <c r="U12" s="93"/>
       <c r="V12" s="92">
-        <v>46090.869606481479</v>
+        <v>46092.416759259257</v>
       </c>
       <c r="W12" s="1" t="s">
         <v>277</v>
@@ -6352,31 +6352,31 @@
         <v>62</v>
       </c>
       <c r="H13" s="93">
-        <v>5.8784999999999998</v>
+        <v>5.8975</v>
       </c>
       <c r="I13" s="93">
-        <v>5.8985000000000003</v>
+        <v>5.8710000000000004</v>
       </c>
       <c r="J13" s="93">
-        <v>5.9</v>
+        <v>5.8724999999999996</v>
       </c>
       <c r="K13" s="93">
-        <v>5.8992500000000003</v>
+        <v>5.8717500000000005</v>
       </c>
       <c r="L13" s="93">
-        <v>5.835</v>
+        <v>5.9790000000000001</v>
       </c>
       <c r="M13" s="93">
-        <v>5.8</v>
+        <v>5.9509999999999996</v>
       </c>
       <c r="N13" s="93">
-        <v>5.8784999999999998</v>
+        <v>5.9669999999999996</v>
       </c>
       <c r="O13" s="93">
-        <v>5.6784999999999997</v>
+        <v>5.8975</v>
       </c>
       <c r="P13" s="93">
-        <v>547</v>
+        <v>22</v>
       </c>
       <c r="Q13" s="93"/>
       <c r="R13" s="93"/>
@@ -6384,7 +6384,7 @@
       <c r="T13" s="93"/>
       <c r="U13" s="93"/>
       <c r="V13" s="92">
-        <v>46090.869606481479</v>
+        <v>46092.416759259257</v>
       </c>
       <c r="W13" s="1" t="s">
         <v>277</v>
@@ -6413,31 +6413,31 @@
         <v>62</v>
       </c>
       <c r="H14" s="93">
+        <v>454.5</v>
+      </c>
+      <c r="I14" s="93">
+        <v>454.5</v>
+      </c>
+      <c r="J14" s="93">
+        <v>454.75</v>
+      </c>
+      <c r="K14" s="93">
+        <v>454.625</v>
+      </c>
+      <c r="L14" s="93">
+        <v>452.25</v>
+      </c>
+      <c r="M14" s="93">
         <v>453.25</v>
       </c>
-      <c r="I14" s="93">
-        <v>-100</v>
-      </c>
-      <c r="J14" s="93">
-        <v>-100</v>
-      </c>
-      <c r="K14" s="93">
-        <v>-100</v>
-      </c>
-      <c r="L14" s="93">
-        <v>460.5</v>
-      </c>
-      <c r="M14" s="93">
-        <v>464</v>
-      </c>
       <c r="N14" s="93">
-        <v>476</v>
+        <v>455.5</v>
       </c>
       <c r="O14" s="93">
-        <v>453</v>
+        <v>451.5</v>
       </c>
       <c r="P14" s="93">
-        <v>411655</v>
+        <v>20510</v>
       </c>
       <c r="Q14" s="93"/>
       <c r="R14" s="93"/>
@@ -6445,7 +6445,7 @@
       <c r="T14" s="93"/>
       <c r="U14" s="93"/>
       <c r="V14" s="92">
-        <v>46090.869606481479</v>
+        <v>46092.416759259257</v>
       </c>
       <c r="W14" s="1" t="s">
         <v>277</v>
@@ -6474,31 +6474,31 @@
         <v>62</v>
       </c>
       <c r="H15" s="93">
-        <v>602.5</v>
+        <v>595.25</v>
       </c>
       <c r="I15" s="93">
-        <v>-100</v>
+        <v>595</v>
       </c>
       <c r="J15" s="93">
-        <v>-100</v>
+        <v>595.25</v>
       </c>
       <c r="K15" s="93">
-        <v>-100</v>
+        <v>595.125</v>
       </c>
       <c r="L15" s="93">
-        <v>616.75</v>
+        <v>591</v>
       </c>
       <c r="M15" s="93">
-        <v>625</v>
+        <v>592.5</v>
       </c>
       <c r="N15" s="93">
-        <v>641.75</v>
+        <v>597.5</v>
       </c>
       <c r="O15" s="93">
-        <v>601.25</v>
+        <v>589.25</v>
       </c>
       <c r="P15" s="93">
-        <v>159696</v>
+        <v>8730</v>
       </c>
       <c r="Q15" s="93"/>
       <c r="R15" s="93"/>
@@ -6506,7 +6506,7 @@
       <c r="T15" s="93"/>
       <c r="U15" s="93"/>
       <c r="V15" s="92">
-        <v>46090.869606481479</v>
+        <v>46092.416759259257</v>
       </c>
       <c r="W15" s="1" t="s">
         <v>277</v>
@@ -6535,31 +6535,31 @@
         <v>62</v>
       </c>
       <c r="H16" s="93">
-        <v>1196.25</v>
+        <v>1208.75</v>
       </c>
       <c r="I16" s="93">
-        <v>-100</v>
+        <v>1208.5</v>
       </c>
       <c r="J16" s="93">
-        <v>-100</v>
+        <v>1208.75</v>
       </c>
       <c r="K16" s="93">
-        <v>-100</v>
+        <v>1208.625</v>
       </c>
       <c r="L16" s="93">
-        <v>1200.75</v>
+        <v>1201.75</v>
       </c>
       <c r="M16" s="93">
-        <v>1219.5</v>
+        <v>1207</v>
       </c>
       <c r="N16" s="93">
-        <v>1233.75</v>
+        <v>1212.75</v>
       </c>
       <c r="O16" s="93">
-        <v>1193</v>
+        <v>1203.5</v>
       </c>
       <c r="P16" s="93">
-        <v>185177</v>
+        <v>15653</v>
       </c>
       <c r="Q16" s="93"/>
       <c r="R16" s="93"/>
@@ -6567,7 +6567,7 @@
       <c r="T16" s="93"/>
       <c r="U16" s="93"/>
       <c r="V16" s="92">
-        <v>46090.869606481479</v>
+        <v>46092.416759259257</v>
       </c>
       <c r="W16" s="1" t="s">
         <v>277</v>
@@ -6596,31 +6596,31 @@
         <v>62</v>
       </c>
       <c r="H17" s="93">
-        <v>14.62</v>
+        <v>14.49</v>
       </c>
       <c r="I17" s="93">
-        <v>-100</v>
+        <v>14.48</v>
       </c>
       <c r="J17" s="93">
-        <v>-100</v>
+        <v>14.49</v>
       </c>
       <c r="K17" s="93">
-        <v>-100</v>
+        <v>14.484999999999999</v>
       </c>
       <c r="L17" s="93">
-        <v>14.1</v>
+        <v>14.38</v>
       </c>
       <c r="M17" s="93">
-        <v>14.26</v>
+        <v>14.37</v>
       </c>
       <c r="N17" s="93">
-        <v>14.64</v>
+        <v>14.53</v>
       </c>
       <c r="O17" s="93">
-        <v>14.25</v>
+        <v>14.37</v>
       </c>
       <c r="P17" s="93">
-        <v>149066</v>
+        <v>4360</v>
       </c>
       <c r="Q17" s="93"/>
       <c r="R17" s="93"/>
@@ -6628,7 +6628,7 @@
       <c r="T17" s="93"/>
       <c r="U17" s="93"/>
       <c r="V17" s="92">
-        <v>46090.869606481479</v>
+        <v>46092.416759259257</v>
       </c>
       <c r="W17" s="1" t="s">
         <v>277</v>
@@ -6657,7 +6657,7 @@
         <v>62</v>
       </c>
       <c r="H18" s="93">
-        <v>297.10000000000002</v>
+        <v>294.7</v>
       </c>
       <c r="I18" s="93">
         <v>-100</v>
@@ -6669,19 +6669,15 @@
         <v>-100</v>
       </c>
       <c r="L18" s="93">
-        <v>293.3</v>
+        <v>295.8</v>
       </c>
       <c r="M18" s="93">
-        <v>296.95</v>
-      </c>
-      <c r="N18" s="93">
-        <v>301.64999999999998</v>
-      </c>
-      <c r="O18" s="93">
-        <v>293.14999999999998</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N18" s="93"/>
+      <c r="O18" s="93"/>
       <c r="P18" s="93">
-        <v>16842</v>
+        <v>0</v>
       </c>
       <c r="Q18" s="93"/>
       <c r="R18" s="93"/>
@@ -6689,7 +6685,7 @@
       <c r="T18" s="93"/>
       <c r="U18" s="93"/>
       <c r="V18" s="92">
-        <v>46090.869606481479</v>
+        <v>46092.416759259257</v>
       </c>
       <c r="W18" s="1" t="s">
         <v>277</v>
@@ -6718,7 +6714,7 @@
         <v>62</v>
       </c>
       <c r="H19" s="93">
-        <v>3322</v>
+        <v>-1</v>
       </c>
       <c r="I19" s="93">
         <v>-1</v>
@@ -6730,19 +6726,15 @@
         <v>-1</v>
       </c>
       <c r="L19" s="93">
-        <v>3230</v>
+        <v>3447</v>
       </c>
       <c r="M19" s="93">
-        <v>3225</v>
-      </c>
-      <c r="N19" s="93">
-        <v>3330</v>
-      </c>
-      <c r="O19" s="93">
-        <v>3179</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N19" s="93"/>
+      <c r="O19" s="93"/>
       <c r="P19" s="93">
-        <v>18447</v>
+        <v>0</v>
       </c>
       <c r="Q19" s="93"/>
       <c r="R19" s="93"/>
@@ -6750,7 +6742,7 @@
       <c r="T19" s="93"/>
       <c r="U19" s="93"/>
       <c r="V19" s="92">
-        <v>46090.869606481479</v>
+        <v>46092.416759259257</v>
       </c>
       <c r="W19" s="1" t="s">
         <v>277</v>
@@ -6779,31 +6771,31 @@
         <v>62</v>
       </c>
       <c r="H20" s="93">
-        <v>64.680000000000007</v>
+        <v>65.349999999999994</v>
       </c>
       <c r="I20" s="93">
-        <v>-100</v>
+        <v>65.34</v>
       </c>
       <c r="J20" s="93">
-        <v>-100</v>
+        <v>65.36</v>
       </c>
       <c r="K20" s="93">
-        <v>-100</v>
+        <v>65.349999999999994</v>
       </c>
       <c r="L20" s="93">
-        <v>64.2</v>
+        <v>65.3</v>
       </c>
       <c r="M20" s="93">
-        <v>64.2</v>
+        <v>65.37</v>
       </c>
       <c r="N20" s="93">
-        <v>65.02</v>
+        <v>65.540000000000006</v>
       </c>
       <c r="O20" s="93">
-        <v>64.08</v>
+        <v>65.209999999999994</v>
       </c>
       <c r="P20" s="93">
-        <v>32607</v>
+        <v>2415</v>
       </c>
       <c r="Q20" s="93"/>
       <c r="R20" s="93"/>
@@ -6811,7 +6803,7 @@
       <c r="T20" s="93"/>
       <c r="U20" s="93"/>
       <c r="V20" s="92">
-        <v>46090.869606481479</v>
+        <v>46092.416759259257</v>
       </c>
       <c r="W20" s="1" t="s">
         <v>277</v>
@@ -6840,7 +6832,7 @@
         <v>62</v>
       </c>
       <c r="H21" s="93">
-        <v>230.125</v>
+        <v>0</v>
       </c>
       <c r="I21" s="93">
         <v>-100</v>
@@ -6852,19 +6844,15 @@
         <v>-100</v>
       </c>
       <c r="L21" s="93">
-        <v>234.57499999999999</v>
+        <v>232.375</v>
       </c>
       <c r="M21" s="93">
-        <v>228.07499999999999</v>
-      </c>
-      <c r="N21" s="93">
-        <v>230.92500000000001</v>
-      </c>
-      <c r="O21" s="93">
-        <v>227.32499999999999</v>
-      </c>
+        <v>231.35</v>
+      </c>
+      <c r="N21" s="93"/>
+      <c r="O21" s="93"/>
       <c r="P21" s="93">
-        <v>38861</v>
+        <v>0</v>
       </c>
       <c r="Q21" s="93"/>
       <c r="R21" s="93"/>
@@ -6872,7 +6860,7 @@
       <c r="T21" s="93"/>
       <c r="U21" s="93"/>
       <c r="V21" s="92">
-        <v>46090.869606481479</v>
+        <v>46092.416759259257</v>
       </c>
       <c r="W21" s="1" t="s">
         <v>277</v>
@@ -6901,7 +6889,7 @@
         <v>62</v>
       </c>
       <c r="H22" s="93">
-        <v>342.95</v>
+        <v>0</v>
       </c>
       <c r="I22" s="93">
         <v>-100</v>
@@ -6913,19 +6901,15 @@
         <v>-100</v>
       </c>
       <c r="L22" s="93">
-        <v>348.07499999999999</v>
+        <v>346.4</v>
       </c>
       <c r="M22" s="93">
-        <v>339.7</v>
-      </c>
-      <c r="N22" s="93">
-        <v>343.625</v>
-      </c>
-      <c r="O22" s="93">
-        <v>338.82499999999999</v>
-      </c>
+        <v>344.67500000000001</v>
+      </c>
+      <c r="N22" s="93"/>
+      <c r="O22" s="93"/>
       <c r="P22" s="93">
-        <v>11896</v>
+        <v>0</v>
       </c>
       <c r="Q22" s="93"/>
       <c r="R22" s="93"/>
@@ -6933,7 +6917,7 @@
       <c r="T22" s="93"/>
       <c r="U22" s="93"/>
       <c r="V22" s="92">
-        <v>46090.869606481479</v>
+        <v>46092.416759259257</v>
       </c>
       <c r="W22" s="1" t="s">
         <v>277</v>
@@ -6962,7 +6946,7 @@
         <v>62</v>
       </c>
       <c r="H23" s="93">
-        <v>94.825000000000003</v>
+        <v>0</v>
       </c>
       <c r="I23" s="93">
         <v>-100</v>
@@ -6974,19 +6958,15 @@
         <v>-100</v>
       </c>
       <c r="L23" s="93">
-        <v>95.625</v>
+        <v>96.075000000000003</v>
       </c>
       <c r="M23" s="93">
-        <v>95.35</v>
-      </c>
-      <c r="N23" s="93">
-        <v>95.5</v>
-      </c>
-      <c r="O23" s="93">
-        <v>94.1</v>
-      </c>
+        <v>95.6</v>
+      </c>
+      <c r="N23" s="93"/>
+      <c r="O23" s="93"/>
       <c r="P23" s="93">
-        <v>30165</v>
+        <v>0</v>
       </c>
       <c r="Q23" s="93"/>
       <c r="R23" s="93"/>
@@ -6994,7 +6974,7 @@
       <c r="T23" s="93"/>
       <c r="U23" s="93"/>
       <c r="V23" s="92">
-        <v>46090.869606481479</v>
+        <v>46092.416759259257</v>
       </c>
       <c r="W23" s="1" t="s">
         <v>277</v>
@@ -7023,31 +7003,31 @@
         <v>62</v>
       </c>
       <c r="H24" s="93">
-        <v>98.625</v>
+        <v>98.715000000000003</v>
       </c>
       <c r="I24" s="93">
-        <v>98.63</v>
+        <v>98.71</v>
       </c>
       <c r="J24" s="93">
-        <v>98.635000000000005</v>
+        <v>98.715000000000003</v>
       </c>
       <c r="K24" s="93">
-        <v>98.632499999999993</v>
+        <v>98.712500000000006</v>
       </c>
       <c r="L24" s="93">
-        <v>98.71</v>
+        <v>98.56</v>
       </c>
       <c r="M24" s="93">
-        <v>99.04</v>
+        <v>98.68</v>
       </c>
       <c r="N24" s="93">
-        <v>99.435000000000002</v>
+        <v>98.715000000000003</v>
       </c>
       <c r="O24" s="93">
-        <v>98.564999999999998</v>
+        <v>98.435000000000002</v>
       </c>
       <c r="P24" s="93">
-        <v>11235</v>
+        <v>1277</v>
       </c>
       <c r="Q24" s="93"/>
       <c r="R24" s="93"/>
@@ -7055,7 +7035,7 @@
       <c r="T24" s="93"/>
       <c r="U24" s="93"/>
       <c r="V24" s="92">
-        <v>46090.869606481479</v>
+        <v>46092.416759259257</v>
       </c>
       <c r="W24" s="1" t="s">
         <v>277</v>
@@ -7084,31 +7064,31 @@
         <v>62</v>
       </c>
       <c r="H25" s="93">
-        <v>1.1669499999999999</v>
+        <v>1.1657999999999999</v>
       </c>
       <c r="I25" s="93">
-        <v>1.1669499999999999</v>
+        <v>1.1657999999999999</v>
       </c>
       <c r="J25" s="93">
-        <v>1.1670499999999999</v>
+        <v>1.1658500000000001</v>
       </c>
       <c r="K25" s="93">
-        <v>1.1669999999999998</v>
+        <v>1.1658249999999999</v>
       </c>
       <c r="L25" s="93">
-        <v>1.1655500000000001</v>
+        <v>1.1677999999999999</v>
       </c>
       <c r="M25" s="93">
-        <v>1.1604000000000001</v>
+        <v>1.1667000000000001</v>
       </c>
       <c r="N25" s="93">
-        <v>1.1675500000000001</v>
+        <v>1.1698500000000001</v>
       </c>
       <c r="O25" s="93">
-        <v>1.1560999999999999</v>
+        <v>1.1656</v>
       </c>
       <c r="P25" s="93">
-        <v>153875</v>
+        <v>29643</v>
       </c>
       <c r="Q25" s="93"/>
       <c r="R25" s="93"/>
@@ -7116,7 +7096,7 @@
       <c r="T25" s="93"/>
       <c r="U25" s="93"/>
       <c r="V25" s="92">
-        <v>46090.869606481479</v>
+        <v>46092.416759259257</v>
       </c>
       <c r="W25" s="1" t="s">
         <v>277</v>
@@ -7145,31 +7125,31 @@
         <v>62</v>
       </c>
       <c r="H26" s="93">
-        <v>1.3428</v>
+        <v>1.3411</v>
       </c>
       <c r="I26" s="93">
-        <v>1.3427</v>
+        <v>1.341</v>
       </c>
       <c r="J26" s="93">
+        <v>1.3411</v>
+      </c>
+      <c r="K26" s="93">
+        <v>1.3410500000000001</v>
+      </c>
+      <c r="L26" s="93">
         <v>1.3429</v>
       </c>
-      <c r="K26" s="93">
-        <v>1.3428</v>
-      </c>
-      <c r="L26" s="93">
-        <v>1.3387</v>
-      </c>
       <c r="M26" s="93">
-        <v>1.3351</v>
+        <v>1.3416999999999999</v>
       </c>
       <c r="N26" s="93">
-        <v>1.3438000000000001</v>
+        <v>1.3456999999999999</v>
       </c>
       <c r="O26" s="93">
-        <v>1.3283</v>
+        <v>1.3409</v>
       </c>
       <c r="P26" s="93">
-        <v>72466</v>
+        <v>11991</v>
       </c>
       <c r="Q26" s="93"/>
       <c r="R26" s="93"/>
@@ -7177,7 +7157,7 @@
       <c r="T26" s="93"/>
       <c r="U26" s="93"/>
       <c r="V26" s="92">
-        <v>46090.869606481479</v>
+        <v>46092.416759259257</v>
       </c>
       <c r="W26" s="1" t="s">
         <v>277</v>
@@ -7206,31 +7186,31 @@
         <v>62</v>
       </c>
       <c r="H27" s="93">
-        <v>6.3889999999999997E-3</v>
+        <v>6.3635000000000002E-3</v>
       </c>
       <c r="I27" s="93">
-        <v>6.3885000000000001E-3</v>
+        <v>6.3629999999999997E-3</v>
       </c>
       <c r="J27" s="93">
-        <v>6.3895000000000002E-3</v>
+        <v>6.3635000000000002E-3</v>
       </c>
       <c r="K27" s="93">
-        <v>6.3890000000000006E-3</v>
+        <v>6.36325E-3</v>
       </c>
       <c r="L27" s="93">
-        <v>6.3879999999999996E-3</v>
+        <v>6.3860000000000002E-3</v>
       </c>
       <c r="M27" s="93">
-        <v>6.3800000000000003E-3</v>
+        <v>6.3784999999999996E-3</v>
       </c>
       <c r="N27" s="93">
-        <v>6.3905000000000003E-3</v>
+        <v>6.3860000000000002E-3</v>
       </c>
       <c r="O27" s="93">
-        <v>6.3464999999999997E-3</v>
+        <v>6.3629999999999997E-3</v>
       </c>
       <c r="P27" s="93">
-        <v>85160</v>
+        <v>17592</v>
       </c>
       <c r="Q27" s="93"/>
       <c r="R27" s="93"/>
@@ -7238,7 +7218,7 @@
       <c r="T27" s="93"/>
       <c r="U27" s="93"/>
       <c r="V27" s="92">
-        <v>46090.869606481479</v>
+        <v>46092.416759259257</v>
       </c>
       <c r="W27" s="1" t="s">
         <v>277</v>
@@ -7267,31 +7247,31 @@
         <v>62</v>
       </c>
       <c r="H28" s="93">
-        <v>0.73980000000000001</v>
+        <v>0.73995</v>
       </c>
       <c r="I28" s="93">
-        <v>0.73975000000000002</v>
+        <v>0.73995</v>
       </c>
       <c r="J28" s="93">
-        <v>0.73985000000000001</v>
+        <v>0.74004999999999999</v>
       </c>
       <c r="K28" s="93">
-        <v>0.73980000000000001</v>
+        <v>0.74</v>
       </c>
       <c r="L28" s="93">
-        <v>0.73919999999999997</v>
+        <v>0.73965000000000003</v>
       </c>
       <c r="M28" s="93">
-        <v>0.73875000000000002</v>
+        <v>0.73929999999999996</v>
       </c>
       <c r="N28" s="93">
-        <v>0.74250000000000005</v>
+        <v>0.74080000000000001</v>
       </c>
       <c r="O28" s="93">
-        <v>0.73799999999999999</v>
+        <v>0.73914999999999997</v>
       </c>
       <c r="P28" s="93">
-        <v>30906</v>
+        <v>3036</v>
       </c>
       <c r="Q28" s="93"/>
       <c r="R28" s="93"/>
@@ -7299,7 +7279,7 @@
       <c r="T28" s="93"/>
       <c r="U28" s="93"/>
       <c r="V28" s="92">
-        <v>46090.869606481479</v>
+        <v>46092.416759259257</v>
       </c>
       <c r="W28" s="1" t="s">
         <v>277</v>
@@ -7328,31 +7308,31 @@
         <v>62</v>
       </c>
       <c r="H29" s="93">
-        <v>0.70650000000000002</v>
+        <v>0.7147</v>
       </c>
       <c r="I29" s="93">
-        <v>0.70650000000000002</v>
+        <v>0.71465000000000001</v>
       </c>
       <c r="J29" s="93">
-        <v>0.70655000000000001</v>
+        <v>0.71475</v>
       </c>
       <c r="K29" s="93">
-        <v>0.70652500000000007</v>
+        <v>0.7147</v>
       </c>
       <c r="L29" s="93">
-        <v>0.70189999999999997</v>
+        <v>0.71260000000000001</v>
       </c>
       <c r="M29" s="93">
-        <v>0.69835000000000003</v>
+        <v>0.71109999999999995</v>
       </c>
       <c r="N29" s="93">
-        <v>0.70730000000000004</v>
+        <v>0.71775</v>
       </c>
       <c r="O29" s="93">
-        <v>0.69489999999999996</v>
+        <v>0.71060000000000001</v>
       </c>
       <c r="P29" s="93">
-        <v>62742</v>
+        <v>25663</v>
       </c>
       <c r="Q29" s="93"/>
       <c r="R29" s="93"/>
@@ -7360,7 +7340,7 @@
       <c r="T29" s="93"/>
       <c r="U29" s="93"/>
       <c r="V29" s="92">
-        <v>46090.869606481479</v>
+        <v>46092.416759259257</v>
       </c>
       <c r="W29" s="1" t="s">
         <v>277</v>
@@ -7389,31 +7369,31 @@
         <v>62</v>
       </c>
       <c r="H30" s="93">
-        <v>116.625</v>
+        <v>115.59375</v>
       </c>
       <c r="I30" s="93">
-        <v>116.625</v>
+        <v>115.59375</v>
       </c>
       <c r="J30" s="93">
-        <v>116.65625</v>
+        <v>115.625</v>
       </c>
       <c r="K30" s="93">
-        <v>116.640625</v>
+        <v>115.609375</v>
       </c>
       <c r="L30" s="93">
-        <v>116.1875</v>
+        <v>116.09375</v>
       </c>
       <c r="M30" s="93">
-        <v>115.8125</v>
+        <v>115.71875</v>
       </c>
       <c r="N30" s="93">
-        <v>116.71875</v>
+        <v>116.03125</v>
       </c>
       <c r="O30" s="93">
-        <v>115.0625</v>
+        <v>115.5625</v>
       </c>
       <c r="P30" s="93">
-        <v>566117</v>
+        <v>42491</v>
       </c>
       <c r="Q30" s="93"/>
       <c r="R30" s="93"/>
@@ -7421,7 +7401,7 @@
       <c r="T30" s="93"/>
       <c r="U30" s="93"/>
       <c r="V30" s="92">
-        <v>46090.869606481479</v>
+        <v>46092.416759259257</v>
       </c>
       <c r="W30" s="1" t="s">
         <v>277</v>
@@ -7450,31 +7430,31 @@
         <v>62</v>
       </c>
       <c r="H31" s="93">
-        <v>112.59375</v>
+        <v>112.28125</v>
       </c>
       <c r="I31" s="93">
-        <v>112.59375</v>
+        <v>112.265625</v>
       </c>
       <c r="J31" s="93">
-        <v>112.609375</v>
+        <v>112.28125</v>
       </c>
       <c r="K31" s="93">
-        <v>112.6015625</v>
+        <v>112.2734375</v>
       </c>
       <c r="L31" s="93">
+        <v>112.453125</v>
+      </c>
+      <c r="M31" s="93">
+        <v>112.28125</v>
+      </c>
+      <c r="N31" s="93">
         <v>112.4375</v>
       </c>
-      <c r="M31" s="93">
-        <v>112.1875</v>
-      </c>
-      <c r="N31" s="93">
-        <v>112.671875</v>
-      </c>
       <c r="O31" s="93">
-        <v>111.828125</v>
+        <v>112.234375</v>
       </c>
       <c r="P31" s="93">
-        <v>2658505</v>
+        <v>272433</v>
       </c>
       <c r="Q31" s="93"/>
       <c r="R31" s="93"/>
@@ -7482,7 +7462,7 @@
       <c r="T31" s="93"/>
       <c r="U31" s="93"/>
       <c r="V31" s="92">
-        <v>46090.869606481479</v>
+        <v>46092.416759259257</v>
       </c>
       <c r="W31" s="1" t="s">
         <v>277</v>
@@ -7511,31 +7491,31 @@
         <v>59</v>
       </c>
       <c r="H32" s="93">
-        <v>127.42</v>
+        <v>126.67</v>
       </c>
       <c r="I32" s="93">
-        <v>127.42</v>
+        <v>126.67</v>
       </c>
       <c r="J32" s="93">
-        <v>127.43</v>
+        <v>126.68</v>
       </c>
       <c r="K32" s="93">
-        <v>127.42500000000001</v>
+        <v>126.67500000000001</v>
       </c>
       <c r="L32" s="93">
-        <v>126.93</v>
+        <v>127.25</v>
       </c>
       <c r="M32" s="93">
-        <v>126.7</v>
+        <v>127.12</v>
       </c>
       <c r="N32" s="93">
-        <v>127.48</v>
+        <v>127.2</v>
       </c>
       <c r="O32" s="93">
-        <v>125.94</v>
+        <v>126.66</v>
       </c>
       <c r="P32" s="93">
-        <v>2145114</v>
+        <v>293889</v>
       </c>
       <c r="Q32" s="93"/>
       <c r="R32" s="93"/>
@@ -7543,7 +7523,7 @@
       <c r="T32" s="93"/>
       <c r="U32" s="93"/>
       <c r="V32" s="92">
-        <v>46090.869606481479</v>
+        <v>46092.416759259257</v>
       </c>
       <c r="W32" s="1" t="s">
         <v>277</v>
@@ -7572,31 +7552,31 @@
         <v>59</v>
       </c>
       <c r="H33" s="93">
-        <v>111.44</v>
+        <v>109.92</v>
       </c>
       <c r="I33" s="93">
-        <v>111.42</v>
+        <v>109.92</v>
       </c>
       <c r="J33" s="93">
-        <v>111.44</v>
+        <v>109.94</v>
       </c>
       <c r="K33" s="93">
-        <v>111.43</v>
+        <v>109.93</v>
       </c>
       <c r="L33" s="93">
-        <v>110.88</v>
+        <v>110.76</v>
       </c>
       <c r="M33" s="93">
-        <v>111</v>
+        <v>110.52</v>
       </c>
       <c r="N33" s="93">
-        <v>111.7</v>
+        <v>110.72</v>
       </c>
       <c r="O33" s="93">
-        <v>110.14</v>
+        <v>109.88</v>
       </c>
       <c r="P33" s="93">
-        <v>328496</v>
+        <v>36217</v>
       </c>
       <c r="Q33" s="93"/>
       <c r="R33" s="93"/>
@@ -7604,7 +7584,7 @@
       <c r="T33" s="93"/>
       <c r="U33" s="93"/>
       <c r="V33" s="92">
-        <v>46090.869606481479</v>
+        <v>46092.416759259257</v>
       </c>
       <c r="W33" s="1" t="s">
         <v>277</v>
@@ -7633,31 +7613,31 @@
         <v>59</v>
       </c>
       <c r="H34" s="93">
-        <v>118.77</v>
+        <v>118.89</v>
       </c>
       <c r="I34" s="93">
-        <v>-1</v>
+        <v>118.89</v>
       </c>
       <c r="J34" s="93">
-        <v>-1</v>
+        <v>118.9</v>
       </c>
       <c r="K34" s="93">
-        <v>-1</v>
+        <v>118.89500000000001</v>
       </c>
       <c r="L34" s="93">
-        <v>118.6</v>
+        <v>119.66</v>
       </c>
       <c r="M34" s="93">
-        <v>117.62</v>
+        <v>119.5</v>
       </c>
       <c r="N34" s="93">
-        <v>118.97</v>
+        <v>119.51</v>
       </c>
       <c r="O34" s="93">
-        <v>117.42</v>
+        <v>118.87</v>
       </c>
       <c r="P34" s="93">
-        <v>705078</v>
+        <v>102070</v>
       </c>
       <c r="Q34" s="93"/>
       <c r="R34" s="93"/>
@@ -7665,7 +7645,7 @@
       <c r="T34" s="93"/>
       <c r="U34" s="93"/>
       <c r="V34" s="92">
-        <v>46090.869606481479</v>
+        <v>46092.416759259257</v>
       </c>
       <c r="W34" s="1" t="s">
         <v>277</v>
@@ -7694,29 +7674,29 @@
         <v>62</v>
       </c>
       <c r="H35" s="93">
-        <v>68902.75</v>
+        <v>69652.25</v>
       </c>
       <c r="I35" s="93">
-        <v>68902.75</v>
+        <v>69615</v>
       </c>
       <c r="J35" s="93">
-        <v>68903</v>
+        <v>69615.25</v>
       </c>
       <c r="K35" s="93">
-        <v>68902.875</v>
+        <v>69615.125</v>
       </c>
       <c r="L35" s="93">
-        <v>67317.25</v>
+        <v>70060.75</v>
       </c>
       <c r="M35" s="93"/>
       <c r="N35" s="93">
-        <v>69646.5</v>
+        <v>71739</v>
       </c>
       <c r="O35" s="93">
-        <v>65471</v>
+        <v>68388.5</v>
       </c>
       <c r="P35" s="93">
-        <v>351.10540517999999</v>
+        <v>114.33914932</v>
       </c>
       <c r="Q35" s="93"/>
       <c r="R35" s="93"/>
@@ -7724,7 +7704,7 @@
       <c r="T35" s="93"/>
       <c r="U35" s="93"/>
       <c r="V35" s="92">
-        <v>46090.869606481479</v>
+        <v>46092.416759259257</v>
       </c>
       <c r="W35" s="1" t="s">
         <v>277</v>
@@ -7753,29 +7733,29 @@
         <v>62</v>
       </c>
       <c r="H36" s="93">
-        <v>2030.35</v>
+        <v>2023.05</v>
       </c>
       <c r="I36" s="93">
-        <v>2030.35</v>
+        <v>2023.05</v>
       </c>
       <c r="J36" s="93">
-        <v>2030.4</v>
+        <v>2023.1</v>
       </c>
       <c r="K36" s="93">
-        <v>2030.375</v>
+        <v>2023.0749999999998</v>
       </c>
       <c r="L36" s="93">
-        <v>1964.3</v>
+        <v>2037.15</v>
       </c>
       <c r="M36" s="93"/>
       <c r="N36" s="93">
-        <v>2056.0500000000002</v>
+        <v>2086.35</v>
       </c>
       <c r="O36" s="93">
-        <v>1914.8</v>
+        <v>1989.75</v>
       </c>
       <c r="P36" s="93">
-        <v>3593.66171377</v>
+        <v>924.18638008000005</v>
       </c>
       <c r="Q36" s="93"/>
       <c r="R36" s="93"/>
@@ -7783,7 +7763,7 @@
       <c r="T36" s="93"/>
       <c r="U36" s="93"/>
       <c r="V36" s="92">
-        <v>46090.869606481479</v>
+        <v>46092.416759259257</v>
       </c>
       <c r="W36" s="1" t="s">
         <v>277</v>
@@ -8079,13 +8059,37 @@
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A11" s="85"/>
+      <c r="A11" s="85">
+        <v>46092.415810185186</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>314</v>
+      </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A12" s="85"/>
+      <c r="A12" s="85">
+        <v>46092.415821759256</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>315</v>
+      </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A13" s="85"/>
+      <c r="A13" s="85">
+        <v>46092.415821759256</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>316</v>
+      </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A14" s="85"/>
@@ -8540,11 +8544,11 @@
       <c r="H5" s="67"/>
       <c r="I5" s="70">
         <f>Blotter!C$4-SUM(NAV!I$4:I4)</f>
-        <v>3664.5906320098998</v>
+        <v>7414.5906320099002</v>
       </c>
       <c r="J5" s="70">
         <f t="shared" si="2"/>
-        <v>1003664.5906320099</v>
+        <v>1007414.5906320099</v>
       </c>
       <c r="K5" s="70">
         <f t="shared" si="3"/>
@@ -8552,19 +8556,19 @@
       </c>
       <c r="L5" s="71">
         <f t="shared" si="4"/>
-        <v>1003.6645906320099</v>
+        <v>1007.4145906320099</v>
       </c>
       <c r="M5" s="72">
         <f t="shared" si="5"/>
-        <v>3.6645906320098565E-3</v>
+        <v>7.4145906320099986E-3</v>
       </c>
       <c r="N5" s="73">
         <f t="shared" ref="N5" si="6">L5/L4-1</f>
-        <v>3.6645906320098565E-3</v>
+        <v>7.4145906320099986E-3</v>
       </c>
       <c r="O5" s="75">
         <f>STDEVP(N$4:N5)*SQRT(12)</f>
-        <v>6.3472571635820136E-3</v>
+        <v>1.2842447691965549E-2</v>
       </c>
     </row>
     <row r="6" spans="2:18" ht="14.25" x14ac:dyDescent="0.4">
@@ -9027,10 +9031,10 @@
         <v>202</v>
       </c>
       <c r="W4" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="X4" s="1" t="s">
         <v>326</v>
-      </c>
-      <c r="X4" s="1" t="s">
-        <v>327</v>
       </c>
     </row>
     <row r="5" spans="2:28" x14ac:dyDescent="0.4">
@@ -9044,7 +9048,7 @@
       </c>
       <c r="D5" s="6">
         <f t="array" ref="D5">SUM((Blotter!C$19:C$1013=C5)*(Blotter!N$19:N$1013)*1)</f>
-        <v>2601.0899999999965</v>
+        <v>6351.0899999999965</v>
       </c>
       <c r="E5" s="6">
         <f t="array" ref="E5">SUM((Blotter!B$19:C$1013=C5)*(Blotter!R$19:R$1013)*1)</f>
@@ -9052,7 +9056,7 @@
       </c>
       <c r="F5" s="30">
         <f t="shared" ref="F5" si="1">IF(ISNUMBER(D5/E5),D5/E5,0)</f>
-        <v>0.2890099999999996</v>
+        <v>0.70567666666666629</v>
       </c>
       <c r="G5" s="36" t="str">
         <f t="array" ref="G5">IF(SUM((Blotter!C$19:C$1013=PLB!C5)*(Blotter!M$19:M$1013))=0,"C","O")</f>
@@ -9060,20 +9064,20 @@
       </c>
       <c r="H5" s="16">
         <f>J4+D5</f>
-        <v>1003123.33063201</v>
+        <v>1006873.33063201</v>
       </c>
       <c r="I5" s="16"/>
       <c r="J5" s="16">
         <f>H5+I5</f>
-        <v>1003123.33063201</v>
+        <v>1006873.33063201</v>
       </c>
       <c r="K5" s="3">
         <f>H5/J4-1</f>
-        <v>2.5997323141531137E-3</v>
+        <v>6.3477749340066225E-3</v>
       </c>
       <c r="L5" s="3">
         <f>(1+K5)*(1+L4)-1</f>
-        <v>3.1233306320099796E-3</v>
+        <v>6.8733306320101217E-3</v>
       </c>
       <c r="M5" s="6">
         <f>O4-IF(G5="O",O4*1%,-D5)</f>
@@ -9111,10 +9115,10 @@
         <v>319</v>
       </c>
       <c r="W5" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="X5" s="1" t="s">
         <v>328</v>
-      </c>
-      <c r="X5" s="1" t="s">
-        <v>329</v>
       </c>
     </row>
     <row r="6" spans="2:28" x14ac:dyDescent="0.4">
@@ -11996,7 +12000,7 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>62</v>
@@ -12008,7 +12012,7 @@
         <v>304</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>68</v>
@@ -12072,7 +12076,7 @@
     </row>
     <row r="3" spans="1:31" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>62</v>
@@ -12084,7 +12088,7 @@
         <v>304</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>68</v>
@@ -12145,22 +12149,22 @@
     </row>
     <row r="4" spans="1:31" x14ac:dyDescent="0.4">
       <c r="A4" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>62</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="E4" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="G4" s="1" t="s">
         <v>324</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>324</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>325</v>
       </c>
       <c r="H4" s="1">
         <v>1</v>

--- a/1XW_TradeBlotter_Web.xlsx
+++ b/1XW_TradeBlotter_Web.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="253" documentId="13_ncr:1_{6F5069F1-F0E7-4440-AA6D-4AFA11BBED1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B131FD68-2782-436E-ACAA-2515342E383A}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="22695" windowHeight="14476" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="22695" windowHeight="14476" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Blotter" sheetId="3" r:id="rId1"/>

--- a/1XW_TradeBlotter_Web.xlsx
+++ b/1XW_TradeBlotter_Web.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0a601c1c2ba3d9f4/Trading/The Strategy Project/1XW Website/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="253" documentId="13_ncr:1_{6F5069F1-F0E7-4440-AA6D-4AFA11BBED1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B131FD68-2782-436E-ACAA-2515342E383A}"/>
+  <xr:revisionPtr revIDLastSave="302" documentId="13_ncr:1_{6F5069F1-F0E7-4440-AA6D-4AFA11BBED1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9212F668-2DA2-444F-804D-06D50913B085}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="22695" windowHeight="14476" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="22695" windowHeight="14476" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Blotter" sheetId="3" r:id="rId1"/>
@@ -85,7 +85,8 @@
             <charset val="1"/>
           </rPr>
           <t xml:space="preserve">
-ATR or Premium</t>
+ATR or Premium
+Negative for short position</t>
         </r>
       </text>
     </comment>
@@ -116,7 +117,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1135" uniqueCount="330">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1165" uniqueCount="326">
   <si>
     <t>WEEK</t>
   </si>
@@ -262,15 +263,6 @@
     <t>BTP</t>
   </si>
   <si>
-    <t>BABA</t>
-  </si>
-  <si>
-    <t>NVDA</t>
-  </si>
-  <si>
-    <t>GOOG</t>
-  </si>
-  <si>
     <t>ENTRY PRICE</t>
   </si>
   <si>
@@ -307,9 +299,6 @@
     <t>USD</t>
   </si>
   <si>
-    <t>ESTX50</t>
-  </si>
-  <si>
     <t>NYMEX</t>
   </si>
   <si>
@@ -496,9 +485,6 @@
     <t>INITIAL RISK $</t>
   </si>
   <si>
-    <t>INDA</t>
-  </si>
-  <si>
     <t>ASSET CLASS</t>
   </si>
   <si>
@@ -583,9 +569,6 @@
     <t>T-BOND CPN</t>
   </si>
   <si>
-    <t>URA</t>
-  </si>
-  <si>
     <t>HEG3</t>
   </si>
   <si>
@@ -593,9 +576,6 @@
   </si>
   <si>
     <t>T-BOND 3 CPN</t>
-  </si>
-  <si>
-    <t>SAVE</t>
   </si>
   <si>
     <t>BoP NAV $</t>
@@ -635,9 +615,6 @@
     <t>WK PLB %</t>
   </si>
   <si>
-    <t>SAVE-S</t>
-  </si>
-  <si>
     <t>Date</t>
   </si>
   <si>
@@ -680,15 +657,9 @@
     <t>Perf. MTD</t>
   </si>
   <si>
-    <t>CYTK-S</t>
-  </si>
-  <si>
     <t>ZWK4</t>
   </si>
   <si>
-    <t>IBB-S</t>
-  </si>
-  <si>
     <t>CLJ4</t>
   </si>
   <si>
@@ -737,9 +708,6 @@
     <t>PAXOS</t>
   </si>
   <si>
-    <t>Long ETH</t>
-  </si>
-  <si>
     <t>3) Your model references Prices sheet cells.</t>
   </si>
   <si>
@@ -878,9 +846,6 @@
     <t>level</t>
   </si>
   <si>
-    <t>FESX</t>
-  </si>
-  <si>
     <t>FDXM</t>
   </si>
   <si>
@@ -902,9 +867,6 @@
     <t>RTYH6</t>
   </si>
   <si>
-    <t>FESXH6</t>
-  </si>
-  <si>
     <t>DAXH6</t>
   </si>
   <si>
@@ -971,9 +933,6 @@
     <t>RTYM6</t>
   </si>
   <si>
-    <t>FESX 20260619 M</t>
-  </si>
-  <si>
     <t>FDXM 20260619 M</t>
   </si>
   <si>
@@ -1088,9 +1047,6 @@
     <t>SELL</t>
   </si>
   <si>
-    <t>Long CC</t>
-  </si>
-  <si>
     <t>DUP242961</t>
   </si>
   <si>
@@ -1119,6 +1075,39 @@
   </si>
   <si>
     <t>Close</t>
+  </si>
+  <si>
+    <t>P</t>
+  </si>
+  <si>
+    <t>LO</t>
+  </si>
+  <si>
+    <t>CLM6P75260514</t>
+  </si>
+  <si>
+    <t>CLM6P55260514</t>
+  </si>
+  <si>
+    <t>Loaded 36 contracts from Symbols sheet.</t>
+  </si>
+  <si>
+    <t>FOP</t>
+  </si>
+  <si>
+    <t>LOM6 P7500</t>
+  </si>
+  <si>
+    <t>LOM6 P5500</t>
+  </si>
+  <si>
+    <t>Long ETH Spot</t>
+  </si>
+  <si>
+    <t>Long CC Futures</t>
+  </si>
+  <si>
+    <t>Long CL Put Spread</t>
   </si>
 </sst>
 </file>
@@ -1786,7 +1775,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>7.4145906320099986E-3</c:v>
+                  <c:v>5.5142806320098714E-3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1940,7 +1929,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>7.4145906320099986E-3</c:v>
+                  <c:v>5.5142806320098714E-3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2331,7 +2320,7 @@
                   <c:v>1000</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1007.4145906320099</c:v>
+                  <c:v>1005.5142806320099</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2605,6 +2594,9 @@
                 <c:pt idx="1">
                   <c:v>-1.9900000000000029E-2</c:v>
                 </c:pt>
+                <c:pt idx="2">
+                  <c:v>-2.9701000000000088E-2</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -2665,6 +2657,9 @@
                 <c:pt idx="1">
                   <c:v>46095</c:v>
                 </c:pt>
+                <c:pt idx="2">
+                  <c:v>46102</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2679,6 +2674,9 @@
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>-9.482981774310062E-3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-1.9388151956566846E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2738,7 +2736,10 @@
                   <c:v>5.2224063201000703E-4</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>6.8733306320101217E-3</c:v>
+                  <c:v>2.9133306320099361E-3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4.513330632009982E-3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3385,21 +3386,22 @@
   <sheetData>
     <row r="1" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B1" s="32" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="C1" s="79">
-        <v>46090</v>
+        <f ca="1">TODAY()</f>
+        <v>46095</v>
       </c>
     </row>
     <row r="2" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B2" s="32" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="C2" s="37" t="s">
-        <v>329</v>
+        <v>314</v>
       </c>
       <c r="E2" s="47" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="F2" s="47" t="s">
         <v>6</v>
@@ -3409,53 +3411,53 @@
     </row>
     <row r="3" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B3" s="32" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C3" s="28">
         <f ca="1">OFFSET(NAV!B1,MATCH(C1,NAV!B:B,1),8)</f>
-        <v>1007414.5906320099</v>
+        <v>1005514.2806320098</v>
       </c>
       <c r="E3" s="47" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="F3" s="47" t="s">
-        <v>317</v>
+        <v>303</v>
       </c>
       <c r="G3" s="47"/>
       <c r="H3" s="28"/>
     </row>
     <row r="4" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B4" s="32" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C4" s="28">
         <f>SUM(N18:N1012)</f>
-        <v>7414.5906320099002</v>
+        <v>5514.2806320099007</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="47" t="s">
         <v>20</v>
       </c>
       <c r="F4" s="47" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="G4" s="47"/>
       <c r="H4" s="28"/>
     </row>
     <row r="5" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B5" s="32" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="C5" s="3">
         <f ca="1">OFFSET(NAV!B1,MATCH(C1,NAV!B:B,1),11)</f>
-        <v>7.4145906320099986E-3</v>
+        <v>5.5142806320098714E-3</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="47" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="F5" s="47" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="G5" s="47"/>
       <c r="H5" s="28"/>
@@ -3463,11 +3465,11 @@
     </row>
     <row r="6" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B6" s="32" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="C6" s="3">
         <f ca="1">OFFSET(NAV!B1,MATCH(C1,NAV!B:B,1),12)</f>
-        <v>7.4145906320099986E-3</v>
+        <v>5.5142806320098714E-3</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="47"/>
@@ -3478,15 +3480,15 @@
     </row>
     <row r="7" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B7" s="32" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="C7" s="28">
         <f>Cash_Mgmt!H13</f>
-        <v>35858.739999999954</v>
+        <v>35399.049999999952</v>
       </c>
       <c r="D7" s="3">
         <f ca="1">C7/C3</f>
-        <v>3.5594818988579149E-2</v>
+        <v>3.5204920190442343E-2</v>
       </c>
       <c r="E7" s="47"/>
       <c r="F7" s="47"/>
@@ -3496,15 +3498,15 @@
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B8" s="32" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="C8" s="28">
         <f>C4+C7</f>
-        <v>43273.330632009856</v>
+        <v>40913.330632009849</v>
       </c>
       <c r="D8" s="3">
         <f ca="1">C5+D7</f>
-        <v>4.3009409620589148E-2</v>
+        <v>4.0719200822452215E-2</v>
       </c>
       <c r="G8" s="47"/>
       <c r="H8" s="51"/>
@@ -3512,15 +3514,15 @@
     </row>
     <row r="9" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B9" s="32" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="C9" s="28">
         <f t="array" ref="C9">SUM((F19:F112="Futures")*(M19:M112))</f>
-        <v>103410</v>
+        <v>99450</v>
       </c>
       <c r="D9" s="3">
         <f ca="1">C9/$C$3</f>
-        <v>0.10264890042452619</v>
+        <v>9.8904612212460385E-2</v>
       </c>
       <c r="E9" s="47"/>
       <c r="F9" s="47"/>
@@ -3530,7 +3532,7 @@
     </row>
     <row r="10" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B10" s="32" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="C10" s="28">
         <f t="array" ref="C10">SUM((F19:F1012="Call")*(M19:M1012))</f>
@@ -3544,61 +3546,61 @@
     </row>
     <row r="11" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B11" s="32" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="C11" s="28">
         <f t="array" ref="C11">SUM((F19:F212="Put")*(M19:M212))</f>
-        <v>0</v>
+        <v>9600</v>
       </c>
       <c r="D11" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
+        <v>9.5473532150791331E-3</v>
       </c>
     </row>
     <row r="12" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B12" s="32" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="C12" s="28" cm="1">
         <f t="array" ref="C12">SUM((PLB!G4:G999="O")*(PLB!E4:E999))</f>
-        <v>9000</v>
+        <v>17233.333333333332</v>
       </c>
       <c r="D12" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>8.933759828070164E-3</v>
+        <v>1.7138825042346914E-2</v>
       </c>
     </row>
     <row r="13" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B13" s="32" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="C13" s="28">
         <f t="array" ref="C13">SUM((PLB!G4:G999="O")*(PLB!D4:D999))</f>
-        <v>6351.0899999999965</v>
+        <v>3991.0899999999965</v>
       </c>
       <c r="D13" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>6.304345856273123E-3</v>
+        <v>3.9692027024135559E-3</v>
       </c>
       <c r="F13" s="59"/>
       <c r="G13" s="59"/>
     </row>
     <row r="14" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B14" s="32" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="C14" s="28">
         <f>C12+C13</f>
-        <v>15351.089999999997</v>
+        <v>21224.423333333329</v>
       </c>
       <c r="D14" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>1.5238105684343289E-2</v>
+        <v>2.110802774476047E-2</v>
       </c>
     </row>
     <row r="17" spans="2:28" x14ac:dyDescent="0.4">
       <c r="B17" s="38" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>0</v>
@@ -3607,16 +3609,16 @@
         <v>1</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="F17" s="4" t="s">
         <v>2</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="I17" s="4" t="s">
         <v>10</v>
@@ -3625,60 +3627,60 @@
         <v>11</v>
       </c>
       <c r="K17" s="4" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="L17" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="M17" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="N17" s="4" t="s">
         <v>52</v>
-      </c>
-      <c r="M17" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="N17" s="4" t="s">
-        <v>55</v>
       </c>
       <c r="O17" s="4" t="s">
         <v>14</v>
       </c>
       <c r="P17" s="4" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="Q17" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="R17" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="S17" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="T17" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="U17" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="V17" s="4" t="s">
         <v>118</v>
-      </c>
-      <c r="R17" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="S17" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="T17" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="U17" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="V17" s="4" t="s">
-        <v>122</v>
       </c>
       <c r="W17" s="32"/>
       <c r="X17" s="33" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="Y17" s="33" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="Z17" s="33" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
     </row>
     <row r="18" spans="2:28" x14ac:dyDescent="0.4">
       <c r="B18" s="9" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="C18" s="12"/>
       <c r="D18" s="12"/>
       <c r="E18" s="10" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="F18" s="12"/>
       <c r="G18" s="12"/>
@@ -3690,7 +3692,7 @@
       <c r="M18" s="12"/>
       <c r="N18" s="95">
         <f>Cash_Mgmt!G13</f>
-        <v>541.25999999990927</v>
+        <v>1000.9499999999098</v>
       </c>
       <c r="O18" s="12"/>
       <c r="P18" s="12"/>
@@ -3707,19 +3709,19 @@
     </row>
     <row r="19" spans="2:28" x14ac:dyDescent="0.4">
       <c r="B19" s="9" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="C19" s="10">
         <v>1</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="F19" s="10" t="s">
-        <v>317</v>
+        <v>303</v>
       </c>
       <c r="G19" s="28">
         <f>VLOOKUP(D19,Multiplier!B:I,8,0)</f>
@@ -3790,13 +3792,13 @@
       </c>
       <c r="Z19" s="35">
         <f>IF(C$2="Last",IF(ISNUMBER(VLOOKUP(B19,Prices!A:L,8,0)),VLOOKUP(B19,Prices!A:L,8,0),0),IF(ISNUMBER(VLOOKUP(B19,Prices!A:L,12,0)),VLOOKUP(B19,Prices!A:L,12,0),0))</f>
-        <v>2037.15</v>
+        <v>2102.25</v>
       </c>
       <c r="AB19" s="29"/>
     </row>
     <row r="20" spans="2:28" x14ac:dyDescent="0.4">
       <c r="B20" s="9" t="s">
-        <v>304</v>
+        <v>290</v>
       </c>
       <c r="C20" s="10">
         <v>2</v>
@@ -3805,7 +3807,7 @@
         <v>34</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="F20" s="10" t="s">
         <v>6</v>
@@ -3831,15 +3833,15 @@
       </c>
       <c r="L20" s="29">
         <f t="shared" ref="L20" si="8">IF(I20=0,IF(H20&gt;0,X20,Y20),Z20)</f>
-        <v>3447</v>
+        <v>3315</v>
       </c>
       <c r="M20" s="28">
         <f t="shared" ref="M20" si="9">I20*J20*L20</f>
-        <v>103410</v>
+        <v>99450</v>
       </c>
       <c r="N20" s="95">
         <f t="array" ref="N20">-SUM((Trades!T$2:T$9999=Blotter!C20)*(Trades!U$2:U$9999=Blotter!B20)*(Trades!V$2:V$9999)*(Trades!W$2:W$9999))*J20+SUM((Trades!T$2:T$9999=Blotter!C20)*(Trades!U$2:U$9999=Blotter!B20)*(Trades!X$2:X$9999))+(L20*I20)*J20</f>
-        <v>6351.0899999999965</v>
+        <v>2391.0899999999965</v>
       </c>
       <c r="O20" s="29">
         <f>VLOOKUP(D20,Multiplier!B:H,3,0)</f>
@@ -3855,11 +3857,11 @@
       </c>
       <c r="S20" s="29">
         <f>IF(OR(F20="Futures",F20="Spot"),IF(I20=0,0,IF(I20&gt;0,L20-O20,L20+O20)),0)</f>
-        <v>3242</v>
+        <v>3110</v>
       </c>
       <c r="T20" s="3">
         <f t="shared" ref="T20" si="11">IF(S20&gt;0,IF(ISNUMBER(S20/L20-1),S20/L20-1,0),0)</f>
-        <v>-5.9472004641717424E-2</v>
+        <v>-6.1840120663650078E-2</v>
       </c>
       <c r="U20" s="29">
         <f t="shared" ref="U20" si="12">IF(OR(F20="Futures",F20="Stocks"),IF(I20=0,0,IF(I20&gt;0,K20-P20,K20+P20)),0)</f>
@@ -3867,7 +3869,7 @@
       </c>
       <c r="V20" s="3">
         <f t="shared" ref="V20" si="13">IF(U20&gt;0,IF(ISNUMBER(U20/L20-1),U20/L20-1,0),0)</f>
-        <v>-0.1484487960545402</v>
+        <v>-0.11454087481146302</v>
       </c>
       <c r="X20" s="34">
         <f t="array" ref="X20">IF(ISNUMBER(SUM((Trades!T$2:T$9999=Blotter!C20)*(Trades!U$2:U$9999=Blotter!B20)*(Trades!W$2:W$9999)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0))/SUM((Trades!T$2:T$9999=Blotter!C20)*(Trades!U$2:U$9999=Blotter!B20)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0))),SUM((Trades!T$2:T$9999=Blotter!C20)*(Trades!U$2:U$9999=Blotter!B20)*(Trades!W$2:W$9999)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0))/SUM((Trades!T$2:T$9999=Blotter!C20)*(Trades!U$2:U$9999=Blotter!B20)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0)),0)</f>
@@ -3879,62 +3881,186 @@
       </c>
       <c r="Z20" s="35">
         <f>IF(C$2="Last",IF(ISNUMBER(VLOOKUP(B20,Prices!A:L,8,0)),VLOOKUP(B20,Prices!A:L,8,0),0),IF(ISNUMBER(VLOOKUP(B20,Prices!A:L,12,0)),VLOOKUP(B20,Prices!A:L,12,0),0))</f>
-        <v>3447</v>
+        <v>3315</v>
       </c>
       <c r="AB20" s="29"/>
     </row>
     <row r="21" spans="2:28" x14ac:dyDescent="0.4">
-      <c r="B21" s="9"/>
-      <c r="C21" s="10"/>
-      <c r="D21" s="10"/>
-      <c r="E21" s="10"/>
-      <c r="F21" s="10"/>
-      <c r="G21" s="28"/>
-      <c r="H21" s="11"/>
-      <c r="I21" s="29"/>
-      <c r="J21" s="28"/>
-      <c r="K21" s="46"/>
-      <c r="L21" s="46"/>
-      <c r="M21" s="28"/>
-      <c r="N21" s="28"/>
-      <c r="O21" s="29"/>
-      <c r="P21" s="27"/>
+      <c r="B21" s="9" t="s">
+        <v>317</v>
+      </c>
+      <c r="C21" s="10">
+        <v>3</v>
+      </c>
+      <c r="D21" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="E21" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="F21" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="G21" s="28">
+        <f>VLOOKUP(D21,Multiplier!B:I,8,0)</f>
+        <v>4</v>
+      </c>
+      <c r="H21" s="11">
+        <v>2</v>
+      </c>
+      <c r="I21" s="28">
+        <f t="array" ref="I21">ROUND(SUM((Trades!V$2:V$9999)*(Trades!U$2:U$9999=Blotter!B21)*(Trades!$T$2:T$9999=Blotter!C21)),8)</f>
+        <v>2</v>
+      </c>
+      <c r="J21" s="28">
+        <f>VLOOKUP(D21,Multiplier!B:D,2,0)</f>
+        <v>1000</v>
+      </c>
+      <c r="K21" s="29">
+        <f t="shared" ref="K21:K22" si="14">L21-N21/(H21*J21)</f>
+        <v>5</v>
+      </c>
+      <c r="L21" s="29">
+        <f t="shared" ref="L21:L22" si="15">IF(I21=0,IF(H21&gt;0,X21,Y21),Z21)</f>
+        <v>5.35</v>
+      </c>
+      <c r="M21" s="28">
+        <f t="shared" ref="M21:M22" si="16">I21*J21*L21</f>
+        <v>10700</v>
+      </c>
+      <c r="N21" s="95">
+        <f t="array" ref="N21">-SUM((Trades!T$2:T$9999=Blotter!C21)*(Trades!U$2:U$9999=Blotter!B21)*(Trades!V$2:V$9999)*(Trades!W$2:W$9999))*J21+SUM((Trades!T$2:T$9999=Blotter!C21)*(Trades!U$2:U$9999=Blotter!B21)*(Trades!X$2:X$9999))+(L21*I21)*J21</f>
+        <v>700</v>
+      </c>
+      <c r="O21" s="29">
+        <f>VLOOKUP(D21,Multiplier!B:H,3,0)</f>
+        <v>2.1</v>
+      </c>
+      <c r="P21" s="27">
+        <v>5.1166666666666663</v>
+      </c>
       <c r="Q21" s="27"/>
-      <c r="R21" s="28"/>
-      <c r="S21" s="29"/>
-      <c r="T21" s="3"/>
-      <c r="U21" s="29"/>
-      <c r="V21" s="3"/>
-      <c r="X21" s="34"/>
-      <c r="Y21" s="34"/>
-      <c r="Z21" s="35"/>
+      <c r="R21" s="28">
+        <f t="shared" ref="R21:R22" si="17">(1-Q21)*P21*J21*H21</f>
+        <v>10233.333333333332</v>
+      </c>
+      <c r="S21" s="29">
+        <f t="shared" ref="S21:S22" si="18">IF(OR(F21="Futures",F21="Spot"),IF(I21=0,0,IF(I21&gt;0,L21-O21,L21+O21)),0)</f>
+        <v>0</v>
+      </c>
+      <c r="T21" s="3">
+        <f t="shared" ref="T21:T22" si="19">IF(S21&gt;0,IF(ISNUMBER(S21/L21-1),S21/L21-1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="U21" s="29">
+        <f t="shared" ref="U21:U22" si="20">IF(OR(F21="Futures",F21="Stocks"),IF(I21=0,0,IF(I21&gt;0,K21-P21,K21+P21)),0)</f>
+        <v>0</v>
+      </c>
+      <c r="V21" s="3">
+        <f t="shared" ref="V21:V22" si="21">IF(U21&gt;0,IF(ISNUMBER(U21/L21-1),U21/L21-1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="X21" s="34">
+        <f t="array" ref="X21">IF(ISNUMBER(SUM((Trades!T$2:T$9999=Blotter!C21)*(Trades!U$2:U$9999=Blotter!B21)*(Trades!W$2:W$9999)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0))/SUM((Trades!T$2:T$9999=Blotter!C21)*(Trades!U$2:U$9999=Blotter!B21)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0))),SUM((Trades!T$2:T$9999=Blotter!C21)*(Trades!U$2:U$9999=Blotter!B21)*(Trades!W$2:W$9999)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0))/SUM((Trades!T$2:T$9999=Blotter!C21)*(Trades!U$2:U$9999=Blotter!B21)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0)),0)</f>
+        <v>0</v>
+      </c>
+      <c r="Y21" s="34">
+        <f t="array" ref="Y21">IF(ISNUMBER(SUM((Trades!T$2:T$9999=Blotter!C21)*(Trades!U$2:U$9999=Blotter!B21)*(Trades!W$2:W$9999)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&gt;0))/SUM((Trades!T$2:T$9999=Blotter!C21)*(Trades!U$2:U$9999=Blotter!B21)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&gt;0))),SUM((Trades!T$2:T$9999=Blotter!C21)*(Trades!U$2:U$9999=Blotter!B21)*(Trades!W$2:W$9999)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&gt;0))/SUM((Trades!T$2:T$9999=Blotter!C21)*(Trades!U$2:U$9999=Blotter!B21)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&gt;0)),0)</f>
+        <v>5</v>
+      </c>
+      <c r="Z21" s="35">
+        <f>IF(C$2="Last",IF(ISNUMBER(VLOOKUP(B21,Prices!A:L,8,0)),VLOOKUP(B21,Prices!A:L,8,0),0),IF(ISNUMBER(VLOOKUP(B21,Prices!A:L,12,0)),VLOOKUP(B21,Prices!A:L,12,0),0))</f>
+        <v>5.35</v>
+      </c>
       <c r="AB21" s="29"/>
     </row>
     <row r="22" spans="2:28" x14ac:dyDescent="0.4">
-      <c r="B22" s="9"/>
-      <c r="C22" s="10"/>
-      <c r="D22" s="10"/>
-      <c r="E22" s="10"/>
-      <c r="F22" s="10"/>
-      <c r="G22" s="28"/>
-      <c r="H22" s="11"/>
-      <c r="I22" s="29"/>
-      <c r="J22" s="28"/>
-      <c r="K22" s="46"/>
-      <c r="L22" s="46"/>
-      <c r="M22" s="28"/>
-      <c r="N22" s="28"/>
-      <c r="O22" s="29"/>
-      <c r="P22" s="27"/>
+      <c r="B22" s="9" t="s">
+        <v>318</v>
+      </c>
+      <c r="C22" s="10">
+        <v>3</v>
+      </c>
+      <c r="D22" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="E22" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="F22" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="G22" s="28">
+        <f>VLOOKUP(D22,Multiplier!B:I,8,0)</f>
+        <v>4</v>
+      </c>
+      <c r="H22" s="11">
+        <v>-2</v>
+      </c>
+      <c r="I22" s="28">
+        <f t="array" ref="I22">ROUND(SUM((Trades!V$2:V$9999)*(Trades!U$2:U$9999=Blotter!B22)*(Trades!$T$2:T$9999=Blotter!C22)),8)</f>
+        <v>-2</v>
+      </c>
+      <c r="J22" s="28">
+        <f>VLOOKUP(D22,Multiplier!B:D,2,0)</f>
+        <v>1000</v>
+      </c>
+      <c r="K22" s="29">
+        <f t="shared" si="14"/>
+        <v>1</v>
+      </c>
+      <c r="L22" s="29">
+        <f t="shared" si="15"/>
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="M22" s="28">
+        <f t="shared" si="16"/>
+        <v>-1100</v>
+      </c>
+      <c r="N22" s="95">
+        <f t="array" ref="N22">-SUM((Trades!T$2:T$9999=Blotter!C22)*(Trades!U$2:U$9999=Blotter!B22)*(Trades!V$2:V$9999)*(Trades!W$2:W$9999))*J22+SUM((Trades!T$2:T$9999=Blotter!C22)*(Trades!U$2:U$9999=Blotter!B22)*(Trades!X$2:X$9999))+(L22*I22)*J22</f>
+        <v>900</v>
+      </c>
+      <c r="O22" s="29">
+        <f>VLOOKUP(D22,Multiplier!B:H,3,0)</f>
+        <v>2.1</v>
+      </c>
+      <c r="P22" s="27">
+        <v>1</v>
+      </c>
       <c r="Q22" s="27"/>
-      <c r="R22" s="28"/>
-      <c r="S22" s="29"/>
-      <c r="T22" s="3"/>
-      <c r="U22" s="29"/>
-      <c r="V22" s="3"/>
-      <c r="X22" s="34"/>
-      <c r="Y22" s="34"/>
-      <c r="Z22" s="35"/>
+      <c r="R22" s="28">
+        <f t="shared" si="17"/>
+        <v>-2000</v>
+      </c>
+      <c r="S22" s="29">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="T22" s="3">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="U22" s="29">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="V22" s="3">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="X22" s="34">
+        <f t="array" ref="X22">IF(ISNUMBER(SUM((Trades!T$2:T$9999=Blotter!C22)*(Trades!U$2:U$9999=Blotter!B22)*(Trades!W$2:W$9999)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0))/SUM((Trades!T$2:T$9999=Blotter!C22)*(Trades!U$2:U$9999=Blotter!B22)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0))),SUM((Trades!T$2:T$9999=Blotter!C22)*(Trades!U$2:U$9999=Blotter!B22)*(Trades!W$2:W$9999)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0))/SUM((Trades!T$2:T$9999=Blotter!C22)*(Trades!U$2:U$9999=Blotter!B22)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0)),0)</f>
+        <v>1</v>
+      </c>
+      <c r="Y22" s="34">
+        <f t="array" ref="Y22">IF(ISNUMBER(SUM((Trades!T$2:T$9999=Blotter!C22)*(Trades!U$2:U$9999=Blotter!B22)*(Trades!W$2:W$9999)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&gt;0))/SUM((Trades!T$2:T$9999=Blotter!C22)*(Trades!U$2:U$9999=Blotter!B22)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&gt;0))),SUM((Trades!T$2:T$9999=Blotter!C22)*(Trades!U$2:U$9999=Blotter!B22)*(Trades!W$2:W$9999)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&gt;0))/SUM((Trades!T$2:T$9999=Blotter!C22)*(Trades!U$2:U$9999=Blotter!B22)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&gt;0)),0)</f>
+        <v>0</v>
+      </c>
+      <c r="Z22" s="35">
+        <f>IF(C$2="Last",IF(ISNUMBER(VLOOKUP(B22,Prices!A:L,8,0)),VLOOKUP(B22,Prices!A:L,8,0),0),IF(ISNUMBER(VLOOKUP(B22,Prices!A:L,12,0)),VLOOKUP(B22,Prices!A:L,12,0),0))</f>
+        <v>0.55000000000000004</v>
+      </c>
       <c r="AB22" s="29"/>
     </row>
     <row r="23" spans="2:28" x14ac:dyDescent="0.4">
@@ -5565,73 +5691,73 @@
   <sheetData>
     <row r="1" spans="1:32" x14ac:dyDescent="0.4">
       <c r="A1" s="86" t="s">
+        <v>217</v>
+      </c>
+      <c r="B1" s="86" t="s">
+        <v>235</v>
+      </c>
+      <c r="C1" s="86" t="s">
+        <v>216</v>
+      </c>
+      <c r="D1" s="86" t="s">
+        <v>215</v>
+      </c>
+      <c r="E1" s="86" t="s">
+        <v>207</v>
+      </c>
+      <c r="F1" s="86" t="s">
+        <v>214</v>
+      </c>
+      <c r="G1" s="86" t="s">
+        <v>213</v>
+      </c>
+      <c r="H1" s="86" t="s">
+        <v>234</v>
+      </c>
+      <c r="I1" s="86" t="s">
+        <v>233</v>
+      </c>
+      <c r="J1" s="86" t="s">
+        <v>232</v>
+      </c>
+      <c r="K1" s="86" t="s">
+        <v>231</v>
+      </c>
+      <c r="L1" s="86" t="s">
+        <v>230</v>
+      </c>
+      <c r="M1" s="86" t="s">
+        <v>229</v>
+      </c>
+      <c r="N1" s="86" t="s">
         <v>228</v>
       </c>
-      <c r="B1" s="86" t="s">
-        <v>246</v>
-      </c>
-      <c r="C1" s="86" t="s">
+      <c r="O1" s="86" t="s">
         <v>227</v>
       </c>
-      <c r="D1" s="86" t="s">
+      <c r="P1" s="86" t="s">
         <v>226</v>
       </c>
-      <c r="E1" s="86" t="s">
-        <v>218</v>
-      </c>
-      <c r="F1" s="86" t="s">
+      <c r="Q1" s="86" t="s">
         <v>225</v>
       </c>
-      <c r="G1" s="86" t="s">
+      <c r="R1" s="86" t="s">
         <v>224</v>
       </c>
-      <c r="H1" s="86" t="s">
-        <v>245</v>
-      </c>
-      <c r="I1" s="86" t="s">
-        <v>244</v>
-      </c>
-      <c r="J1" s="86" t="s">
-        <v>243</v>
-      </c>
-      <c r="K1" s="86" t="s">
-        <v>242</v>
-      </c>
-      <c r="L1" s="86" t="s">
-        <v>241</v>
-      </c>
-      <c r="M1" s="86" t="s">
-        <v>240</v>
-      </c>
-      <c r="N1" s="86" t="s">
-        <v>239</v>
-      </c>
-      <c r="O1" s="86" t="s">
-        <v>238</v>
-      </c>
-      <c r="P1" s="86" t="s">
-        <v>237</v>
-      </c>
-      <c r="Q1" s="86" t="s">
-        <v>236</v>
-      </c>
-      <c r="R1" s="86" t="s">
-        <v>235</v>
-      </c>
       <c r="S1" s="86" t="s">
-        <v>234</v>
+        <v>223</v>
       </c>
       <c r="T1" s="86" t="s">
-        <v>233</v>
+        <v>222</v>
       </c>
       <c r="U1" s="86" t="s">
-        <v>232</v>
+        <v>221</v>
       </c>
       <c r="V1" s="86" t="s">
-        <v>231</v>
+        <v>220</v>
       </c>
       <c r="W1" s="86" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="X1" s="84"/>
       <c r="Y1" s="84"/>
@@ -5645,52 +5771,48 @@
     </row>
     <row r="2" spans="1:32" x14ac:dyDescent="0.4">
       <c r="A2" s="81" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="B2" s="81">
         <v>649180678</v>
       </c>
       <c r="C2" s="81" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D2" s="81" t="s">
         <v>21</v>
       </c>
       <c r="E2" s="81" t="s">
-        <v>276</v>
+        <v>263</v>
       </c>
       <c r="F2" s="81" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="G2" s="81" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="H2" s="91">
-        <v>6832</v>
+        <v>-1</v>
       </c>
       <c r="I2" s="91">
-        <v>6832.75</v>
+        <v>-1</v>
       </c>
       <c r="J2" s="91">
-        <v>6833.75</v>
+        <v>-1</v>
       </c>
       <c r="K2" s="91">
-        <v>6833.25</v>
+        <v>-1</v>
       </c>
       <c r="L2" s="91">
-        <v>6838</v>
+        <v>6727.25</v>
       </c>
       <c r="M2" s="91">
-        <v>6846.25</v>
-      </c>
-      <c r="N2" s="91">
-        <v>6873.25</v>
-      </c>
-      <c r="O2" s="91">
-        <v>6832</v>
-      </c>
+        <v>6735.5</v>
+      </c>
+      <c r="N2" s="91"/>
+      <c r="O2" s="91"/>
       <c r="P2" s="91">
-        <v>2484</v>
+        <v>0</v>
       </c>
       <c r="Q2" s="91"/>
       <c r="R2" s="91"/>
@@ -5698,10 +5820,10 @@
       <c r="T2" s="91"/>
       <c r="U2" s="91"/>
       <c r="V2" s="85">
-        <v>46092.416759259257</v>
+        <v>46095.373206018521</v>
       </c>
       <c r="W2" s="81" t="s">
-        <v>277</v>
+        <v>264</v>
       </c>
       <c r="X2" s="81"/>
       <c r="Y2" s="81"/>
@@ -5709,52 +5831,48 @@
     </row>
     <row r="3" spans="1:32" x14ac:dyDescent="0.4">
       <c r="A3" s="81" t="s">
-        <v>255</v>
+        <v>243</v>
       </c>
       <c r="B3" s="81">
         <v>750150196</v>
       </c>
       <c r="C3" s="81" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D3" s="81" t="s">
         <v>22</v>
       </c>
       <c r="E3" s="81" t="s">
-        <v>278</v>
+        <v>265</v>
       </c>
       <c r="F3" s="81" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="G3" s="81" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="H3" s="91">
-        <v>25199</v>
+        <v>-1</v>
       </c>
       <c r="I3" s="91">
-        <v>25182.75</v>
+        <v>-1</v>
       </c>
       <c r="J3" s="91">
-        <v>25186.75</v>
+        <v>-1</v>
       </c>
       <c r="K3" s="91">
-        <v>25184.75</v>
+        <v>-1</v>
       </c>
       <c r="L3" s="91">
-        <v>25199.5</v>
+        <v>24773.5</v>
       </c>
       <c r="M3" s="91">
-        <v>25220</v>
-      </c>
-      <c r="N3" s="91">
-        <v>25338</v>
-      </c>
-      <c r="O3" s="91">
-        <v>25170.75</v>
-      </c>
+        <v>24783.5</v>
+      </c>
+      <c r="N3" s="91"/>
+      <c r="O3" s="91"/>
       <c r="P3" s="91">
-        <v>742</v>
+        <v>0</v>
       </c>
       <c r="Q3" s="91"/>
       <c r="R3" s="91"/>
@@ -5762,10 +5880,10 @@
       <c r="T3" s="91"/>
       <c r="U3" s="91"/>
       <c r="V3" s="85">
-        <v>46092.416759259257</v>
+        <v>46095.373206018521</v>
       </c>
       <c r="W3" s="81" t="s">
-        <v>277</v>
+        <v>264</v>
       </c>
       <c r="X3" s="81"/>
       <c r="Y3" s="81"/>
@@ -5773,52 +5891,48 @@
     </row>
     <row r="4" spans="1:32" x14ac:dyDescent="0.4">
       <c r="A4" s="81" t="s">
-        <v>256</v>
+        <v>244</v>
       </c>
       <c r="B4" s="81">
         <v>770561234</v>
       </c>
       <c r="C4" s="81" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D4" s="81" t="s">
         <v>23</v>
       </c>
       <c r="E4" s="81" t="s">
-        <v>279</v>
+        <v>266</v>
       </c>
       <c r="F4" s="81" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="G4" s="81" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="H4" s="91">
-        <v>2557.8000000000002</v>
+        <v>-1</v>
       </c>
       <c r="I4" s="91">
-        <v>2556.9</v>
+        <v>-1</v>
       </c>
       <c r="J4" s="91">
-        <v>2557.5</v>
+        <v>-1</v>
       </c>
       <c r="K4" s="91">
-        <v>2557.1999999999998</v>
+        <v>-1</v>
       </c>
       <c r="L4" s="91">
-        <v>2566.9</v>
+        <v>2507</v>
       </c>
       <c r="M4" s="91">
-        <v>2570.3000000000002</v>
-      </c>
-      <c r="N4" s="91">
-        <v>2583.1999999999998</v>
-      </c>
-      <c r="O4" s="91">
-        <v>2556.8000000000002</v>
-      </c>
+        <v>2511.5</v>
+      </c>
+      <c r="N4" s="91"/>
+      <c r="O4" s="91"/>
       <c r="P4" s="91">
-        <v>293</v>
+        <v>0</v>
       </c>
       <c r="Q4" s="91"/>
       <c r="R4" s="91"/>
@@ -5826,10 +5940,10 @@
       <c r="T4" s="91"/>
       <c r="U4" s="91"/>
       <c r="V4" s="85">
-        <v>46092.416759259257</v>
+        <v>46095.373206018521</v>
       </c>
       <c r="W4" s="81" t="s">
-        <v>277</v>
+        <v>264</v>
       </c>
       <c r="X4" s="81"/>
       <c r="Y4" s="81"/>
@@ -5837,52 +5951,44 @@
     </row>
     <row r="5" spans="1:32" x14ac:dyDescent="0.4">
       <c r="A5" s="81" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
       <c r="B5" s="81">
-        <v>638120304</v>
+        <v>638120262</v>
       </c>
       <c r="C5" s="81" t="s">
+        <v>58</v>
+      </c>
+      <c r="D5" s="81" t="s">
         <v>61</v>
       </c>
-      <c r="D5" s="81" t="s">
-        <v>63</v>
-      </c>
       <c r="E5" s="81" t="s">
-        <v>280</v>
+        <v>267</v>
       </c>
       <c r="F5" s="81" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="G5" s="81" t="s">
-        <v>59</v>
-      </c>
-      <c r="H5" s="91">
-        <v>5710</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="H5" s="91"/>
       <c r="I5" s="91">
-        <v>5706</v>
+        <v>-1</v>
       </c>
       <c r="J5" s="91">
-        <v>5707</v>
+        <v>-1</v>
       </c>
       <c r="K5" s="91">
-        <v>5706.5</v>
+        <v>-1</v>
       </c>
       <c r="L5" s="91">
-        <v>5771</v>
-      </c>
-      <c r="M5" s="91">
-        <v>5741</v>
-      </c>
-      <c r="N5" s="91">
-        <v>5770</v>
-      </c>
-      <c r="O5" s="91">
-        <v>5698</v>
-      </c>
+        <v>23796</v>
+      </c>
+      <c r="M5" s="91"/>
+      <c r="N5" s="91"/>
+      <c r="O5" s="91"/>
       <c r="P5" s="91">
-        <v>930</v>
+        <v>0</v>
       </c>
       <c r="Q5" s="91"/>
       <c r="R5" s="91"/>
@@ -5890,10 +5996,10 @@
       <c r="T5" s="91"/>
       <c r="U5" s="91"/>
       <c r="V5" s="85">
-        <v>46092.416759259257</v>
+        <v>46095.373206018521</v>
       </c>
       <c r="W5" s="81" t="s">
-        <v>277</v>
+        <v>264</v>
       </c>
       <c r="X5" s="81"/>
       <c r="Y5" s="81"/>
@@ -5901,52 +6007,48 @@
     </row>
     <row r="6" spans="1:32" x14ac:dyDescent="0.4">
       <c r="A6" s="81" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B6" s="81">
-        <v>638120262</v>
+        <v>635680486</v>
       </c>
       <c r="C6" s="81" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D6" s="81" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E6" s="81" t="s">
-        <v>281</v>
+        <v>296</v>
       </c>
       <c r="F6" s="81" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="G6" s="81" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="H6" s="91">
-        <v>23814</v>
+        <v>0</v>
       </c>
       <c r="I6" s="91">
-        <v>23822</v>
+        <v>0</v>
       </c>
       <c r="J6" s="91">
-        <v>23883</v>
+        <v>0</v>
       </c>
       <c r="K6" s="91">
-        <v>23852.5</v>
+        <v>0</v>
       </c>
       <c r="L6" s="91">
-        <v>24173</v>
+        <v>53570</v>
       </c>
       <c r="M6" s="91">
-        <v>24207</v>
-      </c>
-      <c r="N6" s="91">
-        <v>24207</v>
-      </c>
-      <c r="O6" s="91">
-        <v>23814</v>
-      </c>
+        <v>53540</v>
+      </c>
+      <c r="N6" s="91"/>
+      <c r="O6" s="91"/>
       <c r="P6" s="91">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="Q6" s="91"/>
       <c r="R6" s="91"/>
@@ -5954,10 +6056,10 @@
       <c r="T6" s="91"/>
       <c r="U6" s="91"/>
       <c r="V6" s="85">
-        <v>46092.416759259257</v>
+        <v>46095.373206018521</v>
       </c>
       <c r="W6" s="81" t="s">
-        <v>277</v>
+        <v>264</v>
       </c>
       <c r="X6" s="81"/>
       <c r="Y6" s="81"/>
@@ -5965,52 +6067,48 @@
     </row>
     <row r="7" spans="1:32" x14ac:dyDescent="0.4">
       <c r="A7" s="1" t="s">
-        <v>273</v>
+        <v>176</v>
       </c>
       <c r="B7" s="1">
-        <v>635680486</v>
+        <v>304037436</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>66</v>
+        <v>24</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>310</v>
+        <v>268</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H7" s="93">
-        <v>54405</v>
+        <v>-1</v>
       </c>
       <c r="I7" s="93">
-        <v>54395</v>
+        <v>-1</v>
       </c>
       <c r="J7" s="93">
-        <v>54405</v>
+        <v>-1</v>
       </c>
       <c r="K7" s="93">
-        <v>54400</v>
+        <v>-1</v>
       </c>
       <c r="L7" s="93">
-        <v>54675</v>
+        <v>95.73</v>
       </c>
       <c r="M7" s="93">
-        <v>54700</v>
-      </c>
-      <c r="N7" s="93">
-        <v>55535</v>
-      </c>
-      <c r="O7" s="93">
-        <v>54340</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N7" s="93"/>
+      <c r="O7" s="93"/>
       <c r="P7" s="93">
-        <v>10307</v>
+        <v>0</v>
       </c>
       <c r="Q7" s="93"/>
       <c r="R7" s="93"/>
@@ -6018,60 +6116,60 @@
       <c r="T7" s="93"/>
       <c r="U7" s="93"/>
       <c r="V7" s="92">
-        <v>46092.416759259257</v>
+        <v>46095.373206018521</v>
       </c>
       <c r="W7" s="1" t="s">
-        <v>277</v>
+        <v>264</v>
       </c>
     </row>
     <row r="8" spans="1:32" x14ac:dyDescent="0.4">
       <c r="A8" s="1" t="s">
-        <v>186</v>
+        <v>249</v>
       </c>
       <c r="B8" s="1">
-        <v>304037436</v>
+        <v>269460069</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>282</v>
+        <v>269</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="H8" s="93">
-        <v>85.63</v>
+        <v>3.2559999999999998</v>
       </c>
       <c r="I8" s="93">
-        <v>85.62</v>
+        <v>-1</v>
       </c>
       <c r="J8" s="93">
-        <v>85.64</v>
+        <v>-1</v>
       </c>
       <c r="K8" s="93">
-        <v>85.63</v>
+        <v>-1</v>
       </c>
       <c r="L8" s="93">
-        <v>83.45</v>
+        <v>3.3519999999999999</v>
       </c>
       <c r="M8" s="93">
-        <v>86.89</v>
+        <v>0</v>
       </c>
       <c r="N8" s="93">
-        <v>88.59</v>
+        <v>3.4119999999999999</v>
       </c>
       <c r="O8" s="93">
-        <v>81.790000000000006</v>
+        <v>3.2349999999999999</v>
       </c>
       <c r="P8" s="93">
-        <v>126856</v>
+        <v>35249</v>
       </c>
       <c r="Q8" s="93"/>
       <c r="R8" s="93"/>
@@ -6079,60 +6177,56 @@
       <c r="T8" s="93"/>
       <c r="U8" s="93"/>
       <c r="V8" s="92">
-        <v>46092.416759259257</v>
+        <v>46095.373206018521</v>
       </c>
       <c r="W8" s="1" t="s">
-        <v>277</v>
+        <v>264</v>
       </c>
     </row>
     <row r="9" spans="1:32" x14ac:dyDescent="0.4">
       <c r="A9" s="1" t="s">
-        <v>262</v>
+        <v>250</v>
       </c>
       <c r="B9" s="1">
-        <v>269460069</v>
+        <v>600696533</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>283</v>
+        <v>270</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="H9" s="93">
-        <v>3.2309999999999999</v>
+        <v>-1</v>
       </c>
       <c r="I9" s="93">
-        <v>3.2330000000000001</v>
+        <v>-1</v>
       </c>
       <c r="J9" s="93">
-        <v>3.2349999999999999</v>
+        <v>-1</v>
       </c>
       <c r="K9" s="93">
-        <v>3.234</v>
+        <v>-1</v>
       </c>
       <c r="L9" s="93">
-        <v>3.1829999999999998</v>
+        <v>2.8437000000000001</v>
       </c>
       <c r="M9" s="93">
-        <v>3.2130000000000001</v>
-      </c>
-      <c r="N9" s="93">
-        <v>3.24</v>
-      </c>
-      <c r="O9" s="93">
-        <v>3.1859999999999999</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N9" s="93"/>
+      <c r="O9" s="93"/>
       <c r="P9" s="93">
-        <v>2013</v>
+        <v>0</v>
       </c>
       <c r="Q9" s="93"/>
       <c r="R9" s="93"/>
@@ -6140,60 +6234,56 @@
       <c r="T9" s="93"/>
       <c r="U9" s="93"/>
       <c r="V9" s="92">
-        <v>46092.416759259257</v>
+        <v>46095.373206018521</v>
       </c>
       <c r="W9" s="1" t="s">
-        <v>277</v>
+        <v>264</v>
       </c>
     </row>
     <row r="10" spans="1:32" x14ac:dyDescent="0.4">
       <c r="A10" s="1" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="B10" s="1">
-        <v>600696533</v>
+        <v>430360630</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>284</v>
+        <v>271</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>64</v>
+        <v>81</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="H10" s="93">
-        <v>2.5867</v>
+        <v>-1</v>
       </c>
       <c r="I10" s="93">
-        <v>2.5870000000000002</v>
+        <v>-1</v>
       </c>
       <c r="J10" s="93">
-        <v>2.5878999999999999</v>
+        <v>-1</v>
       </c>
       <c r="K10" s="93">
-        <v>2.58745</v>
+        <v>-1</v>
       </c>
       <c r="L10" s="93">
-        <v>2.5423</v>
+        <v>5163.8</v>
       </c>
       <c r="M10" s="93">
-        <v>2.6063999999999998</v>
-      </c>
-      <c r="N10" s="93">
-        <v>2.6387999999999998</v>
-      </c>
-      <c r="O10" s="93">
-        <v>2.5327999999999999</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N10" s="93"/>
+      <c r="O10" s="93"/>
       <c r="P10" s="93">
-        <v>10234</v>
+        <v>0</v>
       </c>
       <c r="Q10" s="93"/>
       <c r="R10" s="93"/>
@@ -6201,60 +6291,60 @@
       <c r="T10" s="93"/>
       <c r="U10" s="93"/>
       <c r="V10" s="92">
-        <v>46092.416759259257</v>
+        <v>46095.373206018521</v>
       </c>
       <c r="W10" s="1" t="s">
-        <v>277</v>
+        <v>264</v>
       </c>
     </row>
     <row r="11" spans="1:32" x14ac:dyDescent="0.4">
       <c r="A11" s="1" t="s">
-        <v>264</v>
+        <v>252</v>
       </c>
       <c r="B11" s="1">
-        <v>430360630</v>
+        <v>760200596</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>285</v>
+        <v>272</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="H11" s="93">
-        <v>5231.7</v>
+        <v>80.959999999999994</v>
       </c>
       <c r="I11" s="93">
-        <v>5231.8</v>
+        <v>-1</v>
       </c>
       <c r="J11" s="93">
-        <v>5232.3</v>
+        <v>-1</v>
       </c>
       <c r="K11" s="93">
-        <v>5232.05</v>
+        <v>-1</v>
       </c>
       <c r="L11" s="93">
-        <v>5281.5</v>
+        <v>85.424999999999997</v>
       </c>
       <c r="M11" s="93">
-        <v>5234.3999999999996</v>
+        <v>0</v>
       </c>
       <c r="N11" s="93">
-        <v>5269.5</v>
+        <v>85.8</v>
       </c>
       <c r="O11" s="93">
-        <v>5224</v>
+        <v>80</v>
       </c>
       <c r="P11" s="93">
-        <v>2674</v>
+        <v>322</v>
       </c>
       <c r="Q11" s="93"/>
       <c r="R11" s="93"/>
@@ -6262,60 +6352,56 @@
       <c r="T11" s="93"/>
       <c r="U11" s="93"/>
       <c r="V11" s="92">
-        <v>46092.416759259257</v>
+        <v>46095.373206018521</v>
       </c>
       <c r="W11" s="1" t="s">
-        <v>277</v>
+        <v>264</v>
       </c>
     </row>
     <row r="12" spans="1:32" x14ac:dyDescent="0.4">
       <c r="A12" s="1" t="s">
-        <v>265</v>
+        <v>253</v>
       </c>
       <c r="B12" s="1">
-        <v>760200596</v>
+        <v>712565973</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>286</v>
+        <v>273</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="H12" s="93">
-        <v>87.125</v>
+        <v>-1</v>
       </c>
       <c r="I12" s="93">
-        <v>87.655000000000001</v>
+        <v>-1</v>
       </c>
       <c r="J12" s="93">
-        <v>87.7</v>
+        <v>-1</v>
       </c>
       <c r="K12" s="93">
-        <v>87.677500000000009</v>
+        <v>-1</v>
       </c>
       <c r="L12" s="93">
-        <v>89.91</v>
+        <v>5.8955000000000002</v>
       </c>
       <c r="M12" s="93">
-        <v>89.7</v>
-      </c>
-      <c r="N12" s="93">
-        <v>90.015000000000001</v>
-      </c>
-      <c r="O12" s="93">
-        <v>87.125</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N12" s="93"/>
+      <c r="O12" s="93"/>
       <c r="P12" s="93">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="Q12" s="93"/>
       <c r="R12" s="93"/>
@@ -6323,60 +6409,56 @@
       <c r="T12" s="93"/>
       <c r="U12" s="93"/>
       <c r="V12" s="92">
-        <v>46092.416759259257</v>
+        <v>46095.373206018521</v>
       </c>
       <c r="W12" s="1" t="s">
-        <v>277</v>
+        <v>264</v>
       </c>
     </row>
     <row r="13" spans="1:32" x14ac:dyDescent="0.4">
       <c r="A13" s="1" t="s">
-        <v>266</v>
+        <v>137</v>
       </c>
       <c r="B13" s="1">
-        <v>712565973</v>
+        <v>671574022</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="H13" s="93">
-        <v>5.8975</v>
+        <v>-100</v>
       </c>
       <c r="I13" s="93">
-        <v>5.8710000000000004</v>
+        <v>-100</v>
       </c>
       <c r="J13" s="93">
-        <v>5.8724999999999996</v>
+        <v>-100</v>
       </c>
       <c r="K13" s="93">
-        <v>5.8717500000000005</v>
+        <v>-100</v>
       </c>
       <c r="L13" s="93">
-        <v>5.9790000000000001</v>
+        <v>462.5</v>
       </c>
       <c r="M13" s="93">
-        <v>5.9509999999999996</v>
-      </c>
-      <c r="N13" s="93">
-        <v>5.9669999999999996</v>
-      </c>
-      <c r="O13" s="93">
-        <v>5.8975</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N13" s="93"/>
+      <c r="O13" s="93"/>
       <c r="P13" s="93">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="Q13" s="93"/>
       <c r="R13" s="93"/>
@@ -6384,60 +6466,56 @@
       <c r="T13" s="93"/>
       <c r="U13" s="93"/>
       <c r="V13" s="92">
-        <v>46092.416759259257</v>
+        <v>46095.373206018521</v>
       </c>
       <c r="W13" s="1" t="s">
-        <v>277</v>
+        <v>264</v>
       </c>
     </row>
     <row r="14" spans="1:32" x14ac:dyDescent="0.4">
       <c r="A14" s="1" t="s">
-        <v>142</v>
+        <v>175</v>
       </c>
       <c r="B14" s="1">
-        <v>671574022</v>
+        <v>642254817</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>299</v>
+        <v>286</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="H14" s="93">
-        <v>454.5</v>
+        <v>-100</v>
       </c>
       <c r="I14" s="93">
-        <v>454.5</v>
+        <v>-100</v>
       </c>
       <c r="J14" s="93">
-        <v>454.75</v>
+        <v>-100</v>
       </c>
       <c r="K14" s="93">
-        <v>454.625</v>
+        <v>-100</v>
       </c>
       <c r="L14" s="93">
-        <v>452.25</v>
+        <v>598.5</v>
       </c>
       <c r="M14" s="93">
-        <v>453.25</v>
-      </c>
-      <c r="N14" s="93">
-        <v>455.5</v>
-      </c>
-      <c r="O14" s="93">
-        <v>451.5</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N14" s="93"/>
+      <c r="O14" s="93"/>
       <c r="P14" s="93">
-        <v>20510</v>
+        <v>0</v>
       </c>
       <c r="Q14" s="93"/>
       <c r="R14" s="93"/>
@@ -6445,60 +6523,56 @@
       <c r="T14" s="93"/>
       <c r="U14" s="93"/>
       <c r="V14" s="92">
-        <v>46092.416759259257</v>
+        <v>46095.373206018521</v>
       </c>
       <c r="W14" s="1" t="s">
-        <v>277</v>
+        <v>264</v>
       </c>
     </row>
     <row r="15" spans="1:32" x14ac:dyDescent="0.4">
       <c r="A15" s="1" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="B15" s="1">
-        <v>642254817</v>
+        <v>665643569</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>300</v>
+        <v>287</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="H15" s="93">
-        <v>595.25</v>
+        <v>-100</v>
       </c>
       <c r="I15" s="93">
-        <v>595</v>
+        <v>-100</v>
       </c>
       <c r="J15" s="93">
-        <v>595.25</v>
+        <v>-100</v>
       </c>
       <c r="K15" s="93">
-        <v>595.125</v>
+        <v>-100</v>
       </c>
       <c r="L15" s="93">
-        <v>591</v>
+        <v>1227.25</v>
       </c>
       <c r="M15" s="93">
-        <v>592.5</v>
-      </c>
-      <c r="N15" s="93">
-        <v>597.5</v>
-      </c>
-      <c r="O15" s="93">
-        <v>589.25</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N15" s="93"/>
+      <c r="O15" s="93"/>
       <c r="P15" s="93">
-        <v>8730</v>
+        <v>0</v>
       </c>
       <c r="Q15" s="93"/>
       <c r="R15" s="93"/>
@@ -6506,60 +6580,56 @@
       <c r="T15" s="93"/>
       <c r="U15" s="93"/>
       <c r="V15" s="92">
-        <v>46092.416759259257</v>
+        <v>46095.373206018521</v>
       </c>
       <c r="W15" s="1" t="s">
-        <v>277</v>
+        <v>264</v>
       </c>
     </row>
     <row r="16" spans="1:32" x14ac:dyDescent="0.4">
       <c r="A16" s="1" t="s">
-        <v>190</v>
+        <v>134</v>
       </c>
       <c r="B16" s="1">
-        <v>665643569</v>
+        <v>634760175</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>301</v>
+        <v>288</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>86</v>
+        <v>64</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="H16" s="93">
-        <v>1208.75</v>
+        <v>-100</v>
       </c>
       <c r="I16" s="93">
-        <v>1208.5</v>
+        <v>-100</v>
       </c>
       <c r="J16" s="93">
-        <v>1208.75</v>
+        <v>-100</v>
       </c>
       <c r="K16" s="93">
-        <v>1208.625</v>
+        <v>-100</v>
       </c>
       <c r="L16" s="93">
-        <v>1201.75</v>
+        <v>14.38</v>
       </c>
       <c r="M16" s="93">
-        <v>1207</v>
-      </c>
-      <c r="N16" s="93">
-        <v>1212.75</v>
-      </c>
-      <c r="O16" s="93">
-        <v>1203.5</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N16" s="93"/>
+      <c r="O16" s="93"/>
       <c r="P16" s="93">
-        <v>15653</v>
+        <v>0</v>
       </c>
       <c r="Q16" s="93"/>
       <c r="R16" s="93"/>
@@ -6567,60 +6637,56 @@
       <c r="T16" s="93"/>
       <c r="U16" s="93"/>
       <c r="V16" s="92">
-        <v>46092.416759259257</v>
+        <v>46095.373206018521</v>
       </c>
       <c r="W16" s="1" t="s">
-        <v>277</v>
+        <v>264</v>
       </c>
     </row>
     <row r="17" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A17" s="1" t="s">
-        <v>139</v>
+        <v>177</v>
       </c>
       <c r="B17" s="1">
-        <v>634760175</v>
+        <v>634760204</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>302</v>
+        <v>289</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="H17" s="93">
-        <v>14.49</v>
+        <v>-100</v>
       </c>
       <c r="I17" s="93">
-        <v>14.48</v>
+        <v>-100</v>
       </c>
       <c r="J17" s="93">
-        <v>14.49</v>
+        <v>-100</v>
       </c>
       <c r="K17" s="93">
-        <v>14.484999999999999</v>
+        <v>-100</v>
       </c>
       <c r="L17" s="93">
-        <v>14.38</v>
+        <v>291.89999999999998</v>
       </c>
       <c r="M17" s="93">
-        <v>14.37</v>
-      </c>
-      <c r="N17" s="93">
-        <v>14.53</v>
-      </c>
-      <c r="O17" s="93">
-        <v>14.37</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N17" s="93"/>
+      <c r="O17" s="93"/>
       <c r="P17" s="93">
-        <v>4360</v>
+        <v>0</v>
       </c>
       <c r="Q17" s="93"/>
       <c r="R17" s="93"/>
@@ -6628,48 +6694,48 @@
       <c r="T17" s="93"/>
       <c r="U17" s="93"/>
       <c r="V17" s="92">
-        <v>46092.416759259257</v>
+        <v>46095.373206018521</v>
       </c>
       <c r="W17" s="1" t="s">
-        <v>277</v>
+        <v>264</v>
       </c>
     </row>
     <row r="18" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A18" s="1" t="s">
-        <v>187</v>
+        <v>290</v>
       </c>
       <c r="B18" s="1">
-        <v>634760204</v>
+        <v>707621000</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>303</v>
+        <v>290</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="H18" s="93">
-        <v>294.7</v>
+        <v>-1</v>
       </c>
       <c r="I18" s="93">
-        <v>-100</v>
+        <v>-1</v>
       </c>
       <c r="J18" s="93">
-        <v>-100</v>
+        <v>-1</v>
       </c>
       <c r="K18" s="93">
-        <v>-100</v>
+        <v>-1</v>
       </c>
       <c r="L18" s="93">
-        <v>295.8</v>
+        <v>3315</v>
       </c>
       <c r="M18" s="93">
         <v>0</v>
@@ -6685,48 +6751,48 @@
       <c r="T18" s="93"/>
       <c r="U18" s="93"/>
       <c r="V18" s="92">
-        <v>46092.416759259257</v>
+        <v>46095.373206018521</v>
       </c>
       <c r="W18" s="1" t="s">
-        <v>277</v>
+        <v>264</v>
       </c>
     </row>
     <row r="19" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A19" s="1" t="s">
-        <v>304</v>
+        <v>184</v>
       </c>
       <c r="B19" s="1">
-        <v>707621000</v>
+        <v>634760245</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>304</v>
+        <v>291</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="H19" s="93">
-        <v>-1</v>
+        <v>-100</v>
       </c>
       <c r="I19" s="93">
-        <v>-1</v>
+        <v>-100</v>
       </c>
       <c r="J19" s="93">
-        <v>-1</v>
+        <v>-100</v>
       </c>
       <c r="K19" s="93">
-        <v>-1</v>
+        <v>-100</v>
       </c>
       <c r="L19" s="93">
-        <v>3447</v>
+        <v>65.14</v>
       </c>
       <c r="M19" s="93">
         <v>0</v>
@@ -6742,60 +6808,60 @@
       <c r="T19" s="93"/>
       <c r="U19" s="93"/>
       <c r="V19" s="92">
-        <v>46092.416759259257</v>
+        <v>46095.373206018521</v>
       </c>
       <c r="W19" s="1" t="s">
-        <v>277</v>
+        <v>264</v>
       </c>
     </row>
     <row r="20" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A20" s="1" t="s">
-        <v>194</v>
+        <v>35</v>
       </c>
       <c r="B20" s="1">
-        <v>634760245</v>
+        <v>738739101</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>69</v>
+        <v>35</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>305</v>
+        <v>292</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="H20" s="93">
-        <v>65.349999999999994</v>
+        <v>230.85</v>
       </c>
       <c r="I20" s="93">
-        <v>65.34</v>
+        <v>-100</v>
       </c>
       <c r="J20" s="93">
-        <v>65.36</v>
+        <v>-100</v>
       </c>
       <c r="K20" s="93">
-        <v>65.349999999999994</v>
+        <v>-100</v>
       </c>
       <c r="L20" s="93">
-        <v>65.3</v>
+        <v>231.25</v>
       </c>
       <c r="M20" s="93">
-        <v>65.37</v>
+        <v>232</v>
       </c>
       <c r="N20" s="93">
-        <v>65.540000000000006</v>
+        <v>232.55</v>
       </c>
       <c r="O20" s="93">
-        <v>65.209999999999994</v>
+        <v>230.05</v>
       </c>
       <c r="P20" s="93">
-        <v>2415</v>
+        <v>26416</v>
       </c>
       <c r="Q20" s="93"/>
       <c r="R20" s="93"/>
@@ -6803,36 +6869,36 @@
       <c r="T20" s="93"/>
       <c r="U20" s="93"/>
       <c r="V20" s="92">
-        <v>46092.416759259257</v>
+        <v>46095.373206018521</v>
       </c>
       <c r="W20" s="1" t="s">
-        <v>277</v>
+        <v>264</v>
       </c>
     </row>
     <row r="21" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A21" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B21" s="1">
-        <v>738739101</v>
+        <v>786686904</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>306</v>
+        <v>293</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="H21" s="93">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I21" s="93">
         <v>-100</v>
@@ -6844,10 +6910,10 @@
         <v>-100</v>
       </c>
       <c r="L21" s="93">
-        <v>232.375</v>
+        <v>339.92500000000001</v>
       </c>
       <c r="M21" s="93">
-        <v>231.35</v>
+        <v>341.4</v>
       </c>
       <c r="N21" s="93"/>
       <c r="O21" s="93"/>
@@ -6860,36 +6926,36 @@
       <c r="T21" s="93"/>
       <c r="U21" s="93"/>
       <c r="V21" s="92">
-        <v>46092.416759259257</v>
+        <v>46095.373206018521</v>
       </c>
       <c r="W21" s="1" t="s">
-        <v>277</v>
+        <v>264</v>
       </c>
     </row>
     <row r="22" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A22" s="1" t="s">
-        <v>36</v>
+        <v>150</v>
       </c>
       <c r="B22" s="1">
-        <v>786686904</v>
+        <v>735014937</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>307</v>
+        <v>294</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="H22" s="93">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I22" s="93">
         <v>-100</v>
@@ -6901,10 +6967,10 @@
         <v>-100</v>
       </c>
       <c r="L22" s="93">
-        <v>346.4</v>
+        <v>94.35</v>
       </c>
       <c r="M22" s="93">
-        <v>344.67500000000001</v>
+        <v>94.724999999999994</v>
       </c>
       <c r="N22" s="93"/>
       <c r="O22" s="93"/>
@@ -6917,51 +6983,51 @@
       <c r="T22" s="93"/>
       <c r="U22" s="93"/>
       <c r="V22" s="92">
-        <v>46092.416759259257</v>
+        <v>46095.373206018521</v>
       </c>
       <c r="W22" s="1" t="s">
-        <v>277</v>
+        <v>264</v>
       </c>
     </row>
     <row r="23" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A23" s="1" t="s">
-        <v>156</v>
+        <v>259</v>
       </c>
       <c r="B23" s="1">
-        <v>735014937</v>
+        <v>792232100</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>308</v>
+        <v>274</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>83</v>
+        <v>64</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="H23" s="93">
+        <v>100.16</v>
+      </c>
+      <c r="I23" s="93">
+        <v>-1</v>
+      </c>
+      <c r="J23" s="93">
+        <v>-1</v>
+      </c>
+      <c r="K23" s="93">
+        <v>-1</v>
+      </c>
+      <c r="L23" s="93">
+        <v>99.504999999999995</v>
+      </c>
+      <c r="M23" s="93">
         <v>0</v>
-      </c>
-      <c r="I23" s="93">
-        <v>-100</v>
-      </c>
-      <c r="J23" s="93">
-        <v>-100</v>
-      </c>
-      <c r="K23" s="93">
-        <v>-100</v>
-      </c>
-      <c r="L23" s="93">
-        <v>96.075000000000003</v>
-      </c>
-      <c r="M23" s="93">
-        <v>95.6</v>
       </c>
       <c r="N23" s="93"/>
       <c r="O23" s="93"/>
@@ -6974,60 +7040,56 @@
       <c r="T23" s="93"/>
       <c r="U23" s="93"/>
       <c r="V23" s="92">
-        <v>46092.416759259257</v>
+        <v>46095.373206018521</v>
       </c>
       <c r="W23" s="1" t="s">
-        <v>277</v>
+        <v>264</v>
       </c>
     </row>
     <row r="24" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A24" s="1" t="s">
-        <v>272</v>
+        <v>254</v>
       </c>
       <c r="B24" s="1">
-        <v>792232100</v>
+        <v>496647057</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>288</v>
+        <v>275</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="H24" s="93">
-        <v>98.715000000000003</v>
+        <v>-1</v>
       </c>
       <c r="I24" s="93">
-        <v>98.71</v>
+        <v>-1</v>
       </c>
       <c r="J24" s="93">
-        <v>98.715000000000003</v>
+        <v>-1</v>
       </c>
       <c r="K24" s="93">
-        <v>98.712500000000006</v>
+        <v>-1</v>
       </c>
       <c r="L24" s="93">
-        <v>98.56</v>
+        <v>1.15635</v>
       </c>
       <c r="M24" s="93">
-        <v>98.68</v>
-      </c>
-      <c r="N24" s="93">
-        <v>98.715000000000003</v>
-      </c>
-      <c r="O24" s="93">
-        <v>98.435000000000002</v>
-      </c>
+        <v>1.1560999999999999</v>
+      </c>
+      <c r="N24" s="93"/>
+      <c r="O24" s="93"/>
       <c r="P24" s="93">
-        <v>1277</v>
+        <v>0</v>
       </c>
       <c r="Q24" s="93"/>
       <c r="R24" s="93"/>
@@ -7035,60 +7097,56 @@
       <c r="T24" s="93"/>
       <c r="U24" s="93"/>
       <c r="V24" s="92">
-        <v>46092.416759259257</v>
+        <v>46095.373206018521</v>
       </c>
       <c r="W24" s="1" t="s">
-        <v>277</v>
+        <v>264</v>
       </c>
     </row>
     <row r="25" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A25" s="1" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="B25" s="1">
-        <v>496647057</v>
+        <v>496647091</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D25" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="G25" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="E25" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="G25" s="1" t="s">
-        <v>62</v>
-      </c>
       <c r="H25" s="93">
-        <v>1.1657999999999999</v>
+        <v>-1</v>
       </c>
       <c r="I25" s="93">
-        <v>1.1657999999999999</v>
+        <v>-1</v>
       </c>
       <c r="J25" s="93">
-        <v>1.1658500000000001</v>
+        <v>-1</v>
       </c>
       <c r="K25" s="93">
-        <v>1.1658249999999999</v>
+        <v>-1</v>
       </c>
       <c r="L25" s="93">
-        <v>1.1677999999999999</v>
+        <v>1.3341000000000001</v>
       </c>
       <c r="M25" s="93">
-        <v>1.1667000000000001</v>
-      </c>
-      <c r="N25" s="93">
-        <v>1.1698500000000001</v>
-      </c>
-      <c r="O25" s="93">
-        <v>1.1656</v>
-      </c>
+        <v>1.3338000000000001</v>
+      </c>
+      <c r="N25" s="93"/>
+      <c r="O25" s="93"/>
       <c r="P25" s="93">
-        <v>29643</v>
+        <v>0</v>
       </c>
       <c r="Q25" s="93"/>
       <c r="R25" s="93"/>
@@ -7096,60 +7154,56 @@
       <c r="T25" s="93"/>
       <c r="U25" s="93"/>
       <c r="V25" s="92">
-        <v>46092.416759259257</v>
+        <v>46095.373206018521</v>
       </c>
       <c r="W25" s="1" t="s">
-        <v>277</v>
+        <v>264</v>
       </c>
     </row>
     <row r="26" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A26" s="1" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="B26" s="1">
-        <v>496647091</v>
+        <v>496647108</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>78</v>
+        <v>57</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>290</v>
+        <v>277</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="H26" s="93">
-        <v>1.3411</v>
+        <v>-1</v>
       </c>
       <c r="I26" s="93">
-        <v>1.341</v>
+        <v>-1</v>
       </c>
       <c r="J26" s="93">
-        <v>1.3411</v>
+        <v>-1</v>
       </c>
       <c r="K26" s="93">
-        <v>1.3410500000000001</v>
+        <v>-1</v>
       </c>
       <c r="L26" s="93">
-        <v>1.3429</v>
+        <v>6.3229999999999996E-3</v>
       </c>
       <c r="M26" s="93">
-        <v>1.3416999999999999</v>
-      </c>
-      <c r="N26" s="93">
-        <v>1.3456999999999999</v>
-      </c>
-      <c r="O26" s="93">
-        <v>1.3409</v>
-      </c>
+        <v>6.3210000000000002E-3</v>
+      </c>
+      <c r="N26" s="93"/>
+      <c r="O26" s="93"/>
       <c r="P26" s="93">
-        <v>11991</v>
+        <v>0</v>
       </c>
       <c r="Q26" s="93"/>
       <c r="R26" s="93"/>
@@ -7157,60 +7211,60 @@
       <c r="T26" s="93"/>
       <c r="U26" s="93"/>
       <c r="V26" s="92">
-        <v>46092.416759259257</v>
+        <v>46095.373206018521</v>
       </c>
       <c r="W26" s="1" t="s">
-        <v>277</v>
+        <v>264</v>
       </c>
     </row>
     <row r="27" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A27" s="1" t="s">
-        <v>269</v>
+        <v>257</v>
       </c>
       <c r="B27" s="1">
-        <v>496647108</v>
+        <v>496879111</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>291</v>
+        <v>278</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="H27" s="93">
-        <v>6.3635000000000002E-3</v>
+        <v>0.7319</v>
       </c>
       <c r="I27" s="93">
-        <v>6.3629999999999997E-3</v>
+        <v>-1</v>
       </c>
       <c r="J27" s="93">
-        <v>6.3635000000000002E-3</v>
+        <v>-1</v>
       </c>
       <c r="K27" s="93">
-        <v>6.36325E-3</v>
+        <v>-1</v>
       </c>
       <c r="L27" s="93">
-        <v>6.3860000000000002E-3</v>
+        <v>0.73709999999999998</v>
       </c>
       <c r="M27" s="93">
-        <v>6.3784999999999996E-3</v>
+        <v>0.73604999999999998</v>
       </c>
       <c r="N27" s="93">
-        <v>6.3860000000000002E-3</v>
+        <v>0.73709999999999998</v>
       </c>
       <c r="O27" s="93">
-        <v>6.3629999999999997E-3</v>
+        <v>0.73065000000000002</v>
       </c>
       <c r="P27" s="93">
-        <v>17592</v>
+        <v>162821</v>
       </c>
       <c r="Q27" s="93"/>
       <c r="R27" s="93"/>
@@ -7218,60 +7272,56 @@
       <c r="T27" s="93"/>
       <c r="U27" s="93"/>
       <c r="V27" s="92">
-        <v>46092.416759259257</v>
+        <v>46095.373206018521</v>
       </c>
       <c r="W27" s="1" t="s">
-        <v>277</v>
+        <v>264</v>
       </c>
     </row>
     <row r="28" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A28" s="1" t="s">
-        <v>270</v>
+        <v>258</v>
       </c>
       <c r="B28" s="1">
-        <v>496879111</v>
+        <v>496647009</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>292</v>
+        <v>279</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="H28" s="93">
-        <v>0.73995</v>
+        <v>-1</v>
       </c>
       <c r="I28" s="93">
-        <v>0.73995</v>
+        <v>-1</v>
       </c>
       <c r="J28" s="93">
-        <v>0.74004999999999999</v>
+        <v>-1</v>
       </c>
       <c r="K28" s="93">
-        <v>0.74</v>
+        <v>-1</v>
       </c>
       <c r="L28" s="93">
-        <v>0.73965000000000003</v>
+        <v>0.70720000000000005</v>
       </c>
       <c r="M28" s="93">
-        <v>0.73929999999999996</v>
-      </c>
-      <c r="N28" s="93">
-        <v>0.74080000000000001</v>
-      </c>
-      <c r="O28" s="93">
-        <v>0.73914999999999997</v>
-      </c>
+        <v>0.70684999999999998</v>
+      </c>
+      <c r="N28" s="93"/>
+      <c r="O28" s="93"/>
       <c r="P28" s="93">
-        <v>3036</v>
+        <v>0</v>
       </c>
       <c r="Q28" s="93"/>
       <c r="R28" s="93"/>
@@ -7279,60 +7329,56 @@
       <c r="T28" s="93"/>
       <c r="U28" s="93"/>
       <c r="V28" s="92">
-        <v>46092.416759259257</v>
+        <v>46095.373206018521</v>
       </c>
       <c r="W28" s="1" t="s">
-        <v>277</v>
+        <v>264</v>
       </c>
     </row>
     <row r="29" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A29" s="1" t="s">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="B29" s="1">
-        <v>496647009</v>
+        <v>815824224</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D29" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="F29" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="E29" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="F29" s="1" t="s">
-        <v>83</v>
-      </c>
       <c r="G29" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="H29" s="93">
-        <v>0.7147</v>
+        <v>-1</v>
       </c>
       <c r="I29" s="93">
-        <v>0.71465000000000001</v>
+        <v>-1</v>
       </c>
       <c r="J29" s="93">
-        <v>0.71475</v>
+        <v>-1</v>
       </c>
       <c r="K29" s="93">
-        <v>0.7147</v>
+        <v>-1</v>
       </c>
       <c r="L29" s="93">
-        <v>0.71260000000000001</v>
+        <v>114.15625</v>
       </c>
       <c r="M29" s="93">
-        <v>0.71109999999999995</v>
-      </c>
-      <c r="N29" s="93">
-        <v>0.71775</v>
-      </c>
-      <c r="O29" s="93">
-        <v>0.71060000000000001</v>
-      </c>
+        <v>114.125</v>
+      </c>
+      <c r="N29" s="93"/>
+      <c r="O29" s="93"/>
       <c r="P29" s="93">
-        <v>25663</v>
+        <v>0</v>
       </c>
       <c r="Q29" s="93"/>
       <c r="R29" s="93"/>
@@ -7340,60 +7386,56 @@
       <c r="T29" s="93"/>
       <c r="U29" s="93"/>
       <c r="V29" s="92">
-        <v>46092.416759259257</v>
+        <v>46095.373206018521</v>
       </c>
       <c r="W29" s="1" t="s">
-        <v>277</v>
+        <v>264</v>
       </c>
     </row>
     <row r="30" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A30" s="1" t="s">
-        <v>274</v>
+        <v>262</v>
       </c>
       <c r="B30" s="1">
-        <v>815824224</v>
+        <v>815824229</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>46</v>
+        <v>67</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="H30" s="93">
-        <v>115.59375</v>
+        <v>-1</v>
       </c>
       <c r="I30" s="93">
-        <v>115.59375</v>
+        <v>-1</v>
       </c>
       <c r="J30" s="93">
-        <v>115.625</v>
+        <v>-1</v>
       </c>
       <c r="K30" s="93">
-        <v>115.609375</v>
+        <v>-1</v>
       </c>
       <c r="L30" s="93">
-        <v>116.09375</v>
+        <v>111.40625</v>
       </c>
       <c r="M30" s="93">
-        <v>115.71875</v>
-      </c>
-      <c r="N30" s="93">
-        <v>116.03125</v>
-      </c>
-      <c r="O30" s="93">
-        <v>115.5625</v>
-      </c>
+        <v>111.5</v>
+      </c>
+      <c r="N30" s="93"/>
+      <c r="O30" s="93"/>
       <c r="P30" s="93">
-        <v>42491</v>
+        <v>0</v>
       </c>
       <c r="Q30" s="93"/>
       <c r="R30" s="93"/>
@@ -7401,60 +7443,54 @@
       <c r="T30" s="93"/>
       <c r="U30" s="93"/>
       <c r="V30" s="92">
-        <v>46092.416759259257</v>
+        <v>46095.373206018521</v>
       </c>
       <c r="W30" s="1" t="s">
-        <v>277</v>
+        <v>264</v>
       </c>
     </row>
     <row r="31" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A31" s="1" t="s">
-        <v>275</v>
+        <v>246</v>
       </c>
       <c r="B31" s="1">
-        <v>815824229</v>
+        <v>813041669</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>309</v>
+        <v>297</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="H31" s="93">
-        <v>112.28125</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="H31" s="93"/>
       <c r="I31" s="93">
-        <v>112.265625</v>
+        <v>-1</v>
       </c>
       <c r="J31" s="93">
-        <v>112.28125</v>
+        <v>-1</v>
       </c>
       <c r="K31" s="93">
-        <v>112.2734375</v>
+        <v>-1</v>
       </c>
       <c r="L31" s="93">
-        <v>112.453125</v>
+        <v>126.16</v>
       </c>
       <c r="M31" s="93">
-        <v>112.28125</v>
-      </c>
-      <c r="N31" s="93">
-        <v>112.4375</v>
-      </c>
-      <c r="O31" s="93">
-        <v>112.234375</v>
-      </c>
+        <v>125.94</v>
+      </c>
+      <c r="N31" s="93"/>
+      <c r="O31" s="93"/>
       <c r="P31" s="93">
-        <v>272433</v>
+        <v>0</v>
       </c>
       <c r="Q31" s="93"/>
       <c r="R31" s="93"/>
@@ -7462,60 +7498,54 @@
       <c r="T31" s="93"/>
       <c r="U31" s="93"/>
       <c r="V31" s="92">
-        <v>46092.416759259257</v>
+        <v>46095.373206018521</v>
       </c>
       <c r="W31" s="1" t="s">
-        <v>277</v>
+        <v>264</v>
       </c>
     </row>
     <row r="32" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A32" s="1" t="s">
-        <v>259</v>
+        <v>247</v>
       </c>
       <c r="B32" s="1">
-        <v>813041669</v>
+        <v>813041681</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>311</v>
+        <v>281</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="H32" s="93">
-        <v>126.67</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="H32" s="93"/>
       <c r="I32" s="93">
-        <v>126.67</v>
+        <v>-1</v>
       </c>
       <c r="J32" s="93">
-        <v>126.68</v>
+        <v>-1</v>
       </c>
       <c r="K32" s="93">
-        <v>126.67500000000001</v>
+        <v>-1</v>
       </c>
       <c r="L32" s="93">
-        <v>127.25</v>
+        <v>109.2</v>
       </c>
       <c r="M32" s="93">
-        <v>127.12</v>
-      </c>
-      <c r="N32" s="93">
-        <v>127.2</v>
-      </c>
-      <c r="O32" s="93">
-        <v>126.66</v>
-      </c>
+        <v>108.74</v>
+      </c>
+      <c r="N32" s="93"/>
+      <c r="O32" s="93"/>
       <c r="P32" s="93">
-        <v>293889</v>
+        <v>0</v>
       </c>
       <c r="Q32" s="93"/>
       <c r="R32" s="93"/>
@@ -7523,60 +7553,52 @@
       <c r="T32" s="93"/>
       <c r="U32" s="93"/>
       <c r="V32" s="92">
-        <v>46092.416759259257</v>
+        <v>46095.373206018521</v>
       </c>
       <c r="W32" s="1" t="s">
-        <v>277</v>
+        <v>264</v>
       </c>
     </row>
     <row r="33" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A33" s="1" t="s">
-        <v>260</v>
+        <v>248</v>
       </c>
       <c r="B33" s="1">
-        <v>813041681</v>
+        <v>813041663</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>295</v>
+        <v>282</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="H33" s="93">
-        <v>109.92</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="H33" s="93"/>
       <c r="I33" s="93">
-        <v>109.92</v>
+        <v>-1</v>
       </c>
       <c r="J33" s="93">
-        <v>109.94</v>
+        <v>-1</v>
       </c>
       <c r="K33" s="93">
-        <v>109.93</v>
+        <v>-1</v>
       </c>
       <c r="L33" s="93">
-        <v>110.76</v>
-      </c>
-      <c r="M33" s="93">
-        <v>110.52</v>
-      </c>
-      <c r="N33" s="93">
-        <v>110.72</v>
-      </c>
-      <c r="O33" s="93">
-        <v>109.88</v>
-      </c>
+        <v>117.8</v>
+      </c>
+      <c r="M33" s="93"/>
+      <c r="N33" s="93"/>
+      <c r="O33" s="93"/>
       <c r="P33" s="93">
-        <v>36217</v>
+        <v>0</v>
       </c>
       <c r="Q33" s="93"/>
       <c r="R33" s="93"/>
@@ -7584,60 +7606,58 @@
       <c r="T33" s="93"/>
       <c r="U33" s="93"/>
       <c r="V33" s="92">
-        <v>46092.416759259257</v>
+        <v>46095.373206018521</v>
       </c>
       <c r="W33" s="1" t="s">
-        <v>277</v>
+        <v>264</v>
       </c>
     </row>
     <row r="34" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A34" s="1" t="s">
-        <v>261</v>
+        <v>298</v>
       </c>
       <c r="B34" s="1">
-        <v>813041663</v>
+        <v>479624278</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>61</v>
+        <v>187</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>296</v>
+        <v>283</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>84</v>
+        <v>191</v>
       </c>
       <c r="G34" s="1" t="s">
         <v>59</v>
       </c>
       <c r="H34" s="93">
-        <v>118.89</v>
+        <v>70599</v>
       </c>
       <c r="I34" s="93">
-        <v>118.89</v>
+        <v>70598.75</v>
       </c>
       <c r="J34" s="93">
-        <v>118.9</v>
+        <v>70599</v>
       </c>
       <c r="K34" s="93">
-        <v>118.89500000000001</v>
+        <v>70598.875</v>
       </c>
       <c r="L34" s="93">
-        <v>119.66</v>
-      </c>
-      <c r="M34" s="93">
-        <v>119.5</v>
-      </c>
+        <v>71166.25</v>
+      </c>
+      <c r="M34" s="93"/>
       <c r="N34" s="93">
-        <v>119.51</v>
+        <v>74370</v>
       </c>
       <c r="O34" s="93">
-        <v>118.87</v>
+        <v>69650</v>
       </c>
       <c r="P34" s="93">
-        <v>102070</v>
+        <v>111.98166509000001</v>
       </c>
       <c r="Q34" s="93"/>
       <c r="R34" s="93"/>
@@ -7645,58 +7665,58 @@
       <c r="T34" s="93"/>
       <c r="U34" s="93"/>
       <c r="V34" s="92">
-        <v>46092.416759259257</v>
+        <v>46095.373206018521</v>
       </c>
       <c r="W34" s="1" t="s">
-        <v>277</v>
+        <v>264</v>
       </c>
     </row>
     <row r="35" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A35" s="1" t="s">
-        <v>312</v>
+        <v>188</v>
       </c>
       <c r="B35" s="1">
-        <v>479624278</v>
+        <v>495759171</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>297</v>
+        <v>284</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="H35" s="93">
-        <v>69652.25</v>
+        <v>2078</v>
       </c>
       <c r="I35" s="93">
-        <v>69615</v>
+        <v>2078</v>
       </c>
       <c r="J35" s="93">
-        <v>69615.25</v>
+        <v>2078.0500000000002</v>
       </c>
       <c r="K35" s="93">
-        <v>69615.125</v>
+        <v>2078.0250000000001</v>
       </c>
       <c r="L35" s="93">
-        <v>70060.75</v>
+        <v>2102.25</v>
       </c>
       <c r="M35" s="93"/>
       <c r="N35" s="93">
-        <v>71739</v>
+        <v>2209.4499999999998</v>
       </c>
       <c r="O35" s="93">
-        <v>68388.5</v>
+        <v>2056.1</v>
       </c>
       <c r="P35" s="93">
-        <v>114.33914932</v>
+        <v>824.96082965999994</v>
       </c>
       <c r="Q35" s="93"/>
       <c r="R35" s="93"/>
@@ -7704,87 +7724,149 @@
       <c r="T35" s="93"/>
       <c r="U35" s="93"/>
       <c r="V35" s="92">
-        <v>46092.416759259257</v>
+        <v>46095.373206018521</v>
       </c>
       <c r="W35" s="1" t="s">
-        <v>277</v>
+        <v>264</v>
       </c>
     </row>
     <row r="36" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A36" s="1" t="s">
-        <v>198</v>
+        <v>317</v>
       </c>
       <c r="B36" s="1">
-        <v>495759171</v>
+        <v>297507399</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>197</v>
+        <v>320</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>298</v>
+        <v>321</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>201</v>
+        <v>60</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="H36" s="93">
-        <v>2023.05</v>
+        <v>4.3</v>
       </c>
       <c r="I36" s="93">
-        <v>2023.05</v>
+        <v>-1</v>
       </c>
       <c r="J36" s="93">
-        <v>2023.1</v>
+        <v>-1</v>
       </c>
       <c r="K36" s="93">
-        <v>2023.0749999999998</v>
+        <v>-1</v>
       </c>
       <c r="L36" s="93">
-        <v>2037.15</v>
+        <v>5.35</v>
       </c>
       <c r="M36" s="93"/>
       <c r="N36" s="93">
-        <v>2086.35</v>
+        <v>5.1100000000000003</v>
       </c>
       <c r="O36" s="93">
-        <v>1989.75</v>
+        <v>3.76</v>
       </c>
       <c r="P36" s="93">
-        <v>924.18638008000005</v>
-      </c>
-      <c r="Q36" s="93"/>
-      <c r="R36" s="93"/>
-      <c r="S36" s="93"/>
-      <c r="T36" s="93"/>
-      <c r="U36" s="93"/>
+        <v>1957</v>
+      </c>
+      <c r="Q36" s="93">
+        <v>0.79716026823882513</v>
+      </c>
+      <c r="R36" s="93">
+        <v>-0.21376024026296289</v>
+      </c>
+      <c r="S36" s="93">
+        <v>9.7170641044802848E-3</v>
+      </c>
+      <c r="T36" s="93">
+        <v>0.1050583423512963</v>
+      </c>
+      <c r="U36" s="93">
+        <v>-6.7162337566242236E-2</v>
+      </c>
       <c r="V36" s="92">
-        <v>46092.416759259257</v>
+        <v>46095.373206018521</v>
       </c>
       <c r="W36" s="1" t="s">
-        <v>277</v>
+        <v>264</v>
       </c>
     </row>
     <row r="37" spans="1:23" x14ac:dyDescent="0.4">
-      <c r="H37" s="93"/>
-      <c r="I37" s="93"/>
-      <c r="J37" s="93"/>
-      <c r="K37" s="93"/>
-      <c r="L37" s="93"/>
+      <c r="A37" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="B37" s="1">
+        <v>297509218</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="H37" s="93">
+        <v>0.5</v>
+      </c>
+      <c r="I37" s="93">
+        <v>-1</v>
+      </c>
+      <c r="J37" s="93">
+        <v>-1</v>
+      </c>
+      <c r="K37" s="93">
+        <v>-1</v>
+      </c>
+      <c r="L37" s="93">
+        <v>0.55000000000000004</v>
+      </c>
       <c r="M37" s="93"/>
-      <c r="N37" s="93"/>
-      <c r="O37" s="93"/>
-      <c r="P37" s="93"/>
-      <c r="Q37" s="93"/>
-      <c r="R37" s="93"/>
-      <c r="S37" s="93"/>
-      <c r="T37" s="93"/>
-      <c r="U37" s="93"/>
-      <c r="V37" s="92"/>
+      <c r="N37" s="93">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="O37" s="93">
+        <v>0.39</v>
+      </c>
+      <c r="P37" s="93">
+        <v>390</v>
+      </c>
+      <c r="Q37" s="93">
+        <v>0.78003273026450248</v>
+      </c>
+      <c r="R37" s="93">
+        <v>-3.7228576152962482E-2</v>
+      </c>
+      <c r="S37" s="93">
+        <v>2.7816999846245593E-3</v>
+      </c>
+      <c r="T37" s="93">
+        <v>3.0357650321152063E-2</v>
+      </c>
+      <c r="U37" s="93">
+        <v>-1.6835601338734796E-2</v>
+      </c>
+      <c r="V37" s="92">
+        <v>46095.373206018521</v>
+      </c>
+      <c r="W37" s="1" t="s">
+        <v>264</v>
+      </c>
     </row>
     <row r="38" spans="1:23" x14ac:dyDescent="0.4">
       <c r="H38" s="93"/>
@@ -7950,13 +8032,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1" s="86" t="s">
-        <v>231</v>
+        <v>220</v>
       </c>
       <c r="B1" s="86" t="s">
-        <v>248</v>
+        <v>237</v>
       </c>
       <c r="C1" s="86" t="s">
-        <v>247</v>
+        <v>236</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.4">
@@ -7964,10 +8046,10 @@
         <v>46086.543078703704</v>
       </c>
       <c r="B2" s="84" t="s">
-        <v>313</v>
+        <v>299</v>
       </c>
       <c r="C2" s="84" t="s">
-        <v>314</v>
+        <v>300</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.4">
@@ -7975,10 +8057,10 @@
         <v>46086.543090277781</v>
       </c>
       <c r="B3" s="84" t="s">
-        <v>313</v>
+        <v>299</v>
       </c>
       <c r="C3" s="84" t="s">
-        <v>315</v>
+        <v>301</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.4">
@@ -7986,10 +8068,10 @@
         <v>46086.54310185185</v>
       </c>
       <c r="B4" s="84" t="s">
-        <v>313</v>
+        <v>299</v>
       </c>
       <c r="C4" s="84" t="s">
-        <v>316</v>
+        <v>302</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.4">
@@ -7997,10 +8079,10 @@
         <v>46090.383530092593</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>313</v>
+        <v>299</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>314</v>
+        <v>300</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.4">
@@ -8008,10 +8090,10 @@
         <v>46090.38354166667</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>313</v>
+        <v>299</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>315</v>
+        <v>301</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.4">
@@ -8019,10 +8101,10 @@
         <v>46090.38354166667</v>
       </c>
       <c r="B7" s="81" t="s">
-        <v>313</v>
+        <v>299</v>
       </c>
       <c r="C7" s="81" t="s">
-        <v>316</v>
+        <v>302</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.4">
@@ -8030,10 +8112,10 @@
         <v>46090.869409722225</v>
       </c>
       <c r="B8" s="81" t="s">
-        <v>313</v>
+        <v>299</v>
       </c>
       <c r="C8" s="81" t="s">
-        <v>314</v>
+        <v>300</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.4">
@@ -8041,10 +8123,10 @@
         <v>46090.869409722225</v>
       </c>
       <c r="B9" s="81" t="s">
-        <v>313</v>
+        <v>299</v>
       </c>
       <c r="C9" s="81" t="s">
-        <v>315</v>
+        <v>301</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.4">
@@ -8052,10 +8134,10 @@
         <v>46090.869409722225</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>313</v>
+        <v>299</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>316</v>
+        <v>302</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.4">
@@ -8063,10 +8145,10 @@
         <v>46092.415810185186</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>313</v>
+        <v>299</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>314</v>
+        <v>300</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.4">
@@ -8074,10 +8156,10 @@
         <v>46092.415821759256</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>313</v>
+        <v>299</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>315</v>
+        <v>301</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.4">
@@ -8085,67 +8167,115 @@
         <v>46092.415821759256</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>313</v>
+        <v>299</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>316</v>
+        <v>302</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A14" s="85"/>
+      <c r="A14" s="85">
+        <v>46095.370937500003</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>300</v>
+      </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A15" s="85"/>
+      <c r="A15" s="85">
+        <v>46095.370949074073</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>301</v>
+      </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A16" s="85"/>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A17" s="85"/>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A18" s="85"/>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A19" s="85"/>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A16" s="85">
+        <v>46095.370949074073</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A17" s="85">
+        <v>46095.371539351851</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A18" s="85">
+        <v>46095.371539351851</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A19" s="85">
+        <v>46095.371539351851</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A20" s="85"/>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A21" s="85"/>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A22" s="85"/>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A23" s="85"/>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A24" s="85"/>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A25" s="85"/>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A26" s="85"/>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A27" s="85"/>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A28" s="85"/>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A29" s="85"/>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A30" s="85"/>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A31" s="85"/>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A32" s="85"/>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.4">
@@ -8190,27 +8320,27 @@
     <row r="2" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B2" s="56"/>
       <c r="C2" s="4" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E2" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B3" s="17" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="C3" s="17"/>
       <c r="D3" s="10"/>
@@ -8226,23 +8356,23 @@
     </row>
     <row r="4" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B4" s="17" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="C4" s="17"/>
       <c r="D4" s="10"/>
       <c r="E4" s="10"/>
       <c r="F4" s="10"/>
       <c r="G4" s="15">
-        <v>11636.31</v>
+        <v>12096</v>
       </c>
       <c r="H4" s="6">
         <f>-G4</f>
-        <v>-11636.31</v>
+        <v>-12096</v>
       </c>
     </row>
     <row r="5" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B5" s="17" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="C5" s="17"/>
       <c r="D5" s="10"/>
@@ -8253,7 +8383,7 @@
     </row>
     <row r="6" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B6" s="17" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="C6" s="17"/>
       <c r="D6" s="10"/>
@@ -8264,7 +8394,7 @@
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B7" s="17" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="C7" s="17"/>
       <c r="D7" s="10"/>
@@ -8275,7 +8405,7 @@
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B8" s="17" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="C8" s="96">
         <v>2.5000000000000001E-2</v>
@@ -8294,7 +8424,7 @@
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B9" s="17" t="s">
-        <v>192</v>
+        <v>182</v>
       </c>
       <c r="C9" s="62"/>
       <c r="D9" s="27"/>
@@ -8305,7 +8435,7 @@
     </row>
     <row r="10" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B10" s="17" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="C10" s="62"/>
       <c r="D10" s="27"/>
@@ -8316,7 +8446,7 @@
     </row>
     <row r="11" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B11" s="17" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="C11" s="62"/>
       <c r="D11" s="27"/>
@@ -8327,7 +8457,7 @@
     </row>
     <row r="12" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B12" s="52" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="C12" s="58"/>
       <c r="D12" s="54">
@@ -8350,7 +8480,7 @@
     </row>
     <row r="13" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B13" s="17" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="C13" s="17"/>
       <c r="D13" s="10"/>
@@ -8358,11 +8488,11 @@
       <c r="F13" s="10"/>
       <c r="G13" s="6">
         <f>SUM(G3:G12)</f>
-        <v>541.25999999990927</v>
+        <v>1000.9499999999098</v>
       </c>
       <c r="H13" s="6">
         <f>SUM(H3:H12)</f>
-        <v>35858.739999999954</v>
+        <v>35399.049999999952</v>
       </c>
     </row>
   </sheetData>
@@ -8415,46 +8545,46 @@
   <sheetData>
     <row r="2" spans="2:18" x14ac:dyDescent="0.4">
       <c r="B2" s="38" t="s">
+        <v>161</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="J2" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="C2" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>171</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="H2" s="4" t="s">
+      <c r="K2" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="M2" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="I2" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="K2" s="4" t="s">
+      <c r="N2" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="L2" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="M2" s="4" t="s">
-        <v>181</v>
-      </c>
-      <c r="N2" s="4" t="s">
-        <v>182</v>
-      </c>
       <c r="O2" s="4" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
     </row>
     <row r="3" spans="2:18" x14ac:dyDescent="0.4">
@@ -8544,11 +8674,11 @@
       <c r="H5" s="67"/>
       <c r="I5" s="70">
         <f>Blotter!C$4-SUM(NAV!I$4:I4)</f>
-        <v>7414.5906320099002</v>
+        <v>5514.2806320099007</v>
       </c>
       <c r="J5" s="70">
         <f t="shared" si="2"/>
-        <v>1007414.5906320099</v>
+        <v>1005514.2806320098</v>
       </c>
       <c r="K5" s="70">
         <f t="shared" si="3"/>
@@ -8556,19 +8686,19 @@
       </c>
       <c r="L5" s="71">
         <f t="shared" si="4"/>
-        <v>1007.4145906320099</v>
+        <v>1005.5142806320099</v>
       </c>
       <c r="M5" s="72">
         <f t="shared" si="5"/>
-        <v>7.4145906320099986E-3</v>
+        <v>5.5142806320098714E-3</v>
       </c>
       <c r="N5" s="73">
         <f t="shared" ref="N5" si="6">L5/L4-1</f>
-        <v>7.4145906320099986E-3</v>
+        <v>5.5142806320098714E-3</v>
       </c>
       <c r="O5" s="75">
         <f>STDEVP(N$4:N5)*SQRT(12)</f>
-        <v>1.2842447691965549E-2</v>
+        <v>9.5510142218341171E-3</v>
       </c>
     </row>
     <row r="6" spans="2:18" ht="14.25" x14ac:dyDescent="0.4">
@@ -8838,49 +8968,49 @@
         <v>0</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E2" s="7" t="s">
         <v>3</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="G2" s="8" t="s">
         <v>7</v>
       </c>
       <c r="H2" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="I2" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="J2" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="K2" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="L2" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="M2" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="N2" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="O2" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="P2" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="I2" s="8" t="s">
-        <v>164</v>
-      </c>
-      <c r="J2" s="8" t="s">
-        <v>161</v>
-      </c>
-      <c r="K2" s="8" t="s">
-        <v>165</v>
-      </c>
-      <c r="L2" s="8" t="s">
-        <v>166</v>
-      </c>
-      <c r="M2" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="N2" s="8" t="s">
-        <v>164</v>
-      </c>
-      <c r="O2" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="P2" s="4" t="s">
-        <v>167</v>
-      </c>
       <c r="Q2" s="4" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="R2" s="4" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="T2" s="38" t="s">
         <v>8</v>
@@ -8892,20 +9022,20 @@
         <v>2</v>
       </c>
       <c r="W2" s="38" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="X2" s="38" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="Y2" s="12"/>
       <c r="Z2" s="38" t="s">
         <v>2</v>
       </c>
       <c r="AA2" s="38" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="AB2" s="38" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
     </row>
     <row r="3" spans="2:28" x14ac:dyDescent="0.4">
@@ -9028,13 +9158,13 @@
         <v>1</v>
       </c>
       <c r="V4" s="1" t="s">
-        <v>202</v>
+        <v>323</v>
       </c>
       <c r="W4" s="1" t="s">
-        <v>325</v>
+        <v>310</v>
       </c>
       <c r="X4" s="1" t="s">
-        <v>326</v>
+        <v>311</v>
       </c>
     </row>
     <row r="5" spans="2:28" x14ac:dyDescent="0.4">
@@ -9048,7 +9178,7 @@
       </c>
       <c r="D5" s="6">
         <f t="array" ref="D5">SUM((Blotter!C$19:C$1013=C5)*(Blotter!N$19:N$1013)*1)</f>
-        <v>6351.0899999999965</v>
+        <v>2391.0899999999965</v>
       </c>
       <c r="E5" s="6">
         <f t="array" ref="E5">SUM((Blotter!B$19:C$1013=C5)*(Blotter!R$19:R$1013)*1)</f>
@@ -9056,7 +9186,7 @@
       </c>
       <c r="F5" s="30">
         <f t="shared" ref="F5" si="1">IF(ISNUMBER(D5/E5),D5/E5,0)</f>
-        <v>0.70567666666666629</v>
+        <v>0.26567666666666628</v>
       </c>
       <c r="G5" s="36" t="str">
         <f t="array" ref="G5">IF(SUM((Blotter!C$19:C$1013=PLB!C5)*(Blotter!M$19:M$1013))=0,"C","O")</f>
@@ -9064,20 +9194,20 @@
       </c>
       <c r="H5" s="16">
         <f>J4+D5</f>
-        <v>1006873.33063201</v>
+        <v>1002913.33063201</v>
       </c>
       <c r="I5" s="16"/>
       <c r="J5" s="16">
         <f>H5+I5</f>
-        <v>1006873.33063201</v>
+        <v>1002913.33063201</v>
       </c>
       <c r="K5" s="3">
         <f>H5/J4-1</f>
-        <v>6.3477749340066225E-3</v>
+        <v>2.3898419274412941E-3</v>
       </c>
       <c r="L5" s="3">
         <f>(1+K5)*(1+L4)-1</f>
-        <v>6.8733306320101217E-3</v>
+        <v>2.9133306320099361E-3</v>
       </c>
       <c r="M5" s="6">
         <f>O4-IF(G5="O",O4*1%,-D5)</f>
@@ -9112,35 +9242,92 @@
         <v>2</v>
       </c>
       <c r="V5" s="1" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="W5" s="1" t="s">
-        <v>327</v>
+        <v>312</v>
       </c>
       <c r="X5" s="1" t="s">
-        <v>328</v>
+        <v>313</v>
       </c>
     </row>
     <row r="6" spans="2:28" x14ac:dyDescent="0.4">
-      <c r="B6" s="40"/>
-      <c r="C6" s="5"/>
-      <c r="D6" s="6"/>
-      <c r="E6" s="6"/>
-      <c r="F6" s="30"/>
-      <c r="G6" s="36"/>
-      <c r="H6" s="16"/>
+      <c r="B6" s="40">
+        <f>B5+7</f>
+        <v>46102</v>
+      </c>
+      <c r="C6" s="5">
+        <f>C5+1</f>
+        <v>3</v>
+      </c>
+      <c r="D6" s="6">
+        <f t="array" ref="D6">SUM((Blotter!C$19:C$1013=C6)*(Blotter!N$19:N$1013)*1)</f>
+        <v>1600</v>
+      </c>
+      <c r="E6" s="6">
+        <f t="array" ref="E6">SUM((Blotter!B$19:C$1013=C6)*(Blotter!R$19:R$1013)*1)</f>
+        <v>8233.3333333333321</v>
+      </c>
+      <c r="F6" s="30">
+        <f t="shared" ref="F6" si="4">IF(ISNUMBER(D6/E6),D6/E6,0)</f>
+        <v>0.19433198380566805</v>
+      </c>
+      <c r="G6" s="36" t="str">
+        <f t="array" ref="G6">IF(SUM((Blotter!C$19:C$1013=PLB!C6)*(Blotter!M$19:M$1013))=0,"C","O")</f>
+        <v>O</v>
+      </c>
+      <c r="H6" s="16">
+        <f>J5+D6</f>
+        <v>1004513.33063201</v>
+      </c>
       <c r="I6" s="16"/>
-      <c r="J6" s="16"/>
-      <c r="K6" s="3"/>
-      <c r="L6" s="3"/>
-      <c r="M6" s="6"/>
-      <c r="N6" s="16"/>
-      <c r="O6" s="6"/>
-      <c r="P6" s="3"/>
-      <c r="Q6" s="3"/>
-      <c r="R6" s="3"/>
-      <c r="T6" s="40"/>
-      <c r="U6" s="5"/>
+      <c r="J6" s="16">
+        <f>H6+I6</f>
+        <v>1004513.33063201</v>
+      </c>
+      <c r="K6" s="3">
+        <f>H6/J5-1</f>
+        <v>1.5953522115332852E-3</v>
+      </c>
+      <c r="L6" s="3">
+        <f>(1+K6)*(1+L5)-1</f>
+        <v>4.513330632009982E-3</v>
+      </c>
+      <c r="M6" s="6">
+        <f>O5-IF(G6="O",O5*1%,-D6)</f>
+        <v>980611.84804343304</v>
+      </c>
+      <c r="N6" s="16">
+        <f>I6</f>
+        <v>0</v>
+      </c>
+      <c r="O6" s="6">
+        <f>M6+N6</f>
+        <v>980611.84804343304</v>
+      </c>
+      <c r="P6" s="3">
+        <f>M6/O5-1</f>
+        <v>-9.9999999999998979E-3</v>
+      </c>
+      <c r="Q6" s="3">
+        <f>(1+P6)*(1+Q5)-1</f>
+        <v>-1.9388151956566846E-2</v>
+      </c>
+      <c r="R6" s="3">
+        <f>(1-1%)*(1+R5)-1</f>
+        <v>-2.9701000000000088E-2</v>
+      </c>
+      <c r="T6" s="40">
+        <f t="shared" ref="T6" si="5">B6</f>
+        <v>46102</v>
+      </c>
+      <c r="U6" s="5">
+        <f t="shared" ref="U6" si="6">C6</f>
+        <v>3</v>
+      </c>
+      <c r="V6" s="1" t="s">
+        <v>325</v>
+      </c>
       <c r="W6" s="49"/>
     </row>
     <row r="7" spans="2:28" x14ac:dyDescent="0.4">
@@ -10317,7 +10504,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{479B0B21-091C-4007-AD49-B9DC477FBC57}">
-  <dimension ref="B2:R43"/>
+  <dimension ref="B2:R34"/>
   <sheetFormatPr defaultRowHeight="13.15" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="5.6640625" style="1" customWidth="1"/>
@@ -10348,22 +10535,22 @@
         <v>16</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="H2" s="4" t="s">
         <v>18</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>188</v>
+        <v>178</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="N2" s="4" t="s">
         <v>19</v>
@@ -10404,7 +10591,7 @@
         <v>0.01</v>
       </c>
       <c r="H3" s="23">
-        <f t="shared" ref="H3:H36" si="0">(F3*G3)/(C3*D3*E3)</f>
+        <f t="shared" ref="H3:H33" si="0">(F3*G3)/(C3*D3*E3)</f>
         <v>1.5873015873015872</v>
       </c>
       <c r="I3" s="61">
@@ -10442,15 +10629,15 @@
         <v>50.57</v>
       </c>
       <c r="E4" s="20">
-        <f t="shared" ref="E4:E43" si="1">$Q$3</f>
+        <f t="shared" ref="E4:E34" si="1">$Q$3</f>
         <v>1.5</v>
       </c>
       <c r="F4" s="21">
-        <f t="shared" ref="F4:F43" si="2">$P$3</f>
+        <f t="shared" ref="F4:F34" si="2">$P$3</f>
         <v>1000000</v>
       </c>
       <c r="G4" s="22">
-        <f t="shared" ref="G4:G43" si="3">$R$3</f>
+        <f t="shared" ref="G4:G34" si="3">$R$3</f>
         <v>0.01</v>
       </c>
       <c r="H4" s="23">
@@ -10458,7 +10645,7 @@
         <v>2.6366093204139478</v>
       </c>
       <c r="I4" s="61">
-        <f t="shared" ref="I4:I43" si="4">ROUND(H4*1.33,0)</f>
+        <f t="shared" ref="I4:I34" si="4">ROUND(H4*1.33,0)</f>
         <v>4</v>
       </c>
       <c r="J4" s="18">
@@ -10557,7 +10744,7 @@
         <v>1000</v>
       </c>
       <c r="D7" s="19">
-        <v>2.41</v>
+        <v>2.1</v>
       </c>
       <c r="E7" s="20">
         <f t="shared" si="1"/>
@@ -10573,22 +10760,22 @@
       </c>
       <c r="H7" s="23">
         <f t="shared" si="0"/>
-        <v>2.7662517289073305</v>
+        <v>3.1746031746031744</v>
       </c>
       <c r="I7" s="61">
         <f t="shared" si="4"/>
         <v>4</v>
       </c>
       <c r="J7" s="18">
-        <v>82</v>
+        <v>99</v>
       </c>
       <c r="K7" s="3">
         <f>J7*H7*C7/$N$3</f>
-        <v>0.22683264177040111</v>
+        <v>0.31428571428571428</v>
       </c>
       <c r="L7" s="3">
         <f>J7*I7*C7/$N$3</f>
-        <v>0.32800000000000001</v>
+        <v>0.39600000000000002</v>
       </c>
     </row>
     <row r="8" spans="2:18" x14ac:dyDescent="0.4">
@@ -11050,7 +11237,7 @@
     </row>
     <row r="20" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B20" s="17" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C20" s="18">
         <v>500</v>
@@ -11534,14 +11721,14 @@
       <c r="L33" s="61"/>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.4">
-      <c r="B34" s="17" t="s">
-        <v>48</v>
+      <c r="B34" s="9" t="s">
+        <v>190</v>
       </c>
       <c r="C34" s="18">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="D34" s="19">
-        <v>4.1500000000000004</v>
+        <v>140</v>
       </c>
       <c r="E34" s="20">
         <f t="shared" si="1"/>
@@ -11556,336 +11743,22 @@
         <v>0.01</v>
       </c>
       <c r="H34" s="23">
-        <f t="shared" si="0"/>
-        <v>16.064257028112447</v>
+        <f t="shared" ref="H34" si="6">(F34*G34)/(C34*D34*E34)</f>
+        <v>47.61904761904762</v>
       </c>
       <c r="I34" s="61">
         <f t="shared" si="4"/>
-        <v>21</v>
-      </c>
-      <c r="J34" s="61"/>
-      <c r="K34" s="61"/>
-      <c r="L34" s="61"/>
-    </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.4">
-      <c r="B35" s="17" t="s">
-        <v>49</v>
-      </c>
-      <c r="C35" s="18">
-        <v>100</v>
-      </c>
-      <c r="D35" s="19">
-        <v>9.2899999999999991</v>
-      </c>
-      <c r="E35" s="20">
-        <f t="shared" si="1"/>
-        <v>1.5</v>
-      </c>
-      <c r="F35" s="21">
-        <f t="shared" si="2"/>
-        <v>1000000</v>
-      </c>
-      <c r="G35" s="22">
-        <f t="shared" si="3"/>
-        <v>0.01</v>
-      </c>
-      <c r="H35" s="23">
-        <f t="shared" si="0"/>
-        <v>7.1761750986724087</v>
-      </c>
-      <c r="I35" s="61">
-        <f t="shared" si="4"/>
-        <v>10</v>
-      </c>
-      <c r="J35" s="61"/>
-      <c r="K35" s="61"/>
-      <c r="L35" s="61"/>
-    </row>
-    <row r="36" spans="2:12" x14ac:dyDescent="0.4">
-      <c r="B36" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="C36" s="18">
-        <v>100</v>
-      </c>
-      <c r="D36" s="19">
-        <v>3.34</v>
-      </c>
-      <c r="E36" s="20">
-        <f t="shared" si="1"/>
-        <v>1.5</v>
-      </c>
-      <c r="F36" s="21">
-        <f t="shared" si="2"/>
-        <v>1000000</v>
-      </c>
-      <c r="G36" s="22">
-        <f t="shared" si="3"/>
-        <v>0.01</v>
-      </c>
-      <c r="H36" s="23">
-        <f t="shared" si="0"/>
-        <v>19.960079840319363</v>
-      </c>
-      <c r="I36" s="61">
-        <f t="shared" si="4"/>
-        <v>27</v>
-      </c>
-      <c r="J36" s="61"/>
-      <c r="K36" s="61"/>
-      <c r="L36" s="61"/>
-    </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.4">
-      <c r="B37" s="17" t="s">
-        <v>126</v>
-      </c>
-      <c r="C37" s="18">
-        <v>100</v>
-      </c>
-      <c r="D37" s="19">
-        <v>0.3075</v>
-      </c>
-      <c r="E37" s="20">
-        <f t="shared" si="1"/>
-        <v>1.5</v>
-      </c>
-      <c r="F37" s="21">
-        <f t="shared" si="2"/>
-        <v>1000000</v>
-      </c>
-      <c r="G37" s="22">
-        <f t="shared" si="3"/>
-        <v>0.01</v>
-      </c>
-      <c r="H37" s="23">
-        <f t="shared" ref="H37" si="6">(F37*G37)/(C37*D37*E37)</f>
-        <v>216.80216802168022</v>
-      </c>
-      <c r="I37" s="61">
-        <f t="shared" si="4"/>
-        <v>288</v>
-      </c>
-      <c r="J37" s="61"/>
-      <c r="K37" s="61"/>
-      <c r="L37" s="61"/>
-    </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.4">
-      <c r="B38" s="17" t="s">
-        <v>155</v>
-      </c>
-      <c r="C38" s="18">
-        <v>100</v>
-      </c>
-      <c r="D38" s="19">
-        <v>0.85</v>
-      </c>
-      <c r="E38" s="20">
-        <f t="shared" si="1"/>
-        <v>1.5</v>
-      </c>
-      <c r="F38" s="21">
-        <f t="shared" si="2"/>
-        <v>1000000</v>
-      </c>
-      <c r="G38" s="22">
-        <f t="shared" si="3"/>
-        <v>0.01</v>
-      </c>
-      <c r="H38" s="23">
-        <f t="shared" ref="H38" si="7">(F38*G38)/(C38*D38*E38)</f>
-        <v>78.431372549019613</v>
-      </c>
-      <c r="I38" s="61">
-        <f t="shared" si="4"/>
-        <v>104</v>
-      </c>
-      <c r="J38" s="61"/>
-      <c r="K38" s="61"/>
-      <c r="L38" s="61"/>
-    </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.4">
-      <c r="B39" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="C39" s="18">
-        <v>100</v>
-      </c>
-      <c r="D39" s="19">
-        <v>1.06</v>
-      </c>
-      <c r="E39" s="20">
-        <f t="shared" si="1"/>
-        <v>1.5</v>
-      </c>
-      <c r="F39" s="21">
-        <f t="shared" si="2"/>
-        <v>1000000</v>
-      </c>
-      <c r="G39" s="22">
-        <f t="shared" si="3"/>
-        <v>0.01</v>
-      </c>
-      <c r="H39" s="23">
-        <f t="shared" ref="H39" si="8">(F39*G39)/(C39*D39*E39)</f>
-        <v>62.893081761006286</v>
-      </c>
-      <c r="I39" s="61">
-        <f t="shared" si="4"/>
-        <v>84</v>
-      </c>
-      <c r="J39" s="61"/>
-      <c r="K39" s="61"/>
-      <c r="L39" s="61"/>
-    </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.4">
-      <c r="B40" s="17" t="s">
-        <v>168</v>
-      </c>
-      <c r="C40" s="18">
-        <v>1</v>
-      </c>
-      <c r="D40" s="19">
-        <v>1.06</v>
-      </c>
-      <c r="E40" s="20">
-        <f t="shared" si="1"/>
-        <v>1.5</v>
-      </c>
-      <c r="F40" s="21">
-        <f t="shared" si="2"/>
-        <v>1000000</v>
-      </c>
-      <c r="G40" s="22">
-        <f t="shared" si="3"/>
-        <v>0.01</v>
-      </c>
-      <c r="H40" s="23">
-        <f t="shared" ref="H40" si="9">(F40*G40)/(C40*D40*E40)</f>
-        <v>6289.3081761006288</v>
-      </c>
-      <c r="I40" s="61">
-        <f t="shared" si="4"/>
-        <v>8365</v>
-      </c>
-      <c r="J40" s="61"/>
-      <c r="K40" s="61"/>
-      <c r="L40" s="61"/>
-    </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.4">
-      <c r="B41" s="17" t="s">
-        <v>183</v>
-      </c>
-      <c r="C41" s="18">
-        <v>1</v>
-      </c>
-      <c r="D41" s="19">
-        <v>7.23</v>
-      </c>
-      <c r="E41" s="20">
-        <f t="shared" si="1"/>
-        <v>1.5</v>
-      </c>
-      <c r="F41" s="21">
-        <f t="shared" si="2"/>
-        <v>1000000</v>
-      </c>
-      <c r="G41" s="22">
-        <f t="shared" si="3"/>
-        <v>0.01</v>
-      </c>
-      <c r="H41" s="23">
-        <f t="shared" ref="H41" si="10">(F41*G41)/(C41*D41*E41)</f>
-        <v>922.08390963577676</v>
-      </c>
-      <c r="I41" s="61">
-        <f t="shared" si="4"/>
-        <v>1226</v>
-      </c>
-      <c r="J41" s="18">
-        <v>68</v>
-      </c>
-      <c r="K41" s="3">
-        <f>J41*H41*C41/$N$3</f>
-        <v>6.2701705855232825E-2</v>
-      </c>
-      <c r="L41" s="3">
-        <f>J41*I41*C41/$N$3</f>
-        <v>8.3367999999999998E-2</v>
-      </c>
-    </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.4">
-      <c r="B42" s="17" t="s">
-        <v>185</v>
-      </c>
-      <c r="C42" s="18">
-        <v>1</v>
-      </c>
-      <c r="D42" s="19">
-        <v>2.0299999999999998</v>
-      </c>
-      <c r="E42" s="20">
-        <f t="shared" si="1"/>
-        <v>1.5</v>
-      </c>
-      <c r="F42" s="21">
-        <f t="shared" si="2"/>
-        <v>1000000</v>
-      </c>
-      <c r="G42" s="22">
-        <f t="shared" si="3"/>
-        <v>0.01</v>
-      </c>
-      <c r="H42" s="23">
-        <f t="shared" ref="H42" si="11">(F42*G42)/(C42*D42*E42)</f>
-        <v>3284.0722495894911</v>
-      </c>
-      <c r="I42" s="61">
-        <f t="shared" si="4"/>
-        <v>4368</v>
-      </c>
-      <c r="J42" s="61"/>
-      <c r="K42" s="61"/>
-      <c r="L42" s="61"/>
-    </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.4">
-      <c r="B43" s="9" t="s">
-        <v>200</v>
-      </c>
-      <c r="C43" s="18">
-        <v>1</v>
-      </c>
-      <c r="D43" s="19">
-        <v>140</v>
-      </c>
-      <c r="E43" s="20">
-        <f t="shared" si="1"/>
-        <v>1.5</v>
-      </c>
-      <c r="F43" s="21">
-        <f t="shared" si="2"/>
-        <v>1000000</v>
-      </c>
-      <c r="G43" s="22">
-        <f t="shared" si="3"/>
-        <v>0.01</v>
-      </c>
-      <c r="H43" s="23">
-        <f t="shared" ref="H43" si="12">(F43*G43)/(C43*D43*E43)</f>
-        <v>47.61904761904762</v>
-      </c>
-      <c r="I43" s="61">
-        <f t="shared" si="4"/>
         <v>63</v>
       </c>
-      <c r="J43" s="18">
+      <c r="J34" s="18">
         <v>1986</v>
       </c>
-      <c r="K43" s="3">
-        <f>J43*H43*C43/$N$3</f>
+      <c r="K34" s="3">
+        <f>J34*H34*C34/$N$3</f>
         <v>9.4571428571428584E-2</v>
       </c>
-      <c r="L43" s="3">
-        <f>J43*I43*C43/$N$3</f>
+      <c r="L34" s="3">
+        <f>J34*I34*C34/$N$3</f>
         <v>0.12511800000000001</v>
       </c>
     </row>
@@ -11926,96 +11799,96 @@
   <sheetData>
     <row r="1" spans="1:31" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="H1" s="2" t="s">
         <v>13</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="J1" s="48" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="L1" s="48" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="N1" s="2" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="O1" s="2" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="P1" s="2" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="Q1" s="2" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="R1" s="2" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="T1" s="2" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="U1" s="2" t="s">
         <v>12</v>
       </c>
       <c r="V1" s="2" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="W1" s="2" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="X1" s="2" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>320</v>
+        <v>305</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>304</v>
+        <v>290</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>321</v>
+        <v>306</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>34</v>
@@ -12030,7 +11903,7 @@
         <v>46090</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="N2" s="1">
         <v>1</v>
@@ -12045,7 +11918,7 @@
         <v>-2.97</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="T2" s="43">
         <f>IF(ISNUMBER(VLOOKUP(U2,Blotter!B:C,2,0)),VLOOKUP(U2,Blotter!B:C,2,0),"")</f>
@@ -12068,7 +11941,7 @@
         <v>-2.97</v>
       </c>
       <c r="Z2" s="1" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="AC2" s="44"/>
       <c r="AD2" s="45"/>
@@ -12076,22 +11949,22 @@
     </row>
     <row r="3" spans="1:31" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
-        <v>320</v>
+        <v>305</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>304</v>
+        <v>290</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>321</v>
+        <v>306</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>34</v>
@@ -12106,7 +11979,7 @@
         <v>46090</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="N3" s="1">
         <v>2</v>
@@ -12121,7 +11994,7 @@
         <v>-5.94</v>
       </c>
       <c r="R3" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="T3" s="43">
         <f>IF(ISNUMBER(VLOOKUP(U3,Blotter!B:C,2,0)),VLOOKUP(U3,Blotter!B:C,2,0),"")</f>
@@ -12149,22 +12022,22 @@
     </row>
     <row r="4" spans="1:31" x14ac:dyDescent="0.4">
       <c r="A4" s="1" t="s">
-        <v>320</v>
+        <v>305</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>322</v>
+        <v>307</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>323</v>
+        <v>308</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>323</v>
+        <v>308</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>324</v>
+        <v>309</v>
       </c>
       <c r="H4" s="1">
         <v>1</v>
@@ -12173,7 +12046,7 @@
         <v>46090</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="N4" s="1">
         <v>1000000</v>
@@ -12188,7 +12061,7 @@
         <v>-20</v>
       </c>
       <c r="R4" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="T4" s="43" t="str">
         <f>IF(ISNUMBER(VLOOKUP(U4,Blotter!B:C,2,0)),VLOOKUP(U4,Blotter!B:C,2,0),"")</f>
@@ -12216,19 +12089,19 @@
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="H5" s="1">
         <v>1</v>
@@ -12237,7 +12110,7 @@
         <v>46084</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="N5" s="1">
         <f>6.1104122</f>
@@ -12253,7 +12126,7 @@
         <v>-21.810505307</v>
       </c>
       <c r="R5" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="T5" s="43">
         <f>IF(ISNUMBER(VLOOKUP(U5,Blotter!B:C,2,0)),VLOOKUP(U5,Blotter!B:C,2,0),"")</f>
@@ -12281,19 +12154,19 @@
     </row>
     <row r="6" spans="1:31" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="H6" s="1">
         <v>1</v>
@@ -12302,7 +12175,7 @@
         <v>46084</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="N6" s="1">
         <v>5.8970321700000001</v>
@@ -12317,7 +12190,7 @@
         <v>-21.049928092999998</v>
       </c>
       <c r="R6" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="T6" s="43">
         <f>IF(ISNUMBER(VLOOKUP(U6,Blotter!B:C,2,0)),VLOOKUP(U6,Blotter!B:C,2,0),"")</f>
@@ -12345,19 +12218,19 @@
     </row>
     <row r="7" spans="1:31" x14ac:dyDescent="0.4">
       <c r="A7" s="1" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="H7" s="1">
         <v>1</v>
@@ -12366,7 +12239,7 @@
         <v>46084</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="N7" s="1">
         <v>3.9942700000000003E-3</v>
@@ -12381,7 +12254,7 @@
         <v>-1.4257865999999999E-2</v>
       </c>
       <c r="R7" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="T7" s="43">
         <f>IF(ISNUMBER(VLOOKUP(U7,Blotter!B:C,2,0)),VLOOKUP(U7,Blotter!B:C,2,0),"")</f>
@@ -12409,19 +12282,19 @@
     </row>
     <row r="8" spans="1:31" x14ac:dyDescent="0.4">
       <c r="A8" s="1" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="H8" s="1">
         <v>1</v>
@@ -12430,7 +12303,7 @@
         <v>46084</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="N8" s="1">
         <v>0.54177474999999997</v>
@@ -12445,7 +12318,7 @@
         <v>-1.933908312</v>
       </c>
       <c r="R8" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="T8" s="43">
         <f>IF(ISNUMBER(VLOOKUP(U8,Blotter!B:C,2,0)),VLOOKUP(U8,Blotter!B:C,2,0),"")</f>
@@ -12473,19 +12346,19 @@
     </row>
     <row r="9" spans="1:31" x14ac:dyDescent="0.4">
       <c r="A9" s="1" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="H9" s="1">
         <v>1</v>
@@ -12494,7 +12367,7 @@
         <v>46084</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="N9" s="1">
         <v>1.5427200000000001</v>
@@ -12509,7 +12382,7 @@
         <v>-5.5068624579999996</v>
       </c>
       <c r="R9" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="T9" s="43">
         <f>IF(ISNUMBER(VLOOKUP(U9,Blotter!B:C,2,0)),VLOOKUP(U9,Blotter!B:C,2,0),"")</f>
@@ -12537,19 +12410,19 @@
     </row>
     <row r="10" spans="1:31" x14ac:dyDescent="0.4">
       <c r="A10" s="1" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="H10" s="1">
         <v>1</v>
@@ -12558,7 +12431,7 @@
         <v>46084</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="N10" s="1">
         <v>0.22177047999999999</v>
@@ -12573,7 +12446,7 @@
         <v>-0.79162747</v>
       </c>
       <c r="R10" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="T10" s="43">
         <f>IF(ISNUMBER(VLOOKUP(U10,Blotter!B:C,2,0)),VLOOKUP(U10,Blotter!B:C,2,0),"")</f>
@@ -12601,19 +12474,19 @@
     </row>
     <row r="11" spans="1:31" x14ac:dyDescent="0.4">
       <c r="A11" s="1" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="H11" s="1">
         <v>1</v>
@@ -12622,7 +12495,7 @@
         <v>46084</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="N11" s="1">
         <v>0.20808973</v>
@@ -12637,7 +12510,7 @@
         <v>-0.74279293800000001</v>
       </c>
       <c r="R11" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="T11" s="43">
         <f>IF(ISNUMBER(VLOOKUP(U11,Blotter!B:C,2,0)),VLOOKUP(U11,Blotter!B:C,2,0),"")</f>
@@ -12665,19 +12538,19 @@
     </row>
     <row r="12" spans="1:31" x14ac:dyDescent="0.4">
       <c r="A12" s="1" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="H12" s="1">
         <v>1</v>
@@ -12686,7 +12559,7 @@
         <v>46084</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="N12" s="1">
         <v>1.6103536000000001</v>
@@ -12701,7 +12574,7 @@
         <v>-5.7482860029999996</v>
       </c>
       <c r="R12" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="T12" s="43">
         <f>IF(ISNUMBER(VLOOKUP(U12,Blotter!B:C,2,0)),VLOOKUP(U12,Blotter!B:C,2,0),"")</f>
@@ -12729,19 +12602,19 @@
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.4">
       <c r="A13" s="1" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="H13" s="1">
         <v>1</v>
@@ -12750,7 +12623,7 @@
         <v>46084</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="N13" s="1">
         <v>0.21435478999999999</v>
@@ -12765,7 +12638,7 @@
         <v>-0.76515657100000001</v>
       </c>
       <c r="R13" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="T13" s="43">
         <f>IF(ISNUMBER(VLOOKUP(U13,Blotter!B:C,2,0)),VLOOKUP(U13,Blotter!B:C,2,0),"")</f>
@@ -12793,19 +12666,19 @@
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.4">
       <c r="A14" s="1" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="H14" s="1">
         <v>1</v>
@@ -12814,7 +12687,7 @@
         <v>46084</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="N14" s="1">
         <v>0.26617475000000002</v>
@@ -12829,7 +12702,7 @@
         <v>-0.95013206400000005</v>
       </c>
       <c r="R14" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="T14" s="43">
         <f>IF(ISNUMBER(VLOOKUP(U14,Blotter!B:C,2,0)),VLOOKUP(U14,Blotter!B:C,2,0),"")</f>
@@ -12857,19 +12730,19 @@
     </row>
     <row r="15" spans="1:31" x14ac:dyDescent="0.4">
       <c r="A15" s="1" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="H15" s="1">
         <v>1</v>
@@ -12878,7 +12751,7 @@
         <v>46084</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="N15" s="1">
         <v>6.1193113600000002</v>
@@ -12893,7 +12766,7 @@
         <v>-21.843371443999999</v>
       </c>
       <c r="R15" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="T15" s="43">
         <f>IF(ISNUMBER(VLOOKUP(U15,Blotter!B:C,2,0)),VLOOKUP(U15,Blotter!B:C,2,0),"")</f>
@@ -12921,19 +12794,19 @@
     </row>
     <row r="16" spans="1:31" x14ac:dyDescent="0.4">
       <c r="A16" s="1" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="H16" s="1">
         <v>1</v>
@@ -12942,7 +12815,7 @@
         <v>46084</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="N16" s="1">
         <v>6.1754577399999997</v>
@@ -12957,7 +12830,7 @@
         <v>-22.043790439999999</v>
       </c>
       <c r="R16" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="T16" s="43">
         <f>IF(ISNUMBER(VLOOKUP(U16,Blotter!B:C,2,0)),VLOOKUP(U16,Blotter!B:C,2,0),"")</f>
@@ -12985,19 +12858,19 @@
     </row>
     <row r="17" spans="1:31" x14ac:dyDescent="0.4">
       <c r="A17" s="1" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="H17" s="1">
         <v>1</v>
@@ -13006,7 +12879,7 @@
         <v>46084</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="N17" s="1">
         <v>6.1710219200000003</v>
@@ -13021,7 +12894,7 @@
         <v>-22.027956424999999</v>
       </c>
       <c r="R17" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="T17" s="43">
         <f>IF(ISNUMBER(VLOOKUP(U17,Blotter!B:C,2,0)),VLOOKUP(U17,Blotter!B:C,2,0),"")</f>
@@ -13049,19 +12922,19 @@
     </row>
     <row r="18" spans="1:31" x14ac:dyDescent="0.4">
       <c r="A18" s="1" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="H18" s="1">
         <v>1</v>
@@ -13070,7 +12943,7 @@
         <v>46084</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="N18" s="1">
         <v>6.1193113600000002</v>
@@ -13085,7 +12958,7 @@
         <v>-21.843371443999999</v>
       </c>
       <c r="R18" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="T18" s="43">
         <f>IF(ISNUMBER(VLOOKUP(U18,Blotter!B:C,2,0)),VLOOKUP(U18,Blotter!B:C,2,0),"")</f>
@@ -13113,19 +12986,19 @@
     </row>
     <row r="19" spans="1:31" x14ac:dyDescent="0.4">
       <c r="A19" s="1" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="H19" s="1">
         <v>1</v>
@@ -13134,7 +13007,7 @@
         <v>46084</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="N19" s="1">
         <v>6.1193113600000002</v>
@@ -13149,7 +13022,7 @@
         <v>-21.843371443999999</v>
       </c>
       <c r="R19" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="T19" s="43">
         <f>IF(ISNUMBER(VLOOKUP(U19,Blotter!B:C,2,0)),VLOOKUP(U19,Blotter!B:C,2,0),"")</f>
@@ -13177,19 +13050,19 @@
     </row>
     <row r="20" spans="1:31" x14ac:dyDescent="0.4">
       <c r="A20" s="1" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="H20" s="1">
         <v>1</v>
@@ -13198,7 +13071,7 @@
         <v>46084</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="N20" s="1">
         <v>2.6789095199999999</v>
@@ -13213,7 +13086,7 @@
         <v>-9.5625818440000003</v>
       </c>
       <c r="R20" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="T20" s="43">
         <f>IF(ISNUMBER(VLOOKUP(U20,Blotter!B:C,2,0)),VLOOKUP(U20,Blotter!B:C,2,0),"")</f>
@@ -13241,19 +13114,19 @@
     </row>
     <row r="21" spans="1:31" x14ac:dyDescent="0.4">
       <c r="A21" s="1" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="H21" s="1">
         <v>1</v>
@@ -13262,7 +13135,7 @@
         <v>46087</v>
       </c>
       <c r="M21" s="1" t="s">
-        <v>318</v>
+        <v>304</v>
       </c>
       <c r="N21" s="1">
         <v>-3</v>
@@ -13277,7 +13150,7 @@
         <v>-9.2536833119999997</v>
       </c>
       <c r="R21" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="T21" s="43">
         <f>IF(ISNUMBER(VLOOKUP(U21,Blotter!B:C,2,0)),VLOOKUP(U21,Blotter!B:C,2,0),"")</f>
@@ -13305,19 +13178,19 @@
     </row>
     <row r="22" spans="1:31" x14ac:dyDescent="0.4">
       <c r="A22" s="1" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="H22" s="1">
         <v>1</v>
@@ -13326,7 +13199,7 @@
         <v>46087</v>
       </c>
       <c r="M22" s="1" t="s">
-        <v>318</v>
+        <v>304</v>
       </c>
       <c r="N22" s="1">
         <v>-5.4977520200000001</v>
@@ -13341,7 +13214,7 @@
         <v>-16.49325606</v>
       </c>
       <c r="R22" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="T22" s="43">
         <f>IF(ISNUMBER(VLOOKUP(U22,Blotter!B:C,2,0)),VLOOKUP(U22,Blotter!B:C,2,0),"")</f>
@@ -13369,19 +13242,19 @@
     </row>
     <row r="23" spans="1:31" x14ac:dyDescent="0.4">
       <c r="A23" s="1" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="H23" s="1">
         <v>1</v>
@@ -13390,7 +13263,7 @@
         <v>46087</v>
       </c>
       <c r="M23" s="1" t="s">
-        <v>318</v>
+        <v>304</v>
       </c>
       <c r="N23" s="1">
         <v>-5.5477520199999999</v>
@@ -13405,7 +13278,7 @@
         <v>-16.643256059999999</v>
       </c>
       <c r="R23" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="T23" s="43">
         <f>IF(ISNUMBER(VLOOKUP(U23,Blotter!B:C,2,0)),VLOOKUP(U23,Blotter!B:C,2,0),"")</f>
@@ -13433,19 +13306,19 @@
     </row>
     <row r="24" spans="1:31" x14ac:dyDescent="0.4">
       <c r="A24" s="1" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="H24" s="1">
         <v>1</v>
@@ -13454,7 +13327,7 @@
         <v>46087</v>
       </c>
       <c r="M24" s="1" t="s">
-        <v>318</v>
+        <v>304</v>
       </c>
       <c r="N24" s="1">
         <v>-5.7895520200000004</v>
@@ -13469,7 +13342,7 @@
         <v>-17.368656059999999</v>
       </c>
       <c r="R24" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="T24" s="43">
         <f>IF(ISNUMBER(VLOOKUP(U24,Blotter!B:C,2,0)),VLOOKUP(U24,Blotter!B:C,2,0),"")</f>
@@ -13497,19 +13370,19 @@
     </row>
     <row r="25" spans="1:31" x14ac:dyDescent="0.4">
       <c r="A25" s="1" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="H25" s="1">
         <v>1</v>
@@ -13518,7 +13391,7 @@
         <v>46087</v>
       </c>
       <c r="M25" s="1" t="s">
-        <v>318</v>
+        <v>304</v>
       </c>
       <c r="N25" s="1">
         <v>-0.05</v>
@@ -13533,7 +13406,7 @@
         <v>-0.15</v>
       </c>
       <c r="R25" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="T25" s="43">
         <f>IF(ISNUMBER(VLOOKUP(U25,Blotter!B:C,2,0)),VLOOKUP(U25,Blotter!B:C,2,0),"")</f>
@@ -13561,19 +13434,19 @@
     </row>
     <row r="26" spans="1:31" x14ac:dyDescent="0.4">
       <c r="A26" s="1" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="H26" s="1">
         <v>1</v>
@@ -13582,7 +13455,7 @@
         <v>46087</v>
       </c>
       <c r="M26" s="1" t="s">
-        <v>318</v>
+        <v>304</v>
       </c>
       <c r="N26" s="1">
         <v>-0.2918</v>
@@ -13597,7 +13470,7 @@
         <v>-0.87539999999999996</v>
       </c>
       <c r="R26" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="T26" s="43">
         <f>IF(ISNUMBER(VLOOKUP(U26,Blotter!B:C,2,0)),VLOOKUP(U26,Blotter!B:C,2,0),"")</f>
@@ -13625,19 +13498,19 @@
     </row>
     <row r="27" spans="1:31" x14ac:dyDescent="0.4">
       <c r="A27" s="1" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="H27" s="1">
         <v>1</v>
@@ -13646,7 +13519,7 @@
         <v>46087</v>
       </c>
       <c r="M27" s="1" t="s">
-        <v>318</v>
+        <v>304</v>
       </c>
       <c r="N27" s="1">
         <v>-5.7895520200000004</v>
@@ -13661,7 +13534,7 @@
         <v>-17.368656059999999</v>
       </c>
       <c r="R27" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="T27" s="43">
         <f>IF(ISNUMBER(VLOOKUP(U27,Blotter!B:C,2,0)),VLOOKUP(U27,Blotter!B:C,2,0),"")</f>
@@ -13689,19 +13562,19 @@
     </row>
     <row r="28" spans="1:31" x14ac:dyDescent="0.4">
       <c r="A28" s="1" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="H28" s="1">
         <v>1</v>
@@ -13710,7 +13583,7 @@
         <v>46087</v>
       </c>
       <c r="M28" s="1" t="s">
-        <v>318</v>
+        <v>304</v>
       </c>
       <c r="N28" s="1">
         <v>-0.24179999999999999</v>
@@ -13725,7 +13598,7 @@
         <v>-0.72540000000000004</v>
       </c>
       <c r="R28" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="T28" s="43">
         <f>IF(ISNUMBER(VLOOKUP(U28,Blotter!B:C,2,0)),VLOOKUP(U28,Blotter!B:C,2,0),"")</f>
@@ -13753,19 +13626,19 @@
     </row>
     <row r="29" spans="1:31" x14ac:dyDescent="0.4">
       <c r="A29" s="1" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="H29" s="1">
         <v>1</v>
@@ -13774,7 +13647,7 @@
         <v>46087</v>
       </c>
       <c r="M29" s="1" t="s">
-        <v>318</v>
+        <v>304</v>
       </c>
       <c r="N29" s="1">
         <v>-0.24179999999999999</v>
@@ -13789,7 +13662,7 @@
         <v>-0.72540000000000004</v>
       </c>
       <c r="R29" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="T29" s="43">
         <f>IF(ISNUMBER(VLOOKUP(U29,Blotter!B:C,2,0)),VLOOKUP(U29,Blotter!B:C,2,0),"")</f>
@@ -13817,19 +13690,19 @@
     </row>
     <row r="30" spans="1:31" x14ac:dyDescent="0.4">
       <c r="A30" s="1" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="H30" s="1">
         <v>1</v>
@@ -13838,7 +13711,7 @@
         <v>46087</v>
       </c>
       <c r="M30" s="1" t="s">
-        <v>318</v>
+        <v>304</v>
       </c>
       <c r="N30" s="1">
         <v>-5.9996570199999999</v>
@@ -13853,7 +13726,7 @@
         <v>-17.998971059999999</v>
       </c>
       <c r="R30" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="T30" s="43">
         <f>IF(ISNUMBER(VLOOKUP(U30,Blotter!B:C,2,0)),VLOOKUP(U30,Blotter!B:C,2,0),"")</f>
@@ -13881,19 +13754,19 @@
     </row>
     <row r="31" spans="1:31" x14ac:dyDescent="0.4">
       <c r="A31" s="1" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="H31" s="1">
         <v>1</v>
@@ -13902,7 +13775,7 @@
         <v>46087</v>
       </c>
       <c r="M31" s="1" t="s">
-        <v>318</v>
+        <v>304</v>
       </c>
       <c r="N31" s="1">
         <v>-2.4973153799999999</v>
@@ -13917,7 +13790,7 @@
         <v>-7.4999999820000003</v>
       </c>
       <c r="R31" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="T31" s="43">
         <f>IF(ISNUMBER(VLOOKUP(U31,Blotter!B:C,2,0)),VLOOKUP(U31,Blotter!B:C,2,0),"")</f>
@@ -13945,19 +13818,19 @@
     </row>
     <row r="32" spans="1:31" x14ac:dyDescent="0.4">
       <c r="A32" s="1" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="H32" s="1">
         <v>1</v>
@@ -13966,7 +13839,7 @@
         <v>46087</v>
       </c>
       <c r="M32" s="1" t="s">
-        <v>318</v>
+        <v>304</v>
       </c>
       <c r="N32" s="1">
         <v>-1.0847240199999999</v>
@@ -13981,7 +13854,7 @@
         <v>-3.2541720600000001</v>
       </c>
       <c r="R32" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="T32" s="43">
         <f>IF(ISNUMBER(VLOOKUP(U32,Blotter!B:C,2,0)),VLOOKUP(U32,Blotter!B:C,2,0),"")</f>
@@ -14009,19 +13882,19 @@
     </row>
     <row r="33" spans="1:31" x14ac:dyDescent="0.4">
       <c r="A33" s="1" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="H33" s="1">
         <v>1</v>
@@ -14030,7 +13903,7 @@
         <v>46087</v>
       </c>
       <c r="M33" s="1" t="s">
-        <v>318</v>
+        <v>304</v>
       </c>
       <c r="N33" s="1">
         <v>-0.21252689</v>
@@ -14045,7 +13918,7 @@
         <v>-0.63758066999999996</v>
       </c>
       <c r="R33" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="T33" s="43">
         <f>IF(ISNUMBER(VLOOKUP(U33,Blotter!B:C,2,0)),VLOOKUP(U33,Blotter!B:C,2,0),"")</f>
@@ -14073,19 +13946,19 @@
     </row>
     <row r="34" spans="1:31" x14ac:dyDescent="0.4">
       <c r="A34" s="1" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="H34" s="1">
         <v>1</v>
@@ -14094,7 +13967,7 @@
         <v>46087</v>
       </c>
       <c r="M34" s="1" t="s">
-        <v>318</v>
+        <v>304</v>
       </c>
       <c r="N34" s="1">
         <v>-2.2592068799999998</v>
@@ -14109,7 +13982,7 @@
         <v>-6.7776206400000003</v>
       </c>
       <c r="R34" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="T34" s="43">
         <f>IF(ISNUMBER(VLOOKUP(U34,Blotter!B:C,2,0)),VLOOKUP(U34,Blotter!B:C,2,0),"")</f>
@@ -14134,19 +14007,19 @@
     </row>
     <row r="35" spans="1:31" x14ac:dyDescent="0.4">
       <c r="A35" s="1" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="H35" s="1">
         <v>1</v>
@@ -14155,7 +14028,7 @@
         <v>46087</v>
       </c>
       <c r="M35" s="1" t="s">
-        <v>318</v>
+        <v>304</v>
       </c>
       <c r="N35" s="1">
         <v>-1.96740688</v>
@@ -14170,7 +14043,7 @@
         <v>-5.9022206400000004</v>
       </c>
       <c r="R35" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="T35" s="43">
         <f>IF(ISNUMBER(VLOOKUP(U35,Blotter!B:C,2,0)),VLOOKUP(U35,Blotter!B:C,2,0),"")</f>
@@ -14195,19 +14068,19 @@
     </row>
     <row r="36" spans="1:31" x14ac:dyDescent="0.4">
       <c r="A36" s="1" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="H36" s="1">
         <v>1</v>
@@ -14216,7 +14089,7 @@
         <v>46087</v>
       </c>
       <c r="M36" s="1" t="s">
-        <v>318</v>
+        <v>304</v>
       </c>
       <c r="N36" s="1">
         <v>-4.0489291700000001</v>
@@ -14231,7 +14104,7 @@
         <v>-12.146787509999999</v>
       </c>
       <c r="R36" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="T36" s="43">
         <f>IF(ISNUMBER(VLOOKUP(U36,Blotter!B:C,2,0)),VLOOKUP(U36,Blotter!B:C,2,0),"")</f>
@@ -14256,19 +14129,19 @@
     </row>
     <row r="37" spans="1:31" x14ac:dyDescent="0.4">
       <c r="A37" s="1" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="H37" s="1">
         <v>1</v>
@@ -14277,7 +14150,7 @@
         <v>46087</v>
       </c>
       <c r="M37" s="1" t="s">
-        <v>318</v>
+        <v>304</v>
       </c>
       <c r="N37" s="1">
         <v>-3.5134851600000001</v>
@@ -14292,7 +14165,7 @@
         <v>-10.54045548</v>
       </c>
       <c r="R37" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="T37" s="43">
         <f>IF(ISNUMBER(VLOOKUP(U37,Blotter!B:C,2,0)),VLOOKUP(U37,Blotter!B:C,2,0),"")</f>
@@ -14317,19 +14190,19 @@
     </row>
     <row r="38" spans="1:31" x14ac:dyDescent="0.4">
       <c r="A38" s="1" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="H38" s="1">
         <v>1</v>
@@ -14338,7 +14211,7 @@
         <v>46087</v>
       </c>
       <c r="M38" s="1" t="s">
-        <v>318</v>
+        <v>304</v>
       </c>
       <c r="N38" s="1">
         <v>-1.45325536</v>
@@ -14353,7 +14226,7 @@
         <v>-4.35976608</v>
       </c>
       <c r="R38" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="T38" s="43">
         <f>IF(ISNUMBER(VLOOKUP(U38,Blotter!B:C,2,0)),VLOOKUP(U38,Blotter!B:C,2,0),"")</f>
@@ -14378,19 +14251,19 @@
     </row>
     <row r="39" spans="1:31" x14ac:dyDescent="0.4">
       <c r="A39" s="1" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="H39" s="1">
         <v>1</v>
@@ -14399,7 +14272,7 @@
         <v>46087</v>
       </c>
       <c r="M39" s="1" t="s">
-        <v>318</v>
+        <v>304</v>
       </c>
       <c r="N39" s="1">
         <v>-0.51348516</v>
@@ -14414,7 +14287,7 @@
         <v>-1.5404554800000001</v>
       </c>
       <c r="R39" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="T39" s="43">
         <f>IF(ISNUMBER(VLOOKUP(U39,Blotter!B:C,2,0)),VLOOKUP(U39,Blotter!B:C,2,0),"")</f>
@@ -14438,18 +14311,72 @@
       </c>
     </row>
     <row r="40" spans="1:31" x14ac:dyDescent="0.4">
-      <c r="T40" s="43"/>
-      <c r="U40" s="42"/>
-      <c r="V40" s="42"/>
-      <c r="W40" s="42"/>
-      <c r="X40" s="42"/>
+      <c r="D40" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="M40" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="N40" s="1">
+        <v>2</v>
+      </c>
+      <c r="O40" s="1">
+        <v>5</v>
+      </c>
+      <c r="T40" s="43">
+        <f>IF(ISNUMBER(VLOOKUP(U40,Blotter!B:C,2,0)),VLOOKUP(U40,Blotter!B:C,2,0),"")</f>
+        <v>3</v>
+      </c>
+      <c r="U40" s="42" t="str">
+        <f t="shared" ref="U40:U41" si="16">D40</f>
+        <v>CLM6P75260514</v>
+      </c>
+      <c r="V40" s="42">
+        <f t="shared" ref="V40:V41" si="17">N40</f>
+        <v>2</v>
+      </c>
+      <c r="W40" s="42">
+        <f t="shared" ref="W40:W41" si="18">O40</f>
+        <v>5</v>
+      </c>
+      <c r="X40" s="42">
+        <f t="shared" ref="X40:X41" si="19">Q40</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="41" spans="1:31" x14ac:dyDescent="0.4">
-      <c r="T41" s="43"/>
-      <c r="U41" s="42"/>
-      <c r="V41" s="42"/>
-      <c r="W41" s="42"/>
-      <c r="X41" s="42"/>
+      <c r="D41" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="M41" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="N41" s="1">
+        <v>-2</v>
+      </c>
+      <c r="O41" s="1">
+        <v>1</v>
+      </c>
+      <c r="T41" s="43">
+        <f>IF(ISNUMBER(VLOOKUP(U41,Blotter!B:C,2,0)),VLOOKUP(U41,Blotter!B:C,2,0),"")</f>
+        <v>3</v>
+      </c>
+      <c r="U41" s="42" t="str">
+        <f t="shared" si="16"/>
+        <v>CLM6P55260514</v>
+      </c>
+      <c r="V41" s="42">
+        <f t="shared" si="17"/>
+        <v>-2</v>
+      </c>
+      <c r="W41" s="42">
+        <f t="shared" si="18"/>
+        <v>1</v>
+      </c>
+      <c r="X41" s="42">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="42" spans="1:31" x14ac:dyDescent="0.4">
       <c r="T42" s="43"/>
@@ -22109,21 +22036,21 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A1" s="90" t="s">
-        <v>215</v>
+        <v>204</v>
       </c>
       <c r="B1" s="56"/>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A3" s="80" t="s">
-        <v>214</v>
+        <v>203</v>
       </c>
       <c r="B3" s="89" t="s">
-        <v>213</v>
+        <v>202</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A4" s="80" t="s">
-        <v>212</v>
+        <v>201</v>
       </c>
       <c r="B4" s="89">
         <v>7497</v>
@@ -22131,7 +22058,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A5" s="80" t="s">
-        <v>211</v>
+        <v>200</v>
       </c>
       <c r="B5" s="89">
         <v>11</v>
@@ -22139,7 +22066,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A6" s="80" t="s">
-        <v>210</v>
+        <v>199</v>
       </c>
       <c r="B6" s="89">
         <v>0.25</v>
@@ -22147,15 +22074,15 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A7" s="80" t="s">
-        <v>209</v>
+        <v>198</v>
       </c>
       <c r="B7" s="89" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A8" s="80" t="s">
-        <v>207</v>
+        <v>196</v>
       </c>
       <c r="B8" s="89">
         <v>3</v>
@@ -22163,22 +22090,22 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A10" s="1" t="s">
-        <v>206</v>
+        <v>195</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A11" s="1" t="s">
-        <v>205</v>
+        <v>194</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A12" s="1" t="s">
-        <v>204</v>
+        <v>193</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A13" s="1" t="s">
-        <v>203</v>
+        <v>192</v>
       </c>
     </row>
   </sheetData>
@@ -22189,7 +22116,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BC83BD8-F674-453E-9653-9D885B9DE5ED}">
-  <dimension ref="A1:M78"/>
+  <dimension ref="A1:M77"/>
   <sheetFormatPr defaultRowHeight="13.15" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -22209,43 +22136,43 @@
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A1" s="82" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="B1" s="82" t="s">
-        <v>228</v>
+        <v>217</v>
       </c>
       <c r="C1" s="82" t="s">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="D1" s="82" t="s">
-        <v>226</v>
+        <v>215</v>
       </c>
       <c r="E1" s="82" t="s">
-        <v>225</v>
+        <v>214</v>
       </c>
       <c r="F1" s="82" t="s">
-        <v>224</v>
+        <v>213</v>
       </c>
       <c r="G1" s="82" t="s">
-        <v>223</v>
+        <v>212</v>
       </c>
       <c r="H1" s="82" t="s">
-        <v>222</v>
+        <v>211</v>
       </c>
       <c r="I1" s="82" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="J1" s="82" t="s">
-        <v>220</v>
+        <v>209</v>
       </c>
       <c r="K1" s="82" t="s">
-        <v>219</v>
+        <v>208</v>
       </c>
       <c r="L1" s="82" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="M1" s="82" t="s">
-        <v>217</v>
+        <v>206</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.4">
@@ -22253,22 +22180,22 @@
         <v>1</v>
       </c>
       <c r="B2" s="88" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="C2" s="88" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D2" s="88" t="s">
         <v>21</v>
       </c>
       <c r="E2" s="88" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="F2" s="88" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="G2" s="88" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
       <c r="H2" s="88"/>
       <c r="I2" s="88"/>
@@ -22282,22 +22209,22 @@
         <v>1</v>
       </c>
       <c r="B3" s="88" t="s">
-        <v>255</v>
+        <v>243</v>
       </c>
       <c r="C3" s="88" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D3" s="88" t="s">
         <v>22</v>
       </c>
       <c r="E3" s="88" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="F3" s="88" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="G3" s="88" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
       <c r="H3" s="88"/>
       <c r="I3" s="88"/>
@@ -22311,22 +22238,22 @@
         <v>1</v>
       </c>
       <c r="B4" s="88" t="s">
-        <v>256</v>
+        <v>244</v>
       </c>
       <c r="C4" s="88" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D4" s="88" t="s">
         <v>23</v>
       </c>
       <c r="E4" s="88" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="F4" s="88" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="G4" s="88" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
       <c r="H4" s="88"/>
       <c r="I4" s="88"/>
@@ -22340,28 +22267,28 @@
         <v>1</v>
       </c>
       <c r="B5" s="88" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
       <c r="C5" s="88" t="s">
+        <v>58</v>
+      </c>
+      <c r="D5" s="88" t="s">
         <v>61</v>
       </c>
-      <c r="D5" s="88" t="s">
-        <v>249</v>
-      </c>
       <c r="E5" s="88" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="F5" s="88" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="G5" s="88" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
       <c r="H5" s="88"/>
       <c r="I5" s="88"/>
       <c r="J5" s="88"/>
       <c r="K5" s="88" t="s">
-        <v>249</v>
+        <v>238</v>
       </c>
       <c r="L5" s="88"/>
       <c r="M5" s="88"/>
@@ -22371,28 +22298,30 @@
         <v>1</v>
       </c>
       <c r="B6" s="88" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="C6" s="88" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D6" s="88" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E6" s="88" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="F6" s="88" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G6" s="88" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
       <c r="H6" s="88"/>
       <c r="I6" s="88"/>
-      <c r="J6" s="88"/>
+      <c r="J6" s="88">
+        <v>500</v>
+      </c>
       <c r="K6" s="88" t="s">
-        <v>250</v>
+        <v>62</v>
       </c>
       <c r="L6" s="88"/>
       <c r="M6" s="88"/>
@@ -22402,30 +22331,28 @@
         <v>1</v>
       </c>
       <c r="B7" s="88" t="s">
-        <v>273</v>
+        <v>176</v>
       </c>
       <c r="C7" s="88" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D7" s="88" t="s">
-        <v>66</v>
+        <v>24</v>
       </c>
       <c r="E7" s="88" t="s">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="F7" s="88" t="s">
-        <v>60</v>
-      </c>
-      <c r="G7" s="88" t="s">
-        <v>216</v>
+        <v>59</v>
+      </c>
+      <c r="G7" s="88">
+        <v>202604</v>
       </c>
       <c r="H7" s="88"/>
       <c r="I7" s="88"/>
-      <c r="J7" s="88">
-        <v>500</v>
-      </c>
+      <c r="J7" s="88"/>
       <c r="K7" s="88" t="s">
-        <v>66</v>
+        <v>24</v>
       </c>
       <c r="L7" s="88"/>
       <c r="M7" s="88"/>
@@ -22435,28 +22362,28 @@
         <v>1</v>
       </c>
       <c r="B8" s="88" t="s">
-        <v>186</v>
+        <v>249</v>
       </c>
       <c r="C8" s="88" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D8" s="88" t="s">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="E8" s="88" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="F8" s="88" t="s">
-        <v>62</v>
-      </c>
-      <c r="G8" s="88">
-        <v>202604</v>
+        <v>59</v>
+      </c>
+      <c r="G8" s="88" t="s">
+        <v>205</v>
       </c>
       <c r="H8" s="88"/>
       <c r="I8" s="88"/>
       <c r="J8" s="88"/>
       <c r="K8" s="88" t="s">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="L8" s="88"/>
       <c r="M8" s="88"/>
@@ -22466,28 +22393,28 @@
         <v>1</v>
       </c>
       <c r="B9" s="88" t="s">
-        <v>262</v>
+        <v>250</v>
       </c>
       <c r="C9" s="88" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D9" s="88" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E9" s="88" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="F9" s="88" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="G9" s="88" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
       <c r="H9" s="88"/>
       <c r="I9" s="88"/>
       <c r="J9" s="88"/>
       <c r="K9" s="88" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L9" s="88"/>
       <c r="M9" s="88"/>
@@ -22497,28 +22424,28 @@
         <v>1</v>
       </c>
       <c r="B10" s="88" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="C10" s="88" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D10" s="88" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E10" s="88" t="s">
-        <v>64</v>
+        <v>81</v>
       </c>
       <c r="F10" s="88" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="G10" s="88" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
       <c r="H10" s="88"/>
       <c r="I10" s="88"/>
       <c r="J10" s="88"/>
       <c r="K10" s="88" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="L10" s="88"/>
       <c r="M10" s="88"/>
@@ -22528,28 +22455,28 @@
         <v>1</v>
       </c>
       <c r="B11" s="88" t="s">
-        <v>264</v>
+        <v>252</v>
       </c>
       <c r="C11" s="88" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D11" s="88" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E11" s="88" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="F11" s="88" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="G11" s="88" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
       <c r="H11" s="88"/>
       <c r="I11" s="88"/>
       <c r="J11" s="88"/>
       <c r="K11" s="88" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L11" s="88"/>
       <c r="M11" s="88"/>
@@ -22559,28 +22486,28 @@
         <v>1</v>
       </c>
       <c r="B12" s="88" t="s">
-        <v>265</v>
+        <v>253</v>
       </c>
       <c r="C12" s="88" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D12" s="88" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E12" s="88" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="F12" s="88" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="G12" s="88" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
       <c r="H12" s="88"/>
       <c r="I12" s="88"/>
       <c r="J12" s="88"/>
       <c r="K12" s="88" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="L12" s="88"/>
       <c r="M12" s="88"/>
@@ -22590,28 +22517,28 @@
         <v>1</v>
       </c>
       <c r="B13" s="88" t="s">
-        <v>266</v>
+        <v>137</v>
       </c>
       <c r="C13" s="88" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D13" s="88" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E13" s="88" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="F13" s="88" t="s">
-        <v>62</v>
-      </c>
-      <c r="G13" s="88" t="s">
-        <v>216</v>
+        <v>59</v>
+      </c>
+      <c r="G13" s="88">
+        <v>202605</v>
       </c>
       <c r="H13" s="88"/>
       <c r="I13" s="88"/>
       <c r="J13" s="88"/>
       <c r="K13" s="88" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L13" s="88"/>
       <c r="M13" s="88"/>
@@ -22621,19 +22548,19 @@
         <v>1</v>
       </c>
       <c r="B14" s="88" t="s">
-        <v>142</v>
+        <v>175</v>
       </c>
       <c r="C14" s="88" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D14" s="88" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E14" s="88" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="F14" s="88" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="G14" s="88">
         <v>202605</v>
@@ -22642,7 +22569,7 @@
       <c r="I14" s="88"/>
       <c r="J14" s="88"/>
       <c r="K14" s="88" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L14" s="88"/>
       <c r="M14" s="88"/>
@@ -22652,19 +22579,19 @@
         <v>1</v>
       </c>
       <c r="B15" s="88" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="C15" s="88" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D15" s="88" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E15" s="88" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="F15" s="88" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="G15" s="88">
         <v>202605</v>
@@ -22673,7 +22600,7 @@
       <c r="I15" s="88"/>
       <c r="J15" s="88"/>
       <c r="K15" s="88" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L15" s="88"/>
       <c r="M15" s="88"/>
@@ -22683,19 +22610,19 @@
         <v>1</v>
       </c>
       <c r="B16" s="88" t="s">
-        <v>190</v>
+        <v>134</v>
       </c>
       <c r="C16" s="88" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D16" s="88" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E16" s="88" t="s">
-        <v>86</v>
+        <v>64</v>
       </c>
       <c r="F16" s="88" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="G16" s="88">
         <v>202605</v>
@@ -22704,7 +22631,7 @@
       <c r="I16" s="88"/>
       <c r="J16" s="88"/>
       <c r="K16" s="88" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L16" s="88"/>
       <c r="M16" s="88"/>
@@ -22714,19 +22641,19 @@
         <v>1</v>
       </c>
       <c r="B17" s="88" t="s">
-        <v>139</v>
+        <v>177</v>
       </c>
       <c r="C17" s="88" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D17" s="88" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E17" s="88" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="F17" s="88" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="G17" s="88">
         <v>202605</v>
@@ -22735,7 +22662,7 @@
       <c r="I17" s="88"/>
       <c r="J17" s="88"/>
       <c r="K17" s="88" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L17" s="88"/>
       <c r="M17" s="88"/>
@@ -22745,19 +22672,19 @@
         <v>1</v>
       </c>
       <c r="B18" s="88" t="s">
-        <v>187</v>
+        <v>290</v>
       </c>
       <c r="C18" s="88" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D18" s="88" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E18" s="88" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="F18" s="88" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="G18" s="88">
         <v>202605</v>
@@ -22766,7 +22693,7 @@
       <c r="I18" s="88"/>
       <c r="J18" s="88"/>
       <c r="K18" s="88" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L18" s="88"/>
       <c r="M18" s="88"/>
@@ -22776,19 +22703,19 @@
         <v>1</v>
       </c>
       <c r="B19" s="88" t="s">
-        <v>304</v>
+        <v>184</v>
       </c>
       <c r="C19" s="88" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D19" s="88" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="E19" s="88" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="F19" s="88" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="G19" s="88">
         <v>202605</v>
@@ -22797,7 +22724,7 @@
       <c r="I19" s="88"/>
       <c r="J19" s="88"/>
       <c r="K19" s="88" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="L19" s="88"/>
       <c r="M19" s="88"/>
@@ -22807,28 +22734,28 @@
         <v>1</v>
       </c>
       <c r="B20" s="88" t="s">
-        <v>194</v>
+        <v>35</v>
       </c>
       <c r="C20" s="88" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D20" s="88" t="s">
-        <v>69</v>
+        <v>35</v>
       </c>
       <c r="E20" s="88" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="F20" s="88" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="G20" s="88">
-        <v>202605</v>
+        <v>202604</v>
       </c>
       <c r="H20" s="88"/>
       <c r="I20" s="88"/>
       <c r="J20" s="88"/>
       <c r="K20" s="88" t="s">
-        <v>69</v>
+        <v>35</v>
       </c>
       <c r="L20" s="88"/>
       <c r="M20" s="88"/>
@@ -22838,28 +22765,28 @@
         <v>1</v>
       </c>
       <c r="B21" s="88" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C21" s="88" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D21" s="88" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E21" s="88" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="F21" s="88" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="G21" s="88">
-        <v>202604</v>
+        <v>202605</v>
       </c>
       <c r="H21" s="88"/>
       <c r="I21" s="88"/>
       <c r="J21" s="88"/>
       <c r="K21" s="88" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L21" s="88"/>
       <c r="M21" s="88"/>
@@ -22869,28 +22796,28 @@
         <v>1</v>
       </c>
       <c r="B22" s="88" t="s">
-        <v>36</v>
+        <v>150</v>
       </c>
       <c r="C22" s="88" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D22" s="88" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E22" s="88" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="F22" s="88" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="G22" s="88">
-        <v>202605</v>
+        <v>202604</v>
       </c>
       <c r="H22" s="88"/>
       <c r="I22" s="88"/>
       <c r="J22" s="88"/>
       <c r="K22" s="88" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="L22" s="88"/>
       <c r="M22" s="88"/>
@@ -22900,28 +22827,28 @@
         <v>1</v>
       </c>
       <c r="B23" s="88" t="s">
-        <v>156</v>
+        <v>259</v>
       </c>
       <c r="C23" s="88" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D23" s="88" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E23" s="88" t="s">
-        <v>83</v>
+        <v>64</v>
       </c>
       <c r="F23" s="88" t="s">
-        <v>62</v>
-      </c>
-      <c r="G23" s="88">
-        <v>202604</v>
+        <v>59</v>
+      </c>
+      <c r="G23" s="88" t="s">
+        <v>205</v>
       </c>
       <c r="H23" s="88"/>
       <c r="I23" s="88"/>
       <c r="J23" s="88"/>
       <c r="K23" s="88" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L23" s="88"/>
       <c r="M23" s="88"/>
@@ -22931,28 +22858,28 @@
         <v>1</v>
       </c>
       <c r="B24" s="88" t="s">
-        <v>272</v>
+        <v>254</v>
       </c>
       <c r="C24" s="88" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D24" s="88" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E24" s="88" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="F24" s="88" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="G24" s="88" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
       <c r="H24" s="88"/>
       <c r="I24" s="88"/>
       <c r="J24" s="88"/>
       <c r="K24" s="88" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="L24" s="88"/>
       <c r="M24" s="88"/>
@@ -22962,28 +22889,28 @@
         <v>1</v>
       </c>
       <c r="B25" s="88" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="C25" s="88" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D25" s="88" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E25" s="88" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="F25" s="88" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="G25" s="88" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
       <c r="H25" s="88"/>
       <c r="I25" s="88"/>
       <c r="J25" s="88"/>
       <c r="K25" s="88" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="L25" s="88"/>
       <c r="M25" s="88"/>
@@ -22993,28 +22920,28 @@
         <v>1</v>
       </c>
       <c r="B26" s="88" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="C26" s="88" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D26" s="88" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="E26" s="88" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="F26" s="88" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="G26" s="88" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
       <c r="H26" s="88"/>
       <c r="I26" s="88"/>
       <c r="J26" s="88"/>
       <c r="K26" s="88" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="L26" s="88"/>
       <c r="M26" s="88"/>
@@ -23024,28 +22951,28 @@
         <v>1</v>
       </c>
       <c r="B27" s="88" t="s">
-        <v>269</v>
+        <v>257</v>
       </c>
       <c r="C27" s="88" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D27" s="88" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E27" s="88" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="F27" s="88" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="G27" s="88" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
       <c r="H27" s="88"/>
       <c r="I27" s="88"/>
       <c r="J27" s="88"/>
       <c r="K27" s="88" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="L27" s="88"/>
       <c r="M27" s="88"/>
@@ -23055,28 +22982,28 @@
         <v>1</v>
       </c>
       <c r="B28" s="88" t="s">
-        <v>270</v>
+        <v>258</v>
       </c>
       <c r="C28" s="88" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D28" s="88" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E28" s="88" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="F28" s="88" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="G28" s="88" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
       <c r="H28" s="88"/>
       <c r="I28" s="88"/>
       <c r="J28" s="88"/>
       <c r="K28" s="88" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="L28" s="88"/>
       <c r="M28" s="88"/>
@@ -23086,28 +23013,28 @@
         <v>1</v>
       </c>
       <c r="B29" s="88" t="s">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="C29" s="88" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D29" s="88" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="E29" s="88" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F29" s="88" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="G29" s="88" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
       <c r="H29" s="88"/>
       <c r="I29" s="88"/>
       <c r="J29" s="88"/>
       <c r="K29" s="88" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="L29" s="88"/>
       <c r="M29" s="88"/>
@@ -23117,28 +23044,28 @@
         <v>1</v>
       </c>
       <c r="B30" s="88" t="s">
-        <v>274</v>
+        <v>262</v>
       </c>
       <c r="C30" s="88" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D30" s="88" t="s">
-        <v>46</v>
+        <v>67</v>
       </c>
       <c r="E30" s="88" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="F30" s="88" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="G30" s="88" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
       <c r="H30" s="88"/>
       <c r="I30" s="88"/>
       <c r="J30" s="88"/>
       <c r="K30" s="88" t="s">
-        <v>46</v>
+        <v>67</v>
       </c>
       <c r="L30" s="88"/>
       <c r="M30" s="88"/>
@@ -23148,28 +23075,28 @@
         <v>1</v>
       </c>
       <c r="B31" s="88" t="s">
-        <v>275</v>
+        <v>246</v>
       </c>
       <c r="C31" s="88" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D31" s="88" t="s">
-        <v>71</v>
+        <v>239</v>
       </c>
       <c r="E31" s="88" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="F31" s="88" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="G31" s="88" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
       <c r="H31" s="88"/>
       <c r="I31" s="88"/>
       <c r="J31" s="88"/>
       <c r="K31" s="88" t="s">
-        <v>71</v>
+        <v>239</v>
       </c>
       <c r="L31" s="88"/>
       <c r="M31" s="88"/>
@@ -23179,28 +23106,28 @@
         <v>1</v>
       </c>
       <c r="B32" s="88" t="s">
-        <v>259</v>
+        <v>247</v>
       </c>
       <c r="C32" s="88" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D32" s="88" t="s">
-        <v>251</v>
+        <v>240</v>
       </c>
       <c r="E32" s="88" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="F32" s="88" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="G32" s="88" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
       <c r="H32" s="88"/>
       <c r="I32" s="88"/>
       <c r="J32" s="88"/>
       <c r="K32" s="88" t="s">
-        <v>251</v>
+        <v>240</v>
       </c>
       <c r="L32" s="88"/>
       <c r="M32" s="88"/>
@@ -23210,60 +23137,51 @@
         <v>1</v>
       </c>
       <c r="B33" s="88" t="s">
-        <v>260</v>
+        <v>248</v>
       </c>
       <c r="C33" s="88" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D33" s="88" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="E33" s="88" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="F33" s="88" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="G33" s="88" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
       <c r="H33" s="88"/>
       <c r="I33" s="88"/>
       <c r="J33" s="88"/>
       <c r="K33" s="88" t="s">
-        <v>252</v>
-      </c>
-      <c r="L33" s="88"/>
+        <v>241</v>
+      </c>
       <c r="M33" s="88"/>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A34" s="88">
         <v>1</v>
       </c>
-      <c r="B34" s="88" t="s">
-        <v>261</v>
+      <c r="B34" s="9" t="s">
+        <v>298</v>
       </c>
       <c r="C34" s="88" t="s">
-        <v>61</v>
+        <v>187</v>
       </c>
       <c r="D34" s="88" t="s">
-        <v>253</v>
+        <v>44</v>
       </c>
       <c r="E34" s="88" t="s">
-        <v>84</v>
+        <v>191</v>
       </c>
       <c r="F34" s="88" t="s">
         <v>59</v>
       </c>
-      <c r="G34" s="88" t="s">
-        <v>216</v>
-      </c>
-      <c r="H34" s="88"/>
-      <c r="I34" s="88"/>
-      <c r="J34" s="88"/>
-      <c r="K34" s="88" t="s">
-        <v>253</v>
-      </c>
+      <c r="L34" s="88"/>
       <c r="M34" s="88"/>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.4">
@@ -23271,20 +23189,25 @@
         <v>1</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>312</v>
+        <v>188</v>
       </c>
       <c r="C35" s="88" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="D35" s="88" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E35" s="88" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="F35" s="88" t="s">
-        <v>62</v>
-      </c>
+        <v>59</v>
+      </c>
+      <c r="G35" s="88"/>
+      <c r="H35" s="88"/>
+      <c r="I35" s="88"/>
+      <c r="J35" s="88"/>
+      <c r="K35" s="88"/>
       <c r="L35" s="88"/>
       <c r="M35" s="88"/>
     </row>
@@ -23293,33 +23216,79 @@
         <v>1</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>198</v>
+        <v>317</v>
       </c>
       <c r="C36" s="88" t="s">
-        <v>197</v>
+        <v>320</v>
       </c>
       <c r="D36" s="88" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="E36" s="88" t="s">
-        <v>201</v>
+        <v>60</v>
       </c>
       <c r="F36" s="88" t="s">
-        <v>62</v>
-      </c>
-      <c r="G36" s="88"/>
-      <c r="H36" s="88"/>
-      <c r="I36" s="88"/>
-      <c r="J36" s="88"/>
-      <c r="K36" s="88"/>
-      <c r="L36" s="88"/>
+        <v>59</v>
+      </c>
+      <c r="G36" s="88">
+        <v>20260514</v>
+      </c>
+      <c r="H36" s="88">
+        <v>75</v>
+      </c>
+      <c r="I36" s="88" t="s">
+        <v>315</v>
+      </c>
+      <c r="J36" s="88">
+        <v>1000</v>
+      </c>
+      <c r="K36" s="88" t="s">
+        <v>316</v>
+      </c>
       <c r="M36" s="88"/>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A37" s="88">
+        <v>1</v>
+      </c>
+      <c r="B37" s="9" t="s">
+        <v>318</v>
+      </c>
+      <c r="C37" s="88" t="s">
+        <v>320</v>
+      </c>
+      <c r="D37" s="88" t="s">
+        <v>24</v>
+      </c>
+      <c r="E37" s="88" t="s">
+        <v>60</v>
+      </c>
+      <c r="F37" s="88" t="s">
+        <v>59</v>
+      </c>
+      <c r="G37" s="88">
+        <v>20260514</v>
+      </c>
+      <c r="H37" s="88">
+        <v>55</v>
+      </c>
+      <c r="I37" s="88" t="s">
+        <v>315</v>
+      </c>
+      <c r="J37" s="88">
+        <v>1000</v>
+      </c>
+      <c r="K37" s="88" t="s">
+        <v>316</v>
+      </c>
       <c r="M37" s="88"/>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="M38" s="88"/>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="C39" s="31"/>
+      <c r="D39" s="31"/>
+      <c r="E39" s="31"/>
+      <c r="F39" s="31"/>
+      <c r="G39" s="31"/>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.4">
       <c r="C40" s="31"/>
@@ -23420,303 +23389,313 @@
       <c r="G53" s="31"/>
     </row>
     <row r="54" spans="3:7" x14ac:dyDescent="0.4">
-      <c r="C54" s="31"/>
-      <c r="D54" s="31"/>
-      <c r="E54" s="31"/>
-      <c r="F54" s="31"/>
-      <c r="G54" s="31"/>
+      <c r="C54" s="31" t="s">
+        <v>142</v>
+      </c>
+      <c r="D54" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="E54" s="31" t="s">
+        <v>58</v>
+      </c>
+      <c r="F54" s="31" t="s">
+        <v>81</v>
+      </c>
+      <c r="G54" s="31" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="55" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C55" s="31" t="s">
-        <v>147</v>
+        <v>63</v>
       </c>
       <c r="D55" s="31" t="s">
-        <v>27</v>
+        <v>63</v>
       </c>
       <c r="E55" s="31" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="F55" s="31" t="s">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="G55" s="31" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="56" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C56" s="31" t="s">
-        <v>67</v>
+        <v>137</v>
       </c>
       <c r="D56" s="31" t="s">
-        <v>67</v>
+        <v>28</v>
       </c>
       <c r="E56" s="31" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="F56" s="31" t="s">
-        <v>64</v>
+        <v>82</v>
       </c>
       <c r="G56" s="31" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="57" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C57" s="31" t="s">
-        <v>142</v>
+        <v>175</v>
       </c>
       <c r="D57" s="31" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E57" s="31" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="F57" s="31" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="G57" s="31" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="58" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C58" s="31" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="D58" s="31" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E58" s="31" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="F58" s="31" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="G58" s="31" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="59" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C59" s="31" t="s">
-        <v>190</v>
+        <v>134</v>
       </c>
       <c r="D59" s="31" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E59" s="31" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="F59" s="31" t="s">
-        <v>86</v>
+        <v>64</v>
       </c>
       <c r="G59" s="31" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="60" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C60" s="31" t="s">
-        <v>139</v>
+        <v>177</v>
       </c>
       <c r="D60" s="31" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E60" s="31" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="F60" s="31" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="G60" s="31" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="61" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C61" s="31" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D61" s="31" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E61" s="31" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="F61" s="31" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="G61" s="31" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="62" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C62" s="31" t="s">
-        <v>195</v>
+        <v>184</v>
       </c>
       <c r="D62" s="31" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="E62" s="31" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="F62" s="31" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="G62" s="31" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="63" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C63" s="31" t="s">
-        <v>194</v>
+        <v>35</v>
       </c>
       <c r="D63" s="31" t="s">
-        <v>69</v>
+        <v>35</v>
       </c>
       <c r="E63" s="31" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="F63" s="31" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="G63" s="31" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="64" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C64" s="31" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D64" s="31" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E64" s="31" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="F64" s="31" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="G64" s="31" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="65" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C65" s="31" t="s">
-        <v>36</v>
+        <v>150</v>
       </c>
       <c r="D65" s="31" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E65" s="31" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="F65" s="31" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="G65" s="31" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="66" spans="3:7" x14ac:dyDescent="0.4">
-      <c r="C66" s="31" t="s">
-        <v>156</v>
-      </c>
-      <c r="D66" s="31" t="s">
-        <v>37</v>
-      </c>
-      <c r="E66" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="F66" s="31" t="s">
-        <v>83</v>
-      </c>
-      <c r="G66" s="31" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="67" spans="3:7" ht="14.25" x14ac:dyDescent="0.45">
-      <c r="C67"/>
-      <c r="D67"/>
-      <c r="E67"/>
-      <c r="F67"/>
-      <c r="G67"/>
+        <v>59</v>
+      </c>
+    </row>
+    <row r="66" spans="3:7" ht="14.25" x14ac:dyDescent="0.45">
+      <c r="C66"/>
+      <c r="D66"/>
+      <c r="E66"/>
+      <c r="F66"/>
+      <c r="G66"/>
+    </row>
+    <row r="67" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="C67" s="31" t="s">
+        <v>66</v>
+      </c>
+      <c r="D67" s="31" t="s">
+        <v>67</v>
+      </c>
+      <c r="E67" s="31" t="s">
+        <v>58</v>
+      </c>
+      <c r="F67" s="31" t="s">
+        <v>82</v>
+      </c>
+      <c r="G67" s="31" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="68" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C68" s="31" t="s">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="D68" s="31" t="s">
-        <v>71</v>
+        <v>46</v>
       </c>
       <c r="E68" s="31" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="F68" s="31" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="G68" s="31" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="69" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C69" s="31" t="s">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="D69" s="31" t="s">
-        <v>46</v>
+        <v>69</v>
       </c>
       <c r="E69" s="31" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="F69" s="31" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="G69" s="31" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
     </row>
     <row r="70" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C70" s="31" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D70" s="31" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E70" s="31" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="F70" s="31" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="G70" s="31" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="71" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C71" s="31" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D71" s="31" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
       <c r="E71" s="31" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="F71" s="31" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="G71" s="31" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="72" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C72" s="31" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D72" s="31" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="E72" s="31" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="F72" s="31" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="G72" s="31" t="s">
         <v>59</v>
@@ -23724,104 +23703,87 @@
     </row>
     <row r="73" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C73" s="31" t="s">
-        <v>77</v>
+        <v>42</v>
       </c>
       <c r="D73" s="31" t="s">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="E73" s="31" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="F73" s="31" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="G73" s="31" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="74" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C74" s="31" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D74" s="31" t="s">
+        <v>74</v>
+      </c>
+      <c r="E74" s="31" t="s">
+        <v>58</v>
+      </c>
+      <c r="F74" s="31" t="s">
+        <v>79</v>
+      </c>
+      <c r="G74" s="31" t="s">
         <v>59</v>
-      </c>
-      <c r="E74" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="F74" s="31" t="s">
-        <v>83</v>
-      </c>
-      <c r="G74" s="31" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="75" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C75" s="31" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D75" s="31" t="s">
-        <v>78</v>
+        <v>57</v>
       </c>
       <c r="E75" s="31" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="F75" s="31" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="G75" s="31" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="76" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C76" s="31" t="s">
-        <v>43</v>
+        <v>75</v>
       </c>
       <c r="D76" s="31" t="s">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="E76" s="31" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="F76" s="31" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="G76" s="31" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="77" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C77" s="31" t="s">
+        <v>77</v>
+      </c>
+      <c r="D77" s="31" t="s">
+        <v>78</v>
+      </c>
+      <c r="E77" s="31" t="s">
+        <v>58</v>
+      </c>
+      <c r="F77" s="31" t="s">
         <v>79</v>
       </c>
-      <c r="D77" s="31" t="s">
-        <v>80</v>
-      </c>
-      <c r="E77" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="F77" s="31" t="s">
-        <v>83</v>
-      </c>
       <c r="G77" s="31" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="78" spans="3:7" x14ac:dyDescent="0.4">
-      <c r="C78" s="31" t="s">
-        <v>81</v>
-      </c>
-      <c r="D78" s="31" t="s">
-        <v>82</v>
-      </c>
-      <c r="E78" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="F78" s="31" t="s">
-        <v>83</v>
-      </c>
-      <c r="G78" s="31" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>

--- a/1XW_TradeBlotter_Web.xlsx
+++ b/1XW_TradeBlotter_Web.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0a601c1c2ba3d9f4/Trading/The Strategy Project/1XW Website/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="302" documentId="13_ncr:1_{6F5069F1-F0E7-4440-AA6D-4AFA11BBED1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9212F668-2DA2-444F-804D-06D50913B085}"/>
+  <xr:revisionPtr revIDLastSave="304" documentId="13_ncr:1_{6F5069F1-F0E7-4440-AA6D-4AFA11BBED1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{26785960-8DE8-4AD5-918A-DBE38C29D1C8}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="22695" windowHeight="14476" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -117,7 +117,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1165" uniqueCount="326">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1166" uniqueCount="327">
   <si>
     <t>WEEK</t>
   </si>
@@ -1108,6 +1108,9 @@
   </si>
   <si>
     <t>Long CL Put Spread</t>
+  </si>
+  <si>
+    <t>Crytpto</t>
   </si>
 </sst>
 </file>
@@ -3472,7 +3475,9 @@
         <v>5.5142806320098714E-3</v>
       </c>
       <c r="D6" s="3"/>
-      <c r="E6" s="47"/>
+      <c r="E6" s="47" t="s">
+        <v>326</v>
+      </c>
       <c r="F6" s="47"/>
       <c r="G6" s="47"/>
       <c r="H6" s="28"/>
@@ -3718,7 +3723,7 @@
         <v>190</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>123</v>
+        <v>326</v>
       </c>
       <c r="F19" s="10" t="s">
         <v>303</v>

--- a/1XW_TradeBlotter_Web.xlsx
+++ b/1XW_TradeBlotter_Web.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0a601c1c2ba3d9f4/Trading/The Strategy Project/1XW Website/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="304" documentId="13_ncr:1_{6F5069F1-F0E7-4440-AA6D-4AFA11BBED1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{26785960-8DE8-4AD5-918A-DBE38C29D1C8}"/>
+  <xr:revisionPtr revIDLastSave="331" documentId="13_ncr:1_{6F5069F1-F0E7-4440-AA6D-4AFA11BBED1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{62B6AF25-C9C3-4B1F-9FCF-2A167A5EEF45}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="22695" windowHeight="14476" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -117,7 +117,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1166" uniqueCount="327">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1198" uniqueCount="332">
   <si>
     <t>WEEK</t>
   </si>
@@ -1074,43 +1074,58 @@
     <t>Retrace to the pre breakout price region ~$3000. Inside week + weekly up</t>
   </si>
   <si>
+    <t>P</t>
+  </si>
+  <si>
+    <t>LO</t>
+  </si>
+  <si>
+    <t>Loaded 36 contracts from Symbols sheet.</t>
+  </si>
+  <si>
+    <t>FOP</t>
+  </si>
+  <si>
+    <t>LOM6 P7500</t>
+  </si>
+  <si>
+    <t>LOM6 P5500</t>
+  </si>
+  <si>
+    <t>Long ETH Spot</t>
+  </si>
+  <si>
+    <t>Long CC Futures</t>
+  </si>
+  <si>
+    <t>Long CL Put Spread</t>
+  </si>
+  <si>
+    <t>Crytpto</t>
+  </si>
+  <si>
+    <t>NO_DATA</t>
+  </si>
+  <si>
+    <t>ERROR</t>
+  </si>
+  <si>
+    <t>Loop error: (-2147352567, 'Exception occurred.', (0, None, None, None, 0, -2146777998), None). Reconnecting in 2s.</t>
+  </si>
+  <si>
+    <t>Reconnected to TWS.</t>
+  </si>
+  <si>
     <t>Close</t>
   </si>
   <si>
-    <t>P</t>
-  </si>
-  <si>
-    <t>LO</t>
-  </si>
-  <si>
-    <t>CLM6P75260514</t>
-  </si>
-  <si>
-    <t>CLM6P55260514</t>
-  </si>
-  <si>
-    <t>Loaded 36 contracts from Symbols sheet.</t>
-  </si>
-  <si>
-    <t>FOP</t>
-  </si>
-  <si>
-    <t>LOM6 P7500</t>
-  </si>
-  <si>
-    <t>LOM6 P5500</t>
-  </si>
-  <si>
-    <t>Long ETH Spot</t>
-  </si>
-  <si>
-    <t>Long CC Futures</t>
-  </si>
-  <si>
-    <t>Long CL Put Spread</t>
-  </si>
-  <si>
-    <t>Crytpto</t>
+    <t>CL JUN26 55 P</t>
+  </si>
+  <si>
+    <t>CLM6</t>
+  </si>
+  <si>
+    <t>CL JUN26 75 P</t>
   </si>
 </sst>
 </file>
@@ -1132,7 +1147,7 @@
     <numFmt numFmtId="174" formatCode="#,##0.00_-;\-#,##0.00_-;_-;_-@_-"/>
     <numFmt numFmtId="175" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="36" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1277,8 +1292,128 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri Light"/>
+      <family val="2"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C5700"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1303,8 +1438,181 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -1336,11 +1644,159 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="24" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="27" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="10" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="35" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="35" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="35" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="35" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="35" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="35" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="97">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -1587,10 +2043,51 @@
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="44">
+    <cellStyle name="20% - Accent1" xfId="21" builtinId="30" customBuiltin="1"/>
+    <cellStyle name="20% - Accent2" xfId="25" builtinId="34" customBuiltin="1"/>
+    <cellStyle name="20% - Accent3" xfId="29" builtinId="38" customBuiltin="1"/>
+    <cellStyle name="20% - Accent4" xfId="33" builtinId="42" customBuiltin="1"/>
+    <cellStyle name="20% - Accent5" xfId="37" builtinId="46" customBuiltin="1"/>
+    <cellStyle name="20% - Accent6" xfId="41" builtinId="50" customBuiltin="1"/>
+    <cellStyle name="40% - Accent1" xfId="22" builtinId="31" customBuiltin="1"/>
+    <cellStyle name="40% - Accent2" xfId="26" builtinId="35" customBuiltin="1"/>
+    <cellStyle name="40% - Accent3" xfId="30" builtinId="39" customBuiltin="1"/>
+    <cellStyle name="40% - Accent4" xfId="34" builtinId="43" customBuiltin="1"/>
+    <cellStyle name="40% - Accent5" xfId="38" builtinId="47" customBuiltin="1"/>
+    <cellStyle name="40% - Accent6" xfId="42" builtinId="51" customBuiltin="1"/>
+    <cellStyle name="60% - Accent1" xfId="23" builtinId="32" customBuiltin="1"/>
+    <cellStyle name="60% - Accent2" xfId="27" builtinId="36" customBuiltin="1"/>
+    <cellStyle name="60% - Accent3" xfId="31" builtinId="40" customBuiltin="1"/>
+    <cellStyle name="60% - Accent4" xfId="35" builtinId="44" customBuiltin="1"/>
+    <cellStyle name="60% - Accent5" xfId="39" builtinId="48" customBuiltin="1"/>
+    <cellStyle name="60% - Accent6" xfId="43" builtinId="52" customBuiltin="1"/>
+    <cellStyle name="Accent1" xfId="20" builtinId="29" customBuiltin="1"/>
+    <cellStyle name="Accent2" xfId="24" builtinId="33" customBuiltin="1"/>
+    <cellStyle name="Accent3" xfId="28" builtinId="37" customBuiltin="1"/>
+    <cellStyle name="Accent4" xfId="32" builtinId="41" customBuiltin="1"/>
+    <cellStyle name="Accent5" xfId="36" builtinId="45" customBuiltin="1"/>
+    <cellStyle name="Accent6" xfId="40" builtinId="49" customBuiltin="1"/>
+    <cellStyle name="Bad" xfId="9" builtinId="27" customBuiltin="1"/>
+    <cellStyle name="Calculation" xfId="13" builtinId="22" customBuiltin="1"/>
+    <cellStyle name="Check Cell" xfId="15" builtinId="23" customBuiltin="1"/>
     <cellStyle name="Comma" xfId="2" builtinId="3"/>
+    <cellStyle name="Explanatory Text" xfId="18" builtinId="53" customBuiltin="1"/>
+    <cellStyle name="Good" xfId="8" builtinId="26" customBuiltin="1"/>
+    <cellStyle name="Heading 1" xfId="4" builtinId="16" customBuiltin="1"/>
+    <cellStyle name="Heading 2" xfId="5" builtinId="17" customBuiltin="1"/>
+    <cellStyle name="Heading 3" xfId="6" builtinId="18" customBuiltin="1"/>
+    <cellStyle name="Heading 4" xfId="7" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="Input" xfId="11" builtinId="20" customBuiltin="1"/>
+    <cellStyle name="Linked Cell" xfId="14" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="Neutral" xfId="10" builtinId="28" customBuiltin="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Note" xfId="17" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="Output" xfId="12" builtinId="21" customBuiltin="1"/>
     <cellStyle name="Per cent" xfId="1" builtinId="5"/>
+    <cellStyle name="Title" xfId="3" builtinId="15" customBuiltin="1"/>
+    <cellStyle name="Total" xfId="19" builtinId="25" customBuiltin="1"/>
+    <cellStyle name="Warning Text" xfId="16" builtinId="11" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="12">
     <dxf>
@@ -1778,7 +2275,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>5.5142806320098714E-3</c:v>
+                  <c:v>1.0025060632009808E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1932,7 +2429,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>5.5142806320098714E-3</c:v>
+                  <c:v>1.0025060632009808E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2323,7 +2820,7 @@
                   <c:v>1000</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1005.5142806320099</c:v>
+                  <c:v>1010.0250606320099</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2739,10 +3236,10 @@
                   <c:v>5.2224063201000703E-4</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.9133306320099361E-3</c:v>
+                  <c:v>6.0033306320099733E-3</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>4.513330632009982E-3</c:v>
+                  <c:v>8.7491106320098933E-3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3393,7 +3890,7 @@
       </c>
       <c r="C1" s="79">
         <f ca="1">TODAY()</f>
-        <v>46095</v>
+        <v>46098</v>
       </c>
     </row>
     <row r="2" spans="2:11" x14ac:dyDescent="0.4">
@@ -3401,7 +3898,7 @@
         <v>108</v>
       </c>
       <c r="C2" s="37" t="s">
-        <v>314</v>
+        <v>328</v>
       </c>
       <c r="E2" s="47" t="s">
         <v>123</v>
@@ -3418,7 +3915,7 @@
       </c>
       <c r="C3" s="28">
         <f ca="1">OFFSET(NAV!B1,MATCH(C1,NAV!B:B,1),8)</f>
-        <v>1005514.2806320098</v>
+        <v>1010025.0606320099</v>
       </c>
       <c r="E3" s="47" t="s">
         <v>124</v>
@@ -3435,7 +3932,7 @@
       </c>
       <c r="C4" s="28">
         <f>SUM(N18:N1012)</f>
-        <v>5514.2806320099007</v>
+        <v>10025.060632009898</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="47" t="s">
@@ -3453,7 +3950,7 @@
       </c>
       <c r="C5" s="3">
         <f ca="1">OFFSET(NAV!B1,MATCH(C1,NAV!B:B,1),11)</f>
-        <v>5.5142806320098714E-3</v>
+        <v>1.0025060632009808E-2</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="47" t="s">
@@ -3472,11 +3969,11 @@
       </c>
       <c r="C6" s="3">
         <f ca="1">OFFSET(NAV!B1,MATCH(C1,NAV!B:B,1),12)</f>
-        <v>5.5142806320098714E-3</v>
+        <v>1.0025060632009808E-2</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="47" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="F6" s="47"/>
       <c r="G6" s="47"/>
@@ -3489,11 +3986,11 @@
       </c>
       <c r="C7" s="28">
         <f>Cash_Mgmt!H13</f>
-        <v>35399.049999999952</v>
+        <v>35124.049999999952</v>
       </c>
       <c r="D7" s="3">
         <f ca="1">C7/C3</f>
-        <v>3.5204920190442343E-2</v>
+        <v>3.4775424263256936E-2</v>
       </c>
       <c r="E7" s="47"/>
       <c r="F7" s="47"/>
@@ -3507,11 +4004,11 @@
       </c>
       <c r="C8" s="28">
         <f>C4+C7</f>
-        <v>40913.330632009849</v>
+        <v>45149.110632009848</v>
       </c>
       <c r="D8" s="3">
         <f ca="1">C5+D7</f>
-        <v>4.0719200822452215E-2</v>
+        <v>4.4800484895266744E-2</v>
       </c>
       <c r="G8" s="47"/>
       <c r="H8" s="51"/>
@@ -3523,11 +4020,11 @@
       </c>
       <c r="C9" s="28">
         <f t="array" ref="C9">SUM((F19:F112="Futures")*(M19:M112))</f>
-        <v>99450</v>
+        <v>102540</v>
       </c>
       <c r="D9" s="3">
         <f ca="1">C9/$C$3</f>
-        <v>9.8904612212460385E-2</v>
+        <v>0.10152223345412534</v>
       </c>
       <c r="E9" s="47"/>
       <c r="F9" s="47"/>
@@ -3555,11 +4052,11 @@
       </c>
       <c r="C11" s="28">
         <f t="array" ref="C11">SUM((F19:F212="Put")*(M19:M212))</f>
-        <v>9600</v>
+        <v>12330</v>
       </c>
       <c r="D11" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>9.5473532150791331E-3</v>
+        <v>1.2207617890475574E-2</v>
       </c>
     </row>
     <row r="12" spans="2:11" x14ac:dyDescent="0.4">
@@ -3568,11 +4065,11 @@
       </c>
       <c r="C12" s="28" cm="1">
         <f t="array" ref="C12">SUM((PLB!G4:G999="O")*(PLB!E4:E999))</f>
-        <v>17233.333333333332</v>
+        <v>18600</v>
       </c>
       <c r="D12" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>1.7138825042346914E-2</v>
+        <v>1.841538465229892E-2</v>
       </c>
     </row>
     <row r="13" spans="2:11" x14ac:dyDescent="0.4">
@@ -3581,11 +4078,11 @@
       </c>
       <c r="C13" s="28">
         <f t="array" ref="C13">SUM((PLB!G4:G999="O")*(PLB!D4:D999))</f>
-        <v>3991.0899999999965</v>
+        <v>8226.8699999999935</v>
       </c>
       <c r="D13" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>3.9692027024135559E-3</v>
+        <v>8.1452137384117364E-3</v>
       </c>
       <c r="F13" s="59"/>
       <c r="G13" s="59"/>
@@ -3596,11 +4093,11 @@
       </c>
       <c r="C14" s="28">
         <f>C12+C13</f>
-        <v>21224.423333333329</v>
+        <v>26826.869999999995</v>
       </c>
       <c r="D14" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>2.110802774476047E-2</v>
+        <v>2.6560598390710656E-2</v>
       </c>
     </row>
     <row r="17" spans="2:28" x14ac:dyDescent="0.4">
@@ -3697,7 +4194,7 @@
       <c r="M18" s="12"/>
       <c r="N18" s="95">
         <f>Cash_Mgmt!G13</f>
-        <v>1000.9499999999098</v>
+        <v>1275.9499999999098</v>
       </c>
       <c r="O18" s="12"/>
       <c r="P18" s="12"/>
@@ -3723,7 +4220,7 @@
         <v>190</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="F19" s="10" t="s">
         <v>303</v>
@@ -3797,7 +4294,7 @@
       </c>
       <c r="Z19" s="35">
         <f>IF(C$2="Last",IF(ISNUMBER(VLOOKUP(B19,Prices!A:L,8,0)),VLOOKUP(B19,Prices!A:L,8,0),0),IF(ISNUMBER(VLOOKUP(B19,Prices!A:L,12,0)),VLOOKUP(B19,Prices!A:L,12,0),0))</f>
-        <v>2102.25</v>
+        <v>2329.3000000000002</v>
       </c>
       <c r="AB19" s="29"/>
     </row>
@@ -3838,15 +4335,15 @@
       </c>
       <c r="L20" s="29">
         <f t="shared" ref="L20" si="8">IF(I20=0,IF(H20&gt;0,X20,Y20),Z20)</f>
-        <v>3315</v>
+        <v>3418</v>
       </c>
       <c r="M20" s="28">
         <f t="shared" ref="M20" si="9">I20*J20*L20</f>
-        <v>99450</v>
+        <v>102540</v>
       </c>
       <c r="N20" s="95">
         <f t="array" ref="N20">-SUM((Trades!T$2:T$9999=Blotter!C20)*(Trades!U$2:U$9999=Blotter!B20)*(Trades!V$2:V$9999)*(Trades!W$2:W$9999))*J20+SUM((Trades!T$2:T$9999=Blotter!C20)*(Trades!U$2:U$9999=Blotter!B20)*(Trades!X$2:X$9999))+(L20*I20)*J20</f>
-        <v>2391.0899999999965</v>
+        <v>5481.0899999999965</v>
       </c>
       <c r="O20" s="29">
         <f>VLOOKUP(D20,Multiplier!B:H,3,0)</f>
@@ -3862,11 +4359,11 @@
       </c>
       <c r="S20" s="29">
         <f>IF(OR(F20="Futures",F20="Spot"),IF(I20=0,0,IF(I20&gt;0,L20-O20,L20+O20)),0)</f>
-        <v>3110</v>
+        <v>3213</v>
       </c>
       <c r="T20" s="3">
         <f t="shared" ref="T20" si="11">IF(S20&gt;0,IF(ISNUMBER(S20/L20-1),S20/L20-1,0),0)</f>
-        <v>-6.1840120663650078E-2</v>
+        <v>-5.9976594499707381E-2</v>
       </c>
       <c r="U20" s="29">
         <f t="shared" ref="U20" si="12">IF(OR(F20="Futures",F20="Stocks"),IF(I20=0,0,IF(I20&gt;0,K20-P20,K20+P20)),0)</f>
@@ -3874,7 +4371,7 @@
       </c>
       <c r="V20" s="3">
         <f t="shared" ref="V20" si="13">IF(U20&gt;0,IF(ISNUMBER(U20/L20-1),U20/L20-1,0),0)</f>
-        <v>-0.11454087481146302</v>
+        <v>-0.14122381509654769</v>
       </c>
       <c r="X20" s="34">
         <f t="array" ref="X20">IF(ISNUMBER(SUM((Trades!T$2:T$9999=Blotter!C20)*(Trades!U$2:U$9999=Blotter!B20)*(Trades!W$2:W$9999)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0))/SUM((Trades!T$2:T$9999=Blotter!C20)*(Trades!U$2:U$9999=Blotter!B20)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0))),SUM((Trades!T$2:T$9999=Blotter!C20)*(Trades!U$2:U$9999=Blotter!B20)*(Trades!W$2:W$9999)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0))/SUM((Trades!T$2:T$9999=Blotter!C20)*(Trades!U$2:U$9999=Blotter!B20)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0)),0)</f>
@@ -3886,13 +4383,13 @@
       </c>
       <c r="Z20" s="35">
         <f>IF(C$2="Last",IF(ISNUMBER(VLOOKUP(B20,Prices!A:L,8,0)),VLOOKUP(B20,Prices!A:L,8,0),0),IF(ISNUMBER(VLOOKUP(B20,Prices!A:L,12,0)),VLOOKUP(B20,Prices!A:L,12,0),0))</f>
-        <v>3315</v>
+        <v>3418</v>
       </c>
       <c r="AB20" s="29"/>
     </row>
     <row r="21" spans="2:28" x14ac:dyDescent="0.4">
       <c r="B21" s="9" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C21" s="10">
         <v>3</v>
@@ -3911,11 +4408,11 @@
         <v>4</v>
       </c>
       <c r="H21" s="11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I21" s="28">
         <f t="array" ref="I21">ROUND(SUM((Trades!V$2:V$9999)*(Trades!U$2:U$9999=Blotter!B21)*(Trades!$T$2:T$9999=Blotter!C21)),8)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J21" s="28">
         <f>VLOOKUP(D21,Multiplier!B:D,2,0)</f>
@@ -3923,31 +4420,31 @@
       </c>
       <c r="K21" s="29">
         <f t="shared" ref="K21:K22" si="14">L21-N21/(H21*J21)</f>
-        <v>5</v>
+        <v>3.5423700000000009</v>
       </c>
       <c r="L21" s="29">
         <f t="shared" ref="L21:L22" si="15">IF(I21=0,IF(H21&gt;0,X21,Y21),Z21)</f>
-        <v>5.35</v>
+        <v>4.63</v>
       </c>
       <c r="M21" s="28">
         <f t="shared" ref="M21:M22" si="16">I21*J21*L21</f>
-        <v>10700</v>
+        <v>13890</v>
       </c>
       <c r="N21" s="95">
         <f t="array" ref="N21">-SUM((Trades!T$2:T$9999=Blotter!C21)*(Trades!U$2:U$9999=Blotter!B21)*(Trades!V$2:V$9999)*(Trades!W$2:W$9999))*J21+SUM((Trades!T$2:T$9999=Blotter!C21)*(Trades!U$2:U$9999=Blotter!B21)*(Trades!X$2:X$9999))+(L21*I21)*J21</f>
-        <v>700</v>
+        <v>3262.8899999999976</v>
       </c>
       <c r="O21" s="29">
         <f>VLOOKUP(D21,Multiplier!B:H,3,0)</f>
         <v>2.1</v>
       </c>
       <c r="P21" s="27">
-        <v>5.1166666666666663</v>
+        <v>3.54</v>
       </c>
       <c r="Q21" s="27"/>
       <c r="R21" s="28">
         <f t="shared" ref="R21:R22" si="17">(1-Q21)*P21*J21*H21</f>
-        <v>10233.333333333332</v>
+        <v>10620</v>
       </c>
       <c r="S21" s="29">
         <f t="shared" ref="S21:S22" si="18">IF(OR(F21="Futures",F21="Spot"),IF(I21=0,0,IF(I21&gt;0,L21-O21,L21+O21)),0)</f>
@@ -3971,17 +4468,17 @@
       </c>
       <c r="Y21" s="34">
         <f t="array" ref="Y21">IF(ISNUMBER(SUM((Trades!T$2:T$9999=Blotter!C21)*(Trades!U$2:U$9999=Blotter!B21)*(Trades!W$2:W$9999)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&gt;0))/SUM((Trades!T$2:T$9999=Blotter!C21)*(Trades!U$2:U$9999=Blotter!B21)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&gt;0))),SUM((Trades!T$2:T$9999=Blotter!C21)*(Trades!U$2:U$9999=Blotter!B21)*(Trades!W$2:W$9999)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&gt;0))/SUM((Trades!T$2:T$9999=Blotter!C21)*(Trades!U$2:U$9999=Blotter!B21)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&gt;0)),0)</f>
-        <v>5</v>
+        <v>3.5400000000000005</v>
       </c>
       <c r="Z21" s="35">
         <f>IF(C$2="Last",IF(ISNUMBER(VLOOKUP(B21,Prices!A:L,8,0)),VLOOKUP(B21,Prices!A:L,8,0),0),IF(ISNUMBER(VLOOKUP(B21,Prices!A:L,12,0)),VLOOKUP(B21,Prices!A:L,12,0),0))</f>
-        <v>5.35</v>
+        <v>4.63</v>
       </c>
       <c r="AB21" s="29"/>
     </row>
     <row r="22" spans="2:28" x14ac:dyDescent="0.4">
       <c r="B22" s="9" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C22" s="10">
         <v>3</v>
@@ -4000,11 +4497,11 @@
         <v>4</v>
       </c>
       <c r="H22" s="11">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="I22" s="28">
         <f t="array" ref="I22">ROUND(SUM((Trades!V$2:V$9999)*(Trades!U$2:U$9999=Blotter!B22)*(Trades!$T$2:T$9999=Blotter!C22)),8)</f>
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="J22" s="28">
         <f>VLOOKUP(D22,Multiplier!B:D,2,0)</f>
@@ -4012,31 +4509,31 @@
       </c>
       <c r="K22" s="29">
         <f t="shared" si="14"/>
-        <v>1</v>
+        <v>0.34762999999999999</v>
       </c>
       <c r="L22" s="29">
         <f t="shared" si="15"/>
-        <v>0.55000000000000004</v>
+        <v>0.52</v>
       </c>
       <c r="M22" s="28">
         <f t="shared" si="16"/>
-        <v>-1100</v>
+        <v>-1560</v>
       </c>
       <c r="N22" s="95">
         <f t="array" ref="N22">-SUM((Trades!T$2:T$9999=Blotter!C22)*(Trades!U$2:U$9999=Blotter!B22)*(Trades!V$2:V$9999)*(Trades!W$2:W$9999))*J22+SUM((Trades!T$2:T$9999=Blotter!C22)*(Trades!U$2:U$9999=Blotter!B22)*(Trades!X$2:X$9999))+(L22*I22)*J22</f>
-        <v>900</v>
+        <v>-517.11000000000013</v>
       </c>
       <c r="O22" s="29">
         <f>VLOOKUP(D22,Multiplier!B:H,3,0)</f>
         <v>2.1</v>
       </c>
       <c r="P22" s="27">
-        <v>1</v>
+        <v>0.34</v>
       </c>
       <c r="Q22" s="27"/>
       <c r="R22" s="28">
         <f t="shared" si="17"/>
-        <v>-2000</v>
+        <v>-1020</v>
       </c>
       <c r="S22" s="29">
         <f t="shared" si="18"/>
@@ -4056,7 +4553,7 @@
       </c>
       <c r="X22" s="34">
         <f t="array" ref="X22">IF(ISNUMBER(SUM((Trades!T$2:T$9999=Blotter!C22)*(Trades!U$2:U$9999=Blotter!B22)*(Trades!W$2:W$9999)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0))/SUM((Trades!T$2:T$9999=Blotter!C22)*(Trades!U$2:U$9999=Blotter!B22)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0))),SUM((Trades!T$2:T$9999=Blotter!C22)*(Trades!U$2:U$9999=Blotter!B22)*(Trades!W$2:W$9999)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0))/SUM((Trades!T$2:T$9999=Blotter!C22)*(Trades!U$2:U$9999=Blotter!B22)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0)),0)</f>
-        <v>1</v>
+        <v>0.34999999999999992</v>
       </c>
       <c r="Y22" s="34">
         <f t="array" ref="Y22">IF(ISNUMBER(SUM((Trades!T$2:T$9999=Blotter!C22)*(Trades!U$2:U$9999=Blotter!B22)*(Trades!W$2:W$9999)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&gt;0))/SUM((Trades!T$2:T$9999=Blotter!C22)*(Trades!U$2:U$9999=Blotter!B22)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&gt;0))),SUM((Trades!T$2:T$9999=Blotter!C22)*(Trades!U$2:U$9999=Blotter!B22)*(Trades!W$2:W$9999)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&gt;0))/SUM((Trades!T$2:T$9999=Blotter!C22)*(Trades!U$2:U$9999=Blotter!B22)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&gt;0)),0)</f>
@@ -4064,7 +4561,7 @@
       </c>
       <c r="Z22" s="35">
         <f>IF(C$2="Last",IF(ISNUMBER(VLOOKUP(B22,Prices!A:L,8,0)),VLOOKUP(B22,Prices!A:L,8,0),0),IF(ISNUMBER(VLOOKUP(B22,Prices!A:L,12,0)),VLOOKUP(B22,Prices!A:L,12,0),0))</f>
-        <v>0.55000000000000004</v>
+        <v>0.52</v>
       </c>
       <c r="AB22" s="29"/>
     </row>
@@ -5797,27 +6294,31 @@
         <v>59</v>
       </c>
       <c r="H2" s="91">
-        <v>-1</v>
+        <v>6720.5</v>
       </c>
       <c r="I2" s="91">
-        <v>-1</v>
+        <v>6720.25</v>
       </c>
       <c r="J2" s="91">
-        <v>-1</v>
+        <v>6720.5</v>
       </c>
       <c r="K2" s="91">
-        <v>-1</v>
+        <v>6720.375</v>
       </c>
       <c r="L2" s="91">
-        <v>6727.25</v>
+        <v>6755.5</v>
       </c>
       <c r="M2" s="91">
-        <v>6735.5</v>
-      </c>
-      <c r="N2" s="91"/>
-      <c r="O2" s="91"/>
+        <v>6751.75</v>
+      </c>
+      <c r="N2" s="91">
+        <v>6752.5</v>
+      </c>
+      <c r="O2" s="91">
+        <v>6715.75</v>
+      </c>
       <c r="P2" s="91">
-        <v>0</v>
+        <v>69906</v>
       </c>
       <c r="Q2" s="91"/>
       <c r="R2" s="91"/>
@@ -5825,7 +6326,7 @@
       <c r="T2" s="91"/>
       <c r="U2" s="91"/>
       <c r="V2" s="85">
-        <v>46095.373206018521</v>
+        <v>46098.337939814817</v>
       </c>
       <c r="W2" s="81" t="s">
         <v>264</v>
@@ -5857,27 +6358,31 @@
         <v>59</v>
       </c>
       <c r="H3" s="91">
-        <v>-1</v>
+        <v>24748.75</v>
       </c>
       <c r="I3" s="91">
-        <v>-1</v>
+        <v>24747.25</v>
       </c>
       <c r="J3" s="91">
-        <v>-1</v>
+        <v>24748.25</v>
       </c>
       <c r="K3" s="91">
-        <v>-1</v>
+        <v>24747.75</v>
       </c>
       <c r="L3" s="91">
-        <v>24773.5</v>
+        <v>24891.25</v>
       </c>
       <c r="M3" s="91">
-        <v>24783.5</v>
-      </c>
-      <c r="N3" s="91"/>
-      <c r="O3" s="91"/>
+        <v>24870</v>
+      </c>
+      <c r="N3" s="91">
+        <v>24882</v>
+      </c>
+      <c r="O3" s="91">
+        <v>24728.25</v>
+      </c>
       <c r="P3" s="91">
-        <v>0</v>
+        <v>39668</v>
       </c>
       <c r="Q3" s="91"/>
       <c r="R3" s="91"/>
@@ -5885,7 +6390,7 @@
       <c r="T3" s="91"/>
       <c r="U3" s="91"/>
       <c r="V3" s="85">
-        <v>46095.373206018521</v>
+        <v>46098.337939814817</v>
       </c>
       <c r="W3" s="81" t="s">
         <v>264</v>
@@ -5917,27 +6422,31 @@
         <v>59</v>
       </c>
       <c r="H4" s="91">
-        <v>-1</v>
+        <v>2494.3000000000002</v>
       </c>
       <c r="I4" s="91">
-        <v>-1</v>
+        <v>2493.9</v>
       </c>
       <c r="J4" s="91">
-        <v>-1</v>
+        <v>2494.3000000000002</v>
       </c>
       <c r="K4" s="91">
-        <v>-1</v>
+        <v>2494.1000000000004</v>
       </c>
       <c r="L4" s="91">
-        <v>2507</v>
+        <v>2520.9</v>
       </c>
       <c r="M4" s="91">
-        <v>2511.5</v>
-      </c>
-      <c r="N4" s="91"/>
-      <c r="O4" s="91"/>
+        <v>2514.4</v>
+      </c>
+      <c r="N4" s="91">
+        <v>2518.1999999999998</v>
+      </c>
+      <c r="O4" s="91">
+        <v>2490.9</v>
+      </c>
       <c r="P4" s="91">
-        <v>0</v>
+        <v>12229</v>
       </c>
       <c r="Q4" s="91"/>
       <c r="R4" s="91"/>
@@ -5945,7 +6454,7 @@
       <c r="T4" s="91"/>
       <c r="U4" s="91"/>
       <c r="V4" s="85">
-        <v>46095.373206018521</v>
+        <v>46098.337939814817</v>
       </c>
       <c r="W4" s="81" t="s">
         <v>264</v>
@@ -5976,24 +6485,32 @@
       <c r="G5" s="81" t="s">
         <v>56</v>
       </c>
-      <c r="H5" s="91"/>
+      <c r="H5" s="91">
+        <v>23704</v>
+      </c>
       <c r="I5" s="91">
-        <v>-1</v>
+        <v>23702</v>
       </c>
       <c r="J5" s="91">
-        <v>-1</v>
+        <v>23710</v>
       </c>
       <c r="K5" s="91">
-        <v>-1</v>
+        <v>23706</v>
       </c>
       <c r="L5" s="91">
-        <v>23796</v>
-      </c>
-      <c r="M5" s="91"/>
-      <c r="N5" s="91"/>
-      <c r="O5" s="91"/>
+        <v>23787</v>
+      </c>
+      <c r="M5" s="91">
+        <v>23800</v>
+      </c>
+      <c r="N5" s="91">
+        <v>23804</v>
+      </c>
+      <c r="O5" s="91">
+        <v>23636</v>
+      </c>
       <c r="P5" s="91">
-        <v>0</v>
+        <v>113</v>
       </c>
       <c r="Q5" s="91"/>
       <c r="R5" s="91"/>
@@ -6001,7 +6518,7 @@
       <c r="T5" s="91"/>
       <c r="U5" s="91"/>
       <c r="V5" s="85">
-        <v>46095.373206018521</v>
+        <v>46098.337939814817</v>
       </c>
       <c r="W5" s="81" t="s">
         <v>264</v>
@@ -6033,27 +6550,31 @@
         <v>57</v>
       </c>
       <c r="H6" s="91">
-        <v>0</v>
+        <v>53400</v>
       </c>
       <c r="I6" s="91">
-        <v>0</v>
+        <v>53395</v>
       </c>
       <c r="J6" s="91">
-        <v>0</v>
+        <v>53405</v>
       </c>
       <c r="K6" s="91">
-        <v>0</v>
+        <v>53400</v>
       </c>
       <c r="L6" s="91">
-        <v>53570</v>
+        <v>54275</v>
       </c>
       <c r="M6" s="91">
-        <v>53540</v>
-      </c>
-      <c r="N6" s="91"/>
-      <c r="O6" s="91"/>
+        <v>54180</v>
+      </c>
+      <c r="N6" s="91">
+        <v>54255</v>
+      </c>
+      <c r="O6" s="91">
+        <v>53245</v>
+      </c>
       <c r="P6" s="91">
-        <v>0</v>
+        <v>4274</v>
       </c>
       <c r="Q6" s="91"/>
       <c r="R6" s="91"/>
@@ -6061,7 +6582,7 @@
       <c r="T6" s="91"/>
       <c r="U6" s="91"/>
       <c r="V6" s="85">
-        <v>46095.373206018521</v>
+        <v>46098.337939814817</v>
       </c>
       <c r="W6" s="81" t="s">
         <v>264</v>
@@ -6092,39 +6613,25 @@
       <c r="G7" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="H7" s="93">
-        <v>-1</v>
-      </c>
-      <c r="I7" s="93">
-        <v>-1</v>
-      </c>
-      <c r="J7" s="93">
-        <v>-1</v>
-      </c>
-      <c r="K7" s="93">
-        <v>-1</v>
-      </c>
-      <c r="L7" s="93">
-        <v>95.73</v>
-      </c>
-      <c r="M7" s="93">
-        <v>0</v>
-      </c>
+      <c r="H7" s="93"/>
+      <c r="I7" s="93"/>
+      <c r="J7" s="93"/>
+      <c r="K7" s="93"/>
+      <c r="L7" s="93"/>
+      <c r="M7" s="93"/>
       <c r="N7" s="93"/>
       <c r="O7" s="93"/>
-      <c r="P7" s="93">
-        <v>0</v>
-      </c>
+      <c r="P7" s="93"/>
       <c r="Q7" s="93"/>
       <c r="R7" s="93"/>
       <c r="S7" s="93"/>
       <c r="T7" s="93"/>
       <c r="U7" s="93"/>
       <c r="V7" s="92">
-        <v>46095.373206018521</v>
+        <v>46098.337939814817</v>
       </c>
       <c r="W7" s="1" t="s">
-        <v>264</v>
+        <v>324</v>
       </c>
     </row>
     <row r="8" spans="1:32" x14ac:dyDescent="0.4">
@@ -6150,31 +6657,31 @@
         <v>59</v>
       </c>
       <c r="H8" s="93">
-        <v>3.2559999999999998</v>
+        <v>3.1459999999999999</v>
       </c>
       <c r="I8" s="93">
-        <v>-1</v>
+        <v>3.1480000000000001</v>
       </c>
       <c r="J8" s="93">
-        <v>-1</v>
+        <v>3.15</v>
       </c>
       <c r="K8" s="93">
-        <v>-1</v>
+        <v>3.149</v>
       </c>
       <c r="L8" s="93">
-        <v>3.3519999999999999</v>
+        <v>3.1379999999999999</v>
       </c>
       <c r="M8" s="93">
-        <v>0</v>
+        <v>3.1459999999999999</v>
       </c>
       <c r="N8" s="93">
-        <v>3.4119999999999999</v>
+        <v>3.1640000000000001</v>
       </c>
       <c r="O8" s="93">
-        <v>3.2349999999999999</v>
+        <v>3.137</v>
       </c>
       <c r="P8" s="93">
-        <v>35249</v>
+        <v>788</v>
       </c>
       <c r="Q8" s="93"/>
       <c r="R8" s="93"/>
@@ -6182,7 +6689,7 @@
       <c r="T8" s="93"/>
       <c r="U8" s="93"/>
       <c r="V8" s="92">
-        <v>46095.373206018521</v>
+        <v>46098.337939814817</v>
       </c>
       <c r="W8" s="1" t="s">
         <v>264</v>
@@ -6211,27 +6718,31 @@
         <v>59</v>
       </c>
       <c r="H9" s="93">
-        <v>-1</v>
+        <v>2.9365000000000001</v>
       </c>
       <c r="I9" s="93">
-        <v>-1</v>
+        <v>2.9373999999999998</v>
       </c>
       <c r="J9" s="93">
-        <v>-1</v>
+        <v>2.9382999999999999</v>
       </c>
       <c r="K9" s="93">
-        <v>-1</v>
+        <v>2.9378500000000001</v>
       </c>
       <c r="L9" s="93">
-        <v>2.8437000000000001</v>
+        <v>2.8407</v>
       </c>
       <c r="M9" s="93">
-        <v>0</v>
-      </c>
-      <c r="N9" s="93"/>
-      <c r="O9" s="93"/>
+        <v>2.8595999999999999</v>
+      </c>
+      <c r="N9" s="93">
+        <v>2.9523999999999999</v>
+      </c>
+      <c r="O9" s="93">
+        <v>2.8584000000000001</v>
+      </c>
       <c r="P9" s="93">
-        <v>0</v>
+        <v>2963</v>
       </c>
       <c r="Q9" s="93"/>
       <c r="R9" s="93"/>
@@ -6239,7 +6750,7 @@
       <c r="T9" s="93"/>
       <c r="U9" s="93"/>
       <c r="V9" s="92">
-        <v>46095.373206018521</v>
+        <v>46098.337939814817</v>
       </c>
       <c r="W9" s="1" t="s">
         <v>264</v>
@@ -6268,27 +6779,31 @@
         <v>59</v>
       </c>
       <c r="H10" s="93">
-        <v>-1</v>
+        <v>5052</v>
       </c>
       <c r="I10" s="93">
-        <v>-1</v>
+        <v>5052</v>
       </c>
       <c r="J10" s="93">
-        <v>-1</v>
+        <v>5052.6000000000004</v>
       </c>
       <c r="K10" s="93">
-        <v>-1</v>
+        <v>5052.3</v>
       </c>
       <c r="L10" s="93">
-        <v>5163.8</v>
+        <v>5039.3999999999996</v>
       </c>
       <c r="M10" s="93">
-        <v>0</v>
-      </c>
-      <c r="N10" s="93"/>
-      <c r="O10" s="93"/>
+        <v>5049.1000000000004</v>
+      </c>
+      <c r="N10" s="93">
+        <v>5085</v>
+      </c>
+      <c r="O10" s="93">
+        <v>5036.5</v>
+      </c>
       <c r="P10" s="93">
-        <v>0</v>
+        <v>1749</v>
       </c>
       <c r="Q10" s="93"/>
       <c r="R10" s="93"/>
@@ -6296,7 +6811,7 @@
       <c r="T10" s="93"/>
       <c r="U10" s="93"/>
       <c r="V10" s="92">
-        <v>46095.373206018521</v>
+        <v>46098.337939814817</v>
       </c>
       <c r="W10" s="1" t="s">
         <v>264</v>
@@ -6325,31 +6840,31 @@
         <v>59</v>
       </c>
       <c r="H11" s="93">
-        <v>80.959999999999994</v>
+        <v>81.194999999999993</v>
       </c>
       <c r="I11" s="93">
-        <v>-1</v>
+        <v>81.254999999999995</v>
       </c>
       <c r="J11" s="93">
-        <v>-1</v>
+        <v>81.295000000000002</v>
       </c>
       <c r="K11" s="93">
-        <v>-1</v>
+        <v>81.275000000000006</v>
       </c>
       <c r="L11" s="93">
-        <v>85.424999999999997</v>
+        <v>80.974999999999994</v>
       </c>
       <c r="M11" s="93">
-        <v>0</v>
+        <v>81.599999999999994</v>
       </c>
       <c r="N11" s="93">
-        <v>85.8</v>
+        <v>82.8</v>
       </c>
       <c r="O11" s="93">
-        <v>80</v>
+        <v>81.19</v>
       </c>
       <c r="P11" s="93">
-        <v>322</v>
+        <v>26</v>
       </c>
       <c r="Q11" s="93"/>
       <c r="R11" s="93"/>
@@ -6357,7 +6872,7 @@
       <c r="T11" s="93"/>
       <c r="U11" s="93"/>
       <c r="V11" s="92">
-        <v>46095.373206018521</v>
+        <v>46098.337939814817</v>
       </c>
       <c r="W11" s="1" t="s">
         <v>264</v>
@@ -6386,27 +6901,31 @@
         <v>59</v>
       </c>
       <c r="H12" s="93">
-        <v>-1</v>
+        <v>5.8215000000000003</v>
       </c>
       <c r="I12" s="93">
-        <v>-1</v>
+        <v>5.8045</v>
       </c>
       <c r="J12" s="93">
-        <v>-1</v>
+        <v>5.8064999999999998</v>
       </c>
       <c r="K12" s="93">
-        <v>-1</v>
+        <v>5.8055000000000003</v>
       </c>
       <c r="L12" s="93">
-        <v>5.8955000000000002</v>
+        <v>5.8594999999999997</v>
       </c>
       <c r="M12" s="93">
-        <v>0</v>
-      </c>
-      <c r="N12" s="93"/>
-      <c r="O12" s="93"/>
+        <v>5.8630000000000004</v>
+      </c>
+      <c r="N12" s="93">
+        <v>5.8630000000000004</v>
+      </c>
+      <c r="O12" s="93">
+        <v>5.8215000000000003</v>
+      </c>
       <c r="P12" s="93">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Q12" s="93"/>
       <c r="R12" s="93"/>
@@ -6414,7 +6933,7 @@
       <c r="T12" s="93"/>
       <c r="U12" s="93"/>
       <c r="V12" s="92">
-        <v>46095.373206018521</v>
+        <v>46098.337939814817</v>
       </c>
       <c r="W12" s="1" t="s">
         <v>264</v>
@@ -6443,27 +6962,31 @@
         <v>59</v>
       </c>
       <c r="H13" s="93">
-        <v>-100</v>
+        <v>458.5</v>
       </c>
       <c r="I13" s="93">
-        <v>-100</v>
+        <v>458.25</v>
       </c>
       <c r="J13" s="93">
-        <v>-100</v>
+        <v>458.5</v>
       </c>
       <c r="K13" s="93">
-        <v>-100</v>
+        <v>458.375</v>
       </c>
       <c r="L13" s="93">
-        <v>462.5</v>
+        <v>454</v>
       </c>
       <c r="M13" s="93">
-        <v>0</v>
-      </c>
-      <c r="N13" s="93"/>
-      <c r="O13" s="93"/>
+        <v>453.75</v>
+      </c>
+      <c r="N13" s="93">
+        <v>459</v>
+      </c>
+      <c r="O13" s="93">
+        <v>453.5</v>
+      </c>
       <c r="P13" s="93">
-        <v>0</v>
+        <v>19781</v>
       </c>
       <c r="Q13" s="93"/>
       <c r="R13" s="93"/>
@@ -6471,7 +6994,7 @@
       <c r="T13" s="93"/>
       <c r="U13" s="93"/>
       <c r="V13" s="92">
-        <v>46095.373206018521</v>
+        <v>46098.337939814817</v>
       </c>
       <c r="W13" s="1" t="s">
         <v>264</v>
@@ -6500,27 +7023,31 @@
         <v>59</v>
       </c>
       <c r="H14" s="93">
-        <v>-100</v>
+        <v>603</v>
       </c>
       <c r="I14" s="93">
-        <v>-100</v>
+        <v>602.75</v>
       </c>
       <c r="J14" s="93">
-        <v>-100</v>
+        <v>603</v>
       </c>
       <c r="K14" s="93">
-        <v>-100</v>
+        <v>602.875</v>
       </c>
       <c r="L14" s="93">
-        <v>598.5</v>
+        <v>597.25</v>
       </c>
       <c r="M14" s="93">
-        <v>0</v>
-      </c>
-      <c r="N14" s="93"/>
-      <c r="O14" s="93"/>
+        <v>597.25</v>
+      </c>
+      <c r="N14" s="93">
+        <v>607.25</v>
+      </c>
+      <c r="O14" s="93">
+        <v>596.5</v>
+      </c>
       <c r="P14" s="93">
-        <v>0</v>
+        <v>6378</v>
       </c>
       <c r="Q14" s="93"/>
       <c r="R14" s="93"/>
@@ -6528,7 +7055,7 @@
       <c r="T14" s="93"/>
       <c r="U14" s="93"/>
       <c r="V14" s="92">
-        <v>46095.373206018521</v>
+        <v>46098.337939814817</v>
       </c>
       <c r="W14" s="1" t="s">
         <v>264</v>
@@ -6557,27 +7084,31 @@
         <v>59</v>
       </c>
       <c r="H15" s="93">
-        <v>-100</v>
+        <v>1161.75</v>
       </c>
       <c r="I15" s="93">
-        <v>-100</v>
+        <v>1161.5</v>
       </c>
       <c r="J15" s="93">
-        <v>-100</v>
+        <v>1161.75</v>
       </c>
       <c r="K15" s="93">
-        <v>-100</v>
+        <v>1161.625</v>
       </c>
       <c r="L15" s="93">
-        <v>1227.25</v>
+        <v>1155.25</v>
       </c>
       <c r="M15" s="93">
-        <v>0</v>
-      </c>
-      <c r="N15" s="93"/>
-      <c r="O15" s="93"/>
+        <v>1147</v>
+      </c>
+      <c r="N15" s="93">
+        <v>1164.5</v>
+      </c>
+      <c r="O15" s="93">
+        <v>1145.25</v>
+      </c>
       <c r="P15" s="93">
-        <v>0</v>
+        <v>26383</v>
       </c>
       <c r="Q15" s="93"/>
       <c r="R15" s="93"/>
@@ -6585,7 +7116,7 @@
       <c r="T15" s="93"/>
       <c r="U15" s="93"/>
       <c r="V15" s="92">
-        <v>46095.373206018521</v>
+        <v>46098.337939814817</v>
       </c>
       <c r="W15" s="1" t="s">
         <v>264</v>
@@ -6614,7 +7145,7 @@
         <v>59</v>
       </c>
       <c r="H16" s="93">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="I16" s="93">
         <v>-100</v>
@@ -6626,7 +7157,7 @@
         <v>-100</v>
       </c>
       <c r="L16" s="93">
-        <v>14.38</v>
+        <v>14.19</v>
       </c>
       <c r="M16" s="93">
         <v>0</v>
@@ -6642,7 +7173,7 @@
       <c r="T16" s="93"/>
       <c r="U16" s="93"/>
       <c r="V16" s="92">
-        <v>46095.373206018521</v>
+        <v>46098.337939814817</v>
       </c>
       <c r="W16" s="1" t="s">
         <v>264</v>
@@ -6671,7 +7202,7 @@
         <v>59</v>
       </c>
       <c r="H17" s="93">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="I17" s="93">
         <v>-100</v>
@@ -6683,7 +7214,7 @@
         <v>-100</v>
       </c>
       <c r="L17" s="93">
-        <v>291.89999999999998</v>
+        <v>292.85000000000002</v>
       </c>
       <c r="M17" s="93">
         <v>0</v>
@@ -6699,7 +7230,7 @@
       <c r="T17" s="93"/>
       <c r="U17" s="93"/>
       <c r="V17" s="92">
-        <v>46095.373206018521</v>
+        <v>46098.337939814817</v>
       </c>
       <c r="W17" s="1" t="s">
         <v>264</v>
@@ -6728,7 +7259,7 @@
         <v>59</v>
       </c>
       <c r="H18" s="93">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="I18" s="93">
         <v>-1</v>
@@ -6740,7 +7271,7 @@
         <v>-1</v>
       </c>
       <c r="L18" s="93">
-        <v>3315</v>
+        <v>3418</v>
       </c>
       <c r="M18" s="93">
         <v>0</v>
@@ -6756,7 +7287,7 @@
       <c r="T18" s="93"/>
       <c r="U18" s="93"/>
       <c r="V18" s="92">
-        <v>46095.373206018521</v>
+        <v>46098.337939814817</v>
       </c>
       <c r="W18" s="1" t="s">
         <v>264</v>
@@ -6785,27 +7316,31 @@
         <v>59</v>
       </c>
       <c r="H19" s="93">
-        <v>-100</v>
+        <v>68.010000000000005</v>
       </c>
       <c r="I19" s="93">
-        <v>-100</v>
+        <v>68</v>
       </c>
       <c r="J19" s="93">
-        <v>-100</v>
+        <v>68.010000000000005</v>
       </c>
       <c r="K19" s="93">
-        <v>-100</v>
+        <v>68.004999999999995</v>
       </c>
       <c r="L19" s="93">
-        <v>65.14</v>
+        <v>68.19</v>
       </c>
       <c r="M19" s="93">
-        <v>0</v>
-      </c>
-      <c r="N19" s="93"/>
-      <c r="O19" s="93"/>
+        <v>68.260000000000005</v>
+      </c>
+      <c r="N19" s="93">
+        <v>68.63</v>
+      </c>
+      <c r="O19" s="93">
+        <v>67.959999999999994</v>
+      </c>
       <c r="P19" s="93">
-        <v>0</v>
+        <v>5193</v>
       </c>
       <c r="Q19" s="93"/>
       <c r="R19" s="93"/>
@@ -6813,7 +7348,7 @@
       <c r="T19" s="93"/>
       <c r="U19" s="93"/>
       <c r="V19" s="92">
-        <v>46095.373206018521</v>
+        <v>46098.337939814817</v>
       </c>
       <c r="W19" s="1" t="s">
         <v>264</v>
@@ -6842,7 +7377,7 @@
         <v>59</v>
       </c>
       <c r="H20" s="93">
-        <v>230.85</v>
+        <v>0</v>
       </c>
       <c r="I20" s="93">
         <v>-100</v>
@@ -6854,19 +7389,19 @@
         <v>-100</v>
       </c>
       <c r="L20" s="93">
-        <v>231.25</v>
+        <v>233.25</v>
       </c>
       <c r="M20" s="93">
-        <v>232</v>
+        <v>230.9</v>
       </c>
       <c r="N20" s="93">
-        <v>232.55</v>
+        <v>233.95</v>
       </c>
       <c r="O20" s="93">
-        <v>230.05</v>
+        <v>230.82499999999999</v>
       </c>
       <c r="P20" s="93">
-        <v>26416</v>
+        <v>16745</v>
       </c>
       <c r="Q20" s="93"/>
       <c r="R20" s="93"/>
@@ -6874,7 +7409,7 @@
       <c r="T20" s="93"/>
       <c r="U20" s="93"/>
       <c r="V20" s="92">
-        <v>46095.373206018521</v>
+        <v>46098.337939814817</v>
       </c>
       <c r="W20" s="1" t="s">
         <v>264</v>
@@ -6903,7 +7438,7 @@
         <v>59</v>
       </c>
       <c r="H21" s="93">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="I21" s="93">
         <v>-100</v>
@@ -6915,15 +7450,19 @@
         <v>-100</v>
       </c>
       <c r="L21" s="93">
-        <v>339.92500000000001</v>
+        <v>345.55</v>
       </c>
       <c r="M21" s="93">
-        <v>341.4</v>
-      </c>
-      <c r="N21" s="93"/>
-      <c r="O21" s="93"/>
+        <v>340.57499999999999</v>
+      </c>
+      <c r="N21" s="93">
+        <v>346</v>
+      </c>
+      <c r="O21" s="93">
+        <v>340</v>
+      </c>
       <c r="P21" s="93">
-        <v>0</v>
+        <v>5413</v>
       </c>
       <c r="Q21" s="93"/>
       <c r="R21" s="93"/>
@@ -6931,7 +7470,7 @@
       <c r="T21" s="93"/>
       <c r="U21" s="93"/>
       <c r="V21" s="92">
-        <v>46095.373206018521</v>
+        <v>46098.337939814817</v>
       </c>
       <c r="W21" s="1" t="s">
         <v>264</v>
@@ -6960,7 +7499,7 @@
         <v>59</v>
       </c>
       <c r="H22" s="93">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="I22" s="93">
         <v>-100</v>
@@ -6972,15 +7511,19 @@
         <v>-100</v>
       </c>
       <c r="L22" s="93">
-        <v>94.35</v>
+        <v>93.5</v>
       </c>
       <c r="M22" s="93">
-        <v>94.724999999999994</v>
-      </c>
-      <c r="N22" s="93"/>
-      <c r="O22" s="93"/>
+        <v>93.7</v>
+      </c>
+      <c r="N22" s="93">
+        <v>94.15</v>
+      </c>
+      <c r="O22" s="93">
+        <v>93.4</v>
+      </c>
       <c r="P22" s="93">
-        <v>0</v>
+        <v>16618</v>
       </c>
       <c r="Q22" s="93"/>
       <c r="R22" s="93"/>
@@ -6988,7 +7531,7 @@
       <c r="T22" s="93"/>
       <c r="U22" s="93"/>
       <c r="V22" s="92">
-        <v>46095.373206018521</v>
+        <v>46098.337939814817</v>
       </c>
       <c r="W22" s="1" t="s">
         <v>264</v>
@@ -7017,27 +7560,31 @@
         <v>59</v>
       </c>
       <c r="H23" s="93">
-        <v>100.16</v>
+        <v>99.795000000000002</v>
       </c>
       <c r="I23" s="93">
-        <v>-1</v>
+        <v>99.79</v>
       </c>
       <c r="J23" s="93">
-        <v>-1</v>
+        <v>99.8</v>
       </c>
       <c r="K23" s="93">
-        <v>-1</v>
+        <v>99.795000000000002</v>
       </c>
       <c r="L23" s="93">
-        <v>99.504999999999995</v>
+        <v>99.47</v>
       </c>
       <c r="M23" s="93">
-        <v>0</v>
-      </c>
-      <c r="N23" s="93"/>
-      <c r="O23" s="93"/>
+        <v>99.625</v>
+      </c>
+      <c r="N23" s="93">
+        <v>99.87</v>
+      </c>
+      <c r="O23" s="93">
+        <v>99.605000000000004</v>
+      </c>
       <c r="P23" s="93">
-        <v>0</v>
+        <v>2535</v>
       </c>
       <c r="Q23" s="93"/>
       <c r="R23" s="93"/>
@@ -7045,7 +7592,7 @@
       <c r="T23" s="93"/>
       <c r="U23" s="93"/>
       <c r="V23" s="92">
-        <v>46095.373206018521</v>
+        <v>46098.337939814817</v>
       </c>
       <c r="W23" s="1" t="s">
         <v>264</v>
@@ -7074,27 +7621,31 @@
         <v>59</v>
       </c>
       <c r="H24" s="93">
-        <v>-1</v>
+        <v>1.1526000000000001</v>
       </c>
       <c r="I24" s="93">
-        <v>-1</v>
+        <v>1.1526000000000001</v>
       </c>
       <c r="J24" s="93">
-        <v>-1</v>
+        <v>1.15265</v>
       </c>
       <c r="K24" s="93">
-        <v>-1</v>
+        <v>1.152625</v>
       </c>
       <c r="L24" s="93">
-        <v>1.15635</v>
+        <v>1.1568000000000001</v>
       </c>
       <c r="M24" s="93">
-        <v>1.1560999999999999</v>
-      </c>
-      <c r="N24" s="93"/>
-      <c r="O24" s="93"/>
+        <v>1.1555500000000001</v>
+      </c>
+      <c r="N24" s="93">
+        <v>1.1555500000000001</v>
+      </c>
+      <c r="O24" s="93">
+        <v>1.1515500000000001</v>
+      </c>
       <c r="P24" s="93">
-        <v>0</v>
+        <v>27446</v>
       </c>
       <c r="Q24" s="93"/>
       <c r="R24" s="93"/>
@@ -7102,7 +7653,7 @@
       <c r="T24" s="93"/>
       <c r="U24" s="93"/>
       <c r="V24" s="92">
-        <v>46095.373206018521</v>
+        <v>46098.337939814817</v>
       </c>
       <c r="W24" s="1" t="s">
         <v>264</v>
@@ -7131,27 +7682,31 @@
         <v>59</v>
       </c>
       <c r="H25" s="93">
-        <v>-1</v>
+        <v>1.3284</v>
       </c>
       <c r="I25" s="93">
-        <v>-1</v>
+        <v>1.3284</v>
       </c>
       <c r="J25" s="93">
-        <v>-1</v>
+        <v>1.3285</v>
       </c>
       <c r="K25" s="93">
-        <v>-1</v>
+        <v>1.3284500000000001</v>
       </c>
       <c r="L25" s="93">
-        <v>1.3341000000000001</v>
+        <v>1.3331</v>
       </c>
       <c r="M25" s="93">
-        <v>1.3338000000000001</v>
-      </c>
-      <c r="N25" s="93"/>
-      <c r="O25" s="93"/>
+        <v>1.3318000000000001</v>
+      </c>
+      <c r="N25" s="93">
+        <v>1.3319000000000001</v>
+      </c>
+      <c r="O25" s="93">
+        <v>1.3272999999999999</v>
+      </c>
       <c r="P25" s="93">
-        <v>0</v>
+        <v>14032</v>
       </c>
       <c r="Q25" s="93"/>
       <c r="R25" s="93"/>
@@ -7159,7 +7714,7 @@
       <c r="T25" s="93"/>
       <c r="U25" s="93"/>
       <c r="V25" s="92">
-        <v>46095.373206018521</v>
+        <v>46098.337939814817</v>
       </c>
       <c r="W25" s="1" t="s">
         <v>264</v>
@@ -7188,27 +7743,31 @@
         <v>59</v>
       </c>
       <c r="H26" s="93">
-        <v>-1</v>
+        <v>6.3220000000000004E-3</v>
       </c>
       <c r="I26" s="93">
-        <v>-1</v>
+        <v>6.3220000000000004E-3</v>
       </c>
       <c r="J26" s="93">
-        <v>-1</v>
+        <v>6.3225E-3</v>
       </c>
       <c r="K26" s="93">
-        <v>-1</v>
+        <v>6.3222499999999997E-3</v>
       </c>
       <c r="L26" s="93">
-        <v>6.3229999999999996E-3</v>
+        <v>6.339E-3</v>
       </c>
       <c r="M26" s="93">
-        <v>6.3210000000000002E-3</v>
-      </c>
-      <c r="N26" s="93"/>
-      <c r="O26" s="93"/>
+        <v>6.3344999999999999E-3</v>
+      </c>
+      <c r="N26" s="93">
+        <v>6.3365000000000001E-3</v>
+      </c>
+      <c r="O26" s="93">
+        <v>6.3175000000000002E-3</v>
+      </c>
       <c r="P26" s="93">
-        <v>0</v>
+        <v>26200</v>
       </c>
       <c r="Q26" s="93"/>
       <c r="R26" s="93"/>
@@ -7216,7 +7775,7 @@
       <c r="T26" s="93"/>
       <c r="U26" s="93"/>
       <c r="V26" s="92">
-        <v>46095.373206018521</v>
+        <v>46098.337939814817</v>
       </c>
       <c r="W26" s="1" t="s">
         <v>264</v>
@@ -7245,31 +7804,31 @@
         <v>59</v>
       </c>
       <c r="H27" s="93">
-        <v>0.7319</v>
+        <v>0.73294999999999999</v>
       </c>
       <c r="I27" s="93">
-        <v>-1</v>
+        <v>0.7329</v>
       </c>
       <c r="J27" s="93">
-        <v>-1</v>
+        <v>0.73299999999999998</v>
       </c>
       <c r="K27" s="93">
-        <v>-1</v>
+        <v>0.73294999999999999</v>
       </c>
       <c r="L27" s="93">
-        <v>0.73709999999999998</v>
+        <v>0.73419999999999996</v>
       </c>
       <c r="M27" s="93">
-        <v>0.73604999999999998</v>
+        <v>0.73380000000000001</v>
       </c>
       <c r="N27" s="93">
-        <v>0.73709999999999998</v>
+        <v>0.7339</v>
       </c>
       <c r="O27" s="93">
-        <v>0.73065000000000002</v>
+        <v>0.73280000000000001</v>
       </c>
       <c r="P27" s="93">
-        <v>162821</v>
+        <v>7578</v>
       </c>
       <c r="Q27" s="93"/>
       <c r="R27" s="93"/>
@@ -7277,7 +7836,7 @@
       <c r="T27" s="93"/>
       <c r="U27" s="93"/>
       <c r="V27" s="92">
-        <v>46095.373206018521</v>
+        <v>46098.337939814817</v>
       </c>
       <c r="W27" s="1" t="s">
         <v>264</v>
@@ -7306,27 +7865,31 @@
         <v>59</v>
       </c>
       <c r="H28" s="93">
-        <v>-1</v>
+        <v>0.70599999999999996</v>
       </c>
       <c r="I28" s="93">
-        <v>-1</v>
+        <v>0.70594999999999997</v>
       </c>
       <c r="J28" s="93">
-        <v>-1</v>
+        <v>0.70604999999999996</v>
       </c>
       <c r="K28" s="93">
-        <v>-1</v>
+        <v>0.70599999999999996</v>
       </c>
       <c r="L28" s="93">
-        <v>0.70720000000000005</v>
+        <v>0.70674999999999999</v>
       </c>
       <c r="M28" s="93">
-        <v>0.70684999999999998</v>
-      </c>
-      <c r="N28" s="93"/>
-      <c r="O28" s="93"/>
+        <v>0.70655000000000001</v>
+      </c>
+      <c r="N28" s="93">
+        <v>0.70874999999999999</v>
+      </c>
+      <c r="O28" s="93">
+        <v>0.70415000000000005</v>
+      </c>
       <c r="P28" s="93">
-        <v>0</v>
+        <v>40831</v>
       </c>
       <c r="Q28" s="93"/>
       <c r="R28" s="93"/>
@@ -7334,7 +7897,7 @@
       <c r="T28" s="93"/>
       <c r="U28" s="93"/>
       <c r="V28" s="92">
-        <v>46095.373206018521</v>
+        <v>46098.337939814817</v>
       </c>
       <c r="W28" s="1" t="s">
         <v>264</v>
@@ -7363,27 +7926,31 @@
         <v>59</v>
       </c>
       <c r="H29" s="93">
-        <v>-1</v>
+        <v>114.125</v>
       </c>
       <c r="I29" s="93">
-        <v>-1</v>
+        <v>114.125</v>
       </c>
       <c r="J29" s="93">
-        <v>-1</v>
+        <v>114.15625</v>
       </c>
       <c r="K29" s="93">
-        <v>-1</v>
+        <v>114.140625</v>
       </c>
       <c r="L29" s="93">
-        <v>114.15625</v>
+        <v>114.625</v>
       </c>
       <c r="M29" s="93">
+        <v>114.5</v>
+      </c>
+      <c r="N29" s="93">
+        <v>114.5</v>
+      </c>
+      <c r="O29" s="93">
         <v>114.125</v>
       </c>
-      <c r="N29" s="93"/>
-      <c r="O29" s="93"/>
       <c r="P29" s="93">
-        <v>0</v>
+        <v>26274</v>
       </c>
       <c r="Q29" s="93"/>
       <c r="R29" s="93"/>
@@ -7391,7 +7958,7 @@
       <c r="T29" s="93"/>
       <c r="U29" s="93"/>
       <c r="V29" s="92">
-        <v>46095.373206018521</v>
+        <v>46098.337939814817</v>
       </c>
       <c r="W29" s="1" t="s">
         <v>264</v>
@@ -7420,27 +7987,31 @@
         <v>59</v>
       </c>
       <c r="H30" s="93">
-        <v>-1</v>
+        <v>111.71875</v>
       </c>
       <c r="I30" s="93">
-        <v>-1</v>
+        <v>111.71875</v>
       </c>
       <c r="J30" s="93">
-        <v>-1</v>
+        <v>111.734375</v>
       </c>
       <c r="K30" s="93">
-        <v>-1</v>
+        <v>111.7265625</v>
       </c>
       <c r="L30" s="93">
-        <v>111.40625</v>
+        <v>111.890625</v>
       </c>
       <c r="M30" s="93">
-        <v>111.5</v>
-      </c>
-      <c r="N30" s="93"/>
-      <c r="O30" s="93"/>
+        <v>111.875</v>
+      </c>
+      <c r="N30" s="93">
+        <v>111.90625</v>
+      </c>
+      <c r="O30" s="93">
+        <v>111.6875</v>
+      </c>
       <c r="P30" s="93">
-        <v>0</v>
+        <v>121757</v>
       </c>
       <c r="Q30" s="93"/>
       <c r="R30" s="93"/>
@@ -7448,7 +8019,7 @@
       <c r="T30" s="93"/>
       <c r="U30" s="93"/>
       <c r="V30" s="92">
-        <v>46095.373206018521</v>
+        <v>46098.337939814817</v>
       </c>
       <c r="W30" s="1" t="s">
         <v>264</v>
@@ -7476,26 +8047,32 @@
       <c r="G31" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="H31" s="93"/>
+      <c r="H31" s="93">
+        <v>126.07</v>
+      </c>
       <c r="I31" s="93">
-        <v>-1</v>
+        <v>126.06</v>
       </c>
       <c r="J31" s="93">
-        <v>-1</v>
+        <v>126.07</v>
       </c>
       <c r="K31" s="93">
-        <v>-1</v>
+        <v>126.065</v>
       </c>
       <c r="L31" s="93">
-        <v>126.16</v>
+        <v>126.19</v>
       </c>
       <c r="M31" s="93">
-        <v>125.94</v>
-      </c>
-      <c r="N31" s="93"/>
-      <c r="O31" s="93"/>
+        <v>126.22</v>
+      </c>
+      <c r="N31" s="93">
+        <v>126.27</v>
+      </c>
+      <c r="O31" s="93">
+        <v>126.03</v>
+      </c>
       <c r="P31" s="93">
-        <v>0</v>
+        <v>13199</v>
       </c>
       <c r="Q31" s="93"/>
       <c r="R31" s="93"/>
@@ -7503,7 +8080,7 @@
       <c r="T31" s="93"/>
       <c r="U31" s="93"/>
       <c r="V31" s="92">
-        <v>46095.373206018521</v>
+        <v>46098.337939814817</v>
       </c>
       <c r="W31" s="1" t="s">
         <v>264</v>
@@ -7531,26 +8108,32 @@
       <c r="G32" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="H32" s="93"/>
+      <c r="H32" s="93">
+        <v>109.04</v>
+      </c>
       <c r="I32" s="93">
-        <v>-1</v>
+        <v>109.04</v>
       </c>
       <c r="J32" s="93">
-        <v>-1</v>
+        <v>109.06</v>
       </c>
       <c r="K32" s="93">
-        <v>-1</v>
+        <v>109.05000000000001</v>
       </c>
       <c r="L32" s="93">
-        <v>109.2</v>
+        <v>109.22</v>
       </c>
       <c r="M32" s="93">
-        <v>108.74</v>
-      </c>
-      <c r="N32" s="93"/>
-      <c r="O32" s="93"/>
+        <v>109.36</v>
+      </c>
+      <c r="N32" s="93">
+        <v>109.36</v>
+      </c>
+      <c r="O32" s="93">
+        <v>109.02</v>
+      </c>
       <c r="P32" s="93">
-        <v>0</v>
+        <v>1461</v>
       </c>
       <c r="Q32" s="93"/>
       <c r="R32" s="93"/>
@@ -7558,7 +8141,7 @@
       <c r="T32" s="93"/>
       <c r="U32" s="93"/>
       <c r="V32" s="92">
-        <v>46095.373206018521</v>
+        <v>46098.337939814817</v>
       </c>
       <c r="W32" s="1" t="s">
         <v>264</v>
@@ -7586,24 +8169,32 @@
       <c r="G33" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="H33" s="93"/>
+      <c r="H33" s="93">
+        <v>117.8</v>
+      </c>
       <c r="I33" s="93">
-        <v>-1</v>
+        <v>117.8</v>
       </c>
       <c r="J33" s="93">
-        <v>-1</v>
+        <v>117.81</v>
       </c>
       <c r="K33" s="93">
-        <v>-1</v>
+        <v>117.80500000000001</v>
       </c>
       <c r="L33" s="93">
-        <v>117.8</v>
-      </c>
-      <c r="M33" s="93"/>
-      <c r="N33" s="93"/>
-      <c r="O33" s="93"/>
+        <v>117.99</v>
+      </c>
+      <c r="M33" s="93">
+        <v>117.82</v>
+      </c>
+      <c r="N33" s="93">
+        <v>117.83</v>
+      </c>
+      <c r="O33" s="93">
+        <v>117.75</v>
+      </c>
       <c r="P33" s="93">
-        <v>0</v>
+        <v>1082</v>
       </c>
       <c r="Q33" s="93"/>
       <c r="R33" s="93"/>
@@ -7611,7 +8202,7 @@
       <c r="T33" s="93"/>
       <c r="U33" s="93"/>
       <c r="V33" s="92">
-        <v>46095.373206018521</v>
+        <v>46098.337939814817</v>
       </c>
       <c r="W33" s="1" t="s">
         <v>264</v>
@@ -7640,29 +8231,29 @@
         <v>59</v>
       </c>
       <c r="H34" s="93">
-        <v>70599</v>
+        <v>74173.25</v>
       </c>
       <c r="I34" s="93">
-        <v>70598.75</v>
+        <v>74173</v>
       </c>
       <c r="J34" s="93">
-        <v>70599</v>
+        <v>74173.25</v>
       </c>
       <c r="K34" s="93">
-        <v>70598.875</v>
+        <v>74173.125</v>
       </c>
       <c r="L34" s="93">
-        <v>71166.25</v>
+        <v>73946.75</v>
       </c>
       <c r="M34" s="93"/>
       <c r="N34" s="93">
-        <v>74370</v>
+        <v>76128.75</v>
       </c>
       <c r="O34" s="93">
-        <v>69650</v>
+        <v>71142.5</v>
       </c>
       <c r="P34" s="93">
-        <v>111.98166509000001</v>
+        <v>200.06584436</v>
       </c>
       <c r="Q34" s="93"/>
       <c r="R34" s="93"/>
@@ -7670,7 +8261,7 @@
       <c r="T34" s="93"/>
       <c r="U34" s="93"/>
       <c r="V34" s="92">
-        <v>46095.373206018521</v>
+        <v>46098.337939814817</v>
       </c>
       <c r="W34" s="1" t="s">
         <v>264</v>
@@ -7699,29 +8290,29 @@
         <v>59</v>
       </c>
       <c r="H35" s="93">
-        <v>2078</v>
+        <v>2320</v>
       </c>
       <c r="I35" s="93">
-        <v>2078</v>
+        <v>2320</v>
       </c>
       <c r="J35" s="93">
-        <v>2078.0500000000002</v>
+        <v>2320.0500000000002</v>
       </c>
       <c r="K35" s="93">
-        <v>2078.0250000000001</v>
+        <v>2320.0250000000001</v>
       </c>
       <c r="L35" s="93">
-        <v>2102.25</v>
+        <v>2329.3000000000002</v>
       </c>
       <c r="M35" s="93"/>
       <c r="N35" s="93">
-        <v>2209.4499999999998</v>
+        <v>2385</v>
       </c>
       <c r="O35" s="93">
-        <v>2056.1</v>
+        <v>2110.35</v>
       </c>
       <c r="P35" s="93">
-        <v>824.96082965999994</v>
+        <v>1382.66226983</v>
       </c>
       <c r="Q35" s="93"/>
       <c r="R35" s="93"/>
@@ -7729,7 +8320,7 @@
       <c r="T35" s="93"/>
       <c r="U35" s="93"/>
       <c r="V35" s="92">
-        <v>46095.373206018521</v>
+        <v>46098.337939814817</v>
       </c>
       <c r="W35" s="1" t="s">
         <v>264</v>
@@ -7737,19 +8328,19 @@
     </row>
     <row r="36" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A36" s="1" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B36" s="1">
         <v>297507399</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="D36" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>60</v>
@@ -7758,47 +8349,47 @@
         <v>59</v>
       </c>
       <c r="H36" s="93">
-        <v>4.3</v>
+        <v>3.73</v>
       </c>
       <c r="I36" s="93">
-        <v>-1</v>
+        <v>3.63</v>
       </c>
       <c r="J36" s="93">
-        <v>-1</v>
+        <v>3.76</v>
       </c>
       <c r="K36" s="93">
-        <v>-1</v>
+        <v>3.6949999999999998</v>
       </c>
       <c r="L36" s="93">
-        <v>5.35</v>
+        <v>4.63</v>
       </c>
       <c r="M36" s="93"/>
       <c r="N36" s="93">
-        <v>5.1100000000000003</v>
+        <v>3.73</v>
       </c>
       <c r="O36" s="93">
-        <v>3.76</v>
+        <v>3.73</v>
       </c>
       <c r="P36" s="93">
-        <v>1957</v>
+        <v>3</v>
       </c>
       <c r="Q36" s="93">
-        <v>0.79716026823882513</v>
+        <v>0.76379265459558976</v>
       </c>
       <c r="R36" s="93">
-        <v>-0.21376024026296289</v>
+        <v>-0.20077302122016485</v>
       </c>
       <c r="S36" s="93">
-        <v>9.7170641044802848E-3</v>
+        <v>9.939670529318094E-3</v>
       </c>
       <c r="T36" s="93">
-        <v>0.1050583423512963</v>
+        <v>0.10246481654123096</v>
       </c>
       <c r="U36" s="93">
-        <v>-6.7162337566242236E-2</v>
+        <v>-6.6869197110559053E-2</v>
       </c>
       <c r="V36" s="92">
-        <v>46095.373206018521</v>
+        <v>46098.337939814817</v>
       </c>
       <c r="W36" s="1" t="s">
         <v>264</v>
@@ -7806,19 +8397,19 @@
     </row>
     <row r="37" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A37" s="1" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B37" s="1">
         <v>297509218</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="D37" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>60</v>
@@ -7827,47 +8418,47 @@
         <v>59</v>
       </c>
       <c r="H37" s="93">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="I37" s="93">
-        <v>-1</v>
+        <v>0.38</v>
       </c>
       <c r="J37" s="93">
-        <v>-1</v>
+        <v>0.46</v>
       </c>
       <c r="K37" s="93">
-        <v>-1</v>
+        <v>0.42000000000000004</v>
       </c>
       <c r="L37" s="93">
-        <v>0.55000000000000004</v>
+        <v>0.52</v>
       </c>
       <c r="M37" s="93"/>
       <c r="N37" s="93">
-        <v>0.55000000000000004</v>
+        <v>0.43</v>
       </c>
       <c r="O37" s="93">
-        <v>0.39</v>
+        <v>0.43</v>
       </c>
       <c r="P37" s="93">
-        <v>390</v>
+        <v>2</v>
       </c>
       <c r="Q37" s="93">
-        <v>0.78003273026450248</v>
+        <v>0.78339083861671788</v>
       </c>
       <c r="R37" s="93">
-        <v>-3.7228576152962482E-2</v>
+        <v>-3.4546268455653943E-2</v>
       </c>
       <c r="S37" s="93">
-        <v>2.7816999846245593E-3</v>
+        <v>2.640763838621875E-3</v>
       </c>
       <c r="T37" s="93">
-        <v>3.0357650321152063E-2</v>
+        <v>2.6225796728602702E-2</v>
       </c>
       <c r="U37" s="93">
-        <v>-1.6835601338734796E-2</v>
+        <v>-1.7602301867683245E-2</v>
       </c>
       <c r="V37" s="92">
-        <v>46095.373206018521</v>
+        <v>46098.337939814817</v>
       </c>
       <c r="W37" s="1" t="s">
         <v>264</v>
@@ -8208,7 +8799,7 @@
         <v>299</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.4">
@@ -8241,32 +8832,96 @@
         <v>299</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A20" s="85"/>
+      <c r="A20" s="85">
+        <v>46097.672754629632</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>300</v>
+      </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A21" s="85"/>
+      <c r="A21" s="85">
+        <v>46097.672766203701</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>301</v>
+      </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A22" s="85"/>
+      <c r="A22" s="85">
+        <v>46097.672766203701</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>316</v>
+      </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A23" s="85"/>
+      <c r="A23" s="85">
+        <v>46098.335706018515</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>300</v>
+      </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A24" s="85"/>
+      <c r="A24" s="85">
+        <v>46098.335729166669</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>301</v>
+      </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A25" s="85"/>
+      <c r="A25" s="85">
+        <v>46098.335740740738</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>316</v>
+      </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A26" s="85"/>
+      <c r="A26" s="85">
+        <v>46098.336087962962</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>326</v>
+      </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A27" s="85"/>
+      <c r="A27" s="85">
+        <v>46098.336111111108</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>327</v>
+      </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A28" s="85"/>
@@ -8368,11 +9023,11 @@
       <c r="E4" s="10"/>
       <c r="F4" s="10"/>
       <c r="G4" s="15">
-        <v>12096</v>
+        <v>12371</v>
       </c>
       <c r="H4" s="6">
         <f>-G4</f>
-        <v>-12096</v>
+        <v>-12371</v>
       </c>
     </row>
     <row r="5" spans="2:8" x14ac:dyDescent="0.4">
@@ -8493,11 +9148,11 @@
       <c r="F13" s="10"/>
       <c r="G13" s="6">
         <f>SUM(G3:G12)</f>
-        <v>1000.9499999999098</v>
+        <v>1275.9499999999098</v>
       </c>
       <c r="H13" s="6">
         <f>SUM(H3:H12)</f>
-        <v>35399.049999999952</v>
+        <v>35124.049999999952</v>
       </c>
     </row>
   </sheetData>
@@ -8679,11 +9334,11 @@
       <c r="H5" s="67"/>
       <c r="I5" s="70">
         <f>Blotter!C$4-SUM(NAV!I$4:I4)</f>
-        <v>5514.2806320099007</v>
+        <v>10025.060632009898</v>
       </c>
       <c r="J5" s="70">
         <f t="shared" si="2"/>
-        <v>1005514.2806320098</v>
+        <v>1010025.0606320099</v>
       </c>
       <c r="K5" s="70">
         <f t="shared" si="3"/>
@@ -8691,19 +9346,19 @@
       </c>
       <c r="L5" s="71">
         <f t="shared" si="4"/>
-        <v>1005.5142806320099</v>
+        <v>1010.0250606320099</v>
       </c>
       <c r="M5" s="72">
         <f t="shared" si="5"/>
-        <v>5.5142806320098714E-3</v>
+        <v>1.0025060632009808E-2</v>
       </c>
       <c r="N5" s="73">
         <f t="shared" ref="N5" si="6">L5/L4-1</f>
-        <v>5.5142806320098714E-3</v>
+        <v>1.0025060632009808E-2</v>
       </c>
       <c r="O5" s="75">
         <f>STDEVP(N$4:N5)*SQRT(12)</f>
-        <v>9.5510142218341171E-3</v>
+        <v>1.7363914363599547E-2</v>
       </c>
     </row>
     <row r="6" spans="2:18" ht="14.25" x14ac:dyDescent="0.4">
@@ -9163,7 +9818,7 @@
         <v>1</v>
       </c>
       <c r="V4" s="1" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="W4" s="1" t="s">
         <v>310</v>
@@ -9183,7 +9838,7 @@
       </c>
       <c r="D5" s="6">
         <f t="array" ref="D5">SUM((Blotter!C$19:C$1013=C5)*(Blotter!N$19:N$1013)*1)</f>
-        <v>2391.0899999999965</v>
+        <v>5481.0899999999965</v>
       </c>
       <c r="E5" s="6">
         <f t="array" ref="E5">SUM((Blotter!B$19:C$1013=C5)*(Blotter!R$19:R$1013)*1)</f>
@@ -9191,7 +9846,7 @@
       </c>
       <c r="F5" s="30">
         <f t="shared" ref="F5" si="1">IF(ISNUMBER(D5/E5),D5/E5,0)</f>
-        <v>0.26567666666666628</v>
+        <v>0.60900999999999961</v>
       </c>
       <c r="G5" s="36" t="str">
         <f t="array" ref="G5">IF(SUM((Blotter!C$19:C$1013=PLB!C5)*(Blotter!M$19:M$1013))=0,"C","O")</f>
@@ -9199,20 +9854,20 @@
       </c>
       <c r="H5" s="16">
         <f>J4+D5</f>
-        <v>1002913.33063201</v>
+        <v>1006003.33063201</v>
       </c>
       <c r="I5" s="16"/>
       <c r="J5" s="16">
         <f>H5+I5</f>
-        <v>1002913.33063201</v>
+        <v>1006003.33063201</v>
       </c>
       <c r="K5" s="3">
         <f>H5/J4-1</f>
-        <v>2.3898419274412941E-3</v>
+        <v>5.4782290462005445E-3</v>
       </c>
       <c r="L5" s="3">
         <f>(1+K5)*(1+L4)-1</f>
-        <v>2.9133306320099361E-3</v>
+        <v>6.0033306320099733E-3</v>
       </c>
       <c r="M5" s="6">
         <f>O4-IF(G5="O",O4*1%,-D5)</f>
@@ -9247,7 +9902,7 @@
         <v>2</v>
       </c>
       <c r="V5" s="1" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="W5" s="1" t="s">
         <v>312</v>
@@ -9267,15 +9922,15 @@
       </c>
       <c r="D6" s="6">
         <f t="array" ref="D6">SUM((Blotter!C$19:C$1013=C6)*(Blotter!N$19:N$1013)*1)</f>
-        <v>1600</v>
+        <v>2745.7799999999975</v>
       </c>
       <c r="E6" s="6">
         <f t="array" ref="E6">SUM((Blotter!B$19:C$1013=C6)*(Blotter!R$19:R$1013)*1)</f>
-        <v>8233.3333333333321</v>
+        <v>9600</v>
       </c>
       <c r="F6" s="30">
         <f t="shared" ref="F6" si="4">IF(ISNUMBER(D6/E6),D6/E6,0)</f>
-        <v>0.19433198380566805</v>
+        <v>0.28601874999999971</v>
       </c>
       <c r="G6" s="36" t="str">
         <f t="array" ref="G6">IF(SUM((Blotter!C$19:C$1013=PLB!C6)*(Blotter!M$19:M$1013))=0,"C","O")</f>
@@ -9283,20 +9938,20 @@
       </c>
       <c r="H6" s="16">
         <f>J5+D6</f>
-        <v>1004513.33063201</v>
+        <v>1008749.11063201</v>
       </c>
       <c r="I6" s="16"/>
       <c r="J6" s="16">
         <f>H6+I6</f>
-        <v>1004513.33063201</v>
+        <v>1008749.11063201</v>
       </c>
       <c r="K6" s="3">
         <f>H6/J5-1</f>
-        <v>1.5953522115332852E-3</v>
+        <v>2.7293945421382748E-3</v>
       </c>
       <c r="L6" s="3">
         <f>(1+K6)*(1+L5)-1</f>
-        <v>4.513330632009982E-3</v>
+        <v>8.7491106320098933E-3</v>
       </c>
       <c r="M6" s="6">
         <f>O5-IF(G6="O",O5*1%,-D6)</f>
@@ -9331,7 +9986,7 @@
         <v>3</v>
       </c>
       <c r="V6" s="1" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="W6" s="49"/>
     </row>
@@ -14316,17 +14971,59 @@
       </c>
     </row>
     <row r="40" spans="1:31" x14ac:dyDescent="0.4">
+      <c r="A40" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>317</v>
+      </c>
       <c r="D40" s="1" t="s">
-        <v>317</v>
+        <v>319</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="H40" s="1">
+        <v>1000</v>
+      </c>
+      <c r="I40" s="1">
+        <v>55</v>
+      </c>
+      <c r="J40" s="44">
+        <v>46156</v>
+      </c>
+      <c r="K40" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="L40" s="44">
+        <v>46097</v>
       </c>
       <c r="M40" s="1" t="s">
-        <v>86</v>
+        <v>304</v>
       </c>
       <c r="N40" s="1">
-        <v>2</v>
+        <v>-3</v>
       </c>
       <c r="O40" s="1">
-        <v>5</v>
+        <v>0.35</v>
+      </c>
+      <c r="P40" s="1">
+        <v>-1050</v>
+      </c>
+      <c r="Q40" s="1">
+        <v>-7.11</v>
+      </c>
+      <c r="R40" s="1" t="s">
+        <v>59</v>
       </c>
       <c r="T40" s="43">
         <f>IF(ISNUMBER(VLOOKUP(U40,Blotter!B:C,2,0)),VLOOKUP(U40,Blotter!B:C,2,0),"")</f>
@@ -14334,33 +15031,75 @@
       </c>
       <c r="U40" s="42" t="str">
         <f t="shared" ref="U40:U41" si="16">D40</f>
-        <v>CLM6P75260514</v>
+        <v>LOM6 P5500</v>
       </c>
       <c r="V40" s="42">
         <f t="shared" ref="V40:V41" si="17">N40</f>
-        <v>2</v>
+        <v>-3</v>
       </c>
       <c r="W40" s="42">
         <f t="shared" ref="W40:W41" si="18">O40</f>
-        <v>5</v>
+        <v>0.35</v>
       </c>
       <c r="X40" s="42">
         <f t="shared" ref="X40:X41" si="19">Q40</f>
-        <v>0</v>
+        <v>-7.11</v>
       </c>
     </row>
     <row r="41" spans="1:31" x14ac:dyDescent="0.4">
+      <c r="A41" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>317</v>
+      </c>
       <c r="D41" s="1" t="s">
         <v>318</v>
       </c>
+      <c r="E41" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="H41" s="1">
+        <v>1000</v>
+      </c>
+      <c r="I41" s="1">
+        <v>75</v>
+      </c>
+      <c r="J41" s="44">
+        <v>46156</v>
+      </c>
+      <c r="K41" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="L41" s="44">
+        <v>46097</v>
+      </c>
       <c r="M41" s="1" t="s">
-        <v>304</v>
+        <v>86</v>
       </c>
       <c r="N41" s="1">
-        <v>-2</v>
+        <v>3</v>
       </c>
       <c r="O41" s="1">
-        <v>1</v>
+        <v>3.54</v>
+      </c>
+      <c r="P41" s="1">
+        <v>10620</v>
+      </c>
+      <c r="Q41" s="1">
+        <v>-7.11</v>
+      </c>
+      <c r="R41" s="1" t="s">
+        <v>59</v>
       </c>
       <c r="T41" s="43">
         <f>IF(ISNUMBER(VLOOKUP(U41,Blotter!B:C,2,0)),VLOOKUP(U41,Blotter!B:C,2,0),"")</f>
@@ -14368,19 +15107,19 @@
       </c>
       <c r="U41" s="42" t="str">
         <f t="shared" si="16"/>
-        <v>CLM6P55260514</v>
+        <v>LOM6 P7500</v>
       </c>
       <c r="V41" s="42">
         <f t="shared" si="17"/>
-        <v>-2</v>
+        <v>3</v>
       </c>
       <c r="W41" s="42">
         <f t="shared" si="18"/>
-        <v>1</v>
+        <v>3.54</v>
       </c>
       <c r="X41" s="42">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>-7.11</v>
       </c>
     </row>
     <row r="42" spans="1:31" x14ac:dyDescent="0.4">
@@ -23221,10 +23960,10 @@
         <v>1</v>
       </c>
       <c r="B36" s="9" t="s">
+        <v>318</v>
+      </c>
+      <c r="C36" s="88" t="s">
         <v>317</v>
-      </c>
-      <c r="C36" s="88" t="s">
-        <v>320</v>
       </c>
       <c r="D36" s="88" t="s">
         <v>24</v>
@@ -23242,13 +23981,13 @@
         <v>75</v>
       </c>
       <c r="I36" s="88" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="J36" s="88">
         <v>1000</v>
       </c>
       <c r="K36" s="88" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="M36" s="88"/>
     </row>
@@ -23257,10 +23996,10 @@
         <v>1</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C37" s="88" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="D37" s="88" t="s">
         <v>24</v>
@@ -23278,13 +24017,13 @@
         <v>55</v>
       </c>
       <c r="I37" s="88" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="J37" s="88">
         <v>1000</v>
       </c>
       <c r="K37" s="88" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="M37" s="88"/>
     </row>

--- a/1XW_TradeBlotter_Web.xlsx
+++ b/1XW_TradeBlotter_Web.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0a601c1c2ba3d9f4/Trading/The Strategy Project/1XW Website/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="331" documentId="13_ncr:1_{6F5069F1-F0E7-4440-AA6D-4AFA11BBED1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{62B6AF25-C9C3-4B1F-9FCF-2A167A5EEF45}"/>
+  <xr:revisionPtr revIDLastSave="337" documentId="13_ncr:1_{6F5069F1-F0E7-4440-AA6D-4AFA11BBED1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8A8A3694-7DB9-4860-9FDC-29734F00E722}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="22695" windowHeight="14476" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -117,7 +117,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1198" uniqueCount="332">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1204" uniqueCount="331">
   <si>
     <t>WEEK</t>
   </si>
@@ -1101,12 +1101,6 @@
     <t>Long CL Put Spread</t>
   </si>
   <si>
-    <t>Crytpto</t>
-  </si>
-  <si>
-    <t>NO_DATA</t>
-  </si>
-  <si>
     <t>ERROR</t>
   </si>
   <si>
@@ -1126,6 +1120,9 @@
   </si>
   <si>
     <t>CL JUN26 75 P</t>
+  </si>
+  <si>
+    <t>Crypto</t>
   </si>
 </sst>
 </file>
@@ -2275,7 +2272,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.0025060632009808E-2</c:v>
+                  <c:v>4.8650606320099765E-3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2429,7 +2426,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.0025060632009808E-2</c:v>
+                  <c:v>4.8650606320099765E-3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2820,7 +2817,7 @@
                   <c:v>1000</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1010.0250606320099</c:v>
+                  <c:v>1004.8650606320099</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3236,10 +3233,10 @@
                   <c:v>5.2224063201000703E-4</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>6.0033306320099733E-3</c:v>
+                  <c:v>3.933330632009957E-3</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>8.7491106320098933E-3</c:v>
+                  <c:v>3.5891106320100619E-3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3890,7 +3887,7 @@
       </c>
       <c r="C1" s="79">
         <f ca="1">TODAY()</f>
-        <v>46098</v>
+        <v>46100</v>
       </c>
     </row>
     <row r="2" spans="2:11" x14ac:dyDescent="0.4">
@@ -3898,7 +3895,7 @@
         <v>108</v>
       </c>
       <c r="C2" s="37" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="E2" s="47" t="s">
         <v>123</v>
@@ -3915,7 +3912,7 @@
       </c>
       <c r="C3" s="28">
         <f ca="1">OFFSET(NAV!B1,MATCH(C1,NAV!B:B,1),8)</f>
-        <v>1010025.0606320099</v>
+        <v>1004865.0606320099</v>
       </c>
       <c r="E3" s="47" t="s">
         <v>124</v>
@@ -3932,7 +3929,7 @@
       </c>
       <c r="C4" s="28">
         <f>SUM(N18:N1012)</f>
-        <v>10025.060632009898</v>
+        <v>4865.0606320098977</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="47" t="s">
@@ -3950,7 +3947,7 @@
       </c>
       <c r="C5" s="3">
         <f ca="1">OFFSET(NAV!B1,MATCH(C1,NAV!B:B,1),11)</f>
-        <v>1.0025060632009808E-2</v>
+        <v>4.8650606320099765E-3</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="47" t="s">
@@ -3969,11 +3966,11 @@
       </c>
       <c r="C6" s="3">
         <f ca="1">OFFSET(NAV!B1,MATCH(C1,NAV!B:B,1),12)</f>
-        <v>1.0025060632009808E-2</v>
+        <v>4.8650606320099765E-3</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="47" t="s">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="F6" s="47"/>
       <c r="G6" s="47"/>
@@ -3990,7 +3987,7 @@
       </c>
       <c r="D7" s="3">
         <f ca="1">C7/C3</f>
-        <v>3.4775424263256936E-2</v>
+        <v>3.4953996686787656E-2</v>
       </c>
       <c r="E7" s="47"/>
       <c r="F7" s="47"/>
@@ -4004,11 +4001,11 @@
       </c>
       <c r="C8" s="28">
         <f>C4+C7</f>
-        <v>45149.110632009848</v>
+        <v>39989.110632009848</v>
       </c>
       <c r="D8" s="3">
         <f ca="1">C5+D7</f>
-        <v>4.4800484895266744E-2</v>
+        <v>3.9819057318797632E-2</v>
       </c>
       <c r="G8" s="47"/>
       <c r="H8" s="51"/>
@@ -4020,11 +4017,11 @@
       </c>
       <c r="C9" s="28">
         <f t="array" ref="C9">SUM((F19:F112="Futures")*(M19:M112))</f>
-        <v>102540</v>
+        <v>100470</v>
       </c>
       <c r="D9" s="3">
         <f ca="1">C9/$C$3</f>
-        <v>0.10152223345412534</v>
+        <v>9.9983573851009797E-2</v>
       </c>
       <c r="E9" s="47"/>
       <c r="F9" s="47"/>
@@ -4052,11 +4049,11 @@
       </c>
       <c r="C11" s="28">
         <f t="array" ref="C11">SUM((F19:F212="Put")*(M19:M212))</f>
-        <v>12330</v>
+        <v>9240</v>
       </c>
       <c r="D11" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>1.2207617890475574E-2</v>
+        <v>9.195264480773669E-3</v>
       </c>
     </row>
     <row r="12" spans="2:11" x14ac:dyDescent="0.4">
@@ -4069,7 +4066,7 @@
       </c>
       <c r="D12" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>1.841538465229892E-2</v>
+        <v>1.8509947980778166E-2</v>
       </c>
     </row>
     <row r="13" spans="2:11" x14ac:dyDescent="0.4">
@@ -4078,11 +4075,11 @@
       </c>
       <c r="C13" s="28">
         <f t="array" ref="C13">SUM((PLB!G4:G999="O")*(PLB!D4:D999))</f>
-        <v>8226.8699999999935</v>
+        <v>3066.869999999994</v>
       </c>
       <c r="D13" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>8.1452137384117364E-3</v>
+        <v>3.0520217292370443E-3</v>
       </c>
       <c r="F13" s="59"/>
       <c r="G13" s="59"/>
@@ -4093,11 +4090,11 @@
       </c>
       <c r="C14" s="28">
         <f>C12+C13</f>
-        <v>26826.869999999995</v>
+        <v>21666.869999999995</v>
       </c>
       <c r="D14" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>2.6560598390710656E-2</v>
+        <v>2.156196971001521E-2</v>
       </c>
     </row>
     <row r="17" spans="2:28" x14ac:dyDescent="0.4">
@@ -4220,7 +4217,7 @@
         <v>190</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="F19" s="10" t="s">
         <v>303</v>
@@ -4294,7 +4291,7 @@
       </c>
       <c r="Z19" s="35">
         <f>IF(C$2="Last",IF(ISNUMBER(VLOOKUP(B19,Prices!A:L,8,0)),VLOOKUP(B19,Prices!A:L,8,0),0),IF(ISNUMBER(VLOOKUP(B19,Prices!A:L,12,0)),VLOOKUP(B19,Prices!A:L,12,0),0))</f>
-        <v>2329.3000000000002</v>
+        <v>2321.4499999999998</v>
       </c>
       <c r="AB19" s="29"/>
     </row>
@@ -4335,15 +4332,15 @@
       </c>
       <c r="L20" s="29">
         <f t="shared" ref="L20" si="8">IF(I20=0,IF(H20&gt;0,X20,Y20),Z20)</f>
-        <v>3418</v>
+        <v>3349</v>
       </c>
       <c r="M20" s="28">
         <f t="shared" ref="M20" si="9">I20*J20*L20</f>
-        <v>102540</v>
+        <v>100470</v>
       </c>
       <c r="N20" s="95">
         <f t="array" ref="N20">-SUM((Trades!T$2:T$9999=Blotter!C20)*(Trades!U$2:U$9999=Blotter!B20)*(Trades!V$2:V$9999)*(Trades!W$2:W$9999))*J20+SUM((Trades!T$2:T$9999=Blotter!C20)*(Trades!U$2:U$9999=Blotter!B20)*(Trades!X$2:X$9999))+(L20*I20)*J20</f>
-        <v>5481.0899999999965</v>
+        <v>3411.0899999999965</v>
       </c>
       <c r="O20" s="29">
         <f>VLOOKUP(D20,Multiplier!B:H,3,0)</f>
@@ -4359,11 +4356,11 @@
       </c>
       <c r="S20" s="29">
         <f>IF(OR(F20="Futures",F20="Spot"),IF(I20=0,0,IF(I20&gt;0,L20-O20,L20+O20)),0)</f>
-        <v>3213</v>
+        <v>3144</v>
       </c>
       <c r="T20" s="3">
         <f t="shared" ref="T20" si="11">IF(S20&gt;0,IF(ISNUMBER(S20/L20-1),S20/L20-1,0),0)</f>
-        <v>-5.9976594499707381E-2</v>
+        <v>-6.1212302179755151E-2</v>
       </c>
       <c r="U20" s="29">
         <f t="shared" ref="U20" si="12">IF(OR(F20="Futures",F20="Stocks"),IF(I20=0,0,IF(I20&gt;0,K20-P20,K20+P20)),0)</f>
@@ -4371,7 +4368,7 @@
       </c>
       <c r="V20" s="3">
         <f t="shared" ref="V20" si="13">IF(U20&gt;0,IF(ISNUMBER(U20/L20-1),U20/L20-1,0),0)</f>
-        <v>-0.14122381509654769</v>
+        <v>-0.1235303075544939</v>
       </c>
       <c r="X20" s="34">
         <f t="array" ref="X20">IF(ISNUMBER(SUM((Trades!T$2:T$9999=Blotter!C20)*(Trades!U$2:U$9999=Blotter!B20)*(Trades!W$2:W$9999)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0))/SUM((Trades!T$2:T$9999=Blotter!C20)*(Trades!U$2:U$9999=Blotter!B20)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0))),SUM((Trades!T$2:T$9999=Blotter!C20)*(Trades!U$2:U$9999=Blotter!B20)*(Trades!W$2:W$9999)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0))/SUM((Trades!T$2:T$9999=Blotter!C20)*(Trades!U$2:U$9999=Blotter!B20)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0)),0)</f>
@@ -4383,7 +4380,7 @@
       </c>
       <c r="Z20" s="35">
         <f>IF(C$2="Last",IF(ISNUMBER(VLOOKUP(B20,Prices!A:L,8,0)),VLOOKUP(B20,Prices!A:L,8,0),0),IF(ISNUMBER(VLOOKUP(B20,Prices!A:L,12,0)),VLOOKUP(B20,Prices!A:L,12,0),0))</f>
-        <v>3418</v>
+        <v>3349</v>
       </c>
       <c r="AB20" s="29"/>
     </row>
@@ -4424,15 +4421,15 @@
       </c>
       <c r="L21" s="29">
         <f t="shared" ref="L21:L22" si="15">IF(I21=0,IF(H21&gt;0,X21,Y21),Z21)</f>
-        <v>4.63</v>
+        <v>3.52</v>
       </c>
       <c r="M21" s="28">
         <f t="shared" ref="M21:M22" si="16">I21*J21*L21</f>
-        <v>13890</v>
+        <v>10560</v>
       </c>
       <c r="N21" s="95">
         <f t="array" ref="N21">-SUM((Trades!T$2:T$9999=Blotter!C21)*(Trades!U$2:U$9999=Blotter!B21)*(Trades!V$2:V$9999)*(Trades!W$2:W$9999))*J21+SUM((Trades!T$2:T$9999=Blotter!C21)*(Trades!U$2:U$9999=Blotter!B21)*(Trades!X$2:X$9999))+(L21*I21)*J21</f>
-        <v>3262.8899999999976</v>
+        <v>-67.110000000002401</v>
       </c>
       <c r="O21" s="29">
         <f>VLOOKUP(D21,Multiplier!B:H,3,0)</f>
@@ -4472,7 +4469,7 @@
       </c>
       <c r="Z21" s="35">
         <f>IF(C$2="Last",IF(ISNUMBER(VLOOKUP(B21,Prices!A:L,8,0)),VLOOKUP(B21,Prices!A:L,8,0),0),IF(ISNUMBER(VLOOKUP(B21,Prices!A:L,12,0)),VLOOKUP(B21,Prices!A:L,12,0),0))</f>
-        <v>4.63</v>
+        <v>3.52</v>
       </c>
       <c r="AB21" s="29"/>
     </row>
@@ -4509,19 +4506,19 @@
       </c>
       <c r="K22" s="29">
         <f t="shared" si="14"/>
-        <v>0.34762999999999999</v>
+        <v>0.34762999999999994</v>
       </c>
       <c r="L22" s="29">
         <f t="shared" si="15"/>
-        <v>0.52</v>
+        <v>0.44</v>
       </c>
       <c r="M22" s="28">
         <f t="shared" si="16"/>
-        <v>-1560</v>
+        <v>-1320</v>
       </c>
       <c r="N22" s="95">
         <f t="array" ref="N22">-SUM((Trades!T$2:T$9999=Blotter!C22)*(Trades!U$2:U$9999=Blotter!B22)*(Trades!V$2:V$9999)*(Trades!W$2:W$9999))*J22+SUM((Trades!T$2:T$9999=Blotter!C22)*(Trades!U$2:U$9999=Blotter!B22)*(Trades!X$2:X$9999))+(L22*I22)*J22</f>
-        <v>-517.11000000000013</v>
+        <v>-277.11000000000013</v>
       </c>
       <c r="O22" s="29">
         <f>VLOOKUP(D22,Multiplier!B:H,3,0)</f>
@@ -4561,7 +4558,7 @@
       </c>
       <c r="Z22" s="35">
         <f>IF(C$2="Last",IF(ISNUMBER(VLOOKUP(B22,Prices!A:L,8,0)),VLOOKUP(B22,Prices!A:L,8,0),0),IF(ISNUMBER(VLOOKUP(B22,Prices!A:L,12,0)),VLOOKUP(B22,Prices!A:L,12,0),0))</f>
-        <v>0.52</v>
+        <v>0.44</v>
       </c>
       <c r="AB22" s="29"/>
     </row>
@@ -6294,31 +6291,31 @@
         <v>59</v>
       </c>
       <c r="H2" s="91">
-        <v>6720.5</v>
+        <v>6808.75</v>
       </c>
       <c r="I2" s="91">
-        <v>6720.25</v>
+        <v>6808.5</v>
       </c>
       <c r="J2" s="91">
-        <v>6720.5</v>
+        <v>6808.75</v>
       </c>
       <c r="K2" s="91">
-        <v>6720.375</v>
+        <v>6808.625</v>
       </c>
       <c r="L2" s="91">
-        <v>6755.5</v>
+        <v>6773.25</v>
       </c>
       <c r="M2" s="91">
-        <v>6751.75</v>
+        <v>6774</v>
       </c>
       <c r="N2" s="91">
-        <v>6752.5</v>
+        <v>6814</v>
       </c>
       <c r="O2" s="91">
-        <v>6715.75</v>
+        <v>6764.75</v>
       </c>
       <c r="P2" s="91">
-        <v>69906</v>
+        <v>103159</v>
       </c>
       <c r="Q2" s="91"/>
       <c r="R2" s="91"/>
@@ -6326,7 +6323,7 @@
       <c r="T2" s="91"/>
       <c r="U2" s="91"/>
       <c r="V2" s="85">
-        <v>46098.337939814817</v>
+        <v>46099.477071759262</v>
       </c>
       <c r="W2" s="81" t="s">
         <v>264</v>
@@ -6358,31 +6355,31 @@
         <v>59</v>
       </c>
       <c r="H3" s="91">
-        <v>24748.75</v>
+        <v>25187</v>
       </c>
       <c r="I3" s="91">
-        <v>24747.25</v>
+        <v>25186.25</v>
       </c>
       <c r="J3" s="91">
-        <v>24748.25</v>
+        <v>25187.25</v>
       </c>
       <c r="K3" s="91">
-        <v>24747.75</v>
+        <v>25186.75</v>
       </c>
       <c r="L3" s="91">
-        <v>24891.25</v>
+        <v>25015.5</v>
       </c>
       <c r="M3" s="91">
-        <v>24870</v>
+        <v>25019.75</v>
       </c>
       <c r="N3" s="91">
-        <v>24882</v>
+        <v>25210.5</v>
       </c>
       <c r="O3" s="91">
-        <v>24728.25</v>
+        <v>24990.75</v>
       </c>
       <c r="P3" s="91">
-        <v>39668</v>
+        <v>53733</v>
       </c>
       <c r="Q3" s="91"/>
       <c r="R3" s="91"/>
@@ -6390,7 +6387,7 @@
       <c r="T3" s="91"/>
       <c r="U3" s="91"/>
       <c r="V3" s="85">
-        <v>46098.337939814817</v>
+        <v>46099.477071759262</v>
       </c>
       <c r="W3" s="81" t="s">
         <v>264</v>
@@ -6422,31 +6419,31 @@
         <v>59</v>
       </c>
       <c r="H4" s="91">
-        <v>2494.3000000000002</v>
+        <v>2560.3000000000002</v>
       </c>
       <c r="I4" s="91">
-        <v>2493.9</v>
+        <v>2560.1</v>
       </c>
       <c r="J4" s="91">
-        <v>2494.3000000000002</v>
+        <v>2560.4</v>
       </c>
       <c r="K4" s="91">
-        <v>2494.1000000000004</v>
+        <v>2560.25</v>
       </c>
       <c r="L4" s="91">
-        <v>2520.9</v>
+        <v>2536.8000000000002</v>
       </c>
       <c r="M4" s="91">
-        <v>2514.4</v>
+        <v>2537.5</v>
       </c>
       <c r="N4" s="91">
-        <v>2518.1999999999998</v>
+        <v>2564.6</v>
       </c>
       <c r="O4" s="91">
-        <v>2490.9</v>
+        <v>2531.6999999999998</v>
       </c>
       <c r="P4" s="91">
-        <v>12229</v>
+        <v>17807</v>
       </c>
       <c r="Q4" s="91"/>
       <c r="R4" s="91"/>
@@ -6454,7 +6451,7 @@
       <c r="T4" s="91"/>
       <c r="U4" s="91"/>
       <c r="V4" s="85">
-        <v>46098.337939814817</v>
+        <v>46099.477071759262</v>
       </c>
       <c r="W4" s="81" t="s">
         <v>264</v>
@@ -6486,31 +6483,31 @@
         <v>56</v>
       </c>
       <c r="H5" s="91">
-        <v>23704</v>
+        <v>24163</v>
       </c>
       <c r="I5" s="91">
-        <v>23702</v>
+        <v>24161</v>
       </c>
       <c r="J5" s="91">
-        <v>23710</v>
+        <v>24163</v>
       </c>
       <c r="K5" s="91">
-        <v>23706</v>
+        <v>24162</v>
       </c>
       <c r="L5" s="91">
-        <v>23787</v>
+        <v>23942</v>
       </c>
       <c r="M5" s="91">
-        <v>23800</v>
+        <v>23946</v>
       </c>
       <c r="N5" s="91">
-        <v>23804</v>
+        <v>24172</v>
       </c>
       <c r="O5" s="91">
-        <v>23636</v>
+        <v>23921</v>
       </c>
       <c r="P5" s="91">
-        <v>113</v>
+        <v>4255</v>
       </c>
       <c r="Q5" s="91"/>
       <c r="R5" s="91"/>
@@ -6518,7 +6515,7 @@
       <c r="T5" s="91"/>
       <c r="U5" s="91"/>
       <c r="V5" s="85">
-        <v>46098.337939814817</v>
+        <v>46099.477071759262</v>
       </c>
       <c r="W5" s="81" t="s">
         <v>264</v>
@@ -6550,31 +6547,31 @@
         <v>57</v>
       </c>
       <c r="H6" s="91">
-        <v>53400</v>
+        <v>54615</v>
       </c>
       <c r="I6" s="91">
-        <v>53395</v>
+        <v>54615</v>
       </c>
       <c r="J6" s="91">
-        <v>53405</v>
+        <v>54625</v>
       </c>
       <c r="K6" s="91">
-        <v>53400</v>
+        <v>54620</v>
       </c>
       <c r="L6" s="91">
-        <v>54275</v>
+        <v>54105</v>
       </c>
       <c r="M6" s="91">
-        <v>54180</v>
+        <v>54160</v>
       </c>
       <c r="N6" s="91">
-        <v>54255</v>
+        <v>55090</v>
       </c>
       <c r="O6" s="91">
-        <v>53245</v>
+        <v>54040</v>
       </c>
       <c r="P6" s="91">
-        <v>4274</v>
+        <v>8518</v>
       </c>
       <c r="Q6" s="91"/>
       <c r="R6" s="91"/>
@@ -6582,7 +6579,7 @@
       <c r="T6" s="91"/>
       <c r="U6" s="91"/>
       <c r="V6" s="85">
-        <v>46098.337939814817</v>
+        <v>46099.477071759262</v>
       </c>
       <c r="W6" s="81" t="s">
         <v>264</v>
@@ -6613,25 +6610,43 @@
       <c r="G7" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="H7" s="93"/>
-      <c r="I7" s="93"/>
-      <c r="J7" s="93"/>
-      <c r="K7" s="93"/>
-      <c r="L7" s="93"/>
-      <c r="M7" s="93"/>
-      <c r="N7" s="93"/>
-      <c r="O7" s="93"/>
-      <c r="P7" s="93"/>
+      <c r="H7" s="93">
+        <v>94.75</v>
+      </c>
+      <c r="I7" s="93">
+        <v>94.74</v>
+      </c>
+      <c r="J7" s="93">
+        <v>94.76</v>
+      </c>
+      <c r="K7" s="93">
+        <v>94.75</v>
+      </c>
+      <c r="L7" s="93">
+        <v>96.21</v>
+      </c>
+      <c r="M7" s="93">
+        <v>96</v>
+      </c>
+      <c r="N7" s="93">
+        <v>96.41</v>
+      </c>
+      <c r="O7" s="93">
+        <v>91.96</v>
+      </c>
+      <c r="P7" s="93">
+        <v>33724</v>
+      </c>
       <c r="Q7" s="93"/>
       <c r="R7" s="93"/>
       <c r="S7" s="93"/>
       <c r="T7" s="93"/>
       <c r="U7" s="93"/>
       <c r="V7" s="92">
-        <v>46098.337939814817</v>
+        <v>46099.477071759262</v>
       </c>
       <c r="W7" s="1" t="s">
-        <v>324</v>
+        <v>264</v>
       </c>
     </row>
     <row r="8" spans="1:32" x14ac:dyDescent="0.4">
@@ -6657,31 +6672,31 @@
         <v>59</v>
       </c>
       <c r="H8" s="93">
-        <v>3.1459999999999999</v>
+        <v>3.0670000000000002</v>
       </c>
       <c r="I8" s="93">
-        <v>3.1480000000000001</v>
+        <v>3.0649999999999999</v>
       </c>
       <c r="J8" s="93">
-        <v>3.15</v>
+        <v>3.0680000000000001</v>
       </c>
       <c r="K8" s="93">
-        <v>3.149</v>
+        <v>3.0665</v>
       </c>
       <c r="L8" s="93">
         <v>3.1379999999999999</v>
       </c>
       <c r="M8" s="93">
-        <v>3.1459999999999999</v>
+        <v>3.1480000000000001</v>
       </c>
       <c r="N8" s="93">
-        <v>3.1640000000000001</v>
+        <v>3.153</v>
       </c>
       <c r="O8" s="93">
-        <v>3.137</v>
+        <v>3.0259999999999998</v>
       </c>
       <c r="P8" s="93">
-        <v>788</v>
+        <v>4513</v>
       </c>
       <c r="Q8" s="93"/>
       <c r="R8" s="93"/>
@@ -6689,7 +6704,7 @@
       <c r="T8" s="93"/>
       <c r="U8" s="93"/>
       <c r="V8" s="92">
-        <v>46098.337939814817</v>
+        <v>46099.477071759262</v>
       </c>
       <c r="W8" s="1" t="s">
         <v>264</v>
@@ -6718,31 +6733,31 @@
         <v>59</v>
       </c>
       <c r="H9" s="93">
-        <v>2.9365000000000001</v>
+        <v>2.9643000000000002</v>
       </c>
       <c r="I9" s="93">
-        <v>2.9373999999999998</v>
+        <v>2.9676</v>
       </c>
       <c r="J9" s="93">
-        <v>2.9382999999999999</v>
+        <v>2.9685999999999999</v>
       </c>
       <c r="K9" s="93">
-        <v>2.9378500000000001</v>
+        <v>2.9680999999999997</v>
       </c>
       <c r="L9" s="93">
-        <v>2.8407</v>
+        <v>2.9611000000000001</v>
       </c>
       <c r="M9" s="93">
-        <v>2.8595999999999999</v>
+        <v>2.9714999999999998</v>
       </c>
       <c r="N9" s="93">
-        <v>2.9523999999999999</v>
+        <v>2.9719000000000002</v>
       </c>
       <c r="O9" s="93">
-        <v>2.8584000000000001</v>
+        <v>2.9068000000000001</v>
       </c>
       <c r="P9" s="93">
-        <v>2963</v>
+        <v>4567</v>
       </c>
       <c r="Q9" s="93"/>
       <c r="R9" s="93"/>
@@ -6750,7 +6765,7 @@
       <c r="T9" s="93"/>
       <c r="U9" s="93"/>
       <c r="V9" s="92">
-        <v>46098.337939814817</v>
+        <v>46099.477071759262</v>
       </c>
       <c r="W9" s="1" t="s">
         <v>264</v>
@@ -6779,31 +6794,31 @@
         <v>59</v>
       </c>
       <c r="H10" s="93">
-        <v>5052</v>
+        <v>5031.3999999999996</v>
       </c>
       <c r="I10" s="93">
-        <v>5052</v>
+        <v>5028.8999999999996</v>
       </c>
       <c r="J10" s="93">
-        <v>5052.6000000000004</v>
+        <v>5029.3999999999996</v>
       </c>
       <c r="K10" s="93">
-        <v>5052.3</v>
+        <v>5029.1499999999996</v>
       </c>
       <c r="L10" s="93">
-        <v>5039.3999999999996</v>
+        <v>5045.6000000000004</v>
       </c>
       <c r="M10" s="93">
-        <v>5049.1000000000004</v>
+        <v>5046.6000000000004</v>
       </c>
       <c r="N10" s="93">
-        <v>5085</v>
+        <v>5058.3999999999996</v>
       </c>
       <c r="O10" s="93">
-        <v>5036.5</v>
+        <v>5020</v>
       </c>
       <c r="P10" s="93">
-        <v>1749</v>
+        <v>7937</v>
       </c>
       <c r="Q10" s="93"/>
       <c r="R10" s="93"/>
@@ -6811,7 +6826,7 @@
       <c r="T10" s="93"/>
       <c r="U10" s="93"/>
       <c r="V10" s="92">
-        <v>46098.337939814817</v>
+        <v>46099.477071759262</v>
       </c>
       <c r="W10" s="1" t="s">
         <v>264</v>
@@ -6840,31 +6855,31 @@
         <v>59</v>
       </c>
       <c r="H11" s="93">
-        <v>81.194999999999993</v>
+        <v>80.33</v>
       </c>
       <c r="I11" s="93">
-        <v>81.254999999999995</v>
+        <v>80.11</v>
       </c>
       <c r="J11" s="93">
-        <v>81.295000000000002</v>
+        <v>80.144999999999996</v>
       </c>
       <c r="K11" s="93">
-        <v>81.275000000000006</v>
+        <v>80.127499999999998</v>
       </c>
       <c r="L11" s="93">
-        <v>80.974999999999994</v>
+        <v>80.215000000000003</v>
       </c>
       <c r="M11" s="93">
-        <v>81.599999999999994</v>
+        <v>79.375</v>
       </c>
       <c r="N11" s="93">
-        <v>82.8</v>
+        <v>80.5</v>
       </c>
       <c r="O11" s="93">
-        <v>81.19</v>
+        <v>78.73</v>
       </c>
       <c r="P11" s="93">
-        <v>26</v>
+        <v>58</v>
       </c>
       <c r="Q11" s="93"/>
       <c r="R11" s="93"/>
@@ -6872,7 +6887,7 @@
       <c r="T11" s="93"/>
       <c r="U11" s="93"/>
       <c r="V11" s="92">
-        <v>46098.337939814817</v>
+        <v>46099.477071759262</v>
       </c>
       <c r="W11" s="1" t="s">
         <v>264</v>
@@ -6901,31 +6916,31 @@
         <v>59</v>
       </c>
       <c r="H12" s="93">
-        <v>5.8215000000000003</v>
+        <v>5.7629999999999999</v>
       </c>
       <c r="I12" s="93">
-        <v>5.8045</v>
+        <v>5.7625000000000002</v>
       </c>
       <c r="J12" s="93">
-        <v>5.8064999999999998</v>
+        <v>5.7640000000000002</v>
       </c>
       <c r="K12" s="93">
-        <v>5.8055000000000003</v>
+        <v>5.7632500000000002</v>
       </c>
       <c r="L12" s="93">
-        <v>5.8594999999999997</v>
+        <v>5.7949999999999999</v>
       </c>
       <c r="M12" s="93">
-        <v>5.8630000000000004</v>
+        <v>5.8</v>
       </c>
       <c r="N12" s="93">
-        <v>5.8630000000000004</v>
+        <v>5.8</v>
       </c>
       <c r="O12" s="93">
-        <v>5.8215000000000003</v>
+        <v>5.73</v>
       </c>
       <c r="P12" s="93">
-        <v>7</v>
+        <v>37</v>
       </c>
       <c r="Q12" s="93"/>
       <c r="R12" s="93"/>
@@ -6933,7 +6948,7 @@
       <c r="T12" s="93"/>
       <c r="U12" s="93"/>
       <c r="V12" s="92">
-        <v>46098.337939814817</v>
+        <v>46099.477071759262</v>
       </c>
       <c r="W12" s="1" t="s">
         <v>264</v>
@@ -6962,31 +6977,31 @@
         <v>59</v>
       </c>
       <c r="H13" s="93">
-        <v>458.5</v>
+        <v>453</v>
       </c>
       <c r="I13" s="93">
-        <v>458.25</v>
+        <v>453</v>
       </c>
       <c r="J13" s="93">
-        <v>458.5</v>
+        <v>453.25</v>
       </c>
       <c r="K13" s="93">
-        <v>458.375</v>
+        <v>453.125</v>
       </c>
       <c r="L13" s="93">
         <v>454</v>
       </c>
       <c r="M13" s="93">
-        <v>453.75</v>
+        <v>454.75</v>
       </c>
       <c r="N13" s="93">
-        <v>459</v>
+        <v>456.5</v>
       </c>
       <c r="O13" s="93">
-        <v>453.5</v>
+        <v>452.25</v>
       </c>
       <c r="P13" s="93">
-        <v>19781</v>
+        <v>21813</v>
       </c>
       <c r="Q13" s="93"/>
       <c r="R13" s="93"/>
@@ -6994,7 +7009,7 @@
       <c r="T13" s="93"/>
       <c r="U13" s="93"/>
       <c r="V13" s="92">
-        <v>46098.337939814817</v>
+        <v>46099.477071759262</v>
       </c>
       <c r="W13" s="1" t="s">
         <v>264</v>
@@ -7023,31 +7038,31 @@
         <v>59</v>
       </c>
       <c r="H14" s="93">
-        <v>603</v>
+        <v>591</v>
       </c>
       <c r="I14" s="93">
-        <v>602.75</v>
+        <v>591</v>
       </c>
       <c r="J14" s="93">
-        <v>603</v>
+        <v>591.25</v>
       </c>
       <c r="K14" s="93">
-        <v>602.875</v>
+        <v>591.125</v>
       </c>
       <c r="L14" s="93">
-        <v>597.25</v>
+        <v>589.75</v>
       </c>
       <c r="M14" s="93">
-        <v>597.25</v>
+        <v>590</v>
       </c>
       <c r="N14" s="93">
-        <v>607.25</v>
+        <v>593.5</v>
       </c>
       <c r="O14" s="93">
-        <v>596.5</v>
+        <v>586</v>
       </c>
       <c r="P14" s="93">
-        <v>6378</v>
+        <v>7705</v>
       </c>
       <c r="Q14" s="93"/>
       <c r="R14" s="93"/>
@@ -7055,7 +7070,7 @@
       <c r="T14" s="93"/>
       <c r="U14" s="93"/>
       <c r="V14" s="92">
-        <v>46098.337939814817</v>
+        <v>46099.477071759262</v>
       </c>
       <c r="W14" s="1" t="s">
         <v>264</v>
@@ -7084,31 +7099,31 @@
         <v>59</v>
       </c>
       <c r="H15" s="93">
-        <v>1161.75</v>
+        <v>1153</v>
       </c>
       <c r="I15" s="93">
-        <v>1161.5</v>
+        <v>1152.75</v>
       </c>
       <c r="J15" s="93">
-        <v>1161.75</v>
+        <v>1153.25</v>
       </c>
       <c r="K15" s="93">
-        <v>1161.625</v>
+        <v>1153</v>
       </c>
       <c r="L15" s="93">
-        <v>1155.25</v>
+        <v>1157</v>
       </c>
       <c r="M15" s="93">
-        <v>1147</v>
+        <v>1156.25</v>
       </c>
       <c r="N15" s="93">
-        <v>1164.5</v>
+        <v>1160</v>
       </c>
       <c r="O15" s="93">
-        <v>1145.25</v>
+        <v>1149</v>
       </c>
       <c r="P15" s="93">
-        <v>26383</v>
+        <v>15858</v>
       </c>
       <c r="Q15" s="93"/>
       <c r="R15" s="93"/>
@@ -7116,7 +7131,7 @@
       <c r="T15" s="93"/>
       <c r="U15" s="93"/>
       <c r="V15" s="92">
-        <v>46098.337939814817</v>
+        <v>46099.477071759262</v>
       </c>
       <c r="W15" s="1" t="s">
         <v>264</v>
@@ -7145,27 +7160,31 @@
         <v>59</v>
       </c>
       <c r="H16" s="93">
-        <v>0</v>
+        <v>14.52</v>
       </c>
       <c r="I16" s="93">
-        <v>-100</v>
+        <v>14.51</v>
       </c>
       <c r="J16" s="93">
-        <v>-100</v>
+        <v>14.52</v>
       </c>
       <c r="K16" s="93">
-        <v>-100</v>
+        <v>14.515000000000001</v>
       </c>
       <c r="L16" s="93">
-        <v>14.19</v>
+        <v>14.45</v>
       </c>
       <c r="M16" s="93">
-        <v>0</v>
-      </c>
-      <c r="N16" s="93"/>
-      <c r="O16" s="93"/>
+        <v>14.39</v>
+      </c>
+      <c r="N16" s="93">
+        <v>14.57</v>
+      </c>
+      <c r="O16" s="93">
+        <v>14.35</v>
+      </c>
       <c r="P16" s="93">
-        <v>0</v>
+        <v>21909</v>
       </c>
       <c r="Q16" s="93"/>
       <c r="R16" s="93"/>
@@ -7173,7 +7192,7 @@
       <c r="T16" s="93"/>
       <c r="U16" s="93"/>
       <c r="V16" s="92">
-        <v>46098.337939814817</v>
+        <v>46099.477071759262</v>
       </c>
       <c r="W16" s="1" t="s">
         <v>264</v>
@@ -7202,27 +7221,31 @@
         <v>59</v>
       </c>
       <c r="H17" s="93">
-        <v>0</v>
+        <v>293.3</v>
       </c>
       <c r="I17" s="93">
-        <v>-100</v>
+        <v>293.3</v>
       </c>
       <c r="J17" s="93">
-        <v>-100</v>
+        <v>293.39999999999998</v>
       </c>
       <c r="K17" s="93">
-        <v>-100</v>
+        <v>293.35000000000002</v>
       </c>
       <c r="L17" s="93">
-        <v>292.85000000000002</v>
+        <v>294.75</v>
       </c>
       <c r="M17" s="93">
-        <v>0</v>
-      </c>
-      <c r="N17" s="93"/>
-      <c r="O17" s="93"/>
+        <v>294.39999999999998</v>
+      </c>
+      <c r="N17" s="93">
+        <v>295.2</v>
+      </c>
+      <c r="O17" s="93">
+        <v>292.2</v>
+      </c>
       <c r="P17" s="93">
-        <v>0</v>
+        <v>1189</v>
       </c>
       <c r="Q17" s="93"/>
       <c r="R17" s="93"/>
@@ -7230,7 +7253,7 @@
       <c r="T17" s="93"/>
       <c r="U17" s="93"/>
       <c r="V17" s="92">
-        <v>46098.337939814817</v>
+        <v>46099.477071759262</v>
       </c>
       <c r="W17" s="1" t="s">
         <v>264</v>
@@ -7259,27 +7282,31 @@
         <v>59</v>
       </c>
       <c r="H18" s="93">
-        <v>0</v>
+        <v>3367</v>
       </c>
       <c r="I18" s="93">
-        <v>-1</v>
+        <v>3364</v>
       </c>
       <c r="J18" s="93">
-        <v>-1</v>
+        <v>3367</v>
       </c>
       <c r="K18" s="93">
-        <v>-1</v>
+        <v>3365.5</v>
       </c>
       <c r="L18" s="93">
-        <v>3418</v>
+        <v>3349</v>
       </c>
       <c r="M18" s="93">
-        <v>0</v>
-      </c>
-      <c r="N18" s="93"/>
-      <c r="O18" s="93"/>
+        <v>3377</v>
+      </c>
+      <c r="N18" s="93">
+        <v>3386</v>
+      </c>
+      <c r="O18" s="93">
+        <v>3357</v>
+      </c>
       <c r="P18" s="93">
-        <v>0</v>
+        <v>736</v>
       </c>
       <c r="Q18" s="93"/>
       <c r="R18" s="93"/>
@@ -7287,7 +7314,7 @@
       <c r="T18" s="93"/>
       <c r="U18" s="93"/>
       <c r="V18" s="92">
-        <v>46098.337939814817</v>
+        <v>46099.477071759262</v>
       </c>
       <c r="W18" s="1" t="s">
         <v>264</v>
@@ -7316,31 +7343,31 @@
         <v>59</v>
       </c>
       <c r="H19" s="93">
-        <v>68.010000000000005</v>
+        <v>68.53</v>
       </c>
       <c r="I19" s="93">
-        <v>68</v>
+        <v>68.53</v>
       </c>
       <c r="J19" s="93">
-        <v>68.010000000000005</v>
+        <v>68.540000000000006</v>
       </c>
       <c r="K19" s="93">
-        <v>68.004999999999995</v>
+        <v>68.534999999999997</v>
       </c>
       <c r="L19" s="93">
-        <v>68.19</v>
+        <v>68.77</v>
       </c>
       <c r="M19" s="93">
+        <v>68.7</v>
+      </c>
+      <c r="N19" s="93">
+        <v>68.86</v>
+      </c>
+      <c r="O19" s="93">
         <v>68.260000000000005</v>
       </c>
-      <c r="N19" s="93">
-        <v>68.63</v>
-      </c>
-      <c r="O19" s="93">
-        <v>67.959999999999994</v>
-      </c>
       <c r="P19" s="93">
-        <v>5193</v>
+        <v>6793</v>
       </c>
       <c r="Q19" s="93"/>
       <c r="R19" s="93"/>
@@ -7348,7 +7375,7 @@
       <c r="T19" s="93"/>
       <c r="U19" s="93"/>
       <c r="V19" s="92">
-        <v>46098.337939814817</v>
+        <v>46099.477071759262</v>
       </c>
       <c r="W19" s="1" t="s">
         <v>264</v>
@@ -7389,19 +7416,15 @@
         <v>-100</v>
       </c>
       <c r="L20" s="93">
-        <v>233.25</v>
+        <v>235.22499999999999</v>
       </c>
       <c r="M20" s="93">
-        <v>230.9</v>
-      </c>
-      <c r="N20" s="93">
-        <v>233.95</v>
-      </c>
-      <c r="O20" s="93">
-        <v>230.82499999999999</v>
-      </c>
+        <v>233.75</v>
+      </c>
+      <c r="N20" s="93"/>
+      <c r="O20" s="93"/>
       <c r="P20" s="93">
-        <v>16745</v>
+        <v>0</v>
       </c>
       <c r="Q20" s="93"/>
       <c r="R20" s="93"/>
@@ -7409,7 +7432,7 @@
       <c r="T20" s="93"/>
       <c r="U20" s="93"/>
       <c r="V20" s="92">
-        <v>46098.337939814817</v>
+        <v>46099.477071759262</v>
       </c>
       <c r="W20" s="1" t="s">
         <v>264</v>
@@ -7438,7 +7461,7 @@
         <v>59</v>
       </c>
       <c r="H21" s="93">
-        <v>0</v>
+        <v>350.3</v>
       </c>
       <c r="I21" s="93">
         <v>-100</v>
@@ -7450,19 +7473,19 @@
         <v>-100</v>
       </c>
       <c r="L21" s="93">
-        <v>345.55</v>
+        <v>350.625</v>
       </c>
       <c r="M21" s="93">
-        <v>340.57499999999999</v>
+        <v>346.27499999999998</v>
       </c>
       <c r="N21" s="93">
-        <v>346</v>
+        <v>351.3</v>
       </c>
       <c r="O21" s="93">
-        <v>340</v>
+        <v>345.82499999999999</v>
       </c>
       <c r="P21" s="93">
-        <v>5413</v>
+        <v>5629</v>
       </c>
       <c r="Q21" s="93"/>
       <c r="R21" s="93"/>
@@ -7470,7 +7493,7 @@
       <c r="T21" s="93"/>
       <c r="U21" s="93"/>
       <c r="V21" s="92">
-        <v>46098.337939814817</v>
+        <v>46099.477071759262</v>
       </c>
       <c r="W21" s="1" t="s">
         <v>264</v>
@@ -7511,19 +7534,15 @@
         <v>-100</v>
       </c>
       <c r="L22" s="93">
+        <v>93.724999999999994</v>
+      </c>
+      <c r="M22" s="93">
         <v>93.5</v>
       </c>
-      <c r="M22" s="93">
-        <v>93.7</v>
-      </c>
-      <c r="N22" s="93">
-        <v>94.15</v>
-      </c>
-      <c r="O22" s="93">
-        <v>93.4</v>
-      </c>
+      <c r="N22" s="93"/>
+      <c r="O22" s="93"/>
       <c r="P22" s="93">
-        <v>16618</v>
+        <v>0</v>
       </c>
       <c r="Q22" s="93"/>
       <c r="R22" s="93"/>
@@ -7531,7 +7550,7 @@
       <c r="T22" s="93"/>
       <c r="U22" s="93"/>
       <c r="V22" s="92">
-        <v>46098.337939814817</v>
+        <v>46099.477071759262</v>
       </c>
       <c r="W22" s="1" t="s">
         <v>264</v>
@@ -7560,31 +7579,31 @@
         <v>59</v>
       </c>
       <c r="H23" s="93">
-        <v>99.795000000000002</v>
+        <v>99.334999999999994</v>
       </c>
       <c r="I23" s="93">
-        <v>99.79</v>
+        <v>99.325000000000003</v>
       </c>
       <c r="J23" s="93">
-        <v>99.8</v>
+        <v>99.33</v>
       </c>
       <c r="K23" s="93">
-        <v>99.795000000000002</v>
+        <v>99.327500000000001</v>
       </c>
       <c r="L23" s="93">
-        <v>99.47</v>
+        <v>99.33</v>
       </c>
       <c r="M23" s="93">
-        <v>99.625</v>
+        <v>99.32</v>
       </c>
       <c r="N23" s="93">
-        <v>99.87</v>
+        <v>99.474999999999994</v>
       </c>
       <c r="O23" s="93">
-        <v>99.605000000000004</v>
+        <v>99.22</v>
       </c>
       <c r="P23" s="93">
-        <v>2535</v>
+        <v>3344</v>
       </c>
       <c r="Q23" s="93"/>
       <c r="R23" s="93"/>
@@ -7592,7 +7611,7 @@
       <c r="T23" s="93"/>
       <c r="U23" s="93"/>
       <c r="V23" s="92">
-        <v>46098.337939814817</v>
+        <v>46099.477071759262</v>
       </c>
       <c r="W23" s="1" t="s">
         <v>264</v>
@@ -7621,31 +7640,31 @@
         <v>59</v>
       </c>
       <c r="H24" s="93">
-        <v>1.1526000000000001</v>
+        <v>1.1591</v>
       </c>
       <c r="I24" s="93">
-        <v>1.1526000000000001</v>
+        <v>1.1590499999999999</v>
       </c>
       <c r="J24" s="93">
-        <v>1.15265</v>
+        <v>1.1591499999999999</v>
       </c>
       <c r="K24" s="93">
-        <v>1.152625</v>
+        <v>1.1591</v>
       </c>
       <c r="L24" s="93">
-        <v>1.1568000000000001</v>
+        <v>1.1588499999999999</v>
       </c>
       <c r="M24" s="93">
-        <v>1.1555500000000001</v>
+        <v>1.1588000000000001</v>
       </c>
       <c r="N24" s="93">
-        <v>1.1555500000000001</v>
+        <v>1.15985</v>
       </c>
       <c r="O24" s="93">
-        <v>1.1515500000000001</v>
+        <v>1.1567000000000001</v>
       </c>
       <c r="P24" s="93">
-        <v>27446</v>
+        <v>40607</v>
       </c>
       <c r="Q24" s="93"/>
       <c r="R24" s="93"/>
@@ -7653,7 +7672,7 @@
       <c r="T24" s="93"/>
       <c r="U24" s="93"/>
       <c r="V24" s="92">
-        <v>46098.337939814817</v>
+        <v>46099.477071759262</v>
       </c>
       <c r="W24" s="1" t="s">
         <v>264</v>
@@ -7682,31 +7701,31 @@
         <v>59</v>
       </c>
       <c r="H25" s="93">
-        <v>1.3284</v>
+        <v>1.3359000000000001</v>
       </c>
       <c r="I25" s="93">
-        <v>1.3284</v>
+        <v>1.3358000000000001</v>
       </c>
       <c r="J25" s="93">
-        <v>1.3285</v>
+        <v>1.3359000000000001</v>
       </c>
       <c r="K25" s="93">
-        <v>1.3284500000000001</v>
+        <v>1.3358500000000002</v>
       </c>
       <c r="L25" s="93">
-        <v>1.3331</v>
+        <v>1.3355999999999999</v>
       </c>
       <c r="M25" s="93">
-        <v>1.3318000000000001</v>
+        <v>1.3359000000000001</v>
       </c>
       <c r="N25" s="93">
-        <v>1.3319000000000001</v>
+        <v>1.3373999999999999</v>
       </c>
       <c r="O25" s="93">
-        <v>1.3272999999999999</v>
+        <v>1.3341000000000001</v>
       </c>
       <c r="P25" s="93">
-        <v>14032</v>
+        <v>18707</v>
       </c>
       <c r="Q25" s="93"/>
       <c r="R25" s="93"/>
@@ -7714,7 +7733,7 @@
       <c r="T25" s="93"/>
       <c r="U25" s="93"/>
       <c r="V25" s="92">
-        <v>46098.337939814817</v>
+        <v>46099.477071759262</v>
       </c>
       <c r="W25" s="1" t="s">
         <v>264</v>
@@ -7743,31 +7762,31 @@
         <v>59</v>
       </c>
       <c r="H26" s="93">
-        <v>6.3220000000000004E-3</v>
+        <v>6.3355E-3</v>
       </c>
       <c r="I26" s="93">
-        <v>6.3220000000000004E-3</v>
+        <v>6.3350000000000004E-3</v>
       </c>
       <c r="J26" s="93">
-        <v>6.3225E-3</v>
+        <v>6.3355E-3</v>
       </c>
       <c r="K26" s="93">
-        <v>6.3222499999999997E-3</v>
+        <v>6.3352500000000006E-3</v>
       </c>
       <c r="L26" s="93">
-        <v>6.339E-3</v>
+        <v>6.3350000000000004E-3</v>
       </c>
       <c r="M26" s="93">
-        <v>6.3344999999999999E-3</v>
+        <v>6.3369999999999998E-3</v>
       </c>
       <c r="N26" s="93">
-        <v>6.3365000000000001E-3</v>
+        <v>6.3524999999999996E-3</v>
       </c>
       <c r="O26" s="93">
-        <v>6.3175000000000002E-3</v>
+        <v>6.3299999999999997E-3</v>
       </c>
       <c r="P26" s="93">
-        <v>26200</v>
+        <v>35115</v>
       </c>
       <c r="Q26" s="93"/>
       <c r="R26" s="93"/>
@@ -7775,7 +7794,7 @@
       <c r="T26" s="93"/>
       <c r="U26" s="93"/>
       <c r="V26" s="92">
-        <v>46098.337939814817</v>
+        <v>46099.477071759262</v>
       </c>
       <c r="W26" s="1" t="s">
         <v>264</v>
@@ -7804,31 +7823,31 @@
         <v>59</v>
       </c>
       <c r="H27" s="93">
-        <v>0.73294999999999999</v>
+        <v>0.73324999999999996</v>
       </c>
       <c r="I27" s="93">
-        <v>0.7329</v>
+        <v>0.73319999999999996</v>
       </c>
       <c r="J27" s="93">
+        <v>0.73324999999999996</v>
+      </c>
+      <c r="K27" s="93">
+        <v>0.73322500000000002</v>
+      </c>
+      <c r="L27" s="93">
         <v>0.73299999999999998</v>
       </c>
-      <c r="K27" s="93">
-        <v>0.73294999999999999</v>
-      </c>
-      <c r="L27" s="93">
-        <v>0.73419999999999996</v>
-      </c>
       <c r="M27" s="93">
-        <v>0.73380000000000001</v>
+        <v>0.73329999999999995</v>
       </c>
       <c r="N27" s="93">
-        <v>0.7339</v>
+        <v>0.73350000000000004</v>
       </c>
       <c r="O27" s="93">
-        <v>0.73280000000000001</v>
+        <v>0.73209999999999997</v>
       </c>
       <c r="P27" s="93">
-        <v>7578</v>
+        <v>10027</v>
       </c>
       <c r="Q27" s="93"/>
       <c r="R27" s="93"/>
@@ -7836,7 +7855,7 @@
       <c r="T27" s="93"/>
       <c r="U27" s="93"/>
       <c r="V27" s="92">
-        <v>46098.337939814817</v>
+        <v>46099.477071759262</v>
       </c>
       <c r="W27" s="1" t="s">
         <v>264</v>
@@ -7865,31 +7884,31 @@
         <v>59</v>
       </c>
       <c r="H28" s="93">
-        <v>0.70599999999999996</v>
+        <v>0.71014999999999995</v>
       </c>
       <c r="I28" s="93">
-        <v>0.70594999999999997</v>
+        <v>0.71009999999999995</v>
       </c>
       <c r="J28" s="93">
-        <v>0.70604999999999996</v>
+        <v>0.71020000000000005</v>
       </c>
       <c r="K28" s="93">
-        <v>0.70599999999999996</v>
+        <v>0.71015000000000006</v>
       </c>
       <c r="L28" s="93">
-        <v>0.70674999999999999</v>
+        <v>0.70960000000000001</v>
       </c>
       <c r="M28" s="93">
-        <v>0.70655000000000001</v>
+        <v>0.70955000000000001</v>
       </c>
       <c r="N28" s="93">
-        <v>0.70874999999999999</v>
+        <v>0.71145000000000003</v>
       </c>
       <c r="O28" s="93">
-        <v>0.70415000000000005</v>
+        <v>0.70904999999999996</v>
       </c>
       <c r="P28" s="93">
-        <v>40831</v>
+        <v>24405</v>
       </c>
       <c r="Q28" s="93"/>
       <c r="R28" s="93"/>
@@ -7897,7 +7916,7 @@
       <c r="T28" s="93"/>
       <c r="U28" s="93"/>
       <c r="V28" s="92">
-        <v>46098.337939814817</v>
+        <v>46099.477071759262</v>
       </c>
       <c r="W28" s="1" t="s">
         <v>264</v>
@@ -7926,31 +7945,31 @@
         <v>59</v>
       </c>
       <c r="H29" s="93">
-        <v>114.125</v>
+        <v>115.125</v>
       </c>
       <c r="I29" s="93">
-        <v>114.125</v>
+        <v>115.125</v>
       </c>
       <c r="J29" s="93">
-        <v>114.15625</v>
+        <v>115.15625</v>
       </c>
       <c r="K29" s="93">
-        <v>114.140625</v>
+        <v>115.140625</v>
       </c>
       <c r="L29" s="93">
-        <v>114.625</v>
+        <v>114.8125</v>
       </c>
       <c r="M29" s="93">
-        <v>114.5</v>
+        <v>114.84375</v>
       </c>
       <c r="N29" s="93">
-        <v>114.5</v>
+        <v>115.34375</v>
       </c>
       <c r="O29" s="93">
-        <v>114.125</v>
+        <v>114.78125</v>
       </c>
       <c r="P29" s="93">
-        <v>26274</v>
+        <v>52811</v>
       </c>
       <c r="Q29" s="93"/>
       <c r="R29" s="93"/>
@@ -7958,7 +7977,7 @@
       <c r="T29" s="93"/>
       <c r="U29" s="93"/>
       <c r="V29" s="92">
-        <v>46098.337939814817</v>
+        <v>46099.477071759262</v>
       </c>
       <c r="W29" s="1" t="s">
         <v>264</v>
@@ -7987,31 +8006,31 @@
         <v>59</v>
       </c>
       <c r="H30" s="93">
-        <v>111.71875</v>
+        <v>112.109375</v>
       </c>
       <c r="I30" s="93">
-        <v>111.71875</v>
+        <v>112.09375</v>
       </c>
       <c r="J30" s="93">
-        <v>111.734375</v>
+        <v>112.109375</v>
       </c>
       <c r="K30" s="93">
-        <v>111.7265625</v>
+        <v>112.1015625</v>
       </c>
       <c r="L30" s="93">
-        <v>111.890625</v>
+        <v>112</v>
       </c>
       <c r="M30" s="93">
-        <v>111.875</v>
+        <v>111.984375</v>
       </c>
       <c r="N30" s="93">
-        <v>111.90625</v>
+        <v>112.21875</v>
       </c>
       <c r="O30" s="93">
-        <v>111.6875</v>
+        <v>111.953125</v>
       </c>
       <c r="P30" s="93">
-        <v>121757</v>
+        <v>253739</v>
       </c>
       <c r="Q30" s="93"/>
       <c r="R30" s="93"/>
@@ -8019,7 +8038,7 @@
       <c r="T30" s="93"/>
       <c r="U30" s="93"/>
       <c r="V30" s="92">
-        <v>46098.337939814817</v>
+        <v>46099.477071759262</v>
       </c>
       <c r="W30" s="1" t="s">
         <v>264</v>
@@ -8048,31 +8067,31 @@
         <v>56</v>
       </c>
       <c r="H31" s="93">
-        <v>126.07</v>
+        <v>126.8</v>
       </c>
       <c r="I31" s="93">
-        <v>126.06</v>
+        <v>126.8</v>
       </c>
       <c r="J31" s="93">
-        <v>126.07</v>
+        <v>126.81</v>
       </c>
       <c r="K31" s="93">
-        <v>126.065</v>
+        <v>126.80500000000001</v>
       </c>
       <c r="L31" s="93">
-        <v>126.19</v>
+        <v>126.47</v>
       </c>
       <c r="M31" s="93">
-        <v>126.22</v>
+        <v>126.5</v>
       </c>
       <c r="N31" s="93">
-        <v>126.27</v>
+        <v>126.83</v>
       </c>
       <c r="O31" s="93">
-        <v>126.03</v>
+        <v>126.46</v>
       </c>
       <c r="P31" s="93">
-        <v>13199</v>
+        <v>272263</v>
       </c>
       <c r="Q31" s="93"/>
       <c r="R31" s="93"/>
@@ -8080,7 +8099,7 @@
       <c r="T31" s="93"/>
       <c r="U31" s="93"/>
       <c r="V31" s="92">
-        <v>46098.337939814817</v>
+        <v>46099.477071759262</v>
       </c>
       <c r="W31" s="1" t="s">
         <v>264</v>
@@ -8109,31 +8128,31 @@
         <v>56</v>
       </c>
       <c r="H32" s="93">
-        <v>109.04</v>
+        <v>110.48</v>
       </c>
       <c r="I32" s="93">
-        <v>109.04</v>
+        <v>110.46</v>
       </c>
       <c r="J32" s="93">
-        <v>109.06</v>
+        <v>110.48</v>
       </c>
       <c r="K32" s="93">
-        <v>109.05000000000001</v>
+        <v>110.47</v>
       </c>
       <c r="L32" s="93">
-        <v>109.22</v>
+        <v>109.88</v>
       </c>
       <c r="M32" s="93">
-        <v>109.36</v>
+        <v>109.9</v>
       </c>
       <c r="N32" s="93">
-        <v>109.36</v>
+        <v>110.58</v>
       </c>
       <c r="O32" s="93">
-        <v>109.02</v>
+        <v>109.82</v>
       </c>
       <c r="P32" s="93">
-        <v>1461</v>
+        <v>41973</v>
       </c>
       <c r="Q32" s="93"/>
       <c r="R32" s="93"/>
@@ -8141,7 +8160,7 @@
       <c r="T32" s="93"/>
       <c r="U32" s="93"/>
       <c r="V32" s="92">
-        <v>46098.337939814817</v>
+        <v>46099.477071759262</v>
       </c>
       <c r="W32" s="1" t="s">
         <v>264</v>
@@ -8170,31 +8189,31 @@
         <v>56</v>
       </c>
       <c r="H33" s="93">
-        <v>117.8</v>
+        <v>118.85</v>
       </c>
       <c r="I33" s="93">
-        <v>117.8</v>
+        <v>118.84</v>
       </c>
       <c r="J33" s="93">
-        <v>117.81</v>
+        <v>118.85</v>
       </c>
       <c r="K33" s="93">
-        <v>117.80500000000001</v>
+        <v>118.845</v>
       </c>
       <c r="L33" s="93">
-        <v>117.99</v>
+        <v>118.37</v>
       </c>
       <c r="M33" s="93">
-        <v>117.82</v>
+        <v>118.73</v>
       </c>
       <c r="N33" s="93">
-        <v>117.83</v>
+        <v>118.88</v>
       </c>
       <c r="O33" s="93">
-        <v>117.75</v>
+        <v>118.67</v>
       </c>
       <c r="P33" s="93">
-        <v>1082</v>
+        <v>90427</v>
       </c>
       <c r="Q33" s="93"/>
       <c r="R33" s="93"/>
@@ -8202,7 +8221,7 @@
       <c r="T33" s="93"/>
       <c r="U33" s="93"/>
       <c r="V33" s="92">
-        <v>46098.337939814817</v>
+        <v>46099.477071759262</v>
       </c>
       <c r="W33" s="1" t="s">
         <v>264</v>
@@ -8231,29 +8250,29 @@
         <v>59</v>
       </c>
       <c r="H34" s="93">
-        <v>74173.25</v>
+        <v>74198.25</v>
       </c>
       <c r="I34" s="93">
-        <v>74173</v>
+        <v>74198</v>
       </c>
       <c r="J34" s="93">
-        <v>74173.25</v>
+        <v>74198.25</v>
       </c>
       <c r="K34" s="93">
-        <v>74173.125</v>
+        <v>74198.125</v>
       </c>
       <c r="L34" s="93">
-        <v>73946.75</v>
+        <v>74545</v>
       </c>
       <c r="M34" s="93"/>
       <c r="N34" s="93">
-        <v>76128.75</v>
+        <v>74822.25</v>
       </c>
       <c r="O34" s="93">
-        <v>71142.5</v>
+        <v>73304.75</v>
       </c>
       <c r="P34" s="93">
-        <v>200.06584436</v>
+        <v>88.767262759999994</v>
       </c>
       <c r="Q34" s="93"/>
       <c r="R34" s="93"/>
@@ -8261,7 +8280,7 @@
       <c r="T34" s="93"/>
       <c r="U34" s="93"/>
       <c r="V34" s="92">
-        <v>46098.337939814817</v>
+        <v>46099.477071759262</v>
       </c>
       <c r="W34" s="1" t="s">
         <v>264</v>
@@ -8290,29 +8309,29 @@
         <v>59</v>
       </c>
       <c r="H35" s="93">
-        <v>2320</v>
+        <v>2329.3000000000002</v>
       </c>
       <c r="I35" s="93">
-        <v>2320</v>
+        <v>2329.25</v>
       </c>
       <c r="J35" s="93">
-        <v>2320.0500000000002</v>
+        <v>2329.3000000000002</v>
       </c>
       <c r="K35" s="93">
-        <v>2320.0250000000001</v>
+        <v>2329.2750000000001</v>
       </c>
       <c r="L35" s="93">
-        <v>2329.3000000000002</v>
+        <v>2321.4499999999998</v>
       </c>
       <c r="M35" s="93"/>
       <c r="N35" s="93">
-        <v>2385</v>
+        <v>2351.35</v>
       </c>
       <c r="O35" s="93">
-        <v>2110.35</v>
+        <v>2308.85</v>
       </c>
       <c r="P35" s="93">
-        <v>1382.66226983</v>
+        <v>1069.2230012800001</v>
       </c>
       <c r="Q35" s="93"/>
       <c r="R35" s="93"/>
@@ -8320,7 +8339,7 @@
       <c r="T35" s="93"/>
       <c r="U35" s="93"/>
       <c r="V35" s="92">
-        <v>46098.337939814817</v>
+        <v>46099.477071759262</v>
       </c>
       <c r="W35" s="1" t="s">
         <v>264</v>
@@ -8349,47 +8368,47 @@
         <v>59</v>
       </c>
       <c r="H36" s="93">
-        <v>3.73</v>
+        <v>3.72</v>
       </c>
       <c r="I36" s="93">
-        <v>3.63</v>
+        <v>3.55</v>
       </c>
       <c r="J36" s="93">
-        <v>3.76</v>
+        <v>3.59</v>
       </c>
       <c r="K36" s="93">
-        <v>3.6949999999999998</v>
+        <v>3.57</v>
       </c>
       <c r="L36" s="93">
-        <v>4.63</v>
+        <v>3.52</v>
       </c>
       <c r="M36" s="93"/>
       <c r="N36" s="93">
-        <v>3.73</v>
+        <v>3.9</v>
       </c>
       <c r="O36" s="93">
-        <v>3.73</v>
+        <v>3.72</v>
       </c>
       <c r="P36" s="93">
-        <v>3</v>
+        <v>262</v>
       </c>
       <c r="Q36" s="93">
-        <v>0.76379265459558976</v>
+        <v>0.72512493857815341</v>
       </c>
       <c r="R36" s="93">
-        <v>-0.20077302122016485</v>
+        <v>-0.20999233654000748</v>
       </c>
       <c r="S36" s="93">
-        <v>9.939670529318094E-3</v>
+        <v>1.1079477126531177E-2</v>
       </c>
       <c r="T36" s="93">
-        <v>0.10246481654123096</v>
+        <v>0.10064267792560955</v>
       </c>
       <c r="U36" s="93">
-        <v>-6.6869197110559053E-2</v>
+        <v>-6.3596295977592643E-2</v>
       </c>
       <c r="V36" s="92">
-        <v>46098.337939814817</v>
+        <v>46099.477071759262</v>
       </c>
       <c r="W36" s="1" t="s">
         <v>264</v>
@@ -8418,47 +8437,47 @@
         <v>59</v>
       </c>
       <c r="H37" s="93">
-        <v>0.43</v>
+        <v>0.45</v>
       </c>
       <c r="I37" s="93">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="J37" s="93">
-        <v>0.46</v>
+        <v>0.45</v>
       </c>
       <c r="K37" s="93">
-        <v>0.42000000000000004</v>
+        <v>0.44500000000000001</v>
       </c>
       <c r="L37" s="93">
-        <v>0.52</v>
+        <v>0.44</v>
       </c>
       <c r="M37" s="93"/>
       <c r="N37" s="93">
-        <v>0.43</v>
+        <v>0.46</v>
       </c>
       <c r="O37" s="93">
         <v>0.43</v>
       </c>
       <c r="P37" s="93">
-        <v>2</v>
+        <v>112</v>
       </c>
       <c r="Q37" s="93">
-        <v>0.78339083861671788</v>
+        <v>0.77219810289234758</v>
       </c>
       <c r="R37" s="93">
-        <v>-3.4546268455653943E-2</v>
+        <v>-3.64511147092485E-2</v>
       </c>
       <c r="S37" s="93">
-        <v>2.640763838621875E-3</v>
+        <v>2.8861421876029158E-3</v>
       </c>
       <c r="T37" s="93">
-        <v>2.6225796728602702E-2</v>
+        <v>2.5743027944748809E-2</v>
       </c>
       <c r="U37" s="93">
-        <v>-1.7602301867683245E-2</v>
+        <v>-1.7368441701636483E-2</v>
       </c>
       <c r="V37" s="92">
-        <v>46098.337939814817</v>
+        <v>46099.477071759262</v>
       </c>
       <c r="W37" s="1" t="s">
         <v>264</v>
@@ -8906,10 +8925,10 @@
         <v>46098.336087962962</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.4">
@@ -8920,17 +8939,41 @@
         <v>299</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A28" s="85"/>
+      <c r="A28" s="85">
+        <v>46099.474259259259</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>300</v>
+      </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A29" s="85"/>
+      <c r="A29" s="85">
+        <v>46099.474270833336</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>301</v>
+      </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A30" s="85"/>
+      <c r="A30" s="85">
+        <v>46099.474270833336</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>316</v>
+      </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A31" s="85"/>
@@ -9334,11 +9377,11 @@
       <c r="H5" s="67"/>
       <c r="I5" s="70">
         <f>Blotter!C$4-SUM(NAV!I$4:I4)</f>
-        <v>10025.060632009898</v>
+        <v>4865.0606320098977</v>
       </c>
       <c r="J5" s="70">
         <f t="shared" si="2"/>
-        <v>1010025.0606320099</v>
+        <v>1004865.0606320099</v>
       </c>
       <c r="K5" s="70">
         <f t="shared" si="3"/>
@@ -9346,19 +9389,19 @@
       </c>
       <c r="L5" s="71">
         <f t="shared" si="4"/>
-        <v>1010.0250606320099</v>
+        <v>1004.8650606320099</v>
       </c>
       <c r="M5" s="72">
         <f t="shared" si="5"/>
-        <v>1.0025060632009808E-2</v>
+        <v>4.8650606320099765E-3</v>
       </c>
       <c r="N5" s="73">
         <f t="shared" ref="N5" si="6">L5/L4-1</f>
-        <v>1.0025060632009808E-2</v>
+        <v>4.8650606320099765E-3</v>
       </c>
       <c r="O5" s="75">
         <f>STDEVP(N$4:N5)*SQRT(12)</f>
-        <v>1.7363914363599547E-2</v>
+        <v>8.4265321965444322E-3</v>
       </c>
     </row>
     <row r="6" spans="2:18" ht="14.25" x14ac:dyDescent="0.4">
@@ -9838,7 +9881,7 @@
       </c>
       <c r="D5" s="6">
         <f t="array" ref="D5">SUM((Blotter!C$19:C$1013=C5)*(Blotter!N$19:N$1013)*1)</f>
-        <v>5481.0899999999965</v>
+        <v>3411.0899999999965</v>
       </c>
       <c r="E5" s="6">
         <f t="array" ref="E5">SUM((Blotter!B$19:C$1013=C5)*(Blotter!R$19:R$1013)*1)</f>
@@ -9846,7 +9889,7 @@
       </c>
       <c r="F5" s="30">
         <f t="shared" ref="F5" si="1">IF(ISNUMBER(D5/E5),D5/E5,0)</f>
-        <v>0.60900999999999961</v>
+        <v>0.37900999999999962</v>
       </c>
       <c r="G5" s="36" t="str">
         <f t="array" ref="G5">IF(SUM((Blotter!C$19:C$1013=PLB!C5)*(Blotter!M$19:M$1013))=0,"C","O")</f>
@@ -9854,20 +9897,20 @@
       </c>
       <c r="H5" s="16">
         <f>J4+D5</f>
-        <v>1006003.33063201</v>
+        <v>1003933.33063201</v>
       </c>
       <c r="I5" s="16"/>
       <c r="J5" s="16">
         <f>H5+I5</f>
-        <v>1006003.33063201</v>
+        <v>1003933.33063201</v>
       </c>
       <c r="K5" s="3">
         <f>H5/J4-1</f>
-        <v>5.4782290462005445E-3</v>
+        <v>3.4093095200415924E-3</v>
       </c>
       <c r="L5" s="3">
         <f>(1+K5)*(1+L4)-1</f>
-        <v>6.0033306320099733E-3</v>
+        <v>3.933330632009957E-3</v>
       </c>
       <c r="M5" s="6">
         <f>O4-IF(G5="O",O4*1%,-D5)</f>
@@ -9922,7 +9965,7 @@
       </c>
       <c r="D6" s="6">
         <f t="array" ref="D6">SUM((Blotter!C$19:C$1013=C6)*(Blotter!N$19:N$1013)*1)</f>
-        <v>2745.7799999999975</v>
+        <v>-344.22000000000253</v>
       </c>
       <c r="E6" s="6">
         <f t="array" ref="E6">SUM((Blotter!B$19:C$1013=C6)*(Blotter!R$19:R$1013)*1)</f>
@@ -9930,7 +9973,7 @@
       </c>
       <c r="F6" s="30">
         <f t="shared" ref="F6" si="4">IF(ISNUMBER(D6/E6),D6/E6,0)</f>
-        <v>0.28601874999999971</v>
+        <v>-3.5856250000000263E-2</v>
       </c>
       <c r="G6" s="36" t="str">
         <f t="array" ref="G6">IF(SUM((Blotter!C$19:C$1013=PLB!C6)*(Blotter!M$19:M$1013))=0,"C","O")</f>
@@ -9938,20 +9981,20 @@
       </c>
       <c r="H6" s="16">
         <f>J5+D6</f>
-        <v>1008749.11063201</v>
+        <v>1003589.11063201</v>
       </c>
       <c r="I6" s="16"/>
       <c r="J6" s="16">
         <f>H6+I6</f>
-        <v>1008749.11063201</v>
+        <v>1003589.11063201</v>
       </c>
       <c r="K6" s="3">
         <f>H6/J5-1</f>
-        <v>2.7293945421382748E-3</v>
+        <v>-3.4287137352362329E-4</v>
       </c>
       <c r="L6" s="3">
         <f>(1+K6)*(1+L5)-1</f>
-        <v>8.7491106320098933E-3</v>
+        <v>3.5891106320100619E-3</v>
       </c>
       <c r="M6" s="6">
         <f>O5-IF(G6="O",O5*1%,-D6)</f>
@@ -14984,13 +15027,13 @@
         <v>319</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>60</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="H40" s="1">
         <v>1000</v>
@@ -15060,13 +15103,13 @@
         <v>318</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>60</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="H41" s="1">
         <v>1000</v>

--- a/1XW_TradeBlotter_Web.xlsx
+++ b/1XW_TradeBlotter_Web.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0a601c1c2ba3d9f4/Trading/The Strategy Project/1XW Website/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="337" documentId="13_ncr:1_{6F5069F1-F0E7-4440-AA6D-4AFA11BBED1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8A8A3694-7DB9-4860-9FDC-29734F00E722}"/>
+  <xr:revisionPtr revIDLastSave="350" documentId="13_ncr:1_{6F5069F1-F0E7-4440-AA6D-4AFA11BBED1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{536A59FE-DAAC-43F7-881B-FCE6975C8D85}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="22695" windowHeight="14476" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -117,7 +117,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1204" uniqueCount="331">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1222" uniqueCount="331">
   <si>
     <t>WEEK</t>
   </si>
@@ -1110,19 +1110,19 @@
     <t>Reconnected to TWS.</t>
   </si>
   <si>
+    <t>CL JUN26 55 P</t>
+  </si>
+  <si>
+    <t>CLM6</t>
+  </si>
+  <si>
+    <t>CL JUN26 75 P</t>
+  </si>
+  <si>
+    <t>Crypto</t>
+  </si>
+  <si>
     <t>Close</t>
-  </si>
-  <si>
-    <t>CL JUN26 55 P</t>
-  </si>
-  <si>
-    <t>CLM6</t>
-  </si>
-  <si>
-    <t>CL JUN26 75 P</t>
-  </si>
-  <si>
-    <t>Crypto</t>
   </si>
 </sst>
 </file>
@@ -2272,7 +2272,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>4.8650606320099765E-3</c:v>
+                  <c:v>2.9920606320097409E-3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2426,7 +2426,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>4.8650606320099765E-3</c:v>
+                  <c:v>2.9920606320097409E-3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2817,7 +2817,7 @@
                   <c:v>1000</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1004.8650606320099</c:v>
+                  <c:v>1002.9920606320098</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3233,10 +3233,10 @@
                   <c:v>5.2224063201000703E-4</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>3.933330632009957E-3</c:v>
+                  <c:v>3.3933306320099721E-3</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3.5891106320100619E-3</c:v>
+                  <c:v>1.2791106320100276E-3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3887,7 +3887,7 @@
       </c>
       <c r="C1" s="79">
         <f ca="1">TODAY()</f>
-        <v>46100</v>
+        <v>46101</v>
       </c>
     </row>
     <row r="2" spans="2:11" x14ac:dyDescent="0.4">
@@ -3895,7 +3895,7 @@
         <v>108</v>
       </c>
       <c r="C2" s="37" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="E2" s="47" t="s">
         <v>123</v>
@@ -3912,7 +3912,7 @@
       </c>
       <c r="C3" s="28">
         <f ca="1">OFFSET(NAV!B1,MATCH(C1,NAV!B:B,1),8)</f>
-        <v>1004865.0606320099</v>
+        <v>1002992.0606320099</v>
       </c>
       <c r="E3" s="47" t="s">
         <v>124</v>
@@ -3929,7 +3929,7 @@
       </c>
       <c r="C4" s="28">
         <f>SUM(N18:N1012)</f>
-        <v>4865.0606320098977</v>
+        <v>2992.0606320098982</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="47" t="s">
@@ -3947,7 +3947,7 @@
       </c>
       <c r="C5" s="3">
         <f ca="1">OFFSET(NAV!B1,MATCH(C1,NAV!B:B,1),11)</f>
-        <v>4.8650606320099765E-3</v>
+        <v>2.9920606320097409E-3</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="47" t="s">
@@ -3966,11 +3966,11 @@
       </c>
       <c r="C6" s="3">
         <f ca="1">OFFSET(NAV!B1,MATCH(C1,NAV!B:B,1),12)</f>
-        <v>4.8650606320099765E-3</v>
+        <v>2.9920606320097409E-3</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="47" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="F6" s="47"/>
       <c r="G6" s="47"/>
@@ -3983,11 +3983,11 @@
       </c>
       <c r="C7" s="28">
         <f>Cash_Mgmt!H13</f>
-        <v>35124.049999999952</v>
+        <v>34687.049999999952</v>
       </c>
       <c r="D7" s="3">
         <f ca="1">C7/C3</f>
-        <v>3.4953996686787656E-2</v>
+        <v>3.4583573850168657E-2</v>
       </c>
       <c r="E7" s="47"/>
       <c r="F7" s="47"/>
@@ -4001,11 +4001,11 @@
       </c>
       <c r="C8" s="28">
         <f>C4+C7</f>
-        <v>39989.110632009848</v>
+        <v>37679.110632009848</v>
       </c>
       <c r="D8" s="3">
         <f ca="1">C5+D7</f>
-        <v>3.9819057318797632E-2</v>
+        <v>3.7575634482178398E-2</v>
       </c>
       <c r="G8" s="47"/>
       <c r="H8" s="51"/>
@@ -4017,11 +4017,11 @@
       </c>
       <c r="C9" s="28">
         <f t="array" ref="C9">SUM((F19:F112="Futures")*(M19:M112))</f>
-        <v>100470</v>
+        <v>99930</v>
       </c>
       <c r="D9" s="3">
         <f ca="1">C9/$C$3</f>
-        <v>9.9983573851009797E-2</v>
+        <v>9.963189532829568E-2</v>
       </c>
       <c r="E9" s="47"/>
       <c r="F9" s="47"/>
@@ -4049,11 +4049,11 @@
       </c>
       <c r="C11" s="28">
         <f t="array" ref="C11">SUM((F19:F212="Put")*(M19:M212))</f>
-        <v>9240</v>
+        <v>7470</v>
       </c>
       <c r="D11" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>9.195264480773669E-3</v>
+        <v>7.4477159822112348E-3</v>
       </c>
     </row>
     <row r="12" spans="2:11" x14ac:dyDescent="0.4">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="D12" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>1.8509947980778166E-2</v>
+        <v>1.8544513690646448E-2</v>
       </c>
     </row>
     <row r="13" spans="2:11" x14ac:dyDescent="0.4">
@@ -4075,11 +4075,11 @@
       </c>
       <c r="C13" s="28">
         <f t="array" ref="C13">SUM((PLB!G4:G999="O")*(PLB!D4:D999))</f>
-        <v>3066.869999999994</v>
+        <v>756.86999999999398</v>
       </c>
       <c r="D13" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>3.0520217292370443E-3</v>
+        <v>7.5461215467954119E-4</v>
       </c>
       <c r="F13" s="59"/>
       <c r="G13" s="59"/>
@@ -4090,11 +4090,11 @@
       </c>
       <c r="C14" s="28">
         <f>C12+C13</f>
-        <v>21666.869999999995</v>
+        <v>19356.869999999995</v>
       </c>
       <c r="D14" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>2.156196971001521E-2</v>
+        <v>1.929912584532599E-2</v>
       </c>
     </row>
     <row r="17" spans="2:28" x14ac:dyDescent="0.4">
@@ -4191,7 +4191,7 @@
       <c r="M18" s="12"/>
       <c r="N18" s="95">
         <f>Cash_Mgmt!G13</f>
-        <v>1275.9499999999098</v>
+        <v>1712.9499999999098</v>
       </c>
       <c r="O18" s="12"/>
       <c r="P18" s="12"/>
@@ -4217,7 +4217,7 @@
         <v>190</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="F19" s="10" t="s">
         <v>303</v>
@@ -4291,7 +4291,7 @@
       </c>
       <c r="Z19" s="35">
         <f>IF(C$2="Last",IF(ISNUMBER(VLOOKUP(B19,Prices!A:L,8,0)),VLOOKUP(B19,Prices!A:L,8,0),0),IF(ISNUMBER(VLOOKUP(B19,Prices!A:L,12,0)),VLOOKUP(B19,Prices!A:L,12,0),0))</f>
-        <v>2321.4499999999998</v>
+        <v>2141.6999999999998</v>
       </c>
       <c r="AB19" s="29"/>
     </row>
@@ -4332,15 +4332,15 @@
       </c>
       <c r="L20" s="29">
         <f t="shared" ref="L20" si="8">IF(I20=0,IF(H20&gt;0,X20,Y20),Z20)</f>
-        <v>3349</v>
+        <v>3331</v>
       </c>
       <c r="M20" s="28">
         <f t="shared" ref="M20" si="9">I20*J20*L20</f>
-        <v>100470</v>
+        <v>99930</v>
       </c>
       <c r="N20" s="95">
         <f t="array" ref="N20">-SUM((Trades!T$2:T$9999=Blotter!C20)*(Trades!U$2:U$9999=Blotter!B20)*(Trades!V$2:V$9999)*(Trades!W$2:W$9999))*J20+SUM((Trades!T$2:T$9999=Blotter!C20)*(Trades!U$2:U$9999=Blotter!B20)*(Trades!X$2:X$9999))+(L20*I20)*J20</f>
-        <v>3411.0899999999965</v>
+        <v>2871.0899999999965</v>
       </c>
       <c r="O20" s="29">
         <f>VLOOKUP(D20,Multiplier!B:H,3,0)</f>
@@ -4356,11 +4356,11 @@
       </c>
       <c r="S20" s="29">
         <f>IF(OR(F20="Futures",F20="Spot"),IF(I20=0,0,IF(I20&gt;0,L20-O20,L20+O20)),0)</f>
-        <v>3144</v>
+        <v>3126</v>
       </c>
       <c r="T20" s="3">
         <f t="shared" ref="T20" si="11">IF(S20&gt;0,IF(ISNUMBER(S20/L20-1),S20/L20-1,0),0)</f>
-        <v>-6.1212302179755151E-2</v>
+        <v>-6.154308015610932E-2</v>
       </c>
       <c r="U20" s="29">
         <f t="shared" ref="U20" si="12">IF(OR(F20="Futures",F20="Stocks"),IF(I20=0,0,IF(I20&gt;0,K20-P20,K20+P20)),0)</f>
@@ -4368,7 +4368,7 @@
       </c>
       <c r="V20" s="3">
         <f t="shared" ref="V20" si="13">IF(U20&gt;0,IF(ISNUMBER(U20/L20-1),U20/L20-1,0),0)</f>
-        <v>-0.1235303075544939</v>
+        <v>-0.11879405583908731</v>
       </c>
       <c r="X20" s="34">
         <f t="array" ref="X20">IF(ISNUMBER(SUM((Trades!T$2:T$9999=Blotter!C20)*(Trades!U$2:U$9999=Blotter!B20)*(Trades!W$2:W$9999)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0))/SUM((Trades!T$2:T$9999=Blotter!C20)*(Trades!U$2:U$9999=Blotter!B20)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0))),SUM((Trades!T$2:T$9999=Blotter!C20)*(Trades!U$2:U$9999=Blotter!B20)*(Trades!W$2:W$9999)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0))/SUM((Trades!T$2:T$9999=Blotter!C20)*(Trades!U$2:U$9999=Blotter!B20)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0)),0)</f>
@@ -4380,7 +4380,7 @@
       </c>
       <c r="Z20" s="35">
         <f>IF(C$2="Last",IF(ISNUMBER(VLOOKUP(B20,Prices!A:L,8,0)),VLOOKUP(B20,Prices!A:L,8,0),0),IF(ISNUMBER(VLOOKUP(B20,Prices!A:L,12,0)),VLOOKUP(B20,Prices!A:L,12,0),0))</f>
-        <v>3349</v>
+        <v>3331</v>
       </c>
       <c r="AB20" s="29"/>
     </row>
@@ -4421,15 +4421,15 @@
       </c>
       <c r="L21" s="29">
         <f t="shared" ref="L21:L22" si="15">IF(I21=0,IF(H21&gt;0,X21,Y21),Z21)</f>
-        <v>3.52</v>
+        <v>2.91</v>
       </c>
       <c r="M21" s="28">
         <f t="shared" ref="M21:M22" si="16">I21*J21*L21</f>
-        <v>10560</v>
+        <v>8730</v>
       </c>
       <c r="N21" s="95">
         <f t="array" ref="N21">-SUM((Trades!T$2:T$9999=Blotter!C21)*(Trades!U$2:U$9999=Blotter!B21)*(Trades!V$2:V$9999)*(Trades!W$2:W$9999))*J21+SUM((Trades!T$2:T$9999=Blotter!C21)*(Trades!U$2:U$9999=Blotter!B21)*(Trades!X$2:X$9999))+(L21*I21)*J21</f>
-        <v>-67.110000000002401</v>
+        <v>-1897.1100000000024</v>
       </c>
       <c r="O21" s="29">
         <f>VLOOKUP(D21,Multiplier!B:H,3,0)</f>
@@ -4469,7 +4469,7 @@
       </c>
       <c r="Z21" s="35">
         <f>IF(C$2="Last",IF(ISNUMBER(VLOOKUP(B21,Prices!A:L,8,0)),VLOOKUP(B21,Prices!A:L,8,0),0),IF(ISNUMBER(VLOOKUP(B21,Prices!A:L,12,0)),VLOOKUP(B21,Prices!A:L,12,0),0))</f>
-        <v>3.52</v>
+        <v>2.91</v>
       </c>
       <c r="AB21" s="29"/>
     </row>
@@ -4510,15 +4510,15 @@
       </c>
       <c r="L22" s="29">
         <f t="shared" si="15"/>
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="M22" s="28">
         <f t="shared" si="16"/>
-        <v>-1320</v>
+        <v>-1260</v>
       </c>
       <c r="N22" s="95">
         <f t="array" ref="N22">-SUM((Trades!T$2:T$9999=Blotter!C22)*(Trades!U$2:U$9999=Blotter!B22)*(Trades!V$2:V$9999)*(Trades!W$2:W$9999))*J22+SUM((Trades!T$2:T$9999=Blotter!C22)*(Trades!U$2:U$9999=Blotter!B22)*(Trades!X$2:X$9999))+(L22*I22)*J22</f>
-        <v>-277.11000000000013</v>
+        <v>-217.11000000000013</v>
       </c>
       <c r="O22" s="29">
         <f>VLOOKUP(D22,Multiplier!B:H,3,0)</f>
@@ -4558,7 +4558,7 @@
       </c>
       <c r="Z22" s="35">
         <f>IF(C$2="Last",IF(ISNUMBER(VLOOKUP(B22,Prices!A:L,8,0)),VLOOKUP(B22,Prices!A:L,8,0),0),IF(ISNUMBER(VLOOKUP(B22,Prices!A:L,12,0)),VLOOKUP(B22,Prices!A:L,12,0),0))</f>
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="AB22" s="29"/>
     </row>
@@ -6291,31 +6291,31 @@
         <v>59</v>
       </c>
       <c r="H2" s="91">
-        <v>6808.75</v>
+        <v>6652.25</v>
       </c>
       <c r="I2" s="91">
-        <v>6808.5</v>
+        <v>6652</v>
       </c>
       <c r="J2" s="91">
-        <v>6808.75</v>
+        <v>6652.25</v>
       </c>
       <c r="K2" s="91">
-        <v>6808.625</v>
+        <v>6652.125</v>
       </c>
       <c r="L2" s="91">
-        <v>6773.25</v>
+        <v>6660</v>
       </c>
       <c r="M2" s="91">
-        <v>6774</v>
+        <v>6675.5</v>
       </c>
       <c r="N2" s="91">
-        <v>6814</v>
+        <v>6685.5</v>
       </c>
       <c r="O2" s="91">
-        <v>6764.75</v>
+        <v>6643.25</v>
       </c>
       <c r="P2" s="91">
-        <v>103159</v>
+        <v>108788</v>
       </c>
       <c r="Q2" s="91"/>
       <c r="R2" s="91"/>
@@ -6323,7 +6323,7 @@
       <c r="T2" s="91"/>
       <c r="U2" s="91"/>
       <c r="V2" s="85">
-        <v>46099.477071759262</v>
+        <v>46101.448611111111</v>
       </c>
       <c r="W2" s="81" t="s">
         <v>264</v>
@@ -6355,31 +6355,31 @@
         <v>59</v>
       </c>
       <c r="H3" s="91">
-        <v>25187</v>
+        <v>24512.75</v>
       </c>
       <c r="I3" s="91">
-        <v>25186.25</v>
+        <v>24512.25</v>
       </c>
       <c r="J3" s="91">
-        <v>25187.25</v>
+        <v>24513.5</v>
       </c>
       <c r="K3" s="91">
-        <v>25186.75</v>
+        <v>24512.875</v>
       </c>
       <c r="L3" s="91">
-        <v>25015.5</v>
+        <v>24580</v>
       </c>
       <c r="M3" s="91">
-        <v>25019.75</v>
+        <v>24632.75</v>
       </c>
       <c r="N3" s="91">
-        <v>25210.5</v>
+        <v>24660.5</v>
       </c>
       <c r="O3" s="91">
-        <v>24990.75</v>
+        <v>24482.75</v>
       </c>
       <c r="P3" s="91">
-        <v>53733</v>
+        <v>67749</v>
       </c>
       <c r="Q3" s="91"/>
       <c r="R3" s="91"/>
@@ -6387,7 +6387,7 @@
       <c r="T3" s="91"/>
       <c r="U3" s="91"/>
       <c r="V3" s="85">
-        <v>46099.477071759262</v>
+        <v>46101.448611111111</v>
       </c>
       <c r="W3" s="81" t="s">
         <v>264</v>
@@ -6419,31 +6419,31 @@
         <v>59</v>
       </c>
       <c r="H4" s="91">
-        <v>2560.3000000000002</v>
+        <v>2508.4</v>
       </c>
       <c r="I4" s="91">
-        <v>2560.1</v>
+        <v>2508.3000000000002</v>
       </c>
       <c r="J4" s="91">
-        <v>2560.4</v>
+        <v>2508.5</v>
       </c>
       <c r="K4" s="91">
-        <v>2560.25</v>
+        <v>2508.4</v>
       </c>
       <c r="L4" s="91">
-        <v>2536.8000000000002</v>
+        <v>2512.1</v>
       </c>
       <c r="M4" s="91">
-        <v>2537.5</v>
+        <v>2519.3000000000002</v>
       </c>
       <c r="N4" s="91">
-        <v>2564.6</v>
+        <v>2531.9</v>
       </c>
       <c r="O4" s="91">
-        <v>2531.6999999999998</v>
+        <v>2506.1999999999998</v>
       </c>
       <c r="P4" s="91">
-        <v>17807</v>
+        <v>17532</v>
       </c>
       <c r="Q4" s="91"/>
       <c r="R4" s="91"/>
@@ -6451,7 +6451,7 @@
       <c r="T4" s="91"/>
       <c r="U4" s="91"/>
       <c r="V4" s="85">
-        <v>46099.477071759262</v>
+        <v>46101.448611111111</v>
       </c>
       <c r="W4" s="81" t="s">
         <v>264</v>
@@ -6483,31 +6483,31 @@
         <v>56</v>
       </c>
       <c r="H5" s="91">
-        <v>24163</v>
+        <v>23122</v>
       </c>
       <c r="I5" s="91">
-        <v>24161</v>
+        <v>23125</v>
       </c>
       <c r="J5" s="91">
-        <v>24163</v>
+        <v>23128</v>
       </c>
       <c r="K5" s="91">
-        <v>24162</v>
+        <v>23126.5</v>
       </c>
       <c r="L5" s="91">
-        <v>23942</v>
+        <v>23060</v>
       </c>
       <c r="M5" s="91">
-        <v>23946</v>
+        <v>23232</v>
       </c>
       <c r="N5" s="91">
-        <v>24172</v>
+        <v>23383</v>
       </c>
       <c r="O5" s="91">
-        <v>23921</v>
+        <v>23107</v>
       </c>
       <c r="P5" s="91">
-        <v>4255</v>
+        <v>9136</v>
       </c>
       <c r="Q5" s="91"/>
       <c r="R5" s="91"/>
@@ -6515,7 +6515,7 @@
       <c r="T5" s="91"/>
       <c r="U5" s="91"/>
       <c r="V5" s="85">
-        <v>46099.477071759262</v>
+        <v>46101.448611111111</v>
       </c>
       <c r="W5" s="81" t="s">
         <v>264</v>
@@ -6547,31 +6547,31 @@
         <v>57</v>
       </c>
       <c r="H6" s="91">
-        <v>54615</v>
+        <v>53120</v>
       </c>
       <c r="I6" s="91">
-        <v>54615</v>
+        <v>53105</v>
       </c>
       <c r="J6" s="91">
-        <v>54625</v>
+        <v>53115</v>
       </c>
       <c r="K6" s="91">
-        <v>54620</v>
+        <v>53110</v>
       </c>
       <c r="L6" s="91">
-        <v>54105</v>
+        <v>52825</v>
       </c>
       <c r="M6" s="91">
-        <v>54160</v>
+        <v>53115</v>
       </c>
       <c r="N6" s="91">
-        <v>55090</v>
+        <v>53450</v>
       </c>
       <c r="O6" s="91">
-        <v>54040</v>
+        <v>52840</v>
       </c>
       <c r="P6" s="91">
-        <v>8518</v>
+        <v>5631</v>
       </c>
       <c r="Q6" s="91"/>
       <c r="R6" s="91"/>
@@ -6579,7 +6579,7 @@
       <c r="T6" s="91"/>
       <c r="U6" s="91"/>
       <c r="V6" s="85">
-        <v>46099.477071759262</v>
+        <v>46101.448611111111</v>
       </c>
       <c r="W6" s="81" t="s">
         <v>264</v>
@@ -6611,31 +6611,31 @@
         <v>59</v>
       </c>
       <c r="H7" s="93">
-        <v>94.75</v>
+        <v>96.2</v>
       </c>
       <c r="I7" s="93">
-        <v>94.74</v>
+        <v>95.92</v>
       </c>
       <c r="J7" s="93">
-        <v>94.76</v>
+        <v>96.08</v>
       </c>
       <c r="K7" s="93">
-        <v>94.75</v>
+        <v>96</v>
       </c>
       <c r="L7" s="93">
-        <v>96.21</v>
+        <v>96.14</v>
       </c>
       <c r="M7" s="93">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="N7" s="93">
-        <v>96.41</v>
+        <v>96.2</v>
       </c>
       <c r="O7" s="93">
-        <v>91.96</v>
+        <v>93.42</v>
       </c>
       <c r="P7" s="93">
-        <v>33724</v>
+        <v>394</v>
       </c>
       <c r="Q7" s="93"/>
       <c r="R7" s="93"/>
@@ -6643,7 +6643,7 @@
       <c r="T7" s="93"/>
       <c r="U7" s="93"/>
       <c r="V7" s="92">
-        <v>46099.477071759262</v>
+        <v>46101.448611111111</v>
       </c>
       <c r="W7" s="1" t="s">
         <v>264</v>
@@ -6672,31 +6672,31 @@
         <v>59</v>
       </c>
       <c r="H8" s="93">
-        <v>3.0670000000000002</v>
+        <v>3.2210000000000001</v>
       </c>
       <c r="I8" s="93">
-        <v>3.0649999999999999</v>
+        <v>3.222</v>
       </c>
       <c r="J8" s="93">
-        <v>3.0680000000000001</v>
+        <v>3.2240000000000002</v>
       </c>
       <c r="K8" s="93">
-        <v>3.0665</v>
+        <v>3.2229999999999999</v>
       </c>
       <c r="L8" s="93">
-        <v>3.1379999999999999</v>
+        <v>3.2429999999999999</v>
       </c>
       <c r="M8" s="93">
-        <v>3.1480000000000001</v>
+        <v>3.2010000000000001</v>
       </c>
       <c r="N8" s="93">
-        <v>3.153</v>
+        <v>3.2330000000000001</v>
       </c>
       <c r="O8" s="93">
-        <v>3.0259999999999998</v>
+        <v>3.1789999999999998</v>
       </c>
       <c r="P8" s="93">
-        <v>4513</v>
+        <v>1477</v>
       </c>
       <c r="Q8" s="93"/>
       <c r="R8" s="93"/>
@@ -6704,7 +6704,7 @@
       <c r="T8" s="93"/>
       <c r="U8" s="93"/>
       <c r="V8" s="92">
-        <v>46099.477071759262</v>
+        <v>46101.448611111111</v>
       </c>
       <c r="W8" s="1" t="s">
         <v>264</v>
@@ -6733,31 +6733,31 @@
         <v>59</v>
       </c>
       <c r="H9" s="93">
-        <v>2.9643000000000002</v>
+        <v>3.0537999999999998</v>
       </c>
       <c r="I9" s="93">
-        <v>2.9676</v>
+        <v>3.0522</v>
       </c>
       <c r="J9" s="93">
-        <v>2.9685999999999999</v>
+        <v>3.0539000000000001</v>
       </c>
       <c r="K9" s="93">
-        <v>2.9680999999999997</v>
+        <v>3.0530499999999998</v>
       </c>
       <c r="L9" s="93">
-        <v>2.9611000000000001</v>
+        <v>3.0164</v>
       </c>
       <c r="M9" s="93">
-        <v>2.9714999999999998</v>
+        <v>2.9994999999999998</v>
       </c>
       <c r="N9" s="93">
-        <v>2.9719000000000002</v>
+        <v>3.0661999999999998</v>
       </c>
       <c r="O9" s="93">
-        <v>2.9068000000000001</v>
+        <v>2.9527999999999999</v>
       </c>
       <c r="P9" s="93">
-        <v>4567</v>
+        <v>4803</v>
       </c>
       <c r="Q9" s="93"/>
       <c r="R9" s="93"/>
@@ -6765,7 +6765,7 @@
       <c r="T9" s="93"/>
       <c r="U9" s="93"/>
       <c r="V9" s="92">
-        <v>46099.477071759262</v>
+        <v>46101.448611111111</v>
       </c>
       <c r="W9" s="1" t="s">
         <v>264</v>
@@ -6794,31 +6794,31 @@
         <v>59</v>
       </c>
       <c r="H10" s="93">
-        <v>5031.3999999999996</v>
+        <v>4713.8</v>
       </c>
       <c r="I10" s="93">
-        <v>5028.8999999999996</v>
+        <v>4715.7</v>
       </c>
       <c r="J10" s="93">
-        <v>5029.3999999999996</v>
+        <v>4716.3</v>
       </c>
       <c r="K10" s="93">
-        <v>5029.1499999999996</v>
+        <v>4716</v>
       </c>
       <c r="L10" s="93">
-        <v>5045.6000000000004</v>
+        <v>4640.5</v>
       </c>
       <c r="M10" s="93">
-        <v>5046.6000000000004</v>
+        <v>4689.3999999999996</v>
       </c>
       <c r="N10" s="93">
-        <v>5058.3999999999996</v>
+        <v>4773.3</v>
       </c>
       <c r="O10" s="93">
-        <v>5020</v>
+        <v>4672</v>
       </c>
       <c r="P10" s="93">
-        <v>7937</v>
+        <v>8827</v>
       </c>
       <c r="Q10" s="93"/>
       <c r="R10" s="93"/>
@@ -6826,7 +6826,7 @@
       <c r="T10" s="93"/>
       <c r="U10" s="93"/>
       <c r="V10" s="92">
-        <v>46099.477071759262</v>
+        <v>46101.448611111111</v>
       </c>
       <c r="W10" s="1" t="s">
         <v>264</v>
@@ -6855,31 +6855,31 @@
         <v>59</v>
       </c>
       <c r="H11" s="93">
-        <v>80.33</v>
+        <v>73.105000000000004</v>
       </c>
       <c r="I11" s="93">
-        <v>80.11</v>
+        <v>73.114999999999995</v>
       </c>
       <c r="J11" s="93">
-        <v>80.144999999999996</v>
+        <v>73.165000000000006</v>
       </c>
       <c r="K11" s="93">
-        <v>80.127499999999998</v>
+        <v>73.14</v>
       </c>
       <c r="L11" s="93">
-        <v>80.215000000000003</v>
+        <v>71.47</v>
       </c>
       <c r="M11" s="93">
-        <v>79.375</v>
+        <v>73.584999999999994</v>
       </c>
       <c r="N11" s="93">
-        <v>80.5</v>
+        <v>74.86</v>
       </c>
       <c r="O11" s="93">
-        <v>78.73</v>
+        <v>71.655000000000001</v>
       </c>
       <c r="P11" s="93">
-        <v>58</v>
+        <v>197</v>
       </c>
       <c r="Q11" s="93"/>
       <c r="R11" s="93"/>
@@ -6887,7 +6887,7 @@
       <c r="T11" s="93"/>
       <c r="U11" s="93"/>
       <c r="V11" s="92">
-        <v>46099.477071759262</v>
+        <v>46101.448611111111</v>
       </c>
       <c r="W11" s="1" t="s">
         <v>264</v>
@@ -6916,31 +6916,31 @@
         <v>59</v>
       </c>
       <c r="H12" s="93">
-        <v>5.7629999999999999</v>
+        <v>5.5350000000000001</v>
       </c>
       <c r="I12" s="93">
-        <v>5.7625000000000002</v>
+        <v>5.5069999999999997</v>
       </c>
       <c r="J12" s="93">
-        <v>5.7640000000000002</v>
+        <v>5.5090000000000003</v>
       </c>
       <c r="K12" s="93">
-        <v>5.7632500000000002</v>
+        <v>5.508</v>
       </c>
       <c r="L12" s="93">
-        <v>5.7949999999999999</v>
+        <v>5.4969999999999999</v>
       </c>
       <c r="M12" s="93">
-        <v>5.8</v>
+        <v>5.5564999999999998</v>
       </c>
       <c r="N12" s="93">
-        <v>5.8</v>
+        <v>5.5750000000000002</v>
       </c>
       <c r="O12" s="93">
-        <v>5.73</v>
+        <v>5.5145</v>
       </c>
       <c r="P12" s="93">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="Q12" s="93"/>
       <c r="R12" s="93"/>
@@ -6948,7 +6948,7 @@
       <c r="T12" s="93"/>
       <c r="U12" s="93"/>
       <c r="V12" s="92">
-        <v>46099.477071759262</v>
+        <v>46101.448611111111</v>
       </c>
       <c r="W12" s="1" t="s">
         <v>264</v>
@@ -6977,31 +6977,31 @@
         <v>59</v>
       </c>
       <c r="H13" s="93">
-        <v>453</v>
+        <v>467.5</v>
       </c>
       <c r="I13" s="93">
-        <v>453</v>
+        <v>467.25</v>
       </c>
       <c r="J13" s="93">
-        <v>453.25</v>
+        <v>467.5</v>
       </c>
       <c r="K13" s="93">
-        <v>453.125</v>
+        <v>467.375</v>
       </c>
       <c r="L13" s="93">
-        <v>454</v>
+        <v>469.75</v>
       </c>
       <c r="M13" s="93">
-        <v>454.75</v>
+        <v>469</v>
       </c>
       <c r="N13" s="93">
-        <v>456.5</v>
+        <v>469.25</v>
       </c>
       <c r="O13" s="93">
-        <v>452.25</v>
+        <v>466.75</v>
       </c>
       <c r="P13" s="93">
-        <v>21813</v>
+        <v>16671</v>
       </c>
       <c r="Q13" s="93"/>
       <c r="R13" s="93"/>
@@ -7009,7 +7009,7 @@
       <c r="T13" s="93"/>
       <c r="U13" s="93"/>
       <c r="V13" s="92">
-        <v>46099.477071759262</v>
+        <v>46101.448611111111</v>
       </c>
       <c r="W13" s="1" t="s">
         <v>264</v>
@@ -7038,31 +7038,31 @@
         <v>59</v>
       </c>
       <c r="H14" s="93">
-        <v>591</v>
+        <v>602.25</v>
       </c>
       <c r="I14" s="93">
-        <v>591</v>
+        <v>602.25</v>
       </c>
       <c r="J14" s="93">
-        <v>591.25</v>
+        <v>602.5</v>
       </c>
       <c r="K14" s="93">
-        <v>591.125</v>
+        <v>602.375</v>
       </c>
       <c r="L14" s="93">
-        <v>589.75</v>
+        <v>608</v>
       </c>
       <c r="M14" s="93">
-        <v>590</v>
+        <v>608</v>
       </c>
       <c r="N14" s="93">
-        <v>593.5</v>
+        <v>609.25</v>
       </c>
       <c r="O14" s="93">
-        <v>586</v>
+        <v>602.25</v>
       </c>
       <c r="P14" s="93">
-        <v>7705</v>
+        <v>6172</v>
       </c>
       <c r="Q14" s="93"/>
       <c r="R14" s="93"/>
@@ -7070,7 +7070,7 @@
       <c r="T14" s="93"/>
       <c r="U14" s="93"/>
       <c r="V14" s="92">
-        <v>46099.477071759262</v>
+        <v>46101.448611111111</v>
       </c>
       <c r="W14" s="1" t="s">
         <v>264</v>
@@ -7099,31 +7099,31 @@
         <v>59</v>
       </c>
       <c r="H15" s="93">
-        <v>1153</v>
+        <v>1171.5</v>
       </c>
       <c r="I15" s="93">
-        <v>1152.75</v>
+        <v>1171.25</v>
       </c>
       <c r="J15" s="93">
-        <v>1153.25</v>
+        <v>1171.5</v>
       </c>
       <c r="K15" s="93">
-        <v>1153</v>
+        <v>1171.375</v>
       </c>
       <c r="L15" s="93">
-        <v>1157</v>
+        <v>1168.5</v>
       </c>
       <c r="M15" s="93">
-        <v>1156.25</v>
+        <v>1166</v>
       </c>
       <c r="N15" s="93">
-        <v>1160</v>
+        <v>1176</v>
       </c>
       <c r="O15" s="93">
-        <v>1149</v>
+        <v>1165</v>
       </c>
       <c r="P15" s="93">
-        <v>15858</v>
+        <v>11492</v>
       </c>
       <c r="Q15" s="93"/>
       <c r="R15" s="93"/>
@@ -7131,7 +7131,7 @@
       <c r="T15" s="93"/>
       <c r="U15" s="93"/>
       <c r="V15" s="92">
-        <v>46099.477071759262</v>
+        <v>46101.448611111111</v>
       </c>
       <c r="W15" s="1" t="s">
         <v>264</v>
@@ -7160,31 +7160,31 @@
         <v>59</v>
       </c>
       <c r="H16" s="93">
-        <v>14.52</v>
+        <v>15.34</v>
       </c>
       <c r="I16" s="93">
-        <v>14.51</v>
+        <v>15.34</v>
       </c>
       <c r="J16" s="93">
-        <v>14.52</v>
+        <v>15.35</v>
       </c>
       <c r="K16" s="93">
-        <v>14.515000000000001</v>
+        <v>15.344999999999999</v>
       </c>
       <c r="L16" s="93">
-        <v>14.45</v>
+        <v>15.37</v>
       </c>
       <c r="M16" s="93">
-        <v>14.39</v>
+        <v>15.33</v>
       </c>
       <c r="N16" s="93">
-        <v>14.57</v>
+        <v>15.47</v>
       </c>
       <c r="O16" s="93">
-        <v>14.35</v>
+        <v>15.27</v>
       </c>
       <c r="P16" s="93">
-        <v>21909</v>
+        <v>13550</v>
       </c>
       <c r="Q16" s="93"/>
       <c r="R16" s="93"/>
@@ -7192,7 +7192,7 @@
       <c r="T16" s="93"/>
       <c r="U16" s="93"/>
       <c r="V16" s="92">
-        <v>46099.477071759262</v>
+        <v>46101.448611111111</v>
       </c>
       <c r="W16" s="1" t="s">
         <v>264</v>
@@ -7221,31 +7221,31 @@
         <v>59</v>
       </c>
       <c r="H17" s="93">
-        <v>293.3</v>
+        <v>304.3</v>
       </c>
       <c r="I17" s="93">
-        <v>293.3</v>
+        <v>304.25</v>
       </c>
       <c r="J17" s="93">
-        <v>293.39999999999998</v>
+        <v>304.35000000000002</v>
       </c>
       <c r="K17" s="93">
-        <v>293.35000000000002</v>
+        <v>304.3</v>
       </c>
       <c r="L17" s="93">
-        <v>294.75</v>
+        <v>300.89999999999998</v>
       </c>
       <c r="M17" s="93">
-        <v>294.39999999999998</v>
+        <v>303</v>
       </c>
       <c r="N17" s="93">
-        <v>295.2</v>
+        <v>304.39999999999998</v>
       </c>
       <c r="O17" s="93">
-        <v>292.2</v>
+        <v>301.89999999999998</v>
       </c>
       <c r="P17" s="93">
-        <v>1189</v>
+        <v>1175</v>
       </c>
       <c r="Q17" s="93"/>
       <c r="R17" s="93"/>
@@ -7253,7 +7253,7 @@
       <c r="T17" s="93"/>
       <c r="U17" s="93"/>
       <c r="V17" s="92">
-        <v>46099.477071759262</v>
+        <v>46101.448611111111</v>
       </c>
       <c r="W17" s="1" t="s">
         <v>264</v>
@@ -7282,31 +7282,27 @@
         <v>59</v>
       </c>
       <c r="H18" s="93">
-        <v>3367</v>
+        <v>0</v>
       </c>
       <c r="I18" s="93">
-        <v>3364</v>
+        <v>-1</v>
       </c>
       <c r="J18" s="93">
-        <v>3367</v>
+        <v>-1</v>
       </c>
       <c r="K18" s="93">
-        <v>3365.5</v>
+        <v>-1</v>
       </c>
       <c r="L18" s="93">
-        <v>3349</v>
+        <v>3331</v>
       </c>
       <c r="M18" s="93">
-        <v>3377</v>
-      </c>
-      <c r="N18" s="93">
-        <v>3386</v>
-      </c>
-      <c r="O18" s="93">
-        <v>3357</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N18" s="93"/>
+      <c r="O18" s="93"/>
       <c r="P18" s="93">
-        <v>736</v>
+        <v>0</v>
       </c>
       <c r="Q18" s="93"/>
       <c r="R18" s="93"/>
@@ -7314,7 +7310,7 @@
       <c r="T18" s="93"/>
       <c r="U18" s="93"/>
       <c r="V18" s="92">
-        <v>46099.477071759262</v>
+        <v>46101.448611111111</v>
       </c>
       <c r="W18" s="1" t="s">
         <v>264</v>
@@ -7343,31 +7339,31 @@
         <v>59</v>
       </c>
       <c r="H19" s="93">
-        <v>68.53</v>
+        <v>67.33</v>
       </c>
       <c r="I19" s="93">
-        <v>68.53</v>
+        <v>67.319999999999993</v>
       </c>
       <c r="J19" s="93">
-        <v>68.540000000000006</v>
+        <v>67.33</v>
       </c>
       <c r="K19" s="93">
-        <v>68.534999999999997</v>
+        <v>67.324999999999989</v>
       </c>
       <c r="L19" s="93">
-        <v>68.77</v>
+        <v>67.67</v>
       </c>
       <c r="M19" s="93">
-        <v>68.7</v>
+        <v>67.69</v>
       </c>
       <c r="N19" s="93">
-        <v>68.86</v>
+        <v>68.209999999999994</v>
       </c>
       <c r="O19" s="93">
-        <v>68.260000000000005</v>
+        <v>67.290000000000006</v>
       </c>
       <c r="P19" s="93">
-        <v>6793</v>
+        <v>7239</v>
       </c>
       <c r="Q19" s="93"/>
       <c r="R19" s="93"/>
@@ -7375,7 +7371,7 @@
       <c r="T19" s="93"/>
       <c r="U19" s="93"/>
       <c r="V19" s="92">
-        <v>46099.477071759262</v>
+        <v>46101.448611111111</v>
       </c>
       <c r="W19" s="1" t="s">
         <v>264</v>
@@ -7416,15 +7412,19 @@
         <v>-100</v>
       </c>
       <c r="L20" s="93">
-        <v>235.22499999999999</v>
+        <v>233.27500000000001</v>
       </c>
       <c r="M20" s="93">
-        <v>233.75</v>
-      </c>
-      <c r="N20" s="93"/>
-      <c r="O20" s="93"/>
+        <v>234.9</v>
+      </c>
+      <c r="N20" s="93">
+        <v>234.95</v>
+      </c>
+      <c r="O20" s="93">
+        <v>232.65</v>
+      </c>
       <c r="P20" s="93">
-        <v>0</v>
+        <v>13220</v>
       </c>
       <c r="Q20" s="93"/>
       <c r="R20" s="93"/>
@@ -7432,7 +7432,7 @@
       <c r="T20" s="93"/>
       <c r="U20" s="93"/>
       <c r="V20" s="92">
-        <v>46099.477071759262</v>
+        <v>46101.448611111111</v>
       </c>
       <c r="W20" s="1" t="s">
         <v>264</v>
@@ -7461,7 +7461,7 @@
         <v>59</v>
       </c>
       <c r="H21" s="93">
-        <v>350.3</v>
+        <v>0</v>
       </c>
       <c r="I21" s="93">
         <v>-100</v>
@@ -7473,19 +7473,19 @@
         <v>-100</v>
       </c>
       <c r="L21" s="93">
-        <v>350.625</v>
+        <v>343.42500000000001</v>
       </c>
       <c r="M21" s="93">
-        <v>346.27499999999998</v>
+        <v>347</v>
       </c>
       <c r="N21" s="93">
-        <v>351.3</v>
+        <v>347</v>
       </c>
       <c r="O21" s="93">
-        <v>345.82499999999999</v>
+        <v>342.55</v>
       </c>
       <c r="P21" s="93">
-        <v>5629</v>
+        <v>5994</v>
       </c>
       <c r="Q21" s="93"/>
       <c r="R21" s="93"/>
@@ -7493,7 +7493,7 @@
       <c r="T21" s="93"/>
       <c r="U21" s="93"/>
       <c r="V21" s="92">
-        <v>46099.477071759262</v>
+        <v>46101.448611111111</v>
       </c>
       <c r="W21" s="1" t="s">
         <v>264</v>
@@ -7534,15 +7534,19 @@
         <v>-100</v>
       </c>
       <c r="L22" s="93">
+        <v>92.05</v>
+      </c>
+      <c r="M22" s="93">
+        <v>93.65</v>
+      </c>
+      <c r="N22" s="93">
         <v>93.724999999999994</v>
       </c>
-      <c r="M22" s="93">
-        <v>93.5</v>
-      </c>
-      <c r="N22" s="93"/>
-      <c r="O22" s="93"/>
+      <c r="O22" s="93">
+        <v>91.924999999999997</v>
+      </c>
       <c r="P22" s="93">
-        <v>0</v>
+        <v>24371</v>
       </c>
       <c r="Q22" s="93"/>
       <c r="R22" s="93"/>
@@ -7550,7 +7554,7 @@
       <c r="T22" s="93"/>
       <c r="U22" s="93"/>
       <c r="V22" s="92">
-        <v>46099.477071759262</v>
+        <v>46101.448611111111</v>
       </c>
       <c r="W22" s="1" t="s">
         <v>264</v>
@@ -7579,31 +7583,31 @@
         <v>59</v>
       </c>
       <c r="H23" s="93">
-        <v>99.334999999999994</v>
+        <v>99.204999999999998</v>
       </c>
       <c r="I23" s="93">
-        <v>99.325000000000003</v>
+        <v>99.2</v>
       </c>
       <c r="J23" s="93">
-        <v>99.33</v>
+        <v>99.21</v>
       </c>
       <c r="K23" s="93">
-        <v>99.327500000000001</v>
+        <v>99.204999999999998</v>
       </c>
       <c r="L23" s="93">
-        <v>99.33</v>
+        <v>99.06</v>
       </c>
       <c r="M23" s="93">
-        <v>99.32</v>
+        <v>99.1</v>
       </c>
       <c r="N23" s="93">
-        <v>99.474999999999994</v>
+        <v>99.275000000000006</v>
       </c>
       <c r="O23" s="93">
-        <v>99.22</v>
+        <v>99.055000000000007</v>
       </c>
       <c r="P23" s="93">
-        <v>3344</v>
+        <v>5977</v>
       </c>
       <c r="Q23" s="93"/>
       <c r="R23" s="93"/>
@@ -7611,7 +7615,7 @@
       <c r="T23" s="93"/>
       <c r="U23" s="93"/>
       <c r="V23" s="92">
-        <v>46099.477071759262</v>
+        <v>46101.448611111111</v>
       </c>
       <c r="W23" s="1" t="s">
         <v>264</v>
@@ -7640,31 +7644,31 @@
         <v>59</v>
       </c>
       <c r="H24" s="93">
-        <v>1.1591</v>
+        <v>1.1608499999999999</v>
       </c>
       <c r="I24" s="93">
-        <v>1.1590499999999999</v>
+        <v>1.1608499999999999</v>
       </c>
       <c r="J24" s="93">
-        <v>1.1591499999999999</v>
+        <v>1.1609</v>
       </c>
       <c r="K24" s="93">
-        <v>1.1591</v>
+        <v>1.1608749999999999</v>
       </c>
       <c r="L24" s="93">
-        <v>1.1588499999999999</v>
+        <v>1.1629</v>
       </c>
       <c r="M24" s="93">
-        <v>1.1588000000000001</v>
+        <v>1.1634500000000001</v>
       </c>
       <c r="N24" s="93">
-        <v>1.15985</v>
+        <v>1.1641999999999999</v>
       </c>
       <c r="O24" s="93">
-        <v>1.1567000000000001</v>
+        <v>1.1598999999999999</v>
       </c>
       <c r="P24" s="93">
-        <v>40607</v>
+        <v>52393</v>
       </c>
       <c r="Q24" s="93"/>
       <c r="R24" s="93"/>
@@ -7672,7 +7676,7 @@
       <c r="T24" s="93"/>
       <c r="U24" s="93"/>
       <c r="V24" s="92">
-        <v>46099.477071759262</v>
+        <v>46101.448611111111</v>
       </c>
       <c r="W24" s="1" t="s">
         <v>264</v>
@@ -7701,31 +7705,31 @@
         <v>59</v>
       </c>
       <c r="H25" s="93">
-        <v>1.3359000000000001</v>
+        <v>1.3399000000000001</v>
       </c>
       <c r="I25" s="93">
-        <v>1.3358000000000001</v>
+        <v>1.3399000000000001</v>
       </c>
       <c r="J25" s="93">
-        <v>1.3359000000000001</v>
+        <v>1.3401000000000001</v>
       </c>
       <c r="K25" s="93">
-        <v>1.3358500000000002</v>
+        <v>1.34</v>
       </c>
       <c r="L25" s="93">
-        <v>1.3355999999999999</v>
+        <v>1.3414999999999999</v>
       </c>
       <c r="M25" s="93">
-        <v>1.3359000000000001</v>
+        <v>1.3431999999999999</v>
       </c>
       <c r="N25" s="93">
-        <v>1.3373999999999999</v>
+        <v>1.3440000000000001</v>
       </c>
       <c r="O25" s="93">
-        <v>1.3341000000000001</v>
+        <v>1.3394999999999999</v>
       </c>
       <c r="P25" s="93">
-        <v>18707</v>
+        <v>23717</v>
       </c>
       <c r="Q25" s="93"/>
       <c r="R25" s="93"/>
@@ -7733,7 +7737,7 @@
       <c r="T25" s="93"/>
       <c r="U25" s="93"/>
       <c r="V25" s="92">
-        <v>46099.477071759262</v>
+        <v>46101.448611111111</v>
       </c>
       <c r="W25" s="1" t="s">
         <v>264</v>
@@ -7762,31 +7766,31 @@
         <v>59</v>
       </c>
       <c r="H26" s="93">
-        <v>6.3355E-3</v>
+        <v>6.3495000000000001E-3</v>
       </c>
       <c r="I26" s="93">
-        <v>6.3350000000000004E-3</v>
+        <v>6.3489999999999996E-3</v>
       </c>
       <c r="J26" s="93">
-        <v>6.3355E-3</v>
+        <v>6.3499999999999997E-3</v>
       </c>
       <c r="K26" s="93">
-        <v>6.3352500000000006E-3</v>
+        <v>6.3494999999999992E-3</v>
       </c>
       <c r="L26" s="93">
-        <v>6.3350000000000004E-3</v>
+        <v>6.3879999999999996E-3</v>
       </c>
       <c r="M26" s="93">
-        <v>6.3369999999999998E-3</v>
+        <v>6.3854999999999997E-3</v>
       </c>
       <c r="N26" s="93">
-        <v>6.3524999999999996E-3</v>
+        <v>6.3879999999999996E-3</v>
       </c>
       <c r="O26" s="93">
-        <v>6.3299999999999997E-3</v>
+        <v>6.3480000000000003E-3</v>
       </c>
       <c r="P26" s="93">
-        <v>35115</v>
+        <v>42737</v>
       </c>
       <c r="Q26" s="93"/>
       <c r="R26" s="93"/>
@@ -7794,7 +7798,7 @@
       <c r="T26" s="93"/>
       <c r="U26" s="93"/>
       <c r="V26" s="92">
-        <v>46099.477071759262</v>
+        <v>46101.448611111111</v>
       </c>
       <c r="W26" s="1" t="s">
         <v>264</v>
@@ -7823,31 +7827,31 @@
         <v>59</v>
       </c>
       <c r="H27" s="93">
-        <v>0.73324999999999996</v>
+        <v>0.73170000000000002</v>
       </c>
       <c r="I27" s="93">
-        <v>0.73319999999999996</v>
+        <v>0.73170000000000002</v>
       </c>
       <c r="J27" s="93">
-        <v>0.73324999999999996</v>
+        <v>0.73175000000000001</v>
       </c>
       <c r="K27" s="93">
-        <v>0.73322500000000002</v>
+        <v>0.73172499999999996</v>
       </c>
       <c r="L27" s="93">
-        <v>0.73299999999999998</v>
+        <v>0.73134999999999994</v>
       </c>
       <c r="M27" s="93">
-        <v>0.73329999999999995</v>
+        <v>0.73055000000000003</v>
       </c>
       <c r="N27" s="93">
-        <v>0.73350000000000004</v>
+        <v>0.73199999999999998</v>
       </c>
       <c r="O27" s="93">
-        <v>0.73209999999999997</v>
+        <v>0.73035000000000005</v>
       </c>
       <c r="P27" s="93">
-        <v>10027</v>
+        <v>13475</v>
       </c>
       <c r="Q27" s="93"/>
       <c r="R27" s="93"/>
@@ -7855,7 +7859,7 @@
       <c r="T27" s="93"/>
       <c r="U27" s="93"/>
       <c r="V27" s="92">
-        <v>46099.477071759262</v>
+        <v>46101.448611111111</v>
       </c>
       <c r="W27" s="1" t="s">
         <v>264</v>
@@ -7884,31 +7888,31 @@
         <v>59</v>
       </c>
       <c r="H28" s="93">
-        <v>0.71014999999999995</v>
+        <v>0.70709999999999995</v>
       </c>
       <c r="I28" s="93">
-        <v>0.71009999999999995</v>
+        <v>0.70709999999999995</v>
       </c>
       <c r="J28" s="93">
-        <v>0.71020000000000005</v>
+        <v>0.70714999999999995</v>
       </c>
       <c r="K28" s="93">
-        <v>0.71015000000000006</v>
+        <v>0.707125</v>
       </c>
       <c r="L28" s="93">
-        <v>0.70960000000000001</v>
+        <v>0.70655000000000001</v>
       </c>
       <c r="M28" s="93">
-        <v>0.70955000000000001</v>
+        <v>0.70760000000000001</v>
       </c>
       <c r="N28" s="93">
-        <v>0.71145000000000003</v>
+        <v>0.70889999999999997</v>
       </c>
       <c r="O28" s="93">
-        <v>0.70904999999999996</v>
+        <v>0.70650000000000002</v>
       </c>
       <c r="P28" s="93">
-        <v>24405</v>
+        <v>30078</v>
       </c>
       <c r="Q28" s="93"/>
       <c r="R28" s="93"/>
@@ -7916,7 +7920,7 @@
       <c r="T28" s="93"/>
       <c r="U28" s="93"/>
       <c r="V28" s="92">
-        <v>46099.477071759262</v>
+        <v>46101.448611111111</v>
       </c>
       <c r="W28" s="1" t="s">
         <v>264</v>
@@ -7945,31 +7949,31 @@
         <v>59</v>
       </c>
       <c r="H29" s="93">
-        <v>115.125</v>
+        <v>114.21875</v>
       </c>
       <c r="I29" s="93">
-        <v>115.125</v>
+        <v>114.1875</v>
       </c>
       <c r="J29" s="93">
-        <v>115.15625</v>
+        <v>114.21875</v>
       </c>
       <c r="K29" s="93">
-        <v>115.140625</v>
+        <v>114.203125</v>
       </c>
       <c r="L29" s="93">
-        <v>114.8125</v>
+        <v>114.375</v>
       </c>
       <c r="M29" s="93">
-        <v>114.84375</v>
+        <v>114.65625</v>
       </c>
       <c r="N29" s="93">
-        <v>115.34375</v>
+        <v>114.75</v>
       </c>
       <c r="O29" s="93">
-        <v>114.78125</v>
+        <v>114.15625</v>
       </c>
       <c r="P29" s="93">
-        <v>52811</v>
+        <v>46792</v>
       </c>
       <c r="Q29" s="93"/>
       <c r="R29" s="93"/>
@@ -7977,7 +7981,7 @@
       <c r="T29" s="93"/>
       <c r="U29" s="93"/>
       <c r="V29" s="92">
-        <v>46099.477071759262</v>
+        <v>46101.448611111111</v>
       </c>
       <c r="W29" s="1" t="s">
         <v>264</v>
@@ -8006,31 +8010,31 @@
         <v>59</v>
       </c>
       <c r="H30" s="93">
-        <v>112.109375</v>
+        <v>111.125</v>
       </c>
       <c r="I30" s="93">
-        <v>112.09375</v>
+        <v>111.125</v>
       </c>
       <c r="J30" s="93">
-        <v>112.109375</v>
+        <v>111.140625</v>
       </c>
       <c r="K30" s="93">
-        <v>112.1015625</v>
+        <v>111.1328125</v>
       </c>
       <c r="L30" s="93">
-        <v>112</v>
+        <v>111.21875</v>
       </c>
       <c r="M30" s="93">
-        <v>111.984375</v>
+        <v>111.484375</v>
       </c>
       <c r="N30" s="93">
-        <v>112.21875</v>
+        <v>111.53125</v>
       </c>
       <c r="O30" s="93">
-        <v>111.953125</v>
+        <v>111.109375</v>
       </c>
       <c r="P30" s="93">
-        <v>253739</v>
+        <v>293674</v>
       </c>
       <c r="Q30" s="93"/>
       <c r="R30" s="93"/>
@@ -8038,7 +8042,7 @@
       <c r="T30" s="93"/>
       <c r="U30" s="93"/>
       <c r="V30" s="92">
-        <v>46099.477071759262</v>
+        <v>46101.448611111111</v>
       </c>
       <c r="W30" s="1" t="s">
         <v>264</v>
@@ -8067,31 +8071,31 @@
         <v>56</v>
       </c>
       <c r="H31" s="93">
-        <v>126.8</v>
+        <v>125.74</v>
       </c>
       <c r="I31" s="93">
-        <v>126.8</v>
+        <v>125.73</v>
       </c>
       <c r="J31" s="93">
-        <v>126.81</v>
+        <v>125.74</v>
       </c>
       <c r="K31" s="93">
-        <v>126.80500000000001</v>
+        <v>125.735</v>
       </c>
       <c r="L31" s="93">
-        <v>126.47</v>
+        <v>125.97</v>
       </c>
       <c r="M31" s="93">
-        <v>126.5</v>
+        <v>126.16</v>
       </c>
       <c r="N31" s="93">
-        <v>126.83</v>
+        <v>126.27</v>
       </c>
       <c r="O31" s="93">
-        <v>126.46</v>
+        <v>125.74</v>
       </c>
       <c r="P31" s="93">
-        <v>272263</v>
+        <v>291074</v>
       </c>
       <c r="Q31" s="93"/>
       <c r="R31" s="93"/>
@@ -8099,7 +8103,7 @@
       <c r="T31" s="93"/>
       <c r="U31" s="93"/>
       <c r="V31" s="92">
-        <v>46099.477071759262</v>
+        <v>46101.448611111111</v>
       </c>
       <c r="W31" s="1" t="s">
         <v>264</v>
@@ -8128,31 +8132,31 @@
         <v>56</v>
       </c>
       <c r="H32" s="93">
-        <v>110.48</v>
+        <v>109.98</v>
       </c>
       <c r="I32" s="93">
-        <v>110.46</v>
+        <v>109.98</v>
       </c>
       <c r="J32" s="93">
-        <v>110.48</v>
+        <v>110</v>
       </c>
       <c r="K32" s="93">
-        <v>110.47</v>
+        <v>109.99000000000001</v>
       </c>
       <c r="L32" s="93">
-        <v>109.88</v>
+        <v>110.24</v>
       </c>
       <c r="M32" s="93">
-        <v>109.9</v>
+        <v>110.5</v>
       </c>
       <c r="N32" s="93">
-        <v>110.58</v>
+        <v>110.66</v>
       </c>
       <c r="O32" s="93">
-        <v>109.82</v>
+        <v>109.98</v>
       </c>
       <c r="P32" s="93">
-        <v>41973</v>
+        <v>41755</v>
       </c>
       <c r="Q32" s="93"/>
       <c r="R32" s="93"/>
@@ -8160,7 +8164,7 @@
       <c r="T32" s="93"/>
       <c r="U32" s="93"/>
       <c r="V32" s="92">
-        <v>46099.477071759262</v>
+        <v>46101.448611111111</v>
       </c>
       <c r="W32" s="1" t="s">
         <v>264</v>
@@ -8189,31 +8193,31 @@
         <v>56</v>
       </c>
       <c r="H33" s="93">
-        <v>118.85</v>
+        <v>117.06</v>
       </c>
       <c r="I33" s="93">
-        <v>118.84</v>
+        <v>117.05</v>
       </c>
       <c r="J33" s="93">
-        <v>118.85</v>
+        <v>117.06</v>
       </c>
       <c r="K33" s="93">
-        <v>118.845</v>
+        <v>117.05500000000001</v>
       </c>
       <c r="L33" s="93">
-        <v>118.37</v>
+        <v>117.37</v>
       </c>
       <c r="M33" s="93">
-        <v>118.73</v>
+        <v>117.46</v>
       </c>
       <c r="N33" s="93">
-        <v>118.88</v>
+        <v>117.82</v>
       </c>
       <c r="O33" s="93">
-        <v>118.67</v>
+        <v>117.07</v>
       </c>
       <c r="P33" s="93">
-        <v>90427</v>
+        <v>99090</v>
       </c>
       <c r="Q33" s="93"/>
       <c r="R33" s="93"/>
@@ -8221,7 +8225,7 @@
       <c r="T33" s="93"/>
       <c r="U33" s="93"/>
       <c r="V33" s="92">
-        <v>46099.477071759262</v>
+        <v>46101.448611111111</v>
       </c>
       <c r="W33" s="1" t="s">
         <v>264</v>
@@ -8250,29 +8254,29 @@
         <v>59</v>
       </c>
       <c r="H34" s="93">
-        <v>74198.25</v>
+        <v>70571.25</v>
       </c>
       <c r="I34" s="93">
-        <v>74198</v>
+        <v>70571.25</v>
       </c>
       <c r="J34" s="93">
-        <v>74198.25</v>
+        <v>70571.5</v>
       </c>
       <c r="K34" s="93">
-        <v>74198.125</v>
+        <v>70571.375</v>
       </c>
       <c r="L34" s="93">
-        <v>74545</v>
+        <v>70268.25</v>
       </c>
       <c r="M34" s="93"/>
       <c r="N34" s="93">
-        <v>74822.25</v>
+        <v>71605.5</v>
       </c>
       <c r="O34" s="93">
-        <v>73304.75</v>
+        <v>68655</v>
       </c>
       <c r="P34" s="93">
-        <v>88.767262759999994</v>
+        <v>100.22978931999999</v>
       </c>
       <c r="Q34" s="93"/>
       <c r="R34" s="93"/>
@@ -8280,7 +8284,7 @@
       <c r="T34" s="93"/>
       <c r="U34" s="93"/>
       <c r="V34" s="92">
-        <v>46099.477071759262</v>
+        <v>46101.448611111111</v>
       </c>
       <c r="W34" s="1" t="s">
         <v>264</v>
@@ -8309,29 +8313,29 @@
         <v>59</v>
       </c>
       <c r="H35" s="93">
-        <v>2329.3000000000002</v>
+        <v>2145.8000000000002</v>
       </c>
       <c r="I35" s="93">
-        <v>2329.25</v>
+        <v>2144.1</v>
       </c>
       <c r="J35" s="93">
-        <v>2329.3000000000002</v>
+        <v>2144.15</v>
       </c>
       <c r="K35" s="93">
-        <v>2329.2750000000001</v>
+        <v>2144.125</v>
       </c>
       <c r="L35" s="93">
-        <v>2321.4499999999998</v>
+        <v>2141.6999999999998</v>
       </c>
       <c r="M35" s="93"/>
       <c r="N35" s="93">
-        <v>2351.35</v>
+        <v>2232.75</v>
       </c>
       <c r="O35" s="93">
-        <v>2308.85</v>
+        <v>2094.6</v>
       </c>
       <c r="P35" s="93">
-        <v>1069.2230012800001</v>
+        <v>1166.4607209200001</v>
       </c>
       <c r="Q35" s="93"/>
       <c r="R35" s="93"/>
@@ -8339,7 +8343,7 @@
       <c r="T35" s="93"/>
       <c r="U35" s="93"/>
       <c r="V35" s="92">
-        <v>46099.477071759262</v>
+        <v>46101.448611111111</v>
       </c>
       <c r="W35" s="1" t="s">
         <v>264</v>
@@ -8368,47 +8372,47 @@
         <v>59</v>
       </c>
       <c r="H36" s="93">
-        <v>3.72</v>
+        <v>3.21</v>
       </c>
       <c r="I36" s="93">
-        <v>3.55</v>
+        <v>2.93</v>
       </c>
       <c r="J36" s="93">
-        <v>3.59</v>
+        <v>3.01</v>
       </c>
       <c r="K36" s="93">
-        <v>3.57</v>
+        <v>2.9699999999999998</v>
       </c>
       <c r="L36" s="93">
-        <v>3.52</v>
+        <v>2.91</v>
       </c>
       <c r="M36" s="93"/>
       <c r="N36" s="93">
-        <v>3.9</v>
+        <v>3.21</v>
       </c>
       <c r="O36" s="93">
-        <v>3.72</v>
+        <v>3.21</v>
       </c>
       <c r="P36" s="93">
-        <v>262</v>
+        <v>39</v>
       </c>
       <c r="Q36" s="93">
-        <v>0.72512493857815341</v>
+        <v>0.71771421572689076</v>
       </c>
       <c r="R36" s="93">
-        <v>-0.20999233654000748</v>
+        <v>-0.18128491103438815</v>
       </c>
       <c r="S36" s="93">
-        <v>1.1079477126531177E-2</v>
+        <v>1.0173391195764769E-2</v>
       </c>
       <c r="T36" s="93">
-        <v>0.10064267792560955</v>
+        <v>0.10013433884153189</v>
       </c>
       <c r="U36" s="93">
-        <v>-6.3596295977592643E-2</v>
+        <v>-6.4910269707011192E-2</v>
       </c>
       <c r="V36" s="92">
-        <v>46099.477071759262</v>
+        <v>46101.448611111111</v>
       </c>
       <c r="W36" s="1" t="s">
         <v>264</v>
@@ -8437,47 +8441,43 @@
         <v>59</v>
       </c>
       <c r="H37" s="93">
-        <v>0.45</v>
+        <v>-1</v>
       </c>
       <c r="I37" s="93">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="J37" s="93">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="K37" s="93">
-        <v>0.44500000000000001</v>
+        <v>0.43000000000000005</v>
       </c>
       <c r="L37" s="93">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="M37" s="93"/>
-      <c r="N37" s="93">
-        <v>0.46</v>
-      </c>
-      <c r="O37" s="93">
-        <v>0.43</v>
-      </c>
+      <c r="N37" s="93"/>
+      <c r="O37" s="93"/>
       <c r="P37" s="93">
-        <v>112</v>
+        <v>31</v>
       </c>
       <c r="Q37" s="93">
-        <v>0.77219810289234758</v>
+        <v>0.81233159477945005</v>
       </c>
       <c r="R37" s="93">
-        <v>-3.64511147092485E-2</v>
+        <v>-3.4256763347845533E-2</v>
       </c>
       <c r="S37" s="93">
-        <v>2.8861421876029158E-3</v>
+        <v>2.5847785584919365E-3</v>
       </c>
       <c r="T37" s="93">
-        <v>2.5743027944748809E-2</v>
+        <v>2.5575313853269277E-2</v>
       </c>
       <c r="U37" s="93">
-        <v>-1.7368441701636483E-2</v>
+        <v>-1.8803767424097062E-2</v>
       </c>
       <c r="V37" s="92">
-        <v>46099.477071759262</v>
+        <v>46101.448611111111</v>
       </c>
       <c r="W37" s="1" t="s">
         <v>264</v>
@@ -8976,31 +8976,103 @@
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A31" s="85"/>
+      <c r="A31" s="85">
+        <v>46100.744826388887</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>300</v>
+      </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A32" s="85"/>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A33" s="85"/>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A34" s="85"/>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A35" s="85"/>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A36" s="85"/>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A37" s="85"/>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A38" s="85"/>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A39" s="85"/>
+      <c r="A32" s="85">
+        <v>46100.744837962964</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A33" s="85">
+        <v>46100.744837962964</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A34" s="85">
+        <v>46100.756168981483</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A35" s="85">
+        <v>46100.756168981483</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A36" s="85">
+        <v>46100.756168981483</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A37" s="85">
+        <v>46101.447233796294</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A38" s="85">
+        <v>46101.447245370371</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A39" s="85">
+        <v>46101.447245370371</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>316</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9066,11 +9138,11 @@
       <c r="E4" s="10"/>
       <c r="F4" s="10"/>
       <c r="G4" s="15">
-        <v>12371</v>
+        <v>12808</v>
       </c>
       <c r="H4" s="6">
         <f>-G4</f>
-        <v>-12371</v>
+        <v>-12808</v>
       </c>
     </row>
     <row r="5" spans="2:8" x14ac:dyDescent="0.4">
@@ -9191,11 +9263,11 @@
       <c r="F13" s="10"/>
       <c r="G13" s="6">
         <f>SUM(G3:G12)</f>
-        <v>1275.9499999999098</v>
+        <v>1712.9499999999098</v>
       </c>
       <c r="H13" s="6">
         <f>SUM(H3:H12)</f>
-        <v>35124.049999999952</v>
+        <v>34687.049999999952</v>
       </c>
     </row>
   </sheetData>
@@ -9377,11 +9449,11 @@
       <c r="H5" s="67"/>
       <c r="I5" s="70">
         <f>Blotter!C$4-SUM(NAV!I$4:I4)</f>
-        <v>4865.0606320098977</v>
+        <v>2992.0606320098982</v>
       </c>
       <c r="J5" s="70">
         <f t="shared" si="2"/>
-        <v>1004865.0606320099</v>
+        <v>1002992.0606320099</v>
       </c>
       <c r="K5" s="70">
         <f t="shared" si="3"/>
@@ -9389,19 +9461,19 @@
       </c>
       <c r="L5" s="71">
         <f t="shared" si="4"/>
-        <v>1004.8650606320099</v>
+        <v>1002.9920606320098</v>
       </c>
       <c r="M5" s="72">
         <f t="shared" si="5"/>
-        <v>4.8650606320099765E-3</v>
+        <v>2.9920606320097409E-3</v>
       </c>
       <c r="N5" s="73">
         <f t="shared" ref="N5" si="6">L5/L4-1</f>
-        <v>4.8650606320099765E-3</v>
+        <v>2.9920606320097409E-3</v>
       </c>
       <c r="O5" s="75">
         <f>STDEVP(N$4:N5)*SQRT(12)</f>
-        <v>8.4265321965444322E-3</v>
+        <v>5.1824010339675168E-3</v>
       </c>
     </row>
     <row r="6" spans="2:18" ht="14.25" x14ac:dyDescent="0.4">
@@ -9881,7 +9953,7 @@
       </c>
       <c r="D5" s="6">
         <f t="array" ref="D5">SUM((Blotter!C$19:C$1013=C5)*(Blotter!N$19:N$1013)*1)</f>
-        <v>3411.0899999999965</v>
+        <v>2871.0899999999965</v>
       </c>
       <c r="E5" s="6">
         <f t="array" ref="E5">SUM((Blotter!B$19:C$1013=C5)*(Blotter!R$19:R$1013)*1)</f>
@@ -9889,7 +9961,7 @@
       </c>
       <c r="F5" s="30">
         <f t="shared" ref="F5" si="1">IF(ISNUMBER(D5/E5),D5/E5,0)</f>
-        <v>0.37900999999999962</v>
+        <v>0.31900999999999963</v>
       </c>
       <c r="G5" s="36" t="str">
         <f t="array" ref="G5">IF(SUM((Blotter!C$19:C$1013=PLB!C5)*(Blotter!M$19:M$1013))=0,"C","O")</f>
@@ -9897,20 +9969,20 @@
       </c>
       <c r="H5" s="16">
         <f>J4+D5</f>
-        <v>1003933.33063201</v>
+        <v>1003393.33063201</v>
       </c>
       <c r="I5" s="16"/>
       <c r="J5" s="16">
         <f>H5+I5</f>
-        <v>1003933.33063201</v>
+        <v>1003393.33063201</v>
       </c>
       <c r="K5" s="3">
         <f>H5/J4-1</f>
-        <v>3.4093095200415924E-3</v>
+        <v>2.8695913827825326E-3</v>
       </c>
       <c r="L5" s="3">
         <f>(1+K5)*(1+L4)-1</f>
-        <v>3.933330632009957E-3</v>
+        <v>3.3933306320099721E-3</v>
       </c>
       <c r="M5" s="6">
         <f>O4-IF(G5="O",O4*1%,-D5)</f>
@@ -9965,7 +10037,7 @@
       </c>
       <c r="D6" s="6">
         <f t="array" ref="D6">SUM((Blotter!C$19:C$1013=C6)*(Blotter!N$19:N$1013)*1)</f>
-        <v>-344.22000000000253</v>
+        <v>-2114.2200000000025</v>
       </c>
       <c r="E6" s="6">
         <f t="array" ref="E6">SUM((Blotter!B$19:C$1013=C6)*(Blotter!R$19:R$1013)*1)</f>
@@ -9973,7 +10045,7 @@
       </c>
       <c r="F6" s="30">
         <f t="shared" ref="F6" si="4">IF(ISNUMBER(D6/E6),D6/E6,0)</f>
-        <v>-3.5856250000000263E-2</v>
+        <v>-0.22023125000000027</v>
       </c>
       <c r="G6" s="36" t="str">
         <f t="array" ref="G6">IF(SUM((Blotter!C$19:C$1013=PLB!C6)*(Blotter!M$19:M$1013))=0,"C","O")</f>
@@ -9981,20 +10053,20 @@
       </c>
       <c r="H6" s="16">
         <f>J5+D6</f>
-        <v>1003589.11063201</v>
+        <v>1001279.11063201</v>
       </c>
       <c r="I6" s="16"/>
       <c r="J6" s="16">
         <f>H6+I6</f>
-        <v>1003589.11063201</v>
+        <v>1001279.11063201</v>
       </c>
       <c r="K6" s="3">
         <f>H6/J5-1</f>
-        <v>-3.4287137352362329E-4</v>
+        <v>-2.1070700147750587E-3</v>
       </c>
       <c r="L6" s="3">
         <f>(1+K6)*(1+L5)-1</f>
-        <v>3.5891106320100619E-3</v>
+        <v>1.2791106320100276E-3</v>
       </c>
       <c r="M6" s="6">
         <f>O5-IF(G6="O",O5*1%,-D6)</f>
@@ -15027,13 +15099,13 @@
         <v>319</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>60</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H40" s="1">
         <v>1000</v>
@@ -15103,13 +15175,13 @@
         <v>318</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>60</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H41" s="1">
         <v>1000</v>

--- a/1XW_TradeBlotter_Web.xlsx
+++ b/1XW_TradeBlotter_Web.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0a601c1c2ba3d9f4/Trading/The Strategy Project/1XW Website/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="350" documentId="13_ncr:1_{6F5069F1-F0E7-4440-AA6D-4AFA11BBED1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{536A59FE-DAAC-43F7-881B-FCE6975C8D85}"/>
+  <xr:revisionPtr revIDLastSave="380" documentId="13_ncr:1_{6F5069F1-F0E7-4440-AA6D-4AFA11BBED1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1721B188-5711-4DE2-BEB0-E56C6EADEA29}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="22695" windowHeight="14476" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,9 +29,13 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Blotter!$G$19:$G$48</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">Trades!$A$1:$X$1066</definedName>
     <definedName name="DynDate">OFFSET(NAV!$B$3,0,0,COUNTA(NAV!$B:$B),1)</definedName>
+    <definedName name="DynDatePLB">OFFSET(PLB!$B$3,0,0,COUNTA(PLB!$B:$B),1)</definedName>
+    <definedName name="DynInPLBPLB">OFFSET(PLB!$R$3,0,0,COUNTA(PLB!$R:$R)-1,1)</definedName>
     <definedName name="DynITD">OFFSET(NAV!$M$3,0,0,COUNTA(NAV!$M:$M)-1,1)</definedName>
     <definedName name="DynMTD">OFFSET(NAV!$N$3,0,0,COUNTA(NAV!$N:$N)-1,1)</definedName>
     <definedName name="DynNAV">OFFSET(NAV!$L$3,0,0,COUNTA(NAV!$L:$L)-1,1)</definedName>
+    <definedName name="DynPerfPLB">OFFSET(PLB!$L$3,0,0,COUNTA(PLB!$L:$L)-1,1)</definedName>
+    <definedName name="DynPLBPLB">OFFSET(PLB!$Q$3,0,0,COUNTA(PLB!$Q:$Q)-1,1)</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">NAV!$A$25:$P$78</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">PLB!$A$1:$X$55</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">PLB_chart!$A$1:$V$39</definedName>
@@ -117,7 +121,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1222" uniqueCount="331">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1162" uniqueCount="328">
   <si>
     <t>WEEK</t>
   </si>
@@ -891,9 +895,6 @@
     <t>SIH6</t>
   </si>
   <si>
-    <t>HGH6</t>
-  </si>
-  <si>
     <t>6EH6</t>
   </si>
   <si>
@@ -936,9 +937,6 @@
     <t>FDXM 20260619 M</t>
   </si>
   <si>
-    <t>CLJ6</t>
-  </si>
-  <si>
     <t>NGM26</t>
   </si>
   <si>
@@ -951,9 +949,6 @@
     <t>SIM6</t>
   </si>
   <si>
-    <t>HGM6</t>
-  </si>
-  <si>
     <t>DXM6</t>
   </si>
   <si>
@@ -1029,18 +1024,6 @@
     <t>BTC.USD-PAXOS</t>
   </si>
   <si>
-    <t>INFO</t>
-  </si>
-  <si>
-    <t>Starting. host=127.0.0.1 port=7497 clientId=11 mktDataType=3 interval=0.25s</t>
-  </si>
-  <si>
-    <t>Connected to TWS.</t>
-  </si>
-  <si>
-    <t>Loaded 35 contracts from Symbols sheet.</t>
-  </si>
-  <si>
     <t>Spot</t>
   </si>
   <si>
@@ -1080,9 +1063,6 @@
     <t>LO</t>
   </si>
   <si>
-    <t>Loaded 36 contracts from Symbols sheet.</t>
-  </si>
-  <si>
     <t>FOP</t>
   </si>
   <si>
@@ -1101,15 +1081,6 @@
     <t>Long CL Put Spread</t>
   </si>
   <si>
-    <t>ERROR</t>
-  </si>
-  <si>
-    <t>Loop error: (-2147352567, 'Exception occurred.', (0, None, None, None, 0, -2146777998), None). Reconnecting in 2s.</t>
-  </si>
-  <si>
-    <t>Reconnected to TWS.</t>
-  </si>
-  <si>
     <t>CL JUN26 55 P</t>
   </si>
   <si>
@@ -1122,7 +1093,31 @@
     <t>Crypto</t>
   </si>
   <si>
-    <t>Close</t>
+    <t>NO_DATA</t>
+  </si>
+  <si>
+    <t>Last</t>
+  </si>
+  <si>
+    <t>Iran war de-escalation</t>
+  </si>
+  <si>
+    <t>Massive weekly / daily blow-off</t>
+  </si>
+  <si>
+    <t>HGK6</t>
+  </si>
+  <si>
+    <t>Long HG Futures</t>
+  </si>
+  <si>
+    <t>Daily 200SMA test and bounce (after H&amp;S top)</t>
+  </si>
+  <si>
+    <t>Structural deficit (EV, AI, ore grade decay). War de-escalation and improved sentiment</t>
+  </si>
+  <si>
+    <t>HG 27MAY26</t>
   </si>
 </sst>
 </file>
@@ -2272,7 +2267,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2.9920606320097409E-3</c:v>
+                  <c:v>3.4965906320099105E-3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2426,7 +2421,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2.9920606320097409E-3</c:v>
+                  <c:v>3.4965906320099105E-3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2817,7 +2812,7 @@
                   <c:v>1000</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1002.9920606320098</c:v>
+                  <c:v>1003.4965906320099</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3079,20 +3074,50 @@
               <a:effectLst/>
             </c:spPr>
           </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>[0]!DynDatePLB</c:f>
+              <c:numCache>
+                <c:formatCode>d\-mmm\-yy</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>46081</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>46088</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>46095</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>46102</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>46109</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>PLB!$R$4:$R$55</c:f>
+              <c:f>[0]!DynInPLBPLB</c:f>
               <c:numCache>
                 <c:formatCode>0.00%</c:formatCode>
-                <c:ptCount val="52"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>-1.0000000000000009E-2</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
                   <c:v>-1.9900000000000029E-2</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>-2.9701000000000088E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-3.9403990000000055E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3144,36 +3169,48 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>PLB!$B$4:$B$55</c:f>
+              <c:f>[0]!DynDatePLB</c:f>
               <c:numCache>
                 <c:formatCode>d\-mmm\-yy</c:formatCode>
-                <c:ptCount val="52"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
+                  <c:v>46081</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>46088</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
                   <c:v>46095</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>46102</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>46109</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>PLB!$Q$4:$Q$55</c:f>
+              <c:f>[0]!DynPLBPLB</c:f>
               <c:numCache>
                 <c:formatCode>0.00%</c:formatCode>
-                <c:ptCount val="52"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>5.2224063201000703E-4</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
                   <c:v>-9.482981774310062E-3</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>-1.9388151956566846E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-2.919427043700118E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3223,20 +3260,50 @@
               <a:effectLst/>
             </c:spPr>
           </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>[0]!DynDatePLB</c:f>
+              <c:numCache>
+                <c:formatCode>d\-mmm\-yy</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>46081</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>46088</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>46095</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>46102</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>46109</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>PLB!$L$4:$L$55</c:f>
+              <c:f>[0]!DynPerfPLB</c:f>
               <c:numCache>
                 <c:formatCode>0.00%</c:formatCode>
-                <c:ptCount val="52"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>5.2224063201000703E-4</c:v>
                 </c:pt>
-                <c:pt idx="1">
-                  <c:v>3.3933306320099721E-3</c:v>
+                <c:pt idx="2">
+                  <c:v>-2.4566693679900498E-3</c:v>
                 </c:pt>
-                <c:pt idx="2">
-                  <c:v>1.2791106320100276E-3</c:v>
+                <c:pt idx="3">
+                  <c:v>-1.1508893679901266E-3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4.7164063200999529E-4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3367,7 +3434,6 @@
         <c:crossAx val="785358624"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
-        <c:majorUnit val="5.000000000000001E-2"/>
       </c:valAx>
     </c:plotArea>
     <c:legend>
@@ -3887,7 +3953,7 @@
       </c>
       <c r="C1" s="79">
         <f ca="1">TODAY()</f>
-        <v>46101</v>
+        <v>46106</v>
       </c>
     </row>
     <row r="2" spans="2:11" x14ac:dyDescent="0.4">
@@ -3895,7 +3961,7 @@
         <v>108</v>
       </c>
       <c r="C2" s="37" t="s">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="E2" s="47" t="s">
         <v>123</v>
@@ -3912,13 +3978,13 @@
       </c>
       <c r="C3" s="28">
         <f ca="1">OFFSET(NAV!B1,MATCH(C1,NAV!B:B,1),8)</f>
-        <v>1002992.0606320099</v>
+        <v>1003496.5906320099</v>
       </c>
       <c r="E3" s="47" t="s">
         <v>124</v>
       </c>
       <c r="F3" s="47" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="G3" s="47"/>
       <c r="H3" s="28"/>
@@ -3929,7 +3995,7 @@
       </c>
       <c r="C4" s="28">
         <f>SUM(N18:N1012)</f>
-        <v>2992.0606320098982</v>
+        <v>3496.5906320099402</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="47" t="s">
@@ -3947,7 +4013,7 @@
       </c>
       <c r="C5" s="3">
         <f ca="1">OFFSET(NAV!B1,MATCH(C1,NAV!B:B,1),11)</f>
-        <v>2.9920606320097409E-3</v>
+        <v>3.4965906320099105E-3</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="47" t="s">
@@ -3966,11 +4032,11 @@
       </c>
       <c r="C6" s="3">
         <f ca="1">OFFSET(NAV!B1,MATCH(C1,NAV!B:B,1),12)</f>
-        <v>2.9920606320097409E-3</v>
+        <v>3.4965906320099105E-3</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="47" t="s">
-        <v>329</v>
+        <v>318</v>
       </c>
       <c r="F6" s="47"/>
       <c r="G6" s="47"/>
@@ -3983,11 +4049,11 @@
       </c>
       <c r="C7" s="28">
         <f>Cash_Mgmt!H13</f>
-        <v>34687.049999999952</v>
+        <v>34575.049999999952</v>
       </c>
       <c r="D7" s="3">
         <f ca="1">C7/C3</f>
-        <v>3.4583573850168657E-2</v>
+        <v>3.4454576450752381E-2</v>
       </c>
       <c r="E7" s="47"/>
       <c r="F7" s="47"/>
@@ -4001,11 +4067,11 @@
       </c>
       <c r="C8" s="28">
         <f>C4+C7</f>
-        <v>37679.110632009848</v>
+        <v>38071.64063200989</v>
       </c>
       <c r="D8" s="3">
         <f ca="1">C5+D7</f>
-        <v>3.7575634482178398E-2</v>
+        <v>3.7951167082762291E-2</v>
       </c>
       <c r="G8" s="47"/>
       <c r="H8" s="51"/>
@@ -4017,11 +4083,11 @@
       </c>
       <c r="C9" s="28">
         <f t="array" ref="C9">SUM((F19:F112="Futures")*(M19:M112))</f>
-        <v>99930</v>
+        <v>232455</v>
       </c>
       <c r="D9" s="3">
         <f ca="1">C9/$C$3</f>
-        <v>9.963189532829568E-2</v>
+        <v>0.23164503215063048</v>
       </c>
       <c r="E9" s="47"/>
       <c r="F9" s="47"/>
@@ -4049,11 +4115,11 @@
       </c>
       <c r="C11" s="28">
         <f t="array" ref="C11">SUM((F19:F212="Put")*(M19:M212))</f>
-        <v>7470</v>
+        <v>10889.999999999998</v>
       </c>
       <c r="D11" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>7.4477159822112348E-3</v>
+        <v>1.0852054806824399E-2</v>
       </c>
     </row>
     <row r="12" spans="2:11" x14ac:dyDescent="0.4">
@@ -4062,11 +4128,11 @@
       </c>
       <c r="C12" s="28" cm="1">
         <f t="array" ref="C12">SUM((PLB!G4:G999="O")*(PLB!E4:E999))</f>
-        <v>18600</v>
+        <v>25792.5</v>
       </c>
       <c r="D12" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>1.8544513690646448E-2</v>
+        <v>2.5702628430212888E-2</v>
       </c>
     </row>
     <row r="13" spans="2:11" x14ac:dyDescent="0.4">
@@ -4075,11 +4141,11 @@
       </c>
       <c r="C13" s="28">
         <f t="array" ref="C13">SUM((PLB!G4:G999="O")*(PLB!D4:D999))</f>
-        <v>756.86999999999398</v>
+        <v>-50.600000000009004</v>
       </c>
       <c r="D13" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>7.5461215467954119E-4</v>
+        <v>-5.0423689001415276E-5</v>
       </c>
       <c r="F13" s="59"/>
       <c r="G13" s="59"/>
@@ -4090,11 +4156,11 @@
       </c>
       <c r="C14" s="28">
         <f>C12+C13</f>
-        <v>19356.869999999995</v>
+        <v>25741.899999999991</v>
       </c>
       <c r="D14" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>1.929912584532599E-2</v>
+        <v>2.5652204741211472E-2</v>
       </c>
     </row>
     <row r="17" spans="2:28" x14ac:dyDescent="0.4">
@@ -4191,7 +4257,7 @@
       <c r="M18" s="12"/>
       <c r="N18" s="95">
         <f>Cash_Mgmt!G13</f>
-        <v>1712.9499999999098</v>
+        <v>3024.9499999999553</v>
       </c>
       <c r="O18" s="12"/>
       <c r="P18" s="12"/>
@@ -4217,10 +4283,10 @@
         <v>190</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>329</v>
+        <v>318</v>
       </c>
       <c r="F19" s="10" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="G19" s="28">
         <f>VLOOKUP(D19,Multiplier!B:I,8,0)</f>
@@ -4291,13 +4357,13 @@
       </c>
       <c r="Z19" s="35">
         <f>IF(C$2="Last",IF(ISNUMBER(VLOOKUP(B19,Prices!A:L,8,0)),VLOOKUP(B19,Prices!A:L,8,0),0),IF(ISNUMBER(VLOOKUP(B19,Prices!A:L,12,0)),VLOOKUP(B19,Prices!A:L,12,0),0))</f>
-        <v>2141.6999999999998</v>
+        <v>2181.9499999999998</v>
       </c>
       <c r="AB19" s="29"/>
     </row>
     <row r="20" spans="2:28" x14ac:dyDescent="0.4">
       <c r="B20" s="9" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="C20" s="10">
         <v>2</v>
@@ -4332,15 +4398,15 @@
       </c>
       <c r="L20" s="29">
         <f t="shared" ref="L20" si="8">IF(I20=0,IF(H20&gt;0,X20,Y20),Z20)</f>
-        <v>3331</v>
+        <v>3136</v>
       </c>
       <c r="M20" s="28">
         <f t="shared" ref="M20" si="9">I20*J20*L20</f>
-        <v>99930</v>
+        <v>94080</v>
       </c>
       <c r="N20" s="95">
         <f t="array" ref="N20">-SUM((Trades!T$2:T$9999=Blotter!C20)*(Trades!U$2:U$9999=Blotter!B20)*(Trades!V$2:V$9999)*(Trades!W$2:W$9999))*J20+SUM((Trades!T$2:T$9999=Blotter!C20)*(Trades!U$2:U$9999=Blotter!B20)*(Trades!X$2:X$9999))+(L20*I20)*J20</f>
-        <v>2871.0899999999965</v>
+        <v>-2978.9100000000035</v>
       </c>
       <c r="O20" s="29">
         <f>VLOOKUP(D20,Multiplier!B:H,3,0)</f>
@@ -4356,11 +4422,11 @@
       </c>
       <c r="S20" s="29">
         <f>IF(OR(F20="Futures",F20="Spot"),IF(I20=0,0,IF(I20&gt;0,L20-O20,L20+O20)),0)</f>
-        <v>3126</v>
+        <v>2931</v>
       </c>
       <c r="T20" s="3">
         <f t="shared" ref="T20" si="11">IF(S20&gt;0,IF(ISNUMBER(S20/L20-1),S20/L20-1,0),0)</f>
-        <v>-6.154308015610932E-2</v>
+        <v>-6.5369897959183687E-2</v>
       </c>
       <c r="U20" s="29">
         <f t="shared" ref="U20" si="12">IF(OR(F20="Futures",F20="Stocks"),IF(I20=0,0,IF(I20&gt;0,K20-P20,K20+P20)),0)</f>
@@ -4368,7 +4434,7 @@
       </c>
       <c r="V20" s="3">
         <f t="shared" ref="V20" si="13">IF(U20&gt;0,IF(ISNUMBER(U20/L20-1),U20/L20-1,0),0)</f>
-        <v>-0.11879405583908731</v>
+        <v>-6.3999681122449026E-2</v>
       </c>
       <c r="X20" s="34">
         <f t="array" ref="X20">IF(ISNUMBER(SUM((Trades!T$2:T$9999=Blotter!C20)*(Trades!U$2:U$9999=Blotter!B20)*(Trades!W$2:W$9999)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0))/SUM((Trades!T$2:T$9999=Blotter!C20)*(Trades!U$2:U$9999=Blotter!B20)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0))),SUM((Trades!T$2:T$9999=Blotter!C20)*(Trades!U$2:U$9999=Blotter!B20)*(Trades!W$2:W$9999)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0))/SUM((Trades!T$2:T$9999=Blotter!C20)*(Trades!U$2:U$9999=Blotter!B20)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0)),0)</f>
@@ -4380,13 +4446,13 @@
       </c>
       <c r="Z20" s="35">
         <f>IF(C$2="Last",IF(ISNUMBER(VLOOKUP(B20,Prices!A:L,8,0)),VLOOKUP(B20,Prices!A:L,8,0),0),IF(ISNUMBER(VLOOKUP(B20,Prices!A:L,12,0)),VLOOKUP(B20,Prices!A:L,12,0),0))</f>
-        <v>3331</v>
+        <v>3136</v>
       </c>
       <c r="AB20" s="29"/>
     </row>
     <row r="21" spans="2:28" x14ac:dyDescent="0.4">
       <c r="B21" s="9" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="C21" s="10">
         <v>3</v>
@@ -4421,15 +4487,15 @@
       </c>
       <c r="L21" s="29">
         <f t="shared" ref="L21:L22" si="15">IF(I21=0,IF(H21&gt;0,X21,Y21),Z21)</f>
-        <v>2.91</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="M21" s="28">
         <f t="shared" ref="M21:M22" si="16">I21*J21*L21</f>
-        <v>8730</v>
+        <v>12299.999999999998</v>
       </c>
       <c r="N21" s="95">
         <f t="array" ref="N21">-SUM((Trades!T$2:T$9999=Blotter!C21)*(Trades!U$2:U$9999=Blotter!B21)*(Trades!V$2:V$9999)*(Trades!W$2:W$9999))*J21+SUM((Trades!T$2:T$9999=Blotter!C21)*(Trades!U$2:U$9999=Blotter!B21)*(Trades!X$2:X$9999))+(L21*I21)*J21</f>
-        <v>-1897.1100000000024</v>
+        <v>1672.8899999999958</v>
       </c>
       <c r="O21" s="29">
         <f>VLOOKUP(D21,Multiplier!B:H,3,0)</f>
@@ -4469,13 +4535,13 @@
       </c>
       <c r="Z21" s="35">
         <f>IF(C$2="Last",IF(ISNUMBER(VLOOKUP(B21,Prices!A:L,8,0)),VLOOKUP(B21,Prices!A:L,8,0),0),IF(ISNUMBER(VLOOKUP(B21,Prices!A:L,12,0)),VLOOKUP(B21,Prices!A:L,12,0),0))</f>
-        <v>2.91</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="AB21" s="29"/>
     </row>
     <row r="22" spans="2:28" x14ac:dyDescent="0.4">
       <c r="B22" s="9" t="s">
-        <v>319</v>
+        <v>311</v>
       </c>
       <c r="C22" s="10">
         <v>3</v>
@@ -4510,15 +4576,15 @@
       </c>
       <c r="L22" s="29">
         <f t="shared" si="15"/>
-        <v>0.42</v>
+        <v>0.47</v>
       </c>
       <c r="M22" s="28">
         <f t="shared" si="16"/>
-        <v>-1260</v>
+        <v>-1410</v>
       </c>
       <c r="N22" s="95">
         <f t="array" ref="N22">-SUM((Trades!T$2:T$9999=Blotter!C22)*(Trades!U$2:U$9999=Blotter!B22)*(Trades!V$2:V$9999)*(Trades!W$2:W$9999))*J22+SUM((Trades!T$2:T$9999=Blotter!C22)*(Trades!U$2:U$9999=Blotter!B22)*(Trades!X$2:X$9999))+(L22*I22)*J22</f>
-        <v>-217.11000000000013</v>
+        <v>-367.11000000000013</v>
       </c>
       <c r="O22" s="29">
         <f>VLOOKUP(D22,Multiplier!B:H,3,0)</f>
@@ -4558,35 +4624,97 @@
       </c>
       <c r="Z22" s="35">
         <f>IF(C$2="Last",IF(ISNUMBER(VLOOKUP(B22,Prices!A:L,8,0)),VLOOKUP(B22,Prices!A:L,8,0),0),IF(ISNUMBER(VLOOKUP(B22,Prices!A:L,12,0)),VLOOKUP(B22,Prices!A:L,12,0),0))</f>
-        <v>0.42</v>
+        <v>0.47</v>
       </c>
       <c r="AB22" s="29"/>
     </row>
     <row r="23" spans="2:28" x14ac:dyDescent="0.4">
-      <c r="B23" s="9"/>
-      <c r="C23" s="10"/>
-      <c r="D23" s="10"/>
-      <c r="E23" s="10"/>
-      <c r="F23" s="10"/>
-      <c r="G23" s="28"/>
-      <c r="H23" s="11"/>
-      <c r="I23" s="29"/>
-      <c r="J23" s="28"/>
-      <c r="K23" s="46"/>
-      <c r="L23" s="46"/>
-      <c r="M23" s="28"/>
-      <c r="N23" s="28"/>
-      <c r="O23" s="29"/>
-      <c r="P23" s="27"/>
+      <c r="B23" s="9" t="s">
+        <v>323</v>
+      </c>
+      <c r="C23" s="10">
+        <v>4</v>
+      </c>
+      <c r="D23" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="E23" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="F23" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="G23" s="28">
+        <f>VLOOKUP(D23,Multiplier!B:I,8,0)</f>
+        <v>2</v>
+      </c>
+      <c r="H23" s="11">
+        <v>1</v>
+      </c>
+      <c r="I23" s="28">
+        <f t="array" ref="I23">ROUND(SUM((Trades!V$2:V$9999)*(Trades!U$2:U$9999=Blotter!B23)*(Trades!$T$2:T$9999=Blotter!C23)),8)</f>
+        <v>1</v>
+      </c>
+      <c r="J23" s="28">
+        <f>VLOOKUP(D23,Multiplier!B:D,2,0)</f>
+        <v>25000</v>
+      </c>
+      <c r="K23" s="29">
+        <f t="shared" ref="K23" si="22">L23-N23/(H23*J23)</f>
+        <v>5.4700988000000006</v>
+      </c>
+      <c r="L23" s="29">
+        <f t="shared" ref="L23" si="23">IF(I23=0,IF(H23&gt;0,X23,Y23),Z23)</f>
+        <v>5.5350000000000001</v>
+      </c>
+      <c r="M23" s="28">
+        <f t="shared" ref="M23" si="24">I23*J23*L23</f>
+        <v>138375</v>
+      </c>
+      <c r="N23" s="95">
+        <f t="array" ref="N23">-SUM((Trades!T$2:T$9999=Blotter!C23)*(Trades!U$2:U$9999=Blotter!B23)*(Trades!V$2:V$9999)*(Trades!W$2:W$9999))*J23+SUM((Trades!T$2:T$9999=Blotter!C23)*(Trades!U$2:U$9999=Blotter!B23)*(Trades!X$2:X$9999))+(L23*I23)*J23</f>
+        <v>1622.5299999999988</v>
+      </c>
+      <c r="O23" s="29">
+        <f>VLOOKUP(D23,Multiplier!B:H,3,0)</f>
+        <v>0.1918</v>
+      </c>
+      <c r="P23" s="27">
+        <v>0.28770000000000001</v>
+      </c>
       <c r="Q23" s="27"/>
-      <c r="R23" s="28"/>
-      <c r="S23" s="29"/>
-      <c r="T23" s="3"/>
-      <c r="U23" s="29"/>
-      <c r="V23" s="3"/>
-      <c r="X23" s="34"/>
-      <c r="Y23" s="34"/>
-      <c r="Z23" s="35"/>
+      <c r="R23" s="28">
+        <f t="shared" ref="R23" si="25">(1-Q23)*P23*J23*H23</f>
+        <v>7192.5</v>
+      </c>
+      <c r="S23" s="29">
+        <f t="shared" ref="S23" si="26">IF(OR(F23="Futures",F23="Spot"),IF(I23=0,0,IF(I23&gt;0,L23-O23,L23+O23)),0)</f>
+        <v>5.3432000000000004</v>
+      </c>
+      <c r="T23" s="3">
+        <f t="shared" ref="T23" si="27">IF(S23&gt;0,IF(ISNUMBER(S23/L23-1),S23/L23-1,0),0)</f>
+        <v>-3.465221318879852E-2</v>
+      </c>
+      <c r="U23" s="29">
+        <f t="shared" ref="U23" si="28">IF(OR(F23="Futures",F23="Stocks"),IF(I23=0,0,IF(I23&gt;0,K23-P23,K23+P23)),0)</f>
+        <v>5.1823988000000005</v>
+      </c>
+      <c r="V23" s="3">
+        <f t="shared" ref="V23" si="29">IF(U23&gt;0,IF(ISNUMBER(U23/L23-1),U23/L23-1,0),0)</f>
+        <v>-6.3703920505871703E-2</v>
+      </c>
+      <c r="X23" s="34">
+        <f t="array" ref="X23">IF(ISNUMBER(SUM((Trades!T$2:T$9999=Blotter!C23)*(Trades!U$2:U$9999=Blotter!B23)*(Trades!W$2:W$9999)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0))/SUM((Trades!T$2:T$9999=Blotter!C23)*(Trades!U$2:U$9999=Blotter!B23)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0))),SUM((Trades!T$2:T$9999=Blotter!C23)*(Trades!U$2:U$9999=Blotter!B23)*(Trades!W$2:W$9999)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0))/SUM((Trades!T$2:T$9999=Blotter!C23)*(Trades!U$2:U$9999=Blotter!B23)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0)),0)</f>
+        <v>0</v>
+      </c>
+      <c r="Y23" s="34">
+        <f t="array" ref="Y23">IF(ISNUMBER(SUM((Trades!T$2:T$9999=Blotter!C23)*(Trades!U$2:U$9999=Blotter!B23)*(Trades!W$2:W$9999)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&gt;0))/SUM((Trades!T$2:T$9999=Blotter!C23)*(Trades!U$2:U$9999=Blotter!B23)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&gt;0))),SUM((Trades!T$2:T$9999=Blotter!C23)*(Trades!U$2:U$9999=Blotter!B23)*(Trades!W$2:W$9999)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&gt;0))/SUM((Trades!T$2:T$9999=Blotter!C23)*(Trades!U$2:U$9999=Blotter!B23)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&gt;0)),0)</f>
+        <v>5.47</v>
+      </c>
+      <c r="Z23" s="35">
+        <f>IF(C$2="Last",IF(ISNUMBER(VLOOKUP(B23,Prices!A:L,8,0)),VLOOKUP(B23,Prices!A:L,8,0),0),IF(ISNUMBER(VLOOKUP(B23,Prices!A:L,12,0)),VLOOKUP(B23,Prices!A:L,12,0),0))</f>
+        <v>5.5350000000000001</v>
+      </c>
       <c r="AB23" s="29"/>
     </row>
     <row r="24" spans="2:28" x14ac:dyDescent="0.4">
@@ -6282,7 +6410,7 @@
         <v>21</v>
       </c>
       <c r="E2" s="81" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="F2" s="81" t="s">
         <v>79</v>
@@ -6291,31 +6419,31 @@
         <v>59</v>
       </c>
       <c r="H2" s="91">
-        <v>6652.25</v>
+        <v>6648.5</v>
       </c>
       <c r="I2" s="91">
-        <v>6652</v>
+        <v>6648.25</v>
       </c>
       <c r="J2" s="91">
-        <v>6652.25</v>
+        <v>6648.5</v>
       </c>
       <c r="K2" s="91">
-        <v>6652.125</v>
+        <v>6648.375</v>
       </c>
       <c r="L2" s="91">
-        <v>6660</v>
+        <v>6606</v>
       </c>
       <c r="M2" s="91">
-        <v>6675.5</v>
+        <v>6646.5</v>
       </c>
       <c r="N2" s="91">
-        <v>6685.5</v>
+        <v>6684.75</v>
       </c>
       <c r="O2" s="91">
-        <v>6643.25</v>
+        <v>6631.25</v>
       </c>
       <c r="P2" s="91">
-        <v>108788</v>
+        <v>581969</v>
       </c>
       <c r="Q2" s="91"/>
       <c r="R2" s="91"/>
@@ -6323,10 +6451,10 @@
       <c r="T2" s="91"/>
       <c r="U2" s="91"/>
       <c r="V2" s="85">
-        <v>46101.448611111111</v>
+        <v>46106.640856481485</v>
       </c>
       <c r="W2" s="81" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="X2" s="81"/>
       <c r="Y2" s="81"/>
@@ -6346,7 +6474,7 @@
         <v>22</v>
       </c>
       <c r="E3" s="81" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F3" s="81" t="s">
         <v>79</v>
@@ -6355,31 +6483,31 @@
         <v>59</v>
       </c>
       <c r="H3" s="91">
-        <v>24512.75</v>
+        <v>24426.5</v>
       </c>
       <c r="I3" s="91">
-        <v>24512.25</v>
+        <v>24426.5</v>
       </c>
       <c r="J3" s="91">
-        <v>24513.5</v>
+        <v>24427.25</v>
       </c>
       <c r="K3" s="91">
-        <v>24512.875</v>
+        <v>24426.875</v>
       </c>
       <c r="L3" s="91">
-        <v>24580</v>
+        <v>24213.75</v>
       </c>
       <c r="M3" s="91">
-        <v>24632.75</v>
+        <v>24420</v>
       </c>
       <c r="N3" s="91">
-        <v>24660.5</v>
+        <v>24539.75</v>
       </c>
       <c r="O3" s="91">
-        <v>24482.75</v>
+        <v>24320.5</v>
       </c>
       <c r="P3" s="91">
-        <v>67749</v>
+        <v>209095</v>
       </c>
       <c r="Q3" s="91"/>
       <c r="R3" s="91"/>
@@ -6387,10 +6515,10 @@
       <c r="T3" s="91"/>
       <c r="U3" s="91"/>
       <c r="V3" s="85">
-        <v>46101.448611111111</v>
+        <v>46106.640856481485</v>
       </c>
       <c r="W3" s="81" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="X3" s="81"/>
       <c r="Y3" s="81"/>
@@ -6410,7 +6538,7 @@
         <v>23</v>
       </c>
       <c r="E4" s="81" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F4" s="81" t="s">
         <v>79</v>
@@ -6419,31 +6547,31 @@
         <v>59</v>
       </c>
       <c r="H4" s="91">
-        <v>2508.4</v>
+        <v>2552.4</v>
       </c>
       <c r="I4" s="91">
-        <v>2508.3000000000002</v>
+        <v>2552</v>
       </c>
       <c r="J4" s="91">
-        <v>2508.5</v>
+        <v>2552.1999999999998</v>
       </c>
       <c r="K4" s="91">
-        <v>2508.4</v>
+        <v>2552.1</v>
       </c>
       <c r="L4" s="91">
-        <v>2512.1</v>
+        <v>2522.3000000000002</v>
       </c>
       <c r="M4" s="91">
-        <v>2519.3000000000002</v>
+        <v>2551.1</v>
       </c>
       <c r="N4" s="91">
-        <v>2531.9</v>
+        <v>2565.3000000000002</v>
       </c>
       <c r="O4" s="91">
-        <v>2506.1999999999998</v>
+        <v>2535.1999999999998</v>
       </c>
       <c r="P4" s="91">
-        <v>17532</v>
+        <v>65848</v>
       </c>
       <c r="Q4" s="91"/>
       <c r="R4" s="91"/>
@@ -6451,10 +6579,10 @@
       <c r="T4" s="91"/>
       <c r="U4" s="91"/>
       <c r="V4" s="85">
-        <v>46101.448611111111</v>
+        <v>46106.640856481485</v>
       </c>
       <c r="W4" s="81" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="X4" s="81"/>
       <c r="Y4" s="81"/>
@@ -6474,7 +6602,7 @@
         <v>61</v>
       </c>
       <c r="E5" s="81" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="F5" s="81" t="s">
         <v>80</v>
@@ -6483,31 +6611,31 @@
         <v>56</v>
       </c>
       <c r="H5" s="91">
-        <v>23122</v>
+        <v>23205</v>
       </c>
       <c r="I5" s="91">
-        <v>23125</v>
+        <v>23202</v>
       </c>
       <c r="J5" s="91">
-        <v>23128</v>
+        <v>23206</v>
       </c>
       <c r="K5" s="91">
-        <v>23126.5</v>
+        <v>23204</v>
       </c>
       <c r="L5" s="91">
-        <v>23060</v>
+        <v>22833</v>
       </c>
       <c r="M5" s="91">
-        <v>23232</v>
+        <v>23119</v>
       </c>
       <c r="N5" s="91">
-        <v>23383</v>
+        <v>23283</v>
       </c>
       <c r="O5" s="91">
-        <v>23107</v>
+        <v>23004</v>
       </c>
       <c r="P5" s="91">
-        <v>9136</v>
+        <v>19756</v>
       </c>
       <c r="Q5" s="91"/>
       <c r="R5" s="91"/>
@@ -6515,10 +6643,10 @@
       <c r="T5" s="91"/>
       <c r="U5" s="91"/>
       <c r="V5" s="85">
-        <v>46101.448611111111</v>
+        <v>46106.640856481485</v>
       </c>
       <c r="W5" s="81" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="X5" s="81"/>
       <c r="Y5" s="81"/>
@@ -6526,7 +6654,7 @@
     </row>
     <row r="6" spans="1:32" x14ac:dyDescent="0.4">
       <c r="A6" s="81" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B6" s="81">
         <v>635680486</v>
@@ -6538,7 +6666,7 @@
         <v>62</v>
       </c>
       <c r="E6" s="81" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="F6" s="81" t="s">
         <v>79</v>
@@ -6547,31 +6675,31 @@
         <v>57</v>
       </c>
       <c r="H6" s="91">
-        <v>53120</v>
+        <v>53605</v>
       </c>
       <c r="I6" s="91">
-        <v>53105</v>
+        <v>53600</v>
       </c>
       <c r="J6" s="91">
-        <v>53115</v>
+        <v>53610</v>
       </c>
       <c r="K6" s="91">
-        <v>53110</v>
+        <v>53605</v>
       </c>
       <c r="L6" s="91">
-        <v>52825</v>
+        <v>52420</v>
       </c>
       <c r="M6" s="91">
-        <v>53115</v>
+        <v>53060</v>
       </c>
       <c r="N6" s="91">
-        <v>53450</v>
+        <v>54125</v>
       </c>
       <c r="O6" s="91">
-        <v>52840</v>
+        <v>53030</v>
       </c>
       <c r="P6" s="91">
-        <v>5631</v>
+        <v>18174</v>
       </c>
       <c r="Q6" s="91"/>
       <c r="R6" s="91"/>
@@ -6579,10 +6707,10 @@
       <c r="T6" s="91"/>
       <c r="U6" s="91"/>
       <c r="V6" s="85">
-        <v>46101.448611111111</v>
+        <v>46106.640856481485</v>
       </c>
       <c r="W6" s="81" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="X6" s="81"/>
       <c r="Y6" s="81"/>
@@ -6593,7 +6721,7 @@
         <v>176</v>
       </c>
       <c r="B7" s="1">
-        <v>304037436</v>
+        <v>0</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>58</v>
@@ -6601,52 +6729,31 @@
       <c r="D7" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E7" s="1" t="s">
-        <v>268</v>
-      </c>
       <c r="F7" s="1" t="s">
         <v>60</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="H7" s="93">
-        <v>96.2</v>
-      </c>
-      <c r="I7" s="93">
-        <v>95.92</v>
-      </c>
-      <c r="J7" s="93">
-        <v>96.08</v>
-      </c>
-      <c r="K7" s="93">
-        <v>96</v>
-      </c>
-      <c r="L7" s="93">
-        <v>96.14</v>
-      </c>
-      <c r="M7" s="93">
-        <v>95</v>
-      </c>
-      <c r="N7" s="93">
-        <v>96.2</v>
-      </c>
-      <c r="O7" s="93">
-        <v>93.42</v>
-      </c>
-      <c r="P7" s="93">
-        <v>394</v>
-      </c>
+      <c r="H7" s="93"/>
+      <c r="I7" s="93"/>
+      <c r="J7" s="93"/>
+      <c r="K7" s="93"/>
+      <c r="L7" s="93"/>
+      <c r="M7" s="93"/>
+      <c r="N7" s="93"/>
+      <c r="O7" s="93"/>
+      <c r="P7" s="93"/>
       <c r="Q7" s="93"/>
       <c r="R7" s="93"/>
       <c r="S7" s="93"/>
       <c r="T7" s="93"/>
       <c r="U7" s="93"/>
       <c r="V7" s="92">
-        <v>46101.448611111111</v>
+        <v>46106.640856481485</v>
       </c>
       <c r="W7" s="1" t="s">
-        <v>264</v>
+        <v>319</v>
       </c>
     </row>
     <row r="8" spans="1:32" x14ac:dyDescent="0.4">
@@ -6663,7 +6770,7 @@
         <v>5</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>60</v>
@@ -6672,31 +6779,31 @@
         <v>59</v>
       </c>
       <c r="H8" s="93">
-        <v>3.2210000000000001</v>
+        <v>3.008</v>
       </c>
       <c r="I8" s="93">
-        <v>3.222</v>
+        <v>3.0070000000000001</v>
       </c>
       <c r="J8" s="93">
-        <v>3.2240000000000002</v>
+        <v>3.0089999999999999</v>
       </c>
       <c r="K8" s="93">
-        <v>3.2229999999999999</v>
+        <v>3.008</v>
       </c>
       <c r="L8" s="93">
-        <v>3.2429999999999999</v>
+        <v>3.0379999999999998</v>
       </c>
       <c r="M8" s="93">
-        <v>3.2010000000000001</v>
+        <v>2.9940000000000002</v>
       </c>
       <c r="N8" s="93">
-        <v>3.2330000000000001</v>
+        <v>3.0139999999999998</v>
       </c>
       <c r="O8" s="93">
-        <v>3.1789999999999998</v>
+        <v>2.9550000000000001</v>
       </c>
       <c r="P8" s="93">
-        <v>1477</v>
+        <v>10032</v>
       </c>
       <c r="Q8" s="93"/>
       <c r="R8" s="93"/>
@@ -6704,10 +6811,10 @@
       <c r="T8" s="93"/>
       <c r="U8" s="93"/>
       <c r="V8" s="92">
-        <v>46101.448611111111</v>
+        <v>46106.640856481485</v>
       </c>
       <c r="W8" s="1" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="9" spans="1:32" x14ac:dyDescent="0.4">
@@ -6724,7 +6831,7 @@
         <v>9</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>60</v>
@@ -6733,31 +6840,31 @@
         <v>59</v>
       </c>
       <c r="H9" s="93">
-        <v>3.0537999999999998</v>
+        <v>2.8675999999999999</v>
       </c>
       <c r="I9" s="93">
-        <v>3.0522</v>
+        <v>2.8675999999999999</v>
       </c>
       <c r="J9" s="93">
-        <v>3.0539000000000001</v>
+        <v>2.8683000000000001</v>
       </c>
       <c r="K9" s="93">
-        <v>3.0530499999999998</v>
+        <v>2.86795</v>
       </c>
       <c r="L9" s="93">
-        <v>3.0164</v>
+        <v>2.9902000000000002</v>
       </c>
       <c r="M9" s="93">
-        <v>2.9994999999999998</v>
+        <v>2.8841000000000001</v>
       </c>
       <c r="N9" s="93">
-        <v>3.0661999999999998</v>
+        <v>2.91</v>
       </c>
       <c r="O9" s="93">
-        <v>2.9527999999999999</v>
+        <v>2.7875999999999999</v>
       </c>
       <c r="P9" s="93">
-        <v>4803</v>
+        <v>27480</v>
       </c>
       <c r="Q9" s="93"/>
       <c r="R9" s="93"/>
@@ -6765,10 +6872,10 @@
       <c r="T9" s="93"/>
       <c r="U9" s="93"/>
       <c r="V9" s="92">
-        <v>46101.448611111111</v>
+        <v>46106.640856481485</v>
       </c>
       <c r="W9" s="1" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="10" spans="1:32" x14ac:dyDescent="0.4">
@@ -6785,7 +6892,7 @@
         <v>26</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>81</v>
@@ -6794,31 +6901,31 @@
         <v>59</v>
       </c>
       <c r="H10" s="93">
-        <v>4713.8</v>
+        <v>4583.5</v>
       </c>
       <c r="I10" s="93">
-        <v>4715.7</v>
+        <v>4583.3</v>
       </c>
       <c r="J10" s="93">
-        <v>4716.3</v>
+        <v>4583.8999999999996</v>
       </c>
       <c r="K10" s="93">
-        <v>4716</v>
+        <v>4583.6000000000004</v>
       </c>
       <c r="L10" s="93">
-        <v>4640.5</v>
+        <v>4434.1000000000004</v>
       </c>
       <c r="M10" s="93">
-        <v>4689.3999999999996</v>
+        <v>4506.1000000000004</v>
       </c>
       <c r="N10" s="93">
-        <v>4773.3</v>
+        <v>4634</v>
       </c>
       <c r="O10" s="93">
-        <v>4672</v>
+        <v>4491.7</v>
       </c>
       <c r="P10" s="93">
-        <v>8827</v>
+        <v>55878</v>
       </c>
       <c r="Q10" s="93"/>
       <c r="R10" s="93"/>
@@ -6826,10 +6933,10 @@
       <c r="T10" s="93"/>
       <c r="U10" s="93"/>
       <c r="V10" s="92">
-        <v>46101.448611111111</v>
+        <v>46106.640856481485</v>
       </c>
       <c r="W10" s="1" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="11" spans="1:32" x14ac:dyDescent="0.4">
@@ -6846,7 +6953,7 @@
         <v>27</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>81</v>
@@ -6855,31 +6962,31 @@
         <v>59</v>
       </c>
       <c r="H11" s="93">
-        <v>73.105000000000004</v>
+        <v>72.614999999999995</v>
       </c>
       <c r="I11" s="93">
-        <v>73.114999999999995</v>
+        <v>72.8</v>
       </c>
       <c r="J11" s="93">
-        <v>73.165000000000006</v>
+        <v>72.84</v>
       </c>
       <c r="K11" s="93">
-        <v>73.14</v>
+        <v>72.819999999999993</v>
       </c>
       <c r="L11" s="93">
-        <v>71.47</v>
+        <v>69.819999999999993</v>
       </c>
       <c r="M11" s="93">
-        <v>73.584999999999994</v>
+        <v>72</v>
       </c>
       <c r="N11" s="93">
-        <v>74.86</v>
+        <v>74.894999999999996</v>
       </c>
       <c r="O11" s="93">
-        <v>71.655000000000001</v>
+        <v>71.650000000000006</v>
       </c>
       <c r="P11" s="93">
-        <v>197</v>
+        <v>231</v>
       </c>
       <c r="Q11" s="93"/>
       <c r="R11" s="93"/>
@@ -6887,18 +6994,18 @@
       <c r="T11" s="93"/>
       <c r="U11" s="93"/>
       <c r="V11" s="92">
-        <v>46101.448611111111</v>
+        <v>46106.640856481485</v>
       </c>
       <c r="W11" s="1" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="12" spans="1:32" x14ac:dyDescent="0.4">
       <c r="A12" s="1" t="s">
-        <v>253</v>
+        <v>323</v>
       </c>
       <c r="B12" s="1">
-        <v>712565973</v>
+        <v>473509991</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>58</v>
@@ -6907,7 +7014,7 @@
         <v>25</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>273</v>
+        <v>323</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>81</v>
@@ -6919,28 +7026,28 @@
         <v>5.5350000000000001</v>
       </c>
       <c r="I12" s="93">
-        <v>5.5069999999999997</v>
+        <v>5.5339999999999998</v>
       </c>
       <c r="J12" s="93">
-        <v>5.5090000000000003</v>
+        <v>5.5350000000000001</v>
       </c>
       <c r="K12" s="93">
-        <v>5.508</v>
+        <v>5.5344999999999995</v>
       </c>
       <c r="L12" s="93">
-        <v>5.4969999999999999</v>
+        <v>5.4550000000000001</v>
       </c>
       <c r="M12" s="93">
-        <v>5.5564999999999998</v>
+        <v>5.5585000000000004</v>
       </c>
       <c r="N12" s="93">
-        <v>5.5750000000000002</v>
+        <v>5.58</v>
       </c>
       <c r="O12" s="93">
-        <v>5.5145</v>
+        <v>5.5004999999999997</v>
       </c>
       <c r="P12" s="93">
-        <v>47</v>
+        <v>25956</v>
       </c>
       <c r="Q12" s="93"/>
       <c r="R12" s="93"/>
@@ -6948,10 +7055,10 @@
       <c r="T12" s="93"/>
       <c r="U12" s="93"/>
       <c r="V12" s="92">
-        <v>46101.448611111111</v>
+        <v>46106.640856481485</v>
       </c>
       <c r="W12" s="1" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="13" spans="1:32" x14ac:dyDescent="0.4">
@@ -6968,7 +7075,7 @@
         <v>28</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>82</v>
@@ -6977,31 +7084,31 @@
         <v>59</v>
       </c>
       <c r="H13" s="93">
-        <v>467.5</v>
+        <v>461.5</v>
       </c>
       <c r="I13" s="93">
-        <v>467.25</v>
+        <v>461.5</v>
       </c>
       <c r="J13" s="93">
-        <v>467.5</v>
+        <v>461.75</v>
       </c>
       <c r="K13" s="93">
-        <v>467.375</v>
+        <v>461.625</v>
       </c>
       <c r="L13" s="93">
-        <v>469.75</v>
+        <v>462.5</v>
       </c>
       <c r="M13" s="93">
-        <v>469</v>
+        <v>461.25</v>
       </c>
       <c r="N13" s="93">
-        <v>469.25</v>
+        <v>462.5</v>
       </c>
       <c r="O13" s="93">
-        <v>466.75</v>
+        <v>458</v>
       </c>
       <c r="P13" s="93">
-        <v>16671</v>
+        <v>51230</v>
       </c>
       <c r="Q13" s="93"/>
       <c r="R13" s="93"/>
@@ -7009,10 +7116,10 @@
       <c r="T13" s="93"/>
       <c r="U13" s="93"/>
       <c r="V13" s="92">
-        <v>46101.448611111111</v>
+        <v>46106.640856481485</v>
       </c>
       <c r="W13" s="1" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="14" spans="1:32" x14ac:dyDescent="0.4">
@@ -7029,7 +7136,7 @@
         <v>29</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>82</v>
@@ -7038,31 +7145,31 @@
         <v>59</v>
       </c>
       <c r="H14" s="93">
-        <v>602.25</v>
+        <v>589.25</v>
       </c>
       <c r="I14" s="93">
-        <v>602.25</v>
+        <v>589</v>
       </c>
       <c r="J14" s="93">
-        <v>602.5</v>
+        <v>589.25</v>
       </c>
       <c r="K14" s="93">
-        <v>602.375</v>
+        <v>589.125</v>
       </c>
       <c r="L14" s="93">
-        <v>608</v>
+        <v>590</v>
       </c>
       <c r="M14" s="93">
-        <v>608</v>
+        <v>589</v>
       </c>
       <c r="N14" s="93">
-        <v>609.25</v>
+        <v>591.25</v>
       </c>
       <c r="O14" s="93">
-        <v>602.25</v>
+        <v>579.25</v>
       </c>
       <c r="P14" s="93">
-        <v>6172</v>
+        <v>32771</v>
       </c>
       <c r="Q14" s="93"/>
       <c r="R14" s="93"/>
@@ -7070,10 +7177,10 @@
       <c r="T14" s="93"/>
       <c r="U14" s="93"/>
       <c r="V14" s="92">
-        <v>46101.448611111111</v>
+        <v>46106.640856481485</v>
       </c>
       <c r="W14" s="1" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="15" spans="1:32" x14ac:dyDescent="0.4">
@@ -7090,7 +7197,7 @@
         <v>31</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>82</v>
@@ -7099,31 +7206,31 @@
         <v>59</v>
       </c>
       <c r="H15" s="93">
-        <v>1171.5</v>
+        <v>1161</v>
       </c>
       <c r="I15" s="93">
-        <v>1171.25</v>
+        <v>1161</v>
       </c>
       <c r="J15" s="93">
-        <v>1171.5</v>
+        <v>1161.25</v>
       </c>
       <c r="K15" s="93">
-        <v>1171.375</v>
+        <v>1161.125</v>
       </c>
       <c r="L15" s="93">
-        <v>1168.5</v>
+        <v>1155</v>
       </c>
       <c r="M15" s="93">
-        <v>1166</v>
+        <v>1153.5</v>
       </c>
       <c r="N15" s="93">
-        <v>1176</v>
+        <v>1162.75</v>
       </c>
       <c r="O15" s="93">
-        <v>1165</v>
+        <v>1151.5</v>
       </c>
       <c r="P15" s="93">
-        <v>11492</v>
+        <v>34951</v>
       </c>
       <c r="Q15" s="93"/>
       <c r="R15" s="93"/>
@@ -7131,10 +7238,10 @@
       <c r="T15" s="93"/>
       <c r="U15" s="93"/>
       <c r="V15" s="92">
-        <v>46101.448611111111</v>
+        <v>46106.640856481485</v>
       </c>
       <c r="W15" s="1" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="16" spans="1:32" x14ac:dyDescent="0.4">
@@ -7151,7 +7258,7 @@
         <v>32</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>64</v>
@@ -7160,31 +7267,31 @@
         <v>59</v>
       </c>
       <c r="H16" s="93">
-        <v>15.34</v>
+        <v>15.49</v>
       </c>
       <c r="I16" s="93">
-        <v>15.34</v>
+        <v>15.49</v>
       </c>
       <c r="J16" s="93">
-        <v>15.35</v>
+        <v>15.5</v>
       </c>
       <c r="K16" s="93">
-        <v>15.344999999999999</v>
+        <v>15.495000000000001</v>
       </c>
       <c r="L16" s="93">
-        <v>15.37</v>
+        <v>15.88</v>
       </c>
       <c r="M16" s="93">
-        <v>15.33</v>
+        <v>15.8</v>
       </c>
       <c r="N16" s="93">
-        <v>15.47</v>
+        <v>15.83</v>
       </c>
       <c r="O16" s="93">
-        <v>15.27</v>
+        <v>15.32</v>
       </c>
       <c r="P16" s="93">
-        <v>13550</v>
+        <v>52102</v>
       </c>
       <c r="Q16" s="93"/>
       <c r="R16" s="93"/>
@@ -7192,10 +7299,10 @@
       <c r="T16" s="93"/>
       <c r="U16" s="93"/>
       <c r="V16" s="92">
-        <v>46101.448611111111</v>
+        <v>46106.640856481485</v>
       </c>
       <c r="W16" s="1" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="17" spans="1:23" x14ac:dyDescent="0.4">
@@ -7212,7 +7319,7 @@
         <v>33</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>64</v>
@@ -7221,31 +7328,31 @@
         <v>59</v>
       </c>
       <c r="H17" s="93">
-        <v>304.3</v>
+        <v>316.39999999999998</v>
       </c>
       <c r="I17" s="93">
-        <v>304.25</v>
+        <v>316.55</v>
       </c>
       <c r="J17" s="93">
-        <v>304.35000000000002</v>
+        <v>316.64999999999998</v>
       </c>
       <c r="K17" s="93">
-        <v>304.3</v>
+        <v>316.60000000000002</v>
       </c>
       <c r="L17" s="93">
-        <v>300.89999999999998</v>
+        <v>317.85000000000002</v>
       </c>
       <c r="M17" s="93">
-        <v>303</v>
+        <v>317.5</v>
       </c>
       <c r="N17" s="93">
-        <v>304.39999999999998</v>
+        <v>318.5</v>
       </c>
       <c r="O17" s="93">
-        <v>301.89999999999998</v>
+        <v>311.45</v>
       </c>
       <c r="P17" s="93">
-        <v>1175</v>
+        <v>7732</v>
       </c>
       <c r="Q17" s="93"/>
       <c r="R17" s="93"/>
@@ -7253,15 +7360,15 @@
       <c r="T17" s="93"/>
       <c r="U17" s="93"/>
       <c r="V17" s="92">
-        <v>46101.448611111111</v>
+        <v>46106.640856481485</v>
       </c>
       <c r="W17" s="1" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="18" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A18" s="1" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="B18" s="1">
         <v>707621000</v>
@@ -7273,7 +7380,7 @@
         <v>34</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>64</v>
@@ -7282,27 +7389,31 @@
         <v>59</v>
       </c>
       <c r="H18" s="93">
-        <v>0</v>
+        <v>3136</v>
       </c>
       <c r="I18" s="93">
-        <v>-1</v>
+        <v>3134</v>
       </c>
       <c r="J18" s="93">
-        <v>-1</v>
+        <v>3136</v>
       </c>
       <c r="K18" s="93">
-        <v>-1</v>
+        <v>3135</v>
       </c>
       <c r="L18" s="93">
-        <v>3331</v>
+        <v>3235</v>
       </c>
       <c r="M18" s="93">
-        <v>0</v>
-      </c>
-      <c r="N18" s="93"/>
-      <c r="O18" s="93"/>
+        <v>3220</v>
+      </c>
+      <c r="N18" s="93">
+        <v>3233</v>
+      </c>
+      <c r="O18" s="93">
+        <v>3121</v>
+      </c>
       <c r="P18" s="93">
-        <v>0</v>
+        <v>5945</v>
       </c>
       <c r="Q18" s="93"/>
       <c r="R18" s="93"/>
@@ -7310,10 +7421,10 @@
       <c r="T18" s="93"/>
       <c r="U18" s="93"/>
       <c r="V18" s="92">
-        <v>46101.448611111111</v>
+        <v>46106.640856481485</v>
       </c>
       <c r="W18" s="1" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="19" spans="1:23" x14ac:dyDescent="0.4">
@@ -7330,7 +7441,7 @@
         <v>65</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>64</v>
@@ -7339,31 +7450,31 @@
         <v>59</v>
       </c>
       <c r="H19" s="93">
-        <v>67.33</v>
+        <v>67.62</v>
       </c>
       <c r="I19" s="93">
-        <v>67.319999999999993</v>
+        <v>67.61</v>
       </c>
       <c r="J19" s="93">
-        <v>67.33</v>
+        <v>67.63</v>
       </c>
       <c r="K19" s="93">
-        <v>67.324999999999989</v>
+        <v>67.62</v>
       </c>
       <c r="L19" s="93">
-        <v>67.67</v>
+        <v>67.62</v>
       </c>
       <c r="M19" s="93">
-        <v>67.69</v>
+        <v>67.349999999999994</v>
       </c>
       <c r="N19" s="93">
-        <v>68.209999999999994</v>
+        <v>68.37</v>
       </c>
       <c r="O19" s="93">
-        <v>67.290000000000006</v>
+        <v>67.349999999999994</v>
       </c>
       <c r="P19" s="93">
-        <v>7239</v>
+        <v>13810</v>
       </c>
       <c r="Q19" s="93"/>
       <c r="R19" s="93"/>
@@ -7371,10 +7482,10 @@
       <c r="T19" s="93"/>
       <c r="U19" s="93"/>
       <c r="V19" s="92">
-        <v>46101.448611111111</v>
+        <v>46106.640856481485</v>
       </c>
       <c r="W19" s="1" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="20" spans="1:23" x14ac:dyDescent="0.4">
@@ -7391,7 +7502,7 @@
         <v>35</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>79</v>
@@ -7400,31 +7511,31 @@
         <v>59</v>
       </c>
       <c r="H20" s="93">
-        <v>0</v>
+        <v>235.07499999999999</v>
       </c>
       <c r="I20" s="93">
-        <v>-100</v>
+        <v>235.02500000000001</v>
       </c>
       <c r="J20" s="93">
-        <v>-100</v>
+        <v>235.1</v>
       </c>
       <c r="K20" s="93">
-        <v>-100</v>
+        <v>235.0625</v>
       </c>
       <c r="L20" s="93">
-        <v>233.27500000000001</v>
+        <v>235.375</v>
       </c>
       <c r="M20" s="93">
-        <v>234.9</v>
+        <v>235.57499999999999</v>
       </c>
       <c r="N20" s="93">
-        <v>234.95</v>
+        <v>235.625</v>
       </c>
       <c r="O20" s="93">
-        <v>232.65</v>
+        <v>234.2</v>
       </c>
       <c r="P20" s="93">
-        <v>13220</v>
+        <v>3517</v>
       </c>
       <c r="Q20" s="93"/>
       <c r="R20" s="93"/>
@@ -7432,10 +7543,10 @@
       <c r="T20" s="93"/>
       <c r="U20" s="93"/>
       <c r="V20" s="92">
-        <v>46101.448611111111</v>
+        <v>46106.640856481485</v>
       </c>
       <c r="W20" s="1" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="21" spans="1:23" x14ac:dyDescent="0.4">
@@ -7452,7 +7563,7 @@
         <v>36</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>79</v>
@@ -7461,31 +7572,31 @@
         <v>59</v>
       </c>
       <c r="H21" s="93">
-        <v>0</v>
+        <v>351.35</v>
       </c>
       <c r="I21" s="93">
-        <v>-100</v>
+        <v>351.32499999999999</v>
       </c>
       <c r="J21" s="93">
-        <v>-100</v>
+        <v>351.45</v>
       </c>
       <c r="K21" s="93">
-        <v>-100</v>
+        <v>351.38749999999999</v>
       </c>
       <c r="L21" s="93">
-        <v>343.42500000000001</v>
+        <v>350.7</v>
       </c>
       <c r="M21" s="93">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="N21" s="93">
-        <v>347</v>
+        <v>352.35</v>
       </c>
       <c r="O21" s="93">
-        <v>342.55</v>
+        <v>349.52499999999998</v>
       </c>
       <c r="P21" s="93">
-        <v>5994</v>
+        <v>2074</v>
       </c>
       <c r="Q21" s="93"/>
       <c r="R21" s="93"/>
@@ -7493,10 +7604,10 @@
       <c r="T21" s="93"/>
       <c r="U21" s="93"/>
       <c r="V21" s="92">
-        <v>46101.448611111111</v>
+        <v>46106.640856481485</v>
       </c>
       <c r="W21" s="1" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="22" spans="1:23" x14ac:dyDescent="0.4">
@@ -7513,7 +7624,7 @@
         <v>37</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>79</v>
@@ -7522,31 +7633,31 @@
         <v>59</v>
       </c>
       <c r="H22" s="93">
-        <v>0</v>
+        <v>91.325000000000003</v>
       </c>
       <c r="I22" s="93">
-        <v>-100</v>
+        <v>91.3</v>
       </c>
       <c r="J22" s="93">
-        <v>-100</v>
+        <v>91.325000000000003</v>
       </c>
       <c r="K22" s="93">
-        <v>-100</v>
+        <v>91.3125</v>
       </c>
       <c r="L22" s="93">
-        <v>92.05</v>
+        <v>91.05</v>
       </c>
       <c r="M22" s="93">
-        <v>93.65</v>
+        <v>90.75</v>
       </c>
       <c r="N22" s="93">
-        <v>93.724999999999994</v>
+        <v>91.5</v>
       </c>
       <c r="O22" s="93">
-        <v>91.924999999999997</v>
+        <v>90.525000000000006</v>
       </c>
       <c r="P22" s="93">
-        <v>24371</v>
+        <v>3201</v>
       </c>
       <c r="Q22" s="93"/>
       <c r="R22" s="93"/>
@@ -7554,15 +7665,15 @@
       <c r="T22" s="93"/>
       <c r="U22" s="93"/>
       <c r="V22" s="92">
-        <v>46101.448611111111</v>
+        <v>46106.640856481485</v>
       </c>
       <c r="W22" s="1" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="23" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A23" s="1" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B23" s="1">
         <v>792232100</v>
@@ -7574,7 +7685,7 @@
         <v>38</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>64</v>
@@ -7583,31 +7694,31 @@
         <v>59</v>
       </c>
       <c r="H23" s="93">
-        <v>99.204999999999998</v>
+        <v>99.314999999999998</v>
       </c>
       <c r="I23" s="93">
-        <v>99.2</v>
+        <v>99.305000000000007</v>
       </c>
       <c r="J23" s="93">
-        <v>99.21</v>
+        <v>99.31</v>
       </c>
       <c r="K23" s="93">
-        <v>99.204999999999998</v>
+        <v>99.307500000000005</v>
       </c>
       <c r="L23" s="93">
-        <v>99.06</v>
+        <v>99.24</v>
       </c>
       <c r="M23" s="93">
-        <v>99.1</v>
+        <v>98.954999999999998</v>
       </c>
       <c r="N23" s="93">
-        <v>99.275000000000006</v>
+        <v>99.34</v>
       </c>
       <c r="O23" s="93">
-        <v>99.055000000000007</v>
+        <v>98.86</v>
       </c>
       <c r="P23" s="93">
-        <v>5977</v>
+        <v>15812</v>
       </c>
       <c r="Q23" s="93"/>
       <c r="R23" s="93"/>
@@ -7615,15 +7726,15 @@
       <c r="T23" s="93"/>
       <c r="U23" s="93"/>
       <c r="V23" s="92">
-        <v>46101.448611111111</v>
+        <v>46106.640856481485</v>
       </c>
       <c r="W23" s="1" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="24" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A24" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B24" s="1">
         <v>496647057</v>
@@ -7635,7 +7746,7 @@
         <v>56</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>79</v>
@@ -7644,31 +7755,31 @@
         <v>59</v>
       </c>
       <c r="H24" s="93">
-        <v>1.1608499999999999</v>
+        <v>1.1618999999999999</v>
       </c>
       <c r="I24" s="93">
-        <v>1.1608499999999999</v>
+        <v>1.16185</v>
       </c>
       <c r="J24" s="93">
-        <v>1.1609</v>
+        <v>1.1618999999999999</v>
       </c>
       <c r="K24" s="93">
-        <v>1.1608749999999999</v>
+        <v>1.161875</v>
       </c>
       <c r="L24" s="93">
-        <v>1.1629</v>
+        <v>1.16265</v>
       </c>
       <c r="M24" s="93">
-        <v>1.1634500000000001</v>
+        <v>1.1653</v>
       </c>
       <c r="N24" s="93">
-        <v>1.1641999999999999</v>
+        <v>1.1675500000000001</v>
       </c>
       <c r="O24" s="93">
-        <v>1.1598999999999999</v>
+        <v>1.1611499999999999</v>
       </c>
       <c r="P24" s="93">
-        <v>52393</v>
+        <v>127064</v>
       </c>
       <c r="Q24" s="93"/>
       <c r="R24" s="93"/>
@@ -7676,15 +7787,15 @@
       <c r="T24" s="93"/>
       <c r="U24" s="93"/>
       <c r="V24" s="92">
-        <v>46101.448611111111</v>
+        <v>46106.640856481485</v>
       </c>
       <c r="W24" s="1" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="25" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A25" s="1" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B25" s="1">
         <v>496647091</v>
@@ -7696,7 +7807,7 @@
         <v>74</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>79</v>
@@ -7705,31 +7816,31 @@
         <v>59</v>
       </c>
       <c r="H25" s="93">
-        <v>1.3399000000000001</v>
+        <v>1.3365</v>
       </c>
       <c r="I25" s="93">
-        <v>1.3399000000000001</v>
+        <v>1.3364</v>
       </c>
       <c r="J25" s="93">
-        <v>1.3401000000000001</v>
+        <v>1.3365</v>
       </c>
       <c r="K25" s="93">
-        <v>1.34</v>
+        <v>1.3364500000000001</v>
       </c>
       <c r="L25" s="93">
-        <v>1.3414999999999999</v>
+        <v>1.3380000000000001</v>
       </c>
       <c r="M25" s="93">
-        <v>1.3431999999999999</v>
+        <v>1.3408</v>
       </c>
       <c r="N25" s="93">
-        <v>1.3440000000000001</v>
+        <v>1.3432999999999999</v>
       </c>
       <c r="O25" s="93">
-        <v>1.3394999999999999</v>
+        <v>1.3357000000000001</v>
       </c>
       <c r="P25" s="93">
-        <v>23717</v>
+        <v>61665</v>
       </c>
       <c r="Q25" s="93"/>
       <c r="R25" s="93"/>
@@ -7737,15 +7848,15 @@
       <c r="T25" s="93"/>
       <c r="U25" s="93"/>
       <c r="V25" s="92">
-        <v>46101.448611111111</v>
+        <v>46106.640856481485</v>
       </c>
       <c r="W25" s="1" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="26" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A26" s="1" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B26" s="1">
         <v>496647108</v>
@@ -7757,7 +7868,7 @@
         <v>57</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>79</v>
@@ -7766,31 +7877,31 @@
         <v>59</v>
       </c>
       <c r="H26" s="93">
-        <v>6.3495000000000001E-3</v>
+        <v>6.3274999999999998E-3</v>
       </c>
       <c r="I26" s="93">
-        <v>6.3489999999999996E-3</v>
+        <v>6.3270000000000002E-3</v>
       </c>
       <c r="J26" s="93">
-        <v>6.3499999999999997E-3</v>
+        <v>6.3274999999999998E-3</v>
       </c>
       <c r="K26" s="93">
-        <v>6.3494999999999992E-3</v>
+        <v>6.3272499999999995E-3</v>
       </c>
       <c r="L26" s="93">
-        <v>6.3879999999999996E-3</v>
+        <v>6.3350000000000004E-3</v>
       </c>
       <c r="M26" s="93">
-        <v>6.3854999999999997E-3</v>
+        <v>6.3445000000000003E-3</v>
       </c>
       <c r="N26" s="93">
-        <v>6.3879999999999996E-3</v>
+        <v>6.3505000000000002E-3</v>
       </c>
       <c r="O26" s="93">
-        <v>6.3480000000000003E-3</v>
+        <v>6.3249999999999999E-3</v>
       </c>
       <c r="P26" s="93">
-        <v>42737</v>
+        <v>76968</v>
       </c>
       <c r="Q26" s="93"/>
       <c r="R26" s="93"/>
@@ -7798,15 +7909,15 @@
       <c r="T26" s="93"/>
       <c r="U26" s="93"/>
       <c r="V26" s="92">
-        <v>46101.448611111111</v>
+        <v>46106.640856481485</v>
       </c>
       <c r="W26" s="1" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="27" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A27" s="1" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B27" s="1">
         <v>496879111</v>
@@ -7818,7 +7929,7 @@
         <v>76</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>79</v>
@@ -7827,31 +7938,31 @@
         <v>59</v>
       </c>
       <c r="H27" s="93">
-        <v>0.73170000000000002</v>
+        <v>0.72785</v>
       </c>
       <c r="I27" s="93">
-        <v>0.73170000000000002</v>
+        <v>0.72785</v>
       </c>
       <c r="J27" s="93">
-        <v>0.73175000000000001</v>
+        <v>0.72789999999999999</v>
       </c>
       <c r="K27" s="93">
-        <v>0.73172499999999996</v>
+        <v>0.72787500000000005</v>
       </c>
       <c r="L27" s="93">
-        <v>0.73134999999999994</v>
+        <v>0.7288</v>
       </c>
       <c r="M27" s="93">
-        <v>0.73055000000000003</v>
+        <v>0.72894999999999999</v>
       </c>
       <c r="N27" s="93">
-        <v>0.73199999999999998</v>
+        <v>0.72985</v>
       </c>
       <c r="O27" s="93">
-        <v>0.73035000000000005</v>
+        <v>0.72714999999999996</v>
       </c>
       <c r="P27" s="93">
-        <v>13475</v>
+        <v>41014</v>
       </c>
       <c r="Q27" s="93"/>
       <c r="R27" s="93"/>
@@ -7859,15 +7970,15 @@
       <c r="T27" s="93"/>
       <c r="U27" s="93"/>
       <c r="V27" s="92">
-        <v>46101.448611111111</v>
+        <v>46106.640856481485</v>
       </c>
       <c r="W27" s="1" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="28" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A28" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B28" s="1">
         <v>496647009</v>
@@ -7879,7 +7990,7 @@
         <v>78</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>79</v>
@@ -7888,31 +7999,31 @@
         <v>59</v>
       </c>
       <c r="H28" s="93">
-        <v>0.70709999999999995</v>
+        <v>0.69479999999999997</v>
       </c>
       <c r="I28" s="93">
-        <v>0.70709999999999995</v>
+        <v>0.69474999999999998</v>
       </c>
       <c r="J28" s="93">
-        <v>0.70714999999999995</v>
+        <v>0.69479999999999997</v>
       </c>
       <c r="K28" s="93">
-        <v>0.707125</v>
+        <v>0.69477499999999992</v>
       </c>
       <c r="L28" s="93">
-        <v>0.70655000000000001</v>
+        <v>0.69584999999999997</v>
       </c>
       <c r="M28" s="93">
-        <v>0.70760000000000001</v>
+        <v>0.69845000000000002</v>
       </c>
       <c r="N28" s="93">
-        <v>0.70889999999999997</v>
+        <v>0.6996</v>
       </c>
       <c r="O28" s="93">
-        <v>0.70650000000000002</v>
+        <v>0.69350000000000001</v>
       </c>
       <c r="P28" s="93">
-        <v>30078</v>
+        <v>77611</v>
       </c>
       <c r="Q28" s="93"/>
       <c r="R28" s="93"/>
@@ -7920,15 +8031,15 @@
       <c r="T28" s="93"/>
       <c r="U28" s="93"/>
       <c r="V28" s="92">
-        <v>46101.448611111111</v>
+        <v>46106.640856481485</v>
       </c>
       <c r="W28" s="1" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="29" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A29" s="1" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B29" s="1">
         <v>815824224</v>
@@ -7940,7 +8051,7 @@
         <v>46</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>82</v>
@@ -7949,31 +8060,31 @@
         <v>59</v>
       </c>
       <c r="H29" s="93">
-        <v>114.21875</v>
+        <v>113.375</v>
       </c>
       <c r="I29" s="93">
-        <v>114.1875</v>
+        <v>113.375</v>
       </c>
       <c r="J29" s="93">
-        <v>114.21875</v>
+        <v>113.40625</v>
       </c>
       <c r="K29" s="93">
-        <v>114.203125</v>
+        <v>113.390625</v>
       </c>
       <c r="L29" s="93">
-        <v>114.375</v>
+        <v>112.625</v>
       </c>
       <c r="M29" s="93">
-        <v>114.65625</v>
+        <v>113</v>
       </c>
       <c r="N29" s="93">
-        <v>114.75</v>
+        <v>113.78125</v>
       </c>
       <c r="O29" s="93">
-        <v>114.15625</v>
+        <v>112.96875</v>
       </c>
       <c r="P29" s="93">
-        <v>46792</v>
+        <v>281236</v>
       </c>
       <c r="Q29" s="93"/>
       <c r="R29" s="93"/>
@@ -7981,15 +8092,15 @@
       <c r="T29" s="93"/>
       <c r="U29" s="93"/>
       <c r="V29" s="92">
-        <v>46101.448611111111</v>
+        <v>46106.640856481485</v>
       </c>
       <c r="W29" s="1" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="30" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A30" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B30" s="1">
         <v>815824229</v>
@@ -8001,7 +8112,7 @@
         <v>67</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>82</v>
@@ -8010,31 +8121,31 @@
         <v>59</v>
       </c>
       <c r="H30" s="93">
-        <v>111.125</v>
+        <v>110.8125</v>
       </c>
       <c r="I30" s="93">
-        <v>111.125</v>
+        <v>110.8125</v>
       </c>
       <c r="J30" s="93">
-        <v>111.140625</v>
+        <v>110.828125</v>
       </c>
       <c r="K30" s="93">
-        <v>111.1328125</v>
+        <v>110.8203125</v>
       </c>
       <c r="L30" s="93">
-        <v>111.21875</v>
+        <v>110.421875</v>
       </c>
       <c r="M30" s="93">
-        <v>111.484375</v>
+        <v>110.671875</v>
       </c>
       <c r="N30" s="93">
-        <v>111.53125</v>
+        <v>111.046875</v>
       </c>
       <c r="O30" s="93">
-        <v>111.109375</v>
+        <v>110.625</v>
       </c>
       <c r="P30" s="93">
-        <v>293674</v>
+        <v>1312701</v>
       </c>
       <c r="Q30" s="93"/>
       <c r="R30" s="93"/>
@@ -8042,10 +8153,10 @@
       <c r="T30" s="93"/>
       <c r="U30" s="93"/>
       <c r="V30" s="92">
-        <v>46101.448611111111</v>
+        <v>46106.640856481485</v>
       </c>
       <c r="W30" s="1" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="31" spans="1:23" x14ac:dyDescent="0.4">
@@ -8062,7 +8173,7 @@
         <v>69</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>80</v>
@@ -8071,31 +8182,31 @@
         <v>56</v>
       </c>
       <c r="H31" s="93">
-        <v>125.74</v>
+        <v>125.87</v>
       </c>
       <c r="I31" s="93">
-        <v>125.73</v>
+        <v>125.87</v>
       </c>
       <c r="J31" s="93">
-        <v>125.74</v>
+        <v>125.88</v>
       </c>
       <c r="K31" s="93">
-        <v>125.735</v>
+        <v>125.875</v>
       </c>
       <c r="L31" s="93">
-        <v>125.97</v>
+        <v>125.36</v>
       </c>
       <c r="M31" s="93">
-        <v>126.16</v>
+        <v>125.83</v>
       </c>
       <c r="N31" s="93">
-        <v>126.27</v>
+        <v>126.11</v>
       </c>
       <c r="O31" s="93">
-        <v>125.74</v>
+        <v>125.56</v>
       </c>
       <c r="P31" s="93">
-        <v>291074</v>
+        <v>1053010</v>
       </c>
       <c r="Q31" s="93"/>
       <c r="R31" s="93"/>
@@ -8103,10 +8214,10 @@
       <c r="T31" s="93"/>
       <c r="U31" s="93"/>
       <c r="V31" s="92">
-        <v>46101.448611111111</v>
+        <v>46106.640856481485</v>
       </c>
       <c r="W31" s="1" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="32" spans="1:23" x14ac:dyDescent="0.4">
@@ -8123,7 +8234,7 @@
         <v>71</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>80</v>
@@ -8132,31 +8243,31 @@
         <v>56</v>
       </c>
       <c r="H32" s="93">
-        <v>109.98</v>
+        <v>110.96</v>
       </c>
       <c r="I32" s="93">
-        <v>109.98</v>
+        <v>110.96</v>
       </c>
       <c r="J32" s="93">
-        <v>110</v>
+        <v>110.98</v>
       </c>
       <c r="K32" s="93">
-        <v>109.99000000000001</v>
+        <v>110.97</v>
       </c>
       <c r="L32" s="93">
-        <v>110.24</v>
+        <v>109.8</v>
       </c>
       <c r="M32" s="93">
-        <v>110.5</v>
+        <v>110.28</v>
       </c>
       <c r="N32" s="93">
-        <v>110.66</v>
+        <v>111.28</v>
       </c>
       <c r="O32" s="93">
-        <v>109.98</v>
+        <v>109.96</v>
       </c>
       <c r="P32" s="93">
-        <v>41755</v>
+        <v>162914</v>
       </c>
       <c r="Q32" s="93"/>
       <c r="R32" s="93"/>
@@ -8164,10 +8275,10 @@
       <c r="T32" s="93"/>
       <c r="U32" s="93"/>
       <c r="V32" s="92">
-        <v>46101.448611111111</v>
+        <v>46106.640856481485</v>
       </c>
       <c r="W32" s="1" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="33" spans="1:23" x14ac:dyDescent="0.4">
@@ -8184,7 +8295,7 @@
         <v>47</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>80</v>
@@ -8193,31 +8304,31 @@
         <v>56</v>
       </c>
       <c r="H33" s="93">
-        <v>117.06</v>
+        <v>116.93</v>
       </c>
       <c r="I33" s="93">
-        <v>117.05</v>
+        <v>116.93</v>
       </c>
       <c r="J33" s="93">
-        <v>117.06</v>
+        <v>116.94</v>
       </c>
       <c r="K33" s="93">
-        <v>117.05500000000001</v>
+        <v>116.935</v>
       </c>
       <c r="L33" s="93">
-        <v>117.37</v>
+        <v>116.04</v>
       </c>
       <c r="M33" s="93">
-        <v>117.46</v>
+        <v>116.61</v>
       </c>
       <c r="N33" s="93">
-        <v>117.82</v>
+        <v>117.16</v>
       </c>
       <c r="O33" s="93">
-        <v>117.07</v>
+        <v>116.36</v>
       </c>
       <c r="P33" s="93">
-        <v>99090</v>
+        <v>402744</v>
       </c>
       <c r="Q33" s="93"/>
       <c r="R33" s="93"/>
@@ -8225,15 +8336,15 @@
       <c r="T33" s="93"/>
       <c r="U33" s="93"/>
       <c r="V33" s="92">
-        <v>46101.448611111111</v>
+        <v>46106.640856481485</v>
       </c>
       <c r="W33" s="1" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="34" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A34" s="1" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="B34" s="1">
         <v>479624278</v>
@@ -8245,7 +8356,7 @@
         <v>44</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>191</v>
@@ -8254,29 +8365,29 @@
         <v>59</v>
       </c>
       <c r="H34" s="93">
-        <v>70571.25</v>
+        <v>71418.5</v>
       </c>
       <c r="I34" s="93">
-        <v>70571.25</v>
+        <v>71418.5</v>
       </c>
       <c r="J34" s="93">
-        <v>70571.5</v>
+        <v>71418.75</v>
       </c>
       <c r="K34" s="93">
-        <v>70571.375</v>
+        <v>71418.625</v>
       </c>
       <c r="L34" s="93">
-        <v>70268.25</v>
+        <v>69310.5</v>
       </c>
       <c r="M34" s="93"/>
       <c r="N34" s="93">
-        <v>71605.5</v>
+        <v>72360</v>
       </c>
       <c r="O34" s="93">
         <v>68655</v>
       </c>
       <c r="P34" s="93">
-        <v>100.22978931999999</v>
+        <v>154.05609971999999</v>
       </c>
       <c r="Q34" s="93"/>
       <c r="R34" s="93"/>
@@ -8284,10 +8395,10 @@
       <c r="T34" s="93"/>
       <c r="U34" s="93"/>
       <c r="V34" s="92">
-        <v>46101.448611111111</v>
+        <v>46106.640856481485</v>
       </c>
       <c r="W34" s="1" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="35" spans="1:23" x14ac:dyDescent="0.4">
@@ -8304,7 +8415,7 @@
         <v>45</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>191</v>
@@ -8313,29 +8424,29 @@
         <v>59</v>
       </c>
       <c r="H35" s="93">
-        <v>2145.8000000000002</v>
+        <v>2181.9499999999998</v>
       </c>
       <c r="I35" s="93">
-        <v>2144.1</v>
+        <v>2182.0500000000002</v>
       </c>
       <c r="J35" s="93">
-        <v>2144.15</v>
+        <v>2182.1</v>
       </c>
       <c r="K35" s="93">
-        <v>2144.125</v>
+        <v>2182.0749999999998</v>
       </c>
       <c r="L35" s="93">
-        <v>2141.6999999999998</v>
+        <v>2115.5</v>
       </c>
       <c r="M35" s="93"/>
       <c r="N35" s="93">
-        <v>2232.75</v>
+        <v>2198.6</v>
       </c>
       <c r="O35" s="93">
-        <v>2094.6</v>
+        <v>2103</v>
       </c>
       <c r="P35" s="93">
-        <v>1166.4607209200001</v>
+        <v>2143.2549456800002</v>
       </c>
       <c r="Q35" s="93"/>
       <c r="R35" s="93"/>
@@ -8343,27 +8454,27 @@
       <c r="T35" s="93"/>
       <c r="U35" s="93"/>
       <c r="V35" s="92">
-        <v>46101.448611111111</v>
+        <v>46106.640856481485</v>
       </c>
       <c r="W35" s="1" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="36" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A36" s="1" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="B36" s="1">
         <v>297507399</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="D36" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>60</v>
@@ -8372,67 +8483,67 @@
         <v>59</v>
       </c>
       <c r="H36" s="93">
-        <v>3.21</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="I36" s="93">
-        <v>2.93</v>
+        <v>3.86</v>
       </c>
       <c r="J36" s="93">
-        <v>3.01</v>
+        <v>3.91</v>
       </c>
       <c r="K36" s="93">
-        <v>2.9699999999999998</v>
+        <v>3.8849999999999998</v>
       </c>
       <c r="L36" s="93">
-        <v>2.91</v>
+        <v>3.23</v>
       </c>
       <c r="M36" s="93"/>
       <c r="N36" s="93">
-        <v>3.21</v>
+        <v>4.3899999999999997</v>
       </c>
       <c r="O36" s="93">
-        <v>3.21</v>
+        <v>3.9</v>
       </c>
       <c r="P36" s="93">
-        <v>39</v>
+        <v>363</v>
       </c>
       <c r="Q36" s="93">
-        <v>0.71771421572689076</v>
+        <v>0.70559420108447768</v>
       </c>
       <c r="R36" s="93">
-        <v>-0.18128491103438815</v>
+        <v>-0.2532412287832147</v>
       </c>
       <c r="S36" s="93">
-        <v>1.0173391195764769E-2</v>
+        <v>1.4208315346921152E-2</v>
       </c>
       <c r="T36" s="93">
-        <v>0.10013433884153189</v>
+        <v>0.10370583147492995</v>
       </c>
       <c r="U36" s="93">
-        <v>-6.4910269707011192E-2</v>
+        <v>-7.2902923411306997E-2</v>
       </c>
       <c r="V36" s="92">
-        <v>46101.448611111111</v>
+        <v>46106.640856481485</v>
       </c>
       <c r="W36" s="1" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="37" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A37" s="1" t="s">
-        <v>319</v>
+        <v>311</v>
       </c>
       <c r="B37" s="1">
         <v>297509218</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="D37" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>319</v>
+        <v>311</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>60</v>
@@ -8441,46 +8552,50 @@
         <v>59</v>
       </c>
       <c r="H37" s="93">
-        <v>-1</v>
+        <v>0.47</v>
       </c>
       <c r="I37" s="93">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="J37" s="93">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="K37" s="93">
-        <v>0.43000000000000005</v>
+        <v>0.45999999999999996</v>
       </c>
       <c r="L37" s="93">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="M37" s="93"/>
-      <c r="N37" s="93"/>
-      <c r="O37" s="93"/>
+      <c r="N37" s="93">
+        <v>0.47</v>
+      </c>
+      <c r="O37" s="93">
+        <v>0.47</v>
+      </c>
       <c r="P37" s="93">
-        <v>31</v>
+        <v>204</v>
       </c>
       <c r="Q37" s="93">
-        <v>0.81233159477945005</v>
+        <v>0.76564128313294511</v>
       </c>
       <c r="R37" s="93">
-        <v>-3.4256763347845533E-2</v>
+        <v>-4.1588926637533941E-2</v>
       </c>
       <c r="S37" s="93">
-        <v>2.5847785584919365E-3</v>
+        <v>3.6458176819162075E-3</v>
       </c>
       <c r="T37" s="93">
-        <v>2.5575313853269277E-2</v>
+        <v>3.2476826947874682E-2</v>
       </c>
       <c r="U37" s="93">
-        <v>-1.8803767424097062E-2</v>
+        <v>-2.4863250273228388E-2</v>
       </c>
       <c r="V37" s="92">
-        <v>46101.448611111111</v>
+        <v>46106.640856481485</v>
       </c>
       <c r="W37" s="1" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="38" spans="1:23" x14ac:dyDescent="0.4">
@@ -8636,7 +8751,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C571DE7A-BF08-4200-BB11-61B452324713}">
-  <dimension ref="A1:C39"/>
+  <dimension ref="A1:C52"/>
   <sheetFormatPr defaultRowHeight="13.15" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="22" style="81" customWidth="1"/>
@@ -8657,422 +8772,169 @@
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A2" s="87">
-        <v>46086.543078703704</v>
-      </c>
-      <c r="B2" s="84" t="s">
-        <v>299</v>
-      </c>
-      <c r="C2" s="84" t="s">
-        <v>300</v>
-      </c>
+      <c r="A2" s="87"/>
+      <c r="B2" s="84"/>
+      <c r="C2" s="84"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A3" s="87">
-        <v>46086.543090277781</v>
-      </c>
-      <c r="B3" s="84" t="s">
-        <v>299</v>
-      </c>
-      <c r="C3" s="84" t="s">
-        <v>301</v>
-      </c>
+      <c r="A3" s="87"/>
+      <c r="B3" s="84"/>
+      <c r="C3" s="84"/>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A4" s="87">
-        <v>46086.54310185185</v>
-      </c>
-      <c r="B4" s="84" t="s">
-        <v>299</v>
-      </c>
-      <c r="C4" s="84" t="s">
-        <v>302</v>
-      </c>
+      <c r="A4" s="87"/>
+      <c r="B4" s="84"/>
+      <c r="C4" s="84"/>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A5" s="85">
-        <v>46090.383530092593</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>300</v>
-      </c>
+      <c r="A5" s="85"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A6" s="85">
-        <v>46090.38354166667</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>301</v>
-      </c>
+      <c r="A6" s="85"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A7" s="85">
-        <v>46090.38354166667</v>
-      </c>
-      <c r="B7" s="81" t="s">
-        <v>299</v>
-      </c>
-      <c r="C7" s="81" t="s">
-        <v>302</v>
-      </c>
+      <c r="A7" s="85"/>
+      <c r="B7" s="81"/>
+      <c r="C7" s="81"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A8" s="85">
-        <v>46090.869409722225</v>
-      </c>
-      <c r="B8" s="81" t="s">
-        <v>299</v>
-      </c>
-      <c r="C8" s="81" t="s">
-        <v>300</v>
-      </c>
+      <c r="A8" s="85"/>
+      <c r="B8" s="81"/>
+      <c r="C8" s="81"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A9" s="85">
-        <v>46090.869409722225</v>
-      </c>
-      <c r="B9" s="81" t="s">
-        <v>299</v>
-      </c>
-      <c r="C9" s="81" t="s">
-        <v>301</v>
-      </c>
+      <c r="A9" s="85"/>
+      <c r="B9" s="81"/>
+      <c r="C9" s="81"/>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A10" s="85">
-        <v>46090.869409722225</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>302</v>
-      </c>
+      <c r="A10" s="85"/>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A11" s="85">
-        <v>46092.415810185186</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>300</v>
-      </c>
+      <c r="A11" s="85"/>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A12" s="85">
-        <v>46092.415821759256</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>301</v>
-      </c>
+      <c r="A12" s="85"/>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A13" s="85">
-        <v>46092.415821759256</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>302</v>
-      </c>
+      <c r="A13" s="85"/>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A14" s="85">
-        <v>46095.370937500003</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>300</v>
-      </c>
+      <c r="A14" s="85"/>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A15" s="85">
-        <v>46095.370949074073</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>301</v>
-      </c>
+      <c r="A15" s="85"/>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A16" s="85">
-        <v>46095.370949074073</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A17" s="85">
-        <v>46095.371539351851</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A18" s="85">
-        <v>46095.371539351851</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A19" s="85">
-        <v>46095.371539351851</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A20" s="85">
-        <v>46097.672754629632</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A21" s="85">
-        <v>46097.672766203701</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A22" s="85">
-        <v>46097.672766203701</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A23" s="85">
-        <v>46098.335706018515</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A24" s="85">
-        <v>46098.335729166669</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A25" s="85">
-        <v>46098.335740740738</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A26" s="85">
-        <v>46098.336087962962</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>323</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A27" s="85">
-        <v>46098.336111111108</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A28" s="85">
-        <v>46099.474259259259</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A29" s="85">
-        <v>46099.474270833336</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A30" s="85">
-        <v>46099.474270833336</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A31" s="85">
-        <v>46100.744826388887</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A32" s="85">
-        <v>46100.744837962964</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A33" s="85">
-        <v>46100.744837962964</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A34" s="85">
-        <v>46100.756168981483</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A35" s="85">
-        <v>46100.756168981483</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A36" s="85">
-        <v>46100.756168981483</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A37" s="85">
-        <v>46101.447233796294</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A38" s="85">
-        <v>46101.447245370371</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A39" s="85">
-        <v>46101.447245370371</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>316</v>
-      </c>
+      <c r="A16" s="85"/>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A17" s="85"/>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A18" s="85"/>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A19" s="85"/>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A20" s="85"/>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A21" s="85"/>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A22" s="85"/>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A23" s="85"/>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A24" s="85"/>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A25" s="85"/>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A26" s="85"/>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A27" s="85"/>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A28" s="85"/>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A29" s="85"/>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A30" s="85"/>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A31" s="85"/>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A32" s="85"/>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A33" s="85"/>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A34" s="85"/>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A35" s="85"/>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A36" s="85"/>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A37" s="85"/>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A38" s="85"/>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A39" s="85"/>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A40" s="85"/>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A41" s="85"/>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A42" s="85"/>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A43" s="85"/>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A44" s="85"/>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A45" s="85"/>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A46" s="85"/>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A47" s="85"/>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A48" s="85"/>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A49" s="85"/>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A50" s="85"/>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A51" s="85"/>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A52" s="85"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9138,11 +9000,11 @@
       <c r="E4" s="10"/>
       <c r="F4" s="10"/>
       <c r="G4" s="15">
-        <v>12808</v>
+        <v>12920</v>
       </c>
       <c r="H4" s="6">
         <f>-G4</f>
-        <v>-12808</v>
+        <v>-12920</v>
       </c>
     </row>
     <row r="5" spans="2:8" x14ac:dyDescent="0.4">
@@ -9242,11 +9104,11 @@
         <v>10000</v>
       </c>
       <c r="F12" s="54">
-        <v>98.88</v>
+        <v>99</v>
       </c>
       <c r="G12" s="65">
         <f>(F12-D12)*E12</f>
-        <v>99.999999999909051</v>
+        <v>1299.9999999999545</v>
       </c>
       <c r="H12" s="65">
         <f>(100-D12)*E12</f>
@@ -9263,11 +9125,11 @@
       <c r="F13" s="10"/>
       <c r="G13" s="6">
         <f>SUM(G3:G12)</f>
-        <v>1712.9499999999098</v>
+        <v>3024.9499999999553</v>
       </c>
       <c r="H13" s="6">
         <f>SUM(H3:H12)</f>
-        <v>34687.049999999952</v>
+        <v>34575.049999999952</v>
       </c>
     </row>
   </sheetData>
@@ -9449,11 +9311,11 @@
       <c r="H5" s="67"/>
       <c r="I5" s="70">
         <f>Blotter!C$4-SUM(NAV!I$4:I4)</f>
-        <v>2992.0606320098982</v>
+        <v>3496.5906320099402</v>
       </c>
       <c r="J5" s="70">
         <f t="shared" si="2"/>
-        <v>1002992.0606320099</v>
+        <v>1003496.5906320099</v>
       </c>
       <c r="K5" s="70">
         <f t="shared" si="3"/>
@@ -9461,19 +9323,19 @@
       </c>
       <c r="L5" s="71">
         <f t="shared" si="4"/>
-        <v>1002.9920606320098</v>
+        <v>1003.4965906320099</v>
       </c>
       <c r="M5" s="72">
         <f t="shared" si="5"/>
-        <v>2.9920606320097409E-3</v>
+        <v>3.4965906320099105E-3</v>
       </c>
       <c r="N5" s="73">
         <f t="shared" ref="N5" si="6">L5/L4-1</f>
-        <v>2.9920606320097409E-3</v>
+        <v>3.4965906320099105E-3</v>
       </c>
       <c r="O5" s="75">
         <f>STDEVP(N$4:N5)*SQRT(12)</f>
-        <v>5.1824010339675168E-3</v>
+        <v>6.0562726279105358E-3</v>
       </c>
     </row>
     <row r="6" spans="2:18" ht="14.25" x14ac:dyDescent="0.4">
@@ -9933,13 +9795,13 @@
         <v>1</v>
       </c>
       <c r="V4" s="1" t="s">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="W4" s="1" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="X4" s="1" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
     </row>
     <row r="5" spans="2:28" x14ac:dyDescent="0.4">
@@ -9953,7 +9815,7 @@
       </c>
       <c r="D5" s="6">
         <f t="array" ref="D5">SUM((Blotter!C$19:C$1013=C5)*(Blotter!N$19:N$1013)*1)</f>
-        <v>2871.0899999999965</v>
+        <v>-2978.9100000000035</v>
       </c>
       <c r="E5" s="6">
         <f t="array" ref="E5">SUM((Blotter!B$19:C$1013=C5)*(Blotter!R$19:R$1013)*1)</f>
@@ -9961,7 +9823,7 @@
       </c>
       <c r="F5" s="30">
         <f t="shared" ref="F5" si="1">IF(ISNUMBER(D5/E5),D5/E5,0)</f>
-        <v>0.31900999999999963</v>
+        <v>-0.3309900000000004</v>
       </c>
       <c r="G5" s="36" t="str">
         <f t="array" ref="G5">IF(SUM((Blotter!C$19:C$1013=PLB!C5)*(Blotter!M$19:M$1013))=0,"C","O")</f>
@@ -9969,20 +9831,20 @@
       </c>
       <c r="H5" s="16">
         <f>J4+D5</f>
-        <v>1003393.33063201</v>
+        <v>997543.33063201001</v>
       </c>
       <c r="I5" s="16"/>
       <c r="J5" s="16">
         <f>H5+I5</f>
-        <v>1003393.33063201</v>
+        <v>997543.33063201001</v>
       </c>
       <c r="K5" s="3">
         <f>H5/J4-1</f>
-        <v>2.8695913827825326E-3</v>
+        <v>-2.9773551041887281E-3</v>
       </c>
       <c r="L5" s="3">
         <f>(1+K5)*(1+L4)-1</f>
-        <v>3.3933306320099721E-3</v>
+        <v>-2.4566693679900498E-3</v>
       </c>
       <c r="M5" s="6">
         <f>O4-IF(G5="O",O4*1%,-D5)</f>
@@ -10017,13 +9879,13 @@
         <v>2</v>
       </c>
       <c r="V5" s="1" t="s">
-        <v>321</v>
+        <v>313</v>
       </c>
       <c r="W5" s="1" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="X5" s="1" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
     </row>
     <row r="6" spans="2:28" x14ac:dyDescent="0.4">
@@ -10037,7 +9899,7 @@
       </c>
       <c r="D6" s="6">
         <f t="array" ref="D6">SUM((Blotter!C$19:C$1013=C6)*(Blotter!N$19:N$1013)*1)</f>
-        <v>-2114.2200000000025</v>
+        <v>1305.7799999999957</v>
       </c>
       <c r="E6" s="6">
         <f t="array" ref="E6">SUM((Blotter!B$19:C$1013=C6)*(Blotter!R$19:R$1013)*1)</f>
@@ -10045,7 +9907,7 @@
       </c>
       <c r="F6" s="30">
         <f t="shared" ref="F6" si="4">IF(ISNUMBER(D6/E6),D6/E6,0)</f>
-        <v>-0.22023125000000027</v>
+        <v>0.13601874999999955</v>
       </c>
       <c r="G6" s="36" t="str">
         <f t="array" ref="G6">IF(SUM((Blotter!C$19:C$1013=PLB!C6)*(Blotter!M$19:M$1013))=0,"C","O")</f>
@@ -10053,20 +9915,20 @@
       </c>
       <c r="H6" s="16">
         <f>J5+D6</f>
-        <v>1001279.11063201</v>
+        <v>998849.11063201004</v>
       </c>
       <c r="I6" s="16"/>
       <c r="J6" s="16">
         <f>H6+I6</f>
-        <v>1001279.11063201</v>
+        <v>998849.11063201004</v>
       </c>
       <c r="K6" s="3">
         <f>H6/J5-1</f>
-        <v>-2.1070700147750587E-3</v>
+        <v>1.3089957698104726E-3</v>
       </c>
       <c r="L6" s="3">
         <f>(1+K6)*(1+L5)-1</f>
-        <v>1.2791106320100276E-3</v>
+        <v>-1.1508893679901266E-3</v>
       </c>
       <c r="M6" s="6">
         <f>O5-IF(G6="O",O5*1%,-D6)</f>
@@ -10101,30 +9963,98 @@
         <v>3</v>
       </c>
       <c r="V6" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="W6" s="49" t="s">
+        <v>321</v>
+      </c>
+      <c r="X6" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="W6" s="49"/>
     </row>
     <row r="7" spans="2:28" x14ac:dyDescent="0.4">
-      <c r="B7" s="40"/>
-      <c r="C7" s="5"/>
-      <c r="D7" s="6"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="30"/>
-      <c r="G7" s="36"/>
-      <c r="H7" s="16"/>
+      <c r="B7" s="40">
+        <f>B6+7</f>
+        <v>46109</v>
+      </c>
+      <c r="C7" s="5">
+        <f>C6+1</f>
+        <v>4</v>
+      </c>
+      <c r="D7" s="6">
+        <f t="array" ref="D7">SUM((Blotter!C$19:C$1013=C7)*(Blotter!N$19:N$1013)*1)</f>
+        <v>1622.5299999999988</v>
+      </c>
+      <c r="E7" s="6">
+        <f t="array" ref="E7">SUM((Blotter!B$19:C$1013=C7)*(Blotter!R$19:R$1013)*1)</f>
+        <v>7192.5</v>
+      </c>
+      <c r="F7" s="30">
+        <f t="shared" ref="F7" si="7">IF(ISNUMBER(D7/E7),D7/E7,0)</f>
+        <v>0.2255863746958636</v>
+      </c>
+      <c r="G7" s="36" t="str">
+        <f t="array" ref="G7">IF(SUM((Blotter!C$19:C$1013=PLB!C7)*(Blotter!M$19:M$1013))=0,"C","O")</f>
+        <v>O</v>
+      </c>
+      <c r="H7" s="16">
+        <f>J6+D7</f>
+        <v>1000471.6406320101</v>
+      </c>
       <c r="I7" s="16"/>
-      <c r="J7" s="16"/>
-      <c r="K7" s="3"/>
-      <c r="L7" s="3"/>
-      <c r="M7" s="6"/>
-      <c r="N7" s="16"/>
-      <c r="O7" s="6"/>
-      <c r="P7" s="3"/>
-      <c r="Q7" s="3"/>
-      <c r="R7" s="3"/>
-      <c r="T7" s="40"/>
-      <c r="U7" s="5"/>
+      <c r="J7" s="16">
+        <f>H7+I7</f>
+        <v>1000471.6406320101</v>
+      </c>
+      <c r="K7" s="3">
+        <f>H7/J6-1</f>
+        <v>1.6243995041187453E-3</v>
+      </c>
+      <c r="L7" s="3">
+        <f>(1+K7)*(1+L6)-1</f>
+        <v>4.7164063200999529E-4</v>
+      </c>
+      <c r="M7" s="6">
+        <f>O6-IF(G7="O",O6*1%,-D7)</f>
+        <v>970805.72956299875</v>
+      </c>
+      <c r="N7" s="16">
+        <f>I7</f>
+        <v>0</v>
+      </c>
+      <c r="O7" s="6">
+        <f>M7+N7</f>
+        <v>970805.72956299875</v>
+      </c>
+      <c r="P7" s="3">
+        <f>M7/O6-1</f>
+        <v>-1.0000000000000009E-2</v>
+      </c>
+      <c r="Q7" s="3">
+        <f>(1+P7)*(1+Q6)-1</f>
+        <v>-2.919427043700118E-2</v>
+      </c>
+      <c r="R7" s="3">
+        <f>(1-1%)*(1+R6)-1</f>
+        <v>-3.9403990000000055E-2</v>
+      </c>
+      <c r="T7" s="40">
+        <f t="shared" ref="T7" si="8">B7</f>
+        <v>46109</v>
+      </c>
+      <c r="U7" s="5">
+        <f t="shared" ref="U7" si="9">C7</f>
+        <v>4</v>
+      </c>
+      <c r="V7" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="W7" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="X7" s="1" t="s">
+        <v>325</v>
+      </c>
     </row>
     <row r="8" spans="2:28" x14ac:dyDescent="0.4">
       <c r="B8" s="40"/>
@@ -11272,7 +11202,7 @@
   </cols>
   <sheetData/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" scale="71" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>
@@ -11630,7 +11560,7 @@
         <v>25000</v>
       </c>
       <c r="D10" s="19">
-        <v>7.0800000000000002E-2</v>
+        <v>0.1918</v>
       </c>
       <c r="E10" s="20">
         <f t="shared" si="1"/>
@@ -11646,22 +11576,22 @@
       </c>
       <c r="H10" s="23">
         <f t="shared" si="0"/>
-        <v>3.766478342749529</v>
+        <v>1.3903371567605145</v>
       </c>
       <c r="I10" s="61">
         <f t="shared" si="4"/>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J10" s="18">
         <v>4.03</v>
       </c>
       <c r="K10" s="3">
         <f>J10*H10*C10/$N$3</f>
-        <v>0.37947269303201503</v>
+        <v>0.14007646854362182</v>
       </c>
       <c r="L10" s="3">
         <f>J10*I10*C10/$N$3</f>
-        <v>0.50375000000000003</v>
+        <v>0.20150000000000001</v>
       </c>
     </row>
     <row r="11" spans="2:18" x14ac:dyDescent="0.4">
@@ -12648,7 +12578,7 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>59</v>
@@ -12657,10 +12587,10 @@
         <v>58</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>306</v>
+        <v>299</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>64</v>
@@ -12724,7 +12654,7 @@
     </row>
     <row r="3" spans="1:31" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>59</v>
@@ -12733,10 +12663,10 @@
         <v>58</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>306</v>
+        <v>299</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>64</v>
@@ -12797,22 +12727,22 @@
     </row>
     <row r="4" spans="1:31" x14ac:dyDescent="0.4">
       <c r="A4" s="1" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>59</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>307</v>
+        <v>300</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="H4" s="1">
         <v>1</v>
@@ -13910,7 +13840,7 @@
         <v>46087</v>
       </c>
       <c r="M21" s="1" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
       <c r="N21" s="1">
         <v>-3</v>
@@ -13974,7 +13904,7 @@
         <v>46087</v>
       </c>
       <c r="M22" s="1" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
       <c r="N22" s="1">
         <v>-5.4977520200000001</v>
@@ -14038,7 +13968,7 @@
         <v>46087</v>
       </c>
       <c r="M23" s="1" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
       <c r="N23" s="1">
         <v>-5.5477520199999999</v>
@@ -14102,7 +14032,7 @@
         <v>46087</v>
       </c>
       <c r="M24" s="1" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
       <c r="N24" s="1">
         <v>-5.7895520200000004</v>
@@ -14166,7 +14096,7 @@
         <v>46087</v>
       </c>
       <c r="M25" s="1" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
       <c r="N25" s="1">
         <v>-0.05</v>
@@ -14230,7 +14160,7 @@
         <v>46087</v>
       </c>
       <c r="M26" s="1" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
       <c r="N26" s="1">
         <v>-0.2918</v>
@@ -14294,7 +14224,7 @@
         <v>46087</v>
       </c>
       <c r="M27" s="1" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
       <c r="N27" s="1">
         <v>-5.7895520200000004</v>
@@ -14358,7 +14288,7 @@
         <v>46087</v>
       </c>
       <c r="M28" s="1" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
       <c r="N28" s="1">
         <v>-0.24179999999999999</v>
@@ -14422,7 +14352,7 @@
         <v>46087</v>
       </c>
       <c r="M29" s="1" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
       <c r="N29" s="1">
         <v>-0.24179999999999999</v>
@@ -14486,7 +14416,7 @@
         <v>46087</v>
       </c>
       <c r="M30" s="1" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
       <c r="N30" s="1">
         <v>-5.9996570199999999</v>
@@ -14550,7 +14480,7 @@
         <v>46087</v>
       </c>
       <c r="M31" s="1" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
       <c r="N31" s="1">
         <v>-2.4973153799999999</v>
@@ -14614,7 +14544,7 @@
         <v>46087</v>
       </c>
       <c r="M32" s="1" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
       <c r="N32" s="1">
         <v>-1.0847240199999999</v>
@@ -14678,7 +14608,7 @@
         <v>46087</v>
       </c>
       <c r="M33" s="1" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
       <c r="N33" s="1">
         <v>-0.21252689</v>
@@ -14742,7 +14672,7 @@
         <v>46087</v>
       </c>
       <c r="M34" s="1" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
       <c r="N34" s="1">
         <v>-2.2592068799999998</v>
@@ -14803,7 +14733,7 @@
         <v>46087</v>
       </c>
       <c r="M35" s="1" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
       <c r="N35" s="1">
         <v>-1.96740688</v>
@@ -14864,7 +14794,7 @@
         <v>46087</v>
       </c>
       <c r="M36" s="1" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
       <c r="N36" s="1">
         <v>-4.0489291700000001</v>
@@ -14925,7 +14855,7 @@
         <v>46087</v>
       </c>
       <c r="M37" s="1" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
       <c r="N37" s="1">
         <v>-3.5134851600000001</v>
@@ -14986,7 +14916,7 @@
         <v>46087</v>
       </c>
       <c r="M38" s="1" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
       <c r="N38" s="1">
         <v>-1.45325536</v>
@@ -15047,7 +14977,7 @@
         <v>46087</v>
       </c>
       <c r="M39" s="1" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
       <c r="N39" s="1">
         <v>-0.51348516</v>
@@ -15087,25 +15017,25 @@
     </row>
     <row r="40" spans="1:31" x14ac:dyDescent="0.4">
       <c r="A40" s="1" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>59</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>319</v>
+        <v>311</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>326</v>
+        <v>315</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>60</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>327</v>
+        <v>316</v>
       </c>
       <c r="H40" s="1">
         <v>1000</v>
@@ -15117,13 +15047,13 @@
         <v>46156</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="L40" s="44">
         <v>46097</v>
       </c>
       <c r="M40" s="1" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
       <c r="N40" s="1">
         <v>-3</v>
@@ -15163,25 +15093,25 @@
     </row>
     <row r="41" spans="1:31" x14ac:dyDescent="0.4">
       <c r="A41" s="1" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>59</v>
       </c>
       <c r="C41" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="E41" s="1" t="s">
         <v>317</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="E41" s="1" t="s">
-        <v>328</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>60</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>327</v>
+        <v>316</v>
       </c>
       <c r="H41" s="1">
         <v>1000</v>
@@ -15193,7 +15123,7 @@
         <v>46156</v>
       </c>
       <c r="K41" s="1" t="s">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="L41" s="44">
         <v>46097</v>
@@ -15238,11 +15168,74 @@
       </c>
     </row>
     <row r="42" spans="1:31" x14ac:dyDescent="0.4">
-      <c r="T42" s="43"/>
-      <c r="U42" s="42"/>
-      <c r="V42" s="42"/>
-      <c r="W42" s="42"/>
-      <c r="X42" s="42"/>
+      <c r="A42" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H42" s="1">
+        <v>25000</v>
+      </c>
+      <c r="J42" s="44">
+        <v>46169</v>
+      </c>
+      <c r="L42" s="44">
+        <v>46104</v>
+      </c>
+      <c r="M42" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="N42" s="1">
+        <v>1</v>
+      </c>
+      <c r="O42" s="1">
+        <v>5.47</v>
+      </c>
+      <c r="P42" s="1">
+        <v>136750</v>
+      </c>
+      <c r="Q42" s="1">
+        <v>-2.4700000000000002</v>
+      </c>
+      <c r="R42" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="T42" s="43">
+        <f>IF(ISNUMBER(VLOOKUP(U42,Blotter!B:C,2,0)),VLOOKUP(U42,Blotter!B:C,2,0),"")</f>
+        <v>4</v>
+      </c>
+      <c r="U42" s="42" t="str">
+        <f t="shared" ref="U42" si="20">D42</f>
+        <v>HGK6</v>
+      </c>
+      <c r="V42" s="42">
+        <f t="shared" ref="V42" si="21">N42</f>
+        <v>1</v>
+      </c>
+      <c r="W42" s="42">
+        <f t="shared" ref="W42" si="22">O42</f>
+        <v>5.47</v>
+      </c>
+      <c r="X42" s="42">
+        <f t="shared" ref="X42" si="23">Q42</f>
+        <v>-2.4700000000000002</v>
+      </c>
     </row>
     <row r="43" spans="1:31" x14ac:dyDescent="0.4">
       <c r="T43" s="43"/>
@@ -23157,7 +23150,7 @@
         <v>1</v>
       </c>
       <c r="B6" s="88" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C6" s="88" t="s">
         <v>58</v>
@@ -23345,7 +23338,7 @@
         <v>1</v>
       </c>
       <c r="B12" s="88" t="s">
-        <v>253</v>
+        <v>323</v>
       </c>
       <c r="C12" s="88" t="s">
         <v>58</v>
@@ -23359,8 +23352,8 @@
       <c r="F12" s="88" t="s">
         <v>59</v>
       </c>
-      <c r="G12" s="88" t="s">
-        <v>205</v>
+      <c r="G12" s="88">
+        <v>202605</v>
       </c>
       <c r="H12" s="88"/>
       <c r="I12" s="88"/>
@@ -23531,7 +23524,7 @@
         <v>1</v>
       </c>
       <c r="B18" s="88" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="C18" s="88" t="s">
         <v>58</v>
@@ -23686,7 +23679,7 @@
         <v>1</v>
       </c>
       <c r="B23" s="88" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C23" s="88" t="s">
         <v>58</v>
@@ -23717,7 +23710,7 @@
         <v>1</v>
       </c>
       <c r="B24" s="88" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C24" s="88" t="s">
         <v>58</v>
@@ -23748,7 +23741,7 @@
         <v>1</v>
       </c>
       <c r="B25" s="88" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C25" s="88" t="s">
         <v>58</v>
@@ -23779,7 +23772,7 @@
         <v>1</v>
       </c>
       <c r="B26" s="88" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C26" s="88" t="s">
         <v>58</v>
@@ -23810,7 +23803,7 @@
         <v>1</v>
       </c>
       <c r="B27" s="88" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C27" s="88" t="s">
         <v>58</v>
@@ -23841,7 +23834,7 @@
         <v>1</v>
       </c>
       <c r="B28" s="88" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C28" s="88" t="s">
         <v>58</v>
@@ -23872,7 +23865,7 @@
         <v>1</v>
       </c>
       <c r="B29" s="88" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C29" s="88" t="s">
         <v>58</v>
@@ -23903,7 +23896,7 @@
         <v>1</v>
       </c>
       <c r="B30" s="88" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C30" s="88" t="s">
         <v>58</v>
@@ -24026,7 +24019,7 @@
         <v>1</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="C34" s="88" t="s">
         <v>187</v>
@@ -24075,10 +24068,10 @@
         <v>1</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="C36" s="88" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="D36" s="88" t="s">
         <v>24</v>
@@ -24096,13 +24089,13 @@
         <v>75</v>
       </c>
       <c r="I36" s="88" t="s">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="J36" s="88">
         <v>1000</v>
       </c>
       <c r="K36" s="88" t="s">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="M36" s="88"/>
     </row>
@@ -24111,10 +24104,10 @@
         <v>1</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>319</v>
+        <v>311</v>
       </c>
       <c r="C37" s="88" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="D37" s="88" t="s">
         <v>24</v>
@@ -24132,13 +24125,13 @@
         <v>55</v>
       </c>
       <c r="I37" s="88" t="s">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="J37" s="88">
         <v>1000</v>
       </c>
       <c r="K37" s="88" t="s">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="M37" s="88"/>
     </row>

--- a/1XW_TradeBlotter_Web.xlsx
+++ b/1XW_TradeBlotter_Web.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0a601c1c2ba3d9f4/Trading/The Strategy Project/1XW Website/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="445" documentId="13_ncr:1_{6F5069F1-F0E7-4440-AA6D-4AFA11BBED1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E0863A29-C1C6-407B-95C8-00CC040F8DDE}"/>
+  <xr:revisionPtr revIDLastSave="529" documentId="13_ncr:1_{6F5069F1-F0E7-4440-AA6D-4AFA11BBED1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F3315264-5564-4490-BD1A-2DD129804EB4}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="22695" windowHeight="14476" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -121,7 +121,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1383" uniqueCount="336">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1517" uniqueCount="344">
   <si>
     <t>WEEK</t>
   </si>
@@ -478,12 +478,6 @@
   </si>
   <si>
     <t>(potential conflicting VLOOKUP if same instrument traded in different weeks)</t>
-  </si>
-  <si>
-    <t>INITIAL RISK</t>
-  </si>
-  <si>
-    <t>INITIAL RISK $</t>
   </si>
   <si>
     <t>ASSET CLASS</t>
@@ -1138,10 +1132,40 @@
     <t>Reconnected to TWS.</t>
   </si>
   <si>
-    <t>Last</t>
-  </si>
-  <si>
     <t>Long NKD Futures</t>
+  </si>
+  <si>
+    <t>Loop error: (-2147352567, 'Exception occurred.', (0, None, None, None, 0, -2146827284), None). Reconnecting in 2s.</t>
+  </si>
+  <si>
+    <t>OGM6 C5500</t>
+  </si>
+  <si>
+    <t>OGM6 C4930</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>OG</t>
+  </si>
+  <si>
+    <t>Long GC Call Spread</t>
+  </si>
+  <si>
+    <t>Loaded 38 contracts from Symbols sheet.</t>
+  </si>
+  <si>
+    <t>GC JUN26 4930 C</t>
+  </si>
+  <si>
+    <t>GC JUN26 5500 C</t>
+  </si>
+  <si>
+    <t>RISK</t>
+  </si>
+  <si>
+    <t>Close</t>
   </si>
 </sst>
 </file>
@@ -2265,7 +2289,7 @@
               <c:f>[0]!DynDate</c:f>
               <c:numCache>
                 <c:formatCode>d\-mmm</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>46053</c:v>
                 </c:pt>
@@ -2275,6 +2299,9 @@
                 <c:pt idx="2">
                   <c:v>46112</c:v>
                 </c:pt>
+                <c:pt idx="3">
+                  <c:v>46142</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2283,7 +2310,7 @@
               <c:f>[0]!DynMTD</c:f>
               <c:numCache>
                 <c:formatCode>0.00%</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0" formatCode="#,##0.00_-;\-#,##0.00_-;_-;_-@_-">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2291,7 +2318,10 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2.3885740632010988E-2</c:v>
+                  <c:v>2.8744450632010921E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2.4840775553442995E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2419,7 +2449,7 @@
               <c:f>[0]!DynDate</c:f>
               <c:numCache>
                 <c:formatCode>d\-mmm</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>46053</c:v>
                 </c:pt>
@@ -2429,6 +2459,9 @@
                 <c:pt idx="2">
                   <c:v>46112</c:v>
                 </c:pt>
+                <c:pt idx="3">
+                  <c:v>46142</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2437,7 +2470,7 @@
               <c:f>[0]!DynITD</c:f>
               <c:numCache>
                 <c:formatCode>0.00%</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0" formatCode="#,##0.00_-;\-#,##0.00_-;_-;_-@_-">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2445,7 +2478,10 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2.3885740632010988E-2</c:v>
+                  <c:v>2.8744450632010921E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5.4299260632010737E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2810,7 +2846,7 @@
               <c:f>[0]!DynDate</c:f>
               <c:numCache>
                 <c:formatCode>d\-mmm</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>46053</c:v>
                 </c:pt>
@@ -2820,6 +2856,9 @@
                 <c:pt idx="2">
                   <c:v>46112</c:v>
                 </c:pt>
+                <c:pt idx="3">
+                  <c:v>46142</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2828,7 +2867,7 @@
               <c:f>[0]!DynNAV</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00_-;\-#,##0.00_-;_-;_-@_-</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>1000</c:v>
                 </c:pt>
@@ -2836,7 +2875,10 @@
                   <c:v>1000</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1023.885740632011</c:v>
+                  <c:v>1028.744450632011</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1054.2992606320108</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3103,7 +3145,7 @@
               <c:f>[0]!DynDatePLB</c:f>
               <c:numCache>
                 <c:formatCode>d\-mmm\-yy</c:formatCode>
-                <c:ptCount val="7"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
                   <c:v>46081</c:v>
                 </c:pt>
@@ -3122,6 +3164,9 @@
                 <c:pt idx="5">
                   <c:v>46116</c:v>
                 </c:pt>
+                <c:pt idx="6">
+                  <c:v>46123</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3130,7 +3175,7 @@
               <c:f>[0]!DynInPLBPLB</c:f>
               <c:numCache>
                 <c:formatCode>0.00%</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3148,6 +3193,9 @@
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>-4.9009950100000088E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-5.8519850599000112E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3202,7 +3250,7 @@
               <c:f>[0]!DynDatePLB</c:f>
               <c:numCache>
                 <c:formatCode>d\-mmm\-yy</c:formatCode>
-                <c:ptCount val="7"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
                   <c:v>46081</c:v>
                 </c:pt>
@@ -3221,6 +3269,9 @@
                 <c:pt idx="5">
                   <c:v>46116</c:v>
                 </c:pt>
+                <c:pt idx="6">
+                  <c:v>46123</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3229,24 +3280,27 @@
               <c:f>[0]!DynPLBPLB</c:f>
               <c:numCache>
                 <c:formatCode>0.00%</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-1.0000000000000009E-2</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-1.9900000000000029E-2</c:v>
+                  <c:v>-9.000000000000008E-3</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-2.9701000000000088E-2</c:v>
+                  <c:v>-1.8584219999999929E-2</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-3.9403990000000055E-2</c:v>
+                  <c:v>-2.5776719999999975E-2</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-4.9009950100000088E-2</c:v>
+                  <c:v>-1.7031719999999972E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-2.6937720000000054E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3301,7 +3355,7 @@
               <c:f>[0]!DynDatePLB</c:f>
               <c:numCache>
                 <c:formatCode>d\-mmm\-yy</c:formatCode>
-                <c:ptCount val="7"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
                   <c:v>46081</c:v>
                 </c:pt>
@@ -3320,6 +3374,9 @@
                 <c:pt idx="5">
                   <c:v>46116</c:v>
                 </c:pt>
+                <c:pt idx="6">
+                  <c:v>46123</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3328,24 +3385,27 @@
               <c:f>[0]!DynPerfPLB</c:f>
               <c:numCache>
                 <c:formatCode>0.00%</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>5.2226906320109734E-3</c:v>
+                  <c:v>1.2922690632011014E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>6.7137806320110016E-3</c:v>
+                  <c:v>1.0723780632010849E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3.7295606320111307E-3</c:v>
+                  <c:v>6.5995606320108369E-3</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>6.8270906320111457E-3</c:v>
+                  <c:v>1.395959063201091E-2</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2.0505950632011327E-2</c:v>
+                  <c:v>4.909533063201077E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>5.0350290632010575E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3991,11 +4051,11 @@
   <sheetData>
     <row r="1" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B1" s="32" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C1" s="79">
-        <f ca="1">TODAY()-1</f>
-        <v>46111</v>
+        <f ca="1">TODAY()</f>
+        <v>46123</v>
       </c>
     </row>
     <row r="2" spans="2:11" x14ac:dyDescent="0.4">
@@ -4003,10 +4063,10 @@
         <v>107</v>
       </c>
       <c r="C2" s="37" t="s">
-        <v>334</v>
+        <v>343</v>
       </c>
       <c r="E2" s="47" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F2" s="47" t="s">
         <v>6</v>
@@ -4020,13 +4080,13 @@
       </c>
       <c r="C3" s="28">
         <f ca="1">OFFSET(NAV!B1,MATCH(C1,NAV!B:B,1),8)</f>
-        <v>1023885.740632011</v>
+        <v>1054299.2606320109</v>
       </c>
       <c r="E3" s="47" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F3" s="47" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="G3" s="47"/>
       <c r="H3" s="28"/>
@@ -4037,7 +4097,7 @@
       </c>
       <c r="C4" s="28">
         <f>SUM(N18:N1012)</f>
-        <v>23885.740632010933</v>
+        <v>54299.260632010941</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="47" t="s">
@@ -4051,15 +4111,15 @@
     </row>
     <row r="5" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B5" s="32" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C5" s="3">
         <f ca="1">OFFSET(NAV!B1,MATCH(C1,NAV!B:B,1),11)</f>
-        <v>2.3885740632010988E-2</v>
+        <v>5.4299260632010737E-2</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="47" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="F5" s="47" t="s">
         <v>50</v>
@@ -4070,15 +4130,15 @@
     </row>
     <row r="6" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B6" s="32" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C6" s="3">
         <f ca="1">OFFSET(NAV!B1,MATCH(C1,NAV!B:B,1),12)</f>
-        <v>2.3885740632010988E-2</v>
+        <v>2.4840775553442995E-2</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="47" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="F6" s="47"/>
       <c r="G6" s="47"/>
@@ -4087,15 +4147,15 @@
     </row>
     <row r="7" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B7" s="32" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C7" s="28">
         <f>Cash_Mgmt!H13</f>
-        <v>34220.209999999955</v>
+        <v>33651.029999999955</v>
       </c>
       <c r="D7" s="3">
         <f ca="1">C7/C3</f>
-        <v>3.3421903091332188E-2</v>
+        <v>3.191791103014479E-2</v>
       </c>
       <c r="E7" s="47"/>
       <c r="F7" s="47"/>
@@ -4105,15 +4165,15 @@
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B8" s="32" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C8" s="28">
         <f>C4+C7</f>
-        <v>58105.950632010892</v>
+        <v>87950.290632010903</v>
       </c>
       <c r="D8" s="3">
         <f ca="1">C5+D7</f>
-        <v>5.7307643723343175E-2</v>
+        <v>8.6217171662155534E-2</v>
       </c>
       <c r="G8" s="47"/>
       <c r="H8" s="51"/>
@@ -4125,11 +4185,11 @@
       </c>
       <c r="C9" s="28">
         <f t="array" ref="C9">SUM((F19:F112="Futures")*(M19:M112))</f>
-        <v>500400</v>
+        <v>522447.5</v>
       </c>
       <c r="D9" s="3">
         <f ca="1">C9/$C$3</f>
-        <v>0.48872640778366494</v>
+        <v>0.4955400421003931</v>
       </c>
       <c r="E9" s="47"/>
       <c r="F9" s="47"/>
@@ -4143,11 +4203,11 @@
       </c>
       <c r="C10" s="28">
         <f t="array" ref="C10">SUM((F19:F1012="Call")*(M19:M1012))</f>
-        <v>0</v>
+        <v>11160.000000000002</v>
       </c>
       <c r="D10" s="3">
         <f t="shared" ref="D10:D14" ca="1" si="0">C10/$C$3</f>
-        <v>0</v>
+        <v>1.058522984575558E-2</v>
       </c>
       <c r="H10" s="44"/>
     </row>
@@ -4157,11 +4217,11 @@
       </c>
       <c r="C11" s="28">
         <f t="array" ref="C11">SUM((F19:F212="Put")*(M19:M212))</f>
-        <v>6600</v>
+        <v>5459.9999999999991</v>
       </c>
       <c r="D11" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>6.4460317573385066E-3</v>
+        <v>5.1787952471169752E-3</v>
       </c>
     </row>
     <row r="12" spans="2:11" x14ac:dyDescent="0.4">
@@ -4170,39 +4230,39 @@
       </c>
       <c r="C12" s="28" cm="1">
         <f t="array" ref="C12">SUM((PLB!G4:G999="O")*(PLB!E4:E999))</f>
-        <v>45917.5</v>
+        <v>26937.72</v>
       </c>
       <c r="D12" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>4.4846312608725888E-2</v>
+        <v>2.555035463446299E-2</v>
       </c>
     </row>
     <row r="13" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B13" s="32" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C13" s="28">
         <f t="array" ref="C13">SUM((PLB!G4:G999="O")*(PLB!D4:D999))</f>
-        <v>20505.950632010979</v>
+        <v>50350.290632010983</v>
       </c>
       <c r="D13" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>2.0027577119448241E-2</v>
+        <v>4.7757114618318108E-2</v>
       </c>
       <c r="F13" s="59"/>
       <c r="G13" s="59"/>
     </row>
     <row r="14" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B14" s="32" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C14" s="28">
         <f>C12+C13</f>
-        <v>66423.450632010979</v>
+        <v>77288.010632010992</v>
       </c>
       <c r="D14" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>6.4873889728174136E-2</v>
+        <v>7.3307469252781102E-2</v>
       </c>
     </row>
     <row r="17" spans="2:28" x14ac:dyDescent="0.4">
@@ -4216,13 +4276,13 @@
         <v>1</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="F17" s="4" t="s">
         <v>2</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="H17" s="4" t="s">
         <v>101</v>
@@ -4249,13 +4309,13 @@
         <v>14</v>
       </c>
       <c r="P17" s="4" t="s">
-        <v>119</v>
+        <v>342</v>
       </c>
       <c r="Q17" s="4" t="s">
         <v>113</v>
       </c>
       <c r="R17" s="4" t="s">
-        <v>120</v>
+        <v>3</v>
       </c>
       <c r="S17" s="4" t="s">
         <v>114</v>
@@ -4282,12 +4342,12 @@
     </row>
     <row r="18" spans="2:28" x14ac:dyDescent="0.4">
       <c r="B18" s="9" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C18" s="12"/>
       <c r="D18" s="12"/>
       <c r="E18" s="10" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="F18" s="12"/>
       <c r="G18" s="12"/>
@@ -4299,7 +4359,7 @@
       <c r="M18" s="12"/>
       <c r="N18" s="95">
         <f>Cash_Mgmt!G13</f>
-        <v>3379.7899999999545</v>
+        <v>3948.9699999999543</v>
       </c>
       <c r="O18" s="12"/>
       <c r="P18" s="12"/>
@@ -4316,19 +4376,19 @@
     </row>
     <row r="19" spans="2:28" x14ac:dyDescent="0.4">
       <c r="B19" s="9" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C19" s="10">
         <v>1</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="F19" s="10" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="G19" s="28">
         <f>VLOOKUP(D19,Multiplier!B:I,8,0)</f>
@@ -4351,43 +4411,41 @@
       </c>
       <c r="L19" s="29">
         <f t="shared" ref="L19" si="2">IF(I19=0,IF(H19&gt;0,X19,Y19),Z19)</f>
-        <v>2091</v>
+        <v>2245</v>
       </c>
       <c r="M19" s="28">
         <f t="shared" ref="M19" si="3">I19*J19*L19</f>
-        <v>104550</v>
+        <v>112250</v>
       </c>
       <c r="N19" s="95">
         <f t="array" ref="N19">-SUM((Trades!T$2:T$9999=Blotter!C19)*(Trades!U$2:U$9999=Blotter!B19)*(Trades!V$2:V$9999)*(Trades!W$2:W$9999))*J19+SUM((Trades!T$2:T$9999=Blotter!C19)*(Trades!U$2:U$9999=Blotter!B19)*(Trades!X$2:X$9999))+(L19*I19)*J19</f>
-        <v>5222.6906320109993</v>
+        <v>12922.690632010999</v>
       </c>
       <c r="O19" s="29">
         <f>VLOOKUP(D19,Multiplier!B:H,3,0)</f>
         <v>140</v>
       </c>
-      <c r="P19" s="27">
-        <v>210</v>
-      </c>
+      <c r="P19" s="27"/>
       <c r="Q19" s="27"/>
       <c r="R19" s="28">
         <f t="shared" ref="R19" si="4">(1-Q19)*P19*J19*H19</f>
-        <v>10500</v>
+        <v>0</v>
       </c>
       <c r="S19" s="29">
         <f>IF(OR(F19="Futures",F19="Spot"),IF(I19=0,0,IF(I19&gt;0,L19-O19,L19+O19)),0)</f>
-        <v>1951</v>
+        <v>2105</v>
       </c>
       <c r="T19" s="3">
         <f t="shared" ref="T19" si="5">IF(S19&gt;0,IF(ISNUMBER(S19/L19-1),S19/L19-1,0),0)</f>
-        <v>-6.695361071257766E-2</v>
+        <v>-6.2360801781737196E-2</v>
       </c>
       <c r="U19" s="29">
         <f>IF(OR(F19="Futures",F19="Spot"),IF(I19=0,0,IF(I19&gt;0,K19-P19,K19+P19)),0)</f>
-        <v>1776.5461873597801</v>
+        <v>1986.5461873597801</v>
       </c>
       <c r="V19" s="3">
         <f t="shared" ref="V19" si="6">IF(U19&gt;0,IF(ISNUMBER(U19/L19-1),U19/L19-1,0),0)</f>
-        <v>-0.15038441541856518</v>
+        <v>-0.11512419271279284</v>
       </c>
       <c r="X19" s="34">
         <f t="array" ref="X19">IF(ISNUMBER(SUM((Trades!T$2:T$9999=Blotter!C19)*(Trades!U$2:U$9999=Blotter!B19)*(Trades!W$2:W$9999)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0))/SUM((Trades!T$2:T$9999=Blotter!C19)*(Trades!U$2:U$9999=Blotter!B19)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0))),SUM((Trades!T$2:T$9999=Blotter!C19)*(Trades!U$2:U$9999=Blotter!B19)*(Trades!W$2:W$9999)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0))/SUM((Trades!T$2:T$9999=Blotter!C19)*(Trades!U$2:U$9999=Blotter!B19)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0)),0)</f>
@@ -4399,13 +4457,13 @@
       </c>
       <c r="Z19" s="35">
         <f>IF(C$2="Last",IF(ISNUMBER(VLOOKUP(B19,Prices!A:L,8,0)),VLOOKUP(B19,Prices!A:L,8,0),0),IF(ISNUMBER(VLOOKUP(B19,Prices!A:L,12,0)),VLOOKUP(B19,Prices!A:L,12,0),0))</f>
-        <v>2091</v>
+        <v>2245</v>
       </c>
       <c r="AB19" s="29"/>
     </row>
     <row r="20" spans="2:28" x14ac:dyDescent="0.4">
       <c r="B20" s="9" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C20" s="10">
         <v>2</v>
@@ -4414,7 +4472,7 @@
         <v>34</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F20" s="10" t="s">
         <v>6</v>
@@ -4440,15 +4498,15 @@
       </c>
       <c r="L20" s="29">
         <f t="shared" ref="L20" si="8">IF(I20=0,IF(H20&gt;0,X20,Y20),Z20)</f>
-        <v>3285</v>
+        <v>3162</v>
       </c>
       <c r="M20" s="28">
         <f t="shared" ref="M20" si="9">I20*J20*L20</f>
-        <v>98550</v>
+        <v>94860</v>
       </c>
       <c r="N20" s="95">
         <f t="array" ref="N20">-SUM((Trades!T$2:T$9999=Blotter!C20)*(Trades!U$2:U$9999=Blotter!B20)*(Trades!V$2:V$9999)*(Trades!W$2:W$9999))*J20+SUM((Trades!T$2:T$9999=Blotter!C20)*(Trades!U$2:U$9999=Blotter!B20)*(Trades!X$2:X$9999))+(L20*I20)*J20</f>
-        <v>1491.0899999999965</v>
+        <v>-2198.9100000000035</v>
       </c>
       <c r="O20" s="29">
         <f>VLOOKUP(D20,Multiplier!B:H,3,0)</f>
@@ -4464,11 +4522,11 @@
       </c>
       <c r="S20" s="29">
         <f>IF(OR(F20="Futures",F20="Spot"),IF(I20=0,0,IF(I20&gt;0,L20-O20,L20+O20)),0)</f>
-        <v>3080</v>
+        <v>2957</v>
       </c>
       <c r="T20" s="3">
         <f t="shared" ref="T20" si="11">IF(S20&gt;0,IF(ISNUMBER(S20/L20-1),S20/L20-1,0),0)</f>
-        <v>-6.2404870624048758E-2</v>
+        <v>-6.4832384566729906E-2</v>
       </c>
       <c r="U20" s="29">
         <f t="shared" ref="U20" si="12">IF(OR(F20="Futures",F20="Stocks"),IF(I20=0,0,IF(I20&gt;0,K20-P20,K20+P20)),0)</f>
@@ -4476,7 +4534,7 @@
       </c>
       <c r="V20" s="3">
         <f t="shared" ref="V20" si="13">IF(U20&gt;0,IF(ISNUMBER(U20/L20-1),U20/L20-1,0),0)</f>
-        <v>-0.10645449010654484</v>
+        <v>-7.169607843137249E-2</v>
       </c>
       <c r="X20" s="34">
         <f t="array" ref="X20">IF(ISNUMBER(SUM((Trades!T$2:T$9999=Blotter!C20)*(Trades!U$2:U$9999=Blotter!B20)*(Trades!W$2:W$9999)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0))/SUM((Trades!T$2:T$9999=Blotter!C20)*(Trades!U$2:U$9999=Blotter!B20)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0))),SUM((Trades!T$2:T$9999=Blotter!C20)*(Trades!U$2:U$9999=Blotter!B20)*(Trades!W$2:W$9999)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0))/SUM((Trades!T$2:T$9999=Blotter!C20)*(Trades!U$2:U$9999=Blotter!B20)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0)),0)</f>
@@ -4488,13 +4546,13 @@
       </c>
       <c r="Z20" s="35">
         <f>IF(C$2="Last",IF(ISNUMBER(VLOOKUP(B20,Prices!A:L,8,0)),VLOOKUP(B20,Prices!A:L,8,0),0),IF(ISNUMBER(VLOOKUP(B20,Prices!A:L,12,0)),VLOOKUP(B20,Prices!A:L,12,0),0))</f>
-        <v>3285</v>
+        <v>3162</v>
       </c>
       <c r="AB20" s="29"/>
     </row>
     <row r="21" spans="2:28" x14ac:dyDescent="0.4">
       <c r="B21" s="9" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C21" s="10">
         <v>3</v>
@@ -4503,7 +4561,7 @@
         <v>24</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F21" s="10" t="s">
         <v>50</v>
@@ -4529,27 +4587,27 @@
       </c>
       <c r="L21" s="29">
         <f t="shared" ref="L21:L22" si="15">IF(I21=0,IF(H21&gt;0,X21,Y21),Z21)</f>
-        <v>2.5</v>
+        <v>2.0099999999999998</v>
       </c>
       <c r="M21" s="28">
         <f t="shared" ref="M21:M22" si="16">I21*J21*L21</f>
-        <v>7500</v>
+        <v>6029.9999999999991</v>
       </c>
       <c r="N21" s="95">
         <f t="array" ref="N21">-SUM((Trades!T$2:T$9999=Blotter!C21)*(Trades!U$2:U$9999=Blotter!B21)*(Trades!V$2:V$9999)*(Trades!W$2:W$9999))*J21+SUM((Trades!T$2:T$9999=Blotter!C21)*(Trades!U$2:U$9999=Blotter!B21)*(Trades!X$2:X$9999))+(L21*I21)*J21</f>
-        <v>-3127.1100000000024</v>
+        <v>-4597.1100000000033</v>
       </c>
       <c r="O21" s="29">
         <f>VLOOKUP(D21,Multiplier!B:H,3,0)</f>
         <v>2.1</v>
       </c>
       <c r="P21" s="27">
-        <v>3.54</v>
+        <v>3.5423700000000009</v>
       </c>
       <c r="Q21" s="27"/>
       <c r="R21" s="28">
         <f t="shared" ref="R21:R22" si="17">(1-Q21)*P21*J21*H21</f>
-        <v>10620</v>
+        <v>10627.110000000002</v>
       </c>
       <c r="S21" s="29">
         <f t="shared" ref="S21:S22" si="18">IF(OR(F21="Futures",F21="Spot"),IF(I21=0,0,IF(I21&gt;0,L21-O21,L21+O21)),0)</f>
@@ -4577,13 +4635,13 @@
       </c>
       <c r="Z21" s="35">
         <f>IF(C$2="Last",IF(ISNUMBER(VLOOKUP(B21,Prices!A:L,8,0)),VLOOKUP(B21,Prices!A:L,8,0),0),IF(ISNUMBER(VLOOKUP(B21,Prices!A:L,12,0)),VLOOKUP(B21,Prices!A:L,12,0),0))</f>
-        <v>2.5</v>
+        <v>2.0099999999999998</v>
       </c>
       <c r="AB21" s="29"/>
     </row>
     <row r="22" spans="2:28" x14ac:dyDescent="0.4">
       <c r="B22" s="9" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C22" s="10">
         <v>3</v>
@@ -4592,7 +4650,7 @@
         <v>24</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F22" s="10" t="s">
         <v>50</v>
@@ -4614,31 +4672,31 @@
       </c>
       <c r="K22" s="29">
         <f t="shared" si="14"/>
-        <v>0.34762999999999999</v>
+        <v>0.34762999999999988</v>
       </c>
       <c r="L22" s="29">
         <f t="shared" si="15"/>
-        <v>0.3</v>
+        <v>0.19</v>
       </c>
       <c r="M22" s="28">
         <f t="shared" si="16"/>
-        <v>-900</v>
+        <v>-570</v>
       </c>
       <c r="N22" s="95">
         <f t="array" ref="N22">-SUM((Trades!T$2:T$9999=Blotter!C22)*(Trades!U$2:U$9999=Blotter!B22)*(Trades!V$2:V$9999)*(Trades!W$2:W$9999))*J22+SUM((Trades!T$2:T$9999=Blotter!C22)*(Trades!U$2:U$9999=Blotter!B22)*(Trades!X$2:X$9999))+(L22*I22)*J22</f>
-        <v>142.88999999999999</v>
+        <v>472.88999999999976</v>
       </c>
       <c r="O22" s="29">
         <f>VLOOKUP(D22,Multiplier!B:H,3,0)</f>
         <v>2.1</v>
       </c>
       <c r="P22" s="27">
-        <v>0.34</v>
+        <v>0.34762999999999994</v>
       </c>
       <c r="Q22" s="27"/>
       <c r="R22" s="28">
         <f t="shared" si="17"/>
-        <v>-1020</v>
+        <v>-1042.8899999999999</v>
       </c>
       <c r="S22" s="29">
         <f t="shared" si="18"/>
@@ -4666,13 +4724,13 @@
       </c>
       <c r="Z22" s="35">
         <f>IF(C$2="Last",IF(ISNUMBER(VLOOKUP(B22,Prices!A:L,8,0)),VLOOKUP(B22,Prices!A:L,8,0),0),IF(ISNUMBER(VLOOKUP(B22,Prices!A:L,12,0)),VLOOKUP(B22,Prices!A:L,12,0),0))</f>
-        <v>0.3</v>
+        <v>0.19</v>
       </c>
       <c r="AB22" s="29"/>
     </row>
     <row r="23" spans="2:28" x14ac:dyDescent="0.4">
       <c r="B23" s="9" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C23" s="10">
         <v>4</v>
@@ -4681,7 +4739,7 @@
         <v>25</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F23" s="10" t="s">
         <v>6</v>
@@ -4703,19 +4761,19 @@
       </c>
       <c r="K23" s="29">
         <f t="shared" ref="K23" si="22">L23-N23/(H23*J23)</f>
-        <v>5.4700988000000006</v>
+        <v>5.4700987999999997</v>
       </c>
       <c r="L23" s="29">
         <f t="shared" ref="L23" si="23">IF(I23=0,IF(H23&gt;0,X23,Y23),Z23)</f>
-        <v>5.5940000000000003</v>
+        <v>5.7645</v>
       </c>
       <c r="M23" s="28">
         <f t="shared" ref="M23" si="24">I23*J23*L23</f>
-        <v>139850</v>
+        <v>144112.5</v>
       </c>
       <c r="N23" s="95">
         <f t="array" ref="N23">-SUM((Trades!T$2:T$9999=Blotter!C23)*(Trades!U$2:U$9999=Blotter!B23)*(Trades!V$2:V$9999)*(Trades!W$2:W$9999))*J23+SUM((Trades!T$2:T$9999=Blotter!C23)*(Trades!U$2:U$9999=Blotter!B23)*(Trades!X$2:X$9999))+(L23*I23)*J23</f>
-        <v>3097.5299999999988</v>
+        <v>7360.0299999999988</v>
       </c>
       <c r="O23" s="29">
         <f>VLOOKUP(D23,Multiplier!B:H,3,0)</f>
@@ -4731,19 +4789,19 @@
       </c>
       <c r="S23" s="29">
         <f t="shared" ref="S23" si="26">IF(OR(F23="Futures",F23="Spot"),IF(I23=0,0,IF(I23&gt;0,L23-O23,L23+O23)),0)</f>
-        <v>5.4022000000000006</v>
+        <v>5.5727000000000002</v>
       </c>
       <c r="T23" s="3">
         <f t="shared" ref="T23" si="27">IF(S23&gt;0,IF(ISNUMBER(S23/L23-1),S23/L23-1,0),0)</f>
-        <v>-3.4286735788344624E-2</v>
+        <v>-3.3272616879174266E-2</v>
       </c>
       <c r="U23" s="29">
         <f t="shared" ref="U23" si="28">IF(OR(F23="Futures",F23="Stocks"),IF(I23=0,0,IF(I23&gt;0,K23-P23,K23+P23)),0)</f>
-        <v>5.1823988000000005</v>
+        <v>5.1823987999999996</v>
       </c>
       <c r="V23" s="3">
         <f t="shared" ref="V23" si="29">IF(U23&gt;0,IF(ISNUMBER(U23/L23-1),U23/L23-1,0),0)</f>
-        <v>-7.3579048981051054E-2</v>
+        <v>-0.10098034521641086</v>
       </c>
       <c r="X23" s="34">
         <f t="array" ref="X23">IF(ISNUMBER(SUM((Trades!T$2:T$9999=Blotter!C23)*(Trades!U$2:U$9999=Blotter!B23)*(Trades!W$2:W$9999)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0))/SUM((Trades!T$2:T$9999=Blotter!C23)*(Trades!U$2:U$9999=Blotter!B23)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0))),SUM((Trades!T$2:T$9999=Blotter!C23)*(Trades!U$2:U$9999=Blotter!B23)*(Trades!W$2:W$9999)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0))/SUM((Trades!T$2:T$9999=Blotter!C23)*(Trades!U$2:U$9999=Blotter!B23)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0)),0)</f>
@@ -4755,22 +4813,22 @@
       </c>
       <c r="Z23" s="35">
         <f>IF(C$2="Last",IF(ISNUMBER(VLOOKUP(B23,Prices!A:L,8,0)),VLOOKUP(B23,Prices!A:L,8,0),0),IF(ISNUMBER(VLOOKUP(B23,Prices!A:L,12,0)),VLOOKUP(B23,Prices!A:L,12,0),0))</f>
-        <v>5.5940000000000003</v>
+        <v>5.7645</v>
       </c>
       <c r="AB23" s="29"/>
     </row>
     <row r="24" spans="2:28" x14ac:dyDescent="0.4">
       <c r="B24" s="9" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C24" s="10">
         <v>5</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F24" s="10" t="s">
         <v>6</v>
@@ -4792,47 +4850,47 @@
       </c>
       <c r="K24" s="29">
         <f t="shared" ref="K24" si="30">L24-N24/(H24*J24)</f>
-        <v>49664.228000000003</v>
+        <v>49667.851999999999</v>
       </c>
       <c r="L24" s="29">
         <f t="shared" ref="L24" si="31">IF(I24=0,IF(H24&gt;0,X24,Y24),Z24)</f>
-        <v>52400</v>
+        <v>56695</v>
       </c>
       <c r="M24" s="28">
         <f t="shared" ref="M24" si="32">I24*J24*L24</f>
-        <v>262000</v>
+        <v>283475</v>
       </c>
       <c r="N24" s="95">
         <f t="array" ref="N24">-SUM((Trades!T$2:T$9999=Blotter!C24)*(Trades!U$2:U$9999=Blotter!B24)*(Trades!V$2:V$9999)*(Trades!W$2:W$9999))*J24+SUM((Trades!T$2:T$9999=Blotter!C24)*(Trades!U$2:U$9999=Blotter!B24)*(Trades!X$2:X$9999))+(L24*I24)*J24</f>
-        <v>13678.859999999986</v>
+        <v>35135.739999999991</v>
       </c>
       <c r="O24" s="29">
         <f>VLOOKUP(D24,Multiplier!B:H,3,0)</f>
         <v>1749</v>
       </c>
       <c r="P24" s="27">
-        <v>1925</v>
+        <v>-1749</v>
       </c>
       <c r="Q24" s="27"/>
       <c r="R24" s="28">
         <f t="shared" ref="R24" si="33">(1-Q24)*P24*J24*H24</f>
-        <v>9625</v>
+        <v>-8745</v>
       </c>
       <c r="S24" s="29">
         <f t="shared" ref="S24" si="34">IF(OR(F24="Futures",F24="Spot"),IF(I24=0,0,IF(I24&gt;0,L24-O24,L24+O24)),0)</f>
-        <v>50651</v>
+        <v>54946</v>
       </c>
       <c r="T24" s="3">
         <f t="shared" ref="T24" si="35">IF(S24&gt;0,IF(ISNUMBER(S24/L24-1),S24/L24-1,0),0)</f>
-        <v>-3.337786259541986E-2</v>
+        <v>-3.0849281241732029E-2</v>
       </c>
       <c r="U24" s="29">
         <f t="shared" ref="U24" si="36">IF(OR(F24="Futures",F24="Stocks"),IF(I24=0,0,IF(I24&gt;0,K24-P24,K24+P24)),0)</f>
-        <v>47739.228000000003</v>
+        <v>51416.851999999999</v>
       </c>
       <c r="V24" s="3">
         <f t="shared" ref="V24" si="37">IF(U24&gt;0,IF(ISNUMBER(U24/L24-1),U24/L24-1,0),0)</f>
-        <v>-8.8946030534351128E-2</v>
+        <v>-9.3097239615486438E-2</v>
       </c>
       <c r="X24" s="34">
         <f t="array" ref="X24">IF(ISNUMBER(SUM((Trades!T$2:T$9999=Blotter!C24)*(Trades!U$2:U$9999=Blotter!B24)*(Trades!W$2:W$9999)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0))/SUM((Trades!T$2:T$9999=Blotter!C24)*(Trades!U$2:U$9999=Blotter!B24)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0))),SUM((Trades!T$2:T$9999=Blotter!C24)*(Trades!U$2:U$9999=Blotter!B24)*(Trades!W$2:W$9999)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0))/SUM((Trades!T$2:T$9999=Blotter!C24)*(Trades!U$2:U$9999=Blotter!B24)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0)),0)</f>
@@ -4844,62 +4902,186 @@
       </c>
       <c r="Z24" s="35">
         <f>IF(C$2="Last",IF(ISNUMBER(VLOOKUP(B24,Prices!A:L,8,0)),VLOOKUP(B24,Prices!A:L,8,0),0),IF(ISNUMBER(VLOOKUP(B24,Prices!A:L,12,0)),VLOOKUP(B24,Prices!A:L,12,0),0))</f>
-        <v>52400</v>
+        <v>56695</v>
       </c>
       <c r="AB24" s="29"/>
     </row>
     <row r="25" spans="2:28" x14ac:dyDescent="0.4">
-      <c r="B25" s="9"/>
-      <c r="C25" s="10"/>
-      <c r="D25" s="10"/>
-      <c r="E25" s="10"/>
-      <c r="F25" s="10"/>
-      <c r="G25" s="28"/>
-      <c r="H25" s="11"/>
-      <c r="I25" s="29"/>
-      <c r="J25" s="28"/>
-      <c r="K25" s="29"/>
-      <c r="L25" s="29"/>
-      <c r="M25" s="28"/>
-      <c r="N25" s="28"/>
-      <c r="O25" s="29"/>
-      <c r="P25" s="27"/>
+      <c r="B25" s="9" t="s">
+        <v>334</v>
+      </c>
+      <c r="C25" s="10">
+        <v>6</v>
+      </c>
+      <c r="D25" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="E25" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="F25" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="G25" s="28">
+        <f>VLOOKUP(D25,Multiplier!B:I,8,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H25" s="11">
+        <v>-1</v>
+      </c>
+      <c r="I25" s="28">
+        <f t="array" ref="I25">ROUND(SUM((Trades!V$2:V$9999)*(Trades!U$2:U$9999=Blotter!B25)*(Trades!$T$2:T$9999=Blotter!C25)),8)</f>
+        <v>-1</v>
+      </c>
+      <c r="J25" s="28">
+        <f>VLOOKUP(D25,Multiplier!B:D,2,0)</f>
+        <v>100</v>
+      </c>
+      <c r="K25" s="29">
+        <f t="shared" ref="K25:K26" si="38">L25-N25/(H25*J25)</f>
+        <v>26.3748</v>
+      </c>
+      <c r="L25" s="29">
+        <f t="shared" ref="L25:L26" si="39">IF(I25=0,IF(H25&gt;0,X25,Y25),Z25)</f>
+        <v>22.7</v>
+      </c>
+      <c r="M25" s="28">
+        <f t="shared" ref="M25:M26" si="40">I25*J25*L25</f>
+        <v>-2270</v>
+      </c>
+      <c r="N25" s="95">
+        <f t="array" ref="N25">-SUM((Trades!T$2:T$9999=Blotter!C25)*(Trades!U$2:U$9999=Blotter!B25)*(Trades!V$2:V$9999)*(Trades!W$2:W$9999))*J25+SUM((Trades!T$2:T$9999=Blotter!C25)*(Trades!U$2:U$9999=Blotter!B25)*(Trades!X$2:X$9999))+(L25*I25)*J25</f>
+        <v>367.48</v>
+      </c>
+      <c r="O25" s="29">
+        <f>VLOOKUP(D25,Multiplier!B:H,3,0)</f>
+        <v>185.2</v>
+      </c>
+      <c r="P25" s="27">
+        <v>26.37</v>
+      </c>
       <c r="Q25" s="27"/>
-      <c r="R25" s="28"/>
-      <c r="S25" s="29"/>
-      <c r="T25" s="3"/>
-      <c r="U25" s="29"/>
-      <c r="V25" s="3"/>
-      <c r="X25" s="34"/>
-      <c r="Y25" s="34"/>
-      <c r="Z25" s="35"/>
+      <c r="R25" s="28">
+        <f t="shared" ref="R25:R26" si="41">(1-Q25)*P25*J25*H25</f>
+        <v>-2637</v>
+      </c>
+      <c r="S25" s="29">
+        <f t="shared" ref="S25:S26" si="42">IF(OR(F25="Futures",F25="Spot"),IF(I25=0,0,IF(I25&gt;0,L25-O25,L25+O25)),0)</f>
+        <v>0</v>
+      </c>
+      <c r="T25" s="3">
+        <f t="shared" ref="T25:T26" si="43">IF(S25&gt;0,IF(ISNUMBER(S25/L25-1),S25/L25-1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="U25" s="29">
+        <f t="shared" ref="U25:U26" si="44">IF(OR(F25="Futures",F25="Stocks"),IF(I25=0,0,IF(I25&gt;0,K25-P25,K25+P25)),0)</f>
+        <v>0</v>
+      </c>
+      <c r="V25" s="3">
+        <f t="shared" ref="V25:V26" si="45">IF(U25&gt;0,IF(ISNUMBER(U25/L25-1),U25/L25-1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="X25" s="34">
+        <f t="array" ref="X25">IF(ISNUMBER(SUM((Trades!T$2:T$9999=Blotter!C25)*(Trades!U$2:U$9999=Blotter!B25)*(Trades!W$2:W$9999)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0))/SUM((Trades!T$2:T$9999=Blotter!C25)*(Trades!U$2:U$9999=Blotter!B25)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0))),SUM((Trades!T$2:T$9999=Blotter!C25)*(Trades!U$2:U$9999=Blotter!B25)*(Trades!W$2:W$9999)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0))/SUM((Trades!T$2:T$9999=Blotter!C25)*(Trades!U$2:U$9999=Blotter!B25)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0)),0)</f>
+        <v>26.4</v>
+      </c>
+      <c r="Y25" s="34">
+        <f t="array" ref="Y25">IF(ISNUMBER(SUM((Trades!T$2:T$9999=Blotter!C25)*(Trades!U$2:U$9999=Blotter!B25)*(Trades!W$2:W$9999)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&gt;0))/SUM((Trades!T$2:T$9999=Blotter!C25)*(Trades!U$2:U$9999=Blotter!B25)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&gt;0))),SUM((Trades!T$2:T$9999=Blotter!C25)*(Trades!U$2:U$9999=Blotter!B25)*(Trades!W$2:W$9999)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&gt;0))/SUM((Trades!T$2:T$9999=Blotter!C25)*(Trades!U$2:U$9999=Blotter!B25)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&gt;0)),0)</f>
+        <v>0</v>
+      </c>
+      <c r="Z25" s="35">
+        <f>IF(C$2="Last",IF(ISNUMBER(VLOOKUP(B25,Prices!A:L,8,0)),VLOOKUP(B25,Prices!A:L,8,0),0),IF(ISNUMBER(VLOOKUP(B25,Prices!A:L,12,0)),VLOOKUP(B25,Prices!A:L,12,0),0))</f>
+        <v>22.7</v>
+      </c>
       <c r="AB25" s="29"/>
     </row>
     <row r="26" spans="2:28" x14ac:dyDescent="0.4">
-      <c r="B26" s="9"/>
-      <c r="C26" s="10"/>
-      <c r="D26" s="10"/>
-      <c r="E26" s="10"/>
-      <c r="F26" s="10"/>
-      <c r="G26" s="28"/>
-      <c r="H26" s="11"/>
-      <c r="I26" s="29"/>
-      <c r="J26" s="28"/>
-      <c r="K26" s="29"/>
-      <c r="L26" s="29"/>
-      <c r="M26" s="28"/>
-      <c r="N26" s="28"/>
-      <c r="O26" s="29"/>
-      <c r="P26" s="27"/>
+      <c r="B26" s="9" t="s">
+        <v>335</v>
+      </c>
+      <c r="C26" s="10">
+        <v>6</v>
+      </c>
+      <c r="D26" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="E26" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="F26" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="G26" s="28">
+        <f>VLOOKUP(D26,Multiplier!B:I,8,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H26" s="11">
+        <v>1</v>
+      </c>
+      <c r="I26" s="28">
+        <f t="array" ref="I26">ROUND(SUM((Trades!V$2:V$9999)*(Trades!U$2:U$9999=Blotter!B26)*(Trades!$T$2:T$9999=Blotter!C26)),8)</f>
+        <v>1</v>
+      </c>
+      <c r="J26" s="28">
+        <f>VLOOKUP(D26,Multiplier!B:D,2,0)</f>
+        <v>100</v>
+      </c>
+      <c r="K26" s="29">
+        <f t="shared" si="38"/>
+        <v>125.42519999999999</v>
+      </c>
+      <c r="L26" s="29">
+        <f t="shared" si="39"/>
+        <v>134.30000000000001</v>
+      </c>
+      <c r="M26" s="28">
+        <f t="shared" si="40"/>
+        <v>13430.000000000002</v>
+      </c>
+      <c r="N26" s="95">
+        <f t="array" ref="N26">-SUM((Trades!T$2:T$9999=Blotter!C26)*(Trades!U$2:U$9999=Blotter!B26)*(Trades!V$2:V$9999)*(Trades!W$2:W$9999))*J26+SUM((Trades!T$2:T$9999=Blotter!C26)*(Trades!U$2:U$9999=Blotter!B26)*(Trades!X$2:X$9999))+(L26*I26)*J26</f>
+        <v>887.48000000000138</v>
+      </c>
+      <c r="O26" s="29">
+        <f>VLOOKUP(D26,Multiplier!B:H,3,0)</f>
+        <v>185.2</v>
+      </c>
+      <c r="P26" s="27">
+        <v>125.43</v>
+      </c>
       <c r="Q26" s="27"/>
-      <c r="R26" s="28"/>
-      <c r="S26" s="29"/>
-      <c r="T26" s="3"/>
-      <c r="U26" s="29"/>
-      <c r="V26" s="3"/>
-      <c r="X26" s="34"/>
-      <c r="Y26" s="34"/>
-      <c r="Z26" s="35"/>
+      <c r="R26" s="28">
+        <f t="shared" si="41"/>
+        <v>12543</v>
+      </c>
+      <c r="S26" s="29">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="T26" s="3">
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
+      <c r="U26" s="29">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="V26" s="3">
+        <f t="shared" si="45"/>
+        <v>0</v>
+      </c>
+      <c r="X26" s="34">
+        <f t="array" ref="X26">IF(ISNUMBER(SUM((Trades!T$2:T$9999=Blotter!C26)*(Trades!U$2:U$9999=Blotter!B26)*(Trades!W$2:W$9999)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0))/SUM((Trades!T$2:T$9999=Blotter!C26)*(Trades!U$2:U$9999=Blotter!B26)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0))),SUM((Trades!T$2:T$9999=Blotter!C26)*(Trades!U$2:U$9999=Blotter!B26)*(Trades!W$2:W$9999)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0))/SUM((Trades!T$2:T$9999=Blotter!C26)*(Trades!U$2:U$9999=Blotter!B26)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0)),0)</f>
+        <v>0</v>
+      </c>
+      <c r="Y26" s="34">
+        <f t="array" ref="Y26">IF(ISNUMBER(SUM((Trades!T$2:T$9999=Blotter!C26)*(Trades!U$2:U$9999=Blotter!B26)*(Trades!W$2:W$9999)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&gt;0))/SUM((Trades!T$2:T$9999=Blotter!C26)*(Trades!U$2:U$9999=Blotter!B26)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&gt;0))),SUM((Trades!T$2:T$9999=Blotter!C26)*(Trades!U$2:U$9999=Blotter!B26)*(Trades!W$2:W$9999)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&gt;0))/SUM((Trades!T$2:T$9999=Blotter!C26)*(Trades!U$2:U$9999=Blotter!B26)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&gt;0)),0)</f>
+        <v>125.4</v>
+      </c>
+      <c r="Z26" s="35">
+        <f>IF(C$2="Last",IF(ISNUMBER(VLOOKUP(B26,Prices!A:L,8,0)),VLOOKUP(B26,Prices!A:L,8,0),0),IF(ISNUMBER(VLOOKUP(B26,Prices!A:L,12,0)),VLOOKUP(B26,Prices!A:L,12,0),0))</f>
+        <v>134.30000000000001</v>
+      </c>
       <c r="AB26" s="29"/>
     </row>
     <row r="27" spans="2:28" x14ac:dyDescent="0.4">
@@ -6422,73 +6604,73 @@
   <sheetData>
     <row r="1" spans="1:32" x14ac:dyDescent="0.4">
       <c r="A1" s="86" t="s">
+        <v>214</v>
+      </c>
+      <c r="B1" s="86" t="s">
+        <v>232</v>
+      </c>
+      <c r="C1" s="86" t="s">
+        <v>213</v>
+      </c>
+      <c r="D1" s="86" t="s">
+        <v>212</v>
+      </c>
+      <c r="E1" s="86" t="s">
+        <v>204</v>
+      </c>
+      <c r="F1" s="86" t="s">
+        <v>211</v>
+      </c>
+      <c r="G1" s="86" t="s">
+        <v>210</v>
+      </c>
+      <c r="H1" s="86" t="s">
+        <v>231</v>
+      </c>
+      <c r="I1" s="86" t="s">
+        <v>230</v>
+      </c>
+      <c r="J1" s="86" t="s">
+        <v>229</v>
+      </c>
+      <c r="K1" s="86" t="s">
+        <v>228</v>
+      </c>
+      <c r="L1" s="86" t="s">
+        <v>227</v>
+      </c>
+      <c r="M1" s="86" t="s">
+        <v>226</v>
+      </c>
+      <c r="N1" s="86" t="s">
+        <v>225</v>
+      </c>
+      <c r="O1" s="86" t="s">
+        <v>224</v>
+      </c>
+      <c r="P1" s="86" t="s">
+        <v>223</v>
+      </c>
+      <c r="Q1" s="86" t="s">
+        <v>222</v>
+      </c>
+      <c r="R1" s="86" t="s">
+        <v>221</v>
+      </c>
+      <c r="S1" s="86" t="s">
+        <v>220</v>
+      </c>
+      <c r="T1" s="86" t="s">
+        <v>219</v>
+      </c>
+      <c r="U1" s="86" t="s">
+        <v>218</v>
+      </c>
+      <c r="V1" s="86" t="s">
+        <v>217</v>
+      </c>
+      <c r="W1" s="86" t="s">
         <v>216</v>
-      </c>
-      <c r="B1" s="86" t="s">
-        <v>234</v>
-      </c>
-      <c r="C1" s="86" t="s">
-        <v>215</v>
-      </c>
-      <c r="D1" s="86" t="s">
-        <v>214</v>
-      </c>
-      <c r="E1" s="86" t="s">
-        <v>206</v>
-      </c>
-      <c r="F1" s="86" t="s">
-        <v>213</v>
-      </c>
-      <c r="G1" s="86" t="s">
-        <v>212</v>
-      </c>
-      <c r="H1" s="86" t="s">
-        <v>233</v>
-      </c>
-      <c r="I1" s="86" t="s">
-        <v>232</v>
-      </c>
-      <c r="J1" s="86" t="s">
-        <v>231</v>
-      </c>
-      <c r="K1" s="86" t="s">
-        <v>230</v>
-      </c>
-      <c r="L1" s="86" t="s">
-        <v>229</v>
-      </c>
-      <c r="M1" s="86" t="s">
-        <v>228</v>
-      </c>
-      <c r="N1" s="86" t="s">
-        <v>227</v>
-      </c>
-      <c r="O1" s="86" t="s">
-        <v>226</v>
-      </c>
-      <c r="P1" s="86" t="s">
-        <v>225</v>
-      </c>
-      <c r="Q1" s="86" t="s">
-        <v>224</v>
-      </c>
-      <c r="R1" s="86" t="s">
-        <v>223</v>
-      </c>
-      <c r="S1" s="86" t="s">
-        <v>222</v>
-      </c>
-      <c r="T1" s="86" t="s">
-        <v>221</v>
-      </c>
-      <c r="U1" s="86" t="s">
-        <v>220</v>
-      </c>
-      <c r="V1" s="86" t="s">
-        <v>219</v>
-      </c>
-      <c r="W1" s="86" t="s">
-        <v>218</v>
       </c>
       <c r="X1" s="84"/>
       <c r="Y1" s="84"/>
@@ -6502,7 +6684,7 @@
     </row>
     <row r="2" spans="1:32" x14ac:dyDescent="0.4">
       <c r="A2" s="81" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B2" s="81">
         <v>649180678</v>
@@ -6514,7 +6696,7 @@
         <v>21</v>
       </c>
       <c r="E2" s="81" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="F2" s="81" t="s">
         <v>78</v>
@@ -6523,31 +6705,31 @@
         <v>59</v>
       </c>
       <c r="H2" s="91">
-        <v>6530.5</v>
+        <v>-1</v>
       </c>
       <c r="I2" s="91">
-        <v>6530.25</v>
+        <v>-1</v>
       </c>
       <c r="J2" s="91">
-        <v>6530.5</v>
+        <v>-1</v>
       </c>
       <c r="K2" s="91">
-        <v>6530.375</v>
+        <v>-1</v>
       </c>
       <c r="L2" s="91">
-        <v>6388.25</v>
+        <v>6863.25</v>
       </c>
       <c r="M2" s="91">
-        <v>6385.25</v>
+        <v>6858</v>
       </c>
       <c r="N2" s="91">
-        <v>6536.25</v>
+        <v>6888</v>
       </c>
       <c r="O2" s="91">
-        <v>6353.25</v>
+        <v>6846.25</v>
       </c>
       <c r="P2" s="91">
-        <v>1139818</v>
+        <v>1227472</v>
       </c>
       <c r="Q2" s="91"/>
       <c r="R2" s="91"/>
@@ -6555,10 +6737,10 @@
       <c r="T2" s="91"/>
       <c r="U2" s="91"/>
       <c r="V2" s="85">
-        <v>46112.785127314812</v>
+        <v>46123.423333333332</v>
       </c>
       <c r="W2" s="81" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="X2" s="81"/>
       <c r="Y2" s="81"/>
@@ -6566,7 +6748,7 @@
     </row>
     <row r="3" spans="1:32" x14ac:dyDescent="0.4">
       <c r="A3" s="81" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="B3" s="81">
         <v>750150196</v>
@@ -6578,7 +6760,7 @@
         <v>22</v>
       </c>
       <c r="E3" s="81" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="F3" s="81" t="s">
         <v>78</v>
@@ -6587,31 +6769,31 @@
         <v>59</v>
       </c>
       <c r="H3" s="91">
-        <v>23719.5</v>
+        <v>-1</v>
       </c>
       <c r="I3" s="91">
-        <v>23718.5</v>
+        <v>-1</v>
       </c>
       <c r="J3" s="91">
-        <v>23719.75</v>
+        <v>-1</v>
       </c>
       <c r="K3" s="91">
-        <v>23719.125</v>
+        <v>-1</v>
       </c>
       <c r="L3" s="91">
-        <v>23139.75</v>
+        <v>25251.5</v>
       </c>
       <c r="M3" s="91">
-        <v>23119.5</v>
+        <v>25237</v>
       </c>
       <c r="N3" s="91">
-        <v>23743.75</v>
+        <v>25393</v>
       </c>
       <c r="O3" s="91">
-        <v>22961.5</v>
+        <v>25193</v>
       </c>
       <c r="P3" s="91">
-        <v>440628</v>
+        <v>424036</v>
       </c>
       <c r="Q3" s="91"/>
       <c r="R3" s="91"/>
@@ -6619,10 +6801,10 @@
       <c r="T3" s="91"/>
       <c r="U3" s="91"/>
       <c r="V3" s="85">
-        <v>46112.785127314812</v>
+        <v>46123.423333333332</v>
       </c>
       <c r="W3" s="81" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="X3" s="81"/>
       <c r="Y3" s="81"/>
@@ -6630,7 +6812,7 @@
     </row>
     <row r="4" spans="1:32" x14ac:dyDescent="0.4">
       <c r="A4" s="81" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B4" s="81">
         <v>770561234</v>
@@ -6642,7 +6824,7 @@
         <v>23</v>
       </c>
       <c r="E4" s="81" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="F4" s="81" t="s">
         <v>78</v>
@@ -6651,31 +6833,27 @@
         <v>59</v>
       </c>
       <c r="H4" s="91">
-        <v>2495.4</v>
+        <v>-1</v>
       </c>
       <c r="I4" s="91">
-        <v>2495.1</v>
+        <v>-1</v>
       </c>
       <c r="J4" s="91">
-        <v>2495.4</v>
+        <v>-1</v>
       </c>
       <c r="K4" s="91">
-        <v>2495.25</v>
+        <v>-1</v>
       </c>
       <c r="L4" s="91">
-        <v>2428.1999999999998</v>
+        <v>2651.6</v>
       </c>
       <c r="M4" s="91">
-        <v>2427.1999999999998</v>
-      </c>
-      <c r="N4" s="91">
-        <v>2498.1</v>
-      </c>
-      <c r="O4" s="91">
-        <v>2409.4</v>
-      </c>
+        <v>2649.7</v>
+      </c>
+      <c r="N4" s="91"/>
+      <c r="O4" s="91"/>
       <c r="P4" s="91">
-        <v>142468</v>
+        <v>0</v>
       </c>
       <c r="Q4" s="91"/>
       <c r="R4" s="91"/>
@@ -6683,10 +6861,10 @@
       <c r="T4" s="91"/>
       <c r="U4" s="91"/>
       <c r="V4" s="85">
-        <v>46112.785127314812</v>
+        <v>46123.423333333332</v>
       </c>
       <c r="W4" s="81" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="X4" s="81"/>
       <c r="Y4" s="81"/>
@@ -6694,7 +6872,7 @@
     </row>
     <row r="5" spans="1:32" x14ac:dyDescent="0.4">
       <c r="A5" s="81" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B5" s="81">
         <v>638120262</v>
@@ -6706,7 +6884,7 @@
         <v>61</v>
       </c>
       <c r="E5" s="81" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="F5" s="81" t="s">
         <v>79</v>
@@ -6715,31 +6893,27 @@
         <v>56</v>
       </c>
       <c r="H5" s="91">
-        <v>23071</v>
+        <v>23958</v>
       </c>
       <c r="I5" s="91">
-        <v>23070</v>
+        <v>-1</v>
       </c>
       <c r="J5" s="91">
-        <v>23077</v>
+        <v>-1</v>
       </c>
       <c r="K5" s="91">
-        <v>23073.5</v>
+        <v>-1</v>
       </c>
       <c r="L5" s="91">
-        <v>22687</v>
+        <v>23938</v>
       </c>
       <c r="M5" s="91">
-        <v>22521</v>
-      </c>
-      <c r="N5" s="91">
-        <v>23257</v>
-      </c>
-      <c r="O5" s="91">
-        <v>22479</v>
-      </c>
+        <v>24043</v>
+      </c>
+      <c r="N5" s="91"/>
+      <c r="O5" s="91"/>
       <c r="P5" s="91">
-        <v>25537</v>
+        <v>0</v>
       </c>
       <c r="Q5" s="91"/>
       <c r="R5" s="91"/>
@@ -6747,10 +6921,10 @@
       <c r="T5" s="91"/>
       <c r="U5" s="91"/>
       <c r="V5" s="85">
-        <v>46112.785127314812</v>
+        <v>46123.423333333332</v>
       </c>
       <c r="W5" s="81" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="X5" s="81"/>
       <c r="Y5" s="81"/>
@@ -6758,7 +6932,7 @@
     </row>
     <row r="6" spans="1:32" x14ac:dyDescent="0.4">
       <c r="A6" s="81" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="B6" s="81">
         <v>635680489</v>
@@ -6767,10 +6941,10 @@
         <v>58</v>
       </c>
       <c r="D6" s="81" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="E6" s="81" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="F6" s="81" t="s">
         <v>78</v>
@@ -6779,31 +6953,27 @@
         <v>59</v>
       </c>
       <c r="H6" s="91">
-        <v>52400</v>
+        <v>0</v>
       </c>
       <c r="I6" s="91">
-        <v>52370</v>
+        <v>0</v>
       </c>
       <c r="J6" s="91">
-        <v>52390</v>
+        <v>0</v>
       </c>
       <c r="K6" s="91">
-        <v>52380</v>
+        <v>0</v>
       </c>
       <c r="L6" s="91">
-        <v>51115</v>
+        <v>56695</v>
       </c>
       <c r="M6" s="91">
-        <v>51200</v>
-      </c>
-      <c r="N6" s="91">
-        <v>52425</v>
-      </c>
-      <c r="O6" s="91">
-        <v>50625</v>
-      </c>
+        <v>56695</v>
+      </c>
+      <c r="N6" s="91"/>
+      <c r="O6" s="91"/>
       <c r="P6" s="91">
-        <v>5796</v>
+        <v>0</v>
       </c>
       <c r="Q6" s="91"/>
       <c r="R6" s="91"/>
@@ -6811,10 +6981,10 @@
       <c r="T6" s="91"/>
       <c r="U6" s="91"/>
       <c r="V6" s="85">
-        <v>46112.785127314812</v>
+        <v>46123.423333333332</v>
       </c>
       <c r="W6" s="81" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="X6" s="81"/>
       <c r="Y6" s="81"/>
@@ -6822,7 +6992,7 @@
     </row>
     <row r="7" spans="1:32" x14ac:dyDescent="0.4">
       <c r="A7" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B7" s="1">
         <v>0</v>
@@ -6854,15 +7024,15 @@
       <c r="T7" s="93"/>
       <c r="U7" s="93"/>
       <c r="V7" s="92">
-        <v>46112.785127314812</v>
+        <v>46123.423333333332</v>
       </c>
       <c r="W7" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="8" spans="1:32" x14ac:dyDescent="0.4">
       <c r="A8" s="1" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B8" s="1">
         <v>269460069</v>
@@ -6874,7 +7044,7 @@
         <v>5</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>60</v>
@@ -6883,31 +7053,27 @@
         <v>59</v>
       </c>
       <c r="H8" s="93">
-        <v>3.0259999999999998</v>
+        <v>-1</v>
       </c>
       <c r="I8" s="93">
-        <v>3.0259999999999998</v>
+        <v>-1</v>
       </c>
       <c r="J8" s="93">
-        <v>3.028</v>
+        <v>-1</v>
       </c>
       <c r="K8" s="93">
-        <v>3.0270000000000001</v>
+        <v>-1</v>
       </c>
       <c r="L8" s="93">
-        <v>3.0350000000000001</v>
+        <v>2.8140000000000001</v>
       </c>
       <c r="M8" s="93">
-        <v>3.0449999999999999</v>
-      </c>
-      <c r="N8" s="93">
-        <v>3.11</v>
-      </c>
-      <c r="O8" s="93">
-        <v>2.9580000000000002</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N8" s="93"/>
+      <c r="O8" s="93"/>
       <c r="P8" s="93">
-        <v>36517</v>
+        <v>0</v>
       </c>
       <c r="Q8" s="93"/>
       <c r="R8" s="93"/>
@@ -6915,15 +7081,15 @@
       <c r="T8" s="93"/>
       <c r="U8" s="93"/>
       <c r="V8" s="92">
-        <v>46112.785127314812</v>
+        <v>46123.423333333332</v>
       </c>
       <c r="W8" s="1" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="9" spans="1:32" x14ac:dyDescent="0.4">
       <c r="A9" s="1" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B9" s="1">
         <v>600696533</v>
@@ -6935,7 +7101,7 @@
         <v>9</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>60</v>
@@ -6944,31 +7110,31 @@
         <v>59</v>
       </c>
       <c r="H9" s="93">
-        <v>3.0872000000000002</v>
+        <v>2.9369999999999998</v>
       </c>
       <c r="I9" s="93">
-        <v>3.0878000000000001</v>
+        <v>-1</v>
       </c>
       <c r="J9" s="93">
-        <v>3.09</v>
+        <v>-1</v>
       </c>
       <c r="K9" s="93">
-        <v>3.0888999999999998</v>
+        <v>-1</v>
       </c>
       <c r="L9" s="93">
-        <v>3.1257000000000001</v>
+        <v>2.9272</v>
       </c>
       <c r="M9" s="93">
-        <v>3.1583000000000001</v>
+        <v>0</v>
       </c>
       <c r="N9" s="93">
-        <v>3.2364000000000002</v>
+        <v>2.9855</v>
       </c>
       <c r="O9" s="93">
-        <v>3.0773000000000001</v>
+        <v>2.9125999999999999</v>
       </c>
       <c r="P9" s="93">
-        <v>25502</v>
+        <v>52332</v>
       </c>
       <c r="Q9" s="93"/>
       <c r="R9" s="93"/>
@@ -6976,15 +7142,15 @@
       <c r="T9" s="93"/>
       <c r="U9" s="93"/>
       <c r="V9" s="92">
-        <v>46112.785127314812</v>
+        <v>46123.423333333332</v>
       </c>
       <c r="W9" s="1" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="10" spans="1:32" x14ac:dyDescent="0.4">
       <c r="A10" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B10" s="1">
         <v>430360630</v>
@@ -6996,7 +7162,7 @@
         <v>26</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>80</v>
@@ -7005,31 +7171,27 @@
         <v>59</v>
       </c>
       <c r="H10" s="93">
-        <v>4669.3</v>
+        <v>-1</v>
       </c>
       <c r="I10" s="93">
-        <v>4669.2</v>
+        <v>-1</v>
       </c>
       <c r="J10" s="93">
-        <v>4669.6000000000004</v>
+        <v>-1</v>
       </c>
       <c r="K10" s="93">
-        <v>4669.3999999999996</v>
+        <v>-1</v>
       </c>
       <c r="L10" s="93">
-        <v>4557.5</v>
+        <v>4818</v>
       </c>
       <c r="M10" s="93">
-        <v>4538.8999999999996</v>
-      </c>
-      <c r="N10" s="93">
-        <v>4672</v>
-      </c>
-      <c r="O10" s="93">
-        <v>4510</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N10" s="93"/>
+      <c r="O10" s="93"/>
       <c r="P10" s="93">
-        <v>132766</v>
+        <v>0</v>
       </c>
       <c r="Q10" s="93"/>
       <c r="R10" s="93"/>
@@ -7037,15 +7199,15 @@
       <c r="T10" s="93"/>
       <c r="U10" s="93"/>
       <c r="V10" s="92">
-        <v>46112.785127314812</v>
+        <v>46123.423333333332</v>
       </c>
       <c r="W10" s="1" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="11" spans="1:32" x14ac:dyDescent="0.4">
       <c r="A11" s="1" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B11" s="1">
         <v>760200596</v>
@@ -7057,7 +7219,7 @@
         <v>27</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>80</v>
@@ -7066,31 +7228,31 @@
         <v>59</v>
       </c>
       <c r="H11" s="93">
-        <v>74.77</v>
+        <v>76.325000000000003</v>
       </c>
       <c r="I11" s="93">
-        <v>74.844999999999999</v>
+        <v>-1</v>
       </c>
       <c r="J11" s="93">
-        <v>74.88</v>
+        <v>-1</v>
       </c>
       <c r="K11" s="93">
-        <v>74.862499999999997</v>
+        <v>-1</v>
       </c>
       <c r="L11" s="93">
-        <v>70.834999999999994</v>
+        <v>76.724999999999994</v>
       </c>
       <c r="M11" s="93">
-        <v>70.680000000000007</v>
+        <v>0</v>
       </c>
       <c r="N11" s="93">
-        <v>74.77</v>
+        <v>77.245000000000005</v>
       </c>
       <c r="O11" s="93">
-        <v>69.844999999999999</v>
+        <v>75.265000000000001</v>
       </c>
       <c r="P11" s="93">
-        <v>697</v>
+        <v>581</v>
       </c>
       <c r="Q11" s="93"/>
       <c r="R11" s="93"/>
@@ -7098,15 +7260,15 @@
       <c r="T11" s="93"/>
       <c r="U11" s="93"/>
       <c r="V11" s="92">
-        <v>46112.785127314812</v>
+        <v>46123.423333333332</v>
       </c>
       <c r="W11" s="1" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="12" spans="1:32" x14ac:dyDescent="0.4">
       <c r="A12" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="B12" s="1">
         <v>473509991</v>
@@ -7118,7 +7280,7 @@
         <v>25</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>80</v>
@@ -7127,31 +7289,27 @@
         <v>59</v>
       </c>
       <c r="H12" s="93">
-        <v>5.5940000000000003</v>
+        <v>-1</v>
       </c>
       <c r="I12" s="93">
-        <v>5.5919999999999996</v>
+        <v>-1</v>
       </c>
       <c r="J12" s="93">
-        <v>5.593</v>
+        <v>-1</v>
       </c>
       <c r="K12" s="93">
-        <v>5.5924999999999994</v>
+        <v>-1</v>
       </c>
       <c r="L12" s="93">
-        <v>5.5019999999999998</v>
+        <v>5.7645</v>
       </c>
       <c r="M12" s="93">
-        <v>5.4865000000000004</v>
-      </c>
-      <c r="N12" s="93">
-        <v>5.5964999999999998</v>
-      </c>
-      <c r="O12" s="93">
-        <v>5.4645000000000001</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N12" s="93"/>
+      <c r="O12" s="93"/>
       <c r="P12" s="93">
-        <v>35917</v>
+        <v>0</v>
       </c>
       <c r="Q12" s="93"/>
       <c r="R12" s="93"/>
@@ -7159,15 +7317,15 @@
       <c r="T12" s="93"/>
       <c r="U12" s="93"/>
       <c r="V12" s="92">
-        <v>46112.785127314812</v>
+        <v>46123.423333333332</v>
       </c>
       <c r="W12" s="1" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="13" spans="1:32" x14ac:dyDescent="0.4">
       <c r="A13" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B13" s="1">
         <v>671574022</v>
@@ -7179,7 +7337,7 @@
         <v>28</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>81</v>
@@ -7188,31 +7346,27 @@
         <v>59</v>
       </c>
       <c r="H13" s="93">
-        <v>457</v>
+        <v>-100</v>
       </c>
       <c r="I13" s="93">
-        <v>457</v>
+        <v>-100</v>
       </c>
       <c r="J13" s="93">
-        <v>457.25</v>
+        <v>-100</v>
       </c>
       <c r="K13" s="93">
-        <v>457.125</v>
+        <v>-100</v>
       </c>
       <c r="L13" s="93">
-        <v>455.75</v>
+        <v>444</v>
       </c>
       <c r="M13" s="93">
-        <v>455.5</v>
-      </c>
-      <c r="N13" s="93">
-        <v>462</v>
-      </c>
-      <c r="O13" s="93">
-        <v>451.25</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N13" s="93"/>
+      <c r="O13" s="93"/>
       <c r="P13" s="93">
-        <v>196754</v>
+        <v>0</v>
       </c>
       <c r="Q13" s="93"/>
       <c r="R13" s="93"/>
@@ -7220,15 +7374,15 @@
       <c r="T13" s="93"/>
       <c r="U13" s="93"/>
       <c r="V13" s="92">
-        <v>46112.785127314812</v>
+        <v>46123.423333333332</v>
       </c>
       <c r="W13" s="1" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="14" spans="1:32" x14ac:dyDescent="0.4">
       <c r="A14" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B14" s="1">
         <v>642254817</v>
@@ -7240,7 +7394,7 @@
         <v>29</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>81</v>
@@ -7249,31 +7403,27 @@
         <v>59</v>
       </c>
       <c r="H14" s="93">
-        <v>617.5</v>
+        <v>-100</v>
       </c>
       <c r="I14" s="93">
-        <v>617.25</v>
+        <v>-100</v>
       </c>
       <c r="J14" s="93">
-        <v>617.5</v>
+        <v>-100</v>
       </c>
       <c r="K14" s="93">
-        <v>617.375</v>
+        <v>-100</v>
       </c>
       <c r="L14" s="93">
-        <v>607</v>
+        <v>574.5</v>
       </c>
       <c r="M14" s="93">
-        <v>609.75</v>
-      </c>
-      <c r="N14" s="93">
-        <v>625</v>
-      </c>
-      <c r="O14" s="93">
-        <v>605.25</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N14" s="93"/>
+      <c r="O14" s="93"/>
       <c r="P14" s="93">
-        <v>64136</v>
+        <v>0</v>
       </c>
       <c r="Q14" s="93"/>
       <c r="R14" s="93"/>
@@ -7281,15 +7431,15 @@
       <c r="T14" s="93"/>
       <c r="U14" s="93"/>
       <c r="V14" s="92">
-        <v>46112.785127314812</v>
+        <v>46123.423333333332</v>
       </c>
       <c r="W14" s="1" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="15" spans="1:32" x14ac:dyDescent="0.4">
       <c r="A15" s="1" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B15" s="1">
         <v>665643569</v>
@@ -7301,7 +7451,7 @@
         <v>31</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>81</v>
@@ -7310,31 +7460,27 @@
         <v>59</v>
       </c>
       <c r="H15" s="93">
-        <v>1169.25</v>
+        <v>-100</v>
       </c>
       <c r="I15" s="93">
-        <v>1169</v>
+        <v>-100</v>
       </c>
       <c r="J15" s="93">
-        <v>1169.25</v>
+        <v>-100</v>
       </c>
       <c r="K15" s="93">
-        <v>1169.125</v>
+        <v>-100</v>
       </c>
       <c r="L15" s="93">
-        <v>1159.75</v>
+        <v>1165.25</v>
       </c>
       <c r="M15" s="93">
-        <v>1159</v>
-      </c>
-      <c r="N15" s="93">
-        <v>1175.25</v>
-      </c>
-      <c r="O15" s="93">
-        <v>1156</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N15" s="93"/>
+      <c r="O15" s="93"/>
       <c r="P15" s="93">
-        <v>79841</v>
+        <v>0</v>
       </c>
       <c r="Q15" s="93"/>
       <c r="R15" s="93"/>
@@ -7342,15 +7488,15 @@
       <c r="T15" s="93"/>
       <c r="U15" s="93"/>
       <c r="V15" s="92">
-        <v>46112.785127314812</v>
+        <v>46123.423333333332</v>
       </c>
       <c r="W15" s="1" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="16" spans="1:32" x14ac:dyDescent="0.4">
       <c r="A16" s="1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B16" s="1">
         <v>634760175</v>
@@ -7362,7 +7508,7 @@
         <v>32</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>63</v>
@@ -7371,31 +7517,31 @@
         <v>59</v>
       </c>
       <c r="H16" s="93">
-        <v>15.66</v>
+        <v>13.76</v>
       </c>
       <c r="I16" s="93">
-        <v>15.65</v>
+        <v>-100</v>
       </c>
       <c r="J16" s="93">
-        <v>15.67</v>
+        <v>-100</v>
       </c>
       <c r="K16" s="93">
-        <v>15.66</v>
+        <v>-100</v>
       </c>
       <c r="L16" s="93">
-        <v>15.55</v>
+        <v>13.92</v>
       </c>
       <c r="M16" s="93">
-        <v>15.56</v>
+        <v>0</v>
       </c>
       <c r="N16" s="93">
-        <v>15.74</v>
+        <v>14.06</v>
       </c>
       <c r="O16" s="93">
-        <v>15.12</v>
+        <v>13.71</v>
       </c>
       <c r="P16" s="93">
-        <v>63264</v>
+        <v>150962</v>
       </c>
       <c r="Q16" s="93"/>
       <c r="R16" s="93"/>
@@ -7403,15 +7549,15 @@
       <c r="T16" s="93"/>
       <c r="U16" s="93"/>
       <c r="V16" s="92">
-        <v>46112.785127314812</v>
+        <v>46123.423333333332</v>
       </c>
       <c r="W16" s="1" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="17" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A17" s="1" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B17" s="1">
         <v>634760204</v>
@@ -7423,7 +7569,7 @@
         <v>33</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>63</v>
@@ -7432,31 +7578,31 @@
         <v>59</v>
       </c>
       <c r="H17" s="93">
-        <v>298.75</v>
+        <v>300.64999999999998</v>
       </c>
       <c r="I17" s="93">
-        <v>298.64999999999998</v>
+        <v>-100</v>
       </c>
       <c r="J17" s="93">
-        <v>298.8</v>
+        <v>-100</v>
       </c>
       <c r="K17" s="93">
-        <v>298.72500000000002</v>
+        <v>-100</v>
       </c>
       <c r="L17" s="93">
-        <v>292.55</v>
+        <v>293.7</v>
       </c>
       <c r="M17" s="93">
-        <v>294.39999999999998</v>
+        <v>0</v>
       </c>
       <c r="N17" s="93">
-        <v>299</v>
+        <v>301.25</v>
       </c>
       <c r="O17" s="93">
-        <v>292.8</v>
+        <v>291.8</v>
       </c>
       <c r="P17" s="93">
-        <v>13253</v>
+        <v>21696</v>
       </c>
       <c r="Q17" s="93"/>
       <c r="R17" s="93"/>
@@ -7464,15 +7610,15 @@
       <c r="T17" s="93"/>
       <c r="U17" s="93"/>
       <c r="V17" s="92">
-        <v>46112.785127314812</v>
+        <v>46123.423333333332</v>
       </c>
       <c r="W17" s="1" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="18" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A18" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B18" s="1">
         <v>707621000</v>
@@ -7484,7 +7630,7 @@
         <v>34</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>63</v>
@@ -7493,31 +7639,31 @@
         <v>59</v>
       </c>
       <c r="H18" s="93">
-        <v>3285</v>
+        <v>3242</v>
       </c>
       <c r="I18" s="93">
-        <v>3284</v>
+        <v>-1</v>
       </c>
       <c r="J18" s="93">
-        <v>3285</v>
+        <v>-1</v>
       </c>
       <c r="K18" s="93">
-        <v>3284.5</v>
+        <v>-1</v>
       </c>
       <c r="L18" s="93">
-        <v>3155</v>
+        <v>3162</v>
       </c>
       <c r="M18" s="93">
-        <v>3151</v>
+        <v>0</v>
       </c>
       <c r="N18" s="93">
-        <v>3331</v>
+        <v>3261</v>
       </c>
       <c r="O18" s="93">
-        <v>3140</v>
+        <v>3162</v>
       </c>
       <c r="P18" s="93">
-        <v>16944</v>
+        <v>16350</v>
       </c>
       <c r="Q18" s="93"/>
       <c r="R18" s="93"/>
@@ -7525,15 +7671,15 @@
       <c r="T18" s="93"/>
       <c r="U18" s="93"/>
       <c r="V18" s="92">
-        <v>46112.785127314812</v>
+        <v>46123.423333333332</v>
       </c>
       <c r="W18" s="1" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="19" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A19" s="1" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B19" s="1">
         <v>634760245</v>
@@ -7545,7 +7691,7 @@
         <v>64</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>63</v>
@@ -7554,31 +7700,31 @@
         <v>59</v>
       </c>
       <c r="H19" s="93">
-        <v>70.290000000000006</v>
+        <v>73.260000000000005</v>
       </c>
       <c r="I19" s="93">
-        <v>70.27</v>
+        <v>-100</v>
       </c>
       <c r="J19" s="93">
-        <v>70.290000000000006</v>
+        <v>-100</v>
       </c>
       <c r="K19" s="93">
-        <v>70.28</v>
+        <v>-100</v>
       </c>
       <c r="L19" s="93">
-        <v>70.19</v>
+        <v>73.260000000000005</v>
       </c>
       <c r="M19" s="93">
-        <v>70.09</v>
+        <v>0</v>
       </c>
       <c r="N19" s="93">
-        <v>71.38</v>
+        <v>73.64</v>
       </c>
       <c r="O19" s="93">
-        <v>69.91</v>
+        <v>72.709999999999994</v>
       </c>
       <c r="P19" s="93">
-        <v>37866</v>
+        <v>39193</v>
       </c>
       <c r="Q19" s="93"/>
       <c r="R19" s="93"/>
@@ -7586,10 +7732,10 @@
       <c r="T19" s="93"/>
       <c r="U19" s="93"/>
       <c r="V19" s="92">
-        <v>46112.785127314812</v>
+        <v>46123.423333333332</v>
       </c>
       <c r="W19" s="1" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="20" spans="1:23" x14ac:dyDescent="0.4">
@@ -7606,7 +7752,7 @@
         <v>35</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>78</v>
@@ -7615,31 +7761,27 @@
         <v>59</v>
       </c>
       <c r="H20" s="93">
-        <v>241.47499999999999</v>
+        <v>-100</v>
       </c>
       <c r="I20" s="93">
-        <v>241.45</v>
+        <v>-100</v>
       </c>
       <c r="J20" s="93">
-        <v>241.5</v>
+        <v>-100</v>
       </c>
       <c r="K20" s="93">
-        <v>241.47499999999999</v>
+        <v>-100</v>
       </c>
       <c r="L20" s="93">
-        <v>239.55</v>
+        <v>249.77500000000001</v>
       </c>
       <c r="M20" s="93">
-        <v>239.35</v>
-      </c>
-      <c r="N20" s="93">
-        <v>241.5</v>
-      </c>
-      <c r="O20" s="93">
-        <v>239.35</v>
-      </c>
+        <v>250.05</v>
+      </c>
+      <c r="N20" s="93"/>
+      <c r="O20" s="93"/>
       <c r="P20" s="93">
-        <v>6301</v>
+        <v>0</v>
       </c>
       <c r="Q20" s="93"/>
       <c r="R20" s="93"/>
@@ -7647,10 +7789,10 @@
       <c r="T20" s="93"/>
       <c r="U20" s="93"/>
       <c r="V20" s="92">
-        <v>46112.785127314812</v>
+        <v>46123.423333333332</v>
       </c>
       <c r="W20" s="1" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="21" spans="1:23" x14ac:dyDescent="0.4">
@@ -7667,7 +7809,7 @@
         <v>36</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>78</v>
@@ -7676,31 +7818,27 @@
         <v>59</v>
       </c>
       <c r="H21" s="93">
-        <v>365.7</v>
+        <v>-100</v>
       </c>
       <c r="I21" s="93">
-        <v>365.5</v>
+        <v>-100</v>
       </c>
       <c r="J21" s="93">
-        <v>365.6</v>
+        <v>-100</v>
       </c>
       <c r="K21" s="93">
-        <v>365.55</v>
+        <v>-100</v>
       </c>
       <c r="L21" s="93">
-        <v>361.32499999999999</v>
+        <v>370.42500000000001</v>
       </c>
       <c r="M21" s="93">
-        <v>361.32499999999999</v>
-      </c>
-      <c r="N21" s="93">
-        <v>365.7</v>
-      </c>
-      <c r="O21" s="93">
-        <v>361.32499999999999</v>
-      </c>
+        <v>371.5</v>
+      </c>
+      <c r="N21" s="93"/>
+      <c r="O21" s="93"/>
       <c r="P21" s="93">
-        <v>6245</v>
+        <v>0</v>
       </c>
       <c r="Q21" s="93"/>
       <c r="R21" s="93"/>
@@ -7708,15 +7846,15 @@
       <c r="T21" s="93"/>
       <c r="U21" s="93"/>
       <c r="V21" s="92">
-        <v>46112.785127314812</v>
+        <v>46123.423333333332</v>
       </c>
       <c r="W21" s="1" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="22" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A22" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B22" s="1">
         <v>735014937</v>
@@ -7728,7 +7866,7 @@
         <v>37</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>78</v>
@@ -7737,31 +7875,31 @@
         <v>59</v>
       </c>
       <c r="H22" s="93">
-        <v>90.474999999999994</v>
+        <v>90.625</v>
       </c>
       <c r="I22" s="93">
-        <v>90.45</v>
+        <v>-100</v>
       </c>
       <c r="J22" s="93">
+        <v>-100</v>
+      </c>
+      <c r="K22" s="93">
+        <v>-100</v>
+      </c>
+      <c r="L22" s="93">
+        <v>90.674999999999997</v>
+      </c>
+      <c r="M22" s="93">
         <v>90.5</v>
       </c>
-      <c r="K22" s="93">
-        <v>90.474999999999994</v>
-      </c>
-      <c r="L22" s="93">
-        <v>90.474999999999994</v>
-      </c>
-      <c r="M22" s="93">
-        <v>90.674999999999997</v>
-      </c>
       <c r="N22" s="93">
-        <v>90.924999999999997</v>
+        <v>90.775000000000006</v>
       </c>
       <c r="O22" s="93">
-        <v>90.35</v>
+        <v>90.424999999999997</v>
       </c>
       <c r="P22" s="93">
-        <v>3680</v>
+        <v>3304</v>
       </c>
       <c r="Q22" s="93"/>
       <c r="R22" s="93"/>
@@ -7769,15 +7907,15 @@
       <c r="T22" s="93"/>
       <c r="U22" s="93"/>
       <c r="V22" s="92">
-        <v>46112.785127314812</v>
+        <v>46123.423333333332</v>
       </c>
       <c r="W22" s="1" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="23" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A23" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B23" s="1">
         <v>792232100</v>
@@ -7789,7 +7927,7 @@
         <v>38</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>63</v>
@@ -7798,31 +7936,31 @@
         <v>59</v>
       </c>
       <c r="H23" s="93">
-        <v>99.954999999999998</v>
+        <v>98.484999999999999</v>
       </c>
       <c r="I23" s="93">
-        <v>99.95</v>
+        <v>-1</v>
       </c>
       <c r="J23" s="93">
-        <v>99.954999999999998</v>
+        <v>-1</v>
       </c>
       <c r="K23" s="93">
-        <v>99.952500000000001</v>
+        <v>-1</v>
       </c>
       <c r="L23" s="93">
-        <v>100.355</v>
+        <v>98.61</v>
       </c>
       <c r="M23" s="93">
-        <v>100.43</v>
+        <v>0</v>
       </c>
       <c r="N23" s="93">
-        <v>100.5</v>
+        <v>98.795000000000002</v>
       </c>
       <c r="O23" s="93">
-        <v>99.775000000000006</v>
+        <v>98.13</v>
       </c>
       <c r="P23" s="93">
-        <v>27155</v>
+        <v>20679</v>
       </c>
       <c r="Q23" s="93"/>
       <c r="R23" s="93"/>
@@ -7830,15 +7968,15 @@
       <c r="T23" s="93"/>
       <c r="U23" s="93"/>
       <c r="V23" s="92">
-        <v>46112.785127314812</v>
+        <v>46123.423333333332</v>
       </c>
       <c r="W23" s="1" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="24" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A24" s="1" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B24" s="1">
         <v>496647057</v>
@@ -7850,7 +7988,7 @@
         <v>56</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>78</v>
@@ -7859,31 +7997,27 @@
         <v>59</v>
       </c>
       <c r="H24" s="93">
-        <v>1.1586000000000001</v>
+        <v>-1</v>
       </c>
       <c r="I24" s="93">
-        <v>1.15855</v>
+        <v>-1</v>
       </c>
       <c r="J24" s="93">
-        <v>1.1586000000000001</v>
+        <v>-1</v>
       </c>
       <c r="K24" s="93">
-        <v>1.1585749999999999</v>
+        <v>-1</v>
       </c>
       <c r="L24" s="93">
-        <v>1.1503000000000001</v>
+        <v>1.1735500000000001</v>
       </c>
       <c r="M24" s="93">
-        <v>1.1505000000000001</v>
-      </c>
-      <c r="N24" s="93">
-        <v>1.1590499999999999</v>
-      </c>
-      <c r="O24" s="93">
-        <v>1.1488</v>
-      </c>
+        <v>1.1736</v>
+      </c>
+      <c r="N24" s="93"/>
+      <c r="O24" s="93"/>
       <c r="P24" s="93">
-        <v>204276</v>
+        <v>0</v>
       </c>
       <c r="Q24" s="93"/>
       <c r="R24" s="93"/>
@@ -7891,15 +8025,15 @@
       <c r="T24" s="93"/>
       <c r="U24" s="93"/>
       <c r="V24" s="92">
-        <v>46112.785127314812</v>
+        <v>46123.423333333332</v>
       </c>
       <c r="W24" s="1" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="25" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A25" s="1" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="B25" s="1">
         <v>496647091</v>
@@ -7911,7 +8045,7 @@
         <v>73</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>78</v>
@@ -7920,31 +8054,27 @@
         <v>59</v>
       </c>
       <c r="H25" s="93">
-        <v>1.3211999999999999</v>
+        <v>-1</v>
       </c>
       <c r="I25" s="93">
-        <v>1.3210999999999999</v>
+        <v>-1</v>
       </c>
       <c r="J25" s="93">
-        <v>1.3211999999999999</v>
+        <v>-1</v>
       </c>
       <c r="K25" s="93">
-        <v>1.3211499999999998</v>
+        <v>-1</v>
       </c>
       <c r="L25" s="93">
-        <v>1.3182</v>
+        <v>1.3431999999999999</v>
       </c>
       <c r="M25" s="93">
-        <v>1.3180000000000001</v>
-      </c>
-      <c r="N25" s="93">
-        <v>1.3267</v>
-      </c>
-      <c r="O25" s="93">
-        <v>1.3156000000000001</v>
-      </c>
+        <v>1.3435999999999999</v>
+      </c>
+      <c r="N25" s="93"/>
+      <c r="O25" s="93"/>
       <c r="P25" s="93">
-        <v>120050</v>
+        <v>0</v>
       </c>
       <c r="Q25" s="93"/>
       <c r="R25" s="93"/>
@@ -7952,15 +8082,15 @@
       <c r="T25" s="93"/>
       <c r="U25" s="93"/>
       <c r="V25" s="92">
-        <v>46112.785127314812</v>
+        <v>46123.423333333332</v>
       </c>
       <c r="W25" s="1" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="26" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A26" s="1" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B26" s="1">
         <v>496647108</v>
@@ -7972,7 +8102,7 @@
         <v>57</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>78</v>
@@ -7981,31 +8111,27 @@
         <v>59</v>
       </c>
       <c r="H26" s="93">
-        <v>6.3309999999999998E-3</v>
+        <v>-1</v>
       </c>
       <c r="I26" s="93">
-        <v>6.3305000000000002E-3</v>
+        <v>-1</v>
       </c>
       <c r="J26" s="93">
-        <v>6.3315000000000003E-3</v>
+        <v>-1</v>
       </c>
       <c r="K26" s="93">
-        <v>6.3309999999999998E-3</v>
+        <v>-1</v>
       </c>
       <c r="L26" s="93">
-        <v>6.3049999999999998E-3</v>
+        <v>6.3229999999999996E-3</v>
       </c>
       <c r="M26" s="93">
-        <v>6.3E-3</v>
-      </c>
-      <c r="N26" s="93">
-        <v>6.3379999999999999E-3</v>
-      </c>
-      <c r="O26" s="93">
-        <v>6.2905000000000001E-3</v>
-      </c>
+        <v>6.3249999999999999E-3</v>
+      </c>
+      <c r="N26" s="93"/>
+      <c r="O26" s="93"/>
       <c r="P26" s="93">
-        <v>121507</v>
+        <v>0</v>
       </c>
       <c r="Q26" s="93"/>
       <c r="R26" s="93"/>
@@ -8013,15 +8139,15 @@
       <c r="T26" s="93"/>
       <c r="U26" s="93"/>
       <c r="V26" s="92">
-        <v>46112.785127314812</v>
+        <v>46123.423333333332</v>
       </c>
       <c r="W26" s="1" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="27" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A27" s="1" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B27" s="1">
         <v>496879111</v>
@@ -8033,7 +8159,7 @@
         <v>75</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>78</v>
@@ -8042,31 +8168,27 @@
         <v>59</v>
       </c>
       <c r="H27" s="93">
-        <v>0.71994999999999998</v>
+        <v>-1</v>
       </c>
       <c r="I27" s="93">
-        <v>0.71989999999999998</v>
+        <v>-1</v>
       </c>
       <c r="J27" s="93">
-        <v>0.71994999999999998</v>
+        <v>-1</v>
       </c>
       <c r="K27" s="93">
-        <v>0.71992499999999993</v>
+        <v>-1</v>
       </c>
       <c r="L27" s="93">
-        <v>0.72040000000000004</v>
+        <v>0.72575000000000001</v>
       </c>
       <c r="M27" s="93">
-        <v>0.72045000000000003</v>
-      </c>
-      <c r="N27" s="93">
-        <v>0.72089999999999999</v>
-      </c>
-      <c r="O27" s="93">
-        <v>0.71835000000000004</v>
-      </c>
+        <v>0.72570000000000001</v>
+      </c>
+      <c r="N27" s="93"/>
+      <c r="O27" s="93"/>
       <c r="P27" s="93">
-        <v>60110</v>
+        <v>0</v>
       </c>
       <c r="Q27" s="93"/>
       <c r="R27" s="93"/>
@@ -8074,15 +8196,15 @@
       <c r="T27" s="93"/>
       <c r="U27" s="93"/>
       <c r="V27" s="92">
-        <v>46112.785127314812</v>
+        <v>46123.423333333332</v>
       </c>
       <c r="W27" s="1" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="28" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A28" s="1" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B28" s="1">
         <v>496647009</v>
@@ -8094,7 +8216,7 @@
         <v>77</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>78</v>
@@ -8103,31 +8225,27 @@
         <v>59</v>
       </c>
       <c r="H28" s="93">
-        <v>0.68740000000000001</v>
+        <v>-1</v>
       </c>
       <c r="I28" s="93">
-        <v>0.68735000000000002</v>
+        <v>-1</v>
       </c>
       <c r="J28" s="93">
-        <v>0.68740000000000001</v>
+        <v>-1</v>
       </c>
       <c r="K28" s="93">
-        <v>0.68737500000000007</v>
+        <v>-1</v>
       </c>
       <c r="L28" s="93">
-        <v>0.68445</v>
+        <v>0.70720000000000005</v>
       </c>
       <c r="M28" s="93">
-        <v>0.6845</v>
-      </c>
-      <c r="N28" s="93">
-        <v>0.68830000000000002</v>
-      </c>
-      <c r="O28" s="93">
-        <v>0.68264999999999998</v>
-      </c>
+        <v>0.70765</v>
+      </c>
+      <c r="N28" s="93"/>
+      <c r="O28" s="93"/>
       <c r="P28" s="93">
-        <v>127916</v>
+        <v>0</v>
       </c>
       <c r="Q28" s="93"/>
       <c r="R28" s="93"/>
@@ -8135,15 +8253,15 @@
       <c r="T28" s="93"/>
       <c r="U28" s="93"/>
       <c r="V28" s="92">
-        <v>46112.785127314812</v>
+        <v>46123.423333333332</v>
       </c>
       <c r="W28" s="1" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="29" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A29" s="1" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="B29" s="1">
         <v>815824224</v>
@@ -8155,7 +8273,7 @@
         <v>46</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>81</v>
@@ -8164,31 +8282,27 @@
         <v>59</v>
       </c>
       <c r="H29" s="93">
-        <v>114</v>
+        <v>-1</v>
       </c>
       <c r="I29" s="93">
-        <v>113.9375</v>
+        <v>-1</v>
       </c>
       <c r="J29" s="93">
-        <v>113.96875</v>
+        <v>-1</v>
       </c>
       <c r="K29" s="93">
-        <v>113.953125</v>
+        <v>-1</v>
       </c>
       <c r="L29" s="93">
-        <v>113.5</v>
+        <v>114.125</v>
       </c>
       <c r="M29" s="93">
-        <v>113.40625</v>
-      </c>
-      <c r="N29" s="93">
-        <v>114.0625</v>
-      </c>
-      <c r="O29" s="93">
-        <v>113.21875</v>
-      </c>
+        <v>114.3125</v>
+      </c>
+      <c r="N29" s="93"/>
+      <c r="O29" s="93"/>
       <c r="P29" s="93">
-        <v>313343</v>
+        <v>0</v>
       </c>
       <c r="Q29" s="93"/>
       <c r="R29" s="93"/>
@@ -8196,15 +8310,15 @@
       <c r="T29" s="93"/>
       <c r="U29" s="93"/>
       <c r="V29" s="92">
-        <v>46112.785127314812</v>
+        <v>46123.423333333332</v>
       </c>
       <c r="W29" s="1" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="30" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A30" s="1" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="B30" s="1">
         <v>815824229</v>
@@ -8216,7 +8330,7 @@
         <v>66</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>81</v>
@@ -8225,31 +8339,27 @@
         <v>59</v>
       </c>
       <c r="H30" s="93">
-        <v>111.15625</v>
+        <v>-1</v>
       </c>
       <c r="I30" s="93">
-        <v>111.15625</v>
+        <v>-1</v>
       </c>
       <c r="J30" s="93">
-        <v>111.171875</v>
+        <v>-1</v>
       </c>
       <c r="K30" s="93">
-        <v>111.1640625</v>
+        <v>-1</v>
       </c>
       <c r="L30" s="93">
-        <v>110.8125</v>
+        <v>111.234375</v>
       </c>
       <c r="M30" s="93">
-        <v>110.765625</v>
-      </c>
-      <c r="N30" s="93">
-        <v>111.21875</v>
-      </c>
-      <c r="O30" s="93">
-        <v>110.703125</v>
-      </c>
+        <v>111.34375</v>
+      </c>
+      <c r="N30" s="93"/>
+      <c r="O30" s="93"/>
       <c r="P30" s="93">
-        <v>1573402</v>
+        <v>0</v>
       </c>
       <c r="Q30" s="93"/>
       <c r="R30" s="93"/>
@@ -8257,15 +8367,15 @@
       <c r="T30" s="93"/>
       <c r="U30" s="93"/>
       <c r="V30" s="92">
-        <v>46112.785127314812</v>
+        <v>46123.423333333332</v>
       </c>
       <c r="W30" s="1" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="31" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A31" s="1" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B31" s="1">
         <v>813041669</v>
@@ -8277,7 +8387,7 @@
         <v>68</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>79</v>
@@ -8285,32 +8395,24 @@
       <c r="G31" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="H31" s="93">
-        <v>125.85</v>
-      </c>
+      <c r="H31" s="93"/>
       <c r="I31" s="93">
-        <v>125.84</v>
+        <v>-1</v>
       </c>
       <c r="J31" s="93">
-        <v>125.85</v>
+        <v>-1</v>
       </c>
       <c r="K31" s="93">
-        <v>125.845</v>
+        <v>-1</v>
       </c>
       <c r="L31" s="93">
-        <v>125.18</v>
-      </c>
-      <c r="M31" s="93">
-        <v>124.96</v>
-      </c>
-      <c r="N31" s="93">
-        <v>125.95</v>
-      </c>
-      <c r="O31" s="93">
-        <v>124.9</v>
-      </c>
+        <v>125.42</v>
+      </c>
+      <c r="M31" s="93"/>
+      <c r="N31" s="93"/>
+      <c r="O31" s="93"/>
       <c r="P31" s="93">
-        <v>1405787</v>
+        <v>0</v>
       </c>
       <c r="Q31" s="93"/>
       <c r="R31" s="93"/>
@@ -8318,15 +8420,15 @@
       <c r="T31" s="93"/>
       <c r="U31" s="93"/>
       <c r="V31" s="92">
-        <v>46112.785127314812</v>
+        <v>46123.423333333332</v>
       </c>
       <c r="W31" s="1" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="32" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A32" s="1" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B32" s="1">
         <v>813041681</v>
@@ -8338,7 +8440,7 @@
         <v>70</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>79</v>
@@ -8346,32 +8448,24 @@
       <c r="G32" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="H32" s="93">
-        <v>110.82</v>
-      </c>
+      <c r="H32" s="93"/>
       <c r="I32" s="93">
-        <v>110.82</v>
+        <v>-1</v>
       </c>
       <c r="J32" s="93">
-        <v>110.84</v>
+        <v>-1</v>
       </c>
       <c r="K32" s="93">
-        <v>110.83</v>
+        <v>-1</v>
       </c>
       <c r="L32" s="93">
-        <v>109.54</v>
-      </c>
-      <c r="M32" s="93">
-        <v>109.06</v>
-      </c>
-      <c r="N32" s="93">
-        <v>110.98</v>
-      </c>
-      <c r="O32" s="93">
-        <v>109.04</v>
-      </c>
+        <v>108.82</v>
+      </c>
+      <c r="M32" s="93"/>
+      <c r="N32" s="93"/>
+      <c r="O32" s="93"/>
       <c r="P32" s="93">
-        <v>261169</v>
+        <v>0</v>
       </c>
       <c r="Q32" s="93"/>
       <c r="R32" s="93"/>
@@ -8379,15 +8473,15 @@
       <c r="T32" s="93"/>
       <c r="U32" s="93"/>
       <c r="V32" s="92">
-        <v>46112.785127314812</v>
+        <v>46123.423333333332</v>
       </c>
       <c r="W32" s="1" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="33" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A33" s="1" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B33" s="1">
         <v>813041663</v>
@@ -8399,7 +8493,7 @@
         <v>47</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>79</v>
@@ -8407,32 +8501,24 @@
       <c r="G33" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="H33" s="93">
-        <v>116.99</v>
-      </c>
+      <c r="H33" s="93"/>
       <c r="I33" s="93">
-        <v>116.98</v>
+        <v>-1</v>
       </c>
       <c r="J33" s="93">
-        <v>116.99</v>
+        <v>-1</v>
       </c>
       <c r="K33" s="93">
-        <v>116.985</v>
+        <v>-1</v>
       </c>
       <c r="L33" s="93">
-        <v>115.63</v>
-      </c>
-      <c r="M33" s="93">
-        <v>115.89</v>
-      </c>
-      <c r="N33" s="93">
-        <v>117.23</v>
-      </c>
-      <c r="O33" s="93">
-        <v>115.49</v>
-      </c>
+        <v>117.34</v>
+      </c>
+      <c r="M33" s="93"/>
+      <c r="N33" s="93"/>
+      <c r="O33" s="93"/>
       <c r="P33" s="93">
-        <v>480974</v>
+        <v>0</v>
       </c>
       <c r="Q33" s="93"/>
       <c r="R33" s="93"/>
@@ -8440,145 +8526,115 @@
       <c r="T33" s="93"/>
       <c r="U33" s="93"/>
       <c r="V33" s="92">
-        <v>46112.785127314812</v>
+        <v>46123.423333333332</v>
       </c>
       <c r="W33" s="1" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="34" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A34" s="1" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B34" s="1">
         <v>479624278</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D34" s="1" t="s">
         <v>44</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="G34" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="H34" s="93">
-        <v>67599</v>
-      </c>
-      <c r="I34" s="93">
-        <v>67599</v>
-      </c>
-      <c r="J34" s="93">
-        <v>67599.25</v>
-      </c>
-      <c r="K34" s="93">
-        <v>67599.125</v>
-      </c>
-      <c r="L34" s="93">
-        <v>66475.75</v>
-      </c>
+      <c r="H34" s="93"/>
+      <c r="I34" s="93"/>
+      <c r="J34" s="93"/>
+      <c r="K34" s="93"/>
+      <c r="L34" s="93"/>
       <c r="M34" s="93"/>
-      <c r="N34" s="93">
-        <v>68361.5</v>
-      </c>
-      <c r="O34" s="93">
-        <v>65670</v>
-      </c>
-      <c r="P34" s="93">
-        <v>249.85063435000001</v>
-      </c>
+      <c r="N34" s="93"/>
+      <c r="O34" s="93"/>
+      <c r="P34" s="93"/>
       <c r="Q34" s="93"/>
       <c r="R34" s="93"/>
       <c r="S34" s="93"/>
       <c r="T34" s="93"/>
       <c r="U34" s="93"/>
       <c r="V34" s="92">
-        <v>46112.785127314812</v>
+        <v>46123.423333333332</v>
       </c>
       <c r="W34" s="1" t="s">
-        <v>261</v>
+        <v>314</v>
       </c>
     </row>
     <row r="35" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A35" s="1" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B35" s="1">
         <v>495759171</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D35" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="G35" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="H35" s="93">
-        <v>2091</v>
-      </c>
-      <c r="I35" s="93">
-        <v>2090.9499999999998</v>
-      </c>
-      <c r="J35" s="93">
-        <v>2091</v>
-      </c>
-      <c r="K35" s="93">
-        <v>2090.9749999999999</v>
-      </c>
+      <c r="H35" s="93"/>
+      <c r="I35" s="93"/>
+      <c r="J35" s="93"/>
+      <c r="K35" s="93"/>
       <c r="L35" s="93">
-        <v>2021.6</v>
+        <v>2245</v>
       </c>
       <c r="M35" s="93"/>
-      <c r="N35" s="93">
-        <v>2105.5500000000002</v>
-      </c>
-      <c r="O35" s="93">
-        <v>2011.05</v>
-      </c>
-      <c r="P35" s="93">
-        <v>2294.0708261999998</v>
-      </c>
+      <c r="N35" s="93"/>
+      <c r="O35" s="93"/>
+      <c r="P35" s="93"/>
       <c r="Q35" s="93"/>
       <c r="R35" s="93"/>
       <c r="S35" s="93"/>
       <c r="T35" s="93"/>
       <c r="U35" s="93"/>
       <c r="V35" s="92">
-        <v>46112.785127314812</v>
+        <v>46123.423333333332</v>
       </c>
       <c r="W35" s="1" t="s">
-        <v>261</v>
+        <v>314</v>
       </c>
     </row>
     <row r="36" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A36" s="1" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="B36" s="1">
         <v>297507399</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="D36" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>60</v>
@@ -8587,67 +8643,67 @@
         <v>59</v>
       </c>
       <c r="H36" s="93">
-        <v>2.5</v>
+        <v>1.77</v>
       </c>
       <c r="I36" s="93">
-        <v>2.46</v>
+        <v>-1</v>
       </c>
       <c r="J36" s="93">
-        <v>2.6</v>
+        <v>-1</v>
       </c>
       <c r="K36" s="93">
-        <v>2.5300000000000002</v>
+        <v>-1</v>
       </c>
       <c r="L36" s="93">
-        <v>2.4300000000000002</v>
+        <v>2.0099999999999998</v>
       </c>
       <c r="M36" s="93"/>
       <c r="N36" s="93">
-        <v>2.6</v>
+        <v>1.86</v>
       </c>
       <c r="O36" s="93">
-        <v>2.09</v>
+        <v>1.52</v>
       </c>
       <c r="P36" s="93">
-        <v>1344</v>
+        <v>1670</v>
       </c>
       <c r="Q36" s="93">
-        <v>0.78315342735124049</v>
+        <v>0.65885160249112995</v>
       </c>
       <c r="R36" s="93">
-        <v>-0.1627746896519954</v>
+        <v>-0.16528736663356416</v>
       </c>
       <c r="S36" s="93">
-        <v>9.6077069961762688E-3</v>
+        <v>1.3800911666443877E-2</v>
       </c>
       <c r="T36" s="93">
-        <v>7.6835428065668232E-2</v>
+        <v>6.5973985374787825E-2</v>
       </c>
       <c r="U36" s="93">
-        <v>-6.8411659553771376E-2</v>
+        <v>-6.462134828507704E-2</v>
       </c>
       <c r="V36" s="92">
-        <v>46112.785127314812</v>
+        <v>46123.423333333332</v>
       </c>
       <c r="W36" s="1" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="37" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A37" s="1" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="B37" s="1">
         <v>297509218</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="D37" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>60</v>
@@ -8656,85 +8712,185 @@
         <v>59</v>
       </c>
       <c r="H37" s="93">
-        <v>0.3</v>
+        <v>0.16</v>
       </c>
       <c r="I37" s="93">
-        <v>0.28999999999999998</v>
+        <v>-1</v>
       </c>
       <c r="J37" s="93">
-        <v>0.35</v>
+        <v>-1</v>
       </c>
       <c r="K37" s="93">
-        <v>0.31999999999999995</v>
+        <v>-1</v>
       </c>
       <c r="L37" s="93">
-        <v>0.35</v>
+        <v>0.19</v>
       </c>
       <c r="M37" s="93"/>
       <c r="N37" s="93">
-        <v>0.31</v>
+        <v>0.18</v>
       </c>
       <c r="O37" s="93">
-        <v>0.3</v>
+        <v>0.16</v>
       </c>
       <c r="P37" s="93">
-        <v>71</v>
+        <v>1547</v>
       </c>
       <c r="Q37" s="93">
-        <v>0.87363521458481075</v>
+        <v>0.80432662636800079</v>
       </c>
       <c r="R37" s="93">
-        <v>-2.6208574988033508E-2</v>
+        <v>-1.8377543468778772E-2</v>
       </c>
       <c r="S37" s="93">
-        <v>2.1267667614732338E-3</v>
+        <v>2.0303007492177426E-3</v>
       </c>
       <c r="T37" s="93">
-        <v>2.3046552400468656E-2</v>
+        <v>1.3747560853528767E-2</v>
       </c>
       <c r="U37" s="93">
-        <v>-2.2948688044132859E-2</v>
+        <v>-1.6602630535653029E-2</v>
       </c>
       <c r="V37" s="92">
-        <v>46112.785127314812</v>
+        <v>46123.423333333332</v>
       </c>
       <c r="W37" s="1" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="38" spans="1:23" x14ac:dyDescent="0.4">
-      <c r="H38" s="93"/>
-      <c r="I38" s="93"/>
-      <c r="J38" s="93"/>
-      <c r="K38" s="93"/>
-      <c r="L38" s="93"/>
+      <c r="A38" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="B38" s="1">
+        <v>766128347</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="H38" s="93">
+        <v>17.5</v>
+      </c>
+      <c r="I38" s="93">
+        <v>-1</v>
+      </c>
+      <c r="J38" s="93">
+        <v>-1</v>
+      </c>
+      <c r="K38" s="93">
+        <v>-1</v>
+      </c>
+      <c r="L38" s="93">
+        <v>22.7</v>
+      </c>
       <c r="M38" s="93"/>
-      <c r="N38" s="93"/>
-      <c r="O38" s="93"/>
-      <c r="P38" s="93"/>
-      <c r="Q38" s="93"/>
-      <c r="R38" s="93"/>
-      <c r="S38" s="93"/>
-      <c r="T38" s="93"/>
-      <c r="U38" s="93"/>
-      <c r="V38" s="92"/>
+      <c r="N38" s="93">
+        <v>20</v>
+      </c>
+      <c r="O38" s="93">
+        <v>16.600000000000001</v>
+      </c>
+      <c r="P38" s="93">
+        <v>2240</v>
+      </c>
+      <c r="Q38" s="93">
+        <v>0.27853763303498025</v>
+      </c>
+      <c r="R38" s="93">
+        <v>8.4509874691887518E-2</v>
+      </c>
+      <c r="S38" s="93">
+        <v>3.2950952133530318E-4</v>
+      </c>
+      <c r="T38" s="93">
+        <v>2.8650586116076582</v>
+      </c>
+      <c r="U38" s="93">
+        <v>-0.71029378814980859</v>
+      </c>
+      <c r="V38" s="92">
+        <v>46123.423333333332</v>
+      </c>
+      <c r="W38" s="1" t="s">
+        <v>259</v>
+      </c>
     </row>
     <row r="39" spans="1:23" x14ac:dyDescent="0.4">
-      <c r="H39" s="93"/>
-      <c r="I39" s="93"/>
-      <c r="J39" s="93"/>
-      <c r="K39" s="93"/>
-      <c r="L39" s="93"/>
+      <c r="A39" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="B39" s="1">
+        <v>842622669</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="H39" s="93">
+        <v>-1</v>
+      </c>
+      <c r="I39" s="93">
+        <v>-1</v>
+      </c>
+      <c r="J39" s="93">
+        <v>-1</v>
+      </c>
+      <c r="K39" s="93">
+        <v>-1</v>
+      </c>
+      <c r="L39" s="93">
+        <v>134.30000000000001</v>
+      </c>
       <c r="M39" s="93"/>
       <c r="N39" s="93"/>
       <c r="O39" s="93"/>
-      <c r="P39" s="93"/>
-      <c r="Q39" s="93"/>
-      <c r="R39" s="93"/>
-      <c r="S39" s="93"/>
-      <c r="T39" s="93"/>
-      <c r="U39" s="93"/>
-      <c r="V39" s="92"/>
+      <c r="P39" s="93">
+        <v>0</v>
+      </c>
+      <c r="Q39" s="93">
+        <v>0.25354562287399057</v>
+      </c>
+      <c r="R39" s="93">
+        <v>0.38452572188135936</v>
+      </c>
+      <c r="S39" s="93">
+        <v>8.8372043859462324E-4</v>
+      </c>
+      <c r="T39" s="93">
+        <v>6.5455470484210281</v>
+      </c>
+      <c r="U39" s="93">
+        <v>-1.8178938477848303</v>
+      </c>
+      <c r="V39" s="92">
+        <v>46123.423333333332</v>
+      </c>
+      <c r="W39" s="1" t="s">
+        <v>259</v>
+      </c>
     </row>
     <row r="40" spans="1:23" x14ac:dyDescent="0.4">
       <c r="H40" s="93"/>
@@ -8855,7 +9011,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C571DE7A-BF08-4200-BB11-61B452324713}">
-  <dimension ref="A1:C52"/>
+  <dimension ref="A1:C56"/>
   <sheetFormatPr defaultRowHeight="13.15" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="22" style="81" customWidth="1"/>
@@ -8866,13 +9022,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1" s="86" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B1" s="86" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C1" s="86" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.4">
@@ -8880,10 +9036,10 @@
         <v>46111.432708333334</v>
       </c>
       <c r="B2" s="84" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C2" s="84" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.4">
@@ -8891,10 +9047,10 @@
         <v>46111.432708333334</v>
       </c>
       <c r="B3" s="84" t="s">
+        <v>322</v>
+      </c>
+      <c r="C3" s="84" t="s">
         <v>324</v>
-      </c>
-      <c r="C3" s="84" t="s">
-        <v>326</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.4">
@@ -8902,10 +9058,10 @@
         <v>46111.432708333334</v>
       </c>
       <c r="B4" s="84" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C4" s="84" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.4">
@@ -8913,10 +9069,10 @@
         <v>46112.439131944448</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.4">
@@ -8924,10 +9080,10 @@
         <v>46112.439143518517</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>324</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>326</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.4">
@@ -8935,10 +9091,10 @@
         <v>46112.439143518517</v>
       </c>
       <c r="B7" s="81" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C7" s="81" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.4">
@@ -8946,10 +9102,10 @@
         <v>46112.441157407404</v>
       </c>
       <c r="B8" s="81" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C8" s="81" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.4">
@@ -8957,10 +9113,10 @@
         <v>46112.441192129627</v>
       </c>
       <c r="B9" s="81" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C9" s="81" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.4">
@@ -8968,10 +9124,10 @@
         <v>46112.441736111112</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.4">
@@ -8979,10 +9135,10 @@
         <v>46112.441736111112</v>
       </c>
       <c r="B11" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="C11" s="1" t="s">
         <v>324</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>326</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.4">
@@ -8990,10 +9146,10 @@
         <v>46112.441736111112</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.4">
@@ -9001,10 +9157,10 @@
         <v>46112.442106481481</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.4">
@@ -9012,10 +9168,10 @@
         <v>46112.442106481481</v>
       </c>
       <c r="B14" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="C14" s="1" t="s">
         <v>324</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>326</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.4">
@@ -9023,10 +9179,10 @@
         <v>46112.442106481481</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.4">
@@ -9034,10 +9190,10 @@
         <v>46112.442442129628</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.4">
@@ -9045,10 +9201,10 @@
         <v>46112.442476851851</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.4">
@@ -9056,10 +9212,10 @@
         <v>46112.443182870367</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.4">
@@ -9067,10 +9223,10 @@
         <v>46112.443206018521</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.4">
@@ -9078,10 +9234,10 @@
         <v>46112.784872685188</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.4">
@@ -9089,10 +9245,10 @@
         <v>46112.784872685188</v>
       </c>
       <c r="B21" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="C21" s="1" t="s">
         <v>324</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>326</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.4">
@@ -9100,101 +9256,385 @@
         <v>46112.784872685188</v>
       </c>
       <c r="B22" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A23" s="85">
+        <v>46113.463761574072</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A24" s="85">
+        <v>46113.463773148149</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="C24" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="C22" s="1" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A23" s="85"/>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A24" s="85"/>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A25" s="85"/>
+      <c r="A25" s="85">
+        <v>46113.463784722226</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>325</v>
+      </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A26" s="85"/>
+      <c r="A26" s="85">
+        <v>46113.464155092595</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>330</v>
+      </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A27" s="85"/>
+      <c r="A27" s="85">
+        <v>46113.464178240742</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>331</v>
+      </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A28" s="85"/>
+      <c r="A28" s="85">
+        <v>46114.494803240741</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>323</v>
+      </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A29" s="85"/>
+      <c r="A29" s="85">
+        <v>46114.494814814818</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>324</v>
+      </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A30" s="85"/>
+      <c r="A30" s="85">
+        <v>46114.494814814818</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>325</v>
+      </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A31" s="85"/>
+      <c r="A31" s="85">
+        <v>46115.523900462962</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>323</v>
+      </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A32" s="85"/>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A33" s="85"/>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A34" s="85"/>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A35" s="85"/>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A36" s="85"/>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A37" s="85"/>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A38" s="85"/>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A39" s="85"/>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A40" s="85"/>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A41" s="85"/>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A42" s="85"/>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A43" s="85"/>
-    </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A44" s="85"/>
-    </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A45" s="85"/>
-    </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A46" s="85"/>
-    </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A47" s="85"/>
-    </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A48" s="85"/>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A49" s="85"/>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A50" s="85"/>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A51" s="85"/>
-    </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A52" s="85"/>
+      <c r="A32" s="85">
+        <v>46115.523900462962</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A33" s="85">
+        <v>46115.523912037039</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A34" s="85">
+        <v>46115.524907407409</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A35" s="85">
+        <v>46115.524930555555</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A36" s="85">
+        <v>46118.597337962965</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A37" s="85">
+        <v>46118.597349537034</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A38" s="85">
+        <v>46118.597349537034</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A39" s="85">
+        <v>46119.429062499999</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A40" s="85">
+        <v>46119.429062499999</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A41" s="85">
+        <v>46119.429074074076</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A42" s="85">
+        <v>46119.557905092595</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A43" s="85">
+        <v>46119.557962962965</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A44" s="85">
+        <v>46119.557962962965</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A45" s="85">
+        <v>46119.558692129627</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A46" s="85">
+        <v>46119.558703703704</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A47" s="85">
+        <v>46119.558703703704</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A48" s="85">
+        <v>46120.50880787037</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A49" s="85">
+        <v>46120.50880787037</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A50" s="85">
+        <v>46120.508819444447</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A51" s="85">
+        <v>46122.466909722221</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A52" s="85">
+        <v>46122.466909722221</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A53" s="85">
+        <v>46122.466921296298</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A54" s="85">
+        <v>46123.422256944446</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A55" s="85">
+        <v>46123.422268518516</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A56" s="85">
+        <v>46123.422268518516</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>339</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9217,7 +9657,7 @@
     <row r="2" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B2" s="56"/>
       <c r="C2" s="4" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>48</v>
@@ -9229,47 +9669,47 @@
         <v>49</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B3" s="17" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C3" s="17"/>
       <c r="D3" s="10"/>
       <c r="E3" s="10"/>
       <c r="F3" s="10"/>
       <c r="G3" s="15">
-        <v>1304.95</v>
+        <v>2049.7199999999998</v>
       </c>
       <c r="H3" s="6">
         <f>-G3</f>
-        <v>-1304.95</v>
+        <v>-2049.7199999999998</v>
       </c>
     </row>
     <row r="4" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B4" s="17" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C4" s="17"/>
       <c r="D4" s="10"/>
       <c r="E4" s="10"/>
       <c r="F4" s="10"/>
       <c r="G4" s="15">
-        <v>774.84</v>
+        <v>599.25</v>
       </c>
       <c r="H4" s="6">
         <f>-G4</f>
-        <v>-774.84</v>
+        <v>-599.25</v>
       </c>
     </row>
     <row r="5" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B5" s="17" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C5" s="17"/>
       <c r="D5" s="10"/>
@@ -9280,7 +9720,7 @@
     </row>
     <row r="6" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B6" s="17" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C6" s="17"/>
       <c r="D6" s="10"/>
@@ -9291,7 +9731,7 @@
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B7" s="17" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C7" s="17"/>
       <c r="D7" s="10"/>
@@ -9302,7 +9742,7 @@
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B8" s="17" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C8" s="96">
         <v>2.5000000000000001E-2</v>
@@ -9321,7 +9761,7 @@
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B9" s="17" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C9" s="62"/>
       <c r="D9" s="27"/>
@@ -9332,7 +9772,7 @@
     </row>
     <row r="10" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B10" s="17" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C10" s="62"/>
       <c r="D10" s="27"/>
@@ -9343,7 +9783,7 @@
     </row>
     <row r="11" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B11" s="17" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C11" s="62"/>
       <c r="D11" s="27"/>
@@ -9354,7 +9794,7 @@
     </row>
     <row r="12" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B12" s="52" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C12" s="58"/>
       <c r="D12" s="54">
@@ -9377,7 +9817,7 @@
     </row>
     <row r="13" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B13" s="17" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C13" s="17"/>
       <c r="D13" s="10"/>
@@ -9385,11 +9825,11 @@
       <c r="F13" s="10"/>
       <c r="G13" s="6">
         <f>SUM(G3:G12)</f>
-        <v>3379.7899999999545</v>
+        <v>3948.9699999999543</v>
       </c>
       <c r="H13" s="6">
         <f>SUM(H3:H12)</f>
-        <v>34220.209999999955</v>
+        <v>33651.029999999955</v>
       </c>
     </row>
   </sheetData>
@@ -9442,46 +9882,46 @@
   <sheetData>
     <row r="2" spans="2:18" x14ac:dyDescent="0.4">
       <c r="B2" s="38" t="s">
+        <v>158</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="D2" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="E2" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="F2" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="G2" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="H2" s="4" t="s">
         <v>162</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>164</v>
       </c>
       <c r="I2" s="4" t="s">
         <v>52</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="N2" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="O2" s="4" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="3" spans="2:18" x14ac:dyDescent="0.4">
@@ -9569,13 +10009,12 @@
       <c r="F5" s="67"/>
       <c r="G5" s="67"/>
       <c r="H5" s="67"/>
-      <c r="I5" s="70">
-        <f>Blotter!C$4-SUM(NAV!I$4:I4)</f>
-        <v>23885.740632010933</v>
+      <c r="I5" s="67">
+        <v>28744.450632010939</v>
       </c>
       <c r="J5" s="70">
         <f t="shared" si="2"/>
-        <v>1023885.740632011</v>
+        <v>1028744.4506320109</v>
       </c>
       <c r="K5" s="70">
         <f t="shared" si="3"/>
@@ -9583,36 +10022,65 @@
       </c>
       <c r="L5" s="71">
         <f t="shared" si="4"/>
-        <v>1023.885740632011</v>
+        <v>1028.744450632011</v>
       </c>
       <c r="M5" s="72">
         <f t="shared" si="5"/>
-        <v>2.3885740632010988E-2</v>
+        <v>2.8744450632010921E-2</v>
       </c>
       <c r="N5" s="73">
         <f t="shared" ref="N5" si="6">L5/L4-1</f>
-        <v>2.3885740632010988E-2</v>
+        <v>2.8744450632010921E-2</v>
       </c>
       <c r="O5" s="75">
         <f>STDEVP(N$4:N5)*SQRT(12)</f>
-        <v>4.1371316351055377E-2</v>
+        <v>4.9786848930298236E-2</v>
       </c>
     </row>
     <row r="6" spans="2:18" ht="14.25" x14ac:dyDescent="0.4">
-      <c r="B6" s="76"/>
+      <c r="B6" s="76">
+        <v>46142</v>
+      </c>
       <c r="C6" s="67"/>
-      <c r="D6" s="70"/>
-      <c r="E6" s="70"/>
+      <c r="D6" s="70">
+        <f t="shared" ref="D6" si="7">C6*L5</f>
+        <v>0</v>
+      </c>
+      <c r="E6" s="70">
+        <f t="shared" ref="E6" si="8">J5+D6</f>
+        <v>1028744.4506320109</v>
+      </c>
       <c r="F6" s="67"/>
       <c r="G6" s="67"/>
       <c r="H6" s="67"/>
-      <c r="I6" s="67"/>
-      <c r="J6" s="70"/>
-      <c r="K6" s="70"/>
-      <c r="L6" s="71"/>
-      <c r="M6" s="72"/>
-      <c r="N6" s="73"/>
-      <c r="O6" s="75"/>
+      <c r="I6" s="70">
+        <f>Blotter!C$4-SUM(NAV!I$4:I5)</f>
+        <v>25554.81</v>
+      </c>
+      <c r="J6" s="70">
+        <f t="shared" ref="J6" si="9">E6-F6-G6-H6+I6</f>
+        <v>1054299.2606320109</v>
+      </c>
+      <c r="K6" s="70">
+        <f t="shared" ref="K6" si="10">K5+C6</f>
+        <v>1000</v>
+      </c>
+      <c r="L6" s="71">
+        <f t="shared" ref="L6" si="11">J6/K6</f>
+        <v>1054.2992606320108</v>
+      </c>
+      <c r="M6" s="72">
+        <f t="shared" ref="M6" si="12">L6/$L$3-1</f>
+        <v>5.4299260632010737E-2</v>
+      </c>
+      <c r="N6" s="73">
+        <f t="shared" ref="N6" si="13">L6/L5-1</f>
+        <v>2.4840775553442995E-2</v>
+      </c>
+      <c r="O6" s="75">
+        <f>STDEVP(N$4:N6)*SQRT(12)</f>
+        <v>4.4099074084787401E-2</v>
+      </c>
     </row>
     <row r="7" spans="2:18" ht="14.25" x14ac:dyDescent="0.4">
       <c r="B7" s="76"/>
@@ -9877,31 +10345,31 @@
         <v>7</v>
       </c>
       <c r="H2" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="I2" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="J2" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="K2" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="L2" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="M2" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="I2" s="8" t="s">
-        <v>156</v>
-      </c>
-      <c r="J2" s="8" t="s">
+      <c r="N2" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="O2" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="K2" s="8" t="s">
+      <c r="P2" s="4" t="s">
         <v>157</v>
-      </c>
-      <c r="L2" s="8" t="s">
-        <v>158</v>
-      </c>
-      <c r="M2" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="N2" s="8" t="s">
-        <v>156</v>
-      </c>
-      <c r="O2" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="P2" s="4" t="s">
-        <v>159</v>
       </c>
       <c r="Q2" s="4" t="s">
         <v>53</v>
@@ -9919,20 +10387,20 @@
         <v>2</v>
       </c>
       <c r="W2" s="38" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="X2" s="38" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="Y2" s="12"/>
       <c r="Z2" s="38" t="s">
         <v>2</v>
       </c>
       <c r="AA2" s="38" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="AB2" s="38" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="3" spans="2:28" x14ac:dyDescent="0.4">
@@ -9986,64 +10454,64 @@
         <v>46088</v>
       </c>
       <c r="C4" s="5">
-        <f>C3+1</f>
+        <f t="shared" ref="C4:C9" si="2">C3+1</f>
         <v>1</v>
       </c>
       <c r="D4" s="6">
         <f t="array" ref="D4">SUM((Blotter!C$19:C$1013=C4)*(Blotter!N$19:N$1013)*1)</f>
-        <v>5222.6906320109993</v>
+        <v>12922.690632010999</v>
       </c>
       <c r="E4" s="6">
         <f t="array" ref="E4">SUM((Blotter!B$19:C$1013=C4)*(Blotter!R$19:R$1013)*1)</f>
-        <v>10500</v>
+        <v>0</v>
       </c>
       <c r="F4" s="30">
-        <f t="shared" ref="F4" si="2">IF(ISNUMBER(D4/E4),D4/E4,0)</f>
-        <v>0.49739910781057134</v>
+        <f t="shared" ref="F4" si="3">IF(ISNUMBER(D4/E4),D4/E4,0)</f>
+        <v>0</v>
       </c>
       <c r="G4" s="36" t="str">
         <f t="array" ref="G4">IF(SUM((Blotter!C$19:C$1013=PLB!C4)*(Blotter!M$19:M$1013))=0,"C","O")</f>
         <v>O</v>
       </c>
       <c r="H4" s="16">
-        <f>J3+D4</f>
-        <v>1005222.690632011</v>
+        <f t="shared" ref="H4:H9" si="4">J3+D4</f>
+        <v>1012922.690632011</v>
       </c>
       <c r="I4" s="16"/>
       <c r="J4" s="16">
         <f t="shared" si="0"/>
-        <v>1005222.690632011</v>
+        <v>1012922.690632011</v>
       </c>
       <c r="K4" s="3">
-        <f>H4/J3-1</f>
-        <v>5.2226906320109734E-3</v>
+        <f t="shared" ref="K4:K9" si="5">H4/J3-1</f>
+        <v>1.2922690632011014E-2</v>
       </c>
       <c r="L4" s="3">
-        <f>(1+K4)*(1+L3)-1</f>
-        <v>5.2226906320109734E-3</v>
+        <f t="shared" ref="L4:L9" si="6">(1+K4)*(1+L3)-1</f>
+        <v>1.2922690632011014E-2</v>
       </c>
       <c r="M4" s="6">
-        <f>O3-IF(G4="O",O3*1%,-D4)</f>
-        <v>990000</v>
+        <f>O3-IF(G4="O",E4,-D4)</f>
+        <v>1000000</v>
       </c>
       <c r="N4" s="16">
-        <f>I4</f>
+        <f t="shared" ref="N4:N9" si="7">I4</f>
         <v>0</v>
       </c>
       <c r="O4" s="6">
         <f t="shared" si="1"/>
-        <v>990000</v>
+        <v>1000000</v>
       </c>
       <c r="P4" s="3">
-        <f>M4/O3-1</f>
-        <v>-1.0000000000000009E-2</v>
+        <f t="shared" ref="P4:P9" si="8">M4/O3-1</f>
+        <v>0</v>
       </c>
       <c r="Q4" s="3">
-        <f>(1+P4)*(1+Q3)-1</f>
-        <v>-1.0000000000000009E-2</v>
+        <f t="shared" ref="Q4:Q9" si="9">(1+P4)*(1+Q3)-1</f>
+        <v>0</v>
       </c>
       <c r="R4" s="3">
-        <f>(1-1%)*(1+R3)-1</f>
+        <f t="shared" ref="R4:R9" si="10">(1-1%)*(1+R3)-1</f>
         <v>-1.0000000000000009E-2</v>
       </c>
       <c r="T4" s="40">
@@ -10055,13 +10523,13 @@
         <v>1</v>
       </c>
       <c r="V4" s="1" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="W4" s="1" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="X4" s="1" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="5" spans="2:28" x14ac:dyDescent="0.4">
@@ -10070,82 +10538,82 @@
         <v>46095</v>
       </c>
       <c r="C5" s="5">
-        <f>C4+1</f>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="D5" s="6">
         <f t="array" ref="D5">SUM((Blotter!C$19:C$1013=C5)*(Blotter!N$19:N$1013)*1)</f>
-        <v>1491.0899999999965</v>
+        <v>-2198.9100000000035</v>
       </c>
       <c r="E5" s="6">
         <f t="array" ref="E5">SUM((Blotter!B$19:C$1013=C5)*(Blotter!R$19:R$1013)*1)</f>
         <v>9000</v>
       </c>
       <c r="F5" s="30">
-        <f t="shared" ref="F5" si="3">IF(ISNUMBER(D5/E5),D5/E5,0)</f>
-        <v>0.16567666666666628</v>
+        <f t="shared" ref="F5" si="11">IF(ISNUMBER(D5/E5),D5/E5,0)</f>
+        <v>-0.24432333333333373</v>
       </c>
       <c r="G5" s="36" t="str">
         <f t="array" ref="G5">IF(SUM((Blotter!C$19:C$1013=PLB!C5)*(Blotter!M$19:M$1013))=0,"C","O")</f>
         <v>O</v>
       </c>
       <c r="H5" s="16">
-        <f>J4+D5</f>
-        <v>1006713.780632011</v>
+        <f t="shared" si="4"/>
+        <v>1010723.780632011</v>
       </c>
       <c r="I5" s="16"/>
       <c r="J5" s="16">
         <f t="shared" si="0"/>
-        <v>1006713.780632011</v>
+        <v>1010723.780632011</v>
       </c>
       <c r="K5" s="3">
-        <f>H5/J4-1</f>
-        <v>1.483342958625844E-3</v>
+        <f t="shared" si="5"/>
+        <v>-2.1708566905812576E-3</v>
       </c>
       <c r="L5" s="3">
-        <f>(1+K5)*(1+L4)-1</f>
-        <v>6.7137806320110016E-3</v>
+        <f t="shared" si="6"/>
+        <v>1.0723780632010849E-2</v>
       </c>
       <c r="M5" s="6">
-        <f>O4-IF(G5="O",O4*1%,-D5)</f>
-        <v>980100</v>
+        <f t="shared" ref="M5:M8" si="12">O4-IF(G5="O",E5,-D5)</f>
+        <v>991000</v>
       </c>
       <c r="N5" s="16">
-        <f>I5</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="O5" s="6">
         <f t="shared" si="1"/>
-        <v>980100</v>
+        <v>991000</v>
       </c>
       <c r="P5" s="3">
-        <f>M5/O4-1</f>
-        <v>-1.0000000000000009E-2</v>
+        <f t="shared" si="8"/>
+        <v>-9.000000000000008E-3</v>
       </c>
       <c r="Q5" s="3">
-        <f>(1+P5)*(1+Q4)-1</f>
+        <f t="shared" si="9"/>
+        <v>-9.000000000000008E-3</v>
+      </c>
+      <c r="R5" s="3">
+        <f t="shared" si="10"/>
         <v>-1.9900000000000029E-2</v>
       </c>
-      <c r="R5" s="3">
-        <f>(1-1%)*(1+R4)-1</f>
-        <v>-1.9900000000000029E-2</v>
-      </c>
       <c r="T5" s="40">
-        <f t="shared" ref="T5" si="4">B5</f>
+        <f t="shared" ref="T5" si="13">B5</f>
         <v>46095</v>
       </c>
       <c r="U5" s="5">
-        <f t="shared" ref="U5" si="5">C5</f>
+        <f t="shared" ref="U5" si="14">C5</f>
         <v>2</v>
       </c>
       <c r="V5" s="1" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="W5" s="1" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="X5" s="1" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="6" spans="2:28" x14ac:dyDescent="0.4">
@@ -10154,82 +10622,82 @@
         <v>46102</v>
       </c>
       <c r="C6" s="5">
-        <f>C5+1</f>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="D6" s="6">
         <f t="array" ref="D6">SUM((Blotter!C$19:C$1013=C6)*(Blotter!N$19:N$1013)*1)</f>
-        <v>-2984.2200000000025</v>
+        <v>-4124.2200000000039</v>
       </c>
       <c r="E6" s="6">
         <f t="array" ref="E6">SUM((Blotter!B$19:C$1013=C6)*(Blotter!R$19:R$1013)*1)</f>
-        <v>9600</v>
+        <v>9584.220000000003</v>
       </c>
       <c r="F6" s="30">
-        <f t="shared" ref="F6" si="6">IF(ISNUMBER(D6/E6),D6/E6,0)</f>
-        <v>-0.31085625000000028</v>
+        <f t="shared" ref="F6" si="15">IF(ISNUMBER(D6/E6),D6/E6,0)</f>
+        <v>-0.43031357794374531</v>
       </c>
       <c r="G6" s="36" t="str">
         <f t="array" ref="G6">IF(SUM((Blotter!C$19:C$1013=PLB!C6)*(Blotter!M$19:M$1013))=0,"C","O")</f>
         <v>O</v>
       </c>
       <c r="H6" s="16">
-        <f>J5+D6</f>
-        <v>1003729.560632011</v>
+        <f t="shared" si="4"/>
+        <v>1006599.560632011</v>
       </c>
       <c r="I6" s="16"/>
       <c r="J6" s="16">
         <f t="shared" si="0"/>
-        <v>1003729.560632011</v>
+        <v>1006599.560632011</v>
       </c>
       <c r="K6" s="3">
-        <f>H6/J5-1</f>
-        <v>-2.9643182177624405E-3</v>
+        <f t="shared" si="5"/>
+        <v>-4.0804620204157871E-3</v>
       </c>
       <c r="L6" s="3">
-        <f>(1+K6)*(1+L5)-1</f>
-        <v>3.7295606320111307E-3</v>
+        <f t="shared" si="6"/>
+        <v>6.5995606320108369E-3</v>
       </c>
       <c r="M6" s="6">
-        <f>O5-IF(G6="O",O5*1%,-D6)</f>
-        <v>970299</v>
+        <f t="shared" si="12"/>
+        <v>981415.78</v>
       </c>
       <c r="N6" s="16">
-        <f>I6</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="O6" s="6">
         <f t="shared" si="1"/>
-        <v>970299</v>
+        <v>981415.78</v>
       </c>
       <c r="P6" s="3">
-        <f>M6/O5-1</f>
-        <v>-1.0000000000000009E-2</v>
+        <f t="shared" si="8"/>
+        <v>-9.6712613521694468E-3</v>
       </c>
       <c r="Q6" s="3">
-        <f>(1+P6)*(1+Q5)-1</f>
+        <f t="shared" si="9"/>
+        <v>-1.8584219999999929E-2</v>
+      </c>
+      <c r="R6" s="3">
+        <f t="shared" si="10"/>
         <v>-2.9701000000000088E-2</v>
       </c>
-      <c r="R6" s="3">
-        <f>(1-1%)*(1+R5)-1</f>
-        <v>-2.9701000000000088E-2</v>
-      </c>
       <c r="T6" s="40">
-        <f t="shared" ref="T6" si="7">B6</f>
+        <f t="shared" ref="T6" si="16">B6</f>
         <v>46102</v>
       </c>
       <c r="U6" s="5">
-        <f t="shared" ref="U6" si="8">C6</f>
+        <f t="shared" ref="U6" si="17">C6</f>
         <v>3</v>
       </c>
       <c r="V6" s="1" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="W6" s="49" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="X6" s="1" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="7" spans="2:28" x14ac:dyDescent="0.4">
@@ -10238,82 +10706,82 @@
         <v>46109</v>
       </c>
       <c r="C7" s="5">
-        <f>C6+1</f>
+        <f t="shared" si="2"/>
         <v>4</v>
       </c>
       <c r="D7" s="6">
         <f t="array" ref="D7">SUM((Blotter!C$19:C$1013=C7)*(Blotter!N$19:N$1013)*1)</f>
-        <v>3097.5299999999988</v>
+        <v>7360.0299999999988</v>
       </c>
       <c r="E7" s="6">
         <f t="array" ref="E7">SUM((Blotter!B$19:C$1013=C7)*(Blotter!R$19:R$1013)*1)</f>
         <v>7192.5</v>
       </c>
       <c r="F7" s="30">
-        <f t="shared" ref="F7" si="9">IF(ISNUMBER(D7/E7),D7/E7,0)</f>
-        <v>0.43066110531803947</v>
+        <f t="shared" ref="F7" si="18">IF(ISNUMBER(D7/E7),D7/E7,0)</f>
+        <v>1.0232923183872087</v>
       </c>
       <c r="G7" s="36" t="str">
         <f t="array" ref="G7">IF(SUM((Blotter!C$19:C$1013=PLB!C7)*(Blotter!M$19:M$1013))=0,"C","O")</f>
         <v>O</v>
       </c>
       <c r="H7" s="16">
-        <f>J6+D7</f>
-        <v>1006827.0906320111</v>
+        <f t="shared" si="4"/>
+        <v>1013959.5906320111</v>
       </c>
       <c r="I7" s="16"/>
       <c r="J7" s="16">
         <f t="shared" si="0"/>
-        <v>1006827.0906320111</v>
+        <v>1013959.5906320111</v>
       </c>
       <c r="K7" s="3">
-        <f>H7/J6-1</f>
-        <v>3.0860204994358487E-3</v>
+        <f t="shared" si="5"/>
+        <v>7.3117754942977342E-3</v>
       </c>
       <c r="L7" s="3">
-        <f>(1+K7)*(1+L6)-1</f>
-        <v>6.8270906320111457E-3</v>
+        <f t="shared" si="6"/>
+        <v>1.395959063201091E-2</v>
       </c>
       <c r="M7" s="6">
-        <f>O6-IF(G7="O",O6*1%,-D7)</f>
-        <v>960596.01</v>
+        <f t="shared" si="12"/>
+        <v>974223.28</v>
       </c>
       <c r="N7" s="16">
-        <f>I7</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="O7" s="6">
         <f t="shared" si="1"/>
-        <v>960596.01</v>
+        <v>974223.28</v>
       </c>
       <c r="P7" s="3">
-        <f>M7/O6-1</f>
-        <v>-1.0000000000000009E-2</v>
+        <f t="shared" si="8"/>
+        <v>-7.3286981385198846E-3</v>
       </c>
       <c r="Q7" s="3">
-        <f>(1+P7)*(1+Q6)-1</f>
+        <f t="shared" si="9"/>
+        <v>-2.5776719999999975E-2</v>
+      </c>
+      <c r="R7" s="3">
+        <f t="shared" si="10"/>
         <v>-3.9403990000000055E-2</v>
       </c>
-      <c r="R7" s="3">
-        <f>(1-1%)*(1+R6)-1</f>
-        <v>-3.9403990000000055E-2</v>
-      </c>
       <c r="T7" s="40">
-        <f t="shared" ref="T7" si="10">B7</f>
+        <f t="shared" ref="T7" si="19">B7</f>
         <v>46109</v>
       </c>
       <c r="U7" s="5">
-        <f t="shared" ref="U7" si="11">C7</f>
+        <f t="shared" ref="U7" si="20">C7</f>
         <v>4</v>
       </c>
       <c r="V7" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="W7" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="W7" s="1" t="s">
-        <v>322</v>
-      </c>
       <c r="X7" s="1" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
     </row>
     <row r="8" spans="2:28" x14ac:dyDescent="0.4">
@@ -10322,98 +10790,155 @@
         <v>46116</v>
       </c>
       <c r="C8" s="5">
-        <f>C7+1</f>
+        <f t="shared" si="2"/>
         <v>5</v>
       </c>
       <c r="D8" s="6">
         <f t="array" ref="D8">SUM((Blotter!C$19:C$1013=C8)*(Blotter!N$19:N$1013)*1)</f>
-        <v>13678.859999999986</v>
+        <v>35135.739999999991</v>
       </c>
       <c r="E8" s="6">
         <f t="array" ref="E8">SUM((Blotter!B$19:C$1013=C8)*(Blotter!R$19:R$1013)*1)</f>
-        <v>9625</v>
+        <v>-8745</v>
       </c>
       <c r="F8" s="30">
-        <f t="shared" ref="F8" si="12">IF(ISNUMBER(D8/E8),D8/E8,0)</f>
-        <v>1.4211802597402583</v>
+        <f t="shared" ref="F8" si="21">IF(ISNUMBER(D8/E8),D8/E8,0)</f>
+        <v>-4.0178090337335606</v>
       </c>
       <c r="G8" s="36" t="str">
         <f t="array" ref="G8">IF(SUM((Blotter!C$19:C$1013=PLB!C8)*(Blotter!M$19:M$1013))=0,"C","O")</f>
         <v>O</v>
       </c>
       <c r="H8" s="16">
-        <f>J7+D8</f>
-        <v>1020505.9506320111</v>
+        <f t="shared" si="4"/>
+        <v>1049095.3306320109</v>
       </c>
       <c r="I8" s="16"/>
       <c r="J8" s="16">
         <f t="shared" si="0"/>
-        <v>1020505.9506320111</v>
+        <v>1049095.3306320109</v>
       </c>
       <c r="K8" s="3">
-        <f>H8/J7-1</f>
-        <v>1.3586106420133692E-2</v>
+        <f t="shared" si="5"/>
+        <v>3.465201209655655E-2</v>
       </c>
       <c r="L8" s="3">
-        <f>(1+K8)*(1+L7)-1</f>
-        <v>2.0505950632011327E-2</v>
+        <f t="shared" si="6"/>
+        <v>4.909533063201077E-2</v>
       </c>
       <c r="M8" s="6">
-        <f>O7-IF(G8="O",O7*1%,-D8)</f>
-        <v>950990.04989999998</v>
+        <f t="shared" si="12"/>
+        <v>982968.28</v>
       </c>
       <c r="N8" s="16">
-        <f>I8</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="O8" s="6">
         <f t="shared" si="1"/>
-        <v>950990.04989999998</v>
+        <v>982968.28</v>
       </c>
       <c r="P8" s="3">
-        <f>M8/O7-1</f>
-        <v>-1.0000000000000009E-2</v>
+        <f t="shared" si="8"/>
+        <v>8.9763816771037952E-3</v>
       </c>
       <c r="Q8" s="3">
-        <f>(1+P8)*(1+Q7)-1</f>
+        <f t="shared" si="9"/>
+        <v>-1.7031719999999972E-2</v>
+      </c>
+      <c r="R8" s="3">
+        <f t="shared" si="10"/>
         <v>-4.9009950100000088E-2</v>
       </c>
-      <c r="R8" s="3">
-        <f>(1-1%)*(1+R7)-1</f>
-        <v>-4.9009950100000088E-2</v>
-      </c>
       <c r="T8" s="40">
-        <f t="shared" ref="T8" si="13">B8</f>
+        <f t="shared" ref="T8" si="22">B8</f>
         <v>46116</v>
       </c>
       <c r="U8" s="5">
-        <f t="shared" ref="U8" si="14">C8</f>
+        <f t="shared" ref="U8" si="23">C8</f>
         <v>5</v>
       </c>
       <c r="V8" s="1" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
     </row>
     <row r="9" spans="2:28" x14ac:dyDescent="0.4">
-      <c r="B9" s="40"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="6"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="30"/>
-      <c r="G9" s="36"/>
-      <c r="H9" s="16"/>
+      <c r="B9" s="40">
+        <f>B8+7</f>
+        <v>46123</v>
+      </c>
+      <c r="C9" s="5">
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+      <c r="D9" s="6">
+        <f t="array" ref="D9">SUM((Blotter!C$19:C$1013=C9)*(Blotter!N$19:N$1013)*1)</f>
+        <v>1254.9600000000014</v>
+      </c>
+      <c r="E9" s="6">
+        <f t="array" ref="E9">SUM((Blotter!B$19:C$1013=C9)*(Blotter!R$19:R$1013)*1)</f>
+        <v>9906</v>
+      </c>
+      <c r="F9" s="30">
+        <f t="shared" ref="F9" si="24">IF(ISNUMBER(D9/E9),D9/E9,0)</f>
+        <v>0.12668685645063613</v>
+      </c>
+      <c r="G9" s="36" t="str">
+        <f t="array" ref="G9">IF(SUM((Blotter!C$19:C$1013=PLB!C9)*(Blotter!M$19:M$1013))=0,"C","O")</f>
+        <v>O</v>
+      </c>
+      <c r="H9" s="16">
+        <f t="shared" si="4"/>
+        <v>1050350.2906320109</v>
+      </c>
       <c r="I9" s="16"/>
-      <c r="J9" s="16"/>
-      <c r="K9" s="3"/>
-      <c r="L9" s="3"/>
-      <c r="M9" s="6"/>
-      <c r="N9" s="16"/>
-      <c r="O9" s="6"/>
-      <c r="P9" s="3"/>
-      <c r="Q9" s="3"/>
-      <c r="R9" s="3"/>
-      <c r="T9" s="40"/>
-      <c r="U9" s="5"/>
+      <c r="J9" s="16">
+        <f t="shared" ref="J9" si="25">H9+I9</f>
+        <v>1050350.2906320109</v>
+      </c>
+      <c r="K9" s="3">
+        <f t="shared" si="5"/>
+        <v>1.1962306602240069E-3</v>
+      </c>
+      <c r="L9" s="3">
+        <f t="shared" si="6"/>
+        <v>5.0350290632010575E-2</v>
+      </c>
+      <c r="M9" s="6">
+        <f t="shared" ref="M9" si="26">O8-IF(G9="O",E9,-D9)</f>
+        <v>973062.28</v>
+      </c>
+      <c r="N9" s="16">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="O9" s="6">
+        <f t="shared" ref="O9" si="27">M9+N9</f>
+        <v>973062.28</v>
+      </c>
+      <c r="P9" s="3">
+        <f t="shared" si="8"/>
+        <v>-1.0077639534817995E-2</v>
+      </c>
+      <c r="Q9" s="3">
+        <f t="shared" si="9"/>
+        <v>-2.6937720000000054E-2</v>
+      </c>
+      <c r="R9" s="3">
+        <f t="shared" si="10"/>
+        <v>-5.8519850599000112E-2</v>
+      </c>
+      <c r="T9" s="40">
+        <f t="shared" ref="T9" si="28">B9</f>
+        <v>46123</v>
+      </c>
+      <c r="U9" s="5">
+        <f t="shared" ref="U9" si="29">C9</f>
+        <v>6</v>
+      </c>
+      <c r="V9" s="1" t="s">
+        <v>338</v>
+      </c>
       <c r="W9" s="49"/>
     </row>
     <row r="10" spans="2:28" x14ac:dyDescent="0.4">
@@ -11557,22 +12082,22 @@
         <v>16</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="H2" s="4" t="s">
         <v>18</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="J2" s="4" t="s">
         <v>89</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="N2" s="4" t="s">
         <v>19</v>
@@ -11802,7 +12327,7 @@
     </row>
     <row r="8" spans="2:18" x14ac:dyDescent="0.4">
       <c r="B8" s="17" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C8" s="18">
         <v>5</v>
@@ -11961,7 +12486,7 @@
         <v>100</v>
       </c>
       <c r="D12" s="19">
-        <v>28.4</v>
+        <v>185.2</v>
       </c>
       <c r="E12" s="20">
         <f t="shared" si="1"/>
@@ -11977,11 +12502,11 @@
       </c>
       <c r="H12" s="23">
         <f t="shared" si="0"/>
-        <v>2.347417840375587</v>
+        <v>0.35997120230381568</v>
       </c>
       <c r="I12" s="61">
         <f t="shared" si="4"/>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J12" s="61"/>
       <c r="K12" s="61"/>
@@ -12786,7 +13311,7 @@
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B35" s="9" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C35" s="18">
         <v>1</v>
@@ -12937,19 +13462,19 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>59</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>186</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>188</v>
       </c>
       <c r="H2" s="1">
         <v>1</v>
@@ -12996,7 +13521,7 @@
         <v>-21.810505307</v>
       </c>
       <c r="Z2" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="AC2" s="44"/>
       <c r="AD2" s="45"/>
@@ -13004,19 +13529,19 @@
     </row>
     <row r="3" spans="1:31" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>59</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>186</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>188</v>
       </c>
       <c r="H3" s="1">
         <v>1</v>
@@ -13068,19 +13593,19 @@
     </row>
     <row r="4" spans="1:31" x14ac:dyDescent="0.4">
       <c r="A4" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>59</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>186</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>188</v>
       </c>
       <c r="H4" s="1">
         <v>1</v>
@@ -13132,19 +13657,19 @@
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>59</v>
       </c>
       <c r="C5" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>186</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>188</v>
       </c>
       <c r="H5" s="1">
         <v>1</v>
@@ -13196,19 +13721,19 @@
     </row>
     <row r="6" spans="1:31" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>59</v>
       </c>
       <c r="C6" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>186</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>188</v>
       </c>
       <c r="H6" s="1">
         <v>1</v>
@@ -13260,19 +13785,19 @@
     </row>
     <row r="7" spans="1:31" x14ac:dyDescent="0.4">
       <c r="A7" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>59</v>
       </c>
       <c r="C7" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>186</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>188</v>
       </c>
       <c r="H7" s="1">
         <v>1</v>
@@ -13324,19 +13849,19 @@
     </row>
     <row r="8" spans="1:31" x14ac:dyDescent="0.4">
       <c r="A8" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>59</v>
       </c>
       <c r="C8" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>186</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>188</v>
       </c>
       <c r="H8" s="1">
         <v>1</v>
@@ -13388,19 +13913,19 @@
     </row>
     <row r="9" spans="1:31" x14ac:dyDescent="0.4">
       <c r="A9" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>59</v>
       </c>
       <c r="C9" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="E9" s="1" t="s">
         <v>186</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>188</v>
       </c>
       <c r="H9" s="1">
         <v>1</v>
@@ -13452,19 +13977,19 @@
     </row>
     <row r="10" spans="1:31" x14ac:dyDescent="0.4">
       <c r="A10" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>59</v>
       </c>
       <c r="C10" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="E10" s="1" t="s">
         <v>186</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>188</v>
       </c>
       <c r="H10" s="1">
         <v>1</v>
@@ -13516,19 +14041,19 @@
     </row>
     <row r="11" spans="1:31" x14ac:dyDescent="0.4">
       <c r="A11" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>59</v>
       </c>
       <c r="C11" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="E11" s="1" t="s">
         <v>186</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>188</v>
       </c>
       <c r="H11" s="1">
         <v>1</v>
@@ -13580,19 +14105,19 @@
     </row>
     <row r="12" spans="1:31" x14ac:dyDescent="0.4">
       <c r="A12" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>59</v>
       </c>
       <c r="C12" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="E12" s="1" t="s">
         <v>186</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>188</v>
       </c>
       <c r="H12" s="1">
         <v>1</v>
@@ -13644,19 +14169,19 @@
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.4">
       <c r="A13" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>59</v>
       </c>
       <c r="C13" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="E13" s="1" t="s">
         <v>186</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>188</v>
       </c>
       <c r="H13" s="1">
         <v>1</v>
@@ -13708,19 +14233,19 @@
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.4">
       <c r="A14" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>59</v>
       </c>
       <c r="C14" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="E14" s="1" t="s">
         <v>186</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>188</v>
       </c>
       <c r="H14" s="1">
         <v>1</v>
@@ -13772,19 +14297,19 @@
     </row>
     <row r="15" spans="1:31" x14ac:dyDescent="0.4">
       <c r="A15" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>59</v>
       </c>
       <c r="C15" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="E15" s="1" t="s">
         <v>186</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>188</v>
       </c>
       <c r="H15" s="1">
         <v>1</v>
@@ -13836,19 +14361,19 @@
     </row>
     <row r="16" spans="1:31" x14ac:dyDescent="0.4">
       <c r="A16" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>59</v>
       </c>
       <c r="C16" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="E16" s="1" t="s">
         <v>186</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>188</v>
       </c>
       <c r="H16" s="1">
         <v>1</v>
@@ -13900,19 +14425,19 @@
     </row>
     <row r="17" spans="1:31" x14ac:dyDescent="0.4">
       <c r="A17" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>59</v>
       </c>
       <c r="C17" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="E17" s="1" t="s">
         <v>186</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>188</v>
       </c>
       <c r="H17" s="1">
         <v>1</v>
@@ -13964,19 +14489,19 @@
     </row>
     <row r="18" spans="1:31" x14ac:dyDescent="0.4">
       <c r="A18" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>59</v>
       </c>
       <c r="C18" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="E18" s="1" t="s">
         <v>186</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>188</v>
       </c>
       <c r="H18" s="1">
         <v>1</v>
@@ -13985,7 +14510,7 @@
         <v>46087</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="N18" s="1">
         <v>-3</v>
@@ -14028,19 +14553,19 @@
     </row>
     <row r="19" spans="1:31" x14ac:dyDescent="0.4">
       <c r="A19" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>59</v>
       </c>
       <c r="C19" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="E19" s="1" t="s">
         <v>186</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>188</v>
       </c>
       <c r="H19" s="1">
         <v>1</v>
@@ -14049,7 +14574,7 @@
         <v>46087</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="N19" s="1">
         <v>-5.4977520200000001</v>
@@ -14092,19 +14617,19 @@
     </row>
     <row r="20" spans="1:31" x14ac:dyDescent="0.4">
       <c r="A20" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>59</v>
       </c>
       <c r="C20" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="E20" s="1" t="s">
         <v>186</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>188</v>
       </c>
       <c r="H20" s="1">
         <v>1</v>
@@ -14113,7 +14638,7 @@
         <v>46087</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="N20" s="1">
         <v>-5.5477520199999999</v>
@@ -14156,19 +14681,19 @@
     </row>
     <row r="21" spans="1:31" x14ac:dyDescent="0.4">
       <c r="A21" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>59</v>
       </c>
       <c r="C21" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="E21" s="1" t="s">
         <v>186</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>188</v>
       </c>
       <c r="H21" s="1">
         <v>1</v>
@@ -14177,7 +14702,7 @@
         <v>46087</v>
       </c>
       <c r="M21" s="1" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="N21" s="1">
         <v>-5.7895520200000004</v>
@@ -14220,19 +14745,19 @@
     </row>
     <row r="22" spans="1:31" x14ac:dyDescent="0.4">
       <c r="A22" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>59</v>
       </c>
       <c r="C22" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="E22" s="1" t="s">
         <v>186</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>188</v>
       </c>
       <c r="H22" s="1">
         <v>1</v>
@@ -14241,7 +14766,7 @@
         <v>46087</v>
       </c>
       <c r="M22" s="1" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="N22" s="1">
         <v>-0.05</v>
@@ -14284,19 +14809,19 @@
     </row>
     <row r="23" spans="1:31" x14ac:dyDescent="0.4">
       <c r="A23" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>59</v>
       </c>
       <c r="C23" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="E23" s="1" t="s">
         <v>186</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>188</v>
       </c>
       <c r="H23" s="1">
         <v>1</v>
@@ -14305,7 +14830,7 @@
         <v>46087</v>
       </c>
       <c r="M23" s="1" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="N23" s="1">
         <v>-0.2918</v>
@@ -14348,19 +14873,19 @@
     </row>
     <row r="24" spans="1:31" x14ac:dyDescent="0.4">
       <c r="A24" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>59</v>
       </c>
       <c r="C24" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="E24" s="1" t="s">
         <v>186</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>188</v>
       </c>
       <c r="H24" s="1">
         <v>1</v>
@@ -14369,7 +14894,7 @@
         <v>46087</v>
       </c>
       <c r="M24" s="1" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="N24" s="1">
         <v>-5.7895520200000004</v>
@@ -14412,19 +14937,19 @@
     </row>
     <row r="25" spans="1:31" x14ac:dyDescent="0.4">
       <c r="A25" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>59</v>
       </c>
       <c r="C25" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="E25" s="1" t="s">
         <v>186</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>188</v>
       </c>
       <c r="H25" s="1">
         <v>1</v>
@@ -14433,7 +14958,7 @@
         <v>46087</v>
       </c>
       <c r="M25" s="1" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="N25" s="1">
         <v>-0.24179999999999999</v>
@@ -14476,19 +15001,19 @@
     </row>
     <row r="26" spans="1:31" x14ac:dyDescent="0.4">
       <c r="A26" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>59</v>
       </c>
       <c r="C26" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="E26" s="1" t="s">
         <v>186</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>188</v>
       </c>
       <c r="H26" s="1">
         <v>1</v>
@@ -14497,7 +15022,7 @@
         <v>46087</v>
       </c>
       <c r="M26" s="1" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="N26" s="1">
         <v>-0.24179999999999999</v>
@@ -14540,19 +15065,19 @@
     </row>
     <row r="27" spans="1:31" x14ac:dyDescent="0.4">
       <c r="A27" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>59</v>
       </c>
       <c r="C27" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="E27" s="1" t="s">
         <v>186</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>188</v>
       </c>
       <c r="H27" s="1">
         <v>1</v>
@@ -14561,7 +15086,7 @@
         <v>46087</v>
       </c>
       <c r="M27" s="1" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="N27" s="1">
         <v>-5.9996570199999999</v>
@@ -14604,19 +15129,19 @@
     </row>
     <row r="28" spans="1:31" x14ac:dyDescent="0.4">
       <c r="A28" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>59</v>
       </c>
       <c r="C28" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="E28" s="1" t="s">
         <v>186</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>188</v>
       </c>
       <c r="H28" s="1">
         <v>1</v>
@@ -14625,7 +15150,7 @@
         <v>46087</v>
       </c>
       <c r="M28" s="1" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="N28" s="1">
         <v>-2.4973153799999999</v>
@@ -14668,19 +15193,19 @@
     </row>
     <row r="29" spans="1:31" x14ac:dyDescent="0.4">
       <c r="A29" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>59</v>
       </c>
       <c r="C29" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="E29" s="1" t="s">
         <v>186</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>188</v>
       </c>
       <c r="H29" s="1">
         <v>1</v>
@@ -14689,7 +15214,7 @@
         <v>46087</v>
       </c>
       <c r="M29" s="1" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="N29" s="1">
         <v>-1.0847240199999999</v>
@@ -14732,19 +15257,19 @@
     </row>
     <row r="30" spans="1:31" x14ac:dyDescent="0.4">
       <c r="A30" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>59</v>
       </c>
       <c r="C30" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="E30" s="1" t="s">
         <v>186</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>188</v>
       </c>
       <c r="H30" s="1">
         <v>1</v>
@@ -14753,7 +15278,7 @@
         <v>46087</v>
       </c>
       <c r="M30" s="1" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="N30" s="1">
         <v>-0.21252689</v>
@@ -14796,19 +15321,19 @@
     </row>
     <row r="31" spans="1:31" x14ac:dyDescent="0.4">
       <c r="A31" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>59</v>
       </c>
       <c r="C31" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="E31" s="1" t="s">
         <v>186</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>188</v>
       </c>
       <c r="H31" s="1">
         <v>1</v>
@@ -14817,7 +15342,7 @@
         <v>46087</v>
       </c>
       <c r="M31" s="1" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="N31" s="1">
         <v>-2.2592068799999998</v>
@@ -14860,19 +15385,19 @@
     </row>
     <row r="32" spans="1:31" x14ac:dyDescent="0.4">
       <c r="A32" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>59</v>
       </c>
       <c r="C32" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="E32" s="1" t="s">
         <v>186</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>188</v>
       </c>
       <c r="H32" s="1">
         <v>1</v>
@@ -14881,7 +15406,7 @@
         <v>46087</v>
       </c>
       <c r="M32" s="1" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="N32" s="1">
         <v>-1.96740688</v>
@@ -14924,19 +15449,19 @@
     </row>
     <row r="33" spans="1:31" x14ac:dyDescent="0.4">
       <c r="A33" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>59</v>
       </c>
       <c r="C33" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="E33" s="1" t="s">
         <v>186</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>188</v>
       </c>
       <c r="H33" s="1">
         <v>1</v>
@@ -14945,7 +15470,7 @@
         <v>46087</v>
       </c>
       <c r="M33" s="1" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="N33" s="1">
         <v>-4.0489291700000001</v>
@@ -14988,19 +15513,19 @@
     </row>
     <row r="34" spans="1:31" x14ac:dyDescent="0.4">
       <c r="A34" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>59</v>
       </c>
       <c r="C34" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="E34" s="1" t="s">
         <v>186</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>188</v>
       </c>
       <c r="H34" s="1">
         <v>1</v>
@@ -15009,7 +15534,7 @@
         <v>46087</v>
       </c>
       <c r="M34" s="1" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="N34" s="1">
         <v>-3.5134851600000001</v>
@@ -15049,19 +15574,19 @@
     </row>
     <row r="35" spans="1:31" x14ac:dyDescent="0.4">
       <c r="A35" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>59</v>
       </c>
       <c r="C35" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="E35" s="1" t="s">
         <v>186</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>188</v>
       </c>
       <c r="H35" s="1">
         <v>1</v>
@@ -15070,7 +15595,7 @@
         <v>46087</v>
       </c>
       <c r="M35" s="1" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="N35" s="1">
         <v>-1.45325536</v>
@@ -15110,19 +15635,19 @@
     </row>
     <row r="36" spans="1:31" x14ac:dyDescent="0.4">
       <c r="A36" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>59</v>
       </c>
       <c r="C36" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="E36" s="1" t="s">
         <v>186</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>188</v>
       </c>
       <c r="H36" s="1">
         <v>1</v>
@@ -15131,7 +15656,7 @@
         <v>46087</v>
       </c>
       <c r="M36" s="1" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="N36" s="1">
         <v>-0.51348516</v>
@@ -15171,7 +15696,7 @@
     </row>
     <row r="37" spans="1:31" x14ac:dyDescent="0.4">
       <c r="A37" s="1" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>59</v>
@@ -15180,10 +15705,10 @@
         <v>58</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>63</v>
@@ -15241,7 +15766,7 @@
     </row>
     <row r="38" spans="1:31" x14ac:dyDescent="0.4">
       <c r="A38" s="1" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>59</v>
@@ -15250,10 +15775,10 @@
         <v>58</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>63</v>
@@ -15311,22 +15836,22 @@
     </row>
     <row r="39" spans="1:31" x14ac:dyDescent="0.4">
       <c r="A39" s="1" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>59</v>
       </c>
       <c r="C39" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="G39" s="1" t="s">
         <v>297</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>298</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>298</v>
-      </c>
-      <c r="G39" s="1" t="s">
-        <v>299</v>
       </c>
       <c r="H39" s="1">
         <v>1</v>
@@ -15375,25 +15900,25 @@
     </row>
     <row r="40" spans="1:31" x14ac:dyDescent="0.4">
       <c r="A40" s="1" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>59</v>
       </c>
       <c r="C40" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="D40" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="D40" s="1" t="s">
-        <v>308</v>
-      </c>
       <c r="E40" s="1" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>60</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="H40" s="1">
         <v>1000</v>
@@ -15405,13 +15930,13 @@
         <v>46156</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="L40" s="44">
         <v>46097</v>
       </c>
       <c r="M40" s="1" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="N40" s="1">
         <v>-3</v>
@@ -15451,25 +15976,25 @@
     </row>
     <row r="41" spans="1:31" x14ac:dyDescent="0.4">
       <c r="A41" s="1" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>59</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>60</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="H41" s="1">
         <v>1000</v>
@@ -15481,7 +16006,7 @@
         <v>46156</v>
       </c>
       <c r="K41" s="1" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="L41" s="44">
         <v>46097</v>
@@ -15527,7 +16052,7 @@
     </row>
     <row r="42" spans="1:31" x14ac:dyDescent="0.4">
       <c r="A42" s="1" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>59</v>
@@ -15536,10 +16061,10 @@
         <v>58</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>80</v>
@@ -15597,19 +16122,19 @@
     </row>
     <row r="43" spans="1:31" x14ac:dyDescent="0.4">
       <c r="A43" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>59</v>
       </c>
       <c r="C43" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="E43" s="1" t="s">
         <v>186</v>
-      </c>
-      <c r="D43" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="E43" s="1" t="s">
-        <v>188</v>
       </c>
       <c r="H43" s="1">
         <v>1</v>
@@ -15658,19 +16183,19 @@
     </row>
     <row r="44" spans="1:31" x14ac:dyDescent="0.4">
       <c r="A44" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>59</v>
       </c>
       <c r="C44" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="E44" s="1" t="s">
         <v>186</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="E44" s="1" t="s">
-        <v>188</v>
       </c>
       <c r="H44" s="1">
         <v>1</v>
@@ -15719,19 +16244,19 @@
     </row>
     <row r="45" spans="1:31" x14ac:dyDescent="0.4">
       <c r="A45" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>59</v>
       </c>
       <c r="C45" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="E45" s="1" t="s">
         <v>186</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="E45" s="1" t="s">
-        <v>188</v>
       </c>
       <c r="H45" s="1">
         <v>1</v>
@@ -15780,19 +16305,19 @@
     </row>
     <row r="46" spans="1:31" x14ac:dyDescent="0.4">
       <c r="A46" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>59</v>
       </c>
       <c r="C46" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="E46" s="1" t="s">
         <v>186</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="E46" s="1" t="s">
-        <v>188</v>
       </c>
       <c r="H46" s="1">
         <v>1</v>
@@ -15841,19 +16366,19 @@
     </row>
     <row r="47" spans="1:31" x14ac:dyDescent="0.4">
       <c r="A47" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>59</v>
       </c>
       <c r="C47" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="E47" s="1" t="s">
         <v>186</v>
-      </c>
-      <c r="D47" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="E47" s="1" t="s">
-        <v>188</v>
       </c>
       <c r="H47" s="1">
         <v>1</v>
@@ -15902,19 +16427,19 @@
     </row>
     <row r="48" spans="1:31" x14ac:dyDescent="0.4">
       <c r="A48" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>59</v>
       </c>
       <c r="C48" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="E48" s="1" t="s">
         <v>186</v>
-      </c>
-      <c r="D48" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="E48" s="1" t="s">
-        <v>188</v>
       </c>
       <c r="H48" s="1">
         <v>1</v>
@@ -15963,19 +16488,19 @@
     </row>
     <row r="49" spans="1:24" x14ac:dyDescent="0.4">
       <c r="A49" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>59</v>
       </c>
       <c r="C49" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="E49" s="1" t="s">
         <v>186</v>
-      </c>
-      <c r="D49" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="E49" s="1" t="s">
-        <v>188</v>
       </c>
       <c r="H49" s="1">
         <v>1</v>
@@ -16024,19 +16549,19 @@
     </row>
     <row r="50" spans="1:24" x14ac:dyDescent="0.4">
       <c r="A50" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>59</v>
       </c>
       <c r="C50" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="E50" s="1" t="s">
         <v>186</v>
-      </c>
-      <c r="D50" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="E50" s="1" t="s">
-        <v>188</v>
       </c>
       <c r="H50" s="1">
         <v>1</v>
@@ -16085,19 +16610,19 @@
     </row>
     <row r="51" spans="1:24" x14ac:dyDescent="0.4">
       <c r="A51" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>59</v>
       </c>
       <c r="C51" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="E51" s="1" t="s">
         <v>186</v>
-      </c>
-      <c r="D51" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="E51" s="1" t="s">
-        <v>188</v>
       </c>
       <c r="H51" s="1">
         <v>1</v>
@@ -16146,19 +16671,19 @@
     </row>
     <row r="52" spans="1:24" x14ac:dyDescent="0.4">
       <c r="A52" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>59</v>
       </c>
       <c r="C52" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="E52" s="1" t="s">
         <v>186</v>
-      </c>
-      <c r="D52" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="E52" s="1" t="s">
-        <v>188</v>
       </c>
       <c r="H52" s="1">
         <v>1</v>
@@ -16207,19 +16732,19 @@
     </row>
     <row r="53" spans="1:24" x14ac:dyDescent="0.4">
       <c r="A53" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>59</v>
       </c>
       <c r="C53" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="E53" s="1" t="s">
         <v>186</v>
-      </c>
-      <c r="D53" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="E53" s="1" t="s">
-        <v>188</v>
       </c>
       <c r="H53" s="1">
         <v>1</v>
@@ -16268,19 +16793,19 @@
     </row>
     <row r="54" spans="1:24" x14ac:dyDescent="0.4">
       <c r="A54" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>59</v>
       </c>
       <c r="C54" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="E54" s="1" t="s">
         <v>186</v>
-      </c>
-      <c r="D54" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="E54" s="1" t="s">
-        <v>188</v>
       </c>
       <c r="H54" s="1">
         <v>1</v>
@@ -16329,19 +16854,19 @@
     </row>
     <row r="55" spans="1:24" x14ac:dyDescent="0.4">
       <c r="A55" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>59</v>
       </c>
       <c r="C55" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="E55" s="1" t="s">
         <v>186</v>
-      </c>
-      <c r="D55" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="E55" s="1" t="s">
-        <v>188</v>
       </c>
       <c r="H55" s="1">
         <v>1</v>
@@ -16390,19 +16915,19 @@
     </row>
     <row r="56" spans="1:24" x14ac:dyDescent="0.4">
       <c r="A56" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>59</v>
       </c>
       <c r="C56" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="E56" s="1" t="s">
         <v>186</v>
-      </c>
-      <c r="D56" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="E56" s="1" t="s">
-        <v>188</v>
       </c>
       <c r="H56" s="1">
         <v>1</v>
@@ -16451,19 +16976,19 @@
     </row>
     <row r="57" spans="1:24" x14ac:dyDescent="0.4">
       <c r="A57" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>59</v>
       </c>
       <c r="C57" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="E57" s="1" t="s">
         <v>186</v>
-      </c>
-      <c r="D57" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="E57" s="1" t="s">
-        <v>188</v>
       </c>
       <c r="H57" s="1">
         <v>1</v>
@@ -16512,19 +17037,19 @@
     </row>
     <row r="58" spans="1:24" x14ac:dyDescent="0.4">
       <c r="A58" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>59</v>
       </c>
       <c r="C58" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="E58" s="1" t="s">
         <v>186</v>
-      </c>
-      <c r="D58" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="E58" s="1" t="s">
-        <v>188</v>
       </c>
       <c r="H58" s="1">
         <v>1</v>
@@ -16573,19 +17098,19 @@
     </row>
     <row r="59" spans="1:24" x14ac:dyDescent="0.4">
       <c r="A59" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>59</v>
       </c>
       <c r="C59" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="E59" s="1" t="s">
         <v>186</v>
-      </c>
-      <c r="D59" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="E59" s="1" t="s">
-        <v>188</v>
       </c>
       <c r="H59" s="1">
         <v>1</v>
@@ -16634,7 +17159,7 @@
     </row>
     <row r="60" spans="1:24" x14ac:dyDescent="0.4">
       <c r="A60" s="1" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>59</v>
@@ -16643,16 +17168,16 @@
         <v>58</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>78</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="H60" s="1">
         <v>5</v>
@@ -16704,7 +17229,7 @@
     </row>
     <row r="61" spans="1:24" x14ac:dyDescent="0.4">
       <c r="A61" s="1" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>59</v>
@@ -16713,16 +17238,16 @@
         <v>58</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>78</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="H61" s="1">
         <v>5</v>
@@ -16774,7 +17299,7 @@
     </row>
     <row r="62" spans="1:24" x14ac:dyDescent="0.4">
       <c r="A62" s="1" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>59</v>
@@ -16783,16 +17308,16 @@
         <v>58</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>78</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="H62" s="1">
         <v>5</v>
@@ -16844,7 +17369,7 @@
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.4">
       <c r="A63" s="1" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>59</v>
@@ -16853,16 +17378,16 @@
         <v>58</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>78</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="H63" s="1">
         <v>5</v>
@@ -16914,7 +17439,7 @@
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.4">
       <c r="A64" s="1" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>59</v>
@@ -16923,16 +17448,16 @@
         <v>58</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>78</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="H64" s="1">
         <v>5</v>
@@ -16941,10 +17466,10 @@
         <v>46185</v>
       </c>
       <c r="L64" s="44">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="M64" s="1" t="s">
-        <v>85</v>
+        <v>292</v>
       </c>
       <c r="N64" s="1">
         <v>-1</v>
@@ -16953,7 +17478,10 @@
         <v>51510</v>
       </c>
       <c r="P64" s="1">
-        <v>256050</v>
+        <v>-257550</v>
+      </c>
+      <c r="Q64" s="1">
+        <v>-3.02</v>
       </c>
       <c r="R64" s="1" t="s">
         <v>59</v>
@@ -16976,12 +17504,12 @@
       </c>
       <c r="X64" s="42">
         <f t="shared" ref="X64:X65" si="35">Q64</f>
-        <v>0</v>
+        <v>-3.02</v>
       </c>
     </row>
     <row r="65" spans="1:24" x14ac:dyDescent="0.4">
       <c r="A65" s="1" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>59</v>
@@ -16990,16 +17518,16 @@
         <v>58</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>78</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="H65" s="1">
         <v>5</v>
@@ -17008,19 +17536,22 @@
         <v>46185</v>
       </c>
       <c r="L65" s="44">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="M65" s="1" t="s">
-        <v>85</v>
+        <v>292</v>
       </c>
       <c r="N65" s="1">
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="O65" s="1">
         <v>51460</v>
       </c>
       <c r="P65" s="1">
-        <v>256050</v>
+        <v>-257300</v>
+      </c>
+      <c r="Q65" s="1">
+        <v>-3.02</v>
       </c>
       <c r="R65" s="1" t="s">
         <v>59</v>
@@ -17035,7 +17566,7 @@
       </c>
       <c r="V65" s="42">
         <f t="shared" si="33"/>
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="W65" s="42">
         <f t="shared" si="34"/>
@@ -17043,29 +17574,230 @@
       </c>
       <c r="X65" s="42">
         <f t="shared" si="35"/>
-        <v>0</v>
+        <v>-3.02</v>
       </c>
     </row>
     <row r="66" spans="1:24" x14ac:dyDescent="0.4">
-      <c r="T66" s="43"/>
-      <c r="U66" s="42"/>
-      <c r="V66" s="42"/>
-      <c r="W66" s="42"/>
-      <c r="X66" s="42"/>
+      <c r="A66" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="F66" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="G66" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="H66" s="1">
+        <v>5</v>
+      </c>
+      <c r="J66" s="44">
+        <v>46185</v>
+      </c>
+      <c r="L66" s="44">
+        <v>46112</v>
+      </c>
+      <c r="M66" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="N66" s="1">
+        <v>-4</v>
+      </c>
+      <c r="O66" s="1">
+        <v>51460</v>
+      </c>
+      <c r="P66" s="1">
+        <v>-1029200</v>
+      </c>
+      <c r="Q66" s="1">
+        <v>-12.08</v>
+      </c>
+      <c r="R66" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="T66" s="43">
+        <f>IF(ISNUMBER(VLOOKUP(U66,Blotter!B:C,2,0)),VLOOKUP(U66,Blotter!B:C,2,0),"")</f>
+        <v>5</v>
+      </c>
+      <c r="U66" s="42" t="str">
+        <f t="shared" ref="U66" si="36">D66</f>
+        <v>NKDM6</v>
+      </c>
+      <c r="V66" s="42">
+        <f t="shared" ref="V66" si="37">N66</f>
+        <v>-4</v>
+      </c>
+      <c r="W66" s="42">
+        <f t="shared" ref="W66" si="38">O66</f>
+        <v>51460</v>
+      </c>
+      <c r="X66" s="42">
+        <f t="shared" ref="X66" si="39">Q66</f>
+        <v>-12.08</v>
+      </c>
     </row>
     <row r="67" spans="1:24" x14ac:dyDescent="0.4">
-      <c r="T67" s="43"/>
-      <c r="U67" s="42"/>
-      <c r="V67" s="42"/>
-      <c r="W67" s="42"/>
-      <c r="X67" s="42"/>
+      <c r="A67" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="F67" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="G67" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="H67" s="1">
+        <v>100</v>
+      </c>
+      <c r="I67" s="1">
+        <v>4930</v>
+      </c>
+      <c r="J67" s="44">
+        <v>46168</v>
+      </c>
+      <c r="K67" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="L67" s="44">
+        <v>46119</v>
+      </c>
+      <c r="M67" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="N67" s="1">
+        <v>1</v>
+      </c>
+      <c r="O67" s="1">
+        <v>125.4</v>
+      </c>
+      <c r="P67" s="1">
+        <v>12540</v>
+      </c>
+      <c r="Q67" s="1">
+        <v>-2.52</v>
+      </c>
+      <c r="R67" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="T67" s="43">
+        <f>IF(ISNUMBER(VLOOKUP(U67,Blotter!B:C,2,0)),VLOOKUP(U67,Blotter!B:C,2,0),"")</f>
+        <v>6</v>
+      </c>
+      <c r="U67" s="42" t="str">
+        <f t="shared" ref="U67:U68" si="40">D67</f>
+        <v>OGM6 C4930</v>
+      </c>
+      <c r="V67" s="42">
+        <f t="shared" ref="V67:V68" si="41">N67</f>
+        <v>1</v>
+      </c>
+      <c r="W67" s="42">
+        <f t="shared" ref="W67:W68" si="42">O67</f>
+        <v>125.4</v>
+      </c>
+      <c r="X67" s="42">
+        <f t="shared" ref="X67:X68" si="43">Q67</f>
+        <v>-2.52</v>
+      </c>
     </row>
     <row r="68" spans="1:24" x14ac:dyDescent="0.4">
-      <c r="T68" s="43"/>
-      <c r="U68" s="42"/>
-      <c r="V68" s="42"/>
-      <c r="W68" s="42"/>
-      <c r="X68" s="42"/>
+      <c r="A68" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="E68" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="G68" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="H68" s="1">
+        <v>100</v>
+      </c>
+      <c r="I68" s="1">
+        <v>5500</v>
+      </c>
+      <c r="J68" s="44">
+        <v>46168</v>
+      </c>
+      <c r="K68" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="L68" s="44">
+        <v>46119</v>
+      </c>
+      <c r="M68" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="N68" s="1">
+        <v>-1</v>
+      </c>
+      <c r="O68" s="1">
+        <v>26.4</v>
+      </c>
+      <c r="P68" s="1">
+        <v>-2640</v>
+      </c>
+      <c r="Q68" s="1">
+        <v>-2.52</v>
+      </c>
+      <c r="R68" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="T68" s="43">
+        <f>IF(ISNUMBER(VLOOKUP(U68,Blotter!B:C,2,0)),VLOOKUP(U68,Blotter!B:C,2,0),"")</f>
+        <v>6</v>
+      </c>
+      <c r="U68" s="42" t="str">
+        <f t="shared" si="40"/>
+        <v>OGM6 C5500</v>
+      </c>
+      <c r="V68" s="42">
+        <f t="shared" si="41"/>
+        <v>-1</v>
+      </c>
+      <c r="W68" s="42">
+        <f t="shared" si="42"/>
+        <v>26.4</v>
+      </c>
+      <c r="X68" s="42">
+        <f t="shared" si="43"/>
+        <v>-2.52</v>
+      </c>
     </row>
     <row r="69" spans="1:24" x14ac:dyDescent="0.4">
       <c r="T69" s="43"/>
@@ -24536,21 +25268,21 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A1" s="90" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B1" s="56"/>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A3" s="80" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B3" s="89" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A4" s="80" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B4" s="89">
         <v>7497</v>
@@ -24558,7 +25290,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A5" s="80" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B5" s="89">
         <v>11</v>
@@ -24566,7 +25298,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A6" s="80" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B6" s="89">
         <v>0.25</v>
@@ -24574,15 +25306,15 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A7" s="80" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B7" s="89" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A8" s="80" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B8" s="89">
         <v>3</v>
@@ -24590,22 +25322,22 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A10" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A11" s="1" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A12" s="1" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A13" s="1" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
   </sheetData>
@@ -24636,43 +25368,43 @@
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A1" s="82" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B1" s="82" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C1" s="82" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="D1" s="82" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="E1" s="82" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="F1" s="82" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="G1" s="82" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="H1" s="82" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="I1" s="82" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="J1" s="82" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="K1" s="82" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="L1" s="82" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="M1" s="82" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.4">
@@ -24680,7 +25412,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="88" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C2" s="88" t="s">
         <v>58</v>
@@ -24695,7 +25427,7 @@
         <v>59</v>
       </c>
       <c r="G2" s="88" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="H2" s="88"/>
       <c r="I2" s="88"/>
@@ -24709,7 +25441,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="88" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C3" s="88" t="s">
         <v>58</v>
@@ -24724,7 +25456,7 @@
         <v>59</v>
       </c>
       <c r="G3" s="88" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="H3" s="88"/>
       <c r="I3" s="88"/>
@@ -24738,7 +25470,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="88" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C4" s="88" t="s">
         <v>58</v>
@@ -24753,7 +25485,7 @@
         <v>59</v>
       </c>
       <c r="G4" s="88" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="H4" s="88"/>
       <c r="I4" s="88"/>
@@ -24767,7 +25499,7 @@
         <v>1</v>
       </c>
       <c r="B5" s="88" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C5" s="88" t="s">
         <v>58</v>
@@ -24782,13 +25514,13 @@
         <v>56</v>
       </c>
       <c r="G5" s="88" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="H5" s="88"/>
       <c r="I5" s="88"/>
       <c r="J5" s="88"/>
       <c r="K5" s="88" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="L5" s="88"/>
       <c r="M5" s="88"/>
@@ -24798,13 +25530,13 @@
         <v>1</v>
       </c>
       <c r="B6" s="88" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C6" s="88" t="s">
         <v>58</v>
       </c>
       <c r="D6" s="88" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="E6" s="88" t="s">
         <v>78</v>
@@ -24813,7 +25545,7 @@
         <v>59</v>
       </c>
       <c r="G6" s="88" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="H6" s="88"/>
       <c r="I6" s="88"/>
@@ -24821,7 +25553,7 @@
         <v>5</v>
       </c>
       <c r="K6" s="88" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="L6" s="88"/>
       <c r="M6" s="88"/>
@@ -24831,7 +25563,7 @@
         <v>1</v>
       </c>
       <c r="B7" s="88" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C7" s="88" t="s">
         <v>58</v>
@@ -24862,7 +25594,7 @@
         <v>1</v>
       </c>
       <c r="B8" s="88" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C8" s="88" t="s">
         <v>58</v>
@@ -24877,7 +25609,7 @@
         <v>59</v>
       </c>
       <c r="G8" s="88" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="H8" s="88"/>
       <c r="I8" s="88"/>
@@ -24893,7 +25625,7 @@
         <v>1</v>
       </c>
       <c r="B9" s="88" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C9" s="88" t="s">
         <v>58</v>
@@ -24908,7 +25640,7 @@
         <v>59</v>
       </c>
       <c r="G9" s="88" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="H9" s="88"/>
       <c r="I9" s="88"/>
@@ -24924,7 +25656,7 @@
         <v>1</v>
       </c>
       <c r="B10" s="88" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C10" s="88" t="s">
         <v>58</v>
@@ -24939,7 +25671,7 @@
         <v>59</v>
       </c>
       <c r="G10" s="88" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="H10" s="88"/>
       <c r="I10" s="88"/>
@@ -24955,7 +25687,7 @@
         <v>1</v>
       </c>
       <c r="B11" s="88" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C11" s="88" t="s">
         <v>58</v>
@@ -24970,7 +25702,7 @@
         <v>59</v>
       </c>
       <c r="G11" s="88" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="H11" s="88"/>
       <c r="I11" s="88"/>
@@ -24986,7 +25718,7 @@
         <v>1</v>
       </c>
       <c r="B12" s="88" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C12" s="88" t="s">
         <v>58</v>
@@ -25017,7 +25749,7 @@
         <v>1</v>
       </c>
       <c r="B13" s="88" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C13" s="88" t="s">
         <v>58</v>
@@ -25048,7 +25780,7 @@
         <v>1</v>
       </c>
       <c r="B14" s="88" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C14" s="88" t="s">
         <v>58</v>
@@ -25079,7 +25811,7 @@
         <v>1</v>
       </c>
       <c r="B15" s="88" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C15" s="88" t="s">
         <v>58</v>
@@ -25110,7 +25842,7 @@
         <v>1</v>
       </c>
       <c r="B16" s="88" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C16" s="88" t="s">
         <v>58</v>
@@ -25141,7 +25873,7 @@
         <v>1</v>
       </c>
       <c r="B17" s="88" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C17" s="88" t="s">
         <v>58</v>
@@ -25172,7 +25904,7 @@
         <v>1</v>
       </c>
       <c r="B18" s="88" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C18" s="88" t="s">
         <v>58</v>
@@ -25203,7 +25935,7 @@
         <v>1</v>
       </c>
       <c r="B19" s="88" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C19" s="88" t="s">
         <v>58</v>
@@ -25296,7 +26028,7 @@
         <v>1</v>
       </c>
       <c r="B22" s="88" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C22" s="88" t="s">
         <v>58</v>
@@ -25327,7 +26059,7 @@
         <v>1</v>
       </c>
       <c r="B23" s="88" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="C23" s="88" t="s">
         <v>58</v>
@@ -25342,7 +26074,7 @@
         <v>59</v>
       </c>
       <c r="G23" s="88" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="H23" s="88"/>
       <c r="I23" s="88"/>
@@ -25358,7 +26090,7 @@
         <v>1</v>
       </c>
       <c r="B24" s="88" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C24" s="88" t="s">
         <v>58</v>
@@ -25373,7 +26105,7 @@
         <v>59</v>
       </c>
       <c r="G24" s="88" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="H24" s="88"/>
       <c r="I24" s="88"/>
@@ -25389,7 +26121,7 @@
         <v>1</v>
       </c>
       <c r="B25" s="88" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C25" s="88" t="s">
         <v>58</v>
@@ -25404,7 +26136,7 @@
         <v>59</v>
       </c>
       <c r="G25" s="88" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="H25" s="88"/>
       <c r="I25" s="88"/>
@@ -25420,7 +26152,7 @@
         <v>1</v>
       </c>
       <c r="B26" s="88" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C26" s="88" t="s">
         <v>58</v>
@@ -25435,7 +26167,7 @@
         <v>59</v>
       </c>
       <c r="G26" s="88" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="H26" s="88"/>
       <c r="I26" s="88"/>
@@ -25451,7 +26183,7 @@
         <v>1</v>
       </c>
       <c r="B27" s="88" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C27" s="88" t="s">
         <v>58</v>
@@ -25466,7 +26198,7 @@
         <v>59</v>
       </c>
       <c r="G27" s="88" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="H27" s="88"/>
       <c r="I27" s="88"/>
@@ -25482,7 +26214,7 @@
         <v>1</v>
       </c>
       <c r="B28" s="88" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C28" s="88" t="s">
         <v>58</v>
@@ -25497,7 +26229,7 @@
         <v>59</v>
       </c>
       <c r="G28" s="88" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="H28" s="88"/>
       <c r="I28" s="88"/>
@@ -25513,7 +26245,7 @@
         <v>1</v>
       </c>
       <c r="B29" s="88" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C29" s="88" t="s">
         <v>58</v>
@@ -25528,7 +26260,7 @@
         <v>59</v>
       </c>
       <c r="G29" s="88" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="H29" s="88"/>
       <c r="I29" s="88"/>
@@ -25544,7 +26276,7 @@
         <v>1</v>
       </c>
       <c r="B30" s="88" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C30" s="88" t="s">
         <v>58</v>
@@ -25559,7 +26291,7 @@
         <v>59</v>
       </c>
       <c r="G30" s="88" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="H30" s="88"/>
       <c r="I30" s="88"/>
@@ -25575,13 +26307,13 @@
         <v>1</v>
       </c>
       <c r="B31" s="88" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C31" s="88" t="s">
         <v>58</v>
       </c>
       <c r="D31" s="88" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="E31" s="88" t="s">
         <v>79</v>
@@ -25590,13 +26322,13 @@
         <v>56</v>
       </c>
       <c r="G31" s="88" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="H31" s="88"/>
       <c r="I31" s="88"/>
       <c r="J31" s="88"/>
       <c r="K31" s="88" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="L31" s="88"/>
       <c r="M31" s="88"/>
@@ -25606,13 +26338,13 @@
         <v>1</v>
       </c>
       <c r="B32" s="88" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C32" s="88" t="s">
         <v>58</v>
       </c>
       <c r="D32" s="88" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="E32" s="88" t="s">
         <v>79</v>
@@ -25621,13 +26353,13 @@
         <v>56</v>
       </c>
       <c r="G32" s="88" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="H32" s="88"/>
       <c r="I32" s="88"/>
       <c r="J32" s="88"/>
       <c r="K32" s="88" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="L32" s="88"/>
       <c r="M32" s="88"/>
@@ -25637,13 +26369,13 @@
         <v>1</v>
       </c>
       <c r="B33" s="88" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C33" s="88" t="s">
         <v>58</v>
       </c>
       <c r="D33" s="88" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="E33" s="88" t="s">
         <v>79</v>
@@ -25652,13 +26384,13 @@
         <v>56</v>
       </c>
       <c r="G33" s="88" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="H33" s="88"/>
       <c r="I33" s="88"/>
       <c r="J33" s="88"/>
       <c r="K33" s="88" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="M33" s="88"/>
     </row>
@@ -25667,16 +26399,16 @@
         <v>1</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C34" s="88" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D34" s="88" t="s">
         <v>44</v>
       </c>
       <c r="E34" s="88" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="F34" s="88" t="s">
         <v>59</v>
@@ -25689,16 +26421,16 @@
         <v>1</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C35" s="88" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D35" s="88" t="s">
         <v>45</v>
       </c>
       <c r="E35" s="88" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="F35" s="88" t="s">
         <v>59</v>
@@ -25716,10 +26448,10 @@
         <v>1</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C36" s="88" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="D36" s="88" t="s">
         <v>24</v>
@@ -25737,13 +26469,13 @@
         <v>75</v>
       </c>
       <c r="I36" s="88" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="J36" s="88">
         <v>1000</v>
       </c>
       <c r="K36" s="88" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="M36" s="88"/>
     </row>
@@ -25752,10 +26484,10 @@
         <v>1</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C37" s="88" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="D37" s="88" t="s">
         <v>24</v>
@@ -25773,22 +26505,85 @@
         <v>55</v>
       </c>
       <c r="I37" s="88" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="J37" s="88">
         <v>1000</v>
       </c>
       <c r="K37" s="88" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="M37" s="88"/>
     </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A38" s="88">
+        <v>1</v>
+      </c>
+      <c r="B38" s="9" t="s">
+        <v>334</v>
+      </c>
+      <c r="C38" s="88" t="s">
+        <v>304</v>
+      </c>
+      <c r="D38" s="88" t="s">
+        <v>26</v>
+      </c>
+      <c r="E38" s="88" t="s">
+        <v>80</v>
+      </c>
+      <c r="F38" s="88" t="s">
+        <v>59</v>
+      </c>
+      <c r="G38" s="88">
+        <v>20260526</v>
+      </c>
+      <c r="H38" s="88">
+        <v>5500</v>
+      </c>
+      <c r="I38" s="88" t="s">
+        <v>336</v>
+      </c>
+      <c r="J38" s="88">
+        <v>100</v>
+      </c>
+      <c r="K38" s="88" t="s">
+        <v>337</v>
+      </c>
+    </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="C39" s="31"/>
-      <c r="D39" s="31"/>
-      <c r="E39" s="31"/>
-      <c r="F39" s="31"/>
-      <c r="G39" s="31"/>
+      <c r="A39" s="88">
+        <v>1</v>
+      </c>
+      <c r="B39" s="9" t="s">
+        <v>335</v>
+      </c>
+      <c r="C39" s="88" t="s">
+        <v>304</v>
+      </c>
+      <c r="D39" s="88" t="s">
+        <v>26</v>
+      </c>
+      <c r="E39" s="88" t="s">
+        <v>80</v>
+      </c>
+      <c r="F39" s="88" t="s">
+        <v>59</v>
+      </c>
+      <c r="G39" s="88">
+        <v>20260526</v>
+      </c>
+      <c r="H39" s="88">
+        <v>4930</v>
+      </c>
+      <c r="I39" s="88" t="s">
+        <v>336</v>
+      </c>
+      <c r="J39" s="88">
+        <v>100</v>
+      </c>
+      <c r="K39" s="88" t="s">
+        <v>337</v>
+      </c>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.4">
       <c r="C40" s="31"/>
@@ -25890,7 +26685,7 @@
     </row>
     <row r="54" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C54" s="31" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D54" s="31" t="s">
         <v>27</v>
@@ -25924,7 +26719,7 @@
     </row>
     <row r="56" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C56" s="31" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D56" s="31" t="s">
         <v>28</v>
@@ -25941,7 +26736,7 @@
     </row>
     <row r="57" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C57" s="31" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D57" s="31" t="s">
         <v>29</v>
@@ -25958,7 +26753,7 @@
     </row>
     <row r="58" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C58" s="31" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D58" s="31" t="s">
         <v>31</v>
@@ -25975,7 +26770,7 @@
     </row>
     <row r="59" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C59" s="31" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D59" s="31" t="s">
         <v>32</v>
@@ -25992,7 +26787,7 @@
     </row>
     <row r="60" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C60" s="31" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D60" s="31" t="s">
         <v>33</v>
@@ -26009,7 +26804,7 @@
     </row>
     <row r="61" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C61" s="31" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D61" s="31" t="s">
         <v>34</v>
@@ -26026,7 +26821,7 @@
     </row>
     <row r="62" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C62" s="31" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D62" s="31" t="s">
         <v>64</v>
@@ -26077,7 +26872,7 @@
     </row>
     <row r="65" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C65" s="31" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D65" s="31" t="s">
         <v>37</v>

--- a/1XW_TradeBlotter_Web.xlsx
+++ b/1XW_TradeBlotter_Web.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0a601c1c2ba3d9f4/Trading/The Strategy Project/1XW Website/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="529" documentId="13_ncr:1_{6F5069F1-F0E7-4440-AA6D-4AFA11BBED1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F3315264-5564-4490-BD1A-2DD129804EB4}"/>
+  <xr:revisionPtr revIDLastSave="551" documentId="13_ncr:1_{6F5069F1-F0E7-4440-AA6D-4AFA11BBED1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{54424417-0BD1-4588-A603-84F978016F35}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="22695" windowHeight="14476" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -121,7 +121,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1517" uniqueCount="344">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1536" uniqueCount="350">
   <si>
     <t>WEEK</t>
   </si>
@@ -886,9 +886,6 @@
     <t>SIH6</t>
   </si>
   <si>
-    <t>6EH6</t>
-  </si>
-  <si>
     <t>6BH6</t>
   </si>
   <si>
@@ -1166,13 +1163,34 @@
   </si>
   <si>
     <t>Close</t>
+  </si>
+  <si>
+    <t>End of deflation era / pro-growth government policies / attractive valuations</t>
+  </si>
+  <si>
+    <t>Weekly retrace to previous support area and weekly up</t>
+  </si>
+  <si>
+    <t>Weekly hammer after 50% retrace and weekly up</t>
+  </si>
+  <si>
+    <t>Central banks buying spree / geopolitical or dollar shock hedge</t>
+  </si>
+  <si>
+    <t>Rate differential expectations, BCE 2-3 hikes before year-end</t>
+  </si>
+  <si>
+    <t>Weekly doji + weekly up / potential continuation to new highs</t>
+  </si>
+  <si>
+    <t>Long 6E Futures</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="13">
+  <numFmts count="15">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="0.00\x"/>
     <numFmt numFmtId="165" formatCode="#,##0.0"/>
@@ -1186,6 +1204,8 @@
     <numFmt numFmtId="173" formatCode="#,##0_-;\-#,##0_-;_-;_-@_-"/>
     <numFmt numFmtId="174" formatCode="#,##0.00_-;\-#,##0.00_-;_-;_-@_-"/>
     <numFmt numFmtId="175" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="#,##0.000"/>
+    <numFmt numFmtId="177" formatCode="#,##0.0000;\-#,##0.0000"/>
   </numFmts>
   <fonts count="36" x14ac:knownFonts="1">
     <font>
@@ -1838,7 +1858,7 @@
     <xf numFmtId="0" fontId="1" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="97">
+  <cellXfs count="100">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -2082,6 +2102,15 @@
     <xf numFmtId="10" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="44">
     <cellStyle name="20% - Accent1" xfId="21" builtinId="30" customBuiltin="1"/>
@@ -2321,7 +2350,7 @@
                   <c:v>2.8744450632010921E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2.4840775553442995E-2</c:v>
+                  <c:v>3.1763048617103662E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2481,7 +2510,7 @@
                   <c:v>2.8744450632010921E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5.4299260632010737E-2</c:v>
+                  <c:v>6.1420510632011149E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2878,7 +2907,7 @@
                   <c:v>1028.744450632011</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1054.2992606320108</c:v>
+                  <c:v>1061.4205106320112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3145,7 +3174,7 @@
               <c:f>[0]!DynDatePLB</c:f>
               <c:numCache>
                 <c:formatCode>d\-mmm\-yy</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>46081</c:v>
                 </c:pt>
@@ -3167,6 +3196,9 @@
                 <c:pt idx="6">
                   <c:v>46123</c:v>
                 </c:pt>
+                <c:pt idx="7">
+                  <c:v>46130</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3175,7 +3207,7 @@
               <c:f>[0]!DynInPLBPLB</c:f>
               <c:numCache>
                 <c:formatCode>0.00%</c:formatCode>
-                <c:ptCount val="7"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3196,6 +3228,9 @@
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>-5.8519850599000112E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-6.7934652093010084E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3250,7 +3285,7 @@
               <c:f>[0]!DynDatePLB</c:f>
               <c:numCache>
                 <c:formatCode>d\-mmm\-yy</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>46081</c:v>
                 </c:pt>
@@ -3272,6 +3307,9 @@
                 <c:pt idx="6">
                   <c:v>46123</c:v>
                 </c:pt>
+                <c:pt idx="7">
+                  <c:v>46130</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3280,7 +3318,7 @@
               <c:f>[0]!DynPLBPLB</c:f>
               <c:numCache>
                 <c:formatCode>0.00%</c:formatCode>
-                <c:ptCount val="7"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3301,6 +3339,9 @@
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>-2.6937720000000054E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-3.5797095000000057E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3355,7 +3396,7 @@
               <c:f>[0]!DynDatePLB</c:f>
               <c:numCache>
                 <c:formatCode>d\-mmm\-yy</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>46081</c:v>
                 </c:pt>
@@ -3377,6 +3418,9 @@
                 <c:pt idx="6">
                   <c:v>46123</c:v>
                 </c:pt>
+                <c:pt idx="7">
+                  <c:v>46130</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3385,27 +3429,30 @@
               <c:f>[0]!DynPerfPLB</c:f>
               <c:numCache>
                 <c:formatCode>0.00%</c:formatCode>
-                <c:ptCount val="7"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.2922690632011014E-2</c:v>
+                  <c:v>1.0612690632010979E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.0723780632010849E-2</c:v>
+                  <c:v>1.0933780632010892E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>6.5995606320108369E-3</c:v>
+                  <c:v>6.1195606320108009E-3</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.395959063201091E-2</c:v>
+                  <c:v>1.6517090632010678E-2</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>4.909533063201077E-2</c:v>
+                  <c:v>5.5127830632010433E-2</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>5.0350290632010575E-2</c:v>
+                  <c:v>5.4702790632010334E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>5.7471540632010543E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4055,7 +4102,7 @@
       </c>
       <c r="C1" s="79">
         <f ca="1">TODAY()</f>
-        <v>46123</v>
+        <v>46125</v>
       </c>
     </row>
     <row r="2" spans="2:11" x14ac:dyDescent="0.4">
@@ -4063,7 +4110,7 @@
         <v>107</v>
       </c>
       <c r="C2" s="37" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E2" s="47" t="s">
         <v>120</v>
@@ -4080,13 +4127,13 @@
       </c>
       <c r="C3" s="28">
         <f ca="1">OFFSET(NAV!B1,MATCH(C1,NAV!B:B,1),8)</f>
-        <v>1054299.2606320109</v>
+        <v>1061420.5106320111</v>
       </c>
       <c r="E3" s="47" t="s">
         <v>121</v>
       </c>
       <c r="F3" s="47" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="G3" s="47"/>
       <c r="H3" s="28"/>
@@ -4097,7 +4144,7 @@
       </c>
       <c r="C4" s="28">
         <f>SUM(N18:N1012)</f>
-        <v>54299.260632010941</v>
+        <v>61420.510632011181</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="47" t="s">
@@ -4115,7 +4162,7 @@
       </c>
       <c r="C5" s="3">
         <f ca="1">OFFSET(NAV!B1,MATCH(C1,NAV!B:B,1),11)</f>
-        <v>5.4299260632010737E-2</v>
+        <v>6.1420510632011149E-2</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="47" t="s">
@@ -4134,11 +4181,11 @@
       </c>
       <c r="C6" s="3">
         <f ca="1">OFFSET(NAV!B1,MATCH(C1,NAV!B:B,1),12)</f>
-        <v>2.4840775553442995E-2</v>
+        <v>3.1763048617103662E-2</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="47" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F6" s="47"/>
       <c r="G6" s="47"/>
@@ -4155,7 +4202,7 @@
       </c>
       <c r="D7" s="3">
         <f ca="1">C7/C3</f>
-        <v>3.191791103014479E-2</v>
+        <v>3.1703768358464092E-2</v>
       </c>
       <c r="E7" s="47"/>
       <c r="F7" s="47"/>
@@ -4169,11 +4216,11 @@
       </c>
       <c r="C8" s="28">
         <f>C4+C7</f>
-        <v>87950.290632010903</v>
+        <v>95071.540632011136</v>
       </c>
       <c r="D8" s="3">
         <f ca="1">C5+D7</f>
-        <v>8.6217171662155534E-2</v>
+        <v>9.3124278990475234E-2</v>
       </c>
       <c r="G8" s="47"/>
       <c r="H8" s="51"/>
@@ -4185,11 +4232,11 @@
       </c>
       <c r="C9" s="28">
         <f t="array" ref="C9">SUM((F19:F112="Futures")*(M19:M112))</f>
-        <v>522447.5</v>
+        <v>1266855</v>
       </c>
       <c r="D9" s="3">
         <f ca="1">C9/$C$3</f>
-        <v>0.4955400421003931</v>
+        <v>1.1935467492009035</v>
       </c>
       <c r="E9" s="47"/>
       <c r="F9" s="47"/>
@@ -4203,11 +4250,11 @@
       </c>
       <c r="C10" s="28">
         <f t="array" ref="C10">SUM((F19:F1012="Call")*(M19:M1012))</f>
-        <v>11160.000000000002</v>
+        <v>9480</v>
       </c>
       <c r="D10" s="3">
         <f t="shared" ref="D10:D14" ca="1" si="0">C10/$C$3</f>
-        <v>1.058522984575558E-2</v>
+        <v>8.9314271818199918E-3</v>
       </c>
       <c r="H10" s="44"/>
     </row>
@@ -4217,11 +4264,11 @@
       </c>
       <c r="C11" s="28">
         <f t="array" ref="C11">SUM((F19:F212="Put")*(M19:M212))</f>
-        <v>5459.9999999999991</v>
+        <v>4770</v>
       </c>
       <c r="D11" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>5.1787952471169752E-3</v>
+        <v>4.4939776009790466E-3</v>
       </c>
     </row>
     <row r="12" spans="2:11" x14ac:dyDescent="0.4">
@@ -4230,11 +4277,11 @@
       </c>
       <c r="C12" s="28" cm="1">
         <f t="array" ref="C12">SUM((PLB!G4:G999="O")*(PLB!E4:E999))</f>
-        <v>26937.72</v>
+        <v>35797.095000000001</v>
       </c>
       <c r="D12" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>2.555035463446299E-2</v>
+        <v>3.3725648450758705E-2</v>
       </c>
     </row>
     <row r="13" spans="2:11" x14ac:dyDescent="0.4">
@@ -4243,11 +4290,11 @@
       </c>
       <c r="C13" s="28">
         <f t="array" ref="C13">SUM((PLB!G4:G999="O")*(PLB!D4:D999))</f>
-        <v>50350.290632010983</v>
+        <v>57471.540632011231</v>
       </c>
       <c r="D13" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>4.7757114618318108E-2</v>
+        <v>5.4145873436900555E-2</v>
       </c>
       <c r="F13" s="59"/>
       <c r="G13" s="59"/>
@@ -4258,11 +4305,11 @@
       </c>
       <c r="C14" s="28">
         <f>C12+C13</f>
-        <v>77288.010632010992</v>
+        <v>93268.635632011225</v>
       </c>
       <c r="D14" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>7.3307469252781102E-2</v>
+        <v>8.7871521887659246E-2</v>
       </c>
     </row>
     <row r="17" spans="2:28" x14ac:dyDescent="0.4">
@@ -4309,7 +4356,7 @@
         <v>14</v>
       </c>
       <c r="P17" s="4" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="Q17" s="4" t="s">
         <v>113</v>
@@ -4385,10 +4432,10 @@
         <v>187</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F19" s="10" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="G19" s="28">
         <f>VLOOKUP(D19,Multiplier!B:I,8,0)</f>
@@ -4407,19 +4454,19 @@
       </c>
       <c r="K19" s="29">
         <f t="shared" ref="K19" si="1">L19-N19/(H19*J19)</f>
-        <v>1986.5461873597801</v>
+        <v>1986.5461873597799</v>
       </c>
       <c r="L19" s="29">
         <f t="shared" ref="L19" si="2">IF(I19=0,IF(H19&gt;0,X19,Y19),Z19)</f>
-        <v>2245</v>
+        <v>2198.8000000000002</v>
       </c>
       <c r="M19" s="28">
         <f t="shared" ref="M19" si="3">I19*J19*L19</f>
-        <v>112250</v>
+        <v>109940.00000000001</v>
       </c>
       <c r="N19" s="95">
         <f t="array" ref="N19">-SUM((Trades!T$2:T$9999=Blotter!C19)*(Trades!U$2:U$9999=Blotter!B19)*(Trades!V$2:V$9999)*(Trades!W$2:W$9999))*J19+SUM((Trades!T$2:T$9999=Blotter!C19)*(Trades!U$2:U$9999=Blotter!B19)*(Trades!X$2:X$9999))+(L19*I19)*J19</f>
-        <v>12922.690632010999</v>
+        <v>10612.690632011014</v>
       </c>
       <c r="O19" s="29">
         <f>VLOOKUP(D19,Multiplier!B:H,3,0)</f>
@@ -4433,19 +4480,19 @@
       </c>
       <c r="S19" s="29">
         <f>IF(OR(F19="Futures",F19="Spot"),IF(I19=0,0,IF(I19&gt;0,L19-O19,L19+O19)),0)</f>
-        <v>2105</v>
+        <v>2058.8000000000002</v>
       </c>
       <c r="T19" s="3">
         <f t="shared" ref="T19" si="5">IF(S19&gt;0,IF(ISNUMBER(S19/L19-1),S19/L19-1,0),0)</f>
-        <v>-6.2360801781737196E-2</v>
+        <v>-6.3671093323631078E-2</v>
       </c>
       <c r="U19" s="29">
         <f>IF(OR(F19="Futures",F19="Spot"),IF(I19=0,0,IF(I19&gt;0,K19-P19,K19+P19)),0)</f>
-        <v>1986.5461873597801</v>
+        <v>1986.5461873597799</v>
       </c>
       <c r="V19" s="3">
         <f t="shared" ref="V19" si="6">IF(U19&gt;0,IF(ISNUMBER(U19/L19-1),U19/L19-1,0),0)</f>
-        <v>-0.11512419271279284</v>
+        <v>-9.6531659377942614E-2</v>
       </c>
       <c r="X19" s="34">
         <f t="array" ref="X19">IF(ISNUMBER(SUM((Trades!T$2:T$9999=Blotter!C19)*(Trades!U$2:U$9999=Blotter!B19)*(Trades!W$2:W$9999)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0))/SUM((Trades!T$2:T$9999=Blotter!C19)*(Trades!U$2:U$9999=Blotter!B19)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0))),SUM((Trades!T$2:T$9999=Blotter!C19)*(Trades!U$2:U$9999=Blotter!B19)*(Trades!W$2:W$9999)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0))/SUM((Trades!T$2:T$9999=Blotter!C19)*(Trades!U$2:U$9999=Blotter!B19)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0)),0)</f>
@@ -4457,13 +4504,13 @@
       </c>
       <c r="Z19" s="35">
         <f>IF(C$2="Last",IF(ISNUMBER(VLOOKUP(B19,Prices!A:L,8,0)),VLOOKUP(B19,Prices!A:L,8,0),0),IF(ISNUMBER(VLOOKUP(B19,Prices!A:L,12,0)),VLOOKUP(B19,Prices!A:L,12,0),0))</f>
-        <v>2245</v>
+        <v>2198.8000000000002</v>
       </c>
       <c r="AB19" s="29"/>
     </row>
     <row r="20" spans="2:28" x14ac:dyDescent="0.4">
       <c r="B20" s="9" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C20" s="10">
         <v>2</v>
@@ -4498,15 +4545,15 @@
       </c>
       <c r="L20" s="29">
         <f t="shared" ref="L20" si="8">IF(I20=0,IF(H20&gt;0,X20,Y20),Z20)</f>
-        <v>3162</v>
+        <v>3246</v>
       </c>
       <c r="M20" s="28">
         <f t="shared" ref="M20" si="9">I20*J20*L20</f>
-        <v>94860</v>
+        <v>97380</v>
       </c>
       <c r="N20" s="95">
         <f t="array" ref="N20">-SUM((Trades!T$2:T$9999=Blotter!C20)*(Trades!U$2:U$9999=Blotter!B20)*(Trades!V$2:V$9999)*(Trades!W$2:W$9999))*J20+SUM((Trades!T$2:T$9999=Blotter!C20)*(Trades!U$2:U$9999=Blotter!B20)*(Trades!X$2:X$9999))+(L20*I20)*J20</f>
-        <v>-2198.9100000000035</v>
+        <v>321.08999999999651</v>
       </c>
       <c r="O20" s="29">
         <f>VLOOKUP(D20,Multiplier!B:H,3,0)</f>
@@ -4522,11 +4569,11 @@
       </c>
       <c r="S20" s="29">
         <f>IF(OR(F20="Futures",F20="Spot"),IF(I20=0,0,IF(I20&gt;0,L20-O20,L20+O20)),0)</f>
-        <v>2957</v>
+        <v>3041</v>
       </c>
       <c r="T20" s="3">
         <f t="shared" ref="T20" si="11">IF(S20&gt;0,IF(ISNUMBER(S20/L20-1),S20/L20-1,0),0)</f>
-        <v>-6.4832384566729906E-2</v>
+        <v>-6.3154651879235968E-2</v>
       </c>
       <c r="U20" s="29">
         <f t="shared" ref="U20" si="12">IF(OR(F20="Futures",F20="Stocks"),IF(I20=0,0,IF(I20&gt;0,K20-P20,K20+P20)),0)</f>
@@ -4534,7 +4581,7 @@
       </c>
       <c r="V20" s="3">
         <f t="shared" ref="V20" si="13">IF(U20&gt;0,IF(ISNUMBER(U20/L20-1),U20/L20-1,0),0)</f>
-        <v>-7.169607843137249E-2</v>
+        <v>-9.5718730745532943E-2</v>
       </c>
       <c r="X20" s="34">
         <f t="array" ref="X20">IF(ISNUMBER(SUM((Trades!T$2:T$9999=Blotter!C20)*(Trades!U$2:U$9999=Blotter!B20)*(Trades!W$2:W$9999)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0))/SUM((Trades!T$2:T$9999=Blotter!C20)*(Trades!U$2:U$9999=Blotter!B20)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0))),SUM((Trades!T$2:T$9999=Blotter!C20)*(Trades!U$2:U$9999=Blotter!B20)*(Trades!W$2:W$9999)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0))/SUM((Trades!T$2:T$9999=Blotter!C20)*(Trades!U$2:U$9999=Blotter!B20)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0)),0)</f>
@@ -4546,13 +4593,13 @@
       </c>
       <c r="Z20" s="35">
         <f>IF(C$2="Last",IF(ISNUMBER(VLOOKUP(B20,Prices!A:L,8,0)),VLOOKUP(B20,Prices!A:L,8,0),0),IF(ISNUMBER(VLOOKUP(B20,Prices!A:L,12,0)),VLOOKUP(B20,Prices!A:L,12,0),0))</f>
-        <v>3162</v>
+        <v>3246</v>
       </c>
       <c r="AB20" s="29"/>
     </row>
     <row r="21" spans="2:28" x14ac:dyDescent="0.4">
       <c r="B21" s="9" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C21" s="10">
         <v>3</v>
@@ -4587,15 +4634,15 @@
       </c>
       <c r="L21" s="29">
         <f t="shared" ref="L21:L22" si="15">IF(I21=0,IF(H21&gt;0,X21,Y21),Z21)</f>
-        <v>2.0099999999999998</v>
+        <v>1.75</v>
       </c>
       <c r="M21" s="28">
         <f t="shared" ref="M21:M22" si="16">I21*J21*L21</f>
-        <v>6029.9999999999991</v>
+        <v>5250</v>
       </c>
       <c r="N21" s="95">
         <f t="array" ref="N21">-SUM((Trades!T$2:T$9999=Blotter!C21)*(Trades!U$2:U$9999=Blotter!B21)*(Trades!V$2:V$9999)*(Trades!W$2:W$9999))*J21+SUM((Trades!T$2:T$9999=Blotter!C21)*(Trades!U$2:U$9999=Blotter!B21)*(Trades!X$2:X$9999))+(L21*I21)*J21</f>
-        <v>-4597.1100000000033</v>
+        <v>-5377.1100000000024</v>
       </c>
       <c r="O21" s="29">
         <f>VLOOKUP(D21,Multiplier!B:H,3,0)</f>
@@ -4635,13 +4682,13 @@
       </c>
       <c r="Z21" s="35">
         <f>IF(C$2="Last",IF(ISNUMBER(VLOOKUP(B21,Prices!A:L,8,0)),VLOOKUP(B21,Prices!A:L,8,0),0),IF(ISNUMBER(VLOOKUP(B21,Prices!A:L,12,0)),VLOOKUP(B21,Prices!A:L,12,0),0))</f>
-        <v>2.0099999999999998</v>
+        <v>1.75</v>
       </c>
       <c r="AB21" s="29"/>
     </row>
     <row r="22" spans="2:28" x14ac:dyDescent="0.4">
       <c r="B22" s="9" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C22" s="10">
         <v>3</v>
@@ -4672,19 +4719,19 @@
       </c>
       <c r="K22" s="29">
         <f t="shared" si="14"/>
-        <v>0.34762999999999988</v>
+        <v>0.34762999999999999</v>
       </c>
       <c r="L22" s="29">
         <f t="shared" si="15"/>
-        <v>0.19</v>
+        <v>0.16</v>
       </c>
       <c r="M22" s="28">
         <f t="shared" si="16"/>
-        <v>-570</v>
+        <v>-480</v>
       </c>
       <c r="N22" s="95">
         <f t="array" ref="N22">-SUM((Trades!T$2:T$9999=Blotter!C22)*(Trades!U$2:U$9999=Blotter!B22)*(Trades!V$2:V$9999)*(Trades!W$2:W$9999))*J22+SUM((Trades!T$2:T$9999=Blotter!C22)*(Trades!U$2:U$9999=Blotter!B22)*(Trades!X$2:X$9999))+(L22*I22)*J22</f>
-        <v>472.88999999999976</v>
+        <v>562.88999999999987</v>
       </c>
       <c r="O22" s="29">
         <f>VLOOKUP(D22,Multiplier!B:H,3,0)</f>
@@ -4724,13 +4771,13 @@
       </c>
       <c r="Z22" s="35">
         <f>IF(C$2="Last",IF(ISNUMBER(VLOOKUP(B22,Prices!A:L,8,0)),VLOOKUP(B22,Prices!A:L,8,0),0),IF(ISNUMBER(VLOOKUP(B22,Prices!A:L,12,0)),VLOOKUP(B22,Prices!A:L,12,0),0))</f>
-        <v>0.19</v>
+        <v>0.16</v>
       </c>
       <c r="AB22" s="29"/>
     </row>
     <row r="23" spans="2:28" x14ac:dyDescent="0.4">
       <c r="B23" s="9" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C23" s="10">
         <v>4</v>
@@ -4761,19 +4808,19 @@
       </c>
       <c r="K23" s="29">
         <f t="shared" ref="K23" si="22">L23-N23/(H23*J23)</f>
-        <v>5.4700987999999997</v>
+        <v>5.4700988000000006</v>
       </c>
       <c r="L23" s="29">
         <f t="shared" ref="L23" si="23">IF(I23=0,IF(H23&gt;0,X23,Y23),Z23)</f>
-        <v>5.7645</v>
+        <v>5.8860000000000001</v>
       </c>
       <c r="M23" s="28">
         <f t="shared" ref="M23" si="24">I23*J23*L23</f>
-        <v>144112.5</v>
+        <v>147150</v>
       </c>
       <c r="N23" s="95">
         <f t="array" ref="N23">-SUM((Trades!T$2:T$9999=Blotter!C23)*(Trades!U$2:U$9999=Blotter!B23)*(Trades!V$2:V$9999)*(Trades!W$2:W$9999))*J23+SUM((Trades!T$2:T$9999=Blotter!C23)*(Trades!U$2:U$9999=Blotter!B23)*(Trades!X$2:X$9999))+(L23*I23)*J23</f>
-        <v>7360.0299999999988</v>
+        <v>10397.529999999999</v>
       </c>
       <c r="O23" s="29">
         <f>VLOOKUP(D23,Multiplier!B:H,3,0)</f>
@@ -4789,19 +4836,19 @@
       </c>
       <c r="S23" s="29">
         <f t="shared" ref="S23" si="26">IF(OR(F23="Futures",F23="Spot"),IF(I23=0,0,IF(I23&gt;0,L23-O23,L23+O23)),0)</f>
-        <v>5.5727000000000002</v>
+        <v>5.6942000000000004</v>
       </c>
       <c r="T23" s="3">
         <f t="shared" ref="T23" si="27">IF(S23&gt;0,IF(ISNUMBER(S23/L23-1),S23/L23-1,0),0)</f>
-        <v>-3.3272616879174266E-2</v>
+        <v>-3.2585796805980283E-2</v>
       </c>
       <c r="U23" s="29">
         <f t="shared" ref="U23" si="28">IF(OR(F23="Futures",F23="Stocks"),IF(I23=0,0,IF(I23&gt;0,K23-P23,K23+P23)),0)</f>
-        <v>5.1823987999999996</v>
+        <v>5.1823988000000005</v>
       </c>
       <c r="V23" s="3">
         <f t="shared" ref="V23" si="29">IF(U23&gt;0,IF(ISNUMBER(U23/L23-1),U23/L23-1,0),0)</f>
-        <v>-0.10098034521641086</v>
+        <v>-0.1195380903839619</v>
       </c>
       <c r="X23" s="34">
         <f t="array" ref="X23">IF(ISNUMBER(SUM((Trades!T$2:T$9999=Blotter!C23)*(Trades!U$2:U$9999=Blotter!B23)*(Trades!W$2:W$9999)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0))/SUM((Trades!T$2:T$9999=Blotter!C23)*(Trades!U$2:U$9999=Blotter!B23)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0))),SUM((Trades!T$2:T$9999=Blotter!C23)*(Trades!U$2:U$9999=Blotter!B23)*(Trades!W$2:W$9999)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0))/SUM((Trades!T$2:T$9999=Blotter!C23)*(Trades!U$2:U$9999=Blotter!B23)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0)),0)</f>
@@ -4813,19 +4860,19 @@
       </c>
       <c r="Z23" s="35">
         <f>IF(C$2="Last",IF(ISNUMBER(VLOOKUP(B23,Prices!A:L,8,0)),VLOOKUP(B23,Prices!A:L,8,0),0),IF(ISNUMBER(VLOOKUP(B23,Prices!A:L,12,0)),VLOOKUP(B23,Prices!A:L,12,0),0))</f>
-        <v>5.7645</v>
+        <v>5.8860000000000001</v>
       </c>
       <c r="AB23" s="29"/>
     </row>
     <row r="24" spans="2:28" x14ac:dyDescent="0.4">
       <c r="B24" s="9" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C24" s="10">
         <v>5</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="E24" s="10" t="s">
         <v>120</v>
@@ -4854,15 +4901,15 @@
       </c>
       <c r="L24" s="29">
         <f t="shared" ref="L24" si="31">IF(I24=0,IF(H24&gt;0,X24,Y24),Z24)</f>
-        <v>56695</v>
+        <v>57390</v>
       </c>
       <c r="M24" s="28">
         <f t="shared" ref="M24" si="32">I24*J24*L24</f>
-        <v>283475</v>
+        <v>286950</v>
       </c>
       <c r="N24" s="95">
         <f t="array" ref="N24">-SUM((Trades!T$2:T$9999=Blotter!C24)*(Trades!U$2:U$9999=Blotter!B24)*(Trades!V$2:V$9999)*(Trades!W$2:W$9999))*J24+SUM((Trades!T$2:T$9999=Blotter!C24)*(Trades!U$2:U$9999=Blotter!B24)*(Trades!X$2:X$9999))+(L24*I24)*J24</f>
-        <v>35135.739999999991</v>
+        <v>38610.739999999991</v>
       </c>
       <c r="O24" s="29">
         <f>VLOOKUP(D24,Multiplier!B:H,3,0)</f>
@@ -4878,11 +4925,11 @@
       </c>
       <c r="S24" s="29">
         <f t="shared" ref="S24" si="34">IF(OR(F24="Futures",F24="Spot"),IF(I24=0,0,IF(I24&gt;0,L24-O24,L24+O24)),0)</f>
-        <v>54946</v>
+        <v>55641</v>
       </c>
       <c r="T24" s="3">
         <f t="shared" ref="T24" si="35">IF(S24&gt;0,IF(ISNUMBER(S24/L24-1),S24/L24-1,0),0)</f>
-        <v>-3.0849281241732029E-2</v>
+        <v>-3.0475692629377993E-2</v>
       </c>
       <c r="U24" s="29">
         <f t="shared" ref="U24" si="36">IF(OR(F24="Futures",F24="Stocks"),IF(I24=0,0,IF(I24&gt;0,K24-P24,K24+P24)),0)</f>
@@ -4890,7 +4937,7 @@
       </c>
       <c r="V24" s="3">
         <f t="shared" ref="V24" si="37">IF(U24&gt;0,IF(ISNUMBER(U24/L24-1),U24/L24-1,0),0)</f>
-        <v>-9.3097239615486438E-2</v>
+        <v>-0.10407994424115696</v>
       </c>
       <c r="X24" s="34">
         <f t="array" ref="X24">IF(ISNUMBER(SUM((Trades!T$2:T$9999=Blotter!C24)*(Trades!U$2:U$9999=Blotter!B24)*(Trades!W$2:W$9999)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0))/SUM((Trades!T$2:T$9999=Blotter!C24)*(Trades!U$2:U$9999=Blotter!B24)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0))),SUM((Trades!T$2:T$9999=Blotter!C24)*(Trades!U$2:U$9999=Blotter!B24)*(Trades!W$2:W$9999)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0))/SUM((Trades!T$2:T$9999=Blotter!C24)*(Trades!U$2:U$9999=Blotter!B24)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0)),0)</f>
@@ -4902,13 +4949,13 @@
       </c>
       <c r="Z24" s="35">
         <f>IF(C$2="Last",IF(ISNUMBER(VLOOKUP(B24,Prices!A:L,8,0)),VLOOKUP(B24,Prices!A:L,8,0),0),IF(ISNUMBER(VLOOKUP(B24,Prices!A:L,12,0)),VLOOKUP(B24,Prices!A:L,12,0),0))</f>
-        <v>56695</v>
+        <v>57390</v>
       </c>
       <c r="AB24" s="29"/>
     </row>
     <row r="25" spans="2:28" x14ac:dyDescent="0.4">
       <c r="B25" s="9" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C25" s="10">
         <v>6</v>
@@ -4943,15 +4990,15 @@
       </c>
       <c r="L25" s="29">
         <f t="shared" ref="L25:L26" si="39">IF(I25=0,IF(H25&gt;0,X25,Y25),Z25)</f>
-        <v>22.7</v>
+        <v>17.600000000000001</v>
       </c>
       <c r="M25" s="28">
         <f t="shared" ref="M25:M26" si="40">I25*J25*L25</f>
-        <v>-2270</v>
+        <v>-1760.0000000000002</v>
       </c>
       <c r="N25" s="95">
         <f t="array" ref="N25">-SUM((Trades!T$2:T$9999=Blotter!C25)*(Trades!U$2:U$9999=Blotter!B25)*(Trades!V$2:V$9999)*(Trades!W$2:W$9999))*J25+SUM((Trades!T$2:T$9999=Blotter!C25)*(Trades!U$2:U$9999=Blotter!B25)*(Trades!X$2:X$9999))+(L25*I25)*J25</f>
-        <v>367.48</v>
+        <v>877.47999999999979</v>
       </c>
       <c r="O25" s="29">
         <f>VLOOKUP(D25,Multiplier!B:H,3,0)</f>
@@ -4991,13 +5038,13 @@
       </c>
       <c r="Z25" s="35">
         <f>IF(C$2="Last",IF(ISNUMBER(VLOOKUP(B25,Prices!A:L,8,0)),VLOOKUP(B25,Prices!A:L,8,0),0),IF(ISNUMBER(VLOOKUP(B25,Prices!A:L,12,0)),VLOOKUP(B25,Prices!A:L,12,0),0))</f>
-        <v>22.7</v>
+        <v>17.600000000000001</v>
       </c>
       <c r="AB25" s="29"/>
     </row>
     <row r="26" spans="2:28" x14ac:dyDescent="0.4">
       <c r="B26" s="9" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C26" s="10">
         <v>6</v>
@@ -5028,19 +5075,19 @@
       </c>
       <c r="K26" s="29">
         <f t="shared" si="38"/>
-        <v>125.42519999999999</v>
+        <v>125.42520000000002</v>
       </c>
       <c r="L26" s="29">
         <f t="shared" si="39"/>
-        <v>134.30000000000001</v>
+        <v>112.4</v>
       </c>
       <c r="M26" s="28">
         <f t="shared" si="40"/>
-        <v>13430.000000000002</v>
+        <v>11240</v>
       </c>
       <c r="N26" s="95">
         <f t="array" ref="N26">-SUM((Trades!T$2:T$9999=Blotter!C26)*(Trades!U$2:U$9999=Blotter!B26)*(Trades!V$2:V$9999)*(Trades!W$2:W$9999))*J26+SUM((Trades!T$2:T$9999=Blotter!C26)*(Trades!U$2:U$9999=Blotter!B26)*(Trades!X$2:X$9999))+(L26*I26)*J26</f>
-        <v>887.48000000000138</v>
+        <v>-1302.5200000000004</v>
       </c>
       <c r="O26" s="29">
         <f>VLOOKUP(D26,Multiplier!B:H,3,0)</f>
@@ -5080,35 +5127,98 @@
       </c>
       <c r="Z26" s="35">
         <f>IF(C$2="Last",IF(ISNUMBER(VLOOKUP(B26,Prices!A:L,8,0)),VLOOKUP(B26,Prices!A:L,8,0),0),IF(ISNUMBER(VLOOKUP(B26,Prices!A:L,12,0)),VLOOKUP(B26,Prices!A:L,12,0),0))</f>
-        <v>134.30000000000001</v>
+        <v>112.4</v>
       </c>
       <c r="AB26" s="29"/>
     </row>
     <row r="27" spans="2:28" x14ac:dyDescent="0.4">
-      <c r="B27" s="9"/>
-      <c r="C27" s="10"/>
-      <c r="D27" s="10"/>
-      <c r="E27" s="10"/>
-      <c r="F27" s="10"/>
-      <c r="G27" s="28"/>
-      <c r="H27" s="11"/>
-      <c r="I27" s="29"/>
-      <c r="J27" s="28"/>
-      <c r="K27" s="46"/>
-      <c r="L27" s="46"/>
-      <c r="M27" s="28"/>
-      <c r="N27" s="28"/>
-      <c r="O27" s="29"/>
-      <c r="P27" s="27"/>
+      <c r="B27" s="9" t="s">
+        <v>267</v>
+      </c>
+      <c r="C27" s="10">
+        <v>7</v>
+      </c>
+      <c r="D27" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="E27" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="F27" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="G27" s="28">
+        <f>VLOOKUP(D27,Multiplier!B:I,8,0)</f>
+        <v>8</v>
+      </c>
+      <c r="H27" s="11">
+        <v>5</v>
+      </c>
+      <c r="I27" s="28">
+        <f t="array" ref="I27">ROUND(SUM((Trades!V$2:V$9999)*(Trades!U$2:U$9999=Blotter!B27)*(Trades!$T$2:T$9999=Blotter!C27)),8)</f>
+        <v>5</v>
+      </c>
+      <c r="J27" s="28">
+        <f>VLOOKUP(D27,Multiplier!B:D,2,0)</f>
+        <v>125000</v>
+      </c>
+      <c r="K27" s="99">
+        <f t="shared" ref="K27" si="46">L27-N27/(H27*J27)</f>
+        <v>1.1721699999999997</v>
+      </c>
+      <c r="L27" s="99">
+        <f t="shared" ref="L27" si="47">IF(I27=0,IF(H27&gt;0,X27,Y27),Z27)</f>
+        <v>1.1766000000000001</v>
+      </c>
+      <c r="M27" s="28">
+        <f t="shared" ref="M27" si="48">I27*J27*L27</f>
+        <v>735375</v>
+      </c>
+      <c r="N27" s="95">
+        <f t="array" ref="N27">-SUM((Trades!T$2:T$9999=Blotter!C27)*(Trades!U$2:U$9999=Blotter!B27)*(Trades!V$2:V$9999)*(Trades!W$2:W$9999))*J27+SUM((Trades!T$2:T$9999=Blotter!C27)*(Trades!U$2:U$9999=Blotter!B27)*(Trades!X$2:X$9999))+(L27*I27)*J27</f>
+        <v>2768.7500000002328</v>
+      </c>
+      <c r="O27" s="46">
+        <f>VLOOKUP(D27,Multiplier!B:H,3,0)</f>
+        <v>9.4500000000000001E-3</v>
+      </c>
+      <c r="P27" s="98">
+        <f>0.00945*1.5</f>
+        <v>1.4175E-2</v>
+      </c>
       <c r="Q27" s="27"/>
-      <c r="R27" s="28"/>
-      <c r="S27" s="29"/>
-      <c r="T27" s="3"/>
-      <c r="U27" s="29"/>
-      <c r="V27" s="3"/>
-      <c r="X27" s="34"/>
-      <c r="Y27" s="34"/>
-      <c r="Z27" s="35"/>
+      <c r="R27" s="28">
+        <f t="shared" ref="R27" si="49">(1-Q27)*P27*J27*H27</f>
+        <v>8859.375</v>
+      </c>
+      <c r="S27" s="29">
+        <f t="shared" ref="S27" si="50">IF(OR(F27="Futures",F27="Spot"),IF(I27=0,0,IF(I27&gt;0,L27-O27,L27+O27)),0)</f>
+        <v>1.1671500000000001</v>
+      </c>
+      <c r="T27" s="3">
+        <f t="shared" ref="T27" si="51">IF(S27&gt;0,IF(ISNUMBER(S27/L27-1),S27/L27-1,0),0)</f>
+        <v>-8.0316165221825386E-3</v>
+      </c>
+      <c r="U27" s="29">
+        <f t="shared" ref="U27" si="52">IF(OR(F27="Futures",F27="Stocks"),IF(I27=0,0,IF(I27&gt;0,K27-P27,K27+P27)),0)</f>
+        <v>1.1579949999999997</v>
+      </c>
+      <c r="V27" s="3">
+        <f t="shared" ref="V27" si="53">IF(U27&gt;0,IF(ISNUMBER(U27/L27-1),U27/L27-1,0),0)</f>
+        <v>-1.581251062383171E-2</v>
+      </c>
+      <c r="X27" s="34">
+        <f t="array" ref="X27">IF(ISNUMBER(SUM((Trades!T$2:T$9999=Blotter!C27)*(Trades!U$2:U$9999=Blotter!B27)*(Trades!W$2:W$9999)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0))/SUM((Trades!T$2:T$9999=Blotter!C27)*(Trades!U$2:U$9999=Blotter!B27)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0))),SUM((Trades!T$2:T$9999=Blotter!C27)*(Trades!U$2:U$9999=Blotter!B27)*(Trades!W$2:W$9999)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0))/SUM((Trades!T$2:T$9999=Blotter!C27)*(Trades!U$2:U$9999=Blotter!B27)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0)),0)</f>
+        <v>0</v>
+      </c>
+      <c r="Y27" s="34">
+        <f t="array" ref="Y27">IF(ISNUMBER(SUM((Trades!T$2:T$9999=Blotter!C27)*(Trades!U$2:U$9999=Blotter!B27)*(Trades!W$2:W$9999)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&gt;0))/SUM((Trades!T$2:T$9999=Blotter!C27)*(Trades!U$2:U$9999=Blotter!B27)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&gt;0))),SUM((Trades!T$2:T$9999=Blotter!C27)*(Trades!U$2:U$9999=Blotter!B27)*(Trades!W$2:W$9999)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&gt;0))/SUM((Trades!T$2:T$9999=Blotter!C27)*(Trades!U$2:U$9999=Blotter!B27)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&gt;0)),0)</f>
+        <v>1.1721699999999999</v>
+      </c>
+      <c r="Z27" s="35">
+        <f>IF(C$2="Last",IF(ISNUMBER(VLOOKUP(B27,Prices!A:L,8,0)),VLOOKUP(B27,Prices!A:L,8,0),0),IF(ISNUMBER(VLOOKUP(B27,Prices!A:L,12,0)),VLOOKUP(B27,Prices!A:L,12,0),0))</f>
+        <v>1.1766000000000001</v>
+      </c>
       <c r="AB27" s="29"/>
     </row>
     <row r="28" spans="2:28" x14ac:dyDescent="0.4">
@@ -6696,7 +6806,7 @@
         <v>21</v>
       </c>
       <c r="E2" s="81" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="F2" s="81" t="s">
         <v>78</v>
@@ -6705,31 +6815,31 @@
         <v>59</v>
       </c>
       <c r="H2" s="91">
-        <v>-1</v>
+        <v>6812.25</v>
       </c>
       <c r="I2" s="91">
-        <v>-1</v>
+        <v>6812</v>
       </c>
       <c r="J2" s="91">
-        <v>-1</v>
+        <v>6812.5</v>
       </c>
       <c r="K2" s="91">
-        <v>-1</v>
+        <v>6812.25</v>
       </c>
       <c r="L2" s="91">
-        <v>6863.25</v>
+        <v>6855.25</v>
       </c>
       <c r="M2" s="91">
-        <v>6858</v>
+        <v>6780</v>
       </c>
       <c r="N2" s="91">
-        <v>6888</v>
+        <v>6820</v>
       </c>
       <c r="O2" s="91">
-        <v>6846.25</v>
+        <v>6767</v>
       </c>
       <c r="P2" s="91">
-        <v>1227472</v>
+        <v>164382</v>
       </c>
       <c r="Q2" s="91"/>
       <c r="R2" s="91"/>
@@ -6737,10 +6847,10 @@
       <c r="T2" s="91"/>
       <c r="U2" s="91"/>
       <c r="V2" s="85">
-        <v>46123.423333333332</v>
+        <v>46125.517858796295</v>
       </c>
       <c r="W2" s="81" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="X2" s="81"/>
       <c r="Y2" s="81"/>
@@ -6760,7 +6870,7 @@
         <v>22</v>
       </c>
       <c r="E3" s="81" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="F3" s="81" t="s">
         <v>78</v>
@@ -6769,31 +6879,31 @@
         <v>59</v>
       </c>
       <c r="H3" s="91">
-        <v>-1</v>
+        <v>25112.75</v>
       </c>
       <c r="I3" s="91">
-        <v>-1</v>
+        <v>25112.5</v>
       </c>
       <c r="J3" s="91">
-        <v>-1</v>
+        <v>25113</v>
       </c>
       <c r="K3" s="91">
-        <v>-1</v>
+        <v>25112.75</v>
       </c>
       <c r="L3" s="91">
-        <v>25251.5</v>
+        <v>25281.25</v>
       </c>
       <c r="M3" s="91">
-        <v>25237</v>
+        <v>24980</v>
       </c>
       <c r="N3" s="91">
-        <v>25393</v>
+        <v>25133</v>
       </c>
       <c r="O3" s="91">
-        <v>25193</v>
+        <v>24904.5</v>
       </c>
       <c r="P3" s="91">
-        <v>424036</v>
+        <v>86715</v>
       </c>
       <c r="Q3" s="91"/>
       <c r="R3" s="91"/>
@@ -6801,10 +6911,10 @@
       <c r="T3" s="91"/>
       <c r="U3" s="91"/>
       <c r="V3" s="85">
-        <v>46123.423333333332</v>
+        <v>46125.517858796295</v>
       </c>
       <c r="W3" s="81" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="X3" s="81"/>
       <c r="Y3" s="81"/>
@@ -6824,7 +6934,7 @@
         <v>23</v>
       </c>
       <c r="E4" s="81" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F4" s="81" t="s">
         <v>78</v>
@@ -6833,27 +6943,31 @@
         <v>59</v>
       </c>
       <c r="H4" s="91">
-        <v>-1</v>
+        <v>2619.1999999999998</v>
       </c>
       <c r="I4" s="91">
-        <v>-1</v>
+        <v>2619</v>
       </c>
       <c r="J4" s="91">
-        <v>-1</v>
+        <v>2619.3000000000002</v>
       </c>
       <c r="K4" s="91">
-        <v>-1</v>
+        <v>2619.15</v>
       </c>
       <c r="L4" s="91">
-        <v>2651.6</v>
+        <v>2644.4</v>
       </c>
       <c r="M4" s="91">
-        <v>2649.7</v>
-      </c>
-      <c r="N4" s="91"/>
-      <c r="O4" s="91"/>
+        <v>2607.8000000000002</v>
+      </c>
+      <c r="N4" s="91">
+        <v>2622.8</v>
+      </c>
+      <c r="O4" s="91">
+        <v>2591.8000000000002</v>
+      </c>
       <c r="P4" s="91">
-        <v>0</v>
+        <v>23113</v>
       </c>
       <c r="Q4" s="91"/>
       <c r="R4" s="91"/>
@@ -6861,10 +6975,10 @@
       <c r="T4" s="91"/>
       <c r="U4" s="91"/>
       <c r="V4" s="85">
-        <v>46123.423333333332</v>
+        <v>46125.517858796295</v>
       </c>
       <c r="W4" s="81" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="X4" s="81"/>
       <c r="Y4" s="81"/>
@@ -6884,7 +6998,7 @@
         <v>61</v>
       </c>
       <c r="E5" s="81" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="F5" s="81" t="s">
         <v>79</v>
@@ -6893,27 +7007,31 @@
         <v>56</v>
       </c>
       <c r="H5" s="91">
-        <v>23958</v>
+        <v>23745</v>
       </c>
       <c r="I5" s="91">
-        <v>-1</v>
+        <v>23744</v>
       </c>
       <c r="J5" s="91">
-        <v>-1</v>
+        <v>23747</v>
       </c>
       <c r="K5" s="91">
-        <v>-1</v>
+        <v>23745.5</v>
       </c>
       <c r="L5" s="91">
-        <v>23938</v>
+        <v>24037</v>
       </c>
       <c r="M5" s="91">
-        <v>24043</v>
-      </c>
-      <c r="N5" s="91"/>
-      <c r="O5" s="91"/>
+        <v>23695</v>
+      </c>
+      <c r="N5" s="91">
+        <v>23793</v>
+      </c>
+      <c r="O5" s="91">
+        <v>23579</v>
+      </c>
       <c r="P5" s="91">
-        <v>0</v>
+        <v>6413</v>
       </c>
       <c r="Q5" s="91"/>
       <c r="R5" s="91"/>
@@ -6921,10 +7039,10 @@
       <c r="T5" s="91"/>
       <c r="U5" s="91"/>
       <c r="V5" s="85">
-        <v>46123.423333333332</v>
+        <v>46125.517858796295</v>
       </c>
       <c r="W5" s="81" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="X5" s="81"/>
       <c r="Y5" s="81"/>
@@ -6932,7 +7050,7 @@
     </row>
     <row r="6" spans="1:32" x14ac:dyDescent="0.4">
       <c r="A6" s="81" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B6" s="81">
         <v>635680489</v>
@@ -6941,10 +7059,10 @@
         <v>58</v>
       </c>
       <c r="D6" s="81" t="s">
+        <v>325</v>
+      </c>
+      <c r="E6" s="81" t="s">
         <v>326</v>
-      </c>
-      <c r="E6" s="81" t="s">
-        <v>327</v>
       </c>
       <c r="F6" s="81" t="s">
         <v>78</v>
@@ -6953,27 +7071,31 @@
         <v>59</v>
       </c>
       <c r="H6" s="91">
-        <v>0</v>
+        <v>56720</v>
       </c>
       <c r="I6" s="91">
-        <v>0</v>
+        <v>56685</v>
       </c>
       <c r="J6" s="91">
-        <v>0</v>
+        <v>56700</v>
       </c>
       <c r="K6" s="91">
-        <v>0</v>
+        <v>56692.5</v>
       </c>
       <c r="L6" s="91">
-        <v>56695</v>
+        <v>57390</v>
       </c>
       <c r="M6" s="91">
-        <v>56695</v>
-      </c>
-      <c r="N6" s="91"/>
-      <c r="O6" s="91"/>
+        <v>56505</v>
+      </c>
+      <c r="N6" s="91">
+        <v>56880</v>
+      </c>
+      <c r="O6" s="91">
+        <v>55950</v>
+      </c>
       <c r="P6" s="91">
-        <v>0</v>
+        <v>1898</v>
       </c>
       <c r="Q6" s="91"/>
       <c r="R6" s="91"/>
@@ -6981,10 +7103,10 @@
       <c r="T6" s="91"/>
       <c r="U6" s="91"/>
       <c r="V6" s="85">
-        <v>46123.423333333332</v>
+        <v>46125.517858796295</v>
       </c>
       <c r="W6" s="81" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="X6" s="81"/>
       <c r="Y6" s="81"/>
@@ -7024,10 +7146,10 @@
       <c r="T7" s="93"/>
       <c r="U7" s="93"/>
       <c r="V7" s="92">
-        <v>46123.423333333332</v>
+        <v>46125.517858796295</v>
       </c>
       <c r="W7" s="1" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="8" spans="1:32" x14ac:dyDescent="0.4">
@@ -7044,7 +7166,7 @@
         <v>5</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>60</v>
@@ -7053,27 +7175,31 @@
         <v>59</v>
       </c>
       <c r="H8" s="93">
-        <v>-1</v>
+        <v>2.8530000000000002</v>
       </c>
       <c r="I8" s="93">
-        <v>-1</v>
+        <v>2.8519999999999999</v>
       </c>
       <c r="J8" s="93">
-        <v>-1</v>
+        <v>2.8540000000000001</v>
       </c>
       <c r="K8" s="93">
-        <v>-1</v>
+        <v>2.8529999999999998</v>
       </c>
       <c r="L8" s="93">
-        <v>2.8140000000000001</v>
+        <v>2.806</v>
       </c>
       <c r="M8" s="93">
-        <v>0</v>
-      </c>
-      <c r="N8" s="93"/>
-      <c r="O8" s="93"/>
+        <v>2.839</v>
+      </c>
+      <c r="N8" s="93">
+        <v>2.8730000000000002</v>
+      </c>
+      <c r="O8" s="93">
+        <v>2.8220000000000001</v>
+      </c>
       <c r="P8" s="93">
-        <v>0</v>
+        <v>3705</v>
       </c>
       <c r="Q8" s="93"/>
       <c r="R8" s="93"/>
@@ -7081,10 +7207,10 @@
       <c r="T8" s="93"/>
       <c r="U8" s="93"/>
       <c r="V8" s="92">
-        <v>46123.423333333332</v>
+        <v>46125.517858796295</v>
       </c>
       <c r="W8" s="1" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="9" spans="1:32" x14ac:dyDescent="0.4">
@@ -7101,7 +7227,7 @@
         <v>9</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>60</v>
@@ -7110,31 +7236,31 @@
         <v>59</v>
       </c>
       <c r="H9" s="93">
-        <v>2.9369999999999998</v>
+        <v>3.0821000000000001</v>
       </c>
       <c r="I9" s="93">
-        <v>-1</v>
+        <v>3.0819000000000001</v>
       </c>
       <c r="J9" s="93">
-        <v>-1</v>
+        <v>3.0823999999999998</v>
       </c>
       <c r="K9" s="93">
-        <v>-1</v>
+        <v>3.0821499999999999</v>
       </c>
       <c r="L9" s="93">
-        <v>2.9272</v>
+        <v>2.9552</v>
       </c>
       <c r="M9" s="93">
-        <v>0</v>
+        <v>3.0146000000000002</v>
       </c>
       <c r="N9" s="93">
-        <v>2.9855</v>
+        <v>3.1118000000000001</v>
       </c>
       <c r="O9" s="93">
-        <v>2.9125999999999999</v>
+        <v>3.0146000000000002</v>
       </c>
       <c r="P9" s="93">
-        <v>52332</v>
+        <v>9373</v>
       </c>
       <c r="Q9" s="93"/>
       <c r="R9" s="93"/>
@@ -7142,10 +7268,10 @@
       <c r="T9" s="93"/>
       <c r="U9" s="93"/>
       <c r="V9" s="92">
-        <v>46123.423333333332</v>
+        <v>46125.517858796295</v>
       </c>
       <c r="W9" s="1" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="10" spans="1:32" x14ac:dyDescent="0.4">
@@ -7162,7 +7288,7 @@
         <v>26</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>80</v>
@@ -7171,27 +7297,31 @@
         <v>59</v>
       </c>
       <c r="H10" s="93">
-        <v>-1</v>
+        <v>4738.6000000000004</v>
       </c>
       <c r="I10" s="93">
-        <v>-1</v>
+        <v>4738.3</v>
       </c>
       <c r="J10" s="93">
-        <v>-1</v>
+        <v>4738.8</v>
       </c>
       <c r="K10" s="93">
-        <v>-1</v>
+        <v>4738.55</v>
       </c>
       <c r="L10" s="93">
-        <v>4818</v>
+        <v>4787.3999999999996</v>
       </c>
       <c r="M10" s="93">
-        <v>0</v>
-      </c>
-      <c r="N10" s="93"/>
-      <c r="O10" s="93"/>
+        <v>4710</v>
+      </c>
+      <c r="N10" s="93">
+        <v>4762.5</v>
+      </c>
+      <c r="O10" s="93">
+        <v>4626</v>
+      </c>
       <c r="P10" s="93">
-        <v>0</v>
+        <v>51090</v>
       </c>
       <c r="Q10" s="93"/>
       <c r="R10" s="93"/>
@@ -7199,10 +7329,10 @@
       <c r="T10" s="93"/>
       <c r="U10" s="93"/>
       <c r="V10" s="92">
-        <v>46123.423333333332</v>
+        <v>46125.517858796295</v>
       </c>
       <c r="W10" s="1" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="11" spans="1:32" x14ac:dyDescent="0.4">
@@ -7219,7 +7349,7 @@
         <v>27</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>80</v>
@@ -7228,31 +7358,31 @@
         <v>59</v>
       </c>
       <c r="H11" s="93">
-        <v>76.325000000000003</v>
+        <v>74.739999999999995</v>
       </c>
       <c r="I11" s="93">
-        <v>-1</v>
+        <v>74.680000000000007</v>
       </c>
       <c r="J11" s="93">
-        <v>-1</v>
+        <v>74.724999999999994</v>
       </c>
       <c r="K11" s="93">
-        <v>-1</v>
+        <v>74.702500000000001</v>
       </c>
       <c r="L11" s="93">
-        <v>76.724999999999994</v>
+        <v>76.765000000000001</v>
       </c>
       <c r="M11" s="93">
-        <v>0</v>
+        <v>75.290000000000006</v>
       </c>
       <c r="N11" s="93">
-        <v>77.245000000000005</v>
+        <v>75.290000000000006</v>
       </c>
       <c r="O11" s="93">
-        <v>75.265000000000001</v>
+        <v>73.260000000000005</v>
       </c>
       <c r="P11" s="93">
-        <v>581</v>
+        <v>268</v>
       </c>
       <c r="Q11" s="93"/>
       <c r="R11" s="93"/>
@@ -7260,15 +7390,15 @@
       <c r="T11" s="93"/>
       <c r="U11" s="93"/>
       <c r="V11" s="92">
-        <v>46123.423333333332</v>
+        <v>46125.517858796295</v>
       </c>
       <c r="W11" s="1" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="12" spans="1:32" x14ac:dyDescent="0.4">
       <c r="A12" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B12" s="1">
         <v>473509991</v>
@@ -7280,7 +7410,7 @@
         <v>25</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>80</v>
@@ -7289,27 +7419,31 @@
         <v>59</v>
       </c>
       <c r="H12" s="93">
-        <v>-1</v>
+        <v>5.8525</v>
       </c>
       <c r="I12" s="93">
-        <v>-1</v>
+        <v>5.8514999999999997</v>
       </c>
       <c r="J12" s="93">
-        <v>-1</v>
+        <v>5.8529999999999998</v>
       </c>
       <c r="K12" s="93">
-        <v>-1</v>
+        <v>5.8522499999999997</v>
       </c>
       <c r="L12" s="93">
-        <v>5.7645</v>
+        <v>5.8860000000000001</v>
       </c>
       <c r="M12" s="93">
-        <v>0</v>
-      </c>
-      <c r="N12" s="93"/>
-      <c r="O12" s="93"/>
+        <v>5.8174999999999999</v>
+      </c>
+      <c r="N12" s="93">
+        <v>5.8845000000000001</v>
+      </c>
+      <c r="O12" s="93">
+        <v>5.7640000000000002</v>
+      </c>
       <c r="P12" s="93">
-        <v>0</v>
+        <v>14864</v>
       </c>
       <c r="Q12" s="93"/>
       <c r="R12" s="93"/>
@@ -7317,10 +7451,10 @@
       <c r="T12" s="93"/>
       <c r="U12" s="93"/>
       <c r="V12" s="92">
-        <v>46123.423333333332</v>
+        <v>46125.517858796295</v>
       </c>
       <c r="W12" s="1" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="13" spans="1:32" x14ac:dyDescent="0.4">
@@ -7337,7 +7471,7 @@
         <v>28</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>81</v>
@@ -7346,27 +7480,31 @@
         <v>59</v>
       </c>
       <c r="H13" s="93">
-        <v>-100</v>
+        <v>444.5</v>
       </c>
       <c r="I13" s="93">
-        <v>-100</v>
+        <v>444.25</v>
       </c>
       <c r="J13" s="93">
-        <v>-100</v>
+        <v>444.5</v>
       </c>
       <c r="K13" s="93">
-        <v>-100</v>
+        <v>444.375</v>
       </c>
       <c r="L13" s="93">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="M13" s="93">
-        <v>0</v>
-      </c>
-      <c r="N13" s="93"/>
-      <c r="O13" s="93"/>
+        <v>446</v>
+      </c>
+      <c r="N13" s="93">
+        <v>446</v>
+      </c>
+      <c r="O13" s="93">
+        <v>442.75</v>
+      </c>
       <c r="P13" s="93">
-        <v>0</v>
+        <v>28805</v>
       </c>
       <c r="Q13" s="93"/>
       <c r="R13" s="93"/>
@@ -7374,10 +7512,10 @@
       <c r="T13" s="93"/>
       <c r="U13" s="93"/>
       <c r="V13" s="92">
-        <v>46123.423333333332</v>
+        <v>46125.517858796295</v>
       </c>
       <c r="W13" s="1" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="14" spans="1:32" x14ac:dyDescent="0.4">
@@ -7394,7 +7532,7 @@
         <v>29</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>81</v>
@@ -7403,27 +7541,31 @@
         <v>59</v>
       </c>
       <c r="H14" s="93">
-        <v>-100</v>
+        <v>582</v>
       </c>
       <c r="I14" s="93">
-        <v>-100</v>
+        <v>581.75</v>
       </c>
       <c r="J14" s="93">
-        <v>-100</v>
+        <v>582</v>
       </c>
       <c r="K14" s="93">
-        <v>-100</v>
+        <v>581.875</v>
       </c>
       <c r="L14" s="93">
-        <v>574.5</v>
+        <v>571</v>
       </c>
       <c r="M14" s="93">
-        <v>0</v>
-      </c>
-      <c r="N14" s="93"/>
-      <c r="O14" s="93"/>
+        <v>580</v>
+      </c>
+      <c r="N14" s="93">
+        <v>584</v>
+      </c>
+      <c r="O14" s="93">
+        <v>576.25</v>
+      </c>
       <c r="P14" s="93">
-        <v>0</v>
+        <v>15939</v>
       </c>
       <c r="Q14" s="93"/>
       <c r="R14" s="93"/>
@@ -7431,10 +7573,10 @@
       <c r="T14" s="93"/>
       <c r="U14" s="93"/>
       <c r="V14" s="92">
-        <v>46123.423333333332</v>
+        <v>46125.517858796295</v>
       </c>
       <c r="W14" s="1" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="15" spans="1:32" x14ac:dyDescent="0.4">
@@ -7451,7 +7593,7 @@
         <v>31</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>81</v>
@@ -7460,27 +7602,31 @@
         <v>59</v>
       </c>
       <c r="H15" s="93">
-        <v>-100</v>
+        <v>1176.5</v>
       </c>
       <c r="I15" s="93">
-        <v>-100</v>
+        <v>1176.25</v>
       </c>
       <c r="J15" s="93">
-        <v>-100</v>
+        <v>1176.5</v>
       </c>
       <c r="K15" s="93">
-        <v>-100</v>
+        <v>1176.375</v>
       </c>
       <c r="L15" s="93">
-        <v>1165.25</v>
+        <v>1175.75</v>
       </c>
       <c r="M15" s="93">
-        <v>0</v>
-      </c>
-      <c r="N15" s="93"/>
-      <c r="O15" s="93"/>
+        <v>1177</v>
+      </c>
+      <c r="N15" s="93">
+        <v>1183.75</v>
+      </c>
+      <c r="O15" s="93">
+        <v>1171.5</v>
+      </c>
       <c r="P15" s="93">
-        <v>0</v>
+        <v>29866</v>
       </c>
       <c r="Q15" s="93"/>
       <c r="R15" s="93"/>
@@ -7488,10 +7634,10 @@
       <c r="T15" s="93"/>
       <c r="U15" s="93"/>
       <c r="V15" s="92">
-        <v>46123.423333333332</v>
+        <v>46125.517858796295</v>
       </c>
       <c r="W15" s="1" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="16" spans="1:32" x14ac:dyDescent="0.4">
@@ -7508,7 +7654,7 @@
         <v>32</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>63</v>
@@ -7517,31 +7663,31 @@
         <v>59</v>
       </c>
       <c r="H16" s="93">
-        <v>13.76</v>
+        <v>13.86</v>
       </c>
       <c r="I16" s="93">
-        <v>-100</v>
+        <v>13.85</v>
       </c>
       <c r="J16" s="93">
-        <v>-100</v>
+        <v>13.86</v>
       </c>
       <c r="K16" s="93">
-        <v>-100</v>
+        <v>13.855</v>
       </c>
       <c r="L16" s="93">
-        <v>13.92</v>
+        <v>13.75</v>
       </c>
       <c r="M16" s="93">
-        <v>0</v>
+        <v>13.88</v>
       </c>
       <c r="N16" s="93">
-        <v>14.06</v>
+        <v>13.97</v>
       </c>
       <c r="O16" s="93">
-        <v>13.71</v>
+        <v>13.74</v>
       </c>
       <c r="P16" s="93">
-        <v>150962</v>
+        <v>16623</v>
       </c>
       <c r="Q16" s="93"/>
       <c r="R16" s="93"/>
@@ -7549,10 +7695,10 @@
       <c r="T16" s="93"/>
       <c r="U16" s="93"/>
       <c r="V16" s="92">
-        <v>46123.423333333332</v>
+        <v>46125.517858796295</v>
       </c>
       <c r="W16" s="1" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="17" spans="1:23" x14ac:dyDescent="0.4">
@@ -7569,7 +7715,7 @@
         <v>33</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>63</v>
@@ -7578,31 +7724,31 @@
         <v>59</v>
       </c>
       <c r="H17" s="93">
-        <v>300.64999999999998</v>
+        <v>303.35000000000002</v>
       </c>
       <c r="I17" s="93">
-        <v>-100</v>
+        <v>303.25</v>
       </c>
       <c r="J17" s="93">
-        <v>-100</v>
+        <v>303.39999999999998</v>
       </c>
       <c r="K17" s="93">
-        <v>-100</v>
+        <v>303.32499999999999</v>
       </c>
       <c r="L17" s="93">
-        <v>293.7</v>
+        <v>300.10000000000002</v>
       </c>
       <c r="M17" s="93">
-        <v>0</v>
+        <v>299</v>
       </c>
       <c r="N17" s="93">
-        <v>301.25</v>
+        <v>305.75</v>
       </c>
       <c r="O17" s="93">
-        <v>291.8</v>
+        <v>298.3</v>
       </c>
       <c r="P17" s="93">
-        <v>21696</v>
+        <v>2294</v>
       </c>
       <c r="Q17" s="93"/>
       <c r="R17" s="93"/>
@@ -7610,15 +7756,15 @@
       <c r="T17" s="93"/>
       <c r="U17" s="93"/>
       <c r="V17" s="92">
-        <v>46123.423333333332</v>
+        <v>46125.517858796295</v>
       </c>
       <c r="W17" s="1" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="18" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A18" s="1" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B18" s="1">
         <v>707621000</v>
@@ -7630,7 +7776,7 @@
         <v>34</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>63</v>
@@ -7639,31 +7785,31 @@
         <v>59</v>
       </c>
       <c r="H18" s="93">
-        <v>3242</v>
+        <v>3276</v>
       </c>
       <c r="I18" s="93">
-        <v>-1</v>
+        <v>3269</v>
       </c>
       <c r="J18" s="93">
-        <v>-1</v>
+        <v>3273</v>
       </c>
       <c r="K18" s="93">
-        <v>-1</v>
+        <v>3271</v>
       </c>
       <c r="L18" s="93">
-        <v>3162</v>
+        <v>3246</v>
       </c>
       <c r="M18" s="93">
-        <v>0</v>
+        <v>3253</v>
       </c>
       <c r="N18" s="93">
-        <v>3261</v>
+        <v>3299</v>
       </c>
       <c r="O18" s="93">
-        <v>3162</v>
+        <v>3220</v>
       </c>
       <c r="P18" s="93">
-        <v>16350</v>
+        <v>1278</v>
       </c>
       <c r="Q18" s="93"/>
       <c r="R18" s="93"/>
@@ -7671,10 +7817,10 @@
       <c r="T18" s="93"/>
       <c r="U18" s="93"/>
       <c r="V18" s="92">
-        <v>46123.423333333332</v>
+        <v>46125.517858796295</v>
       </c>
       <c r="W18" s="1" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="19" spans="1:23" x14ac:dyDescent="0.4">
@@ -7691,7 +7837,7 @@
         <v>64</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>63</v>
@@ -7700,31 +7846,31 @@
         <v>59</v>
       </c>
       <c r="H19" s="93">
-        <v>73.260000000000005</v>
+        <v>73.540000000000006</v>
       </c>
       <c r="I19" s="93">
-        <v>-100</v>
+        <v>73.53</v>
       </c>
       <c r="J19" s="93">
-        <v>-100</v>
+        <v>73.540000000000006</v>
       </c>
       <c r="K19" s="93">
-        <v>-100</v>
+        <v>73.534999999999997</v>
       </c>
       <c r="L19" s="93">
-        <v>73.260000000000005</v>
+        <v>73.22</v>
       </c>
       <c r="M19" s="93">
-        <v>0</v>
+        <v>73.33</v>
       </c>
       <c r="N19" s="93">
-        <v>73.64</v>
+        <v>73.739999999999995</v>
       </c>
       <c r="O19" s="93">
-        <v>72.709999999999994</v>
+        <v>72.650000000000006</v>
       </c>
       <c r="P19" s="93">
-        <v>39193</v>
+        <v>7182</v>
       </c>
       <c r="Q19" s="93"/>
       <c r="R19" s="93"/>
@@ -7732,10 +7878,10 @@
       <c r="T19" s="93"/>
       <c r="U19" s="93"/>
       <c r="V19" s="92">
-        <v>46123.423333333332</v>
+        <v>46125.517858796295</v>
       </c>
       <c r="W19" s="1" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="20" spans="1:23" x14ac:dyDescent="0.4">
@@ -7752,7 +7898,7 @@
         <v>35</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>78</v>
@@ -7773,10 +7919,10 @@
         <v>-100</v>
       </c>
       <c r="L20" s="93">
-        <v>249.77500000000001</v>
+        <v>251.77500000000001</v>
       </c>
       <c r="M20" s="93">
-        <v>250.05</v>
+        <v>0</v>
       </c>
       <c r="N20" s="93"/>
       <c r="O20" s="93"/>
@@ -7789,10 +7935,10 @@
       <c r="T20" s="93"/>
       <c r="U20" s="93"/>
       <c r="V20" s="92">
-        <v>46123.423333333332</v>
+        <v>46125.517858796295</v>
       </c>
       <c r="W20" s="1" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="21" spans="1:23" x14ac:dyDescent="0.4">
@@ -7809,7 +7955,7 @@
         <v>36</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>78</v>
@@ -7818,7 +7964,7 @@
         <v>59</v>
       </c>
       <c r="H21" s="93">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="I21" s="93">
         <v>-100</v>
@@ -7830,10 +7976,10 @@
         <v>-100</v>
       </c>
       <c r="L21" s="93">
-        <v>370.42500000000001</v>
+        <v>372.35</v>
       </c>
       <c r="M21" s="93">
-        <v>371.5</v>
+        <v>0</v>
       </c>
       <c r="N21" s="93"/>
       <c r="O21" s="93"/>
@@ -7846,10 +7992,10 @@
       <c r="T21" s="93"/>
       <c r="U21" s="93"/>
       <c r="V21" s="92">
-        <v>46123.423333333332</v>
+        <v>46125.517858796295</v>
       </c>
       <c r="W21" s="1" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="22" spans="1:23" x14ac:dyDescent="0.4">
@@ -7866,7 +8012,7 @@
         <v>37</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>78</v>
@@ -7875,7 +8021,7 @@
         <v>59</v>
       </c>
       <c r="H22" s="93">
-        <v>90.625</v>
+        <v>0</v>
       </c>
       <c r="I22" s="93">
         <v>-100</v>
@@ -7887,19 +8033,15 @@
         <v>-100</v>
       </c>
       <c r="L22" s="93">
-        <v>90.674999999999997</v>
+        <v>90.724999999999994</v>
       </c>
       <c r="M22" s="93">
-        <v>90.5</v>
-      </c>
-      <c r="N22" s="93">
-        <v>90.775000000000006</v>
-      </c>
-      <c r="O22" s="93">
-        <v>90.424999999999997</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N22" s="93"/>
+      <c r="O22" s="93"/>
       <c r="P22" s="93">
-        <v>3304</v>
+        <v>0</v>
       </c>
       <c r="Q22" s="93"/>
       <c r="R22" s="93"/>
@@ -7907,15 +8049,15 @@
       <c r="T22" s="93"/>
       <c r="U22" s="93"/>
       <c r="V22" s="92">
-        <v>46123.423333333332</v>
+        <v>46125.517858796295</v>
       </c>
       <c r="W22" s="1" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="23" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A23" s="1" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B23" s="1">
         <v>792232100</v>
@@ -7927,7 +8069,7 @@
         <v>38</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>63</v>
@@ -7936,31 +8078,31 @@
         <v>59</v>
       </c>
       <c r="H23" s="93">
-        <v>98.484999999999999</v>
+        <v>98.775000000000006</v>
       </c>
       <c r="I23" s="93">
-        <v>-1</v>
+        <v>98.775000000000006</v>
       </c>
       <c r="J23" s="93">
-        <v>-1</v>
+        <v>98.784999999999997</v>
       </c>
       <c r="K23" s="93">
-        <v>-1</v>
+        <v>98.78</v>
       </c>
       <c r="L23" s="93">
-        <v>98.61</v>
+        <v>98.44</v>
       </c>
       <c r="M23" s="93">
-        <v>0</v>
+        <v>98.92</v>
       </c>
       <c r="N23" s="93">
-        <v>98.795000000000002</v>
+        <v>98.99</v>
       </c>
       <c r="O23" s="93">
-        <v>98.13</v>
+        <v>98.694999999999993</v>
       </c>
       <c r="P23" s="93">
-        <v>20679</v>
+        <v>8175</v>
       </c>
       <c r="Q23" s="93"/>
       <c r="R23" s="93"/>
@@ -7968,15 +8110,15 @@
       <c r="T23" s="93"/>
       <c r="U23" s="93"/>
       <c r="V23" s="92">
-        <v>46123.423333333332</v>
+        <v>46125.517858796295</v>
       </c>
       <c r="W23" s="1" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="24" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A24" s="1" t="s">
-        <v>250</v>
+        <v>267</v>
       </c>
       <c r="B24" s="1">
         <v>496647057</v>
@@ -7988,7 +8130,7 @@
         <v>56</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>78</v>
@@ -7997,27 +8139,31 @@
         <v>59</v>
       </c>
       <c r="H24" s="93">
-        <v>-1</v>
+        <v>1.1718999999999999</v>
       </c>
       <c r="I24" s="93">
-        <v>-1</v>
+        <v>1.1718500000000001</v>
       </c>
       <c r="J24" s="93">
-        <v>-1</v>
+        <v>1.1718999999999999</v>
       </c>
       <c r="K24" s="93">
-        <v>-1</v>
+        <v>1.171875</v>
       </c>
       <c r="L24" s="93">
-        <v>1.1735500000000001</v>
+        <v>1.1766000000000001</v>
       </c>
       <c r="M24" s="93">
-        <v>1.1736</v>
-      </c>
-      <c r="N24" s="93"/>
-      <c r="O24" s="93"/>
+        <v>1.171</v>
+      </c>
+      <c r="N24" s="93">
+        <v>1.1734</v>
+      </c>
+      <c r="O24" s="93">
+        <v>1.1698500000000001</v>
+      </c>
       <c r="P24" s="93">
-        <v>0</v>
+        <v>48343</v>
       </c>
       <c r="Q24" s="93"/>
       <c r="R24" s="93"/>
@@ -8025,15 +8171,15 @@
       <c r="T24" s="93"/>
       <c r="U24" s="93"/>
       <c r="V24" s="92">
-        <v>46123.423333333332</v>
+        <v>46125.517858796295</v>
       </c>
       <c r="W24" s="1" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="25" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A25" s="1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B25" s="1">
         <v>496647091</v>
@@ -8045,7 +8191,7 @@
         <v>73</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>78</v>
@@ -8054,27 +8200,31 @@
         <v>59</v>
       </c>
       <c r="H25" s="93">
-        <v>-1</v>
+        <v>1.3426</v>
       </c>
       <c r="I25" s="93">
-        <v>-1</v>
+        <v>1.3425</v>
       </c>
       <c r="J25" s="93">
-        <v>-1</v>
+        <v>1.3426</v>
       </c>
       <c r="K25" s="93">
-        <v>-1</v>
+        <v>1.3425500000000001</v>
       </c>
       <c r="L25" s="93">
-        <v>1.3431999999999999</v>
+        <v>1.3467</v>
       </c>
       <c r="M25" s="93">
-        <v>1.3435999999999999</v>
-      </c>
-      <c r="N25" s="93"/>
-      <c r="O25" s="93"/>
+        <v>1.34</v>
+      </c>
+      <c r="N25" s="93">
+        <v>1.3432999999999999</v>
+      </c>
+      <c r="O25" s="93">
+        <v>1.3378000000000001</v>
+      </c>
       <c r="P25" s="93">
-        <v>0</v>
+        <v>19349</v>
       </c>
       <c r="Q25" s="93"/>
       <c r="R25" s="93"/>
@@ -8082,15 +8232,15 @@
       <c r="T25" s="93"/>
       <c r="U25" s="93"/>
       <c r="V25" s="92">
-        <v>46123.423333333332</v>
+        <v>46125.517858796295</v>
       </c>
       <c r="W25" s="1" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="26" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A26" s="1" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B26" s="1">
         <v>496647108</v>
@@ -8102,7 +8252,7 @@
         <v>57</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>78</v>
@@ -8111,27 +8261,31 @@
         <v>59</v>
       </c>
       <c r="H26" s="93">
-        <v>-1</v>
+        <v>6.2940000000000001E-3</v>
       </c>
       <c r="I26" s="93">
-        <v>-1</v>
+        <v>6.2934999999999996E-3</v>
       </c>
       <c r="J26" s="93">
-        <v>-1</v>
+        <v>6.2940000000000001E-3</v>
       </c>
       <c r="K26" s="93">
-        <v>-1</v>
+        <v>6.2937499999999999E-3</v>
       </c>
       <c r="L26" s="93">
-        <v>6.3229999999999996E-3</v>
+        <v>6.3119999999999999E-3</v>
       </c>
       <c r="M26" s="93">
-        <v>6.3249999999999999E-3</v>
-      </c>
-      <c r="N26" s="93"/>
-      <c r="O26" s="93"/>
+        <v>6.2950000000000002E-3</v>
+      </c>
+      <c r="N26" s="93">
+        <v>6.3004999999999997E-3</v>
+      </c>
+      <c r="O26" s="93">
+        <v>6.2874999999999997E-3</v>
+      </c>
       <c r="P26" s="93">
-        <v>0</v>
+        <v>42395</v>
       </c>
       <c r="Q26" s="93"/>
       <c r="R26" s="93"/>
@@ -8139,15 +8293,15 @@
       <c r="T26" s="93"/>
       <c r="U26" s="93"/>
       <c r="V26" s="92">
-        <v>46123.423333333332</v>
+        <v>46125.517858796295</v>
       </c>
       <c r="W26" s="1" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="27" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A27" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B27" s="1">
         <v>496879111</v>
@@ -8159,7 +8313,7 @@
         <v>75</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>78</v>
@@ -8168,27 +8322,31 @@
         <v>59</v>
       </c>
       <c r="H27" s="93">
-        <v>-1</v>
+        <v>0.72430000000000005</v>
       </c>
       <c r="I27" s="93">
-        <v>-1</v>
+        <v>0.72424999999999995</v>
       </c>
       <c r="J27" s="93">
-        <v>-1</v>
+        <v>0.72435000000000005</v>
       </c>
       <c r="K27" s="93">
-        <v>-1</v>
+        <v>0.72429999999999994</v>
       </c>
       <c r="L27" s="93">
-        <v>0.72575000000000001</v>
+        <v>0.72519999999999996</v>
       </c>
       <c r="M27" s="93">
-        <v>0.72570000000000001</v>
-      </c>
-      <c r="N27" s="93"/>
-      <c r="O27" s="93"/>
+        <v>0.72350000000000003</v>
+      </c>
+      <c r="N27" s="93">
+        <v>0.72455000000000003</v>
+      </c>
+      <c r="O27" s="93">
+        <v>0.72255000000000003</v>
+      </c>
       <c r="P27" s="93">
-        <v>0</v>
+        <v>14040</v>
       </c>
       <c r="Q27" s="93"/>
       <c r="R27" s="93"/>
@@ -8196,15 +8354,15 @@
       <c r="T27" s="93"/>
       <c r="U27" s="93"/>
       <c r="V27" s="92">
-        <v>46123.423333333332</v>
+        <v>46125.517858796295</v>
       </c>
       <c r="W27" s="1" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="28" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A28" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B28" s="1">
         <v>496647009</v>
@@ -8216,7 +8374,7 @@
         <v>77</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>78</v>
@@ -8225,27 +8383,31 @@
         <v>59</v>
       </c>
       <c r="H28" s="93">
-        <v>-1</v>
+        <v>0.70409999999999995</v>
       </c>
       <c r="I28" s="93">
-        <v>-1</v>
+        <v>0.70394999999999996</v>
       </c>
       <c r="J28" s="93">
-        <v>-1</v>
+        <v>0.70399999999999996</v>
       </c>
       <c r="K28" s="93">
-        <v>-1</v>
+        <v>0.70397500000000002</v>
       </c>
       <c r="L28" s="93">
-        <v>0.70720000000000005</v>
+        <v>0.70725000000000005</v>
       </c>
       <c r="M28" s="93">
-        <v>0.70765</v>
-      </c>
-      <c r="N28" s="93"/>
-      <c r="O28" s="93"/>
+        <v>0.69899999999999995</v>
+      </c>
+      <c r="N28" s="93">
+        <v>0.70515000000000005</v>
+      </c>
+      <c r="O28" s="93">
+        <v>0.69869999999999999</v>
+      </c>
       <c r="P28" s="93">
-        <v>0</v>
+        <v>40029</v>
       </c>
       <c r="Q28" s="93"/>
       <c r="R28" s="93"/>
@@ -8253,15 +8415,15 @@
       <c r="T28" s="93"/>
       <c r="U28" s="93"/>
       <c r="V28" s="92">
-        <v>46123.423333333332</v>
+        <v>46125.517858796295</v>
       </c>
       <c r="W28" s="1" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="29" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A29" s="1" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B29" s="1">
         <v>815824224</v>
@@ -8273,7 +8435,7 @@
         <v>46</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>81</v>
@@ -8282,27 +8444,31 @@
         <v>59</v>
       </c>
       <c r="H29" s="93">
-        <v>-1</v>
+        <v>113.53125</v>
       </c>
       <c r="I29" s="93">
-        <v>-1</v>
+        <v>113.5</v>
       </c>
       <c r="J29" s="93">
-        <v>-1</v>
+        <v>113.53125</v>
       </c>
       <c r="K29" s="93">
-        <v>-1</v>
+        <v>113.515625</v>
       </c>
       <c r="L29" s="93">
-        <v>114.125</v>
+        <v>113.78125</v>
       </c>
       <c r="M29" s="93">
-        <v>114.3125</v>
-      </c>
-      <c r="N29" s="93"/>
-      <c r="O29" s="93"/>
+        <v>113.3125</v>
+      </c>
+      <c r="N29" s="93">
+        <v>113.65625</v>
+      </c>
+      <c r="O29" s="93">
+        <v>113.09375</v>
+      </c>
       <c r="P29" s="93">
-        <v>0</v>
+        <v>53138</v>
       </c>
       <c r="Q29" s="93"/>
       <c r="R29" s="93"/>
@@ -8310,15 +8476,15 @@
       <c r="T29" s="93"/>
       <c r="U29" s="93"/>
       <c r="V29" s="92">
-        <v>46123.423333333332</v>
+        <v>46125.517858796295</v>
       </c>
       <c r="W29" s="1" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="30" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A30" s="1" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B30" s="1">
         <v>815824229</v>
@@ -8330,7 +8496,7 @@
         <v>66</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>81</v>
@@ -8339,27 +8505,31 @@
         <v>59</v>
       </c>
       <c r="H30" s="93">
-        <v>-1</v>
+        <v>110.9375</v>
       </c>
       <c r="I30" s="93">
-        <v>-1</v>
+        <v>110.9375</v>
       </c>
       <c r="J30" s="93">
-        <v>-1</v>
+        <v>110.953125</v>
       </c>
       <c r="K30" s="93">
-        <v>-1</v>
+        <v>110.9453125</v>
       </c>
       <c r="L30" s="93">
-        <v>111.234375</v>
+        <v>111.09375</v>
       </c>
       <c r="M30" s="93">
-        <v>111.34375</v>
-      </c>
-      <c r="N30" s="93"/>
-      <c r="O30" s="93"/>
+        <v>110.734375</v>
+      </c>
+      <c r="N30" s="93">
+        <v>111</v>
+      </c>
+      <c r="O30" s="93">
+        <v>110.703125</v>
+      </c>
       <c r="P30" s="93">
-        <v>0</v>
+        <v>287022</v>
       </c>
       <c r="Q30" s="93"/>
       <c r="R30" s="93"/>
@@ -8367,10 +8537,10 @@
       <c r="T30" s="93"/>
       <c r="U30" s="93"/>
       <c r="V30" s="92">
-        <v>46123.423333333332</v>
+        <v>46125.517858796295</v>
       </c>
       <c r="W30" s="1" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="31" spans="1:23" x14ac:dyDescent="0.4">
@@ -8387,7 +8557,7 @@
         <v>68</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>79</v>
@@ -8395,24 +8565,32 @@
       <c r="G31" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="H31" s="93"/>
+      <c r="H31" s="93">
+        <v>124.91</v>
+      </c>
       <c r="I31" s="93">
-        <v>-1</v>
+        <v>124.91</v>
       </c>
       <c r="J31" s="93">
-        <v>-1</v>
+        <v>124.92</v>
       </c>
       <c r="K31" s="93">
-        <v>-1</v>
+        <v>124.91499999999999</v>
       </c>
       <c r="L31" s="93">
-        <v>125.42</v>
-      </c>
-      <c r="M31" s="93"/>
-      <c r="N31" s="93"/>
-      <c r="O31" s="93"/>
+        <v>125.2</v>
+      </c>
+      <c r="M31" s="93">
+        <v>124.8</v>
+      </c>
+      <c r="N31" s="93">
+        <v>125.13</v>
+      </c>
+      <c r="O31" s="93">
+        <v>124.68</v>
+      </c>
       <c r="P31" s="93">
-        <v>0</v>
+        <v>294615</v>
       </c>
       <c r="Q31" s="93"/>
       <c r="R31" s="93"/>
@@ -8420,10 +8598,10 @@
       <c r="T31" s="93"/>
       <c r="U31" s="93"/>
       <c r="V31" s="92">
-        <v>46123.423333333332</v>
+        <v>46125.517858796295</v>
       </c>
       <c r="W31" s="1" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="32" spans="1:23" x14ac:dyDescent="0.4">
@@ -8440,7 +8618,7 @@
         <v>70</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>79</v>
@@ -8448,24 +8626,32 @@
       <c r="G32" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="H32" s="93"/>
+      <c r="H32" s="93">
+        <v>107.56</v>
+      </c>
       <c r="I32" s="93">
-        <v>-1</v>
+        <v>107.56</v>
       </c>
       <c r="J32" s="93">
-        <v>-1</v>
+        <v>107.58</v>
       </c>
       <c r="K32" s="93">
-        <v>-1</v>
+        <v>107.57</v>
       </c>
       <c r="L32" s="93">
-        <v>108.82</v>
-      </c>
-      <c r="M32" s="93"/>
-      <c r="N32" s="93"/>
-      <c r="O32" s="93"/>
+        <v>108.06</v>
+      </c>
+      <c r="M32" s="93">
+        <v>107.66</v>
+      </c>
+      <c r="N32" s="93">
+        <v>108</v>
+      </c>
+      <c r="O32" s="93">
+        <v>107.06</v>
+      </c>
       <c r="P32" s="93">
-        <v>0</v>
+        <v>41621</v>
       </c>
       <c r="Q32" s="93"/>
       <c r="R32" s="93"/>
@@ -8473,10 +8659,10 @@
       <c r="T32" s="93"/>
       <c r="U32" s="93"/>
       <c r="V32" s="92">
-        <v>46123.423333333332</v>
+        <v>46125.517858796295</v>
       </c>
       <c r="W32" s="1" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="33" spans="1:23" x14ac:dyDescent="0.4">
@@ -8493,7 +8679,7 @@
         <v>47</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>79</v>
@@ -8501,24 +8687,32 @@
       <c r="G33" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="H33" s="93"/>
+      <c r="H33" s="93">
+        <v>116.81</v>
+      </c>
       <c r="I33" s="93">
-        <v>-1</v>
+        <v>116.8</v>
       </c>
       <c r="J33" s="93">
-        <v>-1</v>
+        <v>116.81</v>
       </c>
       <c r="K33" s="93">
-        <v>-1</v>
+        <v>116.80500000000001</v>
       </c>
       <c r="L33" s="93">
-        <v>117.34</v>
-      </c>
-      <c r="M33" s="93"/>
-      <c r="N33" s="93"/>
-      <c r="O33" s="93"/>
+        <v>117.29</v>
+      </c>
+      <c r="M33" s="93">
+        <v>116.66</v>
+      </c>
+      <c r="N33" s="93">
+        <v>117.15</v>
+      </c>
+      <c r="O33" s="93">
+        <v>116.6</v>
+      </c>
       <c r="P33" s="93">
-        <v>0</v>
+        <v>96206</v>
       </c>
       <c r="Q33" s="93"/>
       <c r="R33" s="93"/>
@@ -8526,15 +8720,15 @@
       <c r="T33" s="93"/>
       <c r="U33" s="93"/>
       <c r="V33" s="92">
-        <v>46123.423333333332</v>
+        <v>46125.517858796295</v>
       </c>
       <c r="W33" s="1" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="34" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A34" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B34" s="1">
         <v>479624278</v>
@@ -8546,7 +8740,7 @@
         <v>44</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>188</v>
@@ -8554,25 +8748,41 @@
       <c r="G34" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="H34" s="93"/>
-      <c r="I34" s="93"/>
-      <c r="J34" s="93"/>
-      <c r="K34" s="93"/>
-      <c r="L34" s="93"/>
+      <c r="H34" s="93">
+        <v>70759</v>
+      </c>
+      <c r="I34" s="93">
+        <v>70758.75</v>
+      </c>
+      <c r="J34" s="93">
+        <v>70759</v>
+      </c>
+      <c r="K34" s="93">
+        <v>70758.875</v>
+      </c>
+      <c r="L34" s="93">
+        <v>71121.25</v>
+      </c>
       <c r="M34" s="93"/>
-      <c r="N34" s="93"/>
-      <c r="O34" s="93"/>
-      <c r="P34" s="93"/>
+      <c r="N34" s="93">
+        <v>73600</v>
+      </c>
+      <c r="O34" s="93">
+        <v>70523</v>
+      </c>
+      <c r="P34" s="93">
+        <v>58.899580450000002</v>
+      </c>
       <c r="Q34" s="93"/>
       <c r="R34" s="93"/>
       <c r="S34" s="93"/>
       <c r="T34" s="93"/>
       <c r="U34" s="93"/>
       <c r="V34" s="92">
-        <v>46123.423333333332</v>
+        <v>46125.517858796295</v>
       </c>
       <c r="W34" s="1" t="s">
-        <v>314</v>
+        <v>258</v>
       </c>
     </row>
     <row r="35" spans="1:23" x14ac:dyDescent="0.4">
@@ -8589,7 +8799,7 @@
         <v>45</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>188</v>
@@ -8597,44 +8807,58 @@
       <c r="G35" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="H35" s="93"/>
-      <c r="I35" s="93"/>
-      <c r="J35" s="93"/>
-      <c r="K35" s="93"/>
+      <c r="H35" s="93">
+        <v>2184.1</v>
+      </c>
+      <c r="I35" s="93">
+        <v>2183.9</v>
+      </c>
+      <c r="J35" s="93">
+        <v>2183.9499999999998</v>
+      </c>
+      <c r="K35" s="93">
+        <v>2183.9250000000002</v>
+      </c>
       <c r="L35" s="93">
-        <v>2245</v>
+        <v>2198.8000000000002</v>
       </c>
       <c r="M35" s="93"/>
-      <c r="N35" s="93"/>
-      <c r="O35" s="93"/>
-      <c r="P35" s="93"/>
+      <c r="N35" s="93">
+        <v>2316.9</v>
+      </c>
+      <c r="O35" s="93">
+        <v>2178.1</v>
+      </c>
+      <c r="P35" s="93">
+        <v>1255.0010072499999</v>
+      </c>
       <c r="Q35" s="93"/>
       <c r="R35" s="93"/>
       <c r="S35" s="93"/>
       <c r="T35" s="93"/>
       <c r="U35" s="93"/>
       <c r="V35" s="92">
-        <v>46123.423333333332</v>
+        <v>46125.517858796295</v>
       </c>
       <c r="W35" s="1" t="s">
-        <v>314</v>
+        <v>258</v>
       </c>
     </row>
     <row r="36" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A36" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B36" s="1">
         <v>297507399</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D36" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>60</v>
@@ -8643,67 +8867,67 @@
         <v>59</v>
       </c>
       <c r="H36" s="93">
-        <v>1.77</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="I36" s="93">
-        <v>-1</v>
+        <v>1.03</v>
       </c>
       <c r="J36" s="93">
-        <v>-1</v>
+        <v>1.0900000000000001</v>
       </c>
       <c r="K36" s="93">
-        <v>-1</v>
+        <v>1.06</v>
       </c>
       <c r="L36" s="93">
-        <v>2.0099999999999998</v>
+        <v>1.75</v>
       </c>
       <c r="M36" s="93"/>
       <c r="N36" s="93">
-        <v>1.86</v>
+        <v>1.25</v>
       </c>
       <c r="O36" s="93">
-        <v>1.52</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="P36" s="93">
-        <v>1670</v>
+        <v>77</v>
       </c>
       <c r="Q36" s="93">
-        <v>0.65885160249112995</v>
+        <v>0.73076881821871087</v>
       </c>
       <c r="R36" s="93">
-        <v>-0.16528736663356416</v>
+        <v>-0.10167648458265198</v>
       </c>
       <c r="S36" s="93">
-        <v>1.3800911666443877E-2</v>
+        <v>8.6463708577047532E-3</v>
       </c>
       <c r="T36" s="93">
-        <v>6.5973985374787825E-2</v>
+        <v>5.377393454248991E-2</v>
       </c>
       <c r="U36" s="93">
-        <v>-6.462134828507704E-2</v>
+        <v>-6.3108329741919711E-2</v>
       </c>
       <c r="V36" s="92">
-        <v>46123.423333333332</v>
+        <v>46125.517858796295</v>
       </c>
       <c r="W36" s="1" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="37" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A37" s="1" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B37" s="1">
         <v>297509218</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D37" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>60</v>
@@ -8712,67 +8936,67 @@
         <v>59</v>
       </c>
       <c r="H37" s="93">
+        <v>0.12</v>
+      </c>
+      <c r="I37" s="93">
+        <v>0.13</v>
+      </c>
+      <c r="J37" s="93">
+        <v>0.15</v>
+      </c>
+      <c r="K37" s="93">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="L37" s="93">
         <v>0.16</v>
-      </c>
-      <c r="I37" s="93">
-        <v>-1</v>
-      </c>
-      <c r="J37" s="93">
-        <v>-1</v>
-      </c>
-      <c r="K37" s="93">
-        <v>-1</v>
-      </c>
-      <c r="L37" s="93">
-        <v>0.19</v>
       </c>
       <c r="M37" s="93"/>
       <c r="N37" s="93">
-        <v>0.18</v>
+        <v>0.12</v>
       </c>
       <c r="O37" s="93">
-        <v>0.16</v>
+        <v>0.12</v>
       </c>
       <c r="P37" s="93">
-        <v>1547</v>
+        <v>27</v>
       </c>
       <c r="Q37" s="93">
-        <v>0.80432662636800079</v>
+        <v>0.92975294633345229</v>
       </c>
       <c r="R37" s="93">
-        <v>-1.8377543468778772E-2</v>
+        <v>-1.4027513907694963E-2</v>
       </c>
       <c r="S37" s="93">
-        <v>2.0303007492177426E-3</v>
+        <v>1.3650567684415512E-3</v>
       </c>
       <c r="T37" s="93">
-        <v>1.3747560853528767E-2</v>
+        <v>9.1233589298894413E-3</v>
       </c>
       <c r="U37" s="93">
-        <v>-1.6602630535653029E-2</v>
+        <v>-1.3632410348751373E-2</v>
       </c>
       <c r="V37" s="92">
-        <v>46123.423333333332</v>
+        <v>46125.517858796295</v>
       </c>
       <c r="W37" s="1" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="38" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A38" s="1" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B38" s="1">
         <v>766128347</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D38" s="1" t="s">
         <v>26</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>80</v>
@@ -8781,67 +9005,67 @@
         <v>59</v>
       </c>
       <c r="H38" s="93">
-        <v>17.5</v>
+        <v>15.8</v>
       </c>
       <c r="I38" s="93">
-        <v>-1</v>
+        <v>13.5</v>
       </c>
       <c r="J38" s="93">
-        <v>-1</v>
+        <v>15.6</v>
       </c>
       <c r="K38" s="93">
-        <v>-1</v>
+        <v>14.55</v>
       </c>
       <c r="L38" s="93">
-        <v>22.7</v>
+        <v>17.600000000000001</v>
       </c>
       <c r="M38" s="93"/>
       <c r="N38" s="93">
-        <v>20</v>
+        <v>15.8</v>
       </c>
       <c r="O38" s="93">
-        <v>16.600000000000001</v>
+        <v>15</v>
       </c>
       <c r="P38" s="93">
-        <v>2240</v>
+        <v>75</v>
       </c>
       <c r="Q38" s="93">
-        <v>0.27853763303498025</v>
+        <v>0.29196264827533414</v>
       </c>
       <c r="R38" s="93">
-        <v>8.4509874691887518E-2</v>
+        <v>7.3778320324366764E-2</v>
       </c>
       <c r="S38" s="93">
-        <v>3.2950952133530318E-4</v>
+        <v>2.936363472983426E-4</v>
       </c>
       <c r="T38" s="93">
-        <v>2.8650586116076582</v>
+        <v>2.2579281448725865</v>
       </c>
       <c r="U38" s="93">
-        <v>-0.71029378814980859</v>
+        <v>-0.76419064617829946</v>
       </c>
       <c r="V38" s="92">
-        <v>46123.423333333332</v>
+        <v>46125.517858796295</v>
       </c>
       <c r="W38" s="1" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="39" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A39" s="1" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B39" s="1">
         <v>842622669</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D39" s="1" t="s">
         <v>26</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>80</v>
@@ -8853,16 +9077,16 @@
         <v>-1</v>
       </c>
       <c r="I39" s="93">
-        <v>-1</v>
+        <v>92.8</v>
       </c>
       <c r="J39" s="93">
-        <v>-1</v>
+        <v>96.1</v>
       </c>
       <c r="K39" s="93">
-        <v>-1</v>
+        <v>94.449999999999989</v>
       </c>
       <c r="L39" s="93">
-        <v>134.30000000000001</v>
+        <v>112.4</v>
       </c>
       <c r="M39" s="93"/>
       <c r="N39" s="93"/>
@@ -8871,25 +9095,25 @@
         <v>0</v>
       </c>
       <c r="Q39" s="93">
-        <v>0.25354562287399057</v>
+        <v>0.26140955767601448</v>
       </c>
       <c r="R39" s="93">
-        <v>0.38452572188135936</v>
+        <v>0.33984830920074593</v>
       </c>
       <c r="S39" s="93">
-        <v>8.8372043859462324E-4</v>
+        <v>8.6106229737902224E-4</v>
       </c>
       <c r="T39" s="93">
-        <v>6.5455470484210281</v>
+        <v>5.8391669572779961</v>
       </c>
       <c r="U39" s="93">
-        <v>-1.8178938477848303</v>
+        <v>-1.7637636608625371</v>
       </c>
       <c r="V39" s="92">
-        <v>46123.423333333332</v>
+        <v>46125.517858796295</v>
       </c>
       <c r="W39" s="1" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="40" spans="1:23" x14ac:dyDescent="0.4">
@@ -9011,7 +9235,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C571DE7A-BF08-4200-BB11-61B452324713}">
-  <dimension ref="A1:C56"/>
+  <dimension ref="A1:C59"/>
   <sheetFormatPr defaultRowHeight="13.15" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="22" style="81" customWidth="1"/>
@@ -9036,10 +9260,10 @@
         <v>46111.432708333334</v>
       </c>
       <c r="B2" s="84" t="s">
+        <v>321</v>
+      </c>
+      <c r="C2" s="84" t="s">
         <v>322</v>
-      </c>
-      <c r="C2" s="84" t="s">
-        <v>323</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.4">
@@ -9047,10 +9271,10 @@
         <v>46111.432708333334</v>
       </c>
       <c r="B3" s="84" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C3" s="84" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.4">
@@ -9058,10 +9282,10 @@
         <v>46111.432708333334</v>
       </c>
       <c r="B4" s="84" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C4" s="84" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.4">
@@ -9069,10 +9293,10 @@
         <v>46112.439131944448</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>322</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>323</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.4">
@@ -9080,10 +9304,10 @@
         <v>46112.439143518517</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.4">
@@ -9091,10 +9315,10 @@
         <v>46112.439143518517</v>
       </c>
       <c r="B7" s="81" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C7" s="81" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.4">
@@ -9102,10 +9326,10 @@
         <v>46112.441157407404</v>
       </c>
       <c r="B8" s="81" t="s">
+        <v>328</v>
+      </c>
+      <c r="C8" s="81" t="s">
         <v>329</v>
-      </c>
-      <c r="C8" s="81" t="s">
-        <v>330</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.4">
@@ -9113,10 +9337,10 @@
         <v>46112.441192129627</v>
       </c>
       <c r="B9" s="81" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C9" s="81" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.4">
@@ -9124,10 +9348,10 @@
         <v>46112.441736111112</v>
       </c>
       <c r="B10" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>322</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>323</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.4">
@@ -9135,10 +9359,10 @@
         <v>46112.441736111112</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.4">
@@ -9146,10 +9370,10 @@
         <v>46112.441736111112</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.4">
@@ -9157,10 +9381,10 @@
         <v>46112.442106481481</v>
       </c>
       <c r="B13" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="C13" s="1" t="s">
         <v>322</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>323</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.4">
@@ -9168,10 +9392,10 @@
         <v>46112.442106481481</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.4">
@@ -9179,10 +9403,10 @@
         <v>46112.442106481481</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.4">
@@ -9190,10 +9414,10 @@
         <v>46112.442442129628</v>
       </c>
       <c r="B16" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="C16" s="1" t="s">
         <v>329</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>330</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.4">
@@ -9201,10 +9425,10 @@
         <v>46112.442476851851</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.4">
@@ -9212,10 +9436,10 @@
         <v>46112.443182870367</v>
       </c>
       <c r="B18" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="C18" s="1" t="s">
         <v>329</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>330</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.4">
@@ -9223,10 +9447,10 @@
         <v>46112.443206018521</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.4">
@@ -9234,10 +9458,10 @@
         <v>46112.784872685188</v>
       </c>
       <c r="B20" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="C20" s="1" t="s">
         <v>322</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>323</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.4">
@@ -9245,10 +9469,10 @@
         <v>46112.784872685188</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.4">
@@ -9256,10 +9480,10 @@
         <v>46112.784872685188</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.4">
@@ -9267,10 +9491,10 @@
         <v>46113.463761574072</v>
       </c>
       <c r="B23" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="C23" s="1" t="s">
         <v>322</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>323</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.4">
@@ -9278,10 +9502,10 @@
         <v>46113.463773148149</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.4">
@@ -9289,10 +9513,10 @@
         <v>46113.463784722226</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.4">
@@ -9300,10 +9524,10 @@
         <v>46113.464155092595</v>
       </c>
       <c r="B26" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="C26" s="1" t="s">
         <v>329</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>330</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.4">
@@ -9311,10 +9535,10 @@
         <v>46113.464178240742</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.4">
@@ -9322,10 +9546,10 @@
         <v>46114.494803240741</v>
       </c>
       <c r="B28" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="C28" s="1" t="s">
         <v>322</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>323</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.4">
@@ -9333,10 +9557,10 @@
         <v>46114.494814814818</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.4">
@@ -9344,10 +9568,10 @@
         <v>46114.494814814818</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.4">
@@ -9355,10 +9579,10 @@
         <v>46115.523900462962</v>
       </c>
       <c r="B31" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="C31" s="1" t="s">
         <v>322</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>323</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.4">
@@ -9366,10 +9590,10 @@
         <v>46115.523900462962</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.4">
@@ -9377,10 +9601,10 @@
         <v>46115.523912037039</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.4">
@@ -9388,10 +9612,10 @@
         <v>46115.524907407409</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.4">
@@ -9399,10 +9623,10 @@
         <v>46115.524930555555</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.4">
@@ -9410,10 +9634,10 @@
         <v>46118.597337962965</v>
       </c>
       <c r="B36" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="C36" s="1" t="s">
         <v>322</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>323</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.4">
@@ -9421,10 +9645,10 @@
         <v>46118.597349537034</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.4">
@@ -9432,10 +9656,10 @@
         <v>46118.597349537034</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.4">
@@ -9443,10 +9667,10 @@
         <v>46119.429062499999</v>
       </c>
       <c r="B39" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="C39" s="1" t="s">
         <v>322</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>323</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.4">
@@ -9454,10 +9678,10 @@
         <v>46119.429062499999</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.4">
@@ -9465,10 +9689,10 @@
         <v>46119.429074074076</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.4">
@@ -9476,10 +9700,10 @@
         <v>46119.557905092595</v>
       </c>
       <c r="B42" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="C42" s="1" t="s">
         <v>322</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>323</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.4">
@@ -9487,10 +9711,10 @@
         <v>46119.557962962965</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.4">
@@ -9498,10 +9722,10 @@
         <v>46119.557962962965</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.4">
@@ -9509,10 +9733,10 @@
         <v>46119.558692129627</v>
       </c>
       <c r="B45" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="C45" s="1" t="s">
         <v>322</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>323</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.4">
@@ -9520,10 +9744,10 @@
         <v>46119.558703703704</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.4">
@@ -9531,10 +9755,10 @@
         <v>46119.558703703704</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.4">
@@ -9542,10 +9766,10 @@
         <v>46120.50880787037</v>
       </c>
       <c r="B48" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="C48" s="1" t="s">
         <v>322</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>323</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.4">
@@ -9553,10 +9777,10 @@
         <v>46120.50880787037</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.4">
@@ -9564,10 +9788,10 @@
         <v>46120.508819444447</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.4">
@@ -9575,10 +9799,10 @@
         <v>46122.466909722221</v>
       </c>
       <c r="B51" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="C51" s="1" t="s">
         <v>322</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>323</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.4">
@@ -9586,10 +9810,10 @@
         <v>46122.466909722221</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.4">
@@ -9597,10 +9821,10 @@
         <v>46122.466921296298</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.4">
@@ -9608,10 +9832,10 @@
         <v>46123.422256944446</v>
       </c>
       <c r="B54" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="C54" s="1" t="s">
         <v>322</v>
-      </c>
-      <c r="C54" s="1" t="s">
-        <v>323</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.4">
@@ -9619,10 +9843,10 @@
         <v>46123.422268518516</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.4">
@@ -9630,10 +9854,43 @@
         <v>46123.422268518516</v>
       </c>
       <c r="B56" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A57" s="85">
+        <v>46125.516909722224</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="C57" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="C56" s="1" t="s">
-        <v>339</v>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A58" s="85">
+        <v>46125.516921296294</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A59" s="85">
+        <v>46125.516921296294</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>338</v>
       </c>
     </row>
   </sheetData>
@@ -10055,11 +10312,11 @@
       <c r="H6" s="67"/>
       <c r="I6" s="70">
         <f>Blotter!C$4-SUM(NAV!I$4:I5)</f>
-        <v>25554.81</v>
+        <v>32676.060000000241</v>
       </c>
       <c r="J6" s="70">
         <f t="shared" ref="J6" si="9">E6-F6-G6-H6+I6</f>
-        <v>1054299.2606320109</v>
+        <v>1061420.5106320111</v>
       </c>
       <c r="K6" s="70">
         <f t="shared" ref="K6" si="10">K5+C6</f>
@@ -10067,19 +10324,19 @@
       </c>
       <c r="L6" s="71">
         <f t="shared" ref="L6" si="11">J6/K6</f>
-        <v>1054.2992606320108</v>
+        <v>1061.4205106320112</v>
       </c>
       <c r="M6" s="72">
         <f t="shared" ref="M6" si="12">L6/$L$3-1</f>
-        <v>5.4299260632010737E-2</v>
+        <v>6.1420510632011149E-2</v>
       </c>
       <c r="N6" s="73">
         <f t="shared" ref="N6" si="13">L6/L5-1</f>
-        <v>2.4840775553442995E-2</v>
+        <v>3.1763048617103662E-2</v>
       </c>
       <c r="O6" s="75">
         <f>STDEVP(N$4:N6)*SQRT(12)</f>
-        <v>4.4099074084787401E-2</v>
+        <v>4.9588259811965033E-2</v>
       </c>
     </row>
     <row r="7" spans="2:18" ht="14.25" x14ac:dyDescent="0.4">
@@ -10454,12 +10711,12 @@
         <v>46088</v>
       </c>
       <c r="C4" s="5">
-        <f t="shared" ref="C4:C9" si="2">C3+1</f>
+        <f t="shared" ref="C4:C10" si="2">C3+1</f>
         <v>1</v>
       </c>
       <c r="D4" s="6">
         <f t="array" ref="D4">SUM((Blotter!C$19:C$1013=C4)*(Blotter!N$19:N$1013)*1)</f>
-        <v>12922.690632010999</v>
+        <v>10612.690632011014</v>
       </c>
       <c r="E4" s="6">
         <f t="array" ref="E4">SUM((Blotter!B$19:C$1013=C4)*(Blotter!R$19:R$1013)*1)</f>
@@ -10475,20 +10732,20 @@
       </c>
       <c r="H4" s="16">
         <f t="shared" ref="H4:H9" si="4">J3+D4</f>
-        <v>1012922.690632011</v>
+        <v>1010612.690632011</v>
       </c>
       <c r="I4" s="16"/>
       <c r="J4" s="16">
         <f t="shared" si="0"/>
-        <v>1012922.690632011</v>
+        <v>1010612.690632011</v>
       </c>
       <c r="K4" s="3">
         <f t="shared" ref="K4:K9" si="5">H4/J3-1</f>
-        <v>1.2922690632011014E-2</v>
+        <v>1.0612690632010979E-2</v>
       </c>
       <c r="L4" s="3">
         <f t="shared" ref="L4:L9" si="6">(1+K4)*(1+L3)-1</f>
-        <v>1.2922690632011014E-2</v>
+        <v>1.0612690632010979E-2</v>
       </c>
       <c r="M4" s="6">
         <f>O3-IF(G4="O",E4,-D4)</f>
@@ -10511,7 +10768,7 @@
         <v>0</v>
       </c>
       <c r="R4" s="3">
-        <f t="shared" ref="R4:R9" si="10">(1-1%)*(1+R3)-1</f>
+        <f t="shared" ref="R4:R10" si="10">(1-1%)*(1+R3)-1</f>
         <v>-1.0000000000000009E-2</v>
       </c>
       <c r="T4" s="40">
@@ -10523,18 +10780,18 @@
         <v>1</v>
       </c>
       <c r="V4" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="W4" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="X4" s="1" t="s">
         <v>298</v>
-      </c>
-      <c r="X4" s="1" t="s">
-        <v>299</v>
       </c>
     </row>
     <row r="5" spans="2:28" x14ac:dyDescent="0.4">
       <c r="B5" s="40">
-        <f>B4+7</f>
+        <f t="shared" ref="B5:B10" si="11">B4+7</f>
         <v>46095</v>
       </c>
       <c r="C5" s="5">
@@ -10543,15 +10800,15 @@
       </c>
       <c r="D5" s="6">
         <f t="array" ref="D5">SUM((Blotter!C$19:C$1013=C5)*(Blotter!N$19:N$1013)*1)</f>
-        <v>-2198.9100000000035</v>
+        <v>321.08999999999651</v>
       </c>
       <c r="E5" s="6">
         <f t="array" ref="E5">SUM((Blotter!B$19:C$1013=C5)*(Blotter!R$19:R$1013)*1)</f>
         <v>9000</v>
       </c>
       <c r="F5" s="30">
-        <f t="shared" ref="F5" si="11">IF(ISNUMBER(D5/E5),D5/E5,0)</f>
-        <v>-0.24432333333333373</v>
+        <f t="shared" ref="F5" si="12">IF(ISNUMBER(D5/E5),D5/E5,0)</f>
+        <v>3.567666666666628E-2</v>
       </c>
       <c r="G5" s="36" t="str">
         <f t="array" ref="G5">IF(SUM((Blotter!C$19:C$1013=PLB!C5)*(Blotter!M$19:M$1013))=0,"C","O")</f>
@@ -10559,23 +10816,23 @@
       </c>
       <c r="H5" s="16">
         <f t="shared" si="4"/>
-        <v>1010723.780632011</v>
+        <v>1010933.780632011</v>
       </c>
       <c r="I5" s="16"/>
       <c r="J5" s="16">
         <f t="shared" si="0"/>
-        <v>1010723.780632011</v>
+        <v>1010933.780632011</v>
       </c>
       <c r="K5" s="3">
         <f t="shared" si="5"/>
-        <v>-2.1708566905812576E-3</v>
+        <v>3.1771815550740712E-4</v>
       </c>
       <c r="L5" s="3">
         <f t="shared" si="6"/>
-        <v>1.0723780632010849E-2</v>
+        <v>1.0933780632010892E-2</v>
       </c>
       <c r="M5" s="6">
-        <f t="shared" ref="M5:M8" si="12">O4-IF(G5="O",E5,-D5)</f>
+        <f t="shared" ref="M5:M8" si="13">O4-IF(G5="O",E5,-D5)</f>
         <v>991000</v>
       </c>
       <c r="N5" s="16">
@@ -10599,26 +10856,26 @@
         <v>-1.9900000000000029E-2</v>
       </c>
       <c r="T5" s="40">
-        <f t="shared" ref="T5" si="13">B5</f>
+        <f t="shared" ref="T5" si="14">B5</f>
         <v>46095</v>
       </c>
       <c r="U5" s="5">
-        <f t="shared" ref="U5" si="14">C5</f>
+        <f t="shared" ref="U5" si="15">C5</f>
         <v>2</v>
       </c>
       <c r="V5" s="1" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="W5" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="X5" s="1" t="s">
         <v>300</v>
-      </c>
-      <c r="X5" s="1" t="s">
-        <v>301</v>
       </c>
     </row>
     <row r="6" spans="2:28" x14ac:dyDescent="0.4">
       <c r="B6" s="40">
-        <f>B5+7</f>
+        <f t="shared" si="11"/>
         <v>46102</v>
       </c>
       <c r="C6" s="5">
@@ -10627,15 +10884,15 @@
       </c>
       <c r="D6" s="6">
         <f t="array" ref="D6">SUM((Blotter!C$19:C$1013=C6)*(Blotter!N$19:N$1013)*1)</f>
-        <v>-4124.2200000000039</v>
+        <v>-4814.220000000003</v>
       </c>
       <c r="E6" s="6">
         <f t="array" ref="E6">SUM((Blotter!B$19:C$1013=C6)*(Blotter!R$19:R$1013)*1)</f>
         <v>9584.220000000003</v>
       </c>
       <c r="F6" s="30">
-        <f t="shared" ref="F6" si="15">IF(ISNUMBER(D6/E6),D6/E6,0)</f>
-        <v>-0.43031357794374531</v>
+        <f t="shared" ref="F6" si="16">IF(ISNUMBER(D6/E6),D6/E6,0)</f>
+        <v>-0.50230691699481034</v>
       </c>
       <c r="G6" s="36" t="str">
         <f t="array" ref="G6">IF(SUM((Blotter!C$19:C$1013=PLB!C6)*(Blotter!M$19:M$1013))=0,"C","O")</f>
@@ -10643,23 +10900,23 @@
       </c>
       <c r="H6" s="16">
         <f t="shared" si="4"/>
-        <v>1006599.560632011</v>
+        <v>1006119.560632011</v>
       </c>
       <c r="I6" s="16"/>
       <c r="J6" s="16">
         <f t="shared" si="0"/>
-        <v>1006599.560632011</v>
+        <v>1006119.560632011</v>
       </c>
       <c r="K6" s="3">
         <f t="shared" si="5"/>
-        <v>-4.0804620204157871E-3</v>
+        <v>-4.7621516782140327E-3</v>
       </c>
       <c r="L6" s="3">
         <f t="shared" si="6"/>
-        <v>6.5995606320108369E-3</v>
+        <v>6.1195606320108009E-3</v>
       </c>
       <c r="M6" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>981415.78</v>
       </c>
       <c r="N6" s="16">
@@ -10683,26 +10940,26 @@
         <v>-2.9701000000000088E-2</v>
       </c>
       <c r="T6" s="40">
-        <f t="shared" ref="T6" si="16">B6</f>
+        <f t="shared" ref="T6" si="17">B6</f>
         <v>46102</v>
       </c>
       <c r="U6" s="5">
-        <f t="shared" ref="U6" si="17">C6</f>
+        <f t="shared" ref="U6" si="18">C6</f>
         <v>3</v>
       </c>
       <c r="V6" s="1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="W6" s="49" t="s">
+        <v>314</v>
+      </c>
+      <c r="X6" s="1" t="s">
         <v>315</v>
-      </c>
-      <c r="X6" s="1" t="s">
-        <v>316</v>
       </c>
     </row>
     <row r="7" spans="2:28" x14ac:dyDescent="0.4">
       <c r="B7" s="40">
-        <f>B6+7</f>
+        <f t="shared" si="11"/>
         <v>46109</v>
       </c>
       <c r="C7" s="5">
@@ -10711,15 +10968,15 @@
       </c>
       <c r="D7" s="6">
         <f t="array" ref="D7">SUM((Blotter!C$19:C$1013=C7)*(Blotter!N$19:N$1013)*1)</f>
-        <v>7360.0299999999988</v>
+        <v>10397.529999999999</v>
       </c>
       <c r="E7" s="6">
         <f t="array" ref="E7">SUM((Blotter!B$19:C$1013=C7)*(Blotter!R$19:R$1013)*1)</f>
         <v>7192.5</v>
       </c>
       <c r="F7" s="30">
-        <f t="shared" ref="F7" si="18">IF(ISNUMBER(D7/E7),D7/E7,0)</f>
-        <v>1.0232923183872087</v>
+        <f t="shared" ref="F7" si="19">IF(ISNUMBER(D7/E7),D7/E7,0)</f>
+        <v>1.445607229753215</v>
       </c>
       <c r="G7" s="36" t="str">
         <f t="array" ref="G7">IF(SUM((Blotter!C$19:C$1013=PLB!C7)*(Blotter!M$19:M$1013))=0,"C","O")</f>
@@ -10727,23 +10984,23 @@
       </c>
       <c r="H7" s="16">
         <f t="shared" si="4"/>
-        <v>1013959.5906320111</v>
+        <v>1016517.0906320111</v>
       </c>
       <c r="I7" s="16"/>
       <c r="J7" s="16">
         <f t="shared" si="0"/>
-        <v>1013959.5906320111</v>
+        <v>1016517.0906320111</v>
       </c>
       <c r="K7" s="3">
         <f t="shared" si="5"/>
-        <v>7.3117754942977342E-3</v>
+        <v>1.033428869374986E-2</v>
       </c>
       <c r="L7" s="3">
         <f t="shared" si="6"/>
-        <v>1.395959063201091E-2</v>
+        <v>1.6517090632010678E-2</v>
       </c>
       <c r="M7" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>974223.28</v>
       </c>
       <c r="N7" s="16">
@@ -10767,26 +11024,26 @@
         <v>-3.9403990000000055E-2</v>
       </c>
       <c r="T7" s="40">
-        <f t="shared" ref="T7" si="19">B7</f>
+        <f t="shared" ref="T7" si="20">B7</f>
         <v>46109</v>
       </c>
       <c r="U7" s="5">
-        <f t="shared" ref="U7" si="20">C7</f>
+        <f t="shared" ref="U7" si="21">C7</f>
         <v>4</v>
       </c>
       <c r="V7" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="W7" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="X7" s="1" t="s">
         <v>318</v>
-      </c>
-      <c r="W7" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="X7" s="1" t="s">
-        <v>319</v>
       </c>
     </row>
     <row r="8" spans="2:28" x14ac:dyDescent="0.4">
       <c r="B8" s="40">
-        <f>B7+7</f>
+        <f t="shared" si="11"/>
         <v>46116</v>
       </c>
       <c r="C8" s="5">
@@ -10795,15 +11052,15 @@
       </c>
       <c r="D8" s="6">
         <f t="array" ref="D8">SUM((Blotter!C$19:C$1013=C8)*(Blotter!N$19:N$1013)*1)</f>
-        <v>35135.739999999991</v>
+        <v>38610.739999999991</v>
       </c>
       <c r="E8" s="6">
         <f t="array" ref="E8">SUM((Blotter!B$19:C$1013=C8)*(Blotter!R$19:R$1013)*1)</f>
         <v>-8745</v>
       </c>
       <c r="F8" s="30">
-        <f t="shared" ref="F8" si="21">IF(ISNUMBER(D8/E8),D8/E8,0)</f>
-        <v>-4.0178090337335606</v>
+        <f t="shared" ref="F8" si="22">IF(ISNUMBER(D8/E8),D8/E8,0)</f>
+        <v>-4.4151789594053739</v>
       </c>
       <c r="G8" s="36" t="str">
         <f t="array" ref="G8">IF(SUM((Blotter!C$19:C$1013=PLB!C8)*(Blotter!M$19:M$1013))=0,"C","O")</f>
@@ -10811,23 +11068,23 @@
       </c>
       <c r="H8" s="16">
         <f t="shared" si="4"/>
-        <v>1049095.3306320109</v>
+        <v>1055127.8306320109</v>
       </c>
       <c r="I8" s="16"/>
       <c r="J8" s="16">
         <f t="shared" si="0"/>
-        <v>1049095.3306320109</v>
+        <v>1055127.8306320109</v>
       </c>
       <c r="K8" s="3">
         <f t="shared" si="5"/>
-        <v>3.465201209655655E-2</v>
+        <v>3.7983365312622475E-2</v>
       </c>
       <c r="L8" s="3">
         <f t="shared" si="6"/>
-        <v>4.909533063201077E-2</v>
+        <v>5.5127830632010433E-2</v>
       </c>
       <c r="M8" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>982968.28</v>
       </c>
       <c r="N8" s="16">
@@ -10851,20 +11108,26 @@
         <v>-4.9009950100000088E-2</v>
       </c>
       <c r="T8" s="40">
-        <f t="shared" ref="T8" si="22">B8</f>
+        <f t="shared" ref="T8" si="23">B8</f>
         <v>46116</v>
       </c>
       <c r="U8" s="5">
-        <f t="shared" ref="U8" si="23">C8</f>
+        <f t="shared" ref="U8" si="24">C8</f>
         <v>5</v>
       </c>
       <c r="V8" s="1" t="s">
-        <v>332</v>
+        <v>331</v>
+      </c>
+      <c r="W8" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="X8" s="1" t="s">
+        <v>344</v>
       </c>
     </row>
     <row r="9" spans="2:28" x14ac:dyDescent="0.4">
       <c r="B9" s="40">
-        <f>B8+7</f>
+        <f t="shared" si="11"/>
         <v>46123</v>
       </c>
       <c r="C9" s="5">
@@ -10873,15 +11136,15 @@
       </c>
       <c r="D9" s="6">
         <f t="array" ref="D9">SUM((Blotter!C$19:C$1013=C9)*(Blotter!N$19:N$1013)*1)</f>
-        <v>1254.9600000000014</v>
+        <v>-425.04000000000065</v>
       </c>
       <c r="E9" s="6">
         <f t="array" ref="E9">SUM((Blotter!B$19:C$1013=C9)*(Blotter!R$19:R$1013)*1)</f>
         <v>9906</v>
       </c>
       <c r="F9" s="30">
-        <f t="shared" ref="F9" si="24">IF(ISNUMBER(D9/E9),D9/E9,0)</f>
-        <v>0.12668685645063613</v>
+        <f t="shared" ref="F9" si="25">IF(ISNUMBER(D9/E9),D9/E9,0)</f>
+        <v>-4.2907328891580929E-2</v>
       </c>
       <c r="G9" s="36" t="str">
         <f t="array" ref="G9">IF(SUM((Blotter!C$19:C$1013=PLB!C9)*(Blotter!M$19:M$1013))=0,"C","O")</f>
@@ -10889,23 +11152,23 @@
       </c>
       <c r="H9" s="16">
         <f t="shared" si="4"/>
-        <v>1050350.2906320109</v>
+        <v>1054702.7906320109</v>
       </c>
       <c r="I9" s="16"/>
       <c r="J9" s="16">
-        <f t="shared" ref="J9" si="25">H9+I9</f>
-        <v>1050350.2906320109</v>
+        <f t="shared" ref="J9" si="26">H9+I9</f>
+        <v>1054702.7906320109</v>
       </c>
       <c r="K9" s="3">
         <f t="shared" si="5"/>
-        <v>1.1962306602240069E-3</v>
+        <v>-4.0283270676833016E-4</v>
       </c>
       <c r="L9" s="3">
         <f t="shared" si="6"/>
-        <v>5.0350290632010575E-2</v>
+        <v>5.4702790632010334E-2</v>
       </c>
       <c r="M9" s="6">
-        <f t="shared" ref="M9" si="26">O8-IF(G9="O",E9,-D9)</f>
+        <f t="shared" ref="M9" si="27">O8-IF(G9="O",E9,-D9)</f>
         <v>973062.28</v>
       </c>
       <c r="N9" s="16">
@@ -10913,7 +11176,7 @@
         <v>0</v>
       </c>
       <c r="O9" s="6">
-        <f t="shared" ref="O9" si="27">M9+N9</f>
+        <f t="shared" ref="O9" si="28">M9+N9</f>
         <v>973062.28</v>
       </c>
       <c r="P9" s="3">
@@ -10929,38 +11192,106 @@
         <v>-5.8519850599000112E-2</v>
       </c>
       <c r="T9" s="40">
-        <f t="shared" ref="T9" si="28">B9</f>
+        <f t="shared" ref="T9" si="29">B9</f>
         <v>46123</v>
       </c>
       <c r="U9" s="5">
-        <f t="shared" ref="U9" si="29">C9</f>
+        <f t="shared" ref="U9" si="30">C9</f>
         <v>6</v>
       </c>
       <c r="V9" s="1" t="s">
-        <v>338</v>
-      </c>
-      <c r="W9" s="49"/>
+        <v>337</v>
+      </c>
+      <c r="W9" s="49" t="s">
+        <v>346</v>
+      </c>
+      <c r="X9" s="1" t="s">
+        <v>345</v>
+      </c>
     </row>
     <row r="10" spans="2:28" x14ac:dyDescent="0.4">
-      <c r="B10" s="40"/>
-      <c r="C10" s="5"/>
-      <c r="D10" s="6"/>
-      <c r="E10" s="6"/>
-      <c r="F10" s="30"/>
-      <c r="G10" s="36"/>
-      <c r="H10" s="16"/>
+      <c r="B10" s="40">
+        <f t="shared" si="11"/>
+        <v>46130</v>
+      </c>
+      <c r="C10" s="5">
+        <f t="shared" si="2"/>
+        <v>7</v>
+      </c>
+      <c r="D10" s="6">
+        <f t="array" ref="D10">SUM((Blotter!C$19:C$1013=C10)*(Blotter!N$19:N$1013)*1)</f>
+        <v>2768.7500000002328</v>
+      </c>
+      <c r="E10" s="6">
+        <f t="array" ref="E10">SUM((Blotter!B$19:C$1013=C10)*(Blotter!R$19:R$1013)*1)</f>
+        <v>8859.375</v>
+      </c>
+      <c r="F10" s="30">
+        <f t="shared" ref="F10" si="31">IF(ISNUMBER(D10/E10),D10/E10,0)</f>
+        <v>0.31252204585540549</v>
+      </c>
+      <c r="G10" s="36" t="str">
+        <f t="array" ref="G10">IF(SUM((Blotter!C$19:C$1013=PLB!C10)*(Blotter!M$19:M$1013))=0,"C","O")</f>
+        <v>O</v>
+      </c>
+      <c r="H10" s="16">
+        <f t="shared" ref="H10" si="32">J9+D10</f>
+        <v>1057471.5406320111</v>
+      </c>
       <c r="I10" s="16"/>
-      <c r="J10" s="16"/>
-      <c r="K10" s="3"/>
-      <c r="L10" s="3"/>
-      <c r="M10" s="6"/>
-      <c r="N10" s="16"/>
-      <c r="O10" s="6"/>
-      <c r="P10" s="3"/>
-      <c r="Q10" s="3"/>
-      <c r="R10" s="3"/>
-      <c r="T10" s="40"/>
-      <c r="U10" s="5"/>
+      <c r="J10" s="16">
+        <f t="shared" ref="J10" si="33">H10+I10</f>
+        <v>1057471.5406320111</v>
+      </c>
+      <c r="K10" s="3">
+        <f t="shared" ref="K10" si="34">H10/J9-1</f>
+        <v>2.6251471263682991E-3</v>
+      </c>
+      <c r="L10" s="3">
+        <f t="shared" ref="L10" si="35">(1+K10)*(1+L9)-1</f>
+        <v>5.7471540632010543E-2</v>
+      </c>
+      <c r="M10" s="6">
+        <f t="shared" ref="M10" si="36">O9-IF(G10="O",E10,-D10)</f>
+        <v>964202.90500000003</v>
+      </c>
+      <c r="N10" s="16">
+        <f t="shared" ref="N10" si="37">I10</f>
+        <v>0</v>
+      </c>
+      <c r="O10" s="6">
+        <f t="shared" ref="O10" si="38">M10+N10</f>
+        <v>964202.90500000003</v>
+      </c>
+      <c r="P10" s="3">
+        <f t="shared" ref="P10" si="39">M10/O9-1</f>
+        <v>-9.1046330559643174E-3</v>
+      </c>
+      <c r="Q10" s="3">
+        <f t="shared" ref="Q10" si="40">(1+P10)*(1+Q9)-1</f>
+        <v>-3.5797095000000057E-2</v>
+      </c>
+      <c r="R10" s="3">
+        <f t="shared" si="10"/>
+        <v>-6.7934652093010084E-2</v>
+      </c>
+      <c r="T10" s="40">
+        <f t="shared" ref="T10" si="41">B10</f>
+        <v>46130</v>
+      </c>
+      <c r="U10" s="5">
+        <f t="shared" ref="U10" si="42">C10</f>
+        <v>7</v>
+      </c>
+      <c r="V10" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="W10" s="49" t="s">
+        <v>347</v>
+      </c>
+      <c r="X10" s="1" t="s">
+        <v>348</v>
+      </c>
     </row>
     <row r="11" spans="2:28" x14ac:dyDescent="0.4">
       <c r="B11" s="40"/>
@@ -12327,7 +12658,7 @@
     </row>
     <row r="8" spans="2:18" x14ac:dyDescent="0.4">
       <c r="B8" s="17" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C8" s="18">
         <v>5</v>
@@ -13112,7 +13443,7 @@
         <v>125000</v>
       </c>
       <c r="D29" s="26">
-        <v>9.5600000000000008E-3</v>
+        <v>9.4500000000000001E-3</v>
       </c>
       <c r="E29" s="20">
         <f t="shared" si="1"/>
@@ -13128,15 +13459,23 @@
       </c>
       <c r="H29" s="23">
         <f t="shared" si="0"/>
-        <v>5.5788005578800561</v>
+        <v>5.6437389770723101</v>
       </c>
       <c r="I29" s="61">
         <f t="shared" si="4"/>
-        <v>7</v>
-      </c>
-      <c r="J29" s="61"/>
-      <c r="K29" s="61"/>
-      <c r="L29" s="61"/>
+        <v>8</v>
+      </c>
+      <c r="J29" s="97">
+        <v>1.1779999999999999</v>
+      </c>
+      <c r="K29" s="3">
+        <f>J29*H29*C29/$N$3</f>
+        <v>0.83104056437389762</v>
+      </c>
+      <c r="L29" s="3">
+        <f>J29*I29*C29/$N$3</f>
+        <v>1.1779999999999999</v>
+      </c>
     </row>
     <row r="30" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B30" s="17" t="s">
@@ -14510,7 +14849,7 @@
         <v>46087</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="N18" s="1">
         <v>-3</v>
@@ -14574,7 +14913,7 @@
         <v>46087</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="N19" s="1">
         <v>-5.4977520200000001</v>
@@ -14638,7 +14977,7 @@
         <v>46087</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="N20" s="1">
         <v>-5.5477520199999999</v>
@@ -14702,7 +15041,7 @@
         <v>46087</v>
       </c>
       <c r="M21" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="N21" s="1">
         <v>-5.7895520200000004</v>
@@ -14766,7 +15105,7 @@
         <v>46087</v>
       </c>
       <c r="M22" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="N22" s="1">
         <v>-0.05</v>
@@ -14830,7 +15169,7 @@
         <v>46087</v>
       </c>
       <c r="M23" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="N23" s="1">
         <v>-0.2918</v>
@@ -14894,7 +15233,7 @@
         <v>46087</v>
       </c>
       <c r="M24" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="N24" s="1">
         <v>-5.7895520200000004</v>
@@ -14958,7 +15297,7 @@
         <v>46087</v>
       </c>
       <c r="M25" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="N25" s="1">
         <v>-0.24179999999999999</v>
@@ -15022,7 +15361,7 @@
         <v>46087</v>
       </c>
       <c r="M26" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="N26" s="1">
         <v>-0.24179999999999999</v>
@@ -15086,7 +15425,7 @@
         <v>46087</v>
       </c>
       <c r="M27" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="N27" s="1">
         <v>-5.9996570199999999</v>
@@ -15150,7 +15489,7 @@
         <v>46087</v>
       </c>
       <c r="M28" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="N28" s="1">
         <v>-2.4973153799999999</v>
@@ -15214,7 +15553,7 @@
         <v>46087</v>
       </c>
       <c r="M29" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="N29" s="1">
         <v>-1.0847240199999999</v>
@@ -15278,7 +15617,7 @@
         <v>46087</v>
       </c>
       <c r="M30" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="N30" s="1">
         <v>-0.21252689</v>
@@ -15342,7 +15681,7 @@
         <v>46087</v>
       </c>
       <c r="M31" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="N31" s="1">
         <v>-2.2592068799999998</v>
@@ -15406,7 +15745,7 @@
         <v>46087</v>
       </c>
       <c r="M32" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="N32" s="1">
         <v>-1.96740688</v>
@@ -15470,7 +15809,7 @@
         <v>46087</v>
       </c>
       <c r="M33" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="N33" s="1">
         <v>-4.0489291700000001</v>
@@ -15534,7 +15873,7 @@
         <v>46087</v>
       </c>
       <c r="M34" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="N34" s="1">
         <v>-3.5134851600000001</v>
@@ -15595,7 +15934,7 @@
         <v>46087</v>
       </c>
       <c r="M35" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="N35" s="1">
         <v>-1.45325536</v>
@@ -15656,7 +15995,7 @@
         <v>46087</v>
       </c>
       <c r="M36" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="N36" s="1">
         <v>-0.51348516</v>
@@ -15696,7 +16035,7 @@
     </row>
     <row r="37" spans="1:31" x14ac:dyDescent="0.4">
       <c r="A37" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>59</v>
@@ -15705,10 +16044,10 @@
         <v>58</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>63</v>
@@ -15766,7 +16105,7 @@
     </row>
     <row r="38" spans="1:31" x14ac:dyDescent="0.4">
       <c r="A38" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>59</v>
@@ -15775,10 +16114,10 @@
         <v>58</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>63</v>
@@ -15836,22 +16175,22 @@
     </row>
     <row r="39" spans="1:31" x14ac:dyDescent="0.4">
       <c r="A39" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>59</v>
       </c>
       <c r="C39" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="D39" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="D39" s="1" t="s">
+      <c r="E39" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="G39" s="1" t="s">
         <v>296</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>296</v>
-      </c>
-      <c r="G39" s="1" t="s">
-        <v>297</v>
       </c>
       <c r="H39" s="1">
         <v>1</v>
@@ -15900,25 +16239,25 @@
     </row>
     <row r="40" spans="1:31" x14ac:dyDescent="0.4">
       <c r="A40" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>59</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>60</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H40" s="1">
         <v>1000</v>
@@ -15930,13 +16269,13 @@
         <v>46156</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L40" s="44">
         <v>46097</v>
       </c>
       <c r="M40" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="N40" s="1">
         <v>-3</v>
@@ -15976,25 +16315,25 @@
     </row>
     <row r="41" spans="1:31" x14ac:dyDescent="0.4">
       <c r="A41" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>59</v>
       </c>
       <c r="C41" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="D41" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="D41" s="1" t="s">
-        <v>305</v>
-      </c>
       <c r="E41" s="1" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>60</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H41" s="1">
         <v>1000</v>
@@ -16006,7 +16345,7 @@
         <v>46156</v>
       </c>
       <c r="K41" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L41" s="44">
         <v>46097</v>
@@ -16052,7 +16391,7 @@
     </row>
     <row r="42" spans="1:31" x14ac:dyDescent="0.4">
       <c r="A42" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>59</v>
@@ -16061,10 +16400,10 @@
         <v>58</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>80</v>
@@ -17159,7 +17498,7 @@
     </row>
     <row r="60" spans="1:24" x14ac:dyDescent="0.4">
       <c r="A60" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>59</v>
@@ -17168,16 +17507,16 @@
         <v>58</v>
       </c>
       <c r="D60" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="E60" s="1" t="s">
         <v>327</v>
-      </c>
-      <c r="E60" s="1" t="s">
-        <v>328</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>78</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H60" s="1">
         <v>5</v>
@@ -17229,7 +17568,7 @@
     </row>
     <row r="61" spans="1:24" x14ac:dyDescent="0.4">
       <c r="A61" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>59</v>
@@ -17238,16 +17577,16 @@
         <v>58</v>
       </c>
       <c r="D61" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="E61" s="1" t="s">
         <v>327</v>
-      </c>
-      <c r="E61" s="1" t="s">
-        <v>328</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>78</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H61" s="1">
         <v>5</v>
@@ -17299,7 +17638,7 @@
     </row>
     <row r="62" spans="1:24" x14ac:dyDescent="0.4">
       <c r="A62" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>59</v>
@@ -17308,16 +17647,16 @@
         <v>58</v>
       </c>
       <c r="D62" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="E62" s="1" t="s">
         <v>327</v>
-      </c>
-      <c r="E62" s="1" t="s">
-        <v>328</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>78</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H62" s="1">
         <v>5</v>
@@ -17369,7 +17708,7 @@
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.4">
       <c r="A63" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>59</v>
@@ -17378,16 +17717,16 @@
         <v>58</v>
       </c>
       <c r="D63" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="E63" s="1" t="s">
         <v>327</v>
-      </c>
-      <c r="E63" s="1" t="s">
-        <v>328</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>78</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H63" s="1">
         <v>5</v>
@@ -17439,7 +17778,7 @@
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.4">
       <c r="A64" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>59</v>
@@ -17448,16 +17787,16 @@
         <v>58</v>
       </c>
       <c r="D64" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="E64" s="1" t="s">
         <v>327</v>
-      </c>
-      <c r="E64" s="1" t="s">
-        <v>328</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>78</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H64" s="1">
         <v>5</v>
@@ -17469,7 +17808,7 @@
         <v>46112</v>
       </c>
       <c r="M64" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="N64" s="1">
         <v>-1</v>
@@ -17509,7 +17848,7 @@
     </row>
     <row r="65" spans="1:24" x14ac:dyDescent="0.4">
       <c r="A65" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>59</v>
@@ -17518,16 +17857,16 @@
         <v>58</v>
       </c>
       <c r="D65" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="E65" s="1" t="s">
         <v>327</v>
-      </c>
-      <c r="E65" s="1" t="s">
-        <v>328</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>78</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H65" s="1">
         <v>5</v>
@@ -17539,7 +17878,7 @@
         <v>46112</v>
       </c>
       <c r="M65" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="N65" s="1">
         <v>-1</v>
@@ -17579,7 +17918,7 @@
     </row>
     <row r="66" spans="1:24" x14ac:dyDescent="0.4">
       <c r="A66" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>59</v>
@@ -17588,16 +17927,16 @@
         <v>58</v>
       </c>
       <c r="D66" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="E66" s="1" t="s">
         <v>327</v>
-      </c>
-      <c r="E66" s="1" t="s">
-        <v>328</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>78</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H66" s="1">
         <v>5</v>
@@ -17609,7 +17948,7 @@
         <v>46112</v>
       </c>
       <c r="M66" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="N66" s="1">
         <v>-4</v>
@@ -17649,25 +17988,25 @@
     </row>
     <row r="67" spans="1:24" x14ac:dyDescent="0.4">
       <c r="A67" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>59</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>80</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H67" s="1">
         <v>100</v>
@@ -17679,7 +18018,7 @@
         <v>46168</v>
       </c>
       <c r="K67" s="1" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="L67" s="44">
         <v>46119</v>
@@ -17707,15 +18046,15 @@
         <v>6</v>
       </c>
       <c r="U67" s="42" t="str">
-        <f t="shared" ref="U67:U68" si="40">D67</f>
+        <f t="shared" ref="U67:U69" si="40">D67</f>
         <v>OGM6 C4930</v>
       </c>
       <c r="V67" s="42">
-        <f t="shared" ref="V67:V68" si="41">N67</f>
+        <f t="shared" ref="V67:V69" si="41">N67</f>
         <v>1</v>
       </c>
       <c r="W67" s="42">
-        <f t="shared" ref="W67:W68" si="42">O67</f>
+        <f t="shared" ref="W67:W69" si="42">O67</f>
         <v>125.4</v>
       </c>
       <c r="X67" s="42">
@@ -17725,25 +18064,25 @@
     </row>
     <row r="68" spans="1:24" x14ac:dyDescent="0.4">
       <c r="A68" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>59</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>80</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H68" s="1">
         <v>100</v>
@@ -17755,13 +18094,13 @@
         <v>46168</v>
       </c>
       <c r="K68" s="1" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="L68" s="44">
         <v>46119</v>
       </c>
       <c r="M68" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="N68" s="1">
         <v>-1</v>
@@ -17800,10 +18139,37 @@
       </c>
     </row>
     <row r="69" spans="1:24" x14ac:dyDescent="0.4">
-      <c r="T69" s="43"/>
-      <c r="U69" s="42"/>
-      <c r="V69" s="42"/>
-      <c r="W69" s="42"/>
+      <c r="C69" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="J69" s="44">
+        <v>46188</v>
+      </c>
+      <c r="N69" s="1">
+        <v>5</v>
+      </c>
+      <c r="O69" s="1">
+        <v>1.1721699999999999</v>
+      </c>
+      <c r="T69" s="43">
+        <f>IF(ISNUMBER(VLOOKUP(U69,Blotter!B:C,2,0)),VLOOKUP(U69,Blotter!B:C,2,0),"")</f>
+        <v>7</v>
+      </c>
+      <c r="U69" s="42" t="str">
+        <f t="shared" si="40"/>
+        <v>6EM6</v>
+      </c>
+      <c r="V69" s="42">
+        <f t="shared" si="41"/>
+        <v>5</v>
+      </c>
+      <c r="W69" s="42">
+        <f t="shared" si="42"/>
+        <v>1.1721699999999999</v>
+      </c>
       <c r="X69" s="42"/>
     </row>
     <row r="70" spans="1:24" x14ac:dyDescent="0.4">
@@ -25530,13 +25896,13 @@
         <v>1</v>
       </c>
       <c r="B6" s="88" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C6" s="88" t="s">
         <v>58</v>
       </c>
       <c r="D6" s="88" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="E6" s="88" t="s">
         <v>78</v>
@@ -25553,7 +25919,7 @@
         <v>5</v>
       </c>
       <c r="K6" s="88" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="L6" s="88"/>
       <c r="M6" s="88"/>
@@ -25718,7 +26084,7 @@
         <v>1</v>
       </c>
       <c r="B12" s="88" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C12" s="88" t="s">
         <v>58</v>
@@ -25904,7 +26270,7 @@
         <v>1</v>
       </c>
       <c r="B18" s="88" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C18" s="88" t="s">
         <v>58</v>
@@ -26059,7 +26425,7 @@
         <v>1</v>
       </c>
       <c r="B23" s="88" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C23" s="88" t="s">
         <v>58</v>
@@ -26090,7 +26456,7 @@
         <v>1</v>
       </c>
       <c r="B24" s="88" t="s">
-        <v>250</v>
+        <v>267</v>
       </c>
       <c r="C24" s="88" t="s">
         <v>58</v>
@@ -26121,7 +26487,7 @@
         <v>1</v>
       </c>
       <c r="B25" s="88" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C25" s="88" t="s">
         <v>58</v>
@@ -26152,7 +26518,7 @@
         <v>1</v>
       </c>
       <c r="B26" s="88" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C26" s="88" t="s">
         <v>58</v>
@@ -26183,7 +26549,7 @@
         <v>1</v>
       </c>
       <c r="B27" s="88" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C27" s="88" t="s">
         <v>58</v>
@@ -26214,7 +26580,7 @@
         <v>1</v>
       </c>
       <c r="B28" s="88" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C28" s="88" t="s">
         <v>58</v>
@@ -26245,7 +26611,7 @@
         <v>1</v>
       </c>
       <c r="B29" s="88" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C29" s="88" t="s">
         <v>58</v>
@@ -26276,7 +26642,7 @@
         <v>1</v>
       </c>
       <c r="B30" s="88" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C30" s="88" t="s">
         <v>58</v>
@@ -26399,7 +26765,7 @@
         <v>1</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C34" s="88" t="s">
         <v>184</v>
@@ -26448,10 +26814,10 @@
         <v>1</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C36" s="88" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D36" s="88" t="s">
         <v>24</v>
@@ -26469,13 +26835,13 @@
         <v>75</v>
       </c>
       <c r="I36" s="88" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="J36" s="88">
         <v>1000</v>
       </c>
       <c r="K36" s="88" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="M36" s="88"/>
     </row>
@@ -26484,10 +26850,10 @@
         <v>1</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C37" s="88" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D37" s="88" t="s">
         <v>24</v>
@@ -26505,13 +26871,13 @@
         <v>55</v>
       </c>
       <c r="I37" s="88" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="J37" s="88">
         <v>1000</v>
       </c>
       <c r="K37" s="88" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="M37" s="88"/>
     </row>
@@ -26520,10 +26886,10 @@
         <v>1</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C38" s="88" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D38" s="88" t="s">
         <v>26</v>
@@ -26541,13 +26907,13 @@
         <v>5500</v>
       </c>
       <c r="I38" s="88" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="J38" s="88">
         <v>100</v>
       </c>
       <c r="K38" s="88" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.4">
@@ -26555,10 +26921,10 @@
         <v>1</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C39" s="88" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D39" s="88" t="s">
         <v>26</v>
@@ -26576,13 +26942,13 @@
         <v>4930</v>
       </c>
       <c r="I39" s="88" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="J39" s="88">
         <v>100</v>
       </c>
       <c r="K39" s="88" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.4">

--- a/1XW_TradeBlotter_Web.xlsx
+++ b/1XW_TradeBlotter_Web.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0a601c1c2ba3d9f4/Trading/The Strategy Project/1XW Website/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="551" documentId="13_ncr:1_{6F5069F1-F0E7-4440-AA6D-4AFA11BBED1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{54424417-0BD1-4588-A603-84F978016F35}"/>
+  <xr:revisionPtr revIDLastSave="564" documentId="13_ncr:1_{6F5069F1-F0E7-4440-AA6D-4AFA11BBED1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2987E0E6-EFAA-4D30-942A-963410FD0CC0}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="22695" windowHeight="14476" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -98,30 +98,8 @@
 </comments>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1536" uniqueCount="350">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1558" uniqueCount="350">
   <si>
     <t>WEEK</t>
   </si>
@@ -2350,7 +2328,7 @@
                   <c:v>2.8744450632010921E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3.1763048617103662E-2</c:v>
+                  <c:v>3.9096016484259977E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2510,7 +2488,7 @@
                   <c:v>2.8744450632010921E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>6.1420510632011149E-2</c:v>
+                  <c:v>6.896426063201111E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2907,7 +2885,7 @@
                   <c:v>1028.744450632011</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1061.4205106320112</c:v>
+                  <c:v>1068.964260632011</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3326,22 +3304,22 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-9.000000000000008E-3</c:v>
+                  <c:v>9.7108999999995227E-4</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-1.8584219999999929E-2</c:v>
+                  <c:v>-8.6131300000000799E-3</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-2.5776719999999975E-2</c:v>
+                  <c:v>-1.5805630000000015E-2</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-1.7031719999999972E-2</c:v>
+                  <c:v>1.0429369999999993E-2</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-2.6937720000000054E-2</c:v>
+                  <c:v>5.2337000000002298E-4</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-3.5797095000000057E-2</c:v>
+                  <c:v>-8.3360049999999797E-3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3434,25 +3412,25 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.0612690632010979E-2</c:v>
+                  <c:v>1.3875190632011147E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.0933780632010892E-2</c:v>
+                  <c:v>1.48462806320111E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>6.1195606320108009E-3</c:v>
+                  <c:v>8.4120606320110536E-3</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.6517090632010678E-2</c:v>
+                  <c:v>2.1422090632011059E-2</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>5.5127830632010433E-2</c:v>
+                  <c:v>6.1457830632010824E-2</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>5.4702790632010334E-2</c:v>
+                  <c:v>6.0152790632010733E-2</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>5.7471540632010543E-2</c:v>
+                  <c:v>6.5015290632010725E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4081,7 +4059,7 @@
     <col min="12" max="12" width="8.53125" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="10" style="1" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="8.73046875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="7.265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="7.53125" style="1" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="9.73046875" style="1" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="4.3984375" style="1" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="11.06640625" style="1" bestFit="1" customWidth="1"/>
@@ -4102,7 +4080,7 @@
       </c>
       <c r="C1" s="79">
         <f ca="1">TODAY()</f>
-        <v>46125</v>
+        <v>46126</v>
       </c>
     </row>
     <row r="2" spans="2:11" x14ac:dyDescent="0.4">
@@ -4127,7 +4105,7 @@
       </c>
       <c r="C3" s="28">
         <f ca="1">OFFSET(NAV!B1,MATCH(C1,NAV!B:B,1),8)</f>
-        <v>1061420.5106320111</v>
+        <v>1068964.2606320111</v>
       </c>
       <c r="E3" s="47" t="s">
         <v>121</v>
@@ -4144,7 +4122,7 @@
       </c>
       <c r="C4" s="28">
         <f>SUM(N18:N1012)</f>
-        <v>61420.510632011181</v>
+        <v>68964.260632011064</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="47" t="s">
@@ -4162,7 +4140,7 @@
       </c>
       <c r="C5" s="3">
         <f ca="1">OFFSET(NAV!B1,MATCH(C1,NAV!B:B,1),11)</f>
-        <v>6.1420510632011149E-2</v>
+        <v>6.896426063201111E-2</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="47" t="s">
@@ -4181,7 +4159,7 @@
       </c>
       <c r="C6" s="3">
         <f ca="1">OFFSET(NAV!B1,MATCH(C1,NAV!B:B,1),12)</f>
-        <v>3.1763048617103662E-2</v>
+        <v>3.9096016484259977E-2</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="47" t="s">
@@ -4202,7 +4180,7 @@
       </c>
       <c r="D7" s="3">
         <f ca="1">C7/C3</f>
-        <v>3.1703768358464092E-2</v>
+        <v>3.1480032812419963E-2</v>
       </c>
       <c r="E7" s="47"/>
       <c r="F7" s="47"/>
@@ -4216,11 +4194,11 @@
       </c>
       <c r="C8" s="28">
         <f>C4+C7</f>
-        <v>95071.540632011136</v>
+        <v>102615.29063201102</v>
       </c>
       <c r="D8" s="3">
         <f ca="1">C5+D7</f>
-        <v>9.3124278990475234E-2</v>
+        <v>0.10044429344443107</v>
       </c>
       <c r="G8" s="47"/>
       <c r="H8" s="51"/>
@@ -4232,11 +4210,11 @@
       </c>
       <c r="C9" s="28">
         <f t="array" ref="C9">SUM((F19:F112="Futures")*(M19:M112))</f>
-        <v>1266855</v>
+        <v>1175606.25</v>
       </c>
       <c r="D9" s="3">
         <f ca="1">C9/$C$3</f>
-        <v>1.1935467492009035</v>
+        <v>1.0997619782956432</v>
       </c>
       <c r="E9" s="47"/>
       <c r="F9" s="47"/>
@@ -4250,11 +4228,11 @@
       </c>
       <c r="C10" s="28">
         <f t="array" ref="C10">SUM((F19:F1012="Call")*(M19:M1012))</f>
-        <v>9480</v>
+        <v>8600</v>
       </c>
       <c r="D10" s="3">
         <f t="shared" ref="D10:D14" ca="1" si="0">C10/$C$3</f>
-        <v>8.9314271818199918E-3</v>
+        <v>8.0451707477248707E-3</v>
       </c>
       <c r="H10" s="44"/>
     </row>
@@ -4264,24 +4242,24 @@
       </c>
       <c r="C11" s="28">
         <f t="array" ref="C11">SUM((F19:F212="Put")*(M19:M212))</f>
-        <v>4770</v>
+        <v>3149.9999999999995</v>
       </c>
       <c r="D11" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>4.4939776009790466E-3</v>
+        <v>2.9467776575968999E-3</v>
       </c>
     </row>
     <row r="12" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B12" s="32" t="s">
         <v>111</v>
       </c>
-      <c r="C12" s="28" cm="1">
+      <c r="C12" s="28">
         <f t="array" ref="C12">SUM((PLB!G4:G999="O")*(PLB!E4:E999))</f>
-        <v>35797.095000000001</v>
+        <v>9307.0950000000012</v>
       </c>
       <c r="D12" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>3.3725648450758705E-2</v>
+        <v>8.7066474930577228E-3</v>
       </c>
     </row>
     <row r="13" spans="2:11" x14ac:dyDescent="0.4">
@@ -4290,11 +4268,11 @@
       </c>
       <c r="C13" s="28">
         <f t="array" ref="C13">SUM((PLB!G4:G999="O")*(PLB!D4:D999))</f>
-        <v>57471.540632011231</v>
+        <v>64044.200632011118</v>
       </c>
       <c r="D13" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>5.4145873436900555E-2</v>
+        <v>5.9912387149544014E-2</v>
       </c>
       <c r="F13" s="59"/>
       <c r="G13" s="59"/>
@@ -4305,11 +4283,11 @@
       </c>
       <c r="C14" s="28">
         <f>C12+C13</f>
-        <v>93268.635632011225</v>
+        <v>73351.295632011112</v>
       </c>
       <c r="D14" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>8.7871521887659246E-2</v>
+        <v>6.8619034642601731E-2</v>
       </c>
     </row>
     <row r="17" spans="2:28" x14ac:dyDescent="0.4">
@@ -4458,15 +4436,15 @@
       </c>
       <c r="L19" s="29">
         <f t="shared" ref="L19" si="2">IF(I19=0,IF(H19&gt;0,X19,Y19),Z19)</f>
-        <v>2198.8000000000002</v>
+        <v>2264.0500000000002</v>
       </c>
       <c r="M19" s="28">
         <f t="shared" ref="M19" si="3">I19*J19*L19</f>
-        <v>109940.00000000001</v>
+        <v>113202.50000000001</v>
       </c>
       <c r="N19" s="95">
         <f t="array" ref="N19">-SUM((Trades!T$2:T$9999=Blotter!C19)*(Trades!U$2:U$9999=Blotter!B19)*(Trades!V$2:V$9999)*(Trades!W$2:W$9999))*J19+SUM((Trades!T$2:T$9999=Blotter!C19)*(Trades!U$2:U$9999=Blotter!B19)*(Trades!X$2:X$9999))+(L19*I19)*J19</f>
-        <v>10612.690632011014</v>
+        <v>13875.190632011014</v>
       </c>
       <c r="O19" s="29">
         <f>VLOOKUP(D19,Multiplier!B:H,3,0)</f>
@@ -4480,11 +4458,11 @@
       </c>
       <c r="S19" s="29">
         <f>IF(OR(F19="Futures",F19="Spot"),IF(I19=0,0,IF(I19&gt;0,L19-O19,L19+O19)),0)</f>
-        <v>2058.8000000000002</v>
+        <v>2124.0500000000002</v>
       </c>
       <c r="T19" s="3">
         <f t="shared" ref="T19" si="5">IF(S19&gt;0,IF(ISNUMBER(S19/L19-1),S19/L19-1,0),0)</f>
-        <v>-6.3671093323631078E-2</v>
+        <v>-6.1836090192354365E-2</v>
       </c>
       <c r="U19" s="29">
         <f>IF(OR(F19="Futures",F19="Spot"),IF(I19=0,0,IF(I19&gt;0,K19-P19,K19+P19)),0)</f>
@@ -4492,7 +4470,7 @@
       </c>
       <c r="V19" s="3">
         <f t="shared" ref="V19" si="6">IF(U19&gt;0,IF(ISNUMBER(U19/L19-1),U19/L19-1,0),0)</f>
-        <v>-9.6531659377942614E-2</v>
+        <v>-0.12256964847959195</v>
       </c>
       <c r="X19" s="34">
         <f t="array" ref="X19">IF(ISNUMBER(SUM((Trades!T$2:T$9999=Blotter!C19)*(Trades!U$2:U$9999=Blotter!B19)*(Trades!W$2:W$9999)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0))/SUM((Trades!T$2:T$9999=Blotter!C19)*(Trades!U$2:U$9999=Blotter!B19)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0))),SUM((Trades!T$2:T$9999=Blotter!C19)*(Trades!U$2:U$9999=Blotter!B19)*(Trades!W$2:W$9999)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0))/SUM((Trades!T$2:T$9999=Blotter!C19)*(Trades!U$2:U$9999=Blotter!B19)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0)),0)</f>
@@ -4504,7 +4482,7 @@
       </c>
       <c r="Z19" s="35">
         <f>IF(C$2="Last",IF(ISNUMBER(VLOOKUP(B19,Prices!A:L,8,0)),VLOOKUP(B19,Prices!A:L,8,0),0),IF(ISNUMBER(VLOOKUP(B19,Prices!A:L,12,0)),VLOOKUP(B19,Prices!A:L,12,0),0))</f>
-        <v>2198.8000000000002</v>
+        <v>2264.0500000000002</v>
       </c>
       <c r="AB19" s="29"/>
     </row>
@@ -4533,7 +4511,7 @@
       </c>
       <c r="I20" s="28">
         <f t="array" ref="I20">ROUND(SUM((Trades!V$2:V$9999)*(Trades!U$2:U$9999=Blotter!B20)*(Trades!$T$2:T$9999=Blotter!C20)),8)</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J20" s="28">
         <f>VLOOKUP(D20,Multiplier!B:D,2,0)</f>
@@ -4545,15 +4523,15 @@
       </c>
       <c r="L20" s="29">
         <f t="shared" ref="L20" si="8">IF(I20=0,IF(H20&gt;0,X20,Y20),Z20)</f>
-        <v>3246</v>
+        <v>3267.6666666666665</v>
       </c>
       <c r="M20" s="28">
         <f t="shared" ref="M20" si="9">I20*J20*L20</f>
-        <v>97380</v>
+        <v>0</v>
       </c>
       <c r="N20" s="95">
         <f t="array" ref="N20">-SUM((Trades!T$2:T$9999=Blotter!C20)*(Trades!U$2:U$9999=Blotter!B20)*(Trades!V$2:V$9999)*(Trades!W$2:W$9999))*J20+SUM((Trades!T$2:T$9999=Blotter!C20)*(Trades!U$2:U$9999=Blotter!B20)*(Trades!X$2:X$9999))+(L20*I20)*J20</f>
-        <v>321.08999999999651</v>
+        <v>971.09</v>
       </c>
       <c r="O20" s="29">
         <f>VLOOKUP(D20,Multiplier!B:H,3,0)</f>
@@ -4569,23 +4547,23 @@
       </c>
       <c r="S20" s="29">
         <f>IF(OR(F20="Futures",F20="Spot"),IF(I20=0,0,IF(I20&gt;0,L20-O20,L20+O20)),0)</f>
-        <v>3041</v>
+        <v>0</v>
       </c>
       <c r="T20" s="3">
         <f t="shared" ref="T20" si="11">IF(S20&gt;0,IF(ISNUMBER(S20/L20-1),S20/L20-1,0),0)</f>
-        <v>-6.3154651879235968E-2</v>
+        <v>0</v>
       </c>
       <c r="U20" s="29">
         <f t="shared" ref="U20" si="12">IF(OR(F20="Futures",F20="Stocks"),IF(I20=0,0,IF(I20&gt;0,K20-P20,K20+P20)),0)</f>
-        <v>2935.297</v>
+        <v>0</v>
       </c>
       <c r="V20" s="3">
         <f t="shared" ref="V20" si="13">IF(U20&gt;0,IF(ISNUMBER(U20/L20-1),U20/L20-1,0),0)</f>
-        <v>-9.5718730745532943E-2</v>
+        <v>0</v>
       </c>
       <c r="X20" s="34">
         <f t="array" ref="X20">IF(ISNUMBER(SUM((Trades!T$2:T$9999=Blotter!C20)*(Trades!U$2:U$9999=Blotter!B20)*(Trades!W$2:W$9999)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0))/SUM((Trades!T$2:T$9999=Blotter!C20)*(Trades!U$2:U$9999=Blotter!B20)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0))),SUM((Trades!T$2:T$9999=Blotter!C20)*(Trades!U$2:U$9999=Blotter!B20)*(Trades!W$2:W$9999)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0))/SUM((Trades!T$2:T$9999=Blotter!C20)*(Trades!U$2:U$9999=Blotter!B20)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0)),0)</f>
-        <v>0</v>
+        <v>3267.6666666666665</v>
       </c>
       <c r="Y20" s="34">
         <f t="array" ref="Y20">IF(ISNUMBER(SUM((Trades!T$2:T$9999=Blotter!C20)*(Trades!U$2:U$9999=Blotter!B20)*(Trades!W$2:W$9999)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&gt;0))/SUM((Trades!T$2:T$9999=Blotter!C20)*(Trades!U$2:U$9999=Blotter!B20)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&gt;0))),SUM((Trades!T$2:T$9999=Blotter!C20)*(Trades!U$2:U$9999=Blotter!B20)*(Trades!W$2:W$9999)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&gt;0))/SUM((Trades!T$2:T$9999=Blotter!C20)*(Trades!U$2:U$9999=Blotter!B20)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&gt;0)),0)</f>
@@ -4593,7 +4571,7 @@
       </c>
       <c r="Z20" s="35">
         <f>IF(C$2="Last",IF(ISNUMBER(VLOOKUP(B20,Prices!A:L,8,0)),VLOOKUP(B20,Prices!A:L,8,0),0),IF(ISNUMBER(VLOOKUP(B20,Prices!A:L,12,0)),VLOOKUP(B20,Prices!A:L,12,0),0))</f>
-        <v>3246</v>
+        <v>3278</v>
       </c>
       <c r="AB20" s="29"/>
     </row>
@@ -4634,15 +4612,15 @@
       </c>
       <c r="L21" s="29">
         <f t="shared" ref="L21:L22" si="15">IF(I21=0,IF(H21&gt;0,X21,Y21),Z21)</f>
-        <v>1.75</v>
+        <v>1.1599999999999999</v>
       </c>
       <c r="M21" s="28">
         <f t="shared" ref="M21:M22" si="16">I21*J21*L21</f>
-        <v>5250</v>
+        <v>3479.9999999999995</v>
       </c>
       <c r="N21" s="95">
         <f t="array" ref="N21">-SUM((Trades!T$2:T$9999=Blotter!C21)*(Trades!U$2:U$9999=Blotter!B21)*(Trades!V$2:V$9999)*(Trades!W$2:W$9999))*J21+SUM((Trades!T$2:T$9999=Blotter!C21)*(Trades!U$2:U$9999=Blotter!B21)*(Trades!X$2:X$9999))+(L21*I21)*J21</f>
-        <v>-5377.1100000000024</v>
+        <v>-7147.1100000000024</v>
       </c>
       <c r="O21" s="29">
         <f>VLOOKUP(D21,Multiplier!B:H,3,0)</f>
@@ -4682,7 +4660,7 @@
       </c>
       <c r="Z21" s="35">
         <f>IF(C$2="Last",IF(ISNUMBER(VLOOKUP(B21,Prices!A:L,8,0)),VLOOKUP(B21,Prices!A:L,8,0),0),IF(ISNUMBER(VLOOKUP(B21,Prices!A:L,12,0)),VLOOKUP(B21,Prices!A:L,12,0),0))</f>
-        <v>1.75</v>
+        <v>1.1599999999999999</v>
       </c>
       <c r="AB21" s="29"/>
     </row>
@@ -4719,19 +4697,19 @@
       </c>
       <c r="K22" s="29">
         <f t="shared" si="14"/>
-        <v>0.34762999999999999</v>
+        <v>0.34762999999999994</v>
       </c>
       <c r="L22" s="29">
         <f t="shared" si="15"/>
-        <v>0.16</v>
+        <v>0.11</v>
       </c>
       <c r="M22" s="28">
         <f t="shared" si="16"/>
-        <v>-480</v>
+        <v>-330</v>
       </c>
       <c r="N22" s="95">
         <f t="array" ref="N22">-SUM((Trades!T$2:T$9999=Blotter!C22)*(Trades!U$2:U$9999=Blotter!B22)*(Trades!V$2:V$9999)*(Trades!W$2:W$9999))*J22+SUM((Trades!T$2:T$9999=Blotter!C22)*(Trades!U$2:U$9999=Blotter!B22)*(Trades!X$2:X$9999))+(L22*I22)*J22</f>
-        <v>562.88999999999987</v>
+        <v>712.88999999999987</v>
       </c>
       <c r="O22" s="29">
         <f>VLOOKUP(D22,Multiplier!B:H,3,0)</f>
@@ -4771,7 +4749,7 @@
       </c>
       <c r="Z22" s="35">
         <f>IF(C$2="Last",IF(ISNUMBER(VLOOKUP(B22,Prices!A:L,8,0)),VLOOKUP(B22,Prices!A:L,8,0),0),IF(ISNUMBER(VLOOKUP(B22,Prices!A:L,12,0)),VLOOKUP(B22,Prices!A:L,12,0),0))</f>
-        <v>0.16</v>
+        <v>0.11</v>
       </c>
       <c r="AB22" s="29"/>
     </row>
@@ -4808,19 +4786,19 @@
       </c>
       <c r="K23" s="29">
         <f t="shared" ref="K23" si="22">L23-N23/(H23*J23)</f>
-        <v>5.4700988000000006</v>
+        <v>5.4700987999999997</v>
       </c>
       <c r="L23" s="29">
         <f t="shared" ref="L23" si="23">IF(I23=0,IF(H23&gt;0,X23,Y23),Z23)</f>
-        <v>5.8860000000000001</v>
+        <v>5.9904999999999999</v>
       </c>
       <c r="M23" s="28">
         <f t="shared" ref="M23" si="24">I23*J23*L23</f>
-        <v>147150</v>
+        <v>149762.5</v>
       </c>
       <c r="N23" s="95">
         <f t="array" ref="N23">-SUM((Trades!T$2:T$9999=Blotter!C23)*(Trades!U$2:U$9999=Blotter!B23)*(Trades!V$2:V$9999)*(Trades!W$2:W$9999))*J23+SUM((Trades!T$2:T$9999=Blotter!C23)*(Trades!U$2:U$9999=Blotter!B23)*(Trades!X$2:X$9999))+(L23*I23)*J23</f>
-        <v>10397.529999999999</v>
+        <v>13010.029999999999</v>
       </c>
       <c r="O23" s="29">
         <f>VLOOKUP(D23,Multiplier!B:H,3,0)</f>
@@ -4836,19 +4814,19 @@
       </c>
       <c r="S23" s="29">
         <f t="shared" ref="S23" si="26">IF(OR(F23="Futures",F23="Spot"),IF(I23=0,0,IF(I23&gt;0,L23-O23,L23+O23)),0)</f>
-        <v>5.6942000000000004</v>
+        <v>5.7987000000000002</v>
       </c>
       <c r="T23" s="3">
         <f t="shared" ref="T23" si="27">IF(S23&gt;0,IF(ISNUMBER(S23/L23-1),S23/L23-1,0),0)</f>
-        <v>-3.2585796805980283E-2</v>
+        <v>-3.2017360821300356E-2</v>
       </c>
       <c r="U23" s="29">
         <f t="shared" ref="U23" si="28">IF(OR(F23="Futures",F23="Stocks"),IF(I23=0,0,IF(I23&gt;0,K23-P23,K23+P23)),0)</f>
-        <v>5.1823988000000005</v>
+        <v>5.1823987999999996</v>
       </c>
       <c r="V23" s="3">
         <f t="shared" ref="V23" si="29">IF(U23&gt;0,IF(ISNUMBER(U23/L23-1),U23/L23-1,0),0)</f>
-        <v>-0.1195380903839619</v>
+        <v>-0.13489712044069779</v>
       </c>
       <c r="X23" s="34">
         <f t="array" ref="X23">IF(ISNUMBER(SUM((Trades!T$2:T$9999=Blotter!C23)*(Trades!U$2:U$9999=Blotter!B23)*(Trades!W$2:W$9999)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0))/SUM((Trades!T$2:T$9999=Blotter!C23)*(Trades!U$2:U$9999=Blotter!B23)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0))),SUM((Trades!T$2:T$9999=Blotter!C23)*(Trades!U$2:U$9999=Blotter!B23)*(Trades!W$2:W$9999)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0))/SUM((Trades!T$2:T$9999=Blotter!C23)*(Trades!U$2:U$9999=Blotter!B23)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0)),0)</f>
@@ -4860,7 +4838,7 @@
       </c>
       <c r="Z23" s="35">
         <f>IF(C$2="Last",IF(ISNUMBER(VLOOKUP(B23,Prices!A:L,8,0)),VLOOKUP(B23,Prices!A:L,8,0),0),IF(ISNUMBER(VLOOKUP(B23,Prices!A:L,12,0)),VLOOKUP(B23,Prices!A:L,12,0),0))</f>
-        <v>5.8860000000000001</v>
+        <v>5.9904999999999999</v>
       </c>
       <c r="AB23" s="29"/>
     </row>
@@ -4901,43 +4879,44 @@
       </c>
       <c r="L24" s="29">
         <f t="shared" ref="L24" si="31">IF(I24=0,IF(H24&gt;0,X24,Y24),Z24)</f>
-        <v>57390</v>
+        <v>57675</v>
       </c>
       <c r="M24" s="28">
         <f t="shared" ref="M24" si="32">I24*J24*L24</f>
-        <v>286950</v>
+        <v>288375</v>
       </c>
       <c r="N24" s="95">
         <f t="array" ref="N24">-SUM((Trades!T$2:T$9999=Blotter!C24)*(Trades!U$2:U$9999=Blotter!B24)*(Trades!V$2:V$9999)*(Trades!W$2:W$9999))*J24+SUM((Trades!T$2:T$9999=Blotter!C24)*(Trades!U$2:U$9999=Blotter!B24)*(Trades!X$2:X$9999))+(L24*I24)*J24</f>
-        <v>38610.739999999991</v>
+        <v>40035.739999999991</v>
       </c>
       <c r="O24" s="29">
         <f>VLOOKUP(D24,Multiplier!B:H,3,0)</f>
         <v>1749</v>
       </c>
       <c r="P24" s="27">
-        <v>-1749</v>
+        <f>-1749*3</f>
+        <v>-5247</v>
       </c>
       <c r="Q24" s="27"/>
       <c r="R24" s="28">
         <f t="shared" ref="R24" si="33">(1-Q24)*P24*J24*H24</f>
-        <v>-8745</v>
+        <v>-26235</v>
       </c>
       <c r="S24" s="29">
         <f t="shared" ref="S24" si="34">IF(OR(F24="Futures",F24="Spot"),IF(I24=0,0,IF(I24&gt;0,L24-O24,L24+O24)),0)</f>
-        <v>55641</v>
+        <v>55926</v>
       </c>
       <c r="T24" s="3">
         <f t="shared" ref="T24" si="35">IF(S24&gt;0,IF(ISNUMBER(S24/L24-1),S24/L24-1,0),0)</f>
-        <v>-3.0475692629377993E-2</v>
+        <v>-3.0325097529258827E-2</v>
       </c>
       <c r="U24" s="29">
         <f t="shared" ref="U24" si="36">IF(OR(F24="Futures",F24="Stocks"),IF(I24=0,0,IF(I24&gt;0,K24-P24,K24+P24)),0)</f>
-        <v>51416.851999999999</v>
+        <v>54914.851999999999</v>
       </c>
       <c r="V24" s="3">
         <f t="shared" ref="V24" si="37">IF(U24&gt;0,IF(ISNUMBER(U24/L24-1),U24/L24-1,0),0)</f>
-        <v>-0.10407994424115696</v>
+        <v>-4.7856922410056346E-2</v>
       </c>
       <c r="X24" s="34">
         <f t="array" ref="X24">IF(ISNUMBER(SUM((Trades!T$2:T$9999=Blotter!C24)*(Trades!U$2:U$9999=Blotter!B24)*(Trades!W$2:W$9999)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0))/SUM((Trades!T$2:T$9999=Blotter!C24)*(Trades!U$2:U$9999=Blotter!B24)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0))),SUM((Trades!T$2:T$9999=Blotter!C24)*(Trades!U$2:U$9999=Blotter!B24)*(Trades!W$2:W$9999)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0))/SUM((Trades!T$2:T$9999=Blotter!C24)*(Trades!U$2:U$9999=Blotter!B24)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0)),0)</f>
@@ -4949,7 +4928,7 @@
       </c>
       <c r="Z24" s="35">
         <f>IF(C$2="Last",IF(ISNUMBER(VLOOKUP(B24,Prices!A:L,8,0)),VLOOKUP(B24,Prices!A:L,8,0),0),IF(ISNUMBER(VLOOKUP(B24,Prices!A:L,12,0)),VLOOKUP(B24,Prices!A:L,12,0),0))</f>
-        <v>57390</v>
+        <v>57675</v>
       </c>
       <c r="AB24" s="29"/>
     </row>
@@ -4990,15 +4969,15 @@
       </c>
       <c r="L25" s="29">
         <f t="shared" ref="L25:L26" si="39">IF(I25=0,IF(H25&gt;0,X25,Y25),Z25)</f>
-        <v>17.600000000000001</v>
+        <v>14.8</v>
       </c>
       <c r="M25" s="28">
         <f t="shared" ref="M25:M26" si="40">I25*J25*L25</f>
-        <v>-1760.0000000000002</v>
+        <v>-1480</v>
       </c>
       <c r="N25" s="95">
         <f t="array" ref="N25">-SUM((Trades!T$2:T$9999=Blotter!C25)*(Trades!U$2:U$9999=Blotter!B25)*(Trades!V$2:V$9999)*(Trades!W$2:W$9999))*J25+SUM((Trades!T$2:T$9999=Blotter!C25)*(Trades!U$2:U$9999=Blotter!B25)*(Trades!X$2:X$9999))+(L25*I25)*J25</f>
-        <v>877.47999999999979</v>
+        <v>1157.48</v>
       </c>
       <c r="O25" s="29">
         <f>VLOOKUP(D25,Multiplier!B:H,3,0)</f>
@@ -5038,7 +5017,7 @@
       </c>
       <c r="Z25" s="35">
         <f>IF(C$2="Last",IF(ISNUMBER(VLOOKUP(B25,Prices!A:L,8,0)),VLOOKUP(B25,Prices!A:L,8,0),0),IF(ISNUMBER(VLOOKUP(B25,Prices!A:L,12,0)),VLOOKUP(B25,Prices!A:L,12,0),0))</f>
-        <v>17.600000000000001</v>
+        <v>14.8</v>
       </c>
       <c r="AB25" s="29"/>
     </row>
@@ -5075,19 +5054,19 @@
       </c>
       <c r="K26" s="29">
         <f t="shared" si="38"/>
-        <v>125.42520000000002</v>
+        <v>125.4252</v>
       </c>
       <c r="L26" s="29">
         <f t="shared" si="39"/>
-        <v>112.4</v>
+        <v>100.8</v>
       </c>
       <c r="M26" s="28">
         <f t="shared" si="40"/>
-        <v>11240</v>
+        <v>10080</v>
       </c>
       <c r="N26" s="95">
         <f t="array" ref="N26">-SUM((Trades!T$2:T$9999=Blotter!C26)*(Trades!U$2:U$9999=Blotter!B26)*(Trades!V$2:V$9999)*(Trades!W$2:W$9999))*J26+SUM((Trades!T$2:T$9999=Blotter!C26)*(Trades!U$2:U$9999=Blotter!B26)*(Trades!X$2:X$9999))+(L26*I26)*J26</f>
-        <v>-1302.5200000000004</v>
+        <v>-2462.5200000000004</v>
       </c>
       <c r="O26" s="29">
         <f>VLOOKUP(D26,Multiplier!B:H,3,0)</f>
@@ -5127,7 +5106,7 @@
       </c>
       <c r="Z26" s="35">
         <f>IF(C$2="Last",IF(ISNUMBER(VLOOKUP(B26,Prices!A:L,8,0)),VLOOKUP(B26,Prices!A:L,8,0),0),IF(ISNUMBER(VLOOKUP(B26,Prices!A:L,12,0)),VLOOKUP(B26,Prices!A:L,12,0),0))</f>
-        <v>112.4</v>
+        <v>100.8</v>
       </c>
       <c r="AB26" s="29"/>
     </row>
@@ -5164,19 +5143,19 @@
       </c>
       <c r="K27" s="99">
         <f t="shared" ref="K27" si="46">L27-N27/(H27*J27)</f>
-        <v>1.1721699999999997</v>
+        <v>1.1721699999999999</v>
       </c>
       <c r="L27" s="99">
         <f t="shared" ref="L27" si="47">IF(I27=0,IF(H27&gt;0,X27,Y27),Z27)</f>
-        <v>1.1766000000000001</v>
+        <v>1.1799500000000001</v>
       </c>
       <c r="M27" s="28">
         <f t="shared" ref="M27" si="48">I27*J27*L27</f>
-        <v>735375</v>
+        <v>737468.75</v>
       </c>
       <c r="N27" s="95">
         <f t="array" ref="N27">-SUM((Trades!T$2:T$9999=Blotter!C27)*(Trades!U$2:U$9999=Blotter!B27)*(Trades!V$2:V$9999)*(Trades!W$2:W$9999))*J27+SUM((Trades!T$2:T$9999=Blotter!C27)*(Trades!U$2:U$9999=Blotter!B27)*(Trades!X$2:X$9999))+(L27*I27)*J27</f>
-        <v>2768.7500000002328</v>
+        <v>4862.5000000001164</v>
       </c>
       <c r="O27" s="46">
         <f>VLOOKUP(D27,Multiplier!B:H,3,0)</f>
@@ -5193,19 +5172,19 @@
       </c>
       <c r="S27" s="29">
         <f t="shared" ref="S27" si="50">IF(OR(F27="Futures",F27="Spot"),IF(I27=0,0,IF(I27&gt;0,L27-O27,L27+O27)),0)</f>
-        <v>1.1671500000000001</v>
+        <v>1.1705000000000001</v>
       </c>
       <c r="T27" s="3">
         <f t="shared" ref="T27" si="51">IF(S27&gt;0,IF(ISNUMBER(S27/L27-1),S27/L27-1,0),0)</f>
-        <v>-8.0316165221825386E-3</v>
+        <v>-8.0088139327937347E-3</v>
       </c>
       <c r="U27" s="29">
         <f t="shared" ref="U27" si="52">IF(OR(F27="Futures",F27="Stocks"),IF(I27=0,0,IF(I27&gt;0,K27-P27,K27+P27)),0)</f>
-        <v>1.1579949999999997</v>
+        <v>1.1579949999999999</v>
       </c>
       <c r="V27" s="3">
         <f t="shared" ref="V27" si="53">IF(U27&gt;0,IF(ISNUMBER(U27/L27-1),U27/L27-1,0),0)</f>
-        <v>-1.581251062383171E-2</v>
+        <v>-1.8606720623755346E-2</v>
       </c>
       <c r="X27" s="34">
         <f t="array" ref="X27">IF(ISNUMBER(SUM((Trades!T$2:T$9999=Blotter!C27)*(Trades!U$2:U$9999=Blotter!B27)*(Trades!W$2:W$9999)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0))/SUM((Trades!T$2:T$9999=Blotter!C27)*(Trades!U$2:U$9999=Blotter!B27)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0))),SUM((Trades!T$2:T$9999=Blotter!C27)*(Trades!U$2:U$9999=Blotter!B27)*(Trades!W$2:W$9999)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0))/SUM((Trades!T$2:T$9999=Blotter!C27)*(Trades!U$2:U$9999=Blotter!B27)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0)),0)</f>
@@ -5217,7 +5196,7 @@
       </c>
       <c r="Z27" s="35">
         <f>IF(C$2="Last",IF(ISNUMBER(VLOOKUP(B27,Prices!A:L,8,0)),VLOOKUP(B27,Prices!A:L,8,0),0),IF(ISNUMBER(VLOOKUP(B27,Prices!A:L,12,0)),VLOOKUP(B27,Prices!A:L,12,0),0))</f>
-        <v>1.1766000000000001</v>
+        <v>1.1799500000000001</v>
       </c>
       <c r="AB27" s="29"/>
     </row>
@@ -6815,31 +6794,31 @@
         <v>59</v>
       </c>
       <c r="H2" s="91">
-        <v>6812.25</v>
+        <v>6934.25</v>
       </c>
       <c r="I2" s="91">
-        <v>6812</v>
+        <v>6934</v>
       </c>
       <c r="J2" s="91">
-        <v>6812.5</v>
+        <v>6934.25</v>
       </c>
       <c r="K2" s="91">
-        <v>6812.25</v>
+        <v>6934.125</v>
       </c>
       <c r="L2" s="91">
-        <v>6855.25</v>
+        <v>6922.75</v>
       </c>
       <c r="M2" s="91">
-        <v>6780</v>
+        <v>6925.25</v>
       </c>
       <c r="N2" s="91">
-        <v>6820</v>
+        <v>6942.25</v>
       </c>
       <c r="O2" s="91">
-        <v>6767</v>
+        <v>6920.25</v>
       </c>
       <c r="P2" s="91">
-        <v>164382</v>
+        <v>89489</v>
       </c>
       <c r="Q2" s="91"/>
       <c r="R2" s="91"/>
@@ -6847,7 +6826,7 @@
       <c r="T2" s="91"/>
       <c r="U2" s="91"/>
       <c r="V2" s="85">
-        <v>46125.517858796295</v>
+        <v>46126.504861111112</v>
       </c>
       <c r="W2" s="81" t="s">
         <v>258</v>
@@ -6879,31 +6858,31 @@
         <v>59</v>
       </c>
       <c r="H3" s="91">
-        <v>25112.75</v>
+        <v>25638.5</v>
       </c>
       <c r="I3" s="91">
-        <v>25112.5</v>
+        <v>25638</v>
       </c>
       <c r="J3" s="91">
-        <v>25113</v>
+        <v>25638.75</v>
       </c>
       <c r="K3" s="91">
-        <v>25112.75</v>
+        <v>25638.375</v>
       </c>
       <c r="L3" s="91">
-        <v>25281.25</v>
+        <v>25543.5</v>
       </c>
       <c r="M3" s="91">
-        <v>24980</v>
+        <v>25575.25</v>
       </c>
       <c r="N3" s="91">
-        <v>25133</v>
+        <v>25674</v>
       </c>
       <c r="O3" s="91">
-        <v>24904.5</v>
+        <v>25560</v>
       </c>
       <c r="P3" s="91">
-        <v>86715</v>
+        <v>54911</v>
       </c>
       <c r="Q3" s="91"/>
       <c r="R3" s="91"/>
@@ -6911,7 +6890,7 @@
       <c r="T3" s="91"/>
       <c r="U3" s="91"/>
       <c r="V3" s="85">
-        <v>46125.517858796295</v>
+        <v>46126.504861111112</v>
       </c>
       <c r="W3" s="81" t="s">
         <v>258</v>
@@ -6943,31 +6922,31 @@
         <v>59</v>
       </c>
       <c r="H4" s="91">
-        <v>2619.1999999999998</v>
+        <v>2693.6</v>
       </c>
       <c r="I4" s="91">
-        <v>2619</v>
+        <v>2693.5</v>
       </c>
       <c r="J4" s="91">
-        <v>2619.3000000000002</v>
+        <v>2693.7</v>
       </c>
       <c r="K4" s="91">
-        <v>2619.15</v>
+        <v>2693.6</v>
       </c>
       <c r="L4" s="91">
-        <v>2644.4</v>
+        <v>2682.3</v>
       </c>
       <c r="M4" s="91">
-        <v>2607.8000000000002</v>
+        <v>2688.2</v>
       </c>
       <c r="N4" s="91">
-        <v>2622.8</v>
+        <v>2698.7</v>
       </c>
       <c r="O4" s="91">
-        <v>2591.8000000000002</v>
+        <v>2684.1</v>
       </c>
       <c r="P4" s="91">
-        <v>23113</v>
+        <v>11258</v>
       </c>
       <c r="Q4" s="91"/>
       <c r="R4" s="91"/>
@@ -6975,7 +6954,7 @@
       <c r="T4" s="91"/>
       <c r="U4" s="91"/>
       <c r="V4" s="85">
-        <v>46125.517858796295</v>
+        <v>46126.504861111112</v>
       </c>
       <c r="W4" s="81" t="s">
         <v>258</v>
@@ -7007,31 +6986,31 @@
         <v>56</v>
       </c>
       <c r="H5" s="91">
-        <v>23745</v>
+        <v>24142</v>
       </c>
       <c r="I5" s="91">
-        <v>23744</v>
+        <v>24141</v>
       </c>
       <c r="J5" s="91">
-        <v>23747</v>
+        <v>24143</v>
       </c>
       <c r="K5" s="91">
-        <v>23745.5</v>
+        <v>24142</v>
       </c>
       <c r="L5" s="91">
-        <v>24037</v>
+        <v>23922</v>
       </c>
       <c r="M5" s="91">
-        <v>23695</v>
+        <v>24120</v>
       </c>
       <c r="N5" s="91">
-        <v>23793</v>
+        <v>24231</v>
       </c>
       <c r="O5" s="91">
-        <v>23579</v>
+        <v>24042</v>
       </c>
       <c r="P5" s="91">
-        <v>6413</v>
+        <v>9378</v>
       </c>
       <c r="Q5" s="91"/>
       <c r="R5" s="91"/>
@@ -7039,7 +7018,7 @@
       <c r="T5" s="91"/>
       <c r="U5" s="91"/>
       <c r="V5" s="85">
-        <v>46125.517858796295</v>
+        <v>46126.504861111112</v>
       </c>
       <c r="W5" s="81" t="s">
         <v>258</v>
@@ -7071,31 +7050,31 @@
         <v>59</v>
       </c>
       <c r="H6" s="91">
-        <v>56720</v>
+        <v>58040</v>
       </c>
       <c r="I6" s="91">
-        <v>56685</v>
+        <v>58030</v>
       </c>
       <c r="J6" s="91">
-        <v>56700</v>
+        <v>58045</v>
       </c>
       <c r="K6" s="91">
-        <v>56692.5</v>
+        <v>58037.5</v>
       </c>
       <c r="L6" s="91">
-        <v>57390</v>
+        <v>57675</v>
       </c>
       <c r="M6" s="91">
-        <v>56505</v>
+        <v>57710</v>
       </c>
       <c r="N6" s="91">
-        <v>56880</v>
+        <v>58305</v>
       </c>
       <c r="O6" s="91">
-        <v>55950</v>
+        <v>57475</v>
       </c>
       <c r="P6" s="91">
-        <v>1898</v>
+        <v>2033</v>
       </c>
       <c r="Q6" s="91"/>
       <c r="R6" s="91"/>
@@ -7103,7 +7082,7 @@
       <c r="T6" s="91"/>
       <c r="U6" s="91"/>
       <c r="V6" s="85">
-        <v>46125.517858796295</v>
+        <v>46126.504861111112</v>
       </c>
       <c r="W6" s="81" t="s">
         <v>258</v>
@@ -7146,7 +7125,7 @@
       <c r="T7" s="93"/>
       <c r="U7" s="93"/>
       <c r="V7" s="92">
-        <v>46125.517858796295</v>
+        <v>46126.504861111112</v>
       </c>
       <c r="W7" s="1" t="s">
         <v>313</v>
@@ -7175,31 +7154,31 @@
         <v>59</v>
       </c>
       <c r="H8" s="93">
-        <v>2.8530000000000002</v>
+        <v>2.774</v>
       </c>
       <c r="I8" s="93">
-        <v>2.8519999999999999</v>
+        <v>2.7730000000000001</v>
       </c>
       <c r="J8" s="93">
-        <v>2.8540000000000001</v>
+        <v>2.7749999999999999</v>
       </c>
       <c r="K8" s="93">
-        <v>2.8529999999999998</v>
+        <v>2.774</v>
       </c>
       <c r="L8" s="93">
-        <v>2.806</v>
+        <v>2.7909999999999999</v>
       </c>
       <c r="M8" s="93">
-        <v>2.839</v>
+        <v>2.7909999999999999</v>
       </c>
       <c r="N8" s="93">
-        <v>2.8730000000000002</v>
+        <v>2.7930000000000001</v>
       </c>
       <c r="O8" s="93">
-        <v>2.8220000000000001</v>
+        <v>2.754</v>
       </c>
       <c r="P8" s="93">
-        <v>3705</v>
+        <v>3853</v>
       </c>
       <c r="Q8" s="93"/>
       <c r="R8" s="93"/>
@@ -7207,7 +7186,7 @@
       <c r="T8" s="93"/>
       <c r="U8" s="93"/>
       <c r="V8" s="92">
-        <v>46125.517858796295</v>
+        <v>46126.504861111112</v>
       </c>
       <c r="W8" s="1" t="s">
         <v>258</v>
@@ -7236,31 +7215,31 @@
         <v>59</v>
       </c>
       <c r="H9" s="93">
-        <v>3.0821000000000001</v>
+        <v>3.0375000000000001</v>
       </c>
       <c r="I9" s="93">
-        <v>3.0819000000000001</v>
+        <v>3.0373000000000001</v>
       </c>
       <c r="J9" s="93">
-        <v>3.0823999999999998</v>
+        <v>3.0377999999999998</v>
       </c>
       <c r="K9" s="93">
-        <v>3.0821499999999999</v>
+        <v>3.03755</v>
       </c>
       <c r="L9" s="93">
-        <v>2.9552</v>
+        <v>3.0428999999999999</v>
       </c>
       <c r="M9" s="93">
-        <v>3.0146000000000002</v>
+        <v>3.028</v>
       </c>
       <c r="N9" s="93">
-        <v>3.1118000000000001</v>
+        <v>3.0409999999999999</v>
       </c>
       <c r="O9" s="93">
-        <v>3.0146000000000002</v>
+        <v>2.9824000000000002</v>
       </c>
       <c r="P9" s="93">
-        <v>9373</v>
+        <v>6156</v>
       </c>
       <c r="Q9" s="93"/>
       <c r="R9" s="93"/>
@@ -7268,7 +7247,7 @@
       <c r="T9" s="93"/>
       <c r="U9" s="93"/>
       <c r="V9" s="92">
-        <v>46125.517858796295</v>
+        <v>46126.504861111112</v>
       </c>
       <c r="W9" s="1" t="s">
         <v>258</v>
@@ -7296,43 +7275,25 @@
       <c r="G10" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="H10" s="93">
-        <v>4738.6000000000004</v>
-      </c>
-      <c r="I10" s="93">
-        <v>4738.3</v>
-      </c>
-      <c r="J10" s="93">
-        <v>4738.8</v>
-      </c>
-      <c r="K10" s="93">
-        <v>4738.55</v>
-      </c>
-      <c r="L10" s="93">
-        <v>4787.3999999999996</v>
-      </c>
-      <c r="M10" s="93">
-        <v>4710</v>
-      </c>
-      <c r="N10" s="93">
-        <v>4762.5</v>
-      </c>
-      <c r="O10" s="93">
-        <v>4626</v>
-      </c>
-      <c r="P10" s="93">
-        <v>51090</v>
-      </c>
+      <c r="H10" s="93"/>
+      <c r="I10" s="93"/>
+      <c r="J10" s="93"/>
+      <c r="K10" s="93"/>
+      <c r="L10" s="93"/>
+      <c r="M10" s="93"/>
+      <c r="N10" s="93"/>
+      <c r="O10" s="93"/>
+      <c r="P10" s="93"/>
       <c r="Q10" s="93"/>
       <c r="R10" s="93"/>
       <c r="S10" s="93"/>
       <c r="T10" s="93"/>
       <c r="U10" s="93"/>
       <c r="V10" s="92">
-        <v>46125.517858796295</v>
+        <v>46126.504861111112</v>
       </c>
       <c r="W10" s="1" t="s">
-        <v>258</v>
+        <v>313</v>
       </c>
     </row>
     <row r="11" spans="1:32" x14ac:dyDescent="0.4">
@@ -7358,31 +7319,31 @@
         <v>59</v>
       </c>
       <c r="H11" s="93">
-        <v>74.739999999999995</v>
+        <v>78.204999999999998</v>
       </c>
       <c r="I11" s="93">
-        <v>74.680000000000007</v>
+        <v>78.254999999999995</v>
       </c>
       <c r="J11" s="93">
-        <v>74.724999999999994</v>
+        <v>78.290000000000006</v>
       </c>
       <c r="K11" s="93">
-        <v>74.702500000000001</v>
+        <v>78.272500000000008</v>
       </c>
       <c r="L11" s="93">
-        <v>76.765000000000001</v>
+        <v>75.94</v>
       </c>
       <c r="M11" s="93">
-        <v>75.290000000000006</v>
+        <v>76.180000000000007</v>
       </c>
       <c r="N11" s="93">
-        <v>75.290000000000006</v>
+        <v>78.44</v>
       </c>
       <c r="O11" s="93">
-        <v>73.260000000000005</v>
+        <v>76.075000000000003</v>
       </c>
       <c r="P11" s="93">
-        <v>268</v>
+        <v>231</v>
       </c>
       <c r="Q11" s="93"/>
       <c r="R11" s="93"/>
@@ -7390,7 +7351,7 @@
       <c r="T11" s="93"/>
       <c r="U11" s="93"/>
       <c r="V11" s="92">
-        <v>46125.517858796295</v>
+        <v>46126.504861111112</v>
       </c>
       <c r="W11" s="1" t="s">
         <v>258</v>
@@ -7419,31 +7380,31 @@
         <v>59</v>
       </c>
       <c r="H12" s="93">
-        <v>5.8525</v>
+        <v>6.0430000000000001</v>
       </c>
       <c r="I12" s="93">
-        <v>5.8514999999999997</v>
+        <v>6.0425000000000004</v>
       </c>
       <c r="J12" s="93">
-        <v>5.8529999999999998</v>
+        <v>6.0434999999999999</v>
       </c>
       <c r="K12" s="93">
-        <v>5.8522499999999997</v>
+        <v>6.0430000000000001</v>
       </c>
       <c r="L12" s="93">
-        <v>5.8860000000000001</v>
+        <v>5.9904999999999999</v>
       </c>
       <c r="M12" s="93">
-        <v>5.8174999999999999</v>
+        <v>6.0034999999999998</v>
       </c>
       <c r="N12" s="93">
-        <v>5.8845000000000001</v>
+        <v>6.0620000000000003</v>
       </c>
       <c r="O12" s="93">
-        <v>5.7640000000000002</v>
+        <v>5.9965000000000002</v>
       </c>
       <c r="P12" s="93">
-        <v>14864</v>
+        <v>13372</v>
       </c>
       <c r="Q12" s="93"/>
       <c r="R12" s="93"/>
@@ -7451,7 +7412,7 @@
       <c r="T12" s="93"/>
       <c r="U12" s="93"/>
       <c r="V12" s="92">
-        <v>46125.517858796295</v>
+        <v>46126.504861111112</v>
       </c>
       <c r="W12" s="1" t="s">
         <v>258</v>
@@ -7480,31 +7441,31 @@
         <v>59</v>
       </c>
       <c r="H13" s="93">
-        <v>444.5</v>
+        <v>442.25</v>
       </c>
       <c r="I13" s="93">
-        <v>444.25</v>
+        <v>442.25</v>
       </c>
       <c r="J13" s="93">
-        <v>444.5</v>
+        <v>442.5</v>
       </c>
       <c r="K13" s="93">
-        <v>444.375</v>
+        <v>442.375</v>
       </c>
       <c r="L13" s="93">
-        <v>441</v>
+        <v>440.25</v>
       </c>
       <c r="M13" s="93">
-        <v>446</v>
+        <v>440.5</v>
       </c>
       <c r="N13" s="93">
-        <v>446</v>
+        <v>443.25</v>
       </c>
       <c r="O13" s="93">
-        <v>442.75</v>
+        <v>440.25</v>
       </c>
       <c r="P13" s="93">
-        <v>28805</v>
+        <v>12892</v>
       </c>
       <c r="Q13" s="93"/>
       <c r="R13" s="93"/>
@@ -7512,7 +7473,7 @@
       <c r="T13" s="93"/>
       <c r="U13" s="93"/>
       <c r="V13" s="92">
-        <v>46125.517858796295</v>
+        <v>46126.504861111112</v>
       </c>
       <c r="W13" s="1" t="s">
         <v>258</v>
@@ -7541,31 +7502,31 @@
         <v>59</v>
       </c>
       <c r="H14" s="93">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="I14" s="93">
-        <v>581.75</v>
+        <v>583</v>
       </c>
       <c r="J14" s="93">
-        <v>582</v>
+        <v>583.5</v>
       </c>
       <c r="K14" s="93">
-        <v>581.875</v>
+        <v>583.25</v>
       </c>
       <c r="L14" s="93">
-        <v>571</v>
+        <v>582.25</v>
       </c>
       <c r="M14" s="93">
-        <v>580</v>
+        <v>581.5</v>
       </c>
       <c r="N14" s="93">
-        <v>584</v>
+        <v>585.25</v>
       </c>
       <c r="O14" s="93">
-        <v>576.25</v>
+        <v>578.5</v>
       </c>
       <c r="P14" s="93">
-        <v>15939</v>
+        <v>6982</v>
       </c>
       <c r="Q14" s="93"/>
       <c r="R14" s="93"/>
@@ -7573,7 +7534,7 @@
       <c r="T14" s="93"/>
       <c r="U14" s="93"/>
       <c r="V14" s="92">
-        <v>46125.517858796295</v>
+        <v>46126.504861111112</v>
       </c>
       <c r="W14" s="1" t="s">
         <v>258</v>
@@ -7602,31 +7563,31 @@
         <v>59</v>
       </c>
       <c r="H15" s="93">
-        <v>1176.5</v>
+        <v>1163.5</v>
       </c>
       <c r="I15" s="93">
-        <v>1176.25</v>
+        <v>1163.5</v>
       </c>
       <c r="J15" s="93">
-        <v>1176.5</v>
+        <v>1163.75</v>
       </c>
       <c r="K15" s="93">
-        <v>1176.375</v>
+        <v>1163.625</v>
       </c>
       <c r="L15" s="93">
-        <v>1175.75</v>
+        <v>1162.25</v>
       </c>
       <c r="M15" s="93">
-        <v>1177</v>
+        <v>1160.5</v>
       </c>
       <c r="N15" s="93">
-        <v>1183.75</v>
+        <v>1165.75</v>
       </c>
       <c r="O15" s="93">
-        <v>1171.5</v>
+        <v>1158.25</v>
       </c>
       <c r="P15" s="93">
-        <v>29866</v>
+        <v>14916</v>
       </c>
       <c r="Q15" s="93"/>
       <c r="R15" s="93"/>
@@ -7634,7 +7595,7 @@
       <c r="T15" s="93"/>
       <c r="U15" s="93"/>
       <c r="V15" s="92">
-        <v>46125.517858796295</v>
+        <v>46126.504861111112</v>
       </c>
       <c r="W15" s="1" t="s">
         <v>258</v>
@@ -7663,31 +7624,31 @@
         <v>59</v>
       </c>
       <c r="H16" s="93">
-        <v>13.86</v>
+        <v>13.84</v>
       </c>
       <c r="I16" s="93">
-        <v>13.85</v>
+        <v>13.83</v>
       </c>
       <c r="J16" s="93">
-        <v>13.86</v>
+        <v>13.84</v>
       </c>
       <c r="K16" s="93">
-        <v>13.855</v>
+        <v>13.835000000000001</v>
       </c>
       <c r="L16" s="93">
-        <v>13.75</v>
+        <v>13.68</v>
       </c>
       <c r="M16" s="93">
-        <v>13.88</v>
+        <v>13.63</v>
       </c>
       <c r="N16" s="93">
-        <v>13.97</v>
+        <v>13.87</v>
       </c>
       <c r="O16" s="93">
-        <v>13.74</v>
+        <v>13.62</v>
       </c>
       <c r="P16" s="93">
-        <v>16623</v>
+        <v>18098</v>
       </c>
       <c r="Q16" s="93"/>
       <c r="R16" s="93"/>
@@ -7695,7 +7656,7 @@
       <c r="T16" s="93"/>
       <c r="U16" s="93"/>
       <c r="V16" s="92">
-        <v>46125.517858796295</v>
+        <v>46126.504861111112</v>
       </c>
       <c r="W16" s="1" t="s">
         <v>258</v>
@@ -7724,31 +7685,31 @@
         <v>59</v>
       </c>
       <c r="H17" s="93">
-        <v>303.35000000000002</v>
+        <v>304.39999999999998</v>
       </c>
       <c r="I17" s="93">
-        <v>303.25</v>
+        <v>304.2</v>
       </c>
       <c r="J17" s="93">
-        <v>303.39999999999998</v>
+        <v>304.45</v>
       </c>
       <c r="K17" s="93">
-        <v>303.32499999999999</v>
+        <v>304.32499999999999</v>
       </c>
       <c r="L17" s="93">
-        <v>300.10000000000002</v>
+        <v>300.85000000000002</v>
       </c>
       <c r="M17" s="93">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="N17" s="93">
-        <v>305.75</v>
+        <v>304.89999999999998</v>
       </c>
       <c r="O17" s="93">
-        <v>298.3</v>
+        <v>299.85000000000002</v>
       </c>
       <c r="P17" s="93">
-        <v>2294</v>
+        <v>1301</v>
       </c>
       <c r="Q17" s="93"/>
       <c r="R17" s="93"/>
@@ -7756,7 +7717,7 @@
       <c r="T17" s="93"/>
       <c r="U17" s="93"/>
       <c r="V17" s="92">
-        <v>46125.517858796295</v>
+        <v>46126.504861111112</v>
       </c>
       <c r="W17" s="1" t="s">
         <v>258</v>
@@ -7785,31 +7746,31 @@
         <v>59</v>
       </c>
       <c r="H18" s="93">
-        <v>3276</v>
+        <v>3302</v>
       </c>
       <c r="I18" s="93">
-        <v>3269</v>
+        <v>3300</v>
       </c>
       <c r="J18" s="93">
-        <v>3273</v>
+        <v>3303</v>
       </c>
       <c r="K18" s="93">
-        <v>3271</v>
+        <v>3301.5</v>
       </c>
       <c r="L18" s="93">
-        <v>3246</v>
+        <v>3278</v>
       </c>
       <c r="M18" s="93">
-        <v>3253</v>
+        <v>3281</v>
       </c>
       <c r="N18" s="93">
-        <v>3299</v>
+        <v>3311</v>
       </c>
       <c r="O18" s="93">
-        <v>3220</v>
+        <v>3272</v>
       </c>
       <c r="P18" s="93">
-        <v>1278</v>
+        <v>873</v>
       </c>
       <c r="Q18" s="93"/>
       <c r="R18" s="93"/>
@@ -7817,7 +7778,7 @@
       <c r="T18" s="93"/>
       <c r="U18" s="93"/>
       <c r="V18" s="92">
-        <v>46125.517858796295</v>
+        <v>46126.504861111112</v>
       </c>
       <c r="W18" s="1" t="s">
         <v>258</v>
@@ -7846,31 +7807,31 @@
         <v>59</v>
       </c>
       <c r="H19" s="93">
-        <v>73.540000000000006</v>
+        <v>74.88</v>
       </c>
       <c r="I19" s="93">
-        <v>73.53</v>
+        <v>74.86</v>
       </c>
       <c r="J19" s="93">
-        <v>73.540000000000006</v>
+        <v>74.89</v>
       </c>
       <c r="K19" s="93">
-        <v>73.534999999999997</v>
+        <v>74.875</v>
       </c>
       <c r="L19" s="93">
-        <v>73.22</v>
+        <v>74.53</v>
       </c>
       <c r="M19" s="93">
-        <v>73.33</v>
+        <v>74.53</v>
       </c>
       <c r="N19" s="93">
-        <v>73.739999999999995</v>
+        <v>74.97</v>
       </c>
       <c r="O19" s="93">
-        <v>72.650000000000006</v>
+        <v>74.459999999999994</v>
       </c>
       <c r="P19" s="93">
-        <v>7182</v>
+        <v>3576</v>
       </c>
       <c r="Q19" s="93"/>
       <c r="R19" s="93"/>
@@ -7878,7 +7839,7 @@
       <c r="T19" s="93"/>
       <c r="U19" s="93"/>
       <c r="V19" s="92">
-        <v>46125.517858796295</v>
+        <v>46126.504861111112</v>
       </c>
       <c r="W19" s="1" t="s">
         <v>258</v>
@@ -7919,15 +7880,19 @@
         <v>-100</v>
       </c>
       <c r="L20" s="93">
-        <v>251.77500000000001</v>
+        <v>250.65</v>
       </c>
       <c r="M20" s="93">
-        <v>0</v>
-      </c>
-      <c r="N20" s="93"/>
-      <c r="O20" s="93"/>
+        <v>250.8</v>
+      </c>
+      <c r="N20" s="93">
+        <v>251.57499999999999</v>
+      </c>
+      <c r="O20" s="93">
+        <v>250.5</v>
+      </c>
       <c r="P20" s="93">
-        <v>0</v>
+        <v>5037</v>
       </c>
       <c r="Q20" s="93"/>
       <c r="R20" s="93"/>
@@ -7935,7 +7900,7 @@
       <c r="T20" s="93"/>
       <c r="U20" s="93"/>
       <c r="V20" s="92">
-        <v>46125.517858796295</v>
+        <v>46126.504861111112</v>
       </c>
       <c r="W20" s="1" t="s">
         <v>258</v>
@@ -7976,15 +7941,19 @@
         <v>-100</v>
       </c>
       <c r="L21" s="93">
-        <v>372.35</v>
+        <v>372.82499999999999</v>
       </c>
       <c r="M21" s="93">
-        <v>0</v>
-      </c>
-      <c r="N21" s="93"/>
-      <c r="O21" s="93"/>
+        <v>371.57499999999999</v>
+      </c>
+      <c r="N21" s="93">
+        <v>373.875</v>
+      </c>
+      <c r="O21" s="93">
+        <v>371.125</v>
+      </c>
       <c r="P21" s="93">
-        <v>0</v>
+        <v>8436</v>
       </c>
       <c r="Q21" s="93"/>
       <c r="R21" s="93"/>
@@ -7992,7 +7961,7 @@
       <c r="T21" s="93"/>
       <c r="U21" s="93"/>
       <c r="V21" s="92">
-        <v>46125.517858796295</v>
+        <v>46126.504861111112</v>
       </c>
       <c r="W21" s="1" t="s">
         <v>258</v>
@@ -8021,7 +7990,7 @@
         <v>59</v>
       </c>
       <c r="H22" s="93">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I22" s="93">
         <v>-100</v>
@@ -8033,15 +8002,19 @@
         <v>-100</v>
       </c>
       <c r="L22" s="93">
-        <v>90.724999999999994</v>
+        <v>90.5</v>
       </c>
       <c r="M22" s="93">
-        <v>0</v>
-      </c>
-      <c r="N22" s="93"/>
-      <c r="O22" s="93"/>
+        <v>90.65</v>
+      </c>
+      <c r="N22" s="93">
+        <v>90.7</v>
+      </c>
+      <c r="O22" s="93">
+        <v>90.424999999999997</v>
+      </c>
       <c r="P22" s="93">
-        <v>0</v>
+        <v>3319</v>
       </c>
       <c r="Q22" s="93"/>
       <c r="R22" s="93"/>
@@ -8049,7 +8022,7 @@
       <c r="T22" s="93"/>
       <c r="U22" s="93"/>
       <c r="V22" s="92">
-        <v>46125.517858796295</v>
+        <v>46126.504861111112</v>
       </c>
       <c r="W22" s="1" t="s">
         <v>258</v>
@@ -8078,31 +8051,31 @@
         <v>59</v>
       </c>
       <c r="H23" s="93">
-        <v>98.775000000000006</v>
+        <v>97.94</v>
       </c>
       <c r="I23" s="93">
-        <v>98.775000000000006</v>
+        <v>97.935000000000002</v>
       </c>
       <c r="J23" s="93">
-        <v>98.784999999999997</v>
+        <v>97.944999999999993</v>
       </c>
       <c r="K23" s="93">
-        <v>98.78</v>
+        <v>97.94</v>
       </c>
       <c r="L23" s="93">
-        <v>98.44</v>
+        <v>98.165000000000006</v>
       </c>
       <c r="M23" s="93">
-        <v>98.92</v>
+        <v>98.15</v>
       </c>
       <c r="N23" s="93">
-        <v>98.99</v>
+        <v>98.2</v>
       </c>
       <c r="O23" s="93">
-        <v>98.694999999999993</v>
+        <v>97.894999999999996</v>
       </c>
       <c r="P23" s="93">
-        <v>8175</v>
+        <v>8004</v>
       </c>
       <c r="Q23" s="93"/>
       <c r="R23" s="93"/>
@@ -8110,7 +8083,7 @@
       <c r="T23" s="93"/>
       <c r="U23" s="93"/>
       <c r="V23" s="92">
-        <v>46125.517858796295</v>
+        <v>46126.504861111112</v>
       </c>
       <c r="W23" s="1" t="s">
         <v>258</v>
@@ -8139,31 +8112,31 @@
         <v>59</v>
       </c>
       <c r="H24" s="93">
-        <v>1.1718999999999999</v>
+        <v>1.18215</v>
       </c>
       <c r="I24" s="93">
-        <v>1.1718500000000001</v>
+        <v>1.18215</v>
       </c>
       <c r="J24" s="93">
-        <v>1.1718999999999999</v>
+        <v>1.1821999999999999</v>
       </c>
       <c r="K24" s="93">
-        <v>1.171875</v>
+        <v>1.182175</v>
       </c>
       <c r="L24" s="93">
-        <v>1.1766000000000001</v>
+        <v>1.1799500000000001</v>
       </c>
       <c r="M24" s="93">
-        <v>1.171</v>
+        <v>1.1795500000000001</v>
       </c>
       <c r="N24" s="93">
-        <v>1.1734</v>
+        <v>1.1831</v>
       </c>
       <c r="O24" s="93">
-        <v>1.1698500000000001</v>
+        <v>1.1790499999999999</v>
       </c>
       <c r="P24" s="93">
-        <v>48343</v>
+        <v>51192</v>
       </c>
       <c r="Q24" s="93"/>
       <c r="R24" s="93"/>
@@ -8171,7 +8144,7 @@
       <c r="T24" s="93"/>
       <c r="U24" s="93"/>
       <c r="V24" s="92">
-        <v>46125.517858796295</v>
+        <v>46126.504861111112</v>
       </c>
       <c r="W24" s="1" t="s">
         <v>258</v>
@@ -8200,31 +8173,31 @@
         <v>59</v>
       </c>
       <c r="H25" s="93">
-        <v>1.3426</v>
+        <v>1.3541000000000001</v>
       </c>
       <c r="I25" s="93">
-        <v>1.3425</v>
+        <v>1.3541000000000001</v>
       </c>
       <c r="J25" s="93">
-        <v>1.3426</v>
+        <v>1.3542000000000001</v>
       </c>
       <c r="K25" s="93">
-        <v>1.3425500000000001</v>
+        <v>1.3541500000000002</v>
       </c>
       <c r="L25" s="93">
-        <v>1.3467</v>
+        <v>1.3506</v>
       </c>
       <c r="M25" s="93">
-        <v>1.34</v>
+        <v>1.3508</v>
       </c>
       <c r="N25" s="93">
-        <v>1.3432999999999999</v>
+        <v>1.355</v>
       </c>
       <c r="O25" s="93">
-        <v>1.3378000000000001</v>
+        <v>1.3503000000000001</v>
       </c>
       <c r="P25" s="93">
-        <v>19349</v>
+        <v>23606</v>
       </c>
       <c r="Q25" s="93"/>
       <c r="R25" s="93"/>
@@ -8232,7 +8205,7 @@
       <c r="T25" s="93"/>
       <c r="U25" s="93"/>
       <c r="V25" s="92">
-        <v>46125.517858796295</v>
+        <v>46126.504861111112</v>
       </c>
       <c r="W25" s="1" t="s">
         <v>258</v>
@@ -8261,31 +8234,31 @@
         <v>59</v>
       </c>
       <c r="H26" s="93">
-        <v>6.2940000000000001E-3</v>
+        <v>6.3235000000000001E-3</v>
       </c>
       <c r="I26" s="93">
-        <v>6.2934999999999996E-3</v>
+        <v>6.3229999999999996E-3</v>
       </c>
       <c r="J26" s="93">
-        <v>6.2940000000000001E-3</v>
+        <v>6.3235000000000001E-3</v>
       </c>
       <c r="K26" s="93">
-        <v>6.2937499999999999E-3</v>
+        <v>6.3232499999999999E-3</v>
       </c>
       <c r="L26" s="93">
-        <v>6.3119999999999999E-3</v>
+        <v>6.3099999999999996E-3</v>
       </c>
       <c r="M26" s="93">
-        <v>6.2950000000000002E-3</v>
+        <v>6.3064999999999996E-3</v>
       </c>
       <c r="N26" s="93">
-        <v>6.3004999999999997E-3</v>
+        <v>6.3284999999999999E-3</v>
       </c>
       <c r="O26" s="93">
-        <v>6.2874999999999997E-3</v>
+        <v>6.3055000000000003E-3</v>
       </c>
       <c r="P26" s="93">
-        <v>42395</v>
+        <v>43031</v>
       </c>
       <c r="Q26" s="93"/>
       <c r="R26" s="93"/>
@@ -8293,7 +8266,7 @@
       <c r="T26" s="93"/>
       <c r="U26" s="93"/>
       <c r="V26" s="92">
-        <v>46125.517858796295</v>
+        <v>46126.504861111112</v>
       </c>
       <c r="W26" s="1" t="s">
         <v>258</v>
@@ -8322,31 +8295,31 @@
         <v>59</v>
       </c>
       <c r="H27" s="93">
-        <v>0.72430000000000005</v>
+        <v>0.72865000000000002</v>
       </c>
       <c r="I27" s="93">
-        <v>0.72424999999999995</v>
+        <v>0.72865000000000002</v>
       </c>
       <c r="J27" s="93">
-        <v>0.72435000000000005</v>
+        <v>0.72870000000000001</v>
       </c>
       <c r="K27" s="93">
-        <v>0.72429999999999994</v>
+        <v>0.72867499999999996</v>
       </c>
       <c r="L27" s="93">
-        <v>0.72519999999999996</v>
+        <v>0.72709999999999997</v>
       </c>
       <c r="M27" s="93">
-        <v>0.72350000000000003</v>
+        <v>0.72704999999999997</v>
       </c>
       <c r="N27" s="93">
-        <v>0.72455000000000003</v>
+        <v>0.72875000000000001</v>
       </c>
       <c r="O27" s="93">
-        <v>0.72255000000000003</v>
+        <v>0.72704999999999997</v>
       </c>
       <c r="P27" s="93">
-        <v>14040</v>
+        <v>9757</v>
       </c>
       <c r="Q27" s="93"/>
       <c r="R27" s="93"/>
@@ -8354,7 +8327,7 @@
       <c r="T27" s="93"/>
       <c r="U27" s="93"/>
       <c r="V27" s="92">
-        <v>46125.517858796295</v>
+        <v>46126.504861111112</v>
       </c>
       <c r="W27" s="1" t="s">
         <v>258</v>
@@ -8383,31 +8356,31 @@
         <v>59</v>
       </c>
       <c r="H28" s="93">
-        <v>0.70409999999999995</v>
+        <v>0.71060000000000001</v>
       </c>
       <c r="I28" s="93">
-        <v>0.70394999999999996</v>
+        <v>0.71055000000000001</v>
       </c>
       <c r="J28" s="93">
-        <v>0.70399999999999996</v>
+        <v>0.71060000000000001</v>
       </c>
       <c r="K28" s="93">
-        <v>0.70397500000000002</v>
+        <v>0.71057499999999996</v>
       </c>
       <c r="L28" s="93">
-        <v>0.70725000000000005</v>
+        <v>0.70925000000000005</v>
       </c>
       <c r="M28" s="93">
-        <v>0.69899999999999995</v>
+        <v>0.70914999999999995</v>
       </c>
       <c r="N28" s="93">
-        <v>0.70515000000000005</v>
+        <v>0.71074999999999999</v>
       </c>
       <c r="O28" s="93">
-        <v>0.69869999999999999</v>
+        <v>0.70699999999999996</v>
       </c>
       <c r="P28" s="93">
-        <v>40029</v>
+        <v>38634</v>
       </c>
       <c r="Q28" s="93"/>
       <c r="R28" s="93"/>
@@ -8415,7 +8388,7 @@
       <c r="T28" s="93"/>
       <c r="U28" s="93"/>
       <c r="V28" s="92">
-        <v>46125.517858796295</v>
+        <v>46126.504861111112</v>
       </c>
       <c r="W28" s="1" t="s">
         <v>258</v>
@@ -8444,31 +8417,31 @@
         <v>59</v>
       </c>
       <c r="H29" s="93">
-        <v>113.53125</v>
+        <v>114.3125</v>
       </c>
       <c r="I29" s="93">
-        <v>113.5</v>
+        <v>114.3125</v>
       </c>
       <c r="J29" s="93">
-        <v>113.53125</v>
+        <v>114.34375</v>
       </c>
       <c r="K29" s="93">
-        <v>113.515625</v>
+        <v>114.328125</v>
       </c>
       <c r="L29" s="93">
-        <v>113.78125</v>
+        <v>114.0625</v>
       </c>
       <c r="M29" s="93">
-        <v>113.3125</v>
+        <v>114.125</v>
       </c>
       <c r="N29" s="93">
-        <v>113.65625</v>
+        <v>114.53125</v>
       </c>
       <c r="O29" s="93">
-        <v>113.09375</v>
+        <v>114.09375</v>
       </c>
       <c r="P29" s="93">
-        <v>53138</v>
+        <v>49589</v>
       </c>
       <c r="Q29" s="93"/>
       <c r="R29" s="93"/>
@@ -8476,7 +8449,7 @@
       <c r="T29" s="93"/>
       <c r="U29" s="93"/>
       <c r="V29" s="92">
-        <v>46125.517858796295</v>
+        <v>46126.504861111112</v>
       </c>
       <c r="W29" s="1" t="s">
         <v>258</v>
@@ -8505,31 +8478,31 @@
         <v>59</v>
       </c>
       <c r="H30" s="93">
-        <v>110.9375</v>
+        <v>111.34375</v>
       </c>
       <c r="I30" s="93">
-        <v>110.9375</v>
+        <v>111.328125</v>
       </c>
       <c r="J30" s="93">
-        <v>110.953125</v>
+        <v>111.34375</v>
       </c>
       <c r="K30" s="93">
-        <v>110.9453125</v>
+        <v>111.3359375</v>
       </c>
       <c r="L30" s="93">
-        <v>111.09375</v>
+        <v>111.234375</v>
       </c>
       <c r="M30" s="93">
-        <v>110.734375</v>
+        <v>111.25</v>
       </c>
       <c r="N30" s="93">
-        <v>111</v>
+        <v>111.453125</v>
       </c>
       <c r="O30" s="93">
-        <v>110.703125</v>
+        <v>111.234375</v>
       </c>
       <c r="P30" s="93">
-        <v>287022</v>
+        <v>270108</v>
       </c>
       <c r="Q30" s="93"/>
       <c r="R30" s="93"/>
@@ -8537,7 +8510,7 @@
       <c r="T30" s="93"/>
       <c r="U30" s="93"/>
       <c r="V30" s="92">
-        <v>46125.517858796295</v>
+        <v>46126.504861111112</v>
       </c>
       <c r="W30" s="1" t="s">
         <v>258</v>
@@ -8566,31 +8539,31 @@
         <v>56</v>
       </c>
       <c r="H31" s="93">
-        <v>124.91</v>
+        <v>125.09</v>
       </c>
       <c r="I31" s="93">
-        <v>124.91</v>
+        <v>125.09</v>
       </c>
       <c r="J31" s="93">
-        <v>124.92</v>
+        <v>125.1</v>
       </c>
       <c r="K31" s="93">
-        <v>124.91499999999999</v>
+        <v>125.095</v>
       </c>
       <c r="L31" s="93">
-        <v>125.2</v>
+        <v>124.75</v>
       </c>
       <c r="M31" s="93">
-        <v>124.8</v>
+        <v>125.1</v>
       </c>
       <c r="N31" s="93">
-        <v>125.13</v>
+        <v>125.25</v>
       </c>
       <c r="O31" s="93">
-        <v>124.68</v>
+        <v>125.03</v>
       </c>
       <c r="P31" s="93">
-        <v>294615</v>
+        <v>331548</v>
       </c>
       <c r="Q31" s="93"/>
       <c r="R31" s="93"/>
@@ -8598,7 +8571,7 @@
       <c r="T31" s="93"/>
       <c r="U31" s="93"/>
       <c r="V31" s="92">
-        <v>46125.517858796295</v>
+        <v>46126.504861111112</v>
       </c>
       <c r="W31" s="1" t="s">
         <v>258</v>
@@ -8627,31 +8600,31 @@
         <v>56</v>
       </c>
       <c r="H32" s="93">
-        <v>107.56</v>
+        <v>107.72</v>
       </c>
       <c r="I32" s="93">
-        <v>107.56</v>
+        <v>107.72</v>
       </c>
       <c r="J32" s="93">
-        <v>107.58</v>
+        <v>107.74</v>
       </c>
       <c r="K32" s="93">
-        <v>107.57</v>
+        <v>107.72999999999999</v>
       </c>
       <c r="L32" s="93">
-        <v>108.06</v>
+        <v>107.26</v>
       </c>
       <c r="M32" s="93">
-        <v>107.66</v>
+        <v>107.82</v>
       </c>
       <c r="N32" s="93">
-        <v>108</v>
+        <v>108.16</v>
       </c>
       <c r="O32" s="93">
-        <v>107.06</v>
+        <v>107.62</v>
       </c>
       <c r="P32" s="93">
-        <v>41621</v>
+        <v>46968</v>
       </c>
       <c r="Q32" s="93"/>
       <c r="R32" s="93"/>
@@ -8659,7 +8632,7 @@
       <c r="T32" s="93"/>
       <c r="U32" s="93"/>
       <c r="V32" s="92">
-        <v>46125.517858796295</v>
+        <v>46126.504861111112</v>
       </c>
       <c r="W32" s="1" t="s">
         <v>258</v>
@@ -8688,31 +8661,31 @@
         <v>56</v>
       </c>
       <c r="H33" s="93">
-        <v>116.81</v>
+        <v>117.16</v>
       </c>
       <c r="I33" s="93">
-        <v>116.8</v>
+        <v>117.15</v>
       </c>
       <c r="J33" s="93">
-        <v>116.81</v>
+        <v>117.17</v>
       </c>
       <c r="K33" s="93">
-        <v>116.80500000000001</v>
+        <v>117.16</v>
       </c>
       <c r="L33" s="93">
-        <v>117.29</v>
+        <v>116.7</v>
       </c>
       <c r="M33" s="93">
-        <v>116.66</v>
+        <v>117.21</v>
       </c>
       <c r="N33" s="93">
-        <v>117.15</v>
+        <v>117.43</v>
       </c>
       <c r="O33" s="93">
-        <v>116.6</v>
+        <v>117.09</v>
       </c>
       <c r="P33" s="93">
-        <v>96206</v>
+        <v>103194</v>
       </c>
       <c r="Q33" s="93"/>
       <c r="R33" s="93"/>
@@ -8720,7 +8693,7 @@
       <c r="T33" s="93"/>
       <c r="U33" s="93"/>
       <c r="V33" s="92">
-        <v>46125.517858796295</v>
+        <v>46126.504861111112</v>
       </c>
       <c r="W33" s="1" t="s">
         <v>258</v>
@@ -8749,29 +8722,29 @@
         <v>59</v>
       </c>
       <c r="H34" s="93">
-        <v>70759</v>
+        <v>74524.5</v>
       </c>
       <c r="I34" s="93">
-        <v>70758.75</v>
+        <v>74524.5</v>
       </c>
       <c r="J34" s="93">
-        <v>70759</v>
+        <v>74524.75</v>
       </c>
       <c r="K34" s="93">
-        <v>70758.875</v>
+        <v>74524.625</v>
       </c>
       <c r="L34" s="93">
-        <v>71121.25</v>
+        <v>73382</v>
       </c>
       <c r="M34" s="93"/>
       <c r="N34" s="93">
-        <v>73600</v>
+        <v>75425.25</v>
       </c>
       <c r="O34" s="93">
-        <v>70523</v>
+        <v>72410.75</v>
       </c>
       <c r="P34" s="93">
-        <v>58.899580450000002</v>
+        <v>116.62393998</v>
       </c>
       <c r="Q34" s="93"/>
       <c r="R34" s="93"/>
@@ -8779,7 +8752,7 @@
       <c r="T34" s="93"/>
       <c r="U34" s="93"/>
       <c r="V34" s="92">
-        <v>46125.517858796295</v>
+        <v>46126.504861111112</v>
       </c>
       <c r="W34" s="1" t="s">
         <v>258</v>
@@ -8808,29 +8781,29 @@
         <v>59</v>
       </c>
       <c r="H35" s="93">
-        <v>2184.1</v>
+        <v>2386.4499999999998</v>
       </c>
       <c r="I35" s="93">
-        <v>2183.9</v>
+        <v>2386.4</v>
       </c>
       <c r="J35" s="93">
-        <v>2183.9499999999998</v>
+        <v>2386.4499999999998</v>
       </c>
       <c r="K35" s="93">
-        <v>2183.9250000000002</v>
+        <v>2386.4250000000002</v>
       </c>
       <c r="L35" s="93">
-        <v>2198.8000000000002</v>
+        <v>2264.0500000000002</v>
       </c>
       <c r="M35" s="93"/>
       <c r="N35" s="93">
-        <v>2316.9</v>
+        <v>2396</v>
       </c>
       <c r="O35" s="93">
-        <v>2178.1</v>
+        <v>2220.6999999999998</v>
       </c>
       <c r="P35" s="93">
-        <v>1255.0010072499999</v>
+        <v>2064.2883861099999</v>
       </c>
       <c r="Q35" s="93"/>
       <c r="R35" s="93"/>
@@ -8838,7 +8811,7 @@
       <c r="T35" s="93"/>
       <c r="U35" s="93"/>
       <c r="V35" s="92">
-        <v>46125.517858796295</v>
+        <v>46126.504861111112</v>
       </c>
       <c r="W35" s="1" t="s">
         <v>258</v>
@@ -8867,47 +8840,47 @@
         <v>59</v>
       </c>
       <c r="H36" s="93">
-        <v>1.1000000000000001</v>
+        <v>1.1100000000000001</v>
       </c>
       <c r="I36" s="93">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="J36" s="93">
-        <v>1.0900000000000001</v>
+        <v>1.08</v>
       </c>
       <c r="K36" s="93">
         <v>1.06</v>
       </c>
       <c r="L36" s="93">
-        <v>1.75</v>
+        <v>1.1599999999999999</v>
       </c>
       <c r="M36" s="93"/>
       <c r="N36" s="93">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="O36" s="93">
-        <v>1.1000000000000001</v>
+        <v>1.0900000000000001</v>
       </c>
       <c r="P36" s="93">
-        <v>77</v>
+        <v>247</v>
       </c>
       <c r="Q36" s="93">
-        <v>0.73076881821871087</v>
+        <v>0.65071262857332568</v>
       </c>
       <c r="R36" s="93">
-        <v>-0.10167648458265198</v>
+        <v>-0.1184779896216942</v>
       </c>
       <c r="S36" s="93">
-        <v>8.6463708577047532E-3</v>
+        <v>1.1499937873466953E-2</v>
       </c>
       <c r="T36" s="93">
-        <v>5.377393454248991E-2</v>
+        <v>5.1829289229028186E-2</v>
       </c>
       <c r="U36" s="93">
-        <v>-6.3108329741919711E-2</v>
+        <v>-5.5921335989600918E-2</v>
       </c>
       <c r="V36" s="92">
-        <v>46125.517858796295</v>
+        <v>46126.504861111112</v>
       </c>
       <c r="W36" s="1" t="s">
         <v>258</v>
@@ -8936,47 +8909,47 @@
         <v>59</v>
       </c>
       <c r="H37" s="93">
+        <v>0.08</v>
+      </c>
+      <c r="I37" s="93">
+        <v>0.08</v>
+      </c>
+      <c r="J37" s="93">
         <v>0.12</v>
       </c>
-      <c r="I37" s="93">
-        <v>0.13</v>
-      </c>
-      <c r="J37" s="93">
-        <v>0.15</v>
-      </c>
       <c r="K37" s="93">
-        <v>0.14000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="L37" s="93">
-        <v>0.16</v>
+        <v>0.11</v>
       </c>
       <c r="M37" s="93"/>
       <c r="N37" s="93">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="O37" s="93">
-        <v>0.12</v>
+        <v>0.08</v>
       </c>
       <c r="P37" s="93">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="Q37" s="93">
-        <v>0.92975294633345229</v>
+        <v>0.8513149860951863</v>
       </c>
       <c r="R37" s="93">
-        <v>-1.4027513907694963E-2</v>
+        <v>-1.3105612197684545E-2</v>
       </c>
       <c r="S37" s="93">
-        <v>1.3650567684415512E-3</v>
+        <v>1.4916616787043501E-3</v>
       </c>
       <c r="T37" s="93">
-        <v>9.1233589298894413E-3</v>
+        <v>8.7953426945819174E-3</v>
       </c>
       <c r="U37" s="93">
-        <v>-1.3632410348751373E-2</v>
+        <v>-1.2430105641466668E-2</v>
       </c>
       <c r="V37" s="92">
-        <v>46125.517858796295</v>
+        <v>46126.504861111112</v>
       </c>
       <c r="W37" s="1" t="s">
         <v>258</v>
@@ -9005,47 +8978,43 @@
         <v>59</v>
       </c>
       <c r="H38" s="93">
-        <v>15.8</v>
+        <v>-1</v>
       </c>
       <c r="I38" s="93">
-        <v>13.5</v>
+        <v>13.9</v>
       </c>
       <c r="J38" s="93">
-        <v>15.6</v>
+        <v>15.1</v>
       </c>
       <c r="K38" s="93">
-        <v>14.55</v>
+        <v>14.5</v>
       </c>
       <c r="L38" s="93">
-        <v>17.600000000000001</v>
+        <v>14.8</v>
       </c>
       <c r="M38" s="93"/>
-      <c r="N38" s="93">
-        <v>15.8</v>
-      </c>
-      <c r="O38" s="93">
-        <v>15</v>
-      </c>
+      <c r="N38" s="93"/>
+      <c r="O38" s="93"/>
       <c r="P38" s="93">
-        <v>75</v>
+        <v>204</v>
       </c>
       <c r="Q38" s="93">
-        <v>0.29196264827533414</v>
+        <v>0.27068357977697705</v>
       </c>
       <c r="R38" s="93">
-        <v>7.3778320324366764E-2</v>
+        <v>7.7067933026295235E-2</v>
       </c>
       <c r="S38" s="93">
-        <v>2.936363472983426E-4</v>
+        <v>3.2653444437705595E-4</v>
       </c>
       <c r="T38" s="93">
-        <v>2.2579281448725865</v>
+        <v>2.2499243906596273</v>
       </c>
       <c r="U38" s="93">
-        <v>-0.76419064617829946</v>
+        <v>-0.72244380295831157</v>
       </c>
       <c r="V38" s="92">
-        <v>46125.517858796295</v>
+        <v>46126.504861111112</v>
       </c>
       <c r="W38" s="1" t="s">
         <v>258</v>
@@ -9077,16 +9046,16 @@
         <v>-1</v>
       </c>
       <c r="I39" s="93">
-        <v>92.8</v>
+        <v>107.2</v>
       </c>
       <c r="J39" s="93">
-        <v>96.1</v>
+        <v>109.1</v>
       </c>
       <c r="K39" s="93">
-        <v>94.449999999999989</v>
+        <v>108.15</v>
       </c>
       <c r="L39" s="93">
-        <v>112.4</v>
+        <v>100.8</v>
       </c>
       <c r="M39" s="93"/>
       <c r="N39" s="93"/>
@@ -9095,22 +9064,22 @@
         <v>0</v>
       </c>
       <c r="Q39" s="93">
-        <v>0.26140955767601448</v>
+        <v>0.24691358230929086</v>
       </c>
       <c r="R39" s="93">
-        <v>0.33984830920074593</v>
+        <v>0.39384066193424688</v>
       </c>
       <c r="S39" s="93">
-        <v>8.6106229737902224E-4</v>
+        <v>9.52843764058605E-4</v>
       </c>
       <c r="T39" s="93">
-        <v>5.8391669572779961</v>
+        <v>6.3015772685447331</v>
       </c>
       <c r="U39" s="93">
-        <v>-1.7637636608625371</v>
+        <v>-1.8391102586627426</v>
       </c>
       <c r="V39" s="92">
-        <v>46125.517858796295</v>
+        <v>46126.504861111112</v>
       </c>
       <c r="W39" s="1" t="s">
         <v>258</v>
@@ -9235,7 +9204,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C571DE7A-BF08-4200-BB11-61B452324713}">
-  <dimension ref="A1:C59"/>
+  <dimension ref="A1:C62"/>
   <sheetFormatPr defaultRowHeight="13.15" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="22" style="81" customWidth="1"/>
@@ -9890,6 +9859,39 @@
         <v>321</v>
       </c>
       <c r="C59" s="1" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A60" s="85">
+        <v>46126.503923611112</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A61" s="85">
+        <v>46126.503935185188</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A62" s="85">
+        <v>46126.503935185188</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="C62" s="1" t="s">
         <v>338</v>
       </c>
     </row>
@@ -10312,11 +10314,11 @@
       <c r="H6" s="67"/>
       <c r="I6" s="70">
         <f>Blotter!C$4-SUM(NAV!I$4:I5)</f>
-        <v>32676.060000000241</v>
+        <v>40219.810000000129</v>
       </c>
       <c r="J6" s="70">
         <f t="shared" ref="J6" si="9">E6-F6-G6-H6+I6</f>
-        <v>1061420.5106320111</v>
+        <v>1068964.2606320111</v>
       </c>
       <c r="K6" s="70">
         <f t="shared" ref="K6" si="10">K5+C6</f>
@@ -10324,19 +10326,19 @@
       </c>
       <c r="L6" s="71">
         <f t="shared" ref="L6" si="11">J6/K6</f>
-        <v>1061.4205106320112</v>
+        <v>1068.964260632011</v>
       </c>
       <c r="M6" s="72">
         <f t="shared" ref="M6" si="12">L6/$L$3-1</f>
-        <v>6.1420510632011149E-2</v>
+        <v>6.896426063201111E-2</v>
       </c>
       <c r="N6" s="73">
         <f t="shared" ref="N6" si="13">L6/L5-1</f>
-        <v>3.1763048617103662E-2</v>
+        <v>3.9096016484259977E-2</v>
       </c>
       <c r="O6" s="75">
         <f>STDEVP(N$4:N6)*SQRT(12)</f>
-        <v>4.9588259811965033E-2</v>
+        <v>5.7293360437513062E-2</v>
       </c>
     </row>
     <row r="7" spans="2:18" ht="14.25" x14ac:dyDescent="0.4">
@@ -10716,7 +10718,7 @@
       </c>
       <c r="D4" s="6">
         <f t="array" ref="D4">SUM((Blotter!C$19:C$1013=C4)*(Blotter!N$19:N$1013)*1)</f>
-        <v>10612.690632011014</v>
+        <v>13875.190632011014</v>
       </c>
       <c r="E4" s="6">
         <f t="array" ref="E4">SUM((Blotter!B$19:C$1013=C4)*(Blotter!R$19:R$1013)*1)</f>
@@ -10732,20 +10734,20 @@
       </c>
       <c r="H4" s="16">
         <f t="shared" ref="H4:H9" si="4">J3+D4</f>
-        <v>1010612.690632011</v>
+        <v>1013875.190632011</v>
       </c>
       <c r="I4" s="16"/>
       <c r="J4" s="16">
         <f t="shared" si="0"/>
-        <v>1010612.690632011</v>
+        <v>1013875.190632011</v>
       </c>
       <c r="K4" s="3">
         <f t="shared" ref="K4:K9" si="5">H4/J3-1</f>
-        <v>1.0612690632010979E-2</v>
+        <v>1.3875190632011147E-2</v>
       </c>
       <c r="L4" s="3">
         <f t="shared" ref="L4:L9" si="6">(1+K4)*(1+L3)-1</f>
-        <v>1.0612690632010979E-2</v>
+        <v>1.3875190632011147E-2</v>
       </c>
       <c r="M4" s="6">
         <f>O3-IF(G4="O",E4,-D4)</f>
@@ -10800,7 +10802,7 @@
       </c>
       <c r="D5" s="6">
         <f t="array" ref="D5">SUM((Blotter!C$19:C$1013=C5)*(Blotter!N$19:N$1013)*1)</f>
-        <v>321.08999999999651</v>
+        <v>971.09</v>
       </c>
       <c r="E5" s="6">
         <f t="array" ref="E5">SUM((Blotter!B$19:C$1013=C5)*(Blotter!R$19:R$1013)*1)</f>
@@ -10808,32 +10810,32 @@
       </c>
       <c r="F5" s="30">
         <f t="shared" ref="F5" si="12">IF(ISNUMBER(D5/E5),D5/E5,0)</f>
-        <v>3.567666666666628E-2</v>
+        <v>0.10789888888888889</v>
       </c>
       <c r="G5" s="36" t="str">
         <f t="array" ref="G5">IF(SUM((Blotter!C$19:C$1013=PLB!C5)*(Blotter!M$19:M$1013))=0,"C","O")</f>
-        <v>O</v>
+        <v>C</v>
       </c>
       <c r="H5" s="16">
         <f t="shared" si="4"/>
-        <v>1010933.780632011</v>
+        <v>1014846.280632011</v>
       </c>
       <c r="I5" s="16"/>
       <c r="J5" s="16">
         <f t="shared" si="0"/>
-        <v>1010933.780632011</v>
+        <v>1014846.280632011</v>
       </c>
       <c r="K5" s="3">
         <f t="shared" si="5"/>
-        <v>3.1771815550740712E-4</v>
+        <v>9.5780033772663309E-4</v>
       </c>
       <c r="L5" s="3">
         <f t="shared" si="6"/>
-        <v>1.0933780632010892E-2</v>
+        <v>1.48462806320111E-2</v>
       </c>
       <c r="M5" s="6">
         <f t="shared" ref="M5:M8" si="13">O4-IF(G5="O",E5,-D5)</f>
-        <v>991000</v>
+        <v>1000971.09</v>
       </c>
       <c r="N5" s="16">
         <f t="shared" si="7"/>
@@ -10841,15 +10843,15 @@
       </c>
       <c r="O5" s="6">
         <f t="shared" si="1"/>
-        <v>991000</v>
+        <v>1000971.09</v>
       </c>
       <c r="P5" s="3">
         <f t="shared" si="8"/>
-        <v>-9.000000000000008E-3</v>
+        <v>9.7108999999995227E-4</v>
       </c>
       <c r="Q5" s="3">
         <f t="shared" si="9"/>
-        <v>-9.000000000000008E-3</v>
+        <v>9.7108999999995227E-4</v>
       </c>
       <c r="R5" s="3">
         <f t="shared" si="10"/>
@@ -10884,7 +10886,7 @@
       </c>
       <c r="D6" s="6">
         <f t="array" ref="D6">SUM((Blotter!C$19:C$1013=C6)*(Blotter!N$19:N$1013)*1)</f>
-        <v>-4814.220000000003</v>
+        <v>-6434.220000000003</v>
       </c>
       <c r="E6" s="6">
         <f t="array" ref="E6">SUM((Blotter!B$19:C$1013=C6)*(Blotter!R$19:R$1013)*1)</f>
@@ -10892,7 +10894,7 @@
       </c>
       <c r="F6" s="30">
         <f t="shared" ref="F6" si="16">IF(ISNUMBER(D6/E6),D6/E6,0)</f>
-        <v>-0.50230691699481034</v>
+        <v>-0.67133475650600682</v>
       </c>
       <c r="G6" s="36" t="str">
         <f t="array" ref="G6">IF(SUM((Blotter!C$19:C$1013=PLB!C6)*(Blotter!M$19:M$1013))=0,"C","O")</f>
@@ -10900,24 +10902,24 @@
       </c>
       <c r="H6" s="16">
         <f t="shared" si="4"/>
-        <v>1006119.560632011</v>
+        <v>1008412.060632011</v>
       </c>
       <c r="I6" s="16"/>
       <c r="J6" s="16">
         <f t="shared" si="0"/>
-        <v>1006119.560632011</v>
+        <v>1008412.060632011</v>
       </c>
       <c r="K6" s="3">
         <f t="shared" si="5"/>
-        <v>-4.7621516782140327E-3</v>
+        <v>-6.340093197161778E-3</v>
       </c>
       <c r="L6" s="3">
         <f t="shared" si="6"/>
-        <v>6.1195606320108009E-3</v>
+        <v>8.4120606320110536E-3</v>
       </c>
       <c r="M6" s="6">
         <f t="shared" si="13"/>
-        <v>981415.78</v>
+        <v>991386.87</v>
       </c>
       <c r="N6" s="16">
         <f t="shared" si="7"/>
@@ -10925,15 +10927,15 @@
       </c>
       <c r="O6" s="6">
         <f t="shared" si="1"/>
-        <v>981415.78</v>
+        <v>991386.87</v>
       </c>
       <c r="P6" s="3">
         <f t="shared" si="8"/>
-        <v>-9.6712613521694468E-3</v>
+        <v>-9.5749218891026944E-3</v>
       </c>
       <c r="Q6" s="3">
         <f t="shared" si="9"/>
-        <v>-1.8584219999999929E-2</v>
+        <v>-8.6131300000000799E-3</v>
       </c>
       <c r="R6" s="3">
         <f t="shared" si="10"/>
@@ -10968,7 +10970,7 @@
       </c>
       <c r="D7" s="6">
         <f t="array" ref="D7">SUM((Blotter!C$19:C$1013=C7)*(Blotter!N$19:N$1013)*1)</f>
-        <v>10397.529999999999</v>
+        <v>13010.029999999999</v>
       </c>
       <c r="E7" s="6">
         <f t="array" ref="E7">SUM((Blotter!B$19:C$1013=C7)*(Blotter!R$19:R$1013)*1)</f>
@@ -10976,7 +10978,7 @@
       </c>
       <c r="F7" s="30">
         <f t="shared" ref="F7" si="19">IF(ISNUMBER(D7/E7),D7/E7,0)</f>
-        <v>1.445607229753215</v>
+        <v>1.8088328119568995</v>
       </c>
       <c r="G7" s="36" t="str">
         <f t="array" ref="G7">IF(SUM((Blotter!C$19:C$1013=PLB!C7)*(Blotter!M$19:M$1013))=0,"C","O")</f>
@@ -10984,24 +10986,24 @@
       </c>
       <c r="H7" s="16">
         <f t="shared" si="4"/>
-        <v>1016517.0906320111</v>
+        <v>1021422.0906320111</v>
       </c>
       <c r="I7" s="16"/>
       <c r="J7" s="16">
         <f t="shared" si="0"/>
-        <v>1016517.0906320111</v>
+        <v>1021422.0906320111</v>
       </c>
       <c r="K7" s="3">
         <f t="shared" si="5"/>
-        <v>1.033428869374986E-2</v>
+        <v>1.2901501784742697E-2</v>
       </c>
       <c r="L7" s="3">
         <f t="shared" si="6"/>
-        <v>1.6517090632010678E-2</v>
+        <v>2.1422090632011059E-2</v>
       </c>
       <c r="M7" s="6">
         <f t="shared" si="13"/>
-        <v>974223.28</v>
+        <v>984194.37</v>
       </c>
       <c r="N7" s="16">
         <f t="shared" si="7"/>
@@ -11009,15 +11011,15 @@
       </c>
       <c r="O7" s="6">
         <f t="shared" si="1"/>
-        <v>974223.28</v>
+        <v>984194.37</v>
       </c>
       <c r="P7" s="3">
         <f t="shared" si="8"/>
-        <v>-7.3286981385198846E-3</v>
+        <v>-7.254988156137232E-3</v>
       </c>
       <c r="Q7" s="3">
         <f t="shared" si="9"/>
-        <v>-2.5776719999999975E-2</v>
+        <v>-1.5805630000000015E-2</v>
       </c>
       <c r="R7" s="3">
         <f t="shared" si="10"/>
@@ -11052,15 +11054,15 @@
       </c>
       <c r="D8" s="6">
         <f t="array" ref="D8">SUM((Blotter!C$19:C$1013=C8)*(Blotter!N$19:N$1013)*1)</f>
-        <v>38610.739999999991</v>
+        <v>40035.739999999991</v>
       </c>
       <c r="E8" s="6">
         <f t="array" ref="E8">SUM((Blotter!B$19:C$1013=C8)*(Blotter!R$19:R$1013)*1)</f>
-        <v>-8745</v>
+        <v>-26235</v>
       </c>
       <c r="F8" s="30">
         <f t="shared" ref="F8" si="22">IF(ISNUMBER(D8/E8),D8/E8,0)</f>
-        <v>-4.4151789594053739</v>
+        <v>-1.5260430722317511</v>
       </c>
       <c r="G8" s="36" t="str">
         <f t="array" ref="G8">IF(SUM((Blotter!C$19:C$1013=PLB!C8)*(Blotter!M$19:M$1013))=0,"C","O")</f>
@@ -11068,24 +11070,24 @@
       </c>
       <c r="H8" s="16">
         <f t="shared" si="4"/>
-        <v>1055127.8306320109</v>
+        <v>1061457.8306320109</v>
       </c>
       <c r="I8" s="16"/>
       <c r="J8" s="16">
         <f t="shared" si="0"/>
-        <v>1055127.8306320109</v>
+        <v>1061457.8306320109</v>
       </c>
       <c r="K8" s="3">
         <f t="shared" si="5"/>
-        <v>3.7983365312622475E-2</v>
+        <v>3.9196078063308271E-2</v>
       </c>
       <c r="L8" s="3">
         <f t="shared" si="6"/>
-        <v>5.5127830632010433E-2</v>
+        <v>6.1457830632010824E-2</v>
       </c>
       <c r="M8" s="6">
         <f t="shared" si="13"/>
-        <v>982968.28</v>
+        <v>1010429.37</v>
       </c>
       <c r="N8" s="16">
         <f t="shared" si="7"/>
@@ -11093,15 +11095,15 @@
       </c>
       <c r="O8" s="6">
         <f t="shared" si="1"/>
-        <v>982968.28</v>
+        <v>1010429.37</v>
       </c>
       <c r="P8" s="3">
         <f t="shared" si="8"/>
-        <v>8.9763816771037952E-3</v>
+        <v>2.6656319929974748E-2</v>
       </c>
       <c r="Q8" s="3">
         <f t="shared" si="9"/>
-        <v>-1.7031719999999972E-2</v>
+        <v>1.0429369999999993E-2</v>
       </c>
       <c r="R8" s="3">
         <f t="shared" si="10"/>
@@ -11136,7 +11138,7 @@
       </c>
       <c r="D9" s="6">
         <f t="array" ref="D9">SUM((Blotter!C$19:C$1013=C9)*(Blotter!N$19:N$1013)*1)</f>
-        <v>-425.04000000000065</v>
+        <v>-1305.0400000000004</v>
       </c>
       <c r="E9" s="6">
         <f t="array" ref="E9">SUM((Blotter!B$19:C$1013=C9)*(Blotter!R$19:R$1013)*1)</f>
@@ -11144,7 +11146,7 @@
       </c>
       <c r="F9" s="30">
         <f t="shared" ref="F9" si="25">IF(ISNUMBER(D9/E9),D9/E9,0)</f>
-        <v>-4.2907328891580929E-2</v>
+        <v>-0.13174237835655161</v>
       </c>
       <c r="G9" s="36" t="str">
         <f t="array" ref="G9">IF(SUM((Blotter!C$19:C$1013=PLB!C9)*(Blotter!M$19:M$1013))=0,"C","O")</f>
@@ -11152,24 +11154,24 @@
       </c>
       <c r="H9" s="16">
         <f t="shared" si="4"/>
-        <v>1054702.7906320109</v>
+        <v>1060152.7906320109</v>
       </c>
       <c r="I9" s="16"/>
       <c r="J9" s="16">
         <f t="shared" ref="J9" si="26">H9+I9</f>
-        <v>1054702.7906320109</v>
+        <v>1060152.7906320109</v>
       </c>
       <c r="K9" s="3">
         <f t="shared" si="5"/>
-        <v>-4.0283270676833016E-4</v>
+        <v>-1.2294788943456592E-3</v>
       </c>
       <c r="L9" s="3">
         <f t="shared" si="6"/>
-        <v>5.4702790632010334E-2</v>
+        <v>6.0152790632010733E-2</v>
       </c>
       <c r="M9" s="6">
         <f t="shared" ref="M9" si="27">O8-IF(G9="O",E9,-D9)</f>
-        <v>973062.28</v>
+        <v>1000523.37</v>
       </c>
       <c r="N9" s="16">
         <f t="shared" si="7"/>
@@ -11177,15 +11179,15 @@
       </c>
       <c r="O9" s="6">
         <f t="shared" ref="O9" si="28">M9+N9</f>
-        <v>973062.28</v>
+        <v>1000523.37</v>
       </c>
       <c r="P9" s="3">
         <f t="shared" si="8"/>
-        <v>-1.0077639534817995E-2</v>
+        <v>-9.8037530322381272E-3</v>
       </c>
       <c r="Q9" s="3">
         <f t="shared" si="9"/>
-        <v>-2.6937720000000054E-2</v>
+        <v>5.2337000000002298E-4</v>
       </c>
       <c r="R9" s="3">
         <f t="shared" si="10"/>
@@ -11220,7 +11222,7 @@
       </c>
       <c r="D10" s="6">
         <f t="array" ref="D10">SUM((Blotter!C$19:C$1013=C10)*(Blotter!N$19:N$1013)*1)</f>
-        <v>2768.7500000002328</v>
+        <v>4862.5000000001164</v>
       </c>
       <c r="E10" s="6">
         <f t="array" ref="E10">SUM((Blotter!B$19:C$1013=C10)*(Blotter!R$19:R$1013)*1)</f>
@@ -11228,7 +11230,7 @@
       </c>
       <c r="F10" s="30">
         <f t="shared" ref="F10" si="31">IF(ISNUMBER(D10/E10),D10/E10,0)</f>
-        <v>0.31252204585540549</v>
+        <v>0.54885361552029532</v>
       </c>
       <c r="G10" s="36" t="str">
         <f t="array" ref="G10">IF(SUM((Blotter!C$19:C$1013=PLB!C10)*(Blotter!M$19:M$1013))=0,"C","O")</f>
@@ -11236,24 +11238,24 @@
       </c>
       <c r="H10" s="16">
         <f t="shared" ref="H10" si="32">J9+D10</f>
-        <v>1057471.5406320111</v>
+        <v>1065015.2906320109</v>
       </c>
       <c r="I10" s="16"/>
       <c r="J10" s="16">
         <f t="shared" ref="J10" si="33">H10+I10</f>
-        <v>1057471.5406320111</v>
+        <v>1065015.2906320109</v>
       </c>
       <c r="K10" s="3">
         <f t="shared" ref="K10" si="34">H10/J9-1</f>
-        <v>2.6251471263682991E-3</v>
+        <v>4.5866030283250314E-3</v>
       </c>
       <c r="L10" s="3">
         <f t="shared" ref="L10" si="35">(1+K10)*(1+L9)-1</f>
-        <v>5.7471540632010543E-2</v>
+        <v>6.5015290632010725E-2</v>
       </c>
       <c r="M10" s="6">
         <f t="shared" ref="M10" si="36">O9-IF(G10="O",E10,-D10)</f>
-        <v>964202.90500000003</v>
+        <v>991663.995</v>
       </c>
       <c r="N10" s="16">
         <f t="shared" ref="N10" si="37">I10</f>
@@ -11261,15 +11263,15 @@
       </c>
       <c r="O10" s="6">
         <f t="shared" ref="O10" si="38">M10+N10</f>
-        <v>964202.90500000003</v>
+        <v>991663.995</v>
       </c>
       <c r="P10" s="3">
         <f t="shared" ref="P10" si="39">M10/O9-1</f>
-        <v>-9.1046330559643174E-3</v>
+        <v>-8.8547406943627616E-3</v>
       </c>
       <c r="Q10" s="3">
         <f t="shared" ref="Q10" si="40">(1+P10)*(1+Q9)-1</f>
-        <v>-3.5797095000000057E-2</v>
+        <v>-8.3360049999999797E-3</v>
       </c>
       <c r="R10" s="3">
         <f t="shared" si="10"/>
@@ -18173,17 +18175,131 @@
       <c r="X69" s="42"/>
     </row>
     <row r="70" spans="1:24" x14ac:dyDescent="0.4">
-      <c r="T70" s="43"/>
-      <c r="U70" s="42"/>
-      <c r="V70" s="42"/>
-      <c r="W70" s="42"/>
+      <c r="B70" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="E70" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="F70" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="G70" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H70" s="1">
+        <v>10</v>
+      </c>
+      <c r="J70" s="44">
+        <v>46156</v>
+      </c>
+      <c r="L70" s="44">
+        <v>46090</v>
+      </c>
+      <c r="M70" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="N70" s="1">
+        <v>-2</v>
+      </c>
+      <c r="O70" s="1">
+        <v>3268</v>
+      </c>
+      <c r="P70" s="1">
+        <v>64700</v>
+      </c>
+      <c r="Q70" s="1">
+        <v>-5.94</v>
+      </c>
+      <c r="R70" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="T70" s="43">
+        <f>IF(ISNUMBER(VLOOKUP(U70,Blotter!B:C,2,0)),VLOOKUP(U70,Blotter!B:C,2,0),"")</f>
+        <v>2</v>
+      </c>
+      <c r="U70" s="42" t="str">
+        <f t="shared" ref="U70:U71" si="44">D70</f>
+        <v>CCK6</v>
+      </c>
+      <c r="V70" s="42">
+        <f t="shared" ref="V70:V71" si="45">N70</f>
+        <v>-2</v>
+      </c>
+      <c r="W70" s="42">
+        <f t="shared" ref="W70:W71" si="46">O70</f>
+        <v>3268</v>
+      </c>
       <c r="X70" s="42"/>
     </row>
     <row r="71" spans="1:24" x14ac:dyDescent="0.4">
-      <c r="T71" s="43"/>
-      <c r="U71" s="42"/>
-      <c r="V71" s="42"/>
-      <c r="W71" s="42"/>
+      <c r="B71" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="F71" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="G71" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H71" s="1">
+        <v>10</v>
+      </c>
+      <c r="J71" s="44">
+        <v>46156</v>
+      </c>
+      <c r="L71" s="44">
+        <v>46090</v>
+      </c>
+      <c r="M71" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="N71" s="1">
+        <v>-1</v>
+      </c>
+      <c r="O71" s="1">
+        <v>3267</v>
+      </c>
+      <c r="P71" s="1">
+        <v>64700</v>
+      </c>
+      <c r="Q71" s="1">
+        <v>-5.94</v>
+      </c>
+      <c r="R71" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="T71" s="43">
+        <f>IF(ISNUMBER(VLOOKUP(U71,Blotter!B:C,2,0)),VLOOKUP(U71,Blotter!B:C,2,0),"")</f>
+        <v>2</v>
+      </c>
+      <c r="U71" s="42" t="str">
+        <f t="shared" si="44"/>
+        <v>CCK6</v>
+      </c>
+      <c r="V71" s="42">
+        <f t="shared" si="45"/>
+        <v>-1</v>
+      </c>
+      <c r="W71" s="42">
+        <f t="shared" si="46"/>
+        <v>3267</v>
+      </c>
       <c r="X71" s="42"/>
     </row>
     <row r="72" spans="1:24" x14ac:dyDescent="0.4">

--- a/1XW_TradeBlotter_Web.xlsx
+++ b/1XW_TradeBlotter_Web.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0a601c1c2ba3d9f4/Trading/The Strategy Project/1XW Website/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="564" documentId="13_ncr:1_{6F5069F1-F0E7-4440-AA6D-4AFA11BBED1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2987E0E6-EFAA-4D30-942A-963410FD0CC0}"/>
+  <xr:revisionPtr revIDLastSave="587" documentId="13_ncr:1_{6F5069F1-F0E7-4440-AA6D-4AFA11BBED1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{51E59DA7-6D39-42AA-AEDE-610B11AB486B}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="22695" windowHeight="14476" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -99,7 +99,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1558" uniqueCount="350">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1469" uniqueCount="346">
   <si>
     <t>WEEK</t>
   </si>
@@ -1077,6 +1077,69 @@
     <t>HG 27MAY26</t>
   </si>
   <si>
+    <t>NKD</t>
+  </si>
+  <si>
+    <t>NKDM6</t>
+  </si>
+  <si>
+    <t>NKD 12JUN26</t>
+  </si>
+  <si>
+    <t>Long NKD Futures</t>
+  </si>
+  <si>
+    <t>OGM6 C5500</t>
+  </si>
+  <si>
+    <t>OGM6 C4930</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>OG</t>
+  </si>
+  <si>
+    <t>Long GC Call Spread</t>
+  </si>
+  <si>
+    <t>GC JUN26 4930 C</t>
+  </si>
+  <si>
+    <t>GC JUN26 5500 C</t>
+  </si>
+  <si>
+    <t>RISK</t>
+  </si>
+  <si>
+    <t>Close</t>
+  </si>
+  <si>
+    <t>End of deflation era / pro-growth government policies / attractive valuations</t>
+  </si>
+  <si>
+    <t>Weekly retrace to previous support area and weekly up</t>
+  </si>
+  <si>
+    <t>Weekly hammer after 50% retrace and weekly up</t>
+  </si>
+  <si>
+    <t>Central banks buying spree / geopolitical or dollar shock hedge</t>
+  </si>
+  <si>
+    <t>Rate differential expectations, BCE 2-3 hikes before year-end</t>
+  </si>
+  <si>
+    <t>Weekly doji + weekly up / potential continuation to new highs</t>
+  </si>
+  <si>
+    <t>Long 6E Futures</t>
+  </si>
+  <si>
+    <t>EUR 15JUN26</t>
+  </si>
+  <si>
     <t>INFO</t>
   </si>
   <si>
@@ -1086,82 +1149,7 @@
     <t>Connected to TWS.</t>
   </si>
   <si>
-    <t>Loaded 36 contracts from Symbols sheet.</t>
-  </si>
-  <si>
-    <t>NKD</t>
-  </si>
-  <si>
-    <t>NKDM6</t>
-  </si>
-  <si>
-    <t>NKD 12JUN26</t>
-  </si>
-  <si>
-    <t>ERROR</t>
-  </si>
-  <si>
-    <t>Loop error: (-2147352567, 'Exception occurred.', (0, None, None, None, 0, -2146777998), None). Reconnecting in 2s.</t>
-  </si>
-  <si>
-    <t>Reconnected to TWS.</t>
-  </si>
-  <si>
-    <t>Long NKD Futures</t>
-  </si>
-  <si>
-    <t>Loop error: (-2147352567, 'Exception occurred.', (0, None, None, None, 0, -2146827284), None). Reconnecting in 2s.</t>
-  </si>
-  <si>
-    <t>OGM6 C5500</t>
-  </si>
-  <si>
-    <t>OGM6 C4930</t>
-  </si>
-  <si>
-    <t>C</t>
-  </si>
-  <si>
-    <t>OG</t>
-  </si>
-  <si>
-    <t>Long GC Call Spread</t>
-  </si>
-  <si>
     <t>Loaded 38 contracts from Symbols sheet.</t>
-  </si>
-  <si>
-    <t>GC JUN26 4930 C</t>
-  </si>
-  <si>
-    <t>GC JUN26 5500 C</t>
-  </si>
-  <si>
-    <t>RISK</t>
-  </si>
-  <si>
-    <t>Close</t>
-  </si>
-  <si>
-    <t>End of deflation era / pro-growth government policies / attractive valuations</t>
-  </si>
-  <si>
-    <t>Weekly retrace to previous support area and weekly up</t>
-  </si>
-  <si>
-    <t>Weekly hammer after 50% retrace and weekly up</t>
-  </si>
-  <si>
-    <t>Central banks buying spree / geopolitical or dollar shock hedge</t>
-  </si>
-  <si>
-    <t>Rate differential expectations, BCE 2-3 hikes before year-end</t>
-  </si>
-  <si>
-    <t>Weekly doji + weekly up / potential continuation to new highs</t>
-  </si>
-  <si>
-    <t>Long 6E Futures</t>
   </si>
 </sst>
 </file>
@@ -2328,7 +2316,7 @@
                   <c:v>2.8744450632010921E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3.9096016484259977E-2</c:v>
+                  <c:v>5.5731100143264323E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2488,7 +2476,7 @@
                   <c:v>2.8744450632010921E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>6.896426063201111E-2</c:v>
+                  <c:v>8.6077510632010856E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2885,7 +2873,7 @@
                   <c:v>1028.744450632011</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1068.964260632011</c:v>
+                  <c:v>1086.0775106320109</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3310,16 +3298,16 @@
                   <c:v>-8.6131300000000799E-3</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-1.5805630000000015E-2</c:v>
+                  <c:v>-8.6131300000000799E-3</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.0429369999999993E-2</c:v>
+                  <c:v>1.7621869999999928E-2</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>5.2337000000002298E-4</c:v>
+                  <c:v>7.715869999999958E-3</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-8.3360049999999797E-3</c:v>
+                  <c:v>-1.1435050000000446E-3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3412,25 +3400,25 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.3875190632011147E-2</c:v>
+                  <c:v>1.9425190632011091E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.48462806320111E-2</c:v>
+                  <c:v>2.0396280632011043E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>8.4120606320110536E-3</c:v>
+                  <c:v>1.4682060632011051E-2</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2.1422090632011059E-2</c:v>
+                  <c:v>3.0054590632011102E-2</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>6.1457830632010824E-2</c:v>
+                  <c:v>7.4665330632011084E-2</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>6.0152790632010733E-2</c:v>
+                  <c:v>7.4770290632011127E-2</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>6.5015290632010725E-2</c:v>
+                  <c:v>8.1832790632011321E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4080,7 +4068,7 @@
       </c>
       <c r="C1" s="79">
         <f ca="1">TODAY()</f>
-        <v>46126</v>
+        <v>46128</v>
       </c>
     </row>
     <row r="2" spans="2:11" x14ac:dyDescent="0.4">
@@ -4088,7 +4076,7 @@
         <v>107</v>
       </c>
       <c r="C2" s="37" t="s">
-        <v>342</v>
+        <v>333</v>
       </c>
       <c r="E2" s="47" t="s">
         <v>120</v>
@@ -4105,7 +4093,7 @@
       </c>
       <c r="C3" s="28">
         <f ca="1">OFFSET(NAV!B1,MATCH(C1,NAV!B:B,1),8)</f>
-        <v>1068964.2606320111</v>
+        <v>1086077.5106320109</v>
       </c>
       <c r="E3" s="47" t="s">
         <v>121</v>
@@ -4122,7 +4110,7 @@
       </c>
       <c r="C4" s="28">
         <f>SUM(N18:N1012)</f>
-        <v>68964.260632011064</v>
+        <v>86077.510632010832</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="47" t="s">
@@ -4140,7 +4128,7 @@
       </c>
       <c r="C5" s="3">
         <f ca="1">OFFSET(NAV!B1,MATCH(C1,NAV!B:B,1),11)</f>
-        <v>6.896426063201111E-2</v>
+        <v>8.6077510632010856E-2</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="47" t="s">
@@ -4159,7 +4147,7 @@
       </c>
       <c r="C6" s="3">
         <f ca="1">OFFSET(NAV!B1,MATCH(C1,NAV!B:B,1),12)</f>
-        <v>3.9096016484259977E-2</v>
+        <v>5.5731100143264323E-2</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="47" t="s">
@@ -4176,11 +4164,11 @@
       </c>
       <c r="C7" s="28">
         <f>Cash_Mgmt!H13</f>
-        <v>33651.029999999955</v>
+        <v>33355.279999999955</v>
       </c>
       <c r="D7" s="3">
         <f ca="1">C7/C3</f>
-        <v>3.1480032812419963E-2</v>
+        <v>3.0711693846408653E-2</v>
       </c>
       <c r="E7" s="47"/>
       <c r="F7" s="47"/>
@@ -4194,11 +4182,11 @@
       </c>
       <c r="C8" s="28">
         <f>C4+C7</f>
-        <v>102615.29063201102</v>
+        <v>119432.79063201079</v>
       </c>
       <c r="D8" s="3">
         <f ca="1">C5+D7</f>
-        <v>0.10044429344443107</v>
+        <v>0.11678920447841951</v>
       </c>
       <c r="G8" s="47"/>
       <c r="H8" s="51"/>
@@ -4210,11 +4198,11 @@
       </c>
       <c r="C9" s="28">
         <f t="array" ref="C9">SUM((F19:F112="Futures")*(M19:M112))</f>
-        <v>1175606.25</v>
+        <v>1184731.25</v>
       </c>
       <c r="D9" s="3">
         <f ca="1">C9/$C$3</f>
-        <v>1.0997619782956432</v>
+        <v>1.0908348975116706</v>
       </c>
       <c r="E9" s="47"/>
       <c r="F9" s="47"/>
@@ -4228,11 +4216,11 @@
       </c>
       <c r="C10" s="28">
         <f t="array" ref="C10">SUM((F19:F1012="Call")*(M19:M1012))</f>
-        <v>8600</v>
+        <v>10010</v>
       </c>
       <c r="D10" s="3">
         <f t="shared" ref="D10:D14" ca="1" si="0">C10/$C$3</f>
-        <v>8.0451707477248707E-3</v>
+        <v>9.2166534174664711E-3</v>
       </c>
       <c r="H10" s="44"/>
     </row>
@@ -4242,11 +4230,11 @@
       </c>
       <c r="C11" s="28">
         <f t="array" ref="C11">SUM((F19:F212="Put")*(M19:M212))</f>
-        <v>3149.9999999999995</v>
+        <v>3870</v>
       </c>
       <c r="D11" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>2.9467776575968999E-3</v>
+        <v>3.5632815909685555E-3</v>
       </c>
     </row>
     <row r="12" spans="2:11" x14ac:dyDescent="0.4">
@@ -4255,11 +4243,11 @@
       </c>
       <c r="C12" s="28">
         <f t="array" ref="C12">SUM((PLB!G4:G999="O")*(PLB!E4:E999))</f>
-        <v>9307.0950000000012</v>
+        <v>2114.5950000000012</v>
       </c>
       <c r="D12" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>8.7066474930577228E-3</v>
+        <v>1.9470019214093428E-3</v>
       </c>
     </row>
     <row r="13" spans="2:11" x14ac:dyDescent="0.4">
@@ -4268,11 +4256,11 @@
       </c>
       <c r="C13" s="28">
         <f t="array" ref="C13">SUM((PLB!G4:G999="O")*(PLB!D4:D999))</f>
-        <v>64044.200632011118</v>
+        <v>80861.700632010892</v>
       </c>
       <c r="D13" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>5.9912387149544014E-2</v>
+        <v>7.4452973973244144E-2</v>
       </c>
       <c r="F13" s="59"/>
       <c r="G13" s="59"/>
@@ -4283,11 +4271,11 @@
       </c>
       <c r="C14" s="28">
         <f>C12+C13</f>
-        <v>73351.295632011112</v>
+        <v>82976.295632010893</v>
       </c>
       <c r="D14" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>6.8619034642601731E-2</v>
+        <v>7.6399975894653485E-2</v>
       </c>
     </row>
     <row r="17" spans="2:28" x14ac:dyDescent="0.4">
@@ -4334,7 +4322,7 @@
         <v>14</v>
       </c>
       <c r="P17" s="4" t="s">
-        <v>341</v>
+        <v>332</v>
       </c>
       <c r="Q17" s="4" t="s">
         <v>113</v>
@@ -4384,7 +4372,7 @@
       <c r="M18" s="12"/>
       <c r="N18" s="95">
         <f>Cash_Mgmt!G13</f>
-        <v>3948.9699999999543</v>
+        <v>4244.7199999999539</v>
       </c>
       <c r="O18" s="12"/>
       <c r="P18" s="12"/>
@@ -4436,15 +4424,15 @@
       </c>
       <c r="L19" s="29">
         <f t="shared" ref="L19" si="2">IF(I19=0,IF(H19&gt;0,X19,Y19),Z19)</f>
-        <v>2264.0500000000002</v>
+        <v>2375.0500000000002</v>
       </c>
       <c r="M19" s="28">
         <f t="shared" ref="M19" si="3">I19*J19*L19</f>
-        <v>113202.50000000001</v>
+        <v>118752.50000000001</v>
       </c>
       <c r="N19" s="95">
         <f t="array" ref="N19">-SUM((Trades!T$2:T$9999=Blotter!C19)*(Trades!U$2:U$9999=Blotter!B19)*(Trades!V$2:V$9999)*(Trades!W$2:W$9999))*J19+SUM((Trades!T$2:T$9999=Blotter!C19)*(Trades!U$2:U$9999=Blotter!B19)*(Trades!X$2:X$9999))+(L19*I19)*J19</f>
-        <v>13875.190632011014</v>
+        <v>19425.190632011014</v>
       </c>
       <c r="O19" s="29">
         <f>VLOOKUP(D19,Multiplier!B:H,3,0)</f>
@@ -4458,11 +4446,11 @@
       </c>
       <c r="S19" s="29">
         <f>IF(OR(F19="Futures",F19="Spot"),IF(I19=0,0,IF(I19&gt;0,L19-O19,L19+O19)),0)</f>
-        <v>2124.0500000000002</v>
+        <v>2235.0500000000002</v>
       </c>
       <c r="T19" s="3">
         <f t="shared" ref="T19" si="5">IF(S19&gt;0,IF(ISNUMBER(S19/L19-1),S19/L19-1,0),0)</f>
-        <v>-6.1836090192354365E-2</v>
+        <v>-5.8946127449948427E-2</v>
       </c>
       <c r="U19" s="29">
         <f>IF(OR(F19="Futures",F19="Spot"),IF(I19=0,0,IF(I19&gt;0,K19-P19,K19+P19)),0)</f>
@@ -4470,7 +4458,7 @@
       </c>
       <c r="V19" s="3">
         <f t="shared" ref="V19" si="6">IF(U19&gt;0,IF(ISNUMBER(U19/L19-1),U19/L19-1,0),0)</f>
-        <v>-0.12256964847959195</v>
+        <v>-0.16357710896200939</v>
       </c>
       <c r="X19" s="34">
         <f t="array" ref="X19">IF(ISNUMBER(SUM((Trades!T$2:T$9999=Blotter!C19)*(Trades!U$2:U$9999=Blotter!B19)*(Trades!W$2:W$9999)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0))/SUM((Trades!T$2:T$9999=Blotter!C19)*(Trades!U$2:U$9999=Blotter!B19)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0))),SUM((Trades!T$2:T$9999=Blotter!C19)*(Trades!U$2:U$9999=Blotter!B19)*(Trades!W$2:W$9999)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0))/SUM((Trades!T$2:T$9999=Blotter!C19)*(Trades!U$2:U$9999=Blotter!B19)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0)),0)</f>
@@ -4482,7 +4470,7 @@
       </c>
       <c r="Z19" s="35">
         <f>IF(C$2="Last",IF(ISNUMBER(VLOOKUP(B19,Prices!A:L,8,0)),VLOOKUP(B19,Prices!A:L,8,0),0),IF(ISNUMBER(VLOOKUP(B19,Prices!A:L,12,0)),VLOOKUP(B19,Prices!A:L,12,0),0))</f>
-        <v>2264.0500000000002</v>
+        <v>2375.0500000000002</v>
       </c>
       <c r="AB19" s="29"/>
     </row>
@@ -4571,7 +4559,7 @@
       </c>
       <c r="Z20" s="35">
         <f>IF(C$2="Last",IF(ISNUMBER(VLOOKUP(B20,Prices!A:L,8,0)),VLOOKUP(B20,Prices!A:L,8,0),0),IF(ISNUMBER(VLOOKUP(B20,Prices!A:L,12,0)),VLOOKUP(B20,Prices!A:L,12,0),0))</f>
-        <v>3278</v>
+        <v>3477</v>
       </c>
       <c r="AB20" s="29"/>
     </row>
@@ -4612,15 +4600,15 @@
       </c>
       <c r="L21" s="29">
         <f t="shared" ref="L21:L22" si="15">IF(I21=0,IF(H21&gt;0,X21,Y21),Z21)</f>
-        <v>1.1599999999999999</v>
+        <v>1.41</v>
       </c>
       <c r="M21" s="28">
         <f t="shared" ref="M21:M22" si="16">I21*J21*L21</f>
-        <v>3479.9999999999995</v>
+        <v>4230</v>
       </c>
       <c r="N21" s="95">
         <f t="array" ref="N21">-SUM((Trades!T$2:T$9999=Blotter!C21)*(Trades!U$2:U$9999=Blotter!B21)*(Trades!V$2:V$9999)*(Trades!W$2:W$9999))*J21+SUM((Trades!T$2:T$9999=Blotter!C21)*(Trades!U$2:U$9999=Blotter!B21)*(Trades!X$2:X$9999))+(L21*I21)*J21</f>
-        <v>-7147.1100000000024</v>
+        <v>-6397.1100000000033</v>
       </c>
       <c r="O21" s="29">
         <f>VLOOKUP(D21,Multiplier!B:H,3,0)</f>
@@ -4660,7 +4648,7 @@
       </c>
       <c r="Z21" s="35">
         <f>IF(C$2="Last",IF(ISNUMBER(VLOOKUP(B21,Prices!A:L,8,0)),VLOOKUP(B21,Prices!A:L,8,0),0),IF(ISNUMBER(VLOOKUP(B21,Prices!A:L,12,0)),VLOOKUP(B21,Prices!A:L,12,0),0))</f>
-        <v>1.1599999999999999</v>
+        <v>1.41</v>
       </c>
       <c r="AB21" s="29"/>
     </row>
@@ -4697,19 +4685,19 @@
       </c>
       <c r="K22" s="29">
         <f t="shared" si="14"/>
-        <v>0.34762999999999994</v>
+        <v>0.34762999999999999</v>
       </c>
       <c r="L22" s="29">
         <f t="shared" si="15"/>
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="M22" s="28">
         <f t="shared" si="16"/>
-        <v>-330</v>
+        <v>-360</v>
       </c>
       <c r="N22" s="95">
         <f t="array" ref="N22">-SUM((Trades!T$2:T$9999=Blotter!C22)*(Trades!U$2:U$9999=Blotter!B22)*(Trades!V$2:V$9999)*(Trades!W$2:W$9999))*J22+SUM((Trades!T$2:T$9999=Blotter!C22)*(Trades!U$2:U$9999=Blotter!B22)*(Trades!X$2:X$9999))+(L22*I22)*J22</f>
-        <v>712.88999999999987</v>
+        <v>682.88999999999987</v>
       </c>
       <c r="O22" s="29">
         <f>VLOOKUP(D22,Multiplier!B:H,3,0)</f>
@@ -4749,7 +4737,7 @@
       </c>
       <c r="Z22" s="35">
         <f>IF(C$2="Last",IF(ISNUMBER(VLOOKUP(B22,Prices!A:L,8,0)),VLOOKUP(B22,Prices!A:L,8,0),0),IF(ISNUMBER(VLOOKUP(B22,Prices!A:L,12,0)),VLOOKUP(B22,Prices!A:L,12,0),0))</f>
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="AB22" s="29"/>
     </row>
@@ -4790,43 +4778,41 @@
       </c>
       <c r="L23" s="29">
         <f t="shared" ref="L23" si="23">IF(I23=0,IF(H23&gt;0,X23,Y23),Z23)</f>
-        <v>5.9904999999999999</v>
+        <v>6.085</v>
       </c>
       <c r="M23" s="28">
         <f t="shared" ref="M23" si="24">I23*J23*L23</f>
-        <v>149762.5</v>
+        <v>152125</v>
       </c>
       <c r="N23" s="95">
         <f t="array" ref="N23">-SUM((Trades!T$2:T$9999=Blotter!C23)*(Trades!U$2:U$9999=Blotter!B23)*(Trades!V$2:V$9999)*(Trades!W$2:W$9999))*J23+SUM((Trades!T$2:T$9999=Blotter!C23)*(Trades!U$2:U$9999=Blotter!B23)*(Trades!X$2:X$9999))+(L23*I23)*J23</f>
-        <v>13010.029999999999</v>
+        <v>15372.529999999999</v>
       </c>
       <c r="O23" s="29">
         <f>VLOOKUP(D23,Multiplier!B:H,3,0)</f>
         <v>0.1918</v>
       </c>
-      <c r="P23" s="27">
-        <v>0.28770000000000001</v>
-      </c>
+      <c r="P23" s="27"/>
       <c r="Q23" s="27"/>
       <c r="R23" s="28">
         <f t="shared" ref="R23" si="25">(1-Q23)*P23*J23*H23</f>
-        <v>7192.5</v>
+        <v>0</v>
       </c>
       <c r="S23" s="29">
         <f t="shared" ref="S23" si="26">IF(OR(F23="Futures",F23="Spot"),IF(I23=0,0,IF(I23&gt;0,L23-O23,L23+O23)),0)</f>
-        <v>5.7987000000000002</v>
+        <v>5.8932000000000002</v>
       </c>
       <c r="T23" s="3">
         <f t="shared" ref="T23" si="27">IF(S23&gt;0,IF(ISNUMBER(S23/L23-1),S23/L23-1,0),0)</f>
-        <v>-3.2017360821300356E-2</v>
+        <v>-3.1520131470829882E-2</v>
       </c>
       <c r="U23" s="29">
         <f t="shared" ref="U23" si="28">IF(OR(F23="Futures",F23="Stocks"),IF(I23=0,0,IF(I23&gt;0,K23-P23,K23+P23)),0)</f>
-        <v>5.1823987999999996</v>
+        <v>5.4700987999999997</v>
       </c>
       <c r="V23" s="3">
         <f t="shared" ref="V23" si="29">IF(U23&gt;0,IF(ISNUMBER(U23/L23-1),U23/L23-1,0),0)</f>
-        <v>-0.13489712044069779</v>
+        <v>-0.10105196384552184</v>
       </c>
       <c r="X23" s="34">
         <f t="array" ref="X23">IF(ISNUMBER(SUM((Trades!T$2:T$9999=Blotter!C23)*(Trades!U$2:U$9999=Blotter!B23)*(Trades!W$2:W$9999)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0))/SUM((Trades!T$2:T$9999=Blotter!C23)*(Trades!U$2:U$9999=Blotter!B23)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0))),SUM((Trades!T$2:T$9999=Blotter!C23)*(Trades!U$2:U$9999=Blotter!B23)*(Trades!W$2:W$9999)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0))/SUM((Trades!T$2:T$9999=Blotter!C23)*(Trades!U$2:U$9999=Blotter!B23)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0)),0)</f>
@@ -4838,19 +4824,19 @@
       </c>
       <c r="Z23" s="35">
         <f>IF(C$2="Last",IF(ISNUMBER(VLOOKUP(B23,Prices!A:L,8,0)),VLOOKUP(B23,Prices!A:L,8,0),0),IF(ISNUMBER(VLOOKUP(B23,Prices!A:L,12,0)),VLOOKUP(B23,Prices!A:L,12,0),0))</f>
-        <v>5.9904999999999999</v>
+        <v>6.085</v>
       </c>
       <c r="AB23" s="29"/>
     </row>
     <row r="24" spans="2:28" x14ac:dyDescent="0.4">
       <c r="B24" s="9" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="C24" s="10">
         <v>5</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="E24" s="10" t="s">
         <v>120</v>
@@ -4879,15 +4865,15 @@
       </c>
       <c r="L24" s="29">
         <f t="shared" ref="L24" si="31">IF(I24=0,IF(H24&gt;0,X24,Y24),Z24)</f>
-        <v>57675</v>
+        <v>58590</v>
       </c>
       <c r="M24" s="28">
         <f t="shared" ref="M24" si="32">I24*J24*L24</f>
-        <v>288375</v>
+        <v>292950</v>
       </c>
       <c r="N24" s="95">
         <f t="array" ref="N24">-SUM((Trades!T$2:T$9999=Blotter!C24)*(Trades!U$2:U$9999=Blotter!B24)*(Trades!V$2:V$9999)*(Trades!W$2:W$9999))*J24+SUM((Trades!T$2:T$9999=Blotter!C24)*(Trades!U$2:U$9999=Blotter!B24)*(Trades!X$2:X$9999))+(L24*I24)*J24</f>
-        <v>40035.739999999991</v>
+        <v>44610.739999999991</v>
       </c>
       <c r="O24" s="29">
         <f>VLOOKUP(D24,Multiplier!B:H,3,0)</f>
@@ -4904,11 +4890,11 @@
       </c>
       <c r="S24" s="29">
         <f t="shared" ref="S24" si="34">IF(OR(F24="Futures",F24="Spot"),IF(I24=0,0,IF(I24&gt;0,L24-O24,L24+O24)),0)</f>
-        <v>55926</v>
+        <v>56841</v>
       </c>
       <c r="T24" s="3">
         <f t="shared" ref="T24" si="35">IF(S24&gt;0,IF(ISNUMBER(S24/L24-1),S24/L24-1,0),0)</f>
-        <v>-3.0325097529258827E-2</v>
+        <v>-2.9851510496671785E-2</v>
       </c>
       <c r="U24" s="29">
         <f t="shared" ref="U24" si="36">IF(OR(F24="Futures",F24="Stocks"),IF(I24=0,0,IF(I24&gt;0,K24-P24,K24+P24)),0)</f>
@@ -4916,7 +4902,7 @@
       </c>
       <c r="V24" s="3">
         <f t="shared" ref="V24" si="37">IF(U24&gt;0,IF(ISNUMBER(U24/L24-1),U24/L24-1,0),0)</f>
-        <v>-4.7856922410056346E-2</v>
+        <v>-6.272654036525005E-2</v>
       </c>
       <c r="X24" s="34">
         <f t="array" ref="X24">IF(ISNUMBER(SUM((Trades!T$2:T$9999=Blotter!C24)*(Trades!U$2:U$9999=Blotter!B24)*(Trades!W$2:W$9999)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0))/SUM((Trades!T$2:T$9999=Blotter!C24)*(Trades!U$2:U$9999=Blotter!B24)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0))),SUM((Trades!T$2:T$9999=Blotter!C24)*(Trades!U$2:U$9999=Blotter!B24)*(Trades!W$2:W$9999)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0))/SUM((Trades!T$2:T$9999=Blotter!C24)*(Trades!U$2:U$9999=Blotter!B24)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0)),0)</f>
@@ -4928,13 +4914,13 @@
       </c>
       <c r="Z24" s="35">
         <f>IF(C$2="Last",IF(ISNUMBER(VLOOKUP(B24,Prices!A:L,8,0)),VLOOKUP(B24,Prices!A:L,8,0),0),IF(ISNUMBER(VLOOKUP(B24,Prices!A:L,12,0)),VLOOKUP(B24,Prices!A:L,12,0),0))</f>
-        <v>57675</v>
+        <v>58590</v>
       </c>
       <c r="AB24" s="29"/>
     </row>
     <row r="25" spans="2:28" x14ac:dyDescent="0.4">
       <c r="B25" s="9" t="s">
-        <v>333</v>
+        <v>325</v>
       </c>
       <c r="C25" s="10">
         <v>6</v>
@@ -4969,15 +4955,15 @@
       </c>
       <c r="L25" s="29">
         <f t="shared" ref="L25:L26" si="39">IF(I25=0,IF(H25&gt;0,X25,Y25),Z25)</f>
-        <v>14.8</v>
+        <v>16.399999999999999</v>
       </c>
       <c r="M25" s="28">
         <f t="shared" ref="M25:M26" si="40">I25*J25*L25</f>
-        <v>-1480</v>
+        <v>-1639.9999999999998</v>
       </c>
       <c r="N25" s="95">
         <f t="array" ref="N25">-SUM((Trades!T$2:T$9999=Blotter!C25)*(Trades!U$2:U$9999=Blotter!B25)*(Trades!V$2:V$9999)*(Trades!W$2:W$9999))*J25+SUM((Trades!T$2:T$9999=Blotter!C25)*(Trades!U$2:U$9999=Blotter!B25)*(Trades!X$2:X$9999))+(L25*I25)*J25</f>
-        <v>1157.48</v>
+        <v>997.48000000000025</v>
       </c>
       <c r="O25" s="29">
         <f>VLOOKUP(D25,Multiplier!B:H,3,0)</f>
@@ -5017,13 +5003,13 @@
       </c>
       <c r="Z25" s="35">
         <f>IF(C$2="Last",IF(ISNUMBER(VLOOKUP(B25,Prices!A:L,8,0)),VLOOKUP(B25,Prices!A:L,8,0),0),IF(ISNUMBER(VLOOKUP(B25,Prices!A:L,12,0)),VLOOKUP(B25,Prices!A:L,12,0),0))</f>
-        <v>14.8</v>
+        <v>16.399999999999999</v>
       </c>
       <c r="AB25" s="29"/>
     </row>
     <row r="26" spans="2:28" x14ac:dyDescent="0.4">
       <c r="B26" s="9" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="C26" s="10">
         <v>6</v>
@@ -5058,15 +5044,15 @@
       </c>
       <c r="L26" s="29">
         <f t="shared" si="39"/>
-        <v>100.8</v>
+        <v>116.5</v>
       </c>
       <c r="M26" s="28">
         <f t="shared" si="40"/>
-        <v>10080</v>
+        <v>11650</v>
       </c>
       <c r="N26" s="95">
         <f t="array" ref="N26">-SUM((Trades!T$2:T$9999=Blotter!C26)*(Trades!U$2:U$9999=Blotter!B26)*(Trades!V$2:V$9999)*(Trades!W$2:W$9999))*J26+SUM((Trades!T$2:T$9999=Blotter!C26)*(Trades!U$2:U$9999=Blotter!B26)*(Trades!X$2:X$9999))+(L26*I26)*J26</f>
-        <v>-2462.5200000000004</v>
+        <v>-892.52000000000044</v>
       </c>
       <c r="O26" s="29">
         <f>VLOOKUP(D26,Multiplier!B:H,3,0)</f>
@@ -5106,7 +5092,7 @@
       </c>
       <c r="Z26" s="35">
         <f>IF(C$2="Last",IF(ISNUMBER(VLOOKUP(B26,Prices!A:L,8,0)),VLOOKUP(B26,Prices!A:L,8,0),0),IF(ISNUMBER(VLOOKUP(B26,Prices!A:L,12,0)),VLOOKUP(B26,Prices!A:L,12,0),0))</f>
-        <v>100.8</v>
+        <v>116.5</v>
       </c>
       <c r="AB26" s="29"/>
     </row>
@@ -5143,19 +5129,19 @@
       </c>
       <c r="K27" s="99">
         <f t="shared" ref="K27" si="46">L27-N27/(H27*J27)</f>
-        <v>1.1721699999999999</v>
+        <v>1.17215</v>
       </c>
       <c r="L27" s="99">
         <f t="shared" ref="L27" si="47">IF(I27=0,IF(H27&gt;0,X27,Y27),Z27)</f>
-        <v>1.1799500000000001</v>
+        <v>1.1834499999999999</v>
       </c>
       <c r="M27" s="28">
         <f t="shared" ref="M27" si="48">I27*J27*L27</f>
-        <v>737468.75</v>
+        <v>739656.24999999988</v>
       </c>
       <c r="N27" s="95">
         <f t="array" ref="N27">-SUM((Trades!T$2:T$9999=Blotter!C27)*(Trades!U$2:U$9999=Blotter!B27)*(Trades!V$2:V$9999)*(Trades!W$2:W$9999))*J27+SUM((Trades!T$2:T$9999=Blotter!C27)*(Trades!U$2:U$9999=Blotter!B27)*(Trades!X$2:X$9999))+(L27*I27)*J27</f>
-        <v>4862.5000000001164</v>
+        <v>7062.4999999998836</v>
       </c>
       <c r="O27" s="46">
         <f>VLOOKUP(D27,Multiplier!B:H,3,0)</f>
@@ -5172,19 +5158,19 @@
       </c>
       <c r="S27" s="29">
         <f t="shared" ref="S27" si="50">IF(OR(F27="Futures",F27="Spot"),IF(I27=0,0,IF(I27&gt;0,L27-O27,L27+O27)),0)</f>
-        <v>1.1705000000000001</v>
+        <v>1.1739999999999999</v>
       </c>
       <c r="T27" s="3">
         <f t="shared" ref="T27" si="51">IF(S27&gt;0,IF(ISNUMBER(S27/L27-1),S27/L27-1,0),0)</f>
-        <v>-8.0088139327937347E-3</v>
+        <v>-7.9851282267945356E-3</v>
       </c>
       <c r="U27" s="29">
         <f t="shared" ref="U27" si="52">IF(OR(F27="Futures",F27="Stocks"),IF(I27=0,0,IF(I27&gt;0,K27-P27,K27+P27)),0)</f>
-        <v>1.1579949999999999</v>
+        <v>1.157975</v>
       </c>
       <c r="V27" s="3">
         <f t="shared" ref="V27" si="53">IF(U27&gt;0,IF(ISNUMBER(U27/L27-1),U27/L27-1,0),0)</f>
-        <v>-1.8606720623755346E-2</v>
+        <v>-2.1526046727787351E-2</v>
       </c>
       <c r="X27" s="34">
         <f t="array" ref="X27">IF(ISNUMBER(SUM((Trades!T$2:T$9999=Blotter!C27)*(Trades!U$2:U$9999=Blotter!B27)*(Trades!W$2:W$9999)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0))/SUM((Trades!T$2:T$9999=Blotter!C27)*(Trades!U$2:U$9999=Blotter!B27)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0))),SUM((Trades!T$2:T$9999=Blotter!C27)*(Trades!U$2:U$9999=Blotter!B27)*(Trades!W$2:W$9999)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0))/SUM((Trades!T$2:T$9999=Blotter!C27)*(Trades!U$2:U$9999=Blotter!B27)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0)),0)</f>
@@ -5192,11 +5178,11 @@
       </c>
       <c r="Y27" s="34">
         <f t="array" ref="Y27">IF(ISNUMBER(SUM((Trades!T$2:T$9999=Blotter!C27)*(Trades!U$2:U$9999=Blotter!B27)*(Trades!W$2:W$9999)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&gt;0))/SUM((Trades!T$2:T$9999=Blotter!C27)*(Trades!U$2:U$9999=Blotter!B27)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&gt;0))),SUM((Trades!T$2:T$9999=Blotter!C27)*(Trades!U$2:U$9999=Blotter!B27)*(Trades!W$2:W$9999)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&gt;0))/SUM((Trades!T$2:T$9999=Blotter!C27)*(Trades!U$2:U$9999=Blotter!B27)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&gt;0)),0)</f>
-        <v>1.1721699999999999</v>
+        <v>1.17215</v>
       </c>
       <c r="Z27" s="35">
         <f>IF(C$2="Last",IF(ISNUMBER(VLOOKUP(B27,Prices!A:L,8,0)),VLOOKUP(B27,Prices!A:L,8,0),0),IF(ISNUMBER(VLOOKUP(B27,Prices!A:L,12,0)),VLOOKUP(B27,Prices!A:L,12,0),0))</f>
-        <v>1.1799500000000001</v>
+        <v>1.1834499999999999</v>
       </c>
       <c r="AB27" s="29"/>
     </row>
@@ -6794,31 +6780,31 @@
         <v>59</v>
       </c>
       <c r="H2" s="91">
-        <v>6934.25</v>
+        <v>7067.5</v>
       </c>
       <c r="I2" s="91">
-        <v>6934</v>
+        <v>7067.25</v>
       </c>
       <c r="J2" s="91">
-        <v>6934.25</v>
+        <v>7067.5</v>
       </c>
       <c r="K2" s="91">
-        <v>6934.125</v>
+        <v>7067.375</v>
       </c>
       <c r="L2" s="91">
-        <v>6922.75</v>
+        <v>7060.5</v>
       </c>
       <c r="M2" s="91">
-        <v>6925.25</v>
+        <v>7057.25</v>
       </c>
       <c r="N2" s="91">
-        <v>6942.25</v>
+        <v>7078.5</v>
       </c>
       <c r="O2" s="91">
-        <v>6920.25</v>
+        <v>7055.5</v>
       </c>
       <c r="P2" s="91">
-        <v>89489</v>
+        <v>90518</v>
       </c>
       <c r="Q2" s="91"/>
       <c r="R2" s="91"/>
@@ -6826,7 +6812,7 @@
       <c r="T2" s="91"/>
       <c r="U2" s="91"/>
       <c r="V2" s="85">
-        <v>46126.504861111112</v>
+        <v>46128.481365740743</v>
       </c>
       <c r="W2" s="81" t="s">
         <v>258</v>
@@ -6858,31 +6844,31 @@
         <v>59</v>
       </c>
       <c r="H3" s="91">
-        <v>25638.5</v>
+        <v>26448.5</v>
       </c>
       <c r="I3" s="91">
-        <v>25638</v>
+        <v>26447.75</v>
       </c>
       <c r="J3" s="91">
-        <v>25638.75</v>
+        <v>26448.5</v>
       </c>
       <c r="K3" s="91">
-        <v>25638.375</v>
+        <v>26448.125</v>
       </c>
       <c r="L3" s="91">
-        <v>25543.5</v>
+        <v>26365.5</v>
       </c>
       <c r="M3" s="91">
-        <v>25575.25</v>
+        <v>26350</v>
       </c>
       <c r="N3" s="91">
-        <v>25674</v>
+        <v>26488</v>
       </c>
       <c r="O3" s="91">
-        <v>25560</v>
+        <v>26345</v>
       </c>
       <c r="P3" s="91">
-        <v>54911</v>
+        <v>60884</v>
       </c>
       <c r="Q3" s="91"/>
       <c r="R3" s="91"/>
@@ -6890,7 +6876,7 @@
       <c r="T3" s="91"/>
       <c r="U3" s="91"/>
       <c r="V3" s="85">
-        <v>46126.504861111112</v>
+        <v>46128.481365740743</v>
       </c>
       <c r="W3" s="81" t="s">
         <v>258</v>
@@ -6922,31 +6908,31 @@
         <v>59</v>
       </c>
       <c r="H4" s="91">
-        <v>2693.6</v>
+        <v>2724.3</v>
       </c>
       <c r="I4" s="91">
-        <v>2693.5</v>
+        <v>2724.2</v>
       </c>
       <c r="J4" s="91">
-        <v>2693.7</v>
+        <v>2724.4</v>
       </c>
       <c r="K4" s="91">
-        <v>2693.6</v>
+        <v>2724.3</v>
       </c>
       <c r="L4" s="91">
-        <v>2682.3</v>
+        <v>2725.5</v>
       </c>
       <c r="M4" s="91">
-        <v>2688.2</v>
+        <v>2724.6</v>
       </c>
       <c r="N4" s="91">
-        <v>2698.7</v>
+        <v>2731</v>
       </c>
       <c r="O4" s="91">
-        <v>2684.1</v>
+        <v>2722.8</v>
       </c>
       <c r="P4" s="91">
-        <v>11258</v>
+        <v>9535</v>
       </c>
       <c r="Q4" s="91"/>
       <c r="R4" s="91"/>
@@ -6954,7 +6940,7 @@
       <c r="T4" s="91"/>
       <c r="U4" s="91"/>
       <c r="V4" s="85">
-        <v>46126.504861111112</v>
+        <v>46128.481365740743</v>
       </c>
       <c r="W4" s="81" t="s">
         <v>258</v>
@@ -6986,31 +6972,31 @@
         <v>56</v>
       </c>
       <c r="H5" s="91">
-        <v>24142</v>
+        <v>24311</v>
       </c>
       <c r="I5" s="91">
-        <v>24141</v>
+        <v>24309</v>
       </c>
       <c r="J5" s="91">
-        <v>24143</v>
+        <v>24312</v>
       </c>
       <c r="K5" s="91">
-        <v>24142</v>
+        <v>24310.5</v>
       </c>
       <c r="L5" s="91">
-        <v>23922</v>
+        <v>24258</v>
       </c>
       <c r="M5" s="91">
-        <v>24120</v>
+        <v>24276</v>
       </c>
       <c r="N5" s="91">
-        <v>24231</v>
+        <v>24356</v>
       </c>
       <c r="O5" s="91">
-        <v>24042</v>
+        <v>24222</v>
       </c>
       <c r="P5" s="91">
-        <v>9378</v>
+        <v>6818</v>
       </c>
       <c r="Q5" s="91"/>
       <c r="R5" s="91"/>
@@ -7018,7 +7004,7 @@
       <c r="T5" s="91"/>
       <c r="U5" s="91"/>
       <c r="V5" s="85">
-        <v>46126.504861111112</v>
+        <v>46128.481365740743</v>
       </c>
       <c r="W5" s="81" t="s">
         <v>258</v>
@@ -7029,7 +7015,7 @@
     </row>
     <row r="6" spans="1:32" x14ac:dyDescent="0.4">
       <c r="A6" s="81" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="B6" s="81">
         <v>635680489</v>
@@ -7038,10 +7024,10 @@
         <v>58</v>
       </c>
       <c r="D6" s="81" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="E6" s="81" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="F6" s="81" t="s">
         <v>78</v>
@@ -7050,31 +7036,31 @@
         <v>59</v>
       </c>
       <c r="H6" s="91">
-        <v>58040</v>
+        <v>59410</v>
       </c>
       <c r="I6" s="91">
-        <v>58030</v>
+        <v>59420</v>
       </c>
       <c r="J6" s="91">
-        <v>58045</v>
+        <v>59430</v>
       </c>
       <c r="K6" s="91">
-        <v>58037.5</v>
+        <v>59425</v>
       </c>
       <c r="L6" s="91">
-        <v>57675</v>
+        <v>58590</v>
       </c>
       <c r="M6" s="91">
-        <v>57710</v>
+        <v>58645</v>
       </c>
       <c r="N6" s="91">
-        <v>58305</v>
+        <v>59805</v>
       </c>
       <c r="O6" s="91">
-        <v>57475</v>
+        <v>58585</v>
       </c>
       <c r="P6" s="91">
-        <v>2033</v>
+        <v>1989</v>
       </c>
       <c r="Q6" s="91"/>
       <c r="R6" s="91"/>
@@ -7082,7 +7068,7 @@
       <c r="T6" s="91"/>
       <c r="U6" s="91"/>
       <c r="V6" s="85">
-        <v>46126.504861111112</v>
+        <v>46128.481365740743</v>
       </c>
       <c r="W6" s="81" t="s">
         <v>258</v>
@@ -7125,7 +7111,7 @@
       <c r="T7" s="93"/>
       <c r="U7" s="93"/>
       <c r="V7" s="92">
-        <v>46126.504861111112</v>
+        <v>46128.481365740743</v>
       </c>
       <c r="W7" s="1" t="s">
         <v>313</v>
@@ -7154,31 +7140,31 @@
         <v>59</v>
       </c>
       <c r="H8" s="93">
-        <v>2.774</v>
+        <v>2.7570000000000001</v>
       </c>
       <c r="I8" s="93">
-        <v>2.7730000000000001</v>
+        <v>2.7570000000000001</v>
       </c>
       <c r="J8" s="93">
-        <v>2.7749999999999999</v>
+        <v>2.758</v>
       </c>
       <c r="K8" s="93">
-        <v>2.774</v>
+        <v>2.7575000000000003</v>
       </c>
       <c r="L8" s="93">
-        <v>2.7909999999999999</v>
+        <v>2.7669999999999999</v>
       </c>
       <c r="M8" s="93">
-        <v>2.7909999999999999</v>
+        <v>2.7679999999999998</v>
       </c>
       <c r="N8" s="93">
-        <v>2.7930000000000001</v>
+        <v>2.7770000000000001</v>
       </c>
       <c r="O8" s="93">
-        <v>2.754</v>
+        <v>2.7410000000000001</v>
       </c>
       <c r="P8" s="93">
-        <v>3853</v>
+        <v>4043</v>
       </c>
       <c r="Q8" s="93"/>
       <c r="R8" s="93"/>
@@ -7186,7 +7172,7 @@
       <c r="T8" s="93"/>
       <c r="U8" s="93"/>
       <c r="V8" s="92">
-        <v>46126.504861111112</v>
+        <v>46128.481365740743</v>
       </c>
       <c r="W8" s="1" t="s">
         <v>258</v>
@@ -7215,31 +7201,31 @@
         <v>59</v>
       </c>
       <c r="H9" s="93">
-        <v>3.0375000000000001</v>
+        <v>3.0274999999999999</v>
       </c>
       <c r="I9" s="93">
-        <v>3.0373000000000001</v>
+        <v>3.0276999999999998</v>
       </c>
       <c r="J9" s="93">
-        <v>3.0377999999999998</v>
+        <v>3.0284</v>
       </c>
       <c r="K9" s="93">
-        <v>3.03755</v>
+        <v>3.0280499999999999</v>
       </c>
       <c r="L9" s="93">
-        <v>3.0428999999999999</v>
+        <v>3.0051000000000001</v>
       </c>
       <c r="M9" s="93">
-        <v>3.028</v>
+        <v>2.9980000000000002</v>
       </c>
       <c r="N9" s="93">
-        <v>3.0409999999999999</v>
+        <v>3.0348999999999999</v>
       </c>
       <c r="O9" s="93">
-        <v>2.9824000000000002</v>
+        <v>2.9849999999999999</v>
       </c>
       <c r="P9" s="93">
-        <v>6156</v>
+        <v>5521</v>
       </c>
       <c r="Q9" s="93"/>
       <c r="R9" s="93"/>
@@ -7247,7 +7233,7 @@
       <c r="T9" s="93"/>
       <c r="U9" s="93"/>
       <c r="V9" s="92">
-        <v>46126.504861111112</v>
+        <v>46128.481365740743</v>
       </c>
       <c r="W9" s="1" t="s">
         <v>258</v>
@@ -7275,25 +7261,43 @@
       <c r="G10" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="H10" s="93"/>
-      <c r="I10" s="93"/>
-      <c r="J10" s="93"/>
-      <c r="K10" s="93"/>
-      <c r="L10" s="93"/>
-      <c r="M10" s="93"/>
-      <c r="N10" s="93"/>
-      <c r="O10" s="93"/>
-      <c r="P10" s="93"/>
+      <c r="H10" s="93">
+        <v>4838.1000000000004</v>
+      </c>
+      <c r="I10" s="93">
+        <v>4837.7</v>
+      </c>
+      <c r="J10" s="93">
+        <v>4838.1000000000004</v>
+      </c>
+      <c r="K10" s="93">
+        <v>4837.8999999999996</v>
+      </c>
+      <c r="L10" s="93">
+        <v>4823.6000000000004</v>
+      </c>
+      <c r="M10" s="93">
+        <v>4813.6000000000004</v>
+      </c>
+      <c r="N10" s="93">
+        <v>4861.3</v>
+      </c>
+      <c r="O10" s="93">
+        <v>4812.3999999999996</v>
+      </c>
+      <c r="P10" s="93">
+        <v>43133</v>
+      </c>
       <c r="Q10" s="93"/>
       <c r="R10" s="93"/>
       <c r="S10" s="93"/>
       <c r="T10" s="93"/>
       <c r="U10" s="93"/>
       <c r="V10" s="92">
-        <v>46126.504861111112</v>
+        <v>46128.481365740743</v>
       </c>
       <c r="W10" s="1" t="s">
-        <v>313</v>
+        <v>258</v>
       </c>
     </row>
     <row r="11" spans="1:32" x14ac:dyDescent="0.4">
@@ -7319,31 +7323,31 @@
         <v>59</v>
       </c>
       <c r="H11" s="93">
-        <v>78.204999999999998</v>
+        <v>80.209999999999994</v>
       </c>
       <c r="I11" s="93">
-        <v>78.254999999999995</v>
+        <v>80.099999999999994</v>
       </c>
       <c r="J11" s="93">
-        <v>78.290000000000006</v>
+        <v>80.13</v>
       </c>
       <c r="K11" s="93">
-        <v>78.272500000000008</v>
+        <v>80.114999999999995</v>
       </c>
       <c r="L11" s="93">
-        <v>75.94</v>
+        <v>79.915000000000006</v>
       </c>
       <c r="M11" s="93">
-        <v>76.180000000000007</v>
+        <v>79.894999999999996</v>
       </c>
       <c r="N11" s="93">
-        <v>78.44</v>
+        <v>81.165000000000006</v>
       </c>
       <c r="O11" s="93">
-        <v>76.075000000000003</v>
+        <v>79.894999999999996</v>
       </c>
       <c r="P11" s="93">
-        <v>231</v>
+        <v>312</v>
       </c>
       <c r="Q11" s="93"/>
       <c r="R11" s="93"/>
@@ -7351,7 +7355,7 @@
       <c r="T11" s="93"/>
       <c r="U11" s="93"/>
       <c r="V11" s="92">
-        <v>46126.504861111112</v>
+        <v>46128.481365740743</v>
       </c>
       <c r="W11" s="1" t="s">
         <v>258</v>
@@ -7380,31 +7384,31 @@
         <v>59</v>
       </c>
       <c r="H12" s="93">
-        <v>6.0430000000000001</v>
+        <v>6.0945</v>
       </c>
       <c r="I12" s="93">
-        <v>6.0425000000000004</v>
+        <v>6.0934999999999997</v>
       </c>
       <c r="J12" s="93">
-        <v>6.0434999999999999</v>
+        <v>6.0949999999999998</v>
       </c>
       <c r="K12" s="93">
-        <v>6.0430000000000001</v>
+        <v>6.0942499999999997</v>
       </c>
       <c r="L12" s="93">
-        <v>5.9904999999999999</v>
+        <v>6.085</v>
       </c>
       <c r="M12" s="93">
-        <v>6.0034999999999998</v>
+        <v>6.0754999999999999</v>
       </c>
       <c r="N12" s="93">
-        <v>6.0620000000000003</v>
+        <v>6.1319999999999997</v>
       </c>
       <c r="O12" s="93">
-        <v>5.9965000000000002</v>
+        <v>6.0754999999999999</v>
       </c>
       <c r="P12" s="93">
-        <v>13372</v>
+        <v>7554</v>
       </c>
       <c r="Q12" s="93"/>
       <c r="R12" s="93"/>
@@ -7412,7 +7416,7 @@
       <c r="T12" s="93"/>
       <c r="U12" s="93"/>
       <c r="V12" s="92">
-        <v>46126.504861111112</v>
+        <v>46128.481365740743</v>
       </c>
       <c r="W12" s="1" t="s">
         <v>258</v>
@@ -7441,31 +7445,31 @@
         <v>59</v>
       </c>
       <c r="H13" s="93">
-        <v>442.25</v>
+        <v>450.75</v>
       </c>
       <c r="I13" s="93">
-        <v>442.25</v>
+        <v>450.75</v>
       </c>
       <c r="J13" s="93">
-        <v>442.5</v>
+        <v>451</v>
       </c>
       <c r="K13" s="93">
-        <v>442.375</v>
+        <v>450.875</v>
       </c>
       <c r="L13" s="93">
-        <v>440.25</v>
+        <v>451.25</v>
       </c>
       <c r="M13" s="93">
-        <v>440.5</v>
+        <v>451</v>
       </c>
       <c r="N13" s="93">
-        <v>443.25</v>
+        <v>452.75</v>
       </c>
       <c r="O13" s="93">
-        <v>440.25</v>
+        <v>449.75</v>
       </c>
       <c r="P13" s="93">
-        <v>12892</v>
+        <v>21091</v>
       </c>
       <c r="Q13" s="93"/>
       <c r="R13" s="93"/>
@@ -7473,7 +7477,7 @@
       <c r="T13" s="93"/>
       <c r="U13" s="93"/>
       <c r="V13" s="92">
-        <v>46126.504861111112</v>
+        <v>46128.481365740743</v>
       </c>
       <c r="W13" s="1" t="s">
         <v>258</v>
@@ -7502,31 +7506,31 @@
         <v>59</v>
       </c>
       <c r="H14" s="93">
-        <v>583</v>
+        <v>602.25</v>
       </c>
       <c r="I14" s="93">
-        <v>583</v>
+        <v>602</v>
       </c>
       <c r="J14" s="93">
-        <v>583.5</v>
+        <v>602.25</v>
       </c>
       <c r="K14" s="93">
-        <v>583.25</v>
+        <v>602.125</v>
       </c>
       <c r="L14" s="93">
-        <v>582.25</v>
+        <v>593.75</v>
       </c>
       <c r="M14" s="93">
-        <v>581.5</v>
+        <v>593</v>
       </c>
       <c r="N14" s="93">
-        <v>585.25</v>
+        <v>602.75</v>
       </c>
       <c r="O14" s="93">
-        <v>578.5</v>
+        <v>590.75</v>
       </c>
       <c r="P14" s="93">
-        <v>6982</v>
+        <v>8824</v>
       </c>
       <c r="Q14" s="93"/>
       <c r="R14" s="93"/>
@@ -7534,7 +7538,7 @@
       <c r="T14" s="93"/>
       <c r="U14" s="93"/>
       <c r="V14" s="92">
-        <v>46126.504861111112</v>
+        <v>46128.481365740743</v>
       </c>
       <c r="W14" s="1" t="s">
         <v>258</v>
@@ -7563,31 +7567,31 @@
         <v>59</v>
       </c>
       <c r="H15" s="93">
-        <v>1163.5</v>
+        <v>1166.25</v>
       </c>
       <c r="I15" s="93">
-        <v>1163.5</v>
+        <v>1166.25</v>
       </c>
       <c r="J15" s="93">
-        <v>1163.75</v>
+        <v>1166.5</v>
       </c>
       <c r="K15" s="93">
-        <v>1163.625</v>
+        <v>1166.375</v>
       </c>
       <c r="L15" s="93">
-        <v>1162.25</v>
+        <v>1167</v>
       </c>
       <c r="M15" s="93">
-        <v>1160.5</v>
+        <v>1165.75</v>
       </c>
       <c r="N15" s="93">
-        <v>1165.75</v>
+        <v>1169.5</v>
       </c>
       <c r="O15" s="93">
-        <v>1158.25</v>
+        <v>1164</v>
       </c>
       <c r="P15" s="93">
-        <v>14916</v>
+        <v>25067</v>
       </c>
       <c r="Q15" s="93"/>
       <c r="R15" s="93"/>
@@ -7595,7 +7599,7 @@
       <c r="T15" s="93"/>
       <c r="U15" s="93"/>
       <c r="V15" s="92">
-        <v>46126.504861111112</v>
+        <v>46128.481365740743</v>
       </c>
       <c r="W15" s="1" t="s">
         <v>258</v>
@@ -7624,31 +7628,31 @@
         <v>59</v>
       </c>
       <c r="H16" s="93">
-        <v>13.84</v>
+        <v>13.63</v>
       </c>
       <c r="I16" s="93">
-        <v>13.83</v>
+        <v>13.62</v>
       </c>
       <c r="J16" s="93">
-        <v>13.84</v>
+        <v>13.63</v>
       </c>
       <c r="K16" s="93">
-        <v>13.835000000000001</v>
+        <v>13.625</v>
       </c>
       <c r="L16" s="93">
+        <v>13.51</v>
+      </c>
+      <c r="M16" s="93">
+        <v>13.58</v>
+      </c>
+      <c r="N16" s="93">
         <v>13.68</v>
       </c>
-      <c r="M16" s="93">
-        <v>13.63</v>
-      </c>
-      <c r="N16" s="93">
-        <v>13.87</v>
-      </c>
       <c r="O16" s="93">
-        <v>13.62</v>
+        <v>13.55</v>
       </c>
       <c r="P16" s="93">
-        <v>18098</v>
+        <v>6355</v>
       </c>
       <c r="Q16" s="93"/>
       <c r="R16" s="93"/>
@@ -7656,7 +7660,7 @@
       <c r="T16" s="93"/>
       <c r="U16" s="93"/>
       <c r="V16" s="92">
-        <v>46126.504861111112</v>
+        <v>46128.481365740743</v>
       </c>
       <c r="W16" s="1" t="s">
         <v>258</v>
@@ -7685,31 +7689,31 @@
         <v>59</v>
       </c>
       <c r="H17" s="93">
-        <v>304.39999999999998</v>
+        <v>299.35000000000002</v>
       </c>
       <c r="I17" s="93">
-        <v>304.2</v>
+        <v>299.2</v>
       </c>
       <c r="J17" s="93">
-        <v>304.45</v>
+        <v>299.35000000000002</v>
       </c>
       <c r="K17" s="93">
-        <v>304.32499999999999</v>
+        <v>299.27499999999998</v>
       </c>
       <c r="L17" s="93">
-        <v>300.85000000000002</v>
+        <v>304.25</v>
       </c>
       <c r="M17" s="93">
-        <v>300</v>
+        <v>302.75</v>
       </c>
       <c r="N17" s="93">
-        <v>304.89999999999998</v>
+        <v>303.60000000000002</v>
       </c>
       <c r="O17" s="93">
-        <v>299.85000000000002</v>
+        <v>298.8</v>
       </c>
       <c r="P17" s="93">
-        <v>1301</v>
+        <v>457</v>
       </c>
       <c r="Q17" s="93"/>
       <c r="R17" s="93"/>
@@ -7717,7 +7721,7 @@
       <c r="T17" s="93"/>
       <c r="U17" s="93"/>
       <c r="V17" s="92">
-        <v>46126.504861111112</v>
+        <v>46128.481365740743</v>
       </c>
       <c r="W17" s="1" t="s">
         <v>258</v>
@@ -7746,31 +7750,31 @@
         <v>59</v>
       </c>
       <c r="H18" s="93">
-        <v>3302</v>
+        <v>3469</v>
       </c>
       <c r="I18" s="93">
-        <v>3300</v>
+        <v>3469</v>
       </c>
       <c r="J18" s="93">
-        <v>3303</v>
+        <v>3473</v>
       </c>
       <c r="K18" s="93">
-        <v>3301.5</v>
+        <v>3471</v>
       </c>
       <c r="L18" s="93">
-        <v>3278</v>
+        <v>3477</v>
       </c>
       <c r="M18" s="93">
-        <v>3281</v>
+        <v>3436</v>
       </c>
       <c r="N18" s="93">
-        <v>3311</v>
+        <v>3473</v>
       </c>
       <c r="O18" s="93">
-        <v>3272</v>
+        <v>3367</v>
       </c>
       <c r="P18" s="93">
-        <v>873</v>
+        <v>293</v>
       </c>
       <c r="Q18" s="93"/>
       <c r="R18" s="93"/>
@@ -7778,7 +7782,7 @@
       <c r="T18" s="93"/>
       <c r="U18" s="93"/>
       <c r="V18" s="92">
-        <v>46126.504861111112</v>
+        <v>46128.481365740743</v>
       </c>
       <c r="W18" s="1" t="s">
         <v>258</v>
@@ -7807,31 +7811,31 @@
         <v>59</v>
       </c>
       <c r="H19" s="93">
-        <v>74.88</v>
+        <v>75.92</v>
       </c>
       <c r="I19" s="93">
-        <v>74.86</v>
+        <v>75.91</v>
       </c>
       <c r="J19" s="93">
-        <v>74.89</v>
+        <v>75.930000000000007</v>
       </c>
       <c r="K19" s="93">
-        <v>74.875</v>
+        <v>75.92</v>
       </c>
       <c r="L19" s="93">
-        <v>74.53</v>
+        <v>75.11</v>
       </c>
       <c r="M19" s="93">
-        <v>74.53</v>
+        <v>75.150000000000006</v>
       </c>
       <c r="N19" s="93">
-        <v>74.97</v>
+        <v>76.09</v>
       </c>
       <c r="O19" s="93">
-        <v>74.459999999999994</v>
+        <v>75.08</v>
       </c>
       <c r="P19" s="93">
-        <v>3576</v>
+        <v>1977</v>
       </c>
       <c r="Q19" s="93"/>
       <c r="R19" s="93"/>
@@ -7839,7 +7843,7 @@
       <c r="T19" s="93"/>
       <c r="U19" s="93"/>
       <c r="V19" s="92">
-        <v>46126.504861111112</v>
+        <v>46128.481365740743</v>
       </c>
       <c r="W19" s="1" t="s">
         <v>258</v>
@@ -7880,19 +7884,19 @@
         <v>-100</v>
       </c>
       <c r="L20" s="93">
-        <v>250.65</v>
+        <v>252.6</v>
       </c>
       <c r="M20" s="93">
-        <v>250.8</v>
+        <v>252.55</v>
       </c>
       <c r="N20" s="93">
-        <v>251.57499999999999</v>
+        <v>253.52500000000001</v>
       </c>
       <c r="O20" s="93">
-        <v>250.5</v>
+        <v>251.55</v>
       </c>
       <c r="P20" s="93">
-        <v>5037</v>
+        <v>2158</v>
       </c>
       <c r="Q20" s="93"/>
       <c r="R20" s="93"/>
@@ -7900,7 +7904,7 @@
       <c r="T20" s="93"/>
       <c r="U20" s="93"/>
       <c r="V20" s="92">
-        <v>46126.504861111112</v>
+        <v>46128.481365740743</v>
       </c>
       <c r="W20" s="1" t="s">
         <v>258</v>
@@ -7941,19 +7945,15 @@
         <v>-100</v>
       </c>
       <c r="L21" s="93">
-        <v>372.82499999999999</v>
+        <v>370.95</v>
       </c>
       <c r="M21" s="93">
-        <v>371.57499999999999</v>
-      </c>
-      <c r="N21" s="93">
-        <v>373.875</v>
-      </c>
-      <c r="O21" s="93">
-        <v>371.125</v>
-      </c>
+        <v>374.95</v>
+      </c>
+      <c r="N21" s="93"/>
+      <c r="O21" s="93"/>
       <c r="P21" s="93">
-        <v>8436</v>
+        <v>0</v>
       </c>
       <c r="Q21" s="93"/>
       <c r="R21" s="93"/>
@@ -7961,7 +7961,7 @@
       <c r="T21" s="93"/>
       <c r="U21" s="93"/>
       <c r="V21" s="92">
-        <v>46126.504861111112</v>
+        <v>46128.481365740743</v>
       </c>
       <c r="W21" s="1" t="s">
         <v>258</v>
@@ -7990,7 +7990,7 @@
         <v>59</v>
       </c>
       <c r="H22" s="93">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="I22" s="93">
         <v>-100</v>
@@ -8002,19 +8002,15 @@
         <v>-100</v>
       </c>
       <c r="L22" s="93">
-        <v>90.5</v>
+        <v>90.7</v>
       </c>
       <c r="M22" s="93">
-        <v>90.65</v>
-      </c>
-      <c r="N22" s="93">
-        <v>90.7</v>
-      </c>
-      <c r="O22" s="93">
-        <v>90.424999999999997</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N22" s="93"/>
+      <c r="O22" s="93"/>
       <c r="P22" s="93">
-        <v>3319</v>
+        <v>0</v>
       </c>
       <c r="Q22" s="93"/>
       <c r="R22" s="93"/>
@@ -8022,7 +8018,7 @@
       <c r="T22" s="93"/>
       <c r="U22" s="93"/>
       <c r="V22" s="92">
-        <v>46126.504861111112</v>
+        <v>46128.481365740743</v>
       </c>
       <c r="W22" s="1" t="s">
         <v>258</v>
@@ -8051,31 +8047,31 @@
         <v>59</v>
       </c>
       <c r="H23" s="93">
-        <v>97.94</v>
+        <v>97.974999999999994</v>
       </c>
       <c r="I23" s="93">
-        <v>97.935000000000002</v>
+        <v>97.984999999999999</v>
       </c>
       <c r="J23" s="93">
-        <v>97.944999999999993</v>
+        <v>97.99</v>
       </c>
       <c r="K23" s="93">
-        <v>97.94</v>
+        <v>97.987499999999997</v>
       </c>
       <c r="L23" s="93">
-        <v>98.165000000000006</v>
+        <v>97.85</v>
       </c>
       <c r="M23" s="93">
-        <v>98.15</v>
+        <v>97.82</v>
       </c>
       <c r="N23" s="93">
-        <v>98.2</v>
+        <v>98.004999999999995</v>
       </c>
       <c r="O23" s="93">
-        <v>97.894999999999996</v>
+        <v>97.63</v>
       </c>
       <c r="P23" s="93">
-        <v>8004</v>
+        <v>3910</v>
       </c>
       <c r="Q23" s="93"/>
       <c r="R23" s="93"/>
@@ -8083,7 +8079,7 @@
       <c r="T23" s="93"/>
       <c r="U23" s="93"/>
       <c r="V23" s="92">
-        <v>46126.504861111112</v>
+        <v>46128.481365740743</v>
       </c>
       <c r="W23" s="1" t="s">
         <v>258</v>
@@ -8112,31 +8108,31 @@
         <v>59</v>
       </c>
       <c r="H24" s="93">
-        <v>1.18215</v>
+        <v>1.1811499999999999</v>
       </c>
       <c r="I24" s="93">
-        <v>1.18215</v>
+        <v>1.1811</v>
       </c>
       <c r="J24" s="93">
-        <v>1.1821999999999999</v>
+        <v>1.1811499999999999</v>
       </c>
       <c r="K24" s="93">
-        <v>1.182175</v>
+        <v>1.181125</v>
       </c>
       <c r="L24" s="93">
-        <v>1.1799500000000001</v>
+        <v>1.1834499999999999</v>
       </c>
       <c r="M24" s="93">
-        <v>1.1795500000000001</v>
+        <v>1.1830000000000001</v>
       </c>
       <c r="N24" s="93">
-        <v>1.1831</v>
+        <v>1.1856500000000001</v>
       </c>
       <c r="O24" s="93">
-        <v>1.1790499999999999</v>
+        <v>1.18085</v>
       </c>
       <c r="P24" s="93">
-        <v>51192</v>
+        <v>39932</v>
       </c>
       <c r="Q24" s="93"/>
       <c r="R24" s="93"/>
@@ -8144,7 +8140,7 @@
       <c r="T24" s="93"/>
       <c r="U24" s="93"/>
       <c r="V24" s="92">
-        <v>46126.504861111112</v>
+        <v>46128.481365740743</v>
       </c>
       <c r="W24" s="1" t="s">
         <v>258</v>
@@ -8173,7 +8169,7 @@
         <v>59</v>
       </c>
       <c r="H25" s="93">
-        <v>1.3541000000000001</v>
+        <v>1.3542000000000001</v>
       </c>
       <c r="I25" s="93">
         <v>1.3541000000000001</v>
@@ -8185,19 +8181,19 @@
         <v>1.3541500000000002</v>
       </c>
       <c r="L25" s="93">
-        <v>1.3506</v>
+        <v>1.3573999999999999</v>
       </c>
       <c r="M25" s="93">
-        <v>1.3508</v>
+        <v>1.3554999999999999</v>
       </c>
       <c r="N25" s="93">
-        <v>1.355</v>
+        <v>1.3593</v>
       </c>
       <c r="O25" s="93">
-        <v>1.3503000000000001</v>
+        <v>1.3542000000000001</v>
       </c>
       <c r="P25" s="93">
-        <v>23606</v>
+        <v>20246</v>
       </c>
       <c r="Q25" s="93"/>
       <c r="R25" s="93"/>
@@ -8205,7 +8201,7 @@
       <c r="T25" s="93"/>
       <c r="U25" s="93"/>
       <c r="V25" s="92">
-        <v>46126.504861111112</v>
+        <v>46128.481365740743</v>
       </c>
       <c r="W25" s="1" t="s">
         <v>258</v>
@@ -8234,31 +8230,31 @@
         <v>59</v>
       </c>
       <c r="H26" s="93">
-        <v>6.3235000000000001E-3</v>
+        <v>6.3185000000000003E-3</v>
       </c>
       <c r="I26" s="93">
-        <v>6.3229999999999996E-3</v>
+        <v>6.3185000000000003E-3</v>
       </c>
       <c r="J26" s="93">
-        <v>6.3235000000000001E-3</v>
+        <v>6.319E-3</v>
       </c>
       <c r="K26" s="93">
-        <v>6.3232499999999999E-3</v>
+        <v>6.3187499999999997E-3</v>
       </c>
       <c r="L26" s="93">
-        <v>6.3099999999999996E-3</v>
+        <v>6.3210000000000002E-3</v>
       </c>
       <c r="M26" s="93">
-        <v>6.3064999999999996E-3</v>
+        <v>6.3245000000000003E-3</v>
       </c>
       <c r="N26" s="93">
-        <v>6.3284999999999999E-3</v>
+        <v>6.3499999999999997E-3</v>
       </c>
       <c r="O26" s="93">
-        <v>6.3055000000000003E-3</v>
+        <v>6.3165000000000001E-3</v>
       </c>
       <c r="P26" s="93">
-        <v>43031</v>
+        <v>57246</v>
       </c>
       <c r="Q26" s="93"/>
       <c r="R26" s="93"/>
@@ -8266,7 +8262,7 @@
       <c r="T26" s="93"/>
       <c r="U26" s="93"/>
       <c r="V26" s="92">
-        <v>46126.504861111112</v>
+        <v>46128.481365740743</v>
       </c>
       <c r="W26" s="1" t="s">
         <v>258</v>
@@ -8295,31 +8291,31 @@
         <v>59</v>
       </c>
       <c r="H27" s="93">
-        <v>0.72865000000000002</v>
+        <v>0.73014999999999997</v>
       </c>
       <c r="I27" s="93">
-        <v>0.72865000000000002</v>
+        <v>0.73009999999999997</v>
       </c>
       <c r="J27" s="93">
-        <v>0.72870000000000001</v>
+        <v>0.73014999999999997</v>
       </c>
       <c r="K27" s="93">
-        <v>0.72867499999999996</v>
+        <v>0.73012499999999991</v>
       </c>
       <c r="L27" s="93">
-        <v>0.72709999999999997</v>
+        <v>0.73024999999999995</v>
       </c>
       <c r="M27" s="93">
-        <v>0.72704999999999997</v>
+        <v>0.7298</v>
       </c>
       <c r="N27" s="93">
-        <v>0.72875000000000001</v>
+        <v>0.73114999999999997</v>
       </c>
       <c r="O27" s="93">
-        <v>0.72704999999999997</v>
+        <v>0.72975000000000001</v>
       </c>
       <c r="P27" s="93">
-        <v>9757</v>
+        <v>8273</v>
       </c>
       <c r="Q27" s="93"/>
       <c r="R27" s="93"/>
@@ -8327,7 +8323,7 @@
       <c r="T27" s="93"/>
       <c r="U27" s="93"/>
       <c r="V27" s="92">
-        <v>46126.504861111112</v>
+        <v>46128.481365740743</v>
       </c>
       <c r="W27" s="1" t="s">
         <v>258</v>
@@ -8356,31 +8352,31 @@
         <v>59</v>
       </c>
       <c r="H28" s="93">
-        <v>0.71060000000000001</v>
+        <v>0.71625000000000005</v>
       </c>
       <c r="I28" s="93">
-        <v>0.71055000000000001</v>
+        <v>0.71619999999999995</v>
       </c>
       <c r="J28" s="93">
-        <v>0.71060000000000001</v>
+        <v>0.71625000000000005</v>
       </c>
       <c r="K28" s="93">
-        <v>0.71057499999999996</v>
+        <v>0.716225</v>
       </c>
       <c r="L28" s="93">
-        <v>0.70925000000000005</v>
+        <v>0.71679999999999999</v>
       </c>
       <c r="M28" s="93">
-        <v>0.70914999999999995</v>
+        <v>0.71640000000000004</v>
       </c>
       <c r="N28" s="93">
-        <v>0.71074999999999999</v>
+        <v>0.71909999999999996</v>
       </c>
       <c r="O28" s="93">
-        <v>0.70699999999999996</v>
+        <v>0.7157</v>
       </c>
       <c r="P28" s="93">
-        <v>38634</v>
+        <v>42282</v>
       </c>
       <c r="Q28" s="93"/>
       <c r="R28" s="93"/>
@@ -8388,7 +8384,7 @@
       <c r="T28" s="93"/>
       <c r="U28" s="93"/>
       <c r="V28" s="92">
-        <v>46126.504861111112</v>
+        <v>46128.481365740743</v>
       </c>
       <c r="W28" s="1" t="s">
         <v>258</v>
@@ -8417,31 +8413,31 @@
         <v>59</v>
       </c>
       <c r="H29" s="93">
-        <v>114.3125</v>
+        <v>114.15625</v>
       </c>
       <c r="I29" s="93">
-        <v>114.3125</v>
+        <v>114.125</v>
       </c>
       <c r="J29" s="93">
+        <v>114.15625</v>
+      </c>
+      <c r="K29" s="93">
+        <v>114.140625</v>
+      </c>
+      <c r="L29" s="93">
         <v>114.34375</v>
       </c>
-      <c r="K29" s="93">
-        <v>114.328125</v>
-      </c>
-      <c r="L29" s="93">
-        <v>114.0625</v>
-      </c>
       <c r="M29" s="93">
-        <v>114.125</v>
+        <v>114.1875</v>
       </c>
       <c r="N29" s="93">
-        <v>114.53125</v>
+        <v>114.46875</v>
       </c>
       <c r="O29" s="93">
-        <v>114.09375</v>
+        <v>114.15625</v>
       </c>
       <c r="P29" s="93">
-        <v>49589</v>
+        <v>31155</v>
       </c>
       <c r="Q29" s="93"/>
       <c r="R29" s="93"/>
@@ -8449,7 +8445,7 @@
       <c r="T29" s="93"/>
       <c r="U29" s="93"/>
       <c r="V29" s="92">
-        <v>46126.504861111112</v>
+        <v>46128.481365740743</v>
       </c>
       <c r="W29" s="1" t="s">
         <v>258</v>
@@ -8478,31 +8474,31 @@
         <v>59</v>
       </c>
       <c r="H30" s="93">
+        <v>111.390625</v>
+      </c>
+      <c r="I30" s="93">
+        <v>111.375</v>
+      </c>
+      <c r="J30" s="93">
+        <v>111.390625</v>
+      </c>
+      <c r="K30" s="93">
+        <v>111.3828125</v>
+      </c>
+      <c r="L30" s="93">
+        <v>111.359375</v>
+      </c>
+      <c r="M30" s="93">
+        <v>111.359375</v>
+      </c>
+      <c r="N30" s="93">
+        <v>111.53125</v>
+      </c>
+      <c r="O30" s="93">
         <v>111.34375</v>
       </c>
-      <c r="I30" s="93">
-        <v>111.328125</v>
-      </c>
-      <c r="J30" s="93">
-        <v>111.34375</v>
-      </c>
-      <c r="K30" s="93">
-        <v>111.3359375</v>
-      </c>
-      <c r="L30" s="93">
-        <v>111.234375</v>
-      </c>
-      <c r="M30" s="93">
-        <v>111.25</v>
-      </c>
-      <c r="N30" s="93">
-        <v>111.453125</v>
-      </c>
-      <c r="O30" s="93">
-        <v>111.234375</v>
-      </c>
       <c r="P30" s="93">
-        <v>270108</v>
+        <v>187972</v>
       </c>
       <c r="Q30" s="93"/>
       <c r="R30" s="93"/>
@@ -8510,7 +8506,7 @@
       <c r="T30" s="93"/>
       <c r="U30" s="93"/>
       <c r="V30" s="92">
-        <v>46126.504861111112</v>
+        <v>46128.481365740743</v>
       </c>
       <c r="W30" s="1" t="s">
         <v>258</v>
@@ -8539,31 +8535,31 @@
         <v>56</v>
       </c>
       <c r="H31" s="93">
-        <v>125.09</v>
+        <v>125.44</v>
       </c>
       <c r="I31" s="93">
-        <v>125.09</v>
+        <v>125.44</v>
       </c>
       <c r="J31" s="93">
-        <v>125.1</v>
+        <v>125.45</v>
       </c>
       <c r="K31" s="93">
-        <v>125.095</v>
+        <v>125.44499999999999</v>
       </c>
       <c r="L31" s="93">
-        <v>124.75</v>
+        <v>125.29</v>
       </c>
       <c r="M31" s="93">
-        <v>125.1</v>
+        <v>125.32</v>
       </c>
       <c r="N31" s="93">
-        <v>125.25</v>
+        <v>125.62</v>
       </c>
       <c r="O31" s="93">
-        <v>125.03</v>
+        <v>125.32</v>
       </c>
       <c r="P31" s="93">
-        <v>331548</v>
+        <v>279289</v>
       </c>
       <c r="Q31" s="93"/>
       <c r="R31" s="93"/>
@@ -8571,7 +8567,7 @@
       <c r="T31" s="93"/>
       <c r="U31" s="93"/>
       <c r="V31" s="92">
-        <v>46126.504861111112</v>
+        <v>46128.481365740743</v>
       </c>
       <c r="W31" s="1" t="s">
         <v>258</v>
@@ -8600,31 +8596,31 @@
         <v>56</v>
       </c>
       <c r="H32" s="93">
-        <v>107.72</v>
+        <v>107.8</v>
       </c>
       <c r="I32" s="93">
-        <v>107.72</v>
+        <v>107.78</v>
       </c>
       <c r="J32" s="93">
-        <v>107.74</v>
+        <v>107.8</v>
       </c>
       <c r="K32" s="93">
-        <v>107.72999999999999</v>
+        <v>107.78999999999999</v>
       </c>
       <c r="L32" s="93">
-        <v>107.26</v>
+        <v>107.62</v>
       </c>
       <c r="M32" s="93">
-        <v>107.82</v>
+        <v>107.6</v>
       </c>
       <c r="N32" s="93">
-        <v>108.16</v>
+        <v>108.04</v>
       </c>
       <c r="O32" s="93">
-        <v>107.62</v>
+        <v>107.52</v>
       </c>
       <c r="P32" s="93">
-        <v>46968</v>
+        <v>45454</v>
       </c>
       <c r="Q32" s="93"/>
       <c r="R32" s="93"/>
@@ -8632,7 +8628,7 @@
       <c r="T32" s="93"/>
       <c r="U32" s="93"/>
       <c r="V32" s="92">
-        <v>46126.504861111112</v>
+        <v>46128.481365740743</v>
       </c>
       <c r="W32" s="1" t="s">
         <v>258</v>
@@ -8661,31 +8657,31 @@
         <v>56</v>
       </c>
       <c r="H33" s="93">
-        <v>117.16</v>
+        <v>117.53</v>
       </c>
       <c r="I33" s="93">
-        <v>117.15</v>
+        <v>117.53</v>
       </c>
       <c r="J33" s="93">
-        <v>117.17</v>
+        <v>117.54</v>
       </c>
       <c r="K33" s="93">
-        <v>117.16</v>
+        <v>117.535</v>
       </c>
       <c r="L33" s="93">
-        <v>116.7</v>
+        <v>117.38</v>
       </c>
       <c r="M33" s="93">
-        <v>117.21</v>
+        <v>117.46</v>
       </c>
       <c r="N33" s="93">
-        <v>117.43</v>
+        <v>117.79</v>
       </c>
       <c r="O33" s="93">
-        <v>117.09</v>
+        <v>117.46</v>
       </c>
       <c r="P33" s="93">
-        <v>103194</v>
+        <v>85988</v>
       </c>
       <c r="Q33" s="93"/>
       <c r="R33" s="93"/>
@@ -8693,7 +8689,7 @@
       <c r="T33" s="93"/>
       <c r="U33" s="93"/>
       <c r="V33" s="92">
-        <v>46126.504861111112</v>
+        <v>46128.481365740743</v>
       </c>
       <c r="W33" s="1" t="s">
         <v>258</v>
@@ -8722,29 +8718,29 @@
         <v>59</v>
       </c>
       <c r="H34" s="93">
-        <v>74524.5</v>
+        <v>74821.5</v>
       </c>
       <c r="I34" s="93">
-        <v>74524.5</v>
+        <v>74821.25</v>
       </c>
       <c r="J34" s="93">
-        <v>74524.75</v>
+        <v>74821.5</v>
       </c>
       <c r="K34" s="93">
-        <v>74524.625</v>
+        <v>74821.375</v>
       </c>
       <c r="L34" s="93">
-        <v>73382</v>
+        <v>75012.5</v>
       </c>
       <c r="M34" s="93"/>
       <c r="N34" s="93">
-        <v>75425.25</v>
+        <v>75446.5</v>
       </c>
       <c r="O34" s="93">
-        <v>72410.75</v>
+        <v>73937.5</v>
       </c>
       <c r="P34" s="93">
-        <v>116.62393998</v>
+        <v>62.95814507</v>
       </c>
       <c r="Q34" s="93"/>
       <c r="R34" s="93"/>
@@ -8752,7 +8748,7 @@
       <c r="T34" s="93"/>
       <c r="U34" s="93"/>
       <c r="V34" s="92">
-        <v>46126.504861111112</v>
+        <v>46128.481365740743</v>
       </c>
       <c r="W34" s="1" t="s">
         <v>258</v>
@@ -8781,29 +8777,29 @@
         <v>59</v>
       </c>
       <c r="H35" s="93">
-        <v>2386.4499999999998</v>
+        <v>2346.4499999999998</v>
       </c>
       <c r="I35" s="93">
-        <v>2386.4</v>
+        <v>2346.0500000000002</v>
       </c>
       <c r="J35" s="93">
-        <v>2386.4499999999998</v>
+        <v>2346.1</v>
       </c>
       <c r="K35" s="93">
-        <v>2386.4250000000002</v>
+        <v>2346.0749999999998</v>
       </c>
       <c r="L35" s="93">
-        <v>2264.0500000000002</v>
+        <v>2375.0500000000002</v>
       </c>
       <c r="M35" s="93"/>
       <c r="N35" s="93">
-        <v>2396</v>
+        <v>2386.85</v>
       </c>
       <c r="O35" s="93">
-        <v>2220.6999999999998</v>
+        <v>2323.9499999999998</v>
       </c>
       <c r="P35" s="93">
-        <v>2064.2883861099999</v>
+        <v>1263.4804576199999</v>
       </c>
       <c r="Q35" s="93"/>
       <c r="R35" s="93"/>
@@ -8811,7 +8807,7 @@
       <c r="T35" s="93"/>
       <c r="U35" s="93"/>
       <c r="V35" s="92">
-        <v>46126.504861111112</v>
+        <v>46128.481365740743</v>
       </c>
       <c r="W35" s="1" t="s">
         <v>258</v>
@@ -8840,47 +8836,47 @@
         <v>59</v>
       </c>
       <c r="H36" s="93">
-        <v>1.1100000000000001</v>
+        <v>1.33</v>
       </c>
       <c r="I36" s="93">
-        <v>1.04</v>
+        <v>1.28</v>
       </c>
       <c r="J36" s="93">
-        <v>1.08</v>
+        <v>1.31</v>
       </c>
       <c r="K36" s="93">
-        <v>1.06</v>
+        <v>1.2949999999999999</v>
       </c>
       <c r="L36" s="93">
-        <v>1.1599999999999999</v>
+        <v>1.41</v>
       </c>
       <c r="M36" s="93"/>
       <c r="N36" s="93">
-        <v>1.3</v>
+        <v>1.46</v>
       </c>
       <c r="O36" s="93">
-        <v>1.0900000000000001</v>
+        <v>1.28</v>
       </c>
       <c r="P36" s="93">
-        <v>247</v>
+        <v>95</v>
       </c>
       <c r="Q36" s="93">
-        <v>0.65071262857332568</v>
+        <v>0.63865588978220611</v>
       </c>
       <c r="R36" s="93">
-        <v>-0.1184779896216942</v>
+        <v>-0.14465314617937799</v>
       </c>
       <c r="S36" s="93">
-        <v>1.1499937873466953E-2</v>
+        <v>1.4388128895769861E-2</v>
       </c>
       <c r="T36" s="93">
-        <v>5.1829289229028186E-2</v>
+        <v>6.0347494708476113E-2</v>
       </c>
       <c r="U36" s="93">
-        <v>-5.5921335989600918E-2</v>
+        <v>-6.8421829273718204E-2</v>
       </c>
       <c r="V36" s="92">
-        <v>46126.504861111112</v>
+        <v>46128.481365740743</v>
       </c>
       <c r="W36" s="1" t="s">
         <v>258</v>
@@ -8909,47 +8905,37 @@
         <v>59</v>
       </c>
       <c r="H37" s="93">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="I37" s="93">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="J37" s="93">
+        <v>0.1</v>
+      </c>
+      <c r="K37" s="93">
+        <v>9.5000000000000001E-2</v>
+      </c>
+      <c r="L37" s="93">
         <v>0.12</v>
-      </c>
-      <c r="K37" s="93">
-        <v>0.1</v>
-      </c>
-      <c r="L37" s="93">
-        <v>0.11</v>
       </c>
       <c r="M37" s="93"/>
       <c r="N37" s="93">
         <v>0.1</v>
       </c>
       <c r="O37" s="93">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="P37" s="93">
-        <v>10</v>
-      </c>
-      <c r="Q37" s="93">
-        <v>0.8513149860951863</v>
-      </c>
-      <c r="R37" s="93">
-        <v>-1.3105612197684545E-2</v>
-      </c>
-      <c r="S37" s="93">
-        <v>1.4916616787043501E-3</v>
-      </c>
-      <c r="T37" s="93">
-        <v>8.7953426945819174E-3</v>
-      </c>
-      <c r="U37" s="93">
-        <v>-1.2430105641466668E-2</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="Q37" s="93"/>
+      <c r="R37" s="93"/>
+      <c r="S37" s="93"/>
+      <c r="T37" s="93"/>
+      <c r="U37" s="93"/>
       <c r="V37" s="92">
-        <v>46126.504861111112</v>
+        <v>46128.481365740743</v>
       </c>
       <c r="W37" s="1" t="s">
         <v>258</v>
@@ -8957,7 +8943,7 @@
     </row>
     <row r="38" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A38" s="1" t="s">
-        <v>333</v>
+        <v>325</v>
       </c>
       <c r="B38" s="1">
         <v>766128347</v>
@@ -8969,7 +8955,7 @@
         <v>26</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>333</v>
+        <v>325</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>80</v>
@@ -8978,43 +8964,47 @@
         <v>59</v>
       </c>
       <c r="H38" s="93">
-        <v>-1</v>
+        <v>16.399999999999999</v>
       </c>
       <c r="I38" s="93">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="J38" s="93">
-        <v>15.1</v>
+        <v>15.9</v>
       </c>
       <c r="K38" s="93">
-        <v>14.5</v>
+        <v>15.25</v>
       </c>
       <c r="L38" s="93">
-        <v>14.8</v>
+        <v>16.399999999999999</v>
       </c>
       <c r="M38" s="93"/>
-      <c r="N38" s="93"/>
-      <c r="O38" s="93"/>
+      <c r="N38" s="93">
+        <v>17.399999999999999</v>
+      </c>
+      <c r="O38" s="93">
+        <v>16.399999999999999</v>
+      </c>
       <c r="P38" s="93">
-        <v>204</v>
+        <v>103</v>
       </c>
       <c r="Q38" s="93">
-        <v>0.27068357977697705</v>
+        <v>0.27093050918244271</v>
       </c>
       <c r="R38" s="93">
-        <v>7.7067933026295235E-2</v>
+        <v>8.0287505687109614E-2</v>
       </c>
       <c r="S38" s="93">
-        <v>3.2653444437705595E-4</v>
+        <v>3.433257159560456E-4</v>
       </c>
       <c r="T38" s="93">
-        <v>2.2499243906596273</v>
+        <v>2.337249328106962</v>
       </c>
       <c r="U38" s="93">
-        <v>-0.72244380295831157</v>
+        <v>-0.74355577437130016</v>
       </c>
       <c r="V38" s="92">
-        <v>46126.504861111112</v>
+        <v>46128.481365740743</v>
       </c>
       <c r="W38" s="1" t="s">
         <v>258</v>
@@ -9022,7 +9012,7 @@
     </row>
     <row r="39" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A39" s="1" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="B39" s="1">
         <v>842622669</v>
@@ -9034,7 +9024,7 @@
         <v>26</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>80</v>
@@ -9046,16 +9036,16 @@
         <v>-1</v>
       </c>
       <c r="I39" s="93">
-        <v>107.2</v>
+        <v>114.2</v>
       </c>
       <c r="J39" s="93">
-        <v>109.1</v>
+        <v>116.5</v>
       </c>
       <c r="K39" s="93">
-        <v>108.15</v>
+        <v>115.35</v>
       </c>
       <c r="L39" s="93">
-        <v>100.8</v>
+        <v>116.5</v>
       </c>
       <c r="M39" s="93"/>
       <c r="N39" s="93"/>
@@ -9064,22 +9054,22 @@
         <v>0</v>
       </c>
       <c r="Q39" s="93">
-        <v>0.24691358230929086</v>
+        <v>0.24180469956730305</v>
       </c>
       <c r="R39" s="93">
-        <v>0.39384066193424688</v>
+        <v>0.41350082272940392</v>
       </c>
       <c r="S39" s="93">
-        <v>9.52843764058605E-4</v>
+        <v>1.0049341986775498E-3</v>
       </c>
       <c r="T39" s="93">
-        <v>6.3015772685447331</v>
+        <v>6.174061775384672</v>
       </c>
       <c r="U39" s="93">
-        <v>-1.8391102586627426</v>
+        <v>-1.8525787677119467</v>
       </c>
       <c r="V39" s="92">
-        <v>46126.504861111112</v>
+        <v>46128.481365740743</v>
       </c>
       <c r="W39" s="1" t="s">
         <v>258</v>
@@ -9204,7 +9194,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C571DE7A-BF08-4200-BB11-61B452324713}">
-  <dimension ref="A1:C62"/>
+  <dimension ref="A1:C68"/>
   <sheetFormatPr defaultRowHeight="13.15" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="22" style="81" customWidth="1"/>
@@ -9226,674 +9216,300 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A2" s="87">
-        <v>46111.432708333334</v>
+        <v>46127.469976851855</v>
       </c>
       <c r="B2" s="84" t="s">
-        <v>321</v>
+        <v>342</v>
       </c>
       <c r="C2" s="84" t="s">
-        <v>322</v>
+        <v>343</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A3" s="87">
-        <v>46111.432708333334</v>
+        <v>46127.469976851855</v>
       </c>
       <c r="B3" s="84" t="s">
-        <v>321</v>
+        <v>342</v>
       </c>
       <c r="C3" s="84" t="s">
-        <v>323</v>
+        <v>344</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A4" s="87">
-        <v>46111.432708333334</v>
+        <v>46127.469988425924</v>
       </c>
       <c r="B4" s="84" t="s">
-        <v>321</v>
+        <v>342</v>
       </c>
       <c r="C4" s="84" t="s">
-        <v>324</v>
+        <v>345</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A5" s="85">
-        <v>46112.439131944448</v>
+        <v>46127.471296296295</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>321</v>
+        <v>342</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>322</v>
+        <v>343</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A6" s="85">
-        <v>46112.439143518517</v>
+        <v>46127.471307870372</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>321</v>
+        <v>342</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>323</v>
+        <v>344</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A7" s="85">
-        <v>46112.439143518517</v>
+        <v>46127.471307870372</v>
       </c>
       <c r="B7" s="81" t="s">
-        <v>321</v>
+        <v>342</v>
       </c>
       <c r="C7" s="81" t="s">
-        <v>324</v>
+        <v>345</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A8" s="85">
-        <v>46112.441157407404</v>
+        <v>46127.475798611114</v>
       </c>
       <c r="B8" s="81" t="s">
-        <v>328</v>
+        <v>342</v>
       </c>
       <c r="C8" s="81" t="s">
-        <v>329</v>
+        <v>343</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A9" s="85">
-        <v>46112.441192129627</v>
+        <v>46127.475798611114</v>
       </c>
       <c r="B9" s="81" t="s">
-        <v>321</v>
+        <v>342</v>
       </c>
       <c r="C9" s="81" t="s">
-        <v>330</v>
+        <v>344</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A10" s="85">
-        <v>46112.441736111112</v>
+        <v>46127.475810185184</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>321</v>
+        <v>342</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>322</v>
+        <v>345</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A11" s="85">
-        <v>46112.441736111112</v>
+        <v>46128.480752314812</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>321</v>
+        <v>342</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>323</v>
+        <v>343</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A12" s="85">
-        <v>46112.441736111112</v>
+        <v>46128.480763888889</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>321</v>
+        <v>342</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>324</v>
+        <v>344</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A13" s="85">
-        <v>46112.442106481481</v>
+        <v>46128.480763888889</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>321</v>
+        <v>342</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>322</v>
+        <v>345</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A14" s="85">
-        <v>46112.442106481481</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>323</v>
-      </c>
+      <c r="A14" s="85"/>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A15" s="85">
-        <v>46112.442106481481</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>324</v>
-      </c>
+      <c r="A15" s="85"/>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A16" s="85">
-        <v>46112.442442129628</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>328</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A17" s="85">
-        <v>46112.442476851851</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A18" s="85">
-        <v>46112.443182870367</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>328</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A19" s="85">
-        <v>46112.443206018521</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A20" s="85">
-        <v>46112.784872685188</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A21" s="85">
-        <v>46112.784872685188</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A22" s="85">
-        <v>46112.784872685188</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A23" s="85">
-        <v>46113.463761574072</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A24" s="85">
-        <v>46113.463773148149</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A25" s="85">
-        <v>46113.463784722226</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A26" s="85">
-        <v>46113.464155092595</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>328</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A27" s="85">
-        <v>46113.464178240742</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A28" s="85">
-        <v>46114.494803240741</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A29" s="85">
-        <v>46114.494814814818</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A30" s="85">
-        <v>46114.494814814818</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A31" s="85">
-        <v>46115.523900462962</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A32" s="85">
-        <v>46115.523900462962</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A33" s="85">
-        <v>46115.523912037039</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A34" s="85">
-        <v>46115.524907407409</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>328</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A35" s="85">
-        <v>46115.524930555555</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A36" s="85">
-        <v>46118.597337962965</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A37" s="85">
-        <v>46118.597349537034</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A38" s="85">
-        <v>46118.597349537034</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A39" s="85">
-        <v>46119.429062499999</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A40" s="85">
-        <v>46119.429062499999</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A41" s="85">
-        <v>46119.429074074076</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A42" s="85">
-        <v>46119.557905092595</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A43" s="85">
-        <v>46119.557962962965</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A44" s="85">
-        <v>46119.557962962965</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A45" s="85">
-        <v>46119.558692129627</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A46" s="85">
-        <v>46119.558703703704</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A47" s="85">
-        <v>46119.558703703704</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A48" s="85">
-        <v>46120.50880787037</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A49" s="85">
-        <v>46120.50880787037</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="C49" s="1" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A50" s="85">
-        <v>46120.508819444447</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A51" s="85">
-        <v>46122.466909722221</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A52" s="85">
-        <v>46122.466909722221</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="C52" s="1" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A53" s="85">
-        <v>46122.466921296298</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="C53" s="1" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A54" s="85">
-        <v>46123.422256944446</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="C54" s="1" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A55" s="85">
-        <v>46123.422268518516</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A56" s="85">
-        <v>46123.422268518516</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="C56" s="1" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A57" s="85">
-        <v>46125.516909722224</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A58" s="85">
-        <v>46125.516921296294</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A59" s="85">
-        <v>46125.516921296294</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="C59" s="1" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A60" s="85">
-        <v>46126.503923611112</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="C60" s="1" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A61" s="85">
-        <v>46126.503935185188</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="C61" s="1" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A62" s="85">
-        <v>46126.503935185188</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="C62" s="1" t="s">
-        <v>338</v>
-      </c>
+      <c r="A16" s="85"/>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A17" s="85"/>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A18" s="85"/>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A19" s="85"/>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A20" s="85"/>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A21" s="85"/>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A22" s="85"/>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A23" s="85"/>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A24" s="85"/>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A25" s="85"/>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A26" s="85"/>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A27" s="85"/>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A28" s="85"/>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A29" s="85"/>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A30" s="85"/>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A31" s="85"/>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A32" s="85"/>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A33" s="85"/>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A34" s="85"/>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A35" s="85"/>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A36" s="85"/>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A37" s="85"/>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A38" s="85"/>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A39" s="85"/>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A40" s="85"/>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A41" s="85"/>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A42" s="85"/>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A43" s="85"/>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A44" s="85"/>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A45" s="85"/>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A46" s="85"/>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A47" s="85"/>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A48" s="85"/>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A49" s="85"/>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A50" s="85"/>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A51" s="85"/>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A52" s="85"/>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A53" s="85"/>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A54" s="85"/>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A55" s="85"/>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A56" s="85"/>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A57" s="85"/>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A58" s="85"/>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A59" s="85"/>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A60" s="85"/>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A61" s="85"/>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A62" s="85"/>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A63" s="85"/>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A64" s="85"/>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A65" s="85"/>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A66" s="85"/>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A67" s="85"/>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A68" s="85"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9959,11 +9575,11 @@
       <c r="E4" s="10"/>
       <c r="F4" s="10"/>
       <c r="G4" s="15">
-        <v>599.25</v>
+        <v>895</v>
       </c>
       <c r="H4" s="6">
         <f>-G4</f>
-        <v>-599.25</v>
+        <v>-895</v>
       </c>
     </row>
     <row r="5" spans="2:8" x14ac:dyDescent="0.4">
@@ -10084,11 +9700,11 @@
       <c r="F13" s="10"/>
       <c r="G13" s="6">
         <f>SUM(G3:G12)</f>
-        <v>3948.9699999999543</v>
+        <v>4244.7199999999539</v>
       </c>
       <c r="H13" s="6">
         <f>SUM(H3:H12)</f>
-        <v>33651.029999999955</v>
+        <v>33355.279999999955</v>
       </c>
     </row>
   </sheetData>
@@ -10314,11 +9930,11 @@
       <c r="H6" s="67"/>
       <c r="I6" s="70">
         <f>Blotter!C$4-SUM(NAV!I$4:I5)</f>
-        <v>40219.810000000129</v>
+        <v>57333.059999999896</v>
       </c>
       <c r="J6" s="70">
         <f t="shared" ref="J6" si="9">E6-F6-G6-H6+I6</f>
-        <v>1068964.2606320111</v>
+        <v>1086077.5106320109</v>
       </c>
       <c r="K6" s="70">
         <f t="shared" ref="K6" si="10">K5+C6</f>
@@ -10326,19 +9942,19 @@
       </c>
       <c r="L6" s="71">
         <f t="shared" ref="L6" si="11">J6/K6</f>
-        <v>1068.964260632011</v>
+        <v>1086.0775106320109</v>
       </c>
       <c r="M6" s="72">
         <f t="shared" ref="M6" si="12">L6/$L$3-1</f>
-        <v>6.896426063201111E-2</v>
+        <v>8.6077510632010856E-2</v>
       </c>
       <c r="N6" s="73">
         <f t="shared" ref="N6" si="13">L6/L5-1</f>
-        <v>3.9096016484259977E-2</v>
+        <v>5.5731100143264323E-2</v>
       </c>
       <c r="O6" s="75">
         <f>STDEVP(N$4:N6)*SQRT(12)</f>
-        <v>5.7293360437513062E-2</v>
+        <v>7.8828744479476132E-2</v>
       </c>
     </row>
     <row r="7" spans="2:18" ht="14.25" x14ac:dyDescent="0.4">
@@ -10718,7 +10334,7 @@
       </c>
       <c r="D4" s="6">
         <f t="array" ref="D4">SUM((Blotter!C$19:C$1013=C4)*(Blotter!N$19:N$1013)*1)</f>
-        <v>13875.190632011014</v>
+        <v>19425.190632011014</v>
       </c>
       <c r="E4" s="6">
         <f t="array" ref="E4">SUM((Blotter!B$19:C$1013=C4)*(Blotter!R$19:R$1013)*1)</f>
@@ -10734,20 +10350,20 @@
       </c>
       <c r="H4" s="16">
         <f t="shared" ref="H4:H9" si="4">J3+D4</f>
-        <v>1013875.190632011</v>
+        <v>1019425.190632011</v>
       </c>
       <c r="I4" s="16"/>
       <c r="J4" s="16">
         <f t="shared" si="0"/>
-        <v>1013875.190632011</v>
+        <v>1019425.190632011</v>
       </c>
       <c r="K4" s="3">
         <f t="shared" ref="K4:K9" si="5">H4/J3-1</f>
-        <v>1.3875190632011147E-2</v>
+        <v>1.9425190632011091E-2</v>
       </c>
       <c r="L4" s="3">
         <f t="shared" ref="L4:L9" si="6">(1+K4)*(1+L3)-1</f>
-        <v>1.3875190632011147E-2</v>
+        <v>1.9425190632011091E-2</v>
       </c>
       <c r="M4" s="6">
         <f>O3-IF(G4="O",E4,-D4)</f>
@@ -10818,20 +10434,20 @@
       </c>
       <c r="H5" s="16">
         <f t="shared" si="4"/>
-        <v>1014846.280632011</v>
+        <v>1020396.280632011</v>
       </c>
       <c r="I5" s="16"/>
       <c r="J5" s="16">
         <f t="shared" si="0"/>
-        <v>1014846.280632011</v>
+        <v>1020396.280632011</v>
       </c>
       <c r="K5" s="3">
         <f t="shared" si="5"/>
-        <v>9.5780033772663309E-4</v>
+        <v>9.525858384937802E-4</v>
       </c>
       <c r="L5" s="3">
         <f t="shared" si="6"/>
-        <v>1.48462806320111E-2</v>
+        <v>2.0396280632011043E-2</v>
       </c>
       <c r="M5" s="6">
         <f t="shared" ref="M5:M8" si="13">O4-IF(G5="O",E5,-D5)</f>
@@ -10886,7 +10502,7 @@
       </c>
       <c r="D6" s="6">
         <f t="array" ref="D6">SUM((Blotter!C$19:C$1013=C6)*(Blotter!N$19:N$1013)*1)</f>
-        <v>-6434.220000000003</v>
+        <v>-5714.220000000003</v>
       </c>
       <c r="E6" s="6">
         <f t="array" ref="E6">SUM((Blotter!B$19:C$1013=C6)*(Blotter!R$19:R$1013)*1)</f>
@@ -10894,7 +10510,7 @@
       </c>
       <c r="F6" s="30">
         <f t="shared" ref="F6" si="16">IF(ISNUMBER(D6/E6),D6/E6,0)</f>
-        <v>-0.67133475650600682</v>
+        <v>-0.59621127227880844</v>
       </c>
       <c r="G6" s="36" t="str">
         <f t="array" ref="G6">IF(SUM((Blotter!C$19:C$1013=PLB!C6)*(Blotter!M$19:M$1013))=0,"C","O")</f>
@@ -10902,20 +10518,20 @@
       </c>
       <c r="H6" s="16">
         <f t="shared" si="4"/>
-        <v>1008412.060632011</v>
+        <v>1014682.060632011</v>
       </c>
       <c r="I6" s="16"/>
       <c r="J6" s="16">
         <f t="shared" si="0"/>
-        <v>1008412.060632011</v>
+        <v>1014682.060632011</v>
       </c>
       <c r="K6" s="3">
         <f t="shared" si="5"/>
-        <v>-6.340093197161778E-3</v>
+        <v>-5.6000008119009292E-3</v>
       </c>
       <c r="L6" s="3">
         <f t="shared" si="6"/>
-        <v>8.4120606320110536E-3</v>
+        <v>1.4682060632011051E-2</v>
       </c>
       <c r="M6" s="6">
         <f t="shared" si="13"/>
@@ -10970,15 +10586,15 @@
       </c>
       <c r="D7" s="6">
         <f t="array" ref="D7">SUM((Blotter!C$19:C$1013=C7)*(Blotter!N$19:N$1013)*1)</f>
-        <v>13010.029999999999</v>
+        <v>15372.529999999999</v>
       </c>
       <c r="E7" s="6">
         <f t="array" ref="E7">SUM((Blotter!B$19:C$1013=C7)*(Blotter!R$19:R$1013)*1)</f>
-        <v>7192.5</v>
+        <v>0</v>
       </c>
       <c r="F7" s="30">
         <f t="shared" ref="F7" si="19">IF(ISNUMBER(D7/E7),D7/E7,0)</f>
-        <v>1.8088328119568995</v>
+        <v>0</v>
       </c>
       <c r="G7" s="36" t="str">
         <f t="array" ref="G7">IF(SUM((Blotter!C$19:C$1013=PLB!C7)*(Blotter!M$19:M$1013))=0,"C","O")</f>
@@ -10986,24 +10602,24 @@
       </c>
       <c r="H7" s="16">
         <f t="shared" si="4"/>
-        <v>1021422.0906320111</v>
+        <v>1030054.5906320111</v>
       </c>
       <c r="I7" s="16"/>
       <c r="J7" s="16">
         <f t="shared" si="0"/>
-        <v>1021422.0906320111</v>
+        <v>1030054.5906320111</v>
       </c>
       <c r="K7" s="3">
         <f t="shared" si="5"/>
-        <v>1.2901501784742697E-2</v>
+        <v>1.5150095381034845E-2</v>
       </c>
       <c r="L7" s="3">
         <f t="shared" si="6"/>
-        <v>2.1422090632011059E-2</v>
+        <v>3.0054590632011102E-2</v>
       </c>
       <c r="M7" s="6">
         <f t="shared" si="13"/>
-        <v>984194.37</v>
+        <v>991386.87</v>
       </c>
       <c r="N7" s="16">
         <f t="shared" si="7"/>
@@ -11011,15 +10627,15 @@
       </c>
       <c r="O7" s="6">
         <f t="shared" si="1"/>
-        <v>984194.37</v>
+        <v>991386.87</v>
       </c>
       <c r="P7" s="3">
         <f t="shared" si="8"/>
-        <v>-7.254988156137232E-3</v>
+        <v>0</v>
       </c>
       <c r="Q7" s="3">
         <f t="shared" si="9"/>
-        <v>-1.5805630000000015E-2</v>
+        <v>-8.6131300000000799E-3</v>
       </c>
       <c r="R7" s="3">
         <f t="shared" si="10"/>
@@ -11054,7 +10670,7 @@
       </c>
       <c r="D8" s="6">
         <f t="array" ref="D8">SUM((Blotter!C$19:C$1013=C8)*(Blotter!N$19:N$1013)*1)</f>
-        <v>40035.739999999991</v>
+        <v>44610.739999999991</v>
       </c>
       <c r="E8" s="6">
         <f t="array" ref="E8">SUM((Blotter!B$19:C$1013=C8)*(Blotter!R$19:R$1013)*1)</f>
@@ -11062,7 +10678,7 @@
       </c>
       <c r="F8" s="30">
         <f t="shared" ref="F8" si="22">IF(ISNUMBER(D8/E8),D8/E8,0)</f>
-        <v>-1.5260430722317511</v>
+        <v>-1.7004284352963595</v>
       </c>
       <c r="G8" s="36" t="str">
         <f t="array" ref="G8">IF(SUM((Blotter!C$19:C$1013=PLB!C8)*(Blotter!M$19:M$1013))=0,"C","O")</f>
@@ -11070,24 +10686,24 @@
       </c>
       <c r="H8" s="16">
         <f t="shared" si="4"/>
-        <v>1061457.8306320109</v>
+        <v>1074665.3306320109</v>
       </c>
       <c r="I8" s="16"/>
       <c r="J8" s="16">
         <f t="shared" si="0"/>
-        <v>1061457.8306320109</v>
+        <v>1074665.3306320109</v>
       </c>
       <c r="K8" s="3">
         <f t="shared" si="5"/>
-        <v>3.9196078063308271E-2</v>
+        <v>4.3309102649237374E-2</v>
       </c>
       <c r="L8" s="3">
         <f t="shared" si="6"/>
-        <v>6.1457830632010824E-2</v>
+        <v>7.4665330632011084E-2</v>
       </c>
       <c r="M8" s="6">
         <f t="shared" si="13"/>
-        <v>1010429.37</v>
+        <v>1017621.87</v>
       </c>
       <c r="N8" s="16">
         <f t="shared" si="7"/>
@@ -11095,15 +10711,15 @@
       </c>
       <c r="O8" s="6">
         <f t="shared" si="1"/>
-        <v>1010429.37</v>
+        <v>1017621.87</v>
       </c>
       <c r="P8" s="3">
         <f t="shared" si="8"/>
-        <v>2.6656319929974748E-2</v>
+        <v>2.6462928644596539E-2</v>
       </c>
       <c r="Q8" s="3">
         <f t="shared" si="9"/>
-        <v>1.0429369999999993E-2</v>
+        <v>1.7621869999999928E-2</v>
       </c>
       <c r="R8" s="3">
         <f t="shared" si="10"/>
@@ -11118,13 +10734,13 @@
         <v>5</v>
       </c>
       <c r="V8" s="1" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="W8" s="1" t="s">
-        <v>343</v>
+        <v>334</v>
       </c>
       <c r="X8" s="1" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
     </row>
     <row r="9" spans="2:28" x14ac:dyDescent="0.4">
@@ -11138,7 +10754,7 @@
       </c>
       <c r="D9" s="6">
         <f t="array" ref="D9">SUM((Blotter!C$19:C$1013=C9)*(Blotter!N$19:N$1013)*1)</f>
-        <v>-1305.0400000000004</v>
+        <v>104.95999999999981</v>
       </c>
       <c r="E9" s="6">
         <f t="array" ref="E9">SUM((Blotter!B$19:C$1013=C9)*(Blotter!R$19:R$1013)*1)</f>
@@ -11146,7 +10762,7 @@
       </c>
       <c r="F9" s="30">
         <f t="shared" ref="F9" si="25">IF(ISNUMBER(D9/E9),D9/E9,0)</f>
-        <v>-0.13174237835655161</v>
+        <v>1.0595598627094671E-2</v>
       </c>
       <c r="G9" s="36" t="str">
         <f t="array" ref="G9">IF(SUM((Blotter!C$19:C$1013=PLB!C9)*(Blotter!M$19:M$1013))=0,"C","O")</f>
@@ -11154,24 +10770,24 @@
       </c>
       <c r="H9" s="16">
         <f t="shared" si="4"/>
-        <v>1060152.7906320109</v>
+        <v>1074770.2906320109</v>
       </c>
       <c r="I9" s="16"/>
       <c r="J9" s="16">
         <f t="shared" ref="J9" si="26">H9+I9</f>
-        <v>1060152.7906320109</v>
+        <v>1074770.2906320109</v>
       </c>
       <c r="K9" s="3">
         <f t="shared" si="5"/>
-        <v>-1.2294788943456592E-3</v>
+        <v>9.7667615217789105E-5</v>
       </c>
       <c r="L9" s="3">
         <f t="shared" si="6"/>
-        <v>6.0152790632010733E-2</v>
+        <v>7.4770290632011127E-2</v>
       </c>
       <c r="M9" s="6">
         <f t="shared" ref="M9" si="27">O8-IF(G9="O",E9,-D9)</f>
-        <v>1000523.37</v>
+        <v>1007715.87</v>
       </c>
       <c r="N9" s="16">
         <f t="shared" si="7"/>
@@ -11179,15 +10795,15 @@
       </c>
       <c r="O9" s="6">
         <f t="shared" ref="O9" si="28">M9+N9</f>
-        <v>1000523.37</v>
+        <v>1007715.87</v>
       </c>
       <c r="P9" s="3">
         <f t="shared" si="8"/>
-        <v>-9.8037530322381272E-3</v>
+        <v>-9.7344606007730983E-3</v>
       </c>
       <c r="Q9" s="3">
         <f t="shared" si="9"/>
-        <v>5.2337000000002298E-4</v>
+        <v>7.715869999999958E-3</v>
       </c>
       <c r="R9" s="3">
         <f t="shared" si="10"/>
@@ -11202,13 +10818,13 @@
         <v>6</v>
       </c>
       <c r="V9" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="W9" s="49" t="s">
         <v>337</v>
       </c>
-      <c r="W9" s="49" t="s">
-        <v>346</v>
-      </c>
       <c r="X9" s="1" t="s">
-        <v>345</v>
+        <v>336</v>
       </c>
     </row>
     <row r="10" spans="2:28" x14ac:dyDescent="0.4">
@@ -11222,7 +10838,7 @@
       </c>
       <c r="D10" s="6">
         <f t="array" ref="D10">SUM((Blotter!C$19:C$1013=C10)*(Blotter!N$19:N$1013)*1)</f>
-        <v>4862.5000000001164</v>
+        <v>7062.4999999998836</v>
       </c>
       <c r="E10" s="6">
         <f t="array" ref="E10">SUM((Blotter!B$19:C$1013=C10)*(Blotter!R$19:R$1013)*1)</f>
@@ -11230,7 +10846,7 @@
       </c>
       <c r="F10" s="30">
         <f t="shared" ref="F10" si="31">IF(ISNUMBER(D10/E10),D10/E10,0)</f>
-        <v>0.54885361552029532</v>
+        <v>0.7971781305114507</v>
       </c>
       <c r="G10" s="36" t="str">
         <f t="array" ref="G10">IF(SUM((Blotter!C$19:C$1013=PLB!C10)*(Blotter!M$19:M$1013))=0,"C","O")</f>
@@ -11238,24 +10854,24 @@
       </c>
       <c r="H10" s="16">
         <f t="shared" ref="H10" si="32">J9+D10</f>
-        <v>1065015.2906320109</v>
+        <v>1081832.7906320109</v>
       </c>
       <c r="I10" s="16"/>
       <c r="J10" s="16">
         <f t="shared" ref="J10" si="33">H10+I10</f>
-        <v>1065015.2906320109</v>
+        <v>1081832.7906320109</v>
       </c>
       <c r="K10" s="3">
         <f t="shared" ref="K10" si="34">H10/J9-1</f>
-        <v>4.5866030283250314E-3</v>
+        <v>6.5711715903935541E-3</v>
       </c>
       <c r="L10" s="3">
         <f t="shared" ref="L10" si="35">(1+K10)*(1+L9)-1</f>
-        <v>6.5015290632010725E-2</v>
+        <v>8.1832790632011321E-2</v>
       </c>
       <c r="M10" s="6">
         <f t="shared" ref="M10" si="36">O9-IF(G10="O",E10,-D10)</f>
-        <v>991663.995</v>
+        <v>998856.495</v>
       </c>
       <c r="N10" s="16">
         <f t="shared" ref="N10" si="37">I10</f>
@@ -11263,15 +10879,15 @@
       </c>
       <c r="O10" s="6">
         <f t="shared" ref="O10" si="38">M10+N10</f>
-        <v>991663.995</v>
+        <v>998856.495</v>
       </c>
       <c r="P10" s="3">
         <f t="shared" ref="P10" si="39">M10/O9-1</f>
-        <v>-8.8547406943627616E-3</v>
+        <v>-8.7915406155110176E-3</v>
       </c>
       <c r="Q10" s="3">
         <f t="shared" ref="Q10" si="40">(1+P10)*(1+Q9)-1</f>
-        <v>-8.3360049999999797E-3</v>
+        <v>-1.1435050000000446E-3</v>
       </c>
       <c r="R10" s="3">
         <f t="shared" si="10"/>
@@ -11286,13 +10902,13 @@
         <v>7</v>
       </c>
       <c r="V10" s="1" t="s">
-        <v>349</v>
+        <v>340</v>
       </c>
       <c r="W10" s="49" t="s">
-        <v>347</v>
+        <v>338</v>
       </c>
       <c r="X10" s="1" t="s">
-        <v>348</v>
+        <v>339</v>
       </c>
     </row>
     <row r="11" spans="2:28" x14ac:dyDescent="0.4">
@@ -12660,7 +12276,7 @@
     </row>
     <row r="8" spans="2:18" x14ac:dyDescent="0.4">
       <c r="B8" s="17" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="C8" s="18">
         <v>5</v>
@@ -17509,16 +17125,16 @@
         <v>58</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>78</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="H60" s="1">
         <v>5</v>
@@ -17579,16 +17195,16 @@
         <v>58</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>78</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="H61" s="1">
         <v>5</v>
@@ -17649,16 +17265,16 @@
         <v>58</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>78</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="H62" s="1">
         <v>5</v>
@@ -17719,16 +17335,16 @@
         <v>58</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>78</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="H63" s="1">
         <v>5</v>
@@ -17789,16 +17405,16 @@
         <v>58</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>78</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="H64" s="1">
         <v>5</v>
@@ -17859,16 +17475,16 @@
         <v>58</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>78</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="H65" s="1">
         <v>5</v>
@@ -17929,16 +17545,16 @@
         <v>58</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>78</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="H66" s="1">
         <v>5</v>
@@ -17999,10 +17615,10 @@
         <v>303</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>339</v>
+        <v>330</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>80</v>
@@ -18020,7 +17636,7 @@
         <v>46168</v>
       </c>
       <c r="K67" s="1" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="L67" s="44">
         <v>46119</v>
@@ -18075,10 +17691,10 @@
         <v>303</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>333</v>
+        <v>325</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>340</v>
+        <v>331</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>80</v>
@@ -18096,7 +17712,7 @@
         <v>46168</v>
       </c>
       <c r="K68" s="1" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="L68" s="44">
         <v>46119</v>
@@ -18141,20 +17757,53 @@
       </c>
     </row>
     <row r="69" spans="1:24" x14ac:dyDescent="0.4">
+      <c r="A69" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>59</v>
+      </c>
       <c r="C69" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D69" s="1" t="s">
         <v>267</v>
       </c>
+      <c r="E69" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="F69" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="G69" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="H69" s="1">
+        <v>125000</v>
+      </c>
       <c r="J69" s="44">
         <v>46188</v>
       </c>
+      <c r="L69" s="44">
+        <v>46125</v>
+      </c>
+      <c r="M69" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="N69" s="1">
         <v>5</v>
       </c>
       <c r="O69" s="1">
-        <v>1.1721699999999999</v>
+        <v>1.17215</v>
+      </c>
+      <c r="P69" s="1">
+        <v>732593.75</v>
+      </c>
+      <c r="Q69" s="1">
+        <v>-12.35</v>
+      </c>
+      <c r="R69" s="1" t="s">
+        <v>59</v>
       </c>
       <c r="T69" s="43">
         <f>IF(ISNUMBER(VLOOKUP(U69,Blotter!B:C,2,0)),VLOOKUP(U69,Blotter!B:C,2,0),"")</f>
@@ -18170,11 +17819,14 @@
       </c>
       <c r="W69" s="42">
         <f t="shared" si="42"/>
-        <v>1.1721699999999999</v>
+        <v>1.17215</v>
       </c>
       <c r="X69" s="42"/>
     </row>
     <row r="70" spans="1:24" x14ac:dyDescent="0.4">
+      <c r="A70" s="1" t="s">
+        <v>292</v>
+      </c>
       <c r="B70" s="1" t="s">
         <v>59</v>
       </c>
@@ -18200,10 +17852,10 @@
         <v>46156</v>
       </c>
       <c r="L70" s="44">
-        <v>46090</v>
+        <v>46125</v>
       </c>
       <c r="M70" s="1" t="s">
-        <v>85</v>
+        <v>291</v>
       </c>
       <c r="N70" s="1">
         <v>-2</v>
@@ -18212,7 +17864,7 @@
         <v>3268</v>
       </c>
       <c r="P70" s="1">
-        <v>64700</v>
+        <v>-65360</v>
       </c>
       <c r="Q70" s="1">
         <v>-5.94</v>
@@ -18239,6 +17891,9 @@
       <c r="X70" s="42"/>
     </row>
     <row r="71" spans="1:24" x14ac:dyDescent="0.4">
+      <c r="A71" s="1" t="s">
+        <v>292</v>
+      </c>
       <c r="B71" s="1" t="s">
         <v>59</v>
       </c>
@@ -18264,10 +17919,10 @@
         <v>46156</v>
       </c>
       <c r="L71" s="44">
-        <v>46090</v>
+        <v>46125</v>
       </c>
       <c r="M71" s="1" t="s">
-        <v>85</v>
+        <v>291</v>
       </c>
       <c r="N71" s="1">
         <v>-1</v>
@@ -18276,10 +17931,10 @@
         <v>3267</v>
       </c>
       <c r="P71" s="1">
-        <v>64700</v>
+        <v>-32670</v>
       </c>
       <c r="Q71" s="1">
-        <v>-5.94</v>
+        <v>-2.97</v>
       </c>
       <c r="R71" s="1" t="s">
         <v>59</v>
@@ -26012,13 +25667,13 @@
         <v>1</v>
       </c>
       <c r="B6" s="88" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="C6" s="88" t="s">
         <v>58</v>
       </c>
       <c r="D6" s="88" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="E6" s="88" t="s">
         <v>78</v>
@@ -26035,7 +25690,7 @@
         <v>5</v>
       </c>
       <c r="K6" s="88" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="L6" s="88"/>
       <c r="M6" s="88"/>
@@ -27002,7 +26657,7 @@
         <v>1</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>333</v>
+        <v>325</v>
       </c>
       <c r="C38" s="88" t="s">
         <v>303</v>
@@ -27023,13 +26678,13 @@
         <v>5500</v>
       </c>
       <c r="I38" s="88" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="J38" s="88">
         <v>100</v>
       </c>
       <c r="K38" s="88" t="s">
-        <v>336</v>
+        <v>328</v>
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.4">
@@ -27037,7 +26692,7 @@
         <v>1</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="C39" s="88" t="s">
         <v>303</v>
@@ -27058,13 +26713,13 @@
         <v>4930</v>
       </c>
       <c r="I39" s="88" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="J39" s="88">
         <v>100</v>
       </c>
       <c r="K39" s="88" t="s">
-        <v>336</v>
+        <v>328</v>
       </c>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.4">

--- a/1XW_TradeBlotter_Web.xlsx
+++ b/1XW_TradeBlotter_Web.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0a601c1c2ba3d9f4/Trading/The Strategy Project/1XW Website/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="587" documentId="13_ncr:1_{6F5069F1-F0E7-4440-AA6D-4AFA11BBED1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{51E59DA7-6D39-42AA-AEDE-610B11AB486B}"/>
+  <xr:revisionPtr revIDLastSave="610" documentId="13_ncr:1_{6F5069F1-F0E7-4440-AA6D-4AFA11BBED1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DDE1467B-DDCA-4BF0-82BF-7636432EFB84}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="22695" windowHeight="14476" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -99,7 +99,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1469" uniqueCount="346">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1498" uniqueCount="350">
   <si>
     <t>WEEK</t>
   </si>
@@ -1113,43 +1113,55 @@
     <t>RISK</t>
   </si>
   <si>
+    <t>End of deflation era / pro-growth government policies / attractive valuations</t>
+  </si>
+  <si>
+    <t>Weekly retrace to previous support area and weekly up</t>
+  </si>
+  <si>
+    <t>Weekly hammer after 50% retrace and weekly up</t>
+  </si>
+  <si>
+    <t>Central banks buying spree / geopolitical or dollar shock hedge</t>
+  </si>
+  <si>
+    <t>Rate differential expectations, BCE 2-3 hikes before year-end</t>
+  </si>
+  <si>
+    <t>Weekly doji + weekly up / potential continuation to new highs</t>
+  </si>
+  <si>
+    <t>Long 6E Futures</t>
+  </si>
+  <si>
+    <t>EUR 15JUN26</t>
+  </si>
+  <si>
+    <t>INFO</t>
+  </si>
+  <si>
+    <t>Starting. host=127.0.0.1 port=7497 clientId=11 mktDataType=3 interval=0.25s</t>
+  </si>
+  <si>
+    <t>Connected to TWS.</t>
+  </si>
+  <si>
+    <t>Loaded 38 contracts from Symbols sheet.</t>
+  </si>
+  <si>
+    <t>ERROR</t>
+  </si>
+  <si>
+    <t>Loop error: (-2147352567, 'Exception occurred.', (0, None, None, None, 0, -2146827284), None). Reconnecting in 2s.</t>
+  </si>
+  <si>
+    <t>Reconnected to TWS.</t>
+  </si>
+  <si>
+    <t>Loop error: (-2147352567, 'Exception occurred.', (0, None, None, None, 0, -2146777998), None). Reconnecting in 2s.</t>
+  </si>
+  <si>
     <t>Close</t>
-  </si>
-  <si>
-    <t>End of deflation era / pro-growth government policies / attractive valuations</t>
-  </si>
-  <si>
-    <t>Weekly retrace to previous support area and weekly up</t>
-  </si>
-  <si>
-    <t>Weekly hammer after 50% retrace and weekly up</t>
-  </si>
-  <si>
-    <t>Central banks buying spree / geopolitical or dollar shock hedge</t>
-  </si>
-  <si>
-    <t>Rate differential expectations, BCE 2-3 hikes before year-end</t>
-  </si>
-  <si>
-    <t>Weekly doji + weekly up / potential continuation to new highs</t>
-  </si>
-  <si>
-    <t>Long 6E Futures</t>
-  </si>
-  <si>
-    <t>EUR 15JUN26</t>
-  </si>
-  <si>
-    <t>INFO</t>
-  </si>
-  <si>
-    <t>Starting. host=127.0.0.1 port=7497 clientId=11 mktDataType=3 interval=0.25s</t>
-  </si>
-  <si>
-    <t>Connected to TWS.</t>
-  </si>
-  <si>
-    <t>Loaded 38 contracts from Symbols sheet.</t>
   </si>
 </sst>
 </file>
@@ -2316,7 +2328,7 @@
                   <c:v>2.8744450632010921E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5.5731100143264323E-2</c:v>
+                  <c:v>6.4782385906487105E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2476,7 +2488,7 @@
                   <c:v>2.8744450632010921E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>8.6077510632010856E-2</c:v>
+                  <c:v>9.5388970632011016E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2873,7 +2885,7 @@
                   <c:v>1028.744450632011</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1086.0775106320109</c:v>
+                  <c:v>1095.388970632011</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3289,25 +3301,25 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>1.0499999999999954E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>9.7108999999995227E-4</c:v>
+                  <c:v>1.1471089999999906E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-8.6131300000000799E-3</c:v>
+                  <c:v>1.886870000000096E-3</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-8.6131300000000799E-3</c:v>
+                  <c:v>1.886870000000096E-3</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.7621869999999928E-2</c:v>
+                  <c:v>5.3272610000000276E-2</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>7.715869999999958E-3</c:v>
+                  <c:v>4.3366610000000305E-2</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-1.1435050000000446E-3</c:v>
+                  <c:v>3.4507235000000192E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3400,25 +3412,25 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.9425190632011091E-2</c:v>
+                  <c:v>2.2185190632010965E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2.0396280632011043E-2</c:v>
+                  <c:v>2.3156280632010917E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.4682060632011051E-2</c:v>
+                  <c:v>1.9632060632010839E-2</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>3.0054590632011102E-2</c:v>
+                  <c:v>3.4792090632010941E-2</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>7.4665330632011084E-2</c:v>
+                  <c:v>8.6177830632010899E-2</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>7.4770290632011127E-2</c:v>
+                  <c:v>8.5162790632010932E-2</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>8.1832790632011321E-2</c:v>
+                  <c:v>9.0819040632011072E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4068,7 +4080,7 @@
       </c>
       <c r="C1" s="79">
         <f ca="1">TODAY()</f>
-        <v>46128</v>
+        <v>46130</v>
       </c>
     </row>
     <row r="2" spans="2:11" x14ac:dyDescent="0.4">
@@ -4076,7 +4088,7 @@
         <v>107</v>
       </c>
       <c r="C2" s="37" t="s">
-        <v>333</v>
+        <v>349</v>
       </c>
       <c r="E2" s="47" t="s">
         <v>120</v>
@@ -4093,7 +4105,7 @@
       </c>
       <c r="C3" s="28">
         <f ca="1">OFFSET(NAV!B1,MATCH(C1,NAV!B:B,1),8)</f>
-        <v>1086077.5106320109</v>
+        <v>1095388.9706320111</v>
       </c>
       <c r="E3" s="47" t="s">
         <v>121</v>
@@ -4110,7 +4122,7 @@
       </c>
       <c r="C4" s="28">
         <f>SUM(N18:N1012)</f>
-        <v>86077.510632010832</v>
+        <v>95388.970632011056</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="47" t="s">
@@ -4128,7 +4140,7 @@
       </c>
       <c r="C5" s="3">
         <f ca="1">OFFSET(NAV!B1,MATCH(C1,NAV!B:B,1),11)</f>
-        <v>8.6077510632010856E-2</v>
+        <v>9.5388970632011016E-2</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="47" t="s">
@@ -4147,7 +4159,7 @@
       </c>
       <c r="C6" s="3">
         <f ca="1">OFFSET(NAV!B1,MATCH(C1,NAV!B:B,1),12)</f>
-        <v>5.5731100143264323E-2</v>
+        <v>6.4782385906487105E-2</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="47" t="s">
@@ -4164,11 +4176,11 @@
       </c>
       <c r="C7" s="28">
         <f>Cash_Mgmt!H13</f>
-        <v>33355.279999999955</v>
+        <v>33030.069999999956</v>
       </c>
       <c r="D7" s="3">
         <f ca="1">C7/C3</f>
-        <v>3.0711693846408653E-2</v>
+        <v>3.0153736148121394E-2</v>
       </c>
       <c r="E7" s="47"/>
       <c r="F7" s="47"/>
@@ -4182,11 +4194,11 @@
       </c>
       <c r="C8" s="28">
         <f>C4+C7</f>
-        <v>119432.79063201079</v>
+        <v>128419.04063201102</v>
       </c>
       <c r="D8" s="3">
         <f ca="1">C5+D7</f>
-        <v>0.11678920447841951</v>
+        <v>0.12554270678013241</v>
       </c>
       <c r="G8" s="47"/>
       <c r="H8" s="51"/>
@@ -4198,11 +4210,11 @@
       </c>
       <c r="C9" s="28">
         <f t="array" ref="C9">SUM((F19:F112="Futures")*(M19:M112))</f>
-        <v>1184731.25</v>
+        <v>890162.5</v>
       </c>
       <c r="D9" s="3">
         <f ca="1">C9/$C$3</f>
-        <v>1.0908348975116706</v>
+        <v>0.81264511864347078</v>
       </c>
       <c r="E9" s="47"/>
       <c r="F9" s="47"/>
@@ -4216,11 +4228,11 @@
       </c>
       <c r="C10" s="28">
         <f t="array" ref="C10">SUM((F19:F1012="Call")*(M19:M1012))</f>
-        <v>10010</v>
+        <v>8890</v>
       </c>
       <c r="D10" s="3">
         <f t="shared" ref="D10:D14" ca="1" si="0">C10/$C$3</f>
-        <v>9.2166534174664711E-3</v>
+        <v>8.1158385179565026E-3</v>
       </c>
       <c r="H10" s="44"/>
     </row>
@@ -4230,11 +4242,11 @@
       </c>
       <c r="C11" s="28">
         <f t="array" ref="C11">SUM((F19:F212="Put")*(M19:M212))</f>
-        <v>3870</v>
+        <v>6060</v>
       </c>
       <c r="D11" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>3.5632815909685555E-3</v>
+        <v>5.5322813744450401E-3</v>
       </c>
     </row>
     <row r="12" spans="2:11" x14ac:dyDescent="0.4">
@@ -4243,11 +4255,11 @@
       </c>
       <c r="C12" s="28">
         <f t="array" ref="C12">SUM((PLB!G4:G999="O")*(PLB!E4:E999))</f>
-        <v>2114.5950000000012</v>
+        <v>17849.595000000001</v>
       </c>
       <c r="D12" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>1.9470019214093428E-3</v>
+        <v>1.6295211544535861E-2</v>
       </c>
     </row>
     <row r="13" spans="2:11" x14ac:dyDescent="0.4">
@@ -4256,11 +4268,11 @@
       </c>
       <c r="C13" s="28">
         <f t="array" ref="C13">SUM((PLB!G4:G999="O")*(PLB!D4:D999))</f>
-        <v>80861.700632010892</v>
+        <v>38462.210632011112</v>
       </c>
       <c r="D13" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>7.4452973973244144E-2</v>
+        <v>3.5112833580768492E-2</v>
       </c>
       <c r="F13" s="59"/>
       <c r="G13" s="59"/>
@@ -4271,11 +4283,11 @@
       </c>
       <c r="C14" s="28">
         <f>C12+C13</f>
-        <v>82976.295632010893</v>
+        <v>56311.805632011114</v>
       </c>
       <c r="D14" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>7.6399975894653485E-2</v>
+        <v>5.1408045125304357E-2</v>
       </c>
     </row>
     <row r="17" spans="2:28" x14ac:dyDescent="0.4">
@@ -4372,7 +4384,7 @@
       <c r="M18" s="12"/>
       <c r="N18" s="95">
         <f>Cash_Mgmt!G13</f>
-        <v>4244.7199999999539</v>
+        <v>4569.9299999999548</v>
       </c>
       <c r="O18" s="12"/>
       <c r="P18" s="12"/>
@@ -4420,45 +4432,47 @@
       </c>
       <c r="K19" s="29">
         <f t="shared" ref="K19" si="1">L19-N19/(H19*J19)</f>
-        <v>1986.5461873597799</v>
+        <v>1986.5461873597801</v>
       </c>
       <c r="L19" s="29">
         <f t="shared" ref="L19" si="2">IF(I19=0,IF(H19&gt;0,X19,Y19),Z19)</f>
-        <v>2375.0500000000002</v>
+        <v>2430.25</v>
       </c>
       <c r="M19" s="28">
         <f t="shared" ref="M19" si="3">I19*J19*L19</f>
-        <v>118752.50000000001</v>
+        <v>121512.5</v>
       </c>
       <c r="N19" s="95">
         <f t="array" ref="N19">-SUM((Trades!T$2:T$9999=Blotter!C19)*(Trades!U$2:U$9999=Blotter!B19)*(Trades!V$2:V$9999)*(Trades!W$2:W$9999))*J19+SUM((Trades!T$2:T$9999=Blotter!C19)*(Trades!U$2:U$9999=Blotter!B19)*(Trades!X$2:X$9999))+(L19*I19)*J19</f>
-        <v>19425.190632011014</v>
+        <v>22185.190632010999</v>
       </c>
       <c r="O19" s="29">
         <f>VLOOKUP(D19,Multiplier!B:H,3,0)</f>
         <v>140</v>
       </c>
-      <c r="P19" s="27"/>
+      <c r="P19" s="27">
+        <v>-210</v>
+      </c>
       <c r="Q19" s="27"/>
       <c r="R19" s="28">
         <f t="shared" ref="R19" si="4">(1-Q19)*P19*J19*H19</f>
-        <v>0</v>
+        <v>-10500</v>
       </c>
       <c r="S19" s="29">
         <f>IF(OR(F19="Futures",F19="Spot"),IF(I19=0,0,IF(I19&gt;0,L19-O19,L19+O19)),0)</f>
-        <v>2235.0500000000002</v>
+        <v>2290.25</v>
       </c>
       <c r="T19" s="3">
         <f t="shared" ref="T19" si="5">IF(S19&gt;0,IF(ISNUMBER(S19/L19-1),S19/L19-1,0),0)</f>
-        <v>-5.8946127449948427E-2</v>
+        <v>-5.7607242053286711E-2</v>
       </c>
       <c r="U19" s="29">
         <f>IF(OR(F19="Futures",F19="Spot"),IF(I19=0,0,IF(I19&gt;0,K19-P19,K19+P19)),0)</f>
-        <v>1986.5461873597799</v>
+        <v>2196.5461873597801</v>
       </c>
       <c r="V19" s="3">
         <f t="shared" ref="V19" si="6">IF(U19&gt;0,IF(ISNUMBER(U19/L19-1),U19/L19-1,0),0)</f>
-        <v>-0.16357710896200939</v>
+        <v>-9.6164515025293662E-2</v>
       </c>
       <c r="X19" s="34">
         <f t="array" ref="X19">IF(ISNUMBER(SUM((Trades!T$2:T$9999=Blotter!C19)*(Trades!U$2:U$9999=Blotter!B19)*(Trades!W$2:W$9999)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0))/SUM((Trades!T$2:T$9999=Blotter!C19)*(Trades!U$2:U$9999=Blotter!B19)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0))),SUM((Trades!T$2:T$9999=Blotter!C19)*(Trades!U$2:U$9999=Blotter!B19)*(Trades!W$2:W$9999)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0))/SUM((Trades!T$2:T$9999=Blotter!C19)*(Trades!U$2:U$9999=Blotter!B19)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0)),0)</f>
@@ -4470,7 +4484,7 @@
       </c>
       <c r="Z19" s="35">
         <f>IF(C$2="Last",IF(ISNUMBER(VLOOKUP(B19,Prices!A:L,8,0)),VLOOKUP(B19,Prices!A:L,8,0),0),IF(ISNUMBER(VLOOKUP(B19,Prices!A:L,12,0)),VLOOKUP(B19,Prices!A:L,12,0),0))</f>
-        <v>2375.0500000000002</v>
+        <v>2430.25</v>
       </c>
       <c r="AB19" s="29"/>
     </row>
@@ -4525,13 +4539,11 @@
         <f>VLOOKUP(D20,Multiplier!B:H,3,0)</f>
         <v>205</v>
       </c>
-      <c r="P20" s="27">
-        <v>300</v>
-      </c>
+      <c r="P20" s="27"/>
       <c r="Q20" s="27"/>
       <c r="R20" s="28">
         <f t="shared" ref="R20" si="10">(1-Q20)*P20*J20*H20</f>
-        <v>9000</v>
+        <v>0</v>
       </c>
       <c r="S20" s="29">
         <f>IF(OR(F20="Futures",F20="Spot"),IF(I20=0,0,IF(I20&gt;0,L20-O20,L20+O20)),0)</f>
@@ -4559,7 +4571,7 @@
       </c>
       <c r="Z20" s="35">
         <f>IF(C$2="Last",IF(ISNUMBER(VLOOKUP(B20,Prices!A:L,8,0)),VLOOKUP(B20,Prices!A:L,8,0),0),IF(ISNUMBER(VLOOKUP(B20,Prices!A:L,12,0)),VLOOKUP(B20,Prices!A:L,12,0),0))</f>
-        <v>3477</v>
+        <v>3367</v>
       </c>
       <c r="AB20" s="29"/>
     </row>
@@ -4600,15 +4612,15 @@
       </c>
       <c r="L21" s="29">
         <f t="shared" ref="L21:L22" si="15">IF(I21=0,IF(H21&gt;0,X21,Y21),Z21)</f>
-        <v>1.41</v>
+        <v>2.13</v>
       </c>
       <c r="M21" s="28">
         <f t="shared" ref="M21:M22" si="16">I21*J21*L21</f>
-        <v>4230</v>
+        <v>6390</v>
       </c>
       <c r="N21" s="95">
         <f t="array" ref="N21">-SUM((Trades!T$2:T$9999=Blotter!C21)*(Trades!U$2:U$9999=Blotter!B21)*(Trades!V$2:V$9999)*(Trades!W$2:W$9999))*J21+SUM((Trades!T$2:T$9999=Blotter!C21)*(Trades!U$2:U$9999=Blotter!B21)*(Trades!X$2:X$9999))+(L21*I21)*J21</f>
-        <v>-6397.1100000000033</v>
+        <v>-4237.1100000000024</v>
       </c>
       <c r="O21" s="29">
         <f>VLOOKUP(D21,Multiplier!B:H,3,0)</f>
@@ -4648,7 +4660,7 @@
       </c>
       <c r="Z21" s="35">
         <f>IF(C$2="Last",IF(ISNUMBER(VLOOKUP(B21,Prices!A:L,8,0)),VLOOKUP(B21,Prices!A:L,8,0),0),IF(ISNUMBER(VLOOKUP(B21,Prices!A:L,12,0)),VLOOKUP(B21,Prices!A:L,12,0),0))</f>
-        <v>1.41</v>
+        <v>2.13</v>
       </c>
       <c r="AB21" s="29"/>
     </row>
@@ -4685,19 +4697,19 @@
       </c>
       <c r="K22" s="29">
         <f t="shared" si="14"/>
-        <v>0.34762999999999999</v>
+        <v>0.34762999999999994</v>
       </c>
       <c r="L22" s="29">
         <f t="shared" si="15"/>
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="M22" s="28">
         <f t="shared" si="16"/>
-        <v>-360</v>
+        <v>-330</v>
       </c>
       <c r="N22" s="95">
         <f t="array" ref="N22">-SUM((Trades!T$2:T$9999=Blotter!C22)*(Trades!U$2:U$9999=Blotter!B22)*(Trades!V$2:V$9999)*(Trades!W$2:W$9999))*J22+SUM((Trades!T$2:T$9999=Blotter!C22)*(Trades!U$2:U$9999=Blotter!B22)*(Trades!X$2:X$9999))+(L22*I22)*J22</f>
-        <v>682.88999999999987</v>
+        <v>712.88999999999987</v>
       </c>
       <c r="O22" s="29">
         <f>VLOOKUP(D22,Multiplier!B:H,3,0)</f>
@@ -4737,7 +4749,7 @@
       </c>
       <c r="Z22" s="35">
         <f>IF(C$2="Last",IF(ISNUMBER(VLOOKUP(B22,Prices!A:L,8,0)),VLOOKUP(B22,Prices!A:L,8,0),0),IF(ISNUMBER(VLOOKUP(B22,Prices!A:L,12,0)),VLOOKUP(B22,Prices!A:L,12,0),0))</f>
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AB22" s="29"/>
     </row>
@@ -4774,19 +4786,19 @@
       </c>
       <c r="K23" s="29">
         <f t="shared" ref="K23" si="22">L23-N23/(H23*J23)</f>
-        <v>5.4700987999999997</v>
+        <v>5.4700988000000006</v>
       </c>
       <c r="L23" s="29">
         <f t="shared" ref="L23" si="23">IF(I23=0,IF(H23&gt;0,X23,Y23),Z23)</f>
-        <v>6.085</v>
+        <v>6.0765000000000002</v>
       </c>
       <c r="M23" s="28">
         <f t="shared" ref="M23" si="24">I23*J23*L23</f>
-        <v>152125</v>
+        <v>151912.5</v>
       </c>
       <c r="N23" s="95">
         <f t="array" ref="N23">-SUM((Trades!T$2:T$9999=Blotter!C23)*(Trades!U$2:U$9999=Blotter!B23)*(Trades!V$2:V$9999)*(Trades!W$2:W$9999))*J23+SUM((Trades!T$2:T$9999=Blotter!C23)*(Trades!U$2:U$9999=Blotter!B23)*(Trades!X$2:X$9999))+(L23*I23)*J23</f>
-        <v>15372.529999999999</v>
+        <v>15160.029999999999</v>
       </c>
       <c r="O23" s="29">
         <f>VLOOKUP(D23,Multiplier!B:H,3,0)</f>
@@ -4800,19 +4812,19 @@
       </c>
       <c r="S23" s="29">
         <f t="shared" ref="S23" si="26">IF(OR(F23="Futures",F23="Spot"),IF(I23=0,0,IF(I23&gt;0,L23-O23,L23+O23)),0)</f>
-        <v>5.8932000000000002</v>
+        <v>5.8847000000000005</v>
       </c>
       <c r="T23" s="3">
         <f t="shared" ref="T23" si="27">IF(S23&gt;0,IF(ISNUMBER(S23/L23-1),S23/L23-1,0),0)</f>
-        <v>-3.1520131470829882E-2</v>
+        <v>-3.1564222825639754E-2</v>
       </c>
       <c r="U23" s="29">
         <f t="shared" ref="U23" si="28">IF(OR(F23="Futures",F23="Stocks"),IF(I23=0,0,IF(I23&gt;0,K23-P23,K23+P23)),0)</f>
-        <v>5.4700987999999997</v>
+        <v>5.4700988000000006</v>
       </c>
       <c r="V23" s="3">
         <f t="shared" ref="V23" si="29">IF(U23&gt;0,IF(ISNUMBER(U23/L23-1),U23/L23-1,0),0)</f>
-        <v>-0.10105196384552184</v>
+        <v>-9.9794486957952677E-2</v>
       </c>
       <c r="X23" s="34">
         <f t="array" ref="X23">IF(ISNUMBER(SUM((Trades!T$2:T$9999=Blotter!C23)*(Trades!U$2:U$9999=Blotter!B23)*(Trades!W$2:W$9999)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0))/SUM((Trades!T$2:T$9999=Blotter!C23)*(Trades!U$2:U$9999=Blotter!B23)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0))),SUM((Trades!T$2:T$9999=Blotter!C23)*(Trades!U$2:U$9999=Blotter!B23)*(Trades!W$2:W$9999)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0))/SUM((Trades!T$2:T$9999=Blotter!C23)*(Trades!U$2:U$9999=Blotter!B23)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0)),0)</f>
@@ -4824,7 +4836,7 @@
       </c>
       <c r="Z23" s="35">
         <f>IF(C$2="Last",IF(ISNUMBER(VLOOKUP(B23,Prices!A:L,8,0)),VLOOKUP(B23,Prices!A:L,8,0),0),IF(ISNUMBER(VLOOKUP(B23,Prices!A:L,12,0)),VLOOKUP(B23,Prices!A:L,12,0),0))</f>
-        <v>6.085</v>
+        <v>6.0765000000000002</v>
       </c>
       <c r="AB23" s="29"/>
     </row>
@@ -4853,7 +4865,7 @@
       </c>
       <c r="I24" s="28">
         <f t="array" ref="I24">ROUND(SUM((Trades!V$2:V$9999)*(Trades!U$2:U$9999=Blotter!B24)*(Trades!$T$2:T$9999=Blotter!C24)),8)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J24" s="28">
         <f>VLOOKUP(D24,Multiplier!B:D,2,0)</f>
@@ -4861,52 +4873,49 @@
       </c>
       <c r="K24" s="29">
         <f t="shared" ref="K24" si="30">L24-N24/(H24*J24)</f>
-        <v>49667.851999999999</v>
+        <v>42402.137714285716</v>
       </c>
       <c r="L24" s="29">
         <f t="shared" ref="L24" si="31">IF(I24=0,IF(H24&gt;0,X24,Y24),Z24)</f>
-        <v>58590</v>
+        <v>52679.285714285717</v>
       </c>
       <c r="M24" s="28">
         <f t="shared" ref="M24" si="32">I24*J24*L24</f>
-        <v>292950</v>
+        <v>0</v>
       </c>
       <c r="N24" s="95">
         <f t="array" ref="N24">-SUM((Trades!T$2:T$9999=Blotter!C24)*(Trades!U$2:U$9999=Blotter!B24)*(Trades!V$2:V$9999)*(Trades!W$2:W$9999))*J24+SUM((Trades!T$2:T$9999=Blotter!C24)*(Trades!U$2:U$9999=Blotter!B24)*(Trades!X$2:X$9999))+(L24*I24)*J24</f>
-        <v>44610.739999999991</v>
+        <v>51385.74</v>
       </c>
       <c r="O24" s="29">
         <f>VLOOKUP(D24,Multiplier!B:H,3,0)</f>
         <v>1749</v>
       </c>
-      <c r="P24" s="27">
-        <f>-1749*3</f>
-        <v>-5247</v>
-      </c>
+      <c r="P24" s="27"/>
       <c r="Q24" s="27"/>
       <c r="R24" s="28">
         <f t="shared" ref="R24" si="33">(1-Q24)*P24*J24*H24</f>
-        <v>-26235</v>
+        <v>0</v>
       </c>
       <c r="S24" s="29">
         <f t="shared" ref="S24" si="34">IF(OR(F24="Futures",F24="Spot"),IF(I24=0,0,IF(I24&gt;0,L24-O24,L24+O24)),0)</f>
-        <v>56841</v>
+        <v>0</v>
       </c>
       <c r="T24" s="3">
         <f t="shared" ref="T24" si="35">IF(S24&gt;0,IF(ISNUMBER(S24/L24-1),S24/L24-1,0),0)</f>
-        <v>-2.9851510496671785E-2</v>
+        <v>0</v>
       </c>
       <c r="U24" s="29">
         <f t="shared" ref="U24" si="36">IF(OR(F24="Futures",F24="Stocks"),IF(I24=0,0,IF(I24&gt;0,K24-P24,K24+P24)),0)</f>
-        <v>54914.851999999999</v>
+        <v>0</v>
       </c>
       <c r="V24" s="3">
         <f t="shared" ref="V24" si="37">IF(U24&gt;0,IF(ISNUMBER(U24/L24-1),U24/L24-1,0),0)</f>
-        <v>-6.272654036525005E-2</v>
+        <v>0</v>
       </c>
       <c r="X24" s="34">
         <f t="array" ref="X24">IF(ISNUMBER(SUM((Trades!T$2:T$9999=Blotter!C24)*(Trades!U$2:U$9999=Blotter!B24)*(Trades!W$2:W$9999)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0))/SUM((Trades!T$2:T$9999=Blotter!C24)*(Trades!U$2:U$9999=Blotter!B24)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0))),SUM((Trades!T$2:T$9999=Blotter!C24)*(Trades!U$2:U$9999=Blotter!B24)*(Trades!W$2:W$9999)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0))/SUM((Trades!T$2:T$9999=Blotter!C24)*(Trades!U$2:U$9999=Blotter!B24)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0)),0)</f>
-        <v>51468.333333333336</v>
+        <v>52679.285714285717</v>
       </c>
       <c r="Y24" s="34">
         <f t="array" ref="Y24">IF(ISNUMBER(SUM((Trades!T$2:T$9999=Blotter!C24)*(Trades!U$2:U$9999=Blotter!B24)*(Trades!W$2:W$9999)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&gt;0))/SUM((Trades!T$2:T$9999=Blotter!C24)*(Trades!U$2:U$9999=Blotter!B24)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&gt;0))),SUM((Trades!T$2:T$9999=Blotter!C24)*(Trades!U$2:U$9999=Blotter!B24)*(Trades!W$2:W$9999)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&gt;0))/SUM((Trades!T$2:T$9999=Blotter!C24)*(Trades!U$2:U$9999=Blotter!B24)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&gt;0)),0)</f>
@@ -4914,7 +4923,7 @@
       </c>
       <c r="Z24" s="35">
         <f>IF(C$2="Last",IF(ISNUMBER(VLOOKUP(B24,Prices!A:L,8,0)),VLOOKUP(B24,Prices!A:L,8,0),0),IF(ISNUMBER(VLOOKUP(B24,Prices!A:L,12,0)),VLOOKUP(B24,Prices!A:L,12,0),0))</f>
-        <v>58590</v>
+        <v>59350</v>
       </c>
       <c r="AB24" s="29"/>
     </row>
@@ -4955,15 +4964,15 @@
       </c>
       <c r="L25" s="29">
         <f t="shared" ref="L25:L26" si="39">IF(I25=0,IF(H25&gt;0,X25,Y25),Z25)</f>
-        <v>16.399999999999999</v>
+        <v>12.6</v>
       </c>
       <c r="M25" s="28">
         <f t="shared" ref="M25:M26" si="40">I25*J25*L25</f>
-        <v>-1639.9999999999998</v>
+        <v>-1260</v>
       </c>
       <c r="N25" s="95">
         <f t="array" ref="N25">-SUM((Trades!T$2:T$9999=Blotter!C25)*(Trades!U$2:U$9999=Blotter!B25)*(Trades!V$2:V$9999)*(Trades!W$2:W$9999))*J25+SUM((Trades!T$2:T$9999=Blotter!C25)*(Trades!U$2:U$9999=Blotter!B25)*(Trades!X$2:X$9999))+(L25*I25)*J25</f>
-        <v>997.48000000000025</v>
+        <v>1377.48</v>
       </c>
       <c r="O25" s="29">
         <f>VLOOKUP(D25,Multiplier!B:H,3,0)</f>
@@ -5003,7 +5012,7 @@
       </c>
       <c r="Z25" s="35">
         <f>IF(C$2="Last",IF(ISNUMBER(VLOOKUP(B25,Prices!A:L,8,0)),VLOOKUP(B25,Prices!A:L,8,0),0),IF(ISNUMBER(VLOOKUP(B25,Prices!A:L,12,0)),VLOOKUP(B25,Prices!A:L,12,0),0))</f>
-        <v>16.399999999999999</v>
+        <v>12.6</v>
       </c>
       <c r="AB25" s="29"/>
     </row>
@@ -5044,15 +5053,15 @@
       </c>
       <c r="L26" s="29">
         <f t="shared" si="39"/>
-        <v>116.5</v>
+        <v>101.5</v>
       </c>
       <c r="M26" s="28">
         <f t="shared" si="40"/>
-        <v>11650</v>
+        <v>10150</v>
       </c>
       <c r="N26" s="95">
         <f t="array" ref="N26">-SUM((Trades!T$2:T$9999=Blotter!C26)*(Trades!U$2:U$9999=Blotter!B26)*(Trades!V$2:V$9999)*(Trades!W$2:W$9999))*J26+SUM((Trades!T$2:T$9999=Blotter!C26)*(Trades!U$2:U$9999=Blotter!B26)*(Trades!X$2:X$9999))+(L26*I26)*J26</f>
-        <v>-892.52000000000044</v>
+        <v>-2392.5200000000004</v>
       </c>
       <c r="O26" s="29">
         <f>VLOOKUP(D26,Multiplier!B:H,3,0)</f>
@@ -5092,7 +5101,7 @@
       </c>
       <c r="Z26" s="35">
         <f>IF(C$2="Last",IF(ISNUMBER(VLOOKUP(B26,Prices!A:L,8,0)),VLOOKUP(B26,Prices!A:L,8,0),0),IF(ISNUMBER(VLOOKUP(B26,Prices!A:L,12,0)),VLOOKUP(B26,Prices!A:L,12,0),0))</f>
-        <v>116.5</v>
+        <v>101.5</v>
       </c>
       <c r="AB26" s="29"/>
     </row>
@@ -5129,19 +5138,19 @@
       </c>
       <c r="K27" s="99">
         <f t="shared" ref="K27" si="46">L27-N27/(H27*J27)</f>
-        <v>1.17215</v>
+        <v>1.1721499999999998</v>
       </c>
       <c r="L27" s="99">
         <f t="shared" ref="L27" si="47">IF(I27=0,IF(H27&gt;0,X27,Y27),Z27)</f>
-        <v>1.1834499999999999</v>
+        <v>1.1812</v>
       </c>
       <c r="M27" s="28">
         <f t="shared" ref="M27" si="48">I27*J27*L27</f>
-        <v>739656.24999999988</v>
+        <v>738250</v>
       </c>
       <c r="N27" s="95">
         <f t="array" ref="N27">-SUM((Trades!T$2:T$9999=Blotter!C27)*(Trades!U$2:U$9999=Blotter!B27)*(Trades!V$2:V$9999)*(Trades!W$2:W$9999))*J27+SUM((Trades!T$2:T$9999=Blotter!C27)*(Trades!U$2:U$9999=Blotter!B27)*(Trades!X$2:X$9999))+(L27*I27)*J27</f>
-        <v>7062.4999999998836</v>
+        <v>5656.2500000001164</v>
       </c>
       <c r="O27" s="46">
         <f>VLOOKUP(D27,Multiplier!B:H,3,0)</f>
@@ -5158,19 +5167,19 @@
       </c>
       <c r="S27" s="29">
         <f t="shared" ref="S27" si="50">IF(OR(F27="Futures",F27="Spot"),IF(I27=0,0,IF(I27&gt;0,L27-O27,L27+O27)),0)</f>
-        <v>1.1739999999999999</v>
+        <v>1.1717500000000001</v>
       </c>
       <c r="T27" s="3">
         <f t="shared" ref="T27" si="51">IF(S27&gt;0,IF(ISNUMBER(S27/L27-1),S27/L27-1,0),0)</f>
-        <v>-7.9851282267945356E-3</v>
+        <v>-8.000338638672555E-3</v>
       </c>
       <c r="U27" s="29">
         <f t="shared" ref="U27" si="52">IF(OR(F27="Futures",F27="Stocks"),IF(I27=0,0,IF(I27&gt;0,K27-P27,K27+P27)),0)</f>
-        <v>1.157975</v>
+        <v>1.1579749999999998</v>
       </c>
       <c r="V27" s="3">
         <f t="shared" ref="V27" si="53">IF(U27&gt;0,IF(ISNUMBER(U27/L27-1),U27/L27-1,0),0)</f>
-        <v>-2.1526046727787351E-2</v>
+        <v>-1.9662207924145192E-2</v>
       </c>
       <c r="X27" s="34">
         <f t="array" ref="X27">IF(ISNUMBER(SUM((Trades!T$2:T$9999=Blotter!C27)*(Trades!U$2:U$9999=Blotter!B27)*(Trades!W$2:W$9999)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0))/SUM((Trades!T$2:T$9999=Blotter!C27)*(Trades!U$2:U$9999=Blotter!B27)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0))),SUM((Trades!T$2:T$9999=Blotter!C27)*(Trades!U$2:U$9999=Blotter!B27)*(Trades!W$2:W$9999)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0))/SUM((Trades!T$2:T$9999=Blotter!C27)*(Trades!U$2:U$9999=Blotter!B27)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0)),0)</f>
@@ -5182,7 +5191,7 @@
       </c>
       <c r="Z27" s="35">
         <f>IF(C$2="Last",IF(ISNUMBER(VLOOKUP(B27,Prices!A:L,8,0)),VLOOKUP(B27,Prices!A:L,8,0),0),IF(ISNUMBER(VLOOKUP(B27,Prices!A:L,12,0)),VLOOKUP(B27,Prices!A:L,12,0),0))</f>
-        <v>1.1834499999999999</v>
+        <v>1.1812</v>
       </c>
       <c r="AB27" s="29"/>
     </row>
@@ -6780,31 +6789,31 @@
         <v>59</v>
       </c>
       <c r="H2" s="91">
-        <v>7067.5</v>
+        <v>-1</v>
       </c>
       <c r="I2" s="91">
-        <v>7067.25</v>
+        <v>-1</v>
       </c>
       <c r="J2" s="91">
-        <v>7067.5</v>
+        <v>-1</v>
       </c>
       <c r="K2" s="91">
-        <v>7067.375</v>
+        <v>-1</v>
       </c>
       <c r="L2" s="91">
-        <v>7060.5</v>
+        <v>7077</v>
       </c>
       <c r="M2" s="91">
-        <v>7057.25</v>
+        <v>7077.25</v>
       </c>
       <c r="N2" s="91">
-        <v>7078.5</v>
+        <v>7185.75</v>
       </c>
       <c r="O2" s="91">
-        <v>7055.5</v>
+        <v>7075.25</v>
       </c>
       <c r="P2" s="91">
-        <v>90518</v>
+        <v>1665226</v>
       </c>
       <c r="Q2" s="91"/>
       <c r="R2" s="91"/>
@@ -6812,7 +6821,7 @@
       <c r="T2" s="91"/>
       <c r="U2" s="91"/>
       <c r="V2" s="85">
-        <v>46128.481365740743</v>
+        <v>46130.458333333336</v>
       </c>
       <c r="W2" s="81" t="s">
         <v>258</v>
@@ -6844,31 +6853,31 @@
         <v>59</v>
       </c>
       <c r="H3" s="91">
-        <v>26448.5</v>
+        <v>-1</v>
       </c>
       <c r="I3" s="91">
-        <v>26447.75</v>
+        <v>-1</v>
       </c>
       <c r="J3" s="91">
-        <v>26448.5</v>
+        <v>-1</v>
       </c>
       <c r="K3" s="91">
-        <v>26448.125</v>
+        <v>-1</v>
       </c>
       <c r="L3" s="91">
-        <v>26365.5</v>
+        <v>26487.25</v>
       </c>
       <c r="M3" s="91">
-        <v>26350</v>
+        <v>26460</v>
       </c>
       <c r="N3" s="91">
-        <v>26488</v>
+        <v>26884.75</v>
       </c>
       <c r="O3" s="91">
-        <v>26345</v>
+        <v>26440</v>
       </c>
       <c r="P3" s="91">
-        <v>60884</v>
+        <v>582607</v>
       </c>
       <c r="Q3" s="91"/>
       <c r="R3" s="91"/>
@@ -6876,7 +6885,7 @@
       <c r="T3" s="91"/>
       <c r="U3" s="91"/>
       <c r="V3" s="85">
-        <v>46128.481365740743</v>
+        <v>46130.458333333336</v>
       </c>
       <c r="W3" s="81" t="s">
         <v>258</v>
@@ -6908,31 +6917,27 @@
         <v>59</v>
       </c>
       <c r="H4" s="91">
-        <v>2724.3</v>
+        <v>-1</v>
       </c>
       <c r="I4" s="91">
-        <v>2724.2</v>
+        <v>-1</v>
       </c>
       <c r="J4" s="91">
-        <v>2724.4</v>
+        <v>-1</v>
       </c>
       <c r="K4" s="91">
-        <v>2724.3</v>
+        <v>-1</v>
       </c>
       <c r="L4" s="91">
-        <v>2725.5</v>
+        <v>2730.8</v>
       </c>
       <c r="M4" s="91">
-        <v>2724.6</v>
-      </c>
-      <c r="N4" s="91">
-        <v>2731</v>
-      </c>
-      <c r="O4" s="91">
-        <v>2722.8</v>
-      </c>
+        <v>2733</v>
+      </c>
+      <c r="N4" s="91"/>
+      <c r="O4" s="91"/>
       <c r="P4" s="91">
-        <v>9535</v>
+        <v>0</v>
       </c>
       <c r="Q4" s="91"/>
       <c r="R4" s="91"/>
@@ -6940,7 +6945,7 @@
       <c r="T4" s="91"/>
       <c r="U4" s="91"/>
       <c r="V4" s="85">
-        <v>46128.481365740743</v>
+        <v>46130.458333333336</v>
       </c>
       <c r="W4" s="81" t="s">
         <v>258</v>
@@ -6972,31 +6977,27 @@
         <v>56</v>
       </c>
       <c r="H5" s="91">
-        <v>24311</v>
+        <v>24820</v>
       </c>
       <c r="I5" s="91">
-        <v>24309</v>
+        <v>-1</v>
       </c>
       <c r="J5" s="91">
-        <v>24312</v>
+        <v>-1</v>
       </c>
       <c r="K5" s="91">
-        <v>24310.5</v>
+        <v>-1</v>
       </c>
       <c r="L5" s="91">
-        <v>24258</v>
+        <v>24319</v>
       </c>
       <c r="M5" s="91">
-        <v>24276</v>
-      </c>
-      <c r="N5" s="91">
-        <v>24356</v>
-      </c>
-      <c r="O5" s="91">
-        <v>24222</v>
-      </c>
+        <v>24275</v>
+      </c>
+      <c r="N5" s="91"/>
+      <c r="O5" s="91"/>
       <c r="P5" s="91">
-        <v>6818</v>
+        <v>0</v>
       </c>
       <c r="Q5" s="91"/>
       <c r="R5" s="91"/>
@@ -7004,7 +7005,7 @@
       <c r="T5" s="91"/>
       <c r="U5" s="91"/>
       <c r="V5" s="85">
-        <v>46128.481365740743</v>
+        <v>46130.458333333336</v>
       </c>
       <c r="W5" s="81" t="s">
         <v>258</v>
@@ -7036,31 +7037,27 @@
         <v>59</v>
       </c>
       <c r="H6" s="91">
-        <v>59410</v>
+        <v>0</v>
       </c>
       <c r="I6" s="91">
-        <v>59420</v>
+        <v>0</v>
       </c>
       <c r="J6" s="91">
-        <v>59430</v>
+        <v>0</v>
       </c>
       <c r="K6" s="91">
-        <v>59425</v>
+        <v>0</v>
       </c>
       <c r="L6" s="91">
-        <v>58590</v>
+        <v>59350</v>
       </c>
       <c r="M6" s="91">
-        <v>58645</v>
-      </c>
-      <c r="N6" s="91">
-        <v>59805</v>
-      </c>
-      <c r="O6" s="91">
-        <v>58585</v>
-      </c>
+        <v>59440</v>
+      </c>
+      <c r="N6" s="91"/>
+      <c r="O6" s="91"/>
       <c r="P6" s="91">
-        <v>1989</v>
+        <v>0</v>
       </c>
       <c r="Q6" s="91"/>
       <c r="R6" s="91"/>
@@ -7068,7 +7065,7 @@
       <c r="T6" s="91"/>
       <c r="U6" s="91"/>
       <c r="V6" s="85">
-        <v>46128.481365740743</v>
+        <v>46130.458333333336</v>
       </c>
       <c r="W6" s="81" t="s">
         <v>258</v>
@@ -7111,7 +7108,7 @@
       <c r="T7" s="93"/>
       <c r="U7" s="93"/>
       <c r="V7" s="92">
-        <v>46128.481365740743</v>
+        <v>46130.458333333336</v>
       </c>
       <c r="W7" s="1" t="s">
         <v>313</v>
@@ -7140,31 +7137,27 @@
         <v>59</v>
       </c>
       <c r="H8" s="93">
-        <v>2.7570000000000001</v>
+        <v>-1</v>
       </c>
       <c r="I8" s="93">
-        <v>2.7570000000000001</v>
+        <v>-1</v>
       </c>
       <c r="J8" s="93">
-        <v>2.758</v>
+        <v>-1</v>
       </c>
       <c r="K8" s="93">
-        <v>2.7575000000000003</v>
+        <v>-1</v>
       </c>
       <c r="L8" s="93">
-        <v>2.7669999999999999</v>
+        <v>2.7909999999999999</v>
       </c>
       <c r="M8" s="93">
-        <v>2.7679999999999998</v>
-      </c>
-      <c r="N8" s="93">
-        <v>2.7770000000000001</v>
-      </c>
-      <c r="O8" s="93">
-        <v>2.7410000000000001</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N8" s="93"/>
+      <c r="O8" s="93"/>
       <c r="P8" s="93">
-        <v>4043</v>
+        <v>0</v>
       </c>
       <c r="Q8" s="93"/>
       <c r="R8" s="93"/>
@@ -7172,7 +7165,7 @@
       <c r="T8" s="93"/>
       <c r="U8" s="93"/>
       <c r="V8" s="92">
-        <v>46128.481365740743</v>
+        <v>46130.458333333336</v>
       </c>
       <c r="W8" s="1" t="s">
         <v>258</v>
@@ -7201,31 +7194,27 @@
         <v>59</v>
       </c>
       <c r="H9" s="93">
-        <v>3.0274999999999999</v>
+        <v>-1</v>
       </c>
       <c r="I9" s="93">
-        <v>3.0276999999999998</v>
+        <v>-1</v>
       </c>
       <c r="J9" s="93">
-        <v>3.0284</v>
+        <v>-1</v>
       </c>
       <c r="K9" s="93">
-        <v>3.0280499999999999</v>
+        <v>-1</v>
       </c>
       <c r="L9" s="93">
-        <v>3.0051000000000001</v>
+        <v>3.0912999999999999</v>
       </c>
       <c r="M9" s="93">
-        <v>2.9980000000000002</v>
-      </c>
-      <c r="N9" s="93">
-        <v>3.0348999999999999</v>
-      </c>
-      <c r="O9" s="93">
-        <v>2.9849999999999999</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N9" s="93"/>
+      <c r="O9" s="93"/>
       <c r="P9" s="93">
-        <v>5521</v>
+        <v>0</v>
       </c>
       <c r="Q9" s="93"/>
       <c r="R9" s="93"/>
@@ -7233,7 +7222,7 @@
       <c r="T9" s="93"/>
       <c r="U9" s="93"/>
       <c r="V9" s="92">
-        <v>46128.481365740743</v>
+        <v>46130.458333333336</v>
       </c>
       <c r="W9" s="1" t="s">
         <v>258</v>
@@ -7262,31 +7251,27 @@
         <v>59</v>
       </c>
       <c r="H10" s="93">
-        <v>4838.1000000000004</v>
+        <v>-1</v>
       </c>
       <c r="I10" s="93">
-        <v>4837.7</v>
+        <v>-1</v>
       </c>
       <c r="J10" s="93">
-        <v>4838.1000000000004</v>
+        <v>-1</v>
       </c>
       <c r="K10" s="93">
-        <v>4837.8999999999996</v>
+        <v>-1</v>
       </c>
       <c r="L10" s="93">
-        <v>4823.6000000000004</v>
+        <v>4808.3</v>
       </c>
       <c r="M10" s="93">
-        <v>4813.6000000000004</v>
-      </c>
-      <c r="N10" s="93">
-        <v>4861.3</v>
-      </c>
-      <c r="O10" s="93">
-        <v>4812.3999999999996</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N10" s="93"/>
+      <c r="O10" s="93"/>
       <c r="P10" s="93">
-        <v>43133</v>
+        <v>0</v>
       </c>
       <c r="Q10" s="93"/>
       <c r="R10" s="93"/>
@@ -7294,7 +7279,7 @@
       <c r="T10" s="93"/>
       <c r="U10" s="93"/>
       <c r="V10" s="92">
-        <v>46128.481365740743</v>
+        <v>46130.458333333336</v>
       </c>
       <c r="W10" s="1" t="s">
         <v>258</v>
@@ -7323,31 +7308,31 @@
         <v>59</v>
       </c>
       <c r="H11" s="93">
-        <v>80.209999999999994</v>
+        <v>81.224999999999994</v>
       </c>
       <c r="I11" s="93">
-        <v>80.099999999999994</v>
+        <v>-1</v>
       </c>
       <c r="J11" s="93">
-        <v>80.13</v>
+        <v>-1</v>
       </c>
       <c r="K11" s="93">
-        <v>80.114999999999995</v>
+        <v>-1</v>
       </c>
       <c r="L11" s="93">
-        <v>79.915000000000006</v>
+        <v>78.989999999999995</v>
       </c>
       <c r="M11" s="93">
-        <v>79.894999999999996</v>
+        <v>0</v>
       </c>
       <c r="N11" s="93">
-        <v>81.165000000000006</v>
+        <v>83.44</v>
       </c>
       <c r="O11" s="93">
-        <v>79.894999999999996</v>
+        <v>78.234999999999999</v>
       </c>
       <c r="P11" s="93">
-        <v>312</v>
+        <v>890</v>
       </c>
       <c r="Q11" s="93"/>
       <c r="R11" s="93"/>
@@ -7355,7 +7340,7 @@
       <c r="T11" s="93"/>
       <c r="U11" s="93"/>
       <c r="V11" s="92">
-        <v>46128.481365740743</v>
+        <v>46130.458333333336</v>
       </c>
       <c r="W11" s="1" t="s">
         <v>258</v>
@@ -7384,31 +7369,27 @@
         <v>59</v>
       </c>
       <c r="H12" s="93">
-        <v>6.0945</v>
+        <v>-1</v>
       </c>
       <c r="I12" s="93">
-        <v>6.0934999999999997</v>
+        <v>-1</v>
       </c>
       <c r="J12" s="93">
-        <v>6.0949999999999998</v>
+        <v>-1</v>
       </c>
       <c r="K12" s="93">
-        <v>6.0942499999999997</v>
+        <v>-1</v>
       </c>
       <c r="L12" s="93">
-        <v>6.085</v>
+        <v>6.0765000000000002</v>
       </c>
       <c r="M12" s="93">
-        <v>6.0754999999999999</v>
-      </c>
-      <c r="N12" s="93">
-        <v>6.1319999999999997</v>
-      </c>
-      <c r="O12" s="93">
-        <v>6.0754999999999999</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N12" s="93"/>
+      <c r="O12" s="93"/>
       <c r="P12" s="93">
-        <v>7554</v>
+        <v>0</v>
       </c>
       <c r="Q12" s="93"/>
       <c r="R12" s="93"/>
@@ -7416,7 +7397,7 @@
       <c r="T12" s="93"/>
       <c r="U12" s="93"/>
       <c r="V12" s="92">
-        <v>46128.481365740743</v>
+        <v>46130.458333333336</v>
       </c>
       <c r="W12" s="1" t="s">
         <v>258</v>
@@ -7445,31 +7426,27 @@
         <v>59</v>
       </c>
       <c r="H13" s="93">
-        <v>450.75</v>
+        <v>-100</v>
       </c>
       <c r="I13" s="93">
-        <v>450.75</v>
+        <v>-100</v>
       </c>
       <c r="J13" s="93">
-        <v>451</v>
+        <v>-100</v>
       </c>
       <c r="K13" s="93">
-        <v>450.875</v>
+        <v>-100</v>
       </c>
       <c r="L13" s="93">
-        <v>451.25</v>
+        <v>448.5</v>
       </c>
       <c r="M13" s="93">
-        <v>451</v>
-      </c>
-      <c r="N13" s="93">
-        <v>452.75</v>
-      </c>
-      <c r="O13" s="93">
-        <v>449.75</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N13" s="93"/>
+      <c r="O13" s="93"/>
       <c r="P13" s="93">
-        <v>21091</v>
+        <v>0</v>
       </c>
       <c r="Q13" s="93"/>
       <c r="R13" s="93"/>
@@ -7477,7 +7454,7 @@
       <c r="T13" s="93"/>
       <c r="U13" s="93"/>
       <c r="V13" s="92">
-        <v>46128.481365740743</v>
+        <v>46130.458333333336</v>
       </c>
       <c r="W13" s="1" t="s">
         <v>258</v>
@@ -7506,31 +7483,27 @@
         <v>59</v>
       </c>
       <c r="H14" s="93">
-        <v>602.25</v>
+        <v>-100</v>
       </c>
       <c r="I14" s="93">
-        <v>602</v>
+        <v>-100</v>
       </c>
       <c r="J14" s="93">
-        <v>602.25</v>
+        <v>-100</v>
       </c>
       <c r="K14" s="93">
-        <v>602.125</v>
+        <v>-100</v>
       </c>
       <c r="L14" s="93">
-        <v>593.75</v>
+        <v>598.5</v>
       </c>
       <c r="M14" s="93">
-        <v>593</v>
-      </c>
-      <c r="N14" s="93">
-        <v>602.75</v>
-      </c>
-      <c r="O14" s="93">
-        <v>590.75</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N14" s="93"/>
+      <c r="O14" s="93"/>
       <c r="P14" s="93">
-        <v>8824</v>
+        <v>0</v>
       </c>
       <c r="Q14" s="93"/>
       <c r="R14" s="93"/>
@@ -7538,7 +7511,7 @@
       <c r="T14" s="93"/>
       <c r="U14" s="93"/>
       <c r="V14" s="92">
-        <v>46128.481365740743</v>
+        <v>46130.458333333336</v>
       </c>
       <c r="W14" s="1" t="s">
         <v>258</v>
@@ -7567,31 +7540,27 @@
         <v>59</v>
       </c>
       <c r="H15" s="93">
-        <v>1166.25</v>
+        <v>-100</v>
       </c>
       <c r="I15" s="93">
-        <v>1166.25</v>
+        <v>-100</v>
       </c>
       <c r="J15" s="93">
-        <v>1166.5</v>
+        <v>-100</v>
       </c>
       <c r="K15" s="93">
-        <v>1166.375</v>
+        <v>-100</v>
       </c>
       <c r="L15" s="93">
-        <v>1167</v>
+        <v>1163.75</v>
       </c>
       <c r="M15" s="93">
-        <v>1165.75</v>
-      </c>
-      <c r="N15" s="93">
-        <v>1169.5</v>
-      </c>
-      <c r="O15" s="93">
-        <v>1164</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N15" s="93"/>
+      <c r="O15" s="93"/>
       <c r="P15" s="93">
-        <v>25067</v>
+        <v>0</v>
       </c>
       <c r="Q15" s="93"/>
       <c r="R15" s="93"/>
@@ -7599,7 +7568,7 @@
       <c r="T15" s="93"/>
       <c r="U15" s="93"/>
       <c r="V15" s="92">
-        <v>46128.481365740743</v>
+        <v>46130.458333333336</v>
       </c>
       <c r="W15" s="1" t="s">
         <v>258</v>
@@ -7628,31 +7597,31 @@
         <v>59</v>
       </c>
       <c r="H16" s="93">
-        <v>13.63</v>
+        <v>13.33</v>
       </c>
       <c r="I16" s="93">
-        <v>13.62</v>
+        <v>-100</v>
       </c>
       <c r="J16" s="93">
-        <v>13.63</v>
+        <v>-100</v>
       </c>
       <c r="K16" s="93">
-        <v>13.625</v>
+        <v>-100</v>
       </c>
       <c r="L16" s="93">
-        <v>13.51</v>
+        <v>13.66</v>
       </c>
       <c r="M16" s="93">
-        <v>13.58</v>
+        <v>0</v>
       </c>
       <c r="N16" s="93">
-        <v>13.68</v>
+        <v>13.74</v>
       </c>
       <c r="O16" s="93">
-        <v>13.55</v>
+        <v>13.22</v>
       </c>
       <c r="P16" s="93">
-        <v>6355</v>
+        <v>24940</v>
       </c>
       <c r="Q16" s="93"/>
       <c r="R16" s="93"/>
@@ -7660,7 +7629,7 @@
       <c r="T16" s="93"/>
       <c r="U16" s="93"/>
       <c r="V16" s="92">
-        <v>46128.481365740743</v>
+        <v>46130.458333333336</v>
       </c>
       <c r="W16" s="1" t="s">
         <v>258</v>
@@ -7689,31 +7658,31 @@
         <v>59</v>
       </c>
       <c r="H17" s="93">
-        <v>299.35000000000002</v>
+        <v>288.64999999999998</v>
       </c>
       <c r="I17" s="93">
-        <v>299.2</v>
+        <v>-100</v>
       </c>
       <c r="J17" s="93">
-        <v>299.35000000000002</v>
+        <v>-100</v>
       </c>
       <c r="K17" s="93">
-        <v>299.27499999999998</v>
+        <v>-100</v>
       </c>
       <c r="L17" s="93">
-        <v>304.25</v>
+        <v>296.45</v>
       </c>
       <c r="M17" s="93">
-        <v>302.75</v>
+        <v>0</v>
       </c>
       <c r="N17" s="93">
-        <v>303.60000000000002</v>
+        <v>298.5</v>
       </c>
       <c r="O17" s="93">
-        <v>298.8</v>
+        <v>288.35000000000002</v>
       </c>
       <c r="P17" s="93">
-        <v>457</v>
+        <v>4534</v>
       </c>
       <c r="Q17" s="93"/>
       <c r="R17" s="93"/>
@@ -7721,7 +7690,7 @@
       <c r="T17" s="93"/>
       <c r="U17" s="93"/>
       <c r="V17" s="92">
-        <v>46128.481365740743</v>
+        <v>46130.458333333336</v>
       </c>
       <c r="W17" s="1" t="s">
         <v>258</v>
@@ -7750,31 +7719,31 @@
         <v>59</v>
       </c>
       <c r="H18" s="93">
-        <v>3469</v>
+        <v>3208</v>
       </c>
       <c r="I18" s="93">
-        <v>3469</v>
+        <v>-1</v>
       </c>
       <c r="J18" s="93">
-        <v>3473</v>
+        <v>-1</v>
       </c>
       <c r="K18" s="93">
-        <v>3471</v>
+        <v>-1</v>
       </c>
       <c r="L18" s="93">
-        <v>3477</v>
+        <v>3367</v>
       </c>
       <c r="M18" s="93">
-        <v>3436</v>
+        <v>0</v>
       </c>
       <c r="N18" s="93">
-        <v>3473</v>
+        <v>3468</v>
       </c>
       <c r="O18" s="93">
-        <v>3367</v>
+        <v>3173</v>
       </c>
       <c r="P18" s="93">
-        <v>293</v>
+        <v>6078</v>
       </c>
       <c r="Q18" s="93"/>
       <c r="R18" s="93"/>
@@ -7782,7 +7751,7 @@
       <c r="T18" s="93"/>
       <c r="U18" s="93"/>
       <c r="V18" s="92">
-        <v>46128.481365740743</v>
+        <v>46130.458333333336</v>
       </c>
       <c r="W18" s="1" t="s">
         <v>258</v>
@@ -7811,31 +7780,31 @@
         <v>59</v>
       </c>
       <c r="H19" s="93">
-        <v>75.92</v>
+        <v>77.48</v>
       </c>
       <c r="I19" s="93">
-        <v>75.91</v>
+        <v>-100</v>
       </c>
       <c r="J19" s="93">
-        <v>75.930000000000007</v>
+        <v>-100</v>
       </c>
       <c r="K19" s="93">
-        <v>75.92</v>
+        <v>-100</v>
       </c>
       <c r="L19" s="93">
-        <v>75.11</v>
+        <v>75.7</v>
       </c>
       <c r="M19" s="93">
-        <v>75.150000000000006</v>
+        <v>0</v>
       </c>
       <c r="N19" s="93">
-        <v>76.09</v>
+        <v>77.5</v>
       </c>
       <c r="O19" s="93">
-        <v>75.08</v>
+        <v>74.33</v>
       </c>
       <c r="P19" s="93">
-        <v>1977</v>
+        <v>11251</v>
       </c>
       <c r="Q19" s="93"/>
       <c r="R19" s="93"/>
@@ -7843,7 +7812,7 @@
       <c r="T19" s="93"/>
       <c r="U19" s="93"/>
       <c r="V19" s="92">
-        <v>46128.481365740743</v>
+        <v>46130.458333333336</v>
       </c>
       <c r="W19" s="1" t="s">
         <v>258</v>
@@ -7872,7 +7841,7 @@
         <v>59</v>
       </c>
       <c r="H20" s="93">
-        <v>-100</v>
+        <v>249.75</v>
       </c>
       <c r="I20" s="93">
         <v>-100</v>
@@ -7884,19 +7853,15 @@
         <v>-100</v>
       </c>
       <c r="L20" s="93">
-        <v>252.6</v>
+        <v>250.3</v>
       </c>
       <c r="M20" s="93">
-        <v>252.55</v>
-      </c>
-      <c r="N20" s="93">
-        <v>253.52500000000001</v>
-      </c>
-      <c r="O20" s="93">
-        <v>251.55</v>
-      </c>
+        <v>250.375</v>
+      </c>
+      <c r="N20" s="93"/>
+      <c r="O20" s="93"/>
       <c r="P20" s="93">
-        <v>2158</v>
+        <v>0</v>
       </c>
       <c r="Q20" s="93"/>
       <c r="R20" s="93"/>
@@ -7904,7 +7869,7 @@
       <c r="T20" s="93"/>
       <c r="U20" s="93"/>
       <c r="V20" s="92">
-        <v>46128.481365740743</v>
+        <v>46130.458333333336</v>
       </c>
       <c r="W20" s="1" t="s">
         <v>258</v>
@@ -7933,7 +7898,7 @@
         <v>59</v>
       </c>
       <c r="H21" s="93">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I21" s="93">
         <v>-100</v>
@@ -7945,10 +7910,10 @@
         <v>-100</v>
       </c>
       <c r="L21" s="93">
-        <v>370.95</v>
+        <v>367.1</v>
       </c>
       <c r="M21" s="93">
-        <v>374.95</v>
+        <v>0</v>
       </c>
       <c r="N21" s="93"/>
       <c r="O21" s="93"/>
@@ -7961,7 +7926,7 @@
       <c r="T21" s="93"/>
       <c r="U21" s="93"/>
       <c r="V21" s="92">
-        <v>46128.481365740743</v>
+        <v>46130.458333333336</v>
       </c>
       <c r="W21" s="1" t="s">
         <v>258</v>
@@ -7990,7 +7955,7 @@
         <v>59</v>
       </c>
       <c r="H22" s="93">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I22" s="93">
         <v>-100</v>
@@ -8018,7 +7983,7 @@
       <c r="T22" s="93"/>
       <c r="U22" s="93"/>
       <c r="V22" s="92">
-        <v>46128.481365740743</v>
+        <v>46130.458333333336</v>
       </c>
       <c r="W22" s="1" t="s">
         <v>258</v>
@@ -8047,31 +8012,31 @@
         <v>59</v>
       </c>
       <c r="H23" s="93">
-        <v>97.974999999999994</v>
+        <v>98.07</v>
       </c>
       <c r="I23" s="93">
-        <v>97.984999999999999</v>
+        <v>-1</v>
       </c>
       <c r="J23" s="93">
-        <v>97.99</v>
+        <v>-1</v>
       </c>
       <c r="K23" s="93">
-        <v>97.987499999999997</v>
+        <v>-1</v>
       </c>
       <c r="L23" s="93">
-        <v>97.85</v>
+        <v>98.02</v>
       </c>
       <c r="M23" s="93">
-        <v>97.82</v>
+        <v>0</v>
       </c>
       <c r="N23" s="93">
-        <v>98.004999999999995</v>
+        <v>98.1</v>
       </c>
       <c r="O23" s="93">
-        <v>97.63</v>
+        <v>97.424999999999997</v>
       </c>
       <c r="P23" s="93">
-        <v>3910</v>
+        <v>29322</v>
       </c>
       <c r="Q23" s="93"/>
       <c r="R23" s="93"/>
@@ -8079,7 +8044,7 @@
       <c r="T23" s="93"/>
       <c r="U23" s="93"/>
       <c r="V23" s="92">
-        <v>46128.481365740743</v>
+        <v>46130.458333333336</v>
       </c>
       <c r="W23" s="1" t="s">
         <v>258</v>
@@ -8108,31 +8073,27 @@
         <v>59</v>
       </c>
       <c r="H24" s="93">
-        <v>1.1811499999999999</v>
+        <v>-1</v>
       </c>
       <c r="I24" s="93">
-        <v>1.1811</v>
+        <v>-1</v>
       </c>
       <c r="J24" s="93">
-        <v>1.1811499999999999</v>
+        <v>-1</v>
       </c>
       <c r="K24" s="93">
-        <v>1.181125</v>
+        <v>-1</v>
       </c>
       <c r="L24" s="93">
-        <v>1.1834499999999999</v>
+        <v>1.1812</v>
       </c>
       <c r="M24" s="93">
-        <v>1.1830000000000001</v>
-      </c>
-      <c r="N24" s="93">
-        <v>1.1856500000000001</v>
-      </c>
-      <c r="O24" s="93">
-        <v>1.18085</v>
-      </c>
+        <v>1.1813</v>
+      </c>
+      <c r="N24" s="93"/>
+      <c r="O24" s="93"/>
       <c r="P24" s="93">
-        <v>39932</v>
+        <v>0</v>
       </c>
       <c r="Q24" s="93"/>
       <c r="R24" s="93"/>
@@ -8140,7 +8101,7 @@
       <c r="T24" s="93"/>
       <c r="U24" s="93"/>
       <c r="V24" s="92">
-        <v>46128.481365740743</v>
+        <v>46130.458333333336</v>
       </c>
       <c r="W24" s="1" t="s">
         <v>258</v>
@@ -8169,31 +8130,27 @@
         <v>59</v>
       </c>
       <c r="H25" s="93">
-        <v>1.3542000000000001</v>
+        <v>-1</v>
       </c>
       <c r="I25" s="93">
-        <v>1.3541000000000001</v>
+        <v>-1</v>
       </c>
       <c r="J25" s="93">
-        <v>1.3542000000000001</v>
+        <v>-1</v>
       </c>
       <c r="K25" s="93">
-        <v>1.3541500000000002</v>
+        <v>-1</v>
       </c>
       <c r="L25" s="93">
-        <v>1.3573999999999999</v>
+        <v>1.3531</v>
       </c>
       <c r="M25" s="93">
-        <v>1.3554999999999999</v>
-      </c>
-      <c r="N25" s="93">
-        <v>1.3593</v>
-      </c>
-      <c r="O25" s="93">
-        <v>1.3542000000000001</v>
-      </c>
+        <v>1.3525</v>
+      </c>
+      <c r="N25" s="93"/>
+      <c r="O25" s="93"/>
       <c r="P25" s="93">
-        <v>20246</v>
+        <v>0</v>
       </c>
       <c r="Q25" s="93"/>
       <c r="R25" s="93"/>
@@ -8201,7 +8158,7 @@
       <c r="T25" s="93"/>
       <c r="U25" s="93"/>
       <c r="V25" s="92">
-        <v>46128.481365740743</v>
+        <v>46130.458333333336</v>
       </c>
       <c r="W25" s="1" t="s">
         <v>258</v>
@@ -8230,31 +8187,27 @@
         <v>59</v>
       </c>
       <c r="H26" s="93">
-        <v>6.3185000000000003E-3</v>
+        <v>-1</v>
       </c>
       <c r="I26" s="93">
-        <v>6.3185000000000003E-3</v>
+        <v>-1</v>
       </c>
       <c r="J26" s="93">
-        <v>6.319E-3</v>
+        <v>-1</v>
       </c>
       <c r="K26" s="93">
-        <v>6.3187499999999997E-3</v>
+        <v>-1</v>
       </c>
       <c r="L26" s="93">
-        <v>6.3210000000000002E-3</v>
+        <v>6.3119999999999999E-3</v>
       </c>
       <c r="M26" s="93">
-        <v>6.3245000000000003E-3</v>
-      </c>
-      <c r="N26" s="93">
-        <v>6.3499999999999997E-3</v>
-      </c>
-      <c r="O26" s="93">
-        <v>6.3165000000000001E-3</v>
-      </c>
+        <v>6.3144999999999998E-3</v>
+      </c>
+      <c r="N26" s="93"/>
+      <c r="O26" s="93"/>
       <c r="P26" s="93">
-        <v>57246</v>
+        <v>0</v>
       </c>
       <c r="Q26" s="93"/>
       <c r="R26" s="93"/>
@@ -8262,7 +8215,7 @@
       <c r="T26" s="93"/>
       <c r="U26" s="93"/>
       <c r="V26" s="92">
-        <v>46128.481365740743</v>
+        <v>46130.458333333336</v>
       </c>
       <c r="W26" s="1" t="s">
         <v>258</v>
@@ -8291,31 +8244,27 @@
         <v>59</v>
       </c>
       <c r="H27" s="93">
-        <v>0.73014999999999997</v>
+        <v>-1</v>
       </c>
       <c r="I27" s="93">
-        <v>0.73009999999999997</v>
+        <v>-1</v>
       </c>
       <c r="J27" s="93">
-        <v>0.73014999999999997</v>
+        <v>-1</v>
       </c>
       <c r="K27" s="93">
-        <v>0.73012499999999991</v>
+        <v>-1</v>
       </c>
       <c r="L27" s="93">
-        <v>0.73024999999999995</v>
+        <v>0.73170000000000002</v>
       </c>
       <c r="M27" s="93">
-        <v>0.7298</v>
-      </c>
-      <c r="N27" s="93">
-        <v>0.73114999999999997</v>
-      </c>
-      <c r="O27" s="93">
-        <v>0.72975000000000001</v>
-      </c>
+        <v>0.73170000000000002</v>
+      </c>
+      <c r="N27" s="93"/>
+      <c r="O27" s="93"/>
       <c r="P27" s="93">
-        <v>8273</v>
+        <v>0</v>
       </c>
       <c r="Q27" s="93"/>
       <c r="R27" s="93"/>
@@ -8323,7 +8272,7 @@
       <c r="T27" s="93"/>
       <c r="U27" s="93"/>
       <c r="V27" s="92">
-        <v>46128.481365740743</v>
+        <v>46130.458333333336</v>
       </c>
       <c r="W27" s="1" t="s">
         <v>258</v>
@@ -8352,31 +8301,27 @@
         <v>59</v>
       </c>
       <c r="H28" s="93">
-        <v>0.71625000000000005</v>
+        <v>-1</v>
       </c>
       <c r="I28" s="93">
-        <v>0.71619999999999995</v>
+        <v>-1</v>
       </c>
       <c r="J28" s="93">
-        <v>0.71625000000000005</v>
+        <v>-1</v>
       </c>
       <c r="K28" s="93">
-        <v>0.716225</v>
+        <v>-1</v>
       </c>
       <c r="L28" s="93">
-        <v>0.71679999999999999</v>
+        <v>0.71514999999999995</v>
       </c>
       <c r="M28" s="93">
-        <v>0.71640000000000004</v>
-      </c>
-      <c r="N28" s="93">
-        <v>0.71909999999999996</v>
-      </c>
-      <c r="O28" s="93">
-        <v>0.7157</v>
-      </c>
+        <v>0.71540000000000004</v>
+      </c>
+      <c r="N28" s="93"/>
+      <c r="O28" s="93"/>
       <c r="P28" s="93">
-        <v>42282</v>
+        <v>0</v>
       </c>
       <c r="Q28" s="93"/>
       <c r="R28" s="93"/>
@@ -8384,7 +8329,7 @@
       <c r="T28" s="93"/>
       <c r="U28" s="93"/>
       <c r="V28" s="92">
-        <v>46128.481365740743</v>
+        <v>46130.458333333336</v>
       </c>
       <c r="W28" s="1" t="s">
         <v>258</v>
@@ -8413,31 +8358,27 @@
         <v>59</v>
       </c>
       <c r="H29" s="93">
-        <v>114.15625</v>
+        <v>-1</v>
       </c>
       <c r="I29" s="93">
-        <v>114.125</v>
+        <v>-1</v>
       </c>
       <c r="J29" s="93">
-        <v>114.15625</v>
+        <v>-1</v>
       </c>
       <c r="K29" s="93">
-        <v>114.140625</v>
+        <v>-1</v>
       </c>
       <c r="L29" s="93">
-        <v>114.34375</v>
+        <v>113.75</v>
       </c>
       <c r="M29" s="93">
-        <v>114.1875</v>
-      </c>
-      <c r="N29" s="93">
-        <v>114.46875</v>
-      </c>
-      <c r="O29" s="93">
-        <v>114.15625</v>
-      </c>
+        <v>113.65625</v>
+      </c>
+      <c r="N29" s="93"/>
+      <c r="O29" s="93"/>
       <c r="P29" s="93">
-        <v>31155</v>
+        <v>0</v>
       </c>
       <c r="Q29" s="93"/>
       <c r="R29" s="93"/>
@@ -8445,7 +8386,7 @@
       <c r="T29" s="93"/>
       <c r="U29" s="93"/>
       <c r="V29" s="92">
-        <v>46128.481365740743</v>
+        <v>46130.458333333336</v>
       </c>
       <c r="W29" s="1" t="s">
         <v>258</v>
@@ -8474,31 +8415,27 @@
         <v>59</v>
       </c>
       <c r="H30" s="93">
-        <v>111.390625</v>
+        <v>-1</v>
       </c>
       <c r="I30" s="93">
-        <v>111.375</v>
+        <v>-1</v>
       </c>
       <c r="J30" s="93">
-        <v>111.390625</v>
+        <v>-1</v>
       </c>
       <c r="K30" s="93">
-        <v>111.3828125</v>
+        <v>-1</v>
       </c>
       <c r="L30" s="93">
-        <v>111.359375</v>
+        <v>111.21875</v>
       </c>
       <c r="M30" s="93">
-        <v>111.359375</v>
-      </c>
-      <c r="N30" s="93">
-        <v>111.53125</v>
-      </c>
-      <c r="O30" s="93">
-        <v>111.34375</v>
-      </c>
+        <v>111.171875</v>
+      </c>
+      <c r="N30" s="93"/>
+      <c r="O30" s="93"/>
       <c r="P30" s="93">
-        <v>187972</v>
+        <v>0</v>
       </c>
       <c r="Q30" s="93"/>
       <c r="R30" s="93"/>
@@ -8506,7 +8443,7 @@
       <c r="T30" s="93"/>
       <c r="U30" s="93"/>
       <c r="V30" s="92">
-        <v>46128.481365740743</v>
+        <v>46130.458333333336</v>
       </c>
       <c r="W30" s="1" t="s">
         <v>258</v>
@@ -8535,31 +8472,27 @@
         <v>56</v>
       </c>
       <c r="H31" s="93">
+        <v>126.06</v>
+      </c>
+      <c r="I31" s="93">
+        <v>-1</v>
+      </c>
+      <c r="J31" s="93">
+        <v>-1</v>
+      </c>
+      <c r="K31" s="93">
+        <v>-1</v>
+      </c>
+      <c r="L31" s="93">
         <v>125.44</v>
       </c>
-      <c r="I31" s="93">
-        <v>125.44</v>
-      </c>
-      <c r="J31" s="93">
-        <v>125.45</v>
-      </c>
-      <c r="K31" s="93">
-        <v>125.44499999999999</v>
-      </c>
-      <c r="L31" s="93">
-        <v>125.29</v>
-      </c>
       <c r="M31" s="93">
-        <v>125.32</v>
-      </c>
-      <c r="N31" s="93">
-        <v>125.62</v>
-      </c>
-      <c r="O31" s="93">
-        <v>125.32</v>
-      </c>
+        <v>125.19</v>
+      </c>
+      <c r="N31" s="93"/>
+      <c r="O31" s="93"/>
       <c r="P31" s="93">
-        <v>279289</v>
+        <v>0</v>
       </c>
       <c r="Q31" s="93"/>
       <c r="R31" s="93"/>
@@ -8567,7 +8500,7 @@
       <c r="T31" s="93"/>
       <c r="U31" s="93"/>
       <c r="V31" s="92">
-        <v>46128.481365740743</v>
+        <v>46130.458333333336</v>
       </c>
       <c r="W31" s="1" t="s">
         <v>258</v>
@@ -8595,32 +8528,24 @@
       <c r="G32" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="H32" s="93">
-        <v>107.8</v>
-      </c>
+      <c r="H32" s="93"/>
       <c r="I32" s="93">
-        <v>107.78</v>
+        <v>-1</v>
       </c>
       <c r="J32" s="93">
-        <v>107.8</v>
+        <v>-1</v>
       </c>
       <c r="K32" s="93">
-        <v>107.78999999999999</v>
+        <v>-1</v>
       </c>
       <c r="L32" s="93">
-        <v>107.62</v>
-      </c>
-      <c r="M32" s="93">
-        <v>107.6</v>
-      </c>
-      <c r="N32" s="93">
-        <v>108.04</v>
-      </c>
-      <c r="O32" s="93">
-        <v>107.52</v>
-      </c>
+        <v>107.86</v>
+      </c>
+      <c r="M32" s="93"/>
+      <c r="N32" s="93"/>
+      <c r="O32" s="93"/>
       <c r="P32" s="93">
-        <v>45454</v>
+        <v>0</v>
       </c>
       <c r="Q32" s="93"/>
       <c r="R32" s="93"/>
@@ -8628,7 +8553,7 @@
       <c r="T32" s="93"/>
       <c r="U32" s="93"/>
       <c r="V32" s="92">
-        <v>46128.481365740743</v>
+        <v>46130.458333333336</v>
       </c>
       <c r="W32" s="1" t="s">
         <v>258</v>
@@ -8656,32 +8581,24 @@
       <c r="G33" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="H33" s="93">
-        <v>117.53</v>
-      </c>
+      <c r="H33" s="93"/>
       <c r="I33" s="93">
-        <v>117.53</v>
+        <v>-1</v>
       </c>
       <c r="J33" s="93">
-        <v>117.54</v>
+        <v>-1</v>
       </c>
       <c r="K33" s="93">
-        <v>117.535</v>
+        <v>-1</v>
       </c>
       <c r="L33" s="93">
-        <v>117.38</v>
-      </c>
-      <c r="M33" s="93">
-        <v>117.46</v>
-      </c>
-      <c r="N33" s="93">
-        <v>117.79</v>
-      </c>
-      <c r="O33" s="93">
-        <v>117.46</v>
-      </c>
+        <v>117.47</v>
+      </c>
+      <c r="M33" s="93"/>
+      <c r="N33" s="93"/>
+      <c r="O33" s="93"/>
       <c r="P33" s="93">
-        <v>85988</v>
+        <v>0</v>
       </c>
       <c r="Q33" s="93"/>
       <c r="R33" s="93"/>
@@ -8689,7 +8606,7 @@
       <c r="T33" s="93"/>
       <c r="U33" s="93"/>
       <c r="V33" s="92">
-        <v>46128.481365740743</v>
+        <v>46130.458333333336</v>
       </c>
       <c r="W33" s="1" t="s">
         <v>258</v>
@@ -8718,29 +8635,29 @@
         <v>59</v>
       </c>
       <c r="H34" s="93">
-        <v>74821.5</v>
+        <v>76757.5</v>
       </c>
       <c r="I34" s="93">
-        <v>74821.25</v>
+        <v>76747.75</v>
       </c>
       <c r="J34" s="93">
-        <v>74821.5</v>
+        <v>76748.75</v>
       </c>
       <c r="K34" s="93">
-        <v>74821.375</v>
+        <v>76748.25</v>
       </c>
       <c r="L34" s="93">
-        <v>75012.5</v>
+        <v>77445.25</v>
       </c>
       <c r="M34" s="93"/>
       <c r="N34" s="93">
-        <v>75446.5</v>
+        <v>78316</v>
       </c>
       <c r="O34" s="93">
-        <v>73937.5</v>
+        <v>74570</v>
       </c>
       <c r="P34" s="93">
-        <v>62.95814507</v>
+        <v>52.801586520000001</v>
       </c>
       <c r="Q34" s="93"/>
       <c r="R34" s="93"/>
@@ -8748,7 +8665,7 @@
       <c r="T34" s="93"/>
       <c r="U34" s="93"/>
       <c r="V34" s="92">
-        <v>46128.481365740743</v>
+        <v>46130.458333333336</v>
       </c>
       <c r="W34" s="1" t="s">
         <v>258</v>
@@ -8777,29 +8694,29 @@
         <v>59</v>
       </c>
       <c r="H35" s="93">
-        <v>2346.4499999999998</v>
+        <v>2381.6</v>
       </c>
       <c r="I35" s="93">
-        <v>2346.0500000000002</v>
+        <v>2381.3000000000002</v>
       </c>
       <c r="J35" s="93">
-        <v>2346.1</v>
+        <v>2381.35</v>
       </c>
       <c r="K35" s="93">
-        <v>2346.0749999999998</v>
+        <v>2381.3249999999998</v>
       </c>
       <c r="L35" s="93">
-        <v>2375.0500000000002</v>
+        <v>2430.25</v>
       </c>
       <c r="M35" s="93"/>
       <c r="N35" s="93">
-        <v>2386.85</v>
+        <v>2465</v>
       </c>
       <c r="O35" s="93">
-        <v>2323.9499999999998</v>
+        <v>2319</v>
       </c>
       <c r="P35" s="93">
-        <v>1263.4804576199999</v>
+        <v>1255.2594833999999</v>
       </c>
       <c r="Q35" s="93"/>
       <c r="R35" s="93"/>
@@ -8807,7 +8724,7 @@
       <c r="T35" s="93"/>
       <c r="U35" s="93"/>
       <c r="V35" s="92">
-        <v>46128.481365740743</v>
+        <v>46130.458333333336</v>
       </c>
       <c r="W35" s="1" t="s">
         <v>258</v>
@@ -8836,47 +8753,47 @@
         <v>59</v>
       </c>
       <c r="H36" s="93">
-        <v>1.33</v>
+        <v>2.13</v>
       </c>
       <c r="I36" s="93">
-        <v>1.28</v>
+        <v>-1</v>
       </c>
       <c r="J36" s="93">
-        <v>1.31</v>
+        <v>-1</v>
       </c>
       <c r="K36" s="93">
-        <v>1.2949999999999999</v>
+        <v>-1</v>
       </c>
       <c r="L36" s="93">
-        <v>1.41</v>
+        <v>2.13</v>
       </c>
       <c r="M36" s="93"/>
       <c r="N36" s="93">
-        <v>1.46</v>
+        <v>3.28</v>
       </c>
       <c r="O36" s="93">
-        <v>1.28</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="P36" s="93">
-        <v>95</v>
+        <v>10304</v>
       </c>
       <c r="Q36" s="93">
-        <v>0.63865588978220611</v>
+        <v>0.6458434992589327</v>
       </c>
       <c r="R36" s="93">
-        <v>-0.14465314617937799</v>
+        <v>-0.24685835549058152</v>
       </c>
       <c r="S36" s="93">
-        <v>1.4388128895769861E-2</v>
+        <v>2.2260925965312549E-2</v>
       </c>
       <c r="T36" s="93">
-        <v>6.0347494708476113E-2</v>
+        <v>7.5197646573315957E-2</v>
       </c>
       <c r="U36" s="93">
-        <v>-6.8421829273718204E-2</v>
+        <v>-8.3749864822902698E-2</v>
       </c>
       <c r="V36" s="92">
-        <v>46128.481365740743</v>
+        <v>46130.458333333336</v>
       </c>
       <c r="W36" s="1" t="s">
         <v>258</v>
@@ -8905,37 +8822,47 @@
         <v>59</v>
       </c>
       <c r="H37" s="93">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="I37" s="93">
-        <v>0.09</v>
+        <v>-1</v>
       </c>
       <c r="J37" s="93">
-        <v>0.1</v>
+        <v>-1</v>
       </c>
       <c r="K37" s="93">
-        <v>9.5000000000000001E-2</v>
+        <v>-1</v>
       </c>
       <c r="L37" s="93">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="M37" s="93"/>
       <c r="N37" s="93">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="O37" s="93">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="P37" s="93">
-        <v>7</v>
-      </c>
-      <c r="Q37" s="93"/>
-      <c r="R37" s="93"/>
-      <c r="S37" s="93"/>
-      <c r="T37" s="93"/>
-      <c r="U37" s="93"/>
+        <v>1394</v>
+      </c>
+      <c r="Q37" s="93">
+        <v>0.7518356639769681</v>
+      </c>
+      <c r="R37" s="93">
+        <v>-1.576738265641954E-2</v>
+      </c>
+      <c r="S37" s="93">
+        <v>2.3502615518014415E-3</v>
+      </c>
+      <c r="T37" s="93">
+        <v>7.9046258094010724E-3</v>
+      </c>
+      <c r="U37" s="93">
+        <v>-1.1036191129346907E-2</v>
+      </c>
       <c r="V37" s="92">
-        <v>46128.481365740743</v>
+        <v>46130.458333333336</v>
       </c>
       <c r="W37" s="1" t="s">
         <v>258</v>
@@ -8964,47 +8891,37 @@
         <v>59</v>
       </c>
       <c r="H38" s="93">
-        <v>16.399999999999999</v>
+        <v>15.4</v>
       </c>
       <c r="I38" s="93">
-        <v>14.6</v>
+        <v>-1</v>
       </c>
       <c r="J38" s="93">
-        <v>15.9</v>
+        <v>-1</v>
       </c>
       <c r="K38" s="93">
-        <v>15.25</v>
+        <v>-1</v>
       </c>
       <c r="L38" s="93">
-        <v>16.399999999999999</v>
+        <v>12.6</v>
       </c>
       <c r="M38" s="93"/>
       <c r="N38" s="93">
-        <v>17.399999999999999</v>
+        <v>17.2</v>
       </c>
       <c r="O38" s="93">
-        <v>16.399999999999999</v>
+        <v>12.3</v>
       </c>
       <c r="P38" s="93">
-        <v>103</v>
-      </c>
-      <c r="Q38" s="93">
-        <v>0.27093050918244271</v>
-      </c>
-      <c r="R38" s="93">
-        <v>8.0287505687109614E-2</v>
-      </c>
-      <c r="S38" s="93">
-        <v>3.433257159560456E-4</v>
-      </c>
-      <c r="T38" s="93">
-        <v>2.337249328106962</v>
-      </c>
-      <c r="U38" s="93">
-        <v>-0.74355577437130016</v>
-      </c>
+        <v>412</v>
+      </c>
+      <c r="Q38" s="93"/>
+      <c r="R38" s="93"/>
+      <c r="S38" s="93"/>
+      <c r="T38" s="93"/>
+      <c r="U38" s="93"/>
       <c r="V38" s="92">
-        <v>46128.481365740743</v>
+        <v>46130.458333333336</v>
       </c>
       <c r="W38" s="1" t="s">
         <v>258</v>
@@ -9033,43 +8950,47 @@
         <v>59</v>
       </c>
       <c r="H39" s="93">
+        <v>132.9</v>
+      </c>
+      <c r="I39" s="93">
         <v>-1</v>
       </c>
-      <c r="I39" s="93">
-        <v>114.2</v>
-      </c>
       <c r="J39" s="93">
-        <v>116.5</v>
+        <v>-1</v>
       </c>
       <c r="K39" s="93">
-        <v>115.35</v>
+        <v>-1</v>
       </c>
       <c r="L39" s="93">
-        <v>116.5</v>
+        <v>101.5</v>
       </c>
       <c r="M39" s="93"/>
-      <c r="N39" s="93"/>
-      <c r="O39" s="93"/>
+      <c r="N39" s="93">
+        <v>137.4</v>
+      </c>
+      <c r="O39" s="93">
+        <v>132.9</v>
+      </c>
       <c r="P39" s="93">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q39" s="93">
-        <v>0.24180469956730305</v>
+        <v>0.23922371392982869</v>
       </c>
       <c r="R39" s="93">
-        <v>0.41350082272940392</v>
+        <v>0.45639444008338903</v>
       </c>
       <c r="S39" s="93">
-        <v>1.0049341986775498E-3</v>
+        <v>1.0509448726014378E-3</v>
       </c>
       <c r="T39" s="93">
-        <v>6.174061775384672</v>
+        <v>6.3412762743999593</v>
       </c>
       <c r="U39" s="93">
-        <v>-1.8525787677119467</v>
+        <v>-1.9371255877682927</v>
       </c>
       <c r="V39" s="92">
-        <v>46128.481365740743</v>
+        <v>46130.458333333336</v>
       </c>
       <c r="W39" s="1" t="s">
         <v>258</v>
@@ -9219,10 +9140,10 @@
         <v>46127.469976851855</v>
       </c>
       <c r="B2" s="84" t="s">
+        <v>341</v>
+      </c>
+      <c r="C2" s="84" t="s">
         <v>342</v>
-      </c>
-      <c r="C2" s="84" t="s">
-        <v>343</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.4">
@@ -9230,10 +9151,10 @@
         <v>46127.469976851855</v>
       </c>
       <c r="B3" s="84" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C3" s="84" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.4">
@@ -9241,10 +9162,10 @@
         <v>46127.469988425924</v>
       </c>
       <c r="B4" s="84" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C4" s="84" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.4">
@@ -9252,10 +9173,10 @@
         <v>46127.471296296295</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>342</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>343</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.4">
@@ -9263,10 +9184,10 @@
         <v>46127.471307870372</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.4">
@@ -9274,10 +9195,10 @@
         <v>46127.471307870372</v>
       </c>
       <c r="B7" s="81" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C7" s="81" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.4">
@@ -9285,10 +9206,10 @@
         <v>46127.475798611114</v>
       </c>
       <c r="B8" s="81" t="s">
+        <v>341</v>
+      </c>
+      <c r="C8" s="81" t="s">
         <v>342</v>
-      </c>
-      <c r="C8" s="81" t="s">
-        <v>343</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.4">
@@ -9296,10 +9217,10 @@
         <v>46127.475798611114</v>
       </c>
       <c r="B9" s="81" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C9" s="81" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.4">
@@ -9307,10 +9228,10 @@
         <v>46127.475810185184</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.4">
@@ -9318,10 +9239,10 @@
         <v>46128.480752314812</v>
       </c>
       <c r="B11" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="C11" s="1" t="s">
         <v>342</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>343</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.4">
@@ -9329,10 +9250,10 @@
         <v>46128.480763888889</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.4">
@@ -9340,67 +9261,147 @@
         <v>46128.480763888889</v>
       </c>
       <c r="B13" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A14" s="85">
+        <v>46129.72892361111</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="C14" s="1" t="s">
         <v>342</v>
       </c>
-      <c r="C13" s="1" t="s">
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A15" s="85">
+        <v>46129.728935185187</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A16" s="85">
+        <v>46129.728935185187</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A17" s="85">
+        <v>46129.72923611111</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>345</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A14" s="85"/>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A15" s="85"/>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A16" s="85"/>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A17" s="85"/>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A18" s="85"/>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A19" s="85"/>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A20" s="85"/>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A21" s="85"/>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A22" s="85"/>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A23" s="85"/>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="C17" s="1" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A18" s="85">
+        <v>46129.729259259257</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A19" s="85">
+        <v>46129.729375000003</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A20" s="85">
+        <v>46129.729398148149</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A21" s="85">
+        <v>46130.457037037035</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A22" s="85">
+        <v>46130.457048611112</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A23" s="85">
+        <v>46130.457048611112</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A24" s="85"/>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A25" s="85"/>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A26" s="85"/>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A27" s="85"/>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A28" s="85"/>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A29" s="85"/>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A30" s="85"/>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A31" s="85"/>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A32" s="85"/>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.4">
@@ -9575,11 +9576,11 @@
       <c r="E4" s="10"/>
       <c r="F4" s="10"/>
       <c r="G4" s="15">
-        <v>895</v>
+        <v>1220.21</v>
       </c>
       <c r="H4" s="6">
         <f>-G4</f>
-        <v>-895</v>
+        <v>-1220.21</v>
       </c>
     </row>
     <row r="5" spans="2:8" x14ac:dyDescent="0.4">
@@ -9700,11 +9701,11 @@
       <c r="F13" s="10"/>
       <c r="G13" s="6">
         <f>SUM(G3:G12)</f>
-        <v>4244.7199999999539</v>
+        <v>4569.9299999999548</v>
       </c>
       <c r="H13" s="6">
         <f>SUM(H3:H12)</f>
-        <v>33355.279999999955</v>
+        <v>33030.069999999956</v>
       </c>
     </row>
   </sheetData>
@@ -9930,11 +9931,11 @@
       <c r="H6" s="67"/>
       <c r="I6" s="70">
         <f>Blotter!C$4-SUM(NAV!I$4:I5)</f>
-        <v>57333.059999999896</v>
+        <v>66644.52000000012</v>
       </c>
       <c r="J6" s="70">
         <f t="shared" ref="J6" si="9">E6-F6-G6-H6+I6</f>
-        <v>1086077.5106320109</v>
+        <v>1095388.9706320111</v>
       </c>
       <c r="K6" s="70">
         <f t="shared" ref="K6" si="10">K5+C6</f>
@@ -9942,19 +9943,19 @@
       </c>
       <c r="L6" s="71">
         <f t="shared" ref="L6" si="11">J6/K6</f>
-        <v>1086.0775106320109</v>
+        <v>1095.388970632011</v>
       </c>
       <c r="M6" s="72">
         <f t="shared" ref="M6" si="12">L6/$L$3-1</f>
-        <v>8.6077510632010856E-2</v>
+        <v>9.5388970632011016E-2</v>
       </c>
       <c r="N6" s="73">
         <f t="shared" ref="N6" si="13">L6/L5-1</f>
-        <v>5.5731100143264323E-2</v>
+        <v>6.4782385906487105E-2</v>
       </c>
       <c r="O6" s="75">
         <f>STDEVP(N$4:N6)*SQRT(12)</f>
-        <v>7.8828744479476132E-2</v>
+        <v>9.1809467519934754E-2</v>
       </c>
     </row>
     <row r="7" spans="2:18" ht="14.25" x14ac:dyDescent="0.4">
@@ -10334,15 +10335,15 @@
       </c>
       <c r="D4" s="6">
         <f t="array" ref="D4">SUM((Blotter!C$19:C$1013=C4)*(Blotter!N$19:N$1013)*1)</f>
-        <v>19425.190632011014</v>
+        <v>22185.190632010999</v>
       </c>
       <c r="E4" s="6">
         <f t="array" ref="E4">SUM((Blotter!B$19:C$1013=C4)*(Blotter!R$19:R$1013)*1)</f>
-        <v>0</v>
+        <v>-10500</v>
       </c>
       <c r="F4" s="30">
         <f t="shared" ref="F4" si="3">IF(ISNUMBER(D4/E4),D4/E4,0)</f>
-        <v>0</v>
+        <v>-2.1128752982867618</v>
       </c>
       <c r="G4" s="36" t="str">
         <f t="array" ref="G4">IF(SUM((Blotter!C$19:C$1013=PLB!C4)*(Blotter!M$19:M$1013))=0,"C","O")</f>
@@ -10350,24 +10351,24 @@
       </c>
       <c r="H4" s="16">
         <f t="shared" ref="H4:H9" si="4">J3+D4</f>
-        <v>1019425.190632011</v>
+        <v>1022185.190632011</v>
       </c>
       <c r="I4" s="16"/>
       <c r="J4" s="16">
         <f t="shared" si="0"/>
-        <v>1019425.190632011</v>
+        <v>1022185.190632011</v>
       </c>
       <c r="K4" s="3">
         <f t="shared" ref="K4:K9" si="5">H4/J3-1</f>
-        <v>1.9425190632011091E-2</v>
+        <v>2.2185190632010965E-2</v>
       </c>
       <c r="L4" s="3">
         <f t="shared" ref="L4:L9" si="6">(1+K4)*(1+L3)-1</f>
-        <v>1.9425190632011091E-2</v>
+        <v>2.2185190632010965E-2</v>
       </c>
       <c r="M4" s="6">
         <f>O3-IF(G4="O",E4,-D4)</f>
-        <v>1000000</v>
+        <v>1010500</v>
       </c>
       <c r="N4" s="16">
         <f t="shared" ref="N4:N9" si="7">I4</f>
@@ -10375,15 +10376,15 @@
       </c>
       <c r="O4" s="6">
         <f t="shared" si="1"/>
-        <v>1000000</v>
+        <v>1010500</v>
       </c>
       <c r="P4" s="3">
         <f t="shared" ref="P4:P9" si="8">M4/O3-1</f>
-        <v>0</v>
+        <v>1.0499999999999954E-2</v>
       </c>
       <c r="Q4" s="3">
         <f t="shared" ref="Q4:Q9" si="9">(1+P4)*(1+Q3)-1</f>
-        <v>0</v>
+        <v>1.0499999999999954E-2</v>
       </c>
       <c r="R4" s="3">
         <f t="shared" ref="R4:R10" si="10">(1-1%)*(1+R3)-1</f>
@@ -10422,11 +10423,11 @@
       </c>
       <c r="E5" s="6">
         <f t="array" ref="E5">SUM((Blotter!B$19:C$1013=C5)*(Blotter!R$19:R$1013)*1)</f>
-        <v>9000</v>
+        <v>0</v>
       </c>
       <c r="F5" s="30">
         <f t="shared" ref="F5" si="12">IF(ISNUMBER(D5/E5),D5/E5,0)</f>
-        <v>0.10789888888888889</v>
+        <v>0</v>
       </c>
       <c r="G5" s="36" t="str">
         <f t="array" ref="G5">IF(SUM((Blotter!C$19:C$1013=PLB!C5)*(Blotter!M$19:M$1013))=0,"C","O")</f>
@@ -10434,24 +10435,24 @@
       </c>
       <c r="H5" s="16">
         <f t="shared" si="4"/>
-        <v>1020396.280632011</v>
+        <v>1023156.280632011</v>
       </c>
       <c r="I5" s="16"/>
       <c r="J5" s="16">
         <f t="shared" si="0"/>
-        <v>1020396.280632011</v>
+        <v>1023156.280632011</v>
       </c>
       <c r="K5" s="3">
         <f t="shared" si="5"/>
-        <v>9.525858384937802E-4</v>
+        <v>9.5001376355252631E-4</v>
       </c>
       <c r="L5" s="3">
         <f t="shared" si="6"/>
-        <v>2.0396280632011043E-2</v>
+        <v>2.3156280632010917E-2</v>
       </c>
       <c r="M5" s="6">
         <f t="shared" ref="M5:M8" si="13">O4-IF(G5="O",E5,-D5)</f>
-        <v>1000971.09</v>
+        <v>1011471.09</v>
       </c>
       <c r="N5" s="16">
         <f t="shared" si="7"/>
@@ -10459,15 +10460,15 @@
       </c>
       <c r="O5" s="6">
         <f t="shared" si="1"/>
-        <v>1000971.09</v>
+        <v>1011471.09</v>
       </c>
       <c r="P5" s="3">
         <f t="shared" si="8"/>
-        <v>9.7108999999995227E-4</v>
+        <v>9.6099950519534794E-4</v>
       </c>
       <c r="Q5" s="3">
         <f t="shared" si="9"/>
-        <v>9.7108999999995227E-4</v>
+        <v>1.1471089999999906E-2</v>
       </c>
       <c r="R5" s="3">
         <f t="shared" si="10"/>
@@ -10502,7 +10503,7 @@
       </c>
       <c r="D6" s="6">
         <f t="array" ref="D6">SUM((Blotter!C$19:C$1013=C6)*(Blotter!N$19:N$1013)*1)</f>
-        <v>-5714.220000000003</v>
+        <v>-3524.2200000000025</v>
       </c>
       <c r="E6" s="6">
         <f t="array" ref="E6">SUM((Blotter!B$19:C$1013=C6)*(Blotter!R$19:R$1013)*1)</f>
@@ -10510,7 +10511,7 @@
       </c>
       <c r="F6" s="30">
         <f t="shared" ref="F6" si="16">IF(ISNUMBER(D6/E6),D6/E6,0)</f>
-        <v>-0.59621127227880844</v>
+        <v>-0.3677106744210798</v>
       </c>
       <c r="G6" s="36" t="str">
         <f t="array" ref="G6">IF(SUM((Blotter!C$19:C$1013=PLB!C6)*(Blotter!M$19:M$1013))=0,"C","O")</f>
@@ -10518,24 +10519,24 @@
       </c>
       <c r="H6" s="16">
         <f t="shared" si="4"/>
-        <v>1014682.060632011</v>
+        <v>1019632.060632011</v>
       </c>
       <c r="I6" s="16"/>
       <c r="J6" s="16">
         <f t="shared" si="0"/>
-        <v>1014682.060632011</v>
+        <v>1019632.060632011</v>
       </c>
       <c r="K6" s="3">
         <f t="shared" si="5"/>
-        <v>-5.6000008119009292E-3</v>
+        <v>-3.4444591375846212E-3</v>
       </c>
       <c r="L6" s="3">
         <f t="shared" si="6"/>
-        <v>1.4682060632011051E-2</v>
+        <v>1.9632060632010839E-2</v>
       </c>
       <c r="M6" s="6">
         <f t="shared" si="13"/>
-        <v>991386.87</v>
+        <v>1001886.87</v>
       </c>
       <c r="N6" s="16">
         <f t="shared" si="7"/>
@@ -10543,15 +10544,15 @@
       </c>
       <c r="O6" s="6">
         <f t="shared" si="1"/>
-        <v>991386.87</v>
+        <v>1001886.87</v>
       </c>
       <c r="P6" s="3">
         <f t="shared" si="8"/>
-        <v>-9.5749218891026944E-3</v>
+        <v>-9.4755253953920926E-3</v>
       </c>
       <c r="Q6" s="3">
         <f t="shared" si="9"/>
-        <v>-8.6131300000000799E-3</v>
+        <v>1.886870000000096E-3</v>
       </c>
       <c r="R6" s="3">
         <f t="shared" si="10"/>
@@ -10586,7 +10587,7 @@
       </c>
       <c r="D7" s="6">
         <f t="array" ref="D7">SUM((Blotter!C$19:C$1013=C7)*(Blotter!N$19:N$1013)*1)</f>
-        <v>15372.529999999999</v>
+        <v>15160.029999999999</v>
       </c>
       <c r="E7" s="6">
         <f t="array" ref="E7">SUM((Blotter!B$19:C$1013=C7)*(Blotter!R$19:R$1013)*1)</f>
@@ -10602,24 +10603,24 @@
       </c>
       <c r="H7" s="16">
         <f t="shared" si="4"/>
-        <v>1030054.5906320111</v>
+        <v>1034792.0906320111</v>
       </c>
       <c r="I7" s="16"/>
       <c r="J7" s="16">
         <f t="shared" si="0"/>
-        <v>1030054.5906320111</v>
+        <v>1034792.0906320111</v>
       </c>
       <c r="K7" s="3">
         <f t="shared" si="5"/>
-        <v>1.5150095381034845E-2</v>
+        <v>1.4868137816893778E-2</v>
       </c>
       <c r="L7" s="3">
         <f t="shared" si="6"/>
-        <v>3.0054590632011102E-2</v>
+        <v>3.4792090632010941E-2</v>
       </c>
       <c r="M7" s="6">
         <f t="shared" si="13"/>
-        <v>991386.87</v>
+        <v>1001886.87</v>
       </c>
       <c r="N7" s="16">
         <f t="shared" si="7"/>
@@ -10627,7 +10628,7 @@
       </c>
       <c r="O7" s="6">
         <f t="shared" si="1"/>
-        <v>991386.87</v>
+        <v>1001886.87</v>
       </c>
       <c r="P7" s="3">
         <f t="shared" si="8"/>
@@ -10635,7 +10636,7 @@
       </c>
       <c r="Q7" s="3">
         <f t="shared" si="9"/>
-        <v>-8.6131300000000799E-3</v>
+        <v>1.886870000000096E-3</v>
       </c>
       <c r="R7" s="3">
         <f t="shared" si="10"/>
@@ -10670,40 +10671,40 @@
       </c>
       <c r="D8" s="6">
         <f t="array" ref="D8">SUM((Blotter!C$19:C$1013=C8)*(Blotter!N$19:N$1013)*1)</f>
-        <v>44610.739999999991</v>
+        <v>51385.74</v>
       </c>
       <c r="E8" s="6">
         <f t="array" ref="E8">SUM((Blotter!B$19:C$1013=C8)*(Blotter!R$19:R$1013)*1)</f>
-        <v>-26235</v>
+        <v>0</v>
       </c>
       <c r="F8" s="30">
         <f t="shared" ref="F8" si="22">IF(ISNUMBER(D8/E8),D8/E8,0)</f>
-        <v>-1.7004284352963595</v>
+        <v>0</v>
       </c>
       <c r="G8" s="36" t="str">
         <f t="array" ref="G8">IF(SUM((Blotter!C$19:C$1013=PLB!C8)*(Blotter!M$19:M$1013))=0,"C","O")</f>
-        <v>O</v>
+        <v>C</v>
       </c>
       <c r="H8" s="16">
         <f t="shared" si="4"/>
-        <v>1074665.3306320109</v>
+        <v>1086177.8306320112</v>
       </c>
       <c r="I8" s="16"/>
       <c r="J8" s="16">
         <f t="shared" si="0"/>
-        <v>1074665.3306320109</v>
+        <v>1086177.8306320112</v>
       </c>
       <c r="K8" s="3">
         <f t="shared" si="5"/>
-        <v>4.3309102649237374E-2</v>
+        <v>4.9658033208019203E-2</v>
       </c>
       <c r="L8" s="3">
         <f t="shared" si="6"/>
-        <v>7.4665330632011084E-2</v>
+        <v>8.6177830632010899E-2</v>
       </c>
       <c r="M8" s="6">
         <f t="shared" si="13"/>
-        <v>1017621.87</v>
+        <v>1053272.6100000001</v>
       </c>
       <c r="N8" s="16">
         <f t="shared" si="7"/>
@@ -10711,15 +10712,15 @@
       </c>
       <c r="O8" s="6">
         <f t="shared" si="1"/>
-        <v>1017621.87</v>
+        <v>1053272.6100000001</v>
       </c>
       <c r="P8" s="3">
         <f t="shared" si="8"/>
-        <v>2.6462928644596539E-2</v>
+        <v>5.1288964391758229E-2</v>
       </c>
       <c r="Q8" s="3">
         <f t="shared" si="9"/>
-        <v>1.7621869999999928E-2</v>
+        <v>5.3272610000000276E-2</v>
       </c>
       <c r="R8" s="3">
         <f t="shared" si="10"/>
@@ -10737,10 +10738,10 @@
         <v>324</v>
       </c>
       <c r="W8" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="X8" s="1" t="s">
         <v>334</v>
-      </c>
-      <c r="X8" s="1" t="s">
-        <v>335</v>
       </c>
     </row>
     <row r="9" spans="2:28" x14ac:dyDescent="0.4">
@@ -10754,7 +10755,7 @@
       </c>
       <c r="D9" s="6">
         <f t="array" ref="D9">SUM((Blotter!C$19:C$1013=C9)*(Blotter!N$19:N$1013)*1)</f>
-        <v>104.95999999999981</v>
+        <v>-1015.0400000000004</v>
       </c>
       <c r="E9" s="6">
         <f t="array" ref="E9">SUM((Blotter!B$19:C$1013=C9)*(Blotter!R$19:R$1013)*1)</f>
@@ -10762,7 +10763,7 @@
       </c>
       <c r="F9" s="30">
         <f t="shared" ref="F9" si="25">IF(ISNUMBER(D9/E9),D9/E9,0)</f>
-        <v>1.0595598627094671E-2</v>
+        <v>-0.10246719160104992</v>
       </c>
       <c r="G9" s="36" t="str">
         <f t="array" ref="G9">IF(SUM((Blotter!C$19:C$1013=PLB!C9)*(Blotter!M$19:M$1013))=0,"C","O")</f>
@@ -10770,24 +10771,24 @@
       </c>
       <c r="H9" s="16">
         <f t="shared" si="4"/>
-        <v>1074770.2906320109</v>
+        <v>1085162.7906320111</v>
       </c>
       <c r="I9" s="16"/>
       <c r="J9" s="16">
         <f t="shared" ref="J9" si="26">H9+I9</f>
-        <v>1074770.2906320109</v>
+        <v>1085162.7906320111</v>
       </c>
       <c r="K9" s="3">
         <f t="shared" si="5"/>
-        <v>9.7667615217789105E-5</v>
+        <v>-9.3450627638880235E-4</v>
       </c>
       <c r="L9" s="3">
         <f t="shared" si="6"/>
-        <v>7.4770290632011127E-2</v>
+        <v>8.5162790632010932E-2</v>
       </c>
       <c r="M9" s="6">
         <f t="shared" ref="M9" si="27">O8-IF(G9="O",E9,-D9)</f>
-        <v>1007715.87</v>
+        <v>1043366.6100000001</v>
       </c>
       <c r="N9" s="16">
         <f t="shared" si="7"/>
@@ -10795,15 +10796,15 @@
       </c>
       <c r="O9" s="6">
         <f t="shared" ref="O9" si="28">M9+N9</f>
-        <v>1007715.87</v>
+        <v>1043366.6100000001</v>
       </c>
       <c r="P9" s="3">
         <f t="shared" si="8"/>
-        <v>-9.7344606007730983E-3</v>
+        <v>-9.4049725645101168E-3</v>
       </c>
       <c r="Q9" s="3">
         <f t="shared" si="9"/>
-        <v>7.715869999999958E-3</v>
+        <v>4.3366610000000305E-2</v>
       </c>
       <c r="R9" s="3">
         <f t="shared" si="10"/>
@@ -10821,10 +10822,10 @@
         <v>329</v>
       </c>
       <c r="W9" s="49" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="X9" s="1" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="10" spans="2:28" x14ac:dyDescent="0.4">
@@ -10838,7 +10839,7 @@
       </c>
       <c r="D10" s="6">
         <f t="array" ref="D10">SUM((Blotter!C$19:C$1013=C10)*(Blotter!N$19:N$1013)*1)</f>
-        <v>7062.4999999998836</v>
+        <v>5656.2500000001164</v>
       </c>
       <c r="E10" s="6">
         <f t="array" ref="E10">SUM((Blotter!B$19:C$1013=C10)*(Blotter!R$19:R$1013)*1)</f>
@@ -10846,7 +10847,7 @@
       </c>
       <c r="F10" s="30">
         <f t="shared" ref="F10" si="31">IF(ISNUMBER(D10/E10),D10/E10,0)</f>
-        <v>0.7971781305114507</v>
+        <v>0.63844797178131829</v>
       </c>
       <c r="G10" s="36" t="str">
         <f t="array" ref="G10">IF(SUM((Blotter!C$19:C$1013=PLB!C10)*(Blotter!M$19:M$1013))=0,"C","O")</f>
@@ -10854,24 +10855,24 @@
       </c>
       <c r="H10" s="16">
         <f t="shared" ref="H10" si="32">J9+D10</f>
-        <v>1081832.7906320109</v>
+        <v>1090819.0406320114</v>
       </c>
       <c r="I10" s="16"/>
       <c r="J10" s="16">
         <f t="shared" ref="J10" si="33">H10+I10</f>
-        <v>1081832.7906320109</v>
+        <v>1090819.0406320114</v>
       </c>
       <c r="K10" s="3">
         <f t="shared" ref="K10" si="34">H10/J9-1</f>
-        <v>6.5711715903935541E-3</v>
+        <v>5.2123515926176811E-3</v>
       </c>
       <c r="L10" s="3">
         <f t="shared" ref="L10" si="35">(1+K10)*(1+L9)-1</f>
-        <v>8.1832790632011321E-2</v>
+        <v>9.0819040632011072E-2</v>
       </c>
       <c r="M10" s="6">
         <f t="shared" ref="M10" si="36">O9-IF(G10="O",E10,-D10)</f>
-        <v>998856.495</v>
+        <v>1034507.2350000001</v>
       </c>
       <c r="N10" s="16">
         <f t="shared" ref="N10" si="37">I10</f>
@@ -10879,15 +10880,15 @@
       </c>
       <c r="O10" s="6">
         <f t="shared" ref="O10" si="38">M10+N10</f>
-        <v>998856.495</v>
+        <v>1034507.2350000001</v>
       </c>
       <c r="P10" s="3">
         <f t="shared" ref="P10" si="39">M10/O9-1</f>
-        <v>-8.7915406155110176E-3</v>
+        <v>-8.4911429166781849E-3</v>
       </c>
       <c r="Q10" s="3">
         <f t="shared" ref="Q10" si="40">(1+P10)*(1+Q9)-1</f>
-        <v>-1.1435050000000446E-3</v>
+        <v>3.4507235000000192E-2</v>
       </c>
       <c r="R10" s="3">
         <f t="shared" si="10"/>
@@ -10902,13 +10903,13 @@
         <v>7</v>
       </c>
       <c r="V10" s="1" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="W10" s="49" t="s">
+        <v>337</v>
+      </c>
+      <c r="X10" s="1" t="s">
         <v>338</v>
-      </c>
-      <c r="X10" s="1" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="11" spans="2:28" x14ac:dyDescent="0.4">
@@ -17770,7 +17771,7 @@
         <v>267</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>78</v>
@@ -17958,10 +17959,70 @@
       <c r="X71" s="42"/>
     </row>
     <row r="72" spans="1:24" x14ac:dyDescent="0.4">
-      <c r="T72" s="43"/>
-      <c r="U72" s="42"/>
-      <c r="V72" s="42"/>
-      <c r="W72" s="42"/>
+      <c r="A72" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="F72" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="G72" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="H72" s="1">
+        <v>5</v>
+      </c>
+      <c r="J72" s="44">
+        <v>46185</v>
+      </c>
+      <c r="L72" s="44">
+        <v>46129</v>
+      </c>
+      <c r="M72" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="N72" s="1">
+        <v>-1</v>
+      </c>
+      <c r="O72" s="1">
+        <v>59945</v>
+      </c>
+      <c r="P72" s="1">
+        <v>-299725</v>
+      </c>
+      <c r="Q72" s="1">
+        <v>-3.02</v>
+      </c>
+      <c r="R72" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="T72" s="43">
+        <f>IF(ISNUMBER(VLOOKUP(U72,Blotter!B:C,2,0)),VLOOKUP(U72,Blotter!B:C,2,0),"")</f>
+        <v>5</v>
+      </c>
+      <c r="U72" s="42" t="str">
+        <f t="shared" ref="U72" si="47">D72</f>
+        <v>NKDM6</v>
+      </c>
+      <c r="V72" s="42">
+        <f t="shared" ref="V72" si="48">N72</f>
+        <v>-1</v>
+      </c>
+      <c r="W72" s="42">
+        <f t="shared" ref="W72" si="49">O72</f>
+        <v>59945</v>
+      </c>
       <c r="X72" s="42"/>
     </row>
     <row r="73" spans="1:24" x14ac:dyDescent="0.4">

--- a/1XW_TradeBlotter_Web.xlsx
+++ b/1XW_TradeBlotter_Web.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0a601c1c2ba3d9f4/Trading/The Strategy Project/1XW Website/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="610" documentId="13_ncr:1_{6F5069F1-F0E7-4440-AA6D-4AFA11BBED1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DDE1467B-DDCA-4BF0-82BF-7636432EFB84}"/>
+  <xr:revisionPtr revIDLastSave="612" documentId="13_ncr:1_{6F5069F1-F0E7-4440-AA6D-4AFA11BBED1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7E9178D4-A5CF-48CF-9368-EA4C28E4207E}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="22695" windowHeight="14476" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="C1" s="79">
         <f ca="1">TODAY()</f>
-        <v>46130</v>
+        <v>46132</v>
       </c>
     </row>
     <row r="2" spans="2:11" x14ac:dyDescent="0.4">
@@ -5173,7 +5173,7 @@
         <f t="shared" ref="T27" si="51">IF(S27&gt;0,IF(ISNUMBER(S27/L27-1),S27/L27-1,0),0)</f>
         <v>-8.000338638672555E-3</v>
       </c>
-      <c r="U27" s="29">
+      <c r="U27" s="99">
         <f t="shared" ref="U27" si="52">IF(OR(F27="Futures",F27="Stocks"),IF(I27=0,0,IF(I27&gt;0,K27-P27,K27+P27)),0)</f>
         <v>1.1579749999999998</v>
       </c>

--- a/1XW_TradeBlotter_Web.xlsx
+++ b/1XW_TradeBlotter_Web.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0a601c1c2ba3d9f4/Trading/The Strategy Project/1XW Website/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="612" documentId="13_ncr:1_{6F5069F1-F0E7-4440-AA6D-4AFA11BBED1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7E9178D4-A5CF-48CF-9368-EA4C28E4207E}"/>
+  <xr:revisionPtr revIDLastSave="613" documentId="13_ncr:1_{6F5069F1-F0E7-4440-AA6D-4AFA11BBED1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0B9541B9-49A1-4F6C-8A68-EAD9F8DC06E7}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="22695" windowHeight="14476" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2328,7 +2328,7 @@
                   <c:v>2.8744450632010921E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>6.4782385906487105E-2</c:v>
+                  <c:v>6.4758784321093277E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2488,7 +2488,7 @@
                   <c:v>2.8744450632010921E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>9.5388970632011016E-2</c:v>
+                  <c:v>9.5364690632010918E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2885,7 +2885,7 @@
                   <c:v>1028.744450632011</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1095.388970632011</c:v>
+                  <c:v>1095.3646906320109</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3304,22 +3304,22 @@
                   <c:v>1.0499999999999954E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.1471089999999906E-2</c:v>
+                  <c:v>1.14621800000001E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.886870000000096E-3</c:v>
+                  <c:v>1.8779600000000674E-3</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.886870000000096E-3</c:v>
+                  <c:v>1.8779600000000674E-3</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>5.3272610000000276E-2</c:v>
+                  <c:v>5.3260680000000171E-2</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>4.3366610000000305E-2</c:v>
+                  <c:v>4.3354680000000201E-2</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>3.4507235000000192E-2</c:v>
+                  <c:v>3.4495305000000087E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3415,22 +3415,22 @@
                   <c:v>2.2185190632010965E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2.3156280632010917E-2</c:v>
+                  <c:v>2.3147370632011111E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.9632060632010839E-2</c:v>
+                  <c:v>1.9623150632011033E-2</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>3.4792090632010941E-2</c:v>
+                  <c:v>3.4783180632010913E-2</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>8.6177830632010899E-2</c:v>
+                  <c:v>8.6165900632011017E-2</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>8.5162790632010932E-2</c:v>
+                  <c:v>8.5150860632011049E-2</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>9.0819040632011072E-2</c:v>
+                  <c:v>9.0794760632011196E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4105,7 +4105,7 @@
       </c>
       <c r="C3" s="28">
         <f ca="1">OFFSET(NAV!B1,MATCH(C1,NAV!B:B,1),8)</f>
-        <v>1095388.9706320111</v>
+        <v>1095364.690632011</v>
       </c>
       <c r="E3" s="47" t="s">
         <v>121</v>
@@ -4122,7 +4122,7 @@
       </c>
       <c r="C4" s="28">
         <f>SUM(N18:N1012)</f>
-        <v>95388.970632011056</v>
+        <v>95364.690632011087</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="47" t="s">
@@ -4140,7 +4140,7 @@
       </c>
       <c r="C5" s="3">
         <f ca="1">OFFSET(NAV!B1,MATCH(C1,NAV!B:B,1),11)</f>
-        <v>9.5388970632011016E-2</v>
+        <v>9.5364690632010918E-2</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="47" t="s">
@@ -4159,7 +4159,7 @@
       </c>
       <c r="C6" s="3">
         <f ca="1">OFFSET(NAV!B1,MATCH(C1,NAV!B:B,1),12)</f>
-        <v>6.4782385906487105E-2</v>
+        <v>6.4758784321093277E-2</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="47" t="s">
@@ -4180,7 +4180,7 @@
       </c>
       <c r="D7" s="3">
         <f ca="1">C7/C3</f>
-        <v>3.0153736148121394E-2</v>
+        <v>3.0154404539863375E-2</v>
       </c>
       <c r="E7" s="47"/>
       <c r="F7" s="47"/>
@@ -4194,11 +4194,11 @@
       </c>
       <c r="C8" s="28">
         <f>C4+C7</f>
-        <v>128419.04063201102</v>
+        <v>128394.76063201105</v>
       </c>
       <c r="D8" s="3">
         <f ca="1">C5+D7</f>
-        <v>0.12554270678013241</v>
+        <v>0.12551909517187429</v>
       </c>
       <c r="G8" s="47"/>
       <c r="H8" s="51"/>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="D9" s="3">
         <f ca="1">C9/$C$3</f>
-        <v>0.81264511864347078</v>
+        <v>0.81266313184368566</v>
       </c>
       <c r="E9" s="47"/>
       <c r="F9" s="47"/>
@@ -4232,7 +4232,7 @@
       </c>
       <c r="D10" s="3">
         <f t="shared" ref="D10:D14" ca="1" si="0">C10/$C$3</f>
-        <v>8.1158385179565026E-3</v>
+        <v>8.116018414716826E-3</v>
       </c>
       <c r="H10" s="44"/>
     </row>
@@ -4246,7 +4246,7 @@
       </c>
       <c r="D11" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>5.5322813744450401E-3</v>
+        <v>5.5324040037327289E-3</v>
       </c>
     </row>
     <row r="12" spans="2:11" x14ac:dyDescent="0.4">
@@ -4259,7 +4259,7 @@
       </c>
       <c r="D12" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>1.6295211544535861E-2</v>
+        <v>1.6295572746370907E-2</v>
       </c>
     </row>
     <row r="13" spans="2:11" x14ac:dyDescent="0.4">
@@ -4268,11 +4268,11 @@
       </c>
       <c r="C13" s="28">
         <f t="array" ref="C13">SUM((PLB!G4:G999="O")*(PLB!D4:D999))</f>
-        <v>38462.210632011112</v>
+        <v>38449.860632011136</v>
       </c>
       <c r="D13" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>3.5112833580768492E-2</v>
+        <v>3.5102337112789414E-2</v>
       </c>
       <c r="F13" s="59"/>
       <c r="G13" s="59"/>
@@ -4283,11 +4283,11 @@
       </c>
       <c r="C14" s="28">
         <f>C12+C13</f>
-        <v>56311.805632011114</v>
+        <v>56299.455632011137</v>
       </c>
       <c r="D14" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>5.1408045125304357E-2</v>
+        <v>5.1397909859160325E-2</v>
       </c>
     </row>
     <row r="17" spans="2:28" x14ac:dyDescent="0.4">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="K20" s="29">
         <f t="shared" ref="K20" si="7">L20-N20/(H20*J20)</f>
-        <v>3235.297</v>
+        <v>3235.5940000000001</v>
       </c>
       <c r="L20" s="29">
         <f t="shared" ref="L20" si="8">IF(I20=0,IF(H20&gt;0,X20,Y20),Z20)</f>
@@ -4533,7 +4533,7 @@
       </c>
       <c r="N20" s="95">
         <f t="array" ref="N20">-SUM((Trades!T$2:T$9999=Blotter!C20)*(Trades!U$2:U$9999=Blotter!B20)*(Trades!V$2:V$9999)*(Trades!W$2:W$9999))*J20+SUM((Trades!T$2:T$9999=Blotter!C20)*(Trades!U$2:U$9999=Blotter!B20)*(Trades!X$2:X$9999))+(L20*I20)*J20</f>
-        <v>971.09</v>
+        <v>962.18</v>
       </c>
       <c r="O20" s="29">
         <f>VLOOKUP(D20,Multiplier!B:H,3,0)</f>
@@ -4873,7 +4873,7 @@
       </c>
       <c r="K24" s="29">
         <f t="shared" ref="K24" si="30">L24-N24/(H24*J24)</f>
-        <v>42402.137714285716</v>
+        <v>42402.741714285716</v>
       </c>
       <c r="L24" s="29">
         <f t="shared" ref="L24" si="31">IF(I24=0,IF(H24&gt;0,X24,Y24),Z24)</f>
@@ -4885,7 +4885,7 @@
       </c>
       <c r="N24" s="95">
         <f t="array" ref="N24">-SUM((Trades!T$2:T$9999=Blotter!C24)*(Trades!U$2:U$9999=Blotter!B24)*(Trades!V$2:V$9999)*(Trades!W$2:W$9999))*J24+SUM((Trades!T$2:T$9999=Blotter!C24)*(Trades!U$2:U$9999=Blotter!B24)*(Trades!X$2:X$9999))+(L24*I24)*J24</f>
-        <v>51385.74</v>
+        <v>51382.720000000001</v>
       </c>
       <c r="O24" s="29">
         <f>VLOOKUP(D24,Multiplier!B:H,3,0)</f>
@@ -5138,7 +5138,7 @@
       </c>
       <c r="K27" s="99">
         <f t="shared" ref="K27" si="46">L27-N27/(H27*J27)</f>
-        <v>1.1721499999999998</v>
+        <v>1.1721697599999998</v>
       </c>
       <c r="L27" s="99">
         <f t="shared" ref="L27" si="47">IF(I27=0,IF(H27&gt;0,X27,Y27),Z27)</f>
@@ -5150,7 +5150,7 @@
       </c>
       <c r="N27" s="95">
         <f t="array" ref="N27">-SUM((Trades!T$2:T$9999=Blotter!C27)*(Trades!U$2:U$9999=Blotter!B27)*(Trades!V$2:V$9999)*(Trades!W$2:W$9999))*J27+SUM((Trades!T$2:T$9999=Blotter!C27)*(Trades!U$2:U$9999=Blotter!B27)*(Trades!X$2:X$9999))+(L27*I27)*J27</f>
-        <v>5656.2500000001164</v>
+        <v>5643.9000000001397</v>
       </c>
       <c r="O27" s="46">
         <f>VLOOKUP(D27,Multiplier!B:H,3,0)</f>
@@ -5175,11 +5175,11 @@
       </c>
       <c r="U27" s="99">
         <f t="shared" ref="U27" si="52">IF(OR(F27="Futures",F27="Stocks"),IF(I27=0,0,IF(I27&gt;0,K27-P27,K27+P27)),0)</f>
-        <v>1.1579749999999998</v>
+        <v>1.1579947599999998</v>
       </c>
       <c r="V27" s="3">
         <f t="shared" ref="V27" si="53">IF(U27&gt;0,IF(ISNUMBER(U27/L27-1),U27/L27-1,0),0)</f>
-        <v>-1.9662207924145192E-2</v>
+        <v>-1.9645479173721836E-2</v>
       </c>
       <c r="X27" s="34">
         <f t="array" ref="X27">IF(ISNUMBER(SUM((Trades!T$2:T$9999=Blotter!C27)*(Trades!U$2:U$9999=Blotter!B27)*(Trades!W$2:W$9999)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0))/SUM((Trades!T$2:T$9999=Blotter!C27)*(Trades!U$2:U$9999=Blotter!B27)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0))),SUM((Trades!T$2:T$9999=Blotter!C27)*(Trades!U$2:U$9999=Blotter!B27)*(Trades!W$2:W$9999)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0))/SUM((Trades!T$2:T$9999=Blotter!C27)*(Trades!U$2:U$9999=Blotter!B27)*(Trades!V$2:V$9999)*(Trades!V$2:V$9999&lt;0)),0)</f>
@@ -9931,11 +9931,11 @@
       <c r="H6" s="67"/>
       <c r="I6" s="70">
         <f>Blotter!C$4-SUM(NAV!I$4:I5)</f>
-        <v>66644.52000000012</v>
+        <v>66620.240000000151</v>
       </c>
       <c r="J6" s="70">
         <f t="shared" ref="J6" si="9">E6-F6-G6-H6+I6</f>
-        <v>1095388.9706320111</v>
+        <v>1095364.690632011</v>
       </c>
       <c r="K6" s="70">
         <f t="shared" ref="K6" si="10">K5+C6</f>
@@ -9943,19 +9943,19 @@
       </c>
       <c r="L6" s="71">
         <f t="shared" ref="L6" si="11">J6/K6</f>
-        <v>1095.388970632011</v>
+        <v>1095.3646906320109</v>
       </c>
       <c r="M6" s="72">
         <f t="shared" ref="M6" si="12">L6/$L$3-1</f>
-        <v>9.5388970632011016E-2</v>
+        <v>9.5364690632010918E-2</v>
       </c>
       <c r="N6" s="73">
         <f t="shared" ref="N6" si="13">L6/L5-1</f>
-        <v>6.4782385906487105E-2</v>
+        <v>6.4758784321093277E-2</v>
       </c>
       <c r="O6" s="75">
         <f>STDEVP(N$4:N6)*SQRT(12)</f>
-        <v>9.1809467519934754E-2</v>
+        <v>9.177491174934875E-2</v>
       </c>
     </row>
     <row r="7" spans="2:18" ht="14.25" x14ac:dyDescent="0.4">
@@ -10419,7 +10419,7 @@
       </c>
       <c r="D5" s="6">
         <f t="array" ref="D5">SUM((Blotter!C$19:C$1013=C5)*(Blotter!N$19:N$1013)*1)</f>
-        <v>971.09</v>
+        <v>962.18</v>
       </c>
       <c r="E5" s="6">
         <f t="array" ref="E5">SUM((Blotter!B$19:C$1013=C5)*(Blotter!R$19:R$1013)*1)</f>
@@ -10435,24 +10435,24 @@
       </c>
       <c r="H5" s="16">
         <f t="shared" si="4"/>
-        <v>1023156.280632011</v>
+        <v>1023147.3706320111</v>
       </c>
       <c r="I5" s="16"/>
       <c r="J5" s="16">
         <f t="shared" si="0"/>
-        <v>1023156.280632011</v>
+        <v>1023147.3706320111</v>
       </c>
       <c r="K5" s="3">
         <f t="shared" si="5"/>
-        <v>9.5001376355252631E-4</v>
+        <v>9.4129714343171855E-4</v>
       </c>
       <c r="L5" s="3">
         <f t="shared" si="6"/>
-        <v>2.3156280632010917E-2</v>
+        <v>2.3147370632011111E-2</v>
       </c>
       <c r="M5" s="6">
         <f t="shared" ref="M5:M8" si="13">O4-IF(G5="O",E5,-D5)</f>
-        <v>1011471.09</v>
+        <v>1011462.18</v>
       </c>
       <c r="N5" s="16">
         <f t="shared" si="7"/>
@@ -10460,15 +10460,15 @@
       </c>
       <c r="O5" s="6">
         <f t="shared" si="1"/>
-        <v>1011471.09</v>
+        <v>1011462.18</v>
       </c>
       <c r="P5" s="3">
         <f t="shared" si="8"/>
-        <v>9.6099950519534794E-4</v>
+        <v>9.5218208807534843E-4</v>
       </c>
       <c r="Q5" s="3">
         <f t="shared" si="9"/>
-        <v>1.1471089999999906E-2</v>
+        <v>1.14621800000001E-2</v>
       </c>
       <c r="R5" s="3">
         <f t="shared" si="10"/>
@@ -10519,24 +10519,24 @@
       </c>
       <c r="H6" s="16">
         <f t="shared" si="4"/>
-        <v>1019632.060632011</v>
+        <v>1019623.1506320111</v>
       </c>
       <c r="I6" s="16"/>
       <c r="J6" s="16">
         <f t="shared" si="0"/>
-        <v>1019632.060632011</v>
+        <v>1019623.1506320111</v>
       </c>
       <c r="K6" s="3">
         <f t="shared" si="5"/>
-        <v>-3.4444591375846212E-3</v>
+        <v>-3.4444891333914596E-3</v>
       </c>
       <c r="L6" s="3">
         <f t="shared" si="6"/>
-        <v>1.9632060632010839E-2</v>
+        <v>1.9623150632011033E-2</v>
       </c>
       <c r="M6" s="6">
         <f t="shared" si="13"/>
-        <v>1001886.87</v>
+        <v>1001877.9600000001</v>
       </c>
       <c r="N6" s="16">
         <f t="shared" si="7"/>
@@ -10544,15 +10544,15 @@
       </c>
       <c r="O6" s="6">
         <f t="shared" si="1"/>
-        <v>1001886.87</v>
+        <v>1001877.9600000001</v>
       </c>
       <c r="P6" s="3">
         <f t="shared" si="8"/>
-        <v>-9.4755253953920926E-3</v>
+        <v>-9.4756088655731929E-3</v>
       </c>
       <c r="Q6" s="3">
         <f t="shared" si="9"/>
-        <v>1.886870000000096E-3</v>
+        <v>1.8779600000000674E-3</v>
       </c>
       <c r="R6" s="3">
         <f t="shared" si="10"/>
@@ -10603,24 +10603,24 @@
       </c>
       <c r="H7" s="16">
         <f t="shared" si="4"/>
-        <v>1034792.0906320111</v>
+        <v>1034783.1806320112</v>
       </c>
       <c r="I7" s="16"/>
       <c r="J7" s="16">
         <f t="shared" si="0"/>
-        <v>1034792.0906320111</v>
+        <v>1034783.1806320112</v>
       </c>
       <c r="K7" s="3">
         <f t="shared" si="5"/>
-        <v>1.4868137816893778E-2</v>
+        <v>1.4868267742452757E-2</v>
       </c>
       <c r="L7" s="3">
         <f t="shared" si="6"/>
-        <v>3.4792090632010941E-2</v>
+        <v>3.4783180632010913E-2</v>
       </c>
       <c r="M7" s="6">
         <f t="shared" si="13"/>
-        <v>1001886.87</v>
+        <v>1001877.9600000001</v>
       </c>
       <c r="N7" s="16">
         <f t="shared" si="7"/>
@@ -10628,7 +10628,7 @@
       </c>
       <c r="O7" s="6">
         <f t="shared" si="1"/>
-        <v>1001886.87</v>
+        <v>1001877.9600000001</v>
       </c>
       <c r="P7" s="3">
         <f t="shared" si="8"/>
@@ -10636,7 +10636,7 @@
       </c>
       <c r="Q7" s="3">
         <f t="shared" si="9"/>
-        <v>1.886870000000096E-3</v>
+        <v>1.8779600000000674E-3</v>
       </c>
       <c r="R7" s="3">
         <f t="shared" si="10"/>
@@ -10671,7 +10671,7 @@
       </c>
       <c r="D8" s="6">
         <f t="array" ref="D8">SUM((Blotter!C$19:C$1013=C8)*(Blotter!N$19:N$1013)*1)</f>
-        <v>51385.74</v>
+        <v>51382.720000000001</v>
       </c>
       <c r="E8" s="6">
         <f t="array" ref="E8">SUM((Blotter!B$19:C$1013=C8)*(Blotter!R$19:R$1013)*1)</f>
@@ -10687,24 +10687,24 @@
       </c>
       <c r="H8" s="16">
         <f t="shared" si="4"/>
-        <v>1086177.8306320112</v>
+        <v>1086165.9006320112</v>
       </c>
       <c r="I8" s="16"/>
       <c r="J8" s="16">
         <f t="shared" si="0"/>
-        <v>1086177.8306320112</v>
+        <v>1086165.9006320112</v>
       </c>
       <c r="K8" s="3">
         <f t="shared" si="5"/>
-        <v>4.9658033208019203E-2</v>
+        <v>4.9655542302704747E-2</v>
       </c>
       <c r="L8" s="3">
         <f t="shared" si="6"/>
-        <v>8.6177830632010899E-2</v>
+        <v>8.6165900632011017E-2</v>
       </c>
       <c r="M8" s="6">
         <f t="shared" si="13"/>
-        <v>1053272.6100000001</v>
+        <v>1053260.6800000002</v>
       </c>
       <c r="N8" s="16">
         <f t="shared" si="7"/>
@@ -10712,15 +10712,15 @@
       </c>
       <c r="O8" s="6">
         <f t="shared" si="1"/>
-        <v>1053272.6100000001</v>
+        <v>1053260.6800000002</v>
       </c>
       <c r="P8" s="3">
         <f t="shared" si="8"/>
-        <v>5.1288964391758229E-2</v>
+        <v>5.1286406180649058E-2</v>
       </c>
       <c r="Q8" s="3">
         <f t="shared" si="9"/>
-        <v>5.3272610000000276E-2</v>
+        <v>5.3260680000000171E-2</v>
       </c>
       <c r="R8" s="3">
         <f t="shared" si="10"/>
@@ -10771,24 +10771,24 @@
       </c>
       <c r="H9" s="16">
         <f t="shared" si="4"/>
-        <v>1085162.7906320111</v>
+        <v>1085150.8606320112</v>
       </c>
       <c r="I9" s="16"/>
       <c r="J9" s="16">
         <f t="shared" ref="J9" si="26">H9+I9</f>
-        <v>1085162.7906320111</v>
+        <v>1085150.8606320112</v>
       </c>
       <c r="K9" s="3">
         <f t="shared" si="5"/>
-        <v>-9.3450627638880235E-4</v>
+        <v>-9.3451654062182143E-4</v>
       </c>
       <c r="L9" s="3">
         <f t="shared" si="6"/>
-        <v>8.5162790632010932E-2</v>
+        <v>8.5150860632011049E-2</v>
       </c>
       <c r="M9" s="6">
         <f t="shared" ref="M9" si="27">O8-IF(G9="O",E9,-D9)</f>
-        <v>1043366.6100000001</v>
+        <v>1043354.6800000002</v>
       </c>
       <c r="N9" s="16">
         <f t="shared" si="7"/>
@@ -10796,15 +10796,15 @@
       </c>
       <c r="O9" s="6">
         <f t="shared" ref="O9" si="28">M9+N9</f>
-        <v>1043366.6100000001</v>
+        <v>1043354.6800000002</v>
       </c>
       <c r="P9" s="3">
         <f t="shared" si="8"/>
-        <v>-9.4049725645101168E-3</v>
+        <v>-9.4050790921008653E-3</v>
       </c>
       <c r="Q9" s="3">
         <f t="shared" si="9"/>
-        <v>4.3366610000000305E-2</v>
+        <v>4.3354680000000201E-2</v>
       </c>
       <c r="R9" s="3">
         <f t="shared" si="10"/>
@@ -10839,7 +10839,7 @@
       </c>
       <c r="D10" s="6">
         <f t="array" ref="D10">SUM((Blotter!C$19:C$1013=C10)*(Blotter!N$19:N$1013)*1)</f>
-        <v>5656.2500000001164</v>
+        <v>5643.9000000001397</v>
       </c>
       <c r="E10" s="6">
         <f t="array" ref="E10">SUM((Blotter!B$19:C$1013=C10)*(Blotter!R$19:R$1013)*1)</f>
@@ -10847,7 +10847,7 @@
       </c>
       <c r="F10" s="30">
         <f t="shared" ref="F10" si="31">IF(ISNUMBER(D10/E10),D10/E10,0)</f>
-        <v>0.63844797178131829</v>
+        <v>0.63705396825398397</v>
       </c>
       <c r="G10" s="36" t="str">
         <f t="array" ref="G10">IF(SUM((Blotter!C$19:C$1013=PLB!C10)*(Blotter!M$19:M$1013))=0,"C","O")</f>
@@ -10855,24 +10855,24 @@
       </c>
       <c r="H10" s="16">
         <f t="shared" ref="H10" si="32">J9+D10</f>
-        <v>1090819.0406320114</v>
+        <v>1090794.7606320113</v>
       </c>
       <c r="I10" s="16"/>
       <c r="J10" s="16">
         <f t="shared" ref="J10" si="33">H10+I10</f>
-        <v>1090819.0406320114</v>
+        <v>1090794.7606320113</v>
       </c>
       <c r="K10" s="3">
         <f t="shared" ref="K10" si="34">H10/J9-1</f>
-        <v>5.2123515926176811E-3</v>
+        <v>5.2010279904428636E-3</v>
       </c>
       <c r="L10" s="3">
         <f t="shared" ref="L10" si="35">(1+K10)*(1+L9)-1</f>
-        <v>9.0819040632011072E-2</v>
+        <v>9.0794760632011196E-2</v>
       </c>
       <c r="M10" s="6">
         <f t="shared" ref="M10" si="36">O9-IF(G10="O",E10,-D10)</f>
-        <v>1034507.2350000001</v>
+        <v>1034495.3050000002</v>
       </c>
       <c r="N10" s="16">
         <f t="shared" ref="N10" si="37">I10</f>
@@ -10880,15 +10880,15 @@
       </c>
       <c r="O10" s="6">
         <f t="shared" ref="O10" si="38">M10+N10</f>
-        <v>1034507.2350000001</v>
+        <v>1034495.3050000002</v>
       </c>
       <c r="P10" s="3">
         <f t="shared" ref="P10" si="39">M10/O9-1</f>
-        <v>-8.4911429166781849E-3</v>
+        <v>-8.4912400067060911E-3</v>
       </c>
       <c r="Q10" s="3">
         <f t="shared" ref="Q10" si="40">(1+P10)*(1+Q9)-1</f>
-        <v>3.4507235000000192E-2</v>
+        <v>3.4495305000000087E-2</v>
       </c>
       <c r="R10" s="3">
         <f t="shared" si="10"/>
@@ -17677,7 +17677,7 @@
         <v>125.4</v>
       </c>
       <c r="X67" s="42">
-        <f t="shared" ref="X67:X68" si="43">Q67</f>
+        <f t="shared" ref="X67:X72" si="43">Q67</f>
         <v>-2.52</v>
       </c>
     </row>
@@ -17822,7 +17822,10 @@
         <f t="shared" si="42"/>
         <v>1.17215</v>
       </c>
-      <c r="X69" s="42"/>
+      <c r="X69" s="42">
+        <f t="shared" si="43"/>
+        <v>-12.35</v>
+      </c>
     </row>
     <row r="70" spans="1:24" x14ac:dyDescent="0.4">
       <c r="A70" s="1" t="s">
@@ -17889,7 +17892,10 @@
         <f t="shared" ref="W70:W71" si="46">O70</f>
         <v>3268</v>
       </c>
-      <c r="X70" s="42"/>
+      <c r="X70" s="42">
+        <f t="shared" si="43"/>
+        <v>-5.94</v>
+      </c>
     </row>
     <row r="71" spans="1:24" x14ac:dyDescent="0.4">
       <c r="A71" s="1" t="s">
@@ -17956,7 +17962,10 @@
         <f t="shared" si="46"/>
         <v>3267</v>
       </c>
-      <c r="X71" s="42"/>
+      <c r="X71" s="42">
+        <f t="shared" si="43"/>
+        <v>-2.97</v>
+      </c>
     </row>
     <row r="72" spans="1:24" x14ac:dyDescent="0.4">
       <c r="A72" s="1" t="s">
@@ -18023,7 +18032,10 @@
         <f t="shared" ref="W72" si="49">O72</f>
         <v>59945</v>
       </c>
-      <c r="X72" s="42"/>
+      <c r="X72" s="42">
+        <f t="shared" si="43"/>
+        <v>-3.02</v>
+      </c>
     </row>
     <row r="73" spans="1:24" x14ac:dyDescent="0.4">
       <c r="T73" s="43"/>
